--- a/radar.xlsx
+++ b/radar.xlsx
@@ -686,7 +686,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-08-03</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>11069.61</v>
+        <v>11021.88</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10917.57</v>
+        <v>10943.27</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>10790.17</v>
+        <v>10877.4</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>10874.3</v>
+        <v>10896.53</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>10924.97</v>
+        <v>10934.91</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>10772.94</v>
+        <v>10856.3</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>10722.27</v>
+        <v>10817.92</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>10620.91</v>
+        <v>10777.69</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>10705.04</v>
+        <v>10833.37</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>10577.64</v>
+        <v>10767.5</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>10425.6</v>
+        <v>10688.89</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>10744.92</v>
+        <v>10847.9</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>10716.89</v>
+        <v>10839.51</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>10823.62</v>
+        <v>10858.14</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>0.96</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="4">
@@ -856,37 +856,37 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>20.69</v>
+        <v>20.97</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.45</v>
+        <v>20.68</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>20.25</v>
+        <v>20.44</v>
       </c>
       <c r="F4" s="27" t="n">
-        <v>20.37</v>
+        <v>20.4</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>20.46</v>
+        <v>20.6</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>20.22</v>
+        <v>20.31</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>20.13</v>
+        <v>20.11</v>
       </c>
       <c r="J4" s="29" t="n">
-        <v>19.98</v>
+        <v>20.02</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>20.11</v>
+        <v>20.27</v>
       </c>
       <c r="L4" s="31" t="n">
-        <v>19.91</v>
+        <v>20.03</v>
       </c>
       <c r="M4" s="31" t="n">
-        <v>19.67</v>
+        <v>19.74</v>
       </c>
       <c r="N4" s="20" t="inlineStr">
         <is>
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="O4" s="32" t="n">
-        <v>20.17</v>
+        <v>20.3</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>20.13</v>
+        <v>20.3</v>
       </c>
       <c r="Q4" s="33" t="n">
-        <v>20.29</v>
+        <v>20.21</v>
       </c>
       <c r="R4" s="34" t="n">
-        <v>0.79</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5">
@@ -918,54 +918,54 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>12.56</v>
+        <v>12.99</v>
       </c>
       <c r="D5" s="25" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="L5" s="31" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="M5" s="31" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O5" s="32" t="n">
         <v>12.39</v>
       </c>
-      <c r="E5" s="26" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="J5" s="29" t="n">
-        <v>12.05</v>
-      </c>
-      <c r="K5" s="30" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="L5" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="M5" s="31" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="N5" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>12.19</v>
-      </c>
       <c r="P5" s="32" t="n">
-        <v>12.16</v>
+        <v>12.36</v>
       </c>
       <c r="Q5" s="33" t="n">
-        <v>12.26</v>
+        <v>12.44</v>
       </c>
       <c r="R5" s="34" t="n">
-        <v>0.74</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="6">
@@ -980,54 +980,54 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>14.44</v>
+        <v>14.43</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14.16</v>
+        <v>14.24</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>13.93</v>
+        <v>14.08</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>14.08</v>
+        <v>14.14</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>14.18</v>
+        <v>14.23</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>13.9</v>
+        <v>14.04</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>13.8</v>
+        <v>13.95</v>
       </c>
       <c r="J6" s="29" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="K6" s="30" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="L6" s="31" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="M6" s="31" t="n">
         <v>13.62</v>
       </c>
-      <c r="K6" s="30" t="n">
-        <v>13.77</v>
-      </c>
-      <c r="L6" s="31" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="M6" s="31" t="n">
-        <v>13.26</v>
-      </c>
       <c r="N6" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>13.85</v>
+        <v>14.01</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>13.79</v>
+        <v>13.99</v>
       </c>
       <c r="Q6" s="33" t="n">
-        <v>13.99</v>
+        <v>14.06</v>
       </c>
       <c r="R6" s="34" t="n">
-        <v>1.16</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="7">
@@ -1042,37 +1042,37 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>21.4</v>
+        <v>20.99</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>20.66</v>
+        <v>20.62</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>20.04</v>
+        <v>20.31</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>20.45</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>20.69</v>
+        <v>20.61</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>19.95</v>
+        <v>20.24</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>19.71</v>
+        <v>20.08</v>
       </c>
       <c r="J7" s="29" t="n">
-        <v>19.21</v>
+        <v>19.87</v>
       </c>
       <c r="K7" s="30" t="n">
-        <v>19.62</v>
+        <v>20.1</v>
       </c>
       <c r="L7" s="31" t="n">
-        <v>19</v>
+        <v>19.79</v>
       </c>
       <c r="M7" s="31" t="n">
-        <v>18.26</v>
+        <v>19.42</v>
       </c>
       <c r="N7" s="20" t="inlineStr">
         <is>
@@ -1080,16 +1080,16 @@
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>19.82</v>
+        <v>20.18</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>19.68</v>
+        <v>20.13</v>
       </c>
       <c r="Q7" s="33" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="R7" s="34" t="n">
-        <v>3.06</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="8">
@@ -1104,37 +1104,37 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>33.93</v>
+        <v>34.07</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>33.43</v>
+        <v>33.63</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>33.01</v>
+        <v>33.26</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>33.25</v>
+        <v>33.29</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>33.43</v>
+        <v>33.55</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>32.93</v>
+        <v>33.11</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>32.75</v>
+        <v>32.85</v>
       </c>
       <c r="J8" s="29" t="n">
-        <v>32.43</v>
+        <v>32.67</v>
       </c>
       <c r="K8" s="30" t="n">
-        <v>32.73</v>
+        <v>33.02</v>
       </c>
       <c r="L8" s="31" t="n">
-        <v>32.31</v>
+        <v>32.65</v>
       </c>
       <c r="M8" s="31" t="n">
-        <v>31.81</v>
+        <v>32.21</v>
       </c>
       <c r="N8" s="35" t="inlineStr">
         <is>
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="O8" s="32" t="n">
-        <v>32.85</v>
+        <v>33.08</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>32.77</v>
+        <v>33.05</v>
       </c>
       <c r="Q8" s="33" t="n">
-        <v>33.06</v>
+        <v>33.04</v>
       </c>
       <c r="R8" s="36" t="n">
-        <v>-2.25</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="9">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>22.51</v>
+        <v>22.73</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>22.12</v>
+        <v>22.39</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>21.79</v>
+        <v>22.11</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>22.01</v>
+        <v>22.29</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>22.14</v>
+        <v>22.41</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>21.75</v>
+        <v>22.07</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>21.62</v>
+        <v>21.95</v>
       </c>
       <c r="J9" s="29" t="n">
-        <v>21.36</v>
+        <v>21.73</v>
       </c>
       <c r="K9" s="30" t="n">
-        <v>21.58</v>
+        <v>21.91</v>
       </c>
       <c r="L9" s="31" t="n">
-        <v>21.25</v>
+        <v>21.63</v>
       </c>
       <c r="M9" s="31" t="n">
-        <v>20.86</v>
+        <v>21.29</v>
       </c>
       <c r="N9" s="20" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="O9" s="32" t="n">
-        <v>21.68</v>
+        <v>22</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>21.61</v>
+        <v>21.94</v>
       </c>
       <c r="Q9" s="33" t="n">
-        <v>21.88</v>
+        <v>22.18</v>
       </c>
       <c r="R9" s="34" t="n">
-        <v>0.05</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="10">
@@ -1228,37 +1228,37 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>126.75</v>
+        <v>128.59</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>123.75</v>
+        <v>125.69</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>121.24</v>
+        <v>123.26</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>122.7</v>
+        <v>123.93</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>123.8</v>
+        <v>125.37</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>120.8</v>
+        <v>122.47</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>119.7</v>
+        <v>121.03</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>117.8</v>
+        <v>119.57</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>119.56</v>
+        <v>121.64</v>
       </c>
       <c r="L10" s="31" t="n">
-        <v>117.05</v>
+        <v>119.21</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>114.05</v>
+        <v>116.31</v>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>120.3</v>
+        <v>122.17</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>119.79</v>
+        <v>121.86</v>
       </c>
       <c r="Q10" s="33" t="n">
-        <v>121.6</v>
+        <v>122.5</v>
       </c>
       <c r="R10" s="34" t="n">
-        <v>1.42</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="11">
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>65.81</v>
+        <v>65.8</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>65.06</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>64.43000000000001</v>
+        <v>64.61</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>64.58</v>
+        <v>64.67</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>64.97</v>
+        <v>65.03</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>64.22</v>
+        <v>64.38</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>63.83</v>
+        <v>64.02</v>
       </c>
       <c r="J11" s="29" t="n">
-        <v>63.47</v>
+        <v>63.73</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>64.01000000000001</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="L11" s="31" t="n">
-        <v>63.39</v>
+        <v>63.7</v>
       </c>
       <c r="M11" s="31" t="n">
-        <v>62.64</v>
+        <v>63.05</v>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>64.15000000000001</v>
+        <v>64.34</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>64.06999999999999</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="Q11" s="33" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
       <c r="R11" s="36" t="n">
-        <v>-0.47</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="12">
@@ -1352,37 +1352,37 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>24.83</v>
+        <v>25.47</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>24.52</v>
+        <v>24.99</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>24.26</v>
+        <v>24.58</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>24.41</v>
+        <v>24.8</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>24.53</v>
+        <v>24.99</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>24.22</v>
+        <v>24.51</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>24.1</v>
+        <v>24.32</v>
       </c>
       <c r="J12" s="29" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="L12" s="31" t="n">
         <v>23.91</v>
       </c>
-      <c r="K12" s="30" t="n">
-        <v>24.09</v>
-      </c>
-      <c r="L12" s="31" t="n">
-        <v>23.83</v>
-      </c>
       <c r="M12" s="31" t="n">
-        <v>23.52</v>
+        <v>23.43</v>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
@@ -1390,16 +1390,16 @@
         </is>
       </c>
       <c r="O12" s="32" t="n">
-        <v>24.16</v>
+        <v>24.43</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>24.11</v>
+        <v>24.35</v>
       </c>
       <c r="Q12" s="33" t="n">
-        <v>24.3</v>
+        <v>24.62</v>
       </c>
       <c r="R12" s="34" t="n">
-        <v>0.41</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="13">
@@ -1414,37 +1414,37 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>24.7</v>
+        <v>25.27</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>24.3</v>
+        <v>24.67</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>23.96</v>
+        <v>24.17</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>24.18</v>
+        <v>24.35</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>24.32</v>
+        <v>24.62</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>23.92</v>
+        <v>24.02</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>23.78</v>
+        <v>23.75</v>
       </c>
       <c r="J13" s="29" t="n">
-        <v>23.52</v>
+        <v>23.42</v>
       </c>
       <c r="K13" s="30" t="n">
-        <v>23.74</v>
+        <v>23.83</v>
       </c>
       <c r="L13" s="31" t="n">
-        <v>23.4</v>
+        <v>23.33</v>
       </c>
       <c r="M13" s="31" t="n">
-        <v>23</v>
+        <v>22.73</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>23.84</v>
+        <v>23.95</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>23.77</v>
+        <v>23.88</v>
       </c>
       <c r="Q13" s="33" t="n">
-        <v>24.05</v>
+        <v>24.07</v>
       </c>
       <c r="R13" s="34" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="14">
@@ -1476,37 +1476,37 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>40.51</v>
+        <v>42</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>39.95</v>
+        <v>41</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>39.48</v>
+        <v>40.16</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>39.73</v>
+        <v>40.71</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>39.95</v>
+        <v>41.05</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>39.39</v>
+        <v>40.05</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>39.17</v>
+        <v>39.71</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>38.83</v>
+        <v>39.05</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>39.16</v>
+        <v>39.6</v>
       </c>
       <c r="L14" s="31" t="n">
-        <v>38.69</v>
+        <v>38.76</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>38.13</v>
+        <v>37.76</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="O14" s="32" t="n">
-        <v>39.3</v>
+        <v>39.86</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>39.21</v>
+        <v>39.68</v>
       </c>
       <c r="Q14" s="33" t="n">
-        <v>39.52</v>
+        <v>40.38</v>
       </c>
       <c r="R14" s="34" t="n">
-        <v>0.82</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="15">
@@ -1538,37 +1538,37 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>10.07</v>
+        <v>9.57</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>9.529999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>9.08</v>
+        <v>9.15</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>9.300000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>9.52</v>
+        <v>9.32</v>
       </c>
       <c r="H15" s="28" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="I15" s="29" t="n">
         <v>8.98</v>
       </c>
-      <c r="I15" s="29" t="n">
-        <v>8.76</v>
-      </c>
       <c r="J15" s="29" t="n">
-        <v>8.44</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="K15" s="30" t="n">
-        <v>8.779999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="L15" s="31" t="n">
-        <v>8.33</v>
+        <v>8.83</v>
       </c>
       <c r="M15" s="31" t="n">
-        <v>7.79</v>
+        <v>8.6</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
@@ -1576,16 +1576,16 @@
         </is>
       </c>
       <c r="O15" s="32" t="n">
-        <v>8.9</v>
+        <v>9.06</v>
       </c>
       <c r="P15" s="32" t="n">
-        <v>8.82</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="Q15" s="33" t="n">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="R15" s="34" t="n">
-        <v>4.37</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="16">
@@ -1600,54 +1600,54 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>15.24</v>
+        <v>15.63</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.94</v>
+        <v>15.18</v>
       </c>
       <c r="E16" s="26" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="H16" s="28" t="n">
         <v>14.68</v>
       </c>
-      <c r="F16" s="27" t="n">
-        <v>14.81</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="H16" s="28" t="n">
+      <c r="I16" s="29" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="J16" s="29" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="K16" s="30" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="L16" s="31" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="M16" s="31" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O16" s="32" t="n">
         <v>14.63</v>
       </c>
-      <c r="I16" s="29" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="J16" s="29" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="K16" s="30" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="L16" s="31" t="n">
-        <v>14.26</v>
-      </c>
-      <c r="M16" s="31" t="n">
-        <v>13.96</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O16" s="32" t="n">
+      <c r="P16" s="32" t="n">
         <v>14.58</v>
       </c>
-      <c r="P16" s="32" t="n">
-        <v>14.54</v>
-      </c>
       <c r="Q16" s="33" t="n">
-        <v>14.69</v>
+        <v>14.7</v>
       </c>
       <c r="R16" s="34" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="17">
@@ -1662,54 +1662,54 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>5.12</v>
+        <v>5.3</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>4.98</v>
+        <v>5.11</v>
       </c>
       <c r="E17" s="26" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="L17" s="31" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="M17" s="31" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O17" s="32" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="P17" s="32" t="n">
         <v>4.86</v>
       </c>
-      <c r="F17" s="27" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="K17" s="30" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="L17" s="31" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="M17" s="31" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="N17" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O17" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P17" s="32" t="n">
-        <v>4.79</v>
-      </c>
       <c r="Q17" s="33" t="n">
-        <v>4.81</v>
+        <v>4.86</v>
       </c>
       <c r="R17" s="34" t="n">
-        <v>1.26</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="18">
@@ -1724,37 +1724,37 @@
         </is>
       </c>
       <c r="C18" s="25" t="n">
-        <v>17.38</v>
+        <v>17.96</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>16.96</v>
+        <v>17.43</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>16.61</v>
+        <v>16.98</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>16.75</v>
+        <v>17.23</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>16.93</v>
+        <v>17.43</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>16.51</v>
+        <v>16.9</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>16.33</v>
+        <v>16.7</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>16.09</v>
+        <v>16.37</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>16.37</v>
+        <v>16.69</v>
       </c>
       <c r="L18" s="31" t="n">
-        <v>16.02</v>
+        <v>16.24</v>
       </c>
       <c r="M18" s="31" t="n">
-        <v>15.6</v>
+        <v>15.71</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
@@ -1762,16 +1762,16 @@
         </is>
       </c>
       <c r="O18" s="32" t="n">
-        <v>16.46</v>
+        <v>16.81</v>
       </c>
       <c r="P18" s="32" t="n">
-        <v>16.41</v>
+        <v>16.73</v>
       </c>
       <c r="Q18" s="33" t="n">
-        <v>16.56</v>
+        <v>17.03</v>
       </c>
       <c r="R18" s="34" t="n">
-        <v>1.85</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="19">
@@ -1786,37 +1786,37 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>23.58</v>
+        <v>24.17</v>
       </c>
       <c r="D19" s="25" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="I19" s="29" t="n">
         <v>23.29</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="J19" s="29" t="n">
         <v>23.05</v>
       </c>
-      <c r="F19" s="27" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="H19" s="28" t="n">
-        <v>23.01</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>22.91</v>
-      </c>
-      <c r="J19" s="29" t="n">
-        <v>22.72</v>
-      </c>
       <c r="K19" s="30" t="n">
-        <v>22.88</v>
+        <v>23.26</v>
       </c>
       <c r="L19" s="31" t="n">
-        <v>22.64</v>
+        <v>22.95</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>22.35</v>
+        <v>22.57</v>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         </is>
       </c>
       <c r="O19" s="32" t="n">
-        <v>22.96</v>
+        <v>23.36</v>
       </c>
       <c r="P19" s="32" t="n">
-        <v>22.91</v>
+        <v>23.29</v>
       </c>
       <c r="Q19" s="33" t="n">
-        <v>23.1</v>
+        <v>23.54</v>
       </c>
       <c r="R19" s="34" t="n">
-        <v>0.92</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="20">
@@ -1848,37 +1848,37 @@
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>60.95</v>
+        <v>61.45</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>59.65</v>
+        <v>60.15</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>58.56</v>
+        <v>59.06</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>58.75</v>
+        <v>59.25</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>59.45</v>
+        <v>59.95</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>58.15</v>
+        <v>58.65</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>57.45</v>
+        <v>57.95</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>56.85</v>
+        <v>57.35</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>57.84</v>
+        <v>58.34</v>
       </c>
       <c r="L20" s="31" t="n">
-        <v>56.75</v>
+        <v>57.25</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>55.45</v>
+        <v>55.95</v>
       </c>
       <c r="N20" s="35" t="inlineStr">
         <is>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="O20" s="32" t="n">
-        <v>58.04</v>
+        <v>58.54</v>
       </c>
       <c r="P20" s="32" t="n">
-        <v>57.94</v>
+        <v>58.44</v>
       </c>
       <c r="Q20" s="33" t="n">
-        <v>58.05</v>
+        <v>58.55</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>-1.28</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="21">
@@ -1910,37 +1910,37 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>13.48</v>
+        <v>14.67</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>12.99</v>
+        <v>13.76</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>12.58</v>
+        <v>13</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>12.65</v>
+        <v>13.37</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>12.91</v>
+        <v>13.74</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>12.42</v>
+        <v>12.83</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>12.16</v>
+        <v>12.46</v>
       </c>
       <c r="J21" s="29" t="n">
-        <v>11.93</v>
+        <v>11.92</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>12.31</v>
+        <v>12.49</v>
       </c>
       <c r="L21" s="31" t="n">
-        <v>11.9</v>
+        <v>11.73</v>
       </c>
       <c r="M21" s="31" t="n">
-        <v>11.41</v>
+        <v>10.82</v>
       </c>
       <c r="N21" s="35" t="inlineStr">
         <is>
@@ -1948,16 +1948,16 @@
         </is>
       </c>
       <c r="O21" s="32" t="n">
-        <v>12.38</v>
+        <v>12.7</v>
       </c>
       <c r="P21" s="32" t="n">
-        <v>12.35</v>
+        <v>12.56</v>
       </c>
       <c r="Q21" s="33" t="n">
-        <v>12.38</v>
+        <v>13</v>
       </c>
       <c r="R21" s="36" t="n">
-        <v>-6.35</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="22">
@@ -1972,37 +1972,37 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>16.9</v>
+        <v>18.9</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>16.56</v>
+        <v>18.29</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>16.28</v>
+        <v>17.78</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>16.42</v>
+        <v>18.11</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>16.56</v>
+        <v>18.32</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>16.22</v>
+        <v>17.71</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>16.08</v>
+        <v>17.5</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>15.88</v>
+        <v>17.1</v>
       </c>
       <c r="K22" s="30" t="n">
-        <v>16.08</v>
+        <v>17.43</v>
       </c>
       <c r="L22" s="31" t="n">
-        <v>15.8</v>
+        <v>16.92</v>
       </c>
       <c r="M22" s="31" t="n">
-        <v>15.46</v>
+        <v>16.31</v>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
@@ -2010,16 +2010,16 @@
         </is>
       </c>
       <c r="O22" s="32" t="n">
-        <v>16.16</v>
+        <v>17.59</v>
       </c>
       <c r="P22" s="32" t="n">
-        <v>16.11</v>
+        <v>17.48</v>
       </c>
       <c r="Q22" s="33" t="n">
-        <v>16.29</v>
+        <v>17.91</v>
       </c>
       <c r="R22" s="34" t="n">
-        <v>0.43</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="23">
@@ -2034,37 +2034,37 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>36.77</v>
+        <v>37.67</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>36.11</v>
+        <v>36.81</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>35.55</v>
+        <v>36.09</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>35.84</v>
+        <v>36.47</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>36.1</v>
+        <v>36.81</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>35.44</v>
+        <v>35.95</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>35.18</v>
+        <v>35.61</v>
       </c>
       <c r="J23" s="29" t="n">
-        <v>34.78</v>
+        <v>35.09</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>35.19</v>
+        <v>35.61</v>
       </c>
       <c r="L23" s="31" t="n">
-        <v>34.63</v>
+        <v>34.89</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>33.97</v>
+        <v>34.03</v>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="O23" s="32" t="n">
-        <v>35.34</v>
+        <v>35.81</v>
       </c>
       <c r="P23" s="32" t="n">
-        <v>35.24</v>
+        <v>35.68</v>
       </c>
       <c r="Q23" s="33" t="n">
-        <v>35.58</v>
+        <v>36.14</v>
       </c>
       <c r="R23" s="34" t="n">
-        <v>0.96</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="24">
@@ -2096,54 +2096,54 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>15.56</v>
+        <v>15.72</v>
       </c>
       <c r="D24" s="25" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="F24" s="27" t="n">
         <v>15.11</v>
       </c>
-      <c r="E24" s="26" t="n">
-        <v>14.73</v>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>14.98</v>
-      </c>
       <c r="G24" s="27" t="n">
-        <v>15.13</v>
+        <v>15.31</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>14.68</v>
+        <v>14.96</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>14.53</v>
+        <v>14.76</v>
       </c>
       <c r="J24" s="29" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="K24" s="30" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="L24" s="31" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="M24" s="31" t="n">
         <v>14.23</v>
       </c>
-      <c r="K24" s="30" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="L24" s="31" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="M24" s="31" t="n">
-        <v>13.65</v>
-      </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O24" s="32" t="n">
-        <v>14.6</v>
+        <v>14.93</v>
       </c>
       <c r="P24" s="32" t="n">
-        <v>14.51</v>
+        <v>14.9</v>
       </c>
       <c r="Q24" s="33" t="n">
-        <v>14.83</v>
+        <v>14.92</v>
       </c>
       <c r="R24" s="34" t="n">
-        <v>1.99</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="25">
@@ -2158,37 +2158,37 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>40.42</v>
+        <v>42.24</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>38.68</v>
+        <v>40.3</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>37.22</v>
+        <v>38.67</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>37.98</v>
+        <v>39.61</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>38.66</v>
+        <v>40.33</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>36.92</v>
+        <v>38.39</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>36.24</v>
+        <v>37.67</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>35.18</v>
+        <v>36.45</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>36.24</v>
+        <v>37.59</v>
       </c>
       <c r="L25" s="31" t="n">
-        <v>34.78</v>
+        <v>35.96</v>
       </c>
       <c r="M25" s="31" t="n">
-        <v>33.04</v>
+        <v>34.02</v>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -2196,16 +2196,16 @@
         </is>
       </c>
       <c r="O25" s="32" t="n">
-        <v>36.65</v>
+        <v>38.06</v>
       </c>
       <c r="P25" s="32" t="n">
-        <v>36.38</v>
+        <v>37.74</v>
       </c>
       <c r="Q25" s="33" t="n">
-        <v>37.3</v>
+        <v>38.9</v>
       </c>
       <c r="R25" s="34" t="n">
-        <v>2.47</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="26">
@@ -2220,37 +2220,37 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>49.12</v>
+        <v>51.97</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>48.22</v>
+        <v>50.07</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>47.46</v>
+        <v>48.48</v>
       </c>
       <c r="F26" s="27" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="G26" s="27" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="H26" s="28" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="I26" s="29" t="n">
         <v>47.51</v>
       </c>
-      <c r="G26" s="27" t="n">
-        <v>48.03</v>
-      </c>
-      <c r="H26" s="28" t="n">
-        <v>47.13</v>
-      </c>
-      <c r="I26" s="29" t="n">
-        <v>46.61</v>
-      </c>
       <c r="J26" s="29" t="n">
-        <v>46.23</v>
+        <v>46.31</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>46.96</v>
+        <v>47.42</v>
       </c>
       <c r="L26" s="31" t="n">
-        <v>46.2</v>
+        <v>45.83</v>
       </c>
       <c r="M26" s="31" t="n">
-        <v>45.3</v>
+        <v>43.93</v>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
@@ -2258,16 +2258,16 @@
         </is>
       </c>
       <c r="O26" s="32" t="n">
-        <v>47.08</v>
+        <v>47.89</v>
       </c>
       <c r="P26" s="32" t="n">
-        <v>47.03</v>
+        <v>47.57</v>
       </c>
       <c r="Q26" s="33" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="R26" s="36" t="n">
-        <v>-0.84</v>
+        <v>48.72</v>
+      </c>
+      <c r="R26" s="34" t="n">
+        <v>2.83</v>
       </c>
     </row>
     <row r="27">
@@ -2282,54 +2282,54 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>193.14</v>
+        <v>196.64</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>188.54</v>
+        <v>192.04</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>184.69</v>
+        <v>188.19</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>186.1</v>
+        <v>188.93</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>188.2</v>
+        <v>191.37</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>183.6</v>
+        <v>186.77</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>181.5</v>
+        <v>184.33</v>
       </c>
       <c r="J27" s="29" t="n">
-        <v>179</v>
+        <v>182.17</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>182.11</v>
+        <v>185.61</v>
       </c>
       <c r="L27" s="31" t="n">
-        <v>178.26</v>
+        <v>181.76</v>
       </c>
       <c r="M27" s="31" t="n">
-        <v>173.66</v>
-      </c>
-      <c r="N27" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>177.16</v>
+      </c>
+      <c r="N27" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O27" s="32" t="n">
-        <v>183.04</v>
+        <v>186.37</v>
       </c>
       <c r="P27" s="32" t="n">
-        <v>182.47</v>
+        <v>185.97</v>
       </c>
       <c r="Q27" s="33" t="n">
-        <v>184</v>
-      </c>
-      <c r="R27" s="36" t="n">
-        <v>-0.65</v>
+        <v>186.5</v>
+      </c>
+      <c r="R27" s="34" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="28">
@@ -2344,37 +2344,37 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>78.40000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>76.3</v>
+        <v>76.42</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>74.54000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>75.06999999999999</v>
+        <v>74.87</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>76.08</v>
+        <v>76.03</v>
       </c>
       <c r="H28" s="28" t="n">
         <v>73.98</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>72.97</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="J28" s="29" t="n">
-        <v>71.88</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>73.36</v>
+        <v>73.55</v>
       </c>
       <c r="L28" s="31" t="n">
-        <v>71.59999999999999</v>
+        <v>71.83</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>69.5</v>
+        <v>69.78</v>
       </c>
       <c r="N28" s="35" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="O28" s="32" t="n">
-        <v>73.75</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="P28" s="32" t="n">
-        <v>73.53</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="Q28" s="33" t="n">
-        <v>74.05</v>
+        <v>73.7</v>
       </c>
       <c r="R28" s="36" t="n">
-        <v>-1.27</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="29">
@@ -2406,37 +2406,37 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>21.37</v>
+        <v>21.24</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>20.97</v>
+        <v>20.93</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>20.63</v>
+        <v>20.67</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>20.96</v>
+        <v>20.87</v>
       </c>
       <c r="H29" s="28" t="n">
         <v>20.56</v>
       </c>
       <c r="I29" s="29" t="n">
-        <v>20.4</v>
+        <v>20.39</v>
       </c>
       <c r="J29" s="29" t="n">
-        <v>20.16</v>
+        <v>20.25</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>20.41</v>
+        <v>20.5</v>
       </c>
       <c r="L29" s="31" t="n">
-        <v>20.07</v>
+        <v>20.24</v>
       </c>
       <c r="M29" s="31" t="n">
-        <v>19.67</v>
+        <v>19.93</v>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
@@ -2444,16 +2444,16 @@
         </is>
       </c>
       <c r="O29" s="32" t="n">
-        <v>20.5</v>
+        <v>20.54</v>
       </c>
       <c r="P29" s="32" t="n">
-        <v>20.44</v>
+        <v>20.52</v>
       </c>
       <c r="Q29" s="33" t="n">
-        <v>20.64</v>
+        <v>20.52</v>
       </c>
       <c r="R29" s="34" t="n">
-        <v>1.03</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="30">
@@ -2468,37 +2468,37 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>92.83</v>
+        <v>88.12</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>87.68000000000001</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>83.37</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>85.78</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>87.72</v>
+        <v>85.5</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>82.56999999999999</v>
+        <v>83.45</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>80.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="J30" s="29" t="n">
-        <v>77.42</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>80.48</v>
+        <v>83.2</v>
       </c>
       <c r="L30" s="31" t="n">
-        <v>76.17</v>
+        <v>81.48</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>71.02</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="O30" s="32" t="n">
-        <v>81.73</v>
+        <v>83.41</v>
       </c>
       <c r="P30" s="32" t="n">
-        <v>80.88</v>
+        <v>83.36</v>
       </c>
       <c r="Q30" s="33" t="n">
-        <v>83.84999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="R30" s="34" t="n">
-        <v>4.62</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="31">
@@ -2530,37 +2530,37 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>41.22</v>
+        <v>36.66</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>37.44</v>
+        <v>35.2</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>34.27</v>
+        <v>33.98</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>35.16</v>
+        <v>33.92</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>37.02</v>
+        <v>34.84</v>
       </c>
       <c r="H31" s="28" t="n">
-        <v>33.24</v>
+        <v>33.38</v>
       </c>
       <c r="I31" s="29" t="n">
-        <v>31.38</v>
+        <v>32.46</v>
       </c>
       <c r="J31" s="29" t="n">
-        <v>29.46</v>
+        <v>31.92</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>32.15</v>
+        <v>33.16</v>
       </c>
       <c r="L31" s="31" t="n">
-        <v>28.98</v>
+        <v>31.94</v>
       </c>
       <c r="M31" s="31" t="n">
-        <v>25.2</v>
+        <v>30.48</v>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
@@ -2568,16 +2568,16 @@
         </is>
       </c>
       <c r="O31" s="32" t="n">
-        <v>32.84</v>
+        <v>33.33</v>
       </c>
       <c r="P31" s="32" t="n">
-        <v>32.45</v>
+        <v>33.28</v>
       </c>
       <c r="Q31" s="33" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="R31" s="34" t="n">
-        <v>3.03</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="32">
@@ -2592,37 +2592,37 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>53.11</v>
+        <v>53.7</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>51.96</v>
+        <v>52.65</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>51</v>
+        <v>51.77</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>51.43</v>
+        <v>51.88</v>
       </c>
       <c r="G32" s="27" t="n">
-        <v>51.92</v>
+        <v>52.47</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>50.77</v>
+        <v>51.42</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>50.28</v>
+        <v>50.83</v>
       </c>
       <c r="J32" s="29" t="n">
-        <v>49.62</v>
+        <v>50.37</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>50.35</v>
+        <v>51.18</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>49.39</v>
+        <v>50.3</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>48.24</v>
+        <v>49.25</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="O32" s="32" t="n">
-        <v>50.6</v>
+        <v>51.34</v>
       </c>
       <c r="P32" s="32" t="n">
-        <v>50.44</v>
+        <v>51.26</v>
       </c>
       <c r="Q32" s="33" t="n">
-        <v>50.95</v>
+        <v>51.3</v>
       </c>
       <c r="R32" s="34" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="33">
@@ -2654,54 +2654,54 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>125.32</v>
+        <v>134.44</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>121.72</v>
+        <v>127.74</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>118.71</v>
+        <v>122.13</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>119.1</v>
+        <v>124.97</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>121.1</v>
+        <v>127.63</v>
       </c>
       <c r="H33" s="28" t="n">
-        <v>117.5</v>
+        <v>120.93</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>115.5</v>
+        <v>118.27</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>113.9</v>
+        <v>114.23</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>116.69</v>
+        <v>118.37</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>113.68</v>
+        <v>112.76</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>110.08</v>
-      </c>
-      <c r="N33" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>106.06</v>
+      </c>
+      <c r="N33" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O33" s="32" t="n">
-        <v>117.24</v>
+        <v>119.91</v>
       </c>
       <c r="P33" s="32" t="n">
-        <v>116.97</v>
+        <v>118.9</v>
       </c>
       <c r="Q33" s="33" t="n">
-        <v>117.1</v>
-      </c>
-      <c r="R33" s="36" t="n">
-        <v>-1.68</v>
+        <v>122.3</v>
+      </c>
+      <c r="R33" s="34" t="n">
+        <v>2.69</v>
       </c>
     </row>
     <row r="34">
@@ -2716,37 +2716,37 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>49.67</v>
+        <v>50.46</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>48.81</v>
+        <v>49.58</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>48.09</v>
+        <v>48.85</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>48.31</v>
+        <v>48.99</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>48.73</v>
+        <v>49.45</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>47.87</v>
+        <v>48.57</v>
       </c>
       <c r="I34" s="29" t="n">
-        <v>47.45</v>
+        <v>48.11</v>
       </c>
       <c r="J34" s="29" t="n">
-        <v>47.01</v>
+        <v>47.69</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>47.61</v>
+        <v>48.35</v>
       </c>
       <c r="L34" s="31" t="n">
-        <v>46.89</v>
+        <v>47.62</v>
       </c>
       <c r="M34" s="31" t="n">
-        <v>46.03</v>
+        <v>46.74</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="O34" s="32" t="n">
-        <v>47.77</v>
+        <v>48.5</v>
       </c>
       <c r="P34" s="32" t="n">
-        <v>47.68</v>
+        <v>48.42</v>
       </c>
       <c r="Q34" s="33" t="n">
-        <v>47.9</v>
+        <v>48.52</v>
       </c>
       <c r="R34" s="34" t="n">
-        <v>1.31</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="35">
@@ -2778,37 +2778,37 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>26.61</v>
+        <v>26.19</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>25.95</v>
+        <v>25.91</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>25.39</v>
+        <v>25.68</v>
       </c>
       <c r="F35" s="27" t="n">
-        <v>25.72</v>
+        <v>25.79</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>25.96</v>
+        <v>25.91</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>25.3</v>
+        <v>25.63</v>
       </c>
       <c r="I35" s="29" t="n">
-        <v>25.06</v>
+        <v>25.51</v>
       </c>
       <c r="J35" s="29" t="n">
-        <v>24.64</v>
+        <v>25.35</v>
       </c>
       <c r="K35" s="30" t="n">
-        <v>25.03</v>
+        <v>25.52</v>
       </c>
       <c r="L35" s="31" t="n">
-        <v>24.47</v>
+        <v>25.29</v>
       </c>
       <c r="M35" s="31" t="n">
-        <v>23.81</v>
+        <v>25.01</v>
       </c>
       <c r="N35" s="20" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="O35" s="32" t="n">
-        <v>25.19</v>
+        <v>25.59</v>
       </c>
       <c r="P35" s="32" t="n">
-        <v>25.08</v>
+        <v>25.54</v>
       </c>
       <c r="Q35" s="33" t="n">
-        <v>25.48</v>
+        <v>25.68</v>
       </c>
       <c r="R35" s="34" t="n">
-        <v>2.12</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="36">
@@ -2840,37 +2840,37 @@
         </is>
       </c>
       <c r="C36" s="25" t="n">
-        <v>27.82</v>
+        <v>27.51</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>27.14</v>
+        <v>26.95</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>26.57</v>
+        <v>26.48</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>26.73</v>
+        <v>26.69</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>27.07</v>
+        <v>26.93</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>26.39</v>
+        <v>26.37</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>26.05</v>
+        <v>26.13</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>25.71</v>
+        <v>25.81</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>26.19</v>
+        <v>26.16</v>
       </c>
       <c r="L36" s="31" t="n">
-        <v>25.62</v>
+        <v>25.69</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>24.94</v>
+        <v>25.13</v>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="O36" s="32" t="n">
-        <v>26.31</v>
+        <v>26.29</v>
       </c>
       <c r="P36" s="32" t="n">
-        <v>26.24</v>
+        <v>26.21</v>
       </c>
       <c r="Q36" s="33" t="n">
-        <v>26.4</v>
+        <v>26.46</v>
       </c>
       <c r="R36" s="34" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="37">
@@ -2902,54 +2902,54 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>9.19</v>
+        <v>9.33</v>
       </c>
       <c r="D37" s="25" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="E37" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="E37" s="26" t="n">
-        <v>8.84</v>
-      </c>
       <c r="F37" s="27" t="n">
-        <v>8.93</v>
+        <v>9.08</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>9</v>
+        <v>9.15</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>8.81</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I37" s="29" t="n">
-        <v>8.74</v>
+        <v>8.9</v>
       </c>
       <c r="J37" s="29" t="n">
-        <v>8.619999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K37" s="30" t="n">
-        <v>8.73</v>
+        <v>8.9</v>
       </c>
       <c r="L37" s="31" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M37" s="31" t="n">
         <v>8.57</v>
       </c>
-      <c r="M37" s="31" t="n">
-        <v>8.380000000000001</v>
-      </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O37" s="32" t="n">
-        <v>8.779999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="P37" s="32" t="n">
-        <v>8.75</v>
+        <v>8.91</v>
       </c>
       <c r="Q37" s="33" t="n">
-        <v>8.859999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="R37" s="34" t="n">
-        <v>1.37</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="38">
@@ -2964,37 +2964,37 @@
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>32.55</v>
+        <v>32.82</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>31.95</v>
+        <v>32.18</v>
       </c>
       <c r="E38" s="26" t="n">
-        <v>31.45</v>
+        <v>31.64</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>31.66</v>
+        <v>31.93</v>
       </c>
       <c r="G38" s="27" t="n">
-        <v>31.92</v>
+        <v>32.17</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>31.32</v>
+        <v>31.53</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>31.06</v>
+        <v>31.29</v>
       </c>
       <c r="J38" s="29" t="n">
-        <v>30.72</v>
+        <v>30.89</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>31.11</v>
+        <v>31.28</v>
       </c>
       <c r="L38" s="31" t="n">
-        <v>30.61</v>
+        <v>30.74</v>
       </c>
       <c r="M38" s="31" t="n">
-        <v>30.01</v>
+        <v>30.1</v>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
@@ -3002,16 +3002,16 @@
         </is>
       </c>
       <c r="O38" s="32" t="n">
-        <v>31.24</v>
+        <v>31.43</v>
       </c>
       <c r="P38" s="32" t="n">
-        <v>31.16</v>
+        <v>31.33</v>
       </c>
       <c r="Q38" s="33" t="n">
-        <v>31.4</v>
+        <v>31.68</v>
       </c>
       <c r="R38" s="34" t="n">
-        <v>1.29</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="39">
@@ -3026,37 +3026,37 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>207.85</v>
+        <v>207.99</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>201.95</v>
+        <v>202.99</v>
       </c>
       <c r="E39" s="26" t="n">
+        <v>198.8</v>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>199.1</v>
+      </c>
+      <c r="G39" s="27" t="n">
+        <v>202</v>
+      </c>
+      <c r="H39" s="28" t="n">
         <v>197</v>
       </c>
-      <c r="F39" s="27" t="n">
-        <v>200.2</v>
-      </c>
-      <c r="G39" s="27" t="n">
-        <v>202.2</v>
-      </c>
-      <c r="H39" s="28" t="n">
-        <v>196.3</v>
-      </c>
       <c r="I39" s="29" t="n">
-        <v>194.3</v>
+        <v>194.1</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>190.4</v>
+        <v>192</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>193.7</v>
+        <v>196</v>
       </c>
       <c r="L39" s="31" t="n">
-        <v>188.75</v>
+        <v>191.81</v>
       </c>
       <c r="M39" s="31" t="n">
-        <v>182.85</v>
+        <v>186.81</v>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
@@ -3064,16 +3064,16 @@
         </is>
       </c>
       <c r="O39" s="32" t="n">
-        <v>195.23</v>
+        <v>196.69</v>
       </c>
       <c r="P39" s="32" t="n">
-        <v>194.16</v>
+        <v>196.39</v>
       </c>
       <c r="Q39" s="33" t="n">
-        <v>198.2</v>
+        <v>196.2</v>
       </c>
       <c r="R39" s="34" t="n">
-        <v>2.64</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="40">
@@ -3088,37 +3088,37 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>14.39</v>
+        <v>14.97</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>14.18</v>
+        <v>14.59</v>
       </c>
       <c r="E40" s="26" t="n">
-        <v>14</v>
+        <v>14.28</v>
       </c>
       <c r="F40" s="27" t="n">
-        <v>14.08</v>
+        <v>14.45</v>
       </c>
       <c r="G40" s="27" t="n">
-        <v>14.17</v>
+        <v>14.6</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>13.96</v>
+        <v>14.22</v>
       </c>
       <c r="I40" s="29" t="n">
-        <v>13.87</v>
+        <v>14.07</v>
       </c>
       <c r="J40" s="29" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="K40" s="30" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="L40" s="31" t="n">
         <v>13.75</v>
       </c>
-      <c r="K40" s="30" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="L40" s="31" t="n">
-        <v>13.71</v>
-      </c>
       <c r="M40" s="31" t="n">
-        <v>13.5</v>
+        <v>13.37</v>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
@@ -3126,16 +3126,16 @@
         </is>
       </c>
       <c r="O40" s="32" t="n">
-        <v>13.93</v>
+        <v>14.15</v>
       </c>
       <c r="P40" s="32" t="n">
-        <v>13.9</v>
+        <v>14.09</v>
       </c>
       <c r="Q40" s="33" t="n">
-        <v>13.99</v>
+        <v>14.31</v>
       </c>
       <c r="R40" s="34" t="n">
-        <v>1.01</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="41">
@@ -3150,37 +3150,37 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>21.96</v>
+        <v>22.54</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>21.49</v>
+        <v>21.95</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>21.1</v>
+        <v>21.46</v>
       </c>
       <c r="F41" s="27" t="n">
-        <v>21.21</v>
+        <v>21.58</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>21.44</v>
+        <v>21.88</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>20.97</v>
+        <v>21.29</v>
       </c>
       <c r="I41" s="29" t="n">
-        <v>20.74</v>
+        <v>20.99</v>
       </c>
       <c r="J41" s="29" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>20.83</v>
+        <v>21.13</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>20.44</v>
+        <v>20.64</v>
       </c>
       <c r="M41" s="31" t="n">
-        <v>19.97</v>
+        <v>20.05</v>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="O41" s="32" t="n">
-        <v>20.92</v>
+        <v>21.23</v>
       </c>
       <c r="P41" s="32" t="n">
-        <v>20.87</v>
+        <v>21.18</v>
       </c>
       <c r="Q41" s="33" t="n">
-        <v>20.98</v>
+        <v>21.28</v>
       </c>
       <c r="R41" s="34" t="n">
-        <v>0.67</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="42">
@@ -3212,37 +3212,37 @@
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>168.99</v>
+        <v>169.66</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>163.99</v>
+        <v>166.16</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>159.8</v>
+        <v>163.23</v>
       </c>
       <c r="F42" s="27" t="n">
-        <v>161.97</v>
+        <v>163.97</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>163.93</v>
+        <v>165.73</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>158.93</v>
+        <v>162.23</v>
       </c>
       <c r="I42" s="29" t="n">
-        <v>156.97</v>
+        <v>160.47</v>
       </c>
       <c r="J42" s="29" t="n">
-        <v>153.93</v>
+        <v>158.73</v>
       </c>
       <c r="K42" s="30" t="n">
-        <v>157</v>
+        <v>161.27</v>
       </c>
       <c r="L42" s="31" t="n">
-        <v>152.81</v>
+        <v>158.34</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>147.81</v>
+        <v>154.84</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
@@ -3250,16 +3250,16 @@
         </is>
       </c>
       <c r="O42" s="32" t="n">
-        <v>158.16</v>
+        <v>161.89</v>
       </c>
       <c r="P42" s="32" t="n">
-        <v>157.39</v>
+        <v>161.54</v>
       </c>
       <c r="Q42" s="33" t="n">
-        <v>160</v>
+        <v>162.2</v>
       </c>
       <c r="R42" s="34" t="n">
-        <v>0.76</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="43">
@@ -3274,37 +3274,37 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>39.22</v>
+        <v>38.15</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>38.16</v>
+        <v>37.71</v>
       </c>
       <c r="E43" s="26" t="n">
-        <v>37.27</v>
+        <v>37.34</v>
       </c>
       <c r="F43" s="27" t="n">
-        <v>37.6</v>
+        <v>37.41</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>38.08</v>
+        <v>37.65</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>37.02</v>
+        <v>37.21</v>
       </c>
       <c r="I43" s="29" t="n">
-        <v>36.54</v>
+        <v>36.97</v>
       </c>
       <c r="J43" s="29" t="n">
-        <v>35.96</v>
+        <v>36.77</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>36.67</v>
+        <v>37.1</v>
       </c>
       <c r="L43" s="31" t="n">
-        <v>35.78</v>
+        <v>36.73</v>
       </c>
       <c r="M43" s="31" t="n">
-        <v>34.72</v>
+        <v>36.29</v>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
@@ -3312,16 +3312,16 @@
         </is>
       </c>
       <c r="O43" s="32" t="n">
-        <v>36.89</v>
+        <v>37.17</v>
       </c>
       <c r="P43" s="32" t="n">
-        <v>36.76</v>
+        <v>37.13</v>
       </c>
       <c r="Q43" s="33" t="n">
-        <v>37.12</v>
+        <v>37.18</v>
       </c>
       <c r="R43" s="34" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="44">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>29.77</v>
+        <v>29.86</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>28.75</v>
+        <v>28.96</v>
       </c>
       <c r="E44" s="26" t="n">
-        <v>27.9</v>
+        <v>28.2</v>
       </c>
       <c r="F44" s="27" t="n">
-        <v>28.26</v>
+        <v>28.5</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>27.68</v>
+        <v>28</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>27.24</v>
+        <v>27.6</v>
       </c>
       <c r="J44" s="29" t="n">
-        <v>26.66</v>
+        <v>27.1</v>
       </c>
       <c r="K44" s="30" t="n">
-        <v>27.32</v>
+        <v>27.7</v>
       </c>
       <c r="L44" s="31" t="n">
-        <v>26.47</v>
+        <v>26.94</v>
       </c>
       <c r="M44" s="31" t="n">
-        <v>25.45</v>
+        <v>26.04</v>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
@@ -3374,16 +3374,16 @@
         </is>
       </c>
       <c r="O44" s="32" t="n">
-        <v>27.54</v>
+        <v>27.88</v>
       </c>
       <c r="P44" s="32" t="n">
-        <v>27.4</v>
+        <v>27.77</v>
       </c>
       <c r="Q44" s="33" t="n">
-        <v>27.82</v>
+        <v>28.1</v>
       </c>
       <c r="R44" s="34" t="n">
-        <v>2.28</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="45">
@@ -3398,37 +3398,37 @@
         </is>
       </c>
       <c r="C45" s="25" t="n">
-        <v>27.99</v>
+        <v>27.84</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>27.45</v>
+        <v>27.48</v>
       </c>
       <c r="E45" s="26" t="n">
-        <v>27</v>
+        <v>27.18</v>
       </c>
       <c r="F45" s="27" t="n">
-        <v>27.3</v>
+        <v>27.14</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>27.48</v>
+        <v>27.38</v>
       </c>
       <c r="H45" s="28" t="n">
-        <v>26.94</v>
+        <v>27.02</v>
       </c>
       <c r="I45" s="29" t="n">
-        <v>26.76</v>
+        <v>26.78</v>
       </c>
       <c r="J45" s="29" t="n">
-        <v>26.4</v>
+        <v>26.66</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>26.7</v>
+        <v>26.98</v>
       </c>
       <c r="L45" s="31" t="n">
-        <v>26.25</v>
+        <v>26.68</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>25.71</v>
+        <v>26.32</v>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
@@ -3436,16 +3436,16 @@
         </is>
       </c>
       <c r="O45" s="32" t="n">
-        <v>26.84</v>
+        <v>27.01</v>
       </c>
       <c r="P45" s="32" t="n">
-        <v>26.74</v>
+        <v>27.01</v>
       </c>
       <c r="Q45" s="33" t="n">
-        <v>27.12</v>
+        <v>26.9</v>
       </c>
       <c r="R45" s="34" t="n">
-        <v>2.03</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="46">
@@ -3460,37 +3460,37 @@
         </is>
       </c>
       <c r="C46" s="25" t="n">
-        <v>8.550000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>8.33</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>8.140000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F46" s="27" t="n">
-        <v>8.220000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="G46" s="27" t="n">
-        <v>8.32</v>
+        <v>8.35</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>8.1</v>
+        <v>8.17</v>
       </c>
       <c r="I46" s="29" t="n">
-        <v>8</v>
+        <v>8.09</v>
       </c>
       <c r="J46" s="29" t="n">
-        <v>7.88</v>
+        <v>7.99</v>
       </c>
       <c r="K46" s="30" t="n">
-        <v>8.02</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L46" s="31" t="n">
-        <v>7.83</v>
+        <v>7.96</v>
       </c>
       <c r="M46" s="31" t="n">
-        <v>7.61</v>
+        <v>7.78</v>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
@@ -3498,16 +3498,16 @@
         </is>
       </c>
       <c r="O46" s="32" t="n">
-        <v>8.07</v>
+        <v>8.15</v>
       </c>
       <c r="P46" s="32" t="n">
-        <v>8.039999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="Q46" s="33" t="n">
-        <v>8.130000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="R46" s="34" t="n">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="47">
@@ -3522,37 +3522,37 @@
         </is>
       </c>
       <c r="C47" s="25" t="n">
-        <v>12.84</v>
+        <v>13.53</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>12.55</v>
+        <v>13.01</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>12.31</v>
+        <v>12.58</v>
       </c>
       <c r="F47" s="27" t="n">
-        <v>12.33</v>
+        <v>12.86</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>12.5</v>
+        <v>13.03</v>
       </c>
       <c r="H47" s="28" t="n">
-        <v>12.21</v>
+        <v>12.51</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>12.04</v>
+        <v>12.34</v>
       </c>
       <c r="J47" s="29" t="n">
-        <v>11.92</v>
+        <v>11.99</v>
       </c>
       <c r="K47" s="30" t="n">
-        <v>12.14</v>
+        <v>12.28</v>
       </c>
       <c r="L47" s="31" t="n">
-        <v>11.9</v>
+        <v>11.85</v>
       </c>
       <c r="M47" s="31" t="n">
-        <v>11.61</v>
+        <v>11.33</v>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
@@ -3560,16 +3560,16 @@
         </is>
       </c>
       <c r="O47" s="32" t="n">
-        <v>12.19</v>
+        <v>12.42</v>
       </c>
       <c r="P47" s="32" t="n">
-        <v>12.17</v>
+        <v>12.32</v>
       </c>
       <c r="Q47" s="33" t="n">
-        <v>12.17</v>
+        <v>12.68</v>
       </c>
       <c r="R47" s="34" t="n">
-        <v>0.58</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="48">
@@ -3584,37 +3584,37 @@
         </is>
       </c>
       <c r="C48" s="25" t="n">
-        <v>211.5</v>
+        <v>210.04</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>208.1</v>
+        <v>206.74</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>205.25</v>
+        <v>203.97</v>
       </c>
       <c r="F48" s="27" t="n">
-        <v>206</v>
+        <v>204.47</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>207.7</v>
+        <v>206.23</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>204.3</v>
+        <v>202.93</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>202.6</v>
+        <v>201.17</v>
       </c>
       <c r="J48" s="29" t="n">
-        <v>200.9</v>
+        <v>199.63</v>
       </c>
       <c r="K48" s="30" t="n">
-        <v>203.35</v>
+        <v>202.13</v>
       </c>
       <c r="L48" s="31" t="n">
-        <v>200.5</v>
+        <v>199.36</v>
       </c>
       <c r="M48" s="31" t="n">
-        <v>197.1</v>
+        <v>196.06</v>
       </c>
       <c r="N48" s="35" t="inlineStr">
         <is>
@@ -3622,16 +3622,16 @@
         </is>
       </c>
       <c r="O48" s="32" t="n">
-        <v>203.96</v>
+        <v>202.66</v>
       </c>
       <c r="P48" s="32" t="n">
-        <v>203.61</v>
+        <v>202.38</v>
       </c>
       <c r="Q48" s="33" t="n">
-        <v>204.3</v>
+        <v>202.7</v>
       </c>
       <c r="R48" s="36" t="n">
-        <v>-0.83</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="49">
@@ -3646,37 +3646,37 @@
         </is>
       </c>
       <c r="C49" s="25" t="n">
-        <v>50.55</v>
+        <v>49.33</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>48.91</v>
+        <v>48.51</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>47.54</v>
+        <v>47.82</v>
       </c>
       <c r="F49" s="27" t="n">
-        <v>48.21</v>
+        <v>48.27</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>48.87</v>
+        <v>48.55</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>47.23</v>
+        <v>47.73</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>46.57</v>
+        <v>47.45</v>
       </c>
       <c r="J49" s="29" t="n">
-        <v>45.59</v>
+        <v>46.91</v>
       </c>
       <c r="K49" s="30" t="n">
-        <v>46.62</v>
+        <v>47.36</v>
       </c>
       <c r="L49" s="31" t="n">
-        <v>45.25</v>
+        <v>46.67</v>
       </c>
       <c r="M49" s="31" t="n">
-        <v>43.61</v>
+        <v>45.85</v>
       </c>
       <c r="N49" s="20" t="inlineStr">
         <is>
@@ -3684,16 +3684,16 @@
         </is>
       </c>
       <c r="O49" s="32" t="n">
-        <v>46.99</v>
+        <v>47.58</v>
       </c>
       <c r="P49" s="32" t="n">
-        <v>46.75</v>
+        <v>47.42</v>
       </c>
       <c r="Q49" s="33" t="n">
-        <v>47.54</v>
+        <v>48</v>
       </c>
       <c r="R49" s="34" t="n">
-        <v>1.28</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="50">
@@ -3708,37 +3708,37 @@
         </is>
       </c>
       <c r="C50" s="25" t="n">
-        <v>33.28</v>
+        <v>32.76</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>32.14</v>
+        <v>32.08</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>31.19</v>
+        <v>31.51</v>
       </c>
       <c r="F50" s="27" t="n">
-        <v>31.53</v>
+        <v>31.65</v>
       </c>
       <c r="G50" s="27" t="n">
-        <v>32.05</v>
+        <v>31.99</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>30.91</v>
+        <v>31.31</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>30.39</v>
+        <v>30.97</v>
       </c>
       <c r="J50" s="29" t="n">
-        <v>29.77</v>
+        <v>30.63</v>
       </c>
       <c r="K50" s="30" t="n">
-        <v>30.55</v>
+        <v>31.13</v>
       </c>
       <c r="L50" s="31" t="n">
-        <v>29.6</v>
+        <v>30.56</v>
       </c>
       <c r="M50" s="31" t="n">
-        <v>28.46</v>
+        <v>29.88</v>
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
@@ -3746,16 +3746,16 @@
         </is>
       </c>
       <c r="O50" s="32" t="n">
-        <v>30.78</v>
+        <v>31.25</v>
       </c>
       <c r="P50" s="32" t="n">
-        <v>30.64</v>
+        <v>31.18</v>
       </c>
       <c r="Q50" s="33" t="n">
-        <v>31</v>
+        <v>31.3</v>
       </c>
       <c r="R50" s="34" t="n">
-        <v>1.97</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="51">
@@ -3770,48 +3770,48 @@
         </is>
       </c>
       <c r="C51" s="25" t="n">
-        <v>13.71</v>
+        <v>13.78</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>13.42</v>
+        <v>13.52</v>
       </c>
       <c r="E51" s="26" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="G51" s="27" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="H51" s="28" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="I51" s="29" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J51" s="29" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="K51" s="30" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="L51" s="31" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="M51" s="31" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="N51" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O51" s="32" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="P51" s="32" t="n">
         <v>13.18</v>
-      </c>
-      <c r="F51" s="27" t="n">
-        <v>13.34</v>
-      </c>
-      <c r="G51" s="27" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="H51" s="28" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="I51" s="29" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="J51" s="29" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="K51" s="30" t="n">
-        <v>13.01</v>
-      </c>
-      <c r="L51" s="31" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="M51" s="31" t="n">
-        <v>12.48</v>
-      </c>
-      <c r="N51" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O51" s="32" t="n">
-        <v>13.09</v>
-      </c>
-      <c r="P51" s="32" t="n">
-        <v>13.04</v>
       </c>
       <c r="Q51" s="33" t="n">
         <v>13.24</v>
@@ -3832,37 +3832,37 @@
         </is>
       </c>
       <c r="C52" s="25" t="n">
-        <v>58.71</v>
+        <v>61.05</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>57.16</v>
+        <v>58.95</v>
       </c>
       <c r="E52" s="26" t="n">
-        <v>55.86</v>
+        <v>57.19</v>
       </c>
       <c r="F52" s="27" t="n">
-        <v>56.42</v>
+        <v>58.08</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>57.08</v>
+        <v>58.92</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>55.53</v>
+        <v>56.82</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>54.87</v>
+        <v>55.98</v>
       </c>
       <c r="J52" s="29" t="n">
-        <v>53.98</v>
+        <v>54.72</v>
       </c>
       <c r="K52" s="30" t="n">
-        <v>54.99</v>
+        <v>56.01</v>
       </c>
       <c r="L52" s="31" t="n">
-        <v>53.69</v>
+        <v>54.25</v>
       </c>
       <c r="M52" s="31" t="n">
-        <v>52.14</v>
+        <v>52.15</v>
       </c>
       <c r="N52" s="20" t="inlineStr">
         <is>
@@ -3870,16 +3870,16 @@
         </is>
       </c>
       <c r="O52" s="32" t="n">
-        <v>55.32</v>
+        <v>56.5</v>
       </c>
       <c r="P52" s="32" t="n">
-        <v>55.11</v>
+        <v>56.18</v>
       </c>
       <c r="Q52" s="33" t="n">
-        <v>55.75</v>
+        <v>57.25</v>
       </c>
       <c r="R52" s="34" t="n">
-        <v>0.09</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="53">
@@ -3894,37 +3894,37 @@
         </is>
       </c>
       <c r="C53" s="25" t="n">
-        <v>24.63</v>
+        <v>24.35</v>
       </c>
       <c r="D53" s="25" t="n">
-        <v>23.71</v>
+        <v>23.79</v>
       </c>
       <c r="E53" s="26" t="n">
-        <v>22.94</v>
+        <v>23.32</v>
       </c>
       <c r="F53" s="27" t="n">
-        <v>23.35</v>
+        <v>23.61</v>
       </c>
       <c r="G53" s="27" t="n">
-        <v>23.71</v>
+        <v>23.81</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>22.79</v>
+        <v>23.25</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>22.43</v>
+        <v>23.05</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>21.87</v>
+        <v>22.69</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>22.42</v>
+        <v>23</v>
       </c>
       <c r="L53" s="31" t="n">
-        <v>21.65</v>
+        <v>22.53</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>20.73</v>
+        <v>21.97</v>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="O53" s="32" t="n">
-        <v>22.64</v>
+        <v>23.15</v>
       </c>
       <c r="P53" s="32" t="n">
-        <v>22.49</v>
+        <v>23.05</v>
       </c>
       <c r="Q53" s="33" t="n">
-        <v>23</v>
+        <v>23.42</v>
       </c>
       <c r="R53" s="34" t="n">
-        <v>3.32</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="54">
@@ -3956,37 +3956,37 @@
         </is>
       </c>
       <c r="C54" s="25" t="n">
-        <v>5.92</v>
+        <v>5.99</v>
       </c>
       <c r="D54" s="25" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="E54" s="26" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="F54" s="27" t="n">
         <v>5.61</v>
       </c>
-      <c r="E54" s="26" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="F54" s="27" t="n">
-        <v>5.51</v>
-      </c>
       <c r="G54" s="27" t="n">
-        <v>5.62</v>
+        <v>5.73</v>
       </c>
       <c r="H54" s="28" t="n">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>5.2</v>
+        <v>5.38</v>
       </c>
       <c r="J54" s="29" t="n">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="K54" s="30" t="n">
-        <v>5.18</v>
+        <v>5.44</v>
       </c>
       <c r="L54" s="31" t="n">
-        <v>4.92</v>
+        <v>5.25</v>
       </c>
       <c r="M54" s="31" t="n">
-        <v>4.61</v>
+        <v>5.02</v>
       </c>
       <c r="N54" s="20" t="inlineStr">
         <is>
@@ -3994,16 +3994,16 @@
         </is>
       </c>
       <c r="O54" s="32" t="n">
-        <v>5.26</v>
+        <v>5.48</v>
       </c>
       <c r="P54" s="32" t="n">
-        <v>5.2</v>
+        <v>5.46</v>
       </c>
       <c r="Q54" s="33" t="n">
-        <v>5.4</v>
+        <v>5.49</v>
       </c>
       <c r="R54" s="34" t="n">
-        <v>5.26</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="55">
@@ -4018,37 +4018,37 @@
         </is>
       </c>
       <c r="C55" s="25" t="n">
-        <v>19.85</v>
+        <v>19.58</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>18.07</v>
+        <v>18.44</v>
       </c>
       <c r="E55" s="26" t="n">
-        <v>16.58</v>
+        <v>17.49</v>
       </c>
       <c r="F55" s="27" t="n">
-        <v>17.56</v>
+        <v>17.62</v>
       </c>
       <c r="G55" s="27" t="n">
-        <v>18.16</v>
+        <v>18.25</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>16.38</v>
+        <v>17.11</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>15.78</v>
+        <v>16.48</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>14.6</v>
+        <v>15.97</v>
       </c>
       <c r="K55" s="30" t="n">
-        <v>15.58</v>
+        <v>16.85</v>
       </c>
       <c r="L55" s="31" t="n">
-        <v>14.09</v>
+        <v>15.9</v>
       </c>
       <c r="M55" s="31" t="n">
-        <v>12.31</v>
+        <v>14.76</v>
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
@@ -4056,16 +4056,16 @@
         </is>
       </c>
       <c r="O55" s="32" t="n">
-        <v>16.05</v>
+        <v>17.02</v>
       </c>
       <c r="P55" s="32" t="n">
-        <v>15.72</v>
+        <v>16.94</v>
       </c>
       <c r="Q55" s="33" t="n">
-        <v>16.97</v>
+        <v>16.99</v>
       </c>
       <c r="R55" s="34" t="n">
-        <v>9.98</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="56">
@@ -4080,37 +4080,37 @@
         </is>
       </c>
       <c r="C56" s="25" t="n">
-        <v>86.65000000000001</v>
+        <v>85.28</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>84.55</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="E56" s="26" t="n">
-        <v>82.79000000000001</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="F56" s="27" t="n">
-        <v>83.58</v>
+        <v>83.2</v>
       </c>
       <c r="G56" s="27" t="n">
-        <v>84.47</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>82.37</v>
+        <v>82.8</v>
       </c>
       <c r="I56" s="29" t="n">
-        <v>81.48</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="J56" s="29" t="n">
-        <v>80.27</v>
+        <v>81.7</v>
       </c>
       <c r="K56" s="30" t="n">
-        <v>81.61</v>
+        <v>82.64</v>
       </c>
       <c r="L56" s="31" t="n">
-        <v>79.84999999999999</v>
+        <v>81.72</v>
       </c>
       <c r="M56" s="31" t="n">
-        <v>77.75</v>
+        <v>80.62</v>
       </c>
       <c r="N56" s="20" t="inlineStr">
         <is>
@@ -4118,16 +4118,16 @@
         </is>
       </c>
       <c r="O56" s="32" t="n">
-        <v>82.06999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="P56" s="32" t="n">
-        <v>81.78</v>
+        <v>82.73</v>
       </c>
       <c r="Q56" s="33" t="n">
-        <v>82.7</v>
+        <v>82.5</v>
       </c>
       <c r="R56" s="34" t="n">
-        <v>0.79</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="57">
@@ -4142,37 +4142,37 @@
         </is>
       </c>
       <c r="C57" s="25" t="n">
-        <v>18.34</v>
+        <v>19.87</v>
       </c>
       <c r="D57" s="25" t="n">
-        <v>17.86</v>
+        <v>18.98</v>
       </c>
       <c r="E57" s="26" t="n">
-        <v>17.45</v>
+        <v>18.23</v>
       </c>
       <c r="F57" s="27" t="n">
-        <v>17.71</v>
+        <v>18.63</v>
       </c>
       <c r="G57" s="27" t="n">
-        <v>17.88</v>
+        <v>18.97</v>
       </c>
       <c r="H57" s="28" t="n">
-        <v>17.4</v>
+        <v>18.08</v>
       </c>
       <c r="I57" s="29" t="n">
-        <v>17.23</v>
+        <v>17.74</v>
       </c>
       <c r="J57" s="29" t="n">
-        <v>16.92</v>
+        <v>17.19</v>
       </c>
       <c r="K57" s="30" t="n">
-        <v>17.19</v>
+        <v>17.74</v>
       </c>
       <c r="L57" s="31" t="n">
-        <v>16.78</v>
+        <v>16.99</v>
       </c>
       <c r="M57" s="31" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="N57" s="20" t="inlineStr">
         <is>
@@ -4180,16 +4180,16 @@
         </is>
       </c>
       <c r="O57" s="32" t="n">
-        <v>17.31</v>
+        <v>17.94</v>
       </c>
       <c r="P57" s="32" t="n">
-        <v>17.22</v>
+        <v>17.81</v>
       </c>
       <c r="Q57" s="33" t="n">
-        <v>17.55</v>
+        <v>18.28</v>
       </c>
       <c r="R57" s="34" t="n">
-        <v>2.33</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="58">
@@ -4204,37 +4204,37 @@
         </is>
       </c>
       <c r="C58" s="25" t="n">
-        <v>22.78</v>
+        <v>22.77</v>
       </c>
       <c r="D58" s="25" t="n">
-        <v>22.44</v>
+        <v>22.53</v>
       </c>
       <c r="E58" s="26" t="n">
-        <v>22.16</v>
+        <v>22.33</v>
       </c>
       <c r="F58" s="27" t="n">
-        <v>22.34</v>
+        <v>22.46</v>
       </c>
       <c r="G58" s="27" t="n">
-        <v>22.46</v>
+        <v>22.54</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>22.12</v>
+        <v>22.3</v>
       </c>
       <c r="I58" s="29" t="n">
-        <v>22</v>
+        <v>22.22</v>
       </c>
       <c r="J58" s="29" t="n">
-        <v>21.78</v>
+        <v>22.06</v>
       </c>
       <c r="K58" s="30" t="n">
-        <v>21.96</v>
+        <v>22.19</v>
       </c>
       <c r="L58" s="31" t="n">
-        <v>21.68</v>
+        <v>21.99</v>
       </c>
       <c r="M58" s="31" t="n">
-        <v>21.34</v>
+        <v>21.75</v>
       </c>
       <c r="N58" s="20" t="inlineStr">
         <is>
@@ -4242,16 +4242,16 @@
         </is>
       </c>
       <c r="O58" s="32" t="n">
-        <v>22.05</v>
+        <v>22.26</v>
       </c>
       <c r="P58" s="32" t="n">
-        <v>21.99</v>
+        <v>22.21</v>
       </c>
       <c r="Q58" s="33" t="n">
-        <v>22.23</v>
+        <v>22.38</v>
       </c>
       <c r="R58" s="34" t="n">
-        <v>0.91</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="59">
@@ -4266,37 +4266,37 @@
         </is>
       </c>
       <c r="C59" s="25" t="n">
-        <v>24.18</v>
+        <v>24.72</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>23.49</v>
+        <v>23.93</v>
       </c>
       <c r="E59" s="26" t="n">
-        <v>22.91</v>
+        <v>23.27</v>
       </c>
       <c r="F59" s="27" t="n">
-        <v>23.2</v>
+        <v>23.58</v>
       </c>
       <c r="G59" s="27" t="n">
-        <v>23.48</v>
+        <v>23.9</v>
       </c>
       <c r="H59" s="28" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="I59" s="29" t="n">
         <v>22.79</v>
       </c>
-      <c r="I59" s="29" t="n">
-        <v>22.51</v>
-      </c>
       <c r="J59" s="29" t="n">
-        <v>22.1</v>
+        <v>22.32</v>
       </c>
       <c r="K59" s="30" t="n">
-        <v>22.52</v>
+        <v>22.82</v>
       </c>
       <c r="L59" s="31" t="n">
-        <v>21.94</v>
+        <v>22.16</v>
       </c>
       <c r="M59" s="31" t="n">
-        <v>21.25</v>
+        <v>21.37</v>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
@@ -4304,16 +4304,16 @@
         </is>
       </c>
       <c r="O59" s="32" t="n">
-        <v>22.68</v>
+        <v>23</v>
       </c>
       <c r="P59" s="32" t="n">
-        <v>22.58</v>
+        <v>22.89</v>
       </c>
       <c r="Q59" s="33" t="n">
-        <v>22.93</v>
+        <v>23.25</v>
       </c>
       <c r="R59" s="34" t="n">
-        <v>2.78</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="60">
@@ -4328,37 +4328,37 @@
         </is>
       </c>
       <c r="C60" s="25" t="n">
-        <v>29.41</v>
+        <v>29.15</v>
       </c>
       <c r="D60" s="25" t="n">
-        <v>28.91</v>
+        <v>28.75</v>
       </c>
       <c r="E60" s="26" t="n">
-        <v>28.49</v>
+        <v>28.41</v>
       </c>
       <c r="F60" s="27" t="n">
-        <v>28.66</v>
+        <v>28.59</v>
       </c>
       <c r="G60" s="27" t="n">
-        <v>28.88</v>
+        <v>28.75</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>28.38</v>
+        <v>28.35</v>
       </c>
       <c r="I60" s="29" t="n">
-        <v>28.16</v>
+        <v>28.19</v>
       </c>
       <c r="J60" s="29" t="n">
-        <v>27.88</v>
+        <v>27.95</v>
       </c>
       <c r="K60" s="30" t="n">
-        <v>28.21</v>
+        <v>28.19</v>
       </c>
       <c r="L60" s="31" t="n">
-        <v>27.79</v>
+        <v>27.85</v>
       </c>
       <c r="M60" s="31" t="n">
-        <v>27.29</v>
+        <v>27.45</v>
       </c>
       <c r="N60" s="20" t="inlineStr">
         <is>
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="O60" s="32" t="n">
-        <v>28.31</v>
+        <v>28.28</v>
       </c>
       <c r="P60" s="32" t="n">
-        <v>28.25</v>
+        <v>28.22</v>
       </c>
       <c r="Q60" s="33" t="n">
         <v>28.44</v>
@@ -4390,37 +4390,37 @@
         </is>
       </c>
       <c r="C61" s="25" t="n">
-        <v>43.77</v>
+        <v>43.88</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>43.53</v>
+        <v>43.62</v>
       </c>
       <c r="E61" s="26" t="n">
-        <v>43.33</v>
+        <v>43.4</v>
       </c>
       <c r="F61" s="27" t="n">
-        <v>43.46</v>
+        <v>43.51</v>
       </c>
       <c r="G61" s="27" t="n">
-        <v>43.54</v>
+        <v>43.61</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>43.3</v>
+        <v>43.35</v>
       </c>
       <c r="I61" s="29" t="n">
-        <v>43.22</v>
+        <v>43.25</v>
       </c>
       <c r="J61" s="29" t="n">
-        <v>43.06</v>
+        <v>43.09</v>
       </c>
       <c r="K61" s="30" t="n">
-        <v>43.19</v>
+        <v>43.26</v>
       </c>
       <c r="L61" s="31" t="n">
-        <v>42.99</v>
+        <v>43.04</v>
       </c>
       <c r="M61" s="31" t="n">
-        <v>42.75</v>
+        <v>42.78</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
@@ -4428,16 +4428,16 @@
         </is>
       </c>
       <c r="O61" s="32" t="n">
-        <v>43.26</v>
+        <v>43.32</v>
       </c>
       <c r="P61" s="32" t="n">
-        <v>43.21</v>
+        <v>43.28</v>
       </c>
       <c r="Q61" s="33" t="n">
-        <v>43.38</v>
+        <v>43.4</v>
       </c>
       <c r="R61" s="34" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="62">
@@ -4452,37 +4452,37 @@
         </is>
       </c>
       <c r="C62" s="25" t="n">
-        <v>18.84</v>
+        <v>19.32</v>
       </c>
       <c r="D62" s="25" t="n">
-        <v>18.74</v>
+        <v>19.11</v>
       </c>
       <c r="E62" s="26" t="n">
-        <v>18.66</v>
+        <v>18.93</v>
       </c>
       <c r="F62" s="27" t="n">
-        <v>18.71</v>
+        <v>19</v>
       </c>
       <c r="G62" s="27" t="n">
-        <v>18.75</v>
+        <v>19.1</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>18.65</v>
+        <v>18.89</v>
       </c>
       <c r="I62" s="29" t="n">
-        <v>18.61</v>
+        <v>18.79</v>
       </c>
       <c r="J62" s="29" t="n">
-        <v>18.55</v>
+        <v>18.68</v>
       </c>
       <c r="K62" s="30" t="n">
-        <v>18.6</v>
+        <v>18.82</v>
       </c>
       <c r="L62" s="31" t="n">
-        <v>18.52</v>
+        <v>18.64</v>
       </c>
       <c r="M62" s="31" t="n">
-        <v>18.42</v>
+        <v>18.43</v>
       </c>
       <c r="N62" s="20" t="inlineStr">
         <is>
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="O62" s="32" t="n">
-        <v>18.63</v>
+        <v>18.86</v>
       </c>
       <c r="P62" s="32" t="n">
-        <v>18.61</v>
+        <v>18.83</v>
       </c>
       <c r="Q62" s="33" t="n">
-        <v>18.68</v>
+        <v>18.91</v>
       </c>
       <c r="R62" s="34" t="n">
-        <v>0.59</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="63">
@@ -4514,54 +4514,54 @@
         </is>
       </c>
       <c r="C63" s="25" t="n">
-        <v>15.24</v>
+        <v>15.64</v>
       </c>
       <c r="D63" s="25" t="n">
-        <v>15.09</v>
+        <v>15.36</v>
       </c>
       <c r="E63" s="26" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="F63" s="27" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="G63" s="27" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="H63" s="28" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="I63" s="29" t="n">
         <v>14.97</v>
       </c>
-      <c r="F63" s="27" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="G63" s="27" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="H63" s="28" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="I63" s="29" t="n">
-        <v>14.87</v>
-      </c>
       <c r="J63" s="29" t="n">
-        <v>14.78</v>
+        <v>14.8</v>
       </c>
       <c r="K63" s="30" t="n">
-        <v>14.88</v>
+        <v>14.97</v>
       </c>
       <c r="L63" s="31" t="n">
-        <v>14.76</v>
+        <v>14.74</v>
       </c>
       <c r="M63" s="31" t="n">
-        <v>14.61</v>
-      </c>
-      <c r="N63" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>14.46</v>
+      </c>
+      <c r="N63" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O63" s="32" t="n">
-        <v>14.91</v>
+        <v>15.04</v>
       </c>
       <c r="P63" s="32" t="n">
-        <v>14.89</v>
+        <v>14.99</v>
       </c>
       <c r="Q63" s="33" t="n">
-        <v>14.95</v>
+        <v>15.14</v>
       </c>
       <c r="R63" s="34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="64">
@@ -4576,37 +4576,37 @@
         </is>
       </c>
       <c r="C64" s="25" t="n">
-        <v>25.98</v>
+        <v>25.52</v>
       </c>
       <c r="D64" s="25" t="n">
-        <v>25.51</v>
+        <v>25.26</v>
       </c>
       <c r="E64" s="26" t="n">
-        <v>25.12</v>
+        <v>25.04</v>
       </c>
       <c r="F64" s="27" t="n">
-        <v>25.16</v>
+        <v>25.05</v>
       </c>
       <c r="G64" s="27" t="n">
-        <v>25.43</v>
+        <v>25.21</v>
       </c>
       <c r="H64" s="28" t="n">
-        <v>24.96</v>
+        <v>24.95</v>
       </c>
       <c r="I64" s="29" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="J64" s="29" t="n">
         <v>24.69</v>
       </c>
-      <c r="J64" s="29" t="n">
-        <v>24.49</v>
-      </c>
       <c r="K64" s="30" t="n">
-        <v>24.85</v>
+        <v>24.9</v>
       </c>
       <c r="L64" s="31" t="n">
-        <v>24.46</v>
+        <v>24.68</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>23.99</v>
+        <v>24.42</v>
       </c>
       <c r="N64" s="35" t="inlineStr">
         <is>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="O64" s="32" t="n">
+        <v>24.93</v>
+      </c>
+      <c r="P64" s="32" t="n">
         <v>24.92</v>
-      </c>
-      <c r="P64" s="32" t="n">
-        <v>24.89</v>
       </c>
       <c r="Q64" s="33" t="n">
         <v>24.9</v>
@@ -4638,54 +4638,54 @@
         </is>
       </c>
       <c r="C65" s="25" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="D65" s="25" t="n">
         <v>7.56</v>
       </c>
-      <c r="D65" s="25" t="n">
-        <v>7.5</v>
-      </c>
       <c r="E65" s="26" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="G65" s="27" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="H65" s="28" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="I65" s="29" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="J65" s="29" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="K65" s="30" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="L65" s="31" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="M65" s="31" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="N65" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O65" s="32" t="n">
         <v>7.45</v>
       </c>
-      <c r="F65" s="27" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="G65" s="27" t="n">
+      <c r="P65" s="32" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="Q65" s="33" t="n">
         <v>7.49</v>
       </c>
-      <c r="H65" s="28" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="I65" s="29" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="J65" s="29" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="K65" s="30" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="L65" s="31" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="M65" s="31" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N65" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O65" s="32" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="P65" s="32" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="Q65" s="33" t="n">
-        <v>7.44</v>
-      </c>
       <c r="R65" s="34" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4700,37 +4700,37 @@
         </is>
       </c>
       <c r="C66" s="25" t="n">
-        <v>5.19</v>
+        <v>5.06</v>
       </c>
       <c r="D66" s="25" t="n">
-        <v>5.06</v>
+        <v>5.01</v>
       </c>
       <c r="E66" s="26" t="n">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="F66" s="27" t="n">
         <v>5</v>
       </c>
       <c r="G66" s="27" t="n">
-        <v>5.06</v>
+        <v>5.01</v>
       </c>
       <c r="H66" s="28" t="n">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="I66" s="29" t="n">
-        <v>4.87</v>
+        <v>4.95</v>
       </c>
       <c r="J66" s="29" t="n">
-        <v>4.8</v>
+        <v>4.91</v>
       </c>
       <c r="K66" s="30" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="L66" s="31" t="n">
-        <v>4.77</v>
+        <v>4.9</v>
       </c>
       <c r="M66" s="31" t="n">
-        <v>4.64</v>
+        <v>4.85</v>
       </c>
       <c r="N66" s="20" t="inlineStr">
         <is>
@@ -4738,16 +4738,16 @@
         </is>
       </c>
       <c r="O66" s="32" t="n">
-        <v>4.91</v>
+        <v>4.95</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>4.89</v>
+        <v>4.94</v>
       </c>
       <c r="Q66" s="33" t="n">
-        <v>4.95</v>
+        <v>4.98</v>
       </c>
       <c r="R66" s="34" t="n">
-        <v>1.64</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="67">
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="C67" s="25" t="n">
-        <v>5.48</v>
+        <v>5.47</v>
       </c>
       <c r="D67" s="25" t="n">
-        <v>5.35</v>
+        <v>5.37</v>
       </c>
       <c r="E67" s="26" t="n">
-        <v>5.24</v>
+        <v>5.29</v>
       </c>
       <c r="F67" s="27" t="n">
-        <v>5.31</v>
+        <v>5.3</v>
       </c>
       <c r="G67" s="27" t="n">
         <v>5.36</v>
       </c>
       <c r="H67" s="28" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="I67" s="29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J67" s="29" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="K67" s="30" t="n">
         <v>5.23</v>
       </c>
-      <c r="I67" s="29" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="J67" s="29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K67" s="30" t="n">
-        <v>5.17</v>
-      </c>
       <c r="L67" s="31" t="n">
-        <v>5.06</v>
+        <v>5.15</v>
       </c>
       <c r="M67" s="31" t="n">
-        <v>4.93</v>
+        <v>5.05</v>
       </c>
       <c r="N67" s="20" t="inlineStr">
         <is>
@@ -4800,16 +4800,16 @@
         </is>
       </c>
       <c r="O67" s="32" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P67" s="32" t="n">
-        <v>5.18</v>
+        <v>5.24</v>
       </c>
       <c r="Q67" s="33" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="R67" s="34" t="n">
-        <v>2.13</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="68">
@@ -4824,37 +4824,37 @@
         </is>
       </c>
       <c r="C68" s="25" t="n">
-        <v>66.81</v>
+        <v>66.17</v>
       </c>
       <c r="D68" s="25" t="n">
-        <v>65.01000000000001</v>
+        <v>64.92</v>
       </c>
       <c r="E68" s="26" t="n">
-        <v>63.5</v>
+        <v>63.88</v>
       </c>
       <c r="F68" s="27" t="n">
-        <v>64.23</v>
+        <v>64.27</v>
       </c>
       <c r="G68" s="27" t="n">
-        <v>64.97</v>
+        <v>64.83</v>
       </c>
       <c r="H68" s="28" t="n">
-        <v>63.17</v>
+        <v>63.58</v>
       </c>
       <c r="I68" s="29" t="n">
-        <v>62.43</v>
+        <v>63.02</v>
       </c>
       <c r="J68" s="29" t="n">
-        <v>61.37</v>
+        <v>62.33</v>
       </c>
       <c r="K68" s="30" t="n">
-        <v>62.5</v>
+        <v>63.18</v>
       </c>
       <c r="L68" s="31" t="n">
-        <v>60.99</v>
+        <v>62.13</v>
       </c>
       <c r="M68" s="31" t="n">
-        <v>59.19</v>
+        <v>60.88</v>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
@@ -4862,16 +4862,16 @@
         </is>
       </c>
       <c r="O68" s="32" t="n">
-        <v>62.9</v>
+        <v>63.43</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>62.64</v>
+        <v>63.27</v>
       </c>
       <c r="Q68" s="33" t="n">
-        <v>63.5</v>
+        <v>63.7</v>
       </c>
       <c r="R68" s="34" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="69">
@@ -4886,37 +4886,37 @@
         </is>
       </c>
       <c r="C69" s="25" t="n">
-        <v>71.56999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>69.67</v>
+        <v>70.05</v>
       </c>
       <c r="E69" s="26" t="n">
-        <v>68.08</v>
+        <v>68.63</v>
       </c>
       <c r="F69" s="27" t="n">
-        <v>68.8</v>
+        <v>69.03</v>
       </c>
       <c r="G69" s="27" t="n">
-        <v>69.59999999999999</v>
+        <v>69.87</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>67.7</v>
+        <v>68.17</v>
       </c>
       <c r="I69" s="29" t="n">
-        <v>66.90000000000001</v>
+        <v>67.33</v>
       </c>
       <c r="J69" s="29" t="n">
-        <v>65.8</v>
+        <v>66.47</v>
       </c>
       <c r="K69" s="30" t="n">
-        <v>67.02</v>
+        <v>67.67</v>
       </c>
       <c r="L69" s="31" t="n">
-        <v>65.43000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>63.53</v>
+        <v>64.55</v>
       </c>
       <c r="N69" s="20" t="inlineStr">
         <is>
@@ -4924,16 +4924,16 @@
         </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>67.43000000000001</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>67.17</v>
+        <v>67.81</v>
       </c>
       <c r="Q69" s="33" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
       <c r="R69" s="34" t="n">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="70">
@@ -4948,54 +4948,54 @@
         </is>
       </c>
       <c r="C70" s="25" t="n">
-        <v>117.42</v>
+        <v>118.4</v>
       </c>
       <c r="D70" s="25" t="n">
-        <v>113.82</v>
+        <v>111.6</v>
       </c>
       <c r="E70" s="26" t="n">
-        <v>110.81</v>
+        <v>105.9</v>
       </c>
       <c r="F70" s="27" t="n">
-        <v>112.67</v>
+        <v>108</v>
       </c>
       <c r="G70" s="27" t="n">
-        <v>113.93</v>
+        <v>111.1</v>
       </c>
       <c r="H70" s="28" t="n">
-        <v>110.33</v>
+        <v>104.3</v>
       </c>
       <c r="I70" s="29" t="n">
-        <v>109.07</v>
+        <v>101.2</v>
       </c>
       <c r="J70" s="29" t="n">
-        <v>106.73</v>
+        <v>97.5</v>
       </c>
       <c r="K70" s="30" t="n">
-        <v>108.79</v>
+        <v>102.1</v>
       </c>
       <c r="L70" s="31" t="n">
-        <v>105.78</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>102.18</v>
-      </c>
-      <c r="N70" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="N70" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>109.7</v>
+        <v>103.46</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>109.07</v>
+        <v>102.63</v>
       </c>
       <c r="Q70" s="33" t="n">
-        <v>111.4</v>
-      </c>
-      <c r="R70" s="34" t="n">
-        <v>0.27</v>
+        <v>104.9</v>
+      </c>
+      <c r="R70" s="36" t="n">
+        <v>-5.58</v>
       </c>
     </row>
     <row r="71">
@@ -5010,37 +5010,37 @@
         </is>
       </c>
       <c r="C71" s="25" t="n">
-        <v>132.83</v>
+        <v>133.15</v>
       </c>
       <c r="D71" s="25" t="n">
-        <v>128.73</v>
+        <v>129.35</v>
       </c>
       <c r="E71" s="26" t="n">
-        <v>125.3</v>
+        <v>126.16</v>
       </c>
       <c r="F71" s="27" t="n">
-        <v>127.23</v>
+        <v>127</v>
       </c>
       <c r="G71" s="27" t="n">
-        <v>128.77</v>
+        <v>128.9</v>
       </c>
       <c r="H71" s="28" t="n">
-        <v>124.67</v>
+        <v>125.1</v>
       </c>
       <c r="I71" s="29" t="n">
-        <v>123.13</v>
+        <v>123.2</v>
       </c>
       <c r="J71" s="29" t="n">
-        <v>120.57</v>
+        <v>121.3</v>
       </c>
       <c r="K71" s="30" t="n">
-        <v>123</v>
+        <v>124.04</v>
       </c>
       <c r="L71" s="31" t="n">
-        <v>119.57</v>
+        <v>120.85</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>115.47</v>
+        <v>117.05</v>
       </c>
       <c r="N71" s="20" t="inlineStr">
         <is>
@@ -5048,16 +5048,16 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>123.99</v>
+        <v>124.72</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>123.32</v>
+        <v>124.33</v>
       </c>
       <c r="Q71" s="33" t="n">
-        <v>125.7</v>
+        <v>125.1</v>
       </c>
       <c r="R71" s="34" t="n">
-        <v>2.95</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="72">
@@ -5072,37 +5072,37 @@
         </is>
       </c>
       <c r="C72" s="25" t="n">
-        <v>29.83</v>
+        <v>29.36</v>
       </c>
       <c r="D72" s="25" t="n">
-        <v>28.55</v>
+        <v>28.42</v>
       </c>
       <c r="E72" s="26" t="n">
-        <v>27.48</v>
+        <v>27.63</v>
       </c>
       <c r="F72" s="27" t="n">
-        <v>28.19</v>
+        <v>27.57</v>
       </c>
       <c r="G72" s="27" t="n">
-        <v>28.61</v>
+        <v>28.17</v>
       </c>
       <c r="H72" s="28" t="n">
-        <v>27.33</v>
+        <v>27.23</v>
       </c>
       <c r="I72" s="29" t="n">
-        <v>26.91</v>
+        <v>26.63</v>
       </c>
       <c r="J72" s="29" t="n">
-        <v>26.05</v>
+        <v>26.29</v>
       </c>
       <c r="K72" s="30" t="n">
-        <v>26.76</v>
+        <v>27.11</v>
       </c>
       <c r="L72" s="31" t="n">
-        <v>25.69</v>
+        <v>26.32</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>24.41</v>
+        <v>25.38</v>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>27.1</v>
+        <v>27.21</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>26.86</v>
+        <v>27.18</v>
       </c>
       <c r="Q72" s="33" t="n">
-        <v>27.76</v>
+        <v>26.96</v>
       </c>
       <c r="R72" s="34" t="n">
-        <v>4.75</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="73">
@@ -5134,37 +5134,37 @@
         </is>
       </c>
       <c r="C73" s="25" t="n">
-        <v>23.28</v>
+        <v>22.89</v>
       </c>
       <c r="D73" s="25" t="n">
-        <v>22.6</v>
+        <v>22.46</v>
       </c>
       <c r="E73" s="26" t="n">
-        <v>22.03</v>
+        <v>22.1</v>
       </c>
       <c r="F73" s="27" t="n">
-        <v>22.25</v>
+        <v>22.05</v>
       </c>
       <c r="G73" s="27" t="n">
-        <v>22.55</v>
+        <v>22.33</v>
       </c>
       <c r="H73" s="28" t="n">
-        <v>21.87</v>
+        <v>21.9</v>
       </c>
       <c r="I73" s="29" t="n">
-        <v>21.57</v>
+        <v>21.62</v>
       </c>
       <c r="J73" s="29" t="n">
-        <v>21.19</v>
+        <v>21.47</v>
       </c>
       <c r="K73" s="30" t="n">
-        <v>21.65</v>
+        <v>21.85</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>21.08</v>
+        <v>21.49</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>20.4</v>
+        <v>21.06</v>
       </c>
       <c r="N73" s="35" t="inlineStr">
         <is>
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="O73" s="32" t="n">
-        <v>21.79</v>
+        <v>21.9</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>21.7</v>
+        <v>21.89</v>
       </c>
       <c r="Q73" s="33" t="n">
-        <v>21.94</v>
+        <v>21.76</v>
       </c>
       <c r="R73" s="36" t="n">
-        <v>-0.41</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="74">
@@ -5196,37 +5196,37 @@
         </is>
       </c>
       <c r="C74" s="25" t="n">
-        <v>250.46</v>
+        <v>250.48</v>
       </c>
       <c r="D74" s="25" t="n">
-        <v>242.76</v>
+        <v>245.18</v>
       </c>
       <c r="E74" s="26" t="n">
-        <v>236.31</v>
+        <v>240.73</v>
       </c>
       <c r="F74" s="27" t="n">
-        <v>240.57</v>
+        <v>241.67</v>
       </c>
       <c r="G74" s="27" t="n">
-        <v>243.13</v>
+        <v>244.43</v>
       </c>
       <c r="H74" s="28" t="n">
-        <v>235.43</v>
+        <v>239.13</v>
       </c>
       <c r="I74" s="29" t="n">
-        <v>232.87</v>
+        <v>236.37</v>
       </c>
       <c r="J74" s="29" t="n">
-        <v>227.73</v>
+        <v>233.83</v>
       </c>
       <c r="K74" s="30" t="n">
-        <v>231.99</v>
+        <v>237.77</v>
       </c>
       <c r="L74" s="31" t="n">
-        <v>225.54</v>
+        <v>233.32</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>217.84</v>
+        <v>228.02</v>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
@@ -5234,16 +5234,16 @@
         </is>
       </c>
       <c r="O74" s="32" t="n">
-        <v>234.01</v>
+        <v>238.66</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>232.59</v>
+        <v>238.18</v>
       </c>
       <c r="Q74" s="33" t="n">
-        <v>238</v>
+        <v>238.9</v>
       </c>
       <c r="R74" s="34" t="n">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="75">
@@ -5258,37 +5258,37 @@
         </is>
       </c>
       <c r="C75" s="25" t="n">
-        <v>17.08</v>
+        <v>17.06</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>16.53</v>
+        <v>16.71</v>
       </c>
       <c r="E75" s="26" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="F75" s="27" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="G75" s="27" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="H75" s="28" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="I75" s="29" t="n">
         <v>16.07</v>
       </c>
-      <c r="F75" s="27" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="G75" s="27" t="n">
-        <v>16.56</v>
-      </c>
-      <c r="H75" s="28" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="I75" s="29" t="n">
-        <v>15.82</v>
-      </c>
       <c r="J75" s="29" t="n">
-        <v>15.46</v>
+        <v>15.93</v>
       </c>
       <c r="K75" s="30" t="n">
-        <v>15.76</v>
+        <v>16.22</v>
       </c>
       <c r="L75" s="31" t="n">
-        <v>15.3</v>
+        <v>15.92</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>14.75</v>
+        <v>15.57</v>
       </c>
       <c r="N75" s="20" t="inlineStr">
         <is>
@@ -5296,16 +5296,16 @@
         </is>
       </c>
       <c r="O75" s="32" t="n">
-        <v>15.91</v>
+        <v>16.26</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>15.8</v>
+        <v>16.24</v>
       </c>
       <c r="Q75" s="33" t="n">
-        <v>16.19</v>
+        <v>16.21</v>
       </c>
       <c r="R75" s="34" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="76">
@@ -5320,37 +5320,37 @@
         </is>
       </c>
       <c r="C76" s="25" t="n">
-        <v>32.68</v>
+        <v>33.1</v>
       </c>
       <c r="D76" s="25" t="n">
-        <v>31.74</v>
+        <v>32.2</v>
       </c>
       <c r="E76" s="26" t="n">
-        <v>30.95</v>
+        <v>31.44</v>
       </c>
       <c r="F76" s="27" t="n">
-        <v>31.26</v>
+        <v>31.65</v>
       </c>
       <c r="G76" s="27" t="n">
-        <v>31.68</v>
+        <v>32.09</v>
       </c>
       <c r="H76" s="28" t="n">
-        <v>30.74</v>
+        <v>31.19</v>
       </c>
       <c r="I76" s="29" t="n">
-        <v>30.32</v>
+        <v>30.75</v>
       </c>
       <c r="J76" s="29" t="n">
-        <v>29.8</v>
+        <v>30.29</v>
       </c>
       <c r="K76" s="30" t="n">
-        <v>30.43</v>
+        <v>30.94</v>
       </c>
       <c r="L76" s="31" t="n">
-        <v>29.64</v>
+        <v>30.18</v>
       </c>
       <c r="M76" s="31" t="n">
-        <v>28.7</v>
+        <v>29.28</v>
       </c>
       <c r="N76" s="20" t="inlineStr">
         <is>
@@ -5358,16 +5358,16 @@
         </is>
       </c>
       <c r="O76" s="32" t="n">
-        <v>30.62</v>
+        <v>31.1</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>30.5</v>
+        <v>31.01</v>
       </c>
       <c r="Q76" s="33" t="n">
-        <v>30.84</v>
+        <v>31.2</v>
       </c>
       <c r="R76" s="34" t="n">
-        <v>1.92</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="77">
@@ -5382,37 +5382,37 @@
         </is>
       </c>
       <c r="C77" s="25" t="n">
-        <v>28.72</v>
+        <v>28.58</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>28.14</v>
+        <v>28.1</v>
       </c>
       <c r="E77" s="26" t="n">
-        <v>27.65</v>
+        <v>27.69</v>
       </c>
       <c r="F77" s="27" t="n">
-        <v>27.85</v>
+        <v>27.8</v>
       </c>
       <c r="G77" s="27" t="n">
-        <v>28.11</v>
+        <v>28.04</v>
       </c>
       <c r="H77" s="28" t="n">
-        <v>27.53</v>
+        <v>27.56</v>
       </c>
       <c r="I77" s="29" t="n">
-        <v>27.27</v>
+        <v>27.32</v>
       </c>
       <c r="J77" s="29" t="n">
-        <v>26.95</v>
+        <v>27.08</v>
       </c>
       <c r="K77" s="30" t="n">
-        <v>27.33</v>
+        <v>27.43</v>
       </c>
       <c r="L77" s="31" t="n">
-        <v>26.84</v>
+        <v>27.02</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>26.26</v>
+        <v>26.54</v>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
@@ -5420,16 +5420,16 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>27.45</v>
+        <v>27.51</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>27.37</v>
+        <v>27.46</v>
       </c>
       <c r="Q77" s="33" t="n">
-        <v>27.6</v>
+        <v>27.56</v>
       </c>
       <c r="R77" s="34" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="78">
@@ -5444,37 +5444,37 @@
         </is>
       </c>
       <c r="C78" s="25" t="n">
-        <v>40.99</v>
+        <v>41.46</v>
       </c>
       <c r="D78" s="25" t="n">
-        <v>40.01</v>
+        <v>40.56</v>
       </c>
       <c r="E78" s="26" t="n">
-        <v>39.18</v>
+        <v>39.8</v>
       </c>
       <c r="F78" s="27" t="n">
-        <v>39.67</v>
+        <v>40.22</v>
       </c>
       <c r="G78" s="27" t="n">
-        <v>40.03</v>
+        <v>40.56</v>
       </c>
       <c r="H78" s="28" t="n">
-        <v>39.05</v>
+        <v>39.66</v>
       </c>
       <c r="I78" s="29" t="n">
-        <v>38.69</v>
+        <v>39.32</v>
       </c>
       <c r="J78" s="29" t="n">
-        <v>38.07</v>
+        <v>38.76</v>
       </c>
       <c r="K78" s="30" t="n">
-        <v>38.64</v>
+        <v>39.3</v>
       </c>
       <c r="L78" s="31" t="n">
-        <v>37.81</v>
+        <v>38.54</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>36.83</v>
+        <v>37.64</v>
       </c>
       <c r="N78" s="20" t="inlineStr">
         <is>
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>38.88</v>
+        <v>39.51</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>38.71</v>
+        <v>39.37</v>
       </c>
       <c r="Q78" s="33" t="n">
-        <v>39.32</v>
+        <v>39.88</v>
       </c>
       <c r="R78" s="34" t="n">
-        <v>2.29</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="79">
@@ -5506,37 +5506,37 @@
         </is>
       </c>
       <c r="C79" s="25" t="n">
-        <v>5.78</v>
+        <v>5.72</v>
       </c>
       <c r="D79" s="25" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="E79" s="26" t="n">
-        <v>5.63</v>
+        <v>5.59</v>
       </c>
       <c r="F79" s="27" t="n">
-        <v>5.63</v>
+        <v>5.61</v>
       </c>
       <c r="G79" s="27" t="n">
-        <v>5.68</v>
+        <v>5.65</v>
       </c>
       <c r="H79" s="28" t="n">
-        <v>5.6</v>
+        <v>5.58</v>
       </c>
       <c r="I79" s="29" t="n">
-        <v>5.55</v>
+        <v>5.54</v>
       </c>
       <c r="J79" s="29" t="n">
-        <v>5.52</v>
+        <v>5.51</v>
       </c>
       <c r="K79" s="30" t="n">
-        <v>5.59</v>
+        <v>5.56</v>
       </c>
       <c r="L79" s="31" t="n">
-        <v>5.52</v>
+        <v>5.5</v>
       </c>
       <c r="M79" s="31" t="n">
-        <v>5.44</v>
+        <v>5.43</v>
       </c>
       <c r="N79" s="20" t="inlineStr">
         <is>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>5.59</v>
+        <v>5.56</v>
       </c>
       <c r="Q79" s="33" t="n">
         <v>5.58</v>
@@ -5568,37 +5568,37 @@
         </is>
       </c>
       <c r="C80" s="25" t="n">
-        <v>19.89</v>
+        <v>19.43</v>
       </c>
       <c r="D80" s="25" t="n">
-        <v>19.13</v>
+        <v>19.03</v>
       </c>
       <c r="E80" s="26" t="n">
-        <v>18.49</v>
+        <v>18.69</v>
       </c>
       <c r="F80" s="27" t="n">
-        <v>18.84</v>
+        <v>18.83</v>
       </c>
       <c r="G80" s="27" t="n">
-        <v>19.13</v>
+        <v>19</v>
       </c>
       <c r="H80" s="28" t="n">
-        <v>18.37</v>
+        <v>18.6</v>
       </c>
       <c r="I80" s="29" t="n">
-        <v>18.08</v>
+        <v>18.43</v>
       </c>
       <c r="J80" s="29" t="n">
-        <v>17.61</v>
+        <v>18.2</v>
       </c>
       <c r="K80" s="30" t="n">
-        <v>18.07</v>
+        <v>18.47</v>
       </c>
       <c r="L80" s="31" t="n">
-        <v>17.43</v>
+        <v>18.13</v>
       </c>
       <c r="M80" s="31" t="n">
-        <v>16.67</v>
+        <v>17.73</v>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
@@ -5606,16 +5606,16 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>18.25</v>
+        <v>18.55</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>18.13</v>
+        <v>18.5</v>
       </c>
       <c r="Q80" s="33" t="n">
-        <v>18.55</v>
+        <v>18.65</v>
       </c>
       <c r="R80" s="34" t="n">
-        <v>3.06</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="81">
@@ -5630,37 +5630,37 @@
         </is>
       </c>
       <c r="C81" s="25" t="n">
-        <v>87.73</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="D81" s="25" t="n">
-        <v>84.28</v>
+        <v>82.91</v>
       </c>
       <c r="E81" s="26" t="n">
-        <v>81.39</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F81" s="27" t="n">
-        <v>82.53</v>
+        <v>81.87</v>
       </c>
       <c r="G81" s="27" t="n">
-        <v>84.06999999999999</v>
+        <v>82.73</v>
       </c>
       <c r="H81" s="28" t="n">
-        <v>80.62</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="I81" s="29" t="n">
-        <v>79.08</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="J81" s="29" t="n">
-        <v>77.17</v>
+        <v>79.13</v>
       </c>
       <c r="K81" s="30" t="n">
-        <v>79.45999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L81" s="31" t="n">
-        <v>76.56999999999999</v>
+        <v>78.89</v>
       </c>
       <c r="M81" s="31" t="n">
-        <v>73.12</v>
+        <v>77.09</v>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>80.17</v>
+        <v>80.73</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>79.73</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="Q81" s="33" t="n">
         <v>81</v>
@@ -5692,54 +5692,54 @@
         </is>
       </c>
       <c r="C82" s="25" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="D82" s="25" t="n">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="E82" s="26" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="F82" s="27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G82" s="27" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H82" s="28" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="I82" s="29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J82" s="29" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="K82" s="30" t="n">
         <v>4.69</v>
       </c>
-      <c r="F82" s="27" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="G82" s="27" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="H82" s="28" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="I82" s="29" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="J82" s="29" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="K82" s="30" t="n">
+      <c r="L82" s="31" t="n">
         <v>4.65</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="M82" s="31" t="n">
         <v>4.6</v>
       </c>
-      <c r="M82" s="31" t="n">
-        <v>4.54</v>
-      </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>4.66</v>
+        <v>4.69</v>
       </c>
       <c r="Q82" s="33" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="R82" s="34" t="n">
-        <v>0.86</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="83">
@@ -5757,34 +5757,34 @@
         <v>63.43</v>
       </c>
       <c r="D83" s="25" t="n">
-        <v>61.93</v>
+        <v>62.33</v>
       </c>
       <c r="E83" s="26" t="n">
-        <v>60.67</v>
+        <v>61.41</v>
       </c>
       <c r="F83" s="27" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="G83" s="27" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="H83" s="28" t="n">
         <v>61.23</v>
       </c>
-      <c r="G83" s="27" t="n">
-        <v>61.87</v>
-      </c>
-      <c r="H83" s="28" t="n">
-        <v>60.37</v>
-      </c>
       <c r="I83" s="29" t="n">
-        <v>59.73</v>
+        <v>60.82</v>
       </c>
       <c r="J83" s="29" t="n">
-        <v>58.87</v>
+        <v>60.13</v>
       </c>
       <c r="K83" s="30" t="n">
-        <v>59.83</v>
+        <v>60.79</v>
       </c>
       <c r="L83" s="31" t="n">
-        <v>58.57</v>
+        <v>59.87</v>
       </c>
       <c r="M83" s="31" t="n">
-        <v>57.07</v>
+        <v>58.77</v>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
@@ -5792,16 +5792,16 @@
         </is>
       </c>
       <c r="O83" s="32" t="n">
-        <v>60.16</v>
+        <v>61.06</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>59.95</v>
+        <v>60.88</v>
       </c>
       <c r="Q83" s="33" t="n">
-        <v>60.6</v>
+        <v>61.5</v>
       </c>
       <c r="R83" s="34" t="n">
-        <v>0.33</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="84">
@@ -5816,37 +5816,37 @@
         </is>
       </c>
       <c r="C84" s="25" t="n">
-        <v>41.82</v>
+        <v>42.12</v>
       </c>
       <c r="D84" s="25" t="n">
-        <v>41.24</v>
+        <v>41.6</v>
       </c>
       <c r="E84" s="26" t="n">
-        <v>40.75</v>
+        <v>41.17</v>
       </c>
       <c r="F84" s="27" t="n">
-        <v>41.05</v>
+        <v>41.37</v>
       </c>
       <c r="G84" s="27" t="n">
-        <v>41.25</v>
+        <v>41.59</v>
       </c>
       <c r="H84" s="28" t="n">
-        <v>40.67</v>
+        <v>41.07</v>
       </c>
       <c r="I84" s="29" t="n">
-        <v>40.47</v>
+        <v>40.85</v>
       </c>
       <c r="J84" s="29" t="n">
-        <v>40.09</v>
+        <v>40.55</v>
       </c>
       <c r="K84" s="30" t="n">
-        <v>40.43</v>
+        <v>40.87</v>
       </c>
       <c r="L84" s="31" t="n">
-        <v>39.94</v>
+        <v>40.44</v>
       </c>
       <c r="M84" s="31" t="n">
-        <v>39.36</v>
+        <v>39.92</v>
       </c>
       <c r="N84" s="20" t="inlineStr">
         <is>
@@ -5854,16 +5854,16 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>40.57</v>
+        <v>40.99</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>40.47</v>
+        <v>40.91</v>
       </c>
       <c r="Q84" s="33" t="n">
-        <v>40.84</v>
+        <v>41.16</v>
       </c>
       <c r="R84" s="34" t="n">
-        <v>0.84</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="85">
@@ -5878,54 +5878,54 @@
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>99.08</v>
+        <v>97.56</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>97.73</v>
+        <v>96.66</v>
       </c>
       <c r="E85" s="26" t="n">
-        <v>96.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F85" s="27" t="n">
-        <v>96.75</v>
+        <v>96.03</v>
       </c>
       <c r="G85" s="27" t="n">
-        <v>97.5</v>
+        <v>96.52</v>
       </c>
       <c r="H85" s="28" t="n">
-        <v>96.15000000000001</v>
+        <v>95.62</v>
       </c>
       <c r="I85" s="29" t="n">
+        <v>95.13</v>
+      </c>
+      <c r="J85" s="29" t="n">
+        <v>94.72</v>
+      </c>
+      <c r="K85" s="30" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="J85" s="29" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="K85" s="30" t="n">
-        <v>95.84999999999999</v>
-      </c>
       <c r="L85" s="31" t="n">
-        <v>94.72</v>
+        <v>94.64</v>
       </c>
       <c r="M85" s="31" t="n">
-        <v>93.37</v>
-      </c>
-      <c r="N85" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>93.73999999999999</v>
+      </c>
+      <c r="N85" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>96.05</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>95.95</v>
+        <v>95.47</v>
       </c>
       <c r="Q85" s="33" t="n">
-        <v>96</v>
-      </c>
-      <c r="R85" s="34" t="n">
-        <v>0</v>
+        <v>95.55</v>
+      </c>
+      <c r="R85" s="36" t="n">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="86">
@@ -5940,37 +5940,37 @@
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>18.21</v>
+        <v>17.65</v>
       </c>
       <c r="D86" s="25" t="n">
-        <v>17.46</v>
+        <v>17.36</v>
       </c>
       <c r="E86" s="26" t="n">
-        <v>16.84</v>
+        <v>17.12</v>
       </c>
       <c r="F86" s="27" t="n">
-        <v>17.25</v>
+        <v>17.24</v>
       </c>
       <c r="G86" s="27" t="n">
-        <v>17.5</v>
+        <v>17.35</v>
       </c>
       <c r="H86" s="28" t="n">
-        <v>16.75</v>
+        <v>17.06</v>
       </c>
       <c r="I86" s="29" t="n">
-        <v>16.5</v>
+        <v>16.95</v>
       </c>
       <c r="J86" s="29" t="n">
-        <v>16</v>
+        <v>16.77</v>
       </c>
       <c r="K86" s="30" t="n">
-        <v>16.41</v>
+        <v>16.95</v>
       </c>
       <c r="L86" s="31" t="n">
-        <v>15.79</v>
+        <v>16.71</v>
       </c>
       <c r="M86" s="31" t="n">
-        <v>15.04</v>
+        <v>16.42</v>
       </c>
       <c r="N86" s="20" t="inlineStr">
         <is>
@@ -5978,16 +5978,16 @@
         </is>
       </c>
       <c r="O86" s="32" t="n">
-        <v>16.61</v>
+        <v>17.02</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>16.47</v>
+        <v>16.98</v>
       </c>
       <c r="Q86" s="33" t="n">
-        <v>17</v>
+        <v>17.12</v>
       </c>
       <c r="R86" s="34" t="n">
-        <v>3.03</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="87">
@@ -6002,37 +6002,37 @@
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>126.4</v>
+        <v>129.27</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>122.2</v>
+        <v>125.27</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>118.68</v>
+        <v>121.92</v>
       </c>
       <c r="F87" s="27" t="n">
-        <v>120.53</v>
+        <v>122.93</v>
       </c>
       <c r="G87" s="27" t="n">
-        <v>122.17</v>
+        <v>124.87</v>
       </c>
       <c r="H87" s="28" t="n">
-        <v>117.97</v>
+        <v>120.87</v>
       </c>
       <c r="I87" s="29" t="n">
+        <v>118.93</v>
+      </c>
+      <c r="J87" s="29" t="n">
+        <v>116.87</v>
+      </c>
+      <c r="K87" s="30" t="n">
+        <v>119.68</v>
+      </c>
+      <c r="L87" s="31" t="n">
         <v>116.33</v>
       </c>
-      <c r="J87" s="29" t="n">
-        <v>113.77</v>
-      </c>
-      <c r="K87" s="30" t="n">
-        <v>116.32</v>
-      </c>
-      <c r="L87" s="31" t="n">
-        <v>112.8</v>
-      </c>
       <c r="M87" s="31" t="n">
-        <v>108.6</v>
+        <v>112.33</v>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>117.31</v>
+        <v>120.43</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>116.65</v>
+        <v>119.99</v>
       </c>
       <c r="Q87" s="33" t="n">
-        <v>118.9</v>
+        <v>121</v>
       </c>
       <c r="R87" s="34" t="n">
-        <v>2.06</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="88">
@@ -6067,34 +6067,34 @@
         <v>67.3</v>
       </c>
       <c r="D88" s="25" t="n">
-        <v>64.95</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E88" s="26" t="n">
-        <v>62.98</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="F88" s="27" t="n">
-        <v>64.12</v>
+        <v>64.72</v>
       </c>
       <c r="G88" s="27" t="n">
-        <v>64.98</v>
+        <v>65.48</v>
       </c>
       <c r="H88" s="28" t="n">
-        <v>62.63</v>
+        <v>63.78</v>
       </c>
       <c r="I88" s="29" t="n">
-        <v>61.77</v>
+        <v>63.02</v>
       </c>
       <c r="J88" s="29" t="n">
-        <v>60.28</v>
+        <v>62.08</v>
       </c>
       <c r="K88" s="30" t="n">
-        <v>61.67</v>
+        <v>63.22</v>
       </c>
       <c r="L88" s="31" t="n">
-        <v>59.7</v>
+        <v>61.8</v>
       </c>
       <c r="M88" s="31" t="n">
-        <v>57.35</v>
+        <v>60.1</v>
       </c>
       <c r="N88" s="20" t="inlineStr">
         <is>
@@ -6102,16 +6102,16 @@
         </is>
       </c>
       <c r="O88" s="32" t="n">
-        <v>62.24</v>
+        <v>63.57</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>61.85</v>
+        <v>63.36</v>
       </c>
       <c r="Q88" s="33" t="n">
-        <v>63.25</v>
+        <v>63.95</v>
       </c>
       <c r="R88" s="34" t="n">
-        <v>2.02</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="89">
@@ -6126,37 +6126,37 @@
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>10.2</v>
+        <v>10.41</v>
       </c>
       <c r="D89" s="25" t="n">
-        <v>9.9</v>
+        <v>10.12</v>
       </c>
       <c r="E89" s="26" t="n">
-        <v>9.640000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F89" s="27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G89" s="27" t="n">
-        <v>9.9</v>
+        <v>10.12</v>
       </c>
       <c r="H89" s="28" t="n">
-        <v>9.6</v>
+        <v>9.83</v>
       </c>
       <c r="I89" s="29" t="n">
-        <v>9.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J89" s="29" t="n">
-        <v>9.300000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="K89" s="30" t="n">
-        <v>9.48</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L89" s="31" t="n">
-        <v>9.220000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M89" s="31" t="n">
-        <v>8.92</v>
+        <v>9.18</v>
       </c>
       <c r="N89" s="20" t="inlineStr">
         <is>
@@ -6164,16 +6164,16 @@
         </is>
       </c>
       <c r="O89" s="32" t="n">
-        <v>9.550000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="P89" s="32" t="n">
-        <v>9.5</v>
+        <v>9.74</v>
       </c>
       <c r="Q89" s="33" t="n">
-        <v>9.69</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="R89" s="34" t="n">
-        <v>2.76</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="90">
@@ -6188,54 +6188,54 @@
         </is>
       </c>
       <c r="C90" s="25" t="n">
-        <v>13.26</v>
+        <v>13.15</v>
       </c>
       <c r="D90" s="25" t="n">
-        <v>12.86</v>
+        <v>12.89</v>
       </c>
       <c r="E90" s="26" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="F90" s="27" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="G90" s="27" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="H90" s="28" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="I90" s="29" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="J90" s="29" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="K90" s="30" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="L90" s="31" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="M90" s="31" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="N90" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O90" s="32" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="P90" s="32" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="Q90" s="33" t="n">
         <v>12.52</v>
       </c>
-      <c r="F90" s="27" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="G90" s="27" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="H90" s="28" t="n">
-        <v>12.46</v>
-      </c>
-      <c r="I90" s="29" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="J90" s="29" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="K90" s="30" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="L90" s="31" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="M90" s="31" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="N90" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O90" s="32" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="P90" s="32" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="Q90" s="33" t="n">
-        <v>12.55</v>
-      </c>
       <c r="R90" s="34" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="91">
@@ -6250,37 +6250,37 @@
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>20.22</v>
+        <v>18.8</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>18.73</v>
+        <v>18.22</v>
       </c>
       <c r="E91" s="26" t="n">
-        <v>17.48</v>
+        <v>17.73</v>
       </c>
       <c r="F91" s="27" t="n">
-        <v>18.3</v>
+        <v>17.95</v>
       </c>
       <c r="G91" s="27" t="n">
-        <v>18.8</v>
+        <v>18.19</v>
       </c>
       <c r="H91" s="28" t="n">
-        <v>17.31</v>
+        <v>17.61</v>
       </c>
       <c r="I91" s="29" t="n">
-        <v>16.81</v>
+        <v>17.37</v>
       </c>
       <c r="J91" s="29" t="n">
-        <v>15.82</v>
+        <v>17.03</v>
       </c>
       <c r="K91" s="30" t="n">
-        <v>16.65</v>
+        <v>17.41</v>
       </c>
       <c r="L91" s="31" t="n">
-        <v>15.4</v>
+        <v>16.92</v>
       </c>
       <c r="M91" s="31" t="n">
-        <v>13.91</v>
+        <v>16.34</v>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
@@ -6288,16 +6288,16 @@
         </is>
       </c>
       <c r="O91" s="32" t="n">
-        <v>17.04</v>
+        <v>17.53</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>16.76</v>
+        <v>17.45</v>
       </c>
       <c r="Q91" s="33" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="R91" s="34" t="n">
-        <v>8.539999999999999</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="92">
@@ -6312,37 +6312,37 @@
         </is>
       </c>
       <c r="C92" s="25" t="n">
-        <v>29.62</v>
+        <v>30.32</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>28.72</v>
+        <v>29.02</v>
       </c>
       <c r="E92" s="26" t="n">
-        <v>27.96</v>
+        <v>27.93</v>
       </c>
       <c r="F92" s="27" t="n">
-        <v>28.15</v>
+        <v>28.4</v>
       </c>
       <c r="G92" s="27" t="n">
-        <v>28.61</v>
+        <v>28.96</v>
       </c>
       <c r="H92" s="28" t="n">
-        <v>27.71</v>
+        <v>27.66</v>
       </c>
       <c r="I92" s="29" t="n">
-        <v>27.25</v>
+        <v>27.1</v>
       </c>
       <c r="J92" s="29" t="n">
-        <v>26.81</v>
+        <v>26.36</v>
       </c>
       <c r="K92" s="30" t="n">
-        <v>27.46</v>
+        <v>27.21</v>
       </c>
       <c r="L92" s="31" t="n">
-        <v>26.7</v>
+        <v>26.12</v>
       </c>
       <c r="M92" s="31" t="n">
-        <v>25.8</v>
+        <v>24.82</v>
       </c>
       <c r="N92" s="20" t="inlineStr">
         <is>
@@ -6350,16 +6350,16 @@
         </is>
       </c>
       <c r="O92" s="32" t="n">
-        <v>27.62</v>
+        <v>27.48</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>27.53</v>
+        <v>27.31</v>
       </c>
       <c r="Q92" s="33" t="n">
-        <v>27.7</v>
+        <v>27.84</v>
       </c>
       <c r="R92" s="34" t="n">
-        <v>0.58</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="93">
@@ -6374,37 +6374,37 @@
         </is>
       </c>
       <c r="C93" s="25" t="n">
-        <v>23.43</v>
+        <v>23.35</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>23</v>
+        <v>22.95</v>
       </c>
       <c r="E93" s="26" t="n">
-        <v>22.64</v>
+        <v>22.61</v>
       </c>
       <c r="F93" s="27" t="n">
-        <v>22.7</v>
+        <v>22.79</v>
       </c>
       <c r="G93" s="27" t="n">
-        <v>22.93</v>
+        <v>22.95</v>
       </c>
       <c r="H93" s="28" t="n">
-        <v>22.5</v>
+        <v>22.55</v>
       </c>
       <c r="I93" s="29" t="n">
-        <v>22.27</v>
+        <v>22.39</v>
       </c>
       <c r="J93" s="29" t="n">
-        <v>22.07</v>
+        <v>22.15</v>
       </c>
       <c r="K93" s="30" t="n">
         <v>22.39</v>
       </c>
       <c r="L93" s="31" t="n">
-        <v>22.03</v>
+        <v>22.05</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>21.6</v>
+        <v>21.65</v>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
@@ -6412,16 +6412,16 @@
         </is>
       </c>
       <c r="O93" s="32" t="n">
-        <v>22.46</v>
+        <v>22.48</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>22.43</v>
+        <v>22.42</v>
       </c>
       <c r="Q93" s="33" t="n">
-        <v>22.47</v>
+        <v>22.64</v>
       </c>
       <c r="R93" s="34" t="n">
-        <v>0.76</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="94">
@@ -6436,37 +6436,37 @@
         </is>
       </c>
       <c r="C94" s="25" t="n">
-        <v>29.49</v>
+        <v>29.78</v>
       </c>
       <c r="D94" s="25" t="n">
-        <v>28.99</v>
+        <v>29.2</v>
       </c>
       <c r="E94" s="26" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="F94" s="27" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="G94" s="27" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="H94" s="28" t="n">
         <v>28.57</v>
       </c>
-      <c r="F94" s="27" t="n">
-        <v>28.73</v>
-      </c>
-      <c r="G94" s="27" t="n">
-        <v>28.95</v>
-      </c>
-      <c r="H94" s="28" t="n">
-        <v>28.45</v>
-      </c>
       <c r="I94" s="29" t="n">
-        <v>28.23</v>
+        <v>28.31</v>
       </c>
       <c r="J94" s="29" t="n">
-        <v>27.95</v>
+        <v>27.99</v>
       </c>
       <c r="K94" s="30" t="n">
-        <v>28.29</v>
+        <v>28.39</v>
       </c>
       <c r="L94" s="31" t="n">
-        <v>27.87</v>
+        <v>27.9</v>
       </c>
       <c r="M94" s="31" t="n">
-        <v>27.37</v>
+        <v>27.32</v>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>28.39</v>
+        <v>28.5</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>28.33</v>
+        <v>28.43</v>
       </c>
       <c r="Q94" s="33" t="n">
-        <v>28.5</v>
+        <v>28.62</v>
       </c>
       <c r="R94" s="34" t="n">
-        <v>0.99</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="95">
@@ -6498,54 +6498,54 @@
         </is>
       </c>
       <c r="C95" s="25" t="n">
-        <v>189.83</v>
+        <v>181.49</v>
       </c>
       <c r="D95" s="25" t="n">
-        <v>181.53</v>
+        <v>177.79</v>
       </c>
       <c r="E95" s="26" t="n">
-        <v>174.57</v>
+        <v>174.69</v>
       </c>
       <c r="F95" s="27" t="n">
-        <v>177.77</v>
+        <v>175.13</v>
       </c>
       <c r="G95" s="27" t="n">
-        <v>181.23</v>
+        <v>177.17</v>
       </c>
       <c r="H95" s="28" t="n">
-        <v>172.93</v>
+        <v>173.47</v>
       </c>
       <c r="I95" s="29" t="n">
-        <v>169.47</v>
+        <v>171.43</v>
       </c>
       <c r="J95" s="29" t="n">
-        <v>164.63</v>
+        <v>169.77</v>
       </c>
       <c r="K95" s="30" t="n">
-        <v>169.93</v>
+        <v>172.61</v>
       </c>
       <c r="L95" s="31" t="n">
-        <v>162.97</v>
+        <v>169.51</v>
       </c>
       <c r="M95" s="31" t="n">
-        <v>154.67</v>
-      </c>
-      <c r="N95" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>165.81</v>
+      </c>
+      <c r="N95" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O95" s="32" t="n">
-        <v>171.75</v>
+        <v>173.18</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>170.57</v>
+        <v>172.9</v>
       </c>
       <c r="Q95" s="33" t="n">
-        <v>174.3</v>
+        <v>173.1</v>
       </c>
       <c r="R95" s="34" t="n">
-        <v>0.75</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="96">
@@ -6560,37 +6560,37 @@
         </is>
       </c>
       <c r="C96" s="25" t="n">
-        <v>12.44</v>
+        <v>12.5</v>
       </c>
       <c r="D96" s="25" t="n">
-        <v>12.18</v>
+        <v>12.22</v>
       </c>
       <c r="E96" s="26" t="n">
-        <v>11.96</v>
+        <v>11.99</v>
       </c>
       <c r="F96" s="27" t="n">
-        <v>11.99</v>
+        <v>12.11</v>
       </c>
       <c r="G96" s="27" t="n">
-        <v>12.13</v>
+        <v>12.22</v>
       </c>
       <c r="H96" s="28" t="n">
-        <v>11.87</v>
+        <v>11.94</v>
       </c>
       <c r="I96" s="29" t="n">
-        <v>11.73</v>
+        <v>11.83</v>
       </c>
       <c r="J96" s="29" t="n">
-        <v>11.61</v>
+        <v>11.66</v>
       </c>
       <c r="K96" s="30" t="n">
-        <v>11.82</v>
+        <v>11.83</v>
       </c>
       <c r="L96" s="31" t="n">
         <v>11.6</v>
       </c>
       <c r="M96" s="31" t="n">
-        <v>11.34</v>
+        <v>11.32</v>
       </c>
       <c r="N96" s="35" t="inlineStr">
         <is>
@@ -6598,16 +6598,16 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>11.86</v>
+        <v>11.9</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>11.84</v>
+        <v>11.85</v>
       </c>
       <c r="Q96" s="33" t="n">
-        <v>11.84</v>
+        <v>12</v>
       </c>
       <c r="R96" s="36" t="n">
-        <v>-1.66</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="97">
@@ -6622,37 +6622,37 @@
         </is>
       </c>
       <c r="C97" s="25" t="n">
-        <v>20.12</v>
+        <v>20.37</v>
       </c>
       <c r="D97" s="25" t="n">
-        <v>19.7</v>
+        <v>19.83</v>
       </c>
       <c r="E97" s="26" t="n">
-        <v>19.35</v>
+        <v>19.38</v>
       </c>
       <c r="F97" s="27" t="n">
-        <v>19.42</v>
+        <v>19.32</v>
       </c>
       <c r="G97" s="27" t="n">
-        <v>19.64</v>
+        <v>19.68</v>
       </c>
       <c r="H97" s="28" t="n">
-        <v>19.22</v>
+        <v>19.14</v>
       </c>
       <c r="I97" s="29" t="n">
-        <v>19</v>
+        <v>18.78</v>
       </c>
       <c r="J97" s="29" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="K97" s="30" t="n">
-        <v>19.11</v>
+        <v>19.08</v>
       </c>
       <c r="L97" s="31" t="n">
-        <v>18.76</v>
+        <v>18.63</v>
       </c>
       <c r="M97" s="31" t="n">
-        <v>18.34</v>
+        <v>18.09</v>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
@@ -6660,16 +6660,16 @@
         </is>
       </c>
       <c r="O97" s="32" t="n">
-        <v>19.18</v>
+        <v>19.13</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>19.15</v>
+        <v>19.12</v>
       </c>
       <c r="Q97" s="33" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="R97" s="34" t="n">
-        <v>1.05</v>
+        <v>18.96</v>
+      </c>
+      <c r="R97" s="36" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="98">
@@ -6684,37 +6684,37 @@
         </is>
       </c>
       <c r="C98" s="25" t="n">
-        <v>16.17</v>
+        <v>16.53</v>
       </c>
       <c r="D98" s="25" t="n">
-        <v>15.96</v>
+        <v>16.19</v>
       </c>
       <c r="E98" s="26" t="n">
-        <v>15.78</v>
+        <v>15.91</v>
       </c>
       <c r="F98" s="27" t="n">
-        <v>15.81</v>
+        <v>16.04</v>
       </c>
       <c r="G98" s="27" t="n">
-        <v>15.93</v>
+        <v>16.18</v>
       </c>
       <c r="H98" s="28" t="n">
-        <v>15.72</v>
+        <v>15.84</v>
       </c>
       <c r="I98" s="29" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="J98" s="29" t="n">
-        <v>15.51</v>
+        <v>15.5</v>
       </c>
       <c r="K98" s="30" t="n">
-        <v>15.67</v>
+        <v>15.71</v>
       </c>
       <c r="L98" s="31" t="n">
-        <v>15.49</v>
+        <v>15.43</v>
       </c>
       <c r="M98" s="31" t="n">
-        <v>15.28</v>
+        <v>15.09</v>
       </c>
       <c r="N98" s="20" t="inlineStr">
         <is>
@@ -6722,16 +6722,16 @@
         </is>
       </c>
       <c r="O98" s="32" t="n">
-        <v>15.7</v>
+        <v>15.79</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>15.68</v>
+        <v>15.74</v>
       </c>
       <c r="Q98" s="33" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="R98" s="34" t="n">
-        <v>0.58</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="99">
@@ -6746,54 +6746,54 @@
         </is>
       </c>
       <c r="C99" s="25" t="n">
-        <v>11.82</v>
+        <v>11.57</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>11.37</v>
+        <v>11.32</v>
       </c>
       <c r="E99" s="26" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="F99" s="27" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="G99" s="27" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="H99" s="28" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="I99" s="29" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="J99" s="29" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="K99" s="30" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="L99" s="31" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="M99" s="31" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="N99" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O99" s="32" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="P99" s="32" t="n">
         <v>10.99</v>
       </c>
-      <c r="F99" s="27" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="G99" s="27" t="n">
-        <v>11.34</v>
-      </c>
-      <c r="H99" s="28" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="I99" s="29" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J99" s="29" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="K99" s="30" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="L99" s="31" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="M99" s="31" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="N99" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O99" s="32" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="P99" s="32" t="n">
-        <v>10.77</v>
-      </c>
       <c r="Q99" s="33" t="n">
-        <v>10.95</v>
+        <v>10.99</v>
       </c>
       <c r="R99" s="34" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="100">
@@ -6808,37 +6808,37 @@
         </is>
       </c>
       <c r="C100" s="25" t="n">
-        <v>28.04</v>
+        <v>27.33</v>
       </c>
       <c r="D100" s="25" t="n">
-        <v>27.36</v>
+        <v>27.05</v>
       </c>
       <c r="E100" s="26" t="n">
-        <v>26.79</v>
+        <v>26.82</v>
       </c>
       <c r="F100" s="27" t="n">
-        <v>27.05</v>
+        <v>26.92</v>
       </c>
       <c r="G100" s="27" t="n">
-        <v>27.33</v>
+        <v>27.04</v>
       </c>
       <c r="H100" s="28" t="n">
-        <v>26.65</v>
+        <v>26.76</v>
       </c>
       <c r="I100" s="29" t="n">
-        <v>26.37</v>
+        <v>26.64</v>
       </c>
       <c r="J100" s="29" t="n">
-        <v>25.97</v>
+        <v>26.48</v>
       </c>
       <c r="K100" s="30" t="n">
-        <v>26.41</v>
+        <v>26.66</v>
       </c>
       <c r="L100" s="31" t="n">
-        <v>25.84</v>
+        <v>26.43</v>
       </c>
       <c r="M100" s="31" t="n">
-        <v>25.16</v>
+        <v>26.15</v>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
@@ -6846,16 +6846,16 @@
         </is>
       </c>
       <c r="O100" s="32" t="n">
-        <v>26.56</v>
+        <v>26.72</v>
       </c>
       <c r="P100" s="32" t="n">
-        <v>26.46</v>
+        <v>26.68</v>
       </c>
       <c r="Q100" s="33" t="n">
-        <v>26.76</v>
+        <v>26.8</v>
       </c>
       <c r="R100" s="34" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="101">
@@ -6870,37 +6870,37 @@
         </is>
       </c>
       <c r="C101" s="25" t="n">
-        <v>18.7</v>
+        <v>18.96</v>
       </c>
       <c r="D101" s="25" t="n">
-        <v>18.08</v>
+        <v>18.29</v>
       </c>
       <c r="E101" s="26" t="n">
-        <v>17.56</v>
+        <v>17.73</v>
       </c>
       <c r="F101" s="27" t="n">
-        <v>17.91</v>
+        <v>17.68</v>
       </c>
       <c r="G101" s="27" t="n">
         <v>18.11</v>
       </c>
       <c r="H101" s="28" t="n">
-        <v>17.49</v>
+        <v>17.44</v>
       </c>
       <c r="I101" s="29" t="n">
-        <v>17.29</v>
+        <v>17.01</v>
       </c>
       <c r="J101" s="29" t="n">
-        <v>16.87</v>
+        <v>16.77</v>
       </c>
       <c r="K101" s="30" t="n">
-        <v>17.22</v>
+        <v>17.36</v>
       </c>
       <c r="L101" s="31" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="M101" s="31" t="n">
-        <v>16.08</v>
+        <v>16.13</v>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
@@ -6908,16 +6908,16 @@
         </is>
       </c>
       <c r="O101" s="32" t="n">
-        <v>17.38</v>
+        <v>17.43</v>
       </c>
       <c r="P101" s="32" t="n">
-        <v>17.26</v>
+        <v>17.41</v>
       </c>
       <c r="Q101" s="33" t="n">
-        <v>17.7</v>
+        <v>17.24</v>
       </c>
       <c r="R101" s="34" t="n">
-        <v>3.87</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="102">
@@ -6932,37 +6932,37 @@
         </is>
       </c>
       <c r="C102" s="25" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="D102" s="25" t="n">
         <v>32.07</v>
       </c>
-      <c r="D102" s="25" t="n">
-        <v>31.63</v>
-      </c>
       <c r="E102" s="26" t="n">
-        <v>31.26</v>
+        <v>31.51</v>
       </c>
       <c r="F102" s="27" t="n">
-        <v>31.49</v>
+        <v>31.8</v>
       </c>
       <c r="G102" s="27" t="n">
-        <v>31.65</v>
+        <v>32.06</v>
       </c>
       <c r="H102" s="28" t="n">
-        <v>31.21</v>
+        <v>31.4</v>
       </c>
       <c r="I102" s="29" t="n">
-        <v>31.05</v>
+        <v>31.14</v>
       </c>
       <c r="J102" s="29" t="n">
-        <v>30.77</v>
+        <v>30.74</v>
       </c>
       <c r="K102" s="30" t="n">
-        <v>31.02</v>
+        <v>31.15</v>
       </c>
       <c r="L102" s="31" t="n">
-        <v>30.65</v>
+        <v>30.59</v>
       </c>
       <c r="M102" s="31" t="n">
-        <v>30.21</v>
+        <v>29.93</v>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
@@ -6970,16 +6970,16 @@
         </is>
       </c>
       <c r="O102" s="32" t="n">
-        <v>31.13</v>
+        <v>31.3</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>31.05</v>
+        <v>31.2</v>
       </c>
       <c r="Q102" s="33" t="n">
-        <v>31.34</v>
+        <v>31.54</v>
       </c>
       <c r="R102" s="34" t="n">
-        <v>1.42</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="103">
@@ -6994,37 +6994,37 @@
         </is>
       </c>
       <c r="C103" s="25" t="n">
-        <v>16.37</v>
+        <v>16.59</v>
       </c>
       <c r="D103" s="25" t="n">
-        <v>15.66</v>
+        <v>15.95</v>
       </c>
       <c r="E103" s="26" t="n">
-        <v>15.06</v>
+        <v>15.41</v>
       </c>
       <c r="F103" s="27" t="n">
-        <v>15.24</v>
+        <v>15.72</v>
       </c>
       <c r="G103" s="27" t="n">
-        <v>15.59</v>
+        <v>15.96</v>
       </c>
       <c r="H103" s="28" t="n">
-        <v>14.88</v>
+        <v>15.32</v>
       </c>
       <c r="I103" s="29" t="n">
-        <v>14.53</v>
+        <v>15.08</v>
       </c>
       <c r="J103" s="29" t="n">
-        <v>14.17</v>
+        <v>14.68</v>
       </c>
       <c r="K103" s="30" t="n">
-        <v>14.67</v>
+        <v>15.05</v>
       </c>
       <c r="L103" s="31" t="n">
-        <v>14.07</v>
+        <v>14.51</v>
       </c>
       <c r="M103" s="31" t="n">
-        <v>13.36</v>
+        <v>13.87</v>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
@@ -7032,16 +7032,16 @@
         </is>
       </c>
       <c r="O103" s="32" t="n">
-        <v>14.8</v>
+        <v>15.21</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>14.72</v>
+        <v>15.1</v>
       </c>
       <c r="Q103" s="33" t="n">
-        <v>14.9</v>
+        <v>15.49</v>
       </c>
       <c r="R103" s="34" t="n">
-        <v>4.93</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="104">
@@ -7056,37 +7056,37 @@
         </is>
       </c>
       <c r="C104" s="25" t="n">
-        <v>70.47</v>
+        <v>74.06</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>69.06999999999999</v>
+        <v>71.61</v>
       </c>
       <c r="E104" s="26" t="n">
-        <v>67.89</v>
+        <v>69.56</v>
       </c>
       <c r="F104" s="27" t="n">
-        <v>68.23</v>
+        <v>70.52</v>
       </c>
       <c r="G104" s="27" t="n">
-        <v>68.92</v>
+        <v>71.53</v>
       </c>
       <c r="H104" s="28" t="n">
-        <v>67.52</v>
+        <v>69.08</v>
       </c>
       <c r="I104" s="29" t="n">
-        <v>66.83</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="J104" s="29" t="n">
-        <v>66.12</v>
+        <v>66.63</v>
       </c>
       <c r="K104" s="30" t="n">
-        <v>67.11</v>
+        <v>68.19</v>
       </c>
       <c r="L104" s="31" t="n">
-        <v>65.93000000000001</v>
+        <v>66.14</v>
       </c>
       <c r="M104" s="31" t="n">
-        <v>64.53</v>
+        <v>63.69</v>
       </c>
       <c r="N104" s="20" t="inlineStr">
         <is>
@@ -7094,16 +7094,16 @@
         </is>
       </c>
       <c r="O104" s="32" t="n">
-        <v>67.37</v>
+        <v>68.73</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>67.22</v>
+        <v>68.38</v>
       </c>
       <c r="Q104" s="33" t="n">
-        <v>67.55</v>
+        <v>69.5</v>
       </c>
       <c r="R104" s="34" t="n">
-        <v>0.67</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="105">
@@ -7118,48 +7118,48 @@
         </is>
       </c>
       <c r="C105" s="25" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>14.84</v>
+        <v>14.68</v>
       </c>
       <c r="E105" s="26" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="F105" s="27" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G105" s="27" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="H105" s="28" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="I105" s="29" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="J105" s="29" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="K105" s="30" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="L105" s="31" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="M105" s="31" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N105" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O105" s="32" t="n">
         <v>14.54</v>
       </c>
-      <c r="F105" s="27" t="n">
-        <v>14.69</v>
-      </c>
-      <c r="G105" s="27" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="H105" s="28" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="I105" s="29" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="J105" s="29" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="K105" s="30" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="L105" s="31" t="n">
-        <v>14.04</v>
-      </c>
-      <c r="M105" s="31" t="n">
-        <v>13.68</v>
-      </c>
-      <c r="N105" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O105" s="32" t="n">
-        <v>14.42</v>
-      </c>
       <c r="P105" s="32" t="n">
-        <v>14.37</v>
+        <v>14.53</v>
       </c>
       <c r="Q105" s="33" t="n">
         <v>14.54</v>
@@ -7180,37 +7180,37 @@
         </is>
       </c>
       <c r="C106" s="25" t="n">
-        <v>15.97</v>
+        <v>15.47</v>
       </c>
       <c r="D106" s="25" t="n">
-        <v>15.48</v>
+        <v>15.21</v>
       </c>
       <c r="E106" s="26" t="n">
-        <v>15.07</v>
+        <v>14.99</v>
       </c>
       <c r="F106" s="27" t="n">
-        <v>15.08</v>
+        <v>15</v>
       </c>
       <c r="G106" s="27" t="n">
-        <v>15.38</v>
+        <v>15.15</v>
       </c>
       <c r="H106" s="28" t="n">
         <v>14.89</v>
       </c>
       <c r="I106" s="29" t="n">
-        <v>14.59</v>
+        <v>14.74</v>
       </c>
       <c r="J106" s="29" t="n">
-        <v>14.4</v>
+        <v>14.63</v>
       </c>
       <c r="K106" s="30" t="n">
-        <v>14.8</v>
+        <v>14.85</v>
       </c>
       <c r="L106" s="31" t="n">
-        <v>14.39</v>
+        <v>14.63</v>
       </c>
       <c r="M106" s="31" t="n">
-        <v>13.9</v>
+        <v>14.37</v>
       </c>
       <c r="N106" s="35" t="inlineStr">
         <is>
@@ -7218,16 +7218,16 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>14.86</v>
+        <v>14.88</v>
       </c>
       <c r="P106" s="32" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="Q106" s="33" t="n">
         <v>14.84</v>
       </c>
-      <c r="Q106" s="33" t="n">
-        <v>14.79</v>
-      </c>
       <c r="R106" s="36" t="n">
-        <v>-1.2</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="107">
@@ -7242,37 +7242,37 @@
         </is>
       </c>
       <c r="C107" s="25" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="D107" s="25" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="E107" s="26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F107" s="27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G107" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H107" s="28" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I107" s="29" t="n">
         <v>2.28</v>
       </c>
-      <c r="F107" s="27" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="G107" s="27" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="H107" s="28" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="I107" s="29" t="n">
-        <v>2.24</v>
-      </c>
       <c r="J107" s="29" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="K107" s="30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L107" s="31" t="n">
         <v>2.25</v>
       </c>
-      <c r="L107" s="31" t="n">
-        <v>2.19</v>
-      </c>
       <c r="M107" s="31" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="N107" s="20" t="inlineStr">
         <is>
@@ -7280,16 +7280,16 @@
         </is>
       </c>
       <c r="O107" s="32" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="P107" s="32" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q107" s="33" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R107" s="34" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="108">
@@ -7304,54 +7304,54 @@
         </is>
       </c>
       <c r="C108" s="25" t="n">
-        <v>45.97</v>
+        <v>45.84</v>
       </c>
       <c r="D108" s="25" t="n">
-        <v>44.79</v>
+        <v>44.58</v>
       </c>
       <c r="E108" s="26" t="n">
-        <v>43.8</v>
+        <v>43.52</v>
       </c>
       <c r="F108" s="27" t="n">
-        <v>44.07</v>
+        <v>43.39</v>
       </c>
       <c r="G108" s="27" t="n">
-        <v>44.65</v>
+        <v>44.23</v>
       </c>
       <c r="H108" s="28" t="n">
-        <v>43.47</v>
+        <v>42.97</v>
       </c>
       <c r="I108" s="29" t="n">
-        <v>42.89</v>
+        <v>42.13</v>
       </c>
       <c r="J108" s="29" t="n">
-        <v>42.29</v>
+        <v>41.71</v>
       </c>
       <c r="K108" s="30" t="n">
-        <v>43.14</v>
+        <v>42.82</v>
       </c>
       <c r="L108" s="31" t="n">
-        <v>42.15</v>
+        <v>41.76</v>
       </c>
       <c r="M108" s="31" t="n">
-        <v>40.97</v>
-      </c>
-      <c r="N108" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>40.5</v>
+      </c>
+      <c r="N108" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O108" s="32" t="n">
-        <v>43.35</v>
+        <v>42.94</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>43.23</v>
+        <v>42.92</v>
       </c>
       <c r="Q108" s="33" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="R108" s="34" t="n">
-        <v>0.6899999999999999</v>
+        <v>42.56</v>
+      </c>
+      <c r="R108" s="36" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="109">
@@ -7366,37 +7366,37 @@
         </is>
       </c>
       <c r="C109" s="25" t="n">
-        <v>8.56</v>
+        <v>9.52</v>
       </c>
       <c r="D109" s="25" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="E109" s="26" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="F109" s="27" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G109" s="27" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="H109" s="28" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="I109" s="29" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="E109" s="26" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="F109" s="27" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="G109" s="27" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="H109" s="28" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="I109" s="29" t="n">
-        <v>8.31</v>
-      </c>
       <c r="J109" s="29" t="n">
-        <v>8.26</v>
+        <v>8.19</v>
       </c>
       <c r="K109" s="30" t="n">
-        <v>8.32</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L109" s="31" t="n">
-        <v>8.24</v>
+        <v>8.1</v>
       </c>
       <c r="M109" s="31" t="n">
-        <v>8.140000000000001</v>
+        <v>7.66</v>
       </c>
       <c r="N109" s="20" t="inlineStr">
         <is>
@@ -7404,16 +7404,16 @@
         </is>
       </c>
       <c r="O109" s="32" t="n">
-        <v>8.34</v>
+        <v>8.57</v>
       </c>
       <c r="P109" s="32" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="Q109" s="33" t="n">
-        <v>8.369999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="R109" s="34" t="n">
-        <v>0.84</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="110">
@@ -7428,54 +7428,54 @@
         </is>
       </c>
       <c r="C110" s="25" t="n">
-        <v>44.57</v>
+        <v>44.25</v>
       </c>
       <c r="D110" s="25" t="n">
-        <v>44.17</v>
+        <v>43.91</v>
       </c>
       <c r="E110" s="26" t="n">
-        <v>43.83</v>
+        <v>43.63</v>
       </c>
       <c r="F110" s="27" t="n">
-        <v>44.05</v>
+        <v>43.71</v>
       </c>
       <c r="G110" s="27" t="n">
-        <v>44.19</v>
+        <v>43.87</v>
       </c>
       <c r="H110" s="28" t="n">
-        <v>43.79</v>
+        <v>43.53</v>
       </c>
       <c r="I110" s="29" t="n">
-        <v>43.65</v>
+        <v>43.37</v>
       </c>
       <c r="J110" s="29" t="n">
-        <v>43.39</v>
+        <v>43.19</v>
       </c>
       <c r="K110" s="30" t="n">
-        <v>43.61</v>
+        <v>43.43</v>
       </c>
       <c r="L110" s="31" t="n">
-        <v>43.27</v>
+        <v>43.15</v>
       </c>
       <c r="M110" s="31" t="n">
-        <v>42.87</v>
-      </c>
-      <c r="N110" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>42.81</v>
+      </c>
+      <c r="N110" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O110" s="32" t="n">
-        <v>43.71</v>
+        <v>43.5</v>
       </c>
       <c r="P110" s="32" t="n">
-        <v>43.64</v>
+        <v>43.46</v>
       </c>
       <c r="Q110" s="33" t="n">
-        <v>43.92</v>
-      </c>
-      <c r="R110" s="34" t="n">
-        <v>0.27</v>
+        <v>43.54</v>
+      </c>
+      <c r="R110" s="36" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="111">
@@ -7490,37 +7490,37 @@
         </is>
       </c>
       <c r="C111" s="25" t="n">
-        <v>64.95</v>
+        <v>64.08</v>
       </c>
       <c r="D111" s="25" t="n">
-        <v>63.65</v>
+        <v>63.23</v>
       </c>
       <c r="E111" s="26" t="n">
-        <v>62.56</v>
+        <v>62.51</v>
       </c>
       <c r="F111" s="27" t="n">
-        <v>62.92</v>
+        <v>62.52</v>
       </c>
       <c r="G111" s="27" t="n">
-        <v>63.53</v>
+        <v>63.03</v>
       </c>
       <c r="H111" s="28" t="n">
-        <v>62.23</v>
+        <v>62.18</v>
       </c>
       <c r="I111" s="29" t="n">
-        <v>61.62</v>
+        <v>61.67</v>
       </c>
       <c r="J111" s="29" t="n">
-        <v>60.93</v>
+        <v>61.33</v>
       </c>
       <c r="K111" s="30" t="n">
-        <v>61.84</v>
+        <v>62.04</v>
       </c>
       <c r="L111" s="31" t="n">
-        <v>60.75</v>
+        <v>61.32</v>
       </c>
       <c r="M111" s="31" t="n">
-        <v>59.45</v>
+        <v>60.47</v>
       </c>
       <c r="N111" s="20" t="inlineStr">
         <is>
@@ -7528,16 +7528,16 @@
         </is>
       </c>
       <c r="O111" s="32" t="n">
-        <v>62.09</v>
+        <v>62.14</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>61.94</v>
+        <v>62.1</v>
       </c>
       <c r="Q111" s="33" t="n">
-        <v>62.3</v>
+        <v>62</v>
       </c>
       <c r="R111" s="36" t="n">
-        <v>-0.32</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="112">
@@ -7552,54 +7552,54 @@
         </is>
       </c>
       <c r="C112" s="25" t="n">
-        <v>10.47</v>
+        <v>10.54</v>
       </c>
       <c r="D112" s="25" t="n">
-        <v>10.38</v>
+        <v>10.45</v>
       </c>
       <c r="E112" s="26" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="F112" s="27" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="G112" s="27" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="H112" s="28" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="I112" s="29" t="n">
         <v>10.3</v>
       </c>
-      <c r="F112" s="27" t="n">
+      <c r="J112" s="29" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="K112" s="30" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="L112" s="31" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="M112" s="31" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="N112" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O112" s="32" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="P112" s="32" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="Q112" s="33" t="n">
         <v>10.35</v>
       </c>
-      <c r="G112" s="27" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="H112" s="28" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="I112" s="29" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="J112" s="29" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="K112" s="30" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="L112" s="31" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="M112" s="31" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="N112" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O112" s="32" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="P112" s="32" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="Q112" s="33" t="n">
-        <v>10.32</v>
-      </c>
       <c r="R112" s="34" t="n">
-        <v>0.49</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="113">
@@ -7614,37 +7614,37 @@
         </is>
       </c>
       <c r="C113" s="25" t="n">
-        <v>297.18</v>
+        <v>293.24</v>
       </c>
       <c r="D113" s="25" t="n">
-        <v>280.38</v>
+        <v>284.44</v>
       </c>
       <c r="E113" s="26" t="n">
-        <v>266.3</v>
+        <v>277.06</v>
       </c>
       <c r="F113" s="27" t="n">
-        <v>274.53</v>
+        <v>281.27</v>
       </c>
       <c r="G113" s="27" t="n">
-        <v>280.67</v>
+        <v>284.53</v>
       </c>
       <c r="H113" s="28" t="n">
-        <v>263.87</v>
+        <v>275.73</v>
       </c>
       <c r="I113" s="29" t="n">
-        <v>257.73</v>
+        <v>272.47</v>
       </c>
       <c r="J113" s="29" t="n">
-        <v>247.07</v>
+        <v>266.93</v>
       </c>
       <c r="K113" s="30" t="n">
-        <v>256.9</v>
+        <v>272.14</v>
       </c>
       <c r="L113" s="31" t="n">
-        <v>242.82</v>
+        <v>264.76</v>
       </c>
       <c r="M113" s="31" t="n">
-        <v>226.02</v>
+        <v>255.96</v>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
@@ -7652,16 +7652,16 @@
         </is>
       </c>
       <c r="O113" s="32" t="n">
-        <v>261.04</v>
+        <v>274.28</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>258.21</v>
+        <v>272.82</v>
       </c>
       <c r="Q113" s="33" t="n">
-        <v>268.4</v>
+        <v>278</v>
       </c>
       <c r="R113" s="34" t="n">
-        <v>5.25</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="114">
@@ -7676,37 +7676,37 @@
         </is>
       </c>
       <c r="C114" s="25" t="n">
-        <v>237.02</v>
+        <v>232.95</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>227.12</v>
+        <v>227.85</v>
       </c>
       <c r="E114" s="26" t="n">
-        <v>218.82</v>
+        <v>223.58</v>
       </c>
       <c r="F114" s="27" t="n">
-        <v>223.17</v>
+        <v>224.67</v>
       </c>
       <c r="G114" s="27" t="n">
-        <v>227.03</v>
+        <v>227.23</v>
       </c>
       <c r="H114" s="28" t="n">
-        <v>217.13</v>
+        <v>222.13</v>
       </c>
       <c r="I114" s="29" t="n">
-        <v>213.27</v>
+        <v>219.57</v>
       </c>
       <c r="J114" s="29" t="n">
-        <v>207.23</v>
+        <v>217.03</v>
       </c>
       <c r="K114" s="30" t="n">
-        <v>213.28</v>
+        <v>220.72</v>
       </c>
       <c r="L114" s="31" t="n">
-        <v>204.98</v>
+        <v>216.45</v>
       </c>
       <c r="M114" s="31" t="n">
-        <v>195.08</v>
+        <v>211.35</v>
       </c>
       <c r="N114" s="20" t="inlineStr">
         <is>
@@ -7714,16 +7714,16 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>215.59</v>
+        <v>221.63</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>214.05</v>
+        <v>221.12</v>
       </c>
       <c r="Q114" s="33" t="n">
-        <v>219.3</v>
+        <v>222.1</v>
       </c>
       <c r="R114" s="34" t="n">
-        <v>2.52</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="115">
@@ -7738,37 +7738,37 @@
         </is>
       </c>
       <c r="C115" s="25" t="n">
-        <v>709.41</v>
+        <v>686.36</v>
       </c>
       <c r="D115" s="25" t="n">
-        <v>669.91</v>
+        <v>666.36</v>
       </c>
       <c r="E115" s="26" t="n">
-        <v>636.8099999999999</v>
+        <v>649.6</v>
       </c>
       <c r="F115" s="27" t="n">
-        <v>656.33</v>
+        <v>649.67</v>
       </c>
       <c r="G115" s="27" t="n">
-        <v>670.67</v>
+        <v>661.83</v>
       </c>
       <c r="H115" s="28" t="n">
-        <v>631.17</v>
+        <v>641.83</v>
       </c>
       <c r="I115" s="29" t="n">
-        <v>616.83</v>
+        <v>629.67</v>
       </c>
       <c r="J115" s="29" t="n">
-        <v>591.67</v>
+        <v>621.83</v>
       </c>
       <c r="K115" s="30" t="n">
-        <v>614.6900000000001</v>
+        <v>638.4</v>
       </c>
       <c r="L115" s="31" t="n">
-        <v>581.59</v>
+        <v>621.64</v>
       </c>
       <c r="M115" s="31" t="n">
-        <v>542.09</v>
+        <v>601.64</v>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
@@ -7776,16 +7776,16 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>624.47</v>
+        <v>640.9</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>617.77</v>
+        <v>639.96</v>
       </c>
       <c r="Q115" s="33" t="n">
-        <v>642</v>
+        <v>637.5</v>
       </c>
       <c r="R115" s="34" t="n">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="116">
@@ -7800,37 +7800,37 @@
         </is>
       </c>
       <c r="C116" s="25" t="n">
-        <v>6.48</v>
+        <v>6.64</v>
       </c>
       <c r="D116" s="25" t="n">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="E116" s="26" t="n">
-        <v>6.24</v>
+        <v>6.38</v>
       </c>
       <c r="F116" s="27" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="G116" s="27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H116" s="28" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="I116" s="29" t="n">
         <v>6.31</v>
       </c>
-      <c r="G116" s="27" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="H116" s="28" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="I116" s="29" t="n">
+      <c r="J116" s="29" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="K116" s="30" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L116" s="31" t="n">
         <v>6.18</v>
       </c>
-      <c r="J116" s="29" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K116" s="30" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="L116" s="31" t="n">
-        <v>6.06</v>
-      </c>
       <c r="M116" s="31" t="n">
-        <v>5.93</v>
+        <v>6.04</v>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
@@ -7838,16 +7838,16 @@
         </is>
       </c>
       <c r="O116" s="32" t="n">
-        <v>6.2</v>
+        <v>6.34</v>
       </c>
       <c r="P116" s="32" t="n">
-        <v>6.18</v>
+        <v>6.31</v>
       </c>
       <c r="Q116" s="33" t="n">
-        <v>6.27</v>
+        <v>6.4</v>
       </c>
       <c r="R116" s="34" t="n">
-        <v>1.46</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="117">
@@ -7862,54 +7862,54 @@
         </is>
       </c>
       <c r="C117" s="25" t="n">
-        <v>140.66</v>
+        <v>143.88</v>
       </c>
       <c r="D117" s="25" t="n">
-        <v>136.36</v>
+        <v>139.38</v>
       </c>
       <c r="E117" s="26" t="n">
-        <v>132.75</v>
+        <v>135.61</v>
       </c>
       <c r="F117" s="27" t="n">
-        <v>134.4</v>
+        <v>137.83</v>
       </c>
       <c r="G117" s="27" t="n">
+        <v>139.47</v>
+      </c>
+      <c r="H117" s="28" t="n">
+        <v>134.97</v>
+      </c>
+      <c r="I117" s="29" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="J117" s="29" t="n">
+        <v>130.47</v>
+      </c>
+      <c r="K117" s="30" t="n">
+        <v>133.09</v>
+      </c>
+      <c r="L117" s="31" t="n">
+        <v>129.32</v>
+      </c>
+      <c r="M117" s="31" t="n">
+        <v>124.82</v>
+      </c>
+      <c r="N117" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O117" s="32" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="P117" s="32" t="n">
+        <v>133.44</v>
+      </c>
+      <c r="Q117" s="33" t="n">
         <v>136.2</v>
       </c>
-      <c r="H117" s="28" t="n">
-        <v>131.9</v>
-      </c>
-      <c r="I117" s="29" t="n">
-        <v>130.1</v>
-      </c>
-      <c r="J117" s="29" t="n">
-        <v>127.6</v>
-      </c>
-      <c r="K117" s="30" t="n">
-        <v>130.35</v>
-      </c>
-      <c r="L117" s="31" t="n">
-        <v>126.74</v>
-      </c>
-      <c r="M117" s="31" t="n">
-        <v>122.44</v>
-      </c>
-      <c r="N117" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O117" s="32" t="n">
-        <v>131.29</v>
-      </c>
-      <c r="P117" s="32" t="n">
-        <v>130.68</v>
-      </c>
-      <c r="Q117" s="33" t="n">
-        <v>132.6</v>
-      </c>
       <c r="R117" s="34" t="n">
-        <v>2</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="118">
@@ -7924,37 +7924,37 @@
         </is>
       </c>
       <c r="C118" s="25" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="D118" s="25" t="n">
         <v>10.79</v>
       </c>
-      <c r="D118" s="25" t="n">
-        <v>10.49</v>
-      </c>
       <c r="E118" s="26" t="n">
-        <v>10.23</v>
+        <v>10.38</v>
       </c>
       <c r="F118" s="27" t="n">
-        <v>10.39</v>
+        <v>10.38</v>
       </c>
       <c r="G118" s="27" t="n">
-        <v>10.49</v>
+        <v>10.67</v>
       </c>
       <c r="H118" s="28" t="n">
         <v>10.19</v>
       </c>
       <c r="I118" s="29" t="n">
-        <v>10.09</v>
+        <v>9.9</v>
       </c>
       <c r="J118" s="29" t="n">
-        <v>9.890000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K118" s="30" t="n">
-        <v>10.07</v>
+        <v>10.12</v>
       </c>
       <c r="L118" s="31" t="n">
-        <v>9.81</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M118" s="31" t="n">
-        <v>9.51</v>
+        <v>9.23</v>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
@@ -7962,16 +7962,16 @@
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>10.14</v>
+        <v>10.17</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>10.09</v>
+        <v>10.15</v>
       </c>
       <c r="Q118" s="33" t="n">
-        <v>10.28</v>
+        <v>10.08</v>
       </c>
       <c r="R118" s="34" t="n">
-        <v>2.59</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="119">
@@ -7986,37 +7986,37 @@
         </is>
       </c>
       <c r="C119" s="25" t="n">
-        <v>16.57</v>
+        <v>18.15</v>
       </c>
       <c r="D119" s="25" t="n">
-        <v>16.01</v>
+        <v>17.52</v>
       </c>
       <c r="E119" s="26" t="n">
-        <v>15.54</v>
+        <v>16.99</v>
       </c>
       <c r="F119" s="27" t="n">
-        <v>15.81</v>
+        <v>17.25</v>
       </c>
       <c r="G119" s="27" t="n">
-        <v>16.01</v>
+        <v>17.51</v>
       </c>
       <c r="H119" s="28" t="n">
-        <v>15.45</v>
+        <v>16.88</v>
       </c>
       <c r="I119" s="29" t="n">
-        <v>15.25</v>
+        <v>16.62</v>
       </c>
       <c r="J119" s="29" t="n">
-        <v>14.89</v>
+        <v>16.25</v>
       </c>
       <c r="K119" s="30" t="n">
-        <v>15.22</v>
+        <v>16.64</v>
       </c>
       <c r="L119" s="31" t="n">
-        <v>14.75</v>
+        <v>16.11</v>
       </c>
       <c r="M119" s="31" t="n">
-        <v>14.19</v>
+        <v>15.48</v>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
@@ -8024,16 +8024,16 @@
         </is>
       </c>
       <c r="O119" s="32" t="n">
-        <v>15.36</v>
+        <v>16.78</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>15.27</v>
+        <v>16.69</v>
       </c>
       <c r="Q119" s="33" t="n">
-        <v>15.6</v>
+        <v>17</v>
       </c>
       <c r="R119" s="34" t="n">
-        <v>3.24</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="120">
@@ -8048,37 +8048,37 @@
         </is>
       </c>
       <c r="C120" s="25" t="n">
-        <v>10.48</v>
+        <v>11.42</v>
       </c>
       <c r="D120" s="25" t="n">
-        <v>10.12</v>
+        <v>10.78</v>
       </c>
       <c r="E120" s="26" t="n">
-        <v>9.82</v>
+        <v>10.24</v>
       </c>
       <c r="F120" s="27" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="G120" s="27" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="H120" s="28" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="I120" s="29" t="n">
         <v>9.91</v>
       </c>
-      <c r="G120" s="27" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="H120" s="28" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="I120" s="29" t="n">
-        <v>9.550000000000001</v>
-      </c>
       <c r="J120" s="29" t="n">
-        <v>9.369999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="K120" s="30" t="n">
-        <v>9.619999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L120" s="31" t="n">
-        <v>9.32</v>
+        <v>9.34</v>
       </c>
       <c r="M120" s="31" t="n">
-        <v>8.960000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
@@ -8086,16 +8086,16 @@
         </is>
       </c>
       <c r="O120" s="32" t="n">
-        <v>9.69</v>
+        <v>10.04</v>
       </c>
       <c r="P120" s="32" t="n">
-        <v>9.65</v>
+        <v>9.93</v>
       </c>
       <c r="Q120" s="33" t="n">
-        <v>9.74</v>
+        <v>10.32</v>
       </c>
       <c r="R120" s="34" t="n">
-        <v>2.1</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="121">
@@ -8110,37 +8110,37 @@
         </is>
       </c>
       <c r="C121" s="25" t="n">
-        <v>12.89</v>
+        <v>12.46</v>
       </c>
       <c r="D121" s="25" t="n">
-        <v>12.24</v>
+        <v>12.15</v>
       </c>
       <c r="E121" s="26" t="n">
-        <v>11.7</v>
+        <v>11.89</v>
       </c>
       <c r="F121" s="27" t="n">
-        <v>11.84</v>
+        <v>11.88</v>
       </c>
       <c r="G121" s="27" t="n">
-        <v>12.16</v>
+        <v>12.08</v>
       </c>
       <c r="H121" s="28" t="n">
-        <v>11.51</v>
+        <v>11.77</v>
       </c>
       <c r="I121" s="29" t="n">
-        <v>11.19</v>
+        <v>11.57</v>
       </c>
       <c r="J121" s="29" t="n">
-        <v>10.86</v>
+        <v>11.46</v>
       </c>
       <c r="K121" s="30" t="n">
-        <v>11.33</v>
+        <v>11.72</v>
       </c>
       <c r="L121" s="31" t="n">
-        <v>10.79</v>
+        <v>11.46</v>
       </c>
       <c r="M121" s="31" t="n">
-        <v>10.14</v>
+        <v>11.15</v>
       </c>
       <c r="N121" s="20" t="inlineStr">
         <is>
@@ -8148,16 +8148,16 @@
         </is>
       </c>
       <c r="O121" s="32" t="n">
-        <v>11.45</v>
+        <v>11.75</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>11.38</v>
+        <v>11.74</v>
       </c>
       <c r="Q121" s="33" t="n">
-        <v>11.51</v>
+        <v>11.69</v>
       </c>
       <c r="R121" s="34" t="n">
-        <v>4.07</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="122">
@@ -8172,37 +8172,37 @@
         </is>
       </c>
       <c r="C122" s="25" t="n">
-        <v>7.45</v>
+        <v>6.92</v>
       </c>
       <c r="D122" s="25" t="n">
-        <v>7.03</v>
+        <v>6.78</v>
       </c>
       <c r="E122" s="26" t="n">
-        <v>6.68</v>
+        <v>6.66</v>
       </c>
       <c r="F122" s="27" t="n">
-        <v>6.78</v>
+        <v>6.7</v>
       </c>
       <c r="G122" s="27" t="n">
-        <v>6.99</v>
+        <v>6.76</v>
       </c>
       <c r="H122" s="28" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="I122" s="29" t="n">
-        <v>6.36</v>
+        <v>6.56</v>
       </c>
       <c r="J122" s="29" t="n">
-        <v>6.15</v>
+        <v>6.48</v>
       </c>
       <c r="K122" s="30" t="n">
-        <v>6.44</v>
+        <v>6.58</v>
       </c>
       <c r="L122" s="31" t="n">
-        <v>6.09</v>
+        <v>6.46</v>
       </c>
       <c r="M122" s="31" t="n">
-        <v>5.67</v>
+        <v>6.32</v>
       </c>
       <c r="N122" s="20" t="inlineStr">
         <is>
@@ -8210,16 +8210,16 @@
         </is>
       </c>
       <c r="O122" s="32" t="n">
-        <v>6.52</v>
+        <v>6.61</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>6.48</v>
+        <v>6.59</v>
       </c>
       <c r="Q122" s="33" t="n">
-        <v>6.58</v>
+        <v>6.63</v>
       </c>
       <c r="R122" s="34" t="n">
-        <v>4.11</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="123">
@@ -8234,54 +8234,54 @@
         </is>
       </c>
       <c r="C123" s="25" t="n">
-        <v>8.74</v>
+        <v>7.95</v>
       </c>
       <c r="D123" s="25" t="n">
-        <v>8.09</v>
+        <v>7.49</v>
       </c>
       <c r="E123" s="26" t="n">
-        <v>7.55</v>
+        <v>7.11</v>
       </c>
       <c r="F123" s="27" t="n">
-        <v>7.78</v>
+        <v>7.17</v>
       </c>
       <c r="G123" s="27" t="n">
-        <v>8.06</v>
+        <v>7.42</v>
       </c>
       <c r="H123" s="28" t="n">
-        <v>7.41</v>
+        <v>6.96</v>
       </c>
       <c r="I123" s="29" t="n">
-        <v>7.13</v>
+        <v>6.71</v>
       </c>
       <c r="J123" s="29" t="n">
-        <v>6.76</v>
+        <v>6.5</v>
       </c>
       <c r="K123" s="30" t="n">
-        <v>7.18</v>
+        <v>6.85</v>
       </c>
       <c r="L123" s="31" t="n">
-        <v>6.64</v>
+        <v>6.47</v>
       </c>
       <c r="M123" s="31" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="N123" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>6.01</v>
+      </c>
+      <c r="N123" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O123" s="32" t="n">
-        <v>7.32</v>
+        <v>6.92</v>
       </c>
       <c r="P123" s="32" t="n">
-        <v>7.23</v>
+        <v>6.89</v>
       </c>
       <c r="Q123" s="33" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R123" s="34" t="n">
-        <v>6.38</v>
+        <v>6.92</v>
+      </c>
+      <c r="R123" s="36" t="n">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="124">
@@ -8296,37 +8296,37 @@
         </is>
       </c>
       <c r="C124" s="25" t="n">
-        <v>27.87</v>
+        <v>26.32</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>26.43</v>
+        <v>25.69</v>
       </c>
       <c r="E124" s="26" t="n">
-        <v>25.22</v>
+        <v>25.16</v>
       </c>
       <c r="F124" s="27" t="n">
-        <v>25.74</v>
+        <v>25.24</v>
       </c>
       <c r="G124" s="27" t="n">
-        <v>26.36</v>
+        <v>25.59</v>
       </c>
       <c r="H124" s="28" t="n">
-        <v>24.92</v>
+        <v>24.96</v>
       </c>
       <c r="I124" s="29" t="n">
-        <v>24.3</v>
+        <v>24.61</v>
       </c>
       <c r="J124" s="29" t="n">
-        <v>23.48</v>
+        <v>24.33</v>
       </c>
       <c r="K124" s="30" t="n">
-        <v>24.42</v>
+        <v>24.81</v>
       </c>
       <c r="L124" s="31" t="n">
-        <v>23.21</v>
+        <v>24.28</v>
       </c>
       <c r="M124" s="31" t="n">
-        <v>21.77</v>
+        <v>23.65</v>
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
@@ -8334,16 +8334,16 @@
         </is>
       </c>
       <c r="O124" s="32" t="n">
-        <v>24.72</v>
+        <v>24.91</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>24.53</v>
+        <v>24.86</v>
       </c>
       <c r="Q124" s="33" t="n">
-        <v>25.12</v>
+        <v>24.9</v>
       </c>
       <c r="R124" s="34" t="n">
-        <v>5.72</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="125">
@@ -8358,37 +8358,37 @@
         </is>
       </c>
       <c r="C125" s="25" t="n">
-        <v>190.05</v>
+        <v>183.84</v>
       </c>
       <c r="D125" s="25" t="n">
-        <v>180.75</v>
+        <v>179.24</v>
       </c>
       <c r="E125" s="26" t="n">
-        <v>172.95</v>
+        <v>175.39</v>
       </c>
       <c r="F125" s="27" t="n">
-        <v>176.63</v>
+        <v>177.87</v>
       </c>
       <c r="G125" s="27" t="n">
-        <v>180.47</v>
+        <v>179.43</v>
       </c>
       <c r="H125" s="28" t="n">
-        <v>171.17</v>
+        <v>174.83</v>
       </c>
       <c r="I125" s="29" t="n">
-        <v>167.33</v>
+        <v>173.27</v>
       </c>
       <c r="J125" s="29" t="n">
-        <v>161.87</v>
+        <v>170.23</v>
       </c>
       <c r="K125" s="30" t="n">
-        <v>167.75</v>
+        <v>172.81</v>
       </c>
       <c r="L125" s="31" t="n">
-        <v>159.95</v>
+        <v>168.96</v>
       </c>
       <c r="M125" s="31" t="n">
-        <v>150.65</v>
+        <v>164.36</v>
       </c>
       <c r="N125" s="20" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         </is>
       </c>
       <c r="O125" s="32" t="n">
-        <v>169.82</v>
+        <v>174</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>168.47</v>
+        <v>173.17</v>
       </c>
       <c r="Q125" s="33" t="n">
-        <v>172.8</v>
+        <v>176.3</v>
       </c>
       <c r="R125" s="34" t="n">
-        <v>3.54</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="126">
@@ -8420,37 +8420,37 @@
         </is>
       </c>
       <c r="C126" s="25" t="n">
-        <v>52.09</v>
+        <v>52.41</v>
       </c>
       <c r="D126" s="25" t="n">
-        <v>51.17</v>
+        <v>51.2</v>
       </c>
       <c r="E126" s="26" t="n">
-        <v>50.4</v>
+        <v>50.18</v>
       </c>
       <c r="F126" s="27" t="n">
-        <v>50.91</v>
+        <v>50.55</v>
       </c>
       <c r="G126" s="27" t="n">
-        <v>51.21</v>
+        <v>51.11</v>
       </c>
       <c r="H126" s="28" t="n">
-        <v>50.29</v>
+        <v>49.9</v>
       </c>
       <c r="I126" s="29" t="n">
-        <v>49.99</v>
+        <v>49.34</v>
       </c>
       <c r="J126" s="29" t="n">
-        <v>49.37</v>
+        <v>48.69</v>
       </c>
       <c r="K126" s="30" t="n">
-        <v>49.88</v>
+        <v>49.51</v>
       </c>
       <c r="L126" s="31" t="n">
-        <v>49.11</v>
+        <v>48.49</v>
       </c>
       <c r="M126" s="31" t="n">
-        <v>48.19</v>
+        <v>47.28</v>
       </c>
       <c r="N126" s="20" t="inlineStr">
         <is>
@@ -8458,16 +8458,16 @@
         </is>
       </c>
       <c r="O126" s="32" t="n">
-        <v>50.12</v>
+        <v>49.75</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>49.95</v>
+        <v>49.6</v>
       </c>
       <c r="Q126" s="33" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="R126" s="34" t="n">
-        <v>1.65</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="127">
@@ -8482,37 +8482,37 @@
         </is>
       </c>
       <c r="C127" s="25" t="n">
-        <v>17.32</v>
+        <v>15.51</v>
       </c>
       <c r="D127" s="25" t="n">
-        <v>16.16</v>
+        <v>14.95</v>
       </c>
       <c r="E127" s="26" t="n">
-        <v>15.18</v>
+        <v>14.48</v>
       </c>
       <c r="F127" s="27" t="n">
-        <v>15.19</v>
+        <v>14.72</v>
       </c>
       <c r="G127" s="27" t="n">
-        <v>15.89</v>
+        <v>14.94</v>
       </c>
       <c r="H127" s="28" t="n">
-        <v>14.73</v>
+        <v>14.38</v>
       </c>
       <c r="I127" s="29" t="n">
-        <v>14.03</v>
+        <v>14.16</v>
       </c>
       <c r="J127" s="29" t="n">
-        <v>13.57</v>
+        <v>13.82</v>
       </c>
       <c r="K127" s="30" t="n">
-        <v>14.54</v>
+        <v>14.16</v>
       </c>
       <c r="L127" s="31" t="n">
-        <v>13.56</v>
+        <v>13.69</v>
       </c>
       <c r="M127" s="31" t="n">
-        <v>12.4</v>
+        <v>13.13</v>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
@@ -8520,16 +8520,16 @@
         </is>
       </c>
       <c r="O127" s="32" t="n">
-        <v>14.68</v>
+        <v>14.29</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>14.63</v>
+        <v>14.21</v>
       </c>
       <c r="Q127" s="33" t="n">
-        <v>14.48</v>
+        <v>14.5</v>
       </c>
       <c r="R127" s="34" t="n">
-        <v>3.13</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="128">
@@ -8544,37 +8544,37 @@
         </is>
       </c>
       <c r="C128" s="25" t="n">
-        <v>12.7</v>
+        <v>12.82</v>
       </c>
       <c r="D128" s="25" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="E128" s="26" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="F128" s="27" t="n">
         <v>12.2</v>
       </c>
-      <c r="E128" s="26" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="F128" s="27" t="n">
-        <v>12.06</v>
-      </c>
       <c r="G128" s="27" t="n">
-        <v>12.22</v>
+        <v>12.38</v>
       </c>
       <c r="H128" s="28" t="n">
-        <v>11.72</v>
+        <v>11.94</v>
       </c>
       <c r="I128" s="29" t="n">
-        <v>11.56</v>
+        <v>11.76</v>
       </c>
       <c r="J128" s="29" t="n">
-        <v>11.22</v>
+        <v>11.5</v>
       </c>
       <c r="K128" s="30" t="n">
-        <v>11.5</v>
+        <v>11.77</v>
       </c>
       <c r="L128" s="31" t="n">
-        <v>11.08</v>
+        <v>11.4</v>
       </c>
       <c r="M128" s="31" t="n">
-        <v>10.58</v>
+        <v>10.96</v>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
@@ -8582,16 +8582,16 @@
         </is>
       </c>
       <c r="O128" s="32" t="n">
-        <v>11.63</v>
+        <v>11.87</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>11.54</v>
+        <v>11.8</v>
       </c>
       <c r="Q128" s="33" t="n">
-        <v>11.89</v>
+        <v>12.03</v>
       </c>
       <c r="R128" s="34" t="n">
-        <v>5.13</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="129">
@@ -8606,54 +8606,54 @@
         </is>
       </c>
       <c r="C129" s="25" t="n">
-        <v>7.39</v>
+        <v>7.38</v>
       </c>
       <c r="D129" s="25" t="n">
-        <v>7.19</v>
+        <v>7.24</v>
       </c>
       <c r="E129" s="26" t="n">
-        <v>7.03</v>
+        <v>7.12</v>
       </c>
       <c r="F129" s="27" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="G129" s="27" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="H129" s="28" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I129" s="29" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="J129" s="29" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="K129" s="30" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="L129" s="31" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="M129" s="31" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="N129" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O129" s="32" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="P129" s="32" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="Q129" s="33" t="n">
         <v>7.13</v>
       </c>
-      <c r="G129" s="27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H129" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="I129" s="29" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="J129" s="29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K129" s="30" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="L129" s="31" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="M129" s="31" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="N129" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O129" s="32" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="P129" s="32" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="Q129" s="33" t="n">
-        <v>7.06</v>
-      </c>
       <c r="R129" s="34" t="n">
-        <v>2.92</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="130">
@@ -8668,37 +8668,37 @@
         </is>
       </c>
       <c r="C130" s="25" t="n">
-        <v>10.28</v>
+        <v>10.12</v>
       </c>
       <c r="D130" s="25" t="n">
-        <v>10.05</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E130" s="26" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="F130" s="27" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="F130" s="27" t="n">
-        <v>9.91</v>
-      </c>
       <c r="G130" s="27" t="n">
-        <v>10.02</v>
+        <v>9.94</v>
       </c>
       <c r="H130" s="28" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I130" s="29" t="n">
-        <v>9.68</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J130" s="29" t="n">
-        <v>9.56</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K130" s="30" t="n">
-        <v>9.73</v>
+        <v>9.74</v>
       </c>
       <c r="L130" s="31" t="n">
-        <v>9.539999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M130" s="31" t="n">
-        <v>9.31</v>
+        <v>9.44</v>
       </c>
       <c r="N130" s="20" t="inlineStr">
         <is>
@@ -8706,16 +8706,16 @@
         </is>
       </c>
       <c r="O130" s="32" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
       <c r="P130" s="32" t="n">
         <v>9.75</v>
       </c>
       <c r="Q130" s="33" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="R130" s="34" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="131">
@@ -8730,37 +8730,37 @@
         </is>
       </c>
       <c r="C131" s="25" t="n">
-        <v>146.41</v>
+        <v>137.74</v>
       </c>
       <c r="D131" s="25" t="n">
-        <v>139.11</v>
+        <v>134.44</v>
       </c>
       <c r="E131" s="26" t="n">
-        <v>132.99</v>
+        <v>131.67</v>
       </c>
       <c r="F131" s="27" t="n">
-        <v>135.3</v>
+        <v>131.3</v>
       </c>
       <c r="G131" s="27" t="n">
-        <v>138.6</v>
+        <v>133.5</v>
       </c>
       <c r="H131" s="28" t="n">
-        <v>131.3</v>
+        <v>130.2</v>
       </c>
       <c r="I131" s="29" t="n">
         <v>128</v>
       </c>
       <c r="J131" s="29" t="n">
-        <v>124</v>
+        <v>126.9</v>
       </c>
       <c r="K131" s="30" t="n">
-        <v>128.91</v>
+        <v>129.83</v>
       </c>
       <c r="L131" s="31" t="n">
-        <v>122.79</v>
+        <v>127.06</v>
       </c>
       <c r="M131" s="31" t="n">
-        <v>115.49</v>
+        <v>123.76</v>
       </c>
       <c r="N131" s="35" t="inlineStr">
         <is>
@@ -8768,16 +8768,16 @@
         </is>
       </c>
       <c r="O131" s="32" t="n">
-        <v>130.39</v>
+        <v>130.14</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>129.48</v>
+        <v>130.08</v>
       </c>
       <c r="Q131" s="33" t="n">
-        <v>132</v>
+        <v>129.1</v>
       </c>
       <c r="R131" s="36" t="n">
-        <v>-1.49</v>
+        <v>-3.66</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -686,7 +686,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-08-09</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>10942.52</v>
+        <v>10958.93</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10891.75</v>
+        <v>10901.81</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>10849.2</v>
+        <v>10853.94</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>10848.39</v>
+        <v>10871.6</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>10879.76</v>
+        <v>10897.61</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>10828.99</v>
+        <v>10840.49</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>10797.62</v>
+        <v>10814.48</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>10778.22</v>
+        <v>10783.37</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>10820.77</v>
+        <v>10821.96</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>10778.22</v>
+        <v>10774.09</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>10727.45</v>
+        <v>10716.97</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>10826.86</v>
+        <v>10833.45</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>10824.73</v>
+        <v>10826.41</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>10817.01</v>
+        <v>10845.58</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>0.9</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="4">
@@ -856,37 +856,37 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>20.69</v>
+        <v>20.74</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.57</v>
+        <v>20.59</v>
       </c>
       <c r="E4" s="26" t="n">
         <v>20.47</v>
       </c>
       <c r="F4" s="27" t="n">
-        <v>20.47</v>
+        <v>20.46</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>20.54</v>
+        <v>20.56</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>20.42</v>
+        <v>20.41</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>20.35</v>
+        <v>20.31</v>
       </c>
       <c r="J4" s="29" t="n">
-        <v>20.3</v>
+        <v>20.26</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>20.41</v>
+        <v>20.38</v>
       </c>
       <c r="L4" s="31" t="n">
-        <v>20.31</v>
+        <v>20.26</v>
       </c>
       <c r="M4" s="31" t="n">
-        <v>20.19</v>
+        <v>20.11</v>
       </c>
       <c r="N4" s="32" t="inlineStr">
         <is>
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="O4" s="33" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
       <c r="P4" s="33" t="n">
-        <v>20.42</v>
+        <v>20.39</v>
       </c>
       <c r="Q4" s="34" t="n">
-        <v>20.39</v>
+        <v>20.37</v>
       </c>
       <c r="R4" s="35" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="5">
@@ -918,54 +918,54 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>12.61</v>
+        <v>12.6</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>12.44</v>
+        <v>12.43</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>12.29</v>
+        <v>12.28</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>12.27</v>
+        <v>12.38</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>12.39</v>
+        <v>12.43</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>12.22</v>
+        <v>12.26</v>
       </c>
       <c r="I5" s="29" t="n">
-        <v>12.1</v>
+        <v>12.21</v>
       </c>
       <c r="J5" s="29" t="n">
-        <v>12.05</v>
+        <v>12.09</v>
       </c>
       <c r="K5" s="30" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="L5" s="31" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="M5" s="31" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O5" s="33" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="P5" s="33" t="n">
         <v>12.2</v>
       </c>
-      <c r="L5" s="31" t="n">
-        <v>12.05</v>
-      </c>
-      <c r="M5" s="31" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="N5" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O5" s="33" t="n">
-        <v>12.21</v>
-      </c>
-      <c r="P5" s="33" t="n">
-        <v>12.21</v>
-      </c>
       <c r="Q5" s="34" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="R5" s="35" t="n">
-        <v>-1.54</v>
+        <v>12.32</v>
+      </c>
+      <c r="R5" s="36" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="6">
@@ -980,54 +980,54 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="G6" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>13.83</v>
-      </c>
-      <c r="E6" s="26" t="n">
+      <c r="H6" s="28" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="I6" s="29" t="n">
         <v>13.68</v>
       </c>
-      <c r="F6" s="27" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>13.79</v>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="I6" s="29" t="n">
+      <c r="J6" s="29" t="n">
         <v>13.52</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="K6" s="30" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="L6" s="31" t="n">
         <v>13.45</v>
       </c>
-      <c r="K6" s="30" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="L6" s="31" t="n">
-        <v>13.44</v>
-      </c>
       <c r="M6" s="31" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="N6" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>13.21</v>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O6" s="33" t="n">
-        <v>13.61</v>
+        <v>13.72</v>
       </c>
       <c r="P6" s="33" t="n">
-        <v>13.6</v>
+        <v>13.67</v>
       </c>
       <c r="Q6" s="34" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="R6" s="35" t="n">
-        <v>-0.95</v>
+        <v>13.84</v>
+      </c>
+      <c r="R6" s="36" t="n">
+        <v>1.84</v>
       </c>
     </row>
     <row r="7">
@@ -1042,54 +1042,54 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>21.22</v>
+        <v>21.11</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>20.81</v>
+        <v>20.73</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>20.47</v>
+        <v>20.42</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>20.45</v>
+        <v>20.37</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>20.71</v>
+        <v>20.63</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>20.3</v>
+        <v>20.25</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>20.04</v>
+        <v>19.99</v>
       </c>
       <c r="J7" s="29" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="L7" s="31" t="n">
         <v>19.89</v>
       </c>
-      <c r="K7" s="30" t="n">
+      <c r="M7" s="31" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="N7" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O7" s="33" t="n">
         <v>20.24</v>
       </c>
-      <c r="L7" s="31" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M7" s="31" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="N7" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O7" s="33" t="n">
-        <v>20.29</v>
-      </c>
       <c r="P7" s="33" t="n">
-        <v>20.27</v>
+        <v>20.23</v>
       </c>
       <c r="Q7" s="34" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="R7" s="36" t="n">
-        <v>0.2</v>
+        <v>20.12</v>
+      </c>
+      <c r="R7" s="35" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="8">
@@ -1104,54 +1104,54 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>34.42</v>
+        <v>34.79</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>33.9</v>
+        <v>34.09</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>33.47</v>
+        <v>33.51</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>33.69</v>
+        <v>33.45</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>33.89</v>
+        <v>33.91</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>33.37</v>
+        <v>33.21</v>
       </c>
       <c r="I8" s="29" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="L8" s="31" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="M8" s="31" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="N8" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O8" s="33" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="P8" s="33" t="n">
         <v>33.17</v>
       </c>
-      <c r="J8" s="29" t="n">
-        <v>32.85</v>
-      </c>
-      <c r="K8" s="30" t="n">
-        <v>33.17</v>
-      </c>
-      <c r="L8" s="31" t="n">
-        <v>32.74</v>
-      </c>
-      <c r="M8" s="31" t="n">
-        <v>32.22</v>
-      </c>
-      <c r="N8" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O8" s="33" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="P8" s="33" t="n">
-        <v>33.21</v>
-      </c>
       <c r="Q8" s="34" t="n">
-        <v>33.48</v>
-      </c>
-      <c r="R8" s="36" t="n">
-        <v>1.21</v>
+        <v>33</v>
+      </c>
+      <c r="R8" s="35" t="n">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="9">
@@ -1175,19 +1175,19 @@
         <v>22.13</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>22.12</v>
+        <v>22.1</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>22.31</v>
+        <v>22.3</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>22</v>
+        <v>21.99</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>21.81</v>
+        <v>21.79</v>
       </c>
       <c r="J9" s="29" t="n">
-        <v>21.69</v>
+        <v>21.68</v>
       </c>
       <c r="K9" s="30" t="n">
         <v>21.96</v>
@@ -1210,10 +1210,10 @@
         <v>21.98</v>
       </c>
       <c r="Q9" s="34" t="n">
-        <v>21.92</v>
-      </c>
-      <c r="R9" s="36" t="n">
-        <v>0.09</v>
+        <v>21.89</v>
+      </c>
+      <c r="R9" s="35" t="n">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="10">
@@ -1228,54 +1228,54 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>126.92</v>
+        <v>126.75</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>123.32</v>
+        <v>122.95</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>120.31</v>
+        <v>119.76</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>120.1</v>
+        <v>121.27</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>122.4</v>
+        <v>122.83</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>118.8</v>
+        <v>119.03</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>116.5</v>
+        <v>117.47</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>115.2</v>
+        <v>115.23</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>118.29</v>
+        <v>117.64</v>
       </c>
       <c r="L10" s="31" t="n">
-        <v>115.28</v>
+        <v>114.45</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>111.68</v>
-      </c>
-      <c r="N10" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>110.65</v>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O10" s="33" t="n">
-        <v>118.69</v>
+        <v>118.48</v>
       </c>
       <c r="P10" s="33" t="n">
-        <v>118.57</v>
+        <v>117.93</v>
       </c>
       <c r="Q10" s="34" t="n">
-        <v>117.8</v>
-      </c>
-      <c r="R10" s="35" t="n">
-        <v>-2.24</v>
+        <v>119.7</v>
+      </c>
+      <c r="R10" s="36" t="n">
+        <v>1.61</v>
       </c>
     </row>
     <row r="11">
@@ -1290,54 +1290,54 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>65.83</v>
+        <v>65.64</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>65.38</v>
+        <v>65.09</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>65</v>
+        <v>64.63</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>65.02</v>
+        <v>64.63</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>65.28</v>
+        <v>64.97</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>64.83</v>
+        <v>64.42</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>64.56999999999999</v>
+        <v>64.08</v>
       </c>
       <c r="J11" s="29" t="n">
-        <v>64.38</v>
+        <v>63.87</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>64.75</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="L11" s="31" t="n">
-        <v>64.37</v>
+        <v>63.86</v>
       </c>
       <c r="M11" s="31" t="n">
-        <v>63.92</v>
-      </c>
-      <c r="N11" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>63.31</v>
+      </c>
+      <c r="N11" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O11" s="33" t="n">
-        <v>64.81</v>
+        <v>64.39</v>
       </c>
       <c r="P11" s="33" t="n">
-        <v>64.78</v>
+        <v>64.36</v>
       </c>
       <c r="Q11" s="34" t="n">
-        <v>64.75</v>
-      </c>
-      <c r="R11" s="36" t="n">
-        <v>0.31</v>
+        <v>64.3</v>
+      </c>
+      <c r="R11" s="35" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1352,54 +1352,54 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>25.33</v>
+        <v>25.24</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>25</v>
+        <v>24.92</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>24.73</v>
+        <v>24.65</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>24.77</v>
+        <v>24.8</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>24.95</v>
+        <v>24.92</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>24.62</v>
+        <v>24.6</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>24.44</v>
+        <v>24.48</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>24.29</v>
+        <v>24.28</v>
       </c>
       <c r="K12" s="30" t="n">
-        <v>24.54</v>
+        <v>24.47</v>
       </c>
       <c r="L12" s="31" t="n">
-        <v>24.27</v>
+        <v>24.2</v>
       </c>
       <c r="M12" s="31" t="n">
-        <v>23.94</v>
-      </c>
-      <c r="N12" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>23.88</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O12" s="33" t="n">
-        <v>24.59</v>
+        <v>24.55</v>
       </c>
       <c r="P12" s="33" t="n">
-        <v>24.57</v>
+        <v>24.5</v>
       </c>
       <c r="Q12" s="34" t="n">
-        <v>24.59</v>
-      </c>
-      <c r="R12" s="35" t="n">
-        <v>-0.36</v>
+        <v>24.68</v>
+      </c>
+      <c r="R12" s="36" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="13">
@@ -1414,54 +1414,54 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>24.2</v>
+        <v>24.63</v>
       </c>
       <c r="D13" s="25" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="H13" s="28" t="n">
         <v>24.09</v>
       </c>
-      <c r="E13" s="26" t="n">
-        <v>24</v>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>24.04</v>
-      </c>
-      <c r="G13" s="27" t="n">
+      <c r="I13" s="29" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="J13" s="29" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="L13" s="31" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="M13" s="31" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O13" s="33" t="n">
         <v>24.08</v>
       </c>
-      <c r="H13" s="28" t="n">
-        <v>23.97</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>23.93</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>23.86</v>
-      </c>
-      <c r="K13" s="30" t="n">
-        <v>23.93</v>
-      </c>
-      <c r="L13" s="31" t="n">
-        <v>23.84</v>
-      </c>
-      <c r="M13" s="31" t="n">
-        <v>23.73</v>
-      </c>
-      <c r="N13" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O13" s="33" t="n">
-        <v>23.96</v>
-      </c>
       <c r="P13" s="33" t="n">
-        <v>23.94</v>
+        <v>24.07</v>
       </c>
       <c r="Q13" s="34" t="n">
-        <v>23.99</v>
+        <v>24.03</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="14">
@@ -1476,54 +1476,54 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>41.65</v>
+        <v>42.1</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>41.35</v>
+        <v>41.62</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>41.09</v>
+        <v>41.21</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>41.22</v>
+        <v>41.27</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>41.34</v>
+        <v>41.53</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>41.04</v>
+        <v>41.05</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>40.92</v>
+        <v>40.79</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>40.74</v>
+        <v>40.57</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>40.93</v>
+        <v>40.95</v>
       </c>
       <c r="L14" s="31" t="n">
-        <v>40.67</v>
+        <v>40.54</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>40.37</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>40.06</v>
+      </c>
+      <c r="N14" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O14" s="33" t="n">
-        <v>40.99</v>
+        <v>41.02</v>
       </c>
       <c r="P14" s="33" t="n">
-        <v>40.95</v>
+        <v>40.98</v>
       </c>
       <c r="Q14" s="34" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="R14" s="36" t="n">
-        <v>0.59</v>
+        <v>41</v>
+      </c>
+      <c r="R14" s="35" t="n">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="15">
@@ -1538,54 +1538,54 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>9.69</v>
+        <v>9.43</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>9.369999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>9.1</v>
+        <v>8.99</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>9.19</v>
+        <v>9</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>9.34</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H15" s="28" t="n">
-        <v>9.02</v>
+        <v>8.9</v>
       </c>
       <c r="I15" s="29" t="n">
-        <v>8.869999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="J15" s="29" t="n">
-        <v>8.699999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="K15" s="30" t="n">
-        <v>8.92</v>
+        <v>8.85</v>
       </c>
       <c r="L15" s="31" t="n">
         <v>8.65</v>
       </c>
       <c r="M15" s="31" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="N15" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>8.41</v>
+      </c>
+      <c r="N15" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O15" s="33" t="n">
-        <v>8.98</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="P15" s="33" t="n">
-        <v>8.949999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="Q15" s="34" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="R15" s="36" t="n">
-        <v>0.89</v>
+        <v>8.859999999999999</v>
+      </c>
+      <c r="R15" s="35" t="n">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="16">
@@ -1600,37 +1600,37 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>15</v>
+        <v>15.01</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.85</v>
+        <v>14.78</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>14.73</v>
+        <v>14.59</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>14.74</v>
+        <v>14.66</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>14.82</v>
+        <v>14.76</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>14.67</v>
+        <v>14.53</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>14.59</v>
+        <v>14.43</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>14.52</v>
+        <v>14.3</v>
       </c>
       <c r="K16" s="30" t="n">
-        <v>14.64</v>
+        <v>14.46</v>
       </c>
       <c r="L16" s="31" t="n">
-        <v>14.52</v>
+        <v>14.27</v>
       </c>
       <c r="M16" s="31" t="n">
-        <v>14.37</v>
+        <v>14.04</v>
       </c>
       <c r="N16" s="32" t="inlineStr">
         <is>
@@ -1638,16 +1638,16 @@
         </is>
       </c>
       <c r="O16" s="33" t="n">
-        <v>14.66</v>
+        <v>14.51</v>
       </c>
       <c r="P16" s="33" t="n">
-        <v>14.65</v>
+        <v>14.48</v>
       </c>
       <c r="Q16" s="34" t="n">
-        <v>14.65</v>
+        <v>14.55</v>
       </c>
       <c r="R16" s="35" t="n">
-        <v>-0.41</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="17">
@@ -1662,54 +1662,54 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>5.62</v>
+        <v>5.14</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>5.3</v>
+        <v>4.99</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>5.03</v>
+        <v>4.87</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>5.07</v>
+        <v>4.85</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="I17" s="29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="L17" s="31" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="M17" s="31" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="N17" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O17" s="33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P17" s="33" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="Q17" s="34" t="n">
         <v>4.75</v>
       </c>
-      <c r="J17" s="29" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="K17" s="30" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="L17" s="31" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="M17" s="31" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O17" s="33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P17" s="33" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="Q17" s="34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R17" s="36" t="n">
-        <v>1.87</v>
+      <c r="R17" s="35" t="n">
+        <v>-3.06</v>
       </c>
     </row>
     <row r="18">
@@ -1724,37 +1724,37 @@
         </is>
       </c>
       <c r="C18" s="25" t="n">
-        <v>18.43</v>
+        <v>18.46</v>
       </c>
       <c r="D18" s="25" t="n">
         <v>17.95</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>17.54</v>
+        <v>17.52</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>17.58</v>
+        <v>17.79</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>17.85</v>
+        <v>17.96</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>17.37</v>
+        <v>17.45</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>17.1</v>
+        <v>17.28</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>16.89</v>
+        <v>16.94</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>17.28</v>
+        <v>17.23</v>
       </c>
       <c r="L18" s="31" t="n">
-        <v>16.87</v>
+        <v>16.8</v>
       </c>
       <c r="M18" s="31" t="n">
-        <v>16.39</v>
+        <v>16.29</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
@@ -1762,16 +1762,16 @@
         </is>
       </c>
       <c r="O18" s="33" t="n">
-        <v>17.34</v>
+        <v>17.36</v>
       </c>
       <c r="P18" s="33" t="n">
-        <v>17.31</v>
+        <v>17.27</v>
       </c>
       <c r="Q18" s="34" t="n">
-        <v>17.3</v>
+        <v>17.61</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>0.17</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="19">
@@ -1786,37 +1786,37 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>26.63</v>
+        <v>26.05</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>25.93</v>
+        <v>25.65</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>25.35</v>
+        <v>25.31</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>25.67</v>
+        <v>25.44</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>25.93</v>
+        <v>25.62</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>25.23</v>
+        <v>25.22</v>
       </c>
       <c r="I19" s="29" t="n">
-        <v>24.97</v>
+        <v>25.04</v>
       </c>
       <c r="J19" s="29" t="n">
-        <v>24.53</v>
+        <v>24.82</v>
       </c>
       <c r="K19" s="30" t="n">
-        <v>24.95</v>
+        <v>25.09</v>
       </c>
       <c r="L19" s="31" t="n">
-        <v>24.37</v>
+        <v>24.75</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>23.67</v>
+        <v>24.35</v>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         </is>
       </c>
       <c r="O19" s="33" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="P19" s="33" t="n">
         <v>25.12</v>
       </c>
-      <c r="P19" s="33" t="n">
-        <v>25.01</v>
-      </c>
       <c r="Q19" s="34" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="R19" s="36" t="n">
-        <v>1.6</v>
+        <v>25.26</v>
+      </c>
+      <c r="R19" s="35" t="n">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="20">
@@ -1848,37 +1848,37 @@
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>65.42</v>
+        <v>70.88</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>63.52</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>61.93</v>
+        <v>65</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>62.48</v>
+        <v>66.23</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>63.37</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>61.47</v>
+        <v>64.37</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>60.58</v>
+        <v>63.03</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>59.57</v>
+        <v>61.17</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>60.87</v>
+        <v>63.2</v>
       </c>
       <c r="L20" s="31" t="n">
-        <v>59.28</v>
+        <v>60.52</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>57.38</v>
+        <v>57.32</v>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="O20" s="33" t="n">
-        <v>61.24</v>
+        <v>63.91</v>
       </c>
       <c r="P20" s="33" t="n">
-        <v>61.02</v>
+        <v>63.45</v>
       </c>
       <c r="Q20" s="34" t="n">
-        <v>61.6</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>1.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="21">
@@ -1910,54 +1910,54 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>13.32</v>
+        <v>12.96</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>12.91</v>
+        <v>12.55</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>12.57</v>
+        <v>12.21</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>12.58</v>
+        <v>12.29</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>12.83</v>
+        <v>12.5</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>12.42</v>
+        <v>12.09</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>12.17</v>
+        <v>11.88</v>
       </c>
       <c r="J21" s="29" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="K21" s="30" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="L21" s="31" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="M21" s="31" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="N21" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O21" s="33" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="P21" s="33" t="n">
         <v>12.01</v>
       </c>
-      <c r="K21" s="30" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="L21" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="M21" s="31" t="n">
-        <v>11.59</v>
-      </c>
-      <c r="N21" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O21" s="33" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="P21" s="33" t="n">
-        <v>12.37</v>
-      </c>
       <c r="Q21" s="34" t="n">
-        <v>12.34</v>
+        <v>12.08</v>
       </c>
       <c r="R21" s="35" t="n">
-        <v>-2.14</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="22">
@@ -1972,37 +1972,37 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>18.77</v>
+        <v>18.82</v>
       </c>
       <c r="D22" s="25" t="n">
         <v>18.47</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>18.21</v>
+        <v>18.17</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>18.24</v>
+        <v>18.13</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>18.41</v>
+        <v>18.37</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.11</v>
+        <v>18.02</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>17.94</v>
+        <v>17.78</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>17.81</v>
+        <v>17.67</v>
       </c>
       <c r="K22" s="30" t="n">
-        <v>18.05</v>
+        <v>17.98</v>
       </c>
       <c r="L22" s="31" t="n">
-        <v>17.79</v>
+        <v>17.68</v>
       </c>
       <c r="M22" s="31" t="n">
-        <v>17.49</v>
+        <v>17.33</v>
       </c>
       <c r="N22" s="32" t="inlineStr">
         <is>
@@ -2010,16 +2010,16 @@
         </is>
       </c>
       <c r="O22" s="33" t="n">
-        <v>18.09</v>
+        <v>18.01</v>
       </c>
       <c r="P22" s="33" t="n">
-        <v>18.07</v>
+        <v>18</v>
       </c>
       <c r="Q22" s="34" t="n">
-        <v>18.07</v>
+        <v>17.9</v>
       </c>
       <c r="R22" s="35" t="n">
-        <v>-0.88</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2034,37 +2034,37 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>37.98</v>
+        <v>35.81</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>36.46</v>
+        <v>34.95</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>35.19</v>
+        <v>34.23</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>35.15</v>
+        <v>34.43</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>36.09</v>
+        <v>34.85</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>34.57</v>
+        <v>33.99</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>33.63</v>
+        <v>33.57</v>
       </c>
       <c r="J23" s="29" t="n">
-        <v>33.05</v>
+        <v>33.13</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>34.33</v>
+        <v>33.75</v>
       </c>
       <c r="L23" s="31" t="n">
-        <v>33.06</v>
+        <v>33.03</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>31.54</v>
+        <v>32.17</v>
       </c>
       <c r="N23" s="32" t="inlineStr">
         <is>
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="O23" s="33" t="n">
-        <v>34.51</v>
+        <v>33.9</v>
       </c>
       <c r="P23" s="33" t="n">
-        <v>34.45</v>
+        <v>33.82</v>
       </c>
       <c r="Q23" s="34" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="R23" s="35" t="n">
-        <v>-3.12</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="24">
@@ -2096,54 +2096,54 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>15.82</v>
+        <v>15.99</v>
       </c>
       <c r="D24" s="25" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="F24" s="27" t="n">
         <v>15.43</v>
       </c>
-      <c r="E24" s="26" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>15.14</v>
-      </c>
       <c r="G24" s="27" t="n">
-        <v>15.36</v>
+        <v>15.57</v>
       </c>
       <c r="H24" s="28" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="J24" s="29" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="K24" s="30" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="L24" s="31" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="M24" s="31" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O24" s="33" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="P24" s="33" t="n">
         <v>14.97</v>
       </c>
-      <c r="I24" s="29" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="J24" s="29" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="K24" s="30" t="n">
-        <v>14.89</v>
-      </c>
-      <c r="L24" s="31" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="M24" s="31" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="N24" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O24" s="33" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="P24" s="33" t="n">
-        <v>14.92</v>
-      </c>
       <c r="Q24" s="34" t="n">
-        <v>14.92</v>
+        <v>15.28</v>
       </c>
       <c r="R24" s="36" t="n">
-        <v>0.13</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="25">
@@ -2158,37 +2158,37 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>45.41</v>
+        <v>41.03</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>42.87</v>
+        <v>39.81</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>40.74</v>
+        <v>38.79</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>40.57</v>
+        <v>38.81</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>42.21</v>
+        <v>39.55</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>39.67</v>
+        <v>38.33</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>38.03</v>
+        <v>37.59</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>37.13</v>
+        <v>37.11</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>39.32</v>
+        <v>38.11</v>
       </c>
       <c r="L25" s="31" t="n">
-        <v>37.19</v>
+        <v>37.09</v>
       </c>
       <c r="M25" s="31" t="n">
-        <v>34.65</v>
+        <v>35.87</v>
       </c>
       <c r="N25" s="32" t="inlineStr">
         <is>
@@ -2196,16 +2196,16 @@
         </is>
       </c>
       <c r="O25" s="33" t="n">
-        <v>39.59</v>
+        <v>38.27</v>
       </c>
       <c r="P25" s="33" t="n">
-        <v>39.52</v>
+        <v>38.2</v>
       </c>
       <c r="Q25" s="34" t="n">
-        <v>38.94</v>
+        <v>38.08</v>
       </c>
       <c r="R25" s="35" t="n">
-        <v>-1.67</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="26">
@@ -2220,54 +2220,54 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>49.87</v>
+        <v>49.64</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>48.47</v>
+        <v>48.32</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>47.29</v>
+        <v>47.21</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>47.33</v>
+        <v>47.78</v>
       </c>
       <c r="G26" s="27" t="n">
-        <v>48.17</v>
+        <v>48.3</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>46.77</v>
+        <v>46.98</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>45.93</v>
+        <v>46.46</v>
       </c>
       <c r="J26" s="29" t="n">
-        <v>45.37</v>
+        <v>45.66</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>46.51</v>
+        <v>46.47</v>
       </c>
       <c r="L26" s="31" t="n">
-        <v>45.33</v>
+        <v>45.36</v>
       </c>
       <c r="M26" s="31" t="n">
-        <v>43.93</v>
-      </c>
-      <c r="N26" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>44.04</v>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O26" s="33" t="n">
-        <v>46.69</v>
+        <v>46.78</v>
       </c>
       <c r="P26" s="33" t="n">
-        <v>46.62</v>
+        <v>46.57</v>
       </c>
       <c r="Q26" s="34" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="R26" s="35" t="n">
-        <v>-2.31</v>
+        <v>47.26</v>
+      </c>
+      <c r="R26" s="36" t="n">
+        <v>1.63</v>
       </c>
     </row>
     <row r="27">
@@ -2282,37 +2282,37 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>201.47</v>
+        <v>204.91</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>197.47</v>
+        <v>199.71</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>194.12</v>
+        <v>195.36</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>194.33</v>
+        <v>197.1</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>196.67</v>
+        <v>199.4</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>192.67</v>
+        <v>194.2</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>190.33</v>
+        <v>191.9</v>
       </c>
       <c r="J27" s="29" t="n">
-        <v>188.67</v>
+        <v>189</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>191.88</v>
+        <v>192.44</v>
       </c>
       <c r="L27" s="31" t="n">
-        <v>188.53</v>
+        <v>188.09</v>
       </c>
       <c r="M27" s="31" t="n">
-        <v>184.53</v>
+        <v>182.89</v>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="O27" s="33" t="n">
-        <v>192.43</v>
+        <v>193.52</v>
       </c>
       <c r="P27" s="33" t="n">
-        <v>192.19</v>
+        <v>192.85</v>
       </c>
       <c r="Q27" s="34" t="n">
-        <v>192</v>
+        <v>194.8</v>
       </c>
       <c r="R27" s="36" t="n">
-        <v>0.37</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="28">
@@ -2344,37 +2344,37 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>86.14</v>
+        <v>87.27</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>83.48999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>81.27</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>82.17</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>83.33</v>
+        <v>84.3</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>80.68000000000001</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>79.52</v>
+        <v>80.2</v>
       </c>
       <c r="J28" s="29" t="n">
-        <v>78.03</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>79.78</v>
+        <v>80.2</v>
       </c>
       <c r="L28" s="31" t="n">
-        <v>77.56</v>
+        <v>77.73</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>74.91</v>
+        <v>74.78</v>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="O28" s="33" t="n">
-        <v>80.34</v>
+        <v>80.89</v>
       </c>
       <c r="P28" s="33" t="n">
-        <v>79.98999999999999</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="Q28" s="34" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R28" s="36" t="n">
-        <v>3.45</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="29">
@@ -2406,54 +2406,54 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>20.65</v>
+        <v>22.69</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>20.37</v>
+        <v>21.71</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>20.14</v>
+        <v>20.88</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>20.11</v>
+        <v>20.83</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>20.3</v>
+        <v>21.45</v>
       </c>
       <c r="H29" s="28" t="n">
-        <v>20.02</v>
+        <v>20.47</v>
       </c>
       <c r="I29" s="29" t="n">
-        <v>19.83</v>
+        <v>19.85</v>
       </c>
       <c r="J29" s="29" t="n">
-        <v>19.74</v>
+        <v>19.49</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>19.98</v>
+        <v>20.34</v>
       </c>
       <c r="L29" s="31" t="n">
-        <v>19.75</v>
+        <v>19.51</v>
       </c>
       <c r="M29" s="31" t="n">
-        <v>19.47</v>
-      </c>
-      <c r="N29" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>18.53</v>
+      </c>
+      <c r="N29" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O29" s="33" t="n">
-        <v>20.01</v>
+        <v>20.44</v>
       </c>
       <c r="P29" s="33" t="n">
-        <v>20</v>
+        <v>20.41</v>
       </c>
       <c r="Q29" s="34" t="n">
-        <v>19.93</v>
-      </c>
-      <c r="R29" s="35" t="n">
-        <v>-0.4</v>
+        <v>20.2</v>
+      </c>
+      <c r="R29" s="36" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="30">
@@ -2468,37 +2468,37 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>86.69</v>
+        <v>84.06</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>84.44</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>82.56</v>
+        <v>80.75</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>82.67</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>83.98</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>81.73</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>80.42</v>
+        <v>79.05</v>
       </c>
       <c r="J30" s="29" t="n">
-        <v>79.48</v>
+        <v>78.3</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>81.3</v>
+        <v>79.75</v>
       </c>
       <c r="L30" s="31" t="n">
-        <v>79.41</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>77.16</v>
+        <v>76.44</v>
       </c>
       <c r="N30" s="32" t="inlineStr">
         <is>
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="O30" s="33" t="n">
-        <v>81.59999999999999</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="P30" s="33" t="n">
-        <v>81.47</v>
+        <v>79.89</v>
       </c>
       <c r="Q30" s="34" t="n">
-        <v>81.34999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="R30" s="35" t="n">
-        <v>-2.05</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="31">
@@ -2530,37 +2530,37 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>32.27</v>
+        <v>32.33</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>31.61</v>
+        <v>31.21</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>31.05</v>
+        <v>30.27</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>30.98</v>
+        <v>30.2</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>31.42</v>
+        <v>30.92</v>
       </c>
       <c r="H31" s="28" t="n">
-        <v>30.76</v>
+        <v>29.8</v>
       </c>
       <c r="I31" s="29" t="n">
-        <v>30.32</v>
+        <v>29.08</v>
       </c>
       <c r="J31" s="29" t="n">
-        <v>30.1</v>
+        <v>28.68</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>30.69</v>
+        <v>29.65</v>
       </c>
       <c r="L31" s="31" t="n">
-        <v>30.13</v>
+        <v>28.71</v>
       </c>
       <c r="M31" s="31" t="n">
-        <v>29.47</v>
+        <v>27.59</v>
       </c>
       <c r="N31" s="32" t="inlineStr">
         <is>
@@ -2568,16 +2568,16 @@
         </is>
       </c>
       <c r="O31" s="33" t="n">
-        <v>30.75</v>
+        <v>29.77</v>
       </c>
       <c r="P31" s="33" t="n">
-        <v>30.74</v>
+        <v>29.73</v>
       </c>
       <c r="Q31" s="34" t="n">
-        <v>30.54</v>
+        <v>29.48</v>
       </c>
       <c r="R31" s="35" t="n">
-        <v>-1.99</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="32">
@@ -2592,54 +2592,54 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>52.35</v>
+        <v>52.03</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>51.7</v>
+        <v>51.58</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>51.16</v>
+        <v>51.2</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>51.42</v>
+        <v>51.25</v>
       </c>
       <c r="G32" s="27" t="n">
-        <v>51.68</v>
+        <v>51.5</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>51.03</v>
+        <v>51.05</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>50.77</v>
+        <v>50.8</v>
       </c>
       <c r="J32" s="29" t="n">
-        <v>50.38</v>
+        <v>50.6</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>50.79</v>
+        <v>50.95</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>50.25</v>
+        <v>50.57</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="N32" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>50.12</v>
+      </c>
+      <c r="N32" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O32" s="33" t="n">
-        <v>50.94</v>
+        <v>51.02</v>
       </c>
       <c r="P32" s="33" t="n">
-        <v>50.84</v>
+        <v>50.98</v>
       </c>
       <c r="Q32" s="34" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="R32" s="36" t="n">
-        <v>1.19</v>
+        <v>51</v>
+      </c>
+      <c r="R32" s="35" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="33">
@@ -2654,37 +2654,37 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>130.5</v>
+        <v>132.44</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>127.1</v>
+        <v>129.14</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>124.25</v>
+        <v>126.37</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>125.73</v>
+        <v>126</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>127.07</v>
+        <v>128.2</v>
       </c>
       <c r="H33" s="28" t="n">
-        <v>123.67</v>
+        <v>124.9</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>122.33</v>
+        <v>122.7</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>120.27</v>
+        <v>121.6</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>122.35</v>
+        <v>124.53</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>119.5</v>
+        <v>121.76</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>116.1</v>
+        <v>118.46</v>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
@@ -2692,16 +2692,16 @@
         </is>
       </c>
       <c r="O33" s="33" t="n">
-        <v>123.14</v>
+        <v>124.84</v>
       </c>
       <c r="P33" s="33" t="n">
-        <v>122.61</v>
+        <v>124.78</v>
       </c>
       <c r="Q33" s="34" t="n">
-        <v>124.4</v>
-      </c>
-      <c r="R33" s="36" t="n">
-        <v>2.3</v>
+        <v>123.8</v>
+      </c>
+      <c r="R33" s="35" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="34">
@@ -2716,54 +2716,54 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>50.05</v>
+        <v>50.04</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>49.03</v>
+        <v>48.88</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>48.18</v>
+        <v>47.9</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>48.13</v>
+        <v>48.37</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>48.77</v>
+        <v>48.85</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>47.75</v>
+        <v>47.69</v>
       </c>
       <c r="I34" s="29" t="n">
-        <v>47.11</v>
+        <v>47.21</v>
       </c>
       <c r="J34" s="29" t="n">
-        <v>46.73</v>
+        <v>46.53</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>47.6</v>
+        <v>47.26</v>
       </c>
       <c r="L34" s="31" t="n">
-        <v>46.75</v>
+        <v>46.28</v>
       </c>
       <c r="M34" s="31" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="N34" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>45.12</v>
+      </c>
+      <c r="N34" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O34" s="33" t="n">
-        <v>47.72</v>
+        <v>47.52</v>
       </c>
       <c r="P34" s="33" t="n">
-        <v>47.68</v>
+        <v>47.35</v>
       </c>
       <c r="Q34" s="34" t="n">
-        <v>47.48</v>
-      </c>
-      <c r="R34" s="35" t="n">
-        <v>-0.38</v>
+        <v>47.9</v>
+      </c>
+      <c r="R34" s="36" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="35">
@@ -2778,37 +2778,37 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>25.81</v>
+        <v>25.54</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>25.51</v>
+        <v>25.22</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>25.25</v>
+        <v>24.95</v>
       </c>
       <c r="F35" s="27" t="n">
-        <v>25.22</v>
+        <v>24.91</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>25.42</v>
+        <v>25.13</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>25.12</v>
+        <v>24.81</v>
       </c>
       <c r="I35" s="29" t="n">
-        <v>24.92</v>
+        <v>24.59</v>
       </c>
       <c r="J35" s="29" t="n">
-        <v>24.82</v>
+        <v>24.49</v>
       </c>
       <c r="K35" s="30" t="n">
-        <v>25.09</v>
+        <v>24.77</v>
       </c>
       <c r="L35" s="31" t="n">
-        <v>24.83</v>
+        <v>24.5</v>
       </c>
       <c r="M35" s="31" t="n">
-        <v>24.53</v>
+        <v>24.18</v>
       </c>
       <c r="N35" s="32" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="O35" s="33" t="n">
-        <v>25.11</v>
+        <v>24.8</v>
       </c>
       <c r="P35" s="33" t="n">
-        <v>25.11</v>
+        <v>24.8</v>
       </c>
       <c r="Q35" s="34" t="n">
-        <v>25.02</v>
+        <v>24.7</v>
       </c>
       <c r="R35" s="35" t="n">
-        <v>-1.03</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="36">
@@ -2840,54 +2840,54 @@
         </is>
       </c>
       <c r="C36" s="25" t="n">
-        <v>27.44</v>
+        <v>27.57</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>26.8</v>
+        <v>26.97</v>
       </c>
       <c r="E36" s="26" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="H36" s="28" t="n">
         <v>26.26</v>
       </c>
-      <c r="F36" s="27" t="n">
-        <v>26.29</v>
-      </c>
-      <c r="G36" s="27" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="H36" s="28" t="n">
-        <v>26.03</v>
-      </c>
       <c r="I36" s="29" t="n">
-        <v>25.65</v>
+        <v>25.92</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>25.39</v>
+        <v>25.66</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>25.9</v>
+        <v>26.13</v>
       </c>
       <c r="L36" s="31" t="n">
-        <v>25.36</v>
+        <v>25.63</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>24.72</v>
-      </c>
-      <c r="N36" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>25.03</v>
+      </c>
+      <c r="N36" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O36" s="33" t="n">
-        <v>25.99</v>
+        <v>26.22</v>
       </c>
       <c r="P36" s="33" t="n">
-        <v>25.95</v>
+        <v>26.18</v>
       </c>
       <c r="Q36" s="34" t="n">
-        <v>25.92</v>
-      </c>
-      <c r="R36" s="35" t="n">
-        <v>-1.44</v>
+        <v>26.18</v>
+      </c>
+      <c r="R36" s="36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2902,54 +2902,54 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>9.449999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>9.050000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="E37" s="26" t="n">
-        <v>8.710000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="F37" s="27" t="n">
-        <v>8.720000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>8.960000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>8.56</v>
+        <v>8.58</v>
       </c>
       <c r="I37" s="29" t="n">
-        <v>8.32</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="J37" s="29" t="n">
-        <v>8.16</v>
+        <v>8.31</v>
       </c>
       <c r="K37" s="30" t="n">
         <v>8.49</v>
       </c>
       <c r="L37" s="31" t="n">
-        <v>8.15</v>
+        <v>8.26</v>
       </c>
       <c r="M37" s="31" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="N37" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>7.99</v>
+      </c>
+      <c r="N37" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O37" s="33" t="n">
-        <v>8.539999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P37" s="33" t="n">
-        <v>8.52</v>
+        <v>8.51</v>
       </c>
       <c r="Q37" s="34" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="R37" s="35" t="n">
-        <v>-4.07</v>
+        <v>8.619999999999999</v>
+      </c>
+      <c r="R37" s="36" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="38">
@@ -2964,54 +2964,54 @@
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>32.86</v>
+        <v>32.48</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>32.08</v>
+        <v>31.84</v>
       </c>
       <c r="E38" s="26" t="n">
-        <v>31.43</v>
+        <v>31.3</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>31.43</v>
+        <v>31.65</v>
       </c>
       <c r="G38" s="27" t="n">
-        <v>31.91</v>
+        <v>31.87</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>31.13</v>
+        <v>31.23</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>30.65</v>
+        <v>31.01</v>
       </c>
       <c r="J38" s="29" t="n">
-        <v>30.35</v>
+        <v>30.59</v>
       </c>
       <c r="K38" s="30" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="L38" s="31" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="M38" s="31" t="n">
+        <v>29.76</v>
+      </c>
+      <c r="N38" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O38" s="33" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="P38" s="33" t="n">
         <v>30.99</v>
       </c>
-      <c r="L38" s="31" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="M38" s="31" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="N38" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O38" s="33" t="n">
-        <v>31.09</v>
-      </c>
-      <c r="P38" s="33" t="n">
-        <v>31.05</v>
-      </c>
       <c r="Q38" s="34" t="n">
-        <v>30.96</v>
-      </c>
-      <c r="R38" s="35" t="n">
-        <v>-1.53</v>
+        <v>31.44</v>
+      </c>
+      <c r="R38" s="36" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="39">
@@ -3026,54 +3026,54 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>197.83</v>
+        <v>198.52</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>192.93</v>
+        <v>192.02</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>188.82</v>
+        <v>186.57</v>
       </c>
       <c r="F39" s="27" t="n">
-        <v>188.27</v>
+        <v>189.57</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>191.53</v>
+        <v>192.03</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>186.63</v>
+        <v>185.53</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>183.37</v>
+        <v>183.07</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>181.73</v>
+        <v>179.03</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>186.08</v>
+        <v>182.93</v>
       </c>
       <c r="L39" s="31" t="n">
-        <v>181.97</v>
+        <v>177.48</v>
       </c>
       <c r="M39" s="31" t="n">
-        <v>177.07</v>
-      </c>
-      <c r="N39" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>170.98</v>
+      </c>
+      <c r="N39" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O39" s="33" t="n">
-        <v>186.55</v>
+        <v>184.49</v>
       </c>
       <c r="P39" s="33" t="n">
-        <v>186.46</v>
+        <v>183.44</v>
       </c>
       <c r="Q39" s="34" t="n">
-        <v>185</v>
-      </c>
-      <c r="R39" s="35" t="n">
-        <v>-4.15</v>
+        <v>187.1</v>
+      </c>
+      <c r="R39" s="36" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="40">
@@ -3088,37 +3088,37 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>14.76</v>
+        <v>14.35</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>14.44</v>
+        <v>14.14</v>
       </c>
       <c r="E40" s="26" t="n">
-        <v>14.17</v>
+        <v>13.96</v>
       </c>
       <c r="F40" s="27" t="n">
-        <v>14.15</v>
+        <v>13.99</v>
       </c>
       <c r="G40" s="27" t="n">
-        <v>14.35</v>
+        <v>14.11</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>14.03</v>
+        <v>13.9</v>
       </c>
       <c r="I40" s="29" t="n">
-        <v>13.83</v>
+        <v>13.78</v>
       </c>
       <c r="J40" s="29" t="n">
-        <v>13.71</v>
+        <v>13.69</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>13.99</v>
+        <v>13.85</v>
       </c>
       <c r="L40" s="31" t="n">
-        <v>13.72</v>
+        <v>13.67</v>
       </c>
       <c r="M40" s="31" t="n">
-        <v>13.4</v>
+        <v>13.46</v>
       </c>
       <c r="N40" s="32" t="inlineStr">
         <is>
@@ -3126,16 +3126,16 @@
         </is>
       </c>
       <c r="O40" s="33" t="n">
-        <v>14.02</v>
+        <v>13.88</v>
       </c>
       <c r="P40" s="33" t="n">
-        <v>14.02</v>
+        <v>13.86</v>
       </c>
       <c r="Q40" s="34" t="n">
-        <v>13.94</v>
+        <v>13.88</v>
       </c>
       <c r="R40" s="35" t="n">
-        <v>-1.62</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="41">
@@ -3150,54 +3150,54 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>21.93</v>
+        <v>23.29</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>21.67</v>
+        <v>22.42</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>21.45</v>
+        <v>21.69</v>
       </c>
       <c r="F41" s="27" t="n">
-        <v>21.46</v>
+        <v>21.84</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>21.61</v>
+        <v>22.3</v>
       </c>
       <c r="H41" s="28" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="I41" s="29" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="J41" s="29" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="K41" s="30" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="L41" s="31" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="M41" s="31" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N41" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O41" s="33" t="n">
         <v>21.35</v>
       </c>
-      <c r="I41" s="29" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J41" s="29" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K41" s="30" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="L41" s="31" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="M41" s="31" t="n">
-        <v>20.83</v>
-      </c>
-      <c r="N41" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O41" s="33" t="n">
-        <v>21.34</v>
-      </c>
       <c r="P41" s="33" t="n">
-        <v>21.33</v>
+        <v>21.27</v>
       </c>
       <c r="Q41" s="34" t="n">
-        <v>21.3</v>
+        <v>21.39</v>
       </c>
       <c r="R41" s="36" t="n">
-        <v>0.24</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="42">
@@ -3212,37 +3212,37 @@
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>188.43</v>
+        <v>189.64</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>178.83</v>
+        <v>182.94</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>170.79</v>
+        <v>177.33</v>
       </c>
       <c r="F42" s="27" t="n">
-        <v>175.57</v>
+        <v>178.63</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>179.03</v>
+        <v>182.07</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>169.43</v>
+        <v>175.37</v>
       </c>
       <c r="I42" s="29" t="n">
-        <v>165.97</v>
+        <v>171.93</v>
       </c>
       <c r="J42" s="29" t="n">
-        <v>159.83</v>
+        <v>168.67</v>
       </c>
       <c r="K42" s="30" t="n">
-        <v>165.41</v>
+        <v>173.57</v>
       </c>
       <c r="L42" s="31" t="n">
-        <v>157.37</v>
+        <v>167.96</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>147.77</v>
+        <v>161.26</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
@@ -3250,16 +3250,16 @@
         </is>
       </c>
       <c r="O42" s="33" t="n">
-        <v>167.8</v>
+        <v>174.73</v>
       </c>
       <c r="P42" s="33" t="n">
-        <v>166.16</v>
+        <v>174.1</v>
       </c>
       <c r="Q42" s="34" t="n">
-        <v>172.1</v>
+        <v>175.2</v>
       </c>
       <c r="R42" s="36" t="n">
-        <v>4.18</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="43">
@@ -3274,37 +3274,37 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>37.78</v>
+        <v>37.74</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>37.42</v>
+        <v>37.28</v>
       </c>
       <c r="E43" s="26" t="n">
-        <v>37.12</v>
+        <v>36.9</v>
       </c>
       <c r="F43" s="27" t="n">
-        <v>37.08</v>
+        <v>36.94</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>37.32</v>
+        <v>37.2</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>36.96</v>
+        <v>36.74</v>
       </c>
       <c r="I43" s="29" t="n">
-        <v>36.72</v>
+        <v>36.48</v>
       </c>
       <c r="J43" s="29" t="n">
-        <v>36.6</v>
+        <v>36.28</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>36.92</v>
+        <v>36.64</v>
       </c>
       <c r="L43" s="31" t="n">
-        <v>36.62</v>
+        <v>36.26</v>
       </c>
       <c r="M43" s="31" t="n">
-        <v>36.26</v>
+        <v>35.8</v>
       </c>
       <c r="N43" s="32" t="inlineStr">
         <is>
@@ -3312,16 +3312,16 @@
         </is>
       </c>
       <c r="O43" s="33" t="n">
-        <v>36.95</v>
+        <v>36.71</v>
       </c>
       <c r="P43" s="33" t="n">
-        <v>36.95</v>
+        <v>36.68</v>
       </c>
       <c r="Q43" s="34" t="n">
-        <v>36.84</v>
+        <v>36.68</v>
       </c>
       <c r="R43" s="35" t="n">
-        <v>-0.27</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="44">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>28.97</v>
+        <v>29.34</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>28.41</v>
+        <v>28.82</v>
       </c>
       <c r="E44" s="26" t="n">
-        <v>27.94</v>
+        <v>28.39</v>
       </c>
       <c r="F44" s="27" t="n">
-        <v>28.21</v>
+        <v>28.37</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>28.41</v>
+        <v>28.69</v>
       </c>
       <c r="H44" s="28" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="I44" s="29" t="n">
         <v>27.85</v>
       </c>
-      <c r="I44" s="29" t="n">
+      <c r="J44" s="29" t="n">
         <v>27.65</v>
       </c>
-      <c r="J44" s="29" t="n">
-        <v>27.29</v>
-      </c>
       <c r="K44" s="30" t="n">
-        <v>27.62</v>
+        <v>28.09</v>
       </c>
       <c r="L44" s="31" t="n">
-        <v>27.15</v>
+        <v>27.66</v>
       </c>
       <c r="M44" s="31" t="n">
-        <v>26.59</v>
+        <v>27.14</v>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
@@ -3374,16 +3374,16 @@
         </is>
       </c>
       <c r="O44" s="33" t="n">
-        <v>27.76</v>
+        <v>28.15</v>
       </c>
       <c r="P44" s="33" t="n">
-        <v>27.67</v>
+        <v>28.13</v>
       </c>
       <c r="Q44" s="34" t="n">
-        <v>28</v>
+        <v>28.04</v>
       </c>
       <c r="R44" s="36" t="n">
-        <v>1.82</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="45">
@@ -3398,22 +3398,22 @@
         </is>
       </c>
       <c r="C45" s="25" t="n">
-        <v>26.97</v>
+        <v>27.17</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>26.79</v>
+        <v>26.93</v>
       </c>
       <c r="E45" s="26" t="n">
-        <v>26.64</v>
+        <v>26.73</v>
       </c>
       <c r="F45" s="27" t="n">
-        <v>26.69</v>
+        <v>26.75</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>26.77</v>
+        <v>26.89</v>
       </c>
       <c r="H45" s="28" t="n">
-        <v>26.59</v>
+        <v>26.65</v>
       </c>
       <c r="I45" s="29" t="n">
         <v>26.51</v>
@@ -3422,13 +3422,13 @@
         <v>26.41</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>26.54</v>
+        <v>26.59</v>
       </c>
       <c r="L45" s="31" t="n">
         <v>26.39</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>26.21</v>
+        <v>26.15</v>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
@@ -3436,16 +3436,16 @@
         </is>
       </c>
       <c r="O45" s="33" t="n">
-        <v>26.57</v>
+        <v>26.63</v>
       </c>
       <c r="P45" s="33" t="n">
-        <v>26.55</v>
+        <v>26.61</v>
       </c>
       <c r="Q45" s="34" t="n">
-        <v>26.6</v>
+        <v>26.62</v>
       </c>
       <c r="R45" s="36" t="n">
-        <v>0.38</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="46">
@@ -3460,54 +3460,54 @@
         </is>
       </c>
       <c r="C46" s="25" t="n">
-        <v>8.23</v>
+        <v>8.43</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>8.140000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>8.06</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F46" s="27" t="n">
-        <v>8.09</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G46" s="27" t="n">
-        <v>8.130000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H46" s="28" t="n">
         <v>8.039999999999999</v>
       </c>
       <c r="I46" s="29" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="J46" s="29" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="K46" s="30" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="L46" s="31" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="M46" s="31" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="N46" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O46" s="33" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="P46" s="33" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="Q46" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="J46" s="29" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="K46" s="30" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="L46" s="31" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="M46" s="31" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="N46" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O46" s="33" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="P46" s="33" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="Q46" s="34" t="n">
-        <v>8.050000000000001</v>
-      </c>
       <c r="R46" s="35" t="n">
-        <v>-0.25</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="47">
@@ -3522,54 +3522,54 @@
         </is>
       </c>
       <c r="C47" s="25" t="n">
-        <v>12.68</v>
+        <v>12.84</v>
       </c>
       <c r="D47" s="25" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="E47" s="26" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="F47" s="27" t="n">
         <v>12.48</v>
       </c>
-      <c r="E47" s="26" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="F47" s="27" t="n">
+      <c r="G47" s="27" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="H47" s="28" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="I47" s="29" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="J47" s="29" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="K47" s="30" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="L47" s="31" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M47" s="31" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="N47" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O47" s="33" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="P47" s="33" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="Q47" s="34" t="n">
         <v>12.37</v>
       </c>
-      <c r="G47" s="27" t="n">
-        <v>12.47</v>
-      </c>
-      <c r="H47" s="28" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="I47" s="29" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="J47" s="29" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="K47" s="30" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="L47" s="31" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="M47" s="31" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="N47" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O47" s="33" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="P47" s="33" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="Q47" s="34" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="R47" s="35" t="n">
-        <v>-0.65</v>
+      <c r="R47" s="36" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="48">
@@ -3584,54 +3584,54 @@
         </is>
       </c>
       <c r="C48" s="25" t="n">
-        <v>205.71</v>
+        <v>207.26</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>203.91</v>
+        <v>205.06</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>202.4</v>
+        <v>203.22</v>
       </c>
       <c r="F48" s="27" t="n">
-        <v>203.33</v>
+        <v>204.43</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>203.97</v>
+        <v>205.17</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>202.17</v>
+        <v>202.97</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>201.53</v>
+        <v>202.23</v>
       </c>
       <c r="J48" s="29" t="n">
-        <v>200.37</v>
+        <v>200.77</v>
       </c>
       <c r="K48" s="30" t="n">
-        <v>201.4</v>
+        <v>201.98</v>
       </c>
       <c r="L48" s="31" t="n">
-        <v>199.89</v>
+        <v>200.14</v>
       </c>
       <c r="M48" s="31" t="n">
-        <v>198.09</v>
-      </c>
-      <c r="N48" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>197.94</v>
+      </c>
+      <c r="N48" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O48" s="33" t="n">
-        <v>201.85</v>
+        <v>202.56</v>
       </c>
       <c r="P48" s="33" t="n">
-        <v>201.54</v>
+        <v>202.16</v>
       </c>
       <c r="Q48" s="34" t="n">
-        <v>202.7</v>
+        <v>203.7</v>
       </c>
       <c r="R48" s="36" t="n">
-        <v>0.15</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="49">
@@ -3646,37 +3646,37 @@
         </is>
       </c>
       <c r="C49" s="25" t="n">
-        <v>48.82</v>
+        <v>50.16</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>48.24</v>
+        <v>49.26</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>47.75</v>
+        <v>48.5</v>
       </c>
       <c r="F49" s="27" t="n">
-        <v>48.02</v>
+        <v>48.73</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>48.24</v>
+        <v>49.17</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>47.66</v>
+        <v>48.27</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>47.44</v>
+        <v>47.83</v>
       </c>
       <c r="J49" s="29" t="n">
-        <v>47.08</v>
+        <v>47.37</v>
       </c>
       <c r="K49" s="30" t="n">
-        <v>47.43</v>
+        <v>48</v>
       </c>
       <c r="L49" s="31" t="n">
-        <v>46.94</v>
+        <v>47.24</v>
       </c>
       <c r="M49" s="31" t="n">
-        <v>46.36</v>
+        <v>46.34</v>
       </c>
       <c r="N49" s="20" t="inlineStr">
         <is>
@@ -3684,16 +3684,16 @@
         </is>
       </c>
       <c r="O49" s="33" t="n">
-        <v>47.57</v>
+        <v>48.17</v>
       </c>
       <c r="P49" s="33" t="n">
-        <v>47.47</v>
+        <v>48.07</v>
       </c>
       <c r="Q49" s="34" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
       <c r="R49" s="36" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="50">
@@ -3708,54 +3708,54 @@
         </is>
       </c>
       <c r="C50" s="25" t="n">
-        <v>30.62</v>
+        <v>31.33</v>
       </c>
       <c r="D50" s="25" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="E50" s="26" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="F50" s="27" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="G50" s="27" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="H50" s="28" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="J50" s="29" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="K50" s="30" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="L50" s="31" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="M50" s="31" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="N50" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O50" s="33" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="P50" s="33" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="Q50" s="34" t="n">
         <v>30.3</v>
       </c>
-      <c r="E50" s="26" t="n">
-        <v>30.03</v>
-      </c>
-      <c r="F50" s="27" t="n">
-        <v>30.15</v>
-      </c>
-      <c r="G50" s="27" t="n">
-        <v>30.29</v>
-      </c>
-      <c r="H50" s="28" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>29.83</v>
-      </c>
-      <c r="J50" s="29" t="n">
-        <v>29.65</v>
-      </c>
-      <c r="K50" s="30" t="n">
-        <v>29.85</v>
-      </c>
-      <c r="L50" s="31" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="M50" s="31" t="n">
-        <v>29.26</v>
-      </c>
-      <c r="N50" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O50" s="33" t="n">
-        <v>29.92</v>
-      </c>
-      <c r="P50" s="33" t="n">
-        <v>29.88</v>
-      </c>
-      <c r="Q50" s="34" t="n">
-        <v>30.02</v>
-      </c>
       <c r="R50" s="36" t="n">
-        <v>0.4</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="51">
@@ -3770,54 +3770,54 @@
         </is>
       </c>
       <c r="C51" s="25" t="n">
-        <v>13.26</v>
+        <v>13.71</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>13.14</v>
+        <v>13.43</v>
       </c>
       <c r="E51" s="26" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F51" s="27" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="G51" s="27" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="H51" s="28" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="I51" s="29" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="J51" s="29" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="K51" s="30" t="n">
         <v>13.04</v>
       </c>
-      <c r="F51" s="27" t="n">
+      <c r="L51" s="31" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="M51" s="31" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="N51" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O51" s="33" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="P51" s="33" t="n">
         <v>13.06</v>
       </c>
-      <c r="G51" s="27" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="H51" s="28" t="n">
-        <v>13.01</v>
-      </c>
-      <c r="I51" s="29" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="J51" s="29" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="K51" s="30" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="L51" s="31" t="n">
-        <v>12.88</v>
-      </c>
-      <c r="M51" s="31" t="n">
-        <v>12.76</v>
-      </c>
-      <c r="N51" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O51" s="33" t="n">
-        <v>13</v>
-      </c>
-      <c r="P51" s="33" t="n">
-        <v>12.99</v>
-      </c>
       <c r="Q51" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="R51" s="35" t="n">
-        <v>-0.08</v>
+        <v>13.2</v>
+      </c>
+      <c r="R51" s="36" t="n">
+        <v>1.54</v>
       </c>
     </row>
     <row r="52">
@@ -3832,37 +3832,37 @@
         </is>
       </c>
       <c r="C52" s="25" t="n">
-        <v>64.11</v>
+        <v>64.52</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>62.56</v>
+        <v>62.62</v>
       </c>
       <c r="E52" s="26" t="n">
-        <v>61.26</v>
+        <v>61.03</v>
       </c>
       <c r="F52" s="27" t="n">
-        <v>61.38</v>
+        <v>61.58</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>62.27</v>
+        <v>62.47</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>60.72</v>
+        <v>60.57</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>59.83</v>
+        <v>59.68</v>
       </c>
       <c r="J52" s="29" t="n">
-        <v>59.17</v>
+        <v>58.67</v>
       </c>
       <c r="K52" s="30" t="n">
-        <v>60.39</v>
+        <v>59.97</v>
       </c>
       <c r="L52" s="31" t="n">
-        <v>59.09</v>
+        <v>58.38</v>
       </c>
       <c r="M52" s="31" t="n">
-        <v>57.54</v>
+        <v>56.48</v>
       </c>
       <c r="N52" s="32" t="inlineStr">
         <is>
@@ -3870,16 +3870,16 @@
         </is>
       </c>
       <c r="O52" s="33" t="n">
-        <v>60.61</v>
+        <v>60.34</v>
       </c>
       <c r="P52" s="33" t="n">
-        <v>60.51</v>
+        <v>60.12</v>
       </c>
       <c r="Q52" s="34" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="R52" s="35" t="n">
-        <v>-0.25</v>
+        <v>60.7</v>
+      </c>
+      <c r="R52" s="36" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="53">
@@ -3894,37 +3894,37 @@
         </is>
       </c>
       <c r="C53" s="25" t="n">
-        <v>24.5</v>
+        <v>26.4</v>
       </c>
       <c r="D53" s="25" t="n">
-        <v>23.81</v>
+        <v>25.14</v>
       </c>
       <c r="E53" s="26" t="n">
-        <v>23.23</v>
+        <v>24.08</v>
       </c>
       <c r="F53" s="27" t="n">
-        <v>23.44</v>
+        <v>24.73</v>
       </c>
       <c r="G53" s="27" t="n">
-        <v>23.75</v>
+        <v>25.17</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>23.06</v>
+        <v>23.91</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>22.75</v>
+        <v>23.47</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>22.37</v>
+        <v>22.65</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>22.84</v>
+        <v>23.38</v>
       </c>
       <c r="L53" s="31" t="n">
-        <v>22.26</v>
+        <v>22.32</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>21.57</v>
+        <v>21.06</v>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="O53" s="33" t="n">
-        <v>22.98</v>
+        <v>23.69</v>
       </c>
       <c r="P53" s="33" t="n">
-        <v>22.9</v>
+        <v>23.48</v>
       </c>
       <c r="Q53" s="34" t="n">
-        <v>23.12</v>
+        <v>24.28</v>
       </c>
       <c r="R53" s="36" t="n">
-        <v>1.23</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="54">
@@ -3956,54 +3956,54 @@
         </is>
       </c>
       <c r="C54" s="25" t="n">
-        <v>5.4</v>
+        <v>5.39</v>
       </c>
       <c r="D54" s="25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E54" s="26" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="G54" s="27" t="n">
         <v>5.29</v>
       </c>
-      <c r="E54" s="26" t="n">
+      <c r="H54" s="28" t="n">
         <v>5.2</v>
       </c>
-      <c r="F54" s="27" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="G54" s="27" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="H54" s="28" t="n">
-        <v>5.16</v>
-      </c>
       <c r="I54" s="29" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="J54" s="29" t="n">
         <v>5.11</v>
       </c>
-      <c r="J54" s="29" t="n">
-        <v>5.05</v>
-      </c>
       <c r="K54" s="30" t="n">
-        <v>5.13</v>
+        <v>5.17</v>
       </c>
       <c r="L54" s="31" t="n">
-        <v>5.04</v>
+        <v>5.09</v>
       </c>
       <c r="M54" s="31" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="N54" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>5</v>
+      </c>
+      <c r="N54" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O54" s="33" t="n">
-        <v>5.15</v>
+        <v>5.19</v>
       </c>
       <c r="P54" s="33" t="n">
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="Q54" s="34" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="R54" s="35" t="n">
-        <v>-0.77</v>
+        <v>5.2</v>
+      </c>
+      <c r="R54" s="36" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="55">
@@ -4018,54 +4018,54 @@
         </is>
       </c>
       <c r="C55" s="25" t="n">
-        <v>17.37</v>
+        <v>18.73</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>16.67</v>
+        <v>17.44</v>
       </c>
       <c r="E55" s="26" t="n">
-        <v>16.09</v>
+        <v>16.36</v>
       </c>
       <c r="F55" s="27" t="n">
-        <v>16.01</v>
+        <v>16.9</v>
       </c>
       <c r="G55" s="27" t="n">
-        <v>16.48</v>
+        <v>17.41</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>15.78</v>
+        <v>16.12</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>15.31</v>
+        <v>15.61</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>15.08</v>
+        <v>14.83</v>
       </c>
       <c r="K55" s="30" t="n">
-        <v>15.69</v>
+        <v>15.63</v>
       </c>
       <c r="L55" s="31" t="n">
-        <v>15.11</v>
+        <v>14.55</v>
       </c>
       <c r="M55" s="31" t="n">
-        <v>14.41</v>
-      </c>
-      <c r="N55" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>13.26</v>
+      </c>
+      <c r="N55" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O55" s="33" t="n">
-        <v>15.76</v>
+        <v>15.93</v>
       </c>
       <c r="P55" s="33" t="n">
-        <v>15.75</v>
+        <v>15.73</v>
       </c>
       <c r="Q55" s="34" t="n">
-        <v>15.55</v>
-      </c>
-      <c r="R55" s="35" t="n">
-        <v>-3.54</v>
+        <v>16.38</v>
+      </c>
+      <c r="R55" s="36" t="n">
+        <v>5.34</v>
       </c>
     </row>
     <row r="56">
@@ -4080,37 +4080,37 @@
         </is>
       </c>
       <c r="C56" s="25" t="n">
-        <v>87.25</v>
+        <v>100.4</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>84.90000000000001</v>
+        <v>92.55</v>
       </c>
       <c r="E56" s="26" t="n">
-        <v>82.93000000000001</v>
+        <v>85.97</v>
       </c>
       <c r="F56" s="27" t="n">
-        <v>83.67</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="G56" s="27" t="n">
-        <v>84.73</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>82.38</v>
+        <v>84.75</v>
       </c>
       <c r="I56" s="29" t="n">
-        <v>81.31999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="J56" s="29" t="n">
-        <v>80.03</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K56" s="30" t="n">
-        <v>81.62</v>
+        <v>81.58</v>
       </c>
       <c r="L56" s="31" t="n">
-        <v>79.65000000000001</v>
+        <v>75</v>
       </c>
       <c r="M56" s="31" t="n">
-        <v>77.3</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="N56" s="20" t="inlineStr">
         <is>
@@ -4118,16 +4118,16 @@
         </is>
       </c>
       <c r="O56" s="33" t="n">
-        <v>82.09</v>
+        <v>83.47</v>
       </c>
       <c r="P56" s="33" t="n">
-        <v>81.8</v>
+        <v>82.19</v>
       </c>
       <c r="Q56" s="34" t="n">
-        <v>82.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="R56" s="36" t="n">
-        <v>1.1</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="57">
@@ -4142,54 +4142,54 @@
         </is>
       </c>
       <c r="C57" s="25" t="n">
-        <v>18.39</v>
+        <v>18.59</v>
       </c>
       <c r="D57" s="25" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E57" s="26" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="F57" s="27" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="G57" s="27" t="n">
         <v>18.05</v>
       </c>
-      <c r="E57" s="26" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="F57" s="27" t="n">
-        <v>17.76</v>
-      </c>
-      <c r="G57" s="27" t="n">
-        <v>17.97</v>
-      </c>
       <c r="H57" s="28" t="n">
-        <v>17.63</v>
+        <v>17.56</v>
       </c>
       <c r="I57" s="29" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="J57" s="29" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="K57" s="30" t="n">
         <v>17.42</v>
       </c>
-      <c r="J57" s="29" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="K57" s="30" t="n">
+      <c r="L57" s="31" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="M57" s="31" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="N57" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O57" s="33" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="P57" s="33" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="Q57" s="34" t="n">
         <v>17.57</v>
       </c>
-      <c r="L57" s="31" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="M57" s="31" t="n">
-        <v>16.95</v>
-      </c>
-      <c r="N57" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O57" s="33" t="n">
-        <v>17.62</v>
-      </c>
-      <c r="P57" s="33" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Q57" s="34" t="n">
-        <v>17.55</v>
-      </c>
-      <c r="R57" s="35" t="n">
-        <v>-0.79</v>
+      <c r="R57" s="36" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="58">
@@ -4204,37 +4204,37 @@
         </is>
       </c>
       <c r="C58" s="25" t="n">
-        <v>22.94</v>
+        <v>22.71</v>
       </c>
       <c r="D58" s="25" t="n">
-        <v>22.65</v>
+        <v>22.47</v>
       </c>
       <c r="E58" s="26" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F58" s="27" t="n">
-        <v>22.4</v>
+        <v>22.36</v>
       </c>
       <c r="G58" s="27" t="n">
-        <v>22.58</v>
+        <v>22.46</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>22.29</v>
+        <v>22.22</v>
       </c>
       <c r="I58" s="29" t="n">
-        <v>22.11</v>
+        <v>22.12</v>
       </c>
       <c r="J58" s="29" t="n">
-        <v>22</v>
+        <v>21.98</v>
       </c>
       <c r="K58" s="30" t="n">
-        <v>22.24</v>
+        <v>22.13</v>
       </c>
       <c r="L58" s="31" t="n">
-        <v>22</v>
+        <v>21.93</v>
       </c>
       <c r="M58" s="31" t="n">
-        <v>21.71</v>
+        <v>21.69</v>
       </c>
       <c r="N58" s="32" t="inlineStr">
         <is>
@@ -4242,16 +4242,16 @@
         </is>
       </c>
       <c r="O58" s="33" t="n">
-        <v>22.28</v>
+        <v>22.19</v>
       </c>
       <c r="P58" s="33" t="n">
-        <v>22.27</v>
+        <v>22.15</v>
       </c>
       <c r="Q58" s="34" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="R58" s="35" t="n">
-        <v>-0.98</v>
+        <v>22.26</v>
+      </c>
+      <c r="R58" s="36" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="59">
@@ -4266,37 +4266,37 @@
         </is>
       </c>
       <c r="C59" s="25" t="n">
-        <v>23.49</v>
+        <v>23.91</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>23.23</v>
+        <v>23.53</v>
       </c>
       <c r="E59" s="26" t="n">
-        <v>23.01</v>
+        <v>23.22</v>
       </c>
       <c r="F59" s="27" t="n">
-        <v>23.11</v>
+        <v>23.36</v>
       </c>
       <c r="G59" s="27" t="n">
-        <v>23.22</v>
+        <v>23.52</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>22.96</v>
+        <v>23.14</v>
       </c>
       <c r="I59" s="29" t="n">
-        <v>22.85</v>
+        <v>22.98</v>
       </c>
       <c r="J59" s="29" t="n">
-        <v>22.7</v>
+        <v>22.76</v>
       </c>
       <c r="K59" s="30" t="n">
-        <v>22.87</v>
+        <v>23</v>
       </c>
       <c r="L59" s="31" t="n">
-        <v>22.65</v>
+        <v>22.69</v>
       </c>
       <c r="M59" s="31" t="n">
-        <v>22.39</v>
+        <v>22.31</v>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
@@ -4304,16 +4304,16 @@
         </is>
       </c>
       <c r="O59" s="33" t="n">
-        <v>22.92</v>
+        <v>23.09</v>
       </c>
       <c r="P59" s="33" t="n">
-        <v>22.89</v>
+        <v>23.03</v>
       </c>
       <c r="Q59" s="34" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="R59" s="36" t="n">
-        <v>0.26</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="60">
@@ -4328,54 +4328,54 @@
         </is>
       </c>
       <c r="C60" s="25" t="n">
-        <v>28.79</v>
+        <v>29.25</v>
       </c>
       <c r="D60" s="25" t="n">
-        <v>28.55</v>
+        <v>28.81</v>
       </c>
       <c r="E60" s="26" t="n">
-        <v>28.35</v>
+        <v>28.44</v>
       </c>
       <c r="F60" s="27" t="n">
-        <v>28.41</v>
+        <v>28.45</v>
       </c>
       <c r="G60" s="27" t="n">
-        <v>28.53</v>
+        <v>28.71</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>28.29</v>
+        <v>28.27</v>
       </c>
       <c r="I60" s="29" t="n">
-        <v>28.17</v>
+        <v>28.01</v>
       </c>
       <c r="J60" s="29" t="n">
-        <v>28.05</v>
+        <v>27.83</v>
       </c>
       <c r="K60" s="30" t="n">
-        <v>28.21</v>
+        <v>28.2</v>
       </c>
       <c r="L60" s="31" t="n">
-        <v>28.01</v>
+        <v>27.83</v>
       </c>
       <c r="M60" s="31" t="n">
-        <v>27.77</v>
-      </c>
-      <c r="N60" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>27.39</v>
+      </c>
+      <c r="N60" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O60" s="33" t="n">
-        <v>28.26</v>
+        <v>28.25</v>
       </c>
       <c r="P60" s="33" t="n">
         <v>28.23</v>
       </c>
       <c r="Q60" s="34" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="R60" s="36" t="n">
-        <v>0.71</v>
+        <v>28.18</v>
+      </c>
+      <c r="R60" s="35" t="n">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="61">
@@ -4390,54 +4390,54 @@
         </is>
       </c>
       <c r="C61" s="25" t="n">
-        <v>43.61</v>
+        <v>46.08</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>43.49</v>
+        <v>45.02</v>
       </c>
       <c r="E61" s="26" t="n">
-        <v>43.39</v>
+        <v>44.13</v>
       </c>
       <c r="F61" s="27" t="n">
-        <v>43.38</v>
+        <v>44.71</v>
       </c>
       <c r="G61" s="27" t="n">
-        <v>43.46</v>
+        <v>45.07</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>43.34</v>
+        <v>44.01</v>
       </c>
       <c r="I61" s="29" t="n">
-        <v>43.26</v>
+        <v>43.65</v>
       </c>
       <c r="J61" s="29" t="n">
-        <v>43.22</v>
+        <v>42.95</v>
       </c>
       <c r="K61" s="30" t="n">
-        <v>43.33</v>
+        <v>43.53</v>
       </c>
       <c r="L61" s="31" t="n">
-        <v>43.23</v>
+        <v>42.64</v>
       </c>
       <c r="M61" s="31" t="n">
-        <v>43.11</v>
-      </c>
-      <c r="N61" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>41.58</v>
+      </c>
+      <c r="N61" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O61" s="33" t="n">
-        <v>43.34</v>
+        <v>43.81</v>
       </c>
       <c r="P61" s="33" t="n">
-        <v>43.34</v>
+        <v>43.62</v>
       </c>
       <c r="Q61" s="34" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="R61" s="35" t="n">
-        <v>-0.05</v>
+        <v>44.36</v>
+      </c>
+      <c r="R61" s="36" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="62">
@@ -4452,37 +4452,37 @@
         </is>
       </c>
       <c r="C62" s="25" t="n">
-        <v>19.05</v>
+        <v>19.39</v>
       </c>
       <c r="D62" s="25" t="n">
-        <v>18.88</v>
+        <v>19.07</v>
       </c>
       <c r="E62" s="26" t="n">
-        <v>18.73</v>
+        <v>18.8</v>
       </c>
       <c r="F62" s="27" t="n">
-        <v>18.81</v>
+        <v>18.76</v>
       </c>
       <c r="G62" s="27" t="n">
-        <v>18.87</v>
+        <v>18.98</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>18.7</v>
+        <v>18.66</v>
       </c>
       <c r="I62" s="29" t="n">
-        <v>18.64</v>
+        <v>18.44</v>
       </c>
       <c r="J62" s="29" t="n">
-        <v>18.53</v>
+        <v>18.34</v>
       </c>
       <c r="K62" s="30" t="n">
-        <v>18.64</v>
+        <v>18.62</v>
       </c>
       <c r="L62" s="31" t="n">
-        <v>18.49</v>
+        <v>18.35</v>
       </c>
       <c r="M62" s="31" t="n">
-        <v>18.32</v>
+        <v>18.03</v>
       </c>
       <c r="N62" s="32" t="inlineStr">
         <is>
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="O62" s="33" t="n">
-        <v>18.68</v>
+        <v>18.65</v>
       </c>
       <c r="P62" s="33" t="n">
         <v>18.65</v>
       </c>
       <c r="Q62" s="34" t="n">
-        <v>18.74</v>
+        <v>18.55</v>
       </c>
       <c r="R62" s="35" t="n">
-        <v>-0.16</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="63">
@@ -4514,37 +4514,37 @@
         </is>
       </c>
       <c r="C63" s="25" t="n">
-        <v>15.23</v>
+        <v>15.19</v>
       </c>
       <c r="D63" s="25" t="n">
-        <v>15.13</v>
+        <v>15.06</v>
       </c>
       <c r="E63" s="26" t="n">
-        <v>15.05</v>
+        <v>14.95</v>
       </c>
       <c r="F63" s="27" t="n">
-        <v>15.04</v>
+        <v>14.95</v>
       </c>
       <c r="G63" s="27" t="n">
-        <v>15.11</v>
+        <v>15.03</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>15.01</v>
+        <v>14.9</v>
       </c>
       <c r="I63" s="29" t="n">
-        <v>14.94</v>
+        <v>14.82</v>
       </c>
       <c r="J63" s="29" t="n">
-        <v>14.91</v>
+        <v>14.77</v>
       </c>
       <c r="K63" s="30" t="n">
-        <v>14.99</v>
+        <v>14.88</v>
       </c>
       <c r="L63" s="31" t="n">
-        <v>14.91</v>
+        <v>14.77</v>
       </c>
       <c r="M63" s="31" t="n">
-        <v>14.81</v>
+        <v>14.64</v>
       </c>
       <c r="N63" s="32" t="inlineStr">
         <is>
@@ -4552,16 +4552,16 @@
         </is>
       </c>
       <c r="O63" s="33" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="P63" s="33" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="Q63" s="34" t="n">
-        <v>14.98</v>
+        <v>14.87</v>
       </c>
       <c r="R63" s="35" t="n">
-        <v>-0.4</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="64">
@@ -4576,37 +4576,37 @@
         </is>
       </c>
       <c r="C64" s="25" t="n">
-        <v>25.87</v>
+        <v>26.16</v>
       </c>
       <c r="D64" s="25" t="n">
-        <v>25.53</v>
+        <v>25.64</v>
       </c>
       <c r="E64" s="26" t="n">
-        <v>25.25</v>
+        <v>25.21</v>
       </c>
       <c r="F64" s="27" t="n">
-        <v>25.31</v>
+        <v>25.4</v>
       </c>
       <c r="G64" s="27" t="n">
-        <v>25.49</v>
+        <v>25.62</v>
       </c>
       <c r="H64" s="28" t="n">
-        <v>25.15</v>
+        <v>25.1</v>
       </c>
       <c r="I64" s="29" t="n">
-        <v>24.97</v>
+        <v>24.88</v>
       </c>
       <c r="J64" s="29" t="n">
-        <v>24.81</v>
+        <v>24.58</v>
       </c>
       <c r="K64" s="30" t="n">
-        <v>25.05</v>
+        <v>24.91</v>
       </c>
       <c r="L64" s="31" t="n">
-        <v>24.77</v>
+        <v>24.48</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>24.43</v>
+        <v>23.96</v>
       </c>
       <c r="N64" s="20" t="inlineStr">
         <is>
@@ -4614,16 +4614,16 @@
         </is>
       </c>
       <c r="O64" s="33" t="n">
-        <v>25.11</v>
+        <v>25.03</v>
       </c>
       <c r="P64" s="33" t="n">
-        <v>25.08</v>
+        <v>24.95</v>
       </c>
       <c r="Q64" s="34" t="n">
-        <v>25.14</v>
+        <v>25.18</v>
       </c>
       <c r="R64" s="36" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="65">
@@ -4638,41 +4638,41 @@
         </is>
       </c>
       <c r="C65" s="25" t="n">
-        <v>7.53</v>
+        <v>7.55</v>
       </c>
       <c r="D65" s="25" t="n">
-        <v>7.48</v>
+        <v>7.49</v>
       </c>
       <c r="E65" s="26" t="n">
         <v>7.44</v>
       </c>
       <c r="F65" s="27" t="n">
-        <v>7.45</v>
+        <v>7.46</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>7.48</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>7.43</v>
+        <v>7.42</v>
       </c>
       <c r="I65" s="29" t="n">
         <v>7.4</v>
       </c>
       <c r="J65" s="29" t="n">
-        <v>7.38</v>
+        <v>7.36</v>
       </c>
       <c r="K65" s="30" t="n">
-        <v>7.41</v>
+        <v>7.4</v>
       </c>
       <c r="L65" s="31" t="n">
-        <v>7.37</v>
+        <v>7.35</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="N65" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>7.29</v>
+      </c>
+      <c r="N65" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O65" s="33" t="n">
@@ -4684,8 +4684,8 @@
       <c r="Q65" s="34" t="n">
         <v>7.43</v>
       </c>
-      <c r="R65" s="35" t="n">
-        <v>-0.93</v>
+      <c r="R65" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4709,19 +4709,19 @@
         <v>4.99</v>
       </c>
       <c r="F66" s="27" t="n">
-        <v>5.01</v>
+        <v>4.98</v>
       </c>
       <c r="G66" s="27" t="n">
-        <v>5.04</v>
+        <v>5.02</v>
       </c>
       <c r="H66" s="28" t="n">
-        <v>4.98</v>
+        <v>4.96</v>
       </c>
       <c r="I66" s="29" t="n">
-        <v>4.95</v>
+        <v>4.92</v>
       </c>
       <c r="J66" s="29" t="n">
-        <v>4.92</v>
+        <v>4.9</v>
       </c>
       <c r="K66" s="30" t="n">
         <v>4.95</v>
@@ -4732,22 +4732,22 @@
       <c r="M66" s="31" t="n">
         <v>4.84</v>
       </c>
-      <c r="N66" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+      <c r="N66" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O66" s="33" t="n">
-        <v>4.97</v>
+        <v>4.96</v>
       </c>
       <c r="P66" s="33" t="n">
         <v>4.96</v>
       </c>
       <c r="Q66" s="34" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="R66" s="36" t="n">
-        <v>0.4</v>
+        <v>4.94</v>
+      </c>
+      <c r="R66" s="35" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="67">
@@ -4762,34 +4762,34 @@
         </is>
       </c>
       <c r="C67" s="25" t="n">
-        <v>5.32</v>
+        <v>5.24</v>
       </c>
       <c r="D67" s="25" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="E67" s="26" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="F67" s="27" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="G67" s="27" t="n">
         <v>5.19</v>
       </c>
-      <c r="F67" s="27" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="G67" s="27" t="n">
-        <v>5.23</v>
-      </c>
       <c r="H67" s="28" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
       <c r="I67" s="29" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="J67" s="29" t="n">
         <v>5.09</v>
       </c>
       <c r="K67" s="30" t="n">
-        <v>5.16</v>
+        <v>5.12</v>
       </c>
       <c r="L67" s="31" t="n">
-        <v>5.1</v>
+        <v>5.08</v>
       </c>
       <c r="M67" s="31" t="n">
         <v>5.03</v>
@@ -4800,16 +4800,16 @@
         </is>
       </c>
       <c r="O67" s="33" t="n">
-        <v>5.16</v>
+        <v>5.13</v>
       </c>
       <c r="P67" s="33" t="n">
-        <v>5.16</v>
+        <v>5.12</v>
       </c>
       <c r="Q67" s="34" t="n">
         <v>5.14</v>
       </c>
-      <c r="R67" s="35" t="n">
-        <v>-0.96</v>
+      <c r="R67" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4824,37 +4824,37 @@
         </is>
       </c>
       <c r="C68" s="25" t="n">
-        <v>65.72</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="D68" s="25" t="n">
-        <v>64.72</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="E68" s="26" t="n">
-        <v>63.88</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F68" s="27" t="n">
-        <v>64.33</v>
+        <v>64.55</v>
       </c>
       <c r="G68" s="27" t="n">
-        <v>64.72</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="H68" s="28" t="n">
-        <v>63.72</v>
+        <v>63.95</v>
       </c>
       <c r="I68" s="29" t="n">
-        <v>63.33</v>
+        <v>63.35</v>
       </c>
       <c r="J68" s="29" t="n">
-        <v>62.72</v>
+        <v>62.75</v>
       </c>
       <c r="K68" s="30" t="n">
-        <v>63.32</v>
+        <v>63.61</v>
       </c>
       <c r="L68" s="31" t="n">
-        <v>62.48</v>
+        <v>62.61</v>
       </c>
       <c r="M68" s="31" t="n">
-        <v>61.48</v>
+        <v>61.41</v>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
@@ -4862,16 +4862,16 @@
         </is>
       </c>
       <c r="O68" s="33" t="n">
-        <v>63.56</v>
+        <v>63.83</v>
       </c>
       <c r="P68" s="33" t="n">
-        <v>63.4</v>
+        <v>63.71</v>
       </c>
       <c r="Q68" s="34" t="n">
         <v>63.95</v>
       </c>
       <c r="R68" s="36" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4886,54 +4886,54 @@
         </is>
       </c>
       <c r="C69" s="25" t="n">
-        <v>71.01000000000001</v>
+        <v>70.69</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>69.86</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="E69" s="26" t="n">
-        <v>68.90000000000001</v>
+        <v>68.94</v>
       </c>
       <c r="F69" s="27" t="n">
-        <v>69.40000000000001</v>
+        <v>69.03</v>
       </c>
       <c r="G69" s="27" t="n">
-        <v>69.84999999999999</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>68.7</v>
+        <v>68.62</v>
       </c>
       <c r="I69" s="29" t="n">
-        <v>68.25</v>
+        <v>68.08</v>
       </c>
       <c r="J69" s="29" t="n">
-        <v>67.55</v>
+        <v>67.67</v>
       </c>
       <c r="K69" s="30" t="n">
-        <v>68.25</v>
+        <v>68.41</v>
       </c>
       <c r="L69" s="31" t="n">
-        <v>67.29000000000001</v>
+        <v>67.61</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>66.14</v>
-      </c>
-      <c r="N69" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>66.66</v>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O69" s="33" t="n">
-        <v>68.52</v>
+        <v>68.55</v>
       </c>
       <c r="P69" s="33" t="n">
-        <v>68.34</v>
+        <v>68.48</v>
       </c>
       <c r="Q69" s="34" t="n">
-        <v>68.95</v>
-      </c>
-      <c r="R69" s="36" t="n">
-        <v>1.55</v>
+        <v>68.5</v>
+      </c>
+      <c r="R69" s="35" t="n">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="70">
@@ -4948,54 +4948,54 @@
         </is>
       </c>
       <c r="C70" s="25" t="n">
-        <v>108.61</v>
+        <v>107.58</v>
       </c>
       <c r="D70" s="25" t="n">
-        <v>106.01</v>
+        <v>105.18</v>
       </c>
       <c r="E70" s="26" t="n">
-        <v>103.83</v>
+        <v>103.17</v>
       </c>
       <c r="F70" s="27" t="n">
-        <v>105</v>
+        <v>103.23</v>
       </c>
       <c r="G70" s="27" t="n">
-        <v>106</v>
+        <v>104.67</v>
       </c>
       <c r="H70" s="28" t="n">
-        <v>103.4</v>
+        <v>102.27</v>
       </c>
       <c r="I70" s="29" t="n">
-        <v>102.4</v>
+        <v>100.83</v>
       </c>
       <c r="J70" s="29" t="n">
-        <v>100.8</v>
+        <v>99.87</v>
       </c>
       <c r="K70" s="30" t="n">
-        <v>102.37</v>
+        <v>101.83</v>
       </c>
       <c r="L70" s="31" t="n">
-        <v>100.19</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>97.59</v>
-      </c>
-      <c r="N70" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>97.42</v>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O70" s="33" t="n">
-        <v>102.99</v>
+        <v>102.14</v>
       </c>
       <c r="P70" s="33" t="n">
-        <v>102.57</v>
+        <v>102.02</v>
       </c>
       <c r="Q70" s="34" t="n">
-        <v>104</v>
-      </c>
-      <c r="R70" s="36" t="n">
-        <v>2.06</v>
+        <v>101.8</v>
+      </c>
+      <c r="R70" s="35" t="n">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="71">
@@ -5010,54 +5010,54 @@
         </is>
       </c>
       <c r="C71" s="25" t="n">
-        <v>129.65</v>
+        <v>130.33</v>
       </c>
       <c r="D71" s="25" t="n">
-        <v>126.65</v>
+        <v>127.53</v>
       </c>
       <c r="E71" s="26" t="n">
-        <v>124.14</v>
+        <v>125.18</v>
       </c>
       <c r="F71" s="27" t="n">
-        <v>125</v>
+        <v>125.53</v>
       </c>
       <c r="G71" s="27" t="n">
-        <v>126.4</v>
+        <v>127.07</v>
       </c>
       <c r="H71" s="28" t="n">
-        <v>123.4</v>
+        <v>124.27</v>
       </c>
       <c r="I71" s="29" t="n">
-        <v>122</v>
+        <v>122.73</v>
       </c>
       <c r="J71" s="29" t="n">
-        <v>120.4</v>
+        <v>121.47</v>
       </c>
       <c r="K71" s="30" t="n">
-        <v>122.46</v>
+        <v>123.62</v>
       </c>
       <c r="L71" s="31" t="n">
-        <v>119.95</v>
+        <v>121.27</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>116.95</v>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>118.47</v>
+      </c>
+      <c r="N71" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O71" s="33" t="n">
-        <v>123.05</v>
+        <v>124.05</v>
       </c>
       <c r="P71" s="33" t="n">
-        <v>122.69</v>
+        <v>123.83</v>
       </c>
       <c r="Q71" s="34" t="n">
-        <v>123.6</v>
-      </c>
-      <c r="R71" s="35" t="n">
-        <v>-1.28</v>
+        <v>124</v>
+      </c>
+      <c r="R71" s="36" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="72">
@@ -5072,37 +5072,37 @@
         </is>
       </c>
       <c r="C72" s="25" t="n">
-        <v>27.39</v>
+        <v>26.7</v>
       </c>
       <c r="D72" s="25" t="n">
-        <v>26.79</v>
+        <v>26.28</v>
       </c>
       <c r="E72" s="26" t="n">
-        <v>26.29</v>
+        <v>25.93</v>
       </c>
       <c r="F72" s="27" t="n">
-        <v>26.25</v>
+        <v>26.08</v>
       </c>
       <c r="G72" s="27" t="n">
-        <v>26.63</v>
+        <v>26.26</v>
       </c>
       <c r="H72" s="28" t="n">
-        <v>26.03</v>
+        <v>25.84</v>
       </c>
       <c r="I72" s="29" t="n">
-        <v>25.65</v>
+        <v>25.66</v>
       </c>
       <c r="J72" s="29" t="n">
-        <v>25.43</v>
+        <v>25.42</v>
       </c>
       <c r="K72" s="30" t="n">
-        <v>25.95</v>
+        <v>25.69</v>
       </c>
       <c r="L72" s="31" t="n">
-        <v>25.45</v>
+        <v>25.34</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>24.85</v>
+        <v>24.92</v>
       </c>
       <c r="N72" s="32" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         </is>
       </c>
       <c r="O72" s="33" t="n">
-        <v>26.02</v>
+        <v>25.78</v>
       </c>
       <c r="P72" s="33" t="n">
-        <v>26</v>
+        <v>25.73</v>
       </c>
       <c r="Q72" s="34" t="n">
-        <v>25.86</v>
-      </c>
-      <c r="R72" s="35" t="n">
-        <v>-1.67</v>
+        <v>25.9</v>
+      </c>
+      <c r="R72" s="36" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="73">
@@ -5134,54 +5134,54 @@
         </is>
       </c>
       <c r="C73" s="25" t="n">
-        <v>22.55</v>
+        <v>22.65</v>
       </c>
       <c r="D73" s="25" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="E73" s="26" t="n">
-        <v>21.23</v>
+        <v>21.18</v>
       </c>
       <c r="F73" s="27" t="n">
-        <v>21.28</v>
+        <v>21.53</v>
       </c>
       <c r="G73" s="27" t="n">
-        <v>21.7</v>
+        <v>21.84</v>
       </c>
       <c r="H73" s="28" t="n">
-        <v>20.98</v>
+        <v>21.04</v>
       </c>
       <c r="I73" s="29" t="n">
-        <v>20.56</v>
+        <v>20.73</v>
       </c>
       <c r="J73" s="29" t="n">
-        <v>20.26</v>
+        <v>20.24</v>
       </c>
       <c r="K73" s="30" t="n">
-        <v>20.83</v>
+        <v>20.74</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>20.23</v>
+        <v>20.07</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>19.27</v>
+      </c>
+      <c r="N73" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O73" s="33" t="n">
-        <v>20.93</v>
+        <v>20.92</v>
       </c>
       <c r="P73" s="33" t="n">
-        <v>20.88</v>
+        <v>20.8</v>
       </c>
       <c r="Q73" s="34" t="n">
-        <v>20.87</v>
-      </c>
-      <c r="R73" s="35" t="n">
-        <v>-3.25</v>
+        <v>21.21</v>
+      </c>
+      <c r="R73" s="36" t="n">
+        <v>1.63</v>
       </c>
     </row>
     <row r="74">
@@ -5196,37 +5196,37 @@
         </is>
       </c>
       <c r="C74" s="25" t="n">
-        <v>239.25</v>
+        <v>239.64</v>
       </c>
       <c r="D74" s="25" t="n">
-        <v>236.25</v>
+        <v>236.34</v>
       </c>
       <c r="E74" s="26" t="n">
-        <v>233.74</v>
+        <v>233.57</v>
       </c>
       <c r="F74" s="27" t="n">
-        <v>234</v>
+        <v>234.27</v>
       </c>
       <c r="G74" s="27" t="n">
-        <v>235.7</v>
+        <v>235.93</v>
       </c>
       <c r="H74" s="28" t="n">
-        <v>232.7</v>
+        <v>232.63</v>
       </c>
       <c r="I74" s="29" t="n">
-        <v>231</v>
+        <v>230.97</v>
       </c>
       <c r="J74" s="29" t="n">
-        <v>229.7</v>
+        <v>229.33</v>
       </c>
       <c r="K74" s="30" t="n">
-        <v>232.06</v>
+        <v>231.73</v>
       </c>
       <c r="L74" s="31" t="n">
-        <v>229.55</v>
+        <v>228.96</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>226.55</v>
+        <v>225.66</v>
       </c>
       <c r="N74" s="32" t="inlineStr">
         <is>
@@ -5234,16 +5234,16 @@
         </is>
       </c>
       <c r="O74" s="33" t="n">
-        <v>232.5</v>
+        <v>232.31</v>
       </c>
       <c r="P74" s="33" t="n">
-        <v>232.29</v>
+        <v>231.98</v>
       </c>
       <c r="Q74" s="34" t="n">
-        <v>232.3</v>
-      </c>
-      <c r="R74" s="35" t="n">
-        <v>-0.9</v>
+        <v>232.6</v>
+      </c>
+      <c r="R74" s="36" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="75">
@@ -5258,37 +5258,37 @@
         </is>
       </c>
       <c r="C75" s="25" t="n">
-        <v>16.81</v>
+        <v>16.55</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>16.37</v>
+        <v>16.15</v>
       </c>
       <c r="E75" s="26" t="n">
-        <v>16</v>
+        <v>15.81</v>
       </c>
       <c r="F75" s="27" t="n">
-        <v>15.97</v>
+        <v>15.83</v>
       </c>
       <c r="G75" s="27" t="n">
-        <v>16.25</v>
+        <v>16.07</v>
       </c>
       <c r="H75" s="28" t="n">
-        <v>15.81</v>
+        <v>15.67</v>
       </c>
       <c r="I75" s="29" t="n">
-        <v>15.53</v>
+        <v>15.43</v>
       </c>
       <c r="J75" s="29" t="n">
-        <v>15.37</v>
+        <v>15.27</v>
       </c>
       <c r="K75" s="30" t="n">
-        <v>15.76</v>
+        <v>15.59</v>
       </c>
       <c r="L75" s="31" t="n">
-        <v>15.39</v>
+        <v>15.25</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>14.95</v>
+        <v>14.85</v>
       </c>
       <c r="N75" s="32" t="inlineStr">
         <is>
@@ -5296,16 +5296,16 @@
         </is>
       </c>
       <c r="O75" s="33" t="n">
-        <v>15.8</v>
+        <v>15.64</v>
       </c>
       <c r="P75" s="33" t="n">
-        <v>15.79</v>
+        <v>15.62</v>
       </c>
       <c r="Q75" s="34" t="n">
-        <v>15.68</v>
+        <v>15.6</v>
       </c>
       <c r="R75" s="35" t="n">
-        <v>-2.49</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="76">
@@ -5320,54 +5320,54 @@
         </is>
       </c>
       <c r="C76" s="25" t="n">
-        <v>31.53</v>
+        <v>32.04</v>
       </c>
       <c r="D76" s="25" t="n">
-        <v>30.87</v>
+        <v>31.26</v>
       </c>
       <c r="E76" s="26" t="n">
-        <v>30.31</v>
+        <v>30.61</v>
       </c>
       <c r="F76" s="27" t="n">
+        <v>30.96</v>
+      </c>
+      <c r="G76" s="27" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="H76" s="28" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="I76" s="29" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="J76" s="29" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="K76" s="30" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="L76" s="31" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="M76" s="31" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="N76" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O76" s="33" t="n">
         <v>30.36</v>
       </c>
-      <c r="G76" s="27" t="n">
-        <v>30.74</v>
-      </c>
-      <c r="H76" s="28" t="n">
-        <v>30.08</v>
-      </c>
-      <c r="I76" s="29" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="J76" s="29" t="n">
-        <v>29.42</v>
-      </c>
-      <c r="K76" s="30" t="n">
-        <v>29.95</v>
-      </c>
-      <c r="L76" s="31" t="n">
-        <v>29.39</v>
-      </c>
-      <c r="M76" s="31" t="n">
-        <v>28.73</v>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O76" s="33" t="n">
-        <v>30.04</v>
-      </c>
       <c r="P76" s="33" t="n">
-        <v>30</v>
+        <v>30.23</v>
       </c>
       <c r="Q76" s="34" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="R76" s="35" t="n">
-        <v>-0.86</v>
+        <v>30.66</v>
+      </c>
+      <c r="R76" s="36" t="n">
+        <v>2.27</v>
       </c>
     </row>
     <row r="77">
@@ -5382,54 +5382,54 @@
         </is>
       </c>
       <c r="C77" s="25" t="n">
-        <v>26.39</v>
+        <v>27.05</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>26.15</v>
+        <v>26.45</v>
       </c>
       <c r="E77" s="26" t="n">
         <v>25.95</v>
       </c>
       <c r="F77" s="27" t="n">
-        <v>25.95</v>
+        <v>26.21</v>
       </c>
       <c r="G77" s="27" t="n">
-        <v>26.09</v>
+        <v>26.45</v>
       </c>
       <c r="H77" s="28" t="n">
         <v>25.85</v>
       </c>
       <c r="I77" s="29" t="n">
-        <v>25.71</v>
+        <v>25.61</v>
       </c>
       <c r="J77" s="29" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="K77" s="30" t="n">
         <v>25.61</v>
       </c>
-      <c r="K77" s="30" t="n">
-        <v>25.81</v>
-      </c>
       <c r="L77" s="31" t="n">
-        <v>25.61</v>
+        <v>25.11</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>25.37</v>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>24.51</v>
+      </c>
+      <c r="N77" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O77" s="33" t="n">
-        <v>25.84</v>
+        <v>25.75</v>
       </c>
       <c r="P77" s="33" t="n">
-        <v>25.83</v>
+        <v>25.66</v>
       </c>
       <c r="Q77" s="34" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R77" s="35" t="n">
-        <v>-0.46</v>
+        <v>25.98</v>
+      </c>
+      <c r="R77" s="36" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="78">
@@ -5444,54 +5444,54 @@
         </is>
       </c>
       <c r="C78" s="25" t="n">
-        <v>40.18</v>
+        <v>40.55</v>
       </c>
       <c r="D78" s="25" t="n">
-        <v>39.08</v>
+        <v>39.27</v>
       </c>
       <c r="E78" s="26" t="n">
-        <v>38.16</v>
+        <v>38.2</v>
       </c>
       <c r="F78" s="27" t="n">
-        <v>38.17</v>
+        <v>38.68</v>
       </c>
       <c r="G78" s="27" t="n">
-        <v>38.83</v>
+        <v>39.22</v>
       </c>
       <c r="H78" s="28" t="n">
-        <v>37.73</v>
+        <v>37.94</v>
       </c>
       <c r="I78" s="29" t="n">
-        <v>37.07</v>
+        <v>37.4</v>
       </c>
       <c r="J78" s="29" t="n">
-        <v>36.63</v>
+        <v>36.66</v>
       </c>
       <c r="K78" s="30" t="n">
-        <v>37.54</v>
+        <v>37.48</v>
       </c>
       <c r="L78" s="31" t="n">
-        <v>36.62</v>
+        <v>36.41</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>35.52</v>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>35.13</v>
+      </c>
+      <c r="N78" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O78" s="33" t="n">
-        <v>37.68</v>
+        <v>37.76</v>
       </c>
       <c r="P78" s="33" t="n">
-        <v>37.63</v>
+        <v>37.58</v>
       </c>
       <c r="Q78" s="34" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="R78" s="35" t="n">
-        <v>-1.37</v>
+        <v>38.14</v>
+      </c>
+      <c r="R78" s="36" t="n">
+        <v>1.71</v>
       </c>
     </row>
     <row r="79">
@@ -5506,54 +5506,54 @@
         </is>
       </c>
       <c r="C79" s="25" t="n">
-        <v>5.81</v>
+        <v>5.87</v>
       </c>
       <c r="D79" s="25" t="n">
-        <v>5.67</v>
+        <v>5.71</v>
       </c>
       <c r="E79" s="26" t="n">
-        <v>5.55</v>
+        <v>5.57</v>
       </c>
       <c r="F79" s="27" t="n">
-        <v>5.56</v>
+        <v>5.62</v>
       </c>
       <c r="G79" s="27" t="n">
-        <v>5.64</v>
+        <v>5.69</v>
       </c>
       <c r="H79" s="28" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="I79" s="29" t="n">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="J79" s="29" t="n">
-        <v>5.36</v>
+        <v>5.37</v>
       </c>
       <c r="K79" s="30" t="n">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="L79" s="31" t="n">
         <v>5.35</v>
       </c>
       <c r="M79" s="31" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>5.19</v>
+      </c>
+      <c r="N79" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O79" s="33" t="n">
-        <v>5.49</v>
+        <v>5.52</v>
       </c>
       <c r="P79" s="33" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="Q79" s="34" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="R79" s="35" t="n">
-        <v>-0.9</v>
+        <v>5.54</v>
+      </c>
+      <c r="R79" s="36" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="80">
@@ -5568,54 +5568,54 @@
         </is>
       </c>
       <c r="C80" s="25" t="n">
-        <v>18.18</v>
+        <v>18.64</v>
       </c>
       <c r="D80" s="25" t="n">
-        <v>18.07</v>
+        <v>18.28</v>
       </c>
       <c r="E80" s="26" t="n">
         <v>17.98</v>
       </c>
       <c r="F80" s="27" t="n">
-        <v>18.02</v>
+        <v>18.07</v>
       </c>
       <c r="G80" s="27" t="n">
-        <v>18.07</v>
+        <v>18.25</v>
       </c>
       <c r="H80" s="28" t="n">
-        <v>17.96</v>
+        <v>17.89</v>
       </c>
       <c r="I80" s="29" t="n">
-        <v>17.91</v>
+        <v>17.71</v>
       </c>
       <c r="J80" s="29" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="K80" s="30" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="L80" s="31" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="M80" s="31" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O80" s="33" t="n">
         <v>17.85</v>
       </c>
-      <c r="K80" s="30" t="n">
-        <v>17.91</v>
-      </c>
-      <c r="L80" s="31" t="n">
-        <v>17.82</v>
-      </c>
-      <c r="M80" s="31" t="n">
-        <v>17.71</v>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O80" s="33" t="n">
-        <v>17.94</v>
-      </c>
       <c r="P80" s="33" t="n">
-        <v>17.92</v>
+        <v>17.81</v>
       </c>
       <c r="Q80" s="34" t="n">
-        <v>17.98</v>
-      </c>
-      <c r="R80" s="36" t="n">
-        <v>0.28</v>
+        <v>17.9</v>
+      </c>
+      <c r="R80" s="35" t="n">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="81">
@@ -5630,37 +5630,37 @@
         </is>
       </c>
       <c r="C81" s="25" t="n">
-        <v>85.34999999999999</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="D81" s="25" t="n">
-        <v>82.84999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="E81" s="26" t="n">
-        <v>80.75</v>
+        <v>79.83</v>
       </c>
       <c r="F81" s="27" t="n">
-        <v>80.83</v>
+        <v>79.73</v>
       </c>
       <c r="G81" s="27" t="n">
-        <v>82.31999999999999</v>
+        <v>81.22</v>
       </c>
       <c r="H81" s="28" t="n">
-        <v>79.81999999999999</v>
+        <v>78.87</v>
       </c>
       <c r="I81" s="29" t="n">
-        <v>78.33</v>
+        <v>77.38</v>
       </c>
       <c r="J81" s="29" t="n">
-        <v>77.31999999999999</v>
+        <v>76.52</v>
       </c>
       <c r="K81" s="30" t="n">
-        <v>79.34999999999999</v>
+        <v>78.52</v>
       </c>
       <c r="L81" s="31" t="n">
-        <v>77.26000000000001</v>
+        <v>76.55</v>
       </c>
       <c r="M81" s="31" t="n">
-        <v>74.76000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="N81" s="32" t="inlineStr">
         <is>
@@ -5668,16 +5668,16 @@
         </is>
       </c>
       <c r="O81" s="33" t="n">
-        <v>79.68000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="P81" s="33" t="n">
-        <v>79.55</v>
+        <v>78.7</v>
       </c>
       <c r="Q81" s="34" t="n">
-        <v>79.34999999999999</v>
+        <v>78.25</v>
       </c>
       <c r="R81" s="35" t="n">
-        <v>-2.4</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="82">
@@ -5692,37 +5692,37 @@
         </is>
       </c>
       <c r="C82" s="25" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="D82" s="25" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="E82" s="26" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="F82" s="27" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="G82" s="27" t="n">
         <v>4.72</v>
       </c>
-      <c r="D82" s="25" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E82" s="26" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="F82" s="27" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="G82" s="27" t="n">
-        <v>4.68</v>
-      </c>
       <c r="H82" s="28" t="n">
-        <v>4.65</v>
+        <v>4.53</v>
       </c>
       <c r="I82" s="29" t="n">
-        <v>4.64</v>
+        <v>4.44</v>
       </c>
       <c r="J82" s="29" t="n">
-        <v>4.62</v>
+        <v>4.34</v>
       </c>
       <c r="K82" s="30" t="n">
-        <v>4.65</v>
+        <v>4.46</v>
       </c>
       <c r="L82" s="31" t="n">
-        <v>4.62</v>
+        <v>4.3</v>
       </c>
       <c r="M82" s="31" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="N82" s="32" t="inlineStr">
         <is>
@@ -5730,16 +5730,16 @@
         </is>
       </c>
       <c r="O82" s="33" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="P82" s="33" t="n">
-        <v>4.65</v>
+        <v>4.48</v>
       </c>
       <c r="Q82" s="34" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="R82" s="36" t="n">
-        <v>0</v>
+        <v>4.55</v>
+      </c>
+      <c r="R82" s="35" t="n">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="83">
@@ -5754,37 +5754,37 @@
         </is>
       </c>
       <c r="C83" s="25" t="n">
-        <v>67.2</v>
+        <v>67.58</v>
       </c>
       <c r="D83" s="25" t="n">
-        <v>65.5</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="E83" s="26" t="n">
-        <v>64.08</v>
+        <v>63.17</v>
       </c>
       <c r="F83" s="27" t="n">
-        <v>64.48</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G83" s="27" t="n">
-        <v>65.31999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H83" s="28" t="n">
-        <v>63.62</v>
+        <v>62.7</v>
       </c>
       <c r="I83" s="29" t="n">
-        <v>62.78</v>
+        <v>61.7</v>
       </c>
       <c r="J83" s="29" t="n">
-        <v>61.92</v>
+        <v>60.3</v>
       </c>
       <c r="K83" s="30" t="n">
-        <v>63.12</v>
+        <v>61.83</v>
       </c>
       <c r="L83" s="31" t="n">
-        <v>61.7</v>
+        <v>59.82</v>
       </c>
       <c r="M83" s="31" t="n">
-        <v>60</v>
+        <v>57.42</v>
       </c>
       <c r="N83" s="32" t="inlineStr">
         <is>
@@ -5792,16 +5792,16 @@
         </is>
       </c>
       <c r="O83" s="33" t="n">
-        <v>63.44</v>
+        <v>62.36</v>
       </c>
       <c r="P83" s="33" t="n">
-        <v>63.26</v>
+        <v>62.02</v>
       </c>
       <c r="Q83" s="34" t="n">
-        <v>63.65</v>
+        <v>63.1</v>
       </c>
       <c r="R83" s="35" t="n">
-        <v>-0.55</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="84">
@@ -5816,37 +5816,37 @@
         </is>
       </c>
       <c r="C84" s="25" t="n">
-        <v>41.59</v>
+        <v>41.58</v>
       </c>
       <c r="D84" s="25" t="n">
-        <v>40.61</v>
+        <v>40.02</v>
       </c>
       <c r="E84" s="26" t="n">
-        <v>39.78</v>
+        <v>38.72</v>
       </c>
       <c r="F84" s="27" t="n">
-        <v>39.91</v>
+        <v>38.87</v>
       </c>
       <c r="G84" s="27" t="n">
-        <v>40.45</v>
+        <v>39.75</v>
       </c>
       <c r="H84" s="28" t="n">
-        <v>39.47</v>
+        <v>38.19</v>
       </c>
       <c r="I84" s="29" t="n">
-        <v>38.93</v>
+        <v>37.31</v>
       </c>
       <c r="J84" s="29" t="n">
-        <v>38.49</v>
+        <v>36.63</v>
       </c>
       <c r="K84" s="30" t="n">
-        <v>39.24</v>
+        <v>37.84</v>
       </c>
       <c r="L84" s="31" t="n">
-        <v>38.41</v>
+        <v>36.54</v>
       </c>
       <c r="M84" s="31" t="n">
-        <v>37.43</v>
+        <v>34.98</v>
       </c>
       <c r="N84" s="32" t="inlineStr">
         <is>
@@ -5854,16 +5854,16 @@
         </is>
       </c>
       <c r="O84" s="33" t="n">
-        <v>39.39</v>
+        <v>38.08</v>
       </c>
       <c r="P84" s="33" t="n">
-        <v>39.31</v>
+        <v>37.96</v>
       </c>
       <c r="Q84" s="34" t="n">
-        <v>39.38</v>
+        <v>38</v>
       </c>
       <c r="R84" s="35" t="n">
-        <v>-3.05</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="85">
@@ -5878,37 +5878,37 @@
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>98.68000000000001</v>
+        <v>99.11</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>97.18000000000001</v>
+        <v>97.56</v>
       </c>
       <c r="E85" s="26" t="n">
-        <v>95.92</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="F85" s="27" t="n">
-        <v>96.22</v>
+        <v>96.92</v>
       </c>
       <c r="G85" s="27" t="n">
-        <v>96.98</v>
+        <v>97.53</v>
       </c>
       <c r="H85" s="28" t="n">
-        <v>95.48</v>
+        <v>95.98</v>
       </c>
       <c r="I85" s="29" t="n">
-        <v>94.72</v>
+        <v>95.37</v>
       </c>
       <c r="J85" s="29" t="n">
-        <v>93.98</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="K85" s="30" t="n">
-        <v>95.08</v>
+        <v>95.39</v>
       </c>
       <c r="L85" s="31" t="n">
-        <v>93.81999999999999</v>
+        <v>94.09</v>
       </c>
       <c r="M85" s="31" t="n">
-        <v>92.31999999999999</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
@@ -5916,16 +5916,16 @@
         </is>
       </c>
       <c r="O85" s="33" t="n">
-        <v>95.34</v>
+        <v>95.75</v>
       </c>
       <c r="P85" s="33" t="n">
-        <v>95.2</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="Q85" s="34" t="n">
-        <v>95.45</v>
+        <v>96.3</v>
       </c>
       <c r="R85" s="36" t="n">
-        <v>0.26</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="86">
@@ -5940,34 +5940,34 @@
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>17.6</v>
+        <v>17.76</v>
       </c>
       <c r="D86" s="25" t="n">
-        <v>17.41</v>
+        <v>17.53</v>
       </c>
       <c r="E86" s="26" t="n">
-        <v>17.25</v>
+        <v>17.34</v>
       </c>
       <c r="F86" s="27" t="n">
-        <v>17.31</v>
+        <v>17.43</v>
       </c>
       <c r="G86" s="27" t="n">
-        <v>17.39</v>
+        <v>17.53</v>
       </c>
       <c r="H86" s="28" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="I86" s="29" t="n">
         <v>17.2</v>
       </c>
-      <c r="I86" s="29" t="n">
-        <v>17.12</v>
-      </c>
       <c r="J86" s="29" t="n">
-        <v>17.01</v>
+        <v>17.07</v>
       </c>
       <c r="K86" s="30" t="n">
-        <v>17.14</v>
+        <v>17.21</v>
       </c>
       <c r="L86" s="31" t="n">
-        <v>16.98</v>
+        <v>17.02</v>
       </c>
       <c r="M86" s="31" t="n">
         <v>16.79</v>
@@ -5978,16 +5978,16 @@
         </is>
       </c>
       <c r="O86" s="33" t="n">
-        <v>17.18</v>
+        <v>17.26</v>
       </c>
       <c r="P86" s="33" t="n">
-        <v>17.16</v>
+        <v>17.23</v>
       </c>
       <c r="Q86" s="34" t="n">
-        <v>17.22</v>
+        <v>17.34</v>
       </c>
       <c r="R86" s="36" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="87">
@@ -6002,37 +6002,37 @@
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>127.01</v>
+        <v>120.65</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>123.11</v>
+        <v>118.95</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>119.84</v>
+        <v>117.53</v>
       </c>
       <c r="F87" s="27" t="n">
-        <v>120.47</v>
+        <v>117.8</v>
       </c>
       <c r="G87" s="27" t="n">
-        <v>122.53</v>
+        <v>118.7</v>
       </c>
       <c r="H87" s="28" t="n">
-        <v>118.63</v>
+        <v>117</v>
       </c>
       <c r="I87" s="29" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="J87" s="29" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="K87" s="30" t="n">
         <v>116.57</v>
       </c>
-      <c r="J87" s="29" t="n">
-        <v>114.73</v>
-      </c>
-      <c r="K87" s="30" t="n">
-        <v>117.66</v>
-      </c>
       <c r="L87" s="31" t="n">
-        <v>114.39</v>
+        <v>115.15</v>
       </c>
       <c r="M87" s="31" t="n">
-        <v>110.49</v>
+        <v>113.45</v>
       </c>
       <c r="N87" s="32" t="inlineStr">
         <is>
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="O87" s="33" t="n">
-        <v>118.3</v>
+        <v>116.85</v>
       </c>
       <c r="P87" s="33" t="n">
-        <v>117.96</v>
+        <v>116.71</v>
       </c>
       <c r="Q87" s="34" t="n">
-        <v>118.4</v>
+        <v>116.9</v>
       </c>
       <c r="R87" s="35" t="n">
-        <v>-1.09</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="88">
@@ -6064,37 +6064,37 @@
         </is>
       </c>
       <c r="C88" s="25" t="n">
-        <v>66.76000000000001</v>
+        <v>65.09</v>
       </c>
       <c r="D88" s="25" t="n">
-        <v>64.81</v>
+        <v>63.49</v>
       </c>
       <c r="E88" s="26" t="n">
-        <v>63.17</v>
+        <v>62.15</v>
       </c>
       <c r="F88" s="27" t="n">
-        <v>63.45</v>
+        <v>62.17</v>
       </c>
       <c r="G88" s="27" t="n">
-        <v>64.5</v>
+        <v>63.13</v>
       </c>
       <c r="H88" s="28" t="n">
-        <v>62.55</v>
+        <v>61.53</v>
       </c>
       <c r="I88" s="29" t="n">
-        <v>61.5</v>
+        <v>60.57</v>
       </c>
       <c r="J88" s="29" t="n">
-        <v>60.6</v>
+        <v>59.93</v>
       </c>
       <c r="K88" s="30" t="n">
-        <v>62.08</v>
+        <v>61.25</v>
       </c>
       <c r="L88" s="31" t="n">
-        <v>60.44</v>
+        <v>59.91</v>
       </c>
       <c r="M88" s="31" t="n">
-        <v>58.49</v>
+        <v>58.31</v>
       </c>
       <c r="N88" s="32" t="inlineStr">
         <is>
@@ -6102,16 +6102,16 @@
         </is>
       </c>
       <c r="O88" s="33" t="n">
-        <v>62.39</v>
+        <v>61.46</v>
       </c>
       <c r="P88" s="33" t="n">
-        <v>62.23</v>
+        <v>61.38</v>
       </c>
       <c r="Q88" s="34" t="n">
-        <v>62.4</v>
+        <v>61.2</v>
       </c>
       <c r="R88" s="35" t="n">
-        <v>-1.89</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="89">
@@ -6126,54 +6126,54 @@
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>10.02</v>
+        <v>10.09</v>
       </c>
       <c r="D89" s="25" t="n">
-        <v>9.82</v>
+        <v>9.85</v>
       </c>
       <c r="E89" s="26" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
       <c r="F89" s="27" t="n">
-        <v>9.640000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="G89" s="27" t="n">
-        <v>9.77</v>
+        <v>9.83</v>
       </c>
       <c r="H89" s="28" t="n">
-        <v>9.57</v>
+        <v>9.59</v>
       </c>
       <c r="I89" s="29" t="n">
-        <v>9.44</v>
+        <v>9.49</v>
       </c>
       <c r="J89" s="29" t="n">
-        <v>9.369999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="K89" s="30" t="n">
-        <v>9.539999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="L89" s="31" t="n">
-        <v>9.380000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="M89" s="31" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="N89" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>9.07</v>
+      </c>
+      <c r="N89" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O89" s="33" t="n">
         <v>9.56</v>
       </c>
       <c r="P89" s="33" t="n">
-        <v>9.56</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="Q89" s="34" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="R89" s="35" t="n">
-        <v>-1.04</v>
+        <v>9.619999999999999</v>
+      </c>
+      <c r="R89" s="36" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="90">
@@ -6188,37 +6188,37 @@
         </is>
       </c>
       <c r="C90" s="25" t="n">
-        <v>12.99</v>
+        <v>12.55</v>
       </c>
       <c r="D90" s="25" t="n">
-        <v>12.65</v>
+        <v>12.34</v>
       </c>
       <c r="E90" s="26" t="n">
-        <v>12.37</v>
+        <v>12.16</v>
       </c>
       <c r="F90" s="27" t="n">
-        <v>12.33</v>
+        <v>12.17</v>
       </c>
       <c r="G90" s="27" t="n">
-        <v>12.55</v>
+        <v>12.3</v>
       </c>
       <c r="H90" s="28" t="n">
-        <v>12.21</v>
+        <v>12.09</v>
       </c>
       <c r="I90" s="29" t="n">
-        <v>11.99</v>
+        <v>11.96</v>
       </c>
       <c r="J90" s="29" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="K90" s="30" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="L90" s="31" t="n">
         <v>11.87</v>
       </c>
-      <c r="K90" s="30" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="L90" s="31" t="n">
-        <v>11.89</v>
-      </c>
       <c r="M90" s="31" t="n">
-        <v>11.55</v>
+        <v>11.66</v>
       </c>
       <c r="N90" s="32" t="inlineStr">
         <is>
@@ -6226,16 +6226,16 @@
         </is>
       </c>
       <c r="O90" s="33" t="n">
-        <v>12.21</v>
+        <v>12.07</v>
       </c>
       <c r="P90" s="33" t="n">
-        <v>12.2</v>
+        <v>12.06</v>
       </c>
       <c r="Q90" s="34" t="n">
-        <v>12.1</v>
+        <v>12.05</v>
       </c>
       <c r="R90" s="35" t="n">
-        <v>-1.31</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="91">
@@ -6250,54 +6250,54 @@
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>18.07</v>
+        <v>18.45</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>17.83</v>
+        <v>18.08</v>
       </c>
       <c r="E91" s="26" t="n">
-        <v>17.63</v>
+        <v>17.77</v>
       </c>
       <c r="F91" s="27" t="n">
-        <v>17.64</v>
+        <v>17.73</v>
       </c>
       <c r="G91" s="27" t="n">
-        <v>17.78</v>
+        <v>17.98</v>
       </c>
       <c r="H91" s="28" t="n">
-        <v>17.54</v>
+        <v>17.61</v>
       </c>
       <c r="I91" s="29" t="n">
-        <v>17.4</v>
+        <v>17.36</v>
       </c>
       <c r="J91" s="29" t="n">
-        <v>17.3</v>
+        <v>17.24</v>
       </c>
       <c r="K91" s="30" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="L91" s="31" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="M91" s="31" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="N91" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O91" s="33" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="P91" s="33" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="Q91" s="34" t="n">
         <v>17.49</v>
       </c>
-      <c r="L91" s="31" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="M91" s="31" t="n">
-        <v>17.05</v>
-      </c>
-      <c r="N91" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O91" s="33" t="n">
-        <v>17.53</v>
-      </c>
-      <c r="P91" s="33" t="n">
-        <v>17.51</v>
-      </c>
-      <c r="Q91" s="34" t="n">
-        <v>17.5</v>
-      </c>
       <c r="R91" s="35" t="n">
-        <v>-0.17</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="92">
@@ -6312,54 +6312,54 @@
         </is>
       </c>
       <c r="C92" s="25" t="n">
-        <v>30.76</v>
+        <v>31.08</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>29.86</v>
+        <v>29.78</v>
       </c>
       <c r="E92" s="26" t="n">
-        <v>29.1</v>
+        <v>28.69</v>
       </c>
       <c r="F92" s="27" t="n">
-        <v>29.17</v>
+        <v>28.76</v>
       </c>
       <c r="G92" s="27" t="n">
-        <v>29.69</v>
+        <v>29.52</v>
       </c>
       <c r="H92" s="28" t="n">
-        <v>28.79</v>
+        <v>28.22</v>
       </c>
       <c r="I92" s="29" t="n">
-        <v>28.27</v>
+        <v>27.46</v>
       </c>
       <c r="J92" s="29" t="n">
-        <v>27.89</v>
+        <v>26.92</v>
       </c>
       <c r="K92" s="30" t="n">
-        <v>28.6</v>
+        <v>27.97</v>
       </c>
       <c r="L92" s="31" t="n">
-        <v>27.84</v>
+        <v>26.88</v>
       </c>
       <c r="M92" s="31" t="n">
-        <v>26.94</v>
-      </c>
-      <c r="N92" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>25.58</v>
+      </c>
+      <c r="N92" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O92" s="33" t="n">
-        <v>28.73</v>
+        <v>28.14</v>
       </c>
       <c r="P92" s="33" t="n">
-        <v>28.67</v>
+        <v>28.07</v>
       </c>
       <c r="Q92" s="34" t="n">
-        <v>28.66</v>
-      </c>
-      <c r="R92" s="36" t="n">
-        <v>3.62</v>
+        <v>28</v>
+      </c>
+      <c r="R92" s="35" t="n">
+        <v>-2.3</v>
       </c>
     </row>
     <row r="93">
@@ -6374,37 +6374,37 @@
         </is>
       </c>
       <c r="C93" s="25" t="n">
-        <v>21.86</v>
+        <v>21.36</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>21.41</v>
+        <v>20.98</v>
       </c>
       <c r="E93" s="26" t="n">
-        <v>21.03</v>
+        <v>20.67</v>
       </c>
       <c r="F93" s="27" t="n">
-        <v>21.02</v>
+        <v>20.77</v>
       </c>
       <c r="G93" s="27" t="n">
-        <v>21.3</v>
+        <v>20.95</v>
       </c>
       <c r="H93" s="28" t="n">
-        <v>20.85</v>
+        <v>20.57</v>
       </c>
       <c r="I93" s="29" t="n">
-        <v>20.57</v>
+        <v>20.39</v>
       </c>
       <c r="J93" s="29" t="n">
-        <v>20.4</v>
+        <v>20.19</v>
       </c>
       <c r="K93" s="30" t="n">
-        <v>20.78</v>
+        <v>20.45</v>
       </c>
       <c r="L93" s="31" t="n">
-        <v>20.4</v>
+        <v>20.14</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>19.95</v>
+        <v>19.76</v>
       </c>
       <c r="N93" s="32" t="inlineStr">
         <is>
@@ -6412,16 +6412,16 @@
         </is>
       </c>
       <c r="O93" s="33" t="n">
-        <v>20.83</v>
+        <v>20.53</v>
       </c>
       <c r="P93" s="33" t="n">
-        <v>20.81</v>
+        <v>20.48</v>
       </c>
       <c r="Q93" s="34" t="n">
-        <v>20.74</v>
+        <v>20.59</v>
       </c>
       <c r="R93" s="35" t="n">
-        <v>-1.24</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="94">
@@ -6436,37 +6436,37 @@
         </is>
       </c>
       <c r="C94" s="25" t="n">
-        <v>28.8</v>
+        <v>27.94</v>
       </c>
       <c r="D94" s="25" t="n">
-        <v>28.06</v>
+        <v>27.36</v>
       </c>
       <c r="E94" s="26" t="n">
-        <v>27.44</v>
+        <v>26.87</v>
       </c>
       <c r="F94" s="27" t="n">
-        <v>27.35</v>
+        <v>27.17</v>
       </c>
       <c r="G94" s="27" t="n">
-        <v>27.85</v>
+        <v>27.37</v>
       </c>
       <c r="H94" s="28" t="n">
-        <v>27.11</v>
+        <v>26.79</v>
       </c>
       <c r="I94" s="29" t="n">
-        <v>26.61</v>
+        <v>26.59</v>
       </c>
       <c r="J94" s="29" t="n">
-        <v>26.37</v>
+        <v>26.21</v>
       </c>
       <c r="K94" s="30" t="n">
-        <v>27.02</v>
+        <v>26.55</v>
       </c>
       <c r="L94" s="31" t="n">
-        <v>26.4</v>
+        <v>26.06</v>
       </c>
       <c r="M94" s="31" t="n">
-        <v>25.66</v>
+        <v>25.48</v>
       </c>
       <c r="N94" s="32" t="inlineStr">
         <is>
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="O94" s="33" t="n">
-        <v>27.09</v>
+        <v>26.69</v>
       </c>
       <c r="P94" s="33" t="n">
-        <v>27.08</v>
+        <v>26.59</v>
       </c>
       <c r="Q94" s="34" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="R94" s="35" t="n">
-        <v>-0.89</v>
+        <v>26.96</v>
+      </c>
+      <c r="R94" s="36" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="95">
@@ -6498,54 +6498,54 @@
         </is>
       </c>
       <c r="C95" s="25" t="n">
-        <v>177.85</v>
+        <v>182.76</v>
       </c>
       <c r="D95" s="25" t="n">
-        <v>174.85</v>
+        <v>177.16</v>
       </c>
       <c r="E95" s="26" t="n">
-        <v>172.34</v>
+        <v>172.47</v>
       </c>
       <c r="F95" s="27" t="n">
-        <v>172</v>
+        <v>175.1</v>
       </c>
       <c r="G95" s="27" t="n">
-        <v>174</v>
+        <v>177.2</v>
       </c>
       <c r="H95" s="28" t="n">
-        <v>171</v>
+        <v>171.6</v>
       </c>
       <c r="I95" s="29" t="n">
-        <v>169</v>
+        <v>169.5</v>
       </c>
       <c r="J95" s="29" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K95" s="30" t="n">
-        <v>170.66</v>
+        <v>169.33</v>
       </c>
       <c r="L95" s="31" t="n">
-        <v>168.15</v>
+        <v>164.64</v>
       </c>
       <c r="M95" s="31" t="n">
-        <v>165.15</v>
-      </c>
-      <c r="N95" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>159.04</v>
+      </c>
+      <c r="N95" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O95" s="33" t="n">
-        <v>170.95</v>
+        <v>170.68</v>
       </c>
       <c r="P95" s="33" t="n">
-        <v>170.89</v>
+        <v>169.77</v>
       </c>
       <c r="Q95" s="34" t="n">
-        <v>170</v>
-      </c>
-      <c r="R95" s="35" t="n">
-        <v>-1.73</v>
+        <v>173</v>
+      </c>
+      <c r="R95" s="36" t="n">
+        <v>1.76</v>
       </c>
     </row>
     <row r="96">
@@ -6560,37 +6560,37 @@
         </is>
       </c>
       <c r="C96" s="25" t="n">
-        <v>14.17</v>
+        <v>14.59</v>
       </c>
       <c r="D96" s="25" t="n">
-        <v>13.57</v>
+        <v>13.82</v>
       </c>
       <c r="E96" s="26" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="F96" s="27" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="G96" s="27" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="H96" s="28" t="n">
         <v>13.07</v>
       </c>
-      <c r="F96" s="27" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="G96" s="27" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="H96" s="28" t="n">
-        <v>12.86</v>
-      </c>
       <c r="I96" s="29" t="n">
-        <v>12.53</v>
+        <v>12.81</v>
       </c>
       <c r="J96" s="29" t="n">
-        <v>12.26</v>
+        <v>12.3</v>
       </c>
       <c r="K96" s="30" t="n">
-        <v>12.73</v>
+        <v>12.74</v>
       </c>
       <c r="L96" s="31" t="n">
-        <v>12.23</v>
+        <v>12.09</v>
       </c>
       <c r="M96" s="31" t="n">
-        <v>11.63</v>
+        <v>11.32</v>
       </c>
       <c r="N96" s="20" t="inlineStr">
         <is>
@@ -6598,16 +6598,16 @@
         </is>
       </c>
       <c r="O96" s="33" t="n">
-        <v>12.82</v>
+        <v>12.94</v>
       </c>
       <c r="P96" s="33" t="n">
-        <v>12.78</v>
+        <v>12.8</v>
       </c>
       <c r="Q96" s="34" t="n">
-        <v>12.79</v>
-      </c>
-      <c r="R96" s="35" t="n">
-        <v>-0.23</v>
+        <v>13.31</v>
+      </c>
+      <c r="R96" s="36" t="n">
+        <v>4.07</v>
       </c>
     </row>
     <row r="97">
@@ -6622,54 +6622,54 @@
         </is>
       </c>
       <c r="C97" s="25" t="n">
-        <v>19.31</v>
+        <v>19.85</v>
       </c>
       <c r="D97" s="25" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="E97" s="26" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="F97" s="27" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="G97" s="27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H97" s="28" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I97" s="29" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="J97" s="29" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K97" s="30" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="L97" s="31" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="M97" s="31" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="N97" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O97" s="33" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="P97" s="33" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="Q97" s="34" t="n">
         <v>19.18</v>
       </c>
-      <c r="E97" s="26" t="n">
-        <v>19.07</v>
-      </c>
-      <c r="F97" s="27" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="G97" s="27" t="n">
-        <v>19.19</v>
-      </c>
-      <c r="H97" s="28" t="n">
-        <v>19.06</v>
-      </c>
-      <c r="I97" s="29" t="n">
-        <v>19.01</v>
-      </c>
-      <c r="J97" s="29" t="n">
-        <v>18.93</v>
-      </c>
-      <c r="K97" s="30" t="n">
-        <v>19</v>
-      </c>
-      <c r="L97" s="31" t="n">
-        <v>18.89</v>
-      </c>
-      <c r="M97" s="31" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="N97" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O97" s="33" t="n">
-        <v>19.03</v>
-      </c>
-      <c r="P97" s="33" t="n">
-        <v>19.01</v>
-      </c>
-      <c r="Q97" s="34" t="n">
-        <v>19.1</v>
-      </c>
       <c r="R97" s="36" t="n">
-        <v>0.74</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="98">
@@ -6684,19 +6684,19 @@
         </is>
       </c>
       <c r="C98" s="25" t="n">
-        <v>16.29</v>
+        <v>16.19</v>
       </c>
       <c r="D98" s="25" t="n">
-        <v>16.11</v>
+        <v>16.07</v>
       </c>
       <c r="E98" s="26" t="n">
-        <v>15.96</v>
+        <v>15.97</v>
       </c>
       <c r="F98" s="27" t="n">
-        <v>16.04</v>
+        <v>15.98</v>
       </c>
       <c r="G98" s="27" t="n">
-        <v>16.11</v>
+        <v>16.05</v>
       </c>
       <c r="H98" s="28" t="n">
         <v>15.93</v>
@@ -6705,16 +6705,16 @@
         <v>15.86</v>
       </c>
       <c r="J98" s="29" t="n">
-        <v>15.75</v>
+        <v>15.81</v>
       </c>
       <c r="K98" s="30" t="n">
-        <v>15.86</v>
+        <v>15.91</v>
       </c>
       <c r="L98" s="31" t="n">
-        <v>15.71</v>
+        <v>15.81</v>
       </c>
       <c r="M98" s="31" t="n">
-        <v>15.53</v>
+        <v>15.69</v>
       </c>
       <c r="N98" s="32" t="inlineStr">
         <is>
@@ -6722,16 +6722,16 @@
         </is>
       </c>
       <c r="O98" s="33" t="n">
-        <v>15.9</v>
+        <v>15.92</v>
       </c>
       <c r="P98" s="33" t="n">
-        <v>15.87</v>
+        <v>15.92</v>
       </c>
       <c r="Q98" s="34" t="n">
-        <v>15.97</v>
+        <v>15.91</v>
       </c>
       <c r="R98" s="35" t="n">
-        <v>-0.13</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="99">
@@ -6746,54 +6746,54 @@
         </is>
       </c>
       <c r="C99" s="25" t="n">
-        <v>10.08</v>
+        <v>9.83</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>9.84</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E99" s="26" t="n">
-        <v>9.640000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="F99" s="27" t="n">
-        <v>9.609999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="G99" s="27" t="n">
-        <v>9.77</v>
+        <v>9.6</v>
       </c>
       <c r="H99" s="28" t="n">
-        <v>9.529999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I99" s="29" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="J99" s="29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K99" s="30" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="L99" s="31" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="M99" s="31" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="N99" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O99" s="33" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="P99" s="33" t="n">
         <v>9.369999999999999</v>
       </c>
-      <c r="J99" s="29" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="K99" s="30" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L99" s="31" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M99" s="31" t="n">
-        <v>9.06</v>
-      </c>
-      <c r="N99" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O99" s="33" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="P99" s="33" t="n">
-        <v>9.52</v>
-      </c>
       <c r="Q99" s="34" t="n">
-        <v>9.449999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="R99" s="35" t="n">
-        <v>-0.53</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="100">
@@ -6808,37 +6808,37 @@
         </is>
       </c>
       <c r="C100" s="25" t="n">
-        <v>27.17</v>
+        <v>26.88</v>
       </c>
       <c r="D100" s="25" t="n">
-        <v>26.79</v>
+        <v>26.52</v>
       </c>
       <c r="E100" s="26" t="n">
-        <v>26.48</v>
+        <v>26.22</v>
       </c>
       <c r="F100" s="27" t="n">
-        <v>26.45</v>
+        <v>26.29</v>
       </c>
       <c r="G100" s="27" t="n">
-        <v>26.69</v>
+        <v>26.47</v>
       </c>
       <c r="H100" s="28" t="n">
-        <v>26.31</v>
+        <v>26.11</v>
       </c>
       <c r="I100" s="29" t="n">
-        <v>26.07</v>
+        <v>25.93</v>
       </c>
       <c r="J100" s="29" t="n">
-        <v>25.93</v>
+        <v>25.75</v>
       </c>
       <c r="K100" s="30" t="n">
-        <v>26.26</v>
+        <v>26.02</v>
       </c>
       <c r="L100" s="31" t="n">
-        <v>25.95</v>
+        <v>25.72</v>
       </c>
       <c r="M100" s="31" t="n">
-        <v>25.57</v>
+        <v>25.36</v>
       </c>
       <c r="N100" s="32" t="inlineStr">
         <is>
@@ -6846,16 +6846,16 @@
         </is>
       </c>
       <c r="O100" s="33" t="n">
-        <v>26.3</v>
+        <v>26.08</v>
       </c>
       <c r="P100" s="33" t="n">
-        <v>26.29</v>
+        <v>26.05</v>
       </c>
       <c r="Q100" s="34" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="R100" s="35" t="n">
-        <v>-0.68</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="101">
@@ -6870,54 +6870,54 @@
         </is>
       </c>
       <c r="C101" s="25" t="n">
-        <v>17.77</v>
+        <v>18.23</v>
       </c>
       <c r="D101" s="25" t="n">
-        <v>17.63</v>
+        <v>17.93</v>
       </c>
       <c r="E101" s="26" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="F101" s="27" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="G101" s="27" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="H101" s="28" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="I101" s="29" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="J101" s="29" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="K101" s="30" t="n">
         <v>17.51</v>
       </c>
-      <c r="F101" s="27" t="n">
+      <c r="L101" s="31" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="M101" s="31" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="N101" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O101" s="33" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="P101" s="33" t="n">
         <v>17.53</v>
       </c>
-      <c r="G101" s="27" t="n">
-        <v>17.61</v>
-      </c>
-      <c r="H101" s="28" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="I101" s="29" t="n">
-        <v>17.39</v>
-      </c>
-      <c r="J101" s="29" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="K101" s="30" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="L101" s="31" t="n">
-        <v>17.31</v>
-      </c>
-      <c r="M101" s="31" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="N101" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O101" s="33" t="n">
-        <v>17.45</v>
-      </c>
-      <c r="P101" s="33" t="n">
-        <v>17.44</v>
-      </c>
       <c r="Q101" s="34" t="n">
-        <v>17.46</v>
-      </c>
-      <c r="R101" s="35" t="n">
-        <v>-0.85</v>
+        <v>17.5</v>
+      </c>
+      <c r="R101" s="36" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="102">
@@ -6932,54 +6932,54 @@
         </is>
       </c>
       <c r="C102" s="25" t="n">
-        <v>33.56</v>
+        <v>32.11</v>
       </c>
       <c r="D102" s="25" t="n">
-        <v>32.2</v>
+        <v>31.41</v>
       </c>
       <c r="E102" s="26" t="n">
-        <v>31.06</v>
+        <v>30.83</v>
       </c>
       <c r="F102" s="27" t="n">
-        <v>31.21</v>
+        <v>31.11</v>
       </c>
       <c r="G102" s="27" t="n">
-        <v>31.97</v>
+        <v>31.39</v>
       </c>
       <c r="H102" s="28" t="n">
-        <v>30.61</v>
+        <v>30.69</v>
       </c>
       <c r="I102" s="29" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="J102" s="29" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="K102" s="30" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="L102" s="31" t="n">
         <v>29.85</v>
       </c>
-      <c r="J102" s="29" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="K102" s="30" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="L102" s="31" t="n">
-        <v>29.16</v>
-      </c>
       <c r="M102" s="31" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="N102" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>29.15</v>
+      </c>
+      <c r="N102" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O102" s="33" t="n">
-        <v>30.51</v>
+        <v>30.59</v>
       </c>
       <c r="P102" s="33" t="n">
-        <v>30.41</v>
+        <v>30.49</v>
       </c>
       <c r="Q102" s="34" t="n">
-        <v>30.46</v>
-      </c>
-      <c r="R102" s="35" t="n">
-        <v>-1.87</v>
+        <v>30.82</v>
+      </c>
+      <c r="R102" s="36" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="103">
@@ -6994,54 +6994,54 @@
         </is>
       </c>
       <c r="C103" s="25" t="n">
-        <v>15.81</v>
+        <v>15.94</v>
       </c>
       <c r="D103" s="25" t="n">
-        <v>15.31</v>
+        <v>15.48</v>
       </c>
       <c r="E103" s="26" t="n">
-        <v>14.89</v>
+        <v>15.1</v>
       </c>
       <c r="F103" s="27" t="n">
-        <v>15.09</v>
+        <v>15.18</v>
       </c>
       <c r="G103" s="27" t="n">
-        <v>15.3</v>
+        <v>15.42</v>
       </c>
       <c r="H103" s="28" t="n">
-        <v>14.8</v>
+        <v>14.96</v>
       </c>
       <c r="I103" s="29" t="n">
-        <v>14.59</v>
+        <v>14.72</v>
       </c>
       <c r="J103" s="29" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="K103" s="30" t="n">
-        <v>14.61</v>
+        <v>14.84</v>
       </c>
       <c r="L103" s="31" t="n">
-        <v>14.19</v>
+        <v>14.46</v>
       </c>
       <c r="M103" s="31" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="N103" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>14</v>
+      </c>
+      <c r="N103" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O103" s="33" t="n">
-        <v>14.72</v>
+        <v>14.92</v>
       </c>
       <c r="P103" s="33" t="n">
-        <v>14.65</v>
+        <v>14.88</v>
       </c>
       <c r="Q103" s="34" t="n">
-        <v>14.89</v>
+        <v>14.94</v>
       </c>
       <c r="R103" s="36" t="n">
-        <v>0.47</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="104">
@@ -7056,37 +7056,37 @@
         </is>
       </c>
       <c r="C104" s="25" t="n">
-        <v>76.52</v>
+        <v>74.64</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>73.56999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="E104" s="26" t="n">
-        <v>71.09999999999999</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="F104" s="27" t="n">
-        <v>72.37</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="G104" s="27" t="n">
-        <v>73.53</v>
+        <v>72.73</v>
       </c>
       <c r="H104" s="28" t="n">
-        <v>70.58</v>
+        <v>70.73</v>
       </c>
       <c r="I104" s="29" t="n">
-        <v>69.42</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="J104" s="29" t="n">
-        <v>67.63</v>
+        <v>68.73</v>
       </c>
       <c r="K104" s="30" t="n">
-        <v>69.45</v>
+        <v>69.84</v>
       </c>
       <c r="L104" s="31" t="n">
-        <v>66.98</v>
+        <v>68.16</v>
       </c>
       <c r="M104" s="31" t="n">
-        <v>64.03</v>
+        <v>66.16</v>
       </c>
       <c r="N104" s="20" t="inlineStr">
         <is>
@@ -7094,16 +7094,16 @@
         </is>
       </c>
       <c r="O104" s="33" t="n">
-        <v>70.13</v>
+        <v>70.36</v>
       </c>
       <c r="P104" s="33" t="n">
-        <v>69.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="Q104" s="34" t="n">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="R104" s="36" t="n">
-        <v>3.19</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="105">
@@ -7118,37 +7118,37 @@
         </is>
       </c>
       <c r="C105" s="25" t="n">
-        <v>14.85</v>
+        <v>14.9</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>14.65</v>
+        <v>14.67</v>
       </c>
       <c r="E105" s="26" t="n">
-        <v>14.49</v>
+        <v>14.48</v>
       </c>
       <c r="F105" s="27" t="n">
-        <v>14.47</v>
+        <v>14.52</v>
       </c>
       <c r="G105" s="27" t="n">
-        <v>14.6</v>
+        <v>14.64</v>
       </c>
       <c r="H105" s="28" t="n">
-        <v>14.4</v>
+        <v>14.41</v>
       </c>
       <c r="I105" s="29" t="n">
-        <v>14.27</v>
+        <v>14.29</v>
       </c>
       <c r="J105" s="29" t="n">
-        <v>14.2</v>
+        <v>14.18</v>
       </c>
       <c r="K105" s="30" t="n">
-        <v>14.37</v>
+        <v>14.35</v>
       </c>
       <c r="L105" s="31" t="n">
-        <v>14.21</v>
+        <v>14.16</v>
       </c>
       <c r="M105" s="31" t="n">
-        <v>14.01</v>
+        <v>13.93</v>
       </c>
       <c r="N105" s="32" t="inlineStr">
         <is>
@@ -7159,13 +7159,13 @@
         <v>14.39</v>
       </c>
       <c r="P105" s="33" t="n">
-        <v>14.39</v>
+        <v>14.37</v>
       </c>
       <c r="Q105" s="34" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="R105" s="35" t="n">
-        <v>-0.14</v>
+        <v>14.4</v>
+      </c>
+      <c r="R105" s="36" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="106">
@@ -7180,54 +7180,54 @@
         </is>
       </c>
       <c r="C106" s="25" t="n">
-        <v>15.37</v>
+        <v>15.77</v>
       </c>
       <c r="D106" s="25" t="n">
-        <v>15.12</v>
+        <v>15.17</v>
       </c>
       <c r="E106" s="26" t="n">
-        <v>14.92</v>
+        <v>14.67</v>
       </c>
       <c r="F106" s="27" t="n">
-        <v>14.97</v>
+        <v>14.71</v>
       </c>
       <c r="G106" s="27" t="n">
-        <v>15.09</v>
+        <v>15.06</v>
       </c>
       <c r="H106" s="28" t="n">
-        <v>14.84</v>
+        <v>14.46</v>
       </c>
       <c r="I106" s="29" t="n">
-        <v>14.72</v>
+        <v>14.11</v>
       </c>
       <c r="J106" s="29" t="n">
-        <v>14.59</v>
+        <v>13.86</v>
       </c>
       <c r="K106" s="30" t="n">
-        <v>14.78</v>
+        <v>14.33</v>
       </c>
       <c r="L106" s="31" t="n">
-        <v>14.57</v>
+        <v>13.83</v>
       </c>
       <c r="M106" s="31" t="n">
-        <v>14.32</v>
-      </c>
-      <c r="N106" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>13.23</v>
+      </c>
+      <c r="N106" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O106" s="33" t="n">
-        <v>14.82</v>
+        <v>14.42</v>
       </c>
       <c r="P106" s="33" t="n">
-        <v>14.79</v>
+        <v>14.38</v>
       </c>
       <c r="Q106" s="34" t="n">
-        <v>14.84</v>
-      </c>
-      <c r="R106" s="36" t="n">
-        <v>1.23</v>
+        <v>14.37</v>
+      </c>
+      <c r="R106" s="35" t="n">
+        <v>-3.17</v>
       </c>
     </row>
     <row r="107">
@@ -7242,54 +7242,54 @@
         </is>
       </c>
       <c r="C107" s="25" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="D107" s="25" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="E107" s="26" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="F107" s="27" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="G107" s="27" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="H107" s="28" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I107" s="29" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="J107" s="29" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="K107" s="30" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="L107" s="31" t="n">
         <v>2.28</v>
       </c>
       <c r="M107" s="31" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="N107" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>2.2</v>
+      </c>
+      <c r="N107" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O107" s="33" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="P107" s="33" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q107" s="34" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="R107" s="36" t="n">
-        <v>1.28</v>
+        <v>2.34</v>
+      </c>
+      <c r="R107" s="35" t="n">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="108">
@@ -7304,37 +7304,37 @@
         </is>
       </c>
       <c r="C108" s="25" t="n">
-        <v>42.94</v>
+        <v>43.92</v>
       </c>
       <c r="D108" s="25" t="n">
-        <v>42.2</v>
+        <v>42.24</v>
       </c>
       <c r="E108" s="26" t="n">
-        <v>41.58</v>
+        <v>40.83</v>
       </c>
       <c r="F108" s="27" t="n">
-        <v>41.63</v>
+        <v>40.88</v>
       </c>
       <c r="G108" s="27" t="n">
-        <v>42.05</v>
+        <v>41.88</v>
       </c>
       <c r="H108" s="28" t="n">
-        <v>41.31</v>
+        <v>40.2</v>
       </c>
       <c r="I108" s="29" t="n">
-        <v>40.89</v>
+        <v>39.2</v>
       </c>
       <c r="J108" s="29" t="n">
-        <v>40.57</v>
+        <v>38.52</v>
       </c>
       <c r="K108" s="30" t="n">
-        <v>41.16</v>
+        <v>39.89</v>
       </c>
       <c r="L108" s="31" t="n">
-        <v>40.54</v>
+        <v>38.48</v>
       </c>
       <c r="M108" s="31" t="n">
-        <v>39.8</v>
+        <v>36.8</v>
       </c>
       <c r="N108" s="32" t="inlineStr">
         <is>
@@ -7342,16 +7342,16 @@
         </is>
       </c>
       <c r="O108" s="33" t="n">
-        <v>41.27</v>
+        <v>40.11</v>
       </c>
       <c r="P108" s="33" t="n">
-        <v>41.22</v>
+        <v>40.02</v>
       </c>
       <c r="Q108" s="34" t="n">
-        <v>41.2</v>
+        <v>39.88</v>
       </c>
       <c r="R108" s="35" t="n">
-        <v>-1.29</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="109">
@@ -7366,37 +7366,37 @@
         </is>
       </c>
       <c r="C109" s="25" t="n">
-        <v>8.970000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="D109" s="25" t="n">
-        <v>8.6</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E109" s="26" t="n">
-        <v>8.289999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="F109" s="27" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="G109" s="27" t="n">
         <v>8.25</v>
       </c>
-      <c r="G109" s="27" t="n">
-        <v>8.49</v>
-      </c>
       <c r="H109" s="28" t="n">
-        <v>8.119999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="I109" s="29" t="n">
-        <v>7.88</v>
+        <v>7.71</v>
       </c>
       <c r="J109" s="29" t="n">
-        <v>7.75</v>
+        <v>7.51</v>
       </c>
       <c r="K109" s="30" t="n">
-        <v>8.08</v>
+        <v>7.77</v>
       </c>
       <c r="L109" s="31" t="n">
-        <v>7.77</v>
+        <v>7.46</v>
       </c>
       <c r="M109" s="31" t="n">
-        <v>7.4</v>
+        <v>7.09</v>
       </c>
       <c r="N109" s="32" t="inlineStr">
         <is>
@@ -7404,16 +7404,16 @@
         </is>
       </c>
       <c r="O109" s="33" t="n">
-        <v>8.119999999999999</v>
+        <v>7.84</v>
       </c>
       <c r="P109" s="33" t="n">
-        <v>8.109999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Q109" s="34" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="R109" s="35" t="n">
-        <v>-3.03</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="110">
@@ -7428,54 +7428,54 @@
         </is>
       </c>
       <c r="C110" s="25" t="n">
-        <v>44.06</v>
+        <v>44.55</v>
       </c>
       <c r="D110" s="25" t="n">
-        <v>43.84</v>
+        <v>44.15</v>
       </c>
       <c r="E110" s="26" t="n">
-        <v>43.65</v>
+        <v>43.81</v>
       </c>
       <c r="F110" s="27" t="n">
-        <v>43.69</v>
+        <v>43.77</v>
       </c>
       <c r="G110" s="27" t="n">
-        <v>43.81</v>
+        <v>44.03</v>
       </c>
       <c r="H110" s="28" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="I110" s="29" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="J110" s="29" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="K110" s="30" t="n">
         <v>43.59</v>
       </c>
-      <c r="I110" s="29" t="n">
-        <v>43.47</v>
-      </c>
-      <c r="J110" s="29" t="n">
-        <v>43.37</v>
-      </c>
-      <c r="K110" s="30" t="n">
-        <v>43.53</v>
-      </c>
       <c r="L110" s="31" t="n">
-        <v>43.34</v>
+        <v>43.25</v>
       </c>
       <c r="M110" s="31" t="n">
-        <v>43.12</v>
-      </c>
-      <c r="N110" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>42.85</v>
+      </c>
+      <c r="N110" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O110" s="33" t="n">
-        <v>43.57</v>
+        <v>43.63</v>
       </c>
       <c r="P110" s="33" t="n">
-        <v>43.55</v>
+        <v>43.62</v>
       </c>
       <c r="Q110" s="34" t="n">
-        <v>43.58</v>
-      </c>
-      <c r="R110" s="36" t="n">
-        <v>0.46</v>
+        <v>43.5</v>
+      </c>
+      <c r="R110" s="35" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="111">
@@ -7490,54 +7490,54 @@
         </is>
       </c>
       <c r="C111" s="25" t="n">
-        <v>63.62</v>
+        <v>64.3</v>
       </c>
       <c r="D111" s="25" t="n">
-        <v>62.62</v>
+        <v>63.25</v>
       </c>
       <c r="E111" s="26" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="F111" s="27" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="G111" s="27" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="H111" s="28" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="I111" s="29" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="J111" s="29" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="K111" s="30" t="n">
         <v>61.78</v>
       </c>
-      <c r="F111" s="27" t="n">
-        <v>62</v>
-      </c>
-      <c r="G111" s="27" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H111" s="28" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="I111" s="29" t="n">
-        <v>61</v>
-      </c>
-      <c r="J111" s="29" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="K111" s="30" t="n">
-        <v>61.22</v>
-      </c>
       <c r="L111" s="31" t="n">
-        <v>60.38</v>
+        <v>60.9</v>
       </c>
       <c r="M111" s="31" t="n">
-        <v>59.38</v>
-      </c>
-      <c r="N111" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>59.85</v>
+      </c>
+      <c r="N111" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O111" s="33" t="n">
-        <v>61.4</v>
+        <v>62.06</v>
       </c>
       <c r="P111" s="33" t="n">
-        <v>61.3</v>
+        <v>61.86</v>
       </c>
       <c r="Q111" s="34" t="n">
-        <v>61.5</v>
+        <v>62.6</v>
       </c>
       <c r="R111" s="36" t="n">
-        <v>0.33</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="112">
@@ -7552,54 +7552,54 @@
         </is>
       </c>
       <c r="C112" s="25" t="n">
-        <v>10.43</v>
+        <v>10.49</v>
       </c>
       <c r="D112" s="25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" s="26" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="F112" s="27" t="n">
         <v>10.36</v>
       </c>
-      <c r="E112" s="26" t="n">
+      <c r="G112" s="27" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="H112" s="28" t="n">
         <v>10.3</v>
       </c>
-      <c r="F112" s="27" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="G112" s="27" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="H112" s="28" t="n">
-        <v>10.29</v>
-      </c>
       <c r="I112" s="29" t="n">
-        <v>10.25</v>
+        <v>10.27</v>
       </c>
       <c r="J112" s="29" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
       <c r="K112" s="30" t="n">
         <v>10.27</v>
       </c>
       <c r="L112" s="31" t="n">
-        <v>10.21</v>
+        <v>10.19</v>
       </c>
       <c r="M112" s="31" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="N112" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>10.1</v>
+      </c>
+      <c r="N112" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O112" s="33" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="P112" s="33" t="n">
         <v>10.28</v>
       </c>
-      <c r="P112" s="33" t="n">
-        <v>10.27</v>
-      </c>
       <c r="Q112" s="34" t="n">
-        <v>10.29</v>
+        <v>10.32</v>
       </c>
       <c r="R112" s="36" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="113">
@@ -7614,37 +7614,37 @@
         </is>
       </c>
       <c r="C113" s="25" t="n">
-        <v>329.88</v>
+        <v>310.94</v>
       </c>
       <c r="D113" s="25" t="n">
-        <v>309.68</v>
+        <v>302.94</v>
       </c>
       <c r="E113" s="26" t="n">
-        <v>292.76</v>
+        <v>296.24</v>
       </c>
       <c r="F113" s="27" t="n">
-        <v>300.6</v>
+        <v>298.27</v>
       </c>
       <c r="G113" s="27" t="n">
-        <v>309</v>
+        <v>302.13</v>
       </c>
       <c r="H113" s="28" t="n">
-        <v>288.8</v>
+        <v>294.13</v>
       </c>
       <c r="I113" s="29" t="n">
-        <v>280.4</v>
+        <v>290.27</v>
       </c>
       <c r="J113" s="29" t="n">
-        <v>268.6</v>
+        <v>286.13</v>
       </c>
       <c r="K113" s="30" t="n">
-        <v>281.44</v>
+        <v>291.76</v>
       </c>
       <c r="L113" s="31" t="n">
-        <v>264.52</v>
+        <v>285.06</v>
       </c>
       <c r="M113" s="31" t="n">
-        <v>244.32</v>
+        <v>277.06</v>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
@@ -7652,16 +7652,16 @@
         </is>
       </c>
       <c r="O113" s="33" t="n">
-        <v>285.91</v>
+        <v>293.26</v>
       </c>
       <c r="P113" s="33" t="n">
-        <v>283.02</v>
+        <v>292.38</v>
       </c>
       <c r="Q113" s="34" t="n">
-        <v>292.2</v>
+        <v>294.4</v>
       </c>
       <c r="R113" s="36" t="n">
-        <v>4.66</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="114">
@@ -7676,54 +7676,54 @@
         </is>
       </c>
       <c r="C114" s="25" t="n">
-        <v>218.59</v>
+        <v>222.05</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>214.89</v>
+        <v>216.95</v>
       </c>
       <c r="E114" s="26" t="n">
-        <v>211.79</v>
+        <v>212.68</v>
       </c>
       <c r="F114" s="27" t="n">
-        <v>211.37</v>
+        <v>214.7</v>
       </c>
       <c r="G114" s="27" t="n">
-        <v>213.83</v>
+        <v>216.8</v>
       </c>
       <c r="H114" s="28" t="n">
-        <v>210.13</v>
+        <v>211.7</v>
       </c>
       <c r="I114" s="29" t="n">
-        <v>207.67</v>
+        <v>209.6</v>
       </c>
       <c r="J114" s="29" t="n">
-        <v>206.43</v>
+        <v>206.6</v>
       </c>
       <c r="K114" s="30" t="n">
-        <v>209.71</v>
+        <v>209.82</v>
       </c>
       <c r="L114" s="31" t="n">
-        <v>206.61</v>
+        <v>205.55</v>
       </c>
       <c r="M114" s="31" t="n">
-        <v>202.91</v>
-      </c>
-      <c r="N114" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>200.45</v>
+      </c>
+      <c r="N114" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O114" s="33" t="n">
-        <v>210.07</v>
+        <v>210.96</v>
       </c>
       <c r="P114" s="33" t="n">
-        <v>210</v>
+        <v>210.22</v>
       </c>
       <c r="Q114" s="34" t="n">
-        <v>208.9</v>
-      </c>
-      <c r="R114" s="35" t="n">
-        <v>-2.06</v>
+        <v>212.6</v>
+      </c>
+      <c r="R114" s="36" t="n">
+        <v>1.77</v>
       </c>
     </row>
     <row r="115">
@@ -7738,54 +7738,54 @@
         </is>
       </c>
       <c r="C115" s="25" t="n">
-        <v>678.89</v>
+        <v>634.27</v>
       </c>
       <c r="D115" s="25" t="n">
-        <v>645.89</v>
+        <v>619.27</v>
       </c>
       <c r="E115" s="26" t="n">
-        <v>618.24</v>
+        <v>606.7</v>
       </c>
       <c r="F115" s="27" t="n">
-        <v>616.5</v>
+        <v>613</v>
       </c>
       <c r="G115" s="27" t="n">
-        <v>637.5</v>
+        <v>619</v>
       </c>
       <c r="H115" s="28" t="n">
-        <v>604.5</v>
+        <v>604</v>
       </c>
       <c r="I115" s="29" t="n">
-        <v>583.5</v>
+        <v>598</v>
       </c>
       <c r="J115" s="29" t="n">
-        <v>571.5</v>
+        <v>589</v>
       </c>
       <c r="K115" s="30" t="n">
-        <v>599.76</v>
+        <v>598.3</v>
       </c>
       <c r="L115" s="31" t="n">
-        <v>572.11</v>
+        <v>585.73</v>
       </c>
       <c r="M115" s="31" t="n">
-        <v>539.11</v>
-      </c>
-      <c r="N115" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>570.73</v>
+      </c>
+      <c r="N115" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O115" s="33" t="n">
-        <v>603.42</v>
+        <v>601.74</v>
       </c>
       <c r="P115" s="33" t="n">
-        <v>602.33</v>
+        <v>599.47</v>
       </c>
       <c r="Q115" s="34" t="n">
-        <v>595.5</v>
-      </c>
-      <c r="R115" s="35" t="n">
-        <v>-4.18</v>
+        <v>607</v>
+      </c>
+      <c r="R115" s="36" t="n">
+        <v>1.93</v>
       </c>
     </row>
     <row r="116">
@@ -7800,54 +7800,54 @@
         </is>
       </c>
       <c r="C116" s="25" t="n">
-        <v>6.8</v>
+        <v>6.66</v>
       </c>
       <c r="D116" s="25" t="n">
-        <v>6.64</v>
+        <v>6.55</v>
       </c>
       <c r="E116" s="26" t="n">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
       <c r="F116" s="27" t="n">
-        <v>6.52</v>
+        <v>6.51</v>
       </c>
       <c r="G116" s="27" t="n">
-        <v>6.61</v>
+        <v>6.55</v>
       </c>
       <c r="H116" s="28" t="n">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
       <c r="I116" s="29" t="n">
-        <v>6.36</v>
+        <v>6.4</v>
       </c>
       <c r="J116" s="29" t="n">
-        <v>6.29</v>
+        <v>6.33</v>
       </c>
       <c r="K116" s="30" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="L116" s="31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M116" s="31" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="N116" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O116" s="33" t="n">
         <v>6.42</v>
       </c>
-      <c r="L116" s="31" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="M116" s="31" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="N116" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O116" s="33" t="n">
-        <v>6.44</v>
-      </c>
       <c r="P116" s="33" t="n">
-        <v>6.43</v>
+        <v>6.4</v>
       </c>
       <c r="Q116" s="34" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="R116" s="35" t="n">
-        <v>-0.31</v>
+        <v>6.47</v>
+      </c>
+      <c r="R116" s="36" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="117">
@@ -7862,37 +7862,37 @@
         </is>
       </c>
       <c r="C117" s="25" t="n">
-        <v>144.59</v>
+        <v>147.97</v>
       </c>
       <c r="D117" s="25" t="n">
-        <v>141.69</v>
+        <v>143.97</v>
       </c>
       <c r="E117" s="26" t="n">
-        <v>139.26</v>
+        <v>140.62</v>
       </c>
       <c r="F117" s="27" t="n">
-        <v>139.47</v>
+        <v>140.17</v>
       </c>
       <c r="G117" s="27" t="n">
-        <v>141.13</v>
+        <v>142.83</v>
       </c>
       <c r="H117" s="28" t="n">
-        <v>138.23</v>
+        <v>138.83</v>
       </c>
       <c r="I117" s="29" t="n">
-        <v>136.57</v>
+        <v>136.17</v>
       </c>
       <c r="J117" s="29" t="n">
-        <v>135.33</v>
+        <v>134.83</v>
       </c>
       <c r="K117" s="30" t="n">
-        <v>137.64</v>
+        <v>138.38</v>
       </c>
       <c r="L117" s="31" t="n">
-        <v>135.21</v>
+        <v>135.03</v>
       </c>
       <c r="M117" s="31" t="n">
-        <v>132.31</v>
+        <v>131.03</v>
       </c>
       <c r="N117" s="32" t="inlineStr">
         <is>
@@ -7900,16 +7900,16 @@
         </is>
       </c>
       <c r="O117" s="33" t="n">
-        <v>138.05</v>
+        <v>138.76</v>
       </c>
       <c r="P117" s="33" t="n">
-        <v>137.86</v>
+        <v>138.69</v>
       </c>
       <c r="Q117" s="34" t="n">
-        <v>137.8</v>
+        <v>137.5</v>
       </c>
       <c r="R117" s="35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="118">
@@ -7924,37 +7924,37 @@
         </is>
       </c>
       <c r="C118" s="25" t="n">
-        <v>11.07</v>
+        <v>10.7</v>
       </c>
       <c r="D118" s="25" t="n">
-        <v>10.74</v>
+        <v>10.51</v>
       </c>
       <c r="E118" s="26" t="n">
-        <v>10.47</v>
+        <v>10.35</v>
       </c>
       <c r="F118" s="27" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="G118" s="27" t="n">
         <v>10.48</v>
       </c>
-      <c r="G118" s="27" t="n">
-        <v>10.67</v>
-      </c>
       <c r="H118" s="28" t="n">
-        <v>10.34</v>
+        <v>10.29</v>
       </c>
       <c r="I118" s="29" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="J118" s="29" t="n">
-        <v>10.01</v>
+        <v>10.1</v>
       </c>
       <c r="K118" s="30" t="n">
-        <v>10.28</v>
+        <v>10.24</v>
       </c>
       <c r="L118" s="31" t="n">
-        <v>10.01</v>
+        <v>10.08</v>
       </c>
       <c r="M118" s="31" t="n">
-        <v>9.68</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="N118" s="32" t="inlineStr">
         <is>
@@ -7962,16 +7962,16 @@
         </is>
       </c>
       <c r="O118" s="33" t="n">
-        <v>10.33</v>
+        <v>10.27</v>
       </c>
       <c r="P118" s="33" t="n">
-        <v>10.31</v>
+        <v>10.26</v>
       </c>
       <c r="Q118" s="34" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
       <c r="R118" s="35" t="n">
-        <v>-0.48</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="119">
@@ -7986,54 +7986,54 @@
         </is>
       </c>
       <c r="C119" s="25" t="n">
-        <v>17.69</v>
+        <v>18.08</v>
       </c>
       <c r="D119" s="25" t="n">
-        <v>17.39</v>
+        <v>17.67</v>
       </c>
       <c r="E119" s="26" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="F119" s="27" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="G119" s="27" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="H119" s="28" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="I119" s="29" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="J119" s="29" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="K119" s="30" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="L119" s="31" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="M119" s="31" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="N119" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O119" s="33" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="P119" s="33" t="n">
         <v>17.13</v>
       </c>
-      <c r="F119" s="27" t="n">
-        <v>17.21</v>
-      </c>
-      <c r="G119" s="27" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="H119" s="28" t="n">
-        <v>17.05</v>
-      </c>
-      <c r="I119" s="29" t="n">
-        <v>16.91</v>
-      </c>
-      <c r="J119" s="29" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="K119" s="30" t="n">
-        <v>16.97</v>
-      </c>
-      <c r="L119" s="31" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="M119" s="31" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="N119" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O119" s="33" t="n">
-        <v>17.02</v>
-      </c>
-      <c r="P119" s="33" t="n">
-        <v>16.99</v>
-      </c>
       <c r="Q119" s="34" t="n">
-        <v>17.06</v>
+        <v>17.11</v>
       </c>
       <c r="R119" s="36" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="120">
@@ -8048,37 +8048,37 @@
         </is>
       </c>
       <c r="C120" s="25" t="n">
-        <v>11.9</v>
+        <v>11.73</v>
       </c>
       <c r="D120" s="25" t="n">
-        <v>11.47</v>
+        <v>11.38</v>
       </c>
       <c r="E120" s="26" t="n">
-        <v>11.11</v>
+        <v>11.08</v>
       </c>
       <c r="F120" s="27" t="n">
         <v>11.22</v>
       </c>
       <c r="G120" s="27" t="n">
-        <v>11.43</v>
+        <v>11.36</v>
       </c>
       <c r="H120" s="28" t="n">
-        <v>11</v>
+        <v>11.01</v>
       </c>
       <c r="I120" s="29" t="n">
-        <v>10.79</v>
+        <v>10.87</v>
       </c>
       <c r="J120" s="29" t="n">
-        <v>10.57</v>
+        <v>10.66</v>
       </c>
       <c r="K120" s="30" t="n">
-        <v>10.86</v>
+        <v>10.89</v>
       </c>
       <c r="L120" s="31" t="n">
-        <v>10.5</v>
+        <v>10.59</v>
       </c>
       <c r="M120" s="31" t="n">
-        <v>10.07</v>
+        <v>10.24</v>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
@@ -8086,16 +8086,16 @@
         </is>
       </c>
       <c r="O120" s="33" t="n">
-        <v>10.95</v>
+        <v>10.96</v>
       </c>
       <c r="P120" s="33" t="n">
-        <v>10.9</v>
+        <v>10.91</v>
       </c>
       <c r="Q120" s="34" t="n">
-        <v>11.02</v>
+        <v>11.07</v>
       </c>
       <c r="R120" s="36" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="121">
@@ -8113,51 +8113,51 @@
         <v>12.87</v>
       </c>
       <c r="D121" s="25" t="n">
-        <v>12.56</v>
+        <v>12.58</v>
       </c>
       <c r="E121" s="26" t="n">
-        <v>12.3</v>
+        <v>12.34</v>
       </c>
       <c r="F121" s="27" t="n">
-        <v>12.39</v>
+        <v>12.35</v>
       </c>
       <c r="G121" s="27" t="n">
-        <v>12.54</v>
+        <v>12.52</v>
       </c>
       <c r="H121" s="28" t="n">
         <v>12.23</v>
       </c>
       <c r="I121" s="29" t="n">
-        <v>12.08</v>
+        <v>12.06</v>
       </c>
       <c r="J121" s="29" t="n">
-        <v>11.92</v>
+        <v>11.94</v>
       </c>
       <c r="K121" s="30" t="n">
-        <v>12.13</v>
+        <v>12.17</v>
       </c>
       <c r="L121" s="31" t="n">
-        <v>11.87</v>
+        <v>11.93</v>
       </c>
       <c r="M121" s="31" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="N121" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>11.64</v>
+      </c>
+      <c r="N121" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O121" s="33" t="n">
-        <v>12.19</v>
+        <v>12.21</v>
       </c>
       <c r="P121" s="33" t="n">
-        <v>12.15</v>
+        <v>12.2</v>
       </c>
       <c r="Q121" s="34" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="R121" s="36" t="n">
-        <v>0.82</v>
+        <v>12.18</v>
+      </c>
+      <c r="R121" s="35" t="n">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="122">
@@ -8172,37 +8172,37 @@
         </is>
       </c>
       <c r="C122" s="25" t="n">
-        <v>9.460000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="D122" s="25" t="n">
-        <v>8.77</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E122" s="26" t="n">
-        <v>8.19</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F122" s="27" t="n">
-        <v>8.57</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G122" s="27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="H122" s="28" t="n">
-        <v>8.109999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="I122" s="29" t="n">
-        <v>7.88</v>
+        <v>8.01</v>
       </c>
       <c r="J122" s="29" t="n">
-        <v>7.42</v>
+        <v>7.72</v>
       </c>
       <c r="K122" s="30" t="n">
-        <v>7.8</v>
+        <v>8.06</v>
       </c>
       <c r="L122" s="31" t="n">
-        <v>7.22</v>
+        <v>7.63</v>
       </c>
       <c r="M122" s="31" t="n">
-        <v>6.53</v>
+        <v>7.11</v>
       </c>
       <c r="N122" s="20" t="inlineStr">
         <is>
@@ -8210,16 +8210,16 @@
         </is>
       </c>
       <c r="O122" s="33" t="n">
-        <v>7.98</v>
+        <v>8.17</v>
       </c>
       <c r="P122" s="33" t="n">
-        <v>7.86</v>
+        <v>8.1</v>
       </c>
       <c r="Q122" s="34" t="n">
-        <v>8.34</v>
-      </c>
-      <c r="R122" s="36" t="n">
-        <v>9.880000000000001</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="R122" s="35" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="123">
@@ -8234,54 +8234,54 @@
         </is>
       </c>
       <c r="C123" s="25" t="n">
-        <v>7.49</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="D123" s="25" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="E123" s="26" t="n">
         <v>7.19</v>
       </c>
-      <c r="E123" s="26" t="n">
-        <v>6.93</v>
-      </c>
       <c r="F123" s="27" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="G123" s="27" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="H123" s="28" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="I123" s="29" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="J123" s="29" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="K123" s="30" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="L123" s="31" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M123" s="31" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="N123" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O123" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="G123" s="27" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="H123" s="28" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="I123" s="29" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J123" s="29" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="K123" s="30" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="L123" s="31" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="M123" s="31" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="N123" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O123" s="33" t="n">
-        <v>6.82</v>
-      </c>
       <c r="P123" s="33" t="n">
-        <v>6.79</v>
+        <v>6.95</v>
       </c>
       <c r="Q123" s="34" t="n">
-        <v>6.85</v>
+        <v>7.08</v>
       </c>
       <c r="R123" s="36" t="n">
-        <v>1.33</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="124">
@@ -8296,54 +8296,54 @@
         </is>
       </c>
       <c r="C124" s="25" t="n">
-        <v>26.71</v>
+        <v>25.67</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>25.52</v>
+        <v>25.06</v>
       </c>
       <c r="E124" s="26" t="n">
-        <v>24.52</v>
+        <v>24.55</v>
       </c>
       <c r="F124" s="27" t="n">
-        <v>24.99</v>
+        <v>24.48</v>
       </c>
       <c r="G124" s="27" t="n">
-        <v>25.48</v>
+        <v>24.88</v>
       </c>
       <c r="H124" s="28" t="n">
-        <v>24.29</v>
+        <v>24.27</v>
       </c>
       <c r="I124" s="29" t="n">
-        <v>23.8</v>
+        <v>23.87</v>
       </c>
       <c r="J124" s="29" t="n">
-        <v>23.1</v>
+        <v>23.66</v>
       </c>
       <c r="K124" s="30" t="n">
-        <v>23.85</v>
+        <v>24.2</v>
       </c>
       <c r="L124" s="31" t="n">
-        <v>22.85</v>
+        <v>23.69</v>
       </c>
       <c r="M124" s="31" t="n">
-        <v>21.66</v>
-      </c>
-      <c r="N124" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>23.08</v>
+      </c>
+      <c r="N124" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O124" s="33" t="n">
-        <v>24.12</v>
+        <v>24.26</v>
       </c>
       <c r="P124" s="33" t="n">
-        <v>23.94</v>
+        <v>24.25</v>
       </c>
       <c r="Q124" s="34" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="R124" s="36" t="n">
-        <v>1.58</v>
+        <v>24.07</v>
+      </c>
+      <c r="R124" s="35" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="125">
@@ -8358,37 +8358,37 @@
         </is>
       </c>
       <c r="C125" s="25" t="n">
-        <v>179.53</v>
+        <v>183.94</v>
       </c>
       <c r="D125" s="25" t="n">
-        <v>176.73</v>
+        <v>179.34</v>
       </c>
       <c r="E125" s="26" t="n">
-        <v>174.38</v>
+        <v>175.49</v>
       </c>
       <c r="F125" s="27" t="n">
-        <v>174.8</v>
+        <v>174.97</v>
       </c>
       <c r="G125" s="27" t="n">
-        <v>176.3</v>
+        <v>178.03</v>
       </c>
       <c r="H125" s="28" t="n">
-        <v>173.5</v>
+        <v>173.43</v>
       </c>
       <c r="I125" s="29" t="n">
-        <v>172</v>
+        <v>170.37</v>
       </c>
       <c r="J125" s="29" t="n">
-        <v>170.7</v>
+        <v>168.83</v>
       </c>
       <c r="K125" s="30" t="n">
-        <v>172.82</v>
+        <v>172.91</v>
       </c>
       <c r="L125" s="31" t="n">
-        <v>170.47</v>
+        <v>169.06</v>
       </c>
       <c r="M125" s="31" t="n">
-        <v>167.67</v>
+        <v>164.46</v>
       </c>
       <c r="N125" s="32" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         </is>
       </c>
       <c r="O125" s="33" t="n">
+        <v>173.35</v>
+      </c>
+      <c r="P125" s="33" t="n">
         <v>173.27</v>
       </c>
-      <c r="P125" s="33" t="n">
-        <v>173.03</v>
-      </c>
       <c r="Q125" s="34" t="n">
-        <v>173.3</v>
-      </c>
-      <c r="R125" s="36" t="n">
-        <v>0.17</v>
+        <v>171.9</v>
+      </c>
+      <c r="R125" s="35" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -8420,54 +8420,54 @@
         </is>
       </c>
       <c r="C126" s="25" t="n">
-        <v>52.94</v>
+        <v>54.46</v>
       </c>
       <c r="D126" s="25" t="n">
-        <v>51.99</v>
+        <v>52.91</v>
       </c>
       <c r="E126" s="26" t="n">
-        <v>51.19</v>
+        <v>51.61</v>
       </c>
       <c r="F126" s="27" t="n">
-        <v>51.28</v>
+        <v>52</v>
       </c>
       <c r="G126" s="27" t="n">
-        <v>51.82</v>
+        <v>52.75</v>
       </c>
       <c r="H126" s="28" t="n">
-        <v>50.87</v>
+        <v>51.2</v>
       </c>
       <c r="I126" s="29" t="n">
-        <v>50.33</v>
+        <v>50.45</v>
       </c>
       <c r="J126" s="29" t="n">
-        <v>49.92</v>
+        <v>49.65</v>
       </c>
       <c r="K126" s="30" t="n">
-        <v>50.66</v>
+        <v>50.74</v>
       </c>
       <c r="L126" s="31" t="n">
-        <v>49.86</v>
+        <v>49.44</v>
       </c>
       <c r="M126" s="31" t="n">
-        <v>48.91</v>
-      </c>
-      <c r="N126" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>47.89</v>
+      </c>
+      <c r="N126" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O126" s="33" t="n">
-        <v>50.8</v>
+        <v>51.03</v>
       </c>
       <c r="P126" s="33" t="n">
-        <v>50.73</v>
+        <v>50.86</v>
       </c>
       <c r="Q126" s="34" t="n">
-        <v>50.75</v>
-      </c>
-      <c r="R126" s="35" t="n">
-        <v>-0.68</v>
+        <v>51.25</v>
+      </c>
+      <c r="R126" s="36" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="127">
@@ -8482,54 +8482,54 @@
         </is>
       </c>
       <c r="C127" s="25" t="n">
-        <v>17.66</v>
+        <v>17.09</v>
       </c>
       <c r="D127" s="25" t="n">
-        <v>16.56</v>
+        <v>16.28</v>
       </c>
       <c r="E127" s="26" t="n">
-        <v>15.64</v>
+        <v>15.6</v>
       </c>
       <c r="F127" s="27" t="n">
-        <v>16.06</v>
+        <v>15.69</v>
       </c>
       <c r="G127" s="27" t="n">
-        <v>16.52</v>
+        <v>16.14</v>
       </c>
       <c r="H127" s="28" t="n">
-        <v>15.42</v>
+        <v>15.33</v>
       </c>
       <c r="I127" s="29" t="n">
-        <v>14.96</v>
+        <v>14.88</v>
       </c>
       <c r="J127" s="29" t="n">
-        <v>14.32</v>
+        <v>14.52</v>
       </c>
       <c r="K127" s="30" t="n">
-        <v>15.02</v>
+        <v>15.15</v>
       </c>
       <c r="L127" s="31" t="n">
-        <v>14.1</v>
+        <v>14.47</v>
       </c>
       <c r="M127" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="N127" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>13.66</v>
+      </c>
+      <c r="N127" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O127" s="33" t="n">
-        <v>15.26</v>
+        <v>15.27</v>
       </c>
       <c r="P127" s="33" t="n">
-        <v>15.11</v>
+        <v>15.21</v>
       </c>
       <c r="Q127" s="34" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="R127" s="36" t="n">
-        <v>5.41</v>
+        <v>15.24</v>
+      </c>
+      <c r="R127" s="35" t="n">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="128">
@@ -8544,37 +8544,37 @@
         </is>
       </c>
       <c r="C128" s="25" t="n">
-        <v>17.68</v>
+        <v>16.26</v>
       </c>
       <c r="D128" s="25" t="n">
-        <v>16.14</v>
+        <v>15.65</v>
       </c>
       <c r="E128" s="26" t="n">
-        <v>14.85</v>
+        <v>15.14</v>
       </c>
       <c r="F128" s="27" t="n">
-        <v>15.7</v>
+        <v>15.39</v>
       </c>
       <c r="G128" s="27" t="n">
-        <v>16.21</v>
+        <v>15.63</v>
       </c>
       <c r="H128" s="28" t="n">
-        <v>14.67</v>
+        <v>15.02</v>
       </c>
       <c r="I128" s="29" t="n">
-        <v>14.16</v>
+        <v>14.78</v>
       </c>
       <c r="J128" s="29" t="n">
-        <v>13.13</v>
+        <v>14.41</v>
       </c>
       <c r="K128" s="30" t="n">
-        <v>13.99</v>
+        <v>14.79</v>
       </c>
       <c r="L128" s="31" t="n">
-        <v>12.7</v>
+        <v>14.28</v>
       </c>
       <c r="M128" s="31" t="n">
-        <v>11.16</v>
+        <v>13.67</v>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
@@ -8582,16 +8582,16 @@
         </is>
       </c>
       <c r="O128" s="33" t="n">
-        <v>14.39</v>
+        <v>14.93</v>
       </c>
       <c r="P128" s="33" t="n">
-        <v>14.11</v>
+        <v>14.84</v>
       </c>
       <c r="Q128" s="34" t="n">
-        <v>15.18</v>
-      </c>
-      <c r="R128" s="36" t="n">
-        <v>9.92</v>
+        <v>15.14</v>
+      </c>
+      <c r="R128" s="35" t="n">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="129">
@@ -8606,37 +8606,37 @@
         </is>
       </c>
       <c r="C129" s="25" t="n">
-        <v>7.76</v>
+        <v>9.15</v>
       </c>
       <c r="D129" s="25" t="n">
-        <v>7.44</v>
+        <v>8.35</v>
       </c>
       <c r="E129" s="26" t="n">
-        <v>7.17</v>
+        <v>7.68</v>
       </c>
       <c r="F129" s="27" t="n">
-        <v>7.34</v>
+        <v>7.94</v>
       </c>
       <c r="G129" s="27" t="n">
-        <v>7.45</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H129" s="28" t="n">
-        <v>7.13</v>
+        <v>7.5</v>
       </c>
       <c r="I129" s="29" t="n">
-        <v>7.02</v>
+        <v>7.14</v>
       </c>
       <c r="J129" s="29" t="n">
-        <v>6.81</v>
+        <v>6.7</v>
       </c>
       <c r="K129" s="30" t="n">
-        <v>6.99</v>
+        <v>7.24</v>
       </c>
       <c r="L129" s="31" t="n">
-        <v>6.72</v>
+        <v>6.57</v>
       </c>
       <c r="M129" s="31" t="n">
-        <v>6.4</v>
+        <v>5.77</v>
       </c>
       <c r="N129" s="20" t="inlineStr">
         <is>
@@ -8644,16 +8644,16 @@
         </is>
       </c>
       <c r="O129" s="33" t="n">
-        <v>7.07</v>
+        <v>7.4</v>
       </c>
       <c r="P129" s="33" t="n">
-        <v>7.02</v>
+        <v>7.3</v>
       </c>
       <c r="Q129" s="34" t="n">
-        <v>7.23</v>
+        <v>7.58</v>
       </c>
       <c r="R129" s="36" t="n">
-        <v>3.58</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="130">
@@ -8668,54 +8668,54 @@
         </is>
       </c>
       <c r="C130" s="25" t="n">
-        <v>9.9</v>
+        <v>11.83</v>
       </c>
       <c r="D130" s="25" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="E130" s="26" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="F130" s="27" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="G130" s="27" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="H130" s="28" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="I130" s="29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J130" s="29" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="K130" s="30" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="L130" s="31" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="M130" s="31" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="N130" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O130" s="33" t="n">
         <v>9.65</v>
       </c>
-      <c r="E130" s="26" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="F130" s="27" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="G130" s="27" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="H130" s="28" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="I130" s="29" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="J130" s="29" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="K130" s="30" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="L130" s="31" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="M130" s="31" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="N130" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O130" s="33" t="n">
-        <v>9.33</v>
-      </c>
       <c r="P130" s="33" t="n">
-        <v>9.32</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="Q130" s="34" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="R130" s="35" t="n">
-        <v>-1.59</v>
+        <v>10.18</v>
+      </c>
+      <c r="R130" s="36" t="n">
+        <v>9.94</v>
       </c>
     </row>
     <row r="131">
@@ -8730,54 +8730,54 @@
         </is>
       </c>
       <c r="C131" s="25" t="n">
-        <v>141.78</v>
+        <v>147.52</v>
       </c>
       <c r="D131" s="25" t="n">
-        <v>137.28</v>
+        <v>139.72</v>
       </c>
       <c r="E131" s="26" t="n">
-        <v>133.51</v>
+        <v>133.18</v>
       </c>
       <c r="F131" s="27" t="n">
-        <v>135</v>
+        <v>134.23</v>
       </c>
       <c r="G131" s="27" t="n">
-        <v>137</v>
+        <v>138.47</v>
       </c>
       <c r="H131" s="28" t="n">
-        <v>132.5</v>
+        <v>130.67</v>
       </c>
       <c r="I131" s="29" t="n">
-        <v>130.5</v>
+        <v>126.43</v>
       </c>
       <c r="J131" s="29" t="n">
-        <v>128</v>
+        <v>122.87</v>
       </c>
       <c r="K131" s="30" t="n">
-        <v>130.99</v>
+        <v>128.82</v>
       </c>
       <c r="L131" s="31" t="n">
-        <v>127.22</v>
+        <v>122.28</v>
       </c>
       <c r="M131" s="31" t="n">
-        <v>122.72</v>
-      </c>
-      <c r="N131" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>114.48</v>
+      </c>
+      <c r="N131" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O131" s="33" t="n">
-        <v>131.92</v>
+        <v>130.05</v>
       </c>
       <c r="P131" s="33" t="n">
-        <v>131.34</v>
+        <v>129.42</v>
       </c>
       <c r="Q131" s="34" t="n">
-        <v>133</v>
-      </c>
-      <c r="R131" s="36" t="n">
-        <v>2.39</v>
+        <v>130</v>
+      </c>
+      <c r="R131" s="35" t="n">
+        <v>-2.26</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -686,7 +686,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-08-19</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-08-20</t>
         </is>
       </c>
     </row>
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>11010.35</v>
+        <v>11045.83</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10968.44</v>
+        <v>10993.58</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>10933.32</v>
+        <v>10949.8</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>10945.28</v>
+        <v>10974.15</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>10964.86</v>
+        <v>10993.85</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>10922.95</v>
+        <v>10941.6</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>10903.37</v>
+        <v>10921.9</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>10881.04</v>
+        <v>10889.35</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>10909.85</v>
+        <v>10920.54</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>10874.73</v>
+        <v>10876.75</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>10832.82</v>
+        <v>10824.5</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>10918.04</v>
+        <v>10933.1</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>10913.12</v>
+        <v>10924.61</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>10925.69</v>
+        <v>10954.46</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="4">
@@ -856,54 +856,54 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>20.71</v>
+        <v>20.78</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.5</v>
+        <v>20.63</v>
       </c>
       <c r="E4" s="26" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="I4" s="29" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="J4" s="29" t="n">
         <v>20.32</v>
       </c>
-      <c r="F4" s="27" t="n">
+      <c r="K4" s="30" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="L4" s="31" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M4" s="31" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O4" s="32" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="P4" s="32" t="n">
         <v>20.43</v>
       </c>
-      <c r="G4" s="27" t="n">
-        <v>20.51</v>
-      </c>
-      <c r="H4" s="28" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="I4" s="29" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="J4" s="29" t="n">
-        <v>20.09</v>
-      </c>
-      <c r="K4" s="30" t="n">
-        <v>20.21</v>
-      </c>
-      <c r="L4" s="31" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="M4" s="31" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O4" s="32" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="P4" s="32" t="n">
-        <v>20.22</v>
-      </c>
       <c r="Q4" s="33" t="n">
-        <v>20.36</v>
+        <v>20.49</v>
       </c>
       <c r="R4" s="34" t="n">
-        <v>0.99</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="5">
@@ -918,54 +918,54 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>12.53</v>
+        <v>12.42</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>12.32</v>
+        <v>12.24</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>12.14</v>
+        <v>12.09</v>
       </c>
       <c r="F5" s="27" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="L5" s="31" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="M5" s="31" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O5" s="32" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="P5" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="33" t="n">
         <v>12.13</v>
       </c>
-      <c r="G5" s="27" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="J5" s="29" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="K5" s="30" t="n">
-        <v>12.03</v>
-      </c>
-      <c r="L5" s="31" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="M5" s="31" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="N5" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>12.05</v>
-      </c>
-      <c r="P5" s="32" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="Q5" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="R5" s="36" t="n">
-        <v>-1.56</v>
+      <c r="R5" s="34" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="6">
@@ -980,54 +980,54 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>14.53</v>
+        <v>14.39</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14.36</v>
+        <v>14.26</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>14.21</v>
+        <v>14.15</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>14.19</v>
+        <v>14.2</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>14.31</v>
+        <v>14.25</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>14.14</v>
+        <v>14.12</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>14.02</v>
+        <v>14.07</v>
       </c>
       <c r="J6" s="29" t="n">
-        <v>13.97</v>
+        <v>13.99</v>
       </c>
       <c r="K6" s="30" t="n">
-        <v>14.12</v>
+        <v>14.08</v>
       </c>
       <c r="L6" s="31" t="n">
         <v>13.97</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="N6" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>13.84</v>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>14.13</v>
+        <v>14.11</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>14.13</v>
+        <v>14.09</v>
       </c>
       <c r="Q6" s="33" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="R6" s="36" t="n">
-        <v>-1.19</v>
+        <v>14.14</v>
+      </c>
+      <c r="R6" s="34" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="7">
@@ -1042,54 +1042,54 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>22.04</v>
+        <v>22.15</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>21.52</v>
+        <v>21.62</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>21.09</v>
+        <v>21.17</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>21.37</v>
+        <v>21.13</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>21.55</v>
+        <v>21.48</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>21.03</v>
+        <v>20.95</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>20.85</v>
+        <v>20.6</v>
       </c>
       <c r="J7" s="29" t="n">
-        <v>20.51</v>
+        <v>20.42</v>
       </c>
       <c r="K7" s="30" t="n">
-        <v>20.79</v>
+        <v>20.88</v>
       </c>
       <c r="L7" s="31" t="n">
-        <v>20.36</v>
+        <v>20.43</v>
       </c>
       <c r="M7" s="31" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="N7" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>19.9</v>
+      </c>
+      <c r="N7" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O7" s="32" t="n">
         <v>20.93</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>20.83</v>
+        <v>20.92</v>
       </c>
       <c r="Q7" s="33" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="R7" s="34" t="n">
-        <v>2.42</v>
+        <v>20.79</v>
+      </c>
+      <c r="R7" s="36" t="n">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="8">
@@ -1104,37 +1104,37 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>34.06</v>
+        <v>34.33</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>33.84</v>
+        <v>34.05</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>33.65</v>
+        <v>33.82</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>33.76</v>
+        <v>33.97</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>33.84</v>
+        <v>34.07</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>33.62</v>
+        <v>33.79</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>33.54</v>
+        <v>33.69</v>
       </c>
       <c r="J8" s="29" t="n">
-        <v>33.4</v>
+        <v>33.51</v>
       </c>
       <c r="K8" s="30" t="n">
-        <v>33.53</v>
+        <v>33.66</v>
       </c>
       <c r="L8" s="31" t="n">
-        <v>33.34</v>
+        <v>33.43</v>
       </c>
       <c r="M8" s="31" t="n">
-        <v>33.12</v>
+        <v>33.15</v>
       </c>
       <c r="N8" s="20" t="inlineStr">
         <is>
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="O8" s="32" t="n">
-        <v>33.58</v>
+        <v>33.74</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>33.55</v>
+        <v>33.68</v>
       </c>
       <c r="Q8" s="33" t="n">
-        <v>33.68</v>
+        <v>33.88</v>
       </c>
       <c r="R8" s="34" t="n">
-        <v>0.42</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="9">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>23.07</v>
+        <v>22.79</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>22.73</v>
+        <v>22.56</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>22.45</v>
+        <v>22.37</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>22.52</v>
+        <v>22.34</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>22.69</v>
+        <v>22.5</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>22.35</v>
+        <v>22.27</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>22.18</v>
+        <v>22.11</v>
       </c>
       <c r="J9" s="29" t="n">
-        <v>22.01</v>
+        <v>22.04</v>
       </c>
       <c r="K9" s="30" t="n">
-        <v>22.25</v>
+        <v>22.24</v>
       </c>
       <c r="L9" s="31" t="n">
-        <v>21.97</v>
+        <v>22.05</v>
       </c>
       <c r="M9" s="31" t="n">
-        <v>21.63</v>
+        <v>21.82</v>
       </c>
       <c r="N9" s="35" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="O9" s="32" t="n">
-        <v>22.32</v>
+        <v>22.26</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>22.28</v>
+        <v>22.26</v>
       </c>
       <c r="Q9" s="33" t="n">
-        <v>22.35</v>
+        <v>22.19</v>
       </c>
       <c r="R9" s="36" t="n">
-        <v>-0.62</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="10">
@@ -1228,54 +1228,54 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>122.93</v>
+        <v>125.42</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>121.43</v>
+        <v>123.12</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>120.17</v>
+        <v>121.19</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>120</v>
+        <v>122.2</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>121</v>
+        <v>123.1</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>119.5</v>
+        <v>120.8</v>
       </c>
       <c r="I10" s="29" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="J10" s="29" t="n">
         <v>118.5</v>
       </c>
-      <c r="J10" s="29" t="n">
-        <v>118</v>
-      </c>
       <c r="K10" s="30" t="n">
-        <v>119.33</v>
+        <v>119.91</v>
       </c>
       <c r="L10" s="31" t="n">
-        <v>118.07</v>
+        <v>117.98</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>116.57</v>
-      </c>
-      <c r="N10" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>115.68</v>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>119.47</v>
+        <v>120.44</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>119.45</v>
+        <v>120.09</v>
       </c>
       <c r="Q10" s="33" t="n">
-        <v>119</v>
-      </c>
-      <c r="R10" s="36" t="n">
-        <v>-0.83</v>
+        <v>121.3</v>
+      </c>
+      <c r="R10" s="34" t="n">
+        <v>1.93</v>
       </c>
     </row>
     <row r="11">
@@ -1290,54 +1290,54 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>65.77</v>
+        <v>66.02</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>65.17</v>
+        <v>65.42</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>64.67</v>
+        <v>64.92</v>
       </c>
       <c r="F11" s="27" t="n">
+        <v>65.08</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="H11" s="28" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="J11" s="29" t="n">
+        <v>64.17</v>
+      </c>
+      <c r="K11" s="30" t="n">
+        <v>64.58</v>
+      </c>
+      <c r="L11" s="31" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="M11" s="31" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O11" s="32" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="P11" s="32" t="n">
+        <v>64.63</v>
+      </c>
+      <c r="Q11" s="33" t="n">
         <v>64.8</v>
       </c>
-      <c r="G11" s="27" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="H11" s="28" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="J11" s="29" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="K11" s="30" t="n">
-        <v>64.33</v>
-      </c>
-      <c r="L11" s="31" t="n">
-        <v>63.83</v>
-      </c>
-      <c r="M11" s="31" t="n">
-        <v>63.23</v>
-      </c>
-      <c r="N11" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O11" s="32" t="n">
-        <v>64.44</v>
-      </c>
-      <c r="P11" s="32" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="Q11" s="33" t="n">
-        <v>64.5</v>
-      </c>
       <c r="R11" s="34" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="12">
@@ -1352,54 +1352,54 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>25.63</v>
+        <v>25.69</v>
       </c>
       <c r="D12" s="25" t="n">
         <v>25.45</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>25.3</v>
+        <v>25.25</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>25.35</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>25.43</v>
+        <v>25.45</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>25.25</v>
+        <v>25.21</v>
       </c>
       <c r="I12" s="29" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="J12" s="29" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="L12" s="31" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="M12" s="31" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O12" s="32" t="n">
         <v>25.17</v>
       </c>
-      <c r="J12" s="29" t="n">
-        <v>25.07</v>
-      </c>
-      <c r="K12" s="30" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="L12" s="31" t="n">
-        <v>25.05</v>
-      </c>
-      <c r="M12" s="31" t="n">
-        <v>24.87</v>
-      </c>
-      <c r="N12" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O12" s="32" t="n">
-        <v>25.23</v>
-      </c>
       <c r="P12" s="32" t="n">
-        <v>25.21</v>
+        <v>25.13</v>
       </c>
       <c r="Q12" s="33" t="n">
         <v>25.26</v>
       </c>
-      <c r="R12" s="36" t="n">
-        <v>-0.55</v>
+      <c r="R12" s="34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1414,54 +1414,54 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>25.36</v>
+        <v>25.6</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>25.08</v>
+        <v>25.23</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>24.85</v>
+        <v>24.92</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>24.92</v>
+        <v>25.03</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>25.06</v>
+        <v>25.2</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>24.78</v>
+        <v>24.83</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>24.64</v>
+        <v>24.66</v>
       </c>
       <c r="J13" s="29" t="n">
-        <v>24.5</v>
+        <v>24.46</v>
       </c>
       <c r="K13" s="30" t="n">
-        <v>24.69</v>
+        <v>24.71</v>
       </c>
       <c r="L13" s="31" t="n">
-        <v>24.46</v>
+        <v>24.4</v>
       </c>
       <c r="M13" s="31" t="n">
-        <v>24.18</v>
-      </c>
-      <c r="N13" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>24.03</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>24.75</v>
+        <v>24.79</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>24.71</v>
+        <v>24.74</v>
       </c>
       <c r="Q13" s="33" t="n">
-        <v>24.79</v>
-      </c>
-      <c r="R13" s="36" t="n">
-        <v>-0.04</v>
+        <v>24.86</v>
+      </c>
+      <c r="R13" s="34" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="14">
@@ -1476,37 +1476,37 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>42.97</v>
+        <v>42.3</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>42.37</v>
+        <v>41.98</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>41.87</v>
+        <v>41.71</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>41.99</v>
+        <v>41.81</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>42.29</v>
+        <v>41.95</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>41.69</v>
+        <v>41.63</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>41.39</v>
+        <v>41.49</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>41.09</v>
+        <v>41.31</v>
       </c>
       <c r="K14" s="30" t="n">
         <v>41.53</v>
       </c>
       <c r="L14" s="31" t="n">
-        <v>41.03</v>
+        <v>41.26</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>40.43</v>
+        <v>40.94</v>
       </c>
       <c r="N14" s="35" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="O14" s="32" t="n">
-        <v>41.64</v>
+        <v>41.59</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>41.58</v>
+        <v>41.56</v>
       </c>
       <c r="Q14" s="33" t="n">
-        <v>41.68</v>
-      </c>
-      <c r="R14" s="34" t="n">
-        <v>0</v>
+        <v>41.66</v>
+      </c>
+      <c r="R14" s="36" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="15">
@@ -1538,54 +1538,54 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>8.94</v>
+        <v>9.17</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>8.869999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>8.81</v>
+        <v>8.84</v>
       </c>
       <c r="F15" s="27" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="28" t="n">
         <v>8.82</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>8.789999999999999</v>
       </c>
       <c r="I15" s="29" t="n">
         <v>8.75</v>
       </c>
       <c r="J15" s="29" t="n">
-        <v>8.720000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K15" s="30" t="n">
-        <v>8.779999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="L15" s="31" t="n">
-        <v>8.720000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="M15" s="31" t="n">
-        <v>8.65</v>
-      </c>
-      <c r="N15" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>8.41</v>
+      </c>
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O15" s="32" t="n">
         <v>8.789999999999999</v>
       </c>
       <c r="P15" s="32" t="n">
-        <v>8.779999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="Q15" s="33" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="R15" s="36" t="n">
-        <v>-0.9</v>
+        <v>8.869999999999999</v>
+      </c>
+      <c r="R15" s="34" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="16">
@@ -1600,54 +1600,54 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>14.63</v>
+        <v>14.65</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.4</v>
+        <v>14.34</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>14.21</v>
+        <v>14.08</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>14.19</v>
+        <v>14.15</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>14.34</v>
+        <v>14.31</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>14.11</v>
+        <v>14</v>
       </c>
       <c r="I16" s="29" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="J16" s="29" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="K16" s="30" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="L16" s="31" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="M16" s="31" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="N16" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O16" s="32" t="n">
         <v>13.96</v>
       </c>
-      <c r="J16" s="29" t="n">
-        <v>13.88</v>
-      </c>
-      <c r="K16" s="30" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="L16" s="31" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="M16" s="31" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="N16" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O16" s="32" t="n">
-        <v>14.1</v>
-      </c>
       <c r="P16" s="32" t="n">
-        <v>14.1</v>
+        <v>13.93</v>
       </c>
       <c r="Q16" s="33" t="n">
-        <v>14.04</v>
+        <v>14</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>-1.4</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="17">
@@ -1662,54 +1662,54 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>5.2</v>
+        <v>5.11</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>5.01</v>
+        <v>4.96</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>4.85</v>
+        <v>4.84</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>4.84</v>
+        <v>4.87</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>4.96</v>
+        <v>4.95</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>4.77</v>
+        <v>4.8</v>
       </c>
       <c r="I17" s="29" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="J17" s="29" t="n">
         <v>4.65</v>
       </c>
-      <c r="J17" s="29" t="n">
-        <v>4.58</v>
-      </c>
       <c r="K17" s="30" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="L17" s="31" t="n">
-        <v>4.58</v>
+        <v>4.63</v>
       </c>
       <c r="M17" s="31" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="N17" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>4.48</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O17" s="32" t="n">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
       <c r="P17" s="32" t="n">
         <v>4.76</v>
       </c>
       <c r="Q17" s="33" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="R17" s="36" t="n">
-        <v>-1.05</v>
+        <v>4.8</v>
+      </c>
+      <c r="R17" s="34" t="n">
+        <v>1.69</v>
       </c>
     </row>
     <row r="18">
@@ -1724,54 +1724,54 @@
         </is>
       </c>
       <c r="C18" s="25" t="n">
-        <v>18.69</v>
+        <v>19.2</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>18.39</v>
+        <v>18.78</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>18.13</v>
+        <v>18.43</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>18.28</v>
+        <v>18.64</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>18.39</v>
+        <v>18.79</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>18.09</v>
+        <v>18.37</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>17.98</v>
+        <v>18.22</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>17.79</v>
+        <v>17.95</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>17.97</v>
+        <v>18.19</v>
       </c>
       <c r="L18" s="31" t="n">
-        <v>17.71</v>
+        <v>17.84</v>
       </c>
       <c r="M18" s="31" t="n">
-        <v>17.41</v>
-      </c>
-      <c r="N18" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>17.42</v>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O18" s="32" t="n">
-        <v>18.04</v>
+        <v>18.3</v>
       </c>
       <c r="P18" s="32" t="n">
-        <v>17.99</v>
+        <v>18.23</v>
       </c>
       <c r="Q18" s="33" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="R18" s="36" t="n">
-        <v>-0.16</v>
+        <v>18.49</v>
+      </c>
+      <c r="R18" s="34" t="n">
+        <v>1.76</v>
       </c>
     </row>
     <row r="19">
@@ -1786,54 +1786,54 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>25.52</v>
+        <v>25.61</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>25.26</v>
+        <v>25.33</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>25.04</v>
+        <v>25.1</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>25.11</v>
+        <v>25.23</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>25.23</v>
+        <v>25.33</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>24.97</v>
+        <v>25.05</v>
       </c>
       <c r="I19" s="29" t="n">
-        <v>24.85</v>
+        <v>24.95</v>
       </c>
       <c r="J19" s="29" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>24.94</v>
+      </c>
+      <c r="L19" s="31" t="n">
         <v>24.71</v>
       </c>
-      <c r="K19" s="30" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="L19" s="31" t="n">
-        <v>24.68</v>
-      </c>
       <c r="M19" s="31" t="n">
-        <v>24.42</v>
-      </c>
-      <c r="N19" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>24.43</v>
+      </c>
+      <c r="N19" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O19" s="32" t="n">
-        <v>24.95</v>
+        <v>25.01</v>
       </c>
       <c r="P19" s="32" t="n">
-        <v>24.92</v>
+        <v>24.96</v>
       </c>
       <c r="Q19" s="33" t="n">
-        <v>24.98</v>
+        <v>25.12</v>
       </c>
       <c r="R19" s="34" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1848,54 +1848,54 @@
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>68.17</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>66.92</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>65.88</v>
+        <v>67.84</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>66.13</v>
+        <v>68.37</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>66.77</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>65.52</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>64.88</v>
+        <v>65.37</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>64.27</v>
+        <v>63.93</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>65.18000000000001</v>
+        <v>66.16</v>
       </c>
       <c r="L20" s="31" t="n">
-        <v>64.13</v>
+        <v>63.65</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>62.88</v>
-      </c>
-      <c r="N20" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>60.65</v>
+      </c>
+      <c r="N20" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O20" s="32" t="n">
-        <v>65.39</v>
+        <v>66.66</v>
       </c>
       <c r="P20" s="32" t="n">
-        <v>65.27</v>
+        <v>66.39</v>
       </c>
       <c r="Q20" s="33" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="R20" s="36" t="n">
-        <v>-0.76</v>
+        <v>66.8</v>
+      </c>
+      <c r="R20" s="34" t="n">
+        <v>1.98</v>
       </c>
     </row>
     <row r="21">
@@ -1910,37 +1910,37 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>11.86</v>
+        <v>13.26</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>11.64</v>
+        <v>12.61</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>11.45</v>
+        <v>12.07</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>11.52</v>
+        <v>12.32</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>11.62</v>
+        <v>12.59</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>11.4</v>
+        <v>11.94</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>11.3</v>
+        <v>11.67</v>
       </c>
       <c r="J21" s="29" t="n">
-        <v>11.18</v>
+        <v>11.29</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>11.33</v>
+        <v>11.7</v>
       </c>
       <c r="L21" s="31" t="n">
-        <v>11.14</v>
+        <v>11.16</v>
       </c>
       <c r="M21" s="31" t="n">
-        <v>10.92</v>
+        <v>10.51</v>
       </c>
       <c r="N21" s="20" t="inlineStr">
         <is>
@@ -1948,16 +1948,16 @@
         </is>
       </c>
       <c r="O21" s="32" t="n">
-        <v>11.37</v>
+        <v>11.85</v>
       </c>
       <c r="P21" s="32" t="n">
-        <v>11.35</v>
+        <v>11.75</v>
       </c>
       <c r="Q21" s="33" t="n">
-        <v>11.42</v>
+        <v>12.05</v>
       </c>
       <c r="R21" s="34" t="n">
-        <v>0.44</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="22">
@@ -1972,54 +1972,54 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>18.54</v>
+        <v>18.93</v>
       </c>
       <c r="D22" s="25" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="H22" s="28" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="J22" s="29" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="K22" s="30" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="L22" s="31" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="M22" s="31" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="N22" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O22" s="32" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="P22" s="32" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="Q22" s="33" t="n">
         <v>18.34</v>
       </c>
-      <c r="E22" s="26" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="G22" s="27" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="H22" s="28" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>17.98</v>
-      </c>
-      <c r="J22" s="29" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="K22" s="30" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="L22" s="31" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="M22" s="31" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="N22" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O22" s="32" t="n">
-        <v>18.09</v>
-      </c>
-      <c r="P22" s="32" t="n">
-        <v>18.08</v>
-      </c>
-      <c r="Q22" s="33" t="n">
-        <v>18.06</v>
-      </c>
       <c r="R22" s="34" t="n">
-        <v>0.11</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="23">
@@ -2034,54 +2034,54 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>35.15</v>
+        <v>36.95</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>34.75</v>
+        <v>35.87</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>34.41</v>
+        <v>34.96</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>34.45</v>
+        <v>35.27</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>34.67</v>
+        <v>35.77</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>34.27</v>
+        <v>34.69</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>34.05</v>
+        <v>34.19</v>
       </c>
       <c r="J23" s="29" t="n">
-        <v>33.87</v>
+        <v>33.61</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>34.19</v>
+        <v>34.36</v>
       </c>
       <c r="L23" s="31" t="n">
-        <v>33.85</v>
+        <v>33.45</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>33.45</v>
-      </c>
-      <c r="N23" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>32.37</v>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O23" s="32" t="n">
-        <v>34.25</v>
+        <v>34.57</v>
       </c>
       <c r="P23" s="32" t="n">
-        <v>34.22</v>
+        <v>34.44</v>
       </c>
       <c r="Q23" s="33" t="n">
-        <v>34.22</v>
-      </c>
-      <c r="R23" s="36" t="n">
-        <v>-0.35</v>
+        <v>34.76</v>
+      </c>
+      <c r="R23" s="34" t="n">
+        <v>1.58</v>
       </c>
     </row>
     <row r="24">
@@ -2096,37 +2096,37 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>15.63</v>
+        <v>15.62</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>15.38</v>
+        <v>15.36</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>15.17</v>
+        <v>15.14</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>15.2</v>
+        <v>15.19</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>15.34</v>
+        <v>15.33</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>15.09</v>
+        <v>15.07</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>14.95</v>
+        <v>14.93</v>
       </c>
       <c r="J24" s="29" t="n">
-        <v>14.84</v>
+        <v>14.81</v>
       </c>
       <c r="K24" s="30" t="n">
-        <v>15.03</v>
+        <v>15</v>
       </c>
       <c r="L24" s="31" t="n">
-        <v>14.83</v>
+        <v>14.78</v>
       </c>
       <c r="M24" s="31" t="n">
-        <v>14.58</v>
+        <v>14.52</v>
       </c>
       <c r="N24" s="35" t="inlineStr">
         <is>
@@ -2134,16 +2134,16 @@
         </is>
       </c>
       <c r="O24" s="32" t="n">
-        <v>15.07</v>
+        <v>15.04</v>
       </c>
       <c r="P24" s="32" t="n">
-        <v>15.05</v>
+        <v>15.02</v>
       </c>
       <c r="Q24" s="33" t="n">
         <v>15.06</v>
       </c>
-      <c r="R24" s="36" t="n">
-        <v>-0.86</v>
+      <c r="R24" s="34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2158,37 +2158,37 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>38.5</v>
+        <v>38.67</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>37.98</v>
+        <v>38.17</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>37.55</v>
+        <v>37.75</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>37.78</v>
+        <v>37.85</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>37.98</v>
+        <v>38.11</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>37.46</v>
+        <v>37.61</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>37.26</v>
+        <v>37.35</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>36.94</v>
+        <v>37.11</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>37.25</v>
+        <v>37.47</v>
       </c>
       <c r="L25" s="31" t="n">
-        <v>36.82</v>
+        <v>37.05</v>
       </c>
       <c r="M25" s="31" t="n">
-        <v>36.3</v>
+        <v>36.55</v>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -2196,16 +2196,16 @@
         </is>
       </c>
       <c r="O25" s="32" t="n">
-        <v>37.38</v>
+        <v>37.56</v>
       </c>
       <c r="P25" s="32" t="n">
-        <v>37.29</v>
+        <v>37.51</v>
       </c>
       <c r="Q25" s="33" t="n">
-        <v>37.58</v>
+        <v>37.6</v>
       </c>
       <c r="R25" s="34" t="n">
-        <v>0.75</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="26">
@@ -2220,37 +2220,37 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>49.65</v>
+        <v>49.12</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>48.41</v>
+        <v>48.4</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>47.37</v>
+        <v>47.8</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>48.03</v>
+        <v>47.76</v>
       </c>
       <c r="G26" s="27" t="n">
-        <v>48.45</v>
+        <v>48.22</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>47.21</v>
+        <v>47.5</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>46.79</v>
+        <v>47.04</v>
       </c>
       <c r="J26" s="29" t="n">
-        <v>45.97</v>
+        <v>46.78</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>46.67</v>
+        <v>47.4</v>
       </c>
       <c r="L26" s="31" t="n">
-        <v>45.63</v>
+        <v>46.8</v>
       </c>
       <c r="M26" s="31" t="n">
-        <v>44.39</v>
+        <v>46.08</v>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
@@ -2258,16 +2258,16 @@
         </is>
       </c>
       <c r="O26" s="32" t="n">
-        <v>46.99</v>
+        <v>47.48</v>
       </c>
       <c r="P26" s="32" t="n">
-        <v>46.77</v>
+        <v>47.45</v>
       </c>
       <c r="Q26" s="33" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="R26" s="34" t="n">
-        <v>2.59</v>
+        <v>47.3</v>
+      </c>
+      <c r="R26" s="36" t="n">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="27">
@@ -2282,37 +2282,37 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>197.67</v>
+        <v>195.29</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>193.67</v>
+        <v>192.39</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>190.32</v>
+        <v>189.96</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>191.73</v>
+        <v>189.77</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>193.47</v>
+        <v>191.63</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>189.47</v>
+        <v>188.73</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>187.73</v>
+        <v>186.87</v>
       </c>
       <c r="J27" s="29" t="n">
-        <v>185.47</v>
+        <v>185.83</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>188.08</v>
+        <v>188.34</v>
       </c>
       <c r="L27" s="31" t="n">
-        <v>184.73</v>
+        <v>185.91</v>
       </c>
       <c r="M27" s="31" t="n">
-        <v>180.73</v>
+        <v>183.01</v>
       </c>
       <c r="N27" s="35" t="inlineStr">
         <is>
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="O27" s="32" t="n">
-        <v>188.93</v>
+        <v>188.65</v>
       </c>
       <c r="P27" s="32" t="n">
-        <v>188.39</v>
+        <v>188.56</v>
       </c>
       <c r="Q27" s="33" t="n">
-        <v>190</v>
-      </c>
-      <c r="R27" s="34" t="n">
-        <v>0</v>
+        <v>187.9</v>
+      </c>
+      <c r="R27" s="36" t="n">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="28">
@@ -2344,54 +2344,54 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>88.68000000000001</v>
+        <v>91.14</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>85.48</v>
+        <v>87.84</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>82.8</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>82.43000000000001</v>
+        <v>86.47</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>84.56999999999999</v>
+        <v>87.78</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>81.37</v>
+        <v>84.48</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>79.23</v>
+        <v>83.17</v>
       </c>
       <c r="J28" s="29" t="n">
-        <v>78.17</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>81</v>
+        <v>83.23</v>
       </c>
       <c r="L28" s="31" t="n">
-        <v>78.31999999999999</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>75.12</v>
-      </c>
-      <c r="N28" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>77.16</v>
+      </c>
+      <c r="N28" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O28" s="32" t="n">
-        <v>81.31</v>
+        <v>83.98</v>
       </c>
       <c r="P28" s="32" t="n">
-        <v>81.25</v>
+        <v>83.48</v>
       </c>
       <c r="Q28" s="33" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="R28" s="36" t="n">
-        <v>-4.35</v>
+        <v>85.15000000000001</v>
+      </c>
+      <c r="R28" s="34" t="n">
+        <v>6.04</v>
       </c>
     </row>
     <row r="29">
@@ -2406,54 +2406,54 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>23.73</v>
+        <v>23.94</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>22.66</v>
+        <v>22.98</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>21.76</v>
+        <v>22.18</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>22.22</v>
+        <v>22.14</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>22.65</v>
+        <v>22.75</v>
       </c>
       <c r="H29" s="28" t="n">
-        <v>21.58</v>
+        <v>21.79</v>
       </c>
       <c r="I29" s="29" t="n">
-        <v>21.15</v>
+        <v>21.18</v>
       </c>
       <c r="J29" s="29" t="n">
-        <v>20.51</v>
+        <v>20.83</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>21.17</v>
+        <v>21.64</v>
       </c>
       <c r="L29" s="31" t="n">
-        <v>20.27</v>
+        <v>20.84</v>
       </c>
       <c r="M29" s="31" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N29" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>19.88</v>
+      </c>
+      <c r="N29" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O29" s="32" t="n">
-        <v>21.41</v>
+        <v>21.75</v>
       </c>
       <c r="P29" s="32" t="n">
-        <v>21.25</v>
+        <v>21.72</v>
       </c>
       <c r="Q29" s="33" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R29" s="34" t="n">
-        <v>4.16</v>
+        <v>21.54</v>
+      </c>
+      <c r="R29" s="36" t="n">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="30">
@@ -2468,54 +2468,54 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>82.36</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>80.81</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>79.51000000000001</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>79.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>80.5</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="I30" s="29" t="n">
         <v>78.95</v>
       </c>
-      <c r="I30" s="29" t="n">
-        <v>78.05</v>
-      </c>
       <c r="J30" s="29" t="n">
-        <v>77.40000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>78.64</v>
+        <v>79.09</v>
       </c>
       <c r="L30" s="31" t="n">
-        <v>77.34</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>75.79000000000001</v>
-      </c>
-      <c r="N30" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>74.95999999999999</v>
+      </c>
+      <c r="N30" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O30" s="32" t="n">
-        <v>78.86</v>
+        <v>79.59</v>
       </c>
       <c r="P30" s="32" t="n">
-        <v>78.76000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="Q30" s="33" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="R30" s="36" t="n">
-        <v>-1.38</v>
+        <v>80.25</v>
+      </c>
+      <c r="R30" s="34" t="n">
+        <v>1.97</v>
       </c>
     </row>
     <row r="31">
@@ -2530,54 +2530,54 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>36.86</v>
+        <v>37.07</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>34.62</v>
+        <v>35.17</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>32.75</v>
+        <v>33.58</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>33.55</v>
+        <v>33.37</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>34.51</v>
+        <v>34.63</v>
       </c>
       <c r="H31" s="28" t="n">
-        <v>32.27</v>
+        <v>32.73</v>
       </c>
       <c r="I31" s="29" t="n">
-        <v>31.31</v>
+        <v>31.47</v>
       </c>
       <c r="J31" s="29" t="n">
-        <v>30.03</v>
+        <v>30.83</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>31.49</v>
+        <v>32.52</v>
       </c>
       <c r="L31" s="31" t="n">
-        <v>29.62</v>
+        <v>30.93</v>
       </c>
       <c r="M31" s="31" t="n">
-        <v>27.38</v>
-      </c>
-      <c r="N31" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>29.03</v>
+      </c>
+      <c r="N31" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O31" s="32" t="n">
-        <v>31.97</v>
+        <v>32.7</v>
       </c>
       <c r="P31" s="32" t="n">
-        <v>31.67</v>
+        <v>32.67</v>
       </c>
       <c r="Q31" s="33" t="n">
-        <v>32.58</v>
-      </c>
-      <c r="R31" s="34" t="n">
-        <v>7.74</v>
+        <v>32.1</v>
+      </c>
+      <c r="R31" s="36" t="n">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="32">
@@ -2592,37 +2592,37 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>50.52</v>
+        <v>50.03</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>50.1</v>
+        <v>49.79</v>
       </c>
       <c r="E32" s="26" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="G32" s="27" t="n">
         <v>49.75</v>
       </c>
-      <c r="F32" s="27" t="n">
-        <v>49.75</v>
-      </c>
-      <c r="G32" s="27" t="n">
-        <v>50.01</v>
-      </c>
       <c r="H32" s="28" t="n">
-        <v>49.59</v>
+        <v>49.51</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>49.33</v>
+        <v>49.39</v>
       </c>
       <c r="J32" s="29" t="n">
-        <v>49.17</v>
+        <v>49.27</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>49.51</v>
+        <v>49.45</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>49.16</v>
+        <v>49.25</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>48.74</v>
+        <v>49.01</v>
       </c>
       <c r="N32" s="35" t="inlineStr">
         <is>
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="O32" s="32" t="n">
-        <v>49.57</v>
+        <v>49.49</v>
       </c>
       <c r="P32" s="32" t="n">
-        <v>49.55</v>
+        <v>49.47</v>
       </c>
       <c r="Q32" s="33" t="n">
         <v>49.5</v>
       </c>
-      <c r="R32" s="36" t="n">
-        <v>-0.2</v>
+      <c r="R32" s="34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2654,54 +2654,54 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>127.79</v>
+        <v>128.23</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>126.19</v>
+        <v>126.73</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>124.85</v>
+        <v>125.47</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>124.93</v>
+        <v>125.43</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>125.87</v>
+        <v>126.37</v>
       </c>
       <c r="H33" s="28" t="n">
-        <v>124.27</v>
+        <v>124.87</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>123.33</v>
+        <v>123.93</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>122.67</v>
+        <v>123.37</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>123.95</v>
+        <v>124.63</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>122.61</v>
+        <v>123.37</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>121.01</v>
-      </c>
-      <c r="N33" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>121.87</v>
+      </c>
+      <c r="N33" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O33" s="32" t="n">
-        <v>124.17</v>
+        <v>124.81</v>
       </c>
       <c r="P33" s="32" t="n">
-        <v>124.08</v>
+        <v>124.75</v>
       </c>
       <c r="Q33" s="33" t="n">
-        <v>124</v>
-      </c>
-      <c r="R33" s="36" t="n">
-        <v>-0.8</v>
+        <v>124.5</v>
+      </c>
+      <c r="R33" s="34" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="34">
@@ -2716,54 +2716,54 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>53.24</v>
+        <v>53.87</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>52.04</v>
+        <v>52.62</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>51.04</v>
+        <v>51.57</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>51.03</v>
+        <v>51.83</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>51.77</v>
+        <v>52.47</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>50.57</v>
+        <v>51.22</v>
       </c>
       <c r="I34" s="29" t="n">
+        <v>50.58</v>
+      </c>
+      <c r="J34" s="29" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="K34" s="30" t="n">
+        <v>50.87</v>
+      </c>
+      <c r="L34" s="31" t="n">
         <v>49.83</v>
       </c>
-      <c r="J34" s="29" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="K34" s="30" t="n">
-        <v>50.36</v>
-      </c>
-      <c r="L34" s="31" t="n">
-        <v>49.36</v>
-      </c>
       <c r="M34" s="31" t="n">
-        <v>48.16</v>
-      </c>
-      <c r="N34" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>48.58</v>
+      </c>
+      <c r="N34" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O34" s="32" t="n">
-        <v>50.51</v>
+        <v>51.09</v>
       </c>
       <c r="P34" s="32" t="n">
-        <v>50.46</v>
+        <v>50.97</v>
       </c>
       <c r="Q34" s="33" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="R34" s="36" t="n">
-        <v>-1.66</v>
+        <v>51.2</v>
+      </c>
+      <c r="R34" s="34" t="n">
+        <v>1.79</v>
       </c>
     </row>
     <row r="35">
@@ -2778,54 +2778,54 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>26.24</v>
+        <v>26.67</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>25.71</v>
+        <v>25.97</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>25.26</v>
+        <v>25.39</v>
       </c>
       <c r="F35" s="27" t="n">
-        <v>25.21</v>
+        <v>25.63</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>25.56</v>
+        <v>25.93</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>25.03</v>
+        <v>25.23</v>
       </c>
       <c r="I35" s="29" t="n">
-        <v>24.68</v>
+        <v>24.93</v>
       </c>
       <c r="J35" s="29" t="n">
-        <v>24.5</v>
+        <v>24.53</v>
       </c>
       <c r="K35" s="30" t="n">
-        <v>24.97</v>
+        <v>24.99</v>
       </c>
       <c r="L35" s="31" t="n">
-        <v>24.52</v>
+        <v>24.41</v>
       </c>
       <c r="M35" s="31" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="N35" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>23.71</v>
+      </c>
+      <c r="N35" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O35" s="32" t="n">
-        <v>25.02</v>
+        <v>25.14</v>
       </c>
       <c r="P35" s="32" t="n">
-        <v>25.01</v>
+        <v>25.05</v>
       </c>
       <c r="Q35" s="33" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="R35" s="36" t="n">
-        <v>-1.27</v>
+        <v>25.32</v>
+      </c>
+      <c r="R35" s="34" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="36">
@@ -2840,37 +2840,37 @@
         </is>
       </c>
       <c r="C36" s="25" t="n">
-        <v>26.28</v>
+        <v>27.34</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>25.86</v>
+        <v>26.6</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>25.51</v>
+        <v>25.98</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>25.69</v>
+        <v>26.39</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>25.85</v>
+        <v>26.63</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>25.43</v>
+        <v>25.89</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>25.27</v>
+        <v>25.65</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>25.01</v>
+        <v>25.15</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>25.27</v>
+        <v>25.56</v>
       </c>
       <c r="L36" s="31" t="n">
-        <v>24.92</v>
+        <v>24.94</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="O36" s="32" t="n">
-        <v>25.37</v>
+        <v>25.76</v>
       </c>
       <c r="P36" s="32" t="n">
-        <v>25.31</v>
+        <v>25.62</v>
       </c>
       <c r="Q36" s="33" t="n">
-        <v>25.52</v>
+        <v>26.14</v>
       </c>
       <c r="R36" s="34" t="n">
-        <v>0.47</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="37">
@@ -2902,54 +2902,54 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="D37" s="25" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="D37" s="25" t="n">
+      <c r="E37" s="26" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="E37" s="26" t="n">
-        <v>9.449999999999999</v>
-      </c>
       <c r="F37" s="27" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="H37" s="28" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="I37" s="29" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="J37" s="29" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K37" s="30" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="L37" s="31" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M37" s="31" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="N37" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O37" s="32" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="G37" s="27" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="H37" s="28" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="I37" s="29" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="J37" s="29" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="K37" s="30" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="L37" s="31" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="M37" s="31" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="N37" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O37" s="32" t="n">
-        <v>9.390000000000001</v>
-      </c>
       <c r="P37" s="32" t="n">
-        <v>9.359999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="Q37" s="33" t="n">
-        <v>9.460000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="R37" s="34" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="38">
@@ -2964,37 +2964,37 @@
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>32.04</v>
+        <v>31.94</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>31.58</v>
+        <v>31.62</v>
       </c>
       <c r="E38" s="26" t="n">
-        <v>31.2</v>
+        <v>31.35</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>31.45</v>
+        <v>31.49</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>31.61</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>31.15</v>
+        <v>31.29</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>30.99</v>
+        <v>31.17</v>
       </c>
       <c r="J38" s="29" t="n">
-        <v>30.69</v>
+        <v>30.97</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>30.94</v>
+        <v>31.17</v>
       </c>
       <c r="L38" s="31" t="n">
-        <v>30.56</v>
+        <v>30.9</v>
       </c>
       <c r="M38" s="31" t="n">
-        <v>30.1</v>
+        <v>30.58</v>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
@@ -3002,16 +3002,16 @@
         </is>
       </c>
       <c r="O38" s="32" t="n">
-        <v>31.06</v>
+        <v>31.24</v>
       </c>
       <c r="P38" s="32" t="n">
-        <v>30.98</v>
+        <v>31.2</v>
       </c>
       <c r="Q38" s="33" t="n">
-        <v>31.3</v>
+        <v>31.36</v>
       </c>
       <c r="R38" s="34" t="n">
-        <v>0.97</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="39">
@@ -3026,37 +3026,37 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>189.61</v>
+        <v>193.66</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>187.01</v>
+        <v>190.16</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>184.83</v>
+        <v>187.23</v>
       </c>
       <c r="F39" s="27" t="n">
-        <v>185.67</v>
+        <v>188.1</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>186.83</v>
+        <v>189.8</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>184.23</v>
+        <v>186.3</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>183.07</v>
+        <v>184.6</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>181.63</v>
+        <v>182.8</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>183.37</v>
+        <v>185.27</v>
       </c>
       <c r="L39" s="31" t="n">
-        <v>181.19</v>
+        <v>182.34</v>
       </c>
       <c r="M39" s="31" t="n">
-        <v>178.59</v>
+        <v>178.84</v>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
@@ -3064,16 +3064,16 @@
         </is>
       </c>
       <c r="O39" s="32" t="n">
-        <v>183.9</v>
+        <v>185.92</v>
       </c>
       <c r="P39" s="32" t="n">
-        <v>183.57</v>
+        <v>185.54</v>
       </c>
       <c r="Q39" s="33" t="n">
-        <v>184.5</v>
+        <v>186.4</v>
       </c>
       <c r="R39" s="34" t="n">
-        <v>0.11</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="40">
@@ -3088,54 +3088,54 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>13.95</v>
+        <v>13.7</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>13.7</v>
+        <v>13.57</v>
       </c>
       <c r="E40" s="26" t="n">
-        <v>13.5</v>
+        <v>13.46</v>
       </c>
       <c r="F40" s="27" t="n">
-        <v>13.53</v>
+        <v>13.46</v>
       </c>
       <c r="G40" s="27" t="n">
-        <v>13.66</v>
+        <v>13.54</v>
       </c>
       <c r="H40" s="28" t="n">
         <v>13.41</v>
       </c>
       <c r="I40" s="29" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="J40" s="29" t="n">
         <v>13.28</v>
       </c>
-      <c r="J40" s="29" t="n">
-        <v>13.16</v>
-      </c>
       <c r="K40" s="30" t="n">
-        <v>13.36</v>
+        <v>13.39</v>
       </c>
       <c r="L40" s="31" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="M40" s="31" t="n">
         <v>13.15</v>
       </c>
-      <c r="M40" s="31" t="n">
-        <v>12.9</v>
-      </c>
       <c r="N40" s="35" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O40" s="32" t="n">
-        <v>13.39</v>
+        <v>13.4</v>
       </c>
       <c r="P40" s="32" t="n">
-        <v>13.37</v>
+        <v>13.4</v>
       </c>
       <c r="Q40" s="33" t="n">
-        <v>13.39</v>
+        <v>13.38</v>
       </c>
       <c r="R40" s="36" t="n">
-        <v>-0.3</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3150,37 +3150,37 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>21.89</v>
+        <v>21.69</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>21.51</v>
+        <v>21.36</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>21.2</v>
+        <v>21.09</v>
       </c>
       <c r="F41" s="27" t="n">
-        <v>21.16</v>
+        <v>21.06</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>21.41</v>
+        <v>21.28</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>21.03</v>
+        <v>20.95</v>
       </c>
       <c r="I41" s="29" t="n">
-        <v>20.78</v>
+        <v>20.73</v>
       </c>
       <c r="J41" s="29" t="n">
-        <v>20.65</v>
+        <v>20.62</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>20.98</v>
+        <v>20.9</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>20.67</v>
+        <v>20.63</v>
       </c>
       <c r="M41" s="31" t="n">
-        <v>20.29</v>
+        <v>20.3</v>
       </c>
       <c r="N41" s="35" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="O41" s="32" t="n">
-        <v>21.02</v>
+        <v>20.94</v>
       </c>
       <c r="P41" s="32" t="n">
-        <v>21.01</v>
+        <v>20.93</v>
       </c>
       <c r="Q41" s="33" t="n">
-        <v>20.91</v>
+        <v>20.85</v>
       </c>
       <c r="R41" s="36" t="n">
-        <v>-1.27</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="42">
@@ -3212,54 +3212,54 @@
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>184.02</v>
+        <v>188.44</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>180.92</v>
+        <v>183.84</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>178.32</v>
+        <v>179.99</v>
       </c>
       <c r="F42" s="27" t="n">
-        <v>178.23</v>
+        <v>181.2</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>180.17</v>
+        <v>183.4</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>177.07</v>
+        <v>178.8</v>
       </c>
       <c r="I42" s="29" t="n">
-        <v>175.13</v>
+        <v>176.6</v>
       </c>
       <c r="J42" s="29" t="n">
-        <v>173.97</v>
+        <v>174.2</v>
       </c>
       <c r="K42" s="30" t="n">
-        <v>176.58</v>
+        <v>177.41</v>
       </c>
       <c r="L42" s="31" t="n">
-        <v>173.98</v>
+        <v>173.56</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>170.88</v>
-      </c>
-      <c r="N42" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>168.96</v>
+      </c>
+      <c r="N42" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O42" s="32" t="n">
-        <v>176.95</v>
+        <v>178.29</v>
       </c>
       <c r="P42" s="32" t="n">
-        <v>176.82</v>
+        <v>177.77</v>
       </c>
       <c r="Q42" s="33" t="n">
-        <v>176.3</v>
-      </c>
-      <c r="R42" s="36" t="n">
-        <v>-0.4</v>
+        <v>179</v>
+      </c>
+      <c r="R42" s="34" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="43">
@@ -3274,37 +3274,37 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>37.38</v>
+        <v>39.15</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>36.7</v>
+        <v>38.03</v>
       </c>
       <c r="E43" s="26" t="n">
-        <v>36.13</v>
+        <v>37.09</v>
       </c>
       <c r="F43" s="27" t="n">
-        <v>36.51</v>
+        <v>37.62</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>36.73</v>
+        <v>38.04</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>36.05</v>
+        <v>36.92</v>
       </c>
       <c r="I43" s="29" t="n">
-        <v>35.83</v>
+        <v>36.5</v>
       </c>
       <c r="J43" s="29" t="n">
-        <v>35.37</v>
+        <v>35.8</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>35.75</v>
+        <v>36.47</v>
       </c>
       <c r="L43" s="31" t="n">
-        <v>35.18</v>
+        <v>35.53</v>
       </c>
       <c r="M43" s="31" t="n">
-        <v>34.5</v>
+        <v>34.41</v>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
@@ -3312,16 +3312,16 @@
         </is>
       </c>
       <c r="O43" s="32" t="n">
-        <v>35.93</v>
+        <v>36.74</v>
       </c>
       <c r="P43" s="32" t="n">
-        <v>35.8</v>
+        <v>36.55</v>
       </c>
       <c r="Q43" s="33" t="n">
-        <v>36.28</v>
+        <v>37.2</v>
       </c>
       <c r="R43" s="34" t="n">
-        <v>1.23</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="44">
@@ -3336,54 +3336,54 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>28.59</v>
+        <v>27.73</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>27.93</v>
+        <v>27.43</v>
       </c>
       <c r="E44" s="26" t="n">
-        <v>27.37</v>
+        <v>27.17</v>
       </c>
       <c r="F44" s="27" t="n">
-        <v>27.34</v>
+        <v>27.31</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>27.76</v>
+        <v>27.43</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>27.1</v>
+        <v>27.13</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>26.68</v>
+        <v>27.01</v>
       </c>
       <c r="J44" s="29" t="n">
-        <v>26.44</v>
+        <v>26.83</v>
       </c>
       <c r="K44" s="30" t="n">
         <v>27.01</v>
       </c>
       <c r="L44" s="31" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="M44" s="31" t="n">
         <v>26.45</v>
       </c>
-      <c r="M44" s="31" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="N44" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+      <c r="N44" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O44" s="32" t="n">
         <v>27.08</v>
       </c>
       <c r="P44" s="32" t="n">
-        <v>27.06</v>
+        <v>27.03</v>
       </c>
       <c r="Q44" s="33" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="R44" s="36" t="n">
-        <v>-1.75</v>
+        <v>27.2</v>
+      </c>
+      <c r="R44" s="34" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="45">
@@ -3398,54 +3398,54 @@
         </is>
       </c>
       <c r="C45" s="25" t="n">
-        <v>26.91</v>
+        <v>26.78</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>26.79</v>
+        <v>26.58</v>
       </c>
       <c r="E45" s="26" t="n">
-        <v>26.69</v>
+        <v>26.42</v>
       </c>
       <c r="F45" s="27" t="n">
-        <v>26.71</v>
+        <v>26.49</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>26.77</v>
+        <v>26.57</v>
       </c>
       <c r="H45" s="28" t="n">
-        <v>26.65</v>
+        <v>26.37</v>
       </c>
       <c r="I45" s="29" t="n">
-        <v>26.59</v>
+        <v>26.29</v>
       </c>
       <c r="J45" s="29" t="n">
-        <v>26.53</v>
+        <v>26.17</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>26.63</v>
+        <v>26.3</v>
       </c>
       <c r="L45" s="31" t="n">
-        <v>26.53</v>
+        <v>26.14</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>26.41</v>
-      </c>
-      <c r="N45" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>25.94</v>
+      </c>
+      <c r="N45" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O45" s="32" t="n">
-        <v>26.64</v>
+        <v>26.35</v>
       </c>
       <c r="P45" s="32" t="n">
-        <v>26.64</v>
+        <v>26.32</v>
       </c>
       <c r="Q45" s="33" t="n">
-        <v>26.64</v>
-      </c>
-      <c r="R45" s="34" t="n">
-        <v>0.23</v>
+        <v>26.4</v>
+      </c>
+      <c r="R45" s="36" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="46">
@@ -3460,54 +3460,54 @@
         </is>
       </c>
       <c r="C46" s="25" t="n">
-        <v>8.08</v>
+        <v>8.23</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>7.94</v>
+        <v>8.06</v>
       </c>
       <c r="E46" s="26" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="H46" s="28" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J46" s="29" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K46" s="30" t="n">
         <v>7.82</v>
       </c>
-      <c r="F46" s="27" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="G46" s="27" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="H46" s="28" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="I46" s="29" t="n">
-        <v>7.74</v>
-      </c>
-      <c r="J46" s="29" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="K46" s="30" t="n">
-        <v>7.74</v>
-      </c>
       <c r="L46" s="31" t="n">
-        <v>7.62</v>
+        <v>7.67</v>
       </c>
       <c r="M46" s="31" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="N46" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>7.5</v>
+      </c>
+      <c r="N46" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O46" s="32" t="n">
-        <v>7.77</v>
+        <v>7.85</v>
       </c>
       <c r="P46" s="32" t="n">
-        <v>7.75</v>
+        <v>7.83</v>
       </c>
       <c r="Q46" s="33" t="n">
-        <v>7.82</v>
+        <v>7.89</v>
       </c>
       <c r="R46" s="34" t="n">
-        <v>0.26</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="47">
@@ -3531,19 +3531,19 @@
         <v>12.34</v>
       </c>
       <c r="F47" s="27" t="n">
-        <v>12.32</v>
+        <v>12.39</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>12.45</v>
+        <v>12.48</v>
       </c>
       <c r="H47" s="28" t="n">
-        <v>12.25</v>
+        <v>12.28</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>12.12</v>
+        <v>12.19</v>
       </c>
       <c r="J47" s="29" t="n">
-        <v>12.05</v>
+        <v>12.08</v>
       </c>
       <c r="K47" s="30" t="n">
         <v>12.22</v>
@@ -3554,22 +3554,22 @@
       <c r="M47" s="31" t="n">
         <v>11.86</v>
       </c>
-      <c r="N47" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+      <c r="N47" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O47" s="32" t="n">
-        <v>12.24</v>
+        <v>12.26</v>
       </c>
       <c r="P47" s="32" t="n">
         <v>12.24</v>
       </c>
       <c r="Q47" s="33" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="R47" s="36" t="n">
-        <v>-0.97</v>
+        <v>12.29</v>
+      </c>
+      <c r="R47" s="34" t="n">
+        <v>0.82</v>
       </c>
     </row>
     <row r="48">
@@ -3584,54 +3584,54 @@
         </is>
       </c>
       <c r="C48" s="25" t="n">
-        <v>201.53</v>
+        <v>201.67</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>200.03</v>
+        <v>200.27</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>198.77</v>
+        <v>199.09</v>
       </c>
       <c r="F48" s="27" t="n">
-        <v>198.93</v>
+        <v>199.33</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>199.77</v>
+        <v>200.07</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>198.27</v>
+        <v>198.67</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>197.43</v>
+        <v>197.93</v>
       </c>
       <c r="J48" s="29" t="n">
-        <v>196.77</v>
+        <v>197.27</v>
       </c>
       <c r="K48" s="30" t="n">
-        <v>197.93</v>
+        <v>198.31</v>
       </c>
       <c r="L48" s="31" t="n">
-        <v>196.67</v>
+        <v>197.13</v>
       </c>
       <c r="M48" s="31" t="n">
-        <v>195.17</v>
-      </c>
-      <c r="N48" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>195.73</v>
+      </c>
+      <c r="N48" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O48" s="32" t="n">
-        <v>198.16</v>
+        <v>198.54</v>
       </c>
       <c r="P48" s="32" t="n">
-        <v>198.05</v>
+        <v>198.42</v>
       </c>
       <c r="Q48" s="33" t="n">
-        <v>198.1</v>
-      </c>
-      <c r="R48" s="36" t="n">
-        <v>-0.05</v>
+        <v>198.6</v>
+      </c>
+      <c r="R48" s="34" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="49">
@@ -3646,54 +3646,54 @@
         </is>
       </c>
       <c r="C49" s="25" t="n">
-        <v>49.73</v>
+        <v>49.68</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>49.03</v>
+        <v>49.04</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>48.45</v>
+        <v>48.5</v>
       </c>
       <c r="F49" s="27" t="n">
-        <v>48.74</v>
+        <v>48.59</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>49.02</v>
+        <v>48.93</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>48.32</v>
+        <v>48.29</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>48.04</v>
+        <v>47.95</v>
       </c>
       <c r="J49" s="29" t="n">
-        <v>47.62</v>
+        <v>47.65</v>
       </c>
       <c r="K49" s="30" t="n">
-        <v>48.05</v>
+        <v>48.14</v>
       </c>
       <c r="L49" s="31" t="n">
-        <v>47.47</v>
+        <v>47.6</v>
       </c>
       <c r="M49" s="31" t="n">
-        <v>46.77</v>
-      </c>
-      <c r="N49" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>46.96</v>
+      </c>
+      <c r="N49" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O49" s="32" t="n">
-        <v>48.21</v>
+        <v>48.24</v>
       </c>
       <c r="P49" s="32" t="n">
-        <v>48.11</v>
+        <v>48.19</v>
       </c>
       <c r="Q49" s="33" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="R49" s="34" t="n">
-        <v>0.04</v>
+        <v>48.24</v>
+      </c>
+      <c r="R49" s="36" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="50">
@@ -3708,54 +3708,54 @@
         </is>
       </c>
       <c r="C50" s="25" t="n">
-        <v>34.17</v>
+        <v>33.32</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>33.41</v>
+        <v>32.9</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>32.77</v>
+        <v>32.55</v>
       </c>
       <c r="F50" s="27" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="G50" s="27" t="n">
         <v>32.87</v>
       </c>
-      <c r="G50" s="27" t="n">
-        <v>33.29</v>
-      </c>
       <c r="H50" s="28" t="n">
-        <v>32.53</v>
+        <v>32.45</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>32.11</v>
+        <v>32.25</v>
       </c>
       <c r="J50" s="29" t="n">
-        <v>31.77</v>
+        <v>32.03</v>
       </c>
       <c r="K50" s="30" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="L50" s="31" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="M50" s="31" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="N50" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O50" s="32" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="P50" s="32" t="n">
         <v>32.35</v>
       </c>
-      <c r="L50" s="31" t="n">
-        <v>31.71</v>
-      </c>
-      <c r="M50" s="31" t="n">
-        <v>30.95</v>
-      </c>
-      <c r="N50" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O50" s="32" t="n">
-        <v>32.47</v>
-      </c>
-      <c r="P50" s="32" t="n">
-        <v>32.41</v>
-      </c>
       <c r="Q50" s="33" t="n">
-        <v>32.46</v>
-      </c>
-      <c r="R50" s="36" t="n">
-        <v>-1.1</v>
+        <v>32.48</v>
+      </c>
+      <c r="R50" s="34" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="51">
@@ -3770,37 +3770,37 @@
         </is>
       </c>
       <c r="C51" s="25" t="n">
-        <v>13.78</v>
+        <v>13.39</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>13.53</v>
+        <v>13.26</v>
       </c>
       <c r="E51" s="26" t="n">
-        <v>13.33</v>
+        <v>13.15</v>
       </c>
       <c r="F51" s="27" t="n">
-        <v>13.3</v>
+        <v>13.22</v>
       </c>
       <c r="G51" s="27" t="n">
-        <v>13.47</v>
+        <v>13.27</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>13.22</v>
+        <v>13.14</v>
       </c>
       <c r="I51" s="29" t="n">
-        <v>13.05</v>
+        <v>13.09</v>
       </c>
       <c r="J51" s="29" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="K51" s="30" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="L51" s="31" t="n">
         <v>12.97</v>
       </c>
-      <c r="K51" s="30" t="n">
-        <v>13.19</v>
-      </c>
-      <c r="L51" s="31" t="n">
-        <v>12.98</v>
-      </c>
       <c r="M51" s="31" t="n">
-        <v>12.73</v>
+        <v>12.84</v>
       </c>
       <c r="N51" s="35" t="inlineStr">
         <is>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="O51" s="32" t="n">
-        <v>13.21</v>
+        <v>13.11</v>
       </c>
       <c r="P51" s="32" t="n">
-        <v>13.2</v>
+        <v>13.09</v>
       </c>
       <c r="Q51" s="33" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="R51" s="36" t="n">
-        <v>-1.2</v>
+        <v>13.18</v>
+      </c>
+      <c r="R51" s="34" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="52">
@@ -3832,54 +3832,54 @@
         </is>
       </c>
       <c r="C52" s="25" t="n">
-        <v>60.43</v>
+        <v>60.48</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>59.58</v>
+        <v>59.63</v>
       </c>
       <c r="E52" s="26" t="n">
-        <v>58.86</v>
+        <v>58.91</v>
       </c>
       <c r="F52" s="27" t="n">
-        <v>58.83</v>
+        <v>59.32</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>59.37</v>
+        <v>59.63</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>58.52</v>
+        <v>58.78</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>57.98</v>
+        <v>58.47</v>
       </c>
       <c r="J52" s="29" t="n">
-        <v>57.67</v>
+        <v>57.93</v>
       </c>
       <c r="K52" s="30" t="n">
-        <v>58.39</v>
+        <v>58.44</v>
       </c>
       <c r="L52" s="31" t="n">
-        <v>57.67</v>
+        <v>57.72</v>
       </c>
       <c r="M52" s="31" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="N52" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>56.87</v>
+      </c>
+      <c r="N52" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O52" s="32" t="n">
-        <v>58.48</v>
+        <v>58.64</v>
       </c>
       <c r="P52" s="32" t="n">
-        <v>58.45</v>
+        <v>58.5</v>
       </c>
       <c r="Q52" s="33" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="R52" s="36" t="n">
-        <v>-1.19</v>
+        <v>59</v>
+      </c>
+      <c r="R52" s="34" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="53">
@@ -3894,54 +3894,54 @@
         </is>
       </c>
       <c r="C53" s="25" t="n">
-        <v>25.24</v>
+        <v>25.56</v>
       </c>
       <c r="D53" s="25" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E53" s="26" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F53" s="27" t="n">
         <v>24.95</v>
       </c>
-      <c r="E53" s="26" t="n">
-        <v>24.71</v>
-      </c>
-      <c r="F53" s="27" t="n">
-        <v>24.79</v>
-      </c>
       <c r="G53" s="27" t="n">
-        <v>24.93</v>
+        <v>25.14</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>24.64</v>
+        <v>24.78</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>24.5</v>
+        <v>24.59</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>24.35</v>
+        <v>24.42</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>24.54</v>
+        <v>24.7</v>
       </c>
       <c r="L53" s="31" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="N53" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>24.04</v>
+      </c>
+      <c r="N53" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O53" s="32" t="n">
-        <v>24.6</v>
+        <v>24.76</v>
       </c>
       <c r="P53" s="32" t="n">
-        <v>24.57</v>
+        <v>24.73</v>
       </c>
       <c r="Q53" s="33" t="n">
-        <v>24.66</v>
+        <v>24.75</v>
       </c>
       <c r="R53" s="34" t="n">
-        <v>0.16</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="54">
@@ -3956,25 +3956,25 @@
         </is>
       </c>
       <c r="C54" s="25" t="n">
-        <v>5.47</v>
+        <v>5.51</v>
       </c>
       <c r="D54" s="25" t="n">
-        <v>5.37</v>
+        <v>5.39</v>
       </c>
       <c r="E54" s="26" t="n">
         <v>5.29</v>
       </c>
       <c r="F54" s="27" t="n">
-        <v>5.29</v>
+        <v>5.35</v>
       </c>
       <c r="G54" s="27" t="n">
-        <v>5.35</v>
+        <v>5.39</v>
       </c>
       <c r="H54" s="28" t="n">
-        <v>5.25</v>
+        <v>5.27</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
       <c r="J54" s="29" t="n">
         <v>5.15</v>
@@ -3983,27 +3983,27 @@
         <v>5.23</v>
       </c>
       <c r="L54" s="31" t="n">
-        <v>5.15</v>
+        <v>5.13</v>
       </c>
       <c r="M54" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="N54" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>5.01</v>
+      </c>
+      <c r="N54" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O54" s="32" t="n">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
       <c r="P54" s="32" t="n">
         <v>5.24</v>
       </c>
       <c r="Q54" s="33" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="R54" s="36" t="n">
-        <v>-1.32</v>
+        <v>5.3</v>
+      </c>
+      <c r="R54" s="34" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="55">
@@ -4018,54 +4018,54 @@
         </is>
       </c>
       <c r="C55" s="25" t="n">
-        <v>19.58</v>
+        <v>19.31</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>18.85</v>
+        <v>18.62</v>
       </c>
       <c r="E55" s="26" t="n">
-        <v>18.24</v>
+        <v>18.04</v>
       </c>
       <c r="F55" s="27" t="n">
-        <v>18.31</v>
+        <v>18.29</v>
       </c>
       <c r="G55" s="27" t="n">
-        <v>18.72</v>
+        <v>18.59</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>17.99</v>
+        <v>17.9</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>17.58</v>
+        <v>17.6</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>17.26</v>
+        <v>17.21</v>
       </c>
       <c r="K55" s="30" t="n">
-        <v>17.83</v>
+        <v>17.65</v>
       </c>
       <c r="L55" s="31" t="n">
-        <v>17.22</v>
+        <v>17.07</v>
       </c>
       <c r="M55" s="31" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="N55" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>16.38</v>
+      </c>
+      <c r="N55" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O55" s="32" t="n">
-        <v>17.94</v>
+        <v>17.8</v>
       </c>
       <c r="P55" s="32" t="n">
-        <v>17.89</v>
+        <v>17.71</v>
       </c>
       <c r="Q55" s="33" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="R55" s="36" t="n">
-        <v>-1.38</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="34" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4080,54 +4080,54 @@
         </is>
       </c>
       <c r="C56" s="25" t="n">
-        <v>90.15000000000001</v>
+        <v>89.34</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>88.45</v>
+        <v>88.39</v>
       </c>
       <c r="E56" s="26" t="n">
-        <v>87.03</v>
+        <v>87.59</v>
       </c>
       <c r="F56" s="27" t="n">
-        <v>87.7</v>
+        <v>87.52</v>
       </c>
       <c r="G56" s="27" t="n">
-        <v>88.40000000000001</v>
+        <v>88.13</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>86.7</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="I56" s="29" t="n">
-        <v>86</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="J56" s="29" t="n">
-        <v>85</v>
+        <v>86.23</v>
       </c>
       <c r="K56" s="30" t="n">
-        <v>86.06999999999999</v>
+        <v>87.06</v>
       </c>
       <c r="L56" s="31" t="n">
-        <v>84.65000000000001</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="M56" s="31" t="n">
-        <v>82.95</v>
-      </c>
-      <c r="N56" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>85.31</v>
+      </c>
+      <c r="N56" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O56" s="32" t="n">
-        <v>86.45</v>
+        <v>87.16</v>
       </c>
       <c r="P56" s="32" t="n">
-        <v>86.20999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="Q56" s="33" t="n">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="R56" s="36" t="n">
-        <v>-0.46</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="57">
@@ -4142,54 +4142,54 @@
         </is>
       </c>
       <c r="C57" s="25" t="n">
-        <v>20.1</v>
+        <v>19.25</v>
       </c>
       <c r="D57" s="25" t="n">
-        <v>19.48</v>
+        <v>19.02</v>
       </c>
       <c r="E57" s="26" t="n">
-        <v>18.96</v>
+        <v>18.83</v>
       </c>
       <c r="F57" s="27" t="n">
-        <v>18.95</v>
+        <v>18.84</v>
       </c>
       <c r="G57" s="27" t="n">
-        <v>19.34</v>
+        <v>18.98</v>
       </c>
       <c r="H57" s="28" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="I57" s="29" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="J57" s="29" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="K57" s="30" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="L57" s="31" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="M57" s="31" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="N57" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O57" s="32" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="P57" s="32" t="n">
         <v>18.72</v>
       </c>
-      <c r="I57" s="29" t="n">
-        <v>18.33</v>
-      </c>
-      <c r="J57" s="29" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="K57" s="30" t="n">
-        <v>18.62</v>
-      </c>
-      <c r="L57" s="31" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="M57" s="31" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="N57" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O57" s="32" t="n">
-        <v>18.69</v>
-      </c>
-      <c r="P57" s="32" t="n">
-        <v>18.66</v>
-      </c>
       <c r="Q57" s="33" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="R57" s="36" t="n">
-        <v>-1.75</v>
+        <v>18.71</v>
+      </c>
+      <c r="R57" s="34" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="58">
@@ -4204,54 +4204,54 @@
         </is>
       </c>
       <c r="C58" s="25" t="n">
-        <v>22.53</v>
+        <v>22.5</v>
       </c>
       <c r="D58" s="25" t="n">
         <v>22.15</v>
       </c>
       <c r="E58" s="26" t="n">
-        <v>21.84</v>
+        <v>21.85</v>
       </c>
       <c r="F58" s="27" t="n">
-        <v>22.05</v>
+        <v>21.92</v>
       </c>
       <c r="G58" s="27" t="n">
-        <v>22.17</v>
+        <v>22.1</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>21.79</v>
+        <v>21.75</v>
       </c>
       <c r="I58" s="29" t="n">
-        <v>21.67</v>
+        <v>21.57</v>
       </c>
       <c r="J58" s="29" t="n">
-        <v>21.41</v>
+        <v>21.4</v>
       </c>
       <c r="K58" s="30" t="n">
-        <v>21.62</v>
+        <v>21.66</v>
       </c>
       <c r="L58" s="31" t="n">
-        <v>21.31</v>
+        <v>21.36</v>
       </c>
       <c r="M58" s="31" t="n">
-        <v>20.93</v>
-      </c>
-      <c r="N58" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>21.01</v>
+      </c>
+      <c r="N58" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O58" s="32" t="n">
         <v>21.72</v>
       </c>
       <c r="P58" s="32" t="n">
-        <v>21.65</v>
+        <v>21.68</v>
       </c>
       <c r="Q58" s="33" t="n">
-        <v>21.92</v>
-      </c>
-      <c r="R58" s="34" t="n">
-        <v>0.6899999999999999</v>
+        <v>21.74</v>
+      </c>
+      <c r="R58" s="36" t="n">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="59">
@@ -4266,37 +4266,37 @@
         </is>
       </c>
       <c r="C59" s="25" t="n">
-        <v>23.63</v>
+        <v>23.75</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>23.44</v>
+        <v>23.56</v>
       </c>
       <c r="E59" s="26" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="G59" s="27" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="H59" s="28" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="I59" s="29" t="n">
         <v>23.28</v>
       </c>
-      <c r="F59" s="27" t="n">
-        <v>23.37</v>
-      </c>
-      <c r="G59" s="27" t="n">
-        <v>23.44</v>
-      </c>
-      <c r="H59" s="28" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="I59" s="29" t="n">
-        <v>23.18</v>
-      </c>
       <c r="J59" s="29" t="n">
-        <v>23.06</v>
+        <v>23.17</v>
       </c>
       <c r="K59" s="30" t="n">
-        <v>23.17</v>
+        <v>23.29</v>
       </c>
       <c r="L59" s="31" t="n">
-        <v>23.01</v>
+        <v>23.13</v>
       </c>
       <c r="M59" s="31" t="n">
-        <v>22.82</v>
+        <v>22.94</v>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
@@ -4304,16 +4304,16 @@
         </is>
       </c>
       <c r="O59" s="32" t="n">
-        <v>23.22</v>
+        <v>23.33</v>
       </c>
       <c r="P59" s="32" t="n">
-        <v>23.19</v>
+        <v>23.31</v>
       </c>
       <c r="Q59" s="33" t="n">
-        <v>23.3</v>
+        <v>23.39</v>
       </c>
       <c r="R59" s="34" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="60">
@@ -4328,54 +4328,54 @@
         </is>
       </c>
       <c r="C60" s="25" t="n">
-        <v>28.57</v>
+        <v>28.92</v>
       </c>
       <c r="D60" s="25" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E60" s="26" t="n">
         <v>28.33</v>
       </c>
-      <c r="E60" s="26" t="n">
+      <c r="F60" s="27" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="G60" s="27" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="H60" s="28" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="I60" s="29" t="n">
         <v>28.13</v>
       </c>
-      <c r="F60" s="27" t="n">
+      <c r="J60" s="29" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="K60" s="30" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="L60" s="31" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="M60" s="31" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O60" s="32" t="n">
+        <v>28.22</v>
+      </c>
+      <c r="P60" s="32" t="n">
         <v>28.18</v>
       </c>
-      <c r="G60" s="27" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="H60" s="28" t="n">
-        <v>28.06</v>
-      </c>
-      <c r="I60" s="29" t="n">
-        <v>27.94</v>
-      </c>
-      <c r="J60" s="29" t="n">
-        <v>27.82</v>
-      </c>
-      <c r="K60" s="30" t="n">
-        <v>27.99</v>
-      </c>
-      <c r="L60" s="31" t="n">
-        <v>27.79</v>
-      </c>
-      <c r="M60" s="31" t="n">
-        <v>27.55</v>
-      </c>
-      <c r="N60" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O60" s="32" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="P60" s="32" t="n">
-        <v>28.01</v>
-      </c>
       <c r="Q60" s="33" t="n">
-        <v>28.06</v>
+        <v>28.32</v>
       </c>
       <c r="R60" s="34" t="n">
-        <v>0.21</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="61">
@@ -4390,54 +4390,54 @@
         </is>
       </c>
       <c r="C61" s="25" t="n">
-        <v>45.51</v>
+        <v>45.84</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>45.01</v>
+        <v>45.26</v>
       </c>
       <c r="E61" s="26" t="n">
-        <v>44.59</v>
+        <v>44.77</v>
       </c>
       <c r="F61" s="27" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="G61" s="27" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="H61" s="28" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="I61" s="29" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="J61" s="29" t="n">
+        <v>44.13</v>
+      </c>
+      <c r="K61" s="30" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="L61" s="31" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="M61" s="31" t="n">
+        <v>43.38</v>
+      </c>
+      <c r="N61" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O61" s="32" t="n">
         <v>44.6</v>
       </c>
-      <c r="G61" s="27" t="n">
+      <c r="P61" s="32" t="n">
+        <v>44.49</v>
+      </c>
+      <c r="Q61" s="33" t="n">
         <v>44.9</v>
       </c>
-      <c r="H61" s="28" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="I61" s="29" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="J61" s="29" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="K61" s="30" t="n">
-        <v>44.31</v>
-      </c>
-      <c r="L61" s="31" t="n">
-        <v>43.89</v>
-      </c>
-      <c r="M61" s="31" t="n">
-        <v>43.39</v>
-      </c>
-      <c r="N61" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O61" s="32" t="n">
-        <v>44.37</v>
-      </c>
-      <c r="P61" s="32" t="n">
-        <v>44.35</v>
-      </c>
-      <c r="Q61" s="33" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="R61" s="36" t="n">
-        <v>-0.32</v>
+      <c r="R61" s="34" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="62">
@@ -4452,54 +4452,54 @@
         </is>
       </c>
       <c r="C62" s="25" t="n">
-        <v>19.5</v>
+        <v>19.47</v>
       </c>
       <c r="D62" s="25" t="n">
-        <v>19.27</v>
+        <v>19.26</v>
       </c>
       <c r="E62" s="26" t="n">
         <v>19.08</v>
       </c>
       <c r="F62" s="27" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="G62" s="27" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="H62" s="28" t="n">
         <v>19.05</v>
       </c>
-      <c r="G62" s="27" t="n">
-        <v>19.21</v>
-      </c>
-      <c r="H62" s="28" t="n">
+      <c r="I62" s="29" t="n">
         <v>18.98</v>
       </c>
-      <c r="I62" s="29" t="n">
-        <v>18.82</v>
-      </c>
       <c r="J62" s="29" t="n">
-        <v>18.75</v>
+        <v>18.84</v>
       </c>
       <c r="K62" s="30" t="n">
-        <v>18.95</v>
+        <v>18.97</v>
       </c>
       <c r="L62" s="31" t="n">
-        <v>18.76</v>
+        <v>18.79</v>
       </c>
       <c r="M62" s="31" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="N62" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>18.58</v>
+      </c>
+      <c r="N62" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O62" s="32" t="n">
-        <v>18.97</v>
+        <v>19.02</v>
       </c>
       <c r="P62" s="32" t="n">
-        <v>18.97</v>
+        <v>18.98</v>
       </c>
       <c r="Q62" s="33" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R62" s="36" t="n">
-        <v>-1.2</v>
+        <v>19.11</v>
+      </c>
+      <c r="R62" s="34" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="63">
@@ -4514,54 +4514,54 @@
         </is>
       </c>
       <c r="C63" s="25" t="n">
-        <v>14.97</v>
+        <v>15.19</v>
       </c>
       <c r="D63" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="E63" s="26" t="n">
         <v>14.84</v>
       </c>
-      <c r="E63" s="26" t="n">
+      <c r="F63" s="27" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="G63" s="27" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="H63" s="28" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="I63" s="29" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="J63" s="29" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="K63" s="30" t="n">
         <v>14.73</v>
       </c>
-      <c r="F63" s="27" t="n">
+      <c r="L63" s="31" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="M63" s="31" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="N63" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O63" s="32" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="P63" s="32" t="n">
         <v>14.75</v>
       </c>
-      <c r="G63" s="27" t="n">
-        <v>14.82</v>
-      </c>
-      <c r="H63" s="28" t="n">
-        <v>14.69</v>
-      </c>
-      <c r="I63" s="29" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="J63" s="29" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="K63" s="30" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="L63" s="31" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="M63" s="31" t="n">
-        <v>14.42</v>
-      </c>
-      <c r="N63" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>14.68</v>
-      </c>
-      <c r="P63" s="32" t="n">
-        <v>14.67</v>
-      </c>
       <c r="Q63" s="33" t="n">
-        <v>14.68</v>
+        <v>14.88</v>
       </c>
       <c r="R63" s="34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="64">
@@ -4576,54 +4576,54 @@
         </is>
       </c>
       <c r="C64" s="25" t="n">
-        <v>25.17</v>
+        <v>25.36</v>
       </c>
       <c r="D64" s="25" t="n">
-        <v>24.95</v>
+        <v>25.13</v>
       </c>
       <c r="E64" s="26" t="n">
-        <v>24.76</v>
+        <v>24.94</v>
       </c>
       <c r="F64" s="27" t="n">
-        <v>24.86</v>
+        <v>25.06</v>
       </c>
       <c r="G64" s="27" t="n">
-        <v>24.95</v>
+        <v>25.14</v>
       </c>
       <c r="H64" s="28" t="n">
-        <v>24.73</v>
+        <v>24.91</v>
       </c>
       <c r="I64" s="29" t="n">
-        <v>24.64</v>
+        <v>24.83</v>
       </c>
       <c r="J64" s="29" t="n">
-        <v>24.51</v>
+        <v>24.68</v>
       </c>
       <c r="K64" s="30" t="n">
-        <v>24.64</v>
+        <v>24.81</v>
       </c>
       <c r="L64" s="31" t="n">
-        <v>24.45</v>
+        <v>24.62</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="N64" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>24.39</v>
+      </c>
+      <c r="N64" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O64" s="32" t="n">
-        <v>24.69</v>
+        <v>24.87</v>
       </c>
       <c r="P64" s="32" t="n">
-        <v>24.66</v>
+        <v>24.83</v>
       </c>
       <c r="Q64" s="33" t="n">
-        <v>24.78</v>
-      </c>
-      <c r="R64" s="36" t="n">
-        <v>-0.16</v>
+        <v>24.98</v>
+      </c>
+      <c r="R64" s="34" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4638,37 +4638,37 @@
         </is>
       </c>
       <c r="C65" s="25" t="n">
-        <v>7.4</v>
+        <v>7.38</v>
       </c>
       <c r="D65" s="25" t="n">
         <v>7.31</v>
       </c>
       <c r="E65" s="26" t="n">
-        <v>7.23</v>
+        <v>7.25</v>
       </c>
       <c r="F65" s="27" t="n">
-        <v>7.28</v>
+        <v>7.29</v>
       </c>
       <c r="G65" s="27" t="n">
         <v>7.31</v>
       </c>
       <c r="H65" s="28" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="I65" s="29" t="n">
         <v>7.22</v>
       </c>
-      <c r="I65" s="29" t="n">
-        <v>7.19</v>
-      </c>
       <c r="J65" s="29" t="n">
-        <v>7.13</v>
+        <v>7.17</v>
       </c>
       <c r="K65" s="30" t="n">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="L65" s="31" t="n">
-        <v>7.1</v>
+        <v>7.16</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>7.01</v>
+        <v>7.09</v>
       </c>
       <c r="N65" s="20" t="inlineStr">
         <is>
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="O65" s="32" t="n">
-        <v>7.2</v>
+        <v>7.23</v>
       </c>
       <c r="P65" s="32" t="n">
-        <v>7.19</v>
+        <v>7.22</v>
       </c>
       <c r="Q65" s="33" t="n">
-        <v>7.25</v>
+        <v>7.26</v>
       </c>
       <c r="R65" s="34" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="66">
@@ -4700,37 +4700,37 @@
         </is>
       </c>
       <c r="C66" s="25" t="n">
-        <v>5.01</v>
+        <v>4.99</v>
       </c>
       <c r="D66" s="25" t="n">
-        <v>4.96</v>
+        <v>4.95</v>
       </c>
       <c r="E66" s="26" t="n">
         <v>4.92</v>
       </c>
       <c r="F66" s="27" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="G66" s="27" t="n">
         <v>4.95</v>
       </c>
       <c r="H66" s="28" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="I66" s="29" t="n">
         <v>4.9</v>
       </c>
-      <c r="I66" s="29" t="n">
-        <v>4.88</v>
-      </c>
       <c r="J66" s="29" t="n">
-        <v>4.85</v>
+        <v>4.87</v>
       </c>
       <c r="K66" s="30" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="L66" s="31" t="n">
-        <v>4.85</v>
+        <v>4.87</v>
       </c>
       <c r="M66" s="31" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="N66" s="20" t="inlineStr">
         <is>
@@ -4738,16 +4738,16 @@
         </is>
       </c>
       <c r="O66" s="32" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="P66" s="32" t="n">
         <v>4.9</v>
       </c>
-      <c r="P66" s="32" t="n">
-        <v>4.89</v>
-      </c>
       <c r="Q66" s="33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R66" s="36" t="n">
-        <v>-0.2</v>
+        <v>4.92</v>
+      </c>
+      <c r="R66" s="34" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="67">
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="C67" s="25" t="n">
-        <v>5.22</v>
+        <v>5.16</v>
       </c>
       <c r="D67" s="25" t="n">
-        <v>5.12</v>
+        <v>5.08</v>
       </c>
       <c r="E67" s="26" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
       <c r="F67" s="27" t="n">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="G67" s="27" t="n">
-        <v>5.09</v>
+        <v>5.06</v>
       </c>
       <c r="H67" s="28" t="n">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
       <c r="I67" s="29" t="n">
-        <v>4.93</v>
+        <v>4.92</v>
       </c>
       <c r="J67" s="29" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="K67" s="30" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="L67" s="31" t="n">
         <v>4.9</v>
       </c>
       <c r="M67" s="31" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="N67" s="35" t="inlineStr">
         <is>
@@ -4800,16 +4800,16 @@
         </is>
       </c>
       <c r="O67" s="32" t="n">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
       <c r="P67" s="32" t="n">
-        <v>4.99</v>
+        <v>4.97</v>
       </c>
       <c r="Q67" s="33" t="n">
-        <v>4.96</v>
+        <v>4.95</v>
       </c>
       <c r="R67" s="36" t="n">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="68">
@@ -4824,37 +4824,37 @@
         </is>
       </c>
       <c r="C68" s="25" t="n">
+        <v>67.31</v>
+      </c>
+      <c r="D68" s="25" t="n">
         <v>65.76000000000001</v>
       </c>
-      <c r="D68" s="25" t="n">
-        <v>64.61</v>
-      </c>
       <c r="E68" s="26" t="n">
-        <v>63.65</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="F68" s="27" t="n">
-        <v>64.28</v>
+        <v>65.05</v>
       </c>
       <c r="G68" s="27" t="n">
-        <v>64.67</v>
+        <v>65.7</v>
       </c>
       <c r="H68" s="28" t="n">
-        <v>63.52</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="I68" s="29" t="n">
-        <v>63.13</v>
+        <v>63.5</v>
       </c>
       <c r="J68" s="29" t="n">
-        <v>62.37</v>
+        <v>62.6</v>
       </c>
       <c r="K68" s="30" t="n">
-        <v>63</v>
+        <v>63.59</v>
       </c>
       <c r="L68" s="31" t="n">
-        <v>62.04</v>
+        <v>62.29</v>
       </c>
       <c r="M68" s="31" t="n">
-        <v>60.89</v>
+        <v>60.74</v>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
@@ -4862,16 +4862,16 @@
         </is>
       </c>
       <c r="O68" s="32" t="n">
-        <v>63.3</v>
+        <v>63.93</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>63.09</v>
+        <v>63.71</v>
       </c>
       <c r="Q68" s="33" t="n">
-        <v>63.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R68" s="34" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="69">
@@ -4886,54 +4886,54 @@
         </is>
       </c>
       <c r="C69" s="25" t="n">
-        <v>66.52</v>
+        <v>66.19</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>65.52</v>
+        <v>65.39</v>
       </c>
       <c r="E69" s="26" t="n">
-        <v>64.68000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="F69" s="27" t="n">
-        <v>65.23</v>
+        <v>64.73</v>
       </c>
       <c r="G69" s="27" t="n">
-        <v>65.56999999999999</v>
+        <v>65.22</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>64.56999999999999</v>
+        <v>64.42</v>
       </c>
       <c r="I69" s="29" t="n">
-        <v>64.23</v>
+        <v>63.93</v>
       </c>
       <c r="J69" s="29" t="n">
-        <v>63.57</v>
+        <v>63.62</v>
       </c>
       <c r="K69" s="30" t="n">
-        <v>64.12</v>
+        <v>64.28</v>
       </c>
       <c r="L69" s="31" t="n">
-        <v>63.28</v>
+        <v>63.61</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>62.28</v>
-      </c>
-      <c r="N69" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>62.81</v>
+      </c>
+      <c r="N69" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O69" s="32" t="n">
         <v>64.38</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>64.2</v>
+        <v>64.34</v>
       </c>
       <c r="Q69" s="33" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="R69" s="34" t="n">
-        <v>1.41</v>
+        <v>64.25</v>
+      </c>
+      <c r="R69" s="36" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="70">
@@ -4948,37 +4948,37 @@
         </is>
       </c>
       <c r="C70" s="25" t="n">
-        <v>108.01</v>
+        <v>104.88</v>
       </c>
       <c r="D70" s="25" t="n">
-        <v>103.06</v>
+        <v>102.73</v>
       </c>
       <c r="E70" s="26" t="n">
-        <v>98.91</v>
+        <v>100.93</v>
       </c>
       <c r="F70" s="27" t="n">
-        <v>101.02</v>
+        <v>101.98</v>
       </c>
       <c r="G70" s="27" t="n">
-        <v>102.98</v>
+        <v>102.77</v>
       </c>
       <c r="H70" s="28" t="n">
-        <v>98.03</v>
+        <v>100.62</v>
       </c>
       <c r="I70" s="29" t="n">
-        <v>96.06999999999999</v>
+        <v>99.83</v>
       </c>
       <c r="J70" s="29" t="n">
-        <v>93.08</v>
+        <v>98.47</v>
       </c>
       <c r="K70" s="30" t="n">
-        <v>96.14</v>
+        <v>99.72</v>
       </c>
       <c r="L70" s="31" t="n">
-        <v>91.98999999999999</v>
+        <v>97.92</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>87.04000000000001</v>
+        <v>95.77</v>
       </c>
       <c r="N70" s="20" t="inlineStr">
         <is>
@@ -4986,16 +4986,16 @@
         </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>97.28</v>
+        <v>100.25</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>96.53</v>
+        <v>99.89</v>
       </c>
       <c r="Q70" s="33" t="n">
-        <v>99.05</v>
+        <v>101.2</v>
       </c>
       <c r="R70" s="34" t="n">
-        <v>3.28</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="71">
@@ -5010,54 +5010,54 @@
         </is>
       </c>
       <c r="C71" s="25" t="n">
-        <v>136.4</v>
+        <v>130.36</v>
       </c>
       <c r="D71" s="25" t="n">
-        <v>130.9</v>
+        <v>128.16</v>
       </c>
       <c r="E71" s="26" t="n">
-        <v>126.29</v>
+        <v>126.32</v>
       </c>
       <c r="F71" s="27" t="n">
-        <v>129.27</v>
+        <v>126.67</v>
       </c>
       <c r="G71" s="27" t="n">
-        <v>131.13</v>
+        <v>127.83</v>
       </c>
       <c r="H71" s="28" t="n">
         <v>125.63</v>
       </c>
       <c r="I71" s="29" t="n">
-        <v>123.77</v>
+        <v>124.47</v>
       </c>
       <c r="J71" s="29" t="n">
-        <v>120.13</v>
+        <v>123.43</v>
       </c>
       <c r="K71" s="30" t="n">
-        <v>123.21</v>
+        <v>125.08</v>
       </c>
       <c r="L71" s="31" t="n">
-        <v>118.6</v>
+        <v>123.24</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>113.1</v>
-      </c>
-      <c r="N71" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>121.04</v>
+      </c>
+      <c r="N71" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>124.64</v>
+        <v>125.44</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>123.64</v>
+        <v>125.26</v>
       </c>
       <c r="Q71" s="33" t="n">
-        <v>127.4</v>
-      </c>
-      <c r="R71" s="34" t="n">
-        <v>4.43</v>
+        <v>125.5</v>
+      </c>
+      <c r="R71" s="36" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="72">
@@ -5072,37 +5072,37 @@
         </is>
       </c>
       <c r="C72" s="25" t="n">
-        <v>25.33</v>
+        <v>26.1</v>
       </c>
       <c r="D72" s="25" t="n">
-        <v>25.11</v>
+        <v>25.63</v>
       </c>
       <c r="E72" s="26" t="n">
-        <v>24.92</v>
+        <v>25.24</v>
       </c>
       <c r="F72" s="27" t="n">
-        <v>24.99</v>
+        <v>25.4</v>
       </c>
       <c r="G72" s="27" t="n">
-        <v>25.09</v>
+        <v>25.61</v>
       </c>
       <c r="H72" s="28" t="n">
-        <v>24.87</v>
+        <v>25.14</v>
       </c>
       <c r="I72" s="29" t="n">
-        <v>24.77</v>
+        <v>24.93</v>
       </c>
       <c r="J72" s="29" t="n">
-        <v>24.65</v>
+        <v>24.67</v>
       </c>
       <c r="K72" s="30" t="n">
-        <v>24.8</v>
+        <v>24.97</v>
       </c>
       <c r="L72" s="31" t="n">
-        <v>24.61</v>
+        <v>24.58</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>24.39</v>
+        <v>24.11</v>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>24.84</v>
+        <v>25.07</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>24.82</v>
+        <v>25.01</v>
       </c>
       <c r="Q72" s="33" t="n">
-        <v>24.89</v>
+        <v>25.2</v>
       </c>
       <c r="R72" s="34" t="n">
-        <v>0.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="73">
@@ -5134,54 +5134,54 @@
         </is>
       </c>
       <c r="C73" s="25" t="n">
-        <v>22.83</v>
+        <v>23.46</v>
       </c>
       <c r="D73" s="25" t="n">
-        <v>22</v>
+        <v>22.37</v>
       </c>
       <c r="E73" s="26" t="n">
-        <v>21.31</v>
+        <v>21.46</v>
       </c>
       <c r="F73" s="27" t="n">
-        <v>21.25</v>
+        <v>21.68</v>
       </c>
       <c r="G73" s="27" t="n">
-        <v>21.78</v>
+        <v>22.24</v>
       </c>
       <c r="H73" s="28" t="n">
-        <v>20.95</v>
+        <v>21.15</v>
       </c>
       <c r="I73" s="29" t="n">
-        <v>20.42</v>
+        <v>20.59</v>
       </c>
       <c r="J73" s="29" t="n">
-        <v>20.12</v>
+        <v>20.06</v>
       </c>
       <c r="K73" s="30" t="n">
-        <v>20.84</v>
+        <v>20.85</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>20.15</v>
+        <v>19.94</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>19.32</v>
-      </c>
-      <c r="N73" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>18.85</v>
+      </c>
+      <c r="N73" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O73" s="32" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="P73" s="32" t="n">
         <v>20.93</v>
       </c>
-      <c r="P73" s="32" t="n">
-        <v>20.91</v>
-      </c>
       <c r="Q73" s="33" t="n">
-        <v>20.71</v>
-      </c>
-      <c r="R73" s="36" t="n">
-        <v>-1.1</v>
+        <v>21.13</v>
+      </c>
+      <c r="R73" s="34" t="n">
+        <v>2.03</v>
       </c>
     </row>
     <row r="74">
@@ -5196,37 +5196,37 @@
         </is>
       </c>
       <c r="C74" s="25" t="n">
-        <v>246.49</v>
+        <v>242.57</v>
       </c>
       <c r="D74" s="25" t="n">
-        <v>241.49</v>
+        <v>239.87</v>
       </c>
       <c r="E74" s="26" t="n">
-        <v>237.3</v>
+        <v>237.61</v>
       </c>
       <c r="F74" s="27" t="n">
-        <v>240.07</v>
+        <v>238.83</v>
       </c>
       <c r="G74" s="27" t="n">
-        <v>241.73</v>
+        <v>239.87</v>
       </c>
       <c r="H74" s="28" t="n">
-        <v>236.73</v>
+        <v>237.17</v>
       </c>
       <c r="I74" s="29" t="n">
-        <v>235.07</v>
+        <v>236.13</v>
       </c>
       <c r="J74" s="29" t="n">
-        <v>231.73</v>
+        <v>234.47</v>
       </c>
       <c r="K74" s="30" t="n">
-        <v>234.5</v>
+        <v>236.09</v>
       </c>
       <c r="L74" s="31" t="n">
-        <v>230.31</v>
+        <v>233.83</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>225.31</v>
+        <v>231.13</v>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
@@ -5234,16 +5234,16 @@
         </is>
       </c>
       <c r="O74" s="32" t="n">
-        <v>235.81</v>
+        <v>236.74</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>234.89</v>
+        <v>236.3</v>
       </c>
       <c r="Q74" s="33" t="n">
-        <v>238.4</v>
-      </c>
-      <c r="R74" s="34" t="n">
-        <v>0.89</v>
+        <v>237.8</v>
+      </c>
+      <c r="R74" s="36" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="75">
@@ -5258,51 +5258,51 @@
         </is>
       </c>
       <c r="C75" s="25" t="n">
-        <v>17.02</v>
+        <v>16.67</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>16.54</v>
+        <v>16.34</v>
       </c>
       <c r="E75" s="26" t="n">
-        <v>16.13</v>
+        <v>16.07</v>
       </c>
       <c r="F75" s="27" t="n">
-        <v>16.23</v>
+        <v>16.16</v>
       </c>
       <c r="G75" s="27" t="n">
-        <v>16.47</v>
+        <v>16.32</v>
       </c>
       <c r="H75" s="28" t="n">
         <v>15.99</v>
       </c>
       <c r="I75" s="29" t="n">
-        <v>15.75</v>
+        <v>15.83</v>
       </c>
       <c r="J75" s="29" t="n">
-        <v>15.51</v>
+        <v>15.66</v>
       </c>
       <c r="K75" s="30" t="n">
-        <v>15.87</v>
+        <v>15.88</v>
       </c>
       <c r="L75" s="31" t="n">
-        <v>15.46</v>
+        <v>15.61</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="N75" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>15.28</v>
+      </c>
+      <c r="N75" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O75" s="32" t="n">
         <v>15.95</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>15.9</v>
+        <v>15.91</v>
       </c>
       <c r="Q75" s="33" t="n">
-        <v>15.98</v>
+        <v>16.01</v>
       </c>
       <c r="R75" s="34" t="n">
         <v>0.19</v>
@@ -5320,37 +5320,37 @@
         </is>
       </c>
       <c r="C76" s="25" t="n">
-        <v>34.71</v>
+        <v>35.79</v>
       </c>
       <c r="D76" s="25" t="n">
-        <v>33.79</v>
+        <v>34.77</v>
       </c>
       <c r="E76" s="26" t="n">
-        <v>33.02</v>
+        <v>33.92</v>
       </c>
       <c r="F76" s="27" t="n">
-        <v>33.41</v>
+        <v>34.44</v>
       </c>
       <c r="G76" s="27" t="n">
-        <v>33.77</v>
+        <v>34.8</v>
       </c>
       <c r="H76" s="28" t="n">
-        <v>32.85</v>
+        <v>33.78</v>
       </c>
       <c r="I76" s="29" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="J76" s="29" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="K76" s="30" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="L76" s="31" t="n">
         <v>32.49</v>
       </c>
-      <c r="J76" s="29" t="n">
-        <v>31.93</v>
-      </c>
-      <c r="K76" s="30" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="L76" s="31" t="n">
-        <v>31.73</v>
-      </c>
       <c r="M76" s="31" t="n">
-        <v>30.81</v>
+        <v>31.47</v>
       </c>
       <c r="N76" s="20" t="inlineStr">
         <is>
@@ -5358,16 +5358,16 @@
         </is>
       </c>
       <c r="O76" s="32" t="n">
-        <v>32.71</v>
+        <v>33.6</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>32.57</v>
+        <v>33.42</v>
       </c>
       <c r="Q76" s="33" t="n">
-        <v>33.04</v>
+        <v>34.08</v>
       </c>
       <c r="R76" s="34" t="n">
-        <v>2.35</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="77">
@@ -5382,37 +5382,37 @@
         </is>
       </c>
       <c r="C77" s="25" t="n">
-        <v>28.39</v>
+        <v>27.63</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>27.53</v>
+        <v>27.25</v>
       </c>
       <c r="E77" s="26" t="n">
-        <v>26.81</v>
+        <v>26.94</v>
       </c>
       <c r="F77" s="27" t="n">
-        <v>27.11</v>
+        <v>27.03</v>
       </c>
       <c r="G77" s="27" t="n">
-        <v>27.49</v>
+        <v>27.21</v>
       </c>
       <c r="H77" s="28" t="n">
-        <v>26.63</v>
+        <v>26.83</v>
       </c>
       <c r="I77" s="29" t="n">
-        <v>26.25</v>
+        <v>26.65</v>
       </c>
       <c r="J77" s="29" t="n">
-        <v>25.77</v>
+        <v>26.45</v>
       </c>
       <c r="K77" s="30" t="n">
-        <v>26.33</v>
+        <v>26.72</v>
       </c>
       <c r="L77" s="31" t="n">
-        <v>25.61</v>
+        <v>26.41</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>24.75</v>
+        <v>26.03</v>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
@@ -5420,16 +5420,16 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>26.51</v>
+        <v>26.79</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>26.4</v>
+        <v>26.75</v>
       </c>
       <c r="Q77" s="33" t="n">
-        <v>26.74</v>
+        <v>26.84</v>
       </c>
       <c r="R77" s="34" t="n">
-        <v>1.36</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="78">
@@ -5444,37 +5444,37 @@
         </is>
       </c>
       <c r="C78" s="25" t="n">
-        <v>43.59</v>
+        <v>49.24</v>
       </c>
       <c r="D78" s="25" t="n">
-        <v>42.37</v>
+        <v>46.16</v>
       </c>
       <c r="E78" s="26" t="n">
-        <v>41.35</v>
+        <v>43.58</v>
       </c>
       <c r="F78" s="27" t="n">
-        <v>41.95</v>
+        <v>44.7</v>
       </c>
       <c r="G78" s="27" t="n">
-        <v>42.39</v>
+        <v>46.02</v>
       </c>
       <c r="H78" s="28" t="n">
-        <v>41.17</v>
+        <v>42.94</v>
       </c>
       <c r="I78" s="29" t="n">
-        <v>40.73</v>
+        <v>41.62</v>
       </c>
       <c r="J78" s="29" t="n">
-        <v>39.95</v>
+        <v>39.86</v>
       </c>
       <c r="K78" s="30" t="n">
-        <v>40.67</v>
+        <v>41.86</v>
       </c>
       <c r="L78" s="31" t="n">
-        <v>39.65</v>
+        <v>39.28</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>38.43</v>
+        <v>36.2</v>
       </c>
       <c r="N78" s="20" t="inlineStr">
         <is>
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>40.97</v>
+        <v>42.52</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>40.76</v>
+        <v>42.1</v>
       </c>
       <c r="Q78" s="33" t="n">
-        <v>41.5</v>
+        <v>43.38</v>
       </c>
       <c r="R78" s="34" t="n">
-        <v>1.52</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="79">
@@ -5506,54 +5506,54 @@
         </is>
       </c>
       <c r="C79" s="25" t="n">
-        <v>5.63</v>
+        <v>5.64</v>
       </c>
       <c r="D79" s="25" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="E79" s="26" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="F79" s="27" t="n">
         <v>5.55</v>
       </c>
-      <c r="E79" s="26" t="n">
+      <c r="G79" s="27" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="H79" s="28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I79" s="29" t="n">
         <v>5.48</v>
       </c>
-      <c r="F79" s="27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G79" s="27" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="H79" s="28" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="I79" s="29" t="n">
+      <c r="J79" s="29" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="K79" s="30" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="L79" s="31" t="n">
         <v>5.42</v>
       </c>
-      <c r="J79" s="29" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="K79" s="30" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>5.37</v>
-      </c>
       <c r="M79" s="31" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="N79" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>5.35</v>
+      </c>
+      <c r="N79" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>5.45</v>
+        <v>5.49</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>5.44</v>
+        <v>5.48</v>
       </c>
       <c r="Q79" s="33" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="R79" s="36" t="n">
-        <v>-0.18</v>
+        <v>5.52</v>
+      </c>
+      <c r="R79" s="34" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="80">
@@ -5568,54 +5568,54 @@
         </is>
       </c>
       <c r="C80" s="25" t="n">
-        <v>19.61</v>
+        <v>18.7</v>
       </c>
       <c r="D80" s="25" t="n">
-        <v>19.01</v>
+        <v>18.53</v>
       </c>
       <c r="E80" s="26" t="n">
-        <v>18.51</v>
+        <v>18.38</v>
       </c>
       <c r="F80" s="27" t="n">
-        <v>18.64</v>
+        <v>18.38</v>
       </c>
       <c r="G80" s="27" t="n">
-        <v>18.94</v>
+        <v>18.49</v>
       </c>
       <c r="H80" s="28" t="n">
-        <v>18.34</v>
+        <v>18.32</v>
       </c>
       <c r="I80" s="29" t="n">
-        <v>18.04</v>
+        <v>18.21</v>
       </c>
       <c r="J80" s="29" t="n">
-        <v>17.74</v>
+        <v>18.15</v>
       </c>
       <c r="K80" s="30" t="n">
-        <v>18.17</v>
+        <v>18.29</v>
       </c>
       <c r="L80" s="31" t="n">
-        <v>17.67</v>
+        <v>18.14</v>
       </c>
       <c r="M80" s="31" t="n">
-        <v>17.07</v>
-      </c>
-      <c r="N80" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>17.97</v>
+      </c>
+      <c r="N80" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O80" s="32" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Q80" s="33" t="n">
         <v>18.28</v>
       </c>
-      <c r="P80" s="32" t="n">
-        <v>18.22</v>
-      </c>
-      <c r="Q80" s="33" t="n">
-        <v>18.34</v>
-      </c>
-      <c r="R80" s="34" t="n">
-        <v>1.66</v>
+      <c r="R80" s="36" t="n">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="81">
@@ -5630,37 +5630,37 @@
         </is>
       </c>
       <c r="C81" s="25" t="n">
-        <v>80.93000000000001</v>
+        <v>83.89</v>
       </c>
       <c r="D81" s="25" t="n">
-        <v>79.43000000000001</v>
+        <v>81.64</v>
       </c>
       <c r="E81" s="26" t="n">
-        <v>78.17</v>
+        <v>79.75</v>
       </c>
       <c r="F81" s="27" t="n">
-        <v>78.8</v>
+        <v>80.5</v>
       </c>
       <c r="G81" s="27" t="n">
-        <v>79.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="H81" s="28" t="n">
-        <v>77.90000000000001</v>
+        <v>79.25</v>
       </c>
       <c r="I81" s="29" t="n">
-        <v>77.3</v>
+        <v>78.25</v>
       </c>
       <c r="J81" s="29" t="n">
-        <v>76.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="K81" s="30" t="n">
-        <v>77.33</v>
+        <v>78.5</v>
       </c>
       <c r="L81" s="31" t="n">
-        <v>76.06999999999999</v>
+        <v>76.61</v>
       </c>
       <c r="M81" s="31" t="n">
-        <v>74.56999999999999</v>
+        <v>74.36</v>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
@@ -5668,16 +5668,16 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>77.67</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>77.45</v>
+        <v>78.67</v>
       </c>
       <c r="Q81" s="33" t="n">
-        <v>78.2</v>
+        <v>79.5</v>
       </c>
       <c r="R81" s="34" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="82">
@@ -5692,54 +5692,54 @@
         </is>
       </c>
       <c r="C82" s="25" t="n">
-        <v>4.76</v>
+        <v>4.88</v>
       </c>
       <c r="D82" s="25" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="E82" s="26" t="n">
         <v>4.7</v>
       </c>
-      <c r="E82" s="26" t="n">
-        <v>4.65</v>
-      </c>
       <c r="F82" s="27" t="n">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="G82" s="27" t="n">
-        <v>4.69</v>
+        <v>4.78</v>
       </c>
       <c r="H82" s="28" t="n">
-        <v>4.63</v>
+        <v>4.68</v>
       </c>
       <c r="I82" s="29" t="n">
-        <v>4.59</v>
+        <v>4.64</v>
       </c>
       <c r="J82" s="29" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="K82" s="30" t="n">
-        <v>4.61</v>
+        <v>4.64</v>
       </c>
       <c r="L82" s="31" t="n">
         <v>4.56</v>
       </c>
       <c r="M82" s="31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N82" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>4.46</v>
+      </c>
+      <c r="N82" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="Q82" s="33" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="R82" s="36" t="n">
-        <v>-0.86</v>
+        <v>4.7</v>
+      </c>
+      <c r="R82" s="34" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="83">
@@ -5754,54 +5754,54 @@
         </is>
       </c>
       <c r="C83" s="25" t="n">
-        <v>64.18000000000001</v>
+        <v>64.73</v>
       </c>
       <c r="D83" s="25" t="n">
-        <v>63.33</v>
+        <v>63.63</v>
       </c>
       <c r="E83" s="26" t="n">
-        <v>62.61</v>
+        <v>62.71</v>
       </c>
       <c r="F83" s="27" t="n">
-        <v>62.58</v>
+        <v>63.15</v>
       </c>
       <c r="G83" s="27" t="n">
-        <v>63.12</v>
+        <v>63.6</v>
       </c>
       <c r="H83" s="28" t="n">
-        <v>62.27</v>
+        <v>62.5</v>
       </c>
       <c r="I83" s="29" t="n">
-        <v>61.73</v>
+        <v>62.05</v>
       </c>
       <c r="J83" s="29" t="n">
-        <v>61.42</v>
+        <v>61.4</v>
       </c>
       <c r="K83" s="30" t="n">
-        <v>62.14</v>
+        <v>62.09</v>
       </c>
       <c r="L83" s="31" t="n">
-        <v>61.42</v>
+        <v>61.17</v>
       </c>
       <c r="M83" s="31" t="n">
-        <v>60.57</v>
-      </c>
-      <c r="N83" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>60.07</v>
+      </c>
+      <c r="N83" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O83" s="32" t="n">
-        <v>62.23</v>
+        <v>62.34</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>62.2</v>
+        <v>62.18</v>
       </c>
       <c r="Q83" s="33" t="n">
-        <v>62.05</v>
-      </c>
-      <c r="R83" s="36" t="n">
-        <v>-0.32</v>
+        <v>62.7</v>
+      </c>
+      <c r="R83" s="34" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="84">
@@ -5816,54 +5816,54 @@
         </is>
       </c>
       <c r="C84" s="25" t="n">
-        <v>39.16</v>
+        <v>39.97</v>
       </c>
       <c r="D84" s="25" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="E84" s="26" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="F84" s="27" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="G84" s="27" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="H84" s="28" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="I84" s="29" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="J84" s="29" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="K84" s="30" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="L84" s="31" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="M84" s="31" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="N84" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O84" s="32" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="P84" s="32" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="Q84" s="33" t="n">
         <v>38.8</v>
       </c>
-      <c r="E84" s="26" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F84" s="27" t="n">
-        <v>38.59</v>
-      </c>
-      <c r="G84" s="27" t="n">
-        <v>38.77</v>
-      </c>
-      <c r="H84" s="28" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="I84" s="29" t="n">
-        <v>38.23</v>
-      </c>
-      <c r="J84" s="29" t="n">
-        <v>38.05</v>
-      </c>
-      <c r="K84" s="30" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="L84" s="31" t="n">
-        <v>38</v>
-      </c>
-      <c r="M84" s="31" t="n">
-        <v>37.64</v>
-      </c>
-      <c r="N84" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O84" s="32" t="n">
-        <v>38.37</v>
-      </c>
-      <c r="P84" s="32" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="Q84" s="33" t="n">
-        <v>38.42</v>
-      </c>
-      <c r="R84" s="36" t="n">
-        <v>-0.41</v>
+      <c r="R84" s="34" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="85">
@@ -5878,54 +5878,54 @@
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>95.44</v>
+        <v>95.28</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>94.48999999999999</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="E85" s="26" t="n">
-        <v>93.69</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="F85" s="27" t="n">
-        <v>93.62</v>
+        <v>93.98</v>
       </c>
       <c r="G85" s="27" t="n">
-        <v>94.23</v>
+        <v>94.37</v>
       </c>
       <c r="H85" s="28" t="n">
-        <v>93.28</v>
+        <v>93.52</v>
       </c>
       <c r="I85" s="29" t="n">
+        <v>93.13</v>
+      </c>
+      <c r="J85" s="29" t="n">
         <v>92.67</v>
       </c>
-      <c r="J85" s="29" t="n">
-        <v>92.33</v>
-      </c>
       <c r="K85" s="30" t="n">
-        <v>93.16</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="L85" s="31" t="n">
-        <v>92.36</v>
+        <v>92.52</v>
       </c>
       <c r="M85" s="31" t="n">
-        <v>91.41</v>
-      </c>
-      <c r="N85" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>91.67</v>
+      </c>
+      <c r="N85" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>93.26000000000001</v>
+        <v>93.41</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>93.23</v>
+        <v>93.3</v>
       </c>
       <c r="Q85" s="33" t="n">
-        <v>93</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="R85" s="34" t="n">
-        <v>0.05</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="86">
@@ -5940,37 +5940,37 @@
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>17.16</v>
+        <v>17.27</v>
       </c>
       <c r="D86" s="25" t="n">
-        <v>16.93</v>
+        <v>17.06</v>
       </c>
       <c r="E86" s="26" t="n">
-        <v>16.74</v>
+        <v>16.88</v>
       </c>
       <c r="F86" s="27" t="n">
         <v>16.87</v>
       </c>
       <c r="G86" s="27" t="n">
-        <v>16.94</v>
+        <v>17</v>
       </c>
       <c r="H86" s="28" t="n">
-        <v>16.71</v>
+        <v>16.79</v>
       </c>
       <c r="I86" s="29" t="n">
-        <v>16.64</v>
+        <v>16.66</v>
       </c>
       <c r="J86" s="29" t="n">
-        <v>16.48</v>
+        <v>16.58</v>
       </c>
       <c r="K86" s="30" t="n">
-        <v>16.61</v>
+        <v>16.77</v>
       </c>
       <c r="L86" s="31" t="n">
-        <v>16.42</v>
+        <v>16.59</v>
       </c>
       <c r="M86" s="31" t="n">
-        <v>16.19</v>
+        <v>16.38</v>
       </c>
       <c r="N86" s="20" t="inlineStr">
         <is>
@@ -5978,16 +5978,16 @@
         </is>
       </c>
       <c r="O86" s="32" t="n">
-        <v>16.67</v>
+        <v>16.79</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>16.63</v>
+        <v>16.78</v>
       </c>
       <c r="Q86" s="33" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="R86" s="34" t="n">
-        <v>1.21</v>
+        <v>16.73</v>
+      </c>
+      <c r="R86" s="36" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="87">
@@ -6002,54 +6002,54 @@
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>123.39</v>
+        <v>123.27</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>121.79</v>
+        <v>121.87</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>120.45</v>
+        <v>120.69</v>
       </c>
       <c r="F87" s="27" t="n">
-        <v>120.93</v>
+        <v>120.8</v>
       </c>
       <c r="G87" s="27" t="n">
-        <v>121.67</v>
+        <v>121.6</v>
       </c>
       <c r="H87" s="28" t="n">
-        <v>120.07</v>
+        <v>120.2</v>
       </c>
       <c r="I87" s="29" t="n">
-        <v>119.33</v>
+        <v>119.4</v>
       </c>
       <c r="J87" s="29" t="n">
-        <v>118.47</v>
+        <v>118.8</v>
       </c>
       <c r="K87" s="30" t="n">
-        <v>119.55</v>
+        <v>119.91</v>
       </c>
       <c r="L87" s="31" t="n">
-        <v>118.21</v>
+        <v>118.73</v>
       </c>
       <c r="M87" s="31" t="n">
-        <v>116.61</v>
-      </c>
-      <c r="N87" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>117.33</v>
+      </c>
+      <c r="N87" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>119.87</v>
+        <v>120.11</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>119.68</v>
+        <v>120.02</v>
       </c>
       <c r="Q87" s="33" t="n">
-        <v>120.2</v>
+        <v>120</v>
       </c>
       <c r="R87" s="36" t="n">
-        <v>-0.5</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="88">
@@ -6064,54 +6064,54 @@
         </is>
       </c>
       <c r="C88" s="25" t="n">
-        <v>61.42</v>
+        <v>60.94</v>
       </c>
       <c r="D88" s="25" t="n">
-        <v>60.17</v>
+        <v>59.74</v>
       </c>
       <c r="E88" s="26" t="n">
-        <v>59.13</v>
+        <v>58.74</v>
       </c>
       <c r="F88" s="27" t="n">
-        <v>59.08</v>
+        <v>59.17</v>
       </c>
       <c r="G88" s="27" t="n">
-        <v>59.87</v>
+        <v>59.68</v>
       </c>
       <c r="H88" s="28" t="n">
-        <v>58.62</v>
+        <v>58.48</v>
       </c>
       <c r="I88" s="29" t="n">
-        <v>57.83</v>
+        <v>57.97</v>
       </c>
       <c r="J88" s="29" t="n">
-        <v>57.37</v>
+        <v>57.28</v>
       </c>
       <c r="K88" s="30" t="n">
-        <v>58.43</v>
+        <v>58.06</v>
       </c>
       <c r="L88" s="31" t="n">
-        <v>57.38</v>
+        <v>57.06</v>
       </c>
       <c r="M88" s="31" t="n">
-        <v>56.13</v>
-      </c>
-      <c r="N88" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>55.86</v>
+      </c>
+      <c r="N88" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O88" s="32" t="n">
-        <v>58.57</v>
+        <v>58.32</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>58.52</v>
+        <v>58.16</v>
       </c>
       <c r="Q88" s="33" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="R88" s="36" t="n">
-        <v>-0.09</v>
+        <v>58.65</v>
+      </c>
+      <c r="R88" s="34" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="89">
@@ -6126,54 +6126,54 @@
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>10.09</v>
+        <v>10.31</v>
       </c>
       <c r="D89" s="25" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E89" s="26" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="F89" s="27" t="n">
         <v>9.92</v>
       </c>
-      <c r="E89" s="26" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="F89" s="27" t="n">
-        <v>9.77</v>
-      </c>
       <c r="G89" s="27" t="n">
-        <v>9.880000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="H89" s="28" t="n">
-        <v>9.710000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="I89" s="29" t="n">
-        <v>9.6</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J89" s="29" t="n">
-        <v>9.539999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="K89" s="30" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="L89" s="31" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="M89" s="31" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="N89" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O89" s="32" t="n">
         <v>9.68</v>
       </c>
-      <c r="L89" s="31" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="M89" s="31" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="N89" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O89" s="32" t="n">
-        <v>9.699999999999999</v>
-      </c>
       <c r="P89" s="32" t="n">
-        <v>9.69</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Q89" s="33" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="R89" s="36" t="n">
-        <v>-0.41</v>
+        <v>9.81</v>
+      </c>
+      <c r="R89" s="34" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="90">
@@ -6188,37 +6188,37 @@
         </is>
       </c>
       <c r="C90" s="25" t="n">
-        <v>19.74</v>
+        <v>20.05</v>
       </c>
       <c r="D90" s="25" t="n">
-        <v>17.98</v>
+        <v>19.01</v>
       </c>
       <c r="E90" s="26" t="n">
-        <v>16.5</v>
+        <v>18.14</v>
       </c>
       <c r="F90" s="27" t="n">
-        <v>17.48</v>
+        <v>18.38</v>
       </c>
       <c r="G90" s="27" t="n">
-        <v>18.06</v>
+        <v>18.9</v>
       </c>
       <c r="H90" s="28" t="n">
-        <v>16.3</v>
+        <v>17.86</v>
       </c>
       <c r="I90" s="29" t="n">
-        <v>15.72</v>
+        <v>17.34</v>
       </c>
       <c r="J90" s="29" t="n">
-        <v>14.54</v>
+        <v>16.82</v>
       </c>
       <c r="K90" s="30" t="n">
-        <v>15.52</v>
+        <v>17.56</v>
       </c>
       <c r="L90" s="31" t="n">
-        <v>14.04</v>
+        <v>16.69</v>
       </c>
       <c r="M90" s="31" t="n">
-        <v>12.28</v>
+        <v>15.65</v>
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
@@ -6226,16 +6226,16 @@
         </is>
       </c>
       <c r="O90" s="32" t="n">
-        <v>15.98</v>
+        <v>17.75</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>15.65</v>
+        <v>17.64</v>
       </c>
       <c r="Q90" s="33" t="n">
-        <v>16.89</v>
+        <v>17.87</v>
       </c>
       <c r="R90" s="34" t="n">
-        <v>9.960000000000001</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="91">
@@ -6250,37 +6250,37 @@
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>19.24</v>
+        <v>19.74</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>18.78</v>
+        <v>19.19</v>
       </c>
       <c r="E91" s="26" t="n">
-        <v>18.4</v>
+        <v>18.73</v>
       </c>
       <c r="F91" s="27" t="n">
-        <v>18.6</v>
+        <v>18.99</v>
       </c>
       <c r="G91" s="27" t="n">
-        <v>18.78</v>
+        <v>19.2</v>
       </c>
       <c r="H91" s="28" t="n">
-        <v>18.32</v>
+        <v>18.65</v>
       </c>
       <c r="I91" s="29" t="n">
-        <v>18.14</v>
+        <v>18.44</v>
       </c>
       <c r="J91" s="29" t="n">
-        <v>17.86</v>
+        <v>18.1</v>
       </c>
       <c r="K91" s="30" t="n">
-        <v>18.14</v>
+        <v>18.42</v>
       </c>
       <c r="L91" s="31" t="n">
-        <v>17.76</v>
+        <v>17.96</v>
       </c>
       <c r="M91" s="31" t="n">
-        <v>17.3</v>
+        <v>17.41</v>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
@@ -6288,16 +6288,16 @@
         </is>
       </c>
       <c r="O91" s="32" t="n">
-        <v>18.25</v>
+        <v>18.56</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>18.18</v>
+        <v>18.46</v>
       </c>
       <c r="Q91" s="33" t="n">
-        <v>18.42</v>
+        <v>18.79</v>
       </c>
       <c r="R91" s="34" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="92">
@@ -6312,54 +6312,54 @@
         </is>
       </c>
       <c r="C92" s="25" t="n">
-        <v>30.88</v>
+        <v>32.63</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>30.4</v>
+        <v>31.55</v>
       </c>
       <c r="E92" s="26" t="n">
-        <v>29.99</v>
+        <v>30.64</v>
       </c>
       <c r="F92" s="27" t="n">
-        <v>30.03</v>
+        <v>31.2</v>
       </c>
       <c r="G92" s="27" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="H92" s="28" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I92" s="29" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="J92" s="29" t="n">
+        <v>29.42</v>
+      </c>
+      <c r="K92" s="30" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="L92" s="31" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="M92" s="31" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="N92" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O92" s="32" t="n">
         <v>30.31</v>
       </c>
-      <c r="H92" s="28" t="n">
-        <v>29.83</v>
-      </c>
-      <c r="I92" s="29" t="n">
-        <v>29.55</v>
-      </c>
-      <c r="J92" s="29" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="K92" s="30" t="n">
-        <v>29.73</v>
-      </c>
-      <c r="L92" s="31" t="n">
-        <v>29.32</v>
-      </c>
-      <c r="M92" s="31" t="n">
-        <v>28.84</v>
-      </c>
-      <c r="N92" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O92" s="32" t="n">
-        <v>29.79</v>
-      </c>
       <c r="P92" s="32" t="n">
-        <v>29.76</v>
+        <v>30.12</v>
       </c>
       <c r="Q92" s="33" t="n">
-        <v>29.76</v>
-      </c>
-      <c r="R92" s="36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>30.82</v>
+      </c>
+      <c r="R92" s="34" t="n">
+        <v>3.56</v>
       </c>
     </row>
     <row r="93">
@@ -6374,37 +6374,37 @@
         </is>
       </c>
       <c r="C93" s="25" t="n">
-        <v>20.93</v>
+        <v>21.3</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>20.68</v>
+        <v>20.98</v>
       </c>
       <c r="E93" s="26" t="n">
-        <v>20.48</v>
+        <v>20.71</v>
       </c>
       <c r="F93" s="27" t="n">
-        <v>20.59</v>
+        <v>20.85</v>
       </c>
       <c r="G93" s="27" t="n">
-        <v>20.68</v>
+        <v>20.98</v>
       </c>
       <c r="H93" s="28" t="n">
-        <v>20.43</v>
+        <v>20.66</v>
       </c>
       <c r="I93" s="29" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="J93" s="29" t="n">
         <v>20.34</v>
       </c>
-      <c r="J93" s="29" t="n">
-        <v>20.18</v>
-      </c>
       <c r="K93" s="30" t="n">
-        <v>20.34</v>
+        <v>20.53</v>
       </c>
       <c r="L93" s="31" t="n">
-        <v>20.13</v>
+        <v>20.26</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>19.88</v>
+        <v>19.94</v>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
@@ -6412,16 +6412,16 @@
         </is>
       </c>
       <c r="O93" s="32" t="n">
-        <v>20.39</v>
+        <v>20.61</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>20.35</v>
+        <v>20.56</v>
       </c>
       <c r="Q93" s="33" t="n">
-        <v>20.49</v>
+        <v>20.73</v>
       </c>
       <c r="R93" s="34" t="n">
-        <v>0.89</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="94">
@@ -6436,37 +6436,37 @@
         </is>
       </c>
       <c r="C94" s="25" t="n">
-        <v>28.6</v>
+        <v>29.24</v>
       </c>
       <c r="D94" s="25" t="n">
-        <v>28.02</v>
+        <v>28.62</v>
       </c>
       <c r="E94" s="26" t="n">
-        <v>27.53</v>
+        <v>28.1</v>
       </c>
       <c r="F94" s="27" t="n">
-        <v>27.79</v>
+        <v>28.18</v>
       </c>
       <c r="G94" s="27" t="n">
-        <v>28.01</v>
+        <v>28.52</v>
       </c>
       <c r="H94" s="28" t="n">
-        <v>27.43</v>
+        <v>27.9</v>
       </c>
       <c r="I94" s="29" t="n">
-        <v>27.21</v>
+        <v>27.56</v>
       </c>
       <c r="J94" s="29" t="n">
-        <v>26.85</v>
+        <v>27.28</v>
       </c>
       <c r="K94" s="30" t="n">
-        <v>27.21</v>
+        <v>27.76</v>
       </c>
       <c r="L94" s="31" t="n">
-        <v>26.72</v>
+        <v>27.24</v>
       </c>
       <c r="M94" s="31" t="n">
-        <v>26.14</v>
+        <v>26.62</v>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>27.34</v>
+        <v>27.85</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>27.25</v>
+        <v>27.8</v>
       </c>
       <c r="Q94" s="33" t="n">
-        <v>27.56</v>
+        <v>27.84</v>
       </c>
       <c r="R94" s="34" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="95">
@@ -6498,54 +6498,54 @@
         </is>
       </c>
       <c r="C95" s="25" t="n">
-        <v>172.71</v>
+        <v>172.85</v>
       </c>
       <c r="D95" s="25" t="n">
-        <v>170.91</v>
+        <v>171.15</v>
       </c>
       <c r="E95" s="26" t="n">
-        <v>169.4</v>
+        <v>169.73</v>
       </c>
       <c r="F95" s="27" t="n">
-        <v>169.67</v>
+        <v>170</v>
       </c>
       <c r="G95" s="27" t="n">
-        <v>170.63</v>
+        <v>170.9</v>
       </c>
       <c r="H95" s="28" t="n">
-        <v>168.83</v>
+        <v>169.2</v>
       </c>
       <c r="I95" s="29" t="n">
-        <v>167.87</v>
+        <v>168.3</v>
       </c>
       <c r="J95" s="29" t="n">
-        <v>167.03</v>
+        <v>167.5</v>
       </c>
       <c r="K95" s="30" t="n">
-        <v>168.4</v>
+        <v>168.77</v>
       </c>
       <c r="L95" s="31" t="n">
-        <v>166.89</v>
+        <v>167.35</v>
       </c>
       <c r="M95" s="31" t="n">
-        <v>165.09</v>
-      </c>
-      <c r="N95" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>165.65</v>
+      </c>
+      <c r="N95" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O95" s="32" t="n">
-        <v>168.68</v>
+        <v>169.05</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>168.54</v>
+        <v>168.91</v>
       </c>
       <c r="Q95" s="33" t="n">
-        <v>168.7</v>
-      </c>
-      <c r="R95" s="36" t="n">
-        <v>-0.71</v>
+        <v>169.1</v>
+      </c>
+      <c r="R95" s="34" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="96">
@@ -6560,37 +6560,37 @@
         </is>
       </c>
       <c r="C96" s="25" t="n">
-        <v>15.23</v>
+        <v>14.43</v>
       </c>
       <c r="D96" s="25" t="n">
-        <v>14.78</v>
+        <v>14.27</v>
       </c>
       <c r="E96" s="26" t="n">
-        <v>14.4</v>
+        <v>14.13</v>
       </c>
       <c r="F96" s="27" t="n">
-        <v>14.46</v>
+        <v>14.14</v>
       </c>
       <c r="G96" s="27" t="n">
-        <v>14.7</v>
+        <v>14.23</v>
       </c>
       <c r="H96" s="28" t="n">
-        <v>14.25</v>
+        <v>14.07</v>
       </c>
       <c r="I96" s="29" t="n">
-        <v>14.01</v>
+        <v>13.98</v>
       </c>
       <c r="J96" s="29" t="n">
-        <v>13.8</v>
+        <v>13.91</v>
       </c>
       <c r="K96" s="30" t="n">
-        <v>14.15</v>
+        <v>14.05</v>
       </c>
       <c r="L96" s="31" t="n">
-        <v>13.77</v>
+        <v>13.91</v>
       </c>
       <c r="M96" s="31" t="n">
-        <v>13.32</v>
+        <v>13.75</v>
       </c>
       <c r="N96" s="35" t="inlineStr">
         <is>
@@ -6598,16 +6598,16 @@
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>14.22</v>
+        <v>14.07</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>14.18</v>
+        <v>14.06</v>
       </c>
       <c r="Q96" s="33" t="n">
-        <v>14.21</v>
+        <v>14.04</v>
       </c>
       <c r="R96" s="36" t="n">
-        <v>-0.21</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="97">
@@ -6622,37 +6622,37 @@
         </is>
       </c>
       <c r="C97" s="25" t="n">
-        <v>21.63</v>
+        <v>21.5</v>
       </c>
       <c r="D97" s="25" t="n">
-        <v>21.03</v>
+        <v>21.12</v>
       </c>
       <c r="E97" s="26" t="n">
-        <v>20.53</v>
+        <v>20.81</v>
       </c>
       <c r="F97" s="27" t="n">
-        <v>20.77</v>
+        <v>20.76</v>
       </c>
       <c r="G97" s="27" t="n">
         <v>21.02</v>
       </c>
       <c r="H97" s="28" t="n">
-        <v>20.42</v>
+        <v>20.64</v>
       </c>
       <c r="I97" s="29" t="n">
-        <v>20.17</v>
+        <v>20.38</v>
       </c>
       <c r="J97" s="29" t="n">
-        <v>19.82</v>
+        <v>20.26</v>
       </c>
       <c r="K97" s="30" t="n">
-        <v>20.19</v>
+        <v>20.59</v>
       </c>
       <c r="L97" s="31" t="n">
-        <v>19.69</v>
+        <v>20.28</v>
       </c>
       <c r="M97" s="31" t="n">
-        <v>19.09</v>
+        <v>19.9</v>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
@@ -6660,16 +6660,16 @@
         </is>
       </c>
       <c r="O97" s="32" t="n">
-        <v>20.33</v>
+        <v>20.63</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>20.24</v>
+        <v>20.62</v>
       </c>
       <c r="Q97" s="33" t="n">
-        <v>20.53</v>
-      </c>
-      <c r="R97" s="34" t="n">
-        <v>0.88</v>
+        <v>20.51</v>
+      </c>
+      <c r="R97" s="36" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="98">
@@ -6684,54 +6684,54 @@
         </is>
       </c>
       <c r="C98" s="25" t="n">
-        <v>16.36</v>
+        <v>17.24</v>
       </c>
       <c r="D98" s="25" t="n">
-        <v>16.18</v>
+        <v>16.75</v>
       </c>
       <c r="E98" s="26" t="n">
-        <v>16.03</v>
+        <v>16.34</v>
       </c>
       <c r="F98" s="27" t="n">
-        <v>16.06</v>
+        <v>16.5</v>
       </c>
       <c r="G98" s="27" t="n">
-        <v>16.15</v>
+        <v>16.72</v>
       </c>
       <c r="H98" s="28" t="n">
-        <v>15.97</v>
+        <v>16.23</v>
       </c>
       <c r="I98" s="29" t="n">
-        <v>15.88</v>
+        <v>16.01</v>
       </c>
       <c r="J98" s="29" t="n">
-        <v>15.79</v>
+        <v>15.74</v>
       </c>
       <c r="K98" s="30" t="n">
-        <v>15.93</v>
+        <v>16.07</v>
       </c>
       <c r="L98" s="31" t="n">
-        <v>15.78</v>
+        <v>15.66</v>
       </c>
       <c r="M98" s="31" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="N98" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>15.17</v>
+      </c>
+      <c r="N98" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O98" s="32" t="n">
-        <v>15.96</v>
+        <v>16.17</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>15.94</v>
+        <v>16.11</v>
       </c>
       <c r="Q98" s="33" t="n">
-        <v>15.96</v>
+        <v>16.28</v>
       </c>
       <c r="R98" s="34" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="99">
@@ -6746,37 +6746,37 @@
         </is>
       </c>
       <c r="C99" s="25" t="n">
-        <v>11.13</v>
+        <v>10.7</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>10.49</v>
+        <v>10.4</v>
       </c>
       <c r="E99" s="26" t="n">
-        <v>9.949999999999999</v>
+        <v>10.14</v>
       </c>
       <c r="F99" s="27" t="n">
         <v>10.2</v>
       </c>
       <c r="G99" s="27" t="n">
-        <v>10.46</v>
+        <v>10.35</v>
       </c>
       <c r="H99" s="28" t="n">
-        <v>9.82</v>
+        <v>10.05</v>
       </c>
       <c r="I99" s="29" t="n">
-        <v>9.56</v>
+        <v>9.9</v>
       </c>
       <c r="J99" s="29" t="n">
-        <v>9.18</v>
+        <v>9.75</v>
       </c>
       <c r="K99" s="30" t="n">
-        <v>9.59</v>
+        <v>9.98</v>
       </c>
       <c r="L99" s="31" t="n">
-        <v>9.050000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M99" s="31" t="n">
-        <v>8.41</v>
+        <v>9.42</v>
       </c>
       <c r="N99" s="20" t="inlineStr">
         <is>
@@ -6784,16 +6784,16 @@
         </is>
       </c>
       <c r="O99" s="32" t="n">
-        <v>9.73</v>
+        <v>10.03</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>9.640000000000001</v>
+        <v>10</v>
       </c>
       <c r="Q99" s="33" t="n">
-        <v>9.93</v>
+        <v>10.04</v>
       </c>
       <c r="R99" s="34" t="n">
-        <v>4.53</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="100">
@@ -6808,54 +6808,54 @@
         </is>
       </c>
       <c r="C100" s="25" t="n">
-        <v>26.83</v>
+        <v>26.71</v>
       </c>
       <c r="D100" s="25" t="n">
-        <v>26.29</v>
+        <v>26.27</v>
       </c>
       <c r="E100" s="26" t="n">
-        <v>25.84</v>
+        <v>25.9</v>
       </c>
       <c r="F100" s="27" t="n">
-        <v>25.85</v>
+        <v>26</v>
       </c>
       <c r="G100" s="27" t="n">
-        <v>26.17</v>
+        <v>26.22</v>
       </c>
       <c r="H100" s="28" t="n">
-        <v>25.63</v>
+        <v>25.78</v>
       </c>
       <c r="I100" s="29" t="n">
-        <v>25.31</v>
+        <v>25.56</v>
       </c>
       <c r="J100" s="29" t="n">
-        <v>25.09</v>
+        <v>25.34</v>
       </c>
       <c r="K100" s="30" t="n">
-        <v>25.54</v>
+        <v>25.66</v>
       </c>
       <c r="L100" s="31" t="n">
-        <v>25.09</v>
+        <v>25.29</v>
       </c>
       <c r="M100" s="31" t="n">
-        <v>24.55</v>
-      </c>
-      <c r="N100" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>24.85</v>
+      </c>
+      <c r="N100" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O100" s="32" t="n">
-        <v>25.61</v>
+        <v>25.74</v>
       </c>
       <c r="P100" s="32" t="n">
-        <v>25.58</v>
+        <v>25.69</v>
       </c>
       <c r="Q100" s="33" t="n">
-        <v>25.52</v>
-      </c>
-      <c r="R100" s="36" t="n">
-        <v>-0.47</v>
+        <v>25.78</v>
+      </c>
+      <c r="R100" s="34" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="101">
@@ -6870,54 +6870,54 @@
         </is>
       </c>
       <c r="C101" s="25" t="n">
-        <v>17.49</v>
+        <v>17.69</v>
       </c>
       <c r="D101" s="25" t="n">
-        <v>17.25</v>
+        <v>17.41</v>
       </c>
       <c r="E101" s="26" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="F101" s="27" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="G101" s="27" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="H101" s="28" t="n">
         <v>17.05</v>
       </c>
-      <c r="F101" s="27" t="n">
-        <v>17.18</v>
-      </c>
-      <c r="G101" s="27" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="H101" s="28" t="n">
+      <c r="I101" s="29" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="J101" s="29" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="K101" s="30" t="n">
         <v>17.02</v>
       </c>
-      <c r="I101" s="29" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="J101" s="29" t="n">
-        <v>16.78</v>
-      </c>
-      <c r="K101" s="30" t="n">
-        <v>16.91</v>
-      </c>
       <c r="L101" s="31" t="n">
-        <v>16.71</v>
+        <v>16.79</v>
       </c>
       <c r="M101" s="31" t="n">
-        <v>16.47</v>
-      </c>
-      <c r="N101" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.51</v>
+      </c>
+      <c r="N101" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O101" s="32" t="n">
-        <v>16.98</v>
+        <v>17.05</v>
       </c>
       <c r="P101" s="32" t="n">
-        <v>16.93</v>
+        <v>17.04</v>
       </c>
       <c r="Q101" s="33" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="R101" s="34" t="n">
-        <v>0.83</v>
+        <v>16.96</v>
+      </c>
+      <c r="R101" s="36" t="n">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="102">
@@ -6932,54 +6932,54 @@
         </is>
       </c>
       <c r="C102" s="25" t="n">
-        <v>33.56</v>
+        <v>32.94</v>
       </c>
       <c r="D102" s="25" t="n">
-        <v>32.88</v>
+        <v>32.58</v>
       </c>
       <c r="E102" s="26" t="n">
-        <v>32.31</v>
+        <v>32.28</v>
       </c>
       <c r="F102" s="27" t="n">
-        <v>32.42</v>
+        <v>32.4</v>
       </c>
       <c r="G102" s="27" t="n">
-        <v>32.78</v>
+        <v>32.56</v>
       </c>
       <c r="H102" s="28" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="I102" s="29" t="n">
-        <v>31.74</v>
+        <v>32.04</v>
       </c>
       <c r="J102" s="29" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="K102" s="30" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="L102" s="31" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="M102" s="31" t="n">
         <v>31.42</v>
       </c>
-      <c r="K102" s="30" t="n">
-        <v>31.93</v>
-      </c>
-      <c r="L102" s="31" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="M102" s="31" t="n">
-        <v>30.68</v>
-      </c>
-      <c r="N102" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+      <c r="N102" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O102" s="32" t="n">
-        <v>32.04</v>
+        <v>32.15</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>31.98</v>
+        <v>32.11</v>
       </c>
       <c r="Q102" s="33" t="n">
-        <v>32.06</v>
+        <v>32.24</v>
       </c>
       <c r="R102" s="34" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -6994,54 +6994,54 @@
         </is>
       </c>
       <c r="C103" s="25" t="n">
-        <v>16.61</v>
+        <v>16.36</v>
       </c>
       <c r="D103" s="25" t="n">
-        <v>16.11</v>
+        <v>15.95</v>
       </c>
       <c r="E103" s="26" t="n">
-        <v>15.69</v>
+        <v>15.61</v>
       </c>
       <c r="F103" s="27" t="n">
-        <v>15.63</v>
+        <v>15.66</v>
       </c>
       <c r="G103" s="27" t="n">
-        <v>15.97</v>
+        <v>15.88</v>
       </c>
       <c r="H103" s="28" t="n">
         <v>15.47</v>
       </c>
       <c r="I103" s="29" t="n">
-        <v>15.13</v>
+        <v>15.25</v>
       </c>
       <c r="J103" s="29" t="n">
-        <v>14.97</v>
+        <v>15.06</v>
       </c>
       <c r="K103" s="30" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="L103" s="31" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="M103" s="31" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="N103" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O103" s="32" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="P103" s="32" t="n">
         <v>15.41</v>
       </c>
-      <c r="L103" s="31" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="M103" s="31" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="N103" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O103" s="32" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="P103" s="32" t="n">
-        <v>15.45</v>
-      </c>
       <c r="Q103" s="33" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="R103" s="36" t="n">
-        <v>-1.29</v>
+        <v>15.43</v>
+      </c>
+      <c r="R103" s="34" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="104">
@@ -7056,54 +7056,54 @@
         </is>
       </c>
       <c r="C104" s="25" t="n">
-        <v>78.38</v>
+        <v>75.63</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>75.58</v>
+        <v>74.13</v>
       </c>
       <c r="E104" s="26" t="n">
-        <v>73.23</v>
+        <v>72.87</v>
       </c>
       <c r="F104" s="27" t="n">
-        <v>74.18000000000001</v>
+        <v>72.83</v>
       </c>
       <c r="G104" s="27" t="n">
-        <v>75.42</v>
+        <v>73.77</v>
       </c>
       <c r="H104" s="28" t="n">
-        <v>72.62</v>
+        <v>72.27</v>
       </c>
       <c r="I104" s="29" t="n">
-        <v>71.38</v>
+        <v>71.33</v>
       </c>
       <c r="J104" s="29" t="n">
-        <v>69.81999999999999</v>
+        <v>70.77</v>
       </c>
       <c r="K104" s="30" t="n">
-        <v>71.67</v>
+        <v>72.03</v>
       </c>
       <c r="L104" s="31" t="n">
-        <v>69.31999999999999</v>
+        <v>70.77</v>
       </c>
       <c r="M104" s="31" t="n">
-        <v>66.52</v>
-      </c>
-      <c r="N104" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>69.27</v>
+      </c>
+      <c r="N104" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O104" s="32" t="n">
-        <v>72.25</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>71.88</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="Q104" s="33" t="n">
-        <v>72.95</v>
-      </c>
-      <c r="R104" s="34" t="n">
-        <v>2.24</v>
+        <v>71.90000000000001</v>
+      </c>
+      <c r="R104" s="36" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="105">
@@ -7118,54 +7118,54 @@
         </is>
       </c>
       <c r="C105" s="25" t="n">
-        <v>14.78</v>
+        <v>15</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>14.61</v>
+        <v>14.77</v>
       </c>
       <c r="E105" s="26" t="n">
-        <v>14.46</v>
+        <v>14.58</v>
       </c>
       <c r="F105" s="27" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="G105" s="27" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="H105" s="28" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="I105" s="29" t="n">
         <v>14.45</v>
       </c>
-      <c r="G105" s="27" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="H105" s="28" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="I105" s="29" t="n">
-        <v>14.28</v>
-      </c>
       <c r="J105" s="29" t="n">
-        <v>14.22</v>
+        <v>14.31</v>
       </c>
       <c r="K105" s="30" t="n">
-        <v>14.37</v>
+        <v>14.45</v>
       </c>
       <c r="L105" s="31" t="n">
-        <v>14.22</v>
+        <v>14.26</v>
       </c>
       <c r="M105" s="31" t="n">
-        <v>14.05</v>
-      </c>
-      <c r="N105" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>14.03</v>
+      </c>
+      <c r="N105" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>14.39</v>
+        <v>14.5</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>14.38</v>
+        <v>14.47</v>
       </c>
       <c r="Q105" s="33" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="R105" s="36" t="n">
-        <v>-0.55</v>
+        <v>14.59</v>
+      </c>
+      <c r="R105" s="34" t="n">
+        <v>1.74</v>
       </c>
     </row>
     <row r="106">
@@ -7180,37 +7180,37 @@
         </is>
       </c>
       <c r="C106" s="25" t="n">
-        <v>21.2</v>
+        <v>21.15</v>
       </c>
       <c r="D106" s="25" t="n">
-        <v>19.47</v>
+        <v>19.2</v>
       </c>
       <c r="E106" s="26" t="n">
-        <v>18.02</v>
+        <v>17.56</v>
       </c>
       <c r="F106" s="27" t="n">
-        <v>17.92</v>
+        <v>18.14</v>
       </c>
       <c r="G106" s="27" t="n">
-        <v>19.02</v>
+        <v>19.04</v>
       </c>
       <c r="H106" s="28" t="n">
-        <v>17.29</v>
+        <v>17.09</v>
       </c>
       <c r="I106" s="29" t="n">
         <v>16.19</v>
       </c>
       <c r="J106" s="29" t="n">
-        <v>15.56</v>
+        <v>15.14</v>
       </c>
       <c r="K106" s="30" t="n">
-        <v>17.05</v>
+        <v>16.47</v>
       </c>
       <c r="L106" s="31" t="n">
-        <v>15.6</v>
+        <v>14.83</v>
       </c>
       <c r="M106" s="31" t="n">
-        <v>13.87</v>
+        <v>12.88</v>
       </c>
       <c r="N106" s="35" t="inlineStr">
         <is>
@@ -7218,16 +7218,16 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="P106" s="32" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="Q106" s="33" t="n">
         <v>17.24</v>
       </c>
-      <c r="P106" s="32" t="n">
-        <v>17.19</v>
-      </c>
-      <c r="Q106" s="33" t="n">
-        <v>16.81</v>
-      </c>
       <c r="R106" s="34" t="n">
-        <v>0.06</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="107">
@@ -7242,37 +7242,37 @@
         </is>
       </c>
       <c r="C107" s="25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D107" s="25" t="n">
         <v>2.53</v>
       </c>
-      <c r="D107" s="25" t="n">
-        <v>2.49</v>
-      </c>
       <c r="E107" s="26" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="F107" s="27" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="G107" s="27" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="H107" s="28" t="n">
         <v>2.45</v>
       </c>
       <c r="I107" s="29" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J107" s="29" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="K107" s="30" t="n">
         <v>2.44</v>
       </c>
       <c r="L107" s="31" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="M107" s="31" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="N107" s="35" t="inlineStr">
         <is>
@@ -7280,16 +7280,16 @@
         </is>
       </c>
       <c r="O107" s="32" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="P107" s="32" t="n">
         <v>2.44</v>
       </c>
       <c r="Q107" s="33" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R107" s="34" t="n">
-        <v>0</v>
+        <v>2.43</v>
+      </c>
+      <c r="R107" s="36" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="108">
@@ -7304,37 +7304,37 @@
         </is>
       </c>
       <c r="C108" s="25" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="D108" s="25" t="n">
-        <v>39.28</v>
+        <v>39.48</v>
       </c>
       <c r="E108" s="26" t="n">
-        <v>38.85</v>
+        <v>38.96</v>
       </c>
       <c r="F108" s="27" t="n">
-        <v>38.93</v>
+        <v>39.31</v>
       </c>
       <c r="G108" s="27" t="n">
-        <v>39.21</v>
+        <v>39.51</v>
       </c>
       <c r="H108" s="28" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="I108" s="29" t="n">
         <v>38.69</v>
       </c>
-      <c r="I108" s="29" t="n">
-        <v>38.41</v>
-      </c>
       <c r="J108" s="29" t="n">
-        <v>38.17</v>
+        <v>38.27</v>
       </c>
       <c r="K108" s="30" t="n">
-        <v>38.55</v>
+        <v>38.62</v>
       </c>
       <c r="L108" s="31" t="n">
-        <v>38.12</v>
+        <v>38.1</v>
       </c>
       <c r="M108" s="31" t="n">
-        <v>37.6</v>
+        <v>37.48</v>
       </c>
       <c r="N108" s="20" t="inlineStr">
         <is>
@@ -7342,16 +7342,16 @@
         </is>
       </c>
       <c r="O108" s="32" t="n">
-        <v>38.64</v>
+        <v>38.78</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>38.59</v>
+        <v>38.66</v>
       </c>
       <c r="Q108" s="33" t="n">
-        <v>38.66</v>
+        <v>39.1</v>
       </c>
       <c r="R108" s="34" t="n">
-        <v>0.42</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="109">
@@ -7375,19 +7375,19 @@
         <v>8.18</v>
       </c>
       <c r="F109" s="27" t="n">
-        <v>8.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G109" s="27" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="H109" s="28" t="n">
-        <v>8.140000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="I109" s="29" t="n">
-        <v>8.07</v>
+        <v>8.09</v>
       </c>
       <c r="J109" s="29" t="n">
-        <v>8.029999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K109" s="30" t="n">
         <v>8.109999999999999</v>
@@ -7398,9 +7398,9 @@
       <c r="M109" s="31" t="n">
         <v>7.91</v>
       </c>
-      <c r="N109" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+      <c r="N109" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O109" s="32" t="n">
@@ -7410,7 +7410,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="Q109" s="33" t="n">
-        <v>8.119999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="R109" s="34" t="n">
         <v>0.37</v>
@@ -7428,54 +7428,54 @@
         </is>
       </c>
       <c r="C110" s="25" t="n">
-        <v>44.31</v>
+        <v>45.05</v>
       </c>
       <c r="D110" s="25" t="n">
-        <v>43.93</v>
+        <v>44.49</v>
       </c>
       <c r="E110" s="26" t="n">
-        <v>43.62</v>
+        <v>44.02</v>
       </c>
       <c r="F110" s="27" t="n">
-        <v>43.76</v>
+        <v>44.33</v>
       </c>
       <c r="G110" s="27" t="n">
-        <v>43.92</v>
+        <v>44.51</v>
       </c>
       <c r="H110" s="28" t="n">
-        <v>43.54</v>
+        <v>43.95</v>
       </c>
       <c r="I110" s="29" t="n">
-        <v>43.38</v>
+        <v>43.77</v>
       </c>
       <c r="J110" s="29" t="n">
-        <v>43.16</v>
+        <v>43.39</v>
       </c>
       <c r="K110" s="30" t="n">
-        <v>43.4</v>
+        <v>43.7</v>
       </c>
       <c r="L110" s="31" t="n">
-        <v>43.09</v>
+        <v>43.23</v>
       </c>
       <c r="M110" s="31" t="n">
-        <v>42.71</v>
-      </c>
-      <c r="N110" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>42.67</v>
+      </c>
+      <c r="N110" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O110" s="32" t="n">
-        <v>43.49</v>
+        <v>43.85</v>
       </c>
       <c r="P110" s="32" t="n">
-        <v>43.43</v>
+        <v>43.75</v>
       </c>
       <c r="Q110" s="33" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="R110" s="36" t="n">
-        <v>-0.23</v>
+        <v>44.14</v>
+      </c>
+      <c r="R110" s="34" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="111">
@@ -7490,54 +7490,54 @@
         </is>
       </c>
       <c r="C111" s="25" t="n">
-        <v>65.73999999999999</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="D111" s="25" t="n">
-        <v>64.79000000000001</v>
+        <v>65.33</v>
       </c>
       <c r="E111" s="26" t="n">
-        <v>63.99</v>
+        <v>64.61</v>
       </c>
       <c r="F111" s="27" t="n">
-        <v>64.12</v>
+        <v>64.55</v>
       </c>
       <c r="G111" s="27" t="n">
-        <v>64.63</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H111" s="28" t="n">
-        <v>63.68</v>
+        <v>64.25</v>
       </c>
       <c r="I111" s="29" t="n">
-        <v>63.17</v>
+        <v>63.7</v>
       </c>
       <c r="J111" s="29" t="n">
-        <v>62.73</v>
+        <v>63.4</v>
       </c>
       <c r="K111" s="30" t="n">
-        <v>63.46</v>
+        <v>64.14</v>
       </c>
       <c r="L111" s="31" t="n">
-        <v>62.66</v>
+        <v>63.42</v>
       </c>
       <c r="M111" s="31" t="n">
-        <v>61.71</v>
-      </c>
-      <c r="N111" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>62.57</v>
+      </c>
+      <c r="N111" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O111" s="32" t="n">
-        <v>63.61</v>
+        <v>64.23</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>63.53</v>
+        <v>64.2</v>
       </c>
       <c r="Q111" s="33" t="n">
-        <v>63.6</v>
+        <v>64</v>
       </c>
       <c r="R111" s="34" t="n">
-        <v>0.08</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="112">
@@ -7552,54 +7552,54 @@
         </is>
       </c>
       <c r="C112" s="25" t="n">
-        <v>10.38</v>
+        <v>10.63</v>
       </c>
       <c r="D112" s="25" t="n">
-        <v>10.32</v>
+        <v>10.48</v>
       </c>
       <c r="E112" s="26" t="n">
-        <v>10.27</v>
+        <v>10.36</v>
       </c>
       <c r="F112" s="27" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="G112" s="27" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="H112" s="28" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="I112" s="29" t="n">
         <v>10.26</v>
-      </c>
-      <c r="G112" s="27" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H112" s="28" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="I112" s="29" t="n">
-        <v>10.2</v>
       </c>
       <c r="J112" s="29" t="n">
         <v>10.18</v>
       </c>
       <c r="K112" s="30" t="n">
-        <v>10.23</v>
+        <v>10.27</v>
       </c>
       <c r="L112" s="31" t="n">
-        <v>10.18</v>
+        <v>10.15</v>
       </c>
       <c r="M112" s="31" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="N112" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>10</v>
+      </c>
+      <c r="N112" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O112" s="32" t="n">
-        <v>10.24</v>
+        <v>10.31</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>10.24</v>
+        <v>10.28</v>
       </c>
       <c r="Q112" s="33" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="R112" s="36" t="n">
-        <v>-0.49</v>
+        <v>10.35</v>
+      </c>
+      <c r="R112" s="34" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="113">
@@ -7614,54 +7614,54 @@
         </is>
       </c>
       <c r="C113" s="25" t="n">
-        <v>309.36</v>
+        <v>320.94</v>
       </c>
       <c r="D113" s="25" t="n">
-        <v>300.36</v>
+        <v>308.74</v>
       </c>
       <c r="E113" s="26" t="n">
-        <v>292.82</v>
+        <v>298.52</v>
       </c>
       <c r="F113" s="27" t="n">
-        <v>294.73</v>
+        <v>305.13</v>
       </c>
       <c r="G113" s="27" t="n">
-        <v>299.27</v>
+        <v>309.27</v>
       </c>
       <c r="H113" s="28" t="n">
-        <v>290.27</v>
+        <v>297.07</v>
       </c>
       <c r="I113" s="29" t="n">
-        <v>285.73</v>
+        <v>292.93</v>
       </c>
       <c r="J113" s="29" t="n">
-        <v>281.27</v>
+        <v>284.87</v>
       </c>
       <c r="K113" s="30" t="n">
-        <v>287.78</v>
+        <v>291.68</v>
       </c>
       <c r="L113" s="31" t="n">
-        <v>280.24</v>
+        <v>281.46</v>
       </c>
       <c r="M113" s="31" t="n">
-        <v>271.24</v>
-      </c>
-      <c r="N113" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>269.26</v>
+      </c>
+      <c r="N113" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O113" s="32" t="n">
-        <v>289.37</v>
+        <v>294.85</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>288.48</v>
+        <v>292.64</v>
       </c>
       <c r="Q113" s="33" t="n">
-        <v>290.2</v>
-      </c>
-      <c r="R113" s="36" t="n">
-        <v>-0.27</v>
+        <v>301</v>
+      </c>
+      <c r="R113" s="34" t="n">
+        <v>3.72</v>
       </c>
     </row>
     <row r="114">
@@ -7676,54 +7676,54 @@
         </is>
       </c>
       <c r="C114" s="25" t="n">
-        <v>210.35</v>
+        <v>208.77</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>206.55</v>
+        <v>206.07</v>
       </c>
       <c r="E114" s="26" t="n">
-        <v>203.36</v>
+        <v>203.81</v>
       </c>
       <c r="F114" s="27" t="n">
-        <v>204.2</v>
+        <v>205.3</v>
       </c>
       <c r="G114" s="27" t="n">
-        <v>206.1</v>
+        <v>206.2</v>
       </c>
       <c r="H114" s="28" t="n">
-        <v>202.3</v>
+        <v>203.5</v>
       </c>
       <c r="I114" s="29" t="n">
-        <v>200.4</v>
+        <v>202.6</v>
       </c>
       <c r="J114" s="29" t="n">
-        <v>198.5</v>
+        <v>200.8</v>
       </c>
       <c r="K114" s="30" t="n">
-        <v>201.24</v>
+        <v>202.29</v>
       </c>
       <c r="L114" s="31" t="n">
-        <v>198.05</v>
+        <v>200.03</v>
       </c>
       <c r="M114" s="31" t="n">
-        <v>194.25</v>
-      </c>
-      <c r="N114" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>197.33</v>
+      </c>
+      <c r="N114" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>201.92</v>
+        <v>203</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>201.53</v>
+        <v>202.5</v>
       </c>
       <c r="Q114" s="33" t="n">
-        <v>202.3</v>
-      </c>
-      <c r="R114" s="36" t="n">
-        <v>-0.39</v>
+        <v>204.4</v>
+      </c>
+      <c r="R114" s="34" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="115">
@@ -7738,37 +7738,37 @@
         </is>
       </c>
       <c r="C115" s="25" t="n">
-        <v>602.47</v>
+        <v>633.08</v>
       </c>
       <c r="D115" s="25" t="n">
-        <v>598.47</v>
+        <v>617.58</v>
       </c>
       <c r="E115" s="26" t="n">
-        <v>595.12</v>
+        <v>604.59</v>
       </c>
       <c r="F115" s="27" t="n">
+        <v>612.83</v>
+      </c>
+      <c r="G115" s="27" t="n">
+        <v>618.17</v>
+      </c>
+      <c r="H115" s="28" t="n">
+        <v>602.67</v>
+      </c>
+      <c r="I115" s="29" t="n">
         <v>597.33</v>
       </c>
-      <c r="G115" s="27" t="n">
-        <v>598.67</v>
-      </c>
-      <c r="H115" s="28" t="n">
-        <v>594.67</v>
-      </c>
-      <c r="I115" s="29" t="n">
-        <v>593.33</v>
-      </c>
       <c r="J115" s="29" t="n">
-        <v>590.67</v>
+        <v>587.17</v>
       </c>
       <c r="K115" s="30" t="n">
-        <v>592.88</v>
+        <v>595.91</v>
       </c>
       <c r="L115" s="31" t="n">
-        <v>589.53</v>
+        <v>582.92</v>
       </c>
       <c r="M115" s="31" t="n">
-        <v>585.53</v>
+        <v>567.42</v>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
@@ -7776,16 +7776,16 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>593.9299999999999</v>
+        <v>599.89</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>593.1900000000001</v>
+        <v>597.12</v>
       </c>
       <c r="Q115" s="33" t="n">
-        <v>596</v>
+        <v>607.5</v>
       </c>
       <c r="R115" s="34" t="n">
-        <v>0.25</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="116">
@@ -7800,54 +7800,54 @@
         </is>
       </c>
       <c r="C116" s="25" t="n">
-        <v>6.73</v>
+        <v>6.84</v>
       </c>
       <c r="D116" s="25" t="n">
-        <v>6.65</v>
+        <v>6.74</v>
       </c>
       <c r="E116" s="26" t="n">
-        <v>6.58</v>
+        <v>6.66</v>
       </c>
       <c r="F116" s="27" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G116" s="27" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="H116" s="28" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="I116" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J116" s="29" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="K116" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L116" s="31" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="M116" s="31" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="N116" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O116" s="32" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="P116" s="32" t="n">
         <v>6.61</v>
       </c>
-      <c r="G116" s="27" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="H116" s="28" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="I116" s="29" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="J116" s="29" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="K116" s="30" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="L116" s="31" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="M116" s="31" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="N116" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O116" s="32" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="P116" s="32" t="n">
-        <v>6.54</v>
-      </c>
       <c r="Q116" s="33" t="n">
-        <v>6.58</v>
+        <v>6.66</v>
       </c>
       <c r="R116" s="34" t="n">
-        <v>0.46</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="117">
@@ -7862,37 +7862,37 @@
         </is>
       </c>
       <c r="C117" s="25" t="n">
-        <v>144.74</v>
+        <v>141.29</v>
       </c>
       <c r="D117" s="25" t="n">
-        <v>142.24</v>
+        <v>139.69</v>
       </c>
       <c r="E117" s="26" t="n">
-        <v>140.15</v>
+        <v>138.35</v>
       </c>
       <c r="F117" s="27" t="n">
-        <v>140.33</v>
+        <v>138.7</v>
       </c>
       <c r="G117" s="27" t="n">
-        <v>141.77</v>
+        <v>139.5</v>
       </c>
       <c r="H117" s="28" t="n">
-        <v>139.27</v>
+        <v>137.9</v>
       </c>
       <c r="I117" s="29" t="n">
-        <v>137.83</v>
+        <v>137.1</v>
       </c>
       <c r="J117" s="29" t="n">
-        <v>136.77</v>
+        <v>136.3</v>
       </c>
       <c r="K117" s="30" t="n">
-        <v>138.75</v>
+        <v>137.45</v>
       </c>
       <c r="L117" s="31" t="n">
-        <v>136.65</v>
+        <v>136.11</v>
       </c>
       <c r="M117" s="31" t="n">
-        <v>134.15</v>
+        <v>134.51</v>
       </c>
       <c r="N117" s="35" t="inlineStr">
         <is>
@@ -7900,16 +7900,16 @@
         </is>
       </c>
       <c r="O117" s="32" t="n">
-        <v>139.11</v>
+        <v>137.74</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>138.94</v>
+        <v>137.58</v>
       </c>
       <c r="Q117" s="33" t="n">
-        <v>138.9</v>
+        <v>137.9</v>
       </c>
       <c r="R117" s="36" t="n">
-        <v>-0.57</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="118">
@@ -7924,54 +7924,54 @@
         </is>
       </c>
       <c r="C118" s="25" t="n">
-        <v>11.41</v>
+        <v>10.63</v>
       </c>
       <c r="D118" s="25" t="n">
-        <v>10.97</v>
+        <v>10.47</v>
       </c>
       <c r="E118" s="26" t="n">
-        <v>10.6</v>
+        <v>10.33</v>
       </c>
       <c r="F118" s="27" t="n">
-        <v>10.65</v>
+        <v>10.34</v>
       </c>
       <c r="G118" s="27" t="n">
-        <v>10.89</v>
+        <v>10.44</v>
       </c>
       <c r="H118" s="28" t="n">
-        <v>10.45</v>
+        <v>10.28</v>
       </c>
       <c r="I118" s="29" t="n">
-        <v>10.21</v>
+        <v>10.18</v>
       </c>
       <c r="J118" s="29" t="n">
-        <v>10.01</v>
+        <v>10.12</v>
       </c>
       <c r="K118" s="30" t="n">
-        <v>10.36</v>
+        <v>10.25</v>
       </c>
       <c r="L118" s="31" t="n">
-        <v>9.99</v>
+        <v>10.11</v>
       </c>
       <c r="M118" s="31" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="N118" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>9.949999999999999</v>
+      </c>
+      <c r="N118" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>10.42</v>
+        <v>10.27</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>10.39</v>
+        <v>10.26</v>
       </c>
       <c r="Q118" s="33" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="R118" s="34" t="n">
-        <v>0.68</v>
+        <v>10.25</v>
+      </c>
+      <c r="R118" s="36" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="119">
@@ -7986,54 +7986,54 @@
         </is>
       </c>
       <c r="C119" s="25" t="n">
-        <v>18.1</v>
+        <v>18.04</v>
       </c>
       <c r="D119" s="25" t="n">
-        <v>17.76</v>
+        <v>17.59</v>
       </c>
       <c r="E119" s="26" t="n">
-        <v>17.48</v>
+        <v>17.21</v>
       </c>
       <c r="F119" s="27" t="n">
-        <v>17.46</v>
+        <v>17.22</v>
       </c>
       <c r="G119" s="27" t="n">
-        <v>17.67</v>
+        <v>17.49</v>
       </c>
       <c r="H119" s="28" t="n">
-        <v>17.33</v>
+        <v>17.04</v>
       </c>
       <c r="I119" s="29" t="n">
-        <v>17.12</v>
+        <v>16.77</v>
       </c>
       <c r="J119" s="29" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="K119" s="30" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="L119" s="31" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="M119" s="31" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="N119" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O119" s="32" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="P119" s="32" t="n">
         <v>16.99</v>
       </c>
-      <c r="K119" s="30" t="n">
-        <v>17.28</v>
-      </c>
-      <c r="L119" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="M119" s="31" t="n">
-        <v>16.66</v>
-      </c>
-      <c r="N119" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O119" s="32" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="P119" s="32" t="n">
-        <v>17.31</v>
-      </c>
       <c r="Q119" s="33" t="n">
-        <v>17.24</v>
+        <v>16.95</v>
       </c>
       <c r="R119" s="36" t="n">
-        <v>-0.35</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="120">
@@ -8051,34 +8051,34 @@
         <v>12.06</v>
       </c>
       <c r="D120" s="25" t="n">
-        <v>11.75</v>
+        <v>11.67</v>
       </c>
       <c r="E120" s="26" t="n">
-        <v>11.49</v>
+        <v>11.34</v>
       </c>
       <c r="F120" s="27" t="n">
-        <v>11.56</v>
+        <v>11.33</v>
       </c>
       <c r="G120" s="27" t="n">
-        <v>11.71</v>
+        <v>11.57</v>
       </c>
       <c r="H120" s="28" t="n">
-        <v>11.4</v>
+        <v>11.18</v>
       </c>
       <c r="I120" s="29" t="n">
-        <v>11.25</v>
+        <v>10.94</v>
       </c>
       <c r="J120" s="29" t="n">
-        <v>11.09</v>
+        <v>10.79</v>
       </c>
       <c r="K120" s="30" t="n">
-        <v>11.32</v>
+        <v>11.13</v>
       </c>
       <c r="L120" s="31" t="n">
-        <v>11.06</v>
+        <v>10.8</v>
       </c>
       <c r="M120" s="31" t="n">
-        <v>10.75</v>
+        <v>10.41</v>
       </c>
       <c r="N120" s="35" t="inlineStr">
         <is>
@@ -8086,16 +8086,16 @@
         </is>
       </c>
       <c r="O120" s="32" t="n">
-        <v>11.37</v>
+        <v>11.17</v>
       </c>
       <c r="P120" s="32" t="n">
-        <v>11.34</v>
+        <v>11.16</v>
       </c>
       <c r="Q120" s="33" t="n">
-        <v>11.4</v>
+        <v>11.08</v>
       </c>
       <c r="R120" s="36" t="n">
-        <v>-0.35</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="121">
@@ -8110,54 +8110,54 @@
         </is>
       </c>
       <c r="C121" s="25" t="n">
-        <v>13.04</v>
+        <v>12.47</v>
       </c>
       <c r="D121" s="25" t="n">
-        <v>12.7</v>
+        <v>12.36</v>
       </c>
       <c r="E121" s="26" t="n">
-        <v>12.42</v>
+        <v>12.27</v>
       </c>
       <c r="F121" s="27" t="n">
-        <v>12.41</v>
+        <v>12.32</v>
       </c>
       <c r="G121" s="27" t="n">
-        <v>12.62</v>
+        <v>12.36</v>
       </c>
       <c r="H121" s="28" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="I121" s="29" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="J121" s="29" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="K121" s="30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L121" s="31" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="M121" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="N121" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O121" s="32" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="P121" s="32" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="Q121" s="33" t="n">
         <v>12.28</v>
       </c>
-      <c r="I121" s="29" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="J121" s="29" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="K121" s="30" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="L121" s="31" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="M121" s="31" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="N121" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O121" s="32" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="P121" s="32" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="Q121" s="33" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="R121" s="36" t="n">
-        <v>-0.41</v>
+      <c r="R121" s="34" t="n">
+        <v>0.66</v>
       </c>
     </row>
     <row r="122">
@@ -8172,37 +8172,37 @@
         </is>
       </c>
       <c r="C122" s="25" t="n">
-        <v>9.300000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="D122" s="25" t="n">
-        <v>8.93</v>
+        <v>8.6</v>
       </c>
       <c r="E122" s="26" t="n">
-        <v>8.619999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F122" s="27" t="n">
-        <v>8.6</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G122" s="27" t="n">
-        <v>8.83</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H122" s="28" t="n">
-        <v>8.460000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I122" s="29" t="n">
-        <v>8.23</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="J122" s="29" t="n">
-        <v>8.09</v>
+        <v>8.02</v>
       </c>
       <c r="K122" s="30" t="n">
-        <v>8.41</v>
+        <v>8.24</v>
       </c>
       <c r="L122" s="31" t="n">
-        <v>8.1</v>
+        <v>8.02</v>
       </c>
       <c r="M122" s="31" t="n">
-        <v>7.73</v>
+        <v>7.76</v>
       </c>
       <c r="N122" s="35" t="inlineStr">
         <is>
@@ -8210,16 +8210,16 @@
         </is>
       </c>
       <c r="O122" s="32" t="n">
-        <v>8.449999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>8.44</v>
+        <v>8.26</v>
       </c>
       <c r="Q122" s="33" t="n">
-        <v>8.359999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="R122" s="36" t="n">
-        <v>-0.48</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="123">
@@ -8234,54 +8234,54 @@
         </is>
       </c>
       <c r="C123" s="25" t="n">
-        <v>10.69</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="D123" s="25" t="n">
-        <v>9.67</v>
+        <v>8.43</v>
       </c>
       <c r="E123" s="26" t="n">
-        <v>8.82</v>
+        <v>8.07</v>
       </c>
       <c r="F123" s="27" t="n">
-        <v>8.710000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G123" s="27" t="n">
-        <v>9.380000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H123" s="28" t="n">
-        <v>8.359999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="I123" s="29" t="n">
-        <v>7.69</v>
+        <v>7.7</v>
       </c>
       <c r="J123" s="29" t="n">
-        <v>7.34</v>
+        <v>7.5</v>
       </c>
       <c r="K123" s="30" t="n">
-        <v>8.24</v>
+        <v>7.82</v>
       </c>
       <c r="L123" s="31" t="n">
-        <v>7.39</v>
+        <v>7.46</v>
       </c>
       <c r="M123" s="31" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="N123" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>7.03</v>
+      </c>
+      <c r="N123" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O123" s="32" t="n">
-        <v>8.34</v>
+        <v>7.89</v>
       </c>
       <c r="P123" s="32" t="n">
-        <v>8.32</v>
+        <v>7.86</v>
       </c>
       <c r="Q123" s="33" t="n">
-        <v>8.029999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="R123" s="36" t="n">
-        <v>-2.31</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="124">
@@ -8296,37 +8296,37 @@
         </is>
       </c>
       <c r="C124" s="25" t="n">
-        <v>25.2</v>
+        <v>24.86</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>24.81</v>
+        <v>24.53</v>
       </c>
       <c r="E124" s="26" t="n">
-        <v>24.48</v>
+        <v>24.26</v>
       </c>
       <c r="F124" s="27" t="n">
-        <v>24.52</v>
+        <v>24.36</v>
       </c>
       <c r="G124" s="27" t="n">
-        <v>24.74</v>
+        <v>24.51</v>
       </c>
       <c r="H124" s="28" t="n">
-        <v>24.35</v>
+        <v>24.18</v>
       </c>
       <c r="I124" s="29" t="n">
-        <v>24.13</v>
+        <v>24.03</v>
       </c>
       <c r="J124" s="29" t="n">
-        <v>23.96</v>
+        <v>23.85</v>
       </c>
       <c r="K124" s="30" t="n">
-        <v>24.27</v>
+        <v>24.07</v>
       </c>
       <c r="L124" s="31" t="n">
-        <v>23.94</v>
+        <v>23.8</v>
       </c>
       <c r="M124" s="31" t="n">
-        <v>23.55</v>
+        <v>23.47</v>
       </c>
       <c r="N124" s="35" t="inlineStr">
         <is>
@@ -8334,16 +8334,16 @@
         </is>
       </c>
       <c r="O124" s="32" t="n">
-        <v>24.32</v>
+        <v>24.14</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="Q124" s="33" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R124" s="34" t="n">
-        <v>0.33</v>
+        <v>24.21</v>
+      </c>
+      <c r="R124" s="36" t="n">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="125">
@@ -8358,37 +8358,37 @@
         </is>
       </c>
       <c r="C125" s="25" t="n">
-        <v>174.52</v>
+        <v>167.11</v>
       </c>
       <c r="D125" s="25" t="n">
-        <v>170.12</v>
+        <v>165.31</v>
       </c>
       <c r="E125" s="26" t="n">
-        <v>166.43</v>
+        <v>163.8</v>
       </c>
       <c r="F125" s="27" t="n">
-        <v>165.93</v>
+        <v>164.33</v>
       </c>
       <c r="G125" s="27" t="n">
-        <v>168.87</v>
+        <v>165.17</v>
       </c>
       <c r="H125" s="28" t="n">
-        <v>164.47</v>
+        <v>163.37</v>
       </c>
       <c r="I125" s="29" t="n">
-        <v>161.53</v>
+        <v>162.53</v>
       </c>
       <c r="J125" s="29" t="n">
-        <v>160.07</v>
+        <v>161.57</v>
       </c>
       <c r="K125" s="30" t="n">
-        <v>163.97</v>
+        <v>162.8</v>
       </c>
       <c r="L125" s="31" t="n">
-        <v>160.28</v>
+        <v>161.29</v>
       </c>
       <c r="M125" s="31" t="n">
-        <v>155.88</v>
+        <v>159.49</v>
       </c>
       <c r="N125" s="35" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         </is>
       </c>
       <c r="O125" s="32" t="n">
-        <v>164.39</v>
+        <v>163.15</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>164.31</v>
+        <v>162.94</v>
       </c>
       <c r="Q125" s="33" t="n">
-        <v>163</v>
-      </c>
-      <c r="R125" s="36" t="n">
-        <v>-1.98</v>
+        <v>163.5</v>
+      </c>
+      <c r="R125" s="34" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="126">
@@ -8420,54 +8420,54 @@
         </is>
       </c>
       <c r="C126" s="25" t="n">
-        <v>57.72</v>
+        <v>56.42</v>
       </c>
       <c r="D126" s="25" t="n">
-        <v>55.42</v>
+        <v>54.77</v>
       </c>
       <c r="E126" s="26" t="n">
-        <v>53.49</v>
+        <v>53.39</v>
       </c>
       <c r="F126" s="27" t="n">
-        <v>54.13</v>
+        <v>53.23</v>
       </c>
       <c r="G126" s="27" t="n">
-        <v>55.22</v>
+        <v>54.32</v>
       </c>
       <c r="H126" s="28" t="n">
-        <v>52.92</v>
+        <v>52.67</v>
       </c>
       <c r="I126" s="29" t="n">
-        <v>51.83</v>
+        <v>51.58</v>
       </c>
       <c r="J126" s="29" t="n">
-        <v>50.62</v>
+        <v>51.02</v>
       </c>
       <c r="K126" s="30" t="n">
-        <v>52.21</v>
+        <v>52.46</v>
       </c>
       <c r="L126" s="31" t="n">
-        <v>50.28</v>
+        <v>51.08</v>
       </c>
       <c r="M126" s="31" t="n">
-        <v>47.98</v>
-      </c>
-      <c r="N126" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>49.43</v>
+      </c>
+      <c r="N126" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O126" s="32" t="n">
-        <v>52.65</v>
+        <v>52.63</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>52.39</v>
+        <v>52.59</v>
       </c>
       <c r="Q126" s="33" t="n">
-        <v>53.05</v>
-      </c>
-      <c r="R126" s="34" t="n">
-        <v>2.22</v>
+        <v>52.15</v>
+      </c>
+      <c r="R126" s="36" t="n">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="127">
@@ -8482,37 +8482,37 @@
         </is>
       </c>
       <c r="C127" s="25" t="n">
-        <v>16.68</v>
+        <v>16.32</v>
       </c>
       <c r="D127" s="25" t="n">
-        <v>16</v>
+        <v>15.71</v>
       </c>
       <c r="E127" s="26" t="n">
-        <v>15.43</v>
+        <v>15.2</v>
       </c>
       <c r="F127" s="27" t="n">
-        <v>15.45</v>
+        <v>15.13</v>
       </c>
       <c r="G127" s="27" t="n">
-        <v>15.86</v>
+        <v>15.53</v>
       </c>
       <c r="H127" s="28" t="n">
-        <v>15.18</v>
+        <v>14.92</v>
       </c>
       <c r="I127" s="29" t="n">
-        <v>14.77</v>
+        <v>14.52</v>
       </c>
       <c r="J127" s="29" t="n">
-        <v>14.5</v>
+        <v>14.31</v>
       </c>
       <c r="K127" s="30" t="n">
-        <v>15.05</v>
+        <v>14.85</v>
       </c>
       <c r="L127" s="31" t="n">
-        <v>14.48</v>
+        <v>14.34</v>
       </c>
       <c r="M127" s="31" t="n">
-        <v>13.8</v>
+        <v>13.73</v>
       </c>
       <c r="N127" s="35" t="inlineStr">
         <is>
@@ -8520,16 +8520,16 @@
         </is>
       </c>
       <c r="O127" s="32" t="n">
-        <v>15.14</v>
+        <v>14.91</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="Q127" s="33" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="R127" s="34" t="n">
-        <v>0.67</v>
+        <v>14.72</v>
+      </c>
+      <c r="R127" s="36" t="n">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="128">
@@ -8544,37 +8544,37 @@
         </is>
       </c>
       <c r="C128" s="25" t="n">
-        <v>16.49</v>
+        <v>16.07</v>
       </c>
       <c r="D128" s="25" t="n">
-        <v>15.81</v>
+        <v>15.53</v>
       </c>
       <c r="E128" s="26" t="n">
-        <v>15.24</v>
+        <v>15.08</v>
       </c>
       <c r="F128" s="27" t="n">
-        <v>15.47</v>
+        <v>15.05</v>
       </c>
       <c r="G128" s="27" t="n">
-        <v>15.77</v>
+        <v>15.39</v>
       </c>
       <c r="H128" s="28" t="n">
-        <v>15.09</v>
+        <v>14.85</v>
       </c>
       <c r="I128" s="29" t="n">
-        <v>14.79</v>
+        <v>14.51</v>
       </c>
       <c r="J128" s="29" t="n">
-        <v>14.41</v>
+        <v>14.31</v>
       </c>
       <c r="K128" s="30" t="n">
-        <v>14.86</v>
+        <v>14.78</v>
       </c>
       <c r="L128" s="31" t="n">
-        <v>14.29</v>
+        <v>14.33</v>
       </c>
       <c r="M128" s="31" t="n">
-        <v>13.61</v>
+        <v>13.79</v>
       </c>
       <c r="N128" s="35" t="inlineStr">
         <is>
@@ -8582,16 +8582,16 @@
         </is>
       </c>
       <c r="O128" s="32" t="n">
-        <v>15</v>
+        <v>14.84</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>14.91</v>
+        <v>14.82</v>
       </c>
       <c r="Q128" s="33" t="n">
-        <v>15.17</v>
+        <v>14.7</v>
       </c>
       <c r="R128" s="36" t="n">
-        <v>-0.2</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="129">
@@ -8606,37 +8606,37 @@
         </is>
       </c>
       <c r="C129" s="25" t="n">
-        <v>7.71</v>
+        <v>7.6</v>
       </c>
       <c r="D129" s="25" t="n">
-        <v>7.55</v>
+        <v>7.47</v>
       </c>
       <c r="E129" s="26" t="n">
-        <v>7.41</v>
+        <v>7.36</v>
       </c>
       <c r="F129" s="27" t="n">
         <v>7.43</v>
       </c>
       <c r="G129" s="27" t="n">
-        <v>7.52</v>
+        <v>7.47</v>
       </c>
       <c r="H129" s="28" t="n">
-        <v>7.36</v>
+        <v>7.34</v>
       </c>
       <c r="I129" s="29" t="n">
-        <v>7.27</v>
+        <v>7.3</v>
       </c>
       <c r="J129" s="29" t="n">
-        <v>7.2</v>
+        <v>7.21</v>
       </c>
       <c r="K129" s="30" t="n">
-        <v>7.33</v>
+        <v>7.29</v>
       </c>
       <c r="L129" s="31" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="M129" s="31" t="n">
-        <v>7.03</v>
+        <v>7.05</v>
       </c>
       <c r="N129" s="20" t="inlineStr">
         <is>
@@ -8644,16 +8644,16 @@
         </is>
       </c>
       <c r="O129" s="32" t="n">
-        <v>7.35</v>
+        <v>7.32</v>
       </c>
       <c r="P129" s="32" t="n">
-        <v>7.34</v>
+        <v>7.3</v>
       </c>
       <c r="Q129" s="33" t="n">
-        <v>7.34</v>
+        <v>7.38</v>
       </c>
       <c r="R129" s="34" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="130">
@@ -8668,37 +8668,37 @@
         </is>
       </c>
       <c r="C130" s="25" t="n">
-        <v>10.33</v>
+        <v>10.1</v>
       </c>
       <c r="D130" s="25" t="n">
-        <v>10.04</v>
+        <v>9.91</v>
       </c>
       <c r="E130" s="26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="F130" s="27" t="n">
-        <v>9.85</v>
+        <v>9.73</v>
       </c>
       <c r="G130" s="27" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H130" s="28" t="n">
-        <v>9.710000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="I130" s="29" t="n">
-        <v>9.56</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="J130" s="29" t="n">
-        <v>9.42</v>
+        <v>9.48</v>
       </c>
       <c r="K130" s="30" t="n">
-        <v>9.630000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L130" s="31" t="n">
-        <v>9.390000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="M130" s="31" t="n">
-        <v>9.1</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="N130" s="35" t="inlineStr">
         <is>
@@ -8706,16 +8706,16 @@
         </is>
       </c>
       <c r="O130" s="32" t="n">
-        <v>9.68</v>
+        <v>9.66</v>
       </c>
       <c r="P130" s="32" t="n">
         <v>9.66</v>
       </c>
       <c r="Q130" s="33" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="R130" s="34" t="n">
-        <v>0.21</v>
+        <v>9.609999999999999</v>
+      </c>
+      <c r="R130" s="36" t="n">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="131">
@@ -8730,37 +8730,37 @@
         </is>
       </c>
       <c r="C131" s="25" t="n">
-        <v>145.88</v>
+        <v>138.85</v>
       </c>
       <c r="D131" s="25" t="n">
-        <v>141.38</v>
+        <v>137.15</v>
       </c>
       <c r="E131" s="26" t="n">
-        <v>137.61</v>
+        <v>135.73</v>
       </c>
       <c r="F131" s="27" t="n">
-        <v>137.83</v>
+        <v>136</v>
       </c>
       <c r="G131" s="27" t="n">
-        <v>140.47</v>
+        <v>136.9</v>
       </c>
       <c r="H131" s="28" t="n">
-        <v>135.97</v>
+        <v>135.2</v>
       </c>
       <c r="I131" s="29" t="n">
-        <v>133.33</v>
+        <v>134.3</v>
       </c>
       <c r="J131" s="29" t="n">
-        <v>131.47</v>
+        <v>133.5</v>
       </c>
       <c r="K131" s="30" t="n">
-        <v>135.09</v>
+        <v>134.77</v>
       </c>
       <c r="L131" s="31" t="n">
-        <v>131.32</v>
+        <v>133.35</v>
       </c>
       <c r="M131" s="31" t="n">
-        <v>126.82</v>
+        <v>131.65</v>
       </c>
       <c r="N131" s="35" t="inlineStr">
         <is>
@@ -8768,16 +8768,16 @@
         </is>
       </c>
       <c r="O131" s="32" t="n">
-        <v>135.7</v>
+        <v>135.05</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>135.44</v>
+        <v>134.91</v>
       </c>
       <c r="Q131" s="33" t="n">
-        <v>135.2</v>
+        <v>135.1</v>
       </c>
       <c r="R131" s="36" t="n">
-        <v>-2.45</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -289,10 +289,10 @@
     <xf numFmtId="2" fontId="4" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="5" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -686,7 +686,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-08-20</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>11045.83</v>
+        <v>11284.01</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>10993.58</v>
+        <v>11160.72</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>10949.8</v>
+        <v>11057.41</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>10974.15</v>
+        <v>11121.73</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>10993.85</v>
+        <v>11164.77</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>10941.6</v>
+        <v>11041.48</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>10921.9</v>
+        <v>10998.44</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>10889.35</v>
+        <v>10918.19</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>10920.54</v>
+        <v>10988.36</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>10876.75</v>
+        <v>10885.05</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>10824.5</v>
+        <v>10761.76</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>10933.1</v>
+        <v>11019.73</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>10924.61</v>
+        <v>10997.98</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>10954.46</v>
+        <v>11078.68</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>2.18</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="4">
@@ -856,54 +856,54 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>20.78</v>
+        <v>20.93</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.63</v>
+        <v>20.76</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>20.51</v>
+        <v>20.61</v>
       </c>
       <c r="F4" s="27" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="I4" s="29" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="J4" s="29" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="K4" s="30" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="L4" s="31" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="M4" s="31" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O4" s="32" t="n">
         <v>20.56</v>
       </c>
-      <c r="G4" s="27" t="n">
+      <c r="P4" s="32" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="Q4" s="33" t="n">
         <v>20.62</v>
       </c>
-      <c r="H4" s="28" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="I4" s="29" t="n">
-        <v>20.41</v>
-      </c>
-      <c r="J4" s="29" t="n">
-        <v>20.32</v>
-      </c>
-      <c r="K4" s="30" t="n">
-        <v>20.42</v>
-      </c>
-      <c r="L4" s="31" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="M4" s="31" t="n">
-        <v>20.15</v>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O4" s="32" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="P4" s="32" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="Q4" s="33" t="n">
-        <v>20.49</v>
-      </c>
       <c r="R4" s="34" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="5">
@@ -918,54 +918,54 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>12.42</v>
+        <v>12.3</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>12.24</v>
+        <v>12.21</v>
       </c>
       <c r="E5" s="26" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="L5" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="M5" s="31" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O5" s="32" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="P5" s="32" t="n">
         <v>12.09</v>
       </c>
-      <c r="F5" s="27" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="J5" s="29" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="K5" s="30" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="L5" s="31" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="M5" s="31" t="n">
-        <v>11.66</v>
-      </c>
-      <c r="N5" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="P5" s="32" t="n">
-        <v>12</v>
-      </c>
       <c r="Q5" s="33" t="n">
-        <v>12.13</v>
-      </c>
-      <c r="R5" s="34" t="n">
-        <v>1.08</v>
+        <v>12.1</v>
+      </c>
+      <c r="R5" s="35" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="6">
@@ -980,54 +980,54 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>14.39</v>
+        <v>14.32</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14.26</v>
+        <v>14.23</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>14.15</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>14.2</v>
+        <v>14.15</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>14.25</v>
+        <v>14.21</v>
       </c>
       <c r="H6" s="28" t="n">
         <v>14.12</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>14.07</v>
+        <v>14.06</v>
       </c>
       <c r="J6" s="29" t="n">
-        <v>13.99</v>
+        <v>14.03</v>
       </c>
       <c r="K6" s="30" t="n">
-        <v>14.08</v>
+        <v>14.1</v>
       </c>
       <c r="L6" s="31" t="n">
-        <v>13.97</v>
+        <v>14.02</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>13.84</v>
-      </c>
-      <c r="N6" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>13.93</v>
+      </c>
+      <c r="N6" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O6" s="32" t="n">
         <v>14.11</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>14.09</v>
+        <v>14.11</v>
       </c>
       <c r="Q6" s="33" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="R6" s="34" t="n">
-        <v>0.43</v>
+        <v>14.1</v>
+      </c>
+      <c r="R6" s="35" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="7">
@@ -1042,54 +1042,54 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>22.15</v>
+        <v>21.65</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>21.62</v>
+        <v>21.24</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>21.17</v>
+        <v>20.9</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>21.13</v>
+        <v>21.07</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>21.48</v>
+        <v>21.23</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>20.95</v>
+        <v>20.82</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>20.6</v>
+        <v>20.66</v>
       </c>
       <c r="J7" s="29" t="n">
-        <v>20.42</v>
+        <v>20.41</v>
       </c>
       <c r="K7" s="30" t="n">
-        <v>20.88</v>
+        <v>20.67</v>
       </c>
       <c r="L7" s="31" t="n">
-        <v>20.43</v>
+        <v>20.33</v>
       </c>
       <c r="M7" s="31" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N7" s="35" t="inlineStr">
+        <v>19.92</v>
+      </c>
+      <c r="N7" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>20.93</v>
+        <v>20.76</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>20.92</v>
+        <v>20.7</v>
       </c>
       <c r="Q7" s="33" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="R7" s="36" t="n">
-        <v>-1.93</v>
+        <v>20.9</v>
+      </c>
+      <c r="R7" s="34" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="8">
@@ -1104,54 +1104,54 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>34.33</v>
+        <v>34.19</v>
       </c>
       <c r="D8" s="25" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="G8" s="27" t="n">
         <v>34.05</v>
       </c>
-      <c r="E8" s="26" t="n">
-        <v>33.82</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>33.97</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>34.07</v>
-      </c>
       <c r="H8" s="28" t="n">
-        <v>33.79</v>
+        <v>33.93</v>
       </c>
       <c r="I8" s="29" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="L8" s="31" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="M8" s="31" t="n">
         <v>33.69</v>
       </c>
-      <c r="J8" s="29" t="n">
-        <v>33.51</v>
-      </c>
-      <c r="K8" s="30" t="n">
-        <v>33.66</v>
-      </c>
-      <c r="L8" s="31" t="n">
-        <v>33.43</v>
-      </c>
-      <c r="M8" s="31" t="n">
-        <v>33.15</v>
-      </c>
       <c r="N8" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O8" s="32" t="n">
-        <v>33.74</v>
+        <v>33.92</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>33.68</v>
+        <v>33.92</v>
       </c>
       <c r="Q8" s="33" t="n">
-        <v>33.88</v>
+        <v>33.92</v>
       </c>
       <c r="R8" s="34" t="n">
-        <v>0.59</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="9">
@@ -1166,54 +1166,54 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>22.79</v>
+        <v>22.75</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>22.56</v>
+        <v>22.55</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>22.37</v>
+        <v>22.39</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>22.34</v>
+        <v>22.38</v>
       </c>
       <c r="G9" s="27" t="n">
         <v>22.5</v>
       </c>
       <c r="H9" s="28" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="J9" s="29" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="K9" s="30" t="n">
         <v>22.27</v>
       </c>
-      <c r="I9" s="29" t="n">
+      <c r="L9" s="31" t="n">
         <v>22.11</v>
       </c>
-      <c r="J9" s="29" t="n">
-        <v>22.04</v>
-      </c>
-      <c r="K9" s="30" t="n">
-        <v>22.24</v>
-      </c>
-      <c r="L9" s="31" t="n">
-        <v>22.05</v>
-      </c>
       <c r="M9" s="31" t="n">
-        <v>21.82</v>
-      </c>
-      <c r="N9" s="35" t="inlineStr">
+        <v>21.91</v>
+      </c>
+      <c r="N9" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O9" s="32" t="n">
-        <v>22.26</v>
+        <v>22.3</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>22.26</v>
+        <v>22.29</v>
       </c>
       <c r="Q9" s="33" t="n">
-        <v>22.19</v>
-      </c>
-      <c r="R9" s="36" t="n">
-        <v>-0.72</v>
+        <v>22.25</v>
+      </c>
+      <c r="R9" s="34" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="10">
@@ -1228,37 +1228,37 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>125.42</v>
+        <v>128.37</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>123.12</v>
+        <v>125.67</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>121.19</v>
+        <v>123.41</v>
       </c>
       <c r="F10" s="27" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="I10" s="29" t="n">
         <v>122.2</v>
       </c>
-      <c r="G10" s="27" t="n">
-        <v>123.1</v>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>120.8</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>119.9</v>
-      </c>
       <c r="J10" s="29" t="n">
-        <v>118.5</v>
+        <v>120.4</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>119.91</v>
+        <v>121.89</v>
       </c>
       <c r="L10" s="31" t="n">
-        <v>117.98</v>
+        <v>119.63</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>115.68</v>
+        <v>116.93</v>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>120.44</v>
+        <v>122.6</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>120.09</v>
+        <v>122.1</v>
       </c>
       <c r="Q10" s="33" t="n">
-        <v>121.3</v>
+        <v>124</v>
       </c>
       <c r="R10" s="34" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="11">
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>66.02</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>65.42</v>
+        <v>66.86</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>64.92</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>65.08</v>
+        <v>66.53</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>65.37</v>
+        <v>66.92</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>64.77</v>
+        <v>65.77</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>64.48</v>
+        <v>65.38</v>
       </c>
       <c r="J11" s="29" t="n">
-        <v>64.17</v>
+        <v>64.62</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>64.58</v>
+        <v>65.25</v>
       </c>
       <c r="L11" s="31" t="n">
-        <v>64.08</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="M11" s="31" t="n">
-        <v>63.48</v>
+        <v>63.14</v>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>64.7</v>
+        <v>65.55</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>64.63</v>
+        <v>65.34</v>
       </c>
       <c r="Q11" s="33" t="n">
-        <v>64.8</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="R11" s="34" t="n">
-        <v>0.47</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="12">
@@ -1352,37 +1352,37 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>25.69</v>
+        <v>25.92</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>25.45</v>
+        <v>25.66</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>25.25</v>
+        <v>25.44</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>25.35</v>
+        <v>25.55</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>25.45</v>
+        <v>25.65</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>25.21</v>
+        <v>25.39</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>25.11</v>
+        <v>25.29</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>24.97</v>
+        <v>25.13</v>
       </c>
       <c r="K12" s="30" t="n">
-        <v>25.11</v>
+        <v>25.3</v>
       </c>
       <c r="L12" s="31" t="n">
-        <v>24.91</v>
+        <v>25.08</v>
       </c>
       <c r="M12" s="31" t="n">
-        <v>24.67</v>
+        <v>24.82</v>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
@@ -1390,16 +1390,16 @@
         </is>
       </c>
       <c r="O12" s="32" t="n">
-        <v>25.17</v>
+        <v>25.36</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>25.13</v>
+        <v>25.32</v>
       </c>
       <c r="Q12" s="33" t="n">
-        <v>25.26</v>
+        <v>25.44</v>
       </c>
       <c r="R12" s="34" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="13">
@@ -1414,37 +1414,37 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>25.6</v>
+        <v>25.91</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>25.23</v>
+        <v>25.51</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>24.92</v>
+        <v>25.17</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>25.03</v>
+        <v>25.37</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>25.2</v>
+        <v>25.51</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>24.83</v>
+        <v>25.11</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>24.66</v>
+        <v>24.97</v>
       </c>
       <c r="J13" s="29" t="n">
-        <v>24.46</v>
+        <v>24.71</v>
       </c>
       <c r="K13" s="30" t="n">
-        <v>24.71</v>
+        <v>24.95</v>
       </c>
       <c r="L13" s="31" t="n">
-        <v>24.4</v>
+        <v>24.61</v>
       </c>
       <c r="M13" s="31" t="n">
-        <v>24.03</v>
+        <v>24.21</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>24.79</v>
+        <v>25.05</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>24.74</v>
+        <v>24.98</v>
       </c>
       <c r="Q13" s="33" t="n">
-        <v>24.86</v>
+        <v>25.22</v>
       </c>
       <c r="R13" s="34" t="n">
-        <v>0.28</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="14">
@@ -1476,54 +1476,54 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>42.3</v>
+        <v>43.82</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>41.98</v>
+        <v>42.94</v>
       </c>
       <c r="E14" s="26" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="J14" s="29" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="K14" s="30" t="n">
         <v>41.71</v>
       </c>
-      <c r="F14" s="27" t="n">
-        <v>41.81</v>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>41.95</v>
-      </c>
-      <c r="H14" s="28" t="n">
-        <v>41.63</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>41.49</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>41.31</v>
-      </c>
-      <c r="K14" s="30" t="n">
-        <v>41.53</v>
-      </c>
       <c r="L14" s="31" t="n">
-        <v>41.26</v>
+        <v>40.98</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>40.94</v>
-      </c>
-      <c r="N14" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>40.1</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O14" s="32" t="n">
-        <v>41.59</v>
+        <v>41.94</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>41.56</v>
+        <v>41.78</v>
       </c>
       <c r="Q14" s="33" t="n">
-        <v>41.66</v>
-      </c>
-      <c r="R14" s="36" t="n">
-        <v>-0.05</v>
+        <v>42.4</v>
+      </c>
+      <c r="R14" s="34" t="n">
+        <v>1.78</v>
       </c>
     </row>
     <row r="15">
@@ -1538,37 +1538,37 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>8.99</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>8.84</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F15" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="H15" s="28" t="n">
         <v>8.93</v>
       </c>
-      <c r="G15" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="H15" s="28" t="n">
+      <c r="I15" s="29" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="J15" s="29" t="n">
         <v>8.82</v>
       </c>
-      <c r="I15" s="29" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>8.640000000000001</v>
-      </c>
       <c r="K15" s="30" t="n">
-        <v>8.74</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L15" s="31" t="n">
-        <v>8.59</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M15" s="31" t="n">
-        <v>8.41</v>
+        <v>8.69</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
@@ -1576,16 +1576,16 @@
         </is>
       </c>
       <c r="O15" s="32" t="n">
-        <v>8.789999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="P15" s="32" t="n">
-        <v>8.75</v>
+        <v>8.9</v>
       </c>
       <c r="Q15" s="33" t="n">
-        <v>8.869999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R15" s="34" t="n">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16">
@@ -1600,54 +1600,54 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>14.65</v>
+        <v>15.85</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.34</v>
+        <v>15.18</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>14.08</v>
+        <v>14.62</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>14.15</v>
+        <v>14.69</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>14.31</v>
+        <v>15.07</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>13.84</v>
+        <v>14.02</v>
       </c>
       <c r="J16" s="29" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="K16" s="30" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="L16" s="31" t="n">
         <v>13.69</v>
       </c>
-      <c r="K16" s="30" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="L16" s="31" t="n">
-        <v>13.65</v>
-      </c>
       <c r="M16" s="31" t="n">
-        <v>13.34</v>
-      </c>
-      <c r="N16" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>13.02</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O16" s="32" t="n">
-        <v>13.96</v>
+        <v>14.35</v>
       </c>
       <c r="P16" s="32" t="n">
-        <v>13.93</v>
+        <v>14.3</v>
       </c>
       <c r="Q16" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="R16" s="36" t="n">
-        <v>-0.28</v>
+        <v>14.32</v>
+      </c>
+      <c r="R16" s="34" t="n">
+        <v>2.29</v>
       </c>
     </row>
     <row r="17">
@@ -1662,54 +1662,54 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>5.11</v>
+        <v>5.03</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>4.87</v>
+        <v>4.86</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>4.95</v>
+        <v>4.91</v>
       </c>
       <c r="H17" s="28" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="L17" s="31" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="M17" s="31" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O17" s="32" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="P17" s="32" t="n">
         <v>4.8</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="K17" s="30" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L17" s="31" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="M17" s="31" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O17" s="32" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="P17" s="32" t="n">
-        <v>4.76</v>
       </c>
       <c r="Q17" s="33" t="n">
         <v>4.8</v>
       </c>
       <c r="R17" s="34" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1724,37 +1724,37 @@
         </is>
       </c>
       <c r="C18" s="25" t="n">
-        <v>19.2</v>
+        <v>20.19</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>18.78</v>
+        <v>19.58</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>18.43</v>
+        <v>19.07</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>18.64</v>
+        <v>19.26</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>18.79</v>
+        <v>19.53</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>18.37</v>
+        <v>18.92</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>18.22</v>
+        <v>18.65</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>17.95</v>
+        <v>18.31</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>18.19</v>
+        <v>18.72</v>
       </c>
       <c r="L18" s="31" t="n">
-        <v>17.84</v>
+        <v>18.21</v>
       </c>
       <c r="M18" s="31" t="n">
-        <v>17.42</v>
+        <v>17.6</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
@@ -1762,16 +1762,16 @@
         </is>
       </c>
       <c r="O18" s="32" t="n">
-        <v>18.3</v>
+        <v>18.85</v>
       </c>
       <c r="P18" s="32" t="n">
-        <v>18.23</v>
+        <v>18.77</v>
       </c>
       <c r="Q18" s="33" t="n">
-        <v>18.49</v>
+        <v>18.98</v>
       </c>
       <c r="R18" s="34" t="n">
-        <v>1.76</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="19">
@@ -1786,54 +1786,54 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>25.61</v>
+        <v>26.26</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>25.33</v>
+        <v>25.74</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>25.1</v>
+        <v>25.31</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>25.23</v>
+        <v>25.31</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>25.33</v>
+        <v>25.63</v>
       </c>
       <c r="H19" s="28" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="J19" s="29" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="L19" s="31" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="M19" s="31" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="N19" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O19" s="32" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="P19" s="32" t="n">
         <v>25.05</v>
       </c>
-      <c r="I19" s="29" t="n">
-        <v>24.95</v>
-      </c>
-      <c r="J19" s="29" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="K19" s="30" t="n">
-        <v>24.94</v>
-      </c>
-      <c r="L19" s="31" t="n">
-        <v>24.71</v>
-      </c>
-      <c r="M19" s="31" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="N19" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O19" s="32" t="n">
-        <v>25.01</v>
-      </c>
-      <c r="P19" s="32" t="n">
-        <v>24.96</v>
-      </c>
       <c r="Q19" s="33" t="n">
-        <v>25.12</v>
-      </c>
-      <c r="R19" s="34" t="n">
-        <v>0.5600000000000001</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="35" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="20">
@@ -1848,37 +1848,37 @@
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>73.34999999999999</v>
+        <v>73.86</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>70.34999999999999</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>67.84</v>
+        <v>69.08</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>68.37</v>
+        <v>70.42</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>69.93000000000001</v>
+        <v>71.33</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>66.93000000000001</v>
+        <v>68.73</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>65.37</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>63.93</v>
+        <v>66.13</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>66.16</v>
+        <v>67.62</v>
       </c>
       <c r="L20" s="31" t="n">
-        <v>63.65</v>
+        <v>65.44</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>60.65</v>
+        <v>62.84</v>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="O20" s="32" t="n">
-        <v>66.66</v>
+        <v>68.28</v>
       </c>
       <c r="P20" s="32" t="n">
-        <v>66.39</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="Q20" s="33" t="n">
-        <v>66.8</v>
+        <v>69.5</v>
       </c>
       <c r="R20" s="34" t="n">
-        <v>1.98</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="21">
@@ -1910,37 +1910,37 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>13.26</v>
+        <v>13.06</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>12.61</v>
+        <v>12.67</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>12.07</v>
+        <v>12.34</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>12.32</v>
+        <v>12.39</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>12.59</v>
+        <v>12.6</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>11.94</v>
+        <v>12.21</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="J21" s="29" t="n">
-        <v>11.29</v>
+        <v>11.82</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>11.7</v>
+        <v>12.13</v>
       </c>
       <c r="L21" s="31" t="n">
-        <v>11.16</v>
+        <v>11.8</v>
       </c>
       <c r="M21" s="31" t="n">
-        <v>10.51</v>
+        <v>11.41</v>
       </c>
       <c r="N21" s="20" t="inlineStr">
         <is>
@@ -1948,16 +1948,16 @@
         </is>
       </c>
       <c r="O21" s="32" t="n">
-        <v>11.85</v>
+        <v>12.18</v>
       </c>
       <c r="P21" s="32" t="n">
-        <v>11.75</v>
+        <v>12.16</v>
       </c>
       <c r="Q21" s="33" t="n">
-        <v>12.05</v>
+        <v>12.17</v>
       </c>
       <c r="R21" s="34" t="n">
-        <v>5.52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1972,37 +1972,37 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>18.93</v>
+        <v>18.63</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>18.62</v>
+        <v>18.55</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>18.36</v>
+        <v>18.48</v>
       </c>
       <c r="F22" s="27" t="n">
         <v>18.47</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>18.61</v>
+        <v>18.53</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.3</v>
+        <v>18.45</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>18.16</v>
+        <v>18.39</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>17.99</v>
+        <v>18.37</v>
       </c>
       <c r="K22" s="30" t="n">
-        <v>18.19</v>
+        <v>18.44</v>
       </c>
       <c r="L22" s="31" t="n">
-        <v>17.93</v>
+        <v>18.37</v>
       </c>
       <c r="M22" s="31" t="n">
-        <v>17.62</v>
+        <v>18.29</v>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
@@ -2010,16 +2010,16 @@
         </is>
       </c>
       <c r="O22" s="32" t="n">
-        <v>18.25</v>
+        <v>18.45</v>
       </c>
       <c r="P22" s="32" t="n">
-        <v>18.21</v>
+        <v>18.44</v>
       </c>
       <c r="Q22" s="33" t="n">
-        <v>18.34</v>
+        <v>18.42</v>
       </c>
       <c r="R22" s="34" t="n">
-        <v>1.55</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="23">
@@ -2034,37 +2034,37 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>36.95</v>
+        <v>37.51</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>35.87</v>
+        <v>36.49</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>34.96</v>
+        <v>35.64</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>35.27</v>
+        <v>36.2</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>35.77</v>
+        <v>36.54</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>34.69</v>
+        <v>35.52</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>34.19</v>
+        <v>35.18</v>
       </c>
       <c r="J23" s="29" t="n">
-        <v>33.61</v>
+        <v>34.5</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>34.36</v>
+        <v>35.06</v>
       </c>
       <c r="L23" s="31" t="n">
-        <v>33.45</v>
+        <v>34.21</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>32.37</v>
+        <v>33.19</v>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="O23" s="32" t="n">
-        <v>34.57</v>
+        <v>35.33</v>
       </c>
       <c r="P23" s="32" t="n">
-        <v>34.44</v>
+        <v>35.14</v>
       </c>
       <c r="Q23" s="33" t="n">
-        <v>34.76</v>
+        <v>35.86</v>
       </c>
       <c r="R23" s="34" t="n">
-        <v>1.58</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="24">
@@ -2096,54 +2096,54 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>15.62</v>
+        <v>15.56</v>
       </c>
       <c r="D24" s="25" t="n">
         <v>15.36</v>
       </c>
       <c r="E24" s="26" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="H24" s="28" t="n">
         <v>15.14</v>
       </c>
-      <c r="F24" s="27" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="G24" s="27" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="H24" s="28" t="n">
-        <v>15.07</v>
-      </c>
       <c r="I24" s="29" t="n">
-        <v>14.93</v>
+        <v>15.03</v>
       </c>
       <c r="J24" s="29" t="n">
-        <v>14.81</v>
+        <v>14.94</v>
       </c>
       <c r="K24" s="30" t="n">
-        <v>15</v>
+        <v>15.08</v>
       </c>
       <c r="L24" s="31" t="n">
-        <v>14.78</v>
+        <v>14.92</v>
       </c>
       <c r="M24" s="31" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="N24" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>14.72</v>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O24" s="32" t="n">
-        <v>15.04</v>
+        <v>15.12</v>
       </c>
       <c r="P24" s="32" t="n">
-        <v>15.02</v>
+        <v>15.1</v>
       </c>
       <c r="Q24" s="33" t="n">
-        <v>15.06</v>
+        <v>15.13</v>
       </c>
       <c r="R24" s="34" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="25">
@@ -2158,37 +2158,37 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>38.67</v>
+        <v>40.19</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>38.17</v>
+        <v>39.21</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>37.75</v>
+        <v>38.38</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>37.85</v>
+        <v>38.87</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>38.11</v>
+        <v>39.23</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>37.61</v>
+        <v>38.25</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>37.35</v>
+        <v>37.89</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>37.11</v>
+        <v>37.27</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>37.47</v>
+        <v>37.84</v>
       </c>
       <c r="L25" s="31" t="n">
-        <v>37.05</v>
+        <v>37.01</v>
       </c>
       <c r="M25" s="31" t="n">
-        <v>36.55</v>
+        <v>36.03</v>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -2196,16 +2196,16 @@
         </is>
       </c>
       <c r="O25" s="32" t="n">
-        <v>37.56</v>
+        <v>38.08</v>
       </c>
       <c r="P25" s="32" t="n">
-        <v>37.51</v>
+        <v>37.91</v>
       </c>
       <c r="Q25" s="33" t="n">
-        <v>37.6</v>
+        <v>38.52</v>
       </c>
       <c r="R25" s="34" t="n">
-        <v>0.05</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="26">
@@ -2220,54 +2220,54 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>49.12</v>
+        <v>49.62</v>
       </c>
       <c r="D26" s="25" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="G26" s="27" t="n">
         <v>48.4</v>
       </c>
-      <c r="E26" s="26" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="F26" s="27" t="n">
-        <v>47.76</v>
-      </c>
-      <c r="G26" s="27" t="n">
-        <v>48.22</v>
-      </c>
       <c r="H26" s="28" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>47.04</v>
+        <v>46.8</v>
       </c>
       <c r="J26" s="29" t="n">
-        <v>46.78</v>
+        <v>46.4</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>47.4</v>
+        <v>47.22</v>
       </c>
       <c r="L26" s="31" t="n">
-        <v>46.8</v>
+        <v>46.38</v>
       </c>
       <c r="M26" s="31" t="n">
-        <v>46.08</v>
-      </c>
-      <c r="N26" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>45.38</v>
+      </c>
+      <c r="N26" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O26" s="32" t="n">
-        <v>47.48</v>
+        <v>47.35</v>
       </c>
       <c r="P26" s="32" t="n">
-        <v>47.45</v>
+        <v>47.3</v>
       </c>
       <c r="Q26" s="33" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="R26" s="36" t="n">
-        <v>-0.63</v>
+        <v>47.2</v>
+      </c>
+      <c r="R26" s="35" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="27">
@@ -2282,54 +2282,54 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>195.29</v>
+        <v>194.03</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>192.39</v>
+        <v>191.23</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>189.96</v>
+        <v>188.88</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>189.77</v>
+        <v>189.37</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>191.63</v>
+        <v>190.83</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>188.73</v>
+        <v>188.03</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>186.87</v>
+        <v>186.57</v>
       </c>
       <c r="J27" s="29" t="n">
-        <v>185.83</v>
+        <v>185.23</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>188.34</v>
+        <v>187.32</v>
       </c>
       <c r="L27" s="31" t="n">
-        <v>185.91</v>
+        <v>184.97</v>
       </c>
       <c r="M27" s="31" t="n">
-        <v>183.01</v>
-      </c>
-      <c r="N27" s="35" t="inlineStr">
+        <v>182.17</v>
+      </c>
+      <c r="N27" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O27" s="32" t="n">
-        <v>188.65</v>
+        <v>187.78</v>
       </c>
       <c r="P27" s="32" t="n">
-        <v>188.56</v>
+        <v>187.53</v>
       </c>
       <c r="Q27" s="33" t="n">
         <v>187.9</v>
       </c>
-      <c r="R27" s="36" t="n">
-        <v>-1.11</v>
+      <c r="R27" s="34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2344,37 +2344,37 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>91.14</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>87.84</v>
+        <v>92</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>85.06999999999999</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>86.47</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>87.78</v>
+        <v>91.7</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>84.48</v>
+        <v>88.3</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>83.17</v>
+        <v>86.7</v>
       </c>
       <c r="J28" s="29" t="n">
-        <v>81.18000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>83.23</v>
+        <v>87.25</v>
       </c>
       <c r="L28" s="31" t="n">
-        <v>80.45999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>77.16</v>
+        <v>81</v>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="O28" s="32" t="n">
-        <v>83.98</v>
+        <v>87.91</v>
       </c>
       <c r="P28" s="32" t="n">
-        <v>83.48</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="Q28" s="33" t="n">
-        <v>85.15000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="R28" s="34" t="n">
-        <v>6.04</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="29">
@@ -2406,54 +2406,54 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>23.94</v>
+        <v>22.75</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>22.98</v>
+        <v>22.15</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>22.18</v>
+        <v>21.65</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>22.14</v>
+        <v>21.61</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>22.75</v>
+        <v>21.99</v>
       </c>
       <c r="H29" s="28" t="n">
-        <v>21.79</v>
+        <v>21.39</v>
       </c>
       <c r="I29" s="29" t="n">
-        <v>21.18</v>
+        <v>21.01</v>
       </c>
       <c r="J29" s="29" t="n">
-        <v>20.83</v>
+        <v>20.79</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>21.64</v>
+        <v>21.31</v>
       </c>
       <c r="L29" s="31" t="n">
-        <v>20.84</v>
+        <v>20.81</v>
       </c>
       <c r="M29" s="31" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="N29" s="35" t="inlineStr">
+        <v>20.21</v>
+      </c>
+      <c r="N29" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O29" s="32" t="n">
-        <v>21.75</v>
+        <v>21.38</v>
       </c>
       <c r="P29" s="32" t="n">
-        <v>21.72</v>
+        <v>21.36</v>
       </c>
       <c r="Q29" s="33" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="R29" s="36" t="n">
-        <v>-1.19</v>
+        <v>21.22</v>
+      </c>
+      <c r="R29" s="35" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="30">
@@ -2468,37 +2468,37 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>84.48999999999999</v>
+        <v>82.89</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>82.23999999999999</v>
+        <v>81.94</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>80.34999999999999</v>
+        <v>81.14</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>81.2</v>
+        <v>81.67</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>82.15000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>79.90000000000001</v>
+        <v>81.03</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>78.95</v>
+        <v>80.72</v>
       </c>
       <c r="J30" s="29" t="n">
-        <v>77.65000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>79.09</v>
+        <v>80.61</v>
       </c>
       <c r="L30" s="31" t="n">
-        <v>77.20999999999999</v>
+        <v>79.81</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>74.95999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="O30" s="32" t="n">
-        <v>79.59</v>
+        <v>80.86</v>
       </c>
       <c r="P30" s="32" t="n">
-        <v>79.27</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="Q30" s="33" t="n">
-        <v>80.25</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="R30" s="34" t="n">
-        <v>1.97</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="31">
@@ -2530,54 +2530,54 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>37.07</v>
+        <v>34.02</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>35.17</v>
+        <v>33.02</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>33.58</v>
+        <v>32.18</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>33.37</v>
+        <v>32.07</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>34.63</v>
+        <v>32.73</v>
       </c>
       <c r="H31" s="28" t="n">
-        <v>32.73</v>
+        <v>31.73</v>
       </c>
       <c r="I31" s="29" t="n">
-        <v>31.47</v>
+        <v>31.07</v>
       </c>
       <c r="J31" s="29" t="n">
-        <v>30.83</v>
+        <v>30.73</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>32.52</v>
+        <v>31.62</v>
       </c>
       <c r="L31" s="31" t="n">
-        <v>30.93</v>
+        <v>30.78</v>
       </c>
       <c r="M31" s="31" t="n">
-        <v>29.03</v>
-      </c>
-      <c r="N31" s="35" t="inlineStr">
+        <v>29.78</v>
+      </c>
+      <c r="N31" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O31" s="32" t="n">
-        <v>32.7</v>
+        <v>31.72</v>
       </c>
       <c r="P31" s="32" t="n">
-        <v>32.67</v>
+        <v>31.7</v>
       </c>
       <c r="Q31" s="33" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="R31" s="36" t="n">
-        <v>-1.47</v>
+        <v>31.4</v>
+      </c>
+      <c r="R31" s="35" t="n">
+        <v>-2.18</v>
       </c>
     </row>
     <row r="32">
@@ -2592,54 +2592,54 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>50.03</v>
+        <v>51.53</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>49.79</v>
+        <v>50.77</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>49.59</v>
+        <v>50.13</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>49.63</v>
+        <v>50.45</v>
       </c>
       <c r="G32" s="27" t="n">
-        <v>49.75</v>
+        <v>50.76</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>49.51</v>
+        <v>50</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>49.39</v>
+        <v>49.69</v>
       </c>
       <c r="J32" s="29" t="n">
-        <v>49.27</v>
+        <v>49.24</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>49.45</v>
+        <v>49.71</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>49.25</v>
+        <v>49.07</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>49.01</v>
-      </c>
-      <c r="N32" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>48.31</v>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O32" s="32" t="n">
-        <v>49.49</v>
+        <v>49.88</v>
       </c>
       <c r="P32" s="32" t="n">
-        <v>49.47</v>
+        <v>49.77</v>
       </c>
       <c r="Q32" s="33" t="n">
-        <v>49.5</v>
+        <v>50.15</v>
       </c>
       <c r="R32" s="34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="33">
@@ -2654,37 +2654,37 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>128.23</v>
+        <v>127.3</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>126.73</v>
+        <v>126</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>125.47</v>
+        <v>124.91</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>125.43</v>
+        <v>125.5</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>126.37</v>
+        <v>126</v>
       </c>
       <c r="H33" s="28" t="n">
-        <v>124.87</v>
+        <v>124.7</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>123.93</v>
+        <v>124.2</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>123.37</v>
+        <v>123.4</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>124.63</v>
+        <v>124.19</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>123.37</v>
+        <v>123.1</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>121.87</v>
+        <v>121.8</v>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
@@ -2692,13 +2692,13 @@
         </is>
       </c>
       <c r="O33" s="32" t="n">
-        <v>124.81</v>
+        <v>124.49</v>
       </c>
       <c r="P33" s="32" t="n">
-        <v>124.75</v>
+        <v>124.29</v>
       </c>
       <c r="Q33" s="33" t="n">
-        <v>124.5</v>
+        <v>125</v>
       </c>
       <c r="R33" s="34" t="n">
         <v>0.4</v>
@@ -2716,37 +2716,37 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>53.87</v>
+        <v>53.89</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>52.62</v>
+        <v>52.94</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>51.57</v>
+        <v>52.14</v>
       </c>
       <c r="F34" s="27" t="n">
+        <v>52.27</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="H34" s="28" t="n">
         <v>51.83</v>
       </c>
-      <c r="G34" s="27" t="n">
-        <v>52.47</v>
-      </c>
-      <c r="H34" s="28" t="n">
-        <v>51.22</v>
-      </c>
       <c r="I34" s="29" t="n">
-        <v>50.58</v>
+        <v>51.32</v>
       </c>
       <c r="J34" s="29" t="n">
-        <v>49.97</v>
+        <v>50.88</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>50.87</v>
+        <v>51.61</v>
       </c>
       <c r="L34" s="31" t="n">
-        <v>49.83</v>
+        <v>50.81</v>
       </c>
       <c r="M34" s="31" t="n">
-        <v>48.58</v>
+        <v>49.86</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="O34" s="32" t="n">
-        <v>51.09</v>
+        <v>51.76</v>
       </c>
       <c r="P34" s="32" t="n">
-        <v>50.97</v>
+        <v>51.68</v>
       </c>
       <c r="Q34" s="33" t="n">
-        <v>51.2</v>
+        <v>51.75</v>
       </c>
       <c r="R34" s="34" t="n">
-        <v>1.79</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="35">
@@ -2778,37 +2778,37 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>26.67</v>
+        <v>27.39</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>25.97</v>
+        <v>26.59</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>25.39</v>
+        <v>25.92</v>
       </c>
       <c r="F35" s="27" t="n">
-        <v>25.63</v>
+        <v>26.3</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>25.93</v>
+        <v>26.6</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>25.23</v>
+        <v>25.8</v>
       </c>
       <c r="I35" s="29" t="n">
-        <v>24.93</v>
+        <v>25.5</v>
       </c>
       <c r="J35" s="29" t="n">
-        <v>24.53</v>
+        <v>25</v>
       </c>
       <c r="K35" s="30" t="n">
-        <v>24.99</v>
+        <v>25.48</v>
       </c>
       <c r="L35" s="31" t="n">
-        <v>24.41</v>
+        <v>24.81</v>
       </c>
       <c r="M35" s="31" t="n">
-        <v>23.71</v>
+        <v>24.01</v>
       </c>
       <c r="N35" s="20" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="O35" s="32" t="n">
-        <v>25.14</v>
+        <v>25.67</v>
       </c>
       <c r="P35" s="32" t="n">
-        <v>25.05</v>
+        <v>25.54</v>
       </c>
       <c r="Q35" s="33" t="n">
-        <v>25.32</v>
+        <v>26</v>
       </c>
       <c r="R35" s="34" t="n">
-        <v>1.85</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="36">
@@ -2840,37 +2840,37 @@
         </is>
       </c>
       <c r="C36" s="25" t="n">
-        <v>27.34</v>
+        <v>26.61</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>26.6</v>
+        <v>26.37</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>25.98</v>
+        <v>26.17</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>26.39</v>
+        <v>26.25</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>26.63</v>
+        <v>26.35</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>25.89</v>
+        <v>26.11</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>25.65</v>
+        <v>26.01</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>25.15</v>
+        <v>25.87</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>25.56</v>
+        <v>26.03</v>
       </c>
       <c r="L36" s="31" t="n">
-        <v>24.94</v>
+        <v>25.83</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>24.2</v>
+        <v>25.59</v>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="O36" s="32" t="n">
-        <v>25.76</v>
+        <v>26.08</v>
       </c>
       <c r="P36" s="32" t="n">
-        <v>25.62</v>
+        <v>26.05</v>
       </c>
       <c r="Q36" s="33" t="n">
         <v>26.14</v>
       </c>
       <c r="R36" s="34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2902,54 +2902,54 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="E37" s="26" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="H37" s="28" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="I37" s="29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J37" s="29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K37" s="30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L37" s="31" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="M37" s="31" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="N37" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O37" s="32" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="P37" s="32" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="F37" s="27" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="H37" s="28" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="I37" s="29" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="J37" s="29" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="K37" s="30" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="L37" s="31" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M37" s="31" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="N37" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O37" s="32" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="P37" s="32" t="n">
-        <v>9.51</v>
-      </c>
       <c r="Q37" s="33" t="n">
-        <v>9.550000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="R37" s="34" t="n">
-        <v>0.95</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="38">
@@ -2964,54 +2964,54 @@
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>31.94</v>
+        <v>32.01</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>31.62</v>
+        <v>31.67</v>
       </c>
       <c r="E38" s="26" t="n">
-        <v>31.35</v>
+        <v>31.39</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>31.49</v>
+        <v>31.43</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>31.61</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>31.29</v>
+        <v>31.27</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>31.17</v>
+        <v>31.09</v>
       </c>
       <c r="J38" s="29" t="n">
-        <v>30.97</v>
+        <v>30.93</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>31.17</v>
+        <v>31.19</v>
       </c>
       <c r="L38" s="31" t="n">
-        <v>30.9</v>
+        <v>30.91</v>
       </c>
       <c r="M38" s="31" t="n">
-        <v>30.58</v>
-      </c>
-      <c r="N38" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>30.57</v>
+      </c>
+      <c r="N38" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O38" s="32" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="P38" s="32" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="Q38" s="33" t="n">
         <v>31.24</v>
       </c>
-      <c r="P38" s="32" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="Q38" s="33" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="R38" s="34" t="n">
-        <v>0.19</v>
+      <c r="R38" s="35" t="n">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="39">
@@ -3026,37 +3026,37 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>193.66</v>
+        <v>192.56</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>190.16</v>
+        <v>190.36</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>187.23</v>
+        <v>188.52</v>
       </c>
       <c r="F39" s="27" t="n">
-        <v>188.1</v>
+        <v>189.47</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>189.8</v>
+        <v>190.33</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>186.3</v>
+        <v>188.13</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>184.6</v>
+        <v>187.27</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>182.8</v>
+        <v>185.93</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>185.27</v>
+        <v>187.28</v>
       </c>
       <c r="L39" s="31" t="n">
-        <v>182.34</v>
+        <v>185.44</v>
       </c>
       <c r="M39" s="31" t="n">
-        <v>178.84</v>
+        <v>183.24</v>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
@@ -3064,16 +3064,16 @@
         </is>
       </c>
       <c r="O39" s="32" t="n">
-        <v>185.92</v>
+        <v>187.79</v>
       </c>
       <c r="P39" s="32" t="n">
-        <v>185.54</v>
+        <v>187.46</v>
       </c>
       <c r="Q39" s="33" t="n">
-        <v>186.4</v>
+        <v>188.6</v>
       </c>
       <c r="R39" s="34" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="40">
@@ -3088,54 +3088,54 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>13.7</v>
+        <v>13.82</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>13.57</v>
+        <v>13.66</v>
       </c>
       <c r="E40" s="26" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="G40" s="27" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="H40" s="28" t="n">
         <v>13.46</v>
       </c>
-      <c r="F40" s="27" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="G40" s="27" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="H40" s="28" t="n">
-        <v>13.41</v>
-      </c>
       <c r="I40" s="29" t="n">
-        <v>13.33</v>
+        <v>13.36</v>
       </c>
       <c r="J40" s="29" t="n">
-        <v>13.28</v>
+        <v>13.3</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>13.39</v>
+        <v>13.44</v>
       </c>
       <c r="L40" s="31" t="n">
-        <v>13.28</v>
+        <v>13.3</v>
       </c>
       <c r="M40" s="31" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="N40" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>13.14</v>
+      </c>
+      <c r="N40" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O40" s="32" t="n">
-        <v>13.4</v>
+        <v>13.45</v>
       </c>
       <c r="P40" s="32" t="n">
-        <v>13.4</v>
+        <v>13.45</v>
       </c>
       <c r="Q40" s="33" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="R40" s="36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>13.42</v>
+      </c>
+      <c r="R40" s="34" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="41">
@@ -3153,51 +3153,51 @@
         <v>21.69</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>21.36</v>
+        <v>21.38</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>21.09</v>
+        <v>21.12</v>
       </c>
       <c r="F41" s="27" t="n">
-        <v>21.06</v>
+        <v>21.14</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>21.28</v>
+        <v>21.32</v>
       </c>
       <c r="H41" s="28" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="I41" s="29" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="J41" s="29" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K41" s="30" t="n">
         <v>20.95</v>
       </c>
-      <c r="I41" s="29" t="n">
-        <v>20.73</v>
-      </c>
-      <c r="J41" s="29" t="n">
-        <v>20.62</v>
-      </c>
-      <c r="K41" s="30" t="n">
-        <v>20.9</v>
-      </c>
       <c r="L41" s="31" t="n">
-        <v>20.63</v>
+        <v>20.69</v>
       </c>
       <c r="M41" s="31" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="N41" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>20.38</v>
+      </c>
+      <c r="N41" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O41" s="32" t="n">
-        <v>20.94</v>
+        <v>20.99</v>
       </c>
       <c r="P41" s="32" t="n">
-        <v>20.93</v>
+        <v>20.97</v>
       </c>
       <c r="Q41" s="33" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="R41" s="36" t="n">
-        <v>-0.29</v>
+        <v>20.96</v>
+      </c>
+      <c r="R41" s="34" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="42">
@@ -3212,37 +3212,37 @@
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>188.44</v>
+        <v>182.17</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>183.84</v>
+        <v>180.77</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>179.99</v>
+        <v>179.59</v>
       </c>
       <c r="F42" s="27" t="n">
-        <v>181.2</v>
+        <v>179.77</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>183.4</v>
+        <v>180.53</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>178.8</v>
+        <v>179.13</v>
       </c>
       <c r="I42" s="29" t="n">
-        <v>176.6</v>
+        <v>178.37</v>
       </c>
       <c r="J42" s="29" t="n">
-        <v>174.2</v>
+        <v>177.73</v>
       </c>
       <c r="K42" s="30" t="n">
-        <v>177.41</v>
+        <v>178.81</v>
       </c>
       <c r="L42" s="31" t="n">
-        <v>173.56</v>
+        <v>177.63</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>168.96</v>
+        <v>176.23</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
@@ -3250,16 +3250,16 @@
         </is>
       </c>
       <c r="O42" s="32" t="n">
-        <v>178.29</v>
+        <v>179.03</v>
       </c>
       <c r="P42" s="32" t="n">
-        <v>177.77</v>
+        <v>178.92</v>
       </c>
       <c r="Q42" s="33" t="n">
         <v>179</v>
       </c>
       <c r="R42" s="34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3274,37 +3274,37 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>39.15</v>
+        <v>42.41</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>38.03</v>
+        <v>40.49</v>
       </c>
       <c r="E43" s="26" t="n">
-        <v>37.09</v>
+        <v>38.88</v>
       </c>
       <c r="F43" s="27" t="n">
-        <v>37.62</v>
+        <v>39.94</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>38.04</v>
+        <v>40.58</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>36.92</v>
+        <v>38.66</v>
       </c>
       <c r="I43" s="29" t="n">
-        <v>36.5</v>
+        <v>38.02</v>
       </c>
       <c r="J43" s="29" t="n">
-        <v>35.8</v>
+        <v>36.74</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>36.47</v>
+        <v>37.8</v>
       </c>
       <c r="L43" s="31" t="n">
-        <v>35.53</v>
+        <v>36.19</v>
       </c>
       <c r="M43" s="31" t="n">
-        <v>34.41</v>
+        <v>34.27</v>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
@@ -3312,16 +3312,16 @@
         </is>
       </c>
       <c r="O43" s="32" t="n">
-        <v>36.74</v>
+        <v>38.31</v>
       </c>
       <c r="P43" s="32" t="n">
-        <v>36.55</v>
+        <v>37.95</v>
       </c>
       <c r="Q43" s="33" t="n">
-        <v>37.2</v>
+        <v>39.3</v>
       </c>
       <c r="R43" s="34" t="n">
-        <v>2.54</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="44">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>27.73</v>
+        <v>28.91</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>27.43</v>
+        <v>28.25</v>
       </c>
       <c r="E44" s="26" t="n">
-        <v>27.17</v>
+        <v>27.69</v>
       </c>
       <c r="F44" s="27" t="n">
-        <v>27.31</v>
+        <v>28.03</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>27.43</v>
+        <v>28.27</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>27.13</v>
+        <v>27.61</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>27.01</v>
+        <v>27.37</v>
       </c>
       <c r="J44" s="29" t="n">
-        <v>26.83</v>
+        <v>26.95</v>
       </c>
       <c r="K44" s="30" t="n">
-        <v>27.01</v>
+        <v>27.33</v>
       </c>
       <c r="L44" s="31" t="n">
-        <v>26.75</v>
+        <v>26.77</v>
       </c>
       <c r="M44" s="31" t="n">
-        <v>26.45</v>
+        <v>26.11</v>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
@@ -3374,16 +3374,16 @@
         </is>
       </c>
       <c r="O44" s="32" t="n">
-        <v>27.08</v>
+        <v>27.49</v>
       </c>
       <c r="P44" s="32" t="n">
-        <v>27.03</v>
+        <v>27.38</v>
       </c>
       <c r="Q44" s="33" t="n">
-        <v>27.2</v>
+        <v>27.8</v>
       </c>
       <c r="R44" s="34" t="n">
-        <v>1.04</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="45">
@@ -3398,13 +3398,13 @@
         </is>
       </c>
       <c r="C45" s="25" t="n">
-        <v>26.78</v>
+        <v>26.75</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>26.58</v>
+        <v>26.61</v>
       </c>
       <c r="E45" s="26" t="n">
-        <v>26.42</v>
+        <v>26.49</v>
       </c>
       <c r="F45" s="27" t="n">
         <v>26.49</v>
@@ -3413,39 +3413,39 @@
         <v>26.57</v>
       </c>
       <c r="H45" s="28" t="n">
-        <v>26.37</v>
+        <v>26.43</v>
       </c>
       <c r="I45" s="29" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="J45" s="29" t="n">
         <v>26.29</v>
       </c>
-      <c r="J45" s="29" t="n">
-        <v>26.17</v>
-      </c>
       <c r="K45" s="30" t="n">
-        <v>26.3</v>
+        <v>26.41</v>
       </c>
       <c r="L45" s="31" t="n">
-        <v>26.14</v>
+        <v>26.29</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>25.94</v>
-      </c>
-      <c r="N45" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>26.15</v>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O45" s="32" t="n">
-        <v>26.35</v>
+        <v>26.43</v>
       </c>
       <c r="P45" s="32" t="n">
-        <v>26.32</v>
+        <v>26.42</v>
       </c>
       <c r="Q45" s="33" t="n">
         <v>26.4</v>
       </c>
-      <c r="R45" s="36" t="n">
-        <v>-0.9</v>
+      <c r="R45" s="34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3460,37 +3460,37 @@
         </is>
       </c>
       <c r="C46" s="25" t="n">
-        <v>8.23</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>8.06</v>
+        <v>8.09</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>7.91</v>
+        <v>7.99</v>
       </c>
       <c r="F46" s="27" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="H46" s="28" t="n">
         <v>7.97</v>
       </c>
-      <c r="G46" s="27" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="H46" s="28" t="n">
-        <v>7.87</v>
-      </c>
       <c r="I46" s="29" t="n">
-        <v>7.8</v>
+        <v>7.92</v>
       </c>
       <c r="J46" s="29" t="n">
-        <v>7.7</v>
+        <v>7.85</v>
       </c>
       <c r="K46" s="30" t="n">
-        <v>7.82</v>
+        <v>7.93</v>
       </c>
       <c r="L46" s="31" t="n">
-        <v>7.67</v>
+        <v>7.83</v>
       </c>
       <c r="M46" s="31" t="n">
-        <v>7.5</v>
+        <v>7.71</v>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
@@ -3498,16 +3498,16 @@
         </is>
       </c>
       <c r="O46" s="32" t="n">
-        <v>7.85</v>
+        <v>7.95</v>
       </c>
       <c r="P46" s="32" t="n">
-        <v>7.83</v>
+        <v>7.94</v>
       </c>
       <c r="Q46" s="33" t="n">
-        <v>7.89</v>
+        <v>7.99</v>
       </c>
       <c r="R46" s="34" t="n">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="47">
@@ -3522,54 +3522,54 @@
         </is>
       </c>
       <c r="C47" s="25" t="n">
-        <v>12.7</v>
+        <v>12.93</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>12.5</v>
+        <v>12.65</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>12.34</v>
+        <v>12.42</v>
       </c>
       <c r="F47" s="27" t="n">
-        <v>12.39</v>
+        <v>12.44</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>12.48</v>
+        <v>12.6</v>
       </c>
       <c r="H47" s="28" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="I47" s="29" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="J47" s="29" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="K47" s="30" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="L47" s="31" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="M47" s="31" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="N47" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O47" s="32" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="P47" s="32" t="n">
         <v>12.28</v>
       </c>
-      <c r="I47" s="29" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="J47" s="29" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="K47" s="30" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="L47" s="31" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="M47" s="31" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="N47" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O47" s="32" t="n">
-        <v>12.26</v>
-      </c>
-      <c r="P47" s="32" t="n">
-        <v>12.24</v>
-      </c>
       <c r="Q47" s="33" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="R47" s="34" t="n">
-        <v>0.82</v>
+        <v>12.28</v>
+      </c>
+      <c r="R47" s="35" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="48">
@@ -3584,37 +3584,37 @@
         </is>
       </c>
       <c r="C48" s="25" t="n">
-        <v>201.67</v>
+        <v>206.19</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>200.27</v>
+        <v>203.29</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>199.09</v>
+        <v>200.86</v>
       </c>
       <c r="F48" s="27" t="n">
-        <v>199.33</v>
+        <v>201.47</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>200.07</v>
+        <v>202.93</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>198.67</v>
+        <v>200.03</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>197.93</v>
+        <v>198.57</v>
       </c>
       <c r="J48" s="29" t="n">
-        <v>197.27</v>
+        <v>197.13</v>
       </c>
       <c r="K48" s="30" t="n">
-        <v>198.31</v>
+        <v>199.24</v>
       </c>
       <c r="L48" s="31" t="n">
-        <v>197.13</v>
+        <v>196.81</v>
       </c>
       <c r="M48" s="31" t="n">
-        <v>195.73</v>
+        <v>193.91</v>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
@@ -3622,16 +3622,16 @@
         </is>
       </c>
       <c r="O48" s="32" t="n">
-        <v>198.54</v>
+        <v>199.75</v>
       </c>
       <c r="P48" s="32" t="n">
-        <v>198.42</v>
+        <v>199.46</v>
       </c>
       <c r="Q48" s="33" t="n">
-        <v>198.6</v>
+        <v>200</v>
       </c>
       <c r="R48" s="34" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="49">
@@ -3646,54 +3646,54 @@
         </is>
       </c>
       <c r="C49" s="25" t="n">
-        <v>49.68</v>
+        <v>49.63</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>49.04</v>
+        <v>49.07</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="F49" s="27" t="n">
-        <v>48.59</v>
+        <v>48.63</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>48.93</v>
+        <v>48.95</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>48.29</v>
+        <v>48.39</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>47.95</v>
+        <v>48.07</v>
       </c>
       <c r="J49" s="29" t="n">
-        <v>47.65</v>
+        <v>47.83</v>
       </c>
       <c r="K49" s="30" t="n">
-        <v>48.14</v>
+        <v>48.28</v>
       </c>
       <c r="L49" s="31" t="n">
-        <v>47.6</v>
+        <v>47.81</v>
       </c>
       <c r="M49" s="31" t="n">
-        <v>46.96</v>
-      </c>
-      <c r="N49" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>47.25</v>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O49" s="32" t="n">
-        <v>48.24</v>
+        <v>48.36</v>
       </c>
       <c r="P49" s="32" t="n">
-        <v>48.19</v>
+        <v>48.33</v>
       </c>
       <c r="Q49" s="33" t="n">
-        <v>48.24</v>
-      </c>
-      <c r="R49" s="36" t="n">
-        <v>-0.45</v>
+        <v>48.3</v>
+      </c>
+      <c r="R49" s="34" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="50">
@@ -3708,54 +3708,54 @@
         </is>
       </c>
       <c r="C50" s="25" t="n">
-        <v>33.32</v>
+        <v>35.38</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>32.9</v>
+        <v>34.28</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>32.55</v>
+        <v>33.36</v>
       </c>
       <c r="F50" s="27" t="n">
-        <v>32.67</v>
+        <v>33.93</v>
       </c>
       <c r="G50" s="27" t="n">
-        <v>32.87</v>
+        <v>34.31</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>32.45</v>
+        <v>33.21</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>32.25</v>
+        <v>32.83</v>
       </c>
       <c r="J50" s="29" t="n">
-        <v>32.03</v>
+        <v>32.11</v>
       </c>
       <c r="K50" s="30" t="n">
-        <v>32.31</v>
+        <v>32.74</v>
       </c>
       <c r="L50" s="31" t="n">
-        <v>31.96</v>
+        <v>31.82</v>
       </c>
       <c r="M50" s="31" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="N50" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>30.72</v>
+      </c>
+      <c r="N50" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O50" s="32" t="n">
-        <v>32.4</v>
+        <v>33.02</v>
       </c>
       <c r="P50" s="32" t="n">
-        <v>32.35</v>
+        <v>32.83</v>
       </c>
       <c r="Q50" s="33" t="n">
-        <v>32.48</v>
+        <v>33.54</v>
       </c>
       <c r="R50" s="34" t="n">
-        <v>0.06</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="51">
@@ -3770,54 +3770,54 @@
         </is>
       </c>
       <c r="C51" s="25" t="n">
-        <v>13.39</v>
+        <v>13.7</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>13.26</v>
+        <v>13.5</v>
       </c>
       <c r="E51" s="26" t="n">
-        <v>13.15</v>
+        <v>13.34</v>
       </c>
       <c r="F51" s="27" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="G51" s="27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H51" s="28" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="I51" s="29" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="J51" s="29" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="K51" s="30" t="n">
         <v>13.22</v>
       </c>
-      <c r="G51" s="27" t="n">
+      <c r="L51" s="31" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="M51" s="31" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="N51" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O51" s="32" t="n">
         <v>13.27</v>
       </c>
-      <c r="H51" s="28" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="I51" s="29" t="n">
-        <v>13.09</v>
-      </c>
-      <c r="J51" s="29" t="n">
-        <v>13.01</v>
-      </c>
-      <c r="K51" s="30" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="L51" s="31" t="n">
-        <v>12.97</v>
-      </c>
-      <c r="M51" s="31" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="N51" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O51" s="32" t="n">
-        <v>13.11</v>
-      </c>
       <c r="P51" s="32" t="n">
-        <v>13.09</v>
+        <v>13.24</v>
       </c>
       <c r="Q51" s="33" t="n">
-        <v>13.18</v>
+        <v>13.35</v>
       </c>
       <c r="R51" s="34" t="n">
-        <v>0.3</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="52">
@@ -3832,37 +3832,37 @@
         </is>
       </c>
       <c r="C52" s="25" t="n">
-        <v>60.48</v>
+        <v>61.36</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>59.63</v>
+        <v>60.46</v>
       </c>
       <c r="E52" s="26" t="n">
-        <v>58.91</v>
+        <v>59.7</v>
       </c>
       <c r="F52" s="27" t="n">
-        <v>59.32</v>
+        <v>59.9</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>59.63</v>
+        <v>60.35</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>58.78</v>
+        <v>59.45</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>58.47</v>
+        <v>59</v>
       </c>
       <c r="J52" s="29" t="n">
-        <v>57.93</v>
+        <v>58.55</v>
       </c>
       <c r="K52" s="30" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="L52" s="31" t="n">
         <v>58.44</v>
       </c>
-      <c r="L52" s="31" t="n">
-        <v>57.72</v>
-      </c>
       <c r="M52" s="31" t="n">
-        <v>56.87</v>
+        <v>57.54</v>
       </c>
       <c r="N52" s="20" t="inlineStr">
         <is>
@@ -3870,16 +3870,16 @@
         </is>
       </c>
       <c r="O52" s="32" t="n">
-        <v>58.64</v>
+        <v>59.36</v>
       </c>
       <c r="P52" s="32" t="n">
-        <v>58.5</v>
+        <v>59.27</v>
       </c>
       <c r="Q52" s="33" t="n">
-        <v>59</v>
+        <v>59.45</v>
       </c>
       <c r="R52" s="34" t="n">
-        <v>1.2</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="53">
@@ -3894,37 +3894,37 @@
         </is>
       </c>
       <c r="C53" s="25" t="n">
-        <v>25.56</v>
+        <v>25.93</v>
       </c>
       <c r="D53" s="25" t="n">
-        <v>25.2</v>
+        <v>25.48</v>
       </c>
       <c r="E53" s="26" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="F53" s="27" t="n">
-        <v>24.95</v>
+        <v>25.23</v>
       </c>
       <c r="G53" s="27" t="n">
-        <v>25.14</v>
+        <v>25.44</v>
       </c>
       <c r="H53" s="28" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="I53" s="29" t="n">
         <v>24.78</v>
       </c>
-      <c r="I53" s="29" t="n">
-        <v>24.59</v>
-      </c>
       <c r="J53" s="29" t="n">
-        <v>24.42</v>
+        <v>24.54</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>24.7</v>
+        <v>24.85</v>
       </c>
       <c r="L53" s="31" t="n">
-        <v>24.4</v>
+        <v>24.47</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>24.04</v>
+        <v>24.02</v>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="O53" s="32" t="n">
-        <v>24.76</v>
+        <v>24.94</v>
       </c>
       <c r="P53" s="32" t="n">
-        <v>24.73</v>
+        <v>24.88</v>
       </c>
       <c r="Q53" s="33" t="n">
-        <v>24.75</v>
+        <v>25.02</v>
       </c>
       <c r="R53" s="34" t="n">
-        <v>0.36</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="54">
@@ -3956,54 +3956,54 @@
         </is>
       </c>
       <c r="C54" s="25" t="n">
-        <v>5.51</v>
+        <v>5.63</v>
       </c>
       <c r="D54" s="25" t="n">
-        <v>5.39</v>
+        <v>5.48</v>
       </c>
       <c r="E54" s="26" t="n">
-        <v>5.29</v>
+        <v>5.36</v>
       </c>
       <c r="F54" s="27" t="n">
-        <v>5.35</v>
+        <v>5.36</v>
       </c>
       <c r="G54" s="27" t="n">
-        <v>5.39</v>
+        <v>5.45</v>
       </c>
       <c r="H54" s="28" t="n">
-        <v>5.27</v>
+        <v>5.3</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>5.23</v>
+        <v>5.21</v>
       </c>
       <c r="J54" s="29" t="n">
         <v>5.15</v>
       </c>
       <c r="K54" s="30" t="n">
-        <v>5.23</v>
+        <v>5.27</v>
       </c>
       <c r="L54" s="31" t="n">
-        <v>5.13</v>
+        <v>5.15</v>
       </c>
       <c r="M54" s="31" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="N54" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>5</v>
+      </c>
+      <c r="N54" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O54" s="32" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="P54" s="32" t="n">
-        <v>5.24</v>
+        <v>5.28</v>
       </c>
       <c r="Q54" s="33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="R54" s="34" t="n">
-        <v>1.34</v>
+        <v>5.27</v>
+      </c>
+      <c r="R54" s="35" t="n">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="55">
@@ -4018,37 +4018,37 @@
         </is>
       </c>
       <c r="C55" s="25" t="n">
-        <v>19.31</v>
+        <v>18.75</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>18.62</v>
+        <v>18.44</v>
       </c>
       <c r="E55" s="26" t="n">
-        <v>18.04</v>
+        <v>18.18</v>
       </c>
       <c r="F55" s="27" t="n">
-        <v>18.29</v>
+        <v>18.23</v>
       </c>
       <c r="G55" s="27" t="n">
-        <v>18.59</v>
+        <v>18.4</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>17.9</v>
+        <v>18.09</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>17.6</v>
+        <v>17.92</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>17.21</v>
+        <v>17.78</v>
       </c>
       <c r="K55" s="30" t="n">
-        <v>17.65</v>
+        <v>18.01</v>
       </c>
       <c r="L55" s="31" t="n">
-        <v>17.07</v>
+        <v>17.75</v>
       </c>
       <c r="M55" s="31" t="n">
-        <v>16.38</v>
+        <v>17.44</v>
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
@@ -4056,16 +4056,16 @@
         </is>
       </c>
       <c r="O55" s="32" t="n">
-        <v>17.8</v>
+        <v>18.06</v>
       </c>
       <c r="P55" s="32" t="n">
-        <v>17.71</v>
+        <v>18.03</v>
       </c>
       <c r="Q55" s="33" t="n">
-        <v>18</v>
+        <v>18.07</v>
       </c>
       <c r="R55" s="34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="56">
@@ -4080,54 +4080,54 @@
         </is>
       </c>
       <c r="C56" s="25" t="n">
-        <v>89.34</v>
+        <v>91.94</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>88.39</v>
+        <v>89.94</v>
       </c>
       <c r="E56" s="26" t="n">
+        <v>88.26000000000001</v>
+      </c>
+      <c r="F56" s="27" t="n">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="G56" s="27" t="n">
+        <v>89.88</v>
+      </c>
+      <c r="H56" s="28" t="n">
+        <v>87.88</v>
+      </c>
+      <c r="I56" s="29" t="n">
+        <v>87.06999999999999</v>
+      </c>
+      <c r="J56" s="29" t="n">
+        <v>85.88</v>
+      </c>
+      <c r="K56" s="30" t="n">
+        <v>87.14</v>
+      </c>
+      <c r="L56" s="31" t="n">
+        <v>85.45999999999999</v>
+      </c>
+      <c r="M56" s="31" t="n">
+        <v>83.45999999999999</v>
+      </c>
+      <c r="N56" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O56" s="32" t="n">
         <v>87.59</v>
       </c>
-      <c r="F56" s="27" t="n">
-        <v>87.52</v>
-      </c>
-      <c r="G56" s="27" t="n">
-        <v>88.13</v>
-      </c>
-      <c r="H56" s="28" t="n">
-        <v>87.18000000000001</v>
-      </c>
-      <c r="I56" s="29" t="n">
-        <v>86.56999999999999</v>
-      </c>
-      <c r="J56" s="29" t="n">
-        <v>86.23</v>
-      </c>
-      <c r="K56" s="30" t="n">
-        <v>87.06</v>
-      </c>
-      <c r="L56" s="31" t="n">
-        <v>86.26000000000001</v>
-      </c>
-      <c r="M56" s="31" t="n">
-        <v>85.31</v>
-      </c>
-      <c r="N56" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O56" s="32" t="n">
-        <v>87.16</v>
-      </c>
       <c r="P56" s="32" t="n">
-        <v>87.13</v>
+        <v>87.3</v>
       </c>
       <c r="Q56" s="33" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="R56" s="36" t="n">
-        <v>-0.11</v>
+        <v>88.25</v>
+      </c>
+      <c r="R56" s="34" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="57">
@@ -4142,54 +4142,54 @@
         </is>
       </c>
       <c r="C57" s="25" t="n">
-        <v>19.25</v>
+        <v>19.54</v>
       </c>
       <c r="D57" s="25" t="n">
-        <v>19.02</v>
+        <v>19.2</v>
       </c>
       <c r="E57" s="26" t="n">
-        <v>18.83</v>
+        <v>18.92</v>
       </c>
       <c r="F57" s="27" t="n">
-        <v>18.84</v>
+        <v>19.08</v>
       </c>
       <c r="G57" s="27" t="n">
-        <v>18.98</v>
+        <v>19.21</v>
       </c>
       <c r="H57" s="28" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="I57" s="29" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="J57" s="29" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="K57" s="30" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="L57" s="31" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="M57" s="31" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="N57" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O57" s="32" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="P57" s="32" t="n">
         <v>18.75</v>
       </c>
-      <c r="I57" s="29" t="n">
-        <v>18.61</v>
-      </c>
-      <c r="J57" s="29" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="K57" s="30" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="L57" s="31" t="n">
-        <v>18.51</v>
-      </c>
-      <c r="M57" s="31" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="N57" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O57" s="32" t="n">
-        <v>18.73</v>
-      </c>
-      <c r="P57" s="32" t="n">
-        <v>18.72</v>
-      </c>
       <c r="Q57" s="33" t="n">
-        <v>18.71</v>
+        <v>18.96</v>
       </c>
       <c r="R57" s="34" t="n">
-        <v>0.75</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="58">
@@ -4204,54 +4204,54 @@
         </is>
       </c>
       <c r="C58" s="25" t="n">
-        <v>22.5</v>
+        <v>22.03</v>
       </c>
       <c r="D58" s="25" t="n">
-        <v>22.15</v>
+        <v>21.91</v>
       </c>
       <c r="E58" s="26" t="n">
-        <v>21.85</v>
+        <v>21.81</v>
       </c>
       <c r="F58" s="27" t="n">
-        <v>21.92</v>
+        <v>21.86</v>
       </c>
       <c r="G58" s="27" t="n">
-        <v>22.1</v>
+        <v>21.91</v>
       </c>
       <c r="H58" s="28" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="I58" s="29" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="J58" s="29" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="K58" s="30" t="n">
         <v>21.75</v>
       </c>
-      <c r="I58" s="29" t="n">
-        <v>21.57</v>
-      </c>
-      <c r="J58" s="29" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="K58" s="30" t="n">
-        <v>21.66</v>
-      </c>
       <c r="L58" s="31" t="n">
-        <v>21.36</v>
+        <v>21.65</v>
       </c>
       <c r="M58" s="31" t="n">
-        <v>21.01</v>
-      </c>
-      <c r="N58" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>21.53</v>
+      </c>
+      <c r="N58" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O58" s="32" t="n">
-        <v>21.72</v>
+        <v>21.77</v>
       </c>
       <c r="P58" s="32" t="n">
-        <v>21.68</v>
+        <v>21.76</v>
       </c>
       <c r="Q58" s="33" t="n">
-        <v>21.74</v>
-      </c>
-      <c r="R58" s="36" t="n">
-        <v>-0.82</v>
+        <v>21.81</v>
+      </c>
+      <c r="R58" s="34" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="59">
@@ -4266,37 +4266,37 @@
         </is>
       </c>
       <c r="C59" s="25" t="n">
-        <v>23.75</v>
+        <v>23.97</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>23.56</v>
+        <v>23.72</v>
       </c>
       <c r="E59" s="26" t="n">
-        <v>23.4</v>
+        <v>23.51</v>
       </c>
       <c r="F59" s="27" t="n">
-        <v>23.47</v>
+        <v>23.52</v>
       </c>
       <c r="G59" s="27" t="n">
-        <v>23.55</v>
+        <v>23.67</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>23.36</v>
+        <v>23.42</v>
       </c>
       <c r="I59" s="29" t="n">
-        <v>23.28</v>
+        <v>23.27</v>
       </c>
       <c r="J59" s="29" t="n">
         <v>23.17</v>
       </c>
       <c r="K59" s="30" t="n">
-        <v>23.29</v>
+        <v>23.37</v>
       </c>
       <c r="L59" s="31" t="n">
-        <v>23.13</v>
+        <v>23.17</v>
       </c>
       <c r="M59" s="31" t="n">
-        <v>22.94</v>
+        <v>22.92</v>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
@@ -4304,16 +4304,16 @@
         </is>
       </c>
       <c r="O59" s="32" t="n">
-        <v>23.33</v>
+        <v>23.41</v>
       </c>
       <c r="P59" s="32" t="n">
-        <v>23.31</v>
+        <v>23.39</v>
       </c>
       <c r="Q59" s="33" t="n">
-        <v>23.39</v>
-      </c>
-      <c r="R59" s="34" t="n">
-        <v>0.39</v>
+        <v>23.37</v>
+      </c>
+      <c r="R59" s="35" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="60">
@@ -4328,54 +4328,54 @@
         </is>
       </c>
       <c r="C60" s="25" t="n">
-        <v>28.92</v>
+        <v>29.79</v>
       </c>
       <c r="D60" s="25" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E60" s="26" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="G60" s="27" t="n">
+        <v>29.19</v>
+      </c>
+      <c r="H60" s="28" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="I60" s="29" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="J60" s="29" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="K60" s="30" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="L60" s="31" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="M60" s="31" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O60" s="32" t="n">
         <v>28.6</v>
       </c>
-      <c r="E60" s="26" t="n">
-        <v>28.33</v>
-      </c>
-      <c r="F60" s="27" t="n">
-        <v>28.45</v>
-      </c>
-      <c r="G60" s="27" t="n">
-        <v>28.59</v>
-      </c>
-      <c r="H60" s="28" t="n">
-        <v>28.27</v>
-      </c>
-      <c r="I60" s="29" t="n">
-        <v>28.13</v>
-      </c>
-      <c r="J60" s="29" t="n">
-        <v>27.95</v>
-      </c>
-      <c r="K60" s="30" t="n">
-        <v>28.15</v>
-      </c>
-      <c r="L60" s="31" t="n">
-        <v>27.88</v>
-      </c>
-      <c r="M60" s="31" t="n">
-        <v>27.56</v>
-      </c>
-      <c r="N60" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O60" s="32" t="n">
-        <v>28.22</v>
-      </c>
       <c r="P60" s="32" t="n">
-        <v>28.18</v>
+        <v>28.54</v>
       </c>
       <c r="Q60" s="33" t="n">
-        <v>28.32</v>
+        <v>28.66</v>
       </c>
       <c r="R60" s="34" t="n">
-        <v>0.93</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="61">
@@ -4390,37 +4390,37 @@
         </is>
       </c>
       <c r="C61" s="25" t="n">
-        <v>45.84</v>
+        <v>45.75</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>45.26</v>
+        <v>45.37</v>
       </c>
       <c r="E61" s="26" t="n">
-        <v>44.77</v>
+        <v>45.06</v>
       </c>
       <c r="F61" s="27" t="n">
-        <v>45.09</v>
+        <v>45.05</v>
       </c>
       <c r="G61" s="27" t="n">
         <v>45.29</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>44.71</v>
+        <v>44.91</v>
       </c>
       <c r="I61" s="29" t="n">
-        <v>44.51</v>
+        <v>44.67</v>
       </c>
       <c r="J61" s="29" t="n">
-        <v>44.13</v>
+        <v>44.53</v>
       </c>
       <c r="K61" s="30" t="n">
-        <v>44.45</v>
+        <v>44.84</v>
       </c>
       <c r="L61" s="31" t="n">
-        <v>43.96</v>
+        <v>44.53</v>
       </c>
       <c r="M61" s="31" t="n">
-        <v>43.38</v>
+        <v>44.15</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
@@ -4428,16 +4428,16 @@
         </is>
       </c>
       <c r="O61" s="32" t="n">
-        <v>44.6</v>
+        <v>44.89</v>
       </c>
       <c r="P61" s="32" t="n">
-        <v>44.49</v>
+        <v>44.87</v>
       </c>
       <c r="Q61" s="33" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="R61" s="34" t="n">
-        <v>1.35</v>
+        <v>44.82</v>
+      </c>
+      <c r="R61" s="35" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="62">
@@ -4452,54 +4452,54 @@
         </is>
       </c>
       <c r="C62" s="25" t="n">
-        <v>19.47</v>
+        <v>19.56</v>
       </c>
       <c r="D62" s="25" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E62" s="26" t="n">
         <v>19.26</v>
       </c>
-      <c r="E62" s="26" t="n">
-        <v>19.08</v>
-      </c>
       <c r="F62" s="27" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="G62" s="27" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="H62" s="28" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="I62" s="29" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="J62" s="29" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="K62" s="30" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="L62" s="31" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="M62" s="31" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="N62" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O62" s="32" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="P62" s="32" t="n">
         <v>19.19</v>
       </c>
-      <c r="G62" s="27" t="n">
+      <c r="Q62" s="33" t="n">
         <v>19.26</v>
       </c>
-      <c r="H62" s="28" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="I62" s="29" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="J62" s="29" t="n">
-        <v>18.84</v>
-      </c>
-      <c r="K62" s="30" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="L62" s="31" t="n">
-        <v>18.79</v>
-      </c>
-      <c r="M62" s="31" t="n">
-        <v>18.58</v>
-      </c>
-      <c r="N62" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O62" s="32" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="P62" s="32" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="Q62" s="33" t="n">
-        <v>19.11</v>
-      </c>
       <c r="R62" s="34" t="n">
-        <v>1.11</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="63">
@@ -4517,34 +4517,34 @@
         <v>15.19</v>
       </c>
       <c r="D63" s="25" t="n">
-        <v>15</v>
+        <v>15.07</v>
       </c>
       <c r="E63" s="26" t="n">
-        <v>14.84</v>
+        <v>14.97</v>
       </c>
       <c r="F63" s="27" t="n">
-        <v>14.94</v>
+        <v>15.03</v>
       </c>
       <c r="G63" s="27" t="n">
-        <v>15.01</v>
+        <v>15.07</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>14.82</v>
+        <v>14.95</v>
       </c>
       <c r="I63" s="29" t="n">
-        <v>14.75</v>
+        <v>14.91</v>
       </c>
       <c r="J63" s="29" t="n">
-        <v>14.63</v>
+        <v>14.83</v>
       </c>
       <c r="K63" s="30" t="n">
-        <v>14.73</v>
+        <v>14.91</v>
       </c>
       <c r="L63" s="31" t="n">
-        <v>14.57</v>
+        <v>14.81</v>
       </c>
       <c r="M63" s="31" t="n">
-        <v>14.38</v>
+        <v>14.69</v>
       </c>
       <c r="N63" s="20" t="inlineStr">
         <is>
@@ -4552,16 +4552,16 @@
         </is>
       </c>
       <c r="O63" s="32" t="n">
-        <v>14.78</v>
+        <v>14.93</v>
       </c>
       <c r="P63" s="32" t="n">
-        <v>14.75</v>
+        <v>14.92</v>
       </c>
       <c r="Q63" s="33" t="n">
-        <v>14.88</v>
+        <v>14.98</v>
       </c>
       <c r="R63" s="34" t="n">
-        <v>1.36</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="64">
@@ -4576,37 +4576,37 @@
         </is>
       </c>
       <c r="C64" s="25" t="n">
-        <v>25.36</v>
+        <v>25.92</v>
       </c>
       <c r="D64" s="25" t="n">
-        <v>25.13</v>
+        <v>25.56</v>
       </c>
       <c r="E64" s="26" t="n">
-        <v>24.94</v>
+        <v>25.26</v>
       </c>
       <c r="F64" s="27" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="G64" s="27" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="H64" s="28" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="I64" s="29" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="J64" s="29" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="K64" s="30" t="n">
         <v>25.06</v>
       </c>
-      <c r="G64" s="27" t="n">
-        <v>25.14</v>
-      </c>
-      <c r="H64" s="28" t="n">
-        <v>24.91</v>
-      </c>
-      <c r="I64" s="29" t="n">
-        <v>24.83</v>
-      </c>
-      <c r="J64" s="29" t="n">
-        <v>24.68</v>
-      </c>
-      <c r="K64" s="30" t="n">
-        <v>24.81</v>
-      </c>
       <c r="L64" s="31" t="n">
-        <v>24.62</v>
+        <v>24.76</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>24.39</v>
+        <v>24.4</v>
       </c>
       <c r="N64" s="20" t="inlineStr">
         <is>
@@ -4614,16 +4614,16 @@
         </is>
       </c>
       <c r="O64" s="32" t="n">
-        <v>24.87</v>
+        <v>25.15</v>
       </c>
       <c r="P64" s="32" t="n">
-        <v>24.83</v>
+        <v>25.09</v>
       </c>
       <c r="Q64" s="33" t="n">
-        <v>24.98</v>
+        <v>25.34</v>
       </c>
       <c r="R64" s="34" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="65">
@@ -4638,37 +4638,37 @@
         </is>
       </c>
       <c r="C65" s="25" t="n">
-        <v>7.38</v>
+        <v>7.42</v>
       </c>
       <c r="D65" s="25" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E65" s="26" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="F65" s="27" t="n">
         <v>7.31</v>
       </c>
-      <c r="E65" s="26" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="F65" s="27" t="n">
-        <v>7.29</v>
-      </c>
       <c r="G65" s="27" t="n">
-        <v>7.31</v>
+        <v>7.34</v>
       </c>
       <c r="H65" s="28" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="I65" s="29" t="n">
         <v>7.24</v>
       </c>
-      <c r="I65" s="29" t="n">
-        <v>7.22</v>
-      </c>
       <c r="J65" s="29" t="n">
-        <v>7.17</v>
+        <v>7.2</v>
       </c>
       <c r="K65" s="30" t="n">
-        <v>7.22</v>
+        <v>7.26</v>
       </c>
       <c r="L65" s="31" t="n">
-        <v>7.16</v>
+        <v>7.2</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>7.09</v>
+        <v>7.13</v>
       </c>
       <c r="N65" s="20" t="inlineStr">
         <is>
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="O65" s="32" t="n">
-        <v>7.23</v>
+        <v>7.27</v>
       </c>
       <c r="P65" s="32" t="n">
-        <v>7.22</v>
+        <v>7.26</v>
       </c>
       <c r="Q65" s="33" t="n">
-        <v>7.26</v>
+        <v>7.27</v>
       </c>
       <c r="R65" s="34" t="n">
         <v>0.14</v>
@@ -4700,37 +4700,37 @@
         </is>
       </c>
       <c r="C66" s="25" t="n">
-        <v>4.99</v>
+        <v>5.07</v>
       </c>
       <c r="D66" s="25" t="n">
-        <v>4.95</v>
+        <v>5.01</v>
       </c>
       <c r="E66" s="26" t="n">
-        <v>4.92</v>
+        <v>4.96</v>
       </c>
       <c r="F66" s="27" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="G66" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H66" s="28" t="n">
         <v>4.94</v>
-      </c>
-      <c r="G66" s="27" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="H66" s="28" t="n">
-        <v>4.91</v>
       </c>
       <c r="I66" s="29" t="n">
         <v>4.9</v>
       </c>
       <c r="J66" s="29" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="K66" s="30" t="n">
-        <v>4.9</v>
+        <v>4.92</v>
       </c>
       <c r="L66" s="31" t="n">
         <v>4.87</v>
       </c>
       <c r="M66" s="31" t="n">
-        <v>4.83</v>
+        <v>4.81</v>
       </c>
       <c r="N66" s="20" t="inlineStr">
         <is>
@@ -4738,16 +4738,16 @@
         </is>
       </c>
       <c r="O66" s="32" t="n">
-        <v>4.91</v>
+        <v>4.93</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="Q66" s="33" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="R66" s="34" t="n">
-        <v>0.41</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="67">
@@ -4762,25 +4762,25 @@
         </is>
       </c>
       <c r="C67" s="25" t="n">
-        <v>5.16</v>
+        <v>5.13</v>
       </c>
       <c r="D67" s="25" t="n">
-        <v>5.08</v>
+        <v>5.06</v>
       </c>
       <c r="E67" s="26" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="F67" s="27" t="n">
         <v>5</v>
       </c>
       <c r="G67" s="27" t="n">
-        <v>5.06</v>
+        <v>5.04</v>
       </c>
       <c r="H67" s="28" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="I67" s="29" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="J67" s="29" t="n">
         <v>4.9</v>
@@ -4789,18 +4789,18 @@
         <v>4.97</v>
       </c>
       <c r="L67" s="31" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="M67" s="31" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="N67" s="35" t="inlineStr">
+        <v>4.84</v>
+      </c>
+      <c r="N67" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O67" s="32" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="P67" s="32" t="n">
         <v>4.97</v>
@@ -4808,8 +4808,8 @@
       <c r="Q67" s="33" t="n">
         <v>4.95</v>
       </c>
-      <c r="R67" s="36" t="n">
-        <v>-0.2</v>
+      <c r="R67" s="34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4824,37 +4824,37 @@
         </is>
       </c>
       <c r="C68" s="25" t="n">
-        <v>67.31</v>
+        <v>65.67</v>
       </c>
       <c r="D68" s="25" t="n">
-        <v>65.76000000000001</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="E68" s="26" t="n">
-        <v>64.45999999999999</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="F68" s="27" t="n">
-        <v>65.05</v>
+        <v>64.83</v>
       </c>
       <c r="G68" s="27" t="n">
-        <v>65.7</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="H68" s="28" t="n">
-        <v>64.15000000000001</v>
+        <v>64.47</v>
       </c>
       <c r="I68" s="29" t="n">
-        <v>63.5</v>
+        <v>64.23</v>
       </c>
       <c r="J68" s="29" t="n">
-        <v>62.6</v>
+        <v>63.87</v>
       </c>
       <c r="K68" s="30" t="n">
-        <v>63.59</v>
+        <v>64.23</v>
       </c>
       <c r="L68" s="31" t="n">
-        <v>62.29</v>
+        <v>63.73</v>
       </c>
       <c r="M68" s="31" t="n">
-        <v>60.74</v>
+        <v>63.13</v>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
@@ -4862,16 +4862,16 @@
         </is>
       </c>
       <c r="O68" s="32" t="n">
-        <v>63.93</v>
+        <v>64.37</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>63.71</v>
+        <v>64.28</v>
       </c>
       <c r="Q68" s="33" t="n">
-        <v>64.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="R68" s="34" t="n">
-        <v>0.78</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="69">
@@ -4886,54 +4886,54 @@
         </is>
       </c>
       <c r="C69" s="25" t="n">
-        <v>66.19</v>
+        <v>67.05</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>65.39</v>
+        <v>66</v>
       </c>
       <c r="E69" s="26" t="n">
-        <v>64.72</v>
+        <v>65.12</v>
       </c>
       <c r="F69" s="27" t="n">
-        <v>64.73</v>
+        <v>65.7</v>
       </c>
       <c r="G69" s="27" t="n">
-        <v>65.22</v>
+        <v>66.05</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>64.42</v>
+        <v>65</v>
       </c>
       <c r="I69" s="29" t="n">
-        <v>63.93</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J69" s="29" t="n">
-        <v>63.62</v>
+        <v>63.95</v>
       </c>
       <c r="K69" s="30" t="n">
-        <v>64.28</v>
+        <v>64.53</v>
       </c>
       <c r="L69" s="31" t="n">
-        <v>63.61</v>
+        <v>63.65</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>62.81</v>
-      </c>
-      <c r="N69" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>62.6</v>
+      </c>
+      <c r="N69" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>64.38</v>
+        <v>64.81</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>64.34</v>
+        <v>64.61</v>
       </c>
       <c r="Q69" s="33" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="R69" s="36" t="n">
-        <v>-1</v>
+        <v>65.34999999999999</v>
+      </c>
+      <c r="R69" s="34" t="n">
+        <v>1.71</v>
       </c>
     </row>
     <row r="70">
@@ -4948,37 +4948,37 @@
         </is>
       </c>
       <c r="C70" s="25" t="n">
-        <v>104.88</v>
+        <v>104.65</v>
       </c>
       <c r="D70" s="25" t="n">
-        <v>102.73</v>
+        <v>102.95</v>
       </c>
       <c r="E70" s="26" t="n">
+        <v>101.53</v>
+      </c>
+      <c r="F70" s="27" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="G70" s="27" t="n">
+        <v>102.63</v>
+      </c>
+      <c r="H70" s="28" t="n">
         <v>100.93</v>
       </c>
-      <c r="F70" s="27" t="n">
-        <v>101.98</v>
-      </c>
-      <c r="G70" s="27" t="n">
-        <v>102.77</v>
-      </c>
-      <c r="H70" s="28" t="n">
-        <v>100.62</v>
-      </c>
       <c r="I70" s="29" t="n">
-        <v>99.83</v>
+        <v>99.97</v>
       </c>
       <c r="J70" s="29" t="n">
-        <v>98.47</v>
+        <v>99.23</v>
       </c>
       <c r="K70" s="30" t="n">
-        <v>99.72</v>
+        <v>100.57</v>
       </c>
       <c r="L70" s="31" t="n">
-        <v>97.92</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>95.77</v>
+        <v>97.45</v>
       </c>
       <c r="N70" s="20" t="inlineStr">
         <is>
@@ -4986,16 +4986,16 @@
         </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>100.25</v>
+        <v>100.82</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>99.89</v>
+        <v>100.71</v>
       </c>
       <c r="Q70" s="33" t="n">
-        <v>101.2</v>
-      </c>
-      <c r="R70" s="34" t="n">
-        <v>2.17</v>
+        <v>100.7</v>
+      </c>
+      <c r="R70" s="35" t="n">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="71">
@@ -5010,54 +5010,54 @@
         </is>
       </c>
       <c r="C71" s="25" t="n">
-        <v>130.36</v>
+        <v>141.19</v>
       </c>
       <c r="D71" s="25" t="n">
-        <v>128.16</v>
+        <v>134.89</v>
       </c>
       <c r="E71" s="26" t="n">
-        <v>126.32</v>
+        <v>129.61</v>
       </c>
       <c r="F71" s="27" t="n">
-        <v>126.67</v>
+        <v>133.1</v>
       </c>
       <c r="G71" s="27" t="n">
-        <v>127.83</v>
+        <v>135.2</v>
       </c>
       <c r="H71" s="28" t="n">
-        <v>125.63</v>
+        <v>128.9</v>
       </c>
       <c r="I71" s="29" t="n">
-        <v>124.47</v>
+        <v>126.8</v>
       </c>
       <c r="J71" s="29" t="n">
-        <v>123.43</v>
+        <v>122.6</v>
       </c>
       <c r="K71" s="30" t="n">
-        <v>125.08</v>
+        <v>126.09</v>
       </c>
       <c r="L71" s="31" t="n">
-        <v>123.24</v>
+        <v>120.81</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>121.04</v>
-      </c>
-      <c r="N71" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>114.51</v>
+      </c>
+      <c r="N71" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>125.44</v>
+        <v>127.74</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>125.26</v>
+        <v>126.58</v>
       </c>
       <c r="Q71" s="33" t="n">
-        <v>125.5</v>
-      </c>
-      <c r="R71" s="36" t="n">
-        <v>-1.49</v>
+        <v>131</v>
+      </c>
+      <c r="R71" s="34" t="n">
+        <v>4.38</v>
       </c>
     </row>
     <row r="72">
@@ -5072,37 +5072,37 @@
         </is>
       </c>
       <c r="C72" s="25" t="n">
-        <v>26.1</v>
+        <v>26.35</v>
       </c>
       <c r="D72" s="25" t="n">
-        <v>25.63</v>
+        <v>25.85</v>
       </c>
       <c r="E72" s="26" t="n">
-        <v>25.24</v>
+        <v>25.43</v>
       </c>
       <c r="F72" s="27" t="n">
-        <v>25.4</v>
+        <v>25.59</v>
       </c>
       <c r="G72" s="27" t="n">
-        <v>25.61</v>
+        <v>25.81</v>
       </c>
       <c r="H72" s="28" t="n">
-        <v>25.14</v>
+        <v>25.31</v>
       </c>
       <c r="I72" s="29" t="n">
-        <v>24.93</v>
+        <v>25.09</v>
       </c>
       <c r="J72" s="29" t="n">
-        <v>24.67</v>
+        <v>24.81</v>
       </c>
       <c r="K72" s="30" t="n">
-        <v>24.97</v>
+        <v>25.15</v>
       </c>
       <c r="L72" s="31" t="n">
-        <v>24.58</v>
+        <v>24.73</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>24.11</v>
+        <v>24.23</v>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>25.07</v>
+        <v>25.25</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>25.01</v>
+        <v>25.19</v>
       </c>
       <c r="Q72" s="33" t="n">
-        <v>25.2</v>
+        <v>25.36</v>
       </c>
       <c r="R72" s="34" t="n">
-        <v>1.25</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="73">
@@ -5134,37 +5134,37 @@
         </is>
       </c>
       <c r="C73" s="25" t="n">
-        <v>23.46</v>
+        <v>22.6</v>
       </c>
       <c r="D73" s="25" t="n">
-        <v>22.37</v>
+        <v>21.95</v>
       </c>
       <c r="E73" s="26" t="n">
-        <v>21.46</v>
+        <v>21.41</v>
       </c>
       <c r="F73" s="27" t="n">
-        <v>21.68</v>
+        <v>21.55</v>
       </c>
       <c r="G73" s="27" t="n">
-        <v>22.24</v>
+        <v>21.88</v>
       </c>
       <c r="H73" s="28" t="n">
-        <v>21.15</v>
+        <v>21.23</v>
       </c>
       <c r="I73" s="29" t="n">
-        <v>20.59</v>
+        <v>20.9</v>
       </c>
       <c r="J73" s="29" t="n">
-        <v>20.06</v>
+        <v>20.58</v>
       </c>
       <c r="K73" s="30" t="n">
-        <v>20.85</v>
+        <v>21.04</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>19.94</v>
+        <v>20.5</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>18.85</v>
+        <v>19.85</v>
       </c>
       <c r="N73" s="20" t="inlineStr">
         <is>
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="O73" s="32" t="n">
-        <v>21.04</v>
+        <v>21.16</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>20.93</v>
+        <v>21.09</v>
       </c>
       <c r="Q73" s="33" t="n">
-        <v>21.13</v>
+        <v>21.23</v>
       </c>
       <c r="R73" s="34" t="n">
-        <v>2.03</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="74">
@@ -5196,37 +5196,37 @@
         </is>
       </c>
       <c r="C74" s="25" t="n">
-        <v>242.57</v>
+        <v>246.73</v>
       </c>
       <c r="D74" s="25" t="n">
-        <v>239.87</v>
+        <v>242.63</v>
       </c>
       <c r="E74" s="26" t="n">
-        <v>237.61</v>
+        <v>239.2</v>
       </c>
       <c r="F74" s="27" t="n">
-        <v>238.83</v>
+        <v>240.33</v>
       </c>
       <c r="G74" s="27" t="n">
-        <v>239.87</v>
+        <v>242.27</v>
       </c>
       <c r="H74" s="28" t="n">
-        <v>237.17</v>
+        <v>238.17</v>
       </c>
       <c r="I74" s="29" t="n">
-        <v>236.13</v>
+        <v>236.23</v>
       </c>
       <c r="J74" s="29" t="n">
-        <v>234.47</v>
+        <v>234.07</v>
       </c>
       <c r="K74" s="30" t="n">
-        <v>236.09</v>
+        <v>236.9</v>
       </c>
       <c r="L74" s="31" t="n">
-        <v>233.83</v>
+        <v>233.47</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>231.13</v>
+        <v>229.37</v>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
@@ -5234,16 +5234,16 @@
         </is>
       </c>
       <c r="O74" s="32" t="n">
-        <v>236.74</v>
+        <v>237.69</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>236.3</v>
+        <v>237.22</v>
       </c>
       <c r="Q74" s="33" t="n">
-        <v>237.8</v>
-      </c>
-      <c r="R74" s="36" t="n">
-        <v>-0.25</v>
+        <v>238.4</v>
+      </c>
+      <c r="R74" s="34" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="75">
@@ -5258,54 +5258,54 @@
         </is>
       </c>
       <c r="C75" s="25" t="n">
-        <v>16.67</v>
+        <v>16.58</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>16.34</v>
+        <v>16.24</v>
       </c>
       <c r="E75" s="26" t="n">
-        <v>16.07</v>
+        <v>15.96</v>
       </c>
       <c r="F75" s="27" t="n">
-        <v>16.16</v>
+        <v>15.97</v>
       </c>
       <c r="G75" s="27" t="n">
-        <v>16.32</v>
+        <v>16.17</v>
       </c>
       <c r="H75" s="28" t="n">
-        <v>15.99</v>
+        <v>15.83</v>
       </c>
       <c r="I75" s="29" t="n">
-        <v>15.83</v>
+        <v>15.63</v>
       </c>
       <c r="J75" s="29" t="n">
-        <v>15.66</v>
+        <v>15.49</v>
       </c>
       <c r="K75" s="30" t="n">
-        <v>15.88</v>
+        <v>15.76</v>
       </c>
       <c r="L75" s="31" t="n">
-        <v>15.61</v>
+        <v>15.48</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="N75" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>15.14</v>
+      </c>
+      <c r="N75" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O75" s="32" t="n">
-        <v>15.95</v>
+        <v>15.81</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>15.91</v>
+        <v>15.79</v>
       </c>
       <c r="Q75" s="33" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="R75" s="34" t="n">
-        <v>0.19</v>
+        <v>15.77</v>
+      </c>
+      <c r="R75" s="35" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="76">
@@ -5320,37 +5320,37 @@
         </is>
       </c>
       <c r="C76" s="25" t="n">
-        <v>35.79</v>
+        <v>42.3</v>
       </c>
       <c r="D76" s="25" t="n">
-        <v>34.77</v>
+        <v>39.32</v>
       </c>
       <c r="E76" s="26" t="n">
-        <v>33.92</v>
+        <v>36.82</v>
       </c>
       <c r="F76" s="27" t="n">
-        <v>34.44</v>
+        <v>38.35</v>
       </c>
       <c r="G76" s="27" t="n">
-        <v>34.8</v>
+        <v>39.41</v>
       </c>
       <c r="H76" s="28" t="n">
-        <v>33.78</v>
+        <v>36.43</v>
       </c>
       <c r="I76" s="29" t="n">
-        <v>33.42</v>
+        <v>35.37</v>
       </c>
       <c r="J76" s="29" t="n">
-        <v>32.76</v>
+        <v>33.45</v>
       </c>
       <c r="K76" s="30" t="n">
-        <v>33.34</v>
+        <v>35.16</v>
       </c>
       <c r="L76" s="31" t="n">
-        <v>32.49</v>
+        <v>32.66</v>
       </c>
       <c r="M76" s="31" t="n">
-        <v>31.47</v>
+        <v>29.68</v>
       </c>
       <c r="N76" s="20" t="inlineStr">
         <is>
@@ -5358,16 +5358,16 @@
         </is>
       </c>
       <c r="O76" s="32" t="n">
-        <v>33.6</v>
+        <v>35.91</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>33.42</v>
+        <v>35.39</v>
       </c>
       <c r="Q76" s="33" t="n">
-        <v>34.08</v>
+        <v>37.3</v>
       </c>
       <c r="R76" s="34" t="n">
-        <v>3.15</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5382,37 +5382,37 @@
         </is>
       </c>
       <c r="C77" s="25" t="n">
-        <v>27.63</v>
+        <v>27.83</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>27.25</v>
+        <v>27.43</v>
       </c>
       <c r="E77" s="26" t="n">
-        <v>26.94</v>
+        <v>27.09</v>
       </c>
       <c r="F77" s="27" t="n">
-        <v>27.03</v>
+        <v>27.11</v>
       </c>
       <c r="G77" s="27" t="n">
-        <v>27.21</v>
+        <v>27.35</v>
       </c>
       <c r="H77" s="28" t="n">
-        <v>26.83</v>
+        <v>26.95</v>
       </c>
       <c r="I77" s="29" t="n">
-        <v>26.65</v>
+        <v>26.71</v>
       </c>
       <c r="J77" s="29" t="n">
-        <v>26.45</v>
+        <v>26.55</v>
       </c>
       <c r="K77" s="30" t="n">
-        <v>26.72</v>
+        <v>26.87</v>
       </c>
       <c r="L77" s="31" t="n">
-        <v>26.41</v>
+        <v>26.53</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>26.03</v>
+        <v>26.13</v>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
@@ -5420,16 +5420,16 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>26.79</v>
+        <v>26.92</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>26.75</v>
+        <v>26.9</v>
       </c>
       <c r="Q77" s="33" t="n">
-        <v>26.84</v>
+        <v>26.88</v>
       </c>
       <c r="R77" s="34" t="n">
-        <v>0.37</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="78">
@@ -5444,37 +5444,37 @@
         </is>
       </c>
       <c r="C78" s="25" t="n">
-        <v>49.24</v>
+        <v>45.94</v>
       </c>
       <c r="D78" s="25" t="n">
-        <v>46.16</v>
+        <v>44.74</v>
       </c>
       <c r="E78" s="26" t="n">
-        <v>43.58</v>
+        <v>43.74</v>
       </c>
       <c r="F78" s="27" t="n">
-        <v>44.7</v>
+        <v>43.84</v>
       </c>
       <c r="G78" s="27" t="n">
-        <v>46.02</v>
+        <v>44.52</v>
       </c>
       <c r="H78" s="28" t="n">
-        <v>42.94</v>
+        <v>43.32</v>
       </c>
       <c r="I78" s="29" t="n">
-        <v>41.62</v>
+        <v>42.64</v>
       </c>
       <c r="J78" s="29" t="n">
-        <v>39.86</v>
+        <v>42.12</v>
       </c>
       <c r="K78" s="30" t="n">
-        <v>41.86</v>
+        <v>43.06</v>
       </c>
       <c r="L78" s="31" t="n">
-        <v>39.28</v>
+        <v>42.06</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>36.2</v>
+        <v>40.86</v>
       </c>
       <c r="N78" s="20" t="inlineStr">
         <is>
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>42.52</v>
+        <v>43.24</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>42.1</v>
+        <v>43.16</v>
       </c>
       <c r="Q78" s="33" t="n">
-        <v>43.38</v>
-      </c>
-      <c r="R78" s="34" t="n">
-        <v>4.53</v>
+        <v>43.16</v>
+      </c>
+      <c r="R78" s="35" t="n">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="79">
@@ -5506,37 +5506,37 @@
         </is>
       </c>
       <c r="C79" s="25" t="n">
-        <v>5.64</v>
+        <v>5.68</v>
       </c>
       <c r="D79" s="25" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="E79" s="26" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="F79" s="27" t="n">
         <v>5.57</v>
       </c>
-      <c r="E79" s="26" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="F79" s="27" t="n">
-        <v>5.55</v>
-      </c>
       <c r="G79" s="27" t="n">
-        <v>5.57</v>
+        <v>5.6</v>
       </c>
       <c r="H79" s="28" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="I79" s="29" t="n">
         <v>5.5</v>
       </c>
-      <c r="I79" s="29" t="n">
-        <v>5.48</v>
-      </c>
       <c r="J79" s="29" t="n">
-        <v>5.43</v>
+        <v>5.46</v>
       </c>
       <c r="K79" s="30" t="n">
-        <v>5.48</v>
+        <v>5.52</v>
       </c>
       <c r="L79" s="31" t="n">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="M79" s="31" t="n">
-        <v>5.35</v>
+        <v>5.39</v>
       </c>
       <c r="N79" s="20" t="inlineStr">
         <is>
@@ -5544,16 +5544,16 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>5.49</v>
+        <v>5.53</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>5.48</v>
+        <v>5.52</v>
       </c>
       <c r="Q79" s="33" t="n">
-        <v>5.52</v>
+        <v>5.53</v>
       </c>
       <c r="R79" s="34" t="n">
-        <v>1.1</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="80">
@@ -5568,54 +5568,54 @@
         </is>
       </c>
       <c r="C80" s="25" t="n">
-        <v>18.7</v>
+        <v>18.86</v>
       </c>
       <c r="D80" s="25" t="n">
-        <v>18.53</v>
+        <v>18.64</v>
       </c>
       <c r="E80" s="26" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="F80" s="27" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="G80" s="27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H80" s="28" t="n">
         <v>18.38</v>
       </c>
-      <c r="F80" s="27" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="G80" s="27" t="n">
-        <v>18.49</v>
-      </c>
-      <c r="H80" s="28" t="n">
-        <v>18.32</v>
-      </c>
       <c r="I80" s="29" t="n">
-        <v>18.21</v>
+        <v>18.25</v>
       </c>
       <c r="J80" s="29" t="n">
-        <v>18.15</v>
+        <v>18.16</v>
       </c>
       <c r="K80" s="30" t="n">
-        <v>18.29</v>
+        <v>18.33</v>
       </c>
       <c r="L80" s="31" t="n">
         <v>18.14</v>
       </c>
       <c r="M80" s="31" t="n">
-        <v>17.97</v>
-      </c>
-      <c r="N80" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>17.92</v>
+      </c>
+      <c r="N80" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>18.31</v>
+        <v>18.36</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>18.3</v>
+        <v>18.35</v>
       </c>
       <c r="Q80" s="33" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="R80" s="36" t="n">
-        <v>-0.33</v>
+        <v>18.35</v>
+      </c>
+      <c r="R80" s="34" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="81">
@@ -5630,37 +5630,37 @@
         </is>
       </c>
       <c r="C81" s="25" t="n">
-        <v>83.89</v>
+        <v>81.62</v>
       </c>
       <c r="D81" s="25" t="n">
-        <v>81.64</v>
+        <v>80.62</v>
       </c>
       <c r="E81" s="26" t="n">
-        <v>79.75</v>
+        <v>79.78</v>
       </c>
       <c r="F81" s="27" t="n">
-        <v>80.5</v>
+        <v>80.33</v>
       </c>
       <c r="G81" s="27" t="n">
-        <v>81.5</v>
+        <v>80.67</v>
       </c>
       <c r="H81" s="28" t="n">
-        <v>79.25</v>
+        <v>79.67</v>
       </c>
       <c r="I81" s="29" t="n">
-        <v>78.25</v>
+        <v>79.33</v>
       </c>
       <c r="J81" s="29" t="n">
-        <v>77</v>
+        <v>78.67</v>
       </c>
       <c r="K81" s="30" t="n">
-        <v>78.5</v>
+        <v>79.22</v>
       </c>
       <c r="L81" s="31" t="n">
-        <v>76.61</v>
+        <v>78.38</v>
       </c>
       <c r="M81" s="31" t="n">
-        <v>74.36</v>
+        <v>77.38</v>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
@@ -5668,16 +5668,16 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>78.95999999999999</v>
+        <v>79.48</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>78.67</v>
+        <v>79.3</v>
       </c>
       <c r="Q81" s="33" t="n">
-        <v>79.5</v>
+        <v>80</v>
       </c>
       <c r="R81" s="34" t="n">
-        <v>1.66</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="82">
@@ -5695,10 +5695,10 @@
         <v>4.88</v>
       </c>
       <c r="D82" s="25" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="E82" s="26" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="F82" s="27" t="n">
         <v>4.74</v>
@@ -5707,22 +5707,22 @@
         <v>4.78</v>
       </c>
       <c r="H82" s="28" t="n">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="I82" s="29" t="n">
-        <v>4.64</v>
+        <v>4.66</v>
       </c>
       <c r="J82" s="29" t="n">
-        <v>4.58</v>
+        <v>4.62</v>
       </c>
       <c r="K82" s="30" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
       <c r="L82" s="31" t="n">
-        <v>4.56</v>
+        <v>4.62</v>
       </c>
       <c r="M82" s="31" t="n">
-        <v>4.46</v>
+        <v>4.54</v>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
@@ -5730,16 +5730,16 @@
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>4.65</v>
+        <v>4.69</v>
       </c>
       <c r="Q82" s="33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R82" s="34" t="n">
-        <v>1.73</v>
+        <v>4.69</v>
+      </c>
+      <c r="R82" s="35" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="83">
@@ -5754,37 +5754,37 @@
         </is>
       </c>
       <c r="C83" s="25" t="n">
-        <v>64.73</v>
+        <v>64.64</v>
       </c>
       <c r="D83" s="25" t="n">
-        <v>63.63</v>
+        <v>63.69</v>
       </c>
       <c r="E83" s="26" t="n">
-        <v>62.71</v>
+        <v>62.89</v>
       </c>
       <c r="F83" s="27" t="n">
-        <v>63.15</v>
+        <v>63.08</v>
       </c>
       <c r="G83" s="27" t="n">
-        <v>63.6</v>
+        <v>63.57</v>
       </c>
       <c r="H83" s="28" t="n">
-        <v>62.5</v>
+        <v>62.62</v>
       </c>
       <c r="I83" s="29" t="n">
-        <v>62.05</v>
+        <v>62.13</v>
       </c>
       <c r="J83" s="29" t="n">
-        <v>61.4</v>
+        <v>61.67</v>
       </c>
       <c r="K83" s="30" t="n">
-        <v>62.09</v>
+        <v>62.36</v>
       </c>
       <c r="L83" s="31" t="n">
-        <v>61.17</v>
+        <v>61.56</v>
       </c>
       <c r="M83" s="31" t="n">
-        <v>60.07</v>
+        <v>60.61</v>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
@@ -5792,16 +5792,16 @@
         </is>
       </c>
       <c r="O83" s="32" t="n">
-        <v>62.34</v>
+        <v>62.52</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>62.18</v>
+        <v>62.43</v>
       </c>
       <c r="Q83" s="33" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="R83" s="34" t="n">
-        <v>1.05</v>
+        <v>62.6</v>
+      </c>
+      <c r="R83" s="35" t="n">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="84">
@@ -5816,54 +5816,54 @@
         </is>
       </c>
       <c r="C84" s="25" t="n">
-        <v>39.97</v>
+        <v>39.85</v>
       </c>
       <c r="D84" s="25" t="n">
-        <v>39.31</v>
+        <v>39.41</v>
       </c>
       <c r="E84" s="26" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="F84" s="27" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="G84" s="27" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="H84" s="28" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="I84" s="29" t="n">
         <v>38.75</v>
       </c>
-      <c r="F84" s="27" t="n">
-        <v>39.05</v>
-      </c>
-      <c r="G84" s="27" t="n">
-        <v>39.31</v>
-      </c>
-      <c r="H84" s="28" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="I84" s="29" t="n">
-        <v>38.39</v>
-      </c>
       <c r="J84" s="29" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="K84" s="30" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="L84" s="31" t="n">
+        <v>38.43</v>
+      </c>
+      <c r="M84" s="31" t="n">
         <v>37.99</v>
       </c>
-      <c r="K84" s="30" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="L84" s="31" t="n">
-        <v>37.83</v>
-      </c>
-      <c r="M84" s="31" t="n">
-        <v>37.17</v>
-      </c>
       <c r="N84" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>38.54</v>
+        <v>38.89</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>38.44</v>
+        <v>38.83</v>
       </c>
       <c r="Q84" s="33" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="R84" s="34" t="n">
-        <v>0.99</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="85">
@@ -5878,54 +5878,54 @@
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>95.28</v>
+        <v>95.8</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>94.43000000000001</v>
+        <v>94.75</v>
       </c>
       <c r="E85" s="26" t="n">
-        <v>93.70999999999999</v>
+        <v>93.87</v>
       </c>
       <c r="F85" s="27" t="n">
-        <v>93.98</v>
+        <v>94.02</v>
       </c>
       <c r="G85" s="27" t="n">
-        <v>94.37</v>
+        <v>94.58</v>
       </c>
       <c r="H85" s="28" t="n">
-        <v>93.52</v>
+        <v>93.53</v>
       </c>
       <c r="I85" s="29" t="n">
-        <v>93.13</v>
+        <v>92.97</v>
       </c>
       <c r="J85" s="29" t="n">
-        <v>92.67</v>
+        <v>92.48</v>
       </c>
       <c r="K85" s="30" t="n">
-        <v>93.23999999999999</v>
+        <v>93.28</v>
       </c>
       <c r="L85" s="31" t="n">
-        <v>92.52</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="M85" s="31" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="N85" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>91.34999999999999</v>
+      </c>
+      <c r="N85" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>93.41</v>
+        <v>93.45</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>93.3</v>
+        <v>93.36</v>
       </c>
       <c r="Q85" s="33" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="R85" s="34" t="n">
-        <v>0.65</v>
+        <v>93.45</v>
+      </c>
+      <c r="R85" s="35" t="n">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="86">
@@ -5940,54 +5940,54 @@
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>17.27</v>
+        <v>17.73</v>
       </c>
       <c r="D86" s="25" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="E86" s="26" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="F86" s="27" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G86" s="27" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="H86" s="28" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="I86" s="29" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="J86" s="29" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="K86" s="30" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L86" s="31" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="M86" s="31" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="N86" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O86" s="32" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="P86" s="32" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="Q86" s="33" t="n">
         <v>17.06</v>
       </c>
-      <c r="E86" s="26" t="n">
-        <v>16.88</v>
-      </c>
-      <c r="F86" s="27" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="G86" s="27" t="n">
-        <v>17</v>
-      </c>
-      <c r="H86" s="28" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="I86" s="29" t="n">
-        <v>16.66</v>
-      </c>
-      <c r="J86" s="29" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="K86" s="30" t="n">
-        <v>16.77</v>
-      </c>
-      <c r="L86" s="31" t="n">
-        <v>16.59</v>
-      </c>
-      <c r="M86" s="31" t="n">
-        <v>16.38</v>
-      </c>
-      <c r="N86" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O86" s="32" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="P86" s="32" t="n">
-        <v>16.78</v>
-      </c>
-      <c r="Q86" s="33" t="n">
-        <v>16.73</v>
-      </c>
-      <c r="R86" s="36" t="n">
-        <v>-0.36</v>
+      <c r="R86" s="34" t="n">
+        <v>1.97</v>
       </c>
     </row>
     <row r="87">
@@ -6002,54 +6002,54 @@
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>123.27</v>
+        <v>123.93</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>121.87</v>
+        <v>122.43</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>120.69</v>
+        <v>121.17</v>
       </c>
       <c r="F87" s="27" t="n">
-        <v>120.8</v>
+        <v>121.8</v>
       </c>
       <c r="G87" s="27" t="n">
-        <v>121.6</v>
+        <v>122.4</v>
       </c>
       <c r="H87" s="28" t="n">
-        <v>120.2</v>
+        <v>120.9</v>
       </c>
       <c r="I87" s="29" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="J87" s="29" t="n">
         <v>119.4</v>
       </c>
-      <c r="J87" s="29" t="n">
-        <v>118.8</v>
-      </c>
       <c r="K87" s="30" t="n">
-        <v>119.91</v>
+        <v>120.33</v>
       </c>
       <c r="L87" s="31" t="n">
-        <v>118.73</v>
+        <v>119.07</v>
       </c>
       <c r="M87" s="31" t="n">
-        <v>117.33</v>
-      </c>
-      <c r="N87" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>117.57</v>
+      </c>
+      <c r="N87" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>120.11</v>
+        <v>120.67</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>120.02</v>
+        <v>120.45</v>
       </c>
       <c r="Q87" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="R87" s="36" t="n">
-        <v>-0.17</v>
+        <v>121.2</v>
+      </c>
+      <c r="R87" s="34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -6064,37 +6064,37 @@
         </is>
       </c>
       <c r="C88" s="25" t="n">
-        <v>60.94</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="D88" s="25" t="n">
-        <v>59.74</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="E88" s="26" t="n">
-        <v>58.74</v>
+        <v>61.77</v>
       </c>
       <c r="F88" s="27" t="n">
-        <v>59.17</v>
+        <v>62.7</v>
       </c>
       <c r="G88" s="27" t="n">
-        <v>59.68</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H88" s="28" t="n">
-        <v>58.48</v>
+        <v>60.85</v>
       </c>
       <c r="I88" s="29" t="n">
-        <v>57.97</v>
+        <v>59.15</v>
       </c>
       <c r="J88" s="29" t="n">
-        <v>57.28</v>
+        <v>57.3</v>
       </c>
       <c r="K88" s="30" t="n">
-        <v>58.06</v>
+        <v>59.78</v>
       </c>
       <c r="L88" s="31" t="n">
-        <v>57.06</v>
+        <v>56.81</v>
       </c>
       <c r="M88" s="31" t="n">
-        <v>55.86</v>
+        <v>53.26</v>
       </c>
       <c r="N88" s="20" t="inlineStr">
         <is>
@@ -6102,16 +6102,16 @@
         </is>
       </c>
       <c r="O88" s="32" t="n">
-        <v>58.32</v>
+        <v>60.45</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>58.16</v>
+        <v>60.06</v>
       </c>
       <c r="Q88" s="33" t="n">
-        <v>58.65</v>
+        <v>61</v>
       </c>
       <c r="R88" s="34" t="n">
-        <v>0.6</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="89">
@@ -6126,54 +6126,54 @@
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>10.31</v>
+        <v>10.27</v>
       </c>
       <c r="D89" s="25" t="n">
-        <v>10.02</v>
+        <v>10.05</v>
       </c>
       <c r="E89" s="26" t="n">
-        <v>9.779999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F89" s="27" t="n">
-        <v>9.92</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G89" s="27" t="n">
-        <v>10.02</v>
+        <v>9.99</v>
       </c>
       <c r="H89" s="28" t="n">
-        <v>9.73</v>
+        <v>9.77</v>
       </c>
       <c r="I89" s="29" t="n">
-        <v>9.630000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="J89" s="29" t="n">
-        <v>9.44</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K89" s="30" t="n">
-        <v>9.609999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="L89" s="31" t="n">
-        <v>9.369999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M89" s="31" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="N89" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>9.33</v>
+      </c>
+      <c r="N89" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O89" s="32" t="n">
-        <v>9.68</v>
+        <v>9.76</v>
       </c>
       <c r="P89" s="32" t="n">
-        <v>9.640000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="Q89" s="33" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="R89" s="34" t="n">
-        <v>1.45</v>
+        <v>9.720000000000001</v>
+      </c>
+      <c r="R89" s="35" t="n">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="90">
@@ -6188,37 +6188,37 @@
         </is>
       </c>
       <c r="C90" s="25" t="n">
-        <v>20.05</v>
+        <v>22.02</v>
       </c>
       <c r="D90" s="25" t="n">
-        <v>19.01</v>
+        <v>20.34</v>
       </c>
       <c r="E90" s="26" t="n">
-        <v>18.14</v>
+        <v>18.93</v>
       </c>
       <c r="F90" s="27" t="n">
-        <v>18.38</v>
+        <v>19.41</v>
       </c>
       <c r="G90" s="27" t="n">
-        <v>18.9</v>
+        <v>20.19</v>
       </c>
       <c r="H90" s="28" t="n">
-        <v>17.86</v>
+        <v>18.51</v>
       </c>
       <c r="I90" s="29" t="n">
-        <v>17.34</v>
+        <v>17.73</v>
       </c>
       <c r="J90" s="29" t="n">
-        <v>16.82</v>
+        <v>16.83</v>
       </c>
       <c r="K90" s="30" t="n">
-        <v>17.56</v>
+        <v>17.99</v>
       </c>
       <c r="L90" s="31" t="n">
-        <v>16.69</v>
+        <v>16.58</v>
       </c>
       <c r="M90" s="31" t="n">
-        <v>15.65</v>
+        <v>14.9</v>
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
@@ -6226,16 +6226,16 @@
         </is>
       </c>
       <c r="O90" s="32" t="n">
-        <v>17.75</v>
+        <v>18.32</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>17.64</v>
+        <v>18.12</v>
       </c>
       <c r="Q90" s="33" t="n">
-        <v>17.87</v>
+        <v>18.62</v>
       </c>
       <c r="R90" s="34" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="91">
@@ -6250,37 +6250,37 @@
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>19.74</v>
+        <v>19.5</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>19.19</v>
+        <v>19.18</v>
       </c>
       <c r="E91" s="26" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="F91" s="27" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="G91" s="27" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="H91" s="28" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="I91" s="29" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="J91" s="29" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="K91" s="30" t="n">
         <v>18.73</v>
       </c>
-      <c r="F91" s="27" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="G91" s="27" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="H91" s="28" t="n">
-        <v>18.65</v>
-      </c>
-      <c r="I91" s="29" t="n">
-        <v>18.44</v>
-      </c>
-      <c r="J91" s="29" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="K91" s="30" t="n">
-        <v>18.42</v>
-      </c>
       <c r="L91" s="31" t="n">
-        <v>17.96</v>
+        <v>18.46</v>
       </c>
       <c r="M91" s="31" t="n">
-        <v>17.41</v>
+        <v>18.14</v>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
@@ -6288,16 +6288,16 @@
         </is>
       </c>
       <c r="O91" s="32" t="n">
-        <v>18.56</v>
+        <v>18.76</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>18.46</v>
+        <v>18.76</v>
       </c>
       <c r="Q91" s="33" t="n">
-        <v>18.79</v>
-      </c>
-      <c r="R91" s="34" t="n">
-        <v>2.01</v>
+        <v>18.66</v>
+      </c>
+      <c r="R91" s="35" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6312,37 +6312,37 @@
         </is>
       </c>
       <c r="C92" s="25" t="n">
-        <v>32.63</v>
+        <v>31.81</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>31.55</v>
+        <v>31.27</v>
       </c>
       <c r="E92" s="26" t="n">
-        <v>30.64</v>
+        <v>30.82</v>
       </c>
       <c r="F92" s="27" t="n">
-        <v>31.2</v>
+        <v>30.89</v>
       </c>
       <c r="G92" s="27" t="n">
-        <v>31.58</v>
+        <v>31.19</v>
       </c>
       <c r="H92" s="28" t="n">
-        <v>30.5</v>
+        <v>30.65</v>
       </c>
       <c r="I92" s="29" t="n">
-        <v>30.12</v>
+        <v>30.35</v>
       </c>
       <c r="J92" s="29" t="n">
-        <v>29.42</v>
+        <v>30.11</v>
       </c>
       <c r="K92" s="30" t="n">
-        <v>30.04</v>
+        <v>30.52</v>
       </c>
       <c r="L92" s="31" t="n">
-        <v>29.13</v>
+        <v>30.07</v>
       </c>
       <c r="M92" s="31" t="n">
-        <v>28.05</v>
+        <v>29.53</v>
       </c>
       <c r="N92" s="20" t="inlineStr">
         <is>
@@ -6350,16 +6350,16 @@
         </is>
       </c>
       <c r="O92" s="32" t="n">
-        <v>30.31</v>
+        <v>30.6</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>30.12</v>
+        <v>30.56</v>
       </c>
       <c r="Q92" s="33" t="n">
-        <v>30.82</v>
-      </c>
-      <c r="R92" s="34" t="n">
-        <v>3.56</v>
+        <v>30.6</v>
+      </c>
+      <c r="R92" s="35" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="93">
@@ -6374,37 +6374,37 @@
         </is>
       </c>
       <c r="C93" s="25" t="n">
-        <v>21.3</v>
+        <v>21.65</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>20.98</v>
+        <v>21.31</v>
       </c>
       <c r="E93" s="26" t="n">
-        <v>20.71</v>
+        <v>21.03</v>
       </c>
       <c r="F93" s="27" t="n">
-        <v>20.85</v>
+        <v>21.15</v>
       </c>
       <c r="G93" s="27" t="n">
-        <v>20.98</v>
+        <v>21.29</v>
       </c>
       <c r="H93" s="28" t="n">
-        <v>20.66</v>
+        <v>20.95</v>
       </c>
       <c r="I93" s="29" t="n">
-        <v>20.53</v>
+        <v>20.81</v>
       </c>
       <c r="J93" s="29" t="n">
-        <v>20.34</v>
+        <v>20.61</v>
       </c>
       <c r="K93" s="30" t="n">
-        <v>20.53</v>
+        <v>20.83</v>
       </c>
       <c r="L93" s="31" t="n">
-        <v>20.26</v>
+        <v>20.55</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>19.94</v>
+        <v>20.21</v>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
@@ -6412,16 +6412,16 @@
         </is>
       </c>
       <c r="O93" s="32" t="n">
-        <v>20.61</v>
+        <v>20.91</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>20.56</v>
+        <v>20.86</v>
       </c>
       <c r="Q93" s="33" t="n">
-        <v>20.73</v>
+        <v>21</v>
       </c>
       <c r="R93" s="34" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="94">
@@ -6436,37 +6436,37 @@
         </is>
       </c>
       <c r="C94" s="25" t="n">
-        <v>29.24</v>
+        <v>30.24</v>
       </c>
       <c r="D94" s="25" t="n">
-        <v>28.62</v>
+        <v>29.36</v>
       </c>
       <c r="E94" s="26" t="n">
-        <v>28.1</v>
+        <v>28.63</v>
       </c>
       <c r="F94" s="27" t="n">
-        <v>28.18</v>
+        <v>28.99</v>
       </c>
       <c r="G94" s="27" t="n">
-        <v>28.52</v>
+        <v>29.35</v>
       </c>
       <c r="H94" s="28" t="n">
-        <v>27.9</v>
+        <v>28.47</v>
       </c>
       <c r="I94" s="29" t="n">
-        <v>27.56</v>
+        <v>28.11</v>
       </c>
       <c r="J94" s="29" t="n">
-        <v>27.28</v>
+        <v>27.59</v>
       </c>
       <c r="K94" s="30" t="n">
-        <v>27.76</v>
+        <v>28.13</v>
       </c>
       <c r="L94" s="31" t="n">
-        <v>27.24</v>
+        <v>27.4</v>
       </c>
       <c r="M94" s="31" t="n">
-        <v>26.62</v>
+        <v>26.52</v>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="O94" s="32" t="n">
-        <v>27.85</v>
+        <v>28.33</v>
       </c>
       <c r="P94" s="32" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="Q94" s="33" t="n">
-        <v>27.84</v>
+        <v>28.64</v>
       </c>
       <c r="R94" s="34" t="n">
-        <v>1.02</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="95">
@@ -6498,37 +6498,37 @@
         </is>
       </c>
       <c r="C95" s="25" t="n">
-        <v>172.85</v>
+        <v>176.43</v>
       </c>
       <c r="D95" s="25" t="n">
-        <v>171.15</v>
+        <v>173.63</v>
       </c>
       <c r="E95" s="26" t="n">
-        <v>169.73</v>
+        <v>171.28</v>
       </c>
       <c r="F95" s="27" t="n">
-        <v>170</v>
+        <v>171.9</v>
       </c>
       <c r="G95" s="27" t="n">
-        <v>170.9</v>
+        <v>173.3</v>
       </c>
       <c r="H95" s="28" t="n">
-        <v>169.2</v>
+        <v>170.5</v>
       </c>
       <c r="I95" s="29" t="n">
-        <v>168.3</v>
+        <v>169.1</v>
       </c>
       <c r="J95" s="29" t="n">
-        <v>167.5</v>
+        <v>167.7</v>
       </c>
       <c r="K95" s="30" t="n">
-        <v>168.77</v>
+        <v>169.72</v>
       </c>
       <c r="L95" s="31" t="n">
-        <v>167.35</v>
+        <v>167.37</v>
       </c>
       <c r="M95" s="31" t="n">
-        <v>165.65</v>
+        <v>164.57</v>
       </c>
       <c r="N95" s="20" t="inlineStr">
         <is>
@@ -6536,16 +6536,16 @@
         </is>
       </c>
       <c r="O95" s="32" t="n">
-        <v>169.05</v>
+        <v>170.22</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>168.91</v>
+        <v>169.93</v>
       </c>
       <c r="Q95" s="33" t="n">
-        <v>169.1</v>
+        <v>170.5</v>
       </c>
       <c r="R95" s="34" t="n">
-        <v>0.24</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="96">
@@ -6560,54 +6560,54 @@
         </is>
       </c>
       <c r="C96" s="25" t="n">
-        <v>14.43</v>
+        <v>14.63</v>
       </c>
       <c r="D96" s="25" t="n">
-        <v>14.27</v>
+        <v>14.36</v>
       </c>
       <c r="E96" s="26" t="n">
         <v>14.13</v>
       </c>
       <c r="F96" s="27" t="n">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="G96" s="27" t="n">
-        <v>14.23</v>
+        <v>14.28</v>
       </c>
       <c r="H96" s="28" t="n">
-        <v>14.07</v>
+        <v>14.01</v>
       </c>
       <c r="I96" s="29" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="J96" s="29" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="K96" s="30" t="n">
         <v>13.98</v>
       </c>
-      <c r="J96" s="29" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="K96" s="30" t="n">
-        <v>14.05</v>
-      </c>
       <c r="L96" s="31" t="n">
-        <v>13.91</v>
+        <v>13.75</v>
       </c>
       <c r="M96" s="31" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="N96" s="35" t="inlineStr">
+        <v>13.48</v>
+      </c>
+      <c r="N96" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>14.07</v>
+        <v>14.01</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>14.06</v>
+        <v>14</v>
       </c>
       <c r="Q96" s="33" t="n">
-        <v>14.04</v>
-      </c>
-      <c r="R96" s="36" t="n">
-        <v>-1.2</v>
+        <v>13.92</v>
+      </c>
+      <c r="R96" s="35" t="n">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="97">
@@ -6622,37 +6622,37 @@
         </is>
       </c>
       <c r="C97" s="25" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D97" s="25" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="E97" s="26" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="F97" s="27" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="G97" s="27" t="n">
         <v>21.5</v>
       </c>
-      <c r="D97" s="25" t="n">
-        <v>21.12</v>
-      </c>
-      <c r="E97" s="26" t="n">
-        <v>20.81</v>
-      </c>
-      <c r="F97" s="27" t="n">
-        <v>20.76</v>
-      </c>
-      <c r="G97" s="27" t="n">
-        <v>21.02</v>
-      </c>
       <c r="H97" s="28" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="I97" s="29" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="J97" s="29" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="K97" s="30" t="n">
         <v>20.64</v>
       </c>
-      <c r="I97" s="29" t="n">
-        <v>20.38</v>
-      </c>
-      <c r="J97" s="29" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="K97" s="30" t="n">
-        <v>20.59</v>
-      </c>
       <c r="L97" s="31" t="n">
-        <v>20.28</v>
+        <v>20.1</v>
       </c>
       <c r="M97" s="31" t="n">
-        <v>19.9</v>
+        <v>19.45</v>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
@@ -6660,16 +6660,16 @@
         </is>
       </c>
       <c r="O97" s="32" t="n">
-        <v>20.63</v>
+        <v>20.77</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>20.62</v>
+        <v>20.69</v>
       </c>
       <c r="Q97" s="33" t="n">
-        <v>20.51</v>
-      </c>
-      <c r="R97" s="36" t="n">
-        <v>-0.1</v>
+        <v>20.91</v>
+      </c>
+      <c r="R97" s="34" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="98">
@@ -6684,54 +6684,54 @@
         </is>
       </c>
       <c r="C98" s="25" t="n">
-        <v>17.24</v>
+        <v>16.92</v>
       </c>
       <c r="D98" s="25" t="n">
-        <v>16.75</v>
+        <v>16.69</v>
       </c>
       <c r="E98" s="26" t="n">
-        <v>16.34</v>
+        <v>16.5</v>
       </c>
       <c r="F98" s="27" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="G98" s="27" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="H98" s="28" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="I98" s="29" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="J98" s="29" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="K98" s="30" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="L98" s="31" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="M98" s="31" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="N98" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O98" s="32" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="P98" s="32" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="Q98" s="33" t="n">
         <v>16.5</v>
       </c>
-      <c r="G98" s="27" t="n">
-        <v>16.72</v>
-      </c>
-      <c r="H98" s="28" t="n">
-        <v>16.23</v>
-      </c>
-      <c r="I98" s="29" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="J98" s="29" t="n">
-        <v>15.74</v>
-      </c>
-      <c r="K98" s="30" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="L98" s="31" t="n">
-        <v>15.66</v>
-      </c>
-      <c r="M98" s="31" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="N98" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O98" s="32" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="P98" s="32" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="Q98" s="33" t="n">
-        <v>16.28</v>
-      </c>
       <c r="R98" s="34" t="n">
-        <v>2.01</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="99">
@@ -6746,54 +6746,54 @@
         </is>
       </c>
       <c r="C99" s="25" t="n">
-        <v>10.7</v>
+        <v>10.44</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>10.4</v>
+        <v>10.26</v>
       </c>
       <c r="E99" s="26" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="F99" s="27" t="n">
         <v>10.14</v>
       </c>
-      <c r="F99" s="27" t="n">
-        <v>10.2</v>
-      </c>
       <c r="G99" s="27" t="n">
-        <v>10.35</v>
+        <v>10.23</v>
       </c>
       <c r="H99" s="28" t="n">
         <v>10.05</v>
       </c>
       <c r="I99" s="29" t="n">
-        <v>9.9</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="J99" s="29" t="n">
-        <v>9.75</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="K99" s="30" t="n">
-        <v>9.98</v>
+        <v>10.01</v>
       </c>
       <c r="L99" s="31" t="n">
-        <v>9.720000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M99" s="31" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="N99" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>9.68</v>
+      </c>
+      <c r="N99" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O99" s="32" t="n">
-        <v>10.03</v>
+        <v>10.04</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="Q99" s="33" t="n">
         <v>10.04</v>
       </c>
       <c r="R99" s="34" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -6808,37 +6808,37 @@
         </is>
       </c>
       <c r="C100" s="25" t="n">
-        <v>26.71</v>
+        <v>27.1</v>
       </c>
       <c r="D100" s="25" t="n">
-        <v>26.27</v>
+        <v>26.64</v>
       </c>
       <c r="E100" s="26" t="n">
-        <v>25.9</v>
+        <v>26.26</v>
       </c>
       <c r="F100" s="27" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="G100" s="27" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="H100" s="28" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="I100" s="29" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="J100" s="29" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="K100" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="G100" s="27" t="n">
-        <v>26.22</v>
-      </c>
-      <c r="H100" s="28" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="I100" s="29" t="n">
-        <v>25.56</v>
-      </c>
-      <c r="J100" s="29" t="n">
-        <v>25.34</v>
-      </c>
-      <c r="K100" s="30" t="n">
-        <v>25.66</v>
-      </c>
       <c r="L100" s="31" t="n">
-        <v>25.29</v>
+        <v>25.62</v>
       </c>
       <c r="M100" s="31" t="n">
-        <v>24.85</v>
+        <v>25.16</v>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
@@ -6846,16 +6846,16 @@
         </is>
       </c>
       <c r="O100" s="32" t="n">
-        <v>25.74</v>
+        <v>26.12</v>
       </c>
       <c r="P100" s="32" t="n">
-        <v>25.69</v>
+        <v>26.04</v>
       </c>
       <c r="Q100" s="33" t="n">
-        <v>25.78</v>
+        <v>26.36</v>
       </c>
       <c r="R100" s="34" t="n">
-        <v>1.02</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="101">
@@ -6870,54 +6870,54 @@
         </is>
       </c>
       <c r="C101" s="25" t="n">
-        <v>17.69</v>
+        <v>17.21</v>
       </c>
       <c r="D101" s="25" t="n">
-        <v>17.41</v>
+        <v>17.1</v>
       </c>
       <c r="E101" s="26" t="n">
-        <v>17.18</v>
+        <v>17.01</v>
       </c>
       <c r="F101" s="27" t="n">
-        <v>17.15</v>
+        <v>17.05</v>
       </c>
       <c r="G101" s="27" t="n">
-        <v>17.33</v>
+        <v>17.1</v>
       </c>
       <c r="H101" s="28" t="n">
-        <v>17.05</v>
+        <v>16.99</v>
       </c>
       <c r="I101" s="29" t="n">
-        <v>16.87</v>
+        <v>16.94</v>
       </c>
       <c r="J101" s="29" t="n">
-        <v>16.77</v>
+        <v>16.88</v>
       </c>
       <c r="K101" s="30" t="n">
-        <v>17.02</v>
+        <v>16.94</v>
       </c>
       <c r="L101" s="31" t="n">
-        <v>16.79</v>
+        <v>16.85</v>
       </c>
       <c r="M101" s="31" t="n">
-        <v>16.51</v>
-      </c>
-      <c r="N101" s="35" t="inlineStr">
+        <v>16.74</v>
+      </c>
+      <c r="N101" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O101" s="32" t="n">
-        <v>17.05</v>
+        <v>16.97</v>
       </c>
       <c r="P101" s="32" t="n">
-        <v>17.04</v>
+        <v>16.95</v>
       </c>
       <c r="Q101" s="33" t="n">
-        <v>16.96</v>
-      </c>
-      <c r="R101" s="36" t="n">
-        <v>-0.82</v>
+        <v>17.01</v>
+      </c>
+      <c r="R101" s="34" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="102">
@@ -6932,54 +6932,54 @@
         </is>
       </c>
       <c r="C102" s="25" t="n">
-        <v>32.94</v>
+        <v>34.06</v>
       </c>
       <c r="D102" s="25" t="n">
-        <v>32.58</v>
+        <v>33.28</v>
       </c>
       <c r="E102" s="26" t="n">
-        <v>32.28</v>
+        <v>32.63</v>
       </c>
       <c r="F102" s="27" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="G102" s="27" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="H102" s="28" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="I102" s="29" t="n">
+        <v>32.01</v>
+      </c>
+      <c r="J102" s="29" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="K102" s="30" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="L102" s="31" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="M102" s="31" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="N102" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O102" s="32" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="P102" s="32" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="Q102" s="33" t="n">
         <v>32.4</v>
       </c>
-      <c r="G102" s="27" t="n">
-        <v>32.56</v>
-      </c>
-      <c r="H102" s="28" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="I102" s="29" t="n">
-        <v>32.04</v>
-      </c>
-      <c r="J102" s="29" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="K102" s="30" t="n">
-        <v>32.08</v>
-      </c>
-      <c r="L102" s="31" t="n">
-        <v>31.78</v>
-      </c>
-      <c r="M102" s="31" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="N102" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O102" s="32" t="n">
-        <v>32.15</v>
-      </c>
-      <c r="P102" s="32" t="n">
-        <v>32.11</v>
-      </c>
-      <c r="Q102" s="33" t="n">
-        <v>32.24</v>
-      </c>
       <c r="R102" s="34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="103">
@@ -6994,54 +6994,54 @@
         </is>
       </c>
       <c r="C103" s="25" t="n">
-        <v>16.36</v>
+        <v>16.06</v>
       </c>
       <c r="D103" s="25" t="n">
-        <v>15.95</v>
+        <v>15.82</v>
       </c>
       <c r="E103" s="26" t="n">
-        <v>15.61</v>
+        <v>15.62</v>
       </c>
       <c r="F103" s="27" t="n">
-        <v>15.66</v>
+        <v>15.68</v>
       </c>
       <c r="G103" s="27" t="n">
-        <v>15.88</v>
+        <v>15.79</v>
       </c>
       <c r="H103" s="28" t="n">
-        <v>15.47</v>
+        <v>15.55</v>
       </c>
       <c r="I103" s="29" t="n">
-        <v>15.25</v>
+        <v>15.44</v>
       </c>
       <c r="J103" s="29" t="n">
-        <v>15.06</v>
+        <v>15.31</v>
       </c>
       <c r="K103" s="30" t="n">
-        <v>15.38</v>
+        <v>15.48</v>
       </c>
       <c r="L103" s="31" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="M103" s="31" t="n">
         <v>15.04</v>
       </c>
-      <c r="M103" s="31" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="N103" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+      <c r="N103" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O103" s="32" t="n">
-        <v>15.44</v>
+        <v>15.53</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>15.41</v>
+        <v>15.5</v>
       </c>
       <c r="Q103" s="33" t="n">
-        <v>15.43</v>
+        <v>15.56</v>
       </c>
       <c r="R103" s="34" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="104">
@@ -7056,54 +7056,54 @@
         </is>
       </c>
       <c r="C104" s="25" t="n">
-        <v>75.63</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>74.13</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="E104" s="26" t="n">
-        <v>72.87</v>
+        <v>72.39</v>
       </c>
       <c r="F104" s="27" t="n">
-        <v>72.83</v>
+        <v>72.5</v>
       </c>
       <c r="G104" s="27" t="n">
-        <v>73.77</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H104" s="28" t="n">
-        <v>72.27</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="I104" s="29" t="n">
-        <v>71.33</v>
+        <v>71.75</v>
       </c>
       <c r="J104" s="29" t="n">
-        <v>70.77</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K104" s="30" t="n">
-        <v>72.03</v>
+        <v>71.97</v>
       </c>
       <c r="L104" s="31" t="n">
-        <v>70.77</v>
+        <v>71.34</v>
       </c>
       <c r="M104" s="31" t="n">
-        <v>69.27</v>
-      </c>
-      <c r="N104" s="35" t="inlineStr">
+        <v>70.59</v>
+      </c>
+      <c r="N104" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O104" s="32" t="n">
-        <v>72.20999999999999</v>
+        <v>72.09</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>72.15000000000001</v>
+        <v>72.02</v>
       </c>
       <c r="Q104" s="33" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="R104" s="36" t="n">
-        <v>-1.44</v>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="R104" s="34" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="105">
@@ -7118,54 +7118,54 @@
         </is>
       </c>
       <c r="C105" s="25" t="n">
-        <v>15</v>
+        <v>15.38</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>14.77</v>
+        <v>15.02</v>
       </c>
       <c r="E105" s="26" t="n">
-        <v>14.58</v>
+        <v>14.72</v>
       </c>
       <c r="F105" s="27" t="n">
         <v>14.68</v>
       </c>
       <c r="G105" s="27" t="n">
-        <v>14.77</v>
+        <v>14.92</v>
       </c>
       <c r="H105" s="28" t="n">
-        <v>14.54</v>
+        <v>14.56</v>
       </c>
       <c r="I105" s="29" t="n">
-        <v>14.45</v>
+        <v>14.32</v>
       </c>
       <c r="J105" s="29" t="n">
-        <v>14.31</v>
+        <v>14.2</v>
       </c>
       <c r="K105" s="30" t="n">
-        <v>14.45</v>
+        <v>14.52</v>
       </c>
       <c r="L105" s="31" t="n">
-        <v>14.26</v>
+        <v>14.22</v>
       </c>
       <c r="M105" s="31" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="N105" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>13.86</v>
+      </c>
+      <c r="N105" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>14.5</v>
+        <v>14.55</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>14.47</v>
+        <v>14.55</v>
       </c>
       <c r="Q105" s="33" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="R105" s="34" t="n">
-        <v>1.74</v>
+        <v>14.44</v>
+      </c>
+      <c r="R105" s="35" t="n">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="106">
@@ -7180,54 +7180,54 @@
         </is>
       </c>
       <c r="C106" s="25" t="n">
-        <v>21.15</v>
+        <v>21.73</v>
       </c>
       <c r="D106" s="25" t="n">
-        <v>19.2</v>
+        <v>20.02</v>
       </c>
       <c r="E106" s="26" t="n">
-        <v>17.56</v>
+        <v>18.58</v>
       </c>
       <c r="F106" s="27" t="n">
-        <v>18.14</v>
+        <v>18.77</v>
       </c>
       <c r="G106" s="27" t="n">
-        <v>19.04</v>
+        <v>19.72</v>
       </c>
       <c r="H106" s="28" t="n">
-        <v>17.09</v>
+        <v>18.01</v>
       </c>
       <c r="I106" s="29" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="J106" s="29" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="K106" s="30" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="L106" s="31" t="n">
         <v>16.19</v>
       </c>
-      <c r="J106" s="29" t="n">
-        <v>15.14</v>
-      </c>
-      <c r="K106" s="30" t="n">
-        <v>16.47</v>
-      </c>
-      <c r="L106" s="31" t="n">
-        <v>14.83</v>
-      </c>
       <c r="M106" s="31" t="n">
-        <v>12.88</v>
-      </c>
-      <c r="N106" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>14.48</v>
+      </c>
+      <c r="N106" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>16.86</v>
+        <v>17.88</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>16.62</v>
+        <v>17.76</v>
       </c>
       <c r="Q106" s="33" t="n">
-        <v>17.24</v>
+        <v>17.82</v>
       </c>
       <c r="R106" s="34" t="n">
-        <v>2.56</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="107">
@@ -7242,54 +7242,54 @@
         </is>
       </c>
       <c r="C107" s="25" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="D107" s="25" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="E107" s="26" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="F107" s="27" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="G107" s="27" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H107" s="28" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="I107" s="29" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="J107" s="29" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="K107" s="30" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="L107" s="31" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="M107" s="31" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="N107" s="35" t="inlineStr">
+        <v>2.3</v>
+      </c>
+      <c r="N107" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O107" s="32" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="P107" s="32" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q107" s="33" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R107" s="36" t="n">
-        <v>-1.22</v>
+        <v>2.41</v>
+      </c>
+      <c r="R107" s="35" t="n">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="108">
@@ -7304,37 +7304,37 @@
         </is>
       </c>
       <c r="C108" s="25" t="n">
-        <v>40.1</v>
+        <v>40.89</v>
       </c>
       <c r="D108" s="25" t="n">
-        <v>39.48</v>
+        <v>40.09</v>
       </c>
       <c r="E108" s="26" t="n">
-        <v>38.96</v>
+        <v>39.42</v>
       </c>
       <c r="F108" s="27" t="n">
-        <v>39.31</v>
+        <v>39.41</v>
       </c>
       <c r="G108" s="27" t="n">
-        <v>39.51</v>
+        <v>39.91</v>
       </c>
       <c r="H108" s="28" t="n">
-        <v>38.89</v>
+        <v>39.11</v>
       </c>
       <c r="I108" s="29" t="n">
-        <v>38.69</v>
+        <v>38.61</v>
       </c>
       <c r="J108" s="29" t="n">
-        <v>38.27</v>
+        <v>38.31</v>
       </c>
       <c r="K108" s="30" t="n">
-        <v>38.62</v>
+        <v>38.98</v>
       </c>
       <c r="L108" s="31" t="n">
-        <v>38.1</v>
+        <v>38.31</v>
       </c>
       <c r="M108" s="31" t="n">
-        <v>37.48</v>
+        <v>37.51</v>
       </c>
       <c r="N108" s="20" t="inlineStr">
         <is>
@@ -7342,16 +7342,16 @@
         </is>
       </c>
       <c r="O108" s="32" t="n">
-        <v>38.78</v>
+        <v>39.07</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>38.66</v>
+        <v>39.04</v>
       </c>
       <c r="Q108" s="33" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R108" s="34" t="n">
-        <v>1.14</v>
+        <v>38.92</v>
+      </c>
+      <c r="R108" s="35" t="n">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="109">
@@ -7366,54 +7366,54 @@
         </is>
       </c>
       <c r="C109" s="25" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="D109" s="25" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="D109" s="25" t="n">
-        <v>8.27</v>
-      </c>
       <c r="E109" s="26" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="F109" s="27" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="G109" s="27" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H109" s="28" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="I109" s="29" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="J109" s="29" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="K109" s="30" t="n">
         <v>8.18</v>
       </c>
-      <c r="F109" s="27" t="n">
+      <c r="L109" s="31" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="M109" s="31" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="N109" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O109" s="32" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G109" s="27" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="H109" s="28" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="I109" s="29" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="J109" s="29" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="K109" s="30" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="L109" s="31" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="M109" s="31" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="N109" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O109" s="32" t="n">
-        <v>8.130000000000001</v>
-      </c>
       <c r="P109" s="32" t="n">
-        <v>8.119999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="Q109" s="33" t="n">
-        <v>8.15</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="R109" s="34" t="n">
-        <v>0.37</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="110">
@@ -7428,37 +7428,37 @@
         </is>
       </c>
       <c r="C110" s="25" t="n">
-        <v>45.05</v>
+        <v>44.81</v>
       </c>
       <c r="D110" s="25" t="n">
-        <v>44.49</v>
+        <v>44.53</v>
       </c>
       <c r="E110" s="26" t="n">
-        <v>44.02</v>
+        <v>44.3</v>
       </c>
       <c r="F110" s="27" t="n">
-        <v>44.33</v>
+        <v>44.45</v>
       </c>
       <c r="G110" s="27" t="n">
-        <v>44.51</v>
+        <v>44.55</v>
       </c>
       <c r="H110" s="28" t="n">
-        <v>43.95</v>
+        <v>44.27</v>
       </c>
       <c r="I110" s="29" t="n">
-        <v>43.77</v>
+        <v>44.17</v>
       </c>
       <c r="J110" s="29" t="n">
-        <v>43.39</v>
+        <v>43.99</v>
       </c>
       <c r="K110" s="30" t="n">
-        <v>43.7</v>
+        <v>44.14</v>
       </c>
       <c r="L110" s="31" t="n">
-        <v>43.23</v>
+        <v>43.91</v>
       </c>
       <c r="M110" s="31" t="n">
-        <v>42.67</v>
+        <v>43.63</v>
       </c>
       <c r="N110" s="20" t="inlineStr">
         <is>
@@ -7466,16 +7466,16 @@
         </is>
       </c>
       <c r="O110" s="32" t="n">
-        <v>43.85</v>
+        <v>44.22</v>
       </c>
       <c r="P110" s="32" t="n">
-        <v>43.75</v>
+        <v>44.16</v>
       </c>
       <c r="Q110" s="33" t="n">
-        <v>44.14</v>
+        <v>44.36</v>
       </c>
       <c r="R110" s="34" t="n">
-        <v>1.24</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="111">
@@ -7490,37 +7490,37 @@
         </is>
       </c>
       <c r="C111" s="25" t="n">
-        <v>66.18000000000001</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="D111" s="25" t="n">
-        <v>65.33</v>
+        <v>66.91</v>
       </c>
       <c r="E111" s="26" t="n">
-        <v>64.61</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F111" s="27" t="n">
-        <v>64.55</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="G111" s="27" t="n">
-        <v>65.09999999999999</v>
+        <v>66.83</v>
       </c>
       <c r="H111" s="28" t="n">
-        <v>64.25</v>
+        <v>65.03</v>
       </c>
       <c r="I111" s="29" t="n">
-        <v>63.7</v>
+        <v>64.27</v>
       </c>
       <c r="J111" s="29" t="n">
-        <v>63.4</v>
+        <v>63.23</v>
       </c>
       <c r="K111" s="30" t="n">
-        <v>64.14</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L111" s="31" t="n">
-        <v>63.42</v>
+        <v>62.89</v>
       </c>
       <c r="M111" s="31" t="n">
-        <v>62.57</v>
+        <v>61.09</v>
       </c>
       <c r="N111" s="20" t="inlineStr">
         <is>
@@ -7528,16 +7528,16 @@
         </is>
       </c>
       <c r="O111" s="32" t="n">
-        <v>64.23</v>
+        <v>64.78</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>64.2</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="Q111" s="33" t="n">
-        <v>64</v>
+        <v>65.3</v>
       </c>
       <c r="R111" s="34" t="n">
-        <v>0.63</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="112">
@@ -7552,37 +7552,37 @@
         </is>
       </c>
       <c r="C112" s="25" t="n">
-        <v>10.63</v>
+        <v>10.56</v>
       </c>
       <c r="D112" s="25" t="n">
         <v>10.48</v>
       </c>
       <c r="E112" s="26" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="F112" s="27" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="G112" s="27" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="H112" s="28" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="I112" s="29" t="n">
         <v>10.36</v>
       </c>
-      <c r="F112" s="27" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="G112" s="27" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="H112" s="28" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="I112" s="29" t="n">
-        <v>10.26</v>
-      </c>
       <c r="J112" s="29" t="n">
-        <v>10.18</v>
+        <v>10.31</v>
       </c>
       <c r="K112" s="30" t="n">
-        <v>10.27</v>
+        <v>10.37</v>
       </c>
       <c r="L112" s="31" t="n">
-        <v>10.15</v>
+        <v>10.3</v>
       </c>
       <c r="M112" s="31" t="n">
-        <v>10</v>
+        <v>10.22</v>
       </c>
       <c r="N112" s="20" t="inlineStr">
         <is>
@@ -7590,16 +7590,16 @@
         </is>
       </c>
       <c r="O112" s="32" t="n">
-        <v>10.31</v>
+        <v>10.38</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>10.28</v>
+        <v>10.37</v>
       </c>
       <c r="Q112" s="33" t="n">
-        <v>10.35</v>
+        <v>10.4</v>
       </c>
       <c r="R112" s="34" t="n">
-        <v>1.27</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="113">
@@ -7614,37 +7614,37 @@
         </is>
       </c>
       <c r="C113" s="25" t="n">
-        <v>320.94</v>
+        <v>311.57</v>
       </c>
       <c r="D113" s="25" t="n">
-        <v>308.74</v>
+        <v>306.77</v>
       </c>
       <c r="E113" s="26" t="n">
-        <v>298.52</v>
+        <v>302.74</v>
       </c>
       <c r="F113" s="27" t="n">
-        <v>305.13</v>
+        <v>303.53</v>
       </c>
       <c r="G113" s="27" t="n">
-        <v>309.27</v>
+        <v>306.07</v>
       </c>
       <c r="H113" s="28" t="n">
-        <v>297.07</v>
+        <v>301.27</v>
       </c>
       <c r="I113" s="29" t="n">
-        <v>292.93</v>
+        <v>298.73</v>
       </c>
       <c r="J113" s="29" t="n">
-        <v>284.87</v>
+        <v>296.47</v>
       </c>
       <c r="K113" s="30" t="n">
-        <v>291.68</v>
+        <v>300.06</v>
       </c>
       <c r="L113" s="31" t="n">
-        <v>281.46</v>
+        <v>296.03</v>
       </c>
       <c r="M113" s="31" t="n">
-        <v>269.26</v>
+        <v>291.23</v>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
@@ -7652,16 +7652,16 @@
         </is>
       </c>
       <c r="O113" s="32" t="n">
-        <v>294.85</v>
+        <v>300.85</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>292.64</v>
+        <v>300.43</v>
       </c>
       <c r="Q113" s="33" t="n">
         <v>301</v>
       </c>
       <c r="R113" s="34" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -7676,37 +7676,37 @@
         </is>
       </c>
       <c r="C114" s="25" t="n">
-        <v>208.77</v>
+        <v>207.77</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>206.07</v>
+        <v>206.37</v>
       </c>
       <c r="E114" s="26" t="n">
-        <v>203.81</v>
+        <v>205.19</v>
       </c>
       <c r="F114" s="27" t="n">
-        <v>205.3</v>
+        <v>205.7</v>
       </c>
       <c r="G114" s="27" t="n">
-        <v>206.2</v>
+        <v>206.3</v>
       </c>
       <c r="H114" s="28" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="I114" s="29" t="n">
+        <v>204.3</v>
+      </c>
+      <c r="J114" s="29" t="n">
         <v>203.5</v>
       </c>
-      <c r="I114" s="29" t="n">
-        <v>202.6</v>
-      </c>
-      <c r="J114" s="29" t="n">
-        <v>200.8</v>
-      </c>
       <c r="K114" s="30" t="n">
-        <v>202.29</v>
+        <v>204.41</v>
       </c>
       <c r="L114" s="31" t="n">
-        <v>200.03</v>
+        <v>203.23</v>
       </c>
       <c r="M114" s="31" t="n">
-        <v>197.33</v>
+        <v>201.83</v>
       </c>
       <c r="N114" s="20" t="inlineStr">
         <is>
@@ -7714,16 +7714,16 @@
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>203</v>
+        <v>204.71</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>202.5</v>
+        <v>204.52</v>
       </c>
       <c r="Q114" s="33" t="n">
-        <v>204.4</v>
+        <v>205.1</v>
       </c>
       <c r="R114" s="34" t="n">
-        <v>1.04</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="115">
@@ -7738,37 +7738,37 @@
         </is>
       </c>
       <c r="C115" s="25" t="n">
-        <v>633.08</v>
+        <v>633.6799999999999</v>
       </c>
       <c r="D115" s="25" t="n">
-        <v>617.58</v>
+        <v>623.6799999999999</v>
       </c>
       <c r="E115" s="26" t="n">
-        <v>604.59</v>
+        <v>615.3</v>
       </c>
       <c r="F115" s="27" t="n">
-        <v>612.83</v>
+        <v>616.5</v>
       </c>
       <c r="G115" s="27" t="n">
-        <v>618.17</v>
+        <v>622</v>
       </c>
       <c r="H115" s="28" t="n">
-        <v>602.67</v>
+        <v>612</v>
       </c>
       <c r="I115" s="29" t="n">
-        <v>597.33</v>
+        <v>606.5</v>
       </c>
       <c r="J115" s="29" t="n">
-        <v>587.17</v>
+        <v>602</v>
       </c>
       <c r="K115" s="30" t="n">
-        <v>595.91</v>
+        <v>609.7</v>
       </c>
       <c r="L115" s="31" t="n">
-        <v>582.92</v>
+        <v>601.3200000000001</v>
       </c>
       <c r="M115" s="31" t="n">
-        <v>567.42</v>
+        <v>591.3200000000001</v>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
@@ -7776,16 +7776,16 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>599.89</v>
+        <v>611.24</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>597.12</v>
+        <v>610.48</v>
       </c>
       <c r="Q115" s="33" t="n">
-        <v>607.5</v>
+        <v>611</v>
       </c>
       <c r="R115" s="34" t="n">
-        <v>1.93</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="116">
@@ -7800,54 +7800,54 @@
         </is>
       </c>
       <c r="C116" s="25" t="n">
-        <v>6.84</v>
+        <v>6.97</v>
       </c>
       <c r="D116" s="25" t="n">
-        <v>6.74</v>
+        <v>6.82</v>
       </c>
       <c r="E116" s="26" t="n">
-        <v>6.66</v>
+        <v>6.7</v>
       </c>
       <c r="F116" s="27" t="n">
-        <v>6.7</v>
+        <v>6.69</v>
       </c>
       <c r="G116" s="27" t="n">
-        <v>6.74</v>
+        <v>6.79</v>
       </c>
       <c r="H116" s="28" t="n">
         <v>6.64</v>
       </c>
       <c r="I116" s="29" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="J116" s="29" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="K116" s="30" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="L116" s="31" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M116" s="31" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="N116" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O116" s="32" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="P116" s="32" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="Q116" s="33" t="n">
         <v>6.6</v>
       </c>
-      <c r="J116" s="29" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="K116" s="30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L116" s="31" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="M116" s="31" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="N116" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O116" s="32" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="P116" s="32" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="Q116" s="33" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="R116" s="34" t="n">
-        <v>1.22</v>
+      <c r="R116" s="35" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="117">
@@ -7862,54 +7862,54 @@
         </is>
       </c>
       <c r="C117" s="25" t="n">
-        <v>141.29</v>
+        <v>142.19</v>
       </c>
       <c r="D117" s="25" t="n">
-        <v>139.69</v>
+        <v>140.59</v>
       </c>
       <c r="E117" s="26" t="n">
+        <v>139.25</v>
+      </c>
+      <c r="F117" s="27" t="n">
+        <v>139.87</v>
+      </c>
+      <c r="G117" s="27" t="n">
+        <v>140.53</v>
+      </c>
+      <c r="H117" s="28" t="n">
+        <v>138.93</v>
+      </c>
+      <c r="I117" s="29" t="n">
+        <v>138.27</v>
+      </c>
+      <c r="J117" s="29" t="n">
+        <v>137.33</v>
+      </c>
+      <c r="K117" s="30" t="n">
         <v>138.35</v>
       </c>
-      <c r="F117" s="27" t="n">
-        <v>138.7</v>
-      </c>
-      <c r="G117" s="27" t="n">
-        <v>139.5</v>
-      </c>
-      <c r="H117" s="28" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="I117" s="29" t="n">
-        <v>137.1</v>
-      </c>
-      <c r="J117" s="29" t="n">
-        <v>136.3</v>
-      </c>
-      <c r="K117" s="30" t="n">
-        <v>137.45</v>
-      </c>
       <c r="L117" s="31" t="n">
-        <v>136.11</v>
+        <v>137.01</v>
       </c>
       <c r="M117" s="31" t="n">
-        <v>134.51</v>
-      </c>
-      <c r="N117" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>135.41</v>
+      </c>
+      <c r="N117" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O117" s="32" t="n">
-        <v>137.74</v>
+        <v>138.71</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>137.58</v>
+        <v>138.48</v>
       </c>
       <c r="Q117" s="33" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="R117" s="36" t="n">
-        <v>-0.72</v>
+        <v>139.2</v>
+      </c>
+      <c r="R117" s="34" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="118">
@@ -7924,54 +7924,54 @@
         </is>
       </c>
       <c r="C118" s="25" t="n">
-        <v>10.63</v>
+        <v>10.65</v>
       </c>
       <c r="D118" s="25" t="n">
-        <v>10.47</v>
+        <v>10.46</v>
       </c>
       <c r="E118" s="26" t="n">
-        <v>10.33</v>
+        <v>10.3</v>
       </c>
       <c r="F118" s="27" t="n">
-        <v>10.34</v>
+        <v>10.3</v>
       </c>
       <c r="G118" s="27" t="n">
-        <v>10.44</v>
+        <v>10.41</v>
       </c>
       <c r="H118" s="28" t="n">
-        <v>10.28</v>
+        <v>10.22</v>
       </c>
       <c r="I118" s="29" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="J118" s="29" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="K118" s="30" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="L118" s="31" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="M118" s="31" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="N118" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O118" s="32" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="P118" s="32" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="Q118" s="33" t="n">
         <v>10.18</v>
       </c>
-      <c r="J118" s="29" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="K118" s="30" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="L118" s="31" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="M118" s="31" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="N118" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O118" s="32" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="P118" s="32" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="Q118" s="33" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="R118" s="36" t="n">
-        <v>-1.44</v>
+      <c r="R118" s="35" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="119">
@@ -7986,54 +7986,54 @@
         </is>
       </c>
       <c r="C119" s="25" t="n">
-        <v>18.04</v>
+        <v>18.73</v>
       </c>
       <c r="D119" s="25" t="n">
-        <v>17.59</v>
+        <v>18.03</v>
       </c>
       <c r="E119" s="26" t="n">
-        <v>17.21</v>
+        <v>17.45</v>
       </c>
       <c r="F119" s="27" t="n">
-        <v>17.22</v>
+        <v>17.39</v>
       </c>
       <c r="G119" s="27" t="n">
-        <v>17.49</v>
+        <v>17.85</v>
       </c>
       <c r="H119" s="28" t="n">
-        <v>17.04</v>
+        <v>17.15</v>
       </c>
       <c r="I119" s="29" t="n">
-        <v>16.77</v>
+        <v>16.69</v>
       </c>
       <c r="J119" s="29" t="n">
-        <v>16.59</v>
+        <v>16.45</v>
       </c>
       <c r="K119" s="30" t="n">
-        <v>16.96</v>
+        <v>17.05</v>
       </c>
       <c r="L119" s="31" t="n">
-        <v>16.58</v>
+        <v>16.47</v>
       </c>
       <c r="M119" s="31" t="n">
-        <v>16.13</v>
-      </c>
-      <c r="N119" s="35" t="inlineStr">
+        <v>15.77</v>
+      </c>
+      <c r="N119" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O119" s="32" t="n">
-        <v>17.02</v>
+        <v>17.13</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>16.99</v>
+        <v>17.11</v>
       </c>
       <c r="Q119" s="33" t="n">
-        <v>16.95</v>
-      </c>
-      <c r="R119" s="36" t="n">
-        <v>-1.68</v>
+        <v>16.94</v>
+      </c>
+      <c r="R119" s="35" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="120">
@@ -8048,54 +8048,54 @@
         </is>
       </c>
       <c r="C120" s="25" t="n">
-        <v>12.06</v>
+        <v>11.54</v>
       </c>
       <c r="D120" s="25" t="n">
-        <v>11.67</v>
+        <v>11.3</v>
       </c>
       <c r="E120" s="26" t="n">
-        <v>11.34</v>
+        <v>11.1</v>
       </c>
       <c r="F120" s="27" t="n">
-        <v>11.33</v>
+        <v>11.09</v>
       </c>
       <c r="G120" s="27" t="n">
-        <v>11.57</v>
+        <v>11.24</v>
       </c>
       <c r="H120" s="28" t="n">
-        <v>11.18</v>
+        <v>11</v>
       </c>
       <c r="I120" s="29" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="J120" s="29" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="K120" s="30" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="L120" s="31" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="M120" s="31" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="N120" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O120" s="32" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="P120" s="32" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="Q120" s="33" t="n">
         <v>10.94</v>
       </c>
-      <c r="J120" s="29" t="n">
-        <v>10.79</v>
-      </c>
-      <c r="K120" s="30" t="n">
-        <v>11.13</v>
-      </c>
-      <c r="L120" s="31" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="M120" s="31" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="N120" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O120" s="32" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="P120" s="32" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="Q120" s="33" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="R120" s="36" t="n">
-        <v>-2.81</v>
+      <c r="R120" s="35" t="n">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="121">
@@ -8110,37 +8110,37 @@
         </is>
       </c>
       <c r="C121" s="25" t="n">
-        <v>12.47</v>
+        <v>12.72</v>
       </c>
       <c r="D121" s="25" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="E121" s="26" t="n">
         <v>12.36</v>
       </c>
-      <c r="E121" s="26" t="n">
-        <v>12.27</v>
-      </c>
       <c r="F121" s="27" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="G121" s="27" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="H121" s="28" t="n">
         <v>12.32</v>
       </c>
-      <c r="G121" s="27" t="n">
-        <v>12.36</v>
-      </c>
-      <c r="H121" s="28" t="n">
-        <v>12.25</v>
-      </c>
       <c r="I121" s="29" t="n">
-        <v>12.21</v>
+        <v>12.23</v>
       </c>
       <c r="J121" s="29" t="n">
-        <v>12.14</v>
+        <v>12.12</v>
       </c>
       <c r="K121" s="30" t="n">
-        <v>12.2</v>
+        <v>12.24</v>
       </c>
       <c r="L121" s="31" t="n">
-        <v>12.11</v>
+        <v>12.08</v>
       </c>
       <c r="M121" s="31" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="N121" s="20" t="inlineStr">
         <is>
@@ -8148,16 +8148,16 @@
         </is>
       </c>
       <c r="O121" s="32" t="n">
-        <v>12.23</v>
+        <v>12.29</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>12.21</v>
+        <v>12.26</v>
       </c>
       <c r="Q121" s="33" t="n">
-        <v>12.28</v>
+        <v>12.35</v>
       </c>
       <c r="R121" s="34" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="122">
@@ -8172,54 +8172,54 @@
         </is>
       </c>
       <c r="C122" s="25" t="n">
-        <v>8.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="D122" s="25" t="n">
-        <v>8.6</v>
+        <v>8.49</v>
       </c>
       <c r="E122" s="26" t="n">
-        <v>8.380000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="F122" s="27" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G122" s="27" t="n">
-        <v>8.539999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H122" s="28" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="I122" s="29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J122" s="29" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="K122" s="30" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="L122" s="31" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="M122" s="31" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="N122" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O122" s="32" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="P122" s="32" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="I122" s="29" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="J122" s="29" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="K122" s="30" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="L122" s="31" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="M122" s="31" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="N122" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O122" s="32" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="P122" s="32" t="n">
+      <c r="Q122" s="33" t="n">
         <v>8.26</v>
       </c>
-      <c r="Q122" s="33" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="R122" s="36" t="n">
-        <v>-1.79</v>
+      <c r="R122" s="34" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="123">
@@ -8234,39 +8234,39 @@
         </is>
       </c>
       <c r="C123" s="25" t="n">
-        <v>8.859999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="D123" s="25" t="n">
-        <v>8.43</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="E123" s="26" t="n">
-        <v>8.07</v>
+        <v>7.96</v>
       </c>
       <c r="F123" s="27" t="n">
-        <v>8.130000000000001</v>
+        <v>8.01</v>
       </c>
       <c r="G123" s="27" t="n">
-        <v>8.359999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="H123" s="28" t="n">
-        <v>7.93</v>
+        <v>7.91</v>
       </c>
       <c r="I123" s="29" t="n">
-        <v>7.7</v>
+        <v>7.83</v>
       </c>
       <c r="J123" s="29" t="n">
-        <v>7.5</v>
+        <v>7.73</v>
       </c>
       <c r="K123" s="30" t="n">
-        <v>7.82</v>
+        <v>7.86</v>
       </c>
       <c r="L123" s="31" t="n">
-        <v>7.46</v>
+        <v>7.71</v>
       </c>
       <c r="M123" s="31" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="N123" s="35" t="inlineStr">
+        <v>7.53</v>
+      </c>
+      <c r="N123" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
@@ -8275,13 +8275,13 @@
         <v>7.89</v>
       </c>
       <c r="P123" s="32" t="n">
-        <v>7.86</v>
+        <v>7.87</v>
       </c>
       <c r="Q123" s="33" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="R123" s="36" t="n">
-        <v>-1.62</v>
+        <v>7.92</v>
+      </c>
+      <c r="R123" s="34" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="124">
@@ -8296,54 +8296,54 @@
         </is>
       </c>
       <c r="C124" s="25" t="n">
-        <v>24.86</v>
+        <v>25.13</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>24.53</v>
+        <v>24.74</v>
       </c>
       <c r="E124" s="26" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="F124" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G124" s="27" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="H124" s="28" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I124" s="29" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="J124" s="29" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="K124" s="30" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="L124" s="31" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="M124" s="31" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="N124" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O124" s="32" t="n">
         <v>24.26</v>
       </c>
-      <c r="F124" s="27" t="n">
-        <v>24.36</v>
-      </c>
-      <c r="G124" s="27" t="n">
-        <v>24.51</v>
-      </c>
-      <c r="H124" s="28" t="n">
-        <v>24.18</v>
-      </c>
-      <c r="I124" s="29" t="n">
-        <v>24.03</v>
-      </c>
-      <c r="J124" s="29" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="K124" s="30" t="n">
-        <v>24.07</v>
-      </c>
-      <c r="L124" s="31" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="M124" s="31" t="n">
-        <v>23.47</v>
-      </c>
-      <c r="N124" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O124" s="32" t="n">
-        <v>24.14</v>
-      </c>
       <c r="P124" s="32" t="n">
-        <v>24.1</v>
+        <v>24.23</v>
       </c>
       <c r="Q124" s="33" t="n">
-        <v>24.21</v>
-      </c>
-      <c r="R124" s="36" t="n">
-        <v>-0.37</v>
+        <v>24.3</v>
+      </c>
+      <c r="R124" s="34" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="125">
@@ -8358,54 +8358,54 @@
         </is>
       </c>
       <c r="C125" s="25" t="n">
-        <v>167.11</v>
+        <v>167.81</v>
       </c>
       <c r="D125" s="25" t="n">
-        <v>165.31</v>
+        <v>166.01</v>
       </c>
       <c r="E125" s="26" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="F125" s="27" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="G125" s="27" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="H125" s="28" t="n">
         <v>163.8</v>
       </c>
-      <c r="F125" s="27" t="n">
-        <v>164.33</v>
-      </c>
-      <c r="G125" s="27" t="n">
-        <v>165.17</v>
-      </c>
-      <c r="H125" s="28" t="n">
-        <v>163.37</v>
-      </c>
       <c r="I125" s="29" t="n">
-        <v>162.53</v>
+        <v>162.7</v>
       </c>
       <c r="J125" s="29" t="n">
-        <v>161.57</v>
+        <v>162</v>
       </c>
       <c r="K125" s="30" t="n">
-        <v>162.8</v>
+        <v>163.5</v>
       </c>
       <c r="L125" s="31" t="n">
-        <v>161.29</v>
+        <v>161.99</v>
       </c>
       <c r="M125" s="31" t="n">
-        <v>159.49</v>
-      </c>
-      <c r="N125" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>160.19</v>
+      </c>
+      <c r="N125" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O125" s="32" t="n">
-        <v>163.15</v>
+        <v>163.72</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>162.94</v>
+        <v>163.64</v>
       </c>
       <c r="Q125" s="33" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="R125" s="34" t="n">
-        <v>0.31</v>
+        <v>163.4</v>
+      </c>
+      <c r="R125" s="35" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="126">
@@ -8420,54 +8420,54 @@
         </is>
       </c>
       <c r="C126" s="25" t="n">
-        <v>56.42</v>
+        <v>56.24</v>
       </c>
       <c r="D126" s="25" t="n">
-        <v>54.77</v>
+        <v>54.64</v>
       </c>
       <c r="E126" s="26" t="n">
-        <v>53.39</v>
+        <v>53.3</v>
       </c>
       <c r="F126" s="27" t="n">
-        <v>53.23</v>
+        <v>54.08</v>
       </c>
       <c r="G126" s="27" t="n">
-        <v>54.32</v>
+        <v>54.67</v>
       </c>
       <c r="H126" s="28" t="n">
-        <v>52.67</v>
+        <v>53.07</v>
       </c>
       <c r="I126" s="29" t="n">
-        <v>51.58</v>
+        <v>52.48</v>
       </c>
       <c r="J126" s="29" t="n">
-        <v>51.02</v>
+        <v>51.47</v>
       </c>
       <c r="K126" s="30" t="n">
-        <v>52.46</v>
+        <v>52.4</v>
       </c>
       <c r="L126" s="31" t="n">
-        <v>51.08</v>
+        <v>51.06</v>
       </c>
       <c r="M126" s="31" t="n">
-        <v>49.43</v>
-      </c>
-      <c r="N126" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>49.46</v>
+      </c>
+      <c r="N126" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O126" s="32" t="n">
-        <v>52.63</v>
+        <v>52.8</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>52.59</v>
+        <v>52.53</v>
       </c>
       <c r="Q126" s="33" t="n">
-        <v>52.15</v>
-      </c>
-      <c r="R126" s="36" t="n">
-        <v>-1.7</v>
+        <v>53.5</v>
+      </c>
+      <c r="R126" s="34" t="n">
+        <v>2.59</v>
       </c>
     </row>
     <row r="127">
@@ -8482,54 +8482,54 @@
         </is>
       </c>
       <c r="C127" s="25" t="n">
-        <v>16.32</v>
+        <v>16.03</v>
       </c>
       <c r="D127" s="25" t="n">
-        <v>15.71</v>
+        <v>15.37</v>
       </c>
       <c r="E127" s="26" t="n">
-        <v>15.2</v>
+        <v>14.81</v>
       </c>
       <c r="F127" s="27" t="n">
-        <v>15.13</v>
+        <v>14.81</v>
       </c>
       <c r="G127" s="27" t="n">
-        <v>15.53</v>
+        <v>15.22</v>
       </c>
       <c r="H127" s="28" t="n">
-        <v>14.92</v>
+        <v>14.56</v>
       </c>
       <c r="I127" s="29" t="n">
-        <v>14.52</v>
+        <v>14.15</v>
       </c>
       <c r="J127" s="29" t="n">
-        <v>14.31</v>
+        <v>13.9</v>
       </c>
       <c r="K127" s="30" t="n">
-        <v>14.85</v>
+        <v>14.45</v>
       </c>
       <c r="L127" s="31" t="n">
-        <v>14.34</v>
+        <v>13.89</v>
       </c>
       <c r="M127" s="31" t="n">
-        <v>13.73</v>
-      </c>
-      <c r="N127" s="35" t="inlineStr">
+        <v>13.23</v>
+      </c>
+      <c r="N127" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O127" s="32" t="n">
-        <v>14.91</v>
+        <v>14.53</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="Q127" s="33" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="R127" s="36" t="n">
-        <v>-2.19</v>
+        <v>14.41</v>
+      </c>
+      <c r="R127" s="35" t="n">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="128">
@@ -8544,54 +8544,54 @@
         </is>
       </c>
       <c r="C128" s="25" t="n">
-        <v>16.07</v>
+        <v>15.57</v>
       </c>
       <c r="D128" s="25" t="n">
-        <v>15.53</v>
+        <v>15.1</v>
       </c>
       <c r="E128" s="26" t="n">
-        <v>15.08</v>
+        <v>14.71</v>
       </c>
       <c r="F128" s="27" t="n">
-        <v>15.05</v>
+        <v>14.71</v>
       </c>
       <c r="G128" s="27" t="n">
-        <v>15.39</v>
+        <v>14.99</v>
       </c>
       <c r="H128" s="28" t="n">
-        <v>14.85</v>
+        <v>14.52</v>
       </c>
       <c r="I128" s="29" t="n">
-        <v>14.51</v>
+        <v>14.24</v>
       </c>
       <c r="J128" s="29" t="n">
-        <v>14.31</v>
+        <v>14.05</v>
       </c>
       <c r="K128" s="30" t="n">
-        <v>14.78</v>
+        <v>14.44</v>
       </c>
       <c r="L128" s="31" t="n">
-        <v>14.33</v>
+        <v>14.05</v>
       </c>
       <c r="M128" s="31" t="n">
-        <v>13.79</v>
-      </c>
-      <c r="N128" s="35" t="inlineStr">
+        <v>13.58</v>
+      </c>
+      <c r="N128" s="36" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O128" s="32" t="n">
-        <v>14.84</v>
+        <v>14.5</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>14.82</v>
+        <v>14.48</v>
       </c>
       <c r="Q128" s="33" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="R128" s="36" t="n">
-        <v>-3.1</v>
+        <v>14.42</v>
+      </c>
+      <c r="R128" s="35" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="129">
@@ -8606,54 +8606,54 @@
         </is>
       </c>
       <c r="C129" s="25" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="D129" s="25" t="n">
-        <v>7.47</v>
+        <v>7.54</v>
       </c>
       <c r="E129" s="26" t="n">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="F129" s="27" t="n">
-        <v>7.43</v>
+        <v>7.4</v>
       </c>
       <c r="G129" s="27" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
       <c r="H129" s="28" t="n">
         <v>7.34</v>
       </c>
       <c r="I129" s="29" t="n">
-        <v>7.3</v>
+        <v>7.24</v>
       </c>
       <c r="J129" s="29" t="n">
-        <v>7.21</v>
+        <v>7.18</v>
       </c>
       <c r="K129" s="30" t="n">
-        <v>7.29</v>
+        <v>7.32</v>
       </c>
       <c r="L129" s="31" t="n">
         <v>7.18</v>
       </c>
       <c r="M129" s="31" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="N129" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>7.02</v>
+      </c>
+      <c r="N129" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O129" s="32" t="n">
-        <v>7.32</v>
+        <v>7.33</v>
       </c>
       <c r="P129" s="32" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="Q129" s="33" t="n">
         <v>7.3</v>
       </c>
-      <c r="Q129" s="33" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="R129" s="34" t="n">
-        <v>0.54</v>
+      <c r="R129" s="35" t="n">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="130">
@@ -8668,54 +8668,54 @@
         </is>
       </c>
       <c r="C130" s="25" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="D130" s="25" t="n">
         <v>9.91</v>
       </c>
       <c r="E130" s="26" t="n">
-        <v>9.75</v>
+        <v>9.76</v>
       </c>
       <c r="F130" s="27" t="n">
-        <v>9.73</v>
+        <v>9.76</v>
       </c>
       <c r="G130" s="27" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H130" s="28" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="I130" s="29" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="J130" s="29" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="K130" s="30" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="L130" s="31" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="M130" s="31" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="N130" s="36" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O130" s="32" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="P130" s="32" t="n">
         <v>9.67</v>
       </c>
-      <c r="I130" s="29" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="J130" s="29" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="K130" s="30" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="L130" s="31" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="M130" s="31" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="N130" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O130" s="32" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="P130" s="32" t="n">
-        <v>9.66</v>
-      </c>
       <c r="Q130" s="33" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="R130" s="36" t="n">
-        <v>-0.93</v>
+        <v>9.65</v>
+      </c>
+      <c r="R130" s="34" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="131">
@@ -8730,54 +8730,54 @@
         </is>
       </c>
       <c r="C131" s="25" t="n">
-        <v>138.85</v>
+        <v>140.56</v>
       </c>
       <c r="D131" s="25" t="n">
-        <v>137.15</v>
+        <v>138.36</v>
       </c>
       <c r="E131" s="26" t="n">
-        <v>135.73</v>
+        <v>136.52</v>
       </c>
       <c r="F131" s="27" t="n">
-        <v>136</v>
+        <v>137.33</v>
       </c>
       <c r="G131" s="27" t="n">
-        <v>136.9</v>
+        <v>138.27</v>
       </c>
       <c r="H131" s="28" t="n">
-        <v>135.2</v>
+        <v>136.07</v>
       </c>
       <c r="I131" s="29" t="n">
-        <v>134.3</v>
+        <v>135.13</v>
       </c>
       <c r="J131" s="29" t="n">
-        <v>133.5</v>
+        <v>133.87</v>
       </c>
       <c r="K131" s="30" t="n">
-        <v>134.77</v>
+        <v>135.28</v>
       </c>
       <c r="L131" s="31" t="n">
-        <v>133.35</v>
+        <v>133.44</v>
       </c>
       <c r="M131" s="31" t="n">
-        <v>131.65</v>
-      </c>
-      <c r="N131" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>131.24</v>
+      </c>
+      <c r="N131" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O131" s="32" t="n">
-        <v>135.05</v>
+        <v>135.76</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>134.91</v>
+        <v>135.46</v>
       </c>
       <c r="Q131" s="33" t="n">
-        <v>135.1</v>
-      </c>
-      <c r="R131" s="36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>136.4</v>
+      </c>
+      <c r="R131" s="34" t="n">
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -289,10 +289,10 @@
     <xf numFmtId="2" fontId="4" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="5" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -686,7 +686,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-08-23</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>11284.01</v>
+        <v>11368.12</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>11160.72</v>
+        <v>11256.86</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>11057.41</v>
+        <v>11163.62</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>11121.73</v>
+        <v>11215.87</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>11164.77</v>
+        <v>11257.62</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>11041.48</v>
+        <v>11146.36</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>10998.44</v>
+        <v>11104.61</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>10918.19</v>
+        <v>11035.1</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>10988.36</v>
+        <v>11101.32</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>10885.05</v>
+        <v>11008.08</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>10761.76</v>
+        <v>10896.82</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>11019.73</v>
+        <v>11128.18</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>10997.98</v>
+        <v>11110</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>11078.68</v>
+        <v>11174.13</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>3.34</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="4">
@@ -856,37 +856,37 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>20.93</v>
+        <v>21.08</v>
       </c>
       <c r="D4" s="25" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="E4" s="26" t="n">
         <v>20.76</v>
       </c>
-      <c r="E4" s="26" t="n">
-        <v>20.61</v>
-      </c>
       <c r="F4" s="27" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="I4" s="29" t="n">
         <v>20.69</v>
       </c>
-      <c r="G4" s="27" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H4" s="28" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="I4" s="29" t="n">
+      <c r="J4" s="29" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="K4" s="30" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="L4" s="31" t="n">
         <v>20.52</v>
       </c>
-      <c r="J4" s="29" t="n">
-        <v>20.41</v>
-      </c>
-      <c r="K4" s="30" t="n">
-        <v>20.52</v>
-      </c>
-      <c r="L4" s="31" t="n">
-        <v>20.37</v>
-      </c>
       <c r="M4" s="31" t="n">
-        <v>20.2</v>
+        <v>20.35</v>
       </c>
       <c r="N4" s="20" t="inlineStr">
         <is>
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="O4" s="32" t="n">
-        <v>20.56</v>
+        <v>20.71</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>20.53</v>
+        <v>20.68</v>
       </c>
       <c r="Q4" s="33" t="n">
-        <v>20.62</v>
+        <v>20.8</v>
       </c>
       <c r="R4" s="34" t="n">
-        <v>0.63</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="5">
@@ -918,54 +918,54 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>12.3</v>
+        <v>12.58</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>12.21</v>
+        <v>12.39</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>12.13</v>
+        <v>12.23</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>12.15</v>
+        <v>12.28</v>
       </c>
       <c r="G5" s="27" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="L5" s="31" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="M5" s="31" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O5" s="32" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="P5" s="32" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="Q5" s="33" t="n">
         <v>12.19</v>
       </c>
-      <c r="H5" s="28" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="J5" s="29" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="K5" s="30" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="L5" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="M5" s="31" t="n">
-        <v>11.91</v>
-      </c>
-      <c r="N5" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="P5" s="32" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="Q5" s="33" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="R5" s="35" t="n">
-        <v>-0.25</v>
+      <c r="R5" s="34" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="6">
@@ -980,54 +980,54 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>14.32</v>
+        <v>14.49</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14.23</v>
+        <v>14.34</v>
       </c>
       <c r="E6" s="26" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I6" s="29" t="n">
         <v>14.15</v>
       </c>
-      <c r="F6" s="27" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="I6" s="29" t="n">
-        <v>14.06</v>
-      </c>
       <c r="J6" s="29" t="n">
-        <v>14.03</v>
+        <v>14.05</v>
       </c>
       <c r="K6" s="30" t="n">
-        <v>14.1</v>
+        <v>14.13</v>
       </c>
       <c r="L6" s="31" t="n">
-        <v>14.02</v>
+        <v>14.01</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="N6" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>13.86</v>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O6" s="32" t="n">
-        <v>14.11</v>
+        <v>14.17</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>14.11</v>
+        <v>14.14</v>
       </c>
       <c r="Q6" s="33" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="R6" s="35" t="n">
-        <v>-0.28</v>
+        <v>14.25</v>
+      </c>
+      <c r="R6" s="34" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="7">
@@ -1042,54 +1042,54 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>21.65</v>
+        <v>22.24</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>21.24</v>
+        <v>21.75</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>20.9</v>
+        <v>21.34</v>
       </c>
       <c r="F7" s="27" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="J7" s="29" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K7" s="30" t="n">
         <v>21.07</v>
       </c>
-      <c r="G7" s="27" t="n">
-        <v>21.23</v>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>20.82</v>
-      </c>
-      <c r="I7" s="29" t="n">
+      <c r="L7" s="31" t="n">
         <v>20.66</v>
       </c>
-      <c r="J7" s="29" t="n">
-        <v>20.41</v>
-      </c>
-      <c r="K7" s="30" t="n">
-        <v>20.67</v>
-      </c>
-      <c r="L7" s="31" t="n">
-        <v>20.33</v>
-      </c>
       <c r="M7" s="31" t="n">
-        <v>19.92</v>
-      </c>
-      <c r="N7" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>20.17</v>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>20.76</v>
+        <v>21.2</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>20.7</v>
+        <v>21.11</v>
       </c>
       <c r="Q7" s="33" t="n">
-        <v>20.9</v>
+        <v>21.45</v>
       </c>
       <c r="R7" s="34" t="n">
-        <v>0.53</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="8">
@@ -1104,37 +1104,37 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>34.19</v>
+        <v>34.81</v>
       </c>
       <c r="D8" s="25" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="H8" s="28" t="n">
         <v>34.07</v>
       </c>
-      <c r="E8" s="26" t="n">
-        <v>33.97</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>34.05</v>
-      </c>
-      <c r="H8" s="28" t="n">
+      <c r="I8" s="29" t="n">
         <v>33.93</v>
       </c>
-      <c r="I8" s="29" t="n">
-        <v>33.87</v>
-      </c>
       <c r="J8" s="29" t="n">
-        <v>33.81</v>
+        <v>33.69</v>
       </c>
       <c r="K8" s="30" t="n">
-        <v>33.91</v>
+        <v>33.9</v>
       </c>
       <c r="L8" s="31" t="n">
-        <v>33.81</v>
+        <v>33.59</v>
       </c>
       <c r="M8" s="31" t="n">
-        <v>33.69</v>
+        <v>33.21</v>
       </c>
       <c r="N8" s="20" t="inlineStr">
         <is>
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="O8" s="32" t="n">
-        <v>33.92</v>
+        <v>34</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>33.92</v>
+        <v>33.93</v>
       </c>
       <c r="Q8" s="33" t="n">
-        <v>33.92</v>
+        <v>34.18</v>
       </c>
       <c r="R8" s="34" t="n">
-        <v>0.12</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="9">
@@ -1166,54 +1166,54 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>22.75</v>
+        <v>22.87</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>22.55</v>
+        <v>22.63</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>22.39</v>
+        <v>22.43</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>22.38</v>
+        <v>22.51</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>22.5</v>
+        <v>22.61</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>22.3</v>
+        <v>22.37</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>22.18</v>
+        <v>22.27</v>
       </c>
       <c r="J9" s="29" t="n">
-        <v>22.1</v>
+        <v>22.13</v>
       </c>
       <c r="K9" s="30" t="n">
-        <v>22.27</v>
+        <v>22.29</v>
       </c>
       <c r="L9" s="31" t="n">
-        <v>22.11</v>
+        <v>22.09</v>
       </c>
       <c r="M9" s="31" t="n">
-        <v>21.91</v>
-      </c>
-      <c r="N9" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>21.85</v>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O9" s="32" t="n">
-        <v>22.3</v>
+        <v>22.34</v>
       </c>
       <c r="P9" s="32" t="n">
-        <v>22.29</v>
+        <v>22.31</v>
       </c>
       <c r="Q9" s="33" t="n">
-        <v>22.25</v>
+        <v>22.4</v>
       </c>
       <c r="R9" s="34" t="n">
-        <v>0.27</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="10">
@@ -1228,37 +1228,37 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>128.37</v>
+        <v>143.53</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>125.67</v>
+        <v>136.03</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>123.41</v>
+        <v>129.75</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>124.9</v>
+        <v>132.63</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>125.8</v>
+        <v>135.77</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>123.1</v>
+        <v>128.27</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>122.2</v>
+        <v>125.13</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>120.4</v>
+        <v>120.77</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>121.89</v>
+        <v>125.55</v>
       </c>
       <c r="L10" s="31" t="n">
-        <v>119.63</v>
+        <v>119.27</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>116.93</v>
+        <v>111.77</v>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>122.6</v>
+        <v>127.2</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>122.1</v>
+        <v>126.13</v>
       </c>
       <c r="Q10" s="33" t="n">
-        <v>124</v>
+        <v>129.5</v>
       </c>
       <c r="R10" s="34" t="n">
-        <v>2.23</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="11">
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>68.01000000000001</v>
+        <v>70</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>66.86</v>
+        <v>68.55</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>65.90000000000001</v>
+        <v>67.33</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>66.53</v>
+        <v>67.87</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>66.92</v>
+        <v>68.48</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>65.77</v>
+        <v>67.03</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>65.38</v>
+        <v>66.42</v>
       </c>
       <c r="J11" s="29" t="n">
-        <v>64.62</v>
+        <v>65.58</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>65.25</v>
+        <v>66.52</v>
       </c>
       <c r="L11" s="31" t="n">
-        <v>64.29000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="M11" s="31" t="n">
-        <v>63.14</v>
+        <v>63.85</v>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>65.55</v>
+        <v>66.83</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>65.34</v>
+        <v>66.63</v>
       </c>
       <c r="Q11" s="33" t="n">
-        <v>66.15000000000001</v>
+        <v>67.25</v>
       </c>
       <c r="R11" s="34" t="n">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="12">
@@ -1352,37 +1352,37 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>25.92</v>
+        <v>26.91</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>25.66</v>
+        <v>26.35</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>25.44</v>
+        <v>25.88</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>25.55</v>
+        <v>26.12</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>25.65</v>
+        <v>26.34</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>25.39</v>
+        <v>25.78</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>25.29</v>
+        <v>25.56</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>25.13</v>
+        <v>25.22</v>
       </c>
       <c r="K12" s="30" t="n">
-        <v>25.3</v>
+        <v>25.56</v>
       </c>
       <c r="L12" s="31" t="n">
-        <v>25.08</v>
+        <v>25.09</v>
       </c>
       <c r="M12" s="31" t="n">
-        <v>24.82</v>
+        <v>24.53</v>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
@@ -1390,16 +1390,16 @@
         </is>
       </c>
       <c r="O12" s="32" t="n">
-        <v>25.36</v>
+        <v>25.69</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>25.32</v>
+        <v>25.61</v>
       </c>
       <c r="Q12" s="33" t="n">
-        <v>25.44</v>
+        <v>25.9</v>
       </c>
       <c r="R12" s="34" t="n">
-        <v>0.71</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="13">
@@ -1414,54 +1414,54 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>25.91</v>
+        <v>25.89</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>25.51</v>
+        <v>25.61</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>25.17</v>
+        <v>25.38</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>25.37</v>
+        <v>25.4</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>25.51</v>
+        <v>25.56</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>25.11</v>
+        <v>25.28</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>24.97</v>
+        <v>25.12</v>
       </c>
       <c r="J13" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="L13" s="31" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="M13" s="31" t="n">
         <v>24.71</v>
       </c>
-      <c r="K13" s="30" t="n">
-        <v>24.95</v>
-      </c>
-      <c r="L13" s="31" t="n">
-        <v>24.61</v>
-      </c>
-      <c r="M13" s="31" t="n">
-        <v>24.21</v>
-      </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>25.05</v>
+        <v>25.26</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>24.98</v>
+        <v>25.24</v>
       </c>
       <c r="Q13" s="33" t="n">
-        <v>25.22</v>
+        <v>25.24</v>
       </c>
       <c r="R13" s="34" t="n">
-        <v>1.45</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="14">
@@ -1476,37 +1476,37 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>43.82</v>
+        <v>44.06</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>42.94</v>
+        <v>43.38</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>42.21</v>
+        <v>42.81</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>42.69</v>
+        <v>43.19</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>42.99</v>
+        <v>43.41</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>42.11</v>
+        <v>42.73</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>41.81</v>
+        <v>42.51</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>41.23</v>
+        <v>42.05</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>41.71</v>
+        <v>42.43</v>
       </c>
       <c r="L14" s="31" t="n">
-        <v>40.98</v>
+        <v>41.86</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>40.1</v>
+        <v>41.18</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="O14" s="32" t="n">
-        <v>41.94</v>
+        <v>42.61</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>41.78</v>
+        <v>42.48</v>
       </c>
       <c r="Q14" s="33" t="n">
-        <v>42.4</v>
+        <v>42.96</v>
       </c>
       <c r="R14" s="34" t="n">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="15">
@@ -1538,54 +1538,54 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>9.16</v>
+        <v>9.19</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>9.050000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>8.960000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>9.039999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H15" s="28" t="n">
-        <v>8.93</v>
+        <v>8.9</v>
       </c>
       <c r="I15" s="29" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="J15" s="29" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="L15" s="31" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="M15" s="31" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="N15" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O15" s="32" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="J15" s="29" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="K15" s="30" t="n">
+      <c r="P15" s="32" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="L15" s="31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="M15" s="31" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="N15" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O15" s="32" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="P15" s="32" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Q15" s="33" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="R15" s="34" t="n">
-        <v>0.9</v>
+        <v>8.869999999999999</v>
+      </c>
+      <c r="R15" s="36" t="n">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="16">
@@ -1600,37 +1600,37 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>15.85</v>
+        <v>14.84</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>15.18</v>
+        <v>14.68</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>14.62</v>
+        <v>14.54</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>14.69</v>
+        <v>14.53</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>15.07</v>
+        <v>14.64</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>14.4</v>
+        <v>14.48</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>14.02</v>
+        <v>14.37</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>13.73</v>
+        <v>14.32</v>
       </c>
       <c r="K16" s="30" t="n">
-        <v>14.25</v>
+        <v>14.46</v>
       </c>
       <c r="L16" s="31" t="n">
-        <v>13.69</v>
+        <v>14.32</v>
       </c>
       <c r="M16" s="31" t="n">
-        <v>13.02</v>
+        <v>14.16</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
@@ -1638,16 +1638,16 @@
         </is>
       </c>
       <c r="O16" s="32" t="n">
-        <v>14.35</v>
+        <v>14.47</v>
       </c>
       <c r="P16" s="32" t="n">
-        <v>14.3</v>
+        <v>14.47</v>
       </c>
       <c r="Q16" s="33" t="n">
-        <v>14.32</v>
+        <v>14.43</v>
       </c>
       <c r="R16" s="34" t="n">
-        <v>2.29</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="17">
@@ -1662,54 +1662,54 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>5.03</v>
+        <v>5.15</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>4.93</v>
+        <v>5.02</v>
       </c>
       <c r="E17" s="26" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="L17" s="31" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="M17" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O17" s="32" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="P17" s="32" t="n">
         <v>4.85</v>
       </c>
-      <c r="F17" s="27" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="K17" s="30" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="L17" s="31" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="M17" s="31" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O17" s="32" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="P17" s="32" t="n">
-        <v>4.8</v>
-      </c>
       <c r="Q17" s="33" t="n">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="R17" s="34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="18">
@@ -1724,54 +1724,54 @@
         </is>
       </c>
       <c r="C18" s="25" t="n">
-        <v>20.19</v>
+        <v>19.85</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>19.58</v>
+        <v>19.44</v>
       </c>
       <c r="E18" s="26" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F18" s="27" t="n">
         <v>19.07</v>
       </c>
-      <c r="F18" s="27" t="n">
-        <v>19.26</v>
-      </c>
       <c r="G18" s="27" t="n">
-        <v>19.53</v>
+        <v>19.33</v>
       </c>
       <c r="H18" s="28" t="n">
         <v>18.92</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>18.65</v>
+        <v>18.66</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>18.31</v>
+        <v>18.51</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>18.72</v>
+        <v>18.87</v>
       </c>
       <c r="L18" s="31" t="n">
-        <v>18.21</v>
+        <v>18.53</v>
       </c>
       <c r="M18" s="31" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="N18" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>18.12</v>
+      </c>
+      <c r="N18" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O18" s="32" t="n">
-        <v>18.85</v>
+        <v>18.91</v>
       </c>
       <c r="P18" s="32" t="n">
-        <v>18.77</v>
+        <v>18.9</v>
       </c>
       <c r="Q18" s="33" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="R18" s="34" t="n">
-        <v>2.65</v>
+        <v>18.8</v>
+      </c>
+      <c r="R18" s="36" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="19">
@@ -1786,54 +1786,54 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>26.26</v>
+        <v>26.53</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>25.74</v>
+        <v>25.99</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>25.31</v>
+        <v>25.54</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>25.31</v>
+        <v>25.68</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>25.63</v>
+        <v>25.94</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>25.11</v>
+        <v>25.4</v>
       </c>
       <c r="I19" s="29" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="J19" s="29" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="L19" s="31" t="n">
         <v>24.79</v>
       </c>
-      <c r="J19" s="29" t="n">
-        <v>24.59</v>
-      </c>
-      <c r="K19" s="30" t="n">
-        <v>25.01</v>
-      </c>
-      <c r="L19" s="31" t="n">
-        <v>24.58</v>
-      </c>
       <c r="M19" s="31" t="n">
-        <v>24.06</v>
-      </c>
-      <c r="N19" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>24.25</v>
+      </c>
+      <c r="N19" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O19" s="32" t="n">
-        <v>25.08</v>
+        <v>25.34</v>
       </c>
       <c r="P19" s="32" t="n">
-        <v>25.05</v>
+        <v>25.28</v>
       </c>
       <c r="Q19" s="33" t="n">
-        <v>25</v>
-      </c>
-      <c r="R19" s="35" t="n">
-        <v>-0.48</v>
+        <v>25.42</v>
+      </c>
+      <c r="R19" s="34" t="n">
+        <v>1.68</v>
       </c>
     </row>
     <row r="20">
@@ -1848,37 +1848,37 @@
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>73.86</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>71.26000000000001</v>
+        <v>72.52</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>69.08</v>
+        <v>70.59</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>70.42</v>
+        <v>71.17</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>71.33</v>
+        <v>72.28</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>68.73</v>
+        <v>69.98</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>67.81999999999999</v>
+        <v>68.87</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>66.13</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>67.62</v>
+        <v>69.31</v>
       </c>
       <c r="L20" s="31" t="n">
-        <v>65.44</v>
+        <v>67.38</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>62.84</v>
+        <v>65.08</v>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="O20" s="32" t="n">
-        <v>68.28</v>
+        <v>69.73</v>
       </c>
       <c r="P20" s="32" t="n">
-        <v>67.81999999999999</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="Q20" s="33" t="n">
-        <v>69.5</v>
+        <v>70.05</v>
       </c>
       <c r="R20" s="34" t="n">
-        <v>4.04</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="21">
@@ -1910,54 +1910,54 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>13.06</v>
+        <v>12.54</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>12.67</v>
+        <v>12.36</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>12.34</v>
+        <v>12.21</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>12.39</v>
+        <v>12.2</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>12.6</v>
+        <v>12.31</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>12.21</v>
+        <v>12.13</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>12</v>
+        <v>12.02</v>
       </c>
       <c r="J21" s="29" t="n">
-        <v>11.82</v>
+        <v>11.95</v>
       </c>
       <c r="K21" s="30" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="L21" s="31" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="M21" s="31" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="N21" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O21" s="32" t="n">
         <v>12.13</v>
       </c>
-      <c r="L21" s="31" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="M21" s="31" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="N21" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O21" s="32" t="n">
-        <v>12.18</v>
-      </c>
       <c r="P21" s="32" t="n">
-        <v>12.16</v>
+        <v>12.12</v>
       </c>
       <c r="Q21" s="33" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="R21" s="34" t="n">
-        <v>1</v>
+        <v>12.08</v>
+      </c>
+      <c r="R21" s="36" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="22">
@@ -1972,37 +1972,37 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>18.63</v>
+        <v>19.66</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>18.55</v>
+        <v>19.2</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>18.48</v>
+        <v>18.82</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>18.47</v>
+        <v>19.06</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>18.53</v>
+        <v>19.22</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.45</v>
+        <v>18.76</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>18.39</v>
+        <v>18.6</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>18.37</v>
+        <v>18.3</v>
       </c>
       <c r="K22" s="30" t="n">
-        <v>18.44</v>
+        <v>18.56</v>
       </c>
       <c r="L22" s="31" t="n">
-        <v>18.37</v>
+        <v>18.18</v>
       </c>
       <c r="M22" s="31" t="n">
-        <v>18.29</v>
+        <v>17.72</v>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
@@ -2010,16 +2010,16 @@
         </is>
       </c>
       <c r="O22" s="32" t="n">
-        <v>18.45</v>
+        <v>18.68</v>
       </c>
       <c r="P22" s="32" t="n">
-        <v>18.44</v>
+        <v>18.6</v>
       </c>
       <c r="Q22" s="33" t="n">
-        <v>18.42</v>
+        <v>18.9</v>
       </c>
       <c r="R22" s="34" t="n">
-        <v>0.44</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="23">
@@ -2034,54 +2034,54 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>37.51</v>
+        <v>37.46</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>36.49</v>
+        <v>36.68</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>35.64</v>
+        <v>36.03</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>36.2</v>
+        <v>35.94</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>36.54</v>
+        <v>36.46</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>35.52</v>
+        <v>35.68</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>35.18</v>
+        <v>35.16</v>
       </c>
       <c r="J23" s="29" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>35.06</v>
+        <v>35.59</v>
       </c>
       <c r="L23" s="31" t="n">
-        <v>34.21</v>
+        <v>34.94</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>33.19</v>
-      </c>
-      <c r="N23" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>34.16</v>
+      </c>
+      <c r="N23" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O23" s="32" t="n">
-        <v>35.33</v>
+        <v>35.67</v>
       </c>
       <c r="P23" s="32" t="n">
-        <v>35.14</v>
+        <v>35.65</v>
       </c>
       <c r="Q23" s="33" t="n">
-        <v>35.86</v>
-      </c>
-      <c r="R23" s="34" t="n">
-        <v>3.16</v>
+        <v>35.42</v>
+      </c>
+      <c r="R23" s="36" t="n">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="24">
@@ -2096,54 +2096,54 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>15.56</v>
+        <v>15.79</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>15.36</v>
+        <v>15.5</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>15.2</v>
+        <v>15.26</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>15.23</v>
+        <v>15.29</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>15.34</v>
+        <v>15.45</v>
       </c>
       <c r="H24" s="28" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" s="29" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="K24" s="30" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="L24" s="31" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="M24" s="31" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="N24" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O24" s="32" t="n">
         <v>15.14</v>
       </c>
-      <c r="I24" s="29" t="n">
-        <v>15.03</v>
-      </c>
-      <c r="J24" s="29" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="K24" s="30" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="L24" s="31" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="M24" s="31" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="N24" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O24" s="32" t="n">
+      <c r="P24" s="32" t="n">
         <v>15.12</v>
-      </c>
-      <c r="P24" s="32" t="n">
-        <v>15.1</v>
       </c>
       <c r="Q24" s="33" t="n">
         <v>15.13</v>
       </c>
       <c r="R24" s="34" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2158,37 +2158,37 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>40.19</v>
+        <v>40.92</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>39.21</v>
+        <v>39.92</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>38.38</v>
+        <v>39.08</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>38.87</v>
+        <v>39.01</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>39.23</v>
+        <v>39.65</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>38.25</v>
+        <v>38.65</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>37.89</v>
+        <v>38.01</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>37.27</v>
+        <v>37.65</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>37.84</v>
+        <v>38.52</v>
       </c>
       <c r="L25" s="31" t="n">
-        <v>37.01</v>
+        <v>37.68</v>
       </c>
       <c r="M25" s="31" t="n">
-        <v>36.03</v>
+        <v>36.68</v>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -2196,16 +2196,16 @@
         </is>
       </c>
       <c r="O25" s="32" t="n">
-        <v>38.08</v>
+        <v>38.63</v>
       </c>
       <c r="P25" s="32" t="n">
-        <v>37.91</v>
+        <v>38.6</v>
       </c>
       <c r="Q25" s="33" t="n">
-        <v>38.52</v>
-      </c>
-      <c r="R25" s="34" t="n">
-        <v>2.45</v>
+        <v>38.36</v>
+      </c>
+      <c r="R25" s="36" t="n">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="26">
@@ -2220,54 +2220,54 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>49.62</v>
+        <v>50.72</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>48.62</v>
+        <v>49.4</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>47.78</v>
+        <v>48.29</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>47.8</v>
+        <v>48.23</v>
       </c>
       <c r="G26" s="27" t="n">
-        <v>48.4</v>
+        <v>49.07</v>
       </c>
       <c r="H26" s="28" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <v>46.91</v>
+      </c>
+      <c r="J26" s="29" t="n">
+        <v>46.43</v>
+      </c>
+      <c r="K26" s="30" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="L26" s="31" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="M26" s="31" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O26" s="32" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="P26" s="32" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="Q26" s="33" t="n">
         <v>47.4</v>
       </c>
-      <c r="I26" s="29" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="J26" s="29" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="K26" s="30" t="n">
-        <v>47.22</v>
-      </c>
-      <c r="L26" s="31" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="M26" s="31" t="n">
-        <v>45.38</v>
-      </c>
-      <c r="N26" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O26" s="32" t="n">
-        <v>47.35</v>
-      </c>
-      <c r="P26" s="32" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="Q26" s="33" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="R26" s="35" t="n">
-        <v>-0.21</v>
+      <c r="R26" s="34" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="27">
@@ -2282,54 +2282,54 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>194.03</v>
+        <v>198.1</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>191.23</v>
+        <v>193.9</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>188.88</v>
+        <v>190.38</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>189.37</v>
+        <v>191.83</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>190.83</v>
+        <v>193.67</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>188.03</v>
+        <v>189.47</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>186.57</v>
+        <v>187.63</v>
       </c>
       <c r="J27" s="29" t="n">
-        <v>185.23</v>
+        <v>185.27</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>187.32</v>
+        <v>188.02</v>
       </c>
       <c r="L27" s="31" t="n">
-        <v>184.97</v>
+        <v>184.5</v>
       </c>
       <c r="M27" s="31" t="n">
-        <v>182.17</v>
-      </c>
-      <c r="N27" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>180.3</v>
+      </c>
+      <c r="N27" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O27" s="32" t="n">
-        <v>187.78</v>
+        <v>188.91</v>
       </c>
       <c r="P27" s="32" t="n">
-        <v>187.53</v>
+        <v>188.35</v>
       </c>
       <c r="Q27" s="33" t="n">
-        <v>187.9</v>
+        <v>190</v>
       </c>
       <c r="R27" s="34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="28">
@@ -2344,37 +2344,37 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>95.40000000000001</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>92</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>89.15000000000001</v>
+        <v>88.56</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>90.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>91.7</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>88.3</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>86.7</v>
+        <v>87.3</v>
       </c>
       <c r="J28" s="29" t="n">
-        <v>84.90000000000001</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>87.25</v>
+        <v>87.44</v>
       </c>
       <c r="L28" s="31" t="n">
-        <v>84.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>81</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="O28" s="32" t="n">
-        <v>87.91</v>
+        <v>87.87</v>
       </c>
       <c r="P28" s="32" t="n">
-        <v>87.51000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="Q28" s="33" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="R28" s="34" t="n">
-        <v>3.93</v>
+        <v>88.45</v>
+      </c>
+      <c r="R28" s="36" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="29">
@@ -2406,54 +2406,54 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>22.75</v>
+        <v>22.69</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>22.15</v>
+        <v>22.14</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>21.65</v>
+        <v>21.68</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>21.61</v>
+        <v>21.89</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>21.99</v>
+        <v>22.12</v>
       </c>
       <c r="H29" s="28" t="n">
-        <v>21.39</v>
+        <v>21.57</v>
       </c>
       <c r="I29" s="29" t="n">
-        <v>21.01</v>
+        <v>21.34</v>
       </c>
       <c r="J29" s="29" t="n">
-        <v>20.79</v>
+        <v>21.02</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>21.31</v>
+        <v>21.37</v>
       </c>
       <c r="L29" s="31" t="n">
-        <v>20.81</v>
+        <v>20.91</v>
       </c>
       <c r="M29" s="31" t="n">
-        <v>20.21</v>
-      </c>
-      <c r="N29" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>20.36</v>
+      </c>
+      <c r="N29" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O29" s="32" t="n">
-        <v>21.38</v>
+        <v>21.49</v>
       </c>
       <c r="P29" s="32" t="n">
-        <v>21.36</v>
+        <v>21.41</v>
       </c>
       <c r="Q29" s="33" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="R29" s="35" t="n">
-        <v>-1.49</v>
+        <v>21.66</v>
+      </c>
+      <c r="R29" s="34" t="n">
+        <v>2.07</v>
       </c>
     </row>
     <row r="30">
@@ -2468,37 +2468,37 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>82.89</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>81.94</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>81.14</v>
+        <v>81.67</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>81.67</v>
+        <v>82.37</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>81.98</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>81.03</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>80.72</v>
+        <v>80.87</v>
       </c>
       <c r="J30" s="29" t="n">
-        <v>80.08</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>80.61</v>
+        <v>80.83</v>
       </c>
       <c r="L30" s="31" t="n">
-        <v>79.81</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>78.86</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="O30" s="32" t="n">
-        <v>80.86</v>
+        <v>81.19</v>
       </c>
       <c r="P30" s="32" t="n">
-        <v>80.68000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="Q30" s="33" t="n">
-        <v>81.34999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="R30" s="34" t="n">
-        <v>1.37</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="31">
@@ -2530,54 +2530,54 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>34.02</v>
+        <v>38.47</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>33.02</v>
+        <v>35.77</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>32.18</v>
+        <v>33.51</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>32.07</v>
+        <v>33.97</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>32.73</v>
+        <v>35.39</v>
       </c>
       <c r="H31" s="28" t="n">
-        <v>31.73</v>
+        <v>32.69</v>
       </c>
       <c r="I31" s="29" t="n">
-        <v>31.07</v>
+        <v>31.27</v>
       </c>
       <c r="J31" s="29" t="n">
-        <v>30.73</v>
+        <v>29.99</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>31.62</v>
+        <v>31.99</v>
       </c>
       <c r="L31" s="31" t="n">
-        <v>30.78</v>
+        <v>29.73</v>
       </c>
       <c r="M31" s="31" t="n">
-        <v>29.78</v>
-      </c>
-      <c r="N31" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>27.03</v>
+      </c>
+      <c r="N31" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O31" s="32" t="n">
-        <v>31.72</v>
+        <v>32.45</v>
       </c>
       <c r="P31" s="32" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="Q31" s="33" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="R31" s="35" t="n">
-        <v>-2.18</v>
+        <v>32.56</v>
+      </c>
+      <c r="R31" s="34" t="n">
+        <v>3.69</v>
       </c>
     </row>
     <row r="32">
@@ -2592,54 +2592,54 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>51.53</v>
+        <v>52.77</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>50.77</v>
+        <v>51.77</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>50.13</v>
+        <v>50.93</v>
       </c>
       <c r="F32" s="27" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="H32" s="28" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="J32" s="29" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="K32" s="30" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="L32" s="31" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="M32" s="31" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O32" s="32" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="P32" s="32" t="n">
         <v>50.45</v>
       </c>
-      <c r="G32" s="27" t="n">
-        <v>50.76</v>
-      </c>
-      <c r="H32" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>49.69</v>
-      </c>
-      <c r="J32" s="29" t="n">
-        <v>49.24</v>
-      </c>
-      <c r="K32" s="30" t="n">
-        <v>49.71</v>
-      </c>
-      <c r="L32" s="31" t="n">
-        <v>49.07</v>
-      </c>
-      <c r="M32" s="31" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="N32" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O32" s="32" t="n">
-        <v>49.88</v>
-      </c>
-      <c r="P32" s="32" t="n">
-        <v>49.77</v>
-      </c>
       <c r="Q32" s="33" t="n">
-        <v>50.15</v>
+        <v>50.95</v>
       </c>
       <c r="R32" s="34" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="33">
@@ -2654,37 +2654,37 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>127.3</v>
+        <v>132.03</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>126</v>
+        <v>129.23</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>124.91</v>
+        <v>126.88</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>125.5</v>
+        <v>128.43</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>126</v>
+        <v>129.37</v>
       </c>
       <c r="H33" s="28" t="n">
-        <v>124.7</v>
+        <v>126.57</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>124.2</v>
+        <v>125.63</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>123.4</v>
+        <v>123.77</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>124.19</v>
+        <v>125.32</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>123.1</v>
+        <v>122.97</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>121.8</v>
+        <v>120.17</v>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
@@ -2692,16 +2692,16 @@
         </is>
       </c>
       <c r="O33" s="32" t="n">
-        <v>124.49</v>
+        <v>126.05</v>
       </c>
       <c r="P33" s="32" t="n">
-        <v>124.29</v>
+        <v>125.53</v>
       </c>
       <c r="Q33" s="33" t="n">
-        <v>125</v>
+        <v>127.5</v>
       </c>
       <c r="R33" s="34" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2716,54 +2716,54 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>53.89</v>
+        <v>54.39</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>52.94</v>
+        <v>53.19</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>52.14</v>
+        <v>52.19</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>52.27</v>
+        <v>52.08</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>52.78</v>
+        <v>52.87</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>51.83</v>
+        <v>51.67</v>
       </c>
       <c r="I34" s="29" t="n">
-        <v>51.32</v>
+        <v>50.88</v>
       </c>
       <c r="J34" s="29" t="n">
-        <v>50.88</v>
+        <v>50.47</v>
       </c>
       <c r="K34" s="30" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="L34" s="31" t="n">
+        <v>50.51</v>
+      </c>
+      <c r="M34" s="31" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="N34" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O34" s="32" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="P34" s="32" t="n">
         <v>51.61</v>
       </c>
-      <c r="L34" s="31" t="n">
-        <v>50.81</v>
-      </c>
-      <c r="M34" s="31" t="n">
-        <v>49.86</v>
-      </c>
-      <c r="N34" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O34" s="32" t="n">
-        <v>51.76</v>
-      </c>
-      <c r="P34" s="32" t="n">
-        <v>51.68</v>
-      </c>
       <c r="Q34" s="33" t="n">
-        <v>51.75</v>
-      </c>
-      <c r="R34" s="34" t="n">
-        <v>1.07</v>
+        <v>51.3</v>
+      </c>
+      <c r="R34" s="36" t="n">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="35">
@@ -2778,54 +2778,54 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>27.39</v>
+        <v>26.89</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>26.59</v>
+        <v>26.45</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>25.92</v>
+        <v>26.08</v>
       </c>
       <c r="F35" s="27" t="n">
-        <v>26.3</v>
+        <v>26.06</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>26.6</v>
+        <v>26.34</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="I35" s="29" t="n">
-        <v>25.5</v>
+        <v>25.62</v>
       </c>
       <c r="J35" s="29" t="n">
-        <v>25</v>
+        <v>25.46</v>
       </c>
       <c r="K35" s="30" t="n">
-        <v>25.48</v>
+        <v>25.84</v>
       </c>
       <c r="L35" s="31" t="n">
-        <v>24.81</v>
+        <v>25.47</v>
       </c>
       <c r="M35" s="31" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="N35" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>25.03</v>
+      </c>
+      <c r="N35" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O35" s="32" t="n">
-        <v>25.67</v>
+        <v>25.89</v>
       </c>
       <c r="P35" s="32" t="n">
-        <v>25.54</v>
+        <v>25.87</v>
       </c>
       <c r="Q35" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="R35" s="34" t="n">
-        <v>2.69</v>
+        <v>25.78</v>
+      </c>
+      <c r="R35" s="36" t="n">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="36">
@@ -2840,37 +2840,37 @@
         </is>
       </c>
       <c r="C36" s="25" t="n">
-        <v>26.61</v>
+        <v>27.68</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>26.37</v>
+        <v>27.04</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>26.17</v>
+        <v>26.5</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>26.25</v>
+        <v>26.64</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>26.35</v>
+        <v>26.96</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>26.11</v>
+        <v>26.32</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>26.01</v>
+        <v>26</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>25.87</v>
+        <v>25.68</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>26.03</v>
+        <v>26.14</v>
       </c>
       <c r="L36" s="31" t="n">
-        <v>25.83</v>
+        <v>25.6</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>25.59</v>
+        <v>24.96</v>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="O36" s="32" t="n">
-        <v>26.08</v>
+        <v>26.26</v>
       </c>
       <c r="P36" s="32" t="n">
-        <v>26.05</v>
+        <v>26.19</v>
       </c>
       <c r="Q36" s="33" t="n">
-        <v>26.14</v>
+        <v>26.32</v>
       </c>
       <c r="R36" s="34" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2902,54 +2902,54 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="D37" s="25" t="n">
         <v>9.84</v>
       </c>
       <c r="E37" s="26" t="n">
-        <v>9.69</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F37" s="27" t="n">
-        <v>9.77</v>
+        <v>9.73</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>9.84</v>
+        <v>9.81</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>9.67</v>
+        <v>9.65</v>
       </c>
       <c r="I37" s="29" t="n">
-        <v>9.6</v>
+        <v>9.57</v>
       </c>
       <c r="J37" s="29" t="n">
-        <v>9.5</v>
+        <v>9.49</v>
       </c>
       <c r="K37" s="30" t="n">
-        <v>9.6</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L37" s="31" t="n">
-        <v>9.449999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="M37" s="31" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="N37" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>9.32</v>
+      </c>
+      <c r="N37" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O37" s="32" t="n">
         <v>9.640000000000001</v>
       </c>
       <c r="P37" s="32" t="n">
-        <v>9.609999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q37" s="33" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="R37" s="34" t="n">
-        <v>1.68</v>
+        <v>9.640000000000001</v>
+      </c>
+      <c r="R37" s="36" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="38">
@@ -2964,53 +2964,53 @@
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>32.01</v>
+        <v>31.89</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>31.67</v>
+        <v>31.59</v>
       </c>
       <c r="E38" s="26" t="n">
-        <v>31.39</v>
+        <v>31.33</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>31.43</v>
+        <v>31.31</v>
       </c>
       <c r="G38" s="27" t="n">
-        <v>31.61</v>
+        <v>31.51</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>31.27</v>
+        <v>31.21</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>31.09</v>
+        <v>31.01</v>
       </c>
       <c r="J38" s="29" t="n">
-        <v>30.93</v>
+        <v>30.91</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>31.19</v>
+        <v>31.17</v>
       </c>
       <c r="L38" s="31" t="n">
         <v>30.91</v>
       </c>
       <c r="M38" s="31" t="n">
-        <v>30.57</v>
-      </c>
-      <c r="N38" s="36" t="inlineStr">
+        <v>30.61</v>
+      </c>
+      <c r="N38" s="35" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O38" s="32" t="n">
-        <v>31.25</v>
+        <v>31.2</v>
       </c>
       <c r="P38" s="32" t="n">
-        <v>31.22</v>
+        <v>31.19</v>
       </c>
       <c r="Q38" s="33" t="n">
-        <v>31.24</v>
-      </c>
-      <c r="R38" s="35" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="R38" s="36" t="n">
         <v>-0.38</v>
       </c>
     </row>
@@ -3026,37 +3026,37 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>192.56</v>
+        <v>203.38</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>190.36</v>
+        <v>197.58</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>188.52</v>
+        <v>192.72</v>
       </c>
       <c r="F39" s="27" t="n">
-        <v>189.47</v>
+        <v>194.87</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>190.33</v>
+        <v>197.33</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>188.13</v>
+        <v>191.53</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>187.27</v>
+        <v>189.07</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>185.93</v>
+        <v>185.73</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>187.28</v>
+        <v>189.48</v>
       </c>
       <c r="L39" s="31" t="n">
-        <v>185.44</v>
+        <v>184.62</v>
       </c>
       <c r="M39" s="31" t="n">
-        <v>183.24</v>
+        <v>178.82</v>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
@@ -3064,16 +3064,16 @@
         </is>
       </c>
       <c r="O39" s="32" t="n">
-        <v>187.79</v>
+        <v>190.73</v>
       </c>
       <c r="P39" s="32" t="n">
-        <v>187.46</v>
+        <v>189.93</v>
       </c>
       <c r="Q39" s="33" t="n">
-        <v>188.6</v>
+        <v>192.4</v>
       </c>
       <c r="R39" s="34" t="n">
-        <v>1.18</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="40">
@@ -3088,37 +3088,37 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>13.82</v>
+        <v>14.58</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>13.66</v>
+        <v>14.13</v>
       </c>
       <c r="E40" s="26" t="n">
-        <v>13.52</v>
+        <v>13.75</v>
       </c>
       <c r="F40" s="27" t="n">
-        <v>13.52</v>
+        <v>13.9</v>
       </c>
       <c r="G40" s="27" t="n">
-        <v>13.62</v>
+        <v>14.1</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>13.46</v>
+        <v>13.65</v>
       </c>
       <c r="I40" s="29" t="n">
-        <v>13.36</v>
+        <v>13.45</v>
       </c>
       <c r="J40" s="29" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>13.44</v>
+        <v>13.5</v>
       </c>
       <c r="L40" s="31" t="n">
-        <v>13.3</v>
+        <v>13.12</v>
       </c>
       <c r="M40" s="31" t="n">
-        <v>13.14</v>
+        <v>12.67</v>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
@@ -3126,16 +3126,16 @@
         </is>
       </c>
       <c r="O40" s="32" t="n">
-        <v>13.45</v>
+        <v>13.59</v>
       </c>
       <c r="P40" s="32" t="n">
-        <v>13.45</v>
+        <v>13.53</v>
       </c>
       <c r="Q40" s="33" t="n">
-        <v>13.42</v>
+        <v>13.7</v>
       </c>
       <c r="R40" s="34" t="n">
-        <v>0.3</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="41">
@@ -3150,37 +3150,37 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>21.69</v>
+        <v>22.26</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>21.38</v>
+        <v>21.76</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>21.12</v>
+        <v>21.34</v>
       </c>
       <c r="F41" s="27" t="n">
-        <v>21.14</v>
+        <v>21.55</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>21.32</v>
+        <v>21.75</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>21.01</v>
+        <v>21.25</v>
       </c>
       <c r="I41" s="29" t="n">
-        <v>20.83</v>
+        <v>21.05</v>
       </c>
       <c r="J41" s="29" t="n">
-        <v>20.7</v>
+        <v>20.75</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>20.95</v>
+        <v>21.06</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>20.69</v>
+        <v>20.64</v>
       </c>
       <c r="M41" s="31" t="n">
-        <v>20.38</v>
+        <v>20.14</v>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="O41" s="32" t="n">
-        <v>20.99</v>
+        <v>21.17</v>
       </c>
       <c r="P41" s="32" t="n">
-        <v>20.97</v>
+        <v>21.1</v>
       </c>
       <c r="Q41" s="33" t="n">
-        <v>20.96</v>
+        <v>21.35</v>
       </c>
       <c r="R41" s="34" t="n">
-        <v>0.53</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="42">
@@ -3212,54 +3212,54 @@
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>182.17</v>
+        <v>183.07</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>180.77</v>
+        <v>180.37</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>179.59</v>
+        <v>178.11</v>
       </c>
       <c r="F42" s="27" t="n">
-        <v>179.77</v>
+        <v>178.33</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>180.53</v>
+        <v>179.87</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>179.13</v>
+        <v>177.17</v>
       </c>
       <c r="I42" s="29" t="n">
-        <v>178.37</v>
+        <v>175.63</v>
       </c>
       <c r="J42" s="29" t="n">
-        <v>177.73</v>
+        <v>174.47</v>
       </c>
       <c r="K42" s="30" t="n">
-        <v>178.81</v>
+        <v>176.59</v>
       </c>
       <c r="L42" s="31" t="n">
-        <v>177.63</v>
+        <v>174.33</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>176.23</v>
-      </c>
-      <c r="N42" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>171.63</v>
+      </c>
+      <c r="N42" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O42" s="32" t="n">
-        <v>179.03</v>
+        <v>176.99</v>
       </c>
       <c r="P42" s="32" t="n">
-        <v>178.92</v>
+        <v>176.8</v>
       </c>
       <c r="Q42" s="33" t="n">
-        <v>179</v>
-      </c>
-      <c r="R42" s="34" t="n">
-        <v>0</v>
+        <v>176.8</v>
+      </c>
+      <c r="R42" s="36" t="n">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="43">
@@ -3274,37 +3274,37 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>42.41</v>
+        <v>41.95</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>40.49</v>
+        <v>40.67</v>
       </c>
       <c r="E43" s="26" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="F43" s="27" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="G43" s="27" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="H43" s="28" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="I43" s="29" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="J43" s="29" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="K43" s="30" t="n">
         <v>38.88</v>
       </c>
-      <c r="F43" s="27" t="n">
-        <v>39.94</v>
-      </c>
-      <c r="G43" s="27" t="n">
-        <v>40.58</v>
-      </c>
-      <c r="H43" s="28" t="n">
-        <v>38.66</v>
-      </c>
-      <c r="I43" s="29" t="n">
-        <v>38.02</v>
-      </c>
-      <c r="J43" s="29" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="K43" s="30" t="n">
-        <v>37.8</v>
-      </c>
       <c r="L43" s="31" t="n">
-        <v>36.19</v>
+        <v>37.81</v>
       </c>
       <c r="M43" s="31" t="n">
-        <v>34.27</v>
+        <v>36.53</v>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
@@ -3312,16 +3312,16 @@
         </is>
       </c>
       <c r="O43" s="32" t="n">
-        <v>38.31</v>
+        <v>39.08</v>
       </c>
       <c r="P43" s="32" t="n">
-        <v>37.95</v>
+        <v>38.98</v>
       </c>
       <c r="Q43" s="33" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="R43" s="34" t="n">
-        <v>5.65</v>
+        <v>39.08</v>
+      </c>
+      <c r="R43" s="36" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>28.91</v>
+        <v>29.94</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>28.25</v>
+        <v>29.1</v>
       </c>
       <c r="E44" s="26" t="n">
-        <v>27.69</v>
+        <v>28.4</v>
       </c>
       <c r="F44" s="27" t="n">
-        <v>28.03</v>
+        <v>28.51</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>28.27</v>
+        <v>28.97</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>27.61</v>
+        <v>28.13</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>27.37</v>
+        <v>27.67</v>
       </c>
       <c r="J44" s="29" t="n">
-        <v>26.95</v>
+        <v>27.29</v>
       </c>
       <c r="K44" s="30" t="n">
-        <v>27.33</v>
+        <v>27.92</v>
       </c>
       <c r="L44" s="31" t="n">
-        <v>26.77</v>
+        <v>27.22</v>
       </c>
       <c r="M44" s="31" t="n">
-        <v>26.11</v>
+        <v>26.38</v>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
@@ -3374,16 +3374,16 @@
         </is>
       </c>
       <c r="O44" s="32" t="n">
-        <v>27.49</v>
+        <v>28.06</v>
       </c>
       <c r="P44" s="32" t="n">
-        <v>27.38</v>
+        <v>27.99</v>
       </c>
       <c r="Q44" s="33" t="n">
-        <v>27.8</v>
+        <v>28.06</v>
       </c>
       <c r="R44" s="34" t="n">
-        <v>2.21</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -3398,37 +3398,37 @@
         </is>
       </c>
       <c r="C45" s="25" t="n">
-        <v>26.75</v>
+        <v>26.9</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>26.61</v>
+        <v>26.7</v>
       </c>
       <c r="E45" s="26" t="n">
-        <v>26.49</v>
+        <v>26.54</v>
       </c>
       <c r="F45" s="27" t="n">
-        <v>26.49</v>
+        <v>26.65</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>26.57</v>
+        <v>26.71</v>
       </c>
       <c r="H45" s="28" t="n">
-        <v>26.43</v>
+        <v>26.51</v>
       </c>
       <c r="I45" s="29" t="n">
-        <v>26.35</v>
+        <v>26.45</v>
       </c>
       <c r="J45" s="29" t="n">
-        <v>26.29</v>
+        <v>26.31</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>26.41</v>
+        <v>26.42</v>
       </c>
       <c r="L45" s="31" t="n">
-        <v>26.29</v>
+        <v>26.26</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>26.15</v>
+        <v>26.06</v>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
@@ -3436,16 +3436,16 @@
         </is>
       </c>
       <c r="O45" s="32" t="n">
-        <v>26.43</v>
+        <v>26.48</v>
       </c>
       <c r="P45" s="32" t="n">
-        <v>26.42</v>
+        <v>26.44</v>
       </c>
       <c r="Q45" s="33" t="n">
-        <v>26.4</v>
+        <v>26.58</v>
       </c>
       <c r="R45" s="34" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="46">
@@ -3460,54 +3460,54 @@
         </is>
       </c>
       <c r="C46" s="25" t="n">
-        <v>8.210000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>8.09</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E46" s="26" t="n">
         <v>7.99</v>
       </c>
       <c r="F46" s="27" t="n">
-        <v>8.039999999999999</v>
+        <v>7.99</v>
       </c>
       <c r="G46" s="27" t="n">
         <v>8.09</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>7.97</v>
+        <v>7.92</v>
       </c>
       <c r="I46" s="29" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="J46" s="29" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="K46" s="30" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L46" s="31" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="M46" s="31" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="N46" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O46" s="32" t="n">
         <v>7.92</v>
       </c>
-      <c r="J46" s="29" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="K46" s="30" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="L46" s="31" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="M46" s="31" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="N46" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O46" s="32" t="n">
-        <v>7.95</v>
-      </c>
       <c r="P46" s="32" t="n">
-        <v>7.94</v>
+        <v>7.91</v>
       </c>
       <c r="Q46" s="33" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="R46" s="34" t="n">
-        <v>1.27</v>
+        <v>7.88</v>
+      </c>
+      <c r="R46" s="36" t="n">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="47">
@@ -3522,54 +3522,54 @@
         </is>
       </c>
       <c r="C47" s="25" t="n">
-        <v>12.93</v>
+        <v>12.76</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>12.65</v>
+        <v>12.58</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="F47" s="27" t="n">
-        <v>12.44</v>
+        <v>12.48</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>12.6</v>
+        <v>12.56</v>
       </c>
       <c r="H47" s="28" t="n">
-        <v>12.32</v>
+        <v>12.38</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>12.16</v>
+        <v>12.3</v>
       </c>
       <c r="J47" s="29" t="n">
-        <v>12.04</v>
+        <v>12.2</v>
       </c>
       <c r="K47" s="30" t="n">
-        <v>12.26</v>
+        <v>12.33</v>
       </c>
       <c r="L47" s="31" t="n">
-        <v>12.03</v>
+        <v>12.18</v>
       </c>
       <c r="M47" s="31" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="N47" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>12</v>
+      </c>
+      <c r="N47" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O47" s="32" t="n">
-        <v>12.3</v>
+        <v>12.36</v>
       </c>
       <c r="P47" s="32" t="n">
-        <v>12.28</v>
+        <v>12.34</v>
       </c>
       <c r="Q47" s="33" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="R47" s="35" t="n">
-        <v>-0.08</v>
+        <v>12.39</v>
+      </c>
+      <c r="R47" s="34" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="48">
@@ -3584,37 +3584,37 @@
         </is>
       </c>
       <c r="C48" s="25" t="n">
-        <v>206.19</v>
+        <v>210.37</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>203.29</v>
+        <v>206.37</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>200.86</v>
+        <v>203.02</v>
       </c>
       <c r="F48" s="27" t="n">
-        <v>201.47</v>
+        <v>204.5</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>202.93</v>
+        <v>206.2</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>200.03</v>
+        <v>202.2</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>198.57</v>
+        <v>200.5</v>
       </c>
       <c r="J48" s="29" t="n">
-        <v>197.13</v>
+        <v>198.2</v>
       </c>
       <c r="K48" s="30" t="n">
-        <v>199.24</v>
+        <v>200.78</v>
       </c>
       <c r="L48" s="31" t="n">
-        <v>196.81</v>
+        <v>197.43</v>
       </c>
       <c r="M48" s="31" t="n">
-        <v>193.91</v>
+        <v>193.43</v>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
@@ -3622,16 +3622,16 @@
         </is>
       </c>
       <c r="O48" s="32" t="n">
-        <v>199.75</v>
+        <v>201.65</v>
       </c>
       <c r="P48" s="32" t="n">
-        <v>199.46</v>
+        <v>201.09</v>
       </c>
       <c r="Q48" s="33" t="n">
-        <v>200</v>
+        <v>202.8</v>
       </c>
       <c r="R48" s="34" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="49">
@@ -3646,54 +3646,54 @@
         </is>
       </c>
       <c r="C49" s="25" t="n">
-        <v>49.63</v>
+        <v>49.27</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>49.07</v>
+        <v>48.77</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>48.6</v>
+        <v>48.35</v>
       </c>
       <c r="F49" s="27" t="n">
-        <v>48.63</v>
+        <v>48.45</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>48.95</v>
+        <v>48.71</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>48.39</v>
+        <v>48.21</v>
       </c>
       <c r="I49" s="29" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="J49" s="29" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="K49" s="30" t="n">
         <v>48.07</v>
       </c>
-      <c r="J49" s="29" t="n">
-        <v>47.83</v>
-      </c>
-      <c r="K49" s="30" t="n">
-        <v>48.28</v>
-      </c>
       <c r="L49" s="31" t="n">
-        <v>47.81</v>
+        <v>47.65</v>
       </c>
       <c r="M49" s="31" t="n">
-        <v>47.25</v>
-      </c>
-      <c r="N49" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>47.15</v>
+      </c>
+      <c r="N49" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O49" s="32" t="n">
-        <v>48.36</v>
+        <v>48.16</v>
       </c>
       <c r="P49" s="32" t="n">
-        <v>48.33</v>
+        <v>48.11</v>
       </c>
       <c r="Q49" s="33" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="R49" s="34" t="n">
-        <v>0.12</v>
+        <v>48.2</v>
+      </c>
+      <c r="R49" s="36" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="50">
@@ -3708,37 +3708,37 @@
         </is>
       </c>
       <c r="C50" s="25" t="n">
-        <v>35.38</v>
+        <v>36.2</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>34.28</v>
+        <v>35.2</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>33.36</v>
+        <v>34.36</v>
       </c>
       <c r="F50" s="27" t="n">
-        <v>33.93</v>
+        <v>34.73</v>
       </c>
       <c r="G50" s="27" t="n">
-        <v>34.31</v>
+        <v>35.15</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>33.21</v>
+        <v>34.15</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>32.83</v>
+        <v>33.73</v>
       </c>
       <c r="J50" s="29" t="n">
-        <v>32.11</v>
+        <v>33.15</v>
       </c>
       <c r="K50" s="30" t="n">
-        <v>32.74</v>
+        <v>33.8</v>
       </c>
       <c r="L50" s="31" t="n">
-        <v>31.82</v>
+        <v>32.96</v>
       </c>
       <c r="M50" s="31" t="n">
-        <v>30.72</v>
+        <v>31.96</v>
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
@@ -3746,16 +3746,16 @@
         </is>
       </c>
       <c r="O50" s="32" t="n">
-        <v>33.02</v>
+        <v>34.02</v>
       </c>
       <c r="P50" s="32" t="n">
-        <v>32.83</v>
+        <v>33.88</v>
       </c>
       <c r="Q50" s="33" t="n">
-        <v>33.54</v>
+        <v>34.3</v>
       </c>
       <c r="R50" s="34" t="n">
-        <v>3.26</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="51">
@@ -3770,37 +3770,37 @@
         </is>
       </c>
       <c r="C51" s="25" t="n">
-        <v>13.7</v>
+        <v>14.18</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>13.5</v>
+        <v>13.85</v>
       </c>
       <c r="E51" s="26" t="n">
-        <v>13.34</v>
+        <v>13.58</v>
       </c>
       <c r="F51" s="27" t="n">
-        <v>13.43</v>
+        <v>13.73</v>
       </c>
       <c r="G51" s="27" t="n">
-        <v>13.5</v>
+        <v>13.85</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>13.3</v>
+        <v>13.52</v>
       </c>
       <c r="I51" s="29" t="n">
-        <v>13.23</v>
+        <v>13.4</v>
       </c>
       <c r="J51" s="29" t="n">
-        <v>13.1</v>
+        <v>13.19</v>
       </c>
       <c r="K51" s="30" t="n">
-        <v>13.22</v>
+        <v>13.39</v>
       </c>
       <c r="L51" s="31" t="n">
-        <v>13.06</v>
+        <v>13.12</v>
       </c>
       <c r="M51" s="31" t="n">
-        <v>12.86</v>
+        <v>12.79</v>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="O51" s="32" t="n">
-        <v>13.27</v>
+        <v>13.47</v>
       </c>
       <c r="P51" s="32" t="n">
-        <v>13.24</v>
+        <v>13.42</v>
       </c>
       <c r="Q51" s="33" t="n">
-        <v>13.35</v>
+        <v>13.6</v>
       </c>
       <c r="R51" s="34" t="n">
-        <v>1.29</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="52">
@@ -3832,54 +3832,54 @@
         </is>
       </c>
       <c r="C52" s="25" t="n">
-        <v>61.36</v>
+        <v>61.81</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>60.46</v>
+        <v>60.91</v>
       </c>
       <c r="E52" s="26" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="F52" s="27" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="G52" s="27" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="H52" s="28" t="n">
+        <v>59.83</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="J52" s="29" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="K52" s="30" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="L52" s="31" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="M52" s="31" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="N52" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O52" s="32" t="n">
+        <v>59.78</v>
+      </c>
+      <c r="P52" s="32" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="Q52" s="33" t="n">
         <v>59.7</v>
       </c>
-      <c r="F52" s="27" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="G52" s="27" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="H52" s="28" t="n">
-        <v>59.45</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>59</v>
-      </c>
-      <c r="J52" s="29" t="n">
-        <v>58.55</v>
-      </c>
-      <c r="K52" s="30" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="L52" s="31" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="M52" s="31" t="n">
-        <v>57.54</v>
-      </c>
-      <c r="N52" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O52" s="32" t="n">
-        <v>59.36</v>
-      </c>
-      <c r="P52" s="32" t="n">
-        <v>59.27</v>
-      </c>
-      <c r="Q52" s="33" t="n">
-        <v>59.45</v>
-      </c>
       <c r="R52" s="34" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="53">
@@ -3894,54 +3894,54 @@
         </is>
       </c>
       <c r="C53" s="25" t="n">
-        <v>25.93</v>
+        <v>25.96</v>
       </c>
       <c r="D53" s="25" t="n">
-        <v>25.48</v>
+        <v>25.55</v>
       </c>
       <c r="E53" s="26" t="n">
-        <v>25.1</v>
+        <v>25.21</v>
       </c>
       <c r="F53" s="27" t="n">
-        <v>25.23</v>
+        <v>25.18</v>
       </c>
       <c r="G53" s="27" t="n">
-        <v>25.44</v>
+        <v>25.45</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>24.99</v>
+        <v>25.04</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>24.78</v>
+        <v>24.77</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>24.54</v>
+        <v>24.63</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>24.85</v>
+        <v>24.98</v>
       </c>
       <c r="L53" s="31" t="n">
-        <v>24.47</v>
+        <v>24.64</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>24.02</v>
-      </c>
-      <c r="N53" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>24.23</v>
+      </c>
+      <c r="N53" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O53" s="32" t="n">
-        <v>24.94</v>
+        <v>25.02</v>
       </c>
       <c r="P53" s="32" t="n">
-        <v>24.88</v>
+        <v>25.01</v>
       </c>
       <c r="Q53" s="33" t="n">
-        <v>25.02</v>
-      </c>
-      <c r="R53" s="34" t="n">
-        <v>1.09</v>
+        <v>24.92</v>
+      </c>
+      <c r="R53" s="36" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="54">
@@ -3956,41 +3956,41 @@
         </is>
       </c>
       <c r="C54" s="25" t="n">
-        <v>5.63</v>
+        <v>5.42</v>
       </c>
       <c r="D54" s="25" t="n">
-        <v>5.48</v>
+        <v>5.36</v>
       </c>
       <c r="E54" s="26" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="G54" s="27" t="n">
         <v>5.36</v>
-      </c>
-      <c r="F54" s="27" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="G54" s="27" t="n">
-        <v>5.45</v>
       </c>
       <c r="H54" s="28" t="n">
         <v>5.3</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="J54" s="29" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
       <c r="K54" s="30" t="n">
         <v>5.27</v>
       </c>
       <c r="L54" s="31" t="n">
-        <v>5.15</v>
+        <v>5.22</v>
       </c>
       <c r="M54" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N54" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>5.16</v>
+      </c>
+      <c r="N54" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O54" s="32" t="n">
@@ -4000,10 +4000,10 @@
         <v>5.28</v>
       </c>
       <c r="Q54" s="33" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="R54" s="35" t="n">
-        <v>-0.57</v>
+        <v>5.31</v>
+      </c>
+      <c r="R54" s="34" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="55">
@@ -4018,37 +4018,37 @@
         </is>
       </c>
       <c r="C55" s="25" t="n">
-        <v>18.75</v>
+        <v>19.01</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>18.44</v>
+        <v>18.57</v>
       </c>
       <c r="E55" s="26" t="n">
-        <v>18.18</v>
+        <v>18.2</v>
       </c>
       <c r="F55" s="27" t="n">
-        <v>18.23</v>
+        <v>18.35</v>
       </c>
       <c r="G55" s="27" t="n">
-        <v>18.4</v>
+        <v>18.54</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>18.09</v>
+        <v>18.1</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>17.92</v>
+        <v>17.91</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>17.78</v>
+        <v>17.66</v>
       </c>
       <c r="K55" s="30" t="n">
-        <v>18.01</v>
+        <v>17.96</v>
       </c>
       <c r="L55" s="31" t="n">
-        <v>17.75</v>
+        <v>17.59</v>
       </c>
       <c r="M55" s="31" t="n">
-        <v>17.44</v>
+        <v>17.15</v>
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
@@ -4056,16 +4056,16 @@
         </is>
       </c>
       <c r="O55" s="32" t="n">
-        <v>18.06</v>
+        <v>18.05</v>
       </c>
       <c r="P55" s="32" t="n">
-        <v>18.03</v>
+        <v>17.99</v>
       </c>
       <c r="Q55" s="33" t="n">
-        <v>18.07</v>
+        <v>18.15</v>
       </c>
       <c r="R55" s="34" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="56">
@@ -4080,37 +4080,37 @@
         </is>
       </c>
       <c r="C56" s="25" t="n">
-        <v>91.94</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>89.94</v>
+        <v>91.55</v>
       </c>
       <c r="E56" s="26" t="n">
-        <v>88.26000000000001</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F56" s="27" t="n">
-        <v>89.06999999999999</v>
+        <v>90.78</v>
       </c>
       <c r="G56" s="27" t="n">
-        <v>89.88</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>87.88</v>
+        <v>89.47</v>
       </c>
       <c r="I56" s="29" t="n">
-        <v>87.06999999999999</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="J56" s="29" t="n">
-        <v>85.88</v>
+        <v>87.37</v>
       </c>
       <c r="K56" s="30" t="n">
-        <v>87.14</v>
+        <v>88.61</v>
       </c>
       <c r="L56" s="31" t="n">
-        <v>85.45999999999999</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="M56" s="31" t="n">
-        <v>83.45999999999999</v>
+        <v>84.75</v>
       </c>
       <c r="N56" s="20" t="inlineStr">
         <is>
@@ -4118,16 +4118,16 @@
         </is>
       </c>
       <c r="O56" s="32" t="n">
-        <v>87.59</v>
+        <v>89.12</v>
       </c>
       <c r="P56" s="32" t="n">
-        <v>87.3</v>
+        <v>88.78</v>
       </c>
       <c r="Q56" s="33" t="n">
-        <v>88.25</v>
+        <v>90</v>
       </c>
       <c r="R56" s="34" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="57">
@@ -4142,37 +4142,37 @@
         </is>
       </c>
       <c r="C57" s="25" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="D57" s="25" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="E57" s="26" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="F57" s="27" t="n">
         <v>19.54</v>
       </c>
-      <c r="D57" s="25" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="E57" s="26" t="n">
-        <v>18.92</v>
-      </c>
-      <c r="F57" s="27" t="n">
-        <v>19.08</v>
-      </c>
       <c r="G57" s="27" t="n">
-        <v>19.21</v>
+        <v>19.81</v>
       </c>
       <c r="H57" s="28" t="n">
-        <v>18.87</v>
+        <v>19.23</v>
       </c>
       <c r="I57" s="29" t="n">
-        <v>18.74</v>
+        <v>18.96</v>
       </c>
       <c r="J57" s="29" t="n">
-        <v>18.53</v>
+        <v>18.65</v>
       </c>
       <c r="K57" s="30" t="n">
-        <v>18.72</v>
+        <v>19.05</v>
       </c>
       <c r="L57" s="31" t="n">
-        <v>18.44</v>
+        <v>18.56</v>
       </c>
       <c r="M57" s="31" t="n">
-        <v>18.1</v>
+        <v>17.98</v>
       </c>
       <c r="N57" s="20" t="inlineStr">
         <is>
@@ -4180,16 +4180,16 @@
         </is>
       </c>
       <c r="O57" s="32" t="n">
-        <v>18.81</v>
+        <v>19.16</v>
       </c>
       <c r="P57" s="32" t="n">
-        <v>18.75</v>
+        <v>19.09</v>
       </c>
       <c r="Q57" s="33" t="n">
-        <v>18.96</v>
+        <v>19.27</v>
       </c>
       <c r="R57" s="34" t="n">
-        <v>1.34</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="58">
@@ -4204,54 +4204,54 @@
         </is>
       </c>
       <c r="C58" s="25" t="n">
-        <v>22.03</v>
+        <v>22.63</v>
       </c>
       <c r="D58" s="25" t="n">
-        <v>21.91</v>
+        <v>22.22</v>
       </c>
       <c r="E58" s="26" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="F58" s="27" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="G58" s="27" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="H58" s="28" t="n">
         <v>21.81</v>
       </c>
-      <c r="F58" s="27" t="n">
-        <v>21.86</v>
-      </c>
-      <c r="G58" s="27" t="n">
-        <v>21.91</v>
-      </c>
-      <c r="H58" s="28" t="n">
-        <v>21.79</v>
-      </c>
       <c r="I58" s="29" t="n">
-        <v>21.74</v>
+        <v>21.65</v>
       </c>
       <c r="J58" s="29" t="n">
-        <v>21.67</v>
+        <v>21.4</v>
       </c>
       <c r="K58" s="30" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="L58" s="31" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="M58" s="31" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N58" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O58" s="32" t="n">
         <v>21.75</v>
       </c>
-      <c r="L58" s="31" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="M58" s="31" t="n">
-        <v>21.53</v>
-      </c>
-      <c r="N58" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O58" s="32" t="n">
-        <v>21.77</v>
-      </c>
       <c r="P58" s="32" t="n">
-        <v>21.76</v>
+        <v>21.68</v>
       </c>
       <c r="Q58" s="33" t="n">
-        <v>21.81</v>
+        <v>21.9</v>
       </c>
       <c r="R58" s="34" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="59">
@@ -4266,54 +4266,54 @@
         </is>
       </c>
       <c r="C59" s="25" t="n">
-        <v>23.97</v>
+        <v>23.84</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>23.72</v>
+        <v>23.65</v>
       </c>
       <c r="E59" s="26" t="n">
-        <v>23.51</v>
+        <v>23.49</v>
       </c>
       <c r="F59" s="27" t="n">
-        <v>23.52</v>
+        <v>23.54</v>
       </c>
       <c r="G59" s="27" t="n">
-        <v>23.67</v>
+        <v>23.63</v>
       </c>
       <c r="H59" s="28" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="I59" s="29" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="J59" s="29" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="K59" s="30" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="L59" s="31" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="M59" s="31" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="N59" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O59" s="32" t="n">
         <v>23.42</v>
       </c>
-      <c r="I59" s="29" t="n">
-        <v>23.27</v>
-      </c>
-      <c r="J59" s="29" t="n">
-        <v>23.17</v>
-      </c>
-      <c r="K59" s="30" t="n">
-        <v>23.37</v>
-      </c>
-      <c r="L59" s="31" t="n">
-        <v>23.17</v>
-      </c>
-      <c r="M59" s="31" t="n">
-        <v>22.92</v>
-      </c>
-      <c r="N59" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O59" s="32" t="n">
-        <v>23.41</v>
-      </c>
       <c r="P59" s="32" t="n">
-        <v>23.39</v>
+        <v>23.4</v>
       </c>
       <c r="Q59" s="33" t="n">
-        <v>23.37</v>
-      </c>
-      <c r="R59" s="35" t="n">
-        <v>-0.09</v>
+        <v>23.45</v>
+      </c>
+      <c r="R59" s="34" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="60">
@@ -4328,37 +4328,37 @@
         </is>
       </c>
       <c r="C60" s="25" t="n">
-        <v>29.79</v>
+        <v>29.43</v>
       </c>
       <c r="D60" s="25" t="n">
-        <v>29.25</v>
+        <v>29.13</v>
       </c>
       <c r="E60" s="26" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="F60" s="27" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="G60" s="27" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="H60" s="28" t="n">
         <v>28.8</v>
       </c>
-      <c r="F60" s="27" t="n">
-        <v>28.93</v>
-      </c>
-      <c r="G60" s="27" t="n">
-        <v>29.19</v>
-      </c>
-      <c r="H60" s="28" t="n">
-        <v>28.65</v>
-      </c>
       <c r="I60" s="29" t="n">
-        <v>28.39</v>
+        <v>28.66</v>
       </c>
       <c r="J60" s="29" t="n">
-        <v>28.11</v>
+        <v>28.5</v>
       </c>
       <c r="K60" s="30" t="n">
-        <v>28.5</v>
+        <v>28.71</v>
       </c>
       <c r="L60" s="31" t="n">
-        <v>28.05</v>
+        <v>28.45</v>
       </c>
       <c r="M60" s="31" t="n">
-        <v>27.51</v>
+        <v>28.15</v>
       </c>
       <c r="N60" s="20" t="inlineStr">
         <is>
@@ -4366,16 +4366,16 @@
         </is>
       </c>
       <c r="O60" s="32" t="n">
-        <v>28.6</v>
+        <v>28.76</v>
       </c>
       <c r="P60" s="32" t="n">
-        <v>28.54</v>
+        <v>28.73</v>
       </c>
       <c r="Q60" s="33" t="n">
-        <v>28.66</v>
+        <v>28.82</v>
       </c>
       <c r="R60" s="34" t="n">
-        <v>1.2</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4390,37 +4390,37 @@
         </is>
       </c>
       <c r="C61" s="25" t="n">
-        <v>45.75</v>
+        <v>45.6</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>45.37</v>
+        <v>45.28</v>
       </c>
       <c r="E61" s="26" t="n">
-        <v>45.06</v>
+        <v>45.01</v>
       </c>
       <c r="F61" s="27" t="n">
-        <v>45.05</v>
+        <v>45.12</v>
       </c>
       <c r="G61" s="27" t="n">
-        <v>45.29</v>
+        <v>45.26</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>44.91</v>
+        <v>44.94</v>
       </c>
       <c r="I61" s="29" t="n">
-        <v>44.67</v>
+        <v>44.8</v>
       </c>
       <c r="J61" s="29" t="n">
-        <v>44.53</v>
+        <v>44.62</v>
       </c>
       <c r="K61" s="30" t="n">
-        <v>44.84</v>
+        <v>44.83</v>
       </c>
       <c r="L61" s="31" t="n">
-        <v>44.53</v>
+        <v>44.56</v>
       </c>
       <c r="M61" s="31" t="n">
-        <v>44.15</v>
+        <v>44.24</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
@@ -4428,16 +4428,16 @@
         </is>
       </c>
       <c r="O61" s="32" t="n">
-        <v>44.89</v>
+        <v>44.9</v>
       </c>
       <c r="P61" s="32" t="n">
-        <v>44.87</v>
+        <v>44.86</v>
       </c>
       <c r="Q61" s="33" t="n">
-        <v>44.82</v>
-      </c>
-      <c r="R61" s="35" t="n">
-        <v>-0.18</v>
+        <v>44.98</v>
+      </c>
+      <c r="R61" s="34" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="62">
@@ -4452,37 +4452,37 @@
         </is>
       </c>
       <c r="C62" s="25" t="n">
-        <v>19.56</v>
+        <v>20.51</v>
       </c>
       <c r="D62" s="25" t="n">
-        <v>19.4</v>
+        <v>20.01</v>
       </c>
       <c r="E62" s="26" t="n">
-        <v>19.26</v>
+        <v>19.59</v>
       </c>
       <c r="F62" s="27" t="n">
-        <v>19.33</v>
+        <v>19.81</v>
       </c>
       <c r="G62" s="27" t="n">
-        <v>19.39</v>
+        <v>20</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>19.23</v>
+        <v>19.5</v>
       </c>
       <c r="I62" s="29" t="n">
-        <v>19.17</v>
+        <v>19.31</v>
       </c>
       <c r="J62" s="29" t="n">
-        <v>19.07</v>
+        <v>19</v>
       </c>
       <c r="K62" s="30" t="n">
-        <v>19.18</v>
+        <v>19.31</v>
       </c>
       <c r="L62" s="31" t="n">
-        <v>19.04</v>
+        <v>18.89</v>
       </c>
       <c r="M62" s="31" t="n">
-        <v>18.88</v>
+        <v>18.39</v>
       </c>
       <c r="N62" s="20" t="inlineStr">
         <is>
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="O62" s="32" t="n">
-        <v>19.21</v>
+        <v>19.43</v>
       </c>
       <c r="P62" s="32" t="n">
-        <v>19.19</v>
+        <v>19.35</v>
       </c>
       <c r="Q62" s="33" t="n">
-        <v>19.26</v>
+        <v>19.61</v>
       </c>
       <c r="R62" s="34" t="n">
-        <v>0.78</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="63">
@@ -4514,37 +4514,37 @@
         </is>
       </c>
       <c r="C63" s="25" t="n">
-        <v>15.19</v>
+        <v>15.44</v>
       </c>
       <c r="D63" s="25" t="n">
-        <v>15.07</v>
+        <v>15.24</v>
       </c>
       <c r="E63" s="26" t="n">
-        <v>14.97</v>
+        <v>15.08</v>
       </c>
       <c r="F63" s="27" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="G63" s="27" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="H63" s="28" t="n">
         <v>15.03</v>
       </c>
-      <c r="G63" s="27" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="H63" s="28" t="n">
-        <v>14.95</v>
-      </c>
       <c r="I63" s="29" t="n">
-        <v>14.91</v>
+        <v>14.94</v>
       </c>
       <c r="J63" s="29" t="n">
         <v>14.83</v>
       </c>
       <c r="K63" s="30" t="n">
-        <v>14.91</v>
+        <v>14.96</v>
       </c>
       <c r="L63" s="31" t="n">
-        <v>14.81</v>
+        <v>14.8</v>
       </c>
       <c r="M63" s="31" t="n">
-        <v>14.69</v>
+        <v>14.6</v>
       </c>
       <c r="N63" s="20" t="inlineStr">
         <is>
@@ -4552,16 +4552,16 @@
         </is>
       </c>
       <c r="O63" s="32" t="n">
-        <v>14.93</v>
+        <v>15</v>
       </c>
       <c r="P63" s="32" t="n">
-        <v>14.92</v>
+        <v>14.98</v>
       </c>
       <c r="Q63" s="33" t="n">
-        <v>14.98</v>
+        <v>15.05</v>
       </c>
       <c r="R63" s="34" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="64">
@@ -4579,34 +4579,34 @@
         <v>25.92</v>
       </c>
       <c r="D64" s="25" t="n">
-        <v>25.56</v>
+        <v>25.66</v>
       </c>
       <c r="E64" s="26" t="n">
-        <v>25.26</v>
+        <v>25.44</v>
       </c>
       <c r="F64" s="27" t="n">
-        <v>25.46</v>
+        <v>25.47</v>
       </c>
       <c r="G64" s="27" t="n">
-        <v>25.58</v>
+        <v>25.61</v>
       </c>
       <c r="H64" s="28" t="n">
-        <v>25.22</v>
+        <v>25.35</v>
       </c>
       <c r="I64" s="29" t="n">
-        <v>25.1</v>
+        <v>25.21</v>
       </c>
       <c r="J64" s="29" t="n">
-        <v>24.86</v>
+        <v>25.09</v>
       </c>
       <c r="K64" s="30" t="n">
-        <v>25.06</v>
+        <v>25.3</v>
       </c>
       <c r="L64" s="31" t="n">
-        <v>24.76</v>
+        <v>25.08</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>24.4</v>
+        <v>24.82</v>
       </c>
       <c r="N64" s="20" t="inlineStr">
         <is>
@@ -4614,16 +4614,16 @@
         </is>
       </c>
       <c r="O64" s="32" t="n">
-        <v>25.15</v>
+        <v>25.34</v>
       </c>
       <c r="P64" s="32" t="n">
-        <v>25.09</v>
+        <v>25.32</v>
       </c>
       <c r="Q64" s="33" t="n">
-        <v>25.34</v>
-      </c>
-      <c r="R64" s="34" t="n">
-        <v>1.44</v>
+        <v>25.32</v>
+      </c>
+      <c r="R64" s="36" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="65">
@@ -4638,54 +4638,54 @@
         </is>
       </c>
       <c r="C65" s="25" t="n">
-        <v>7.42</v>
+        <v>7.75</v>
       </c>
       <c r="D65" s="25" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="E65" s="26" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="G65" s="27" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="H65" s="28" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="I65" s="29" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="J65" s="29" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="K65" s="30" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="L65" s="31" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="M65" s="31" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="N65" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="P65" s="32" t="n">
         <v>7.35</v>
       </c>
-      <c r="E65" s="26" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="F65" s="27" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="G65" s="27" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="H65" s="28" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="I65" s="29" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="J65" s="29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K65" s="30" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="L65" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="M65" s="31" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="N65" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O65" s="32" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="P65" s="32" t="n">
-        <v>7.26</v>
-      </c>
       <c r="Q65" s="33" t="n">
-        <v>7.27</v>
+        <v>7.4</v>
       </c>
       <c r="R65" s="34" t="n">
-        <v>0.14</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="66">
@@ -4700,37 +4700,37 @@
         </is>
       </c>
       <c r="C66" s="25" t="n">
-        <v>5.07</v>
+        <v>5.16</v>
       </c>
       <c r="D66" s="25" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="E66" s="26" t="n">
         <v>5.01</v>
       </c>
-      <c r="E66" s="26" t="n">
+      <c r="F66" s="27" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G66" s="27" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="H66" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I66" s="29" t="n">
         <v>4.96</v>
       </c>
-      <c r="F66" s="27" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="G66" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H66" s="28" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="I66" s="29" t="n">
+      <c r="J66" s="29" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="K66" s="30" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L66" s="31" t="n">
         <v>4.9</v>
       </c>
-      <c r="J66" s="29" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="K66" s="30" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="L66" s="31" t="n">
-        <v>4.87</v>
-      </c>
       <c r="M66" s="31" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="N66" s="20" t="inlineStr">
         <is>
@@ -4738,16 +4738,16 @@
         </is>
       </c>
       <c r="O66" s="32" t="n">
-        <v>4.93</v>
+        <v>4.99</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>4.93</v>
+        <v>4.97</v>
       </c>
       <c r="Q66" s="33" t="n">
-        <v>4.93</v>
+        <v>5.01</v>
       </c>
       <c r="R66" s="34" t="n">
-        <v>0.2</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="67">
@@ -4762,39 +4762,39 @@
         </is>
       </c>
       <c r="C67" s="25" t="n">
-        <v>5.13</v>
+        <v>5.15</v>
       </c>
       <c r="D67" s="25" t="n">
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
       <c r="E67" s="26" t="n">
         <v>5</v>
       </c>
       <c r="F67" s="27" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="G67" s="27" t="n">
-        <v>5.04</v>
+        <v>5.05</v>
       </c>
       <c r="H67" s="28" t="n">
         <v>4.97</v>
       </c>
       <c r="I67" s="29" t="n">
-        <v>4.93</v>
+        <v>4.91</v>
       </c>
       <c r="J67" s="29" t="n">
-        <v>4.9</v>
+        <v>4.89</v>
       </c>
       <c r="K67" s="30" t="n">
-        <v>4.97</v>
+        <v>4.96</v>
       </c>
       <c r="L67" s="31" t="n">
-        <v>4.91</v>
+        <v>4.89</v>
       </c>
       <c r="M67" s="31" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="N67" s="36" t="inlineStr">
+        <v>4.81</v>
+      </c>
+      <c r="N67" s="35" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
@@ -4803,13 +4803,13 @@
         <v>4.97</v>
       </c>
       <c r="P67" s="32" t="n">
-        <v>4.97</v>
+        <v>4.96</v>
       </c>
       <c r="Q67" s="33" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R67" s="34" t="n">
-        <v>0</v>
+        <v>4.94</v>
+      </c>
+      <c r="R67" s="36" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="68">
@@ -4824,37 +4824,37 @@
         </is>
       </c>
       <c r="C68" s="25" t="n">
-        <v>65.67</v>
+        <v>66.28</v>
       </c>
       <c r="D68" s="25" t="n">
-        <v>65.06999999999999</v>
+        <v>65.58</v>
       </c>
       <c r="E68" s="26" t="n">
-        <v>64.56999999999999</v>
+        <v>65</v>
       </c>
       <c r="F68" s="27" t="n">
-        <v>64.83</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="G68" s="27" t="n">
-        <v>65.06999999999999</v>
+        <v>65.58</v>
       </c>
       <c r="H68" s="28" t="n">
-        <v>64.47</v>
+        <v>64.88</v>
       </c>
       <c r="I68" s="29" t="n">
-        <v>64.23</v>
+        <v>64.62</v>
       </c>
       <c r="J68" s="29" t="n">
-        <v>63.87</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="K68" s="30" t="n">
-        <v>64.23</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L68" s="31" t="n">
-        <v>63.73</v>
+        <v>64.02</v>
       </c>
       <c r="M68" s="31" t="n">
-        <v>63.13</v>
+        <v>63.32</v>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
@@ -4862,16 +4862,16 @@
         </is>
       </c>
       <c r="O68" s="32" t="n">
-        <v>64.37</v>
+        <v>64.77</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>64.28</v>
+        <v>64.66</v>
       </c>
       <c r="Q68" s="33" t="n">
-        <v>64.59999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="R68" s="34" t="n">
-        <v>0.31</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="69">
@@ -4886,37 +4886,37 @@
         </is>
       </c>
       <c r="C69" s="25" t="n">
-        <v>67.05</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="D69" s="25" t="n">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="E69" s="26" t="n">
+        <v>65.89</v>
+      </c>
+      <c r="F69" s="27" t="n">
         <v>66</v>
       </c>
-      <c r="E69" s="26" t="n">
-        <v>65.12</v>
-      </c>
-      <c r="F69" s="27" t="n">
-        <v>65.7</v>
-      </c>
       <c r="G69" s="27" t="n">
-        <v>66.05</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>65</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="I69" s="29" t="n">
-        <v>64.65000000000001</v>
+        <v>65.25</v>
       </c>
       <c r="J69" s="29" t="n">
-        <v>63.95</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K69" s="30" t="n">
-        <v>64.53</v>
+        <v>65.47</v>
       </c>
       <c r="L69" s="31" t="n">
-        <v>63.65</v>
+        <v>64.84</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>62.6</v>
+        <v>64.09</v>
       </c>
       <c r="N69" s="20" t="inlineStr">
         <is>
@@ -4924,16 +4924,16 @@
         </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>64.81</v>
+        <v>65.59</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>64.61</v>
+        <v>65.52</v>
       </c>
       <c r="Q69" s="33" t="n">
-        <v>65.34999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="R69" s="34" t="n">
-        <v>1.71</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="70">
@@ -4948,37 +4948,37 @@
         </is>
       </c>
       <c r="C70" s="25" t="n">
-        <v>104.65</v>
+        <v>109.8</v>
       </c>
       <c r="D70" s="25" t="n">
-        <v>102.95</v>
+        <v>106.4</v>
       </c>
       <c r="E70" s="26" t="n">
-        <v>101.53</v>
+        <v>103.55</v>
       </c>
       <c r="F70" s="27" t="n">
-        <v>101.67</v>
+        <v>103.9</v>
       </c>
       <c r="G70" s="27" t="n">
-        <v>102.63</v>
+        <v>105.8</v>
       </c>
       <c r="H70" s="28" t="n">
-        <v>100.93</v>
+        <v>102.4</v>
       </c>
       <c r="I70" s="29" t="n">
-        <v>99.97</v>
+        <v>100.5</v>
       </c>
       <c r="J70" s="29" t="n">
-        <v>99.23</v>
+        <v>99</v>
       </c>
       <c r="K70" s="30" t="n">
-        <v>100.57</v>
+        <v>101.65</v>
       </c>
       <c r="L70" s="31" t="n">
-        <v>99.15000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>97.45</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="N70" s="20" t="inlineStr">
         <is>
@@ -4986,16 +4986,16 @@
         </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>100.82</v>
+        <v>102.16</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>100.71</v>
+        <v>101.91</v>
       </c>
       <c r="Q70" s="33" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="R70" s="35" t="n">
-        <v>-0.49</v>
+        <v>102</v>
+      </c>
+      <c r="R70" s="34" t="n">
+        <v>1.29</v>
       </c>
     </row>
     <row r="71">
@@ -5010,54 +5010,54 @@
         </is>
       </c>
       <c r="C71" s="25" t="n">
-        <v>141.19</v>
+        <v>135.19</v>
       </c>
       <c r="D71" s="25" t="n">
-        <v>134.89</v>
+        <v>131.49</v>
       </c>
       <c r="E71" s="26" t="n">
-        <v>129.61</v>
+        <v>128.39</v>
       </c>
       <c r="F71" s="27" t="n">
-        <v>133.1</v>
+        <v>128.3</v>
       </c>
       <c r="G71" s="27" t="n">
-        <v>135.2</v>
+        <v>130.6</v>
       </c>
       <c r="H71" s="28" t="n">
-        <v>128.9</v>
+        <v>126.9</v>
       </c>
       <c r="I71" s="29" t="n">
-        <v>126.8</v>
+        <v>124.6</v>
       </c>
       <c r="J71" s="29" t="n">
-        <v>122.6</v>
+        <v>123.2</v>
       </c>
       <c r="K71" s="30" t="n">
-        <v>126.09</v>
+        <v>126.31</v>
       </c>
       <c r="L71" s="31" t="n">
-        <v>120.81</v>
+        <v>123.21</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>114.51</v>
-      </c>
-      <c r="N71" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>119.51</v>
+      </c>
+      <c r="N71" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>127.74</v>
+        <v>126.75</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>126.58</v>
+        <v>126.6</v>
       </c>
       <c r="Q71" s="33" t="n">
-        <v>131</v>
-      </c>
-      <c r="R71" s="34" t="n">
-        <v>4.38</v>
+        <v>126</v>
+      </c>
+      <c r="R71" s="36" t="n">
+        <v>-3.82</v>
       </c>
     </row>
     <row r="72">
@@ -5072,37 +5072,37 @@
         </is>
       </c>
       <c r="C72" s="25" t="n">
-        <v>26.35</v>
+        <v>26.21</v>
       </c>
       <c r="D72" s="25" t="n">
-        <v>25.85</v>
+        <v>25.83</v>
       </c>
       <c r="E72" s="26" t="n">
-        <v>25.43</v>
+        <v>25.52</v>
       </c>
       <c r="F72" s="27" t="n">
-        <v>25.59</v>
+        <v>25.62</v>
       </c>
       <c r="G72" s="27" t="n">
-        <v>25.81</v>
+        <v>25.8</v>
       </c>
       <c r="H72" s="28" t="n">
-        <v>25.31</v>
+        <v>25.42</v>
       </c>
       <c r="I72" s="29" t="n">
-        <v>25.09</v>
+        <v>25.24</v>
       </c>
       <c r="J72" s="29" t="n">
-        <v>24.81</v>
+        <v>25.04</v>
       </c>
       <c r="K72" s="30" t="n">
-        <v>25.15</v>
+        <v>25.3</v>
       </c>
       <c r="L72" s="31" t="n">
-        <v>24.73</v>
+        <v>24.99</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>24.23</v>
+        <v>24.61</v>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>25.25</v>
+        <v>25.38</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>25.19</v>
+        <v>25.33</v>
       </c>
       <c r="Q72" s="33" t="n">
-        <v>25.36</v>
+        <v>25.44</v>
       </c>
       <c r="R72" s="34" t="n">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="73">
@@ -5134,54 +5134,54 @@
         </is>
       </c>
       <c r="C73" s="25" t="n">
-        <v>22.6</v>
+        <v>21.88</v>
       </c>
       <c r="D73" s="25" t="n">
-        <v>21.95</v>
+        <v>21.6</v>
       </c>
       <c r="E73" s="26" t="n">
-        <v>21.41</v>
+        <v>21.37</v>
       </c>
       <c r="F73" s="27" t="n">
-        <v>21.55</v>
+        <v>21.45</v>
       </c>
       <c r="G73" s="27" t="n">
-        <v>21.88</v>
+        <v>21.58</v>
       </c>
       <c r="H73" s="28" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="I73" s="29" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="J73" s="29" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="K73" s="30" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="N73" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="P73" s="32" t="n">
         <v>21.23</v>
       </c>
-      <c r="I73" s="29" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J73" s="29" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="K73" s="30" t="n">
-        <v>21.04</v>
-      </c>
-      <c r="L73" s="31" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="M73" s="31" t="n">
-        <v>19.85</v>
-      </c>
-      <c r="N73" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>21.16</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>21.09</v>
-      </c>
       <c r="Q73" s="33" t="n">
-        <v>21.23</v>
+        <v>21.32</v>
       </c>
       <c r="R73" s="34" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="74">
@@ -5196,54 +5196,54 @@
         </is>
       </c>
       <c r="C74" s="25" t="n">
-        <v>246.73</v>
+        <v>243.16</v>
       </c>
       <c r="D74" s="25" t="n">
-        <v>242.63</v>
+        <v>240.96</v>
       </c>
       <c r="E74" s="26" t="n">
-        <v>239.2</v>
+        <v>239.12</v>
       </c>
       <c r="F74" s="27" t="n">
-        <v>240.33</v>
+        <v>239.27</v>
       </c>
       <c r="G74" s="27" t="n">
-        <v>242.27</v>
+        <v>240.53</v>
       </c>
       <c r="H74" s="28" t="n">
-        <v>238.17</v>
+        <v>238.33</v>
       </c>
       <c r="I74" s="29" t="n">
-        <v>236.23</v>
+        <v>237.07</v>
       </c>
       <c r="J74" s="29" t="n">
-        <v>234.07</v>
+        <v>236.13</v>
       </c>
       <c r="K74" s="30" t="n">
-        <v>236.9</v>
+        <v>237.88</v>
       </c>
       <c r="L74" s="31" t="n">
-        <v>233.47</v>
+        <v>236.04</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>229.37</v>
-      </c>
-      <c r="N74" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>233.84</v>
+      </c>
+      <c r="N74" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O74" s="32" t="n">
-        <v>237.69</v>
+        <v>238.19</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>237.22</v>
+        <v>238.06</v>
       </c>
       <c r="Q74" s="33" t="n">
-        <v>238.4</v>
-      </c>
-      <c r="R74" s="34" t="n">
-        <v>0.25</v>
+        <v>238</v>
+      </c>
+      <c r="R74" s="36" t="n">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="75">
@@ -5258,54 +5258,54 @@
         </is>
       </c>
       <c r="C75" s="25" t="n">
-        <v>16.58</v>
+        <v>16.12</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>16.24</v>
+        <v>15.94</v>
       </c>
       <c r="E75" s="26" t="n">
-        <v>15.96</v>
+        <v>15.79</v>
       </c>
       <c r="F75" s="27" t="n">
-        <v>15.97</v>
+        <v>15.78</v>
       </c>
       <c r="G75" s="27" t="n">
-        <v>16.17</v>
+        <v>15.9</v>
       </c>
       <c r="H75" s="28" t="n">
-        <v>15.83</v>
+        <v>15.72</v>
       </c>
       <c r="I75" s="29" t="n">
-        <v>15.63</v>
+        <v>15.6</v>
       </c>
       <c r="J75" s="29" t="n">
-        <v>15.49</v>
+        <v>15.54</v>
       </c>
       <c r="K75" s="30" t="n">
-        <v>15.76</v>
+        <v>15.69</v>
       </c>
       <c r="L75" s="31" t="n">
-        <v>15.48</v>
+        <v>15.54</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>15.14</v>
-      </c>
-      <c r="N75" s="36" t="inlineStr">
+        <v>15.36</v>
+      </c>
+      <c r="N75" s="35" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O75" s="32" t="n">
-        <v>15.81</v>
+        <v>15.71</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>15.79</v>
+        <v>15.7</v>
       </c>
       <c r="Q75" s="33" t="n">
-        <v>15.77</v>
-      </c>
-      <c r="R75" s="35" t="n">
-        <v>-1.5</v>
+        <v>15.67</v>
+      </c>
+      <c r="R75" s="36" t="n">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="76">
@@ -5320,37 +5320,37 @@
         </is>
       </c>
       <c r="C76" s="25" t="n">
-        <v>42.3</v>
+        <v>39.12</v>
       </c>
       <c r="D76" s="25" t="n">
-        <v>39.32</v>
+        <v>38.08</v>
       </c>
       <c r="E76" s="26" t="n">
-        <v>36.82</v>
+        <v>37.21</v>
       </c>
       <c r="F76" s="27" t="n">
-        <v>38.35</v>
+        <v>37.23</v>
       </c>
       <c r="G76" s="27" t="n">
-        <v>39.41</v>
+        <v>37.85</v>
       </c>
       <c r="H76" s="28" t="n">
-        <v>36.43</v>
+        <v>36.81</v>
       </c>
       <c r="I76" s="29" t="n">
-        <v>35.37</v>
+        <v>36.19</v>
       </c>
       <c r="J76" s="29" t="n">
-        <v>33.45</v>
+        <v>35.77</v>
       </c>
       <c r="K76" s="30" t="n">
-        <v>35.16</v>
+        <v>36.63</v>
       </c>
       <c r="L76" s="31" t="n">
-        <v>32.66</v>
+        <v>35.76</v>
       </c>
       <c r="M76" s="31" t="n">
-        <v>29.68</v>
+        <v>34.72</v>
       </c>
       <c r="N76" s="20" t="inlineStr">
         <is>
@@ -5358,16 +5358,16 @@
         </is>
       </c>
       <c r="O76" s="32" t="n">
-        <v>35.91</v>
+        <v>36.76</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>35.39</v>
+        <v>36.71</v>
       </c>
       <c r="Q76" s="33" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="R76" s="34" t="n">
-        <v>9.449999999999999</v>
+        <v>36.6</v>
+      </c>
+      <c r="R76" s="36" t="n">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="77">
@@ -5382,54 +5382,54 @@
         </is>
       </c>
       <c r="C77" s="25" t="n">
-        <v>27.83</v>
+        <v>27.4</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>27.43</v>
+        <v>27.14</v>
       </c>
       <c r="E77" s="26" t="n">
-        <v>27.09</v>
+        <v>26.92</v>
       </c>
       <c r="F77" s="27" t="n">
-        <v>27.11</v>
+        <v>27.04</v>
       </c>
       <c r="G77" s="27" t="n">
-        <v>27.35</v>
+        <v>27.14</v>
       </c>
       <c r="H77" s="28" t="n">
-        <v>26.95</v>
+        <v>26.88</v>
       </c>
       <c r="I77" s="29" t="n">
-        <v>26.71</v>
+        <v>26.78</v>
       </c>
       <c r="J77" s="29" t="n">
-        <v>26.55</v>
+        <v>26.62</v>
       </c>
       <c r="K77" s="30" t="n">
-        <v>26.87</v>
+        <v>26.78</v>
       </c>
       <c r="L77" s="31" t="n">
-        <v>26.53</v>
+        <v>26.56</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>26.13</v>
-      </c>
-      <c r="N77" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>26.3</v>
+      </c>
+      <c r="N77" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>26.92</v>
+        <v>26.84</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="Q77" s="33" t="n">
-        <v>26.88</v>
+        <v>26.94</v>
       </c>
       <c r="R77" s="34" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="78">
@@ -5444,54 +5444,54 @@
         </is>
       </c>
       <c r="C78" s="25" t="n">
-        <v>45.94</v>
+        <v>44.54</v>
       </c>
       <c r="D78" s="25" t="n">
-        <v>44.74</v>
+        <v>43.92</v>
       </c>
       <c r="E78" s="26" t="n">
-        <v>43.74</v>
+        <v>43.4</v>
       </c>
       <c r="F78" s="27" t="n">
-        <v>43.84</v>
+        <v>43.4</v>
       </c>
       <c r="G78" s="27" t="n">
-        <v>44.52</v>
+        <v>43.78</v>
       </c>
       <c r="H78" s="28" t="n">
-        <v>43.32</v>
+        <v>43.16</v>
       </c>
       <c r="I78" s="29" t="n">
-        <v>42.64</v>
+        <v>42.78</v>
       </c>
       <c r="J78" s="29" t="n">
-        <v>42.12</v>
+        <v>42.54</v>
       </c>
       <c r="K78" s="30" t="n">
         <v>43.06</v>
       </c>
       <c r="L78" s="31" t="n">
-        <v>42.06</v>
+        <v>42.54</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>40.86</v>
-      </c>
-      <c r="N78" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>41.92</v>
+      </c>
+      <c r="N78" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>43.24</v>
+        <v>43.13</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>43.16</v>
+        <v>43.1</v>
       </c>
       <c r="Q78" s="33" t="n">
-        <v>43.16</v>
-      </c>
-      <c r="R78" s="35" t="n">
-        <v>-0.51</v>
+        <v>43.02</v>
+      </c>
+      <c r="R78" s="36" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="79">
@@ -5506,37 +5506,37 @@
         </is>
       </c>
       <c r="C79" s="25" t="n">
-        <v>5.68</v>
+        <v>5.63</v>
       </c>
       <c r="D79" s="25" t="n">
-        <v>5.61</v>
+        <v>5.59</v>
       </c>
       <c r="E79" s="26" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="F79" s="27" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="G79" s="27" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="H79" s="28" t="n">
         <v>5.55</v>
       </c>
-      <c r="F79" s="27" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="G79" s="27" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H79" s="28" t="n">
-        <v>5.53</v>
-      </c>
       <c r="I79" s="29" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="J79" s="29" t="n">
-        <v>5.46</v>
+        <v>5.51</v>
       </c>
       <c r="K79" s="30" t="n">
-        <v>5.52</v>
+        <v>5.54</v>
       </c>
       <c r="L79" s="31" t="n">
-        <v>5.46</v>
+        <v>5.51</v>
       </c>
       <c r="M79" s="31" t="n">
-        <v>5.39</v>
+        <v>5.47</v>
       </c>
       <c r="N79" s="20" t="inlineStr">
         <is>
@@ -5544,16 +5544,16 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>5.53</v>
+        <v>5.55</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>5.52</v>
+        <v>5.54</v>
       </c>
       <c r="Q79" s="33" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="R79" s="34" t="n">
-        <v>0.18</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="80">
@@ -5568,37 +5568,37 @@
         </is>
       </c>
       <c r="C80" s="25" t="n">
-        <v>18.86</v>
+        <v>18.72</v>
       </c>
       <c r="D80" s="25" t="n">
-        <v>18.64</v>
+        <v>18.56</v>
       </c>
       <c r="E80" s="26" t="n">
-        <v>18.45</v>
+        <v>18.42</v>
       </c>
       <c r="F80" s="27" t="n">
-        <v>18.47</v>
+        <v>18.49</v>
       </c>
       <c r="G80" s="27" t="n">
-        <v>18.6</v>
+        <v>18.55</v>
       </c>
       <c r="H80" s="28" t="n">
-        <v>18.38</v>
+        <v>18.39</v>
       </c>
       <c r="I80" s="29" t="n">
-        <v>18.25</v>
+        <v>18.33</v>
       </c>
       <c r="J80" s="29" t="n">
-        <v>18.16</v>
+        <v>18.23</v>
       </c>
       <c r="K80" s="30" t="n">
-        <v>18.33</v>
+        <v>18.34</v>
       </c>
       <c r="L80" s="31" t="n">
-        <v>18.14</v>
+        <v>18.2</v>
       </c>
       <c r="M80" s="31" t="n">
-        <v>17.92</v>
+        <v>18.04</v>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
@@ -5606,13 +5606,13 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>18.36</v>
+        <v>18.37</v>
       </c>
       <c r="P80" s="32" t="n">
         <v>18.35</v>
       </c>
       <c r="Q80" s="33" t="n">
-        <v>18.35</v>
+        <v>18.42</v>
       </c>
       <c r="R80" s="34" t="n">
         <v>0.38</v>
@@ -5630,37 +5630,37 @@
         </is>
       </c>
       <c r="C81" s="25" t="n">
-        <v>81.62</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D81" s="25" t="n">
-        <v>80.62</v>
+        <v>83.3</v>
       </c>
       <c r="E81" s="26" t="n">
-        <v>79.78</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F81" s="27" t="n">
-        <v>80.33</v>
+        <v>82.7</v>
       </c>
       <c r="G81" s="27" t="n">
-        <v>80.67</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H81" s="28" t="n">
-        <v>79.67</v>
+        <v>81.3</v>
       </c>
       <c r="I81" s="29" t="n">
-        <v>79.33</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="J81" s="29" t="n">
-        <v>78.67</v>
+        <v>79.2</v>
       </c>
       <c r="K81" s="30" t="n">
-        <v>79.22</v>
+        <v>80.36</v>
       </c>
       <c r="L81" s="31" t="n">
-        <v>78.38</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="M81" s="31" t="n">
-        <v>77.38</v>
+        <v>76.5</v>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
@@ -5668,16 +5668,16 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>79.48</v>
+        <v>80.91</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>79.3</v>
+        <v>80.53</v>
       </c>
       <c r="Q81" s="33" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R81" s="34" t="n">
-        <v>0.63</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="82">
@@ -5692,54 +5692,54 @@
         </is>
       </c>
       <c r="C82" s="25" t="n">
-        <v>4.88</v>
+        <v>4.81</v>
       </c>
       <c r="D82" s="25" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="E82" s="26" t="n">
-        <v>4.73</v>
+        <v>4.7</v>
       </c>
       <c r="F82" s="27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G82" s="27" t="n">
         <v>4.74</v>
       </c>
-      <c r="G82" s="27" t="n">
-        <v>4.78</v>
-      </c>
       <c r="H82" s="28" t="n">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="I82" s="29" t="n">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="J82" s="29" t="n">
         <v>4.62</v>
       </c>
       <c r="K82" s="30" t="n">
-        <v>4.69</v>
+        <v>4.66</v>
       </c>
       <c r="L82" s="31" t="n">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="M82" s="31" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="N82" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>4.55</v>
+      </c>
+      <c r="N82" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O82" s="32" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>4.69</v>
+        <v>4.67</v>
       </c>
       <c r="Q82" s="33" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="R82" s="35" t="n">
-        <v>-0.21</v>
+        <v>4.67</v>
+      </c>
+      <c r="R82" s="36" t="n">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="83">
@@ -5754,54 +5754,54 @@
         </is>
       </c>
       <c r="C83" s="25" t="n">
-        <v>64.64</v>
+        <v>65.44</v>
       </c>
       <c r="D83" s="25" t="n">
-        <v>63.69</v>
+        <v>63.84</v>
       </c>
       <c r="E83" s="26" t="n">
-        <v>62.89</v>
+        <v>62.5</v>
       </c>
       <c r="F83" s="27" t="n">
-        <v>63.08</v>
+        <v>62.38</v>
       </c>
       <c r="G83" s="27" t="n">
-        <v>63.57</v>
+        <v>63.42</v>
       </c>
       <c r="H83" s="28" t="n">
-        <v>62.62</v>
+        <v>61.82</v>
       </c>
       <c r="I83" s="29" t="n">
-        <v>62.13</v>
+        <v>60.78</v>
       </c>
       <c r="J83" s="29" t="n">
-        <v>61.67</v>
+        <v>60.22</v>
       </c>
       <c r="K83" s="30" t="n">
-        <v>62.36</v>
+        <v>61.6</v>
       </c>
       <c r="L83" s="31" t="n">
-        <v>61.56</v>
+        <v>60.26</v>
       </c>
       <c r="M83" s="31" t="n">
-        <v>60.61</v>
-      </c>
-      <c r="N83" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>58.66</v>
+      </c>
+      <c r="N83" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O83" s="32" t="n">
-        <v>62.52</v>
+        <v>61.77</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>62.43</v>
+        <v>61.73</v>
       </c>
       <c r="Q83" s="33" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="R83" s="35" t="n">
-        <v>-0.16</v>
+        <v>61.35</v>
+      </c>
+      <c r="R83" s="36" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="84">
@@ -5816,37 +5816,37 @@
         </is>
       </c>
       <c r="C84" s="25" t="n">
-        <v>39.85</v>
+        <v>40.27</v>
       </c>
       <c r="D84" s="25" t="n">
-        <v>39.41</v>
+        <v>39.71</v>
       </c>
       <c r="E84" s="26" t="n">
-        <v>39.04</v>
+        <v>39.24</v>
       </c>
       <c r="F84" s="27" t="n">
-        <v>39.19</v>
+        <v>39.35</v>
       </c>
       <c r="G84" s="27" t="n">
-        <v>39.39</v>
+        <v>39.63</v>
       </c>
       <c r="H84" s="28" t="n">
-        <v>38.95</v>
+        <v>39.07</v>
       </c>
       <c r="I84" s="29" t="n">
-        <v>38.75</v>
+        <v>38.79</v>
       </c>
       <c r="J84" s="29" t="n">
         <v>38.51</v>
       </c>
       <c r="K84" s="30" t="n">
-        <v>38.8</v>
+        <v>38.92</v>
       </c>
       <c r="L84" s="31" t="n">
-        <v>38.43</v>
+        <v>38.45</v>
       </c>
       <c r="M84" s="31" t="n">
-        <v>37.99</v>
+        <v>37.89</v>
       </c>
       <c r="N84" s="20" t="inlineStr">
         <is>
@@ -5854,16 +5854,16 @@
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>38.89</v>
+        <v>39.02</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>38.83</v>
+        <v>38.97</v>
       </c>
       <c r="Q84" s="33" t="n">
-        <v>39</v>
+        <v>39.06</v>
       </c>
       <c r="R84" s="34" t="n">
-        <v>0.52</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="85">
@@ -5878,54 +5878,54 @@
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>95.8</v>
+        <v>94.97</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>94.75</v>
+        <v>94.37</v>
       </c>
       <c r="E85" s="26" t="n">
         <v>93.87</v>
       </c>
       <c r="F85" s="27" t="n">
-        <v>94.02</v>
+        <v>94.03</v>
       </c>
       <c r="G85" s="27" t="n">
-        <v>94.58</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="H85" s="28" t="n">
+        <v>93.72</v>
+      </c>
+      <c r="I85" s="29" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="J85" s="29" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="K85" s="30" t="n">
         <v>93.53</v>
       </c>
-      <c r="I85" s="29" t="n">
-        <v>92.97</v>
-      </c>
-      <c r="J85" s="29" t="n">
-        <v>92.48</v>
-      </c>
-      <c r="K85" s="30" t="n">
-        <v>93.28</v>
-      </c>
       <c r="L85" s="31" t="n">
-        <v>92.40000000000001</v>
+        <v>93.03</v>
       </c>
       <c r="M85" s="31" t="n">
-        <v>91.34999999999999</v>
-      </c>
-      <c r="N85" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>92.43000000000001</v>
+      </c>
+      <c r="N85" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>93.45</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>93.36</v>
+        <v>93.58</v>
       </c>
       <c r="Q85" s="33" t="n">
-        <v>93.45</v>
-      </c>
-      <c r="R85" s="35" t="n">
-        <v>-0.16</v>
+        <v>93.75</v>
+      </c>
+      <c r="R85" s="34" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="86">
@@ -5940,37 +5940,37 @@
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>17.73</v>
+        <v>17.87</v>
       </c>
       <c r="D86" s="25" t="n">
-        <v>17.34</v>
+        <v>17.51</v>
       </c>
       <c r="E86" s="26" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="F86" s="27" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="G86" s="27" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="H86" s="28" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="I86" s="29" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="J86" s="29" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="K86" s="30" t="n">
         <v>17.01</v>
       </c>
-      <c r="F86" s="27" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="G86" s="27" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="H86" s="28" t="n">
-        <v>16.96</v>
-      </c>
-      <c r="I86" s="29" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="J86" s="29" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="K86" s="30" t="n">
-        <v>16.8</v>
-      </c>
       <c r="L86" s="31" t="n">
-        <v>16.47</v>
+        <v>16.71</v>
       </c>
       <c r="M86" s="31" t="n">
-        <v>16.08</v>
+        <v>16.35</v>
       </c>
       <c r="N86" s="20" t="inlineStr">
         <is>
@@ -5978,16 +5978,16 @@
         </is>
       </c>
       <c r="O86" s="32" t="n">
-        <v>16.89</v>
+        <v>17.08</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>16.83</v>
+        <v>17.04</v>
       </c>
       <c r="Q86" s="33" t="n">
-        <v>17.06</v>
+        <v>17.15</v>
       </c>
       <c r="R86" s="34" t="n">
-        <v>1.97</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="87">
@@ -6002,54 +6002,54 @@
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>123.93</v>
+        <v>124.31</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>122.43</v>
+        <v>122.51</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>121.17</v>
+        <v>121</v>
       </c>
       <c r="F87" s="27" t="n">
-        <v>121.8</v>
+        <v>121.07</v>
       </c>
       <c r="G87" s="27" t="n">
-        <v>122.4</v>
+        <v>122.13</v>
       </c>
       <c r="H87" s="28" t="n">
-        <v>120.9</v>
+        <v>120.33</v>
       </c>
       <c r="I87" s="29" t="n">
-        <v>120.3</v>
+        <v>119.27</v>
       </c>
       <c r="J87" s="29" t="n">
-        <v>119.4</v>
+        <v>118.53</v>
       </c>
       <c r="K87" s="30" t="n">
-        <v>120.33</v>
+        <v>120</v>
       </c>
       <c r="L87" s="31" t="n">
-        <v>119.07</v>
+        <v>118.49</v>
       </c>
       <c r="M87" s="31" t="n">
-        <v>117.57</v>
-      </c>
-      <c r="N87" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>116.69</v>
+      </c>
+      <c r="N87" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>120.67</v>
+        <v>120.23</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>120.45</v>
+        <v>120.14</v>
       </c>
       <c r="Q87" s="33" t="n">
-        <v>121.2</v>
-      </c>
-      <c r="R87" s="34" t="n">
-        <v>1</v>
+        <v>120</v>
+      </c>
+      <c r="R87" s="36" t="n">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="88">
@@ -6064,37 +6064,37 @@
         </is>
       </c>
       <c r="C88" s="25" t="n">
-        <v>68.29000000000001</v>
+        <v>76.05</v>
       </c>
       <c r="D88" s="25" t="n">
-        <v>64.73999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="E88" s="26" t="n">
-        <v>61.77</v>
+        <v>65.48</v>
       </c>
       <c r="F88" s="27" t="n">
-        <v>62.7</v>
+        <v>67.2</v>
       </c>
       <c r="G88" s="27" t="n">
-        <v>64.40000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H88" s="28" t="n">
-        <v>60.85</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I88" s="29" t="n">
-        <v>59.15</v>
+        <v>61.45</v>
       </c>
       <c r="J88" s="29" t="n">
-        <v>57.3</v>
+        <v>58.35</v>
       </c>
       <c r="K88" s="30" t="n">
-        <v>59.78</v>
+        <v>62.27</v>
       </c>
       <c r="L88" s="31" t="n">
-        <v>56.81</v>
+        <v>57.45</v>
       </c>
       <c r="M88" s="31" t="n">
-        <v>53.26</v>
+        <v>51.7</v>
       </c>
       <c r="N88" s="20" t="inlineStr">
         <is>
@@ -6102,16 +6102,16 @@
         </is>
       </c>
       <c r="O88" s="32" t="n">
-        <v>60.45</v>
+        <v>63.41</v>
       </c>
       <c r="P88" s="32" t="n">
-        <v>60.06</v>
+        <v>62.71</v>
       </c>
       <c r="Q88" s="33" t="n">
-        <v>61</v>
+        <v>64.55</v>
       </c>
       <c r="R88" s="34" t="n">
-        <v>4.01</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="89">
@@ -6126,54 +6126,54 @@
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>10.27</v>
+        <v>10.55</v>
       </c>
       <c r="D89" s="25" t="n">
-        <v>10.05</v>
+        <v>10.23</v>
       </c>
       <c r="E89" s="26" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="F89" s="27" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G89" s="27" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="H89" s="28" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="I89" s="29" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="J89" s="29" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="K89" s="30" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="L89" s="31" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="M89" s="31" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="N89" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O89" s="32" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="F89" s="27" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="G89" s="27" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="H89" s="28" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="I89" s="29" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="J89" s="29" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="K89" s="30" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="L89" s="31" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="M89" s="31" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="N89" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O89" s="32" t="n">
-        <v>9.76</v>
-      </c>
       <c r="P89" s="32" t="n">
-        <v>9.76</v>
+        <v>9.81</v>
       </c>
       <c r="Q89" s="33" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="R89" s="35" t="n">
-        <v>-0.92</v>
+        <v>9.98</v>
+      </c>
+      <c r="R89" s="34" t="n">
+        <v>2.67</v>
       </c>
     </row>
     <row r="90">
@@ -6188,54 +6188,54 @@
         </is>
       </c>
       <c r="C90" s="25" t="n">
-        <v>22.02</v>
+        <v>20.35</v>
       </c>
       <c r="D90" s="25" t="n">
-        <v>20.34</v>
+        <v>19.51</v>
       </c>
       <c r="E90" s="26" t="n">
-        <v>18.93</v>
+        <v>18.81</v>
       </c>
       <c r="F90" s="27" t="n">
-        <v>19.41</v>
+        <v>18.91</v>
       </c>
       <c r="G90" s="27" t="n">
-        <v>20.19</v>
+        <v>19.37</v>
       </c>
       <c r="H90" s="28" t="n">
-        <v>18.51</v>
+        <v>18.53</v>
       </c>
       <c r="I90" s="29" t="n">
-        <v>17.73</v>
+        <v>18.07</v>
       </c>
       <c r="J90" s="29" t="n">
-        <v>16.83</v>
+        <v>17.69</v>
       </c>
       <c r="K90" s="30" t="n">
-        <v>17.99</v>
+        <v>18.33</v>
       </c>
       <c r="L90" s="31" t="n">
-        <v>16.58</v>
+        <v>17.63</v>
       </c>
       <c r="M90" s="31" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="N90" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.79</v>
+      </c>
+      <c r="N90" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O90" s="32" t="n">
-        <v>18.32</v>
+        <v>18.47</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>18.12</v>
+        <v>18.4</v>
       </c>
       <c r="Q90" s="33" t="n">
-        <v>18.62</v>
-      </c>
-      <c r="R90" s="34" t="n">
-        <v>4.2</v>
+        <v>18.45</v>
+      </c>
+      <c r="R90" s="36" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="91">
@@ -6250,37 +6250,37 @@
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>19.5</v>
+        <v>19.35</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>19.18</v>
+        <v>19.08</v>
       </c>
       <c r="E91" s="26" t="n">
-        <v>18.91</v>
+        <v>18.85</v>
       </c>
       <c r="F91" s="27" t="n">
-        <v>18.87</v>
+        <v>18.97</v>
       </c>
       <c r="G91" s="27" t="n">
-        <v>19.09</v>
+        <v>19.07</v>
       </c>
       <c r="H91" s="28" t="n">
-        <v>18.77</v>
+        <v>18.8</v>
       </c>
       <c r="I91" s="29" t="n">
-        <v>18.55</v>
+        <v>18.7</v>
       </c>
       <c r="J91" s="29" t="n">
-        <v>18.45</v>
+        <v>18.53</v>
       </c>
       <c r="K91" s="30" t="n">
-        <v>18.73</v>
+        <v>18.7</v>
       </c>
       <c r="L91" s="31" t="n">
-        <v>18.46</v>
+        <v>18.47</v>
       </c>
       <c r="M91" s="31" t="n">
-        <v>18.14</v>
+        <v>18.2</v>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
@@ -6291,13 +6291,13 @@
         <v>18.76</v>
       </c>
       <c r="P91" s="32" t="n">
-        <v>18.76</v>
+        <v>18.72</v>
       </c>
       <c r="Q91" s="33" t="n">
-        <v>18.66</v>
-      </c>
-      <c r="R91" s="35" t="n">
-        <v>-0.6899999999999999</v>
+        <v>18.86</v>
+      </c>
+      <c r="R91" s="34" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="92">
@@ -6312,37 +6312,37 @@
         </is>
       </c>
       <c r="C92" s="25" t="n">
-        <v>31.81</v>
+        <v>31.89</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>31.27</v>
+        <v>31.29</v>
       </c>
       <c r="E92" s="26" t="n">
-        <v>30.82</v>
+        <v>30.79</v>
       </c>
       <c r="F92" s="27" t="n">
-        <v>30.89</v>
+        <v>30.97</v>
       </c>
       <c r="G92" s="27" t="n">
-        <v>31.19</v>
+        <v>31.25</v>
       </c>
       <c r="H92" s="28" t="n">
         <v>30.65</v>
       </c>
       <c r="I92" s="29" t="n">
-        <v>30.35</v>
+        <v>30.37</v>
       </c>
       <c r="J92" s="29" t="n">
-        <v>30.11</v>
+        <v>30.05</v>
       </c>
       <c r="K92" s="30" t="n">
-        <v>30.52</v>
+        <v>30.45</v>
       </c>
       <c r="L92" s="31" t="n">
-        <v>30.07</v>
+        <v>29.95</v>
       </c>
       <c r="M92" s="31" t="n">
-        <v>29.53</v>
+        <v>29.35</v>
       </c>
       <c r="N92" s="20" t="inlineStr">
         <is>
@@ -6350,16 +6350,16 @@
         </is>
       </c>
       <c r="O92" s="32" t="n">
-        <v>30.6</v>
+        <v>30.57</v>
       </c>
       <c r="P92" s="32" t="n">
-        <v>30.56</v>
+        <v>30.5</v>
       </c>
       <c r="Q92" s="33" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R92" s="35" t="n">
-        <v>-0.71</v>
+        <v>30.7</v>
+      </c>
+      <c r="R92" s="34" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="93">
@@ -6374,54 +6374,54 @@
         </is>
       </c>
       <c r="C93" s="25" t="n">
-        <v>21.65</v>
+        <v>21.8</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>21.31</v>
+        <v>21.43</v>
       </c>
       <c r="E93" s="26" t="n">
-        <v>21.03</v>
+        <v>21.12</v>
       </c>
       <c r="F93" s="27" t="n">
-        <v>21.15</v>
+        <v>21.14</v>
       </c>
       <c r="G93" s="27" t="n">
-        <v>21.29</v>
+        <v>21.36</v>
       </c>
       <c r="H93" s="28" t="n">
-        <v>20.95</v>
+        <v>20.99</v>
       </c>
       <c r="I93" s="29" t="n">
-        <v>20.81</v>
+        <v>20.77</v>
       </c>
       <c r="J93" s="29" t="n">
-        <v>20.61</v>
+        <v>20.62</v>
       </c>
       <c r="K93" s="30" t="n">
-        <v>20.83</v>
+        <v>20.91</v>
       </c>
       <c r="L93" s="31" t="n">
-        <v>20.55</v>
+        <v>20.6</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>20.21</v>
-      </c>
-      <c r="N93" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>20.23</v>
+      </c>
+      <c r="N93" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O93" s="32" t="n">
-        <v>20.91</v>
+        <v>20.96</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>20.86</v>
+        <v>20.94</v>
       </c>
       <c r="Q93" s="33" t="n">
-        <v>21</v>
-      </c>
-      <c r="R93" s="34" t="n">
-        <v>1.3</v>
+        <v>20.93</v>
+      </c>
+      <c r="R93" s="36" t="n">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="94">
@@ -6436,54 +6436,54 @@
         </is>
       </c>
       <c r="C94" s="25" t="n">
-        <v>30.24</v>
+        <v>29.25</v>
       </c>
       <c r="D94" s="25" t="n">
-        <v>29.36</v>
+        <v>28.91</v>
       </c>
       <c r="E94" s="26" t="n">
         <v>28.63</v>
       </c>
       <c r="F94" s="27" t="n">
-        <v>28.99</v>
+        <v>28.61</v>
       </c>
       <c r="G94" s="27" t="n">
-        <v>29.35</v>
+        <v>28.83</v>
       </c>
       <c r="H94" s="28" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="I94" s="29" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="J94" s="29" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="K94" s="30" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="L94" s="31" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="M94" s="31" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="N94" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O94" s="32" t="n">
         <v>28.47</v>
       </c>
-      <c r="I94" s="29" t="n">
-        <v>28.11</v>
-      </c>
-      <c r="J94" s="29" t="n">
-        <v>27.59</v>
-      </c>
-      <c r="K94" s="30" t="n">
-        <v>28.13</v>
-      </c>
-      <c r="L94" s="31" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="M94" s="31" t="n">
-        <v>26.52</v>
-      </c>
-      <c r="N94" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O94" s="32" t="n">
-        <v>28.33</v>
-      </c>
       <c r="P94" s="32" t="n">
-        <v>28.2</v>
+        <v>28.46</v>
       </c>
       <c r="Q94" s="33" t="n">
-        <v>28.64</v>
-      </c>
-      <c r="R94" s="34" t="n">
-        <v>2.87</v>
+        <v>28.4</v>
+      </c>
+      <c r="R94" s="36" t="n">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="95">
@@ -6498,37 +6498,37 @@
         </is>
       </c>
       <c r="C95" s="25" t="n">
-        <v>176.43</v>
+        <v>176.88</v>
       </c>
       <c r="D95" s="25" t="n">
-        <v>173.63</v>
+        <v>174.48</v>
       </c>
       <c r="E95" s="26" t="n">
-        <v>171.28</v>
+        <v>172.47</v>
       </c>
       <c r="F95" s="27" t="n">
+        <v>173.2</v>
+      </c>
+      <c r="G95" s="27" t="n">
+        <v>174.3</v>
+      </c>
+      <c r="H95" s="28" t="n">
         <v>171.9</v>
       </c>
-      <c r="G95" s="27" t="n">
-        <v>173.3</v>
-      </c>
-      <c r="H95" s="28" t="n">
-        <v>170.5</v>
-      </c>
       <c r="I95" s="29" t="n">
-        <v>169.1</v>
+        <v>170.8</v>
       </c>
       <c r="J95" s="29" t="n">
-        <v>167.7</v>
+        <v>169.5</v>
       </c>
       <c r="K95" s="30" t="n">
-        <v>169.72</v>
+        <v>171.13</v>
       </c>
       <c r="L95" s="31" t="n">
-        <v>167.37</v>
+        <v>169.12</v>
       </c>
       <c r="M95" s="31" t="n">
-        <v>164.57</v>
+        <v>166.72</v>
       </c>
       <c r="N95" s="20" t="inlineStr">
         <is>
@@ -6536,16 +6536,16 @@
         </is>
       </c>
       <c r="O95" s="32" t="n">
-        <v>170.22</v>
+        <v>171.61</v>
       </c>
       <c r="P95" s="32" t="n">
-        <v>169.93</v>
+        <v>171.32</v>
       </c>
       <c r="Q95" s="33" t="n">
-        <v>170.5</v>
+        <v>172.1</v>
       </c>
       <c r="R95" s="34" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6560,54 +6560,54 @@
         </is>
       </c>
       <c r="C96" s="25" t="n">
-        <v>14.63</v>
+        <v>14.86</v>
       </c>
       <c r="D96" s="25" t="n">
-        <v>14.36</v>
+        <v>14.39</v>
       </c>
       <c r="E96" s="26" t="n">
-        <v>14.13</v>
+        <v>14</v>
       </c>
       <c r="F96" s="27" t="n">
-        <v>14.1</v>
+        <v>14.02</v>
       </c>
       <c r="G96" s="27" t="n">
-        <v>14.28</v>
+        <v>14.3</v>
       </c>
       <c r="H96" s="28" t="n">
-        <v>14.01</v>
+        <v>13.83</v>
       </c>
       <c r="I96" s="29" t="n">
-        <v>13.83</v>
+        <v>13.55</v>
       </c>
       <c r="J96" s="29" t="n">
-        <v>13.74</v>
+        <v>13.36</v>
       </c>
       <c r="K96" s="30" t="n">
-        <v>13.98</v>
+        <v>13.73</v>
       </c>
       <c r="L96" s="31" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="M96" s="31" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="N96" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O96" s="32" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="P96" s="32" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="Q96" s="33" t="n">
         <v>13.75</v>
       </c>
-      <c r="M96" s="31" t="n">
-        <v>13.48</v>
-      </c>
-      <c r="N96" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O96" s="32" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="P96" s="32" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q96" s="33" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="R96" s="35" t="n">
-        <v>-0.85</v>
+      <c r="R96" s="36" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="97">
@@ -6622,54 +6622,54 @@
         </is>
       </c>
       <c r="C97" s="25" t="n">
-        <v>22.2</v>
+        <v>21.53</v>
       </c>
       <c r="D97" s="25" t="n">
-        <v>21.55</v>
+        <v>21.2</v>
       </c>
       <c r="E97" s="26" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="F97" s="27" t="n">
         <v>21.01</v>
       </c>
-      <c r="F97" s="27" t="n">
-        <v>21.21</v>
-      </c>
       <c r="G97" s="27" t="n">
-        <v>21.5</v>
+        <v>21.17</v>
       </c>
       <c r="H97" s="28" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="I97" s="29" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="J97" s="29" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="K97" s="30" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="L97" s="31" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="M97" s="31" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="N97" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O97" s="32" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="P97" s="32" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="Q97" s="33" t="n">
         <v>20.85</v>
       </c>
-      <c r="I97" s="29" t="n">
-        <v>20.56</v>
-      </c>
-      <c r="J97" s="29" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="K97" s="30" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="L97" s="31" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="M97" s="31" t="n">
-        <v>19.45</v>
-      </c>
-      <c r="N97" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O97" s="32" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="P97" s="32" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="Q97" s="33" t="n">
-        <v>20.91</v>
-      </c>
-      <c r="R97" s="34" t="n">
-        <v>1.95</v>
+      <c r="R97" s="36" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="98">
@@ -6684,54 +6684,54 @@
         </is>
       </c>
       <c r="C98" s="25" t="n">
-        <v>16.92</v>
+        <v>16.85</v>
       </c>
       <c r="D98" s="25" t="n">
-        <v>16.69</v>
+        <v>16.65</v>
       </c>
       <c r="E98" s="26" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="F98" s="27" t="n">
         <v>16.5</v>
       </c>
-      <c r="F98" s="27" t="n">
-        <v>16.59</v>
-      </c>
       <c r="G98" s="27" t="n">
-        <v>16.69</v>
+        <v>16.62</v>
       </c>
       <c r="H98" s="28" t="n">
-        <v>16.46</v>
+        <v>16.42</v>
       </c>
       <c r="I98" s="29" t="n">
-        <v>16.36</v>
+        <v>16.3</v>
       </c>
       <c r="J98" s="29" t="n">
-        <v>16.23</v>
+        <v>16.22</v>
       </c>
       <c r="K98" s="30" t="n">
         <v>16.37</v>
       </c>
       <c r="L98" s="31" t="n">
-        <v>16.18</v>
+        <v>16.21</v>
       </c>
       <c r="M98" s="31" t="n">
-        <v>15.95</v>
-      </c>
-      <c r="N98" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.01</v>
+      </c>
+      <c r="N98" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O98" s="32" t="n">
-        <v>16.42</v>
+        <v>16.4</v>
       </c>
       <c r="P98" s="32" t="n">
         <v>16.39</v>
       </c>
       <c r="Q98" s="33" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="R98" s="34" t="n">
-        <v>1.35</v>
+        <v>16.39</v>
+      </c>
+      <c r="R98" s="36" t="n">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="99">
@@ -6746,54 +6746,54 @@
         </is>
       </c>
       <c r="C99" s="25" t="n">
-        <v>10.44</v>
+        <v>10.53</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>10.26</v>
+        <v>10.33</v>
       </c>
       <c r="E99" s="26" t="n">
-        <v>10.11</v>
+        <v>10.17</v>
       </c>
       <c r="F99" s="27" t="n">
-        <v>10.14</v>
+        <v>10.16</v>
       </c>
       <c r="G99" s="27" t="n">
-        <v>10.23</v>
+        <v>10.28</v>
       </c>
       <c r="H99" s="28" t="n">
-        <v>10.05</v>
+        <v>10.08</v>
       </c>
       <c r="I99" s="29" t="n">
         <v>9.960000000000001</v>
       </c>
       <c r="J99" s="29" t="n">
-        <v>9.869999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="K99" s="30" t="n">
-        <v>10.01</v>
+        <v>10.05</v>
       </c>
       <c r="L99" s="31" t="n">
-        <v>9.859999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M99" s="31" t="n">
-        <v>9.68</v>
-      </c>
-      <c r="N99" s="36" t="inlineStr">
+        <v>9.69</v>
+      </c>
+      <c r="N99" s="35" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O99" s="32" t="n">
-        <v>10.04</v>
+        <v>10.08</v>
       </c>
       <c r="P99" s="32" t="n">
-        <v>10.02</v>
+        <v>10.07</v>
       </c>
       <c r="Q99" s="33" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="R99" s="34" t="n">
-        <v>0</v>
+        <v>10.03</v>
+      </c>
+      <c r="R99" s="36" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="100">
@@ -6808,37 +6808,37 @@
         </is>
       </c>
       <c r="C100" s="25" t="n">
-        <v>27.1</v>
+        <v>27.43</v>
       </c>
       <c r="D100" s="25" t="n">
-        <v>26.64</v>
+        <v>27.03</v>
       </c>
       <c r="E100" s="26" t="n">
-        <v>26.26</v>
+        <v>26.69</v>
       </c>
       <c r="F100" s="27" t="n">
-        <v>26.51</v>
+        <v>26.73</v>
       </c>
       <c r="G100" s="27" t="n">
-        <v>26.67</v>
+        <v>26.95</v>
       </c>
       <c r="H100" s="28" t="n">
-        <v>26.21</v>
+        <v>26.55</v>
       </c>
       <c r="I100" s="29" t="n">
-        <v>26.05</v>
+        <v>26.33</v>
       </c>
       <c r="J100" s="29" t="n">
-        <v>25.75</v>
+        <v>26.15</v>
       </c>
       <c r="K100" s="30" t="n">
-        <v>26</v>
+        <v>26.47</v>
       </c>
       <c r="L100" s="31" t="n">
-        <v>25.62</v>
+        <v>26.13</v>
       </c>
       <c r="M100" s="31" t="n">
-        <v>25.16</v>
+        <v>25.73</v>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
@@ -6846,16 +6846,16 @@
         </is>
       </c>
       <c r="O100" s="32" t="n">
-        <v>26.12</v>
+        <v>26.53</v>
       </c>
       <c r="P100" s="32" t="n">
-        <v>26.04</v>
+        <v>26.5</v>
       </c>
       <c r="Q100" s="33" t="n">
-        <v>26.36</v>
+        <v>26.5</v>
       </c>
       <c r="R100" s="34" t="n">
-        <v>2.25</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="101">
@@ -6870,54 +6870,54 @@
         </is>
       </c>
       <c r="C101" s="25" t="n">
-        <v>17.21</v>
+        <v>17.63</v>
       </c>
       <c r="D101" s="25" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="E101" s="26" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="F101" s="27" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="G101" s="27" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="H101" s="28" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="I101" s="29" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="J101" s="29" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="K101" s="30" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="L101" s="31" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="M101" s="31" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="N101" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O101" s="32" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="P101" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q101" s="33" t="n">
         <v>17.1</v>
       </c>
-      <c r="E101" s="26" t="n">
-        <v>17.01</v>
-      </c>
-      <c r="F101" s="27" t="n">
-        <v>17.05</v>
-      </c>
-      <c r="G101" s="27" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H101" s="28" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="I101" s="29" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="J101" s="29" t="n">
-        <v>16.88</v>
-      </c>
-      <c r="K101" s="30" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="L101" s="31" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="M101" s="31" t="n">
-        <v>16.74</v>
-      </c>
-      <c r="N101" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O101" s="32" t="n">
-        <v>16.97</v>
-      </c>
-      <c r="P101" s="32" t="n">
-        <v>16.95</v>
-      </c>
-      <c r="Q101" s="33" t="n">
-        <v>17.01</v>
-      </c>
       <c r="R101" s="34" t="n">
-        <v>0.29</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="102">
@@ -6932,54 +6932,54 @@
         </is>
       </c>
       <c r="C102" s="25" t="n">
-        <v>34.06</v>
+        <v>33.7</v>
       </c>
       <c r="D102" s="25" t="n">
-        <v>33.28</v>
+        <v>33.08</v>
       </c>
       <c r="E102" s="26" t="n">
-        <v>32.63</v>
+        <v>32.56</v>
       </c>
       <c r="F102" s="27" t="n">
-        <v>32.79</v>
+        <v>32.49</v>
       </c>
       <c r="G102" s="27" t="n">
-        <v>33.19</v>
+        <v>32.91</v>
       </c>
       <c r="H102" s="28" t="n">
-        <v>32.41</v>
+        <v>32.29</v>
       </c>
       <c r="I102" s="29" t="n">
-        <v>32.01</v>
+        <v>31.87</v>
       </c>
       <c r="J102" s="29" t="n">
-        <v>31.63</v>
+        <v>31.67</v>
       </c>
       <c r="K102" s="30" t="n">
-        <v>32.19</v>
+        <v>32.22</v>
       </c>
       <c r="L102" s="31" t="n">
-        <v>31.54</v>
+        <v>31.7</v>
       </c>
       <c r="M102" s="31" t="n">
-        <v>30.76</v>
-      </c>
-      <c r="N102" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>31.08</v>
+      </c>
+      <c r="N102" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O102" s="32" t="n">
-        <v>32.33</v>
+        <v>32.28</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="Q102" s="33" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="R102" s="34" t="n">
-        <v>0.5</v>
+        <v>32.08</v>
+      </c>
+      <c r="R102" s="36" t="n">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="103">
@@ -6994,37 +6994,37 @@
         </is>
       </c>
       <c r="C103" s="25" t="n">
-        <v>16.06</v>
+        <v>17.1</v>
       </c>
       <c r="D103" s="25" t="n">
-        <v>15.82</v>
+        <v>16.51</v>
       </c>
       <c r="E103" s="26" t="n">
-        <v>15.62</v>
+        <v>16.02</v>
       </c>
       <c r="F103" s="27" t="n">
-        <v>15.68</v>
+        <v>16.01</v>
       </c>
       <c r="G103" s="27" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="H103" s="28" t="n">
         <v>15.79</v>
       </c>
-      <c r="H103" s="28" t="n">
-        <v>15.55</v>
-      </c>
       <c r="I103" s="29" t="n">
-        <v>15.44</v>
+        <v>15.42</v>
       </c>
       <c r="J103" s="29" t="n">
-        <v>15.31</v>
+        <v>15.2</v>
       </c>
       <c r="K103" s="30" t="n">
-        <v>15.48</v>
+        <v>15.69</v>
       </c>
       <c r="L103" s="31" t="n">
-        <v>15.28</v>
+        <v>15.2</v>
       </c>
       <c r="M103" s="31" t="n">
-        <v>15.04</v>
+        <v>14.61</v>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
@@ -7032,16 +7032,16 @@
         </is>
       </c>
       <c r="O103" s="32" t="n">
-        <v>15.53</v>
+        <v>15.76</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>15.5</v>
+        <v>15.74</v>
       </c>
       <c r="Q103" s="33" t="n">
-        <v>15.56</v>
+        <v>15.65</v>
       </c>
       <c r="R103" s="34" t="n">
-        <v>0.84</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="104">
@@ -7056,54 +7056,54 @@
         </is>
       </c>
       <c r="C104" s="25" t="n">
-        <v>73.76000000000001</v>
+        <v>74.38</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>73.01000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="E104" s="26" t="n">
-        <v>72.39</v>
+        <v>72.81</v>
       </c>
       <c r="F104" s="27" t="n">
-        <v>72.5</v>
+        <v>73.02</v>
       </c>
       <c r="G104" s="27" t="n">
-        <v>72.90000000000001</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="H104" s="28" t="n">
-        <v>72.15000000000001</v>
+        <v>72.58</v>
       </c>
       <c r="I104" s="29" t="n">
-        <v>71.75</v>
+        <v>72.17</v>
       </c>
       <c r="J104" s="29" t="n">
-        <v>71.40000000000001</v>
+        <v>71.73</v>
       </c>
       <c r="K104" s="30" t="n">
-        <v>71.97</v>
+        <v>72.34</v>
       </c>
       <c r="L104" s="31" t="n">
-        <v>71.34</v>
+        <v>71.62</v>
       </c>
       <c r="M104" s="31" t="n">
-        <v>70.59</v>
-      </c>
-      <c r="N104" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>70.77</v>
+      </c>
+      <c r="N104" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O104" s="32" t="n">
-        <v>72.09</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>72.02</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Q104" s="33" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="R104" s="34" t="n">
-        <v>0.28</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -7118,54 +7118,54 @@
         </is>
       </c>
       <c r="C105" s="25" t="n">
-        <v>15.38</v>
+        <v>15.14</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>15.02</v>
+        <v>14.87</v>
       </c>
       <c r="E105" s="26" t="n">
-        <v>14.72</v>
+        <v>14.64</v>
       </c>
       <c r="F105" s="27" t="n">
-        <v>14.68</v>
+        <v>14.76</v>
       </c>
       <c r="G105" s="27" t="n">
-        <v>14.92</v>
+        <v>14.86</v>
       </c>
       <c r="H105" s="28" t="n">
-        <v>14.56</v>
+        <v>14.59</v>
       </c>
       <c r="I105" s="29" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="J105" s="29" t="n">
         <v>14.32</v>
       </c>
-      <c r="J105" s="29" t="n">
-        <v>14.2</v>
-      </c>
       <c r="K105" s="30" t="n">
-        <v>14.52</v>
+        <v>14.49</v>
       </c>
       <c r="L105" s="31" t="n">
-        <v>14.22</v>
+        <v>14.26</v>
       </c>
       <c r="M105" s="31" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="N105" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>13.99</v>
+      </c>
+      <c r="N105" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O105" s="32" t="n">
         <v>14.55</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>14.55</v>
+        <v>14.51</v>
       </c>
       <c r="Q105" s="33" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="R105" s="35" t="n">
-        <v>-1.03</v>
+        <v>14.65</v>
+      </c>
+      <c r="R105" s="34" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="106">
@@ -7180,54 +7180,54 @@
         </is>
       </c>
       <c r="C106" s="25" t="n">
-        <v>21.73</v>
+        <v>19.2</v>
       </c>
       <c r="D106" s="25" t="n">
-        <v>20.02</v>
+        <v>18.52</v>
       </c>
       <c r="E106" s="26" t="n">
-        <v>18.58</v>
+        <v>17.95</v>
       </c>
       <c r="F106" s="27" t="n">
-        <v>18.77</v>
+        <v>17.89</v>
       </c>
       <c r="G106" s="27" t="n">
-        <v>19.72</v>
+        <v>18.34</v>
       </c>
       <c r="H106" s="28" t="n">
-        <v>18.01</v>
+        <v>17.66</v>
       </c>
       <c r="I106" s="29" t="n">
-        <v>17.06</v>
+        <v>17.21</v>
       </c>
       <c r="J106" s="29" t="n">
-        <v>16.3</v>
+        <v>16.98</v>
       </c>
       <c r="K106" s="30" t="n">
-        <v>17.63</v>
+        <v>17.57</v>
       </c>
       <c r="L106" s="31" t="n">
-        <v>16.19</v>
+        <v>17</v>
       </c>
       <c r="M106" s="31" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="N106" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.32</v>
+      </c>
+      <c r="N106" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>17.88</v>
+        <v>17.64</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>17.76</v>
+        <v>17.62</v>
       </c>
       <c r="Q106" s="33" t="n">
-        <v>17.82</v>
-      </c>
-      <c r="R106" s="34" t="n">
-        <v>3.36</v>
+        <v>17.45</v>
+      </c>
+      <c r="R106" s="36" t="n">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="107">
@@ -7245,51 +7245,51 @@
         <v>2.56</v>
       </c>
       <c r="D107" s="25" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="E107" s="26" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="F107" s="27" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="G107" s="27" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H107" s="28" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="I107" s="29" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="J107" s="29" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="K107" s="30" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="L107" s="31" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="M107" s="31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N107" s="36" t="inlineStr">
+        <v>2.22</v>
+      </c>
+      <c r="N107" s="35" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O107" s="32" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="P107" s="32" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="Q107" s="33" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="R107" s="35" t="n">
-        <v>-0.82</v>
+        <v>2.37</v>
+      </c>
+      <c r="R107" s="36" t="n">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="108">
@@ -7304,37 +7304,37 @@
         </is>
       </c>
       <c r="C108" s="25" t="n">
-        <v>40.89</v>
+        <v>41.46</v>
       </c>
       <c r="D108" s="25" t="n">
-        <v>40.09</v>
+        <v>40.52</v>
       </c>
       <c r="E108" s="26" t="n">
-        <v>39.42</v>
+        <v>39.73</v>
       </c>
       <c r="F108" s="27" t="n">
-        <v>39.41</v>
+        <v>39.8</v>
       </c>
       <c r="G108" s="27" t="n">
-        <v>39.91</v>
+        <v>40.34</v>
       </c>
       <c r="H108" s="28" t="n">
-        <v>39.11</v>
+        <v>39.4</v>
       </c>
       <c r="I108" s="29" t="n">
-        <v>38.61</v>
+        <v>38.86</v>
       </c>
       <c r="J108" s="29" t="n">
-        <v>38.31</v>
+        <v>38.46</v>
       </c>
       <c r="K108" s="30" t="n">
-        <v>38.98</v>
+        <v>39.21</v>
       </c>
       <c r="L108" s="31" t="n">
-        <v>38.31</v>
+        <v>38.42</v>
       </c>
       <c r="M108" s="31" t="n">
-        <v>37.51</v>
+        <v>37.48</v>
       </c>
       <c r="N108" s="20" t="inlineStr">
         <is>
@@ -7342,16 +7342,16 @@
         </is>
       </c>
       <c r="O108" s="32" t="n">
-        <v>39.07</v>
+        <v>39.34</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>39.04</v>
+        <v>39.28</v>
       </c>
       <c r="Q108" s="33" t="n">
-        <v>38.92</v>
-      </c>
-      <c r="R108" s="35" t="n">
-        <v>-0.46</v>
+        <v>39.26</v>
+      </c>
+      <c r="R108" s="34" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="109">
@@ -7366,54 +7366,54 @@
         </is>
       </c>
       <c r="C109" s="25" t="n">
-        <v>8.52</v>
+        <v>8.5</v>
       </c>
       <c r="D109" s="25" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E109" s="26" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F109" s="27" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="G109" s="27" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="E109" s="26" t="n">
+      <c r="H109" s="28" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I109" s="29" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="J109" s="29" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="K109" s="30" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="L109" s="31" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="M109" s="31" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="N109" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O109" s="32" t="n">
         <v>8.26</v>
       </c>
-      <c r="F109" s="27" t="n">
+      <c r="P109" s="32" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="Q109" s="33" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="G109" s="27" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="H109" s="28" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="I109" s="29" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="J109" s="29" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="K109" s="30" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="L109" s="31" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="M109" s="31" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="N109" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O109" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P109" s="32" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="Q109" s="33" t="n">
-        <v>8.210000000000001</v>
-      </c>
       <c r="R109" s="34" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="110">
@@ -7428,37 +7428,37 @@
         </is>
       </c>
       <c r="C110" s="25" t="n">
-        <v>44.81</v>
+        <v>45.09</v>
       </c>
       <c r="D110" s="25" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="E110" s="26" t="n">
         <v>44.53</v>
       </c>
-      <c r="E110" s="26" t="n">
-        <v>44.3</v>
-      </c>
       <c r="F110" s="27" t="n">
-        <v>44.45</v>
+        <v>44.54</v>
       </c>
       <c r="G110" s="27" t="n">
-        <v>44.55</v>
+        <v>44.72</v>
       </c>
       <c r="H110" s="28" t="n">
-        <v>44.27</v>
+        <v>44.42</v>
       </c>
       <c r="I110" s="29" t="n">
-        <v>44.17</v>
+        <v>44.24</v>
       </c>
       <c r="J110" s="29" t="n">
-        <v>43.99</v>
+        <v>44.12</v>
       </c>
       <c r="K110" s="30" t="n">
-        <v>44.14</v>
+        <v>44.37</v>
       </c>
       <c r="L110" s="31" t="n">
-        <v>43.91</v>
+        <v>44.11</v>
       </c>
       <c r="M110" s="31" t="n">
-        <v>43.63</v>
+        <v>43.81</v>
       </c>
       <c r="N110" s="20" t="inlineStr">
         <is>
@@ -7466,16 +7466,16 @@
         </is>
       </c>
       <c r="O110" s="32" t="n">
-        <v>44.22</v>
+        <v>44.4</v>
       </c>
       <c r="P110" s="32" t="n">
-        <v>44.16</v>
+        <v>44.39</v>
       </c>
       <c r="Q110" s="33" t="n">
         <v>44.36</v>
       </c>
       <c r="R110" s="34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -7490,37 +7490,37 @@
         </is>
       </c>
       <c r="C111" s="25" t="n">
-        <v>68.70999999999999</v>
+        <v>67.33</v>
       </c>
       <c r="D111" s="25" t="n">
-        <v>66.91</v>
+        <v>66.48</v>
       </c>
       <c r="E111" s="26" t="n">
-        <v>65.40000000000001</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="F111" s="27" t="n">
-        <v>66.06999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G111" s="27" t="n">
-        <v>66.83</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="H111" s="28" t="n">
-        <v>65.03</v>
+        <v>65.5</v>
       </c>
       <c r="I111" s="29" t="n">
-        <v>64.27</v>
+        <v>65.05</v>
       </c>
       <c r="J111" s="29" t="n">
-        <v>63.23</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K111" s="30" t="n">
-        <v>64.40000000000001</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="L111" s="31" t="n">
-        <v>62.89</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="M111" s="31" t="n">
-        <v>61.09</v>
+        <v>63.72</v>
       </c>
       <c r="N111" s="20" t="inlineStr">
         <is>
@@ -7528,16 +7528,16 @@
         </is>
       </c>
       <c r="O111" s="32" t="n">
-        <v>64.78</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>64.54000000000001</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="Q111" s="33" t="n">
-        <v>65.3</v>
+        <v>65.45</v>
       </c>
       <c r="R111" s="34" t="n">
-        <v>2.03</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="112">
@@ -7552,54 +7552,54 @@
         </is>
       </c>
       <c r="C112" s="25" t="n">
-        <v>10.56</v>
+        <v>10.7</v>
       </c>
       <c r="D112" s="25" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="E112" s="26" t="n">
         <v>10.48</v>
       </c>
-      <c r="E112" s="26" t="n">
-        <v>10.41</v>
-      </c>
       <c r="F112" s="27" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="G112" s="27" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="H112" s="28" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="I112" s="29" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="J112" s="29" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="K112" s="30" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="L112" s="31" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="M112" s="31" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N112" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O112" s="32" t="n">
         <v>10.44</v>
       </c>
-      <c r="G112" s="27" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="H112" s="28" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="I112" s="29" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="J112" s="29" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="K112" s="30" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="L112" s="31" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M112" s="31" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="N112" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O112" s="32" t="n">
-        <v>10.38</v>
-      </c>
       <c r="P112" s="32" t="n">
-        <v>10.37</v>
+        <v>10.43</v>
       </c>
       <c r="Q112" s="33" t="n">
-        <v>10.4</v>
+        <v>10.49</v>
       </c>
       <c r="R112" s="34" t="n">
-        <v>0.48</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="113">
@@ -7614,37 +7614,37 @@
         </is>
       </c>
       <c r="C113" s="25" t="n">
-        <v>311.57</v>
+        <v>318</v>
       </c>
       <c r="D113" s="25" t="n">
-        <v>306.77</v>
+        <v>311.2</v>
       </c>
       <c r="E113" s="26" t="n">
-        <v>302.74</v>
+        <v>305.5</v>
       </c>
       <c r="F113" s="27" t="n">
-        <v>303.53</v>
+        <v>307.27</v>
       </c>
       <c r="G113" s="27" t="n">
-        <v>306.07</v>
+        <v>310.53</v>
       </c>
       <c r="H113" s="28" t="n">
-        <v>301.27</v>
+        <v>303.73</v>
       </c>
       <c r="I113" s="29" t="n">
-        <v>298.73</v>
+        <v>300.47</v>
       </c>
       <c r="J113" s="29" t="n">
-        <v>296.47</v>
+        <v>296.93</v>
       </c>
       <c r="K113" s="30" t="n">
-        <v>300.06</v>
+        <v>301.7</v>
       </c>
       <c r="L113" s="31" t="n">
-        <v>296.03</v>
+        <v>296</v>
       </c>
       <c r="M113" s="31" t="n">
-        <v>291.23</v>
+        <v>289.2</v>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
@@ -7652,16 +7652,16 @@
         </is>
       </c>
       <c r="O113" s="32" t="n">
-        <v>300.85</v>
+        <v>302.98</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>300.43</v>
+        <v>302.23</v>
       </c>
       <c r="Q113" s="33" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="R113" s="34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -7676,54 +7676,54 @@
         </is>
       </c>
       <c r="C114" s="25" t="n">
-        <v>207.77</v>
+        <v>209.94</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>206.37</v>
+        <v>207.44</v>
       </c>
       <c r="E114" s="26" t="n">
-        <v>205.19</v>
+        <v>205.35</v>
       </c>
       <c r="F114" s="27" t="n">
-        <v>205.7</v>
+        <v>205.07</v>
       </c>
       <c r="G114" s="27" t="n">
-        <v>206.3</v>
+        <v>206.73</v>
       </c>
       <c r="H114" s="28" t="n">
-        <v>204.9</v>
+        <v>204.23</v>
       </c>
       <c r="I114" s="29" t="n">
-        <v>204.3</v>
+        <v>202.57</v>
       </c>
       <c r="J114" s="29" t="n">
-        <v>203.5</v>
+        <v>201.73</v>
       </c>
       <c r="K114" s="30" t="n">
-        <v>204.41</v>
+        <v>203.95</v>
       </c>
       <c r="L114" s="31" t="n">
-        <v>203.23</v>
+        <v>201.85</v>
       </c>
       <c r="M114" s="31" t="n">
-        <v>201.83</v>
-      </c>
-      <c r="N114" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>199.35</v>
+      </c>
+      <c r="N114" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>204.71</v>
+        <v>204.19</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>204.52</v>
+        <v>204.14</v>
       </c>
       <c r="Q114" s="33" t="n">
-        <v>205.1</v>
-      </c>
-      <c r="R114" s="34" t="n">
-        <v>0.34</v>
+        <v>203.4</v>
+      </c>
+      <c r="R114" s="36" t="n">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="115">
@@ -7738,37 +7738,37 @@
         </is>
       </c>
       <c r="C115" s="25" t="n">
-        <v>633.6799999999999</v>
+        <v>635.87</v>
       </c>
       <c r="D115" s="25" t="n">
-        <v>623.6799999999999</v>
+        <v>626.37</v>
       </c>
       <c r="E115" s="26" t="n">
-        <v>615.3</v>
+        <v>618.41</v>
       </c>
       <c r="F115" s="27" t="n">
-        <v>616.5</v>
+        <v>621.33</v>
       </c>
       <c r="G115" s="27" t="n">
-        <v>622</v>
+        <v>625.67</v>
       </c>
       <c r="H115" s="28" t="n">
-        <v>612</v>
+        <v>616.17</v>
       </c>
       <c r="I115" s="29" t="n">
-        <v>606.5</v>
+        <v>611.83</v>
       </c>
       <c r="J115" s="29" t="n">
-        <v>602</v>
+        <v>606.67</v>
       </c>
       <c r="K115" s="30" t="n">
-        <v>609.7</v>
+        <v>613.09</v>
       </c>
       <c r="L115" s="31" t="n">
-        <v>601.3200000000001</v>
+        <v>605.13</v>
       </c>
       <c r="M115" s="31" t="n">
-        <v>591.3200000000001</v>
+        <v>595.63</v>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
@@ -7776,16 +7776,16 @@
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>611.24</v>
+        <v>615</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>610.48</v>
+        <v>613.83</v>
       </c>
       <c r="Q115" s="33" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="R115" s="34" t="n">
-        <v>0.58</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="116">
@@ -7800,54 +7800,54 @@
         </is>
       </c>
       <c r="C116" s="25" t="n">
-        <v>6.97</v>
+        <v>6.77</v>
       </c>
       <c r="D116" s="25" t="n">
-        <v>6.82</v>
+        <v>6.7</v>
       </c>
       <c r="E116" s="26" t="n">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
       <c r="F116" s="27" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="G116" s="27" t="n">
         <v>6.69</v>
       </c>
-      <c r="G116" s="27" t="n">
-        <v>6.79</v>
-      </c>
       <c r="H116" s="28" t="n">
-        <v>6.64</v>
+        <v>6.62</v>
       </c>
       <c r="I116" s="29" t="n">
-        <v>6.54</v>
+        <v>6.59</v>
       </c>
       <c r="J116" s="29" t="n">
-        <v>6.49</v>
+        <v>6.55</v>
       </c>
       <c r="K116" s="30" t="n">
         <v>6.61</v>
       </c>
       <c r="L116" s="31" t="n">
-        <v>6.49</v>
+        <v>6.55</v>
       </c>
       <c r="M116" s="31" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="N116" s="36" t="inlineStr">
+        <v>6.48</v>
+      </c>
+      <c r="N116" s="35" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O116" s="32" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="P116" s="32" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="Q116" s="33" t="n">
         <v>6.62</v>
       </c>
-      <c r="Q116" s="33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="R116" s="35" t="n">
-        <v>-0.9</v>
+      <c r="R116" s="34" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="117">
@@ -7862,54 +7862,54 @@
         </is>
       </c>
       <c r="C117" s="25" t="n">
-        <v>142.19</v>
+        <v>144.53</v>
       </c>
       <c r="D117" s="25" t="n">
-        <v>140.59</v>
+        <v>141.73</v>
       </c>
       <c r="E117" s="26" t="n">
-        <v>139.25</v>
+        <v>139.38</v>
       </c>
       <c r="F117" s="27" t="n">
-        <v>139.87</v>
+        <v>139.73</v>
       </c>
       <c r="G117" s="27" t="n">
-        <v>140.53</v>
+        <v>141.27</v>
       </c>
       <c r="H117" s="28" t="n">
-        <v>138.93</v>
+        <v>138.47</v>
       </c>
       <c r="I117" s="29" t="n">
-        <v>138.27</v>
+        <v>136.93</v>
       </c>
       <c r="J117" s="29" t="n">
-        <v>137.33</v>
+        <v>135.67</v>
       </c>
       <c r="K117" s="30" t="n">
-        <v>138.35</v>
+        <v>137.82</v>
       </c>
       <c r="L117" s="31" t="n">
-        <v>137.01</v>
+        <v>135.47</v>
       </c>
       <c r="M117" s="31" t="n">
-        <v>135.41</v>
-      </c>
-      <c r="N117" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>132.67</v>
+      </c>
+      <c r="N117" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O117" s="32" t="n">
-        <v>138.71</v>
+        <v>138.25</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>138.48</v>
+        <v>138.03</v>
       </c>
       <c r="Q117" s="33" t="n">
-        <v>139.2</v>
-      </c>
-      <c r="R117" s="34" t="n">
-        <v>0.9399999999999999</v>
+        <v>138.2</v>
+      </c>
+      <c r="R117" s="36" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="118">
@@ -7924,54 +7924,54 @@
         </is>
       </c>
       <c r="C118" s="25" t="n">
-        <v>10.65</v>
+        <v>10.48</v>
       </c>
       <c r="D118" s="25" t="n">
-        <v>10.46</v>
+        <v>10.34</v>
       </c>
       <c r="E118" s="26" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="F118" s="27" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="G118" s="27" t="n">
         <v>10.3</v>
       </c>
-      <c r="F118" s="27" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="G118" s="27" t="n">
-        <v>10.41</v>
-      </c>
       <c r="H118" s="28" t="n">
-        <v>10.22</v>
+        <v>10.16</v>
       </c>
       <c r="I118" s="29" t="n">
-        <v>10.11</v>
+        <v>10.07</v>
       </c>
       <c r="J118" s="29" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
       <c r="K118" s="30" t="n">
-        <v>10.19</v>
+        <v>10.14</v>
       </c>
       <c r="L118" s="31" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
       <c r="M118" s="31" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="N118" s="36" t="inlineStr">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="N118" s="35" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>10.21</v>
+        <v>10.16</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>10.21</v>
+        <v>10.15</v>
       </c>
       <c r="Q118" s="33" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="R118" s="35" t="n">
-        <v>-0.68</v>
+        <v>10.12</v>
+      </c>
+      <c r="R118" s="36" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="119">
@@ -7986,54 +7986,54 @@
         </is>
       </c>
       <c r="C119" s="25" t="n">
-        <v>18.73</v>
+        <v>17.94</v>
       </c>
       <c r="D119" s="25" t="n">
-        <v>18.03</v>
+        <v>17.57</v>
       </c>
       <c r="E119" s="26" t="n">
-        <v>17.45</v>
+        <v>17.26</v>
       </c>
       <c r="F119" s="27" t="n">
-        <v>17.39</v>
+        <v>17.35</v>
       </c>
       <c r="G119" s="27" t="n">
-        <v>17.85</v>
+        <v>17.53</v>
       </c>
       <c r="H119" s="28" t="n">
-        <v>17.15</v>
+        <v>17.16</v>
       </c>
       <c r="I119" s="29" t="n">
-        <v>16.69</v>
+        <v>16.98</v>
       </c>
       <c r="J119" s="29" t="n">
-        <v>16.45</v>
+        <v>16.79</v>
       </c>
       <c r="K119" s="30" t="n">
         <v>17.05</v>
       </c>
       <c r="L119" s="31" t="n">
-        <v>16.47</v>
+        <v>16.74</v>
       </c>
       <c r="M119" s="31" t="n">
-        <v>15.77</v>
-      </c>
-      <c r="N119" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>16.37</v>
+      </c>
+      <c r="N119" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O119" s="32" t="n">
-        <v>17.13</v>
+        <v>17.12</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>17.11</v>
+        <v>17.08</v>
       </c>
       <c r="Q119" s="33" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="R119" s="35" t="n">
-        <v>-0.06</v>
+        <v>17.17</v>
+      </c>
+      <c r="R119" s="34" t="n">
+        <v>1.36</v>
       </c>
     </row>
     <row r="120">
@@ -8048,54 +8048,54 @@
         </is>
       </c>
       <c r="C120" s="25" t="n">
-        <v>11.54</v>
+        <v>11.29</v>
       </c>
       <c r="D120" s="25" t="n">
-        <v>11.3</v>
+        <v>11.14</v>
       </c>
       <c r="E120" s="26" t="n">
-        <v>11.1</v>
+        <v>11.02</v>
       </c>
       <c r="F120" s="27" t="n">
-        <v>11.09</v>
+        <v>11.05</v>
       </c>
       <c r="G120" s="27" t="n">
-        <v>11.24</v>
+        <v>11.12</v>
       </c>
       <c r="H120" s="28" t="n">
-        <v>11</v>
+        <v>10.97</v>
       </c>
       <c r="I120" s="29" t="n">
-        <v>10.85</v>
+        <v>10.9</v>
       </c>
       <c r="J120" s="29" t="n">
-        <v>10.76</v>
+        <v>10.82</v>
       </c>
       <c r="K120" s="30" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="L120" s="31" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="M120" s="31" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="N120" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O120" s="32" t="n">
         <v>10.96</v>
       </c>
-      <c r="L120" s="31" t="n">
-        <v>10.76</v>
-      </c>
-      <c r="M120" s="31" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="N120" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O120" s="32" t="n">
-        <v>10.99</v>
-      </c>
       <c r="P120" s="32" t="n">
-        <v>10.98</v>
+        <v>10.94</v>
       </c>
       <c r="Q120" s="33" t="n">
-        <v>10.94</v>
-      </c>
-      <c r="R120" s="35" t="n">
-        <v>-1.26</v>
+        <v>10.97</v>
+      </c>
+      <c r="R120" s="34" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="121">
@@ -8110,37 +8110,37 @@
         </is>
       </c>
       <c r="C121" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="D121" s="25" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E121" s="26" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="F121" s="27" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="G121" s="27" t="n">
         <v>12.72</v>
       </c>
-      <c r="D121" s="25" t="n">
-        <v>12.52</v>
-      </c>
-      <c r="E121" s="26" t="n">
-        <v>12.36</v>
-      </c>
-      <c r="F121" s="27" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="G121" s="27" t="n">
-        <v>12.52</v>
-      </c>
       <c r="H121" s="28" t="n">
-        <v>12.32</v>
+        <v>12.47</v>
       </c>
       <c r="I121" s="29" t="n">
-        <v>12.23</v>
+        <v>12.33</v>
       </c>
       <c r="J121" s="29" t="n">
-        <v>12.12</v>
+        <v>12.22</v>
       </c>
       <c r="K121" s="30" t="n">
-        <v>12.24</v>
+        <v>12.41</v>
       </c>
       <c r="L121" s="31" t="n">
-        <v>12.08</v>
+        <v>12.2</v>
       </c>
       <c r="M121" s="31" t="n">
-        <v>11.88</v>
+        <v>11.95</v>
       </c>
       <c r="N121" s="20" t="inlineStr">
         <is>
@@ -8148,16 +8148,16 @@
         </is>
       </c>
       <c r="O121" s="32" t="n">
-        <v>12.29</v>
+        <v>12.45</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>12.26</v>
+        <v>12.42</v>
       </c>
       <c r="Q121" s="33" t="n">
-        <v>12.35</v>
+        <v>12.45</v>
       </c>
       <c r="R121" s="34" t="n">
-        <v>0.57</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -8172,54 +8172,54 @@
         </is>
       </c>
       <c r="C122" s="25" t="n">
-        <v>8.65</v>
+        <v>9.02</v>
       </c>
       <c r="D122" s="25" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="E122" s="26" t="n">
         <v>8.49</v>
       </c>
-      <c r="E122" s="26" t="n">
+      <c r="F122" s="27" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="G122" s="27" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="H122" s="28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I122" s="29" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J122" s="29" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="K122" s="30" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="L122" s="31" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="M122" s="31" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="N122" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O122" s="32" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="P122" s="32" t="n">
         <v>8.35</v>
       </c>
-      <c r="F122" s="27" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="G122" s="27" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="H122" s="28" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="I122" s="29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J122" s="29" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="K122" s="30" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="L122" s="31" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="M122" s="31" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="N122" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O122" s="32" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="P122" s="32" t="n">
-        <v>8.279999999999999</v>
-      </c>
       <c r="Q122" s="33" t="n">
-        <v>8.26</v>
+        <v>8.4</v>
       </c>
       <c r="R122" s="34" t="n">
-        <v>0.61</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="123">
@@ -8234,39 +8234,39 @@
         </is>
       </c>
       <c r="C123" s="25" t="n">
-        <v>8.289999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="D123" s="25" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="E123" s="26" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="F123" s="27" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="G123" s="27" t="n">
         <v>8.109999999999999</v>
-      </c>
-      <c r="E123" s="26" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="F123" s="27" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="G123" s="27" t="n">
-        <v>8.09</v>
       </c>
       <c r="H123" s="28" t="n">
         <v>7.91</v>
       </c>
       <c r="I123" s="29" t="n">
-        <v>7.83</v>
+        <v>7.79</v>
       </c>
       <c r="J123" s="29" t="n">
-        <v>7.73</v>
+        <v>7.71</v>
       </c>
       <c r="K123" s="30" t="n">
         <v>7.86</v>
       </c>
       <c r="L123" s="31" t="n">
-        <v>7.71</v>
+        <v>7.7</v>
       </c>
       <c r="M123" s="31" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="N123" s="36" t="inlineStr">
+        <v>7.5</v>
+      </c>
+      <c r="N123" s="35" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
@@ -8275,13 +8275,13 @@
         <v>7.89</v>
       </c>
       <c r="P123" s="32" t="n">
-        <v>7.87</v>
+        <v>7.88</v>
       </c>
       <c r="Q123" s="33" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="R123" s="34" t="n">
-        <v>0.25</v>
+        <v>7.88</v>
+      </c>
+      <c r="R123" s="36" t="n">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="124">
@@ -8296,37 +8296,37 @@
         </is>
       </c>
       <c r="C124" s="25" t="n">
-        <v>25.13</v>
+        <v>30.8</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>24.74</v>
+        <v>28.28</v>
       </c>
       <c r="E124" s="26" t="n">
-        <v>24.41</v>
+        <v>26.17</v>
       </c>
       <c r="F124" s="27" t="n">
-        <v>24.5</v>
+        <v>27.56</v>
       </c>
       <c r="G124" s="27" t="n">
-        <v>24.69</v>
+        <v>28.4</v>
       </c>
       <c r="H124" s="28" t="n">
-        <v>24.3</v>
+        <v>25.88</v>
       </c>
       <c r="I124" s="29" t="n">
-        <v>24.11</v>
+        <v>25.04</v>
       </c>
       <c r="J124" s="29" t="n">
-        <v>23.91</v>
+        <v>23.36</v>
       </c>
       <c r="K124" s="30" t="n">
-        <v>24.2</v>
+        <v>24.75</v>
       </c>
       <c r="L124" s="31" t="n">
-        <v>23.87</v>
+        <v>22.64</v>
       </c>
       <c r="M124" s="31" t="n">
-        <v>23.48</v>
+        <v>20.12</v>
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
@@ -8334,16 +8334,16 @@
         </is>
       </c>
       <c r="O124" s="32" t="n">
-        <v>24.26</v>
+        <v>25.42</v>
       </c>
       <c r="P124" s="32" t="n">
-        <v>24.23</v>
+        <v>24.95</v>
       </c>
       <c r="Q124" s="33" t="n">
-        <v>24.3</v>
+        <v>26.72</v>
       </c>
       <c r="R124" s="34" t="n">
-        <v>0.37</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -8358,37 +8358,37 @@
         </is>
       </c>
       <c r="C125" s="25" t="n">
-        <v>167.81</v>
+        <v>170.29</v>
       </c>
       <c r="D125" s="25" t="n">
-        <v>166.01</v>
+        <v>167.39</v>
       </c>
       <c r="E125" s="26" t="n">
-        <v>164.5</v>
+        <v>164.96</v>
       </c>
       <c r="F125" s="27" t="n">
-        <v>164.5</v>
+        <v>165.97</v>
       </c>
       <c r="G125" s="27" t="n">
-        <v>165.6</v>
+        <v>167.23</v>
       </c>
       <c r="H125" s="28" t="n">
-        <v>163.8</v>
+        <v>164.33</v>
       </c>
       <c r="I125" s="29" t="n">
-        <v>162.7</v>
+        <v>163.07</v>
       </c>
       <c r="J125" s="29" t="n">
-        <v>162</v>
+        <v>161.43</v>
       </c>
       <c r="K125" s="30" t="n">
-        <v>163.5</v>
+        <v>163.34</v>
       </c>
       <c r="L125" s="31" t="n">
-        <v>161.99</v>
+        <v>160.91</v>
       </c>
       <c r="M125" s="31" t="n">
-        <v>160.19</v>
+        <v>158.01</v>
       </c>
       <c r="N125" s="20" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         </is>
       </c>
       <c r="O125" s="32" t="n">
-        <v>163.72</v>
+        <v>163.95</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>163.64</v>
+        <v>163.56</v>
       </c>
       <c r="Q125" s="33" t="n">
-        <v>163.4</v>
-      </c>
-      <c r="R125" s="35" t="n">
-        <v>-0.06</v>
+        <v>164.7</v>
+      </c>
+      <c r="R125" s="34" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="126">
@@ -8420,37 +8420,37 @@
         </is>
       </c>
       <c r="C126" s="25" t="n">
-        <v>56.24</v>
+        <v>55.23</v>
       </c>
       <c r="D126" s="25" t="n">
-        <v>54.64</v>
+        <v>54.38</v>
       </c>
       <c r="E126" s="26" t="n">
-        <v>53.3</v>
+        <v>53.66</v>
       </c>
       <c r="F126" s="27" t="n">
-        <v>54.08</v>
+        <v>53.87</v>
       </c>
       <c r="G126" s="27" t="n">
-        <v>54.67</v>
+        <v>54.28</v>
       </c>
       <c r="H126" s="28" t="n">
-        <v>53.07</v>
+        <v>53.43</v>
       </c>
       <c r="I126" s="29" t="n">
-        <v>52.48</v>
+        <v>53.02</v>
       </c>
       <c r="J126" s="29" t="n">
-        <v>51.47</v>
+        <v>52.58</v>
       </c>
       <c r="K126" s="30" t="n">
-        <v>52.4</v>
+        <v>53.19</v>
       </c>
       <c r="L126" s="31" t="n">
-        <v>51.06</v>
+        <v>52.47</v>
       </c>
       <c r="M126" s="31" t="n">
-        <v>49.46</v>
+        <v>51.62</v>
       </c>
       <c r="N126" s="20" t="inlineStr">
         <is>
@@ -8458,16 +8458,16 @@
         </is>
       </c>
       <c r="O126" s="32" t="n">
-        <v>52.8</v>
+        <v>53.34</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>52.53</v>
+        <v>53.25</v>
       </c>
       <c r="Q126" s="33" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="R126" s="34" t="n">
-        <v>2.59</v>
+        <v>53.45</v>
+      </c>
+      <c r="R126" s="36" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="127">
@@ -8482,54 +8482,54 @@
         </is>
       </c>
       <c r="C127" s="25" t="n">
-        <v>16.03</v>
+        <v>15.45</v>
       </c>
       <c r="D127" s="25" t="n">
-        <v>15.37</v>
+        <v>15.03</v>
       </c>
       <c r="E127" s="26" t="n">
-        <v>14.81</v>
+        <v>14.68</v>
       </c>
       <c r="F127" s="27" t="n">
-        <v>14.81</v>
+        <v>14.79</v>
       </c>
       <c r="G127" s="27" t="n">
-        <v>15.22</v>
+        <v>14.99</v>
       </c>
       <c r="H127" s="28" t="n">
-        <v>14.56</v>
+        <v>14.57</v>
       </c>
       <c r="I127" s="29" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="J127" s="29" t="n">
         <v>14.15</v>
       </c>
-      <c r="J127" s="29" t="n">
-        <v>13.9</v>
-      </c>
       <c r="K127" s="30" t="n">
-        <v>14.45</v>
+        <v>14.44</v>
       </c>
       <c r="L127" s="31" t="n">
-        <v>13.89</v>
+        <v>14.09</v>
       </c>
       <c r="M127" s="31" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="N127" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>13.67</v>
+      </c>
+      <c r="N127" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O127" s="32" t="n">
-        <v>14.53</v>
+        <v>14.52</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>14.5</v>
+        <v>14.48</v>
       </c>
       <c r="Q127" s="33" t="n">
-        <v>14.41</v>
-      </c>
-      <c r="R127" s="35" t="n">
-        <v>-2.11</v>
+        <v>14.59</v>
+      </c>
+      <c r="R127" s="34" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="128">
@@ -8544,54 +8544,54 @@
         </is>
       </c>
       <c r="C128" s="25" t="n">
-        <v>15.57</v>
+        <v>15.39</v>
       </c>
       <c r="D128" s="25" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="E128" s="26" t="n">
-        <v>14.71</v>
+        <v>14.67</v>
       </c>
       <c r="F128" s="27" t="n">
-        <v>14.71</v>
+        <v>14.84</v>
       </c>
       <c r="G128" s="27" t="n">
-        <v>14.99</v>
+        <v>15</v>
       </c>
       <c r="H128" s="28" t="n">
-        <v>14.52</v>
+        <v>14.61</v>
       </c>
       <c r="I128" s="29" t="n">
-        <v>14.24</v>
+        <v>14.45</v>
       </c>
       <c r="J128" s="29" t="n">
-        <v>14.05</v>
+        <v>14.22</v>
       </c>
       <c r="K128" s="30" t="n">
-        <v>14.44</v>
+        <v>14.46</v>
       </c>
       <c r="L128" s="31" t="n">
-        <v>14.05</v>
+        <v>14.13</v>
       </c>
       <c r="M128" s="31" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="N128" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>13.74</v>
+      </c>
+      <c r="N128" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O128" s="32" t="n">
-        <v>14.5</v>
+        <v>14.55</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>14.48</v>
+        <v>14.49</v>
       </c>
       <c r="Q128" s="33" t="n">
-        <v>14.42</v>
-      </c>
-      <c r="R128" s="35" t="n">
-        <v>-1.9</v>
+        <v>14.69</v>
+      </c>
+      <c r="R128" s="34" t="n">
+        <v>1.87</v>
       </c>
     </row>
     <row r="129">
@@ -8606,54 +8606,54 @@
         </is>
       </c>
       <c r="C129" s="25" t="n">
-        <v>7.7</v>
+        <v>7.55</v>
       </c>
       <c r="D129" s="25" t="n">
-        <v>7.54</v>
+        <v>7.46</v>
       </c>
       <c r="E129" s="26" t="n">
-        <v>7.4</v>
+        <v>7.38</v>
       </c>
       <c r="F129" s="27" t="n">
-        <v>7.4</v>
+        <v>7.39</v>
       </c>
       <c r="G129" s="27" t="n">
-        <v>7.5</v>
+        <v>7.44</v>
       </c>
       <c r="H129" s="28" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="I129" s="29" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J129" s="29" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="K129" s="30" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="L129" s="31" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="M129" s="31" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="N129" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O129" s="32" t="n">
         <v>7.34</v>
       </c>
-      <c r="I129" s="29" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="J129" s="29" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="K129" s="30" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="L129" s="31" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="M129" s="31" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="N129" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O129" s="32" t="n">
-        <v>7.33</v>
-      </c>
       <c r="P129" s="32" t="n">
-        <v>7.33</v>
+        <v>7.34</v>
       </c>
       <c r="Q129" s="33" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="R129" s="35" t="n">
-        <v>-1.08</v>
+        <v>7.34</v>
+      </c>
+      <c r="R129" s="34" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="130">
@@ -8668,54 +8668,54 @@
         </is>
       </c>
       <c r="C130" s="25" t="n">
-        <v>10.09</v>
+        <v>10.54</v>
       </c>
       <c r="D130" s="25" t="n">
-        <v>9.91</v>
+        <v>10.22</v>
       </c>
       <c r="E130" s="26" t="n">
-        <v>9.76</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F130" s="27" t="n">
-        <v>9.76</v>
+        <v>10.03</v>
       </c>
       <c r="G130" s="27" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="H130" s="28" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="H130" s="28" t="n">
-        <v>9.69</v>
-      </c>
       <c r="I130" s="29" t="n">
-        <v>9.58</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J130" s="29" t="n">
-        <v>9.51</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K130" s="30" t="n">
-        <v>9.66</v>
+        <v>9.77</v>
       </c>
       <c r="L130" s="31" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
       <c r="M130" s="31" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="N130" s="36" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>9.18</v>
+      </c>
+      <c r="N130" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O130" s="32" t="n">
-        <v>9.68</v>
+        <v>9.83</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>9.67</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q130" s="33" t="n">
-        <v>9.65</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="R130" s="34" t="n">
-        <v>0.42</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="131">
@@ -8730,54 +8730,54 @@
         </is>
       </c>
       <c r="C131" s="25" t="n">
-        <v>140.56</v>
+        <v>145.78</v>
       </c>
       <c r="D131" s="25" t="n">
-        <v>138.36</v>
+        <v>141.28</v>
       </c>
       <c r="E131" s="26" t="n">
-        <v>136.52</v>
+        <v>137.51</v>
       </c>
       <c r="F131" s="27" t="n">
-        <v>137.33</v>
+        <v>137.73</v>
       </c>
       <c r="G131" s="27" t="n">
-        <v>138.27</v>
+        <v>140.37</v>
       </c>
       <c r="H131" s="28" t="n">
-        <v>136.07</v>
+        <v>135.87</v>
       </c>
       <c r="I131" s="29" t="n">
-        <v>135.13</v>
+        <v>133.23</v>
       </c>
       <c r="J131" s="29" t="n">
-        <v>133.87</v>
+        <v>131.37</v>
       </c>
       <c r="K131" s="30" t="n">
-        <v>135.28</v>
+        <v>134.99</v>
       </c>
       <c r="L131" s="31" t="n">
-        <v>133.44</v>
+        <v>131.22</v>
       </c>
       <c r="M131" s="31" t="n">
-        <v>131.24</v>
-      </c>
-      <c r="N131" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>126.72</v>
+      </c>
+      <c r="N131" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O131" s="32" t="n">
-        <v>135.76</v>
+        <v>135.6</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>135.46</v>
+        <v>135.34</v>
       </c>
       <c r="Q131" s="33" t="n">
-        <v>136.4</v>
-      </c>
-      <c r="R131" s="34" t="n">
-        <v>0.96</v>
+        <v>135.1</v>
+      </c>
+      <c r="R131" s="36" t="n">
+        <v>-0.95</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -650,7 +650,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-08-25</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-08-26</t>
         </is>
       </c>
     </row>
@@ -758,37 +758,37 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="G3" s="15" t="n">
         <v>21.19</v>
       </c>
-      <c r="D3" s="13" t="n">
-        <v>21.01</v>
-      </c>
-      <c r="E3" s="14" t="n">
-        <v>20.86</v>
-      </c>
-      <c r="F3" s="15" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G3" s="15" t="n">
-        <v>21.02</v>
-      </c>
       <c r="H3" s="16" t="n">
-        <v>20.84</v>
+        <v>20.99</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>20.77</v>
+        <v>20.93</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>20.66</v>
+        <v>20.79</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>20.76</v>
+        <v>20.9</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>20.61</v>
+        <v>20.74</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>20.43</v>
+        <v>20.54</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>20.81</v>
+        <v>20.96</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>20.77</v>
+        <v>20.92</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>20.89</v>
+        <v>21.06</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>1.31</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -820,54 +820,54 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>12.49</v>
+        <v>12.72</v>
       </c>
       <c r="D4" s="13" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="P4" s="21" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="Q4" s="22" t="n">
         <v>12.36</v>
       </c>
-      <c r="E4" s="14" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>12.36</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>12.23</v>
-      </c>
-      <c r="I4" s="17" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="J4" s="17" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="K4" s="18" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="L4" s="19" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="M4" s="19" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>12.21</v>
-      </c>
-      <c r="P4" s="21" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="Q4" s="22" t="n">
-        <v>12.25</v>
-      </c>
       <c r="R4" s="23" t="n">
-        <v>1.24</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5">
@@ -882,54 +882,54 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>14.81</v>
+        <v>14.65</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>14.58</v>
+        <v>14.56</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>14.39</v>
+        <v>14.48</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>14.52</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>14.59</v>
+        <v>14.56</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>14.36</v>
+        <v>14.47</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>14.29</v>
+        <v>14.43</v>
       </c>
       <c r="J5" s="17" t="n">
-        <v>14.13</v>
+        <v>14.38</v>
       </c>
       <c r="K5" s="18" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="L5" s="19" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="M5" s="19" t="n">
         <v>14.26</v>
       </c>
-      <c r="L5" s="19" t="n">
-        <v>14.07</v>
-      </c>
-      <c r="M5" s="19" t="n">
-        <v>13.84</v>
-      </c>
       <c r="N5" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O5" s="21" t="n">
-        <v>14.32</v>
+        <v>14.45</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>14.28</v>
+        <v>14.44</v>
       </c>
       <c r="Q5" s="22" t="n">
-        <v>14.44</v>
+        <v>14.49</v>
       </c>
       <c r="R5" s="23" t="n">
-        <v>2.41</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="6">
@@ -944,37 +944,37 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>23.08</v>
+        <v>23.39</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>22.41</v>
+        <v>22.72</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>21.85</v>
+        <v>22.16</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>22.12</v>
+        <v>22.31</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>22.4</v>
+        <v>22.65</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>21.73</v>
+        <v>21.98</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>21.45</v>
+        <v>21.64</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>21.06</v>
+        <v>21.31</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>21.48</v>
+        <v>21.79</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>20.92</v>
+        <v>21.23</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>20.25</v>
+        <v>20.56</v>
       </c>
       <c r="N6" s="20" t="inlineStr">
         <is>
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="O6" s="21" t="n">
-        <v>21.63</v>
+        <v>21.91</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>21.53</v>
+        <v>21.84</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>21.85</v>
+        <v>21.98</v>
       </c>
       <c r="R6" s="23" t="n">
-        <v>4.55</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="7">
@@ -1006,37 +1006,37 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>35.03</v>
+        <v>35.39</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>34.65</v>
+        <v>34.95</v>
       </c>
       <c r="E7" s="14" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="K7" s="18" t="n">
         <v>34.34</v>
       </c>
-      <c r="F7" s="15" t="n">
-        <v>34.43</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>34.61</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>34.23</v>
-      </c>
-      <c r="I7" s="17" t="n">
-        <v>34.05</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>33.85</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>34.12</v>
-      </c>
       <c r="L7" s="19" t="n">
-        <v>33.81</v>
+        <v>33.97</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>33.43</v>
+        <v>33.53</v>
       </c>
       <c r="N7" s="20" t="inlineStr">
         <is>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="O7" s="21" t="n">
-        <v>34.19</v>
+        <v>34.41</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>34.15</v>
+        <v>34.37</v>
       </c>
       <c r="Q7" s="22" t="n">
-        <v>34.24</v>
+        <v>34.4</v>
       </c>
       <c r="R7" s="23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="8">
@@ -1068,54 +1068,54 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>23.84</v>
+        <v>23.99</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>23.3</v>
+        <v>23.42</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>22.85</v>
+        <v>22.94</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>23.04</v>
+        <v>22.88</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>23.27</v>
+        <v>23.26</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>22.73</v>
+        <v>22.69</v>
       </c>
       <c r="I8" s="17" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="L8" s="19" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="M8" s="19" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="N8" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O8" s="21" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="P8" s="21" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="Q8" s="22" t="n">
         <v>22.5</v>
       </c>
-      <c r="J8" s="17" t="n">
-        <v>22.19</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>22.55</v>
-      </c>
-      <c r="L8" s="19" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="M8" s="19" t="n">
-        <v>21.56</v>
-      </c>
-      <c r="N8" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O8" s="21" t="n">
-        <v>22.66</v>
-      </c>
-      <c r="P8" s="21" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="Q8" s="22" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R8" s="23" t="n">
-        <v>2.47</v>
+      <c r="R8" s="25" t="n">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="9">
@@ -1130,37 +1130,37 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>134.82</v>
+        <v>149.5</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>132.52</v>
+        <v>141.9</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>130.59</v>
+        <v>135.53</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>131.13</v>
+        <v>138.27</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>132.27</v>
+        <v>141.53</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>129.97</v>
+        <v>133.93</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>128.83</v>
+        <v>130.67</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>127.67</v>
+        <v>126.33</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>129.31</v>
+        <v>131.27</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>127.38</v>
+        <v>124.9</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>125.08</v>
+        <v>117.3</v>
       </c>
       <c r="N9" s="20" t="inlineStr">
         <is>
@@ -1168,16 +1168,16 @@
         </is>
       </c>
       <c r="O9" s="21" t="n">
-        <v>129.73</v>
+        <v>132.9</v>
       </c>
       <c r="P9" s="21" t="n">
-        <v>129.49</v>
+        <v>131.86</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="R9" s="23" t="n">
-        <v>4.84</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="10">
@@ -1192,37 +1192,37 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>71.94</v>
+        <v>71.09</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>70.09</v>
+        <v>70.14</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>68.54000000000001</v>
+        <v>69.34</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>69.56999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>70.18000000000001</v>
+        <v>70</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>68.33</v>
+        <v>69.05</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>67.72</v>
+        <v>68.55</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>66.48</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>67.51000000000001</v>
+        <v>68.81</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>65.95999999999999</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>64.11</v>
+        <v>67.06</v>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
@@ -1230,16 +1230,16 @@
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>67.98999999999999</v>
+        <v>68.97</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>67.65000000000001</v>
+        <v>68.88</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>68.95</v>
+        <v>69</v>
       </c>
       <c r="R10" s="23" t="n">
-        <v>4.23</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1254,37 +1254,37 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>26.77</v>
+        <v>27.32</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>26.39</v>
+        <v>26.8</v>
       </c>
       <c r="E11" s="14" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="I11" s="17" t="n">
         <v>26.08</v>
       </c>
-      <c r="F11" s="15" t="n">
-        <v>26.22</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>26.38</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>25.84</v>
-      </c>
       <c r="J11" s="17" t="n">
-        <v>25.62</v>
+        <v>25.76</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>25.86</v>
+        <v>26.07</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>25.55</v>
+        <v>25.64</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>25.17</v>
+        <v>25.12</v>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
@@ -1292,16 +1292,16 @@
         </is>
       </c>
       <c r="O11" s="21" t="n">
-        <v>25.95</v>
+        <v>26.2</v>
       </c>
       <c r="P11" s="21" t="n">
-        <v>25.89</v>
+        <v>26.11</v>
       </c>
       <c r="Q11" s="22" t="n">
-        <v>26.06</v>
+        <v>26.4</v>
       </c>
       <c r="R11" s="23" t="n">
-        <v>2.44</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="12">
@@ -1316,37 +1316,37 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>26.11</v>
+        <v>27.04</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>25.73</v>
+        <v>26.4</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>25.42</v>
+        <v>25.86</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>25.57</v>
+        <v>26.15</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>25.73</v>
+        <v>26.39</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>25.35</v>
+        <v>25.75</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>25.19</v>
+        <v>25.51</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>24.97</v>
+        <v>25.11</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>24.89</v>
+        <v>24.96</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>24.51</v>
+        <v>24.32</v>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
@@ -1354,16 +1354,16 @@
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>25.29</v>
+        <v>25.65</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>25.23</v>
+        <v>25.55</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>25.42</v>
+        <v>25.9</v>
       </c>
       <c r="R12" s="23" t="n">
-        <v>0.79</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="13">
@@ -1378,37 +1378,37 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>44.01</v>
+        <v>44.39</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>43.45</v>
+        <v>43.79</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>42.98</v>
+        <v>43.29</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>43.23</v>
+        <v>43.61</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>43.45</v>
+        <v>43.81</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>42.89</v>
+        <v>43.21</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>42.67</v>
+        <v>43.01</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>42.33</v>
+        <v>42.61</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>42.66</v>
+        <v>42.95</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>42.19</v>
+        <v>42.45</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>41.63</v>
+        <v>41.85</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="O13" s="21" t="n">
-        <v>42.8</v>
+        <v>43.11</v>
       </c>
       <c r="P13" s="21" t="n">
-        <v>42.71</v>
+        <v>43</v>
       </c>
       <c r="Q13" s="22" t="n">
-        <v>43.02</v>
+        <v>43.4</v>
       </c>
       <c r="R13" s="23" t="n">
-        <v>1.46</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="14">
@@ -1440,54 +1440,54 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>9.109999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>9.01</v>
+        <v>8.99</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>8.93</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>8.960000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>9.01</v>
+        <v>8.99</v>
       </c>
       <c r="H14" s="16" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L14" s="19" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="n">
         <v>8.91</v>
       </c>
-      <c r="I14" s="17" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="L14" s="19" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="N14" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O14" s="21" t="n">
-        <v>8.890000000000001</v>
-      </c>
       <c r="P14" s="21" t="n">
-        <v>8.880000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="Q14" s="22" t="n">
         <v>8.92</v>
       </c>
-      <c r="R14" s="25" t="n">
-        <v>-0.34</v>
+      <c r="R14" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>15.23</v>
+        <v>15.01</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>14.92</v>
+        <v>14.81</v>
       </c>
       <c r="E15" s="14" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="F15" s="15" t="n">
         <v>14.66</v>
       </c>
-      <c r="F15" s="15" t="n">
-        <v>14.67</v>
-      </c>
       <c r="G15" s="15" t="n">
-        <v>14.85</v>
+        <v>14.78</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>14.54</v>
+        <v>14.58</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>14.36</v>
+        <v>14.46</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>14.23</v>
+        <v>14.38</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>14.49</v>
+        <v>14.53</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>14.23</v>
+        <v>14.37</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>13.92</v>
+        <v>14.17</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="O15" s="21" t="n">
-        <v>14.53</v>
+        <v>14.56</v>
       </c>
       <c r="P15" s="21" t="n">
-        <v>14.51</v>
+        <v>14.55</v>
       </c>
       <c r="Q15" s="22" t="n">
-        <v>14.48</v>
+        <v>14.55</v>
       </c>
       <c r="R15" s="23" t="n">
-        <v>1.12</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="16">
@@ -1564,54 +1564,54 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>5.03</v>
+        <v>4.99</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>4.95</v>
+        <v>4.91</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>4.88</v>
+        <v>4.84</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>4.88</v>
+        <v>4.86</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4.93</v>
+        <v>4.9</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="I16" s="17" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K16" s="18" t="n">
         <v>4.8</v>
       </c>
-      <c r="J16" s="17" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>4.84</v>
-      </c>
       <c r="L16" s="19" t="n">
-        <v>4.77</v>
+        <v>4.73</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>4.65</v>
+      </c>
+      <c r="N16" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O16" s="21" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="P16" s="21" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="R16" s="23" t="n">
-        <v>0.62</v>
+        <v>4.82</v>
+      </c>
+      <c r="R16" s="25" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="17">
@@ -1626,54 +1626,54 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>19.42</v>
+        <v>19.66</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>19.12</v>
+        <v>19.28</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>18.86</v>
+        <v>18.97</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>18.87</v>
+        <v>19.1</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>19.05</v>
+        <v>19.26</v>
       </c>
       <c r="H17" s="16" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="K17" s="18" t="n">
         <v>18.75</v>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="J17" s="17" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>18.7</v>
       </c>
       <c r="L17" s="19" t="n">
         <v>18.44</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>18.14</v>
-      </c>
-      <c r="N17" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>18.06</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O17" s="21" t="n">
-        <v>18.73</v>
+        <v>18.83</v>
       </c>
       <c r="P17" s="21" t="n">
-        <v>18.72</v>
+        <v>18.78</v>
       </c>
       <c r="Q17" s="22" t="n">
-        <v>18.69</v>
-      </c>
-      <c r="R17" s="25" t="n">
-        <v>-1.53</v>
+        <v>18.93</v>
+      </c>
+      <c r="R17" s="23" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="18">
@@ -1688,54 +1688,54 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>25.95</v>
+        <v>25.97</v>
       </c>
       <c r="D18" s="13" t="n">
         <v>25.67</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>25.44</v>
+        <v>25.41</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>25.45</v>
+        <v>25.43</v>
       </c>
       <c r="G18" s="15" t="n">
         <v>25.61</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>25.33</v>
+        <v>25.31</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>25.17</v>
+        <v>25.13</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>25.05</v>
+        <v>25.01</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>25.28</v>
+        <v>25.25</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>25.05</v>
+        <v>24.99</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="N18" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>24.69</v>
+      </c>
+      <c r="N18" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O18" s="21" t="n">
-        <v>25.32</v>
+        <v>25.29</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>25.3</v>
+        <v>25.27</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>25.28</v>
-      </c>
-      <c r="R18" s="23" t="n">
-        <v>1.12</v>
+        <v>25.26</v>
+      </c>
+      <c r="R18" s="25" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="19">
@@ -1750,37 +1750,37 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>72.2</v>
+        <v>72.75</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>71.15000000000001</v>
+        <v>71.45</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>70.27</v>
+        <v>70.36</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>70.18000000000001</v>
+        <v>70.92</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>70.87</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>69.81999999999999</v>
+        <v>70.13</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>69.13</v>
+        <v>69.62</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>68.77</v>
+        <v>68.83</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>69.68000000000001</v>
+        <v>69.64</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>68.8</v>
+        <v>68.55</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>67.75</v>
+        <v>67.25</v>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
@@ -1788,16 +1788,16 @@
         </is>
       </c>
       <c r="O19" s="21" t="n">
-        <v>69.79000000000001</v>
+        <v>69.94</v>
       </c>
       <c r="P19" s="21" t="n">
-        <v>69.76000000000001</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="Q19" s="22" t="n">
-        <v>69.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="20">
@@ -1812,34 +1812,34 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>12.44</v>
+        <v>12.33</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>12.24</v>
+        <v>12.16</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>12.08</v>
+        <v>12.01</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>12.08</v>
+        <v>12.06</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>12.2</v>
+        <v>12.14</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>12</v>
+        <v>11.97</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="J20" s="17" t="n">
         <v>11.8</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>11.96</v>
+        <v>11.92</v>
       </c>
       <c r="L20" s="19" t="n">
-        <v>11.8</v>
+        <v>11.77</v>
       </c>
       <c r="M20" s="19" t="n">
         <v>11.6</v>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="O20" s="21" t="n">
-        <v>11.99</v>
+        <v>11.95</v>
       </c>
       <c r="P20" s="21" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="Q20" s="22" t="n">
         <v>11.98</v>
       </c>
-      <c r="Q20" s="22" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="R20" s="25" t="n">
-        <v>-1.73</v>
+      <c r="R20" s="23" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="21">
@@ -1874,54 +1874,54 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>20.28</v>
+        <v>20.45</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>19.8</v>
+        <v>19.86</v>
       </c>
       <c r="E21" s="14" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="F21" s="15" t="n">
         <v>19.39</v>
       </c>
-      <c r="F21" s="15" t="n">
-        <v>19.54</v>
-      </c>
       <c r="G21" s="15" t="n">
-        <v>19.76</v>
+        <v>19.74</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>19.28</v>
+        <v>19.15</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>19.06</v>
+        <v>18.8</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>18.8</v>
+        <v>18.56</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>19.13</v>
+        <v>19.04</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>18.72</v>
+        <v>18.55</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>18.24</v>
-      </c>
-      <c r="N21" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>17.96</v>
+      </c>
+      <c r="N21" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O21" s="21" t="n">
-        <v>19.22</v>
+        <v>19.12</v>
       </c>
       <c r="P21" s="21" t="n">
-        <v>19.16</v>
+        <v>19.09</v>
       </c>
       <c r="Q21" s="22" t="n">
-        <v>19.32</v>
-      </c>
-      <c r="R21" s="23" t="n">
-        <v>4.89</v>
+        <v>19.04</v>
+      </c>
+      <c r="R21" s="25" t="n">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="22">
@@ -1936,54 +1936,54 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>37.65</v>
+        <v>36.87</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>36.63</v>
+        <v>36.21</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>35.78</v>
+        <v>35.65</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>35.77</v>
+        <v>35.89</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>36.39</v>
+        <v>36.17</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>35.37</v>
+        <v>35.51</v>
       </c>
       <c r="I22" s="17" t="n">
-        <v>34.75</v>
+        <v>35.23</v>
       </c>
       <c r="J22" s="17" t="n">
-        <v>34.35</v>
+        <v>34.85</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>35.2</v>
+        <v>35.29</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>34.35</v>
+        <v>34.73</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="N22" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>34.07</v>
+      </c>
+      <c r="N22" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O22" s="21" t="n">
-        <v>35.33</v>
+        <v>35.43</v>
       </c>
       <c r="P22" s="21" t="n">
-        <v>35.28</v>
+        <v>35.34</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>35.14</v>
-      </c>
-      <c r="R22" s="25" t="n">
-        <v>-2.01</v>
+        <v>35.6</v>
+      </c>
+      <c r="R22" s="23" t="n">
+        <v>1.31</v>
       </c>
     </row>
     <row r="23">
@@ -1998,37 +1998,37 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>16.56</v>
+        <v>16.54</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>15.99</v>
+        <v>16.02</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>15.51</v>
+        <v>15.59</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>15.66</v>
+        <v>15.73</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>15.93</v>
+        <v>15.97</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>15.36</v>
+        <v>15.45</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>15.09</v>
+        <v>15.21</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>14.79</v>
+        <v>14.93</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>15.2</v>
+        <v>15.29</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>14.72</v>
+        <v>14.86</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>14.15</v>
+        <v>14.34</v>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         </is>
       </c>
       <c r="O23" s="21" t="n">
-        <v>15.3</v>
+        <v>15.39</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>15.24</v>
+        <v>15.33</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>15.38</v>
+        <v>15.48</v>
       </c>
       <c r="R23" s="23" t="n">
-        <v>1.65</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="24">
@@ -2060,37 +2060,37 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>40.67</v>
+        <v>39.34</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>39.39</v>
+        <v>38.5</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>38.32</v>
+        <v>37.8</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>38.2</v>
+        <v>38.07</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>39.04</v>
+        <v>38.45</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>37.76</v>
+        <v>37.61</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>36.92</v>
+        <v>37.23</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>36.48</v>
+        <v>36.77</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>37.6</v>
+        <v>37.32</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>36.53</v>
+        <v>36.62</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>35.25</v>
+        <v>35.78</v>
       </c>
       <c r="N24" s="24" t="inlineStr">
         <is>
@@ -2098,16 +2098,16 @@
         </is>
       </c>
       <c r="O24" s="21" t="n">
-        <v>37.73</v>
+        <v>37.5</v>
       </c>
       <c r="P24" s="21" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="Q24" s="22" t="n">
         <v>37.7</v>
       </c>
-      <c r="Q24" s="22" t="n">
-        <v>37.36</v>
-      </c>
-      <c r="R24" s="25" t="n">
-        <v>-3.01</v>
+      <c r="R24" s="23" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="25">
@@ -2122,37 +2122,37 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>53.53</v>
+        <v>57.41</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>51.35</v>
+        <v>54.22</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>49.52</v>
+        <v>51.55</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>50.09</v>
+        <v>52.95</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>51.13</v>
+        <v>54.19</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>48.95</v>
+        <v>51</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>47.91</v>
+        <v>49.76</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>46.77</v>
+        <v>47.81</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>48.3</v>
+        <v>49.76</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>46.47</v>
+        <v>47.09</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>44.29</v>
+        <v>43.9</v>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -2160,16 +2160,16 @@
         </is>
       </c>
       <c r="O25" s="21" t="n">
-        <v>48.71</v>
+        <v>50.51</v>
       </c>
       <c r="P25" s="21" t="n">
-        <v>48.47</v>
+        <v>50.01</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>49.04</v>
+        <v>51.7</v>
       </c>
       <c r="R25" s="23" t="n">
-        <v>3.9</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="26">
@@ -2184,54 +2184,54 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>199.78</v>
+        <v>199.39</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>195.28</v>
+        <v>194.39</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>191.51</v>
+        <v>190.2</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>192.33</v>
+        <v>191.1</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>194.67</v>
+        <v>193.7</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>190.17</v>
+        <v>188.7</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>187.83</v>
+        <v>186.1</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>185.67</v>
+        <v>183.7</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>188.99</v>
+        <v>187.4</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>185.22</v>
+        <v>183.21</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>180.72</v>
-      </c>
-      <c r="N26" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>178.21</v>
+      </c>
+      <c r="N26" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O26" s="21" t="n">
-        <v>189.75</v>
+        <v>188.25</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>189.34</v>
+        <v>187.79</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>190</v>
-      </c>
-      <c r="R26" s="23" t="n">
-        <v>1.12</v>
+        <v>188.5</v>
+      </c>
+      <c r="R26" s="25" t="n">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="27">
@@ -2246,37 +2246,37 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>91.58</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>90.23</v>
+        <v>90.3</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>89.09999999999999</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>89.05</v>
+        <v>89.3</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>89.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>88.55</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>87.7</v>
+        <v>87.2</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>87.2</v>
+        <v>86</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>88.34999999999999</v>
+        <v>87.36</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>87.22</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>85.87</v>
+        <v>83.5</v>
       </c>
       <c r="N27" s="24" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="O27" s="21" t="n">
-        <v>88.5</v>
+        <v>87.81</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>88.45</v>
+        <v>87.53</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="R27" s="25" t="n">
-        <v>-0.34</v>
+        <v>88.40000000000001</v>
+      </c>
+      <c r="R27" s="23" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="28">
@@ -2308,54 +2308,54 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>22.04</v>
+        <v>21.69</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>21.57</v>
+        <v>21.43</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>21.69</v>
+        <v>21.41</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>21.97</v>
+        <v>21.61</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>21.41</v>
+        <v>21.3</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>21.13</v>
+        <v>21.1</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>20.85</v>
+        <v>20.99</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>21.25</v>
+        <v>21.26</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>20.78</v>
+        <v>21</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="N28" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>20.69</v>
+      </c>
+      <c r="N28" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O28" s="21" t="n">
-        <v>21.35</v>
+        <v>21.29</v>
       </c>
       <c r="P28" s="21" t="n">
-        <v>21.3</v>
+        <v>21.28</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>21.41</v>
-      </c>
-      <c r="R28" s="23" t="n">
-        <v>0.9</v>
+        <v>21.21</v>
+      </c>
+      <c r="R28" s="25" t="n">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="29">
@@ -2370,54 +2370,54 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>84.06999999999999</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>82.67</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>81.48999999999999</v>
+        <v>81.67</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>81.5</v>
+        <v>82.47</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>82.34999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="H29" s="16" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>80.97</v>
+      </c>
+      <c r="J29" s="17" t="n">
+        <v>79.98</v>
+      </c>
+      <c r="K29" s="18" t="n">
+        <v>80.83</v>
+      </c>
+      <c r="L29" s="19" t="n">
+        <v>79.56999999999999</v>
+      </c>
+      <c r="M29" s="19" t="n">
+        <v>78.06999999999999</v>
+      </c>
+      <c r="N29" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O29" s="21" t="n">
+        <v>81.22</v>
+      </c>
+      <c r="P29" s="21" t="n">
         <v>80.95</v>
       </c>
-      <c r="I29" s="17" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="J29" s="17" t="n">
-        <v>79.55</v>
-      </c>
-      <c r="K29" s="18" t="n">
-        <v>80.70999999999999</v>
-      </c>
-      <c r="L29" s="19" t="n">
-        <v>79.53</v>
-      </c>
-      <c r="M29" s="19" t="n">
-        <v>78.13</v>
-      </c>
-      <c r="N29" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O29" s="21" t="n">
-        <v>80.88</v>
-      </c>
-      <c r="P29" s="21" t="n">
-        <v>80.81999999999999</v>
-      </c>
       <c r="Q29" s="22" t="n">
-        <v>80.65000000000001</v>
-      </c>
-      <c r="R29" s="25" t="n">
-        <v>-0.86</v>
+        <v>81.95</v>
+      </c>
+      <c r="R29" s="23" t="n">
+        <v>1.61</v>
       </c>
     </row>
     <row r="30">
@@ -2432,54 +2432,54 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>34.66</v>
+        <v>33.6</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>33.6</v>
+        <v>32.82</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>32.71</v>
+        <v>32.17</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>32.6</v>
+        <v>32.37</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>33.3</v>
+        <v>32.75</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>32.24</v>
+        <v>31.97</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>31.54</v>
+        <v>31.59</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>31.18</v>
+        <v>31.19</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>32.11</v>
+        <v>31.73</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>31.22</v>
+        <v>31.08</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>30.16</v>
-      </c>
-      <c r="N30" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>30.3</v>
+      </c>
+      <c r="N30" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O30" s="21" t="n">
-        <v>32.22</v>
+        <v>31.88</v>
       </c>
       <c r="P30" s="21" t="n">
-        <v>32.2</v>
+        <v>31.79</v>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="R30" s="23" t="n">
-        <v>1.59</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="31">
@@ -2494,54 +2494,54 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>52</v>
+        <v>51.07</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>51.35</v>
+        <v>50.72</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>50.81</v>
+        <v>50.42</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>50.73</v>
+        <v>50.52</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>51.17</v>
+        <v>50.68</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>50.52</v>
+        <v>50.33</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>50.08</v>
+        <v>50.17</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>49.87</v>
+        <v>49.98</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>50.44</v>
+        <v>50.23</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>49.9</v>
+        <v>49.93</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>49.25</v>
-      </c>
-      <c r="N31" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>49.58</v>
+      </c>
+      <c r="N31" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O31" s="21" t="n">
-        <v>50.51</v>
+        <v>50.29</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>50.49</v>
+        <v>50.25</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>50.3</v>
+        <v>50.35</v>
       </c>
       <c r="R31" s="23" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32">
@@ -2556,37 +2556,37 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>136.69</v>
+        <v>133.53</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>132.99</v>
+        <v>132.03</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>129.89</v>
+        <v>130.77</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>131.33</v>
+        <v>130.87</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>132.87</v>
+        <v>131.73</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>129.17</v>
+        <v>130.23</v>
       </c>
       <c r="I32" s="17" t="n">
-        <v>127.63</v>
+        <v>129.37</v>
       </c>
       <c r="J32" s="17" t="n">
-        <v>125.47</v>
+        <v>128.73</v>
       </c>
       <c r="K32" s="18" t="n">
-        <v>127.81</v>
+        <v>129.93</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>124.71</v>
+        <v>128.67</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>121.01</v>
+        <v>127.17</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
@@ -2594,16 +2594,16 @@
         </is>
       </c>
       <c r="O32" s="21" t="n">
-        <v>128.63</v>
+        <v>130.14</v>
       </c>
       <c r="P32" s="21" t="n">
-        <v>128.1</v>
+        <v>130.05</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>129.8</v>
+        <v>130</v>
       </c>
       <c r="R32" s="23" t="n">
-        <v>3.84</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="33">
@@ -2618,37 +2618,37 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>54.16</v>
+        <v>55.02</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>52.61</v>
+        <v>53.12</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>51.31</v>
+        <v>51.53</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>51.23</v>
+        <v>51.72</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>52.22</v>
+        <v>52.78</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>50.67</v>
+        <v>50.88</v>
       </c>
       <c r="I33" s="17" t="n">
-        <v>49.68</v>
+        <v>49.82</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>49.12</v>
+        <v>48.98</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>50.44</v>
+        <v>50.47</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>49.14</v>
+        <v>48.88</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>47.59</v>
+        <v>46.98</v>
       </c>
       <c r="N33" s="24" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         </is>
       </c>
       <c r="O33" s="21" t="n">
-        <v>50.61</v>
+        <v>50.75</v>
       </c>
       <c r="P33" s="21" t="n">
-        <v>50.56</v>
+        <v>50.62</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="R33" s="25" t="n">
-        <v>-2.9</v>
+        <v>50.65</v>
+      </c>
+      <c r="R33" s="23" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="34">
@@ -2680,54 +2680,54 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>26.53</v>
+        <v>26.41</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>26.25</v>
+        <v>26.17</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>26.02</v>
+        <v>25.97</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>26.09</v>
+        <v>25.97</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>26.23</v>
+        <v>26.11</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>25.95</v>
+        <v>25.87</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>25.81</v>
+        <v>25.73</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>25.67</v>
+        <v>25.63</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>25.86</v>
+        <v>25.83</v>
       </c>
       <c r="L34" s="19" t="n">
         <v>25.63</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="N34" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>25.39</v>
+      </c>
+      <c r="N34" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O34" s="21" t="n">
-        <v>25.92</v>
+        <v>25.86</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>25.88</v>
+        <v>25.85</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>25.96</v>
+        <v>25.82</v>
       </c>
       <c r="R34" s="25" t="n">
-        <v>-0.15</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="35">
@@ -2742,54 +2742,54 @@
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>26.86</v>
+        <v>26.79</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>26.5</v>
+        <v>26.45</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>26.2</v>
+        <v>26.17</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>26.21</v>
+        <v>26.31</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>26.43</v>
+        <v>26.45</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>26.07</v>
+        <v>26.11</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>25.85</v>
+        <v>25.97</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>25.71</v>
+        <v>25.77</v>
       </c>
       <c r="K35" s="18" t="n">
-        <v>26</v>
+        <v>25.97</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>25.7</v>
+        <v>25.69</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>25.34</v>
-      </c>
-      <c r="N35" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>25.35</v>
+      </c>
+      <c r="N35" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O35" s="21" t="n">
         <v>26.05</v>
       </c>
       <c r="P35" s="21" t="n">
-        <v>26.03</v>
+        <v>26</v>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="R35" s="25" t="n">
-        <v>-0.54</v>
+        <v>26.18</v>
+      </c>
+      <c r="R35" s="23" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -2804,37 +2804,37 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>10.01</v>
+        <v>10.35</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>9.82</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>9.66</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>9.640000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>9.76</v>
+        <v>9.83</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>9.57</v>
+        <v>9.43</v>
       </c>
       <c r="I36" s="17" t="n">
-        <v>9.449999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="J36" s="17" t="n">
-        <v>9.380000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K36" s="18" t="n">
-        <v>9.550000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>9.390000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="N36" s="24" t="inlineStr">
         <is>
@@ -2842,16 +2842,16 @@
         </is>
       </c>
       <c r="O36" s="21" t="n">
-        <v>9.57</v>
+        <v>9.43</v>
       </c>
       <c r="P36" s="21" t="n">
-        <v>9.57</v>
+        <v>9.42</v>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>9.51</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="R36" s="25" t="n">
-        <v>-2.06</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="37">
@@ -2866,37 +2866,37 @@
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>31.93</v>
+        <v>31.9</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>31.55</v>
+        <v>31.44</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>31.24</v>
+        <v>31.06</v>
       </c>
       <c r="F37" s="15" t="n">
         <v>31.23</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>31.47</v>
+        <v>31.43</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>31.09</v>
+        <v>30.97</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>30.85</v>
+        <v>30.77</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>30.71</v>
+        <v>30.51</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>31.02</v>
+        <v>30.8</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>30.71</v>
+        <v>30.42</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>30.33</v>
+        <v>29.96</v>
       </c>
       <c r="N37" s="24" t="inlineStr">
         <is>
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="O37" s="21" t="n">
-        <v>31.07</v>
+        <v>30.9</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>31.05</v>
+        <v>30.84</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>31</v>
-      </c>
-      <c r="R37" s="25" t="n">
-        <v>-0.77</v>
+        <v>31.04</v>
+      </c>
+      <c r="R37" s="23" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="38">
@@ -2928,37 +2928,37 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>207.59</v>
+        <v>203.56</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>201.29</v>
+        <v>200.06</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>196.01</v>
+        <v>197.13</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>199.5</v>
+        <v>198.33</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>201.6</v>
+        <v>199.87</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>195.3</v>
+        <v>196.37</v>
       </c>
       <c r="I38" s="17" t="n">
-        <v>193.2</v>
+        <v>194.83</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>189</v>
+        <v>192.87</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>192.49</v>
+        <v>195.17</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>187.21</v>
+        <v>192.24</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>180.91</v>
+        <v>188.74</v>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="O38" s="21" t="n">
-        <v>194.14</v>
+        <v>195.9</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>192.98</v>
+        <v>195.44</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>197.4</v>
-      </c>
-      <c r="R38" s="23" t="n">
-        <v>4.67</v>
+        <v>196.8</v>
+      </c>
+      <c r="R38" s="25" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="39">
@@ -2990,37 +2990,37 @@
         </is>
       </c>
       <c r="C39" s="13" t="n">
-        <v>14.06</v>
+        <v>14.12</v>
       </c>
       <c r="D39" s="13" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="G39" s="15" t="n">
         <v>13.89</v>
       </c>
-      <c r="E39" s="14" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>13.84</v>
-      </c>
       <c r="H39" s="16" t="n">
-        <v>13.67</v>
+        <v>13.69</v>
       </c>
       <c r="I39" s="17" t="n">
-        <v>13.55</v>
+        <v>13.59</v>
       </c>
       <c r="J39" s="17" t="n">
-        <v>13.5</v>
+        <v>13.49</v>
       </c>
       <c r="K39" s="18" t="n">
-        <v>13.65</v>
+        <v>13.64</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>13.5</v>
+        <v>13.48</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>13.33</v>
+        <v>13.28</v>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
@@ -3028,16 +3028,16 @@
         </is>
       </c>
       <c r="O39" s="21" t="n">
-        <v>13.66</v>
+        <v>13.68</v>
       </c>
       <c r="P39" s="21" t="n">
         <v>13.66</v>
       </c>
       <c r="Q39" s="22" t="n">
-        <v>13.61</v>
+        <v>13.68</v>
       </c>
       <c r="R39" s="23" t="n">
-        <v>1.42</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="40">
@@ -3052,54 +3052,54 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>22.6</v>
+        <v>21.77</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>22.05</v>
+        <v>21.52</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>21.59</v>
+        <v>21.32</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>21.6</v>
+        <v>21.31</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>21.93</v>
+        <v>21.47</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>21.38</v>
+        <v>21.22</v>
       </c>
       <c r="I40" s="17" t="n">
-        <v>21.05</v>
+        <v>21.06</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>20.83</v>
+        <v>20.97</v>
       </c>
       <c r="K40" s="18" t="n">
-        <v>21.28</v>
+        <v>21.18</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>20.82</v>
+        <v>20.97</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>20.27</v>
-      </c>
-      <c r="N40" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>20.72</v>
+      </c>
+      <c r="N40" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O40" s="21" t="n">
-        <v>21.35</v>
+        <v>21.21</v>
       </c>
       <c r="P40" s="21" t="n">
-        <v>21.32</v>
+        <v>21.19</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>21.27</v>
-      </c>
-      <c r="R40" s="23" t="n">
-        <v>1.48</v>
+        <v>21.16</v>
+      </c>
+      <c r="R40" s="25" t="n">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="41">
@@ -3114,54 +3114,54 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>200.36</v>
+        <v>189.74</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>191.36</v>
+        <v>184.34</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>183.82</v>
+        <v>179.81</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>184.4</v>
+        <v>179.47</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>189.6</v>
+        <v>182.93</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>180.6</v>
+        <v>177.53</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>175.4</v>
+        <v>174.07</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>171.6</v>
+        <v>172.13</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>178.78</v>
+        <v>176.79</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>171.24</v>
+        <v>172.26</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>162.24</v>
-      </c>
-      <c r="N41" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>166.86</v>
+      </c>
+      <c r="N41" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O41" s="21" t="n">
-        <v>180.04</v>
+        <v>177.37</v>
       </c>
       <c r="P41" s="21" t="n">
-        <v>179.48</v>
+        <v>177.21</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>179.2</v>
-      </c>
-      <c r="R41" s="23" t="n">
-        <v>0.11</v>
+        <v>176</v>
+      </c>
+      <c r="R41" s="25" t="n">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="42">
@@ -3176,37 +3176,37 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>40.25</v>
+        <v>40.84</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>39.65</v>
+        <v>40.06</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>39.15</v>
+        <v>39.41</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>39.36</v>
+        <v>39.81</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>39.62</v>
+        <v>40.09</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>39.02</v>
+        <v>39.31</v>
       </c>
       <c r="I42" s="17" t="n">
-        <v>38.76</v>
+        <v>39.03</v>
       </c>
       <c r="J42" s="17" t="n">
-        <v>38.42</v>
+        <v>38.53</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>38.81</v>
+        <v>38.97</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>38.31</v>
+        <v>38.32</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>37.71</v>
+        <v>37.54</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
@@ -3214,16 +3214,16 @@
         </is>
       </c>
       <c r="O42" s="21" t="n">
-        <v>38.94</v>
+        <v>39.17</v>
       </c>
       <c r="P42" s="21" t="n">
-        <v>38.86</v>
+        <v>39.03</v>
       </c>
       <c r="Q42" s="22" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R42" s="25" t="n">
-        <v>-0.51</v>
+        <v>39.54</v>
+      </c>
+      <c r="R42" s="23" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="43">
@@ -3238,54 +3238,54 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>28.9</v>
+        <v>29.15</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>28.44</v>
+        <v>28.49</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>28.06</v>
+        <v>27.93</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>28.17</v>
+        <v>27.94</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>28.39</v>
+        <v>28.34</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>27.93</v>
+        <v>27.68</v>
       </c>
       <c r="I43" s="17" t="n">
-        <v>27.71</v>
+        <v>27.28</v>
       </c>
       <c r="J43" s="17" t="n">
-        <v>27.47</v>
+        <v>27.02</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>27.8</v>
+        <v>27.57</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>27.42</v>
+        <v>27.01</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>26.96</v>
-      </c>
-      <c r="N43" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>26.35</v>
+      </c>
+      <c r="N43" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O43" s="21" t="n">
-        <v>27.89</v>
+        <v>27.65</v>
       </c>
       <c r="P43" s="21" t="n">
-        <v>27.84</v>
+        <v>27.62</v>
       </c>
       <c r="Q43" s="22" t="n">
-        <v>27.94</v>
-      </c>
-      <c r="R43" s="23" t="n">
-        <v>0.5</v>
+        <v>27.54</v>
+      </c>
+      <c r="R43" s="25" t="n">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="44">
@@ -3300,54 +3300,54 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>27.01</v>
+        <v>26.67</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>26.73</v>
+        <v>26.43</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>26.5</v>
+        <v>26.23</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>26.47</v>
+        <v>26.24</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>26.65</v>
+        <v>26.38</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>26.37</v>
+        <v>26.14</v>
       </c>
       <c r="I44" s="17" t="n">
-        <v>26.19</v>
+        <v>26</v>
       </c>
       <c r="J44" s="17" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="K44" s="18" t="n">
         <v>26.09</v>
       </c>
-      <c r="K44" s="18" t="n">
-        <v>26.34</v>
-      </c>
       <c r="L44" s="19" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="N44" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O44" s="21" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="P44" s="21" t="n">
         <v>26.11</v>
       </c>
-      <c r="M44" s="19" t="n">
-        <v>25.83</v>
-      </c>
-      <c r="N44" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O44" s="21" t="n">
-        <v>26.37</v>
-      </c>
-      <c r="P44" s="21" t="n">
-        <v>26.36</v>
-      </c>
       <c r="Q44" s="22" t="n">
-        <v>26.28</v>
+        <v>26.1</v>
       </c>
       <c r="R44" s="25" t="n">
-        <v>-0.45</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="45">
@@ -3362,54 +3362,54 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>8.1</v>
+        <v>8.02</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>7.99</v>
+        <v>7.94</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>7.9</v>
+        <v>7.87</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>7.97</v>
+        <v>7.94</v>
       </c>
       <c r="H45" s="16" t="n">
         <v>7.86</v>
       </c>
       <c r="I45" s="17" t="n">
-        <v>7.79</v>
+        <v>7.83</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>7.75</v>
+        <v>7.78</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>7.83</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>7.74</v>
+        <v>7.76</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="N45" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>7.68</v>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O45" s="21" t="n">
         <v>7.85</v>
       </c>
       <c r="P45" s="21" t="n">
-        <v>7.84</v>
+        <v>7.83</v>
       </c>
       <c r="Q45" s="22" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="R45" s="25" t="n">
-        <v>-1.88</v>
+        <v>7.88</v>
+      </c>
+      <c r="R45" s="23" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="46">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>12.89</v>
+        <v>13.01</v>
       </c>
       <c r="D46" s="13" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F46" s="15" t="n">
         <v>12.69</v>
       </c>
-      <c r="E46" s="14" t="n">
+      <c r="G46" s="15" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="H46" s="16" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="K46" s="18" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="L46" s="19" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="M46" s="19" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="N46" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O46" s="21" t="n">
         <v>12.53</v>
       </c>
-      <c r="F46" s="15" t="n">
+      <c r="P46" s="21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q46" s="22" t="n">
         <v>12.6</v>
       </c>
-      <c r="G46" s="15" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="H46" s="16" t="n">
-        <v>12.49</v>
-      </c>
-      <c r="I46" s="17" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J46" s="17" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="K46" s="18" t="n">
-        <v>12.41</v>
-      </c>
-      <c r="L46" s="19" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="M46" s="19" t="n">
-        <v>12.05</v>
-      </c>
-      <c r="N46" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O46" s="21" t="n">
-        <v>12.46</v>
-      </c>
-      <c r="P46" s="21" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="Q46" s="22" t="n">
-        <v>12.52</v>
-      </c>
       <c r="R46" s="23" t="n">
-        <v>1.95</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="47">
@@ -3486,37 +3486,37 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>210.29</v>
+        <v>208.09</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>207.39</v>
+        <v>206.49</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>204.96</v>
+        <v>205.15</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>205.97</v>
+        <v>205.7</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>207.23</v>
+        <v>206.4</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>204.33</v>
+        <v>204.8</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>203.07</v>
+        <v>204.1</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>201.43</v>
+        <v>203.2</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>203.34</v>
+        <v>204.25</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>200.91</v>
+        <v>202.91</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>198.01</v>
+        <v>201.31</v>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
@@ -3524,16 +3524,16 @@
         </is>
       </c>
       <c r="O47" s="21" t="n">
-        <v>203.95</v>
+        <v>204.59</v>
       </c>
       <c r="P47" s="21" t="n">
-        <v>203.56</v>
+        <v>204.38</v>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>204.7</v>
+        <v>205</v>
       </c>
       <c r="R47" s="23" t="n">
-        <v>2.35</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="48">
@@ -3548,54 +3548,54 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="F48" s="15" t="n">
         <v>49.61</v>
       </c>
-      <c r="D48" s="13" t="n">
-        <v>49.01</v>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>48.51</v>
-      </c>
-      <c r="F48" s="15" t="n">
-        <v>48.61</v>
-      </c>
       <c r="G48" s="15" t="n">
-        <v>48.93</v>
+        <v>50.13</v>
       </c>
       <c r="H48" s="16" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="I48" s="17" t="n">
         <v>48.33</v>
       </c>
-      <c r="I48" s="17" t="n">
-        <v>48.01</v>
-      </c>
       <c r="J48" s="17" t="n">
-        <v>47.73</v>
+        <v>47.57</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>48.17</v>
+        <v>48.38</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>47.67</v>
+        <v>47.31</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="N48" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>46.03</v>
+      </c>
+      <c r="N48" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O48" s="21" t="n">
-        <v>48.27</v>
+        <v>48.67</v>
       </c>
       <c r="P48" s="21" t="n">
-        <v>48.22</v>
+        <v>48.48</v>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>48.3</v>
+        <v>49.08</v>
       </c>
       <c r="R48" s="23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="49">
@@ -3610,54 +3610,54 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>36.41</v>
+        <v>34.56</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>35.45</v>
+        <v>34.2</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>34.65</v>
+        <v>33.9</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>34.59</v>
+        <v>33.9</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>35.21</v>
+        <v>34.12</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>34.25</v>
+        <v>33.76</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>33.63</v>
+        <v>33.54</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>33.29</v>
+        <v>33.4</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>34.11</v>
+        <v>33.7</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>33.31</v>
+        <v>33.4</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="N49" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>33.04</v>
+      </c>
+      <c r="N49" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O49" s="21" t="n">
-        <v>34.22</v>
+        <v>33.74</v>
       </c>
       <c r="P49" s="21" t="n">
-        <v>34.19</v>
+        <v>33.73</v>
       </c>
       <c r="Q49" s="22" t="n">
-        <v>33.98</v>
-      </c>
-      <c r="R49" s="23" t="n">
-        <v>1.31</v>
+        <v>33.68</v>
+      </c>
+      <c r="R49" s="25" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="50">
@@ -3672,37 +3672,37 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>14.14</v>
+        <v>13.84</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>13.84</v>
+        <v>13.63</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>13.58</v>
+        <v>13.45</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>13.55</v>
+        <v>13.56</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>13.75</v>
+        <v>13.64</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>13.45</v>
+        <v>13.43</v>
       </c>
       <c r="I50" s="17" t="n">
-        <v>13.25</v>
+        <v>13.35</v>
       </c>
       <c r="J50" s="17" t="n">
-        <v>13.15</v>
+        <v>13.22</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>13.42</v>
+        <v>13.34</v>
       </c>
       <c r="L50" s="19" t="n">
         <v>13.16</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>12.86</v>
+        <v>12.95</v>
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="O50" s="21" t="n">
-        <v>13.44</v>
+        <v>13.39</v>
       </c>
       <c r="P50" s="21" t="n">
-        <v>13.44</v>
+        <v>13.35</v>
       </c>
       <c r="Q50" s="22" t="n">
-        <v>13.35</v>
+        <v>13.49</v>
       </c>
       <c r="R50" s="23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="51">
@@ -3734,41 +3734,41 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>63.25</v>
+        <v>62.09</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>61.8</v>
+        <v>61.14</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>60.58</v>
+        <v>60.34</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>60.68</v>
+        <v>60.53</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>61.52</v>
+        <v>61.02</v>
       </c>
       <c r="H51" s="16" t="n">
         <v>60.07</v>
       </c>
       <c r="I51" s="17" t="n">
-        <v>59.23</v>
+        <v>59.58</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>58.62</v>
+        <v>59.12</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>59.77</v>
+        <v>59.81</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>58.55</v>
+        <v>59.01</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="N51" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>58.06</v>
+      </c>
+      <c r="N51" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O51" s="21" t="n">
@@ -3778,10 +3778,10 @@
         <v>59.88</v>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>59.85</v>
+        <v>60.05</v>
       </c>
       <c r="R51" s="23" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="52">
@@ -3796,37 +3796,37 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>25.49</v>
+        <v>25.86</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>25.25</v>
+        <v>25.32</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>25.05</v>
+        <v>24.87</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>25.02</v>
+        <v>24.91</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>25.18</v>
+        <v>25.22</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>24.94</v>
+        <v>24.68</v>
       </c>
       <c r="I52" s="17" t="n">
-        <v>24.78</v>
+        <v>24.37</v>
       </c>
       <c r="J52" s="17" t="n">
-        <v>24.7</v>
+        <v>24.14</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>24.91</v>
+        <v>24.57</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>24.71</v>
+        <v>24.12</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>24.47</v>
+        <v>23.58</v>
       </c>
       <c r="N52" s="24" t="inlineStr">
         <is>
@@ -3834,16 +3834,16 @@
         </is>
       </c>
       <c r="O52" s="21" t="n">
-        <v>24.94</v>
+        <v>24.65</v>
       </c>
       <c r="P52" s="21" t="n">
-        <v>24.93</v>
+        <v>24.61</v>
       </c>
       <c r="Q52" s="22" t="n">
-        <v>24.86</v>
+        <v>24.6</v>
       </c>
       <c r="R52" s="25" t="n">
-        <v>-0.64</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="53">
@@ -3858,25 +3858,25 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="D53" s="13" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="G53" s="15" t="n">
         <v>5.38</v>
       </c>
-      <c r="E53" s="14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F53" s="15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G53" s="15" t="n">
-        <v>5.36</v>
-      </c>
       <c r="H53" s="16" t="n">
-        <v>5.27</v>
+        <v>5.28</v>
       </c>
       <c r="I53" s="17" t="n">
-        <v>5.21</v>
+        <v>5.23</v>
       </c>
       <c r="J53" s="17" t="n">
         <v>5.18</v>
@@ -3888,24 +3888,24 @@
         <v>5.17</v>
       </c>
       <c r="M53" s="19" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="N53" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>5.07</v>
+      </c>
+      <c r="N53" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O53" s="21" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
       <c r="P53" s="21" t="n">
         <v>5.26</v>
       </c>
       <c r="Q53" s="22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R53" s="25" t="n">
-        <v>-0.38</v>
+        <v>5.28</v>
+      </c>
+      <c r="R53" s="23" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="54">
@@ -3920,37 +3920,37 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>18.87</v>
+        <v>19.24</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>18.52</v>
+        <v>18.51</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>18.22</v>
+        <v>17.9</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>18.24</v>
+        <v>17.86</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>18.45</v>
+        <v>18.33</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="I54" s="17" t="n">
-        <v>17.89</v>
+        <v>17.13</v>
       </c>
       <c r="J54" s="17" t="n">
-        <v>17.75</v>
+        <v>16.87</v>
       </c>
       <c r="K54" s="18" t="n">
-        <v>18.03</v>
+        <v>17.49</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>17.73</v>
+        <v>16.88</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>17.38</v>
+        <v>16.15</v>
       </c>
       <c r="N54" s="24" t="inlineStr">
         <is>
@@ -3958,16 +3958,16 @@
         </is>
       </c>
       <c r="O54" s="21" t="n">
-        <v>18.08</v>
+        <v>17.57</v>
       </c>
       <c r="P54" s="21" t="n">
-        <v>18.05</v>
+        <v>17.55</v>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>18.04</v>
+        <v>17.4</v>
       </c>
       <c r="R54" s="25" t="n">
-        <v>-0.17</v>
+        <v>-3.55</v>
       </c>
     </row>
     <row r="55">
@@ -3982,37 +3982,37 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>94.87</v>
+        <v>96.39</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>92.97</v>
+        <v>94.39</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>91.38</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>92.23</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>92.97</v>
+        <v>94.5</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>91.06999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>90.33</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>89.17</v>
+        <v>90.5</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>90.31999999999999</v>
+        <v>91.59</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>88.73</v>
+        <v>89.91</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>86.83</v>
+        <v>87.91</v>
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
@@ -4020,16 +4020,16 @@
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>90.77</v>
+        <v>92.12</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>90.47</v>
+        <v>91.75</v>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>91.5</v>
+        <v>93.2</v>
       </c>
       <c r="R55" s="23" t="n">
-        <v>3.68</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="56">
@@ -4044,54 +4044,54 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>19.91</v>
+        <v>20.33</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>19.62</v>
+        <v>19.63</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>19.38</v>
+        <v>19.05</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>19.38</v>
+        <v>19.05</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>19.55</v>
+        <v>19.47</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>19.26</v>
+        <v>18.77</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>19.09</v>
+        <v>18.35</v>
       </c>
       <c r="J56" s="17" t="n">
-        <v>18.97</v>
+        <v>18.07</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>19.21</v>
+        <v>18.65</v>
       </c>
       <c r="L56" s="19" t="n">
-        <v>18.97</v>
+        <v>18.07</v>
       </c>
       <c r="M56" s="19" t="n">
-        <v>18.68</v>
-      </c>
-      <c r="N56" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>17.37</v>
+      </c>
+      <c r="N56" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O56" s="21" t="n">
-        <v>19.25</v>
+        <v>18.74</v>
       </c>
       <c r="P56" s="21" t="n">
-        <v>19.24</v>
+        <v>18.71</v>
       </c>
       <c r="Q56" s="22" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="R56" s="23" t="n">
-        <v>1.27</v>
+        <v>18.62</v>
+      </c>
+      <c r="R56" s="25" t="n">
+        <v>-3.02</v>
       </c>
     </row>
     <row r="57">
@@ -4109,51 +4109,51 @@
         <v>22.09</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>21.98</v>
+        <v>21.96</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>21.89</v>
+        <v>21.85</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>21.89</v>
+        <v>21.85</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>21.95</v>
+        <v>21.93</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>21.84</v>
+        <v>21.8</v>
       </c>
       <c r="I57" s="17" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="J57" s="17" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="K57" s="18" t="n">
         <v>21.78</v>
       </c>
-      <c r="J57" s="17" t="n">
-        <v>21.73</v>
-      </c>
-      <c r="K57" s="18" t="n">
-        <v>21.82</v>
-      </c>
       <c r="L57" s="19" t="n">
-        <v>21.73</v>
+        <v>21.67</v>
       </c>
       <c r="M57" s="19" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="N57" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>21.54</v>
+      </c>
+      <c r="N57" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O57" s="21" t="n">
-        <v>21.84</v>
+        <v>21.79</v>
       </c>
       <c r="P57" s="21" t="n">
-        <v>21.83</v>
+        <v>21.79</v>
       </c>
       <c r="Q57" s="22" t="n">
-        <v>21.82</v>
-      </c>
-      <c r="R57" s="23" t="n">
-        <v>0.05</v>
+        <v>21.77</v>
+      </c>
+      <c r="R57" s="25" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="58">
@@ -4168,37 +4168,37 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>23.65</v>
+        <v>24.07</v>
       </c>
       <c r="D58" s="13" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="F58" s="15" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G58" s="15" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="H58" s="16" t="n">
         <v>23.53</v>
       </c>
-      <c r="E58" s="14" t="n">
+      <c r="I58" s="17" t="n">
         <v>23.43</v>
       </c>
-      <c r="F58" s="15" t="n">
-        <v>23.47</v>
-      </c>
-      <c r="G58" s="15" t="n">
-        <v>23.53</v>
-      </c>
-      <c r="H58" s="16" t="n">
-        <v>23.41</v>
-      </c>
-      <c r="I58" s="17" t="n">
-        <v>23.35</v>
-      </c>
       <c r="J58" s="17" t="n">
-        <v>23.29</v>
+        <v>23.26</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>23.37</v>
+        <v>23.42</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>23.27</v>
+        <v>23.19</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>23.15</v>
+        <v>22.92</v>
       </c>
       <c r="N58" s="20" t="inlineStr">
         <is>
@@ -4206,16 +4206,16 @@
         </is>
       </c>
       <c r="O58" s="21" t="n">
-        <v>23.39</v>
+        <v>23.49</v>
       </c>
       <c r="P58" s="21" t="n">
-        <v>23.38</v>
+        <v>23.44</v>
       </c>
       <c r="Q58" s="22" t="n">
-        <v>23.42</v>
+        <v>23.6</v>
       </c>
       <c r="R58" s="23" t="n">
-        <v>0.21</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="59">
@@ -4230,37 +4230,37 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>29.34</v>
+        <v>29.46</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>29.12</v>
+        <v>29.2</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>28.93</v>
+        <v>28.98</v>
       </c>
       <c r="F59" s="15" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="G59" s="15" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="H59" s="16" t="n">
         <v>28.91</v>
       </c>
-      <c r="G59" s="15" t="n">
-        <v>29.05</v>
-      </c>
-      <c r="H59" s="16" t="n">
-        <v>28.83</v>
-      </c>
       <c r="I59" s="17" t="n">
-        <v>28.69</v>
+        <v>28.77</v>
       </c>
       <c r="J59" s="17" t="n">
-        <v>28.61</v>
+        <v>28.65</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>28.81</v>
+        <v>28.84</v>
       </c>
       <c r="L59" s="19" t="n">
         <v>28.62</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>28.4</v>
+        <v>28.36</v>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
@@ -4268,16 +4268,16 @@
         </is>
       </c>
       <c r="O59" s="21" t="n">
-        <v>28.83</v>
+        <v>28.88</v>
       </c>
       <c r="P59" s="21" t="n">
-        <v>28.83</v>
+        <v>28.86</v>
       </c>
       <c r="Q59" s="22" t="n">
-        <v>28.76</v>
+        <v>28.9</v>
       </c>
       <c r="R59" s="23" t="n">
-        <v>0.35</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="60">
@@ -4292,37 +4292,37 @@
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>45.5</v>
+        <v>45.42</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>45.3</v>
+        <v>45.26</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>45.14</v>
+        <v>45.12</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>45.14</v>
+        <v>45.2</v>
       </c>
       <c r="G60" s="15" t="n">
         <v>45.26</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>45.06</v>
+        <v>45.1</v>
       </c>
       <c r="I60" s="17" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="J60" s="17" t="n">
         <v>44.94</v>
       </c>
-      <c r="J60" s="17" t="n">
-        <v>44.86</v>
-      </c>
       <c r="K60" s="18" t="n">
-        <v>45.02</v>
+        <v>45.04</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>44.86</v>
+        <v>44.9</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>44.66</v>
+        <v>44.74</v>
       </c>
       <c r="N60" s="20" t="inlineStr">
         <is>
@@ -4330,16 +4330,16 @@
         </is>
       </c>
       <c r="O60" s="21" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="P60" s="21" t="n">
         <v>45.05</v>
       </c>
-      <c r="P60" s="21" t="n">
-        <v>45.04</v>
-      </c>
       <c r="Q60" s="22" t="n">
-        <v>45.02</v>
+        <v>45.14</v>
       </c>
       <c r="R60" s="23" t="n">
-        <v>0.45</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="61">
@@ -4354,37 +4354,37 @@
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>20.27</v>
+        <v>20.51</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>19.96</v>
+        <v>19.98</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>19.7</v>
+        <v>19.53</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>19.67</v>
+        <v>19.81</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>19.88</v>
+        <v>19.99</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>19.57</v>
+        <v>19.46</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>19.36</v>
+        <v>19.28</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>19.26</v>
+        <v>18.93</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>19.53</v>
+        <v>19.24</v>
       </c>
       <c r="L61" s="19" t="n">
-        <v>19.27</v>
+        <v>18.79</v>
       </c>
       <c r="M61" s="19" t="n">
-        <v>18.96</v>
+        <v>18.26</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
@@ -4392,16 +4392,16 @@
         </is>
       </c>
       <c r="O61" s="21" t="n">
-        <v>19.56</v>
+        <v>19.37</v>
       </c>
       <c r="P61" s="21" t="n">
-        <v>19.55</v>
+        <v>19.28</v>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>19.47</v>
+        <v>19.62</v>
       </c>
       <c r="R61" s="23" t="n">
-        <v>1.09</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="62">
@@ -4416,37 +4416,37 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>15.33</v>
+        <v>15.46</v>
       </c>
       <c r="D62" s="13" t="n">
-        <v>15.19</v>
+        <v>15.26</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>15.07</v>
+        <v>15.1</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>15.05</v>
+        <v>15.14</v>
       </c>
       <c r="G62" s="15" t="n">
-        <v>15.15</v>
+        <v>15.24</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>15.01</v>
+        <v>15.04</v>
       </c>
       <c r="I62" s="17" t="n">
-        <v>14.91</v>
+        <v>14.94</v>
       </c>
       <c r="J62" s="17" t="n">
-        <v>14.87</v>
+        <v>14.84</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>14.99</v>
+        <v>14.98</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>14.87</v>
+        <v>14.82</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>14.73</v>
+        <v>14.62</v>
       </c>
       <c r="N62" s="20" t="inlineStr">
         <is>
@@ -4454,16 +4454,16 @@
         </is>
       </c>
       <c r="O62" s="21" t="n">
-        <v>15</v>
+        <v>15.02</v>
       </c>
       <c r="P62" s="21" t="n">
         <v>15</v>
       </c>
       <c r="Q62" s="22" t="n">
-        <v>14.96</v>
-      </c>
-      <c r="R62" s="25" t="n">
-        <v>-0.13</v>
+        <v>15.04</v>
+      </c>
+      <c r="R62" s="23" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="63">
@@ -4478,54 +4478,54 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>25.84</v>
+        <v>25.68</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>25.64</v>
+        <v>25.52</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>25.48</v>
+        <v>25.38</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>25.55</v>
+        <v>25.39</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>25.63</v>
+        <v>25.49</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>25.43</v>
+        <v>25.33</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>25.35</v>
+        <v>25.23</v>
       </c>
       <c r="J63" s="17" t="n">
-        <v>25.23</v>
+        <v>25.17</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>25.36</v>
+        <v>25.3</v>
       </c>
       <c r="L63" s="19" t="n">
-        <v>25.2</v>
+        <v>25.16</v>
       </c>
       <c r="M63" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="N63" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+      <c r="N63" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O63" s="21" t="n">
-        <v>25.41</v>
+        <v>25.32</v>
       </c>
       <c r="P63" s="21" t="n">
-        <v>25.38</v>
+        <v>25.31</v>
       </c>
       <c r="Q63" s="22" t="n">
-        <v>25.46</v>
-      </c>
-      <c r="R63" s="23" t="n">
-        <v>0.47</v>
+        <v>25.3</v>
+      </c>
+      <c r="R63" s="25" t="n">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="64">
@@ -4540,54 +4540,54 @@
         </is>
       </c>
       <c r="C64" s="13" t="n">
-        <v>7.6</v>
+        <v>7.52</v>
       </c>
       <c r="D64" s="13" t="n">
-        <v>7.5</v>
+        <v>7.46</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>7.42</v>
+        <v>7.41</v>
       </c>
       <c r="F64" s="15" t="n">
         <v>7.41</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>7.48</v>
+        <v>7.44</v>
       </c>
       <c r="H64" s="16" t="n">
         <v>7.38</v>
       </c>
       <c r="I64" s="17" t="n">
-        <v>7.31</v>
+        <v>7.35</v>
       </c>
       <c r="J64" s="17" t="n">
-        <v>7.28</v>
+        <v>7.32</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>7.36</v>
+        <v>7.37</v>
       </c>
       <c r="L64" s="19" t="n">
-        <v>7.28</v>
+        <v>7.32</v>
       </c>
       <c r="M64" s="19" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="N64" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>7.26</v>
+      </c>
+      <c r="N64" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O64" s="21" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="P64" s="21" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="Q64" s="22" t="n">
         <v>7.37</v>
       </c>
-      <c r="P64" s="21" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="Q64" s="22" t="n">
-        <v>7.35</v>
-      </c>
       <c r="R64" s="23" t="n">
-        <v>1.1</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="65">
@@ -4602,41 +4602,41 @@
         </is>
       </c>
       <c r="C65" s="13" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="D65" s="13" t="n">
-        <v>5.07</v>
+        <v>5.06</v>
       </c>
       <c r="E65" s="14" t="n">
         <v>5.01</v>
       </c>
       <c r="F65" s="15" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="G65" s="15" t="n">
         <v>5.05</v>
       </c>
-      <c r="G65" s="15" t="n">
-        <v>5.07</v>
-      </c>
       <c r="H65" s="16" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="I65" s="17" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="J65" s="17" t="n">
         <v>4.93</v>
       </c>
       <c r="K65" s="18" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="L65" s="19" t="n">
         <v>4.92</v>
       </c>
       <c r="M65" s="19" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="N65" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>4.86</v>
+      </c>
+      <c r="N65" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O65" s="21" t="n">
@@ -4646,10 +4646,10 @@
         <v>4.98</v>
       </c>
       <c r="Q65" s="22" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="R65" s="23" t="n">
-        <v>1.83</v>
+        <v>5</v>
+      </c>
+      <c r="R65" s="25" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="66">
@@ -4664,54 +4664,54 @@
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>5.04</v>
+        <v>5.1</v>
       </c>
       <c r="D66" s="13" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="F66" s="15" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="G66" s="15" t="n">
         <v>5.01</v>
       </c>
-      <c r="E66" s="14" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="F66" s="15" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="G66" s="15" t="n">
-        <v>5</v>
-      </c>
       <c r="H66" s="16" t="n">
-        <v>4.97</v>
+        <v>4.94</v>
       </c>
       <c r="I66" s="17" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="J66" s="17" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="K66" s="18" t="n">
         <v>4.94</v>
       </c>
-      <c r="K66" s="18" t="n">
-        <v>4.97</v>
-      </c>
       <c r="L66" s="19" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="M66" s="19" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="N66" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O66" s="21" t="n">
         <v>4.94</v>
       </c>
-      <c r="M66" s="19" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="N66" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O66" s="21" t="n">
-        <v>4.97</v>
-      </c>
       <c r="P66" s="21" t="n">
-        <v>4.97</v>
+        <v>4.94</v>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="R66" s="23" t="n">
-        <v>0.2</v>
+        <v>4.92</v>
+      </c>
+      <c r="R66" s="25" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4726,54 +4726,54 @@
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>67.28</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>66.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>65.26000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>65.43000000000001</v>
+        <v>65.05</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>66.02</v>
+        <v>65.25</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>64.92</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I67" s="17" t="n">
-        <v>64.33</v>
+        <v>64.45</v>
       </c>
       <c r="J67" s="17" t="n">
-        <v>63.82</v>
+        <v>64.05</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>64.64</v>
+        <v>64.38</v>
       </c>
       <c r="L67" s="19" t="n">
-        <v>63.72</v>
+        <v>63.88</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>62.62</v>
-      </c>
-      <c r="N67" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>63.28</v>
+      </c>
+      <c r="N67" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O67" s="21" t="n">
-        <v>64.81999999999999</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="P67" s="21" t="n">
-        <v>64.73</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="Q67" s="22" t="n">
         <v>64.84999999999999</v>
       </c>
       <c r="R67" s="23" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4788,37 +4788,37 @@
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>69.51000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>67.95999999999999</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>66.66</v>
+        <v>66.61</v>
       </c>
       <c r="F68" s="15" t="n">
-        <v>66.84999999999999</v>
+        <v>66.63</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>67.7</v>
+        <v>67.02</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>66.15000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>65.3</v>
+        <v>65.98</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>64.59999999999999</v>
+        <v>65.72</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>65.79000000000001</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>64.48999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>62.94</v>
+        <v>65.05</v>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
@@ -4826,16 +4826,16 @@
         </is>
       </c>
       <c r="O68" s="21" t="n">
-        <v>66.03</v>
+        <v>66.33</v>
       </c>
       <c r="P68" s="21" t="n">
-        <v>65.91</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>66</v>
+        <v>66.25</v>
       </c>
       <c r="R68" s="23" t="n">
-        <v>0.99</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="69">
@@ -4850,54 +4850,54 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>103.78</v>
+        <v>104.17</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>102.68</v>
+        <v>102.77</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>101.76</v>
+        <v>101.59</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>101.97</v>
+        <v>101.43</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>102.53</v>
+        <v>102.37</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>101.43</v>
+        <v>100.97</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>100.87</v>
+        <v>100.03</v>
       </c>
       <c r="J69" s="17" t="n">
-        <v>100.33</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>101.14</v>
+        <v>100.81</v>
       </c>
       <c r="L69" s="19" t="n">
-        <v>100.22</v>
+        <v>99.63</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>99.12</v>
-      </c>
-      <c r="N69" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>98.23</v>
+      </c>
+      <c r="N69" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O69" s="21" t="n">
-        <v>101.33</v>
+        <v>100.94</v>
       </c>
       <c r="P69" s="21" t="n">
-        <v>101.23</v>
+        <v>100.92</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>101.4</v>
-      </c>
-      <c r="R69" s="23" t="n">
-        <v>0.7</v>
+        <v>100.5</v>
+      </c>
+      <c r="R69" s="25" t="n">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="70">
@@ -4912,37 +4912,37 @@
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>130.25</v>
+        <v>132.12</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>128.55</v>
+        <v>129.02</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>127.13</v>
+        <v>126.42</v>
       </c>
       <c r="F70" s="15" t="n">
-        <v>126.93</v>
+        <v>126.07</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>128.07</v>
+        <v>128.13</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>126.37</v>
+        <v>125.03</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>125.23</v>
+        <v>122.97</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>124.67</v>
+        <v>121.93</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>126.17</v>
+        <v>124.68</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>124.75</v>
+        <v>122.08</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>123.05</v>
+        <v>118.98</v>
       </c>
       <c r="N70" s="24" t="inlineStr">
         <is>
@@ -4950,16 +4950,16 @@
         </is>
       </c>
       <c r="O70" s="21" t="n">
-        <v>126.34</v>
+        <v>124.98</v>
       </c>
       <c r="P70" s="21" t="n">
-        <v>126.31</v>
+        <v>124.92</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>125.8</v>
+        <v>124</v>
       </c>
       <c r="R70" s="25" t="n">
-        <v>-3.97</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="71">
@@ -4974,37 +4974,37 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>26.28</v>
+        <v>26.55</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>25.92</v>
+        <v>26.11</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>25.62</v>
+        <v>25.74</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>25.75</v>
+        <v>25.85</v>
       </c>
       <c r="G71" s="15" t="n">
-        <v>25.91</v>
+        <v>26.07</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>25.55</v>
+        <v>25.63</v>
       </c>
       <c r="I71" s="17" t="n">
-        <v>25.39</v>
+        <v>25.41</v>
       </c>
       <c r="J71" s="17" t="n">
         <v>25.19</v>
       </c>
       <c r="K71" s="18" t="n">
-        <v>25.42</v>
+        <v>25.5</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>25.12</v>
+        <v>25.13</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>24.76</v>
+        <v>24.69</v>
       </c>
       <c r="N71" s="20" t="inlineStr">
         <is>
@@ -5012,16 +5012,16 @@
         </is>
       </c>
       <c r="O71" s="21" t="n">
-        <v>25.5</v>
+        <v>25.58</v>
       </c>
       <c r="P71" s="21" t="n">
-        <v>25.45</v>
+        <v>25.53</v>
       </c>
       <c r="Q71" s="22" t="n">
-        <v>25.6</v>
+        <v>25.64</v>
       </c>
       <c r="R71" s="23" t="n">
-        <v>0.95</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="72">
@@ -5036,34 +5036,34 @@
         </is>
       </c>
       <c r="C72" s="13" t="n">
-        <v>22</v>
+        <v>21.87</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>21.63</v>
+        <v>21.53</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>21.32</v>
+        <v>21.25</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>21.32</v>
+        <v>21.22</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>21.54</v>
+        <v>21.44</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>21.17</v>
+        <v>21.1</v>
       </c>
       <c r="I72" s="17" t="n">
-        <v>20.95</v>
+        <v>20.88</v>
       </c>
       <c r="J72" s="17" t="n">
-        <v>20.8</v>
+        <v>20.76</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>21.11</v>
+        <v>21.05</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>20.8</v>
+        <v>20.77</v>
       </c>
       <c r="M72" s="19" t="n">
         <v>20.43</v>
@@ -5074,16 +5074,16 @@
         </is>
       </c>
       <c r="O72" s="21" t="n">
-        <v>21.16</v>
+        <v>21.09</v>
       </c>
       <c r="P72" s="21" t="n">
-        <v>21.14</v>
+        <v>21.08</v>
       </c>
       <c r="Q72" s="22" t="n">
-        <v>21.09</v>
+        <v>21</v>
       </c>
       <c r="R72" s="25" t="n">
-        <v>-0.66</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="73">
@@ -5098,37 +5098,37 @@
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>251.1</v>
+        <v>248.08</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>245.6</v>
+        <v>244.88</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>240.99</v>
+        <v>242.2</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>243.03</v>
+        <v>242.03</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>245.37</v>
+        <v>244.07</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>239.87</v>
+        <v>240.87</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>237.53</v>
+        <v>238.83</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>234.37</v>
+        <v>237.67</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>237.91</v>
+        <v>240.4</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>233.3</v>
+        <v>237.72</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>227.8</v>
+        <v>234.52</v>
       </c>
       <c r="N73" s="20" t="inlineStr">
         <is>
@@ -5136,16 +5136,16 @@
         </is>
       </c>
       <c r="O73" s="21" t="n">
-        <v>239.1</v>
+        <v>240.76</v>
       </c>
       <c r="P73" s="21" t="n">
-        <v>238.34</v>
+        <v>240.65</v>
       </c>
       <c r="Q73" s="22" t="n">
-        <v>240.7</v>
-      </c>
-      <c r="R73" s="23" t="n">
-        <v>0.96</v>
+        <v>240</v>
+      </c>
+      <c r="R73" s="25" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="74">
@@ -5160,54 +5160,54 @@
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>16.14</v>
+        <v>16.88</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>15.92</v>
+        <v>16.39</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>15.73</v>
+        <v>15.98</v>
       </c>
       <c r="F74" s="15" t="n">
-        <v>15.73</v>
+        <v>16.13</v>
       </c>
       <c r="G74" s="15" t="n">
-        <v>15.87</v>
+        <v>16.35</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>15.65</v>
+        <v>15.86</v>
       </c>
       <c r="I74" s="17" t="n">
-        <v>15.51</v>
+        <v>15.64</v>
       </c>
       <c r="J74" s="17" t="n">
-        <v>15.43</v>
+        <v>15.37</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>15.61</v>
+        <v>15.71</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>15.42</v>
+        <v>15.3</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="N74" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>14.81</v>
+      </c>
+      <c r="N74" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O74" s="21" t="n">
-        <v>15.64</v>
+        <v>15.8</v>
       </c>
       <c r="P74" s="21" t="n">
-        <v>15.63</v>
+        <v>15.75</v>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="R74" s="25" t="n">
-        <v>-1.08</v>
+        <v>15.9</v>
+      </c>
+      <c r="R74" s="23" t="n">
+        <v>1.92</v>
       </c>
     </row>
     <row r="75">
@@ -5222,54 +5222,54 @@
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>39.15</v>
+        <v>38.55</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>37.91</v>
+        <v>37.43</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>36.87</v>
+        <v>36.49</v>
       </c>
       <c r="F75" s="15" t="n">
-        <v>37.38</v>
+        <v>36.65</v>
       </c>
       <c r="G75" s="15" t="n">
-        <v>37.88</v>
+        <v>37.25</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>36.64</v>
+        <v>36.13</v>
       </c>
       <c r="I75" s="17" t="n">
-        <v>36.14</v>
+        <v>35.53</v>
       </c>
       <c r="J75" s="17" t="n">
-        <v>35.4</v>
+        <v>35.01</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>36.17</v>
+        <v>35.87</v>
       </c>
       <c r="L75" s="19" t="n">
-        <v>35.13</v>
+        <v>34.93</v>
       </c>
       <c r="M75" s="19" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="N75" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>33.81</v>
+      </c>
+      <c r="N75" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O75" s="21" t="n">
-        <v>36.45</v>
+        <v>36.04</v>
       </c>
       <c r="P75" s="21" t="n">
-        <v>36.27</v>
+        <v>35.95</v>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>36.88</v>
+        <v>36.04</v>
       </c>
       <c r="R75" s="25" t="n">
-        <v>-1.13</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="76">
@@ -5284,54 +5284,54 @@
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>27.59</v>
+        <v>27.7</v>
       </c>
       <c r="D76" s="13" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="E76" s="14" t="n">
         <v>27.29</v>
       </c>
-      <c r="E76" s="14" t="n">
-        <v>27.03</v>
-      </c>
       <c r="F76" s="15" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="G76" s="15" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="H76" s="16" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="I76" s="17" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="J76" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="K76" s="18" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="L76" s="19" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="M76" s="19" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="N76" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O76" s="21" t="n">
         <v>27.2</v>
       </c>
-      <c r="G76" s="15" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="H76" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="I76" s="17" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="J76" s="17" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="K76" s="18" t="n">
-        <v>26.87</v>
-      </c>
-      <c r="L76" s="19" t="n">
-        <v>26.61</v>
-      </c>
-      <c r="M76" s="19" t="n">
-        <v>26.31</v>
-      </c>
-      <c r="N76" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O76" s="21" t="n">
-        <v>26.94</v>
-      </c>
       <c r="P76" s="21" t="n">
-        <v>26.89</v>
+        <v>27.19</v>
       </c>
       <c r="Q76" s="22" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="R76" s="23" t="n">
-        <v>0.82</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="77">
@@ -5346,37 +5346,37 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>44.18</v>
+        <v>44.27</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>43.6</v>
+        <v>43.57</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>43.11</v>
+        <v>42.99</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>43.19</v>
+        <v>43.09</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>43.51</v>
+        <v>43.47</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>42.93</v>
+        <v>42.77</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>42.61</v>
+        <v>42.39</v>
       </c>
       <c r="J77" s="17" t="n">
-        <v>42.35</v>
+        <v>42.07</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>42.79</v>
+        <v>42.59</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>42.3</v>
+        <v>42.01</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>41.72</v>
+        <v>41.31</v>
       </c>
       <c r="N77" s="24" t="inlineStr">
         <is>
@@ -5384,16 +5384,16 @@
         </is>
       </c>
       <c r="O77" s="21" t="n">
-        <v>42.88</v>
+        <v>42.71</v>
       </c>
       <c r="P77" s="21" t="n">
-        <v>42.83</v>
+        <v>42.65</v>
       </c>
       <c r="Q77" s="22" t="n">
-        <v>42.88</v>
+        <v>42.72</v>
       </c>
       <c r="R77" s="25" t="n">
-        <v>-0.65</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="78">
@@ -5408,54 +5408,54 @@
         </is>
       </c>
       <c r="C78" s="13" t="n">
-        <v>5.78</v>
+        <v>5.71</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>5.69</v>
+        <v>5.63</v>
       </c>
       <c r="E78" s="14" t="n">
-        <v>5.61</v>
+        <v>5.56</v>
       </c>
       <c r="F78" s="15" t="n">
-        <v>5.62</v>
+        <v>5.6</v>
       </c>
       <c r="G78" s="15" t="n">
-        <v>5.67</v>
+        <v>5.63</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>5.58</v>
+        <v>5.55</v>
       </c>
       <c r="I78" s="17" t="n">
-        <v>5.53</v>
+        <v>5.52</v>
       </c>
       <c r="J78" s="17" t="n">
-        <v>5.49</v>
+        <v>5.47</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>5.56</v>
+        <v>5.52</v>
       </c>
       <c r="L78" s="19" t="n">
-        <v>5.48</v>
+        <v>5.45</v>
       </c>
       <c r="M78" s="19" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="N78" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>5.37</v>
+      </c>
+      <c r="N78" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O78" s="21" t="n">
-        <v>5.57</v>
+        <v>5.54</v>
       </c>
       <c r="P78" s="21" t="n">
-        <v>5.57</v>
+        <v>5.52</v>
       </c>
       <c r="Q78" s="22" t="n">
         <v>5.57</v>
       </c>
       <c r="R78" s="23" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -5470,37 +5470,37 @@
         </is>
       </c>
       <c r="C79" s="13" t="n">
-        <v>19</v>
+        <v>19.42</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>18.75</v>
+        <v>19.1</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>18.55</v>
+        <v>18.83</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>18.67</v>
+        <v>18.94</v>
       </c>
       <c r="G79" s="15" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="H79" s="16" t="n">
         <v>18.76</v>
       </c>
-      <c r="H79" s="16" t="n">
-        <v>18.51</v>
-      </c>
       <c r="I79" s="17" t="n">
-        <v>18.42</v>
+        <v>18.62</v>
       </c>
       <c r="J79" s="17" t="n">
-        <v>18.26</v>
+        <v>18.44</v>
       </c>
       <c r="K79" s="18" t="n">
-        <v>18.41</v>
+        <v>18.65</v>
       </c>
       <c r="L79" s="19" t="n">
-        <v>18.2</v>
+        <v>18.38</v>
       </c>
       <c r="M79" s="19" t="n">
-        <v>17.95</v>
+        <v>18.06</v>
       </c>
       <c r="N79" s="20" t="inlineStr">
         <is>
@@ -5508,16 +5508,16 @@
         </is>
       </c>
       <c r="O79" s="21" t="n">
-        <v>18.47</v>
+        <v>18.72</v>
       </c>
       <c r="P79" s="21" t="n">
-        <v>18.42</v>
+        <v>18.68</v>
       </c>
       <c r="Q79" s="22" t="n">
-        <v>18.58</v>
+        <v>18.8</v>
       </c>
       <c r="R79" s="23" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="80">
@@ -5532,37 +5532,37 @@
         </is>
       </c>
       <c r="C80" s="13" t="n">
-        <v>86</v>
+        <v>85.87</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>84.3</v>
+        <v>84.62</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>82.88</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="F80" s="15" t="n">
-        <v>83.72</v>
+        <v>83.83</v>
       </c>
       <c r="G80" s="15" t="n">
-        <v>84.33</v>
+        <v>84.47</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>82.63</v>
+        <v>83.22</v>
       </c>
       <c r="I80" s="17" t="n">
-        <v>82.02</v>
+        <v>82.58</v>
       </c>
       <c r="J80" s="17" t="n">
-        <v>80.93000000000001</v>
+        <v>81.97</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>81.92</v>
+        <v>82.87</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>80.5</v>
+        <v>81.83</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>78.8</v>
+        <v>80.58</v>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
@@ -5570,16 +5570,16 @@
         </is>
       </c>
       <c r="O80" s="21" t="n">
-        <v>82.34</v>
+        <v>83.09</v>
       </c>
       <c r="P80" s="21" t="n">
-        <v>82.06</v>
+        <v>82.97</v>
       </c>
       <c r="Q80" s="22" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="R80" s="23" t="n">
-        <v>3.87</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="81">
@@ -5594,54 +5594,54 @@
         </is>
       </c>
       <c r="C81" s="13" t="n">
-        <v>4.85</v>
+        <v>4.87</v>
       </c>
       <c r="D81" s="13" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="E81" s="14" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="G81" s="15" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H81" s="16" t="n">
         <v>4.7</v>
       </c>
-      <c r="F81" s="15" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="G81" s="15" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="H81" s="16" t="n">
+      <c r="I81" s="17" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="J81" s="17" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="K81" s="18" t="n">
         <v>4.68</v>
       </c>
-      <c r="I81" s="17" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="J81" s="17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K81" s="18" t="n">
-        <v>4.66</v>
-      </c>
       <c r="L81" s="19" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="M81" s="19" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="N81" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>4.53</v>
+      </c>
+      <c r="N81" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O81" s="21" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="P81" s="21" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="Q81" s="22" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="R81" s="23" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="82">
@@ -5656,54 +5656,54 @@
         </is>
       </c>
       <c r="C82" s="13" t="n">
-        <v>63.19</v>
+        <v>64.75</v>
       </c>
       <c r="D82" s="13" t="n">
-        <v>62.24</v>
+        <v>63.3</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>61.44</v>
+        <v>62.08</v>
       </c>
       <c r="F82" s="15" t="n">
-        <v>61.9</v>
+        <v>61.92</v>
       </c>
       <c r="G82" s="15" t="n">
-        <v>62.25</v>
+        <v>62.88</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>61.3</v>
+        <v>61.43</v>
       </c>
       <c r="I82" s="17" t="n">
+        <v>60.47</v>
+      </c>
+      <c r="J82" s="17" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="K82" s="18" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="L82" s="19" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="M82" s="19" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="N82" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O82" s="21" t="n">
+        <v>61.41</v>
+      </c>
+      <c r="P82" s="21" t="n">
+        <v>61.38</v>
+      </c>
+      <c r="Q82" s="22" t="n">
         <v>60.95</v>
       </c>
-      <c r="J82" s="17" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="K82" s="18" t="n">
-        <v>60.91</v>
-      </c>
-      <c r="L82" s="19" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="M82" s="19" t="n">
-        <v>59.16</v>
-      </c>
-      <c r="N82" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O82" s="21" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="P82" s="21" t="n">
-        <v>60.98</v>
-      </c>
-      <c r="Q82" s="22" t="n">
-        <v>61.55</v>
-      </c>
       <c r="R82" s="25" t="n">
-        <v>-1.68</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="83">
@@ -5718,37 +5718,37 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>39.75</v>
+        <v>40.05</v>
       </c>
       <c r="D83" s="13" t="n">
-        <v>39.41</v>
+        <v>39.65</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>39.13</v>
+        <v>39.31</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>39.23</v>
+        <v>39.35</v>
       </c>
       <c r="G83" s="15" t="n">
-        <v>39.39</v>
+        <v>39.57</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>39.05</v>
+        <v>39.17</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>38.89</v>
+        <v>38.95</v>
       </c>
       <c r="J83" s="17" t="n">
-        <v>38.71</v>
+        <v>38.77</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>38.93</v>
+        <v>39.09</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>38.65</v>
+        <v>38.75</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>38.31</v>
+        <v>38.35</v>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
@@ -5756,16 +5756,16 @@
         </is>
       </c>
       <c r="O83" s="21" t="n">
-        <v>39</v>
+        <v>39.15</v>
       </c>
       <c r="P83" s="21" t="n">
-        <v>38.96</v>
+        <v>39.12</v>
       </c>
       <c r="Q83" s="22" t="n">
-        <v>39.08</v>
+        <v>39.12</v>
       </c>
       <c r="R83" s="23" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="84">
@@ -5780,37 +5780,37 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>95.37</v>
+        <v>96.58</v>
       </c>
       <c r="D84" s="13" t="n">
-        <v>94.77</v>
+        <v>95.48</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>94.27</v>
+        <v>94.56</v>
       </c>
       <c r="F84" s="15" t="n">
-        <v>94.2</v>
+        <v>94.8</v>
       </c>
       <c r="G84" s="15" t="n">
-        <v>94.59999999999999</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>94</v>
+        <v>94.25</v>
       </c>
       <c r="I84" s="17" t="n">
-        <v>93.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="J84" s="17" t="n">
-        <v>93.40000000000001</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>93.93000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="L84" s="19" t="n">
-        <v>93.43000000000001</v>
+        <v>93.02</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>92.83</v>
+        <v>91.92</v>
       </c>
       <c r="N84" s="20" t="inlineStr">
         <is>
@@ -5818,16 +5818,16 @@
         </is>
       </c>
       <c r="O84" s="21" t="n">
-        <v>93.98999999999999</v>
+        <v>94.14</v>
       </c>
       <c r="P84" s="21" t="n">
-        <v>93.98</v>
+        <v>94.03</v>
       </c>
       <c r="Q84" s="22" t="n">
-        <v>93.8</v>
+        <v>94.25</v>
       </c>
       <c r="R84" s="23" t="n">
-        <v>0.37</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="85">
@@ -5842,54 +5842,54 @@
         </is>
       </c>
       <c r="C85" s="13" t="n">
-        <v>17.59</v>
+        <v>17.47</v>
       </c>
       <c r="D85" s="13" t="n">
-        <v>17.38</v>
+        <v>17.29</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>17.2</v>
+        <v>17.14</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>17.24</v>
+        <v>17.16</v>
       </c>
       <c r="G85" s="15" t="n">
-        <v>17.35</v>
+        <v>17.26</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>17.14</v>
+        <v>17.08</v>
       </c>
       <c r="I85" s="17" t="n">
-        <v>17.03</v>
+        <v>16.98</v>
       </c>
       <c r="J85" s="17" t="n">
-        <v>16.93</v>
+        <v>16.9</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>17.09</v>
+        <v>17.04</v>
       </c>
       <c r="L85" s="19" t="n">
-        <v>16.91</v>
+        <v>16.89</v>
       </c>
       <c r="M85" s="19" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="N85" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.71</v>
+      </c>
+      <c r="N85" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O85" s="21" t="n">
-        <v>17.12</v>
+        <v>17.07</v>
       </c>
       <c r="P85" s="21" t="n">
-        <v>17.1</v>
+        <v>17.05</v>
       </c>
       <c r="Q85" s="22" t="n">
-        <v>17.13</v>
-      </c>
-      <c r="R85" s="23" t="n">
-        <v>0.41</v>
+        <v>17.06</v>
+      </c>
+      <c r="R85" s="25" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="86">
@@ -5904,54 +5904,54 @@
         </is>
       </c>
       <c r="C86" s="13" t="n">
-        <v>121.92</v>
+        <v>122.18</v>
       </c>
       <c r="D86" s="13" t="n">
-        <v>120.92</v>
+        <v>121.08</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>120.08</v>
+        <v>120.16</v>
       </c>
       <c r="F86" s="15" t="n">
-        <v>120.23</v>
+        <v>120.63</v>
       </c>
       <c r="G86" s="15" t="n">
-        <v>120.77</v>
+        <v>121.07</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>119.77</v>
+        <v>119.97</v>
       </c>
       <c r="I86" s="17" t="n">
-        <v>119.23</v>
+        <v>119.53</v>
       </c>
       <c r="J86" s="17" t="n">
-        <v>118.77</v>
+        <v>118.87</v>
       </c>
       <c r="K86" s="18" t="n">
-        <v>119.52</v>
+        <v>119.54</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>118.68</v>
+        <v>118.62</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>117.68</v>
-      </c>
-      <c r="N86" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>117.52</v>
+      </c>
+      <c r="N86" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O86" s="21" t="n">
-        <v>119.68</v>
+        <v>119.8</v>
       </c>
       <c r="P86" s="21" t="n">
-        <v>119.6</v>
+        <v>119.63</v>
       </c>
       <c r="Q86" s="22" t="n">
-        <v>119.7</v>
-      </c>
-      <c r="R86" s="25" t="n">
-        <v>-1.24</v>
+        <v>120.2</v>
+      </c>
+      <c r="R86" s="23" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="87">
@@ -5966,54 +5966,54 @@
         </is>
       </c>
       <c r="C87" s="13" t="n">
-        <v>71.51000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>67.61</v>
+        <v>63.6</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>64.34</v>
+        <v>62.72</v>
       </c>
       <c r="F87" s="15" t="n">
-        <v>64.43000000000001</v>
+        <v>62.97</v>
       </c>
       <c r="G87" s="15" t="n">
-        <v>66.77</v>
+        <v>63.48</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>62.87</v>
+        <v>62.43</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>60.53</v>
+        <v>61.92</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>58.97</v>
+        <v>61.38</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>62.16</v>
+        <v>62.13</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>58.89</v>
+        <v>61.25</v>
       </c>
       <c r="M87" s="19" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="N87" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>60.2</v>
+      </c>
+      <c r="N87" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>62.66</v>
+        <v>62.32</v>
       </c>
       <c r="P87" s="21" t="n">
-        <v>62.46</v>
+        <v>62.21</v>
       </c>
       <c r="Q87" s="22" t="n">
-        <v>62.1</v>
+        <v>62.45</v>
       </c>
       <c r="R87" s="23" t="n">
-        <v>1.8</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -6028,37 +6028,37 @@
         </is>
       </c>
       <c r="C88" s="13" t="n">
-        <v>10.33</v>
+        <v>10.6</v>
       </c>
       <c r="D88" s="13" t="n">
-        <v>10.16</v>
+        <v>10.35</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>10.01</v>
+        <v>10.14</v>
       </c>
       <c r="F88" s="15" t="n">
-        <v>10.04</v>
+        <v>10.23</v>
       </c>
       <c r="G88" s="15" t="n">
-        <v>10.13</v>
+        <v>10.34</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>9.960000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="I88" s="17" t="n">
-        <v>9.869999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="J88" s="17" t="n">
-        <v>9.789999999999999</v>
+        <v>9.84</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="L88" s="19" t="n">
-        <v>9.77</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>9.6</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="N88" s="20" t="inlineStr">
         <is>
@@ -6066,16 +6066,16 @@
         </is>
       </c>
       <c r="O88" s="21" t="n">
-        <v>9.949999999999999</v>
+        <v>10.06</v>
       </c>
       <c r="P88" s="21" t="n">
-        <v>9.93</v>
+        <v>10.02</v>
       </c>
       <c r="Q88" s="22" t="n">
-        <v>9.949999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="R88" s="23" t="n">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="89">
@@ -6090,37 +6090,37 @@
         </is>
       </c>
       <c r="C89" s="13" t="n">
-        <v>20.86</v>
+        <v>19.02</v>
       </c>
       <c r="D89" s="13" t="n">
-        <v>19.69</v>
+        <v>18.37</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>18.71</v>
+        <v>17.83</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>18.58</v>
+        <v>17.77</v>
       </c>
       <c r="G89" s="15" t="n">
-        <v>19.36</v>
+        <v>18.2</v>
       </c>
       <c r="H89" s="16" t="n">
-        <v>18.19</v>
+        <v>17.55</v>
       </c>
       <c r="I89" s="17" t="n">
-        <v>17.41</v>
+        <v>17.12</v>
       </c>
       <c r="J89" s="17" t="n">
-        <v>17.02</v>
+        <v>16.9</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>18.06</v>
+        <v>17.46</v>
       </c>
       <c r="L89" s="19" t="n">
-        <v>17.08</v>
+        <v>16.92</v>
       </c>
       <c r="M89" s="19" t="n">
-        <v>15.91</v>
+        <v>16.27</v>
       </c>
       <c r="N89" s="24" t="inlineStr">
         <is>
@@ -6128,16 +6128,16 @@
         </is>
       </c>
       <c r="O89" s="21" t="n">
-        <v>18.17</v>
+        <v>17.53</v>
       </c>
       <c r="P89" s="21" t="n">
-        <v>18.15</v>
+        <v>17.51</v>
       </c>
       <c r="Q89" s="22" t="n">
-        <v>17.8</v>
+        <v>17.35</v>
       </c>
       <c r="R89" s="25" t="n">
-        <v>-4.4</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="90">
@@ -6152,37 +6152,37 @@
         </is>
       </c>
       <c r="C90" s="13" t="n">
-        <v>19.6</v>
+        <v>19.41</v>
       </c>
       <c r="D90" s="13" t="n">
-        <v>19.29</v>
+        <v>19.21</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>19.03</v>
+        <v>19.05</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>19.14</v>
+        <v>19.1</v>
       </c>
       <c r="G90" s="15" t="n">
-        <v>19.27</v>
+        <v>19.19</v>
       </c>
       <c r="H90" s="16" t="n">
-        <v>18.96</v>
+        <v>18.99</v>
       </c>
       <c r="I90" s="17" t="n">
-        <v>18.83</v>
+        <v>18.9</v>
       </c>
       <c r="J90" s="17" t="n">
-        <v>18.65</v>
+        <v>18.79</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>18.86</v>
+        <v>18.93</v>
       </c>
       <c r="L90" s="19" t="n">
-        <v>18.6</v>
+        <v>18.77</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>18.29</v>
+        <v>18.57</v>
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
@@ -6190,16 +6190,16 @@
         </is>
       </c>
       <c r="O90" s="21" t="n">
-        <v>18.92</v>
+        <v>18.97</v>
       </c>
       <c r="P90" s="21" t="n">
-        <v>18.88</v>
+        <v>18.95</v>
       </c>
       <c r="Q90" s="22" t="n">
         <v>19</v>
       </c>
       <c r="R90" s="23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -6214,37 +6214,37 @@
         </is>
       </c>
       <c r="C91" s="13" t="n">
-        <v>34.99</v>
+        <v>33.38</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>33.33</v>
+        <v>32.8</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>31.93</v>
+        <v>32.31</v>
       </c>
       <c r="F91" s="15" t="n">
-        <v>32.76</v>
+        <v>32.38</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>33.36</v>
+        <v>32.7</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>31.7</v>
+        <v>32.12</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>31.1</v>
+        <v>31.8</v>
       </c>
       <c r="J91" s="17" t="n">
-        <v>30.04</v>
+        <v>31.54</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>31.01</v>
+        <v>31.99</v>
       </c>
       <c r="L91" s="19" t="n">
-        <v>29.61</v>
+        <v>31.5</v>
       </c>
       <c r="M91" s="19" t="n">
-        <v>27.95</v>
+        <v>30.92</v>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
@@ -6252,16 +6252,16 @@
         </is>
       </c>
       <c r="O91" s="21" t="n">
-        <v>31.42</v>
+        <v>32.08</v>
       </c>
       <c r="P91" s="21" t="n">
-        <v>31.13</v>
+        <v>32.03</v>
       </c>
       <c r="Q91" s="22" t="n">
-        <v>32.16</v>
-      </c>
-      <c r="R91" s="23" t="n">
-        <v>5.1</v>
+        <v>32.06</v>
+      </c>
+      <c r="R91" s="25" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="92">
@@ -6276,54 +6276,54 @@
         </is>
       </c>
       <c r="C92" s="13" t="n">
-        <v>21.61</v>
+        <v>22.17</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>21.27</v>
+        <v>21.71</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>20.99</v>
+        <v>21.33</v>
       </c>
       <c r="F92" s="15" t="n">
-        <v>21.1</v>
+        <v>21.48</v>
       </c>
       <c r="G92" s="15" t="n">
-        <v>21.25</v>
+        <v>21.69</v>
       </c>
       <c r="H92" s="16" t="n">
-        <v>20.91</v>
+        <v>21.23</v>
       </c>
       <c r="I92" s="17" t="n">
-        <v>20.76</v>
+        <v>21.02</v>
       </c>
       <c r="J92" s="17" t="n">
-        <v>20.57</v>
+        <v>20.77</v>
       </c>
       <c r="K92" s="18" t="n">
-        <v>20.79</v>
+        <v>21.07</v>
       </c>
       <c r="L92" s="19" t="n">
-        <v>20.51</v>
+        <v>20.69</v>
       </c>
       <c r="M92" s="19" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="N92" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>20.23</v>
+      </c>
+      <c r="N92" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O92" s="21" t="n">
-        <v>20.87</v>
+        <v>21.17</v>
       </c>
       <c r="P92" s="21" t="n">
-        <v>20.82</v>
+        <v>21.11</v>
       </c>
       <c r="Q92" s="22" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="R92" s="25" t="n">
-        <v>-0.24</v>
+        <v>21.28</v>
+      </c>
+      <c r="R92" s="23" t="n">
+        <v>1.58</v>
       </c>
     </row>
     <row r="93">
@@ -6338,37 +6338,37 @@
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>30</v>
+        <v>29.33</v>
       </c>
       <c r="D93" s="13" t="n">
-        <v>29.32</v>
+        <v>28.99</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>28.75</v>
+        <v>28.71</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>28.89</v>
+        <v>28.81</v>
       </c>
       <c r="G93" s="15" t="n">
-        <v>29.23</v>
+        <v>28.97</v>
       </c>
       <c r="H93" s="16" t="n">
-        <v>28.55</v>
+        <v>28.63</v>
       </c>
       <c r="I93" s="17" t="n">
-        <v>28.21</v>
+        <v>28.47</v>
       </c>
       <c r="J93" s="17" t="n">
-        <v>27.87</v>
+        <v>28.29</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>28.37</v>
+        <v>28.51</v>
       </c>
       <c r="L93" s="19" t="n">
-        <v>27.8</v>
+        <v>28.23</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>27.12</v>
+        <v>27.89</v>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
@@ -6376,16 +6376,16 @@
         </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>28.49</v>
+        <v>28.58</v>
       </c>
       <c r="P93" s="21" t="n">
-        <v>28.42</v>
+        <v>28.54</v>
       </c>
       <c r="Q93" s="22" t="n">
-        <v>28.54</v>
-      </c>
-      <c r="R93" s="25" t="n">
-        <v>-0.35</v>
+        <v>28.66</v>
+      </c>
+      <c r="R93" s="23" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="94">
@@ -6400,37 +6400,37 @@
         </is>
       </c>
       <c r="C94" s="13" t="n">
-        <v>179.4</v>
+        <v>174.57</v>
       </c>
       <c r="D94" s="13" t="n">
-        <v>175.2</v>
+        <v>171.87</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>171.68</v>
+        <v>169.61</v>
       </c>
       <c r="F94" s="15" t="n">
-        <v>171.47</v>
+        <v>169.5</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>174.13</v>
+        <v>171.2</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>169.93</v>
+        <v>168.5</v>
       </c>
       <c r="I94" s="17" t="n">
-        <v>167.27</v>
+        <v>166.8</v>
       </c>
       <c r="J94" s="17" t="n">
-        <v>165.73</v>
+        <v>165.8</v>
       </c>
       <c r="K94" s="18" t="n">
-        <v>169.32</v>
+        <v>168.09</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>165.8</v>
+        <v>165.83</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>161.6</v>
+        <v>163.13</v>
       </c>
       <c r="N94" s="24" t="inlineStr">
         <is>
@@ -6438,16 +6438,16 @@
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>169.79</v>
+        <v>168.4</v>
       </c>
       <c r="P94" s="21" t="n">
-        <v>169.65</v>
+        <v>168.3</v>
       </c>
       <c r="Q94" s="22" t="n">
-        <v>168.8</v>
+        <v>167.8</v>
       </c>
       <c r="R94" s="25" t="n">
-        <v>-1</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="95">
@@ -6462,54 +6462,54 @@
         </is>
       </c>
       <c r="C95" s="13" t="n">
-        <v>14.51</v>
+        <v>14.59</v>
       </c>
       <c r="D95" s="13" t="n">
-        <v>14.19</v>
+        <v>14.29</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>13.92</v>
+        <v>14.03</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>13.98</v>
+        <v>14.17</v>
       </c>
       <c r="G95" s="15" t="n">
-        <v>14.15</v>
+        <v>14.29</v>
       </c>
       <c r="H95" s="16" t="n">
-        <v>13.83</v>
+        <v>13.99</v>
       </c>
       <c r="I95" s="17" t="n">
-        <v>13.66</v>
+        <v>13.87</v>
       </c>
       <c r="J95" s="17" t="n">
-        <v>13.51</v>
+        <v>13.69</v>
       </c>
       <c r="K95" s="18" t="n">
-        <v>13.74</v>
+        <v>13.87</v>
       </c>
       <c r="L95" s="19" t="n">
-        <v>13.47</v>
+        <v>13.61</v>
       </c>
       <c r="M95" s="19" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="N95" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>13.31</v>
+      </c>
+      <c r="N95" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O95" s="21" t="n">
-        <v>13.8</v>
+        <v>13.94</v>
       </c>
       <c r="P95" s="21" t="n">
-        <v>13.77</v>
+        <v>13.89</v>
       </c>
       <c r="Q95" s="22" t="n">
-        <v>13.82</v>
-      </c>
-      <c r="R95" s="25" t="n">
-        <v>-0.72</v>
+        <v>14.06</v>
+      </c>
+      <c r="R95" s="23" t="n">
+        <v>1.74</v>
       </c>
     </row>
     <row r="96">
@@ -6524,54 +6524,54 @@
         </is>
       </c>
       <c r="C96" s="13" t="n">
-        <v>21.46</v>
+        <v>22.41</v>
       </c>
       <c r="D96" s="13" t="n">
-        <v>21.05</v>
+        <v>21.63</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>20.71</v>
+        <v>20.98</v>
       </c>
       <c r="F96" s="15" t="n">
-        <v>20.7</v>
+        <v>21.41</v>
       </c>
       <c r="G96" s="15" t="n">
-        <v>20.96</v>
+        <v>21.67</v>
       </c>
       <c r="H96" s="16" t="n">
-        <v>20.55</v>
+        <v>20.89</v>
       </c>
       <c r="I96" s="17" t="n">
-        <v>20.29</v>
+        <v>20.63</v>
       </c>
       <c r="J96" s="17" t="n">
-        <v>20.14</v>
+        <v>20.11</v>
       </c>
       <c r="K96" s="18" t="n">
-        <v>20.48</v>
+        <v>20.54</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>20.14</v>
+        <v>19.89</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>19.73</v>
-      </c>
-      <c r="N96" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>19.11</v>
+      </c>
+      <c r="N96" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O96" s="21" t="n">
-        <v>20.53</v>
+        <v>20.75</v>
       </c>
       <c r="P96" s="21" t="n">
-        <v>20.51</v>
+        <v>20.6</v>
       </c>
       <c r="Q96" s="22" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="R96" s="25" t="n">
-        <v>-2.2</v>
+        <v>21.15</v>
+      </c>
+      <c r="R96" s="23" t="n">
+        <v>3.42</v>
       </c>
     </row>
     <row r="97">
@@ -6586,54 +6586,54 @@
         </is>
       </c>
       <c r="C97" s="13" t="n">
-        <v>16.71</v>
+        <v>16.55</v>
       </c>
       <c r="D97" s="13" t="n">
-        <v>16.51</v>
+        <v>16.4</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>16.35</v>
+        <v>16.28</v>
       </c>
       <c r="F97" s="15" t="n">
-        <v>16.32</v>
+        <v>16.33</v>
       </c>
       <c r="G97" s="15" t="n">
-        <v>16.46</v>
+        <v>16.4</v>
       </c>
       <c r="H97" s="16" t="n">
-        <v>16.26</v>
+        <v>16.25</v>
       </c>
       <c r="I97" s="17" t="n">
-        <v>16.12</v>
+        <v>16.18</v>
       </c>
       <c r="J97" s="17" t="n">
-        <v>16.06</v>
+        <v>16.1</v>
       </c>
       <c r="K97" s="18" t="n">
-        <v>16.23</v>
+        <v>16.19</v>
       </c>
       <c r="L97" s="19" t="n">
         <v>16.07</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="N97" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>15.92</v>
+      </c>
+      <c r="N97" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O97" s="21" t="n">
-        <v>16.25</v>
+        <v>16.23</v>
       </c>
       <c r="P97" s="21" t="n">
-        <v>16.25</v>
+        <v>16.2</v>
       </c>
       <c r="Q97" s="22" t="n">
-        <v>16.19</v>
-      </c>
-      <c r="R97" s="25" t="n">
-        <v>-1.88</v>
+        <v>16.27</v>
+      </c>
+      <c r="R97" s="23" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="98">
@@ -6648,37 +6648,37 @@
         </is>
       </c>
       <c r="C98" s="13" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="D98" s="13" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="E98" s="14" t="n">
-        <v>10.14</v>
+        <v>10.04</v>
       </c>
       <c r="F98" s="15" t="n">
-        <v>10.13</v>
+        <v>10.08</v>
       </c>
       <c r="G98" s="15" t="n">
-        <v>10.25</v>
+        <v>10.18</v>
       </c>
       <c r="H98" s="16" t="n">
-        <v>10.05</v>
+        <v>9.98</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>9.93</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J98" s="17" t="n">
-        <v>9.85</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>10.02</v>
+        <v>9.92</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>9.859999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>9.66</v>
+        <v>9.56</v>
       </c>
       <c r="N98" s="24" t="inlineStr">
         <is>
@@ -6686,16 +6686,16 @@
         </is>
       </c>
       <c r="O98" s="21" t="n">
-        <v>10.05</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P98" s="21" t="n">
-        <v>10.04</v>
+        <v>9.94</v>
       </c>
       <c r="Q98" s="22" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="R98" s="25" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="99">
@@ -6710,54 +6710,54 @@
         </is>
       </c>
       <c r="C99" s="13" t="n">
-        <v>27.85</v>
+        <v>27.27</v>
       </c>
       <c r="D99" s="13" t="n">
-        <v>27.25</v>
+        <v>26.97</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>26.75</v>
+        <v>26.71</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>26.89</v>
+        <v>26.76</v>
       </c>
       <c r="G99" s="15" t="n">
-        <v>27.19</v>
+        <v>26.92</v>
       </c>
       <c r="H99" s="16" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="I99" s="17" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="J99" s="17" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="K99" s="18" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="L99" s="19" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="M99" s="19" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="N99" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O99" s="21" t="n">
         <v>26.59</v>
       </c>
-      <c r="I99" s="17" t="n">
-        <v>26.29</v>
-      </c>
-      <c r="J99" s="17" t="n">
-        <v>25.99</v>
-      </c>
-      <c r="K99" s="18" t="n">
-        <v>26.41</v>
-      </c>
-      <c r="L99" s="19" t="n">
-        <v>25.91</v>
-      </c>
-      <c r="M99" s="19" t="n">
-        <v>25.31</v>
-      </c>
-      <c r="N99" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O99" s="21" t="n">
-        <v>26.52</v>
-      </c>
       <c r="P99" s="21" t="n">
-        <v>26.46</v>
+        <v>26.57</v>
       </c>
       <c r="Q99" s="22" t="n">
         <v>26.6</v>
       </c>
       <c r="R99" s="23" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -6772,54 +6772,54 @@
         </is>
       </c>
       <c r="C100" s="13" t="n">
-        <v>17.65</v>
+        <v>17.68</v>
       </c>
       <c r="D100" s="13" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="E100" s="14" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F100" s="15" t="n">
         <v>17.34</v>
       </c>
-      <c r="E100" s="14" t="n">
+      <c r="G100" s="15" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="H100" s="16" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="I100" s="17" t="n">
         <v>17.08</v>
       </c>
-      <c r="F100" s="15" t="n">
-        <v>17.11</v>
-      </c>
-      <c r="G100" s="15" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="H100" s="16" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="I100" s="17" t="n">
-        <v>16.8</v>
-      </c>
       <c r="J100" s="17" t="n">
-        <v>16.67</v>
+        <v>16.91</v>
       </c>
       <c r="K100" s="18" t="n">
-        <v>16.91</v>
+        <v>17.06</v>
       </c>
       <c r="L100" s="19" t="n">
-        <v>16.65</v>
+        <v>16.84</v>
       </c>
       <c r="M100" s="19" t="n">
-        <v>16.34</v>
-      </c>
-      <c r="N100" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>16.58</v>
+      </c>
+      <c r="N100" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O100" s="21" t="n">
-        <v>16.95</v>
+        <v>17.12</v>
       </c>
       <c r="P100" s="21" t="n">
-        <v>16.93</v>
+        <v>17.08</v>
       </c>
       <c r="Q100" s="22" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="R100" s="25" t="n">
-        <v>-0.41</v>
+        <v>17.25</v>
+      </c>
+      <c r="R100" s="23" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="101">
@@ -6834,37 +6834,37 @@
         </is>
       </c>
       <c r="C101" s="13" t="n">
-        <v>32.96</v>
+        <v>32.58</v>
       </c>
       <c r="D101" s="13" t="n">
-        <v>32.6</v>
+        <v>32.36</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>32.3</v>
+        <v>32.17</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>32.3</v>
+        <v>32.15</v>
       </c>
       <c r="G101" s="15" t="n">
-        <v>32.52</v>
+        <v>32.29</v>
       </c>
       <c r="H101" s="16" t="n">
-        <v>32.16</v>
+        <v>32.07</v>
       </c>
       <c r="I101" s="17" t="n">
-        <v>31.94</v>
+        <v>31.93</v>
       </c>
       <c r="J101" s="17" t="n">
-        <v>31.8</v>
+        <v>31.85</v>
       </c>
       <c r="K101" s="18" t="n">
-        <v>32.1</v>
+        <v>32.05</v>
       </c>
       <c r="L101" s="19" t="n">
-        <v>31.8</v>
+        <v>31.86</v>
       </c>
       <c r="M101" s="19" t="n">
-        <v>31.44</v>
+        <v>31.64</v>
       </c>
       <c r="N101" s="24" t="inlineStr">
         <is>
@@ -6872,16 +6872,16 @@
         </is>
       </c>
       <c r="O101" s="21" t="n">
-        <v>32.14</v>
+        <v>32.07</v>
       </c>
       <c r="P101" s="21" t="n">
-        <v>32.13</v>
+        <v>32.07</v>
       </c>
       <c r="Q101" s="22" t="n">
-        <v>32.08</v>
+        <v>32</v>
       </c>
       <c r="R101" s="25" t="n">
-        <v>-0.99</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="102">
@@ -6896,37 +6896,37 @@
         </is>
       </c>
       <c r="C102" s="13" t="n">
-        <v>16.03</v>
+        <v>17.08</v>
       </c>
       <c r="D102" s="13" t="n">
-        <v>15.85</v>
+        <v>16.54</v>
       </c>
       <c r="E102" s="14" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="F102" s="15" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="G102" s="15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H102" s="16" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="I102" s="17" t="n">
         <v>15.7</v>
       </c>
-      <c r="F102" s="15" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="G102" s="15" t="n">
-        <v>15.84</v>
-      </c>
-      <c r="H102" s="16" t="n">
-        <v>15.66</v>
-      </c>
-      <c r="I102" s="17" t="n">
-        <v>15.57</v>
-      </c>
       <c r="J102" s="17" t="n">
-        <v>15.48</v>
+        <v>15.42</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>15.6</v>
+        <v>15.79</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>15.45</v>
+        <v>15.34</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>15.27</v>
+        <v>14.8</v>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
@@ -6934,16 +6934,16 @@
         </is>
       </c>
       <c r="O102" s="21" t="n">
-        <v>15.64</v>
+        <v>15.89</v>
       </c>
       <c r="P102" s="21" t="n">
-        <v>15.61</v>
+        <v>15.83</v>
       </c>
       <c r="Q102" s="22" t="n">
-        <v>15.67</v>
+        <v>15.99</v>
       </c>
       <c r="R102" s="23" t="n">
-        <v>0.71</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="103">
@@ -6958,37 +6958,37 @@
         </is>
       </c>
       <c r="C103" s="13" t="n">
-        <v>75.86</v>
+        <v>75.02</v>
       </c>
       <c r="D103" s="13" t="n">
-        <v>74.31</v>
+        <v>74.02</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>73.01000000000001</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>73.37</v>
+        <v>73.47</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>74.13</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>72.58</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>71.81999999999999</v>
+        <v>72.47</v>
       </c>
       <c r="J103" s="17" t="n">
-        <v>71.03</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>72.14</v>
+        <v>72.62</v>
       </c>
       <c r="L103" s="19" t="n">
-        <v>70.84</v>
+        <v>71.78</v>
       </c>
       <c r="M103" s="19" t="n">
-        <v>69.29000000000001</v>
+        <v>70.78</v>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
@@ -6996,16 +6996,16 @@
         </is>
       </c>
       <c r="O103" s="21" t="n">
-        <v>72.42</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="P103" s="21" t="n">
-        <v>72.26000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="Q103" s="22" t="n">
-        <v>72.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="R103" s="23" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="104">
@@ -7020,54 +7020,54 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>15.63</v>
+        <v>15.98</v>
       </c>
       <c r="D104" s="13" t="n">
-        <v>15.25</v>
+        <v>15.56</v>
       </c>
       <c r="E104" s="14" t="n">
-        <v>14.94</v>
+        <v>15.21</v>
       </c>
       <c r="F104" s="15" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="G104" s="15" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="H104" s="16" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I104" s="17" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="J104" s="17" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="K104" s="18" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="L104" s="19" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="M104" s="19" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N104" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O104" s="21" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="P104" s="21" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="Q104" s="22" t="n">
         <v>15.13</v>
       </c>
-      <c r="G104" s="15" t="n">
-        <v>15.27</v>
-      </c>
-      <c r="H104" s="16" t="n">
-        <v>14.89</v>
-      </c>
-      <c r="I104" s="17" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="J104" s="17" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="K104" s="18" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="L104" s="19" t="n">
-        <v>14.41</v>
-      </c>
-      <c r="M104" s="19" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="N104" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O104" s="21" t="n">
-        <v>14.82</v>
-      </c>
-      <c r="P104" s="21" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="Q104" s="22" t="n">
-        <v>15</v>
-      </c>
       <c r="R104" s="23" t="n">
-        <v>3.88</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="105">
@@ -7082,37 +7082,37 @@
         </is>
       </c>
       <c r="C105" s="13" t="n">
-        <v>19.43</v>
+        <v>18.1</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>18.61</v>
+        <v>17.72</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>17.92</v>
+        <v>17.41</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>17.87</v>
+        <v>17.38</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>18.39</v>
+        <v>17.62</v>
       </c>
       <c r="H105" s="16" t="n">
-        <v>17.57</v>
+        <v>17.24</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>17.05</v>
+        <v>17</v>
       </c>
       <c r="J105" s="17" t="n">
-        <v>16.75</v>
+        <v>16.86</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>17.46</v>
+        <v>17.19</v>
       </c>
       <c r="L105" s="19" t="n">
-        <v>16.77</v>
+        <v>16.88</v>
       </c>
       <c r="M105" s="19" t="n">
-        <v>15.95</v>
+        <v>16.5</v>
       </c>
       <c r="N105" s="24" t="inlineStr">
         <is>
@@ -7120,16 +7120,16 @@
         </is>
       </c>
       <c r="O105" s="21" t="n">
-        <v>17.55</v>
+        <v>17.23</v>
       </c>
       <c r="P105" s="21" t="n">
-        <v>17.52</v>
+        <v>17.22</v>
       </c>
       <c r="Q105" s="22" t="n">
-        <v>17.34</v>
+        <v>17.13</v>
       </c>
       <c r="R105" s="25" t="n">
-        <v>-2.69</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="106">
@@ -7144,54 +7144,54 @@
         </is>
       </c>
       <c r="C106" s="13" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="D106" s="13" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="E106" s="14" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="F106" s="15" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="G106" s="15" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="H106" s="16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I106" s="17" t="n">
         <v>2.36</v>
       </c>
-      <c r="I106" s="17" t="n">
+      <c r="J106" s="17" t="n">
         <v>2.34</v>
       </c>
-      <c r="J106" s="17" t="n">
+      <c r="K106" s="18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L106" s="19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M106" s="19" t="n">
         <v>2.31</v>
       </c>
-      <c r="K106" s="18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="L106" s="19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M106" s="19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="N106" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+      <c r="N106" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O106" s="21" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="P106" s="21" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q106" s="22" t="n">
         <v>2.37</v>
       </c>
-      <c r="R106" s="25" t="n">
-        <v>-1.66</v>
+      <c r="R106" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -7206,54 +7206,54 @@
         </is>
       </c>
       <c r="C107" s="13" t="n">
-        <v>44.38</v>
+        <v>40.88</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>42.4</v>
+        <v>40.52</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>40.74</v>
+        <v>40.22</v>
       </c>
       <c r="F107" s="15" t="n">
-        <v>41.21</v>
+        <v>40.25</v>
       </c>
       <c r="G107" s="15" t="n">
-        <v>42.19</v>
+        <v>40.45</v>
       </c>
       <c r="H107" s="16" t="n">
-        <v>40.21</v>
+        <v>40.09</v>
       </c>
       <c r="I107" s="17" t="n">
-        <v>39.23</v>
+        <v>39.89</v>
       </c>
       <c r="J107" s="17" t="n">
-        <v>38.23</v>
+        <v>39.73</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>39.64</v>
+        <v>40.02</v>
       </c>
       <c r="L107" s="19" t="n">
-        <v>37.98</v>
+        <v>39.72</v>
       </c>
       <c r="M107" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="N107" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>39.36</v>
+      </c>
+      <c r="N107" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O107" s="21" t="n">
-        <v>40</v>
+        <v>40.07</v>
       </c>
       <c r="P107" s="21" t="n">
-        <v>39.79</v>
+        <v>40.05</v>
       </c>
       <c r="Q107" s="22" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="R107" s="23" t="n">
-        <v>3.39</v>
+        <v>40.04</v>
+      </c>
+      <c r="R107" s="25" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="108">
@@ -7268,54 +7268,54 @@
         </is>
       </c>
       <c r="C108" s="13" t="n">
-        <v>8.619999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="D108" s="13" t="n">
-        <v>8.44</v>
+        <v>8.31</v>
       </c>
       <c r="E108" s="14" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="F108" s="15" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="G108" s="15" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="F108" s="15" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="G108" s="15" t="n">
-        <v>8.4</v>
-      </c>
       <c r="H108" s="16" t="n">
-        <v>8.220000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="I108" s="17" t="n">
-        <v>8.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="J108" s="17" t="n">
-        <v>8.039999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="K108" s="18" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="L108" s="19" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="M108" s="19" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="N108" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O108" s="21" t="n">
         <v>8.19</v>
       </c>
-      <c r="L108" s="19" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="M108" s="19" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="N108" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O108" s="21" t="n">
-        <v>8.210000000000001</v>
-      </c>
       <c r="P108" s="21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="Q108" s="22" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="R108" s="25" t="n">
-        <v>-0.49</v>
+        <v>8.18</v>
+      </c>
+      <c r="R108" s="23" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="109">
@@ -7330,37 +7330,37 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>45.07</v>
+        <v>45.72</v>
       </c>
       <c r="D109" s="13" t="n">
-        <v>44.69</v>
+        <v>45.14</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>44.38</v>
+        <v>44.65</v>
       </c>
       <c r="F109" s="15" t="n">
-        <v>44.47</v>
+        <v>44.85</v>
       </c>
       <c r="G109" s="15" t="n">
-        <v>44.65</v>
+        <v>45.11</v>
       </c>
       <c r="H109" s="16" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="I109" s="17" t="n">
         <v>44.27</v>
       </c>
-      <c r="I109" s="17" t="n">
-        <v>44.09</v>
-      </c>
       <c r="J109" s="17" t="n">
-        <v>43.89</v>
+        <v>43.95</v>
       </c>
       <c r="K109" s="18" t="n">
-        <v>44.16</v>
+        <v>44.33</v>
       </c>
       <c r="L109" s="19" t="n">
-        <v>43.85</v>
+        <v>43.84</v>
       </c>
       <c r="M109" s="19" t="n">
-        <v>43.47</v>
+        <v>43.26</v>
       </c>
       <c r="N109" s="20" t="inlineStr">
         <is>
@@ -7368,16 +7368,16 @@
         </is>
       </c>
       <c r="O109" s="21" t="n">
-        <v>44.23</v>
+        <v>44.45</v>
       </c>
       <c r="P109" s="21" t="n">
-        <v>44.19</v>
+        <v>44.37</v>
       </c>
       <c r="Q109" s="22" t="n">
-        <v>44.28</v>
-      </c>
-      <c r="R109" s="25" t="n">
-        <v>-0.18</v>
+        <v>44.6</v>
+      </c>
+      <c r="R109" s="23" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="110">
@@ -7392,37 +7392,37 @@
         </is>
       </c>
       <c r="C110" s="13" t="n">
-        <v>66.58</v>
+        <v>73.11</v>
       </c>
       <c r="D110" s="13" t="n">
-        <v>66.13</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="E110" s="14" t="n">
-        <v>65.75</v>
+        <v>67.87</v>
       </c>
       <c r="F110" s="15" t="n">
-        <v>65.73</v>
+        <v>68.75</v>
       </c>
       <c r="G110" s="15" t="n">
-        <v>66.02</v>
+        <v>70.05</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>65.56999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>65.28</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J110" s="17" t="n">
-        <v>65.12</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="K110" s="18" t="n">
-        <v>65.5</v>
+        <v>66.28</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>65.12</v>
+        <v>63.89</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>64.67</v>
+        <v>61.04</v>
       </c>
       <c r="N110" s="20" t="inlineStr">
         <is>
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="O110" s="21" t="n">
-        <v>65.55</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="P110" s="21" t="n">
-        <v>65.53</v>
+        <v>66.5</v>
       </c>
       <c r="Q110" s="22" t="n">
-        <v>65.45</v>
+        <v>67.45</v>
       </c>
       <c r="R110" s="23" t="n">
-        <v>0.23</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="111">
@@ -7454,54 +7454,54 @@
         </is>
       </c>
       <c r="C111" s="13" t="n">
-        <v>10.67</v>
+        <v>10.71</v>
       </c>
       <c r="D111" s="13" t="n">
-        <v>10.58</v>
+        <v>10.6</v>
       </c>
       <c r="E111" s="14" t="n">
-        <v>10.5</v>
+        <v>10.51</v>
       </c>
       <c r="F111" s="15" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="G111" s="15" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H111" s="16" t="n">
         <v>10.49</v>
       </c>
-      <c r="G111" s="15" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="H111" s="16" t="n">
-        <v>10.46</v>
-      </c>
       <c r="I111" s="17" t="n">
-        <v>10.4</v>
+        <v>10.45</v>
       </c>
       <c r="J111" s="17" t="n">
-        <v>10.37</v>
+        <v>10.38</v>
       </c>
       <c r="K111" s="18" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="L111" s="19" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="M111" s="19" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="N111" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O111" s="21" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="P111" s="21" t="n">
         <v>10.45</v>
       </c>
-      <c r="L111" s="19" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="M111" s="19" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="N111" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O111" s="21" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="P111" s="21" t="n">
-        <v>10.46</v>
-      </c>
       <c r="Q111" s="22" t="n">
-        <v>10.43</v>
+        <v>10.52</v>
       </c>
       <c r="R111" s="23" t="n">
-        <v>0.29</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="112">
@@ -7516,54 +7516,54 @@
         </is>
       </c>
       <c r="C112" s="13" t="n">
-        <v>372.18</v>
+        <v>383.3</v>
       </c>
       <c r="D112" s="13" t="n">
-        <v>344.38</v>
+        <v>355.3</v>
       </c>
       <c r="E112" s="14" t="n">
-        <v>321.08</v>
+        <v>331.84</v>
       </c>
       <c r="F112" s="15" t="n">
-        <v>332.6</v>
+        <v>329.6</v>
       </c>
       <c r="G112" s="15" t="n">
-        <v>343.8</v>
+        <v>347.8</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>316</v>
+        <v>319.8</v>
       </c>
       <c r="I112" s="17" t="n">
-        <v>304.8</v>
+        <v>301.6</v>
       </c>
       <c r="J112" s="17" t="n">
-        <v>288.2</v>
+        <v>291.8</v>
       </c>
       <c r="K112" s="18" t="n">
-        <v>305.52</v>
+        <v>316.16</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>282.22</v>
+        <v>292.7</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>254.42</v>
-      </c>
-      <c r="N112" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>264.7</v>
+      </c>
+      <c r="N112" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O112" s="21" t="n">
-        <v>311.84</v>
+        <v>319.07</v>
       </c>
       <c r="P112" s="21" t="n">
-        <v>307.68</v>
+        <v>318.34</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>321.4</v>
-      </c>
-      <c r="R112" s="23" t="n">
-        <v>6.78</v>
+        <v>311.4</v>
+      </c>
+      <c r="R112" s="25" t="n">
+        <v>-3.11</v>
       </c>
     </row>
     <row r="113">
@@ -7578,37 +7578,37 @@
         </is>
       </c>
       <c r="C113" s="13" t="n">
-        <v>212.4</v>
+        <v>226.73</v>
       </c>
       <c r="D113" s="13" t="n">
-        <v>209</v>
+        <v>218.43</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>206.15</v>
+        <v>211.47</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>208.03</v>
+        <v>215.13</v>
       </c>
       <c r="G113" s="15" t="n">
-        <v>209.17</v>
+        <v>218.37</v>
       </c>
       <c r="H113" s="16" t="n">
-        <v>205.77</v>
+        <v>210.07</v>
       </c>
       <c r="I113" s="17" t="n">
-        <v>204.63</v>
+        <v>206.83</v>
       </c>
       <c r="J113" s="17" t="n">
-        <v>202.37</v>
+        <v>201.77</v>
       </c>
       <c r="K113" s="18" t="n">
-        <v>204.25</v>
+        <v>206.83</v>
       </c>
       <c r="L113" s="19" t="n">
-        <v>201.4</v>
+        <v>199.87</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>198</v>
+        <v>191.57</v>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
@@ -7616,16 +7616,16 @@
         </is>
       </c>
       <c r="O113" s="21" t="n">
-        <v>205.14</v>
+        <v>208.77</v>
       </c>
       <c r="P113" s="21" t="n">
-        <v>204.51</v>
+        <v>207.47</v>
       </c>
       <c r="Q113" s="22" t="n">
-        <v>206.9</v>
+        <v>211.9</v>
       </c>
       <c r="R113" s="23" t="n">
-        <v>0.88</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="114">
@@ -7640,37 +7640,37 @@
         </is>
       </c>
       <c r="C114" s="13" t="n">
-        <v>679.83</v>
+        <v>667.73</v>
       </c>
       <c r="D114" s="13" t="n">
-        <v>655.83</v>
+        <v>655.23</v>
       </c>
       <c r="E114" s="14" t="n">
-        <v>635.72</v>
+        <v>644.75</v>
       </c>
       <c r="F114" s="15" t="n">
-        <v>648.33</v>
+        <v>649.33</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>656.67</v>
+        <v>654.67</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>632.67</v>
+        <v>642.17</v>
       </c>
       <c r="I114" s="17" t="n">
-        <v>624.33</v>
+        <v>636.83</v>
       </c>
       <c r="J114" s="17" t="n">
-        <v>608.67</v>
+        <v>629.67</v>
       </c>
       <c r="K114" s="18" t="n">
-        <v>622.28</v>
+        <v>637.75</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>602.17</v>
+        <v>627.27</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>578.17</v>
+        <v>614.77</v>
       </c>
       <c r="N114" s="20" t="inlineStr">
         <is>
@@ -7678,16 +7678,16 @@
         </is>
       </c>
       <c r="O114" s="21" t="n">
-        <v>628.41</v>
+        <v>640.45</v>
       </c>
       <c r="P114" s="21" t="n">
-        <v>624.15</v>
+        <v>638.73</v>
       </c>
       <c r="Q114" s="22" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="R114" s="23" t="n">
-        <v>4.75</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="115">
@@ -7702,54 +7702,54 @@
         </is>
       </c>
       <c r="C115" s="13" t="n">
-        <v>6.74</v>
+        <v>7.18</v>
       </c>
       <c r="D115" s="13" t="n">
-        <v>6.67</v>
+        <v>6.97</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>6.61</v>
+        <v>6.79</v>
       </c>
       <c r="F115" s="15" t="n">
-        <v>6.61</v>
+        <v>6.78</v>
       </c>
       <c r="G115" s="15" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="H115" s="16" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="I115" s="17" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="J115" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K115" s="18" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="L115" s="19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M115" s="19" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="N115" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O115" s="21" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="P115" s="21" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="Q115" s="22" t="n">
         <v>6.65</v>
       </c>
-      <c r="H115" s="16" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="I115" s="17" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="J115" s="17" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="K115" s="18" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="L115" s="19" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="M115" s="19" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="N115" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O115" s="21" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="P115" s="21" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="Q115" s="22" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="R115" s="25" t="n">
-        <v>-0.61</v>
+      <c r="R115" s="23" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="116">
@@ -7764,54 +7764,54 @@
         </is>
       </c>
       <c r="C116" s="13" t="n">
-        <v>147.79</v>
+        <v>148.3</v>
       </c>
       <c r="D116" s="13" t="n">
-        <v>144.09</v>
+        <v>144.9</v>
       </c>
       <c r="E116" s="14" t="n">
-        <v>140.99</v>
+        <v>142.05</v>
       </c>
       <c r="F116" s="15" t="n">
-        <v>142.77</v>
+        <v>141.67</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>144.13</v>
+        <v>143.93</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>140.43</v>
+        <v>140.53</v>
       </c>
       <c r="I116" s="17" t="n">
-        <v>139.07</v>
+        <v>138.27</v>
       </c>
       <c r="J116" s="17" t="n">
-        <v>136.73</v>
+        <v>137.13</v>
       </c>
       <c r="K116" s="18" t="n">
-        <v>138.91</v>
+        <v>140.15</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>135.81</v>
+        <v>137.3</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>132.11</v>
-      </c>
-      <c r="N116" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>133.9</v>
+      </c>
+      <c r="N116" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>139.82</v>
+        <v>140.47</v>
       </c>
       <c r="P116" s="21" t="n">
-        <v>139.2</v>
+        <v>140.41</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>141.4</v>
-      </c>
-      <c r="R116" s="23" t="n">
-        <v>1.58</v>
+        <v>139.4</v>
+      </c>
+      <c r="R116" s="25" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="117">
@@ -7826,54 +7826,54 @@
         </is>
       </c>
       <c r="C117" s="13" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="D117" s="13" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="E117" s="14" t="n">
         <v>10.51</v>
       </c>
-      <c r="D117" s="13" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="E117" s="14" t="n">
-        <v>10.21</v>
-      </c>
       <c r="F117" s="15" t="n">
-        <v>10.24</v>
+        <v>10.64</v>
       </c>
       <c r="G117" s="15" t="n">
-        <v>10.32</v>
+        <v>10.79</v>
       </c>
       <c r="H117" s="16" t="n">
-        <v>10.16</v>
+        <v>10.43</v>
       </c>
       <c r="I117" s="17" t="n">
-        <v>10.08</v>
+        <v>10.28</v>
       </c>
       <c r="J117" s="17" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="K117" s="18" t="n">
-        <v>10.13</v>
+        <v>10.31</v>
       </c>
       <c r="L117" s="19" t="n">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="M117" s="19" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="N117" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>9.65</v>
+      </c>
+      <c r="N117" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O117" s="21" t="n">
-        <v>10.15</v>
+        <v>10.39</v>
       </c>
       <c r="P117" s="21" t="n">
-        <v>10.14</v>
+        <v>10.34</v>
       </c>
       <c r="Q117" s="22" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="R117" s="25" t="n">
-        <v>-0.29</v>
+        <v>10.48</v>
+      </c>
+      <c r="R117" s="23" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="118">
@@ -7888,54 +7888,54 @@
         </is>
       </c>
       <c r="C118" s="13" t="n">
-        <v>17.86</v>
+        <v>18.87</v>
       </c>
       <c r="D118" s="13" t="n">
-        <v>17.57</v>
+        <v>18.21</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>17.33</v>
+        <v>17.65</v>
       </c>
       <c r="F118" s="15" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="G118" s="15" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="H118" s="16" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="I118" s="17" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="J118" s="17" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="K118" s="18" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="L118" s="19" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="M118" s="19" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="N118" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O118" s="21" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="P118" s="21" t="n">
         <v>17.34</v>
       </c>
-      <c r="G118" s="15" t="n">
-        <v>17.51</v>
-      </c>
-      <c r="H118" s="16" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="I118" s="17" t="n">
-        <v>17.05</v>
-      </c>
-      <c r="J118" s="17" t="n">
-        <v>16.93</v>
-      </c>
-      <c r="K118" s="18" t="n">
-        <v>17.16</v>
-      </c>
-      <c r="L118" s="19" t="n">
-        <v>16.92</v>
-      </c>
-      <c r="M118" s="19" t="n">
-        <v>16.63</v>
-      </c>
-      <c r="N118" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O118" s="21" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="P118" s="21" t="n">
-        <v>17.19</v>
-      </c>
       <c r="Q118" s="22" t="n">
-        <v>17.17</v>
+        <v>17.5</v>
       </c>
       <c r="R118" s="23" t="n">
-        <v>1.36</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="119">
@@ -7950,37 +7950,37 @@
         </is>
       </c>
       <c r="C119" s="13" t="n">
-        <v>11.73</v>
+        <v>11.71</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>11.42</v>
+        <v>11.49</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>11.16</v>
+        <v>11.3</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>11.27</v>
+        <v>11.34</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>11.41</v>
+        <v>11.46</v>
       </c>
       <c r="H119" s="16" t="n">
-        <v>11.1</v>
+        <v>11.24</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>10.96</v>
+        <v>11.12</v>
       </c>
       <c r="J119" s="17" t="n">
-        <v>10.79</v>
+        <v>11.02</v>
       </c>
       <c r="K119" s="18" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="L119" s="19" t="n">
         <v>10.99</v>
       </c>
-      <c r="L119" s="19" t="n">
-        <v>10.73</v>
-      </c>
       <c r="M119" s="19" t="n">
-        <v>10.42</v>
+        <v>10.77</v>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
@@ -7988,16 +7988,16 @@
         </is>
       </c>
       <c r="O119" s="21" t="n">
-        <v>11.05</v>
+        <v>11.22</v>
       </c>
       <c r="P119" s="21" t="n">
-        <v>11.01</v>
+        <v>11.2</v>
       </c>
       <c r="Q119" s="22" t="n">
-        <v>11.14</v>
+        <v>11.23</v>
       </c>
       <c r="R119" s="23" t="n">
-        <v>1.83</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="120">
@@ -8012,37 +8012,37 @@
         </is>
       </c>
       <c r="C120" s="13" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="D120" s="13" t="n">
-        <v>12.68</v>
+        <v>12.71</v>
       </c>
       <c r="E120" s="14" t="n">
-        <v>12.5</v>
+        <v>12.55</v>
       </c>
       <c r="F120" s="15" t="n">
-        <v>12.52</v>
+        <v>12.61</v>
       </c>
       <c r="G120" s="15" t="n">
-        <v>12.64</v>
+        <v>12.7</v>
       </c>
       <c r="H120" s="16" t="n">
-        <v>12.43</v>
+        <v>12.51</v>
       </c>
       <c r="I120" s="17" t="n">
-        <v>12.31</v>
+        <v>12.42</v>
       </c>
       <c r="J120" s="17" t="n">
-        <v>12.22</v>
+        <v>12.32</v>
       </c>
       <c r="K120" s="18" t="n">
-        <v>12.39</v>
+        <v>12.44</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>12.21</v>
+        <v>12.28</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>12</v>
+        <v>12.09</v>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
@@ -8050,16 +8050,16 @@
         </is>
       </c>
       <c r="O120" s="21" t="n">
-        <v>12.42</v>
+        <v>12.48</v>
       </c>
       <c r="P120" s="21" t="n">
-        <v>12.4</v>
+        <v>12.46</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>12.4</v>
+        <v>12.53</v>
       </c>
       <c r="R120" s="23" t="n">
-        <v>0.4</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="121">
@@ -8074,37 +8074,37 @@
         </is>
       </c>
       <c r="C121" s="13" t="n">
-        <v>8.74</v>
+        <v>10.02</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>8.57</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="E121" s="14" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="F121" s="15" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="G121" s="15" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="H121" s="16" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="I121" s="17" t="n">
         <v>8.42</v>
       </c>
-      <c r="F121" s="15" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="G121" s="15" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="H121" s="16" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="I121" s="17" t="n">
-        <v>8.25</v>
-      </c>
       <c r="J121" s="17" t="n">
-        <v>8.18</v>
+        <v>8.08</v>
       </c>
       <c r="K121" s="18" t="n">
-        <v>8.33</v>
+        <v>8.51</v>
       </c>
       <c r="L121" s="19" t="n">
-        <v>8.18</v>
+        <v>7.98</v>
       </c>
       <c r="M121" s="19" t="n">
-        <v>8.01</v>
+        <v>7.35</v>
       </c>
       <c r="N121" s="20" t="inlineStr">
         <is>
@@ -8112,16 +8112,16 @@
         </is>
       </c>
       <c r="O121" s="21" t="n">
-        <v>8.35</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="P121" s="21" t="n">
-        <v>8.34</v>
+        <v>8.56</v>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>8.31</v>
+        <v>8.76</v>
       </c>
       <c r="R121" s="23" t="n">
-        <v>0.61</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="122">
@@ -8136,54 +8136,54 @@
         </is>
       </c>
       <c r="C122" s="13" t="n">
-        <v>8.220000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="D122" s="13" t="n">
-        <v>8.050000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="E122" s="14" t="n">
-        <v>7.9</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F122" s="15" t="n">
-        <v>7.94</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>8.02</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H122" s="16" t="n">
-        <v>7.85</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I122" s="17" t="n">
-        <v>7.77</v>
+        <v>7.89</v>
       </c>
       <c r="J122" s="17" t="n">
-        <v>7.68</v>
+        <v>7.58</v>
       </c>
       <c r="K122" s="18" t="n">
-        <v>7.81</v>
+        <v>7.96</v>
       </c>
       <c r="L122" s="19" t="n">
-        <v>7.66</v>
+        <v>7.49</v>
       </c>
       <c r="M122" s="19" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="N122" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>6.93</v>
+      </c>
+      <c r="N122" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O122" s="21" t="n">
-        <v>7.84</v>
+        <v>8.08</v>
       </c>
       <c r="P122" s="21" t="n">
-        <v>7.82</v>
+        <v>8.01</v>
       </c>
       <c r="Q122" s="22" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="R122" s="25" t="n">
-        <v>-0.88</v>
+        <v>8.19</v>
+      </c>
+      <c r="R122" s="23" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="123">
@@ -8198,54 +8198,54 @@
         </is>
       </c>
       <c r="C123" s="13" t="n">
-        <v>30.56</v>
+        <v>28.57</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>29.2</v>
+        <v>27.91</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>28.06</v>
+        <v>27.35</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>28.2</v>
+        <v>27.36</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>28.96</v>
+        <v>27.76</v>
       </c>
       <c r="H123" s="16" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="I123" s="17" t="n">
-        <v>26.84</v>
+        <v>26.7</v>
       </c>
       <c r="J123" s="17" t="n">
-        <v>26.24</v>
+        <v>26.44</v>
       </c>
       <c r="K123" s="18" t="n">
-        <v>27.3</v>
+        <v>26.99</v>
       </c>
       <c r="L123" s="19" t="n">
-        <v>26.16</v>
+        <v>26.43</v>
       </c>
       <c r="M123" s="19" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="N123" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>25.77</v>
+      </c>
+      <c r="N123" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O123" s="21" t="n">
-        <v>27.5</v>
+        <v>27.07</v>
       </c>
       <c r="P123" s="21" t="n">
-        <v>27.41</v>
+        <v>27.04</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>27.44</v>
-      </c>
-      <c r="R123" s="23" t="n">
-        <v>12.92</v>
+        <v>26.96</v>
+      </c>
+      <c r="R123" s="25" t="n">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="124">
@@ -8260,54 +8260,54 @@
         </is>
       </c>
       <c r="C124" s="13" t="n">
-        <v>174.12</v>
+        <v>175.64</v>
       </c>
       <c r="D124" s="13" t="n">
-        <v>170.52</v>
+        <v>171.04</v>
       </c>
       <c r="E124" s="14" t="n">
-        <v>167.51</v>
+        <v>167.19</v>
       </c>
       <c r="F124" s="15" t="n">
-        <v>169.5</v>
+        <v>167.07</v>
       </c>
       <c r="G124" s="15" t="n">
-        <v>170.7</v>
+        <v>169.93</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>167.1</v>
+        <v>165.33</v>
       </c>
       <c r="I124" s="17" t="n">
-        <v>165.9</v>
+        <v>162.47</v>
       </c>
       <c r="J124" s="17" t="n">
-        <v>163.5</v>
+        <v>160.73</v>
       </c>
       <c r="K124" s="18" t="n">
-        <v>165.49</v>
+        <v>164.61</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>162.48</v>
+        <v>160.76</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>158.88</v>
-      </c>
-      <c r="N124" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>156.16</v>
+      </c>
+      <c r="N124" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O124" s="21" t="n">
-        <v>166.44</v>
+        <v>165.15</v>
       </c>
       <c r="P124" s="21" t="n">
-        <v>165.77</v>
+        <v>164.97</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="R124" s="23" t="n">
-        <v>3</v>
+        <v>164.2</v>
+      </c>
+      <c r="R124" s="25" t="n">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="125">
@@ -8322,37 +8322,37 @@
         </is>
       </c>
       <c r="C125" s="13" t="n">
-        <v>55.99</v>
+        <v>56.21</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>55.04</v>
+        <v>55.31</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>54.24</v>
+        <v>54.55</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>54.6</v>
+        <v>54.85</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>55</v>
+        <v>55.25</v>
       </c>
       <c r="H125" s="16" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="I125" s="17" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="J125" s="17" t="n">
+        <v>53.45</v>
+      </c>
+      <c r="K125" s="18" t="n">
         <v>54.05</v>
       </c>
-      <c r="I125" s="17" t="n">
-        <v>53.65</v>
-      </c>
-      <c r="J125" s="17" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="K125" s="18" t="n">
-        <v>53.71</v>
-      </c>
       <c r="L125" s="19" t="n">
-        <v>52.91</v>
+        <v>53.29</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>51.96</v>
+        <v>52.39</v>
       </c>
       <c r="N125" s="20" t="inlineStr">
         <is>
@@ -8360,16 +8360,16 @@
         </is>
       </c>
       <c r="O125" s="21" t="n">
-        <v>53.92</v>
+        <v>54.23</v>
       </c>
       <c r="P125" s="21" t="n">
-        <v>53.78</v>
+        <v>54.12</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>54.2</v>
+        <v>54.45</v>
       </c>
       <c r="R125" s="23" t="n">
-        <v>1.31</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="126">
@@ -8384,54 +8384,54 @@
         </is>
       </c>
       <c r="C126" s="13" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="D126" s="13" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="E126" s="14" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="F126" s="15" t="n">
         <v>15.03</v>
       </c>
-      <c r="D126" s="13" t="n">
-        <v>14.81</v>
-      </c>
-      <c r="E126" s="14" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="F126" s="15" t="n">
-        <v>14.62</v>
-      </c>
       <c r="G126" s="15" t="n">
-        <v>14.75</v>
+        <v>15.27</v>
       </c>
       <c r="H126" s="16" t="n">
-        <v>14.53</v>
+        <v>14.76</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>14.4</v>
+        <v>14.52</v>
       </c>
       <c r="J126" s="17" t="n">
-        <v>14.31</v>
+        <v>14.25</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>14.5</v>
+        <v>14.59</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>14.31</v>
+        <v>14.16</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="N126" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>13.65</v>
+      </c>
+      <c r="N126" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O126" s="21" t="n">
-        <v>14.52</v>
+        <v>14.69</v>
       </c>
       <c r="P126" s="21" t="n">
-        <v>14.52</v>
+        <v>14.63</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>14.48</v>
+        <v>14.8</v>
       </c>
       <c r="R126" s="23" t="n">
-        <v>0.49</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="127">
@@ -8446,37 +8446,37 @@
         </is>
       </c>
       <c r="C127" s="13" t="n">
-        <v>15.04</v>
+        <v>15.4</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>14.86</v>
+        <v>15.05</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>14.71</v>
+        <v>14.75</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>14.71</v>
+        <v>14.87</v>
       </c>
       <c r="G127" s="15" t="n">
-        <v>14.82</v>
+        <v>15.03</v>
       </c>
       <c r="H127" s="16" t="n">
-        <v>14.64</v>
+        <v>14.68</v>
       </c>
       <c r="I127" s="17" t="n">
-        <v>14.53</v>
+        <v>14.52</v>
       </c>
       <c r="J127" s="17" t="n">
-        <v>14.46</v>
+        <v>14.33</v>
       </c>
       <c r="K127" s="18" t="n">
-        <v>14.61</v>
+        <v>14.56</v>
       </c>
       <c r="L127" s="19" t="n">
-        <v>14.46</v>
+        <v>14.26</v>
       </c>
       <c r="M127" s="19" t="n">
-        <v>14.28</v>
+        <v>13.91</v>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
@@ -8487,13 +8487,13 @@
         <v>14.63</v>
       </c>
       <c r="P127" s="21" t="n">
-        <v>14.62</v>
+        <v>14.58</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>14.6</v>
+        <v>14.72</v>
       </c>
       <c r="R127" s="23" t="n">
-        <v>1.25</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="128">
@@ -8508,37 +8508,37 @@
         </is>
       </c>
       <c r="C128" s="13" t="n">
-        <v>7.97</v>
+        <v>9.27</v>
       </c>
       <c r="D128" s="13" t="n">
-        <v>7.73</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E128" s="14" t="n">
-        <v>7.53</v>
+        <v>7.93</v>
       </c>
       <c r="F128" s="15" t="n">
-        <v>7.51</v>
+        <v>8.33</v>
       </c>
       <c r="G128" s="15" t="n">
-        <v>7.67</v>
+        <v>8.58</v>
       </c>
       <c r="H128" s="16" t="n">
-        <v>7.43</v>
+        <v>7.85</v>
       </c>
       <c r="I128" s="17" t="n">
-        <v>7.27</v>
+        <v>7.6</v>
       </c>
       <c r="J128" s="17" t="n">
-        <v>7.19</v>
+        <v>7.12</v>
       </c>
       <c r="K128" s="18" t="n">
-        <v>7.39</v>
+        <v>7.52</v>
       </c>
       <c r="L128" s="19" t="n">
-        <v>7.19</v>
+        <v>6.91</v>
       </c>
       <c r="M128" s="19" t="n">
-        <v>6.95</v>
+        <v>6.18</v>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
@@ -8546,16 +8546,16 @@
         </is>
       </c>
       <c r="O128" s="21" t="n">
-        <v>7.42</v>
+        <v>7.71</v>
       </c>
       <c r="P128" s="21" t="n">
-        <v>7.41</v>
+        <v>7.58</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>7.36</v>
+        <v>8.09</v>
       </c>
       <c r="R128" s="23" t="n">
-        <v>0.82</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="129">
@@ -8570,37 +8570,37 @@
         </is>
       </c>
       <c r="C129" s="13" t="n">
-        <v>11.59</v>
+        <v>12.51</v>
       </c>
       <c r="D129" s="13" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="E129" s="14" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F129" s="15" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="G129" s="15" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="H129" s="16" t="n">
         <v>10.89</v>
       </c>
-      <c r="E129" s="14" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="F129" s="15" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="G129" s="15" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="H129" s="16" t="n">
-        <v>10.13</v>
-      </c>
       <c r="I129" s="17" t="n">
-        <v>9.789999999999999</v>
+        <v>10.62</v>
       </c>
       <c r="J129" s="17" t="n">
-        <v>9.43</v>
+        <v>10.06</v>
       </c>
       <c r="K129" s="18" t="n">
-        <v>9.91</v>
+        <v>10.52</v>
       </c>
       <c r="L129" s="19" t="n">
-        <v>9.33</v>
+        <v>9.83</v>
       </c>
       <c r="M129" s="19" t="n">
-        <v>8.630000000000001</v>
+        <v>9</v>
       </c>
       <c r="N129" s="20" t="inlineStr">
         <is>
@@ -8608,16 +8608,16 @@
         </is>
       </c>
       <c r="O129" s="21" t="n">
-        <v>10.05</v>
+        <v>10.74</v>
       </c>
       <c r="P129" s="21" t="n">
-        <v>9.970000000000001</v>
+        <v>10.59</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>10.16</v>
+        <v>11.17</v>
       </c>
       <c r="R129" s="23" t="n">
-        <v>5.28</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="130">
@@ -8632,54 +8632,54 @@
         </is>
       </c>
       <c r="C130" s="13" t="n">
-        <v>161.18</v>
+        <v>149.3</v>
       </c>
       <c r="D130" s="13" t="n">
-        <v>151.18</v>
+        <v>145.9</v>
       </c>
       <c r="E130" s="14" t="n">
-        <v>142.8</v>
+        <v>143.05</v>
       </c>
       <c r="F130" s="15" t="n">
-        <v>147</v>
+        <v>143.07</v>
       </c>
       <c r="G130" s="15" t="n">
-        <v>151</v>
+        <v>145.13</v>
       </c>
       <c r="H130" s="16" t="n">
+        <v>141.73</v>
+      </c>
+      <c r="I130" s="17" t="n">
+        <v>139.67</v>
+      </c>
+      <c r="J130" s="17" t="n">
+        <v>138.33</v>
+      </c>
+      <c r="K130" s="18" t="n">
+        <v>141.15</v>
+      </c>
+      <c r="L130" s="19" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="M130" s="19" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="N130" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O130" s="21" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="P130" s="21" t="n">
+        <v>141.41</v>
+      </c>
+      <c r="Q130" s="22" t="n">
         <v>141</v>
       </c>
-      <c r="I130" s="17" t="n">
-        <v>137</v>
-      </c>
-      <c r="J130" s="17" t="n">
-        <v>131</v>
-      </c>
-      <c r="K130" s="18" t="n">
-        <v>137.2</v>
-      </c>
-      <c r="L130" s="19" t="n">
-        <v>128.82</v>
-      </c>
-      <c r="M130" s="19" t="n">
-        <v>118.82</v>
-      </c>
-      <c r="N130" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O130" s="21" t="n">
-        <v>139.49</v>
-      </c>
-      <c r="P130" s="21" t="n">
-        <v>137.98</v>
-      </c>
-      <c r="Q130" s="22" t="n">
-        <v>143</v>
-      </c>
-      <c r="R130" s="23" t="n">
-        <v>4.84</v>
+      <c r="R130" s="25" t="n">
+        <v>-1.4</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -3982,37 +3982,37 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>96.39</v>
+        <v>96.52</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>94.39</v>
+        <v>94.47</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>92.70999999999999</v>
+        <v>92.75</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>93.84999999999999</v>
+        <v>93.88</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>94.5</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>92.5</v>
+        <v>92.52</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>91.84999999999999</v>
+        <v>91.83</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>90.5</v>
+        <v>90.47</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>91.59</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>89.91</v>
+        <v>89.88</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>87.91</v>
+        <v>87.83</v>
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>92.12</v>
+        <v>92.14</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>91.75</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="Q55" s="22" t="n">
         <v>93.2</v>
@@ -4416,19 +4416,19 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>15.46</v>
+        <v>15.49</v>
       </c>
       <c r="D62" s="13" t="n">
-        <v>15.26</v>
+        <v>15.28</v>
       </c>
       <c r="E62" s="14" t="n">
         <v>15.1</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>15.14</v>
+        <v>15.15</v>
       </c>
       <c r="G62" s="15" t="n">
-        <v>15.24</v>
+        <v>15.25</v>
       </c>
       <c r="H62" s="16" t="n">
         <v>15.04</v>
@@ -4437,16 +4437,16 @@
         <v>14.94</v>
       </c>
       <c r="J62" s="17" t="n">
-        <v>14.84</v>
+        <v>14.83</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>14.98</v>
+        <v>14.99</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>14.82</v>
+        <v>14.81</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>14.62</v>
+        <v>14.6</v>
       </c>
       <c r="N62" s="20" t="inlineStr">
         <is>
@@ -5346,37 +5346,37 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>44.27</v>
+        <v>44.43</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>43.57</v>
+        <v>43.67</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>42.99</v>
+        <v>43.03</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>43.09</v>
+        <v>43.13</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>43.47</v>
+        <v>43.55</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>42.77</v>
+        <v>42.79</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>42.39</v>
+        <v>42.37</v>
       </c>
       <c r="J77" s="17" t="n">
-        <v>42.07</v>
+        <v>42.03</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>42.59</v>
+        <v>42.61</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>42.01</v>
+        <v>41.97</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>41.31</v>
+        <v>41.21</v>
       </c>
       <c r="N77" s="24" t="inlineStr">
         <is>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="O77" s="21" t="n">
-        <v>42.71</v>
+        <v>42.73</v>
       </c>
       <c r="P77" s="21" t="n">
-        <v>42.65</v>
+        <v>42.67</v>
       </c>
       <c r="Q77" s="22" t="n">
         <v>42.72</v>
@@ -6276,19 +6276,19 @@
         </is>
       </c>
       <c r="C92" s="13" t="n">
-        <v>22.17</v>
+        <v>22.2</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>21.71</v>
+        <v>21.73</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>21.33</v>
+        <v>21.34</v>
       </c>
       <c r="F92" s="15" t="n">
-        <v>21.48</v>
+        <v>21.49</v>
       </c>
       <c r="G92" s="15" t="n">
-        <v>21.69</v>
+        <v>21.7</v>
       </c>
       <c r="H92" s="16" t="n">
         <v>21.23</v>
@@ -6297,16 +6297,16 @@
         <v>21.02</v>
       </c>
       <c r="J92" s="17" t="n">
-        <v>20.77</v>
+        <v>20.76</v>
       </c>
       <c r="K92" s="18" t="n">
         <v>21.07</v>
       </c>
       <c r="L92" s="19" t="n">
-        <v>20.69</v>
+        <v>20.68</v>
       </c>
       <c r="M92" s="19" t="n">
-        <v>20.23</v>
+        <v>20.21</v>
       </c>
       <c r="N92" s="20" t="inlineStr">
         <is>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -36,11 +36,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
     </font>
   </fonts>
   <fills count="23">
@@ -137,7 +137,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +152,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -650,7 +650,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-08-26</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -758,54 +758,54 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>21.38</v>
+        <v>21.3</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>21.18</v>
+        <v>21.06</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>21.02</v>
+        <v>20.86</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>21.13</v>
+        <v>20.86</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>21.19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>20.99</v>
+        <v>20.76</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>20.93</v>
+        <v>20.62</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>20.79</v>
+        <v>20.52</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>20.9</v>
+        <v>20.72</v>
       </c>
       <c r="L3" s="19" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="M3" s="19" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="N3" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O3" s="21" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="P3" s="21" t="n">
         <v>20.74</v>
       </c>
-      <c r="M3" s="19" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="N3" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O3" s="21" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="P3" s="21" t="n">
-        <v>20.92</v>
-      </c>
       <c r="Q3" s="22" t="n">
-        <v>21.06</v>
+        <v>20.71</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="4">
@@ -820,54 +820,54 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>12.72</v>
+        <v>12.82</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>12.53</v>
+        <v>12.57</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>12.37</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>12.44</v>
+        <v>12.34</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>12.52</v>
+        <v>12.5</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>12.33</v>
+        <v>12.25</v>
       </c>
       <c r="I4" s="17" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="n">
         <v>12.25</v>
       </c>
-      <c r="J4" s="17" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="K4" s="18" t="n">
-        <v>12.26</v>
-      </c>
-      <c r="L4" s="19" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M4" s="19" t="n">
-        <v>11.91</v>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>12.3</v>
-      </c>
       <c r="P4" s="21" t="n">
-        <v>12.28</v>
+        <v>12.24</v>
       </c>
       <c r="Q4" s="22" t="n">
-        <v>12.36</v>
+        <v>12.17</v>
       </c>
       <c r="R4" s="23" t="n">
-        <v>0.9</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="5">
@@ -882,54 +882,54 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>14.65</v>
+        <v>15.93</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>14.56</v>
+        <v>15.34</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>14.48</v>
+        <v>14.85</v>
       </c>
       <c r="F5" s="15" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="K5" s="18" t="n">
         <v>14.52</v>
       </c>
-      <c r="G5" s="15" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="I5" s="17" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="J5" s="17" t="n">
-        <v>14.38</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>14.43</v>
-      </c>
       <c r="L5" s="19" t="n">
-        <v>14.35</v>
+        <v>14.03</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>14.26</v>
-      </c>
-      <c r="N5" s="20" t="inlineStr">
+        <v>13.44</v>
+      </c>
+      <c r="N5" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O5" s="21" t="n">
-        <v>14.45</v>
+        <v>14.6</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>14.44</v>
+        <v>14.57</v>
       </c>
       <c r="Q5" s="22" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="R5" s="23" t="n">
-        <v>0.35</v>
+        <v>14.55</v>
+      </c>
+      <c r="R5" s="25" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="6">
@@ -944,54 +944,54 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>23.39</v>
+        <v>23.12</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>22.72</v>
+        <v>22.47</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>22.16</v>
+        <v>21.93</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>22.31</v>
+        <v>22.07</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>22.65</v>
+        <v>22.4</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>21.98</v>
+        <v>21.75</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>21.64</v>
+        <v>21.42</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>21.31</v>
+        <v>21.1</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>21.79</v>
+        <v>21.56</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>21.23</v>
+        <v>21.02</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>20.56</v>
+        <v>20.37</v>
       </c>
       <c r="N6" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O6" s="21" t="n">
-        <v>21.91</v>
+        <v>21.68</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>21.84</v>
+        <v>21.61</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>21.98</v>
+        <v>21.75</v>
       </c>
       <c r="R6" s="23" t="n">
-        <v>0.59</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="7">
@@ -1006,54 +1006,54 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>35.39</v>
+        <v>35.2</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>34.95</v>
+        <v>34.74</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>34.58</v>
+        <v>34.36</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>34.64</v>
+        <v>34.43</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>34.88</v>
+        <v>34.67</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>34.44</v>
+        <v>34.21</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>34.2</v>
+        <v>33.97</v>
       </c>
       <c r="J7" s="17" t="n">
-        <v>34</v>
+        <v>33.75</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>34.34</v>
+        <v>34.1</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>33.97</v>
+        <v>33.72</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>33.53</v>
+        <v>33.26</v>
       </c>
       <c r="N7" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O7" s="21" t="n">
-        <v>34.41</v>
+        <v>34.18</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>34.37</v>
+        <v>34.14</v>
       </c>
       <c r="Q7" s="22" t="n">
-        <v>34.4</v>
+        <v>34.18</v>
       </c>
       <c r="R7" s="23" t="n">
-        <v>0.47</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="8">
@@ -1068,54 +1068,54 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>23.99</v>
+        <v>23.5</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>23.42</v>
+        <v>22.93</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>22.94</v>
+        <v>22.45</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>22.88</v>
+        <v>22.48</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>23.26</v>
+        <v>22.81</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>22.69</v>
+        <v>22.24</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>22.31</v>
+        <v>21.91</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>22.12</v>
+        <v>21.67</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>22.63</v>
+        <v>22.14</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>22.15</v>
+        <v>21.66</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>21.58</v>
-      </c>
-      <c r="N8" s="24" t="inlineStr">
+        <v>21.09</v>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O8" s="21" t="n">
-        <v>22.68</v>
+        <v>22.21</v>
       </c>
       <c r="P8" s="21" t="n">
-        <v>22.67</v>
+        <v>22.18</v>
       </c>
       <c r="Q8" s="22" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="R8" s="25" t="n">
-        <v>-1.32</v>
+        <v>22.14</v>
+      </c>
+      <c r="R8" s="23" t="n">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="9">
@@ -1130,54 +1130,54 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>149.5</v>
+        <v>143.05</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>141.9</v>
+        <v>139.25</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>135.53</v>
+        <v>136.06</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>138.27</v>
+        <v>137.7</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>141.53</v>
+        <v>139.2</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>133.93</v>
+        <v>135.4</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>130.67</v>
+        <v>133.9</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>126.33</v>
+        <v>131.6</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>131.27</v>
+        <v>133.94</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>124.9</v>
+        <v>130.75</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>117.3</v>
-      </c>
-      <c r="N9" s="20" t="inlineStr">
+        <v>126.95</v>
+      </c>
+      <c r="N9" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O9" s="21" t="n">
-        <v>132.9</v>
+        <v>134.82</v>
       </c>
       <c r="P9" s="21" t="n">
-        <v>131.86</v>
+        <v>134.23</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>135</v>
-      </c>
-      <c r="R9" s="23" t="n">
-        <v>3.85</v>
+        <v>136.2</v>
+      </c>
+      <c r="R9" s="25" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="10">
@@ -1192,54 +1192,54 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>71.09</v>
+        <v>70.17</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>70.14</v>
+        <v>69.17</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>69.34</v>
+        <v>68.33</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>69.5</v>
+        <v>68.38</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>70</v>
+        <v>68.97</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>69.05</v>
+        <v>67.97</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>68.55</v>
+        <v>67.38</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>68.09999999999999</v>
+        <v>66.97</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>68.81</v>
+        <v>67.77</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>68.01000000000001</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>67.06</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>68.97</v>
+        <v>67.91</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>68.88</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>69</v>
+        <v>67.8</v>
       </c>
       <c r="R10" s="23" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="11">
@@ -1254,54 +1254,54 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>27.32</v>
+        <v>27.07</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>26.8</v>
+        <v>26.63</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>26.37</v>
+        <v>26.26</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>26.8</v>
+        <v>26.5</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>26.28</v>
+        <v>26.06</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>26.08</v>
+        <v>25.76</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>25.76</v>
+        <v>25.62</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>26.07</v>
+        <v>26.02</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>25.64</v>
+        <v>25.65</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>25.12</v>
+        <v>25.21</v>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O11" s="21" t="n">
-        <v>26.2</v>
+        <v>26.06</v>
       </c>
       <c r="P11" s="21" t="n">
-        <v>26.11</v>
+        <v>26.05</v>
       </c>
       <c r="Q11" s="22" t="n">
-        <v>26.4</v>
+        <v>25.9</v>
       </c>
       <c r="R11" s="23" t="n">
-        <v>1.3</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="12">
@@ -1316,54 +1316,54 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>27.04</v>
+        <v>26.55</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>26.4</v>
+        <v>26.15</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>25.86</v>
+        <v>25.81</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>26.15</v>
+        <v>25.77</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>26.39</v>
+        <v>26.03</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>25.75</v>
+        <v>25.63</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>25.51</v>
+        <v>25.37</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>25.11</v>
+        <v>25.23</v>
       </c>
       <c r="K12" s="18" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="L12" s="19" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="M12" s="19" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O12" s="21" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="P12" s="21" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="Q12" s="22" t="n">
         <v>25.5</v>
       </c>
-      <c r="L12" s="19" t="n">
-        <v>24.96</v>
-      </c>
-      <c r="M12" s="19" t="n">
-        <v>24.32</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O12" s="21" t="n">
-        <v>25.65</v>
-      </c>
-      <c r="P12" s="21" t="n">
-        <v>25.55</v>
-      </c>
-      <c r="Q12" s="22" t="n">
-        <v>25.9</v>
-      </c>
       <c r="R12" s="23" t="n">
-        <v>1.89</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="13">
@@ -1378,54 +1378,54 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>44.39</v>
+        <v>44.73</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>43.79</v>
+        <v>43.91</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>43.29</v>
+        <v>43.22</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>43.61</v>
+        <v>43.33</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>43.81</v>
+        <v>43.77</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>43.21</v>
+        <v>42.95</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>43.01</v>
+        <v>42.51</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>42.61</v>
+        <v>42.13</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>42.95</v>
+        <v>42.76</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>42.45</v>
+        <v>42.07</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>41.85</v>
+        <v>41.25</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O13" s="21" t="n">
-        <v>43.11</v>
+        <v>42.89</v>
       </c>
       <c r="P13" s="21" t="n">
-        <v>43</v>
+        <v>42.82</v>
       </c>
       <c r="Q13" s="22" t="n">
-        <v>43.4</v>
+        <v>42.88</v>
       </c>
       <c r="R13" s="23" t="n">
-        <v>0.88</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="14">
@@ -1440,41 +1440,41 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>9.06</v>
+        <v>9.16</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>8.99</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>8.93</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>8.949999999999999</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>8.99</v>
+        <v>9.02</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>8.92</v>
+        <v>8.91</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>8.880000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="J14" s="17" t="n">
-        <v>8.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>8.77</v>
+        <v>8.69</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O14" s="21" t="n">
@@ -1484,10 +1484,10 @@
         <v>8.9</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>8.92</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="R14" s="23" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="15">
@@ -1502,54 +1502,54 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>15.01</v>
+        <v>14.84</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>14.81</v>
+        <v>14.68</v>
       </c>
       <c r="E15" s="14" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="G15" s="15" t="n">
         <v>14.65</v>
       </c>
-      <c r="F15" s="15" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>14.78</v>
-      </c>
       <c r="H15" s="16" t="n">
-        <v>14.58</v>
+        <v>14.49</v>
       </c>
       <c r="I15" s="17" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="K15" s="18" t="n">
         <v>14.46</v>
       </c>
-      <c r="J15" s="17" t="n">
-        <v>14.38</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>14.53</v>
-      </c>
       <c r="L15" s="19" t="n">
-        <v>14.37</v>
+        <v>14.32</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>14.17</v>
+        <v>14.16</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O15" s="21" t="n">
-        <v>14.56</v>
+        <v>14.48</v>
       </c>
       <c r="P15" s="21" t="n">
-        <v>14.55</v>
+        <v>14.47</v>
       </c>
       <c r="Q15" s="22" t="n">
-        <v>14.55</v>
+        <v>14.46</v>
       </c>
       <c r="R15" s="23" t="n">
-        <v>0.48</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="16">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
       <c r="D16" s="13" t="n">
         <v>4.91</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4.9</v>
+        <v>4.89</v>
       </c>
       <c r="H16" s="16" t="n">
         <v>4.82</v>
@@ -1585,33 +1585,33 @@
         <v>4.78</v>
       </c>
       <c r="J16" s="17" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="K16" s="18" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="L16" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="M16" s="19" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O16" s="21" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="P16" s="21" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="Q16" s="22" t="n">
         <v>4.8</v>
       </c>
-      <c r="L16" s="19" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="N16" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O16" s="21" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="P16" s="21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q16" s="22" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="R16" s="25" t="n">
-        <v>-0.21</v>
+      <c r="R16" s="23" t="n">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="17">
@@ -1626,54 +1626,54 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>19.66</v>
+        <v>19.78</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>19.28</v>
+        <v>19.49</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>18.97</v>
+        <v>19.25</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>19.1</v>
+        <v>19.24</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>19.26</v>
+        <v>19.42</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>18.88</v>
+        <v>19.13</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>18.72</v>
+        <v>18.95</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>18.5</v>
+        <v>18.84</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>18.75</v>
+        <v>19.08</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>18.44</v>
+        <v>18.84</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
+        <v>18.55</v>
+      </c>
+      <c r="N17" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O17" s="21" t="n">
-        <v>18.83</v>
+        <v>19.12</v>
       </c>
       <c r="P17" s="21" t="n">
-        <v>18.78</v>
+        <v>19.11</v>
       </c>
       <c r="Q17" s="22" t="n">
-        <v>18.93</v>
-      </c>
-      <c r="R17" s="23" t="n">
-        <v>1.28</v>
+        <v>19.06</v>
+      </c>
+      <c r="R17" s="25" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="18">
@@ -1688,54 +1688,54 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>25.97</v>
+        <v>25.79</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>25.67</v>
+        <v>25.51</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>25.41</v>
+        <v>25.28</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>25.43</v>
+        <v>25.3</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>25.61</v>
+        <v>25.46</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>25.31</v>
+        <v>25.18</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>25.13</v>
+        <v>25.02</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>25.01</v>
+        <v>24.9</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>25.25</v>
+        <v>25.12</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>24.99</v>
+        <v>24.89</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="N18" s="24" t="inlineStr">
+        <v>24.61</v>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O18" s="21" t="n">
-        <v>25.29</v>
+        <v>25.16</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>25.27</v>
+        <v>25.14</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>25.26</v>
-      </c>
-      <c r="R18" s="25" t="n">
-        <v>-0.08</v>
+        <v>25.14</v>
+      </c>
+      <c r="R18" s="23" t="n">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="19">
@@ -1750,54 +1750,54 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>72.75</v>
+        <v>72.53</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>71.45</v>
+        <v>70.38</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>70.36</v>
+        <v>68.58</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>70.92</v>
+        <v>68.67</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>71.43000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>70.13</v>
+        <v>67.78</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>69.62</v>
+        <v>66.52</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>68.83</v>
+        <v>65.63</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>69.64</v>
+        <v>67.37</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>68.55</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>67.25</v>
+        <v>63.42</v>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O19" s="21" t="n">
-        <v>69.94</v>
+        <v>67.66</v>
       </c>
       <c r="P19" s="21" t="n">
-        <v>69.73999999999999</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="Q19" s="22" t="n">
-        <v>70.40000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>1.29</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="20">
@@ -1812,54 +1812,54 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>12.33</v>
+        <v>12.8</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>12.16</v>
+        <v>12.55</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>12.01</v>
+        <v>12.34</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>12.06</v>
+        <v>12.36</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>12.14</v>
+        <v>12.5</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>11.97</v>
+        <v>12.25</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>11.89</v>
+        <v>12.11</v>
       </c>
       <c r="J20" s="17" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>11.92</v>
+        <v>12.2</v>
       </c>
       <c r="L20" s="19" t="n">
-        <v>11.77</v>
+        <v>12</v>
       </c>
       <c r="M20" s="19" t="n">
-        <v>11.6</v>
+        <v>11.75</v>
       </c>
       <c r="N20" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O20" s="21" t="n">
-        <v>11.95</v>
+        <v>12.24</v>
       </c>
       <c r="P20" s="21" t="n">
-        <v>11.93</v>
+        <v>12.22</v>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>11.98</v>
-      </c>
-      <c r="R20" s="23" t="n">
-        <v>0.17</v>
+        <v>12.21</v>
+      </c>
+      <c r="R20" s="25" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="21">
@@ -1874,54 +1874,54 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>20.45</v>
+        <v>19.39</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>19.86</v>
+        <v>19.11</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>19.37</v>
+        <v>18.88</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>19.39</v>
+        <v>18.92</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>19.74</v>
+        <v>19.07</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>19.15</v>
+        <v>18.79</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>18.8</v>
+        <v>18.64</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>18.56</v>
+        <v>18.51</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>19.04</v>
+        <v>18.72</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>18.55</v>
+        <v>18.49</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="N21" s="24" t="inlineStr">
+        <v>18.21</v>
+      </c>
+      <c r="N21" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O21" s="21" t="n">
-        <v>19.12</v>
+        <v>18.77</v>
       </c>
       <c r="P21" s="21" t="n">
-        <v>19.09</v>
+        <v>18.74</v>
       </c>
       <c r="Q21" s="22" t="n">
-        <v>19.04</v>
-      </c>
-      <c r="R21" s="25" t="n">
-        <v>-1.45</v>
+        <v>18.77</v>
+      </c>
+      <c r="R21" s="23" t="n">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="22">
@@ -1936,54 +1936,54 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>36.87</v>
+        <v>41.55</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>36.21</v>
+        <v>39.43</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>35.65</v>
+        <v>37.65</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>35.89</v>
+        <v>38.77</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>36.17</v>
+        <v>39.51</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>35.51</v>
+        <v>37.39</v>
       </c>
       <c r="I22" s="17" t="n">
-        <v>35.23</v>
+        <v>36.65</v>
       </c>
       <c r="J22" s="17" t="n">
-        <v>34.85</v>
+        <v>35.27</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>35.29</v>
+        <v>36.47</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>34.73</v>
+        <v>34.69</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="N22" s="20" t="inlineStr">
+        <v>32.57</v>
+      </c>
+      <c r="N22" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O22" s="21" t="n">
-        <v>35.43</v>
+        <v>37.01</v>
       </c>
       <c r="P22" s="21" t="n">
-        <v>35.34</v>
+        <v>36.63</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="R22" s="23" t="n">
-        <v>1.31</v>
+        <v>38.04</v>
+      </c>
+      <c r="R22" s="25" t="n">
+        <v>5.84</v>
       </c>
     </row>
     <row r="23">
@@ -1998,54 +1998,54 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>16.54</v>
+        <v>16.08</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>16.02</v>
+        <v>15.84</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>15.59</v>
+        <v>15.64</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>15.73</v>
+        <v>15.72</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>15.97</v>
+        <v>15.82</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>15.45</v>
+        <v>15.58</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>15.21</v>
+        <v>15.48</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>14.93</v>
+        <v>15.34</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>15.29</v>
+        <v>15.5</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>14.86</v>
+        <v>15.3</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="N23" s="20" t="inlineStr">
+        <v>15.06</v>
+      </c>
+      <c r="N23" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O23" s="21" t="n">
-        <v>15.39</v>
+        <v>15.55</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>15.33</v>
+        <v>15.52</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>15.48</v>
-      </c>
-      <c r="R23" s="23" t="n">
-        <v>0.65</v>
+        <v>15.61</v>
+      </c>
+      <c r="R23" s="25" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="24">
@@ -2060,54 +2060,54 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>39.34</v>
+        <v>39.98</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>38.5</v>
+        <v>39.04</v>
       </c>
       <c r="E24" s="14" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>37.96</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>37.46</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="L24" s="19" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="M24" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="N24" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O24" s="21" t="n">
+        <v>37.88</v>
+      </c>
+      <c r="P24" s="21" t="n">
         <v>37.8</v>
       </c>
-      <c r="F24" s="15" t="n">
-        <v>38.07</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>38.45</v>
-      </c>
-      <c r="H24" s="16" t="n">
-        <v>37.61</v>
-      </c>
-      <c r="I24" s="17" t="n">
-        <v>37.23</v>
-      </c>
-      <c r="J24" s="17" t="n">
-        <v>36.77</v>
-      </c>
-      <c r="K24" s="18" t="n">
-        <v>37.32</v>
-      </c>
-      <c r="L24" s="19" t="n">
-        <v>36.62</v>
-      </c>
-      <c r="M24" s="19" t="n">
-        <v>35.78</v>
-      </c>
-      <c r="N24" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O24" s="21" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="P24" s="21" t="n">
-        <v>37.39</v>
-      </c>
       <c r="Q24" s="22" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="R24" s="23" t="n">
-        <v>0.91</v>
+        <v>37.9</v>
+      </c>
+      <c r="R24" s="25" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="25">
@@ -2122,54 +2122,54 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>57.41</v>
+        <v>55.01</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>54.22</v>
+        <v>53.46</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>51.55</v>
+        <v>52.16</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>52.95</v>
+        <v>52.28</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>54.19</v>
+        <v>53.17</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>51</v>
+        <v>51.62</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>49.76</v>
+        <v>50.73</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>47.81</v>
+        <v>50.07</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>49.76</v>
+        <v>51.29</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>47.09</v>
+        <v>49.99</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>43.9</v>
+        <v>48.44</v>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O25" s="21" t="n">
-        <v>50.51</v>
+        <v>51.51</v>
       </c>
       <c r="P25" s="21" t="n">
-        <v>50.01</v>
+        <v>51.41</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="R25" s="23" t="n">
-        <v>5.42</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="26">
@@ -2184,54 +2184,54 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>199.39</v>
+        <v>195.42</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>194.39</v>
+        <v>191.82</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>190.2</v>
+        <v>188.81</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>191.1</v>
+        <v>188.87</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>193.7</v>
+        <v>191.03</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>188.7</v>
+        <v>187.43</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>186.1</v>
+        <v>185.27</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>183.7</v>
+        <v>183.83</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>187.4</v>
+        <v>186.79</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>183.21</v>
+        <v>183.78</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>178.21</v>
-      </c>
-      <c r="N26" s="24" t="inlineStr">
+        <v>180.18</v>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O26" s="21" t="n">
-        <v>188.25</v>
+        <v>187.25</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>187.79</v>
+        <v>187.07</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>188.5</v>
-      </c>
-      <c r="R26" s="25" t="n">
-        <v>-0.79</v>
+        <v>186.7</v>
+      </c>
+      <c r="R26" s="23" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="27">
@@ -2246,54 +2246,54 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>92.40000000000001</v>
+        <v>91.37</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>90.3</v>
+        <v>88.67</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>88.54000000000001</v>
+        <v>86.41</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>89.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>90.2</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>88.09999999999999</v>
+        <v>85.45</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>87.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>86</v>
+        <v>82.75</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>87.36</v>
+        <v>84.89</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>85.59999999999999</v>
+        <v>82.63</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="N27" s="24" t="inlineStr">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="N27" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O27" s="21" t="n">
-        <v>87.81</v>
+        <v>85.28</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>87.53</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>88.40000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="R27" s="23" t="n">
-        <v>0.23</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="28">
@@ -2308,54 +2308,54 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>22</v>
+        <v>22.61</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>21.69</v>
+        <v>22.07</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>21.43</v>
+        <v>21.62</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>21.41</v>
+        <v>21.6</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>21.61</v>
+        <v>21.94</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>21.1</v>
+        <v>21.06</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>20.99</v>
+        <v>20.86</v>
       </c>
       <c r="K28" s="18" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="L28" s="19" t="n">
+        <v>20.87</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="N28" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="Q28" s="22" t="n">
         <v>21.26</v>
       </c>
-      <c r="L28" s="19" t="n">
-        <v>21</v>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="N28" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O28" s="21" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="Q28" s="22" t="n">
-        <v>21.21</v>
-      </c>
-      <c r="R28" s="25" t="n">
-        <v>-0.93</v>
+      <c r="R28" s="23" t="n">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="29">
@@ -2370,54 +2370,54 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>84.43000000000001</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>82.93000000000001</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>81.67</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>82.47</v>
+        <v>80.62</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>82.98</v>
+        <v>81.73</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>81.48</v>
+        <v>79.98</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>80.97</v>
+        <v>78.87</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>79.98</v>
+        <v>78.23</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>80.83</v>
+        <v>79.73</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>79.56999999999999</v>
+        <v>78.27</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>78.06999999999999</v>
+        <v>76.52</v>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O29" s="21" t="n">
-        <v>81.22</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>80.95</v>
+        <v>79.87</v>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>81.95</v>
+        <v>79.5</v>
       </c>
       <c r="R29" s="23" t="n">
-        <v>1.61</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="30">
@@ -2432,54 +2432,54 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>33.6</v>
+        <v>32.92</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>32.82</v>
+        <v>32.04</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>32.17</v>
+        <v>31.31</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>32.37</v>
+        <v>31.39</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>32.75</v>
+        <v>31.89</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>31.97</v>
+        <v>31.01</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>31.59</v>
+        <v>30.51</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>31.19</v>
+        <v>30.13</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>31.73</v>
+        <v>30.81</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>31.08</v>
+        <v>30.08</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="N30" s="24" t="inlineStr">
+        <v>29.2</v>
+      </c>
+      <c r="N30" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O30" s="21" t="n">
-        <v>31.88</v>
+        <v>30.94</v>
       </c>
       <c r="P30" s="21" t="n">
-        <v>31.79</v>
+        <v>30.88</v>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>32</v>
+        <v>30.9</v>
       </c>
       <c r="R30" s="23" t="n">
-        <v>0.31</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="31">
@@ -2494,54 +2494,54 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>51.07</v>
+        <v>50.67</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>50.72</v>
+        <v>50.47</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>50.42</v>
+        <v>50.31</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>50.52</v>
+        <v>50.38</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>50.68</v>
+        <v>50.47</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>50.33</v>
+        <v>50.27</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>50.17</v>
+        <v>50.18</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>49.98</v>
+        <v>50.07</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>50.23</v>
+        <v>50.19</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>49.93</v>
+        <v>50.03</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>49.58</v>
+        <v>49.83</v>
       </c>
       <c r="N31" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O31" s="21" t="n">
-        <v>50.29</v>
+        <v>50.24</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>50.25</v>
+        <v>50.21</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>50.35</v>
-      </c>
-      <c r="R31" s="23" t="n">
-        <v>0.1</v>
+        <v>50.3</v>
+      </c>
+      <c r="R31" s="25" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="32">
@@ -2556,54 +2556,54 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>133.53</v>
+        <v>134.57</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>132.03</v>
+        <v>132.67</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>130.77</v>
+        <v>131.08</v>
       </c>
       <c r="F32" s="15" t="n">
         <v>130.87</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>131.73</v>
+        <v>132.13</v>
       </c>
       <c r="H32" s="16" t="n">
         <v>130.23</v>
       </c>
       <c r="I32" s="17" t="n">
-        <v>129.37</v>
+        <v>128.97</v>
       </c>
       <c r="J32" s="17" t="n">
-        <v>128.73</v>
+        <v>128.33</v>
       </c>
       <c r="K32" s="18" t="n">
-        <v>129.93</v>
+        <v>130.02</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>128.67</v>
+        <v>128.43</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>127.17</v>
+        <v>126.53</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O32" s="21" t="n">
-        <v>130.14</v>
+        <v>130.2</v>
       </c>
       <c r="P32" s="21" t="n">
-        <v>130.05</v>
+        <v>130.17</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>130</v>
+        <v>129.6</v>
       </c>
       <c r="R32" s="23" t="n">
-        <v>0.15</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2618,54 +2618,54 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>55.02</v>
+        <v>53.08</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>53.12</v>
+        <v>52.23</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>51.53</v>
+        <v>51.51</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>51.72</v>
+        <v>51.58</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>52.78</v>
+        <v>52.07</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>50.88</v>
+        <v>51.22</v>
       </c>
       <c r="I33" s="17" t="n">
-        <v>49.82</v>
+        <v>50.73</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>48.98</v>
+        <v>50.37</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>50.47</v>
+        <v>51.04</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>48.88</v>
+        <v>50.32</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>46.98</v>
+        <v>49.47</v>
       </c>
       <c r="N33" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O33" s="21" t="n">
-        <v>50.75</v>
+        <v>51.16</v>
       </c>
       <c r="P33" s="21" t="n">
-        <v>50.62</v>
+        <v>51.1</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>50.65</v>
-      </c>
-      <c r="R33" s="23" t="n">
-        <v>0.8</v>
+        <v>51.1</v>
+      </c>
+      <c r="R33" s="25" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="34">
@@ -2680,54 +2680,54 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
+        <v>26.79</v>
+      </c>
+      <c r="D34" s="13" t="n">
         <v>26.41</v>
       </c>
-      <c r="D34" s="13" t="n">
-        <v>26.17</v>
-      </c>
       <c r="E34" s="14" t="n">
-        <v>25.97</v>
+        <v>26.1</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>25.97</v>
+        <v>26.07</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>26.11</v>
+        <v>26.31</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>25.87</v>
+        <v>25.93</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>25.73</v>
+        <v>25.69</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>25.63</v>
+        <v>25.55</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>25.83</v>
+        <v>25.88</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>25.63</v>
+        <v>25.57</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>25.39</v>
-      </c>
-      <c r="N34" s="24" t="inlineStr">
+        <v>25.19</v>
+      </c>
+      <c r="N34" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O34" s="21" t="n">
-        <v>25.86</v>
+        <v>25.92</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>25.85</v>
+        <v>25.91</v>
       </c>
       <c r="Q34" s="22" t="n">
         <v>25.82</v>
       </c>
-      <c r="R34" s="25" t="n">
-        <v>-0.54</v>
+      <c r="R34" s="23" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="35">
@@ -2742,54 +2742,54 @@
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>26.79</v>
+        <v>27.69</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>26.45</v>
+        <v>26.99</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>26.17</v>
+        <v>26.41</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>26.31</v>
+        <v>26.35</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>26.45</v>
+        <v>26.81</v>
       </c>
       <c r="H35" s="16" t="n">
         <v>26.11</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>25.97</v>
+        <v>25.65</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>25.77</v>
+        <v>25.41</v>
       </c>
       <c r="K35" s="18" t="n">
-        <v>25.97</v>
+        <v>26.01</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>25.69</v>
+        <v>25.43</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>25.35</v>
+        <v>24.73</v>
       </c>
       <c r="N35" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O35" s="21" t="n">
-        <v>26.05</v>
+        <v>26.09</v>
       </c>
       <c r="P35" s="21" t="n">
-        <v>26</v>
+        <v>26.07</v>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>26.18</v>
+        <v>25.9</v>
       </c>
       <c r="R35" s="23" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="36">
@@ -2804,54 +2804,54 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>10.35</v>
+        <v>10.5</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>9.949999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>9.609999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>9.57</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>9.43</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="I36" s="17" t="n">
-        <v>9.17</v>
+        <v>8.93</v>
       </c>
       <c r="J36" s="17" t="n">
-        <v>9.029999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="K36" s="18" t="n">
-        <v>9.390000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>9.050000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>8.65</v>
-      </c>
-      <c r="N36" s="24" t="inlineStr">
+        <v>8.25</v>
+      </c>
+      <c r="N36" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O36" s="21" t="n">
-        <v>9.43</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="P36" s="21" t="n">
-        <v>9.42</v>
+        <v>9.27</v>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="R36" s="25" t="n">
-        <v>-2.21</v>
+        <v>9.109999999999999</v>
+      </c>
+      <c r="R36" s="23" t="n">
+        <v>-3.8</v>
       </c>
     </row>
     <row r="37">
@@ -2866,54 +2866,54 @@
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>31.9</v>
+        <v>31.36</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>31.44</v>
+        <v>31.1</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>31.06</v>
+        <v>30.88</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>31.23</v>
+        <v>30.91</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>31.43</v>
+        <v>31.05</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>30.97</v>
+        <v>30.79</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>30.77</v>
+        <v>30.65</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>30.51</v>
+        <v>30.53</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>30.8</v>
+        <v>30.74</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>30.42</v>
+        <v>30.52</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="N37" s="24" t="inlineStr">
+        <v>30.26</v>
+      </c>
+      <c r="N37" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O37" s="21" t="n">
-        <v>30.9</v>
+        <v>30.78</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>30.84</v>
+        <v>30.76</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>31.04</v>
+        <v>30.76</v>
       </c>
       <c r="R37" s="23" t="n">
-        <v>0.13</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="38">
@@ -2928,54 +2928,54 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>203.56</v>
+        <v>201.22</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>200.06</v>
+        <v>198.12</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>197.13</v>
+        <v>195.52</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>198.33</v>
+        <v>195.3</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>199.87</v>
+        <v>197.3</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>196.37</v>
+        <v>194.2</v>
       </c>
       <c r="I38" s="17" t="n">
-        <v>194.83</v>
+        <v>192.2</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>192.87</v>
+        <v>191.1</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>195.17</v>
+        <v>193.78</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>192.24</v>
+        <v>191.18</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>188.74</v>
+        <v>188.08</v>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O38" s="21" t="n">
-        <v>195.9</v>
+        <v>194.11</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>195.44</v>
+        <v>194.02</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>196.8</v>
-      </c>
-      <c r="R38" s="25" t="n">
-        <v>-0.3</v>
+        <v>193.3</v>
+      </c>
+      <c r="R38" s="23" t="n">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="39">
@@ -2990,54 +2990,54 @@
         </is>
       </c>
       <c r="C39" s="13" t="n">
-        <v>14.12</v>
+        <v>14.26</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>13.92</v>
+        <v>13.97</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>13.76</v>
+        <v>13.73</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>13.79</v>
+        <v>13.69</v>
       </c>
       <c r="G39" s="15" t="n">
         <v>13.89</v>
       </c>
       <c r="H39" s="16" t="n">
-        <v>13.69</v>
+        <v>13.6</v>
       </c>
       <c r="I39" s="17" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="K39" s="18" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="L39" s="19" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="M39" s="19" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="N39" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O39" s="21" t="n">
         <v>13.59</v>
       </c>
-      <c r="J39" s="17" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="K39" s="18" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="L39" s="19" t="n">
-        <v>13.48</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>13.28</v>
-      </c>
-      <c r="N39" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O39" s="21" t="n">
-        <v>13.68</v>
-      </c>
       <c r="P39" s="21" t="n">
-        <v>13.66</v>
+        <v>13.59</v>
       </c>
       <c r="Q39" s="22" t="n">
-        <v>13.68</v>
+        <v>13.5</v>
       </c>
       <c r="R39" s="23" t="n">
-        <v>0.51</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="40">
@@ -3052,54 +3052,54 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>21.77</v>
+        <v>23.49</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>21.52</v>
+        <v>22.69</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>21.32</v>
+        <v>22.02</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>21.31</v>
+        <v>22.33</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>21.47</v>
+        <v>22.67</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>21.22</v>
+        <v>21.87</v>
       </c>
       <c r="I40" s="17" t="n">
-        <v>21.06</v>
+        <v>21.53</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>20.97</v>
+        <v>21.07</v>
       </c>
       <c r="K40" s="18" t="n">
-        <v>21.18</v>
+        <v>21.58</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>20.97</v>
+        <v>20.91</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>20.72</v>
+        <v>20.11</v>
       </c>
       <c r="N40" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O40" s="21" t="n">
-        <v>21.21</v>
+        <v>21.75</v>
       </c>
       <c r="P40" s="21" t="n">
-        <v>21.19</v>
+        <v>21.64</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>21.16</v>
+        <v>22</v>
       </c>
       <c r="R40" s="25" t="n">
-        <v>-0.52</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="41">
@@ -3114,54 +3114,54 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>189.74</v>
+        <v>182.17</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>184.34</v>
+        <v>179.47</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>179.81</v>
+        <v>177.21</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>179.47</v>
+        <v>176.97</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>182.93</v>
+        <v>178.73</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>177.53</v>
+        <v>176.03</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>174.07</v>
+        <v>174.27</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>172.13</v>
+        <v>173.33</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>176.79</v>
+        <v>175.69</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>172.26</v>
+        <v>173.43</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>166.86</v>
-      </c>
-      <c r="N41" s="24" t="inlineStr">
+        <v>170.73</v>
+      </c>
+      <c r="N41" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O41" s="21" t="n">
-        <v>177.37</v>
+        <v>175.97</v>
       </c>
       <c r="P41" s="21" t="n">
-        <v>177.21</v>
+        <v>175.9</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>176</v>
-      </c>
-      <c r="R41" s="25" t="n">
-        <v>-1.79</v>
+        <v>175.2</v>
+      </c>
+      <c r="R41" s="23" t="n">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="42">
@@ -3176,54 +3176,54 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>40.84</v>
+        <v>39.93</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>40.06</v>
+        <v>39.59</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>39.41</v>
+        <v>39.31</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>39.81</v>
+        <v>39.31</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>40.09</v>
+        <v>39.51</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>39.31</v>
+        <v>39.17</v>
       </c>
       <c r="I42" s="17" t="n">
-        <v>39.03</v>
+        <v>38.97</v>
       </c>
       <c r="J42" s="17" t="n">
-        <v>38.53</v>
+        <v>38.83</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>38.97</v>
+        <v>39.11</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>38.32</v>
+        <v>38.83</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>37.54</v>
+        <v>38.49</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O42" s="21" t="n">
-        <v>39.17</v>
+        <v>39.16</v>
       </c>
       <c r="P42" s="21" t="n">
-        <v>39.03</v>
+        <v>39.14</v>
       </c>
       <c r="Q42" s="22" t="n">
-        <v>39.54</v>
+        <v>39.1</v>
       </c>
       <c r="R42" s="23" t="n">
-        <v>1.13</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="43">
@@ -3238,54 +3238,54 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>29.15</v>
+        <v>28.16</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>28.49</v>
+        <v>27.84</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>27.93</v>
+        <v>27.57</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>27.94</v>
+        <v>27.59</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>28.34</v>
+        <v>27.77</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>27.68</v>
+        <v>27.45</v>
       </c>
       <c r="I43" s="17" t="n">
-        <v>27.28</v>
+        <v>27.27</v>
       </c>
       <c r="J43" s="17" t="n">
-        <v>27.02</v>
+        <v>27.13</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>27.57</v>
+        <v>27.39</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>27.01</v>
+        <v>27.12</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>26.35</v>
-      </c>
-      <c r="N43" s="24" t="inlineStr">
+        <v>26.8</v>
+      </c>
+      <c r="N43" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O43" s="21" t="n">
-        <v>27.65</v>
+        <v>27.43</v>
       </c>
       <c r="P43" s="21" t="n">
-        <v>27.62</v>
+        <v>27.42</v>
       </c>
       <c r="Q43" s="22" t="n">
-        <v>27.54</v>
-      </c>
-      <c r="R43" s="25" t="n">
-        <v>-1.43</v>
+        <v>27.4</v>
+      </c>
+      <c r="R43" s="23" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="44">
@@ -3300,54 +3300,54 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>26.67</v>
+        <v>26.41</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>26.43</v>
+        <v>26.27</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>26.23</v>
+        <v>26.15</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>26.24</v>
+        <v>26.2</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>26.38</v>
+        <v>26.26</v>
       </c>
       <c r="H44" s="16" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="J44" s="17" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="K44" s="18" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="L44" s="19" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="N44" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O44" s="21" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="P44" s="21" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="Q44" s="22" t="n">
         <v>26.14</v>
       </c>
-      <c r="I44" s="17" t="n">
-        <v>26</v>
-      </c>
-      <c r="J44" s="17" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="K44" s="18" t="n">
-        <v>26.09</v>
-      </c>
-      <c r="L44" s="19" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="M44" s="19" t="n">
-        <v>25.65</v>
-      </c>
-      <c r="N44" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O44" s="21" t="n">
-        <v>26.13</v>
-      </c>
-      <c r="P44" s="21" t="n">
-        <v>26.11</v>
-      </c>
-      <c r="Q44" s="22" t="n">
-        <v>26.1</v>
-      </c>
       <c r="R44" s="25" t="n">
-        <v>-0.68</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="45">
@@ -3362,54 +3362,54 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>8.02</v>
+        <v>8</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>7.94</v>
+        <v>7.92</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>7.87</v>
+        <v>7.85</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>7.91</v>
+        <v>7.88</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>7.94</v>
+        <v>7.92</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>7.86</v>
+        <v>7.84</v>
       </c>
       <c r="I45" s="17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J45" s="17" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="K45" s="18" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="L45" s="19" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="M45" s="19" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="N45" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O45" s="21" t="n">
         <v>7.83</v>
       </c>
-      <c r="J45" s="17" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="K45" s="18" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="L45" s="19" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="M45" s="19" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="N45" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O45" s="21" t="n">
+      <c r="P45" s="21" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="Q45" s="22" t="n">
         <v>7.85</v>
       </c>
-      <c r="P45" s="21" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="Q45" s="22" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="R45" s="23" t="n">
-        <v>0.51</v>
+      <c r="R45" s="25" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="46">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>13.01</v>
+        <v>13.05</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>12.79</v>
+        <v>12.88</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>12.6</v>
+        <v>12.73</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>12.69</v>
+        <v>12.72</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>12.78</v>
+        <v>12.83</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>12.56</v>
+        <v>12.66</v>
       </c>
       <c r="I46" s="17" t="n">
-        <v>12.47</v>
+        <v>12.55</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>12.34</v>
+        <v>12.49</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>12.48</v>
+        <v>12.64</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>12.29</v>
+        <v>12.49</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>12.07</v>
+        <v>12.32</v>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O46" s="21" t="n">
-        <v>12.53</v>
+        <v>12.66</v>
       </c>
       <c r="P46" s="21" t="n">
-        <v>12.5</v>
+        <v>12.65</v>
       </c>
       <c r="Q46" s="22" t="n">
-        <v>12.6</v>
+        <v>12.61</v>
       </c>
       <c r="R46" s="23" t="n">
-        <v>0.64</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="47">
@@ -3486,54 +3486,54 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>208.09</v>
+        <v>213.53</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>206.49</v>
+        <v>210.73</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>205.15</v>
+        <v>208.38</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>205.7</v>
+        <v>209.2</v>
       </c>
       <c r="G47" s="15" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="H47" s="16" t="n">
+        <v>207.7</v>
+      </c>
+      <c r="I47" s="17" t="n">
         <v>206.4</v>
       </c>
-      <c r="H47" s="16" t="n">
-        <v>204.8</v>
-      </c>
-      <c r="I47" s="17" t="n">
-        <v>204.1</v>
-      </c>
       <c r="J47" s="17" t="n">
-        <v>203.2</v>
+        <v>204.9</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>204.25</v>
+        <v>206.82</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>202.91</v>
+        <v>204.47</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>201.31</v>
-      </c>
-      <c r="N47" s="20" t="inlineStr">
+        <v>201.67</v>
+      </c>
+      <c r="N47" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O47" s="21" t="n">
-        <v>204.59</v>
+        <v>207.37</v>
       </c>
       <c r="P47" s="21" t="n">
-        <v>204.38</v>
+        <v>207.03</v>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>205</v>
-      </c>
-      <c r="R47" s="23" t="n">
-        <v>0.15</v>
+        <v>207.9</v>
+      </c>
+      <c r="R47" s="25" t="n">
+        <v>0.82</v>
       </c>
     </row>
     <row r="48">
@@ -3548,54 +3548,54 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>51.45</v>
+        <v>51.07</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>50.17</v>
+        <v>50.37</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>49.1</v>
+        <v>49.79</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>49.61</v>
+        <v>49.72</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>50.13</v>
+        <v>50.18</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>48.85</v>
+        <v>49.48</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>48.33</v>
+        <v>49.02</v>
       </c>
       <c r="J48" s="17" t="n">
-        <v>47.57</v>
+        <v>48.78</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>48.38</v>
+        <v>49.39</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>47.31</v>
+        <v>48.81</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>46.03</v>
+        <v>48.11</v>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O48" s="21" t="n">
-        <v>48.67</v>
+        <v>49.46</v>
       </c>
       <c r="P48" s="21" t="n">
-        <v>48.48</v>
+        <v>49.45</v>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>49.08</v>
+        <v>49.26</v>
       </c>
       <c r="R48" s="23" t="n">
-        <v>1.61</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="49">
@@ -3610,54 +3610,54 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>34.56</v>
+        <v>34.96</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>34.2</v>
+        <v>34.6</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>33.9</v>
+        <v>34.3</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>33.9</v>
+        <v>34.27</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>34.12</v>
+        <v>34.51</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>33.76</v>
+        <v>34.15</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>33.54</v>
+        <v>33.91</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>33.4</v>
+        <v>33.79</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>33.7</v>
+        <v>34.1</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>33.4</v>
+        <v>33.8</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>33.04</v>
+        <v>33.44</v>
       </c>
       <c r="N49" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O49" s="21" t="n">
-        <v>33.74</v>
+        <v>34.14</v>
       </c>
       <c r="P49" s="21" t="n">
-        <v>33.73</v>
+        <v>34.13</v>
       </c>
       <c r="Q49" s="22" t="n">
-        <v>33.68</v>
-      </c>
-      <c r="R49" s="25" t="n">
-        <v>-0.88</v>
+        <v>34.04</v>
+      </c>
+      <c r="R49" s="23" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="50">
@@ -3672,54 +3672,54 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>13.84</v>
+        <v>13.77</v>
       </c>
       <c r="D50" s="13" t="n">
         <v>13.63</v>
       </c>
       <c r="E50" s="14" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H50" s="16" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="L50" s="19" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="M50" s="19" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="N50" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O50" s="21" t="n">
         <v>13.45</v>
       </c>
-      <c r="F50" s="15" t="n">
-        <v>13.56</v>
-      </c>
-      <c r="G50" s="15" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="H50" s="16" t="n">
+      <c r="P50" s="21" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="Q50" s="22" t="n">
         <v>13.43</v>
       </c>
-      <c r="I50" s="17" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="J50" s="17" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="K50" s="18" t="n">
-        <v>13.34</v>
-      </c>
-      <c r="L50" s="19" t="n">
-        <v>13.16</v>
-      </c>
-      <c r="M50" s="19" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="N50" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O50" s="21" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="P50" s="21" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="Q50" s="22" t="n">
-        <v>13.49</v>
-      </c>
       <c r="R50" s="23" t="n">
-        <v>1.05</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="51">
@@ -3734,54 +3734,54 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>62.09</v>
+        <v>68.13</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>61.14</v>
+        <v>65.58</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>60.34</v>
+        <v>63.44</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>60.53</v>
+        <v>63.15</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>61.02</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>60.07</v>
+        <v>62.3</v>
       </c>
       <c r="I51" s="17" t="n">
-        <v>59.58</v>
+        <v>60.6</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>59.12</v>
+        <v>59.75</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>59.81</v>
+        <v>62.01</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>59.01</v>
+        <v>59.87</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>58.06</v>
-      </c>
-      <c r="N51" s="24" t="inlineStr">
+        <v>57.32</v>
+      </c>
+      <c r="N51" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O51" s="21" t="n">
-        <v>59.97</v>
+        <v>62.25</v>
       </c>
       <c r="P51" s="21" t="n">
-        <v>59.88</v>
+        <v>62.21</v>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>60.05</v>
+        <v>61.45</v>
       </c>
       <c r="R51" s="23" t="n">
-        <v>0.33</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="52">
@@ -3796,54 +3796,54 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>25.86</v>
+        <v>25.39</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>25.32</v>
+        <v>24.87</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>24.87</v>
+        <v>24.44</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>24.91</v>
+        <v>24.47</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>25.22</v>
+        <v>24.77</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>24.68</v>
+        <v>24.25</v>
       </c>
       <c r="I52" s="17" t="n">
-        <v>24.37</v>
+        <v>23.95</v>
       </c>
       <c r="J52" s="17" t="n">
+        <v>23.73</v>
+      </c>
+      <c r="K52" s="18" t="n">
         <v>24.14</v>
       </c>
-      <c r="K52" s="18" t="n">
-        <v>24.57</v>
-      </c>
       <c r="L52" s="19" t="n">
-        <v>24.12</v>
+        <v>23.71</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>23.58</v>
-      </c>
-      <c r="N52" s="24" t="inlineStr">
+        <v>23.19</v>
+      </c>
+      <c r="N52" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O52" s="21" t="n">
-        <v>24.65</v>
+        <v>24.22</v>
       </c>
       <c r="P52" s="21" t="n">
-        <v>24.61</v>
+        <v>24.18</v>
       </c>
       <c r="Q52" s="22" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="R52" s="25" t="n">
-        <v>-1.05</v>
+        <v>24.17</v>
+      </c>
+      <c r="R52" s="23" t="n">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="53">
@@ -3858,54 +3858,54 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>5.49</v>
+        <v>5.6</v>
       </c>
       <c r="D53" s="13" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F53" s="15" t="n">
         <v>5.39</v>
       </c>
-      <c r="E53" s="14" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="F53" s="15" t="n">
+      <c r="G53" s="15" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="I53" s="17" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="J53" s="17" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="K53" s="18" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="L53" s="19" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="M53" s="19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N53" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O53" s="21" t="n">
         <v>5.33</v>
       </c>
-      <c r="G53" s="15" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="H53" s="16" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="I53" s="17" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="J53" s="17" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="K53" s="18" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L53" s="19" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="M53" s="19" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="N53" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O53" s="21" t="n">
-        <v>5.27</v>
-      </c>
       <c r="P53" s="21" t="n">
-        <v>5.26</v>
+        <v>5.33</v>
       </c>
       <c r="Q53" s="22" t="n">
-        <v>5.28</v>
+        <v>5.32</v>
       </c>
       <c r="R53" s="23" t="n">
-        <v>0.57</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="54">
@@ -3920,54 +3920,54 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>19.24</v>
+        <v>18.44</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>18.51</v>
+        <v>17.75</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>17.9</v>
+        <v>17.17</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>17.86</v>
+        <v>17.1</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>18.33</v>
+        <v>17.55</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>17.6</v>
+        <v>16.86</v>
       </c>
       <c r="I54" s="17" t="n">
-        <v>17.13</v>
+        <v>16.41</v>
       </c>
       <c r="J54" s="17" t="n">
-        <v>16.87</v>
+        <v>16.17</v>
       </c>
       <c r="K54" s="18" t="n">
-        <v>17.49</v>
+        <v>16.78</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>16.88</v>
+        <v>16.2</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="N54" s="24" t="inlineStr">
+        <v>15.51</v>
+      </c>
+      <c r="N54" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O54" s="21" t="n">
-        <v>17.57</v>
+        <v>16.85</v>
       </c>
       <c r="P54" s="21" t="n">
-        <v>17.55</v>
+        <v>16.84</v>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="R54" s="25" t="n">
-        <v>-3.55</v>
+        <v>16.64</v>
+      </c>
+      <c r="R54" s="23" t="n">
+        <v>-4.09</v>
       </c>
     </row>
     <row r="55">
@@ -3982,54 +3982,54 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>96.52</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>94.47</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>92.75</v>
+        <v>95.06</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>93.88</v>
+        <v>95.17</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>94.56999999999999</v>
+        <v>96.33</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>92.52</v>
+        <v>94.33</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>91.83</v>
+        <v>93.17</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>90.47</v>
+        <v>92.33</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>91.59999999999999</v>
+        <v>93.94</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>89.88</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>87.83</v>
-      </c>
-      <c r="N55" s="20" t="inlineStr">
+        <v>90.26000000000001</v>
+      </c>
+      <c r="N55" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>92.14</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>91.76000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="R55" s="23" t="n">
-        <v>1.86</v>
+        <v>94</v>
+      </c>
+      <c r="R55" s="25" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="56">
@@ -4044,54 +4044,54 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>20.33</v>
+        <v>18.84</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>19.63</v>
+        <v>18.56</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>19.05</v>
+        <v>18.33</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>19.05</v>
+        <v>18.33</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>19.47</v>
+        <v>18.5</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>18.77</v>
+        <v>18.22</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>18.35</v>
+        <v>18.05</v>
       </c>
       <c r="J56" s="17" t="n">
-        <v>18.07</v>
+        <v>17.94</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>18.65</v>
+        <v>18.17</v>
       </c>
       <c r="L56" s="19" t="n">
-        <v>18.07</v>
+        <v>17.94</v>
       </c>
       <c r="M56" s="19" t="n">
-        <v>17.37</v>
-      </c>
-      <c r="N56" s="24" t="inlineStr">
+        <v>17.66</v>
+      </c>
+      <c r="N56" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O56" s="21" t="n">
-        <v>18.74</v>
+        <v>18.21</v>
       </c>
       <c r="P56" s="21" t="n">
-        <v>18.71</v>
+        <v>18.19</v>
       </c>
       <c r="Q56" s="22" t="n">
-        <v>18.62</v>
-      </c>
-      <c r="R56" s="25" t="n">
-        <v>-3.02</v>
+        <v>18.16</v>
+      </c>
+      <c r="R56" s="23" t="n">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="57">
@@ -4106,54 +4106,54 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>22.09</v>
+        <v>22.18</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>21.96</v>
+        <v>22.02</v>
       </c>
       <c r="E57" s="14" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="F57" s="15" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="G57" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H57" s="16" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="I57" s="17" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="J57" s="17" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="K57" s="18" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="L57" s="19" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="M57" s="19" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="N57" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O57" s="21" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="P57" s="21" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="Q57" s="22" t="n">
         <v>21.85</v>
       </c>
-      <c r="F57" s="15" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="G57" s="15" t="n">
-        <v>21.93</v>
-      </c>
-      <c r="H57" s="16" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I57" s="17" t="n">
-        <v>21.72</v>
-      </c>
-      <c r="J57" s="17" t="n">
-        <v>21.67</v>
-      </c>
-      <c r="K57" s="18" t="n">
-        <v>21.78</v>
-      </c>
-      <c r="L57" s="19" t="n">
-        <v>21.67</v>
-      </c>
-      <c r="M57" s="19" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="N57" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O57" s="21" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="P57" s="21" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="Q57" s="22" t="n">
-        <v>21.77</v>
-      </c>
       <c r="R57" s="25" t="n">
-        <v>-0.23</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="58">
@@ -4168,54 +4168,54 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>24.07</v>
+        <v>23.96</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>23.8</v>
+        <v>23.78</v>
       </c>
       <c r="E58" s="14" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="F58" s="15" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="G58" s="15" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="H58" s="16" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="I58" s="17" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="J58" s="17" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="K58" s="18" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="L58" s="19" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="M58" s="19" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="N58" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O58" s="21" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="P58" s="21" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="Q58" s="22" t="n">
         <v>23.57</v>
       </c>
-      <c r="F58" s="15" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G58" s="15" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="H58" s="16" t="n">
-        <v>23.53</v>
-      </c>
-      <c r="I58" s="17" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="J58" s="17" t="n">
-        <v>23.26</v>
-      </c>
-      <c r="K58" s="18" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="L58" s="19" t="n">
-        <v>23.19</v>
-      </c>
-      <c r="M58" s="19" t="n">
-        <v>22.92</v>
-      </c>
-      <c r="N58" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O58" s="21" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="P58" s="21" t="n">
-        <v>23.44</v>
-      </c>
-      <c r="Q58" s="22" t="n">
-        <v>23.6</v>
-      </c>
       <c r="R58" s="23" t="n">
-        <v>0.77</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="59">
@@ -4230,54 +4230,54 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>29.46</v>
+        <v>29.37</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>29.2</v>
+        <v>29.13</v>
       </c>
       <c r="E59" s="14" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="F59" s="15" t="n">
         <v>28.98</v>
       </c>
-      <c r="F59" s="15" t="n">
-        <v>29.03</v>
-      </c>
       <c r="G59" s="15" t="n">
-        <v>29.17</v>
+        <v>29.1</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>28.91</v>
+        <v>28.86</v>
       </c>
       <c r="I59" s="17" t="n">
-        <v>28.77</v>
+        <v>28.74</v>
       </c>
       <c r="J59" s="17" t="n">
-        <v>28.65</v>
+        <v>28.62</v>
       </c>
       <c r="K59" s="18" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="L59" s="19" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="M59" s="19" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="N59" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O59" s="21" t="n">
         <v>28.84</v>
       </c>
-      <c r="L59" s="19" t="n">
-        <v>28.62</v>
-      </c>
-      <c r="M59" s="19" t="n">
-        <v>28.36</v>
-      </c>
-      <c r="N59" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O59" s="21" t="n">
-        <v>28.88</v>
-      </c>
       <c r="P59" s="21" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="Q59" s="22" t="n">
         <v>28.86</v>
       </c>
-      <c r="Q59" s="22" t="n">
-        <v>28.9</v>
-      </c>
       <c r="R59" s="23" t="n">
-        <v>0.49</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="60">
@@ -4292,54 +4292,54 @@
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>45.42</v>
+        <v>45.89</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>45.26</v>
+        <v>45.61</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>45.12</v>
+        <v>45.38</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>45.2</v>
+        <v>45.44</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>45.26</v>
+        <v>45.58</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="I60" s="17" t="n">
-        <v>45.04</v>
+        <v>45.16</v>
       </c>
       <c r="J60" s="17" t="n">
-        <v>44.94</v>
+        <v>45.02</v>
       </c>
       <c r="K60" s="18" t="n">
-        <v>45.04</v>
+        <v>45.22</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>44.9</v>
+        <v>44.99</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>44.74</v>
+        <v>44.71</v>
       </c>
       <c r="N60" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O60" s="21" t="n">
-        <v>45.07</v>
+        <v>45.27</v>
       </c>
       <c r="P60" s="21" t="n">
-        <v>45.05</v>
+        <v>45.24</v>
       </c>
       <c r="Q60" s="22" t="n">
-        <v>45.14</v>
-      </c>
-      <c r="R60" s="23" t="n">
-        <v>0.27</v>
+        <v>45.3</v>
+      </c>
+      <c r="R60" s="25" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="61">
@@ -4354,54 +4354,54 @@
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>20.51</v>
+        <v>20.08</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>19.98</v>
+        <v>19.87</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>19.53</v>
+        <v>19.69</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>19.81</v>
+        <v>19.7</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>19.99</v>
+        <v>19.83</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>19.46</v>
+        <v>19.62</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>19.28</v>
+        <v>19.49</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>18.93</v>
+        <v>19.41</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>19.24</v>
+        <v>19.58</v>
       </c>
       <c r="L61" s="19" t="n">
-        <v>18.79</v>
+        <v>19.4</v>
       </c>
       <c r="M61" s="19" t="n">
-        <v>18.26</v>
+        <v>19.19</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O61" s="21" t="n">
-        <v>19.37</v>
+        <v>19.6</v>
       </c>
       <c r="P61" s="21" t="n">
-        <v>19.28</v>
+        <v>19.59</v>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>19.62</v>
+        <v>19.58</v>
       </c>
       <c r="R61" s="23" t="n">
-        <v>0.77</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="62">
@@ -4416,54 +4416,54 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="D62" s="13" t="n">
         <v>15.49</v>
       </c>
-      <c r="D62" s="13" t="n">
+      <c r="E62" s="14" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="F62" s="15" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="G62" s="15" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="H62" s="16" t="n">
         <v>15.28</v>
       </c>
-      <c r="E62" s="14" t="n">
+      <c r="I62" s="17" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="J62" s="17" t="n">
         <v>15.1</v>
       </c>
-      <c r="F62" s="15" t="n">
-        <v>15.15</v>
-      </c>
-      <c r="G62" s="15" t="n">
+      <c r="K62" s="18" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="L62" s="19" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="M62" s="19" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="N62" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O62" s="21" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="P62" s="21" t="n">
         <v>15.25</v>
       </c>
-      <c r="H62" s="16" t="n">
-        <v>15.04</v>
-      </c>
-      <c r="I62" s="17" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="J62" s="17" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="K62" s="18" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="L62" s="19" t="n">
-        <v>14.81</v>
-      </c>
-      <c r="M62" s="19" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N62" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O62" s="21" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="P62" s="21" t="n">
-        <v>15</v>
-      </c>
       <c r="Q62" s="22" t="n">
-        <v>15.04</v>
-      </c>
-      <c r="R62" s="23" t="n">
-        <v>0.53</v>
+        <v>15.27</v>
+      </c>
+      <c r="R62" s="25" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="63">
@@ -4478,54 +4478,54 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>25.68</v>
+        <v>26.2</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>25.52</v>
+        <v>25.84</v>
       </c>
       <c r="E63" s="14" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="F63" s="15" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="G63" s="15" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="H63" s="16" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="I63" s="17" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="J63" s="17" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="K63" s="18" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="L63" s="19" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="M63" s="19" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="N63" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O63" s="21" t="n">
         <v>25.38</v>
       </c>
-      <c r="F63" s="15" t="n">
-        <v>25.39</v>
-      </c>
-      <c r="G63" s="15" t="n">
-        <v>25.49</v>
-      </c>
-      <c r="H63" s="16" t="n">
-        <v>25.33</v>
-      </c>
-      <c r="I63" s="17" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="J63" s="17" t="n">
-        <v>25.17</v>
-      </c>
-      <c r="K63" s="18" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="L63" s="19" t="n">
-        <v>25.16</v>
-      </c>
-      <c r="M63" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="N63" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O63" s="21" t="n">
-        <v>25.32</v>
-      </c>
       <c r="P63" s="21" t="n">
-        <v>25.31</v>
+        <v>25.37</v>
       </c>
       <c r="Q63" s="22" t="n">
         <v>25.3</v>
       </c>
-      <c r="R63" s="25" t="n">
-        <v>-0.63</v>
+      <c r="R63" s="23" t="n">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="64">
@@ -4540,54 +4540,54 @@
         </is>
       </c>
       <c r="C64" s="13" t="n">
-        <v>7.52</v>
+        <v>7.55</v>
       </c>
       <c r="D64" s="13" t="n">
-        <v>7.46</v>
+        <v>7.49</v>
       </c>
       <c r="E64" s="14" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="F64" s="15" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="G64" s="15" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="H64" s="16" t="n">
         <v>7.41</v>
       </c>
-      <c r="F64" s="15" t="n">
+      <c r="I64" s="17" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="J64" s="17" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="K64" s="18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L64" s="19" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="M64" s="19" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="N64" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O64" s="21" t="n">
         <v>7.41</v>
       </c>
-      <c r="G64" s="15" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="H64" s="16" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="I64" s="17" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="J64" s="17" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="K64" s="18" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="L64" s="19" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="M64" s="19" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="N64" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O64" s="21" t="n">
-        <v>7.38</v>
-      </c>
       <c r="P64" s="21" t="n">
-        <v>7.38</v>
+        <v>7.41</v>
       </c>
       <c r="Q64" s="22" t="n">
-        <v>7.37</v>
+        <v>7.39</v>
       </c>
       <c r="R64" s="23" t="n">
-        <v>0.27</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4602,54 +4602,54 @@
         </is>
       </c>
       <c r="C65" s="13" t="n">
-        <v>5.12</v>
+        <v>5.09</v>
       </c>
       <c r="D65" s="13" t="n">
-        <v>5.06</v>
+        <v>5.03</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>5.01</v>
+        <v>4.98</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="G65" s="15" t="n">
-        <v>5.05</v>
+        <v>5.02</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>4.99</v>
+        <v>4.96</v>
       </c>
       <c r="I65" s="17" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="J65" s="17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K65" s="18" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="L65" s="19" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="M65" s="19" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="N65" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O65" s="21" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="P65" s="21" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Q65" s="22" t="n">
         <v>4.97</v>
       </c>
-      <c r="J65" s="17" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="K65" s="18" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="L65" s="19" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="M65" s="19" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="N65" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O65" s="21" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="P65" s="21" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="Q65" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="R65" s="25" t="n">
-        <v>-0.4</v>
+      <c r="R65" s="23" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="66">
@@ -4664,54 +4664,54 @@
         </is>
       </c>
       <c r="C66" s="13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="F66" s="15" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="G66" s="15" t="n">
         <v>5.1</v>
       </c>
-      <c r="D66" s="13" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="E66" s="14" t="n">
+      <c r="H66" s="16" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I66" s="17" t="n">
         <v>4.97</v>
       </c>
-      <c r="F66" s="15" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="G66" s="15" t="n">
+      <c r="J66" s="17" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="K66" s="18" t="n">
         <v>5.01</v>
       </c>
-      <c r="H66" s="16" t="n">
+      <c r="L66" s="19" t="n">
         <v>4.94</v>
       </c>
-      <c r="I66" s="17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J66" s="17" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="K66" s="18" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="L66" s="19" t="n">
-        <v>4.88</v>
-      </c>
       <c r="M66" s="19" t="n">
-        <v>4.81</v>
+        <v>4.86</v>
       </c>
       <c r="N66" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O66" s="21" t="n">
-        <v>4.94</v>
+        <v>5.02</v>
       </c>
       <c r="P66" s="21" t="n">
-        <v>4.94</v>
+        <v>5.01</v>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="R66" s="25" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="67">
@@ -4726,54 +4726,54 @@
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>65.81999999999999</v>
+        <v>67.23</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>65.22</v>
+        <v>66.53</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>64.72</v>
+        <v>65.95</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>65.05</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>65.25</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>64.65000000000001</v>
+        <v>65.73</v>
       </c>
       <c r="I67" s="17" t="n">
-        <v>64.45</v>
+        <v>65.37</v>
       </c>
       <c r="J67" s="17" t="n">
-        <v>64.05</v>
+        <v>65.03</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>64.38</v>
+        <v>65.55</v>
       </c>
       <c r="L67" s="19" t="n">
-        <v>63.88</v>
+        <v>64.97</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>63.28</v>
+        <v>64.27</v>
       </c>
       <c r="N67" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O67" s="21" t="n">
-        <v>64.54000000000001</v>
+        <v>65.67</v>
       </c>
       <c r="P67" s="21" t="n">
-        <v>64.43000000000001</v>
+        <v>65.61</v>
       </c>
       <c r="Q67" s="22" t="n">
-        <v>64.84999999999999</v>
-      </c>
-      <c r="R67" s="23" t="n">
-        <v>0</v>
+        <v>65.7</v>
+      </c>
+      <c r="R67" s="25" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="68">
@@ -4788,54 +4788,54 @@
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>67.8</v>
+        <v>68.16</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>67.15000000000001</v>
+        <v>67.41</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>66.61</v>
+        <v>66.78</v>
       </c>
       <c r="F68" s="15" t="n">
-        <v>66.63</v>
+        <v>67.03</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>67.02</v>
+        <v>67.37</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>66.37</v>
+        <v>66.62</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>65.98</v>
+        <v>66.28</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>65.72</v>
+        <v>65.87</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>66.23999999999999</v>
+        <v>66.36</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>65.7</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>65.05</v>
-      </c>
-      <c r="N68" s="20" t="inlineStr">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="N68" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O68" s="21" t="n">
-        <v>66.33</v>
+        <v>66.52</v>
       </c>
       <c r="P68" s="21" t="n">
-        <v>66.29000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="R68" s="23" t="n">
-        <v>0.38</v>
+        <v>66.7</v>
+      </c>
+      <c r="R68" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4850,54 +4850,54 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>104.17</v>
+        <v>107.78</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>102.77</v>
+        <v>105.38</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>101.59</v>
+        <v>103.37</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>101.43</v>
+        <v>103.77</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>102.37</v>
+        <v>105.03</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>100.97</v>
+        <v>102.63</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>100.03</v>
+        <v>101.37</v>
       </c>
       <c r="J69" s="17" t="n">
-        <v>99.56999999999999</v>
+        <v>100.23</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>100.81</v>
+        <v>102.03</v>
       </c>
       <c r="L69" s="19" t="n">
-        <v>99.63</v>
+        <v>100.02</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>98.23</v>
+        <v>97.62</v>
       </c>
       <c r="N69" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O69" s="21" t="n">
-        <v>100.94</v>
+        <v>102.42</v>
       </c>
       <c r="P69" s="21" t="n">
-        <v>100.92</v>
+        <v>102.22</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>100.5</v>
+        <v>102.5</v>
       </c>
       <c r="R69" s="25" t="n">
-        <v>-0.89</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="70">
@@ -4912,54 +4912,54 @@
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>132.12</v>
+        <v>130.73</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>129.02</v>
+        <v>127.93</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>126.42</v>
+        <v>125.58</v>
       </c>
       <c r="F70" s="15" t="n">
-        <v>126.07</v>
+        <v>125.4</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>128.13</v>
+        <v>127.2</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>125.03</v>
+        <v>124.4</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>122.97</v>
+        <v>122.6</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>121.93</v>
+        <v>121.6</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>124.68</v>
+        <v>124.02</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>122.08</v>
+        <v>121.67</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>118.98</v>
-      </c>
-      <c r="N70" s="24" t="inlineStr">
+        <v>118.87</v>
+      </c>
+      <c r="N70" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O70" s="21" t="n">
-        <v>124.98</v>
+        <v>124.32</v>
       </c>
       <c r="P70" s="21" t="n">
-        <v>124.92</v>
+        <v>124.23</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>124</v>
-      </c>
-      <c r="R70" s="25" t="n">
-        <v>-1.43</v>
+        <v>123.6</v>
+      </c>
+      <c r="R70" s="23" t="n">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="71">
@@ -4974,54 +4974,54 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>26.55</v>
+        <v>26.01</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>26.11</v>
+        <v>25.63</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>25.74</v>
+        <v>25.32</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>25.85</v>
+        <v>25.3</v>
       </c>
       <c r="G71" s="15" t="n">
-        <v>26.07</v>
+        <v>25.54</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>25.63</v>
+        <v>25.16</v>
       </c>
       <c r="I71" s="17" t="n">
-        <v>25.41</v>
+        <v>24.92</v>
       </c>
       <c r="J71" s="17" t="n">
-        <v>25.19</v>
+        <v>24.78</v>
       </c>
       <c r="K71" s="18" t="n">
-        <v>25.5</v>
+        <v>25.1</v>
       </c>
       <c r="L71" s="19" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="M71" s="19" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="N71" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O71" s="21" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="P71" s="21" t="n">
         <v>25.13</v>
       </c>
-      <c r="M71" s="19" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="N71" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O71" s="21" t="n">
-        <v>25.58</v>
-      </c>
-      <c r="P71" s="21" t="n">
-        <v>25.53</v>
-      </c>
       <c r="Q71" s="22" t="n">
-        <v>25.64</v>
+        <v>25.06</v>
       </c>
       <c r="R71" s="23" t="n">
-        <v>0.16</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="72">
@@ -5036,54 +5036,54 @@
         </is>
       </c>
       <c r="C72" s="13" t="n">
-        <v>21.87</v>
+        <v>21.97</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>21.53</v>
+        <v>21.56</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>21.22</v>
+        <v>21.23</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>21.44</v>
+        <v>21.47</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>21.1</v>
+        <v>21.06</v>
       </c>
       <c r="I72" s="17" t="n">
-        <v>20.88</v>
+        <v>20.82</v>
       </c>
       <c r="J72" s="17" t="n">
-        <v>20.76</v>
+        <v>20.65</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>21.05</v>
+        <v>20.99</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>20.77</v>
+        <v>20.65</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="N72" s="24" t="inlineStr">
+        <v>20.24</v>
+      </c>
+      <c r="N72" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O72" s="21" t="n">
-        <v>21.09</v>
+        <v>21.04</v>
       </c>
       <c r="P72" s="21" t="n">
-        <v>21.08</v>
+        <v>21.02</v>
       </c>
       <c r="Q72" s="22" t="n">
-        <v>21</v>
-      </c>
-      <c r="R72" s="25" t="n">
-        <v>-0.43</v>
+        <v>20.98</v>
+      </c>
+      <c r="R72" s="23" t="n">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="73">
@@ -5098,54 +5098,54 @@
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>248.08</v>
+        <v>247.16</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>244.88</v>
+        <v>243.66</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>242.2</v>
+        <v>240.73</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>242.03</v>
+        <v>240.33</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>244.07</v>
+        <v>242.67</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>240.87</v>
+        <v>239.17</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>238.83</v>
+        <v>236.83</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>237.67</v>
+        <v>235.67</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>240.4</v>
+        <v>238.77</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>237.72</v>
+        <v>235.84</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>234.52</v>
+        <v>232.34</v>
       </c>
       <c r="N73" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O73" s="21" t="n">
-        <v>240.76</v>
+        <v>239.1</v>
       </c>
       <c r="P73" s="21" t="n">
-        <v>240.65</v>
+        <v>239.04</v>
       </c>
       <c r="Q73" s="22" t="n">
-        <v>240</v>
-      </c>
-      <c r="R73" s="25" t="n">
-        <v>-0.29</v>
+        <v>238</v>
+      </c>
+      <c r="R73" s="23" t="n">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="74">
@@ -5160,54 +5160,54 @@
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>16.88</v>
+        <v>16.1</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>16.39</v>
+        <v>15.92</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>15.98</v>
+        <v>15.77</v>
       </c>
       <c r="F74" s="15" t="n">
-        <v>16.13</v>
+        <v>15.76</v>
       </c>
       <c r="G74" s="15" t="n">
-        <v>16.35</v>
+        <v>15.88</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>15.86</v>
+        <v>15.7</v>
       </c>
       <c r="I74" s="17" t="n">
-        <v>15.64</v>
+        <v>15.58</v>
       </c>
       <c r="J74" s="17" t="n">
-        <v>15.37</v>
+        <v>15.52</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>15.71</v>
+        <v>15.67</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>15.3</v>
+        <v>15.52</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>14.81</v>
+        <v>15.34</v>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O74" s="21" t="n">
-        <v>15.8</v>
+        <v>15.69</v>
       </c>
       <c r="P74" s="21" t="n">
-        <v>15.75</v>
+        <v>15.68</v>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>15.9</v>
+        <v>15.65</v>
       </c>
       <c r="R74" s="23" t="n">
-        <v>1.92</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="75">
@@ -5222,54 +5222,54 @@
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>38.55</v>
+        <v>37.14</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>37.43</v>
+        <v>36.36</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>36.49</v>
+        <v>35.71</v>
       </c>
       <c r="F75" s="15" t="n">
-        <v>36.65</v>
+        <v>35.75</v>
       </c>
       <c r="G75" s="15" t="n">
-        <v>37.25</v>
+        <v>36.21</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>36.13</v>
+        <v>35.43</v>
       </c>
       <c r="I75" s="17" t="n">
-        <v>35.53</v>
+        <v>34.97</v>
       </c>
       <c r="J75" s="17" t="n">
-        <v>35.01</v>
+        <v>34.65</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>35.87</v>
+        <v>35.27</v>
       </c>
       <c r="L75" s="19" t="n">
-        <v>34.93</v>
+        <v>34.62</v>
       </c>
       <c r="M75" s="19" t="n">
-        <v>33.81</v>
-      </c>
-      <c r="N75" s="24" t="inlineStr">
+        <v>33.84</v>
+      </c>
+      <c r="N75" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O75" s="21" t="n">
-        <v>36.04</v>
+        <v>35.38</v>
       </c>
       <c r="P75" s="21" t="n">
-        <v>35.95</v>
+        <v>35.33</v>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>36.04</v>
-      </c>
-      <c r="R75" s="25" t="n">
-        <v>-2.28</v>
+        <v>35.3</v>
+      </c>
+      <c r="R75" s="23" t="n">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="76">
@@ -5284,54 +5284,54 @@
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>27.7</v>
+        <v>28.03</v>
       </c>
       <c r="D76" s="13" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="E76" s="14" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="F76" s="15" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="G76" s="15" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="H76" s="16" t="n">
         <v>27.48</v>
       </c>
-      <c r="E76" s="14" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="F76" s="15" t="n">
+      <c r="I76" s="17" t="n">
         <v>27.32</v>
       </c>
-      <c r="G76" s="15" t="n">
-        <v>27.44</v>
-      </c>
-      <c r="H76" s="16" t="n">
-        <v>27.22</v>
-      </c>
-      <c r="I76" s="17" t="n">
-        <v>27.1</v>
-      </c>
       <c r="J76" s="17" t="n">
-        <v>27</v>
+        <v>27.24</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>27.17</v>
+        <v>27.45</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>26.98</v>
+        <v>27.25</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>26.76</v>
-      </c>
-      <c r="N76" s="20" t="inlineStr">
+        <v>27.01</v>
+      </c>
+      <c r="N76" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O76" s="21" t="n">
-        <v>27.2</v>
+        <v>27.48</v>
       </c>
       <c r="P76" s="21" t="n">
-        <v>27.19</v>
+        <v>27.47</v>
       </c>
       <c r="Q76" s="22" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R76" s="23" t="n">
-        <v>0.37</v>
+        <v>27.4</v>
+      </c>
+      <c r="R76" s="25" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="77">
@@ -5346,54 +5346,54 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>44.43</v>
+        <v>44.67</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>43.67</v>
+        <v>43.55</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>43.03</v>
+        <v>42.61</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>43.13</v>
+        <v>42.58</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>43.55</v>
+        <v>43.28</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>42.79</v>
+        <v>42.16</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>42.37</v>
+        <v>41.46</v>
       </c>
       <c r="J77" s="17" t="n">
-        <v>42.03</v>
+        <v>41.04</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>42.61</v>
+        <v>41.99</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>41.97</v>
+        <v>41.05</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>41.21</v>
-      </c>
-      <c r="N77" s="24" t="inlineStr">
+        <v>39.93</v>
+      </c>
+      <c r="N77" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O77" s="21" t="n">
-        <v>42.73</v>
+        <v>42.12</v>
       </c>
       <c r="P77" s="21" t="n">
-        <v>42.67</v>
+        <v>42.07</v>
       </c>
       <c r="Q77" s="22" t="n">
-        <v>42.72</v>
-      </c>
-      <c r="R77" s="25" t="n">
-        <v>-0.37</v>
+        <v>41.88</v>
+      </c>
+      <c r="R77" s="23" t="n">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="78">
@@ -5408,54 +5408,54 @@
         </is>
       </c>
       <c r="C78" s="13" t="n">
-        <v>5.71</v>
+        <v>5.59</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>5.63</v>
+        <v>5.55</v>
       </c>
       <c r="E78" s="14" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="F78" s="15" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="G78" s="15" t="n">
         <v>5.56</v>
       </c>
-      <c r="F78" s="15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G78" s="15" t="n">
-        <v>5.63</v>
-      </c>
       <c r="H78" s="16" t="n">
-        <v>5.55</v>
+        <v>5.52</v>
       </c>
       <c r="I78" s="17" t="n">
-        <v>5.52</v>
+        <v>5.5</v>
       </c>
       <c r="J78" s="17" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="K78" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L78" s="19" t="n">
         <v>5.47</v>
       </c>
-      <c r="K78" s="18" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="L78" s="19" t="n">
-        <v>5.45</v>
-      </c>
       <c r="M78" s="19" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="N78" s="24" t="inlineStr">
+        <v>5.43</v>
+      </c>
+      <c r="N78" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O78" s="21" t="n">
-        <v>5.54</v>
+        <v>5.51</v>
       </c>
       <c r="P78" s="21" t="n">
-        <v>5.52</v>
+        <v>5.5</v>
       </c>
       <c r="Q78" s="22" t="n">
-        <v>5.57</v>
+        <v>5.53</v>
       </c>
       <c r="R78" s="23" t="n">
-        <v>0</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="79">
@@ -5470,16 +5470,16 @@
         </is>
       </c>
       <c r="C79" s="13" t="n">
-        <v>19.42</v>
+        <v>19.46</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>19.1</v>
+        <v>19.14</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>18.83</v>
+        <v>18.87</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>18.94</v>
+        <v>18.9</v>
       </c>
       <c r="G79" s="15" t="n">
         <v>19.08</v>
@@ -5488,36 +5488,36 @@
         <v>18.76</v>
       </c>
       <c r="I79" s="17" t="n">
-        <v>18.62</v>
+        <v>18.58</v>
       </c>
       <c r="J79" s="17" t="n">
         <v>18.44</v>
       </c>
       <c r="K79" s="18" t="n">
-        <v>18.65</v>
+        <v>18.69</v>
       </c>
       <c r="L79" s="19" t="n">
-        <v>18.38</v>
+        <v>18.42</v>
       </c>
       <c r="M79" s="19" t="n">
-        <v>18.06</v>
+        <v>18.1</v>
       </c>
       <c r="N79" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O79" s="21" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="P79" s="21" t="n">
         <v>18.72</v>
       </c>
-      <c r="P79" s="21" t="n">
-        <v>18.68</v>
-      </c>
       <c r="Q79" s="22" t="n">
-        <v>18.8</v>
+        <v>18.72</v>
       </c>
       <c r="R79" s="23" t="n">
-        <v>1.18</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="80">
@@ -5532,54 +5532,54 @@
         </is>
       </c>
       <c r="C80" s="13" t="n">
-        <v>85.87</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>84.62</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>83.56999999999999</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F80" s="15" t="n">
-        <v>83.83</v>
+        <v>83.05</v>
       </c>
       <c r="G80" s="15" t="n">
-        <v>84.47</v>
+        <v>83.75</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>83.22</v>
+        <v>82.3</v>
       </c>
       <c r="I80" s="17" t="n">
-        <v>82.58</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J80" s="17" t="n">
-        <v>81.97</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>82.87</v>
+        <v>81.87</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>81.83</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>80.58</v>
+        <v>79.2</v>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O80" s="21" t="n">
-        <v>83.09</v>
+        <v>82.14</v>
       </c>
       <c r="P80" s="21" t="n">
-        <v>82.97</v>
+        <v>81.98</v>
       </c>
       <c r="Q80" s="22" t="n">
-        <v>83.2</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="R80" s="23" t="n">
-        <v>0.12</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="81">
@@ -5594,54 +5594,54 @@
         </is>
       </c>
       <c r="C81" s="13" t="n">
-        <v>4.87</v>
+        <v>5.24</v>
       </c>
       <c r="D81" s="13" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="G81" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" s="16" t="n">
         <v>4.79</v>
       </c>
-      <c r="E81" s="14" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="F81" s="15" t="n">
+      <c r="I81" s="17" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="J81" s="17" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="K81" s="18" t="n">
         <v>4.74</v>
       </c>
-      <c r="G81" s="15" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="H81" s="16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I81" s="17" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="J81" s="17" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="K81" s="18" t="n">
-        <v>4.68</v>
-      </c>
       <c r="L81" s="19" t="n">
-        <v>4.61</v>
+        <v>4.56</v>
       </c>
       <c r="M81" s="19" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N81" s="20" t="inlineStr">
+        <v>4.35</v>
+      </c>
+      <c r="N81" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O81" s="21" t="n">
-        <v>4.69</v>
+        <v>4.77</v>
       </c>
       <c r="P81" s="21" t="n">
-        <v>4.68</v>
+        <v>4.75</v>
       </c>
       <c r="Q81" s="22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R81" s="23" t="n">
-        <v>0.21</v>
+        <v>4.77</v>
+      </c>
+      <c r="R81" s="25" t="n">
+        <v>1.71</v>
       </c>
     </row>
     <row r="82">
@@ -5656,54 +5656,54 @@
         </is>
       </c>
       <c r="C82" s="13" t="n">
-        <v>64.75</v>
+        <v>65.39</v>
       </c>
       <c r="D82" s="13" t="n">
-        <v>63.3</v>
+        <v>63.79</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>62.08</v>
+        <v>62.45</v>
       </c>
       <c r="F82" s="15" t="n">
-        <v>61.92</v>
+        <v>62.3</v>
       </c>
       <c r="G82" s="15" t="n">
-        <v>62.88</v>
+        <v>63.35</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>61.43</v>
+        <v>61.75</v>
       </c>
       <c r="I82" s="17" t="n">
-        <v>60.47</v>
+        <v>60.7</v>
       </c>
       <c r="J82" s="17" t="n">
-        <v>59.98</v>
+        <v>60.15</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>61.27</v>
+        <v>61.55</v>
       </c>
       <c r="L82" s="19" t="n">
-        <v>60.05</v>
+        <v>60.21</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>58.6</v>
+        <v>58.61</v>
       </c>
       <c r="N82" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O82" s="21" t="n">
-        <v>61.41</v>
+        <v>61.71</v>
       </c>
       <c r="P82" s="21" t="n">
-        <v>61.38</v>
+        <v>61.68</v>
       </c>
       <c r="Q82" s="22" t="n">
-        <v>60.95</v>
-      </c>
-      <c r="R82" s="25" t="n">
-        <v>-0.97</v>
+        <v>61.25</v>
+      </c>
+      <c r="R82" s="23" t="n">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="83">
@@ -5718,54 +5718,54 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>40.05</v>
+        <v>39.59</v>
       </c>
       <c r="D83" s="13" t="n">
-        <v>39.65</v>
+        <v>39.29</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>39.31</v>
+        <v>39.03</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>39.35</v>
+        <v>39.08</v>
       </c>
       <c r="G83" s="15" t="n">
-        <v>39.57</v>
+        <v>39.24</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>39.17</v>
+        <v>38.94</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>38.95</v>
+        <v>38.78</v>
       </c>
       <c r="J83" s="17" t="n">
-        <v>38.77</v>
+        <v>38.64</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>39.09</v>
+        <v>38.87</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>38.75</v>
+        <v>38.61</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>38.35</v>
+        <v>38.31</v>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O83" s="21" t="n">
-        <v>39.15</v>
+        <v>38.91</v>
       </c>
       <c r="P83" s="21" t="n">
-        <v>39.12</v>
+        <v>38.89</v>
       </c>
       <c r="Q83" s="22" t="n">
-        <v>39.12</v>
+        <v>38.92</v>
       </c>
       <c r="R83" s="23" t="n">
-        <v>0.1</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="84">
@@ -5780,54 +5780,54 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>96.58</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D84" s="13" t="n">
-        <v>95.48</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>94.56</v>
+        <v>94.48</v>
       </c>
       <c r="F84" s="15" t="n">
-        <v>94.8</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="G84" s="15" t="n">
-        <v>95.34999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>94.25</v>
+        <v>93.75</v>
       </c>
       <c r="I84" s="17" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="J84" s="17" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="K84" s="18" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="L84" s="19" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="M84" s="19" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="N84" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O84" s="21" t="n">
         <v>93.7</v>
       </c>
-      <c r="J84" s="17" t="n">
-        <v>93.15000000000001</v>
-      </c>
-      <c r="K84" s="18" t="n">
-        <v>93.94</v>
-      </c>
-      <c r="L84" s="19" t="n">
-        <v>93.02</v>
-      </c>
-      <c r="M84" s="19" t="n">
-        <v>91.92</v>
-      </c>
-      <c r="N84" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O84" s="21" t="n">
-        <v>94.14</v>
-      </c>
       <c r="P84" s="21" t="n">
-        <v>94.03</v>
+        <v>93.66</v>
       </c>
       <c r="Q84" s="22" t="n">
-        <v>94.25</v>
+        <v>93.25</v>
       </c>
       <c r="R84" s="23" t="n">
-        <v>0.48</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5842,54 +5842,54 @@
         </is>
       </c>
       <c r="C85" s="13" t="n">
-        <v>17.47</v>
+        <v>17.25</v>
       </c>
       <c r="D85" s="13" t="n">
-        <v>17.29</v>
+        <v>17.16</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>17.14</v>
+        <v>17.08</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>17.16</v>
+        <v>17.11</v>
       </c>
       <c r="G85" s="15" t="n">
-        <v>17.26</v>
+        <v>17.15</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>17.08</v>
+        <v>17.06</v>
       </c>
       <c r="I85" s="17" t="n">
-        <v>16.98</v>
+        <v>17.02</v>
       </c>
       <c r="J85" s="17" t="n">
-        <v>16.9</v>
+        <v>16.97</v>
       </c>
       <c r="K85" s="18" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="L85" s="19" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="M85" s="19" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="N85" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O85" s="21" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="P85" s="21" t="n">
         <v>17.04</v>
       </c>
-      <c r="L85" s="19" t="n">
-        <v>16.89</v>
-      </c>
-      <c r="M85" s="19" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="N85" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O85" s="21" t="n">
+      <c r="Q85" s="22" t="n">
         <v>17.07</v>
       </c>
-      <c r="P85" s="21" t="n">
-        <v>17.05</v>
-      </c>
-      <c r="Q85" s="22" t="n">
-        <v>17.06</v>
-      </c>
-      <c r="R85" s="25" t="n">
-        <v>-0.41</v>
+      <c r="R85" s="23" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="86">
@@ -5904,54 +5904,54 @@
         </is>
       </c>
       <c r="C86" s="13" t="n">
-        <v>122.18</v>
+        <v>121.35</v>
       </c>
       <c r="D86" s="13" t="n">
-        <v>121.08</v>
+        <v>119.65</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>120.16</v>
+        <v>118.23</v>
       </c>
       <c r="F86" s="15" t="n">
-        <v>120.63</v>
+        <v>118.3</v>
       </c>
       <c r="G86" s="15" t="n">
-        <v>121.07</v>
+        <v>119.3</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>119.97</v>
+        <v>117.6</v>
       </c>
       <c r="I86" s="17" t="n">
-        <v>119.53</v>
+        <v>116.6</v>
       </c>
       <c r="J86" s="17" t="n">
-        <v>118.87</v>
+        <v>115.9</v>
       </c>
       <c r="K86" s="18" t="n">
-        <v>119.54</v>
+        <v>117.27</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>118.62</v>
+        <v>115.85</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>117.52</v>
+        <v>114.15</v>
       </c>
       <c r="N86" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O86" s="21" t="n">
-        <v>119.8</v>
+        <v>117.5</v>
       </c>
       <c r="P86" s="21" t="n">
-        <v>119.63</v>
+        <v>117.41</v>
       </c>
       <c r="Q86" s="22" t="n">
-        <v>120.2</v>
+        <v>117.3</v>
       </c>
       <c r="R86" s="23" t="n">
-        <v>0.42</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="87">
@@ -5966,54 +5966,54 @@
         </is>
       </c>
       <c r="C87" s="13" t="n">
-        <v>64.65000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>63.6</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>62.72</v>
+        <v>62.89</v>
       </c>
       <c r="F87" s="15" t="n">
-        <v>62.97</v>
+        <v>63.13</v>
       </c>
       <c r="G87" s="15" t="n">
-        <v>63.48</v>
+        <v>63.87</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>62.43</v>
+        <v>62.47</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>61.92</v>
+        <v>61.73</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>61.38</v>
+        <v>61.07</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>62.13</v>
+        <v>62.11</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>61.25</v>
+        <v>60.93</v>
       </c>
       <c r="M87" s="19" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="N87" s="24" t="inlineStr">
+        <v>59.53</v>
+      </c>
+      <c r="N87" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>62.32</v>
+        <v>62.34</v>
       </c>
       <c r="P87" s="21" t="n">
-        <v>62.21</v>
+        <v>62.22</v>
       </c>
       <c r="Q87" s="22" t="n">
-        <v>62.45</v>
-      </c>
-      <c r="R87" s="23" t="n">
-        <v>0.5600000000000001</v>
+        <v>62.4</v>
+      </c>
+      <c r="R87" s="25" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="88">
@@ -6031,51 +6031,51 @@
         <v>10.6</v>
       </c>
       <c r="D88" s="13" t="n">
-        <v>10.35</v>
+        <v>10.37</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>10.14</v>
+        <v>10.18</v>
       </c>
       <c r="F88" s="15" t="n">
-        <v>10.23</v>
+        <v>10.16</v>
       </c>
       <c r="G88" s="15" t="n">
-        <v>10.34</v>
+        <v>10.31</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
       <c r="I88" s="17" t="n">
-        <v>9.98</v>
+        <v>9.93</v>
       </c>
       <c r="J88" s="17" t="n">
-        <v>9.84</v>
+        <v>9.85</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>10</v>
+        <v>10.05</v>
       </c>
       <c r="L88" s="19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>9.550000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N88" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O88" s="21" t="n">
-        <v>10.06</v>
+        <v>10.07</v>
       </c>
       <c r="P88" s="21" t="n">
-        <v>10.02</v>
+        <v>10.07</v>
       </c>
       <c r="Q88" s="22" t="n">
-        <v>10.12</v>
+        <v>10.01</v>
       </c>
       <c r="R88" s="23" t="n">
-        <v>1.71</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="89">
@@ -6090,54 +6090,54 @@
         </is>
       </c>
       <c r="C89" s="13" t="n">
-        <v>19.02</v>
+        <v>18.44</v>
       </c>
       <c r="D89" s="13" t="n">
-        <v>18.37</v>
+        <v>17.86</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>17.83</v>
+        <v>17.37</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>17.77</v>
+        <v>17.42</v>
       </c>
       <c r="G89" s="15" t="n">
-        <v>18.2</v>
+        <v>17.75</v>
       </c>
       <c r="H89" s="16" t="n">
-        <v>17.55</v>
+        <v>17.17</v>
       </c>
       <c r="I89" s="17" t="n">
-        <v>17.12</v>
+        <v>16.84</v>
       </c>
       <c r="J89" s="17" t="n">
-        <v>16.9</v>
+        <v>16.59</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>17.46</v>
+        <v>17.05</v>
       </c>
       <c r="L89" s="19" t="n">
-        <v>16.92</v>
+        <v>16.56</v>
       </c>
       <c r="M89" s="19" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="N89" s="24" t="inlineStr">
+        <v>15.98</v>
+      </c>
+      <c r="N89" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O89" s="21" t="n">
-        <v>17.53</v>
+        <v>17.13</v>
       </c>
       <c r="P89" s="21" t="n">
-        <v>17.51</v>
+        <v>17.09</v>
       </c>
       <c r="Q89" s="22" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="R89" s="25" t="n">
-        <v>-2.53</v>
+        <v>17.09</v>
+      </c>
+      <c r="R89" s="23" t="n">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="90">
@@ -6152,54 +6152,54 @@
         </is>
       </c>
       <c r="C90" s="13" t="n">
-        <v>19.41</v>
+        <v>19.79</v>
       </c>
       <c r="D90" s="13" t="n">
-        <v>19.21</v>
+        <v>19.24</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>19.05</v>
+        <v>18.78</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>19.1</v>
+        <v>18.78</v>
       </c>
       <c r="G90" s="15" t="n">
-        <v>19.19</v>
+        <v>19.12</v>
       </c>
       <c r="H90" s="16" t="n">
-        <v>18.99</v>
+        <v>18.57</v>
       </c>
       <c r="I90" s="17" t="n">
-        <v>18.9</v>
+        <v>18.23</v>
       </c>
       <c r="J90" s="17" t="n">
-        <v>18.79</v>
+        <v>18.02</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>18.93</v>
+        <v>18.47</v>
       </c>
       <c r="L90" s="19" t="n">
-        <v>18.77</v>
+        <v>18.01</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>18.57</v>
+        <v>17.46</v>
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O90" s="21" t="n">
-        <v>18.97</v>
+        <v>18.54</v>
       </c>
       <c r="P90" s="21" t="n">
-        <v>18.95</v>
+        <v>18.51</v>
       </c>
       <c r="Q90" s="22" t="n">
-        <v>19</v>
+        <v>18.45</v>
       </c>
       <c r="R90" s="23" t="n">
-        <v>0</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="91">
@@ -6214,54 +6214,54 @@
         </is>
       </c>
       <c r="C91" s="13" t="n">
-        <v>33.38</v>
+        <v>34.1</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>32.8</v>
+        <v>33.1</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>32.31</v>
+        <v>32.26</v>
       </c>
       <c r="F91" s="15" t="n">
-        <v>32.38</v>
+        <v>32.29</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>32.7</v>
+        <v>32.89</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>32.12</v>
+        <v>31.89</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>31.8</v>
+        <v>31.29</v>
       </c>
       <c r="J91" s="17" t="n">
-        <v>31.54</v>
+        <v>30.89</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>31.99</v>
+        <v>31.7</v>
       </c>
       <c r="L91" s="19" t="n">
-        <v>31.5</v>
+        <v>30.86</v>
       </c>
       <c r="M91" s="19" t="n">
-        <v>30.92</v>
+        <v>29.86</v>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O91" s="21" t="n">
-        <v>32.08</v>
+        <v>31.83</v>
       </c>
       <c r="P91" s="21" t="n">
-        <v>32.03</v>
+        <v>31.78</v>
       </c>
       <c r="Q91" s="22" t="n">
-        <v>32.06</v>
-      </c>
-      <c r="R91" s="25" t="n">
-        <v>-0.31</v>
+        <v>31.7</v>
+      </c>
+      <c r="R91" s="23" t="n">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="92">
@@ -6276,54 +6276,54 @@
         </is>
       </c>
       <c r="C92" s="13" t="n">
-        <v>22.2</v>
+        <v>23.09</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>21.73</v>
+        <v>22.46</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>21.34</v>
+        <v>21.93</v>
       </c>
       <c r="F92" s="15" t="n">
-        <v>21.49</v>
+        <v>21.95</v>
       </c>
       <c r="G92" s="15" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="H92" s="16" t="n">
         <v>21.7</v>
       </c>
-      <c r="H92" s="16" t="n">
-        <v>21.23</v>
-      </c>
       <c r="I92" s="17" t="n">
-        <v>21.02</v>
+        <v>21.32</v>
       </c>
       <c r="J92" s="17" t="n">
-        <v>20.76</v>
+        <v>21.07</v>
       </c>
       <c r="K92" s="18" t="n">
-        <v>21.07</v>
+        <v>21.58</v>
       </c>
       <c r="L92" s="19" t="n">
-        <v>20.68</v>
+        <v>21.05</v>
       </c>
       <c r="M92" s="19" t="n">
-        <v>20.21</v>
-      </c>
-      <c r="N92" s="20" t="inlineStr">
+        <v>20.42</v>
+      </c>
+      <c r="N92" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O92" s="21" t="n">
-        <v>21.17</v>
+        <v>21.66</v>
       </c>
       <c r="P92" s="21" t="n">
-        <v>21.11</v>
+        <v>21.63</v>
       </c>
       <c r="Q92" s="22" t="n">
-        <v>21.28</v>
+        <v>21.58</v>
       </c>
       <c r="R92" s="23" t="n">
-        <v>1.58</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="93">
@@ -6338,54 +6338,54 @@
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>29.33</v>
+        <v>29.47</v>
       </c>
       <c r="D93" s="13" t="n">
-        <v>28.99</v>
+        <v>29.17</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>28.71</v>
+        <v>28.91</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>28.81</v>
+        <v>28.92</v>
       </c>
       <c r="G93" s="15" t="n">
-        <v>28.97</v>
+        <v>29.1</v>
       </c>
       <c r="H93" s="16" t="n">
-        <v>28.63</v>
+        <v>28.8</v>
       </c>
       <c r="I93" s="17" t="n">
-        <v>28.47</v>
+        <v>28.62</v>
       </c>
       <c r="J93" s="17" t="n">
-        <v>28.29</v>
+        <v>28.5</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>28.51</v>
+        <v>28.75</v>
       </c>
       <c r="L93" s="19" t="n">
-        <v>28.23</v>
+        <v>28.49</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>27.89</v>
-      </c>
-      <c r="N93" s="20" t="inlineStr">
+        <v>28.19</v>
+      </c>
+      <c r="N93" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>28.58</v>
+        <v>28.78</v>
       </c>
       <c r="P93" s="21" t="n">
-        <v>28.54</v>
+        <v>28.77</v>
       </c>
       <c r="Q93" s="22" t="n">
-        <v>28.66</v>
+        <v>28.74</v>
       </c>
       <c r="R93" s="23" t="n">
-        <v>0.42</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -6400,54 +6400,54 @@
         </is>
       </c>
       <c r="C94" s="13" t="n">
-        <v>174.57</v>
+        <v>173.11</v>
       </c>
       <c r="D94" s="13" t="n">
-        <v>171.87</v>
+        <v>171.31</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>169.61</v>
+        <v>169.8</v>
       </c>
       <c r="F94" s="15" t="n">
-        <v>169.5</v>
+        <v>169.93</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>171.2</v>
+        <v>170.97</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>168.5</v>
+        <v>169.17</v>
       </c>
       <c r="I94" s="17" t="n">
-        <v>166.8</v>
+        <v>168.13</v>
       </c>
       <c r="J94" s="17" t="n">
-        <v>165.8</v>
+        <v>167.37</v>
       </c>
       <c r="K94" s="18" t="n">
-        <v>168.09</v>
+        <v>168.8</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>165.83</v>
+        <v>167.29</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>163.13</v>
+        <v>165.49</v>
       </c>
       <c r="N94" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>168.4</v>
+        <v>169.05</v>
       </c>
       <c r="P94" s="21" t="n">
-        <v>168.3</v>
+        <v>168.94</v>
       </c>
       <c r="Q94" s="22" t="n">
-        <v>167.8</v>
+        <v>168.9</v>
       </c>
       <c r="R94" s="25" t="n">
-        <v>-0.59</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="95">
@@ -6462,54 +6462,54 @@
         </is>
       </c>
       <c r="C95" s="13" t="n">
-        <v>14.59</v>
+        <v>15.63</v>
       </c>
       <c r="D95" s="13" t="n">
-        <v>14.29</v>
+        <v>15.11</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>14.03</v>
+        <v>14.68</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>14.17</v>
+        <v>14.72</v>
       </c>
       <c r="G95" s="15" t="n">
-        <v>14.29</v>
+        <v>15.02</v>
       </c>
       <c r="H95" s="16" t="n">
-        <v>13.99</v>
+        <v>14.5</v>
       </c>
       <c r="I95" s="17" t="n">
-        <v>13.87</v>
+        <v>14.2</v>
       </c>
       <c r="J95" s="17" t="n">
-        <v>13.69</v>
+        <v>13.98</v>
       </c>
       <c r="K95" s="18" t="n">
-        <v>13.87</v>
+        <v>14.38</v>
       </c>
       <c r="L95" s="19" t="n">
-        <v>13.61</v>
+        <v>13.95</v>
       </c>
       <c r="M95" s="19" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="N95" s="20" t="inlineStr">
+        <v>13.43</v>
+      </c>
+      <c r="N95" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O95" s="21" t="n">
-        <v>13.94</v>
+        <v>14.46</v>
       </c>
       <c r="P95" s="21" t="n">
-        <v>13.89</v>
+        <v>14.42</v>
       </c>
       <c r="Q95" s="22" t="n">
-        <v>14.06</v>
-      </c>
-      <c r="R95" s="23" t="n">
-        <v>1.74</v>
+        <v>14.43</v>
+      </c>
+      <c r="R95" s="25" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="96">
@@ -6524,54 +6524,54 @@
         </is>
       </c>
       <c r="C96" s="13" t="n">
-        <v>22.41</v>
+        <v>22.23</v>
       </c>
       <c r="D96" s="13" t="n">
-        <v>21.63</v>
+        <v>21.72</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>20.98</v>
+        <v>21.29</v>
       </c>
       <c r="F96" s="15" t="n">
-        <v>21.41</v>
+        <v>21.28</v>
       </c>
       <c r="G96" s="15" t="n">
-        <v>21.67</v>
+        <v>21.6</v>
       </c>
       <c r="H96" s="16" t="n">
-        <v>20.89</v>
+        <v>21.09</v>
       </c>
       <c r="I96" s="17" t="n">
-        <v>20.63</v>
+        <v>20.77</v>
       </c>
       <c r="J96" s="17" t="n">
-        <v>20.11</v>
+        <v>20.58</v>
       </c>
       <c r="K96" s="18" t="n">
-        <v>20.54</v>
+        <v>21</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>19.89</v>
+        <v>20.57</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>19.11</v>
+        <v>20.06</v>
       </c>
       <c r="N96" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O96" s="21" t="n">
-        <v>20.75</v>
+        <v>21.06</v>
       </c>
       <c r="P96" s="21" t="n">
-        <v>20.6</v>
+        <v>21.04</v>
       </c>
       <c r="Q96" s="22" t="n">
-        <v>21.15</v>
+        <v>20.97</v>
       </c>
       <c r="R96" s="23" t="n">
-        <v>3.42</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="97">
@@ -6586,54 +6586,54 @@
         </is>
       </c>
       <c r="C97" s="13" t="n">
-        <v>16.55</v>
+        <v>16.67</v>
       </c>
       <c r="D97" s="13" t="n">
-        <v>16.4</v>
+        <v>16.53</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>16.28</v>
+        <v>16.41</v>
       </c>
       <c r="F97" s="15" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="G97" s="15" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="H97" s="16" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="I97" s="17" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="J97" s="17" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="K97" s="18" t="n">
         <v>16.33</v>
       </c>
-      <c r="G97" s="15" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="H97" s="16" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="I97" s="17" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="J97" s="17" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="K97" s="18" t="n">
-        <v>16.19</v>
-      </c>
       <c r="L97" s="19" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="M97" s="19" t="n">
         <v>16.07</v>
       </c>
-      <c r="M97" s="19" t="n">
-        <v>15.92</v>
-      </c>
-      <c r="N97" s="20" t="inlineStr">
+      <c r="N97" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O97" s="21" t="n">
-        <v>16.23</v>
+        <v>16.35</v>
       </c>
       <c r="P97" s="21" t="n">
-        <v>16.2</v>
+        <v>16.34</v>
       </c>
       <c r="Q97" s="22" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="R97" s="23" t="n">
-        <v>0.49</v>
+        <v>16.36</v>
+      </c>
+      <c r="R97" s="25" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="98">
@@ -6648,54 +6648,54 @@
         </is>
       </c>
       <c r="C98" s="13" t="n">
-        <v>10.4</v>
+        <v>10.42</v>
       </c>
       <c r="D98" s="13" t="n">
-        <v>10.2</v>
+        <v>10.16</v>
       </c>
       <c r="E98" s="14" t="n">
-        <v>10.04</v>
+        <v>9.94</v>
       </c>
       <c r="F98" s="15" t="n">
-        <v>10.08</v>
+        <v>9.93</v>
       </c>
       <c r="G98" s="15" t="n">
-        <v>10.18</v>
+        <v>10.1</v>
       </c>
       <c r="H98" s="16" t="n">
-        <v>9.98</v>
+        <v>9.84</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>9.880000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="J98" s="17" t="n">
-        <v>9.779999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>9.92</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>9.76</v>
+        <v>9.58</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="N98" s="24" t="inlineStr">
+        <v>9.32</v>
+      </c>
+      <c r="N98" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O98" s="21" t="n">
-        <v>9.960000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="P98" s="21" t="n">
-        <v>9.94</v>
+        <v>9.82</v>
       </c>
       <c r="Q98" s="22" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="R98" s="25" t="n">
-        <v>-0.2</v>
+        <v>9.77</v>
+      </c>
+      <c r="R98" s="23" t="n">
+        <v>-2.79</v>
       </c>
     </row>
     <row r="99">
@@ -6710,54 +6710,54 @@
         </is>
       </c>
       <c r="C99" s="13" t="n">
-        <v>27.27</v>
+        <v>27.48</v>
       </c>
       <c r="D99" s="13" t="n">
-        <v>26.97</v>
+        <v>27.12</v>
       </c>
       <c r="E99" s="14" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="F99" s="15" t="n">
+        <v>26.87</v>
+      </c>
+      <c r="G99" s="15" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="H99" s="16" t="n">
         <v>26.71</v>
       </c>
-      <c r="F99" s="15" t="n">
-        <v>26.76</v>
-      </c>
-      <c r="G99" s="15" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="H99" s="16" t="n">
+      <c r="I99" s="17" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="J99" s="17" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="K99" s="18" t="n">
         <v>26.62</v>
       </c>
-      <c r="I99" s="17" t="n">
-        <v>26.46</v>
-      </c>
-      <c r="J99" s="17" t="n">
+      <c r="L99" s="19" t="n">
         <v>26.32</v>
       </c>
-      <c r="K99" s="18" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="L99" s="19" t="n">
-        <v>26.29</v>
-      </c>
       <c r="M99" s="19" t="n">
-        <v>25.99</v>
-      </c>
-      <c r="N99" s="20" t="inlineStr">
+        <v>25.96</v>
+      </c>
+      <c r="N99" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O99" s="21" t="n">
-        <v>26.59</v>
+        <v>26.68</v>
       </c>
       <c r="P99" s="21" t="n">
-        <v>26.57</v>
+        <v>26.65</v>
       </c>
       <c r="Q99" s="22" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R99" s="23" t="n">
-        <v>0</v>
+        <v>26.68</v>
+      </c>
+      <c r="R99" s="25" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="100">
@@ -6772,54 +6772,54 @@
         </is>
       </c>
       <c r="C100" s="13" t="n">
-        <v>17.68</v>
+        <v>17.75</v>
       </c>
       <c r="D100" s="13" t="n">
-        <v>17.42</v>
+        <v>17.52</v>
       </c>
       <c r="E100" s="14" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="F100" s="15" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="G100" s="15" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="H100" s="16" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="I100" s="17" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J100" s="17" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="K100" s="18" t="n">
         <v>17.2</v>
       </c>
-      <c r="F100" s="15" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="G100" s="15" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="H100" s="16" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="I100" s="17" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="J100" s="17" t="n">
-        <v>16.91</v>
-      </c>
-      <c r="K100" s="18" t="n">
-        <v>17.06</v>
-      </c>
       <c r="L100" s="19" t="n">
-        <v>16.84</v>
+        <v>17.01</v>
       </c>
       <c r="M100" s="19" t="n">
-        <v>16.58</v>
+        <v>16.78</v>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O100" s="21" t="n">
-        <v>17.12</v>
+        <v>17.23</v>
       </c>
       <c r="P100" s="21" t="n">
-        <v>17.08</v>
+        <v>17.22</v>
       </c>
       <c r="Q100" s="22" t="n">
-        <v>17.25</v>
+        <v>17.19</v>
       </c>
       <c r="R100" s="23" t="n">
-        <v>1.83</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="101">
@@ -6834,54 +6834,54 @@
         </is>
       </c>
       <c r="C101" s="13" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="D101" s="13" t="n">
+        <v>33.31</v>
+      </c>
+      <c r="E101" s="14" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="F101" s="15" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="G101" s="15" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="H101" s="16" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="I101" s="17" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="J101" s="17" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="K101" s="18" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="L101" s="19" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="M101" s="19" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="N101" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O101" s="21" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="P101" s="21" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="Q101" s="22" t="n">
         <v>32.58</v>
       </c>
-      <c r="D101" s="13" t="n">
-        <v>32.36</v>
-      </c>
-      <c r="E101" s="14" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="F101" s="15" t="n">
-        <v>32.15</v>
-      </c>
-      <c r="G101" s="15" t="n">
-        <v>32.29</v>
-      </c>
-      <c r="H101" s="16" t="n">
-        <v>32.07</v>
-      </c>
-      <c r="I101" s="17" t="n">
-        <v>31.93</v>
-      </c>
-      <c r="J101" s="17" t="n">
-        <v>31.85</v>
-      </c>
-      <c r="K101" s="18" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="L101" s="19" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="M101" s="19" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="N101" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O101" s="21" t="n">
-        <v>32.07</v>
-      </c>
-      <c r="P101" s="21" t="n">
-        <v>32.07</v>
-      </c>
-      <c r="Q101" s="22" t="n">
-        <v>32</v>
-      </c>
       <c r="R101" s="25" t="n">
-        <v>-0.25</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="102">
@@ -6896,54 +6896,54 @@
         </is>
       </c>
       <c r="C102" s="13" t="n">
-        <v>17.08</v>
+        <v>16.51</v>
       </c>
       <c r="D102" s="13" t="n">
-        <v>16.54</v>
+        <v>16.24</v>
       </c>
       <c r="E102" s="14" t="n">
-        <v>16.09</v>
+        <v>16.01</v>
       </c>
       <c r="F102" s="15" t="n">
-        <v>16.24</v>
+        <v>16.16</v>
       </c>
       <c r="G102" s="15" t="n">
-        <v>16.5</v>
+        <v>16.25</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>15.96</v>
+        <v>15.98</v>
       </c>
       <c r="I102" s="17" t="n">
-        <v>15.7</v>
+        <v>15.89</v>
       </c>
       <c r="J102" s="17" t="n">
-        <v>15.42</v>
+        <v>15.71</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>15.79</v>
+        <v>15.86</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>15.34</v>
+        <v>15.63</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="N102" s="20" t="inlineStr">
+        <v>15.36</v>
+      </c>
+      <c r="N102" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O102" s="21" t="n">
-        <v>15.89</v>
+        <v>15.93</v>
       </c>
       <c r="P102" s="21" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="Q102" s="22" t="n">
-        <v>15.99</v>
-      </c>
-      <c r="R102" s="23" t="n">
-        <v>2.04</v>
+        <v>16.07</v>
+      </c>
+      <c r="R102" s="25" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="103">
@@ -6958,54 +6958,54 @@
         </is>
       </c>
       <c r="C103" s="13" t="n">
-        <v>75.02</v>
+        <v>73.88</v>
       </c>
       <c r="D103" s="13" t="n">
-        <v>74.02</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>73.18000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>73.47</v>
+        <v>72.75</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>73.93000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>72.93000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>72.47</v>
+        <v>72.05</v>
       </c>
       <c r="J103" s="17" t="n">
-        <v>71.93000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>72.62</v>
+        <v>72.2</v>
       </c>
       <c r="L103" s="19" t="n">
-        <v>71.78</v>
+        <v>71.62</v>
       </c>
       <c r="M103" s="19" t="n">
-        <v>70.78</v>
-      </c>
-      <c r="N103" s="20" t="inlineStr">
+        <v>70.92</v>
+      </c>
+      <c r="N103" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O103" s="21" t="n">
-        <v>72.81999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="P103" s="21" t="n">
-        <v>72.7</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="Q103" s="22" t="n">
-        <v>73</v>
-      </c>
-      <c r="R103" s="23" t="n">
-        <v>0.55</v>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="R103" s="25" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="104">
@@ -7020,54 +7020,54 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>15.98</v>
+        <v>15.69</v>
       </c>
       <c r="D104" s="13" t="n">
-        <v>15.56</v>
+        <v>15.51</v>
       </c>
       <c r="E104" s="14" t="n">
-        <v>15.21</v>
+        <v>15.36</v>
       </c>
       <c r="F104" s="15" t="n">
-        <v>15.33</v>
+        <v>15.41</v>
       </c>
       <c r="G104" s="15" t="n">
-        <v>15.52</v>
+        <v>15.49</v>
       </c>
       <c r="H104" s="16" t="n">
-        <v>15.1</v>
+        <v>15.31</v>
       </c>
       <c r="I104" s="17" t="n">
-        <v>14.91</v>
+        <v>15.23</v>
       </c>
       <c r="J104" s="17" t="n">
-        <v>14.68</v>
+        <v>15.13</v>
       </c>
       <c r="K104" s="18" t="n">
-        <v>14.97</v>
+        <v>15.26</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>14.62</v>
+        <v>15.11</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N104" s="20" t="inlineStr">
+        <v>14.93</v>
+      </c>
+      <c r="N104" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O104" s="21" t="n">
-        <v>15.05</v>
+        <v>15.29</v>
       </c>
       <c r="P104" s="21" t="n">
-        <v>15.01</v>
+        <v>15.27</v>
       </c>
       <c r="Q104" s="22" t="n">
-        <v>15.13</v>
-      </c>
-      <c r="R104" s="23" t="n">
-        <v>0.87</v>
+        <v>15.32</v>
+      </c>
+      <c r="R104" s="25" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="105">
@@ -7082,54 +7082,54 @@
         </is>
       </c>
       <c r="C105" s="13" t="n">
-        <v>18.1</v>
+        <v>17.72</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>17.72</v>
+        <v>17.45</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>17.41</v>
+        <v>17.22</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>17.38</v>
+        <v>17.31</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>17.62</v>
+        <v>17.43</v>
       </c>
       <c r="H105" s="16" t="n">
-        <v>17.24</v>
+        <v>17.16</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>17</v>
+        <v>17.04</v>
       </c>
       <c r="J105" s="17" t="n">
-        <v>16.86</v>
+        <v>16.89</v>
       </c>
       <c r="K105" s="18" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="L105" s="19" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="M105" s="19" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="N105" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O105" s="21" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="P105" s="21" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="Q105" s="22" t="n">
         <v>17.19</v>
       </c>
-      <c r="L105" s="19" t="n">
-        <v>16.88</v>
-      </c>
-      <c r="M105" s="19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N105" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O105" s="21" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="P105" s="21" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="Q105" s="22" t="n">
-        <v>17.13</v>
-      </c>
-      <c r="R105" s="25" t="n">
-        <v>-1.21</v>
+      <c r="R105" s="23" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="106">
@@ -7144,54 +7144,54 @@
         </is>
       </c>
       <c r="C106" s="13" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="D106" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E106" s="14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F106" s="15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G106" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H106" s="16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I106" s="17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J106" s="17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K106" s="18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L106" s="19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M106" s="19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N106" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O106" s="21" t="n">
         <v>2.43</v>
       </c>
-      <c r="E106" s="14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F106" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G106" s="15" t="n">
+      <c r="P106" s="21" t="n">
         <v>2.42</v>
       </c>
-      <c r="H106" s="16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="I106" s="17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J106" s="17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="K106" s="18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="L106" s="19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M106" s="19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="N106" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O106" s="21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P106" s="21" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q106" s="22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="R106" s="23" t="n">
-        <v>0</v>
+        <v>2.46</v>
+      </c>
+      <c r="R106" s="25" t="n">
+        <v>4.24</v>
       </c>
     </row>
     <row r="107">
@@ -7206,54 +7206,54 @@
         </is>
       </c>
       <c r="C107" s="13" t="n">
-        <v>40.88</v>
+        <v>41.4</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>40.52</v>
+        <v>40.92</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>40.22</v>
+        <v>40.51</v>
       </c>
       <c r="F107" s="15" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="G107" s="15" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="H107" s="16" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="I107" s="17" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="J107" s="17" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="K107" s="18" t="n">
         <v>40.25</v>
       </c>
-      <c r="G107" s="15" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="H107" s="16" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="I107" s="17" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="J107" s="17" t="n">
-        <v>39.73</v>
-      </c>
-      <c r="K107" s="18" t="n">
-        <v>40.02</v>
-      </c>
       <c r="L107" s="19" t="n">
-        <v>39.72</v>
+        <v>39.84</v>
       </c>
       <c r="M107" s="19" t="n">
         <v>39.36</v>
       </c>
-      <c r="N107" s="24" t="inlineStr">
+      <c r="N107" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O107" s="21" t="n">
-        <v>40.07</v>
+        <v>40.3</v>
       </c>
       <c r="P107" s="21" t="n">
-        <v>40.05</v>
+        <v>40.28</v>
       </c>
       <c r="Q107" s="22" t="n">
-        <v>40.04</v>
-      </c>
-      <c r="R107" s="25" t="n">
-        <v>-0.5</v>
+        <v>40.18</v>
+      </c>
+      <c r="R107" s="23" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="108">
@@ -7268,54 +7268,54 @@
         </is>
       </c>
       <c r="C108" s="13" t="n">
-        <v>8.41</v>
+        <v>8.74</v>
       </c>
       <c r="D108" s="13" t="n">
-        <v>8.31</v>
+        <v>8.52</v>
       </c>
       <c r="E108" s="14" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="F108" s="15" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="G108" s="15" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="H108" s="16" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I108" s="17" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="J108" s="17" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="K108" s="18" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="L108" s="19" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="M108" s="19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="N108" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O108" s="21" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="P108" s="21" t="n">
         <v>8.23</v>
       </c>
-      <c r="F108" s="15" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="G108" s="15" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="H108" s="16" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="I108" s="17" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="J108" s="17" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="K108" s="18" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="L108" s="19" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="M108" s="19" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="N108" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O108" s="21" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="P108" s="21" t="n">
-        <v>8.18</v>
-      </c>
       <c r="Q108" s="22" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="R108" s="23" t="n">
-        <v>0.12</v>
+        <v>8.359999999999999</v>
+      </c>
+      <c r="R108" s="25" t="n">
+        <v>2.08</v>
       </c>
     </row>
     <row r="109">
@@ -7330,54 +7330,54 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>45.72</v>
+        <v>45.28</v>
       </c>
       <c r="D109" s="13" t="n">
-        <v>45.14</v>
+        <v>44.92</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>44.65</v>
+        <v>44.62</v>
       </c>
       <c r="F109" s="15" t="n">
-        <v>44.85</v>
+        <v>44.62</v>
       </c>
       <c r="G109" s="15" t="n">
-        <v>45.11</v>
+        <v>44.84</v>
       </c>
       <c r="H109" s="16" t="n">
-        <v>44.53</v>
+        <v>44.48</v>
       </c>
       <c r="I109" s="17" t="n">
-        <v>44.27</v>
+        <v>44.26</v>
       </c>
       <c r="J109" s="17" t="n">
-        <v>43.95</v>
+        <v>44.12</v>
       </c>
       <c r="K109" s="18" t="n">
-        <v>44.33</v>
+        <v>44.42</v>
       </c>
       <c r="L109" s="19" t="n">
-        <v>43.84</v>
+        <v>44.12</v>
       </c>
       <c r="M109" s="19" t="n">
-        <v>43.26</v>
+        <v>43.76</v>
       </c>
       <c r="N109" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O109" s="21" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="P109" s="21" t="n">
         <v>44.45</v>
       </c>
-      <c r="P109" s="21" t="n">
-        <v>44.37</v>
-      </c>
       <c r="Q109" s="22" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="R109" s="23" t="n">
-        <v>0.72</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="110">
@@ -7392,54 +7392,54 @@
         </is>
       </c>
       <c r="C110" s="13" t="n">
-        <v>73.11</v>
+        <v>71.52</v>
       </c>
       <c r="D110" s="13" t="n">
-        <v>70.26000000000001</v>
+        <v>69.62</v>
       </c>
       <c r="E110" s="14" t="n">
-        <v>67.87</v>
+        <v>68.03</v>
       </c>
       <c r="F110" s="15" t="n">
-        <v>68.75</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="G110" s="15" t="n">
-        <v>70.05</v>
+        <v>69.08</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>67.2</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>65.90000000000001</v>
+        <v>65.92</v>
       </c>
       <c r="J110" s="17" t="n">
-        <v>64.34999999999999</v>
+        <v>65.28</v>
       </c>
       <c r="K110" s="18" t="n">
-        <v>66.28</v>
+        <v>66.97</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>63.89</v>
+        <v>65.38</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>61.04</v>
+        <v>63.48</v>
       </c>
       <c r="N110" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O110" s="21" t="n">
-        <v>66.84999999999999</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="P110" s="21" t="n">
-        <v>66.5</v>
+        <v>67.12</v>
       </c>
       <c r="Q110" s="22" t="n">
-        <v>67.45</v>
+        <v>66.55</v>
       </c>
       <c r="R110" s="23" t="n">
-        <v>3.06</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="111">
@@ -7454,54 +7454,54 @@
         </is>
       </c>
       <c r="C111" s="13" t="n">
-        <v>10.71</v>
+        <v>10.73</v>
       </c>
       <c r="D111" s="13" t="n">
-        <v>10.6</v>
+        <v>10.63</v>
       </c>
       <c r="E111" s="14" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="F111" s="15" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="G111" s="15" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="H111" s="16" t="n">
         <v>10.51</v>
       </c>
-      <c r="F111" s="15" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="G111" s="15" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H111" s="16" t="n">
+      <c r="I111" s="17" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="J111" s="17" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="K111" s="18" t="n">
         <v>10.49</v>
       </c>
-      <c r="I111" s="17" t="n">
-        <v>10.45</v>
-      </c>
-      <c r="J111" s="17" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="K111" s="18" t="n">
-        <v>10.44</v>
-      </c>
       <c r="L111" s="19" t="n">
-        <v>10.35</v>
+        <v>10.41</v>
       </c>
       <c r="M111" s="19" t="n">
-        <v>10.24</v>
+        <v>10.31</v>
       </c>
       <c r="N111" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O111" s="21" t="n">
-        <v>10.47</v>
+        <v>10.5</v>
       </c>
       <c r="P111" s="21" t="n">
-        <v>10.45</v>
+        <v>10.5</v>
       </c>
       <c r="Q111" s="22" t="n">
-        <v>10.52</v>
+        <v>10.48</v>
       </c>
       <c r="R111" s="23" t="n">
-        <v>0.86</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="112">
@@ -7516,54 +7516,54 @@
         </is>
       </c>
       <c r="C112" s="13" t="n">
-        <v>383.3</v>
+        <v>329.53</v>
       </c>
       <c r="D112" s="13" t="n">
-        <v>355.3</v>
+        <v>315.73</v>
       </c>
       <c r="E112" s="14" t="n">
-        <v>331.84</v>
+        <v>304.16</v>
       </c>
       <c r="F112" s="15" t="n">
-        <v>329.6</v>
+        <v>305.53</v>
       </c>
       <c r="G112" s="15" t="n">
-        <v>347.8</v>
+        <v>313.27</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>319.8</v>
+        <v>299.47</v>
       </c>
       <c r="I112" s="17" t="n">
-        <v>301.6</v>
+        <v>291.73</v>
       </c>
       <c r="J112" s="17" t="n">
-        <v>291.8</v>
+        <v>285.67</v>
       </c>
       <c r="K112" s="18" t="n">
-        <v>316.16</v>
+        <v>296.44</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>292.7</v>
+        <v>284.87</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>264.7</v>
-      </c>
-      <c r="N112" s="24" t="inlineStr">
+        <v>271.07</v>
+      </c>
+      <c r="N112" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O112" s="21" t="n">
-        <v>319.07</v>
+        <v>298.49</v>
       </c>
       <c r="P112" s="21" t="n">
-        <v>318.34</v>
+        <v>297.51</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>311.4</v>
-      </c>
-      <c r="R112" s="25" t="n">
-        <v>-3.11</v>
+        <v>297.8</v>
+      </c>
+      <c r="R112" s="23" t="n">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="113">
@@ -7578,54 +7578,54 @@
         </is>
       </c>
       <c r="C113" s="13" t="n">
-        <v>226.73</v>
+        <v>225.64</v>
       </c>
       <c r="D113" s="13" t="n">
-        <v>218.43</v>
+        <v>220.24</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>211.47</v>
+        <v>215.71</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>215.13</v>
+        <v>215.3</v>
       </c>
       <c r="G113" s="15" t="n">
-        <v>218.37</v>
+        <v>218.8</v>
       </c>
       <c r="H113" s="16" t="n">
-        <v>210.07</v>
+        <v>213.4</v>
       </c>
       <c r="I113" s="17" t="n">
-        <v>206.83</v>
+        <v>209.9</v>
       </c>
       <c r="J113" s="17" t="n">
-        <v>201.77</v>
+        <v>208</v>
       </c>
       <c r="K113" s="18" t="n">
-        <v>206.83</v>
+        <v>212.69</v>
       </c>
       <c r="L113" s="19" t="n">
-        <v>199.87</v>
+        <v>208.16</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>191.57</v>
+        <v>202.76</v>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O113" s="21" t="n">
-        <v>208.77</v>
+        <v>213.25</v>
       </c>
       <c r="P113" s="21" t="n">
-        <v>207.47</v>
+        <v>213.11</v>
       </c>
       <c r="Q113" s="22" t="n">
-        <v>211.9</v>
+        <v>211.8</v>
       </c>
       <c r="R113" s="23" t="n">
-        <v>2.42</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="114">
@@ -7640,54 +7640,54 @@
         </is>
       </c>
       <c r="C114" s="13" t="n">
-        <v>667.73</v>
+        <v>687.3200000000001</v>
       </c>
       <c r="D114" s="13" t="n">
-        <v>655.23</v>
+        <v>669.8200000000001</v>
       </c>
       <c r="E114" s="14" t="n">
-        <v>644.75</v>
+        <v>655.15</v>
       </c>
       <c r="F114" s="15" t="n">
-        <v>649.33</v>
+        <v>655.5</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>654.67</v>
+        <v>666</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>642.17</v>
+        <v>648.5</v>
       </c>
       <c r="I114" s="17" t="n">
-        <v>636.83</v>
+        <v>638</v>
       </c>
       <c r="J114" s="17" t="n">
-        <v>629.67</v>
+        <v>631</v>
       </c>
       <c r="K114" s="18" t="n">
-        <v>637.75</v>
+        <v>645.35</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>627.27</v>
+        <v>630.6799999999999</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>614.77</v>
+        <v>613.1799999999999</v>
       </c>
       <c r="N114" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O114" s="21" t="n">
-        <v>640.45</v>
+        <v>647.61</v>
       </c>
       <c r="P114" s="21" t="n">
-        <v>638.73</v>
+        <v>646.72</v>
       </c>
       <c r="Q114" s="22" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="R114" s="23" t="n">
-        <v>0.62</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="115">
@@ -7702,54 +7702,54 @@
         </is>
       </c>
       <c r="C115" s="13" t="n">
-        <v>7.18</v>
+        <v>7.36</v>
       </c>
       <c r="D115" s="13" t="n">
-        <v>6.97</v>
+        <v>7.16</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>6.79</v>
+        <v>7</v>
       </c>
       <c r="F115" s="15" t="n">
-        <v>6.78</v>
+        <v>7.01</v>
       </c>
       <c r="G115" s="15" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="H115" s="16" t="n">
         <v>6.92</v>
       </c>
-      <c r="H115" s="16" t="n">
-        <v>6.71</v>
-      </c>
       <c r="I115" s="17" t="n">
-        <v>6.57</v>
+        <v>6.81</v>
       </c>
       <c r="J115" s="17" t="n">
-        <v>6.5</v>
+        <v>6.72</v>
       </c>
       <c r="K115" s="18" t="n">
-        <v>6.68</v>
+        <v>6.88</v>
       </c>
       <c r="L115" s="19" t="n">
-        <v>6.5</v>
+        <v>6.72</v>
       </c>
       <c r="M115" s="19" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="N115" s="20" t="inlineStr">
+        <v>6.52</v>
+      </c>
+      <c r="N115" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O115" s="21" t="n">
-        <v>6.7</v>
+        <v>6.91</v>
       </c>
       <c r="P115" s="21" t="n">
-        <v>6.69</v>
+        <v>6.9</v>
       </c>
       <c r="Q115" s="22" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="R115" s="23" t="n">
-        <v>1.37</v>
+        <v>6.89</v>
+      </c>
+      <c r="R115" s="25" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="116">
@@ -7764,54 +7764,54 @@
         </is>
       </c>
       <c r="C116" s="13" t="n">
-        <v>148.3</v>
+        <v>144.02</v>
       </c>
       <c r="D116" s="13" t="n">
-        <v>144.9</v>
+        <v>141.72</v>
       </c>
       <c r="E116" s="14" t="n">
-        <v>142.05</v>
+        <v>139.79</v>
       </c>
       <c r="F116" s="15" t="n">
-        <v>141.67</v>
+        <v>140.13</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>143.93</v>
+        <v>141.37</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>140.53</v>
+        <v>139.07</v>
       </c>
       <c r="I116" s="17" t="n">
-        <v>138.27</v>
+        <v>137.83</v>
       </c>
       <c r="J116" s="17" t="n">
-        <v>137.13</v>
+        <v>136.77</v>
       </c>
       <c r="K116" s="18" t="n">
-        <v>140.15</v>
+        <v>138.51</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>137.3</v>
+        <v>136.58</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>133.9</v>
-      </c>
-      <c r="N116" s="24" t="inlineStr">
+        <v>134.28</v>
+      </c>
+      <c r="N116" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>140.47</v>
+        <v>138.88</v>
       </c>
       <c r="P116" s="21" t="n">
-        <v>140.41</v>
+        <v>138.69</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>139.4</v>
-      </c>
-      <c r="R116" s="25" t="n">
-        <v>-1.41</v>
+        <v>138.9</v>
+      </c>
+      <c r="R116" s="23" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7826,54 +7826,54 @@
         </is>
       </c>
       <c r="C117" s="13" t="n">
-        <v>11.17</v>
+        <v>11.12</v>
       </c>
       <c r="D117" s="13" t="n">
         <v>10.81</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>10.51</v>
+        <v>10.55</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>10.64</v>
+        <v>10.52</v>
       </c>
       <c r="G117" s="15" t="n">
-        <v>10.79</v>
+        <v>10.72</v>
       </c>
       <c r="H117" s="16" t="n">
-        <v>10.43</v>
+        <v>10.41</v>
       </c>
       <c r="I117" s="17" t="n">
-        <v>10.28</v>
+        <v>10.21</v>
       </c>
       <c r="J117" s="17" t="n">
-        <v>10.07</v>
+        <v>10.1</v>
       </c>
       <c r="K117" s="18" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="L117" s="19" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="M117" s="19" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="N117" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O117" s="21" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="P117" s="21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q117" s="22" t="n">
         <v>10.31</v>
       </c>
-      <c r="L117" s="19" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="M117" s="19" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="N117" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O117" s="21" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="P117" s="21" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="Q117" s="22" t="n">
-        <v>10.48</v>
-      </c>
       <c r="R117" s="23" t="n">
-        <v>3.25</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="118">
@@ -7888,54 +7888,54 @@
         </is>
       </c>
       <c r="C118" s="13" t="n">
-        <v>18.87</v>
+        <v>18.07</v>
       </c>
       <c r="D118" s="13" t="n">
-        <v>18.21</v>
+        <v>17.75</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>17.65</v>
+        <v>17.48</v>
       </c>
       <c r="F118" s="15" t="n">
-        <v>17.82</v>
+        <v>17.45</v>
       </c>
       <c r="G118" s="15" t="n">
-        <v>18.14</v>
+        <v>17.66</v>
       </c>
       <c r="H118" s="16" t="n">
-        <v>17.48</v>
+        <v>17.34</v>
       </c>
       <c r="I118" s="17" t="n">
-        <v>17.16</v>
+        <v>17.13</v>
       </c>
       <c r="J118" s="17" t="n">
-        <v>16.82</v>
+        <v>17.02</v>
       </c>
       <c r="K118" s="18" t="n">
-        <v>17.29</v>
+        <v>17.3</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>16.73</v>
+        <v>17.03</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>16.07</v>
+        <v>16.71</v>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O118" s="21" t="n">
-        <v>17.41</v>
+        <v>17.33</v>
       </c>
       <c r="P118" s="21" t="n">
-        <v>17.34</v>
+        <v>17.33</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>17.5</v>
+        <v>17.24</v>
       </c>
       <c r="R118" s="23" t="n">
-        <v>1.92</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="119">
@@ -7950,54 +7950,54 @@
         </is>
       </c>
       <c r="C119" s="13" t="n">
-        <v>11.71</v>
+        <v>11.85</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>11.49</v>
+        <v>11.6</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>11.3</v>
+        <v>11.39</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>11.34</v>
+        <v>11.37</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>11.46</v>
+        <v>11.53</v>
       </c>
       <c r="H119" s="16" t="n">
-        <v>11.24</v>
+        <v>11.28</v>
       </c>
       <c r="I119" s="17" t="n">
         <v>11.12</v>
       </c>
       <c r="J119" s="17" t="n">
-        <v>11.02</v>
+        <v>11.03</v>
       </c>
       <c r="K119" s="18" t="n">
-        <v>11.18</v>
+        <v>11.25</v>
       </c>
       <c r="L119" s="19" t="n">
-        <v>10.99</v>
+        <v>11.05</v>
       </c>
       <c r="M119" s="19" t="n">
-        <v>10.77</v>
+        <v>10.8</v>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O119" s="21" t="n">
-        <v>11.22</v>
+        <v>11.28</v>
       </c>
       <c r="P119" s="21" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="Q119" s="22" t="n">
         <v>11.2</v>
       </c>
-      <c r="Q119" s="22" t="n">
-        <v>11.23</v>
-      </c>
       <c r="R119" s="23" t="n">
-        <v>0.8100000000000001</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="120">
@@ -8012,54 +8012,54 @@
         </is>
       </c>
       <c r="C120" s="13" t="n">
-        <v>12.9</v>
+        <v>13.09</v>
       </c>
       <c r="D120" s="13" t="n">
-        <v>12.71</v>
+        <v>12.86</v>
       </c>
       <c r="E120" s="14" t="n">
-        <v>12.55</v>
+        <v>12.67</v>
       </c>
       <c r="F120" s="15" t="n">
-        <v>12.61</v>
+        <v>12.65</v>
       </c>
       <c r="G120" s="15" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="H120" s="16" t="n">
-        <v>12.51</v>
+        <v>12.57</v>
       </c>
       <c r="I120" s="17" t="n">
         <v>12.42</v>
       </c>
       <c r="J120" s="17" t="n">
-        <v>12.32</v>
+        <v>12.34</v>
       </c>
       <c r="K120" s="18" t="n">
-        <v>12.44</v>
+        <v>12.54</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>12.28</v>
+        <v>12.35</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>12.09</v>
+        <v>12.12</v>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O120" s="21" t="n">
-        <v>12.48</v>
+        <v>12.56</v>
       </c>
       <c r="P120" s="21" t="n">
-        <v>12.46</v>
+        <v>12.56</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>12.53</v>
+        <v>12.5</v>
       </c>
       <c r="R120" s="23" t="n">
-        <v>1.05</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="121">
@@ -8074,54 +8074,54 @@
         </is>
       </c>
       <c r="C121" s="13" t="n">
-        <v>10.02</v>
+        <v>8.94</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>9.390000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>8.859999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>9.050000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="G121" s="15" t="n">
-        <v>9.34</v>
+        <v>8.6</v>
       </c>
       <c r="H121" s="16" t="n">
-        <v>8.710000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="I121" s="17" t="n">
-        <v>8.42</v>
+        <v>8.17</v>
       </c>
       <c r="J121" s="17" t="n">
-        <v>8.08</v>
+        <v>8.06</v>
       </c>
       <c r="K121" s="18" t="n">
-        <v>8.51</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L121" s="19" t="n">
-        <v>7.98</v>
+        <v>8.06</v>
       </c>
       <c r="M121" s="19" t="n">
-        <v>7.35</v>
+        <v>7.79</v>
       </c>
       <c r="N121" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O121" s="21" t="n">
-        <v>8.630000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="P121" s="21" t="n">
-        <v>8.56</v>
+        <v>8.31</v>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>8.76</v>
+        <v>8.27</v>
       </c>
       <c r="R121" s="23" t="n">
-        <v>5.42</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="122">
@@ -8136,54 +8136,54 @@
         </is>
       </c>
       <c r="C122" s="13" t="n">
-        <v>9.31</v>
+        <v>9.01</v>
       </c>
       <c r="D122" s="13" t="n">
-        <v>8.75</v>
+        <v>8.56</v>
       </c>
       <c r="E122" s="14" t="n">
-        <v>8.279999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="F122" s="15" t="n">
-        <v>8.449999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H122" s="16" t="n">
-        <v>8.140000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="I122" s="17" t="n">
         <v>7.89</v>
       </c>
       <c r="J122" s="17" t="n">
-        <v>7.58</v>
+        <v>7.64</v>
       </c>
       <c r="K122" s="18" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="L122" s="19" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="M122" s="19" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="N122" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O122" s="21" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="P122" s="21" t="n">
         <v>7.96</v>
       </c>
-      <c r="L122" s="19" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="M122" s="19" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="N122" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O122" s="21" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="P122" s="21" t="n">
-        <v>8.01</v>
-      </c>
       <c r="Q122" s="22" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="R122" s="23" t="n">
-        <v>4.33</v>
+        <v>8.15</v>
+      </c>
+      <c r="R122" s="25" t="n">
+        <v>2.13</v>
       </c>
     </row>
     <row r="123">
@@ -8198,54 +8198,54 @@
         </is>
       </c>
       <c r="C123" s="13" t="n">
-        <v>28.57</v>
+        <v>28.34</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>27.91</v>
+        <v>27.76</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>27.35</v>
+        <v>27.27</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>27.36</v>
+        <v>27.41</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>27.76</v>
+        <v>27.69</v>
       </c>
       <c r="H123" s="16" t="n">
-        <v>27.1</v>
+        <v>27.11</v>
       </c>
       <c r="I123" s="17" t="n">
-        <v>26.7</v>
+        <v>26.83</v>
       </c>
       <c r="J123" s="17" t="n">
-        <v>26.44</v>
+        <v>26.53</v>
       </c>
       <c r="K123" s="18" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="L123" s="19" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="M123" s="19" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="N123" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O123" s="21" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="P123" s="21" t="n">
         <v>26.99</v>
       </c>
-      <c r="L123" s="19" t="n">
-        <v>26.43</v>
-      </c>
-      <c r="M123" s="19" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="N123" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O123" s="21" t="n">
-        <v>27.07</v>
-      </c>
-      <c r="P123" s="21" t="n">
-        <v>27.04</v>
-      </c>
       <c r="Q123" s="22" t="n">
-        <v>26.96</v>
+        <v>27.12</v>
       </c>
       <c r="R123" s="25" t="n">
-        <v>-1.75</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="124">
@@ -8260,54 +8260,54 @@
         </is>
       </c>
       <c r="C124" s="13" t="n">
-        <v>175.64</v>
+        <v>167.02</v>
       </c>
       <c r="D124" s="13" t="n">
-        <v>171.04</v>
+        <v>163.92</v>
       </c>
       <c r="E124" s="14" t="n">
-        <v>167.19</v>
+        <v>161.32</v>
       </c>
       <c r="F124" s="15" t="n">
-        <v>167.07</v>
+        <v>160.97</v>
       </c>
       <c r="G124" s="15" t="n">
-        <v>169.93</v>
+        <v>163.03</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>165.33</v>
+        <v>159.93</v>
       </c>
       <c r="I124" s="17" t="n">
-        <v>162.47</v>
+        <v>157.87</v>
       </c>
       <c r="J124" s="17" t="n">
-        <v>160.73</v>
+        <v>156.83</v>
       </c>
       <c r="K124" s="18" t="n">
-        <v>164.61</v>
+        <v>159.58</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>160.76</v>
+        <v>156.98</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>156.16</v>
-      </c>
-      <c r="N124" s="24" t="inlineStr">
+        <v>153.88</v>
+      </c>
+      <c r="N124" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O124" s="21" t="n">
-        <v>165.15</v>
+        <v>159.88</v>
       </c>
       <c r="P124" s="21" t="n">
-        <v>164.97</v>
+        <v>159.82</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>164.2</v>
-      </c>
-      <c r="R124" s="25" t="n">
-        <v>-2.44</v>
+        <v>158.9</v>
+      </c>
+      <c r="R124" s="23" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -8322,54 +8322,54 @@
         </is>
       </c>
       <c r="C125" s="13" t="n">
-        <v>56.21</v>
+        <v>60.79</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>55.31</v>
+        <v>58.94</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>54.55</v>
+        <v>57.39</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>54.85</v>
+        <v>57.72</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>55.25</v>
+        <v>58.68</v>
       </c>
       <c r="H125" s="16" t="n">
-        <v>54.35</v>
+        <v>56.83</v>
       </c>
       <c r="I125" s="17" t="n">
-        <v>53.95</v>
+        <v>55.87</v>
       </c>
       <c r="J125" s="17" t="n">
-        <v>53.45</v>
+        <v>54.98</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>54.05</v>
+        <v>56.36</v>
       </c>
       <c r="L125" s="19" t="n">
-        <v>53.29</v>
+        <v>54.81</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>52.39</v>
-      </c>
-      <c r="N125" s="20" t="inlineStr">
+        <v>52.96</v>
+      </c>
+      <c r="N125" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O125" s="21" t="n">
-        <v>54.23</v>
+        <v>56.67</v>
       </c>
       <c r="P125" s="21" t="n">
-        <v>54.12</v>
+        <v>56.5</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>54.45</v>
+        <v>56.75</v>
       </c>
       <c r="R125" s="23" t="n">
-        <v>0.46</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="126">
@@ -8384,54 +8384,54 @@
         </is>
       </c>
       <c r="C126" s="13" t="n">
-        <v>15.82</v>
+        <v>16.15</v>
       </c>
       <c r="D126" s="13" t="n">
-        <v>15.31</v>
+        <v>15.75</v>
       </c>
       <c r="E126" s="14" t="n">
-        <v>14.88</v>
+        <v>15.41</v>
       </c>
       <c r="F126" s="15" t="n">
-        <v>15.03</v>
+        <v>15.41</v>
       </c>
       <c r="G126" s="15" t="n">
-        <v>15.27</v>
+        <v>15.66</v>
       </c>
       <c r="H126" s="16" t="n">
-        <v>14.76</v>
+        <v>15.26</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>14.52</v>
+        <v>15.01</v>
       </c>
       <c r="J126" s="17" t="n">
-        <v>14.25</v>
+        <v>14.86</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>14.59</v>
+        <v>15.19</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>14.16</v>
+        <v>14.85</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="N126" s="20" t="inlineStr">
+        <v>14.45</v>
+      </c>
+      <c r="N126" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O126" s="21" t="n">
-        <v>14.69</v>
+        <v>15.24</v>
       </c>
       <c r="P126" s="21" t="n">
-        <v>14.63</v>
+        <v>15.22</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>14.8</v>
+        <v>15.17</v>
       </c>
       <c r="R126" s="23" t="n">
-        <v>2.21</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="127">
@@ -8446,54 +8446,54 @@
         </is>
       </c>
       <c r="C127" s="13" t="n">
-        <v>15.4</v>
+        <v>15.93</v>
       </c>
       <c r="D127" s="13" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="E127" s="14" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="F127" s="15" t="n">
         <v>15.05</v>
       </c>
-      <c r="E127" s="14" t="n">
+      <c r="G127" s="15" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="H127" s="16" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="I127" s="17" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="J127" s="17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K127" s="18" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L127" s="19" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="M127" s="19" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="N127" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O127" s="21" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="P127" s="21" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="Q127" s="22" t="n">
         <v>14.75</v>
       </c>
-      <c r="F127" s="15" t="n">
-        <v>14.87</v>
-      </c>
-      <c r="G127" s="15" t="n">
-        <v>15.03</v>
-      </c>
-      <c r="H127" s="16" t="n">
-        <v>14.68</v>
-      </c>
-      <c r="I127" s="17" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="J127" s="17" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="K127" s="18" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="L127" s="19" t="n">
-        <v>14.26</v>
-      </c>
-      <c r="M127" s="19" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="N127" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O127" s="21" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="P127" s="21" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="Q127" s="22" t="n">
-        <v>14.72</v>
-      </c>
       <c r="R127" s="23" t="n">
-        <v>0.82</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="128">
@@ -8508,54 +8508,54 @@
         </is>
       </c>
       <c r="C128" s="13" t="n">
-        <v>9.27</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="D128" s="13" t="n">
-        <v>8.539999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E128" s="14" t="n">
-        <v>7.93</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="F128" s="15" t="n">
-        <v>8.33</v>
+        <v>8.1</v>
       </c>
       <c r="G128" s="15" t="n">
-        <v>8.58</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H128" s="16" t="n">
-        <v>7.85</v>
+        <v>8.01</v>
       </c>
       <c r="I128" s="17" t="n">
-        <v>7.6</v>
+        <v>7.83</v>
       </c>
       <c r="J128" s="17" t="n">
-        <v>7.12</v>
+        <v>7.74</v>
       </c>
       <c r="K128" s="18" t="n">
-        <v>7.52</v>
+        <v>7.98</v>
       </c>
       <c r="L128" s="19" t="n">
-        <v>6.91</v>
+        <v>7.75</v>
       </c>
       <c r="M128" s="19" t="n">
-        <v>6.18</v>
+        <v>7.48</v>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O128" s="21" t="n">
-        <v>7.71</v>
+        <v>8.01</v>
       </c>
       <c r="P128" s="21" t="n">
-        <v>7.58</v>
+        <v>8</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>8.09</v>
+        <v>7.92</v>
       </c>
       <c r="R128" s="23" t="n">
-        <v>9.92</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="129">
@@ -8570,54 +8570,54 @@
         </is>
       </c>
       <c r="C129" s="13" t="n">
-        <v>12.51</v>
+        <v>12.97</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>11.68</v>
+        <v>12.37</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>10.99</v>
+        <v>11.87</v>
       </c>
       <c r="F129" s="15" t="n">
-        <v>11.45</v>
+        <v>12.02</v>
       </c>
       <c r="G129" s="15" t="n">
-        <v>11.72</v>
+        <v>12.31</v>
       </c>
       <c r="H129" s="16" t="n">
-        <v>10.89</v>
+        <v>11.71</v>
       </c>
       <c r="I129" s="17" t="n">
-        <v>10.62</v>
+        <v>11.42</v>
       </c>
       <c r="J129" s="17" t="n">
-        <v>10.06</v>
+        <v>11.11</v>
       </c>
       <c r="K129" s="18" t="n">
-        <v>10.52</v>
+        <v>11.53</v>
       </c>
       <c r="L129" s="19" t="n">
-        <v>9.83</v>
+        <v>11.03</v>
       </c>
       <c r="M129" s="19" t="n">
-        <v>9</v>
+        <v>10.43</v>
       </c>
       <c r="N129" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O129" s="21" t="n">
-        <v>10.74</v>
+        <v>11.64</v>
       </c>
       <c r="P129" s="21" t="n">
-        <v>10.59</v>
+        <v>11.58</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>11.17</v>
+        <v>11.73</v>
       </c>
       <c r="R129" s="23" t="n">
-        <v>9.94</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="130">
@@ -8632,54 +8632,54 @@
         </is>
       </c>
       <c r="C130" s="13" t="n">
-        <v>149.3</v>
+        <v>147.95</v>
       </c>
       <c r="D130" s="13" t="n">
-        <v>145.9</v>
+        <v>144.15</v>
       </c>
       <c r="E130" s="14" t="n">
-        <v>143.05</v>
+        <v>140.96</v>
       </c>
       <c r="F130" s="15" t="n">
+        <v>140.53</v>
+      </c>
+      <c r="G130" s="15" t="n">
         <v>143.07</v>
       </c>
-      <c r="G130" s="15" t="n">
-        <v>145.13</v>
-      </c>
       <c r="H130" s="16" t="n">
-        <v>141.73</v>
+        <v>139.27</v>
       </c>
       <c r="I130" s="17" t="n">
-        <v>139.67</v>
+        <v>136.73</v>
       </c>
       <c r="J130" s="17" t="n">
-        <v>138.33</v>
+        <v>135.47</v>
       </c>
       <c r="K130" s="18" t="n">
-        <v>141.15</v>
+        <v>138.84</v>
       </c>
       <c r="L130" s="19" t="n">
-        <v>138.3</v>
+        <v>135.65</v>
       </c>
       <c r="M130" s="19" t="n">
-        <v>134.9</v>
+        <v>131.85</v>
       </c>
       <c r="N130" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O130" s="21" t="n">
-        <v>141.57</v>
+        <v>139.2</v>
       </c>
       <c r="P130" s="21" t="n">
-        <v>141.41</v>
+        <v>139.13</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>141</v>
-      </c>
-      <c r="R130" s="25" t="n">
-        <v>-1.4</v>
+        <v>138</v>
+      </c>
+      <c r="R130" s="23" t="n">
+        <v>-1.22</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -686,7 +686,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-01</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>11301.5</v>
+        <v>11253.33</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>11213.94</v>
+        <v>11155.86</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>11140.57</v>
+        <v>11074.18</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>11149.62</v>
+        <v>11072.48</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>11198.51</v>
+        <v>11132.79</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>11110.95</v>
+        <v>11035.32</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>11062.06</v>
+        <v>10975.01</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>11023.39</v>
+        <v>10937.85</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>11091.53</v>
+        <v>11019.59</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>11018.16</v>
+        <v>10937.91</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>10930.6</v>
+        <v>10840.44</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>11104.65</v>
+        <v>11031.26</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>11098.36</v>
+        <v>11027.2</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>11100.74</v>
+        <v>11012.18</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>3.55</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="4">
@@ -856,37 +856,37 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>21.3</v>
+        <v>21.11</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>21.05</v>
+        <v>20.87</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>20.84</v>
+        <v>20.67</v>
       </c>
       <c r="F4" s="27" t="n">
-        <v>20.82</v>
+        <v>20.64</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>20.99</v>
+        <v>20.8</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>20.74</v>
+        <v>20.56</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>20.57</v>
+        <v>20.4</v>
       </c>
       <c r="J4" s="29" t="n">
-        <v>20.49</v>
+        <v>20.32</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>20.7</v>
+        <v>20.53</v>
       </c>
       <c r="L4" s="31" t="n">
-        <v>20.5</v>
+        <v>20.33</v>
       </c>
       <c r="M4" s="31" t="n">
-        <v>20.25</v>
+        <v>20.09</v>
       </c>
       <c r="N4" s="32" t="inlineStr">
         <is>
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="O4" s="33" t="n">
-        <v>20.73</v>
+        <v>20.56</v>
       </c>
       <c r="P4" s="33" t="n">
-        <v>20.72</v>
+        <v>20.55</v>
       </c>
       <c r="Q4" s="34" t="n">
-        <v>20.66</v>
+        <v>20.48</v>
       </c>
       <c r="R4" s="35" t="n">
-        <v>-1.15</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="5">
@@ -918,54 +918,54 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>12.59</v>
+        <v>12.49</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>12.39</v>
+        <v>12.34</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>12.23</v>
+        <v>12.22</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>12.26</v>
+        <v>12.21</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>12.37</v>
+        <v>12.3</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>12.17</v>
+        <v>12.15</v>
       </c>
       <c r="I5" s="29" t="n">
         <v>12.06</v>
       </c>
       <c r="J5" s="29" t="n">
-        <v>11.97</v>
+        <v>12</v>
       </c>
       <c r="K5" s="30" t="n">
-        <v>12.11</v>
+        <v>12.13</v>
       </c>
       <c r="L5" s="31" t="n">
-        <v>11.95</v>
+        <v>12.01</v>
       </c>
       <c r="M5" s="31" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="N5" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>11.86</v>
+      </c>
+      <c r="N5" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O5" s="33" t="n">
         <v>12.15</v>
       </c>
       <c r="P5" s="33" t="n">
-        <v>12.13</v>
+        <v>12.14</v>
       </c>
       <c r="Q5" s="34" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="R5" s="36" t="n">
-        <v>1.33</v>
+        <v>12.11</v>
+      </c>
+      <c r="R5" s="35" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="6">
@@ -980,54 +980,54 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>15.07</v>
+        <v>14.78</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14.86</v>
+        <v>14.67</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>14.68</v>
+        <v>14.58</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>14.66</v>
+        <v>14.64</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>14.8</v>
+        <v>14.67</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>14.59</v>
+        <v>14.56</v>
       </c>
       <c r="I6" s="29" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="J6" s="29" t="n">
         <v>14.45</v>
       </c>
-      <c r="J6" s="29" t="n">
-        <v>14.38</v>
-      </c>
       <c r="K6" s="30" t="n">
-        <v>14.57</v>
+        <v>14.51</v>
       </c>
       <c r="L6" s="31" t="n">
-        <v>14.39</v>
+        <v>14.42</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="N6" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>14.31</v>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O6" s="33" t="n">
-        <v>14.59</v>
+        <v>14.54</v>
       </c>
       <c r="P6" s="33" t="n">
-        <v>14.58</v>
+        <v>14.52</v>
       </c>
       <c r="Q6" s="34" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="R6" s="35" t="n">
-        <v>-1.02</v>
+        <v>14.6</v>
+      </c>
+      <c r="R6" s="36" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="7">
@@ -1042,37 +1042,37 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>24.38</v>
+        <v>22.12</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>23.21</v>
+        <v>21.86</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>22.23</v>
+        <v>21.64</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>22.21</v>
+        <v>21.78</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>22.94</v>
+        <v>21.87</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>21.77</v>
+        <v>21.61</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>21.04</v>
+        <v>21.52</v>
       </c>
       <c r="J7" s="29" t="n">
-        <v>20.6</v>
+        <v>21.35</v>
       </c>
       <c r="K7" s="30" t="n">
-        <v>21.58</v>
+        <v>21.5</v>
       </c>
       <c r="L7" s="31" t="n">
-        <v>20.6</v>
+        <v>21.28</v>
       </c>
       <c r="M7" s="31" t="n">
-        <v>19.43</v>
+        <v>21.02</v>
       </c>
       <c r="N7" s="32" t="inlineStr">
         <is>
@@ -1080,16 +1080,16 @@
         </is>
       </c>
       <c r="O7" s="33" t="n">
-        <v>21.72</v>
+        <v>21.56</v>
       </c>
       <c r="P7" s="33" t="n">
-        <v>21.67</v>
+        <v>21.52</v>
       </c>
       <c r="Q7" s="34" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="R7" s="35" t="n">
-        <v>-1.92</v>
+        <v>21.69</v>
+      </c>
+      <c r="R7" s="36" t="n">
+        <v>0.93</v>
       </c>
     </row>
     <row r="8">
@@ -1104,54 +1104,54 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>35.21</v>
+        <v>34.76</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>34.65</v>
+        <v>34.4</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>34.18</v>
+        <v>34.1</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>34.22</v>
+        <v>34.27</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>34.54</v>
+        <v>34.41</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>33.98</v>
+        <v>34.05</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>33.66</v>
+        <v>33.91</v>
       </c>
       <c r="J8" s="29" t="n">
-        <v>33.42</v>
+        <v>33.69</v>
       </c>
       <c r="K8" s="30" t="n">
-        <v>33.86</v>
+        <v>33.9</v>
       </c>
       <c r="L8" s="31" t="n">
-        <v>33.39</v>
+        <v>33.6</v>
       </c>
       <c r="M8" s="31" t="n">
-        <v>32.83</v>
-      </c>
-      <c r="N8" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>33.24</v>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O8" s="33" t="n">
-        <v>33.94</v>
+        <v>33.99</v>
       </c>
       <c r="P8" s="33" t="n">
-        <v>33.91</v>
+        <v>33.93</v>
       </c>
       <c r="Q8" s="34" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="R8" s="35" t="n">
-        <v>-0.59</v>
+        <v>34.14</v>
+      </c>
+      <c r="R8" s="36" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="9">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>23.07</v>
+        <v>23.25</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>22.77</v>
+        <v>22.92</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>22.51</v>
+        <v>22.65</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>22.56</v>
+        <v>22.74</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>22.72</v>
+        <v>22.9</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>22.42</v>
+        <v>22.57</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>22.26</v>
+        <v>22.41</v>
       </c>
       <c r="J9" s="29" t="n">
-        <v>22.12</v>
+        <v>22.24</v>
       </c>
       <c r="K9" s="30" t="n">
-        <v>22.35</v>
+        <v>22.46</v>
       </c>
       <c r="L9" s="31" t="n">
-        <v>22.09</v>
+        <v>22.19</v>
       </c>
       <c r="M9" s="31" t="n">
-        <v>21.79</v>
+        <v>21.86</v>
       </c>
       <c r="N9" s="20" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="O9" s="33" t="n">
-        <v>22.39</v>
+        <v>22.53</v>
       </c>
       <c r="P9" s="33" t="n">
-        <v>22.37</v>
+        <v>22.49</v>
       </c>
       <c r="Q9" s="34" t="n">
-        <v>22.4</v>
+        <v>22.59</v>
       </c>
       <c r="R9" s="36" t="n">
-        <v>0.36</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="10">
@@ -1228,37 +1228,37 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>136.32</v>
+        <v>138.49</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>134.02</v>
+        <v>134.79</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>132.09</v>
+        <v>131.69</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>132.7</v>
+        <v>131.4</v>
       </c>
       <c r="G10" s="27" t="n">
         <v>133.8</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>131.5</v>
+        <v>130.1</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>130.4</v>
+        <v>127.7</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>129.2</v>
+        <v>126.4</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>130.81</v>
+        <v>129.61</v>
       </c>
       <c r="L10" s="31" t="n">
-        <v>128.88</v>
+        <v>126.51</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>126.58</v>
+        <v>122.81</v>
       </c>
       <c r="N10" s="32" t="inlineStr">
         <is>
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="O10" s="33" t="n">
-        <v>131.24</v>
+        <v>130</v>
       </c>
       <c r="P10" s="33" t="n">
-        <v>130.99</v>
+        <v>129.9</v>
       </c>
       <c r="Q10" s="34" t="n">
-        <v>131.6</v>
-      </c>
-      <c r="R10" s="36" t="n">
-        <v>1.23</v>
+        <v>129</v>
+      </c>
+      <c r="R10" s="35" t="n">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="11">
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>70.23</v>
+        <v>68.83</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>68.88</v>
+        <v>67.73</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>67.75</v>
+        <v>66.81</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>67.8</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>68.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>67.25</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>66.45</v>
+        <v>65.75</v>
       </c>
       <c r="J11" s="29" t="n">
-        <v>65.90000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>67</v>
+        <v>66.19</v>
       </c>
       <c r="L11" s="31" t="n">
-        <v>65.87</v>
+        <v>65.27</v>
       </c>
       <c r="M11" s="31" t="n">
-        <v>64.52</v>
+        <v>64.17</v>
       </c>
       <c r="N11" s="32" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="O11" s="33" t="n">
-        <v>67.18000000000001</v>
+        <v>66.34</v>
       </c>
       <c r="P11" s="33" t="n">
-        <v>67.09999999999999</v>
+        <v>66.28</v>
       </c>
       <c r="Q11" s="34" t="n">
-        <v>67</v>
+        <v>66.2</v>
       </c>
       <c r="R11" s="35" t="n">
-        <v>-0.67</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="12">
@@ -1352,54 +1352,54 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>26.65</v>
+        <v>26.67</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>26.37</v>
+        <v>26.27</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>26.14</v>
+        <v>25.93</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>26.16</v>
+        <v>25.91</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>26.32</v>
+        <v>26.17</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>26.04</v>
+        <v>25.77</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>25.88</v>
+        <v>25.51</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>25.76</v>
+        <v>25.37</v>
       </c>
       <c r="K12" s="30" t="n">
-        <v>25.98</v>
+        <v>25.71</v>
       </c>
       <c r="L12" s="31" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="M12" s="31" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="N12" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O12" s="33" t="n">
         <v>25.75</v>
       </c>
-      <c r="M12" s="31" t="n">
-        <v>25.47</v>
-      </c>
-      <c r="N12" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O12" s="33" t="n">
-        <v>26.02</v>
-      </c>
       <c r="P12" s="33" t="n">
-        <v>26</v>
+        <v>25.74</v>
       </c>
       <c r="Q12" s="34" t="n">
-        <v>26</v>
+        <v>25.66</v>
       </c>
       <c r="R12" s="35" t="n">
-        <v>-0.46</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="13">
@@ -1414,37 +1414,37 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>26.02</v>
+        <v>25.82</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>25.61</v>
+        <v>25.33</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>25.63</v>
+        <v>25.35</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>25.91</v>
+        <v>25.69</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>25.43</v>
+        <v>25.11</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>25.15</v>
+        <v>24.77</v>
       </c>
       <c r="J13" s="29" t="n">
-        <v>24.95</v>
+        <v>24.53</v>
       </c>
       <c r="K13" s="30" t="n">
-        <v>25.35</v>
+        <v>25.01</v>
       </c>
       <c r="L13" s="31" t="n">
-        <v>24.94</v>
+        <v>24.52</v>
       </c>
       <c r="M13" s="31" t="n">
-        <v>24.46</v>
+        <v>23.94</v>
       </c>
       <c r="N13" s="32" t="inlineStr">
         <is>
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="O13" s="33" t="n">
-        <v>25.41</v>
+        <v>25.08</v>
       </c>
       <c r="P13" s="33" t="n">
-        <v>25.38</v>
+        <v>25.05</v>
       </c>
       <c r="Q13" s="34" t="n">
-        <v>25.34</v>
+        <v>25</v>
       </c>
       <c r="R13" s="35" t="n">
-        <v>-1.48</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="14">
@@ -1476,37 +1476,37 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>44.24</v>
+        <v>44.22</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>43.6</v>
+        <v>43.38</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>43.06</v>
+        <v>42.68</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>43.16</v>
+        <v>42.66</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>43.5</v>
+        <v>43.18</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>42.86</v>
+        <v>42.34</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>42.52</v>
+        <v>41.82</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>42.22</v>
+        <v>41.5</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>42.7</v>
+        <v>42.2</v>
       </c>
       <c r="L14" s="31" t="n">
-        <v>42.16</v>
+        <v>41.5</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>41.52</v>
+        <v>40.66</v>
       </c>
       <c r="N14" s="32" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="O14" s="33" t="n">
-        <v>42.81</v>
+        <v>42.31</v>
       </c>
       <c r="P14" s="33" t="n">
-        <v>42.75</v>
+        <v>42.27</v>
       </c>
       <c r="Q14" s="34" t="n">
-        <v>42.82</v>
+        <v>42.14</v>
       </c>
       <c r="R14" s="35" t="n">
-        <v>-1.11</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="15">
@@ -1538,37 +1538,37 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>8.720000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="F15" s="27" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="G15" s="27" t="n">
         <v>8.76</v>
       </c>
-      <c r="G15" s="27" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="H15" s="28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I15" s="29" t="n">
-        <v>8.66</v>
+        <v>8.57</v>
       </c>
       <c r="J15" s="29" t="n">
-        <v>8.6</v>
+        <v>8.52</v>
       </c>
       <c r="K15" s="30" t="n">
-        <v>8.66</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L15" s="31" t="n">
-        <v>8.58</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M15" s="31" t="n">
-        <v>8.48</v>
+        <v>8.41</v>
       </c>
       <c r="N15" s="32" t="inlineStr">
         <is>
@@ -1576,16 +1576,16 @@
         </is>
       </c>
       <c r="O15" s="33" t="n">
-        <v>8.68</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="P15" s="33" t="n">
-        <v>8.67</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="Q15" s="34" t="n">
-        <v>8.720000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="R15" s="35" t="n">
-        <v>-0.34</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="16">
@@ -1600,54 +1600,54 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="G16" s="27" t="n">
         <v>15.17</v>
       </c>
-      <c r="D16" s="25" t="n">
-        <v>14.87</v>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>14.61</v>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>14.86</v>
-      </c>
       <c r="H16" s="28" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="J16" s="29" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="K16" s="30" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="L16" s="31" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="M16" s="31" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O16" s="33" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="P16" s="33" t="n">
         <v>14.56</v>
       </c>
-      <c r="I16" s="29" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="J16" s="29" t="n">
-        <v>14.26</v>
-      </c>
-      <c r="K16" s="30" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="L16" s="31" t="n">
-        <v>14.19</v>
-      </c>
-      <c r="M16" s="31" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O16" s="33" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="P16" s="33" t="n">
-        <v>14.47</v>
-      </c>
       <c r="Q16" s="34" t="n">
-        <v>14.62</v>
+        <v>14.73</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17">
@@ -1662,37 +1662,37 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>5.12</v>
+        <v>4.95</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>4.98</v>
+        <v>4.84</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>4.94</v>
+        <v>4.81</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I17" s="29" t="n">
-        <v>4.71</v>
+        <v>4.64</v>
       </c>
       <c r="J17" s="29" t="n">
-        <v>4.66</v>
+        <v>4.59</v>
       </c>
       <c r="K17" s="30" t="n">
-        <v>4.78</v>
+        <v>4.68</v>
       </c>
       <c r="L17" s="31" t="n">
-        <v>4.66</v>
+        <v>4.59</v>
       </c>
       <c r="M17" s="31" t="n">
-        <v>4.52</v>
+        <v>4.48</v>
       </c>
       <c r="N17" s="32" t="inlineStr">
         <is>
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="O17" s="33" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P17" s="33" t="n">
-        <v>4.79</v>
+        <v>4.69</v>
       </c>
       <c r="Q17" s="34" t="n">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="R17" s="35" t="n">
-        <v>-0.21</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="18">
@@ -1724,37 +1724,37 @@
         </is>
       </c>
       <c r="C18" s="25" t="n">
-        <v>19.76</v>
+        <v>18.98</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>19.32</v>
+        <v>18.78</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>18.95</v>
+        <v>18.62</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>18.94</v>
+        <v>18.64</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>19.21</v>
+        <v>18.75</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>18.77</v>
+        <v>18.55</v>
       </c>
       <c r="I18" s="29" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="J18" s="29" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="K18" s="30" t="n">
         <v>18.5</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>18.33</v>
-      </c>
-      <c r="K18" s="30" t="n">
-        <v>18.71</v>
       </c>
       <c r="L18" s="31" t="n">
         <v>18.34</v>
       </c>
       <c r="M18" s="31" t="n">
-        <v>17.9</v>
+        <v>18.14</v>
       </c>
       <c r="N18" s="32" t="inlineStr">
         <is>
@@ -1762,16 +1762,16 @@
         </is>
       </c>
       <c r="O18" s="33" t="n">
-        <v>18.76</v>
+        <v>18.53</v>
       </c>
       <c r="P18" s="33" t="n">
-        <v>18.74</v>
+        <v>18.52</v>
       </c>
       <c r="Q18" s="34" t="n">
-        <v>18.66</v>
+        <v>18.53</v>
       </c>
       <c r="R18" s="35" t="n">
-        <v>-1.84</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="19">
@@ -1786,54 +1786,54 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>25.48</v>
+        <v>25.64</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>25.32</v>
+        <v>25.38</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>25.18</v>
+        <v>25.16</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>25.27</v>
+        <v>25.2</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>25.33</v>
+        <v>25.34</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>25.17</v>
+        <v>25.08</v>
       </c>
       <c r="I19" s="29" t="n">
-        <v>25.11</v>
+        <v>24.94</v>
       </c>
       <c r="J19" s="29" t="n">
-        <v>25.01</v>
+        <v>24.82</v>
       </c>
       <c r="K19" s="30" t="n">
-        <v>25.1</v>
+        <v>25.02</v>
       </c>
       <c r="L19" s="31" t="n">
-        <v>24.96</v>
+        <v>24.8</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="N19" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>24.54</v>
+      </c>
+      <c r="N19" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O19" s="33" t="n">
-        <v>25.14</v>
+        <v>25.06</v>
       </c>
       <c r="P19" s="33" t="n">
-        <v>25.11</v>
+        <v>25.04</v>
       </c>
       <c r="Q19" s="34" t="n">
-        <v>25.22</v>
-      </c>
-      <c r="R19" s="36" t="n">
-        <v>0.8</v>
+        <v>25.06</v>
+      </c>
+      <c r="R19" s="35" t="n">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="20">
@@ -1848,37 +1848,37 @@
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>69.67</v>
+        <v>68.47</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>68.27</v>
+        <v>67.22</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>67.09</v>
+        <v>66.17</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>67.33</v>
+        <v>66.37</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>68.06999999999999</v>
+        <v>67.03</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>66.67</v>
+        <v>65.78</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>65.93000000000001</v>
+        <v>65.12</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>65.27</v>
+        <v>64.53</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>66.31</v>
+        <v>65.47</v>
       </c>
       <c r="L20" s="31" t="n">
-        <v>65.13</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>63.73</v>
+        <v>63.18</v>
       </c>
       <c r="N20" s="32" t="inlineStr">
         <is>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="O20" s="33" t="n">
-        <v>66.54000000000001</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="P20" s="33" t="n">
-        <v>66.42</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="Q20" s="34" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="R20" s="36" t="n">
-        <v>0.76</v>
+        <v>65.7</v>
+      </c>
+      <c r="R20" s="35" t="n">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="21">
@@ -1910,54 +1910,54 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>12.81</v>
+        <v>12.46</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>12.55</v>
+        <v>12.3</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>12.33</v>
+        <v>12.16</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>12.34</v>
+        <v>12.16</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>12.5</v>
+        <v>12.26</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>12.24</v>
+        <v>12.1</v>
       </c>
       <c r="I21" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="J21" s="29" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="K21" s="30" t="n">
         <v>12.08</v>
       </c>
-      <c r="J21" s="29" t="n">
-        <v>11.98</v>
-      </c>
-      <c r="K21" s="30" t="n">
-        <v>12.19</v>
-      </c>
       <c r="L21" s="31" t="n">
-        <v>11.97</v>
+        <v>11.94</v>
       </c>
       <c r="M21" s="31" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="N21" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>11.78</v>
+      </c>
+      <c r="N21" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O21" s="33" t="n">
-        <v>12.22</v>
+        <v>12.09</v>
       </c>
       <c r="P21" s="33" t="n">
-        <v>12.21</v>
+        <v>12.09</v>
       </c>
       <c r="Q21" s="34" t="n">
-        <v>12.19</v>
-      </c>
-      <c r="R21" s="36" t="n">
-        <v>0.58</v>
+        <v>12.06</v>
+      </c>
+      <c r="R21" s="35" t="n">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="22">
@@ -1972,37 +1972,37 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>19.23</v>
+        <v>19.59</v>
       </c>
       <c r="D22" s="25" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="G22" s="27" t="n">
         <v>18.98</v>
       </c>
-      <c r="E22" s="26" t="n">
-        <v>18.77</v>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>18.77</v>
-      </c>
-      <c r="G22" s="27" t="n">
-        <v>18.93</v>
-      </c>
       <c r="H22" s="28" t="n">
-        <v>18.68</v>
+        <v>18.49</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>18.52</v>
+        <v>18.18</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>18.43</v>
+        <v>18</v>
       </c>
       <c r="K22" s="30" t="n">
-        <v>18.63</v>
+        <v>18.42</v>
       </c>
       <c r="L22" s="31" t="n">
-        <v>18.43</v>
+        <v>18.01</v>
       </c>
       <c r="M22" s="31" t="n">
-        <v>18.18</v>
+        <v>17.52</v>
       </c>
       <c r="N22" s="32" t="inlineStr">
         <is>
@@ -2010,16 +2010,16 @@
         </is>
       </c>
       <c r="O22" s="33" t="n">
-        <v>18.67</v>
+        <v>18.47</v>
       </c>
       <c r="P22" s="33" t="n">
-        <v>18.65</v>
+        <v>18.46</v>
       </c>
       <c r="Q22" s="34" t="n">
-        <v>18.62</v>
-      </c>
-      <c r="R22" s="36" t="n">
-        <v>0</v>
+        <v>18.36</v>
+      </c>
+      <c r="R22" s="35" t="n">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="23">
@@ -2034,54 +2034,54 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>39.88</v>
+        <v>39.3</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>38.56</v>
+        <v>38.16</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>37.45</v>
+        <v>37.21</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>37.41</v>
+        <v>37.75</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>38.23</v>
+        <v>38.17</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>36.91</v>
+        <v>37.03</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>36.09</v>
+        <v>36.61</v>
       </c>
       <c r="J23" s="29" t="n">
-        <v>35.59</v>
+        <v>35.89</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>36.71</v>
+        <v>36.57</v>
       </c>
       <c r="L23" s="31" t="n">
-        <v>35.6</v>
+        <v>35.62</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="N23" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>34.48</v>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O23" s="33" t="n">
-        <v>36.86</v>
+        <v>36.85</v>
       </c>
       <c r="P23" s="33" t="n">
-        <v>36.81</v>
+        <v>36.66</v>
       </c>
       <c r="Q23" s="34" t="n">
-        <v>36.58</v>
-      </c>
-      <c r="R23" s="35" t="n">
-        <v>-3.12</v>
+        <v>37.32</v>
+      </c>
+      <c r="R23" s="36" t="n">
+        <v>2.02</v>
       </c>
     </row>
     <row r="24">
@@ -2096,54 +2096,54 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>16.33</v>
+        <v>16.54</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>15.92</v>
+        <v>16.05</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>15.58</v>
+        <v>15.64</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>15.59</v>
+        <v>15.88</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>15.83</v>
+        <v>16.06</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>15.42</v>
+        <v>15.57</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>15.18</v>
+        <v>15.39</v>
       </c>
       <c r="J24" s="29" t="n">
-        <v>15.01</v>
+        <v>15.08</v>
       </c>
       <c r="K24" s="30" t="n">
-        <v>15.35</v>
+        <v>15.37</v>
       </c>
       <c r="L24" s="31" t="n">
-        <v>15.01</v>
+        <v>14.96</v>
       </c>
       <c r="M24" s="31" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N24" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>14.47</v>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O24" s="33" t="n">
-        <v>15.4</v>
+        <v>15.49</v>
       </c>
       <c r="P24" s="33" t="n">
-        <v>15.38</v>
+        <v>15.41</v>
       </c>
       <c r="Q24" s="34" t="n">
-        <v>15.34</v>
-      </c>
-      <c r="R24" s="35" t="n">
-        <v>-1.35</v>
+        <v>15.7</v>
+      </c>
+      <c r="R24" s="36" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="25">
@@ -2158,37 +2158,37 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>40.54</v>
+        <v>38.04</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>38.98</v>
+        <v>37.26</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>37.68</v>
+        <v>36.61</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>37.71</v>
+        <v>36.72</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>38.65</v>
+        <v>37.14</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>37.09</v>
+        <v>36.36</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>36.15</v>
+        <v>35.94</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>35.53</v>
+        <v>35.58</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>36.8</v>
+        <v>36.17</v>
       </c>
       <c r="L25" s="31" t="n">
-        <v>35.5</v>
+        <v>35.52</v>
       </c>
       <c r="M25" s="31" t="n">
-        <v>33.94</v>
+        <v>34.74</v>
       </c>
       <c r="N25" s="32" t="inlineStr">
         <is>
@@ -2196,16 +2196,16 @@
         </is>
       </c>
       <c r="O25" s="33" t="n">
-        <v>37.01</v>
+        <v>36.3</v>
       </c>
       <c r="P25" s="33" t="n">
-        <v>36.92</v>
+        <v>36.23</v>
       </c>
       <c r="Q25" s="34" t="n">
-        <v>36.78</v>
+        <v>36.3</v>
       </c>
       <c r="R25" s="35" t="n">
-        <v>-3.11</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="26">
@@ -2220,37 +2220,37 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>57.71</v>
+        <v>59.86</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>55.91</v>
+        <v>57.41</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>54.4</v>
+        <v>55.36</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>54.9</v>
+        <v>55.95</v>
       </c>
       <c r="G26" s="27" t="n">
-        <v>55.75</v>
+        <v>57.15</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>53.95</v>
+        <v>54.7</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>53.1</v>
+        <v>53.5</v>
       </c>
       <c r="J26" s="29" t="n">
-        <v>52.15</v>
+        <v>52.25</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>53.4</v>
+        <v>53.99</v>
       </c>
       <c r="L26" s="31" t="n">
-        <v>51.89</v>
+        <v>51.94</v>
       </c>
       <c r="M26" s="31" t="n">
-        <v>50.09</v>
+        <v>49.49</v>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
@@ -2258,16 +2258,16 @@
         </is>
       </c>
       <c r="O26" s="33" t="n">
-        <v>53.74</v>
+        <v>54.44</v>
       </c>
       <c r="P26" s="33" t="n">
-        <v>53.54</v>
+        <v>54.18</v>
       </c>
       <c r="Q26" s="34" t="n">
-        <v>54.05</v>
+        <v>54.75</v>
       </c>
       <c r="R26" s="36" t="n">
-        <v>0.65</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="27">
@@ -2282,37 +2282,37 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>208.16</v>
+        <v>227.69</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>201.26</v>
+        <v>215.09</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>195.48</v>
+        <v>204.53</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>198.57</v>
+        <v>210.1</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>201.23</v>
+        <v>215</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>194.33</v>
+        <v>202.4</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>191.67</v>
+        <v>197.5</v>
       </c>
       <c r="J27" s="29" t="n">
-        <v>187.43</v>
+        <v>189.8</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>191.62</v>
+        <v>197.47</v>
       </c>
       <c r="L27" s="31" t="n">
-        <v>185.84</v>
+        <v>186.91</v>
       </c>
       <c r="M27" s="31" t="n">
-        <v>178.94</v>
+        <v>174.31</v>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="O27" s="33" t="n">
-        <v>193.24</v>
+        <v>200.43</v>
       </c>
       <c r="P27" s="33" t="n">
-        <v>192.16</v>
+        <v>198.45</v>
       </c>
       <c r="Q27" s="34" t="n">
-        <v>195.9</v>
-      </c>
-      <c r="R27" s="35" t="n">
-        <v>-0.41</v>
+        <v>205.2</v>
+      </c>
+      <c r="R27" s="36" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="28">
@@ -2344,54 +2344,54 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>87.31999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>85.67</v>
+        <v>85.23</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>84.29000000000001</v>
+        <v>82.88</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>84.8</v>
+        <v>83.03</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>85.55</v>
+        <v>84.67</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>83.90000000000001</v>
+        <v>81.87</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>83.15000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="J28" s="29" t="n">
-        <v>82.25</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>83.36</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="L28" s="31" t="n">
-        <v>81.98</v>
+        <v>78.97</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>80.33</v>
-      </c>
-      <c r="N28" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>76.17</v>
+      </c>
+      <c r="N28" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O28" s="33" t="n">
-        <v>83.7</v>
+        <v>81.7</v>
       </c>
       <c r="P28" s="33" t="n">
-        <v>83.48999999999999</v>
+        <v>81.53</v>
       </c>
       <c r="Q28" s="34" t="n">
-        <v>84.05</v>
-      </c>
-      <c r="R28" s="36" t="n">
-        <v>1.39</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="R28" s="35" t="n">
+        <v>-3.15</v>
       </c>
     </row>
     <row r="29">
@@ -2406,37 +2406,37 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>23.42</v>
+        <v>23.57</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>22.73</v>
+        <v>22.97</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>22.15</v>
+        <v>22.47</v>
       </c>
       <c r="F29" s="27" t="n">
         <v>22.53</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>22.76</v>
+        <v>22.86</v>
       </c>
       <c r="H29" s="28" t="n">
-        <v>22.07</v>
+        <v>22.26</v>
       </c>
       <c r="I29" s="29" t="n">
-        <v>21.84</v>
+        <v>21.93</v>
       </c>
       <c r="J29" s="29" t="n">
-        <v>21.38</v>
+        <v>21.66</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>21.76</v>
+        <v>22.13</v>
       </c>
       <c r="L29" s="31" t="n">
-        <v>21.18</v>
+        <v>21.63</v>
       </c>
       <c r="M29" s="31" t="n">
-        <v>20.49</v>
+        <v>21.03</v>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
@@ -2444,16 +2444,16 @@
         </is>
       </c>
       <c r="O29" s="33" t="n">
-        <v>21.94</v>
+        <v>22.22</v>
       </c>
       <c r="P29" s="33" t="n">
-        <v>21.82</v>
+        <v>22.18</v>
       </c>
       <c r="Q29" s="34" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R29" s="36" t="n">
-        <v>2.34</v>
+        <v>22.19</v>
+      </c>
+      <c r="R29" s="35" t="n">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="30">
@@ -2468,37 +2468,37 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>83.72</v>
+        <v>80.91</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>81.42</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>79.48999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>79.7</v>
+        <v>79</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>81</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>78.7</v>
+        <v>78.45</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>77.40000000000001</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="J30" s="29" t="n">
-        <v>76.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>78.20999999999999</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="L30" s="31" t="n">
-        <v>76.28</v>
+        <v>77.19</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>73.98</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="N30" s="32" t="inlineStr">
         <is>
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="O30" s="33" t="n">
-        <v>78.54000000000001</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="P30" s="33" t="n">
-        <v>78.39</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="Q30" s="34" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="R30" s="35" t="n">
-        <v>-0.13</v>
+      <c r="R30" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2530,37 +2530,37 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>31.11</v>
+        <v>31.89</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>30.57</v>
+        <v>30.93</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>30.12</v>
+        <v>30.13</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>30.09</v>
+        <v>30.03</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>30.43</v>
+        <v>30.67</v>
       </c>
       <c r="H31" s="28" t="n">
-        <v>29.89</v>
+        <v>29.71</v>
       </c>
       <c r="I31" s="29" t="n">
-        <v>29.55</v>
+        <v>29.07</v>
       </c>
       <c r="J31" s="29" t="n">
-        <v>29.35</v>
+        <v>28.75</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>29.82</v>
+        <v>29.59</v>
       </c>
       <c r="L31" s="31" t="n">
-        <v>29.37</v>
+        <v>28.79</v>
       </c>
       <c r="M31" s="31" t="n">
-        <v>28.83</v>
+        <v>27.83</v>
       </c>
       <c r="N31" s="32" t="inlineStr">
         <is>
@@ -2568,16 +2568,16 @@
         </is>
       </c>
       <c r="O31" s="33" t="n">
-        <v>29.88</v>
+        <v>29.69</v>
       </c>
       <c r="P31" s="33" t="n">
-        <v>29.86</v>
+        <v>29.67</v>
       </c>
       <c r="Q31" s="34" t="n">
-        <v>29.74</v>
+        <v>29.4</v>
       </c>
       <c r="R31" s="35" t="n">
-        <v>-1.72</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="32">
@@ -2592,54 +2592,54 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>51.07</v>
+        <v>50.76</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>50.5</v>
+        <v>50.28</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>50.02</v>
+        <v>49.87</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>50.09</v>
+        <v>49.82</v>
       </c>
       <c r="G32" s="27" t="n">
-        <v>50.41</v>
+        <v>50.14</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>49.84</v>
+        <v>49.66</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>49.52</v>
+        <v>49.34</v>
       </c>
       <c r="J32" s="29" t="n">
-        <v>49.27</v>
+        <v>49.18</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>49.71</v>
+        <v>49.61</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>49.23</v>
+        <v>49.2</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>48.66</v>
-      </c>
-      <c r="N32" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>48.72</v>
+      </c>
+      <c r="N32" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O32" s="33" t="n">
-        <v>49.79</v>
+        <v>49.65</v>
       </c>
       <c r="P32" s="33" t="n">
-        <v>49.75</v>
+        <v>49.64</v>
       </c>
       <c r="Q32" s="34" t="n">
-        <v>49.78</v>
-      </c>
-      <c r="R32" s="36" t="n">
-        <v>0.6899999999999999</v>
+        <v>49.5</v>
+      </c>
+      <c r="R32" s="35" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2654,37 +2654,37 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>136.69</v>
+        <v>136.04</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>133.79</v>
+        <v>133.54</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>131.36</v>
+        <v>131.45</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>132.3</v>
+        <v>132.7</v>
       </c>
       <c r="G33" s="27" t="n">
         <v>133.6</v>
       </c>
       <c r="H33" s="28" t="n">
-        <v>130.7</v>
+        <v>131.1</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>129.4</v>
+        <v>130.2</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>127.8</v>
+        <v>128.6</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>129.74</v>
+        <v>130.05</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>127.31</v>
+        <v>127.95</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>124.41</v>
+        <v>125.45</v>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
@@ -2692,16 +2692,16 @@
         </is>
       </c>
       <c r="O33" s="33" t="n">
-        <v>130.33</v>
+        <v>130.67</v>
       </c>
       <c r="P33" s="33" t="n">
-        <v>129.96</v>
+        <v>130.25</v>
       </c>
       <c r="Q33" s="34" t="n">
-        <v>131</v>
+        <v>131.8</v>
       </c>
       <c r="R33" s="36" t="n">
-        <v>0.31</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="34">
@@ -2716,37 +2716,37 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>52.45</v>
+        <v>52.79</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>51.8</v>
+        <v>51.99</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>51.26</v>
+        <v>51.32</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>51.35</v>
+        <v>51.77</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>51.7</v>
+        <v>52.03</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>51.05</v>
+        <v>51.23</v>
       </c>
       <c r="I34" s="29" t="n">
-        <v>50.7</v>
+        <v>50.97</v>
       </c>
       <c r="J34" s="29" t="n">
-        <v>50.4</v>
+        <v>50.43</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>50.89</v>
+        <v>50.88</v>
       </c>
       <c r="L34" s="31" t="n">
-        <v>50.35</v>
+        <v>50.21</v>
       </c>
       <c r="M34" s="31" t="n">
-        <v>49.7</v>
+        <v>49.41</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="O34" s="33" t="n">
-        <v>51</v>
+        <v>51.09</v>
       </c>
       <c r="P34" s="33" t="n">
         <v>50.94</v>
       </c>
       <c r="Q34" s="34" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="R34" s="36" t="n">
-        <v>0.49</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="35">
@@ -2778,37 +2778,37 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>26.2</v>
+        <v>25.87</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>25.78</v>
+        <v>25.57</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>25.43</v>
+        <v>25.31</v>
       </c>
       <c r="F35" s="27" t="n">
-        <v>25.57</v>
+        <v>25.28</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>25.75</v>
+        <v>25.48</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>25.33</v>
+        <v>25.18</v>
       </c>
       <c r="I35" s="29" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="J35" s="29" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="K35" s="30" t="n">
         <v>25.15</v>
       </c>
-      <c r="J35" s="29" t="n">
-        <v>24.91</v>
-      </c>
-      <c r="K35" s="30" t="n">
-        <v>25.19</v>
-      </c>
       <c r="L35" s="31" t="n">
-        <v>24.84</v>
+        <v>24.89</v>
       </c>
       <c r="M35" s="31" t="n">
-        <v>24.42</v>
+        <v>24.59</v>
       </c>
       <c r="N35" s="32" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="O35" s="33" t="n">
-        <v>25.28</v>
+        <v>25.17</v>
       </c>
       <c r="P35" s="33" t="n">
-        <v>25.23</v>
+        <v>25.17</v>
       </c>
       <c r="Q35" s="34" t="n">
-        <v>25.38</v>
+        <v>25.08</v>
       </c>
       <c r="R35" s="35" t="n">
-        <v>-0.39</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="36">
@@ -2840,37 +2840,37 @@
         </is>
       </c>
       <c r="C36" s="25" t="n">
-        <v>27.3</v>
+        <v>28.01</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>26.68</v>
+        <v>27.31</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>26.16</v>
+        <v>26.73</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>26.44</v>
+        <v>27.07</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>26.68</v>
+        <v>27.33</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>26.06</v>
+        <v>26.63</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>25.82</v>
+        <v>26.37</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>25.44</v>
+        <v>25.93</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>25.82</v>
+        <v>26.33</v>
       </c>
       <c r="L36" s="31" t="n">
-        <v>25.3</v>
+        <v>25.75</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>24.68</v>
+        <v>25.05</v>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="O36" s="33" t="n">
-        <v>25.96</v>
+        <v>26.51</v>
       </c>
       <c r="P36" s="33" t="n">
-        <v>25.86</v>
+        <v>26.39</v>
       </c>
       <c r="Q36" s="34" t="n">
-        <v>26.2</v>
+        <v>26.82</v>
       </c>
       <c r="R36" s="36" t="n">
-        <v>1.08</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="37">
@@ -2902,37 +2902,37 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>9.380000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="E37" s="26" t="n">
-        <v>9.050000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="F37" s="27" t="n">
-        <v>9.09</v>
+        <v>9.15</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>9.18</v>
+        <v>9.33</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="I37" s="29" t="n">
-        <v>8.91</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="J37" s="29" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="K37" s="30" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="L37" s="31" t="n">
         <v>8.82</v>
       </c>
-      <c r="K37" s="30" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="L37" s="31" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="M37" s="31" t="n">
-        <v>8.619999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="N37" s="32" t="inlineStr">
         <is>
@@ -2940,16 +2940,16 @@
         </is>
       </c>
       <c r="O37" s="33" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="P37" s="33" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="Q37" s="34" t="n">
         <v>8.98</v>
       </c>
-      <c r="P37" s="33" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="Q37" s="34" t="n">
-        <v>9</v>
-      </c>
-      <c r="R37" s="36" t="n">
-        <v>1.24</v>
+      <c r="R37" s="35" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="38">
@@ -2964,37 +2964,37 @@
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>31.94</v>
+        <v>31.97</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>31.32</v>
+        <v>31.43</v>
       </c>
       <c r="E38" s="26" t="n">
-        <v>30.8</v>
+        <v>30.98</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>31.15</v>
+        <v>31.05</v>
       </c>
       <c r="G38" s="27" t="n">
         <v>31.35</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>30.73</v>
+        <v>30.81</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>30.53</v>
+        <v>30.51</v>
       </c>
       <c r="J38" s="29" t="n">
-        <v>30.11</v>
+        <v>30.27</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>30.46</v>
+        <v>30.68</v>
       </c>
       <c r="L38" s="31" t="n">
-        <v>29.94</v>
+        <v>30.23</v>
       </c>
       <c r="M38" s="31" t="n">
-        <v>29.32</v>
+        <v>29.69</v>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
@@ -3002,16 +3002,16 @@
         </is>
       </c>
       <c r="O38" s="33" t="n">
-        <v>30.62</v>
+        <v>30.76</v>
       </c>
       <c r="P38" s="33" t="n">
-        <v>30.5</v>
+        <v>30.72</v>
       </c>
       <c r="Q38" s="34" t="n">
-        <v>30.94</v>
-      </c>
-      <c r="R38" s="36" t="n">
-        <v>2.04</v>
+        <v>30.76</v>
+      </c>
+      <c r="R38" s="35" t="n">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="39">
@@ -3026,37 +3026,37 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>204.28</v>
+        <v>196.13</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>198.48</v>
+        <v>193.33</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>193.62</v>
+        <v>190.98</v>
       </c>
       <c r="F39" s="27" t="n">
-        <v>194.7</v>
+        <v>191.87</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>197.7</v>
+        <v>193.13</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>191.9</v>
+        <v>190.33</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>188.9</v>
+        <v>189.07</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>186.1</v>
+        <v>187.53</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>190.38</v>
+        <v>189.42</v>
       </c>
       <c r="L39" s="31" t="n">
-        <v>185.52</v>
+        <v>187.07</v>
       </c>
       <c r="M39" s="31" t="n">
-        <v>179.72</v>
+        <v>184.27</v>
       </c>
       <c r="N39" s="32" t="inlineStr">
         <is>
@@ -3064,16 +3064,16 @@
         </is>
       </c>
       <c r="O39" s="33" t="n">
-        <v>191.36</v>
+        <v>189.98</v>
       </c>
       <c r="P39" s="33" t="n">
-        <v>190.83</v>
+        <v>189.63</v>
       </c>
       <c r="Q39" s="34" t="n">
-        <v>191.7</v>
+        <v>190.6</v>
       </c>
       <c r="R39" s="35" t="n">
-        <v>-0.1</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="40">
@@ -3088,37 +3088,37 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>13.78</v>
+        <v>13.65</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>13.6</v>
+        <v>13.44</v>
       </c>
       <c r="E40" s="26" t="n">
-        <v>13.45</v>
+        <v>13.26</v>
       </c>
       <c r="F40" s="27" t="n">
-        <v>13.43</v>
+        <v>13.29</v>
       </c>
       <c r="G40" s="27" t="n">
-        <v>13.55</v>
+        <v>13.41</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>13.37</v>
+        <v>13.2</v>
       </c>
       <c r="I40" s="29" t="n">
-        <v>13.25</v>
+        <v>13.08</v>
       </c>
       <c r="J40" s="29" t="n">
-        <v>13.19</v>
+        <v>12.99</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>13.35</v>
+        <v>13.15</v>
       </c>
       <c r="L40" s="31" t="n">
-        <v>13.2</v>
+        <v>12.97</v>
       </c>
       <c r="M40" s="31" t="n">
-        <v>13.02</v>
+        <v>12.76</v>
       </c>
       <c r="N40" s="32" t="inlineStr">
         <is>
@@ -3126,16 +3126,16 @@
         </is>
       </c>
       <c r="O40" s="33" t="n">
-        <v>13.37</v>
+        <v>13.18</v>
       </c>
       <c r="P40" s="33" t="n">
-        <v>13.36</v>
+        <v>13.16</v>
       </c>
       <c r="Q40" s="34" t="n">
-        <v>13.31</v>
+        <v>13.18</v>
       </c>
       <c r="R40" s="35" t="n">
-        <v>-0.52</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="41">
@@ -3150,37 +3150,37 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>24.46</v>
+        <v>23.35</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>23.56</v>
+        <v>22.76</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>22.8</v>
+        <v>22.27</v>
       </c>
       <c r="F41" s="27" t="n">
-        <v>22.95</v>
+        <v>22.33</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>23.43</v>
+        <v>22.66</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>22.53</v>
+        <v>22.07</v>
       </c>
       <c r="I41" s="29" t="n">
-        <v>22.05</v>
+        <v>21.74</v>
       </c>
       <c r="J41" s="29" t="n">
-        <v>21.63</v>
+        <v>21.48</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>22.3</v>
+        <v>21.94</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>21.54</v>
+        <v>21.45</v>
       </c>
       <c r="M41" s="31" t="n">
-        <v>20.64</v>
+        <v>20.86</v>
       </c>
       <c r="N41" s="32" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="O41" s="33" t="n">
-        <v>22.45</v>
+        <v>22.03</v>
       </c>
       <c r="P41" s="33" t="n">
-        <v>22.37</v>
+        <v>21.99</v>
       </c>
       <c r="Q41" s="34" t="n">
-        <v>22.48</v>
+        <v>22</v>
       </c>
       <c r="R41" s="35" t="n">
-        <v>-1.53</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="42">
@@ -3212,54 +3212,54 @@
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>192.5</v>
+        <v>191.8</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>187.89</v>
+        <v>188.28</v>
       </c>
       <c r="F42" s="27" t="n">
-        <v>190.4</v>
+        <v>188.47</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>192.5</v>
+        <v>190.93</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>187</v>
+        <v>186.73</v>
       </c>
       <c r="I42" s="29" t="n">
-        <v>184.9</v>
+        <v>184.27</v>
       </c>
       <c r="J42" s="29" t="n">
-        <v>181.5</v>
+        <v>182.53</v>
       </c>
       <c r="K42" s="30" t="n">
-        <v>184.81</v>
+        <v>185.92</v>
       </c>
       <c r="L42" s="31" t="n">
-        <v>180.2</v>
+        <v>182.4</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>174.7</v>
-      </c>
-      <c r="N42" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>178.2</v>
+      </c>
+      <c r="N42" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O42" s="33" t="n">
-        <v>186.12</v>
+        <v>186.49</v>
       </c>
       <c r="P42" s="33" t="n">
-        <v>185.24</v>
+        <v>186.25</v>
       </c>
       <c r="Q42" s="34" t="n">
-        <v>188.3</v>
-      </c>
-      <c r="R42" s="36" t="n">
-        <v>2.62</v>
+        <v>186</v>
+      </c>
+      <c r="R42" s="35" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="43">
@@ -3274,37 +3274,37 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>39.83</v>
+        <v>39.26</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>39.23</v>
+        <v>38.78</v>
       </c>
       <c r="E43" s="26" t="n">
-        <v>38.73</v>
+        <v>38.37</v>
       </c>
       <c r="F43" s="27" t="n">
-        <v>38.77</v>
+        <v>38.35</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>39.11</v>
+        <v>38.65</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>38.51</v>
+        <v>38.17</v>
       </c>
       <c r="I43" s="29" t="n">
-        <v>38.17</v>
+        <v>37.87</v>
       </c>
       <c r="J43" s="29" t="n">
-        <v>37.91</v>
+        <v>37.69</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>38.39</v>
+        <v>38.11</v>
       </c>
       <c r="L43" s="31" t="n">
-        <v>37.89</v>
+        <v>37.7</v>
       </c>
       <c r="M43" s="31" t="n">
-        <v>37.29</v>
+        <v>37.22</v>
       </c>
       <c r="N43" s="32" t="inlineStr">
         <is>
@@ -3312,16 +3312,16 @@
         </is>
       </c>
       <c r="O43" s="33" t="n">
-        <v>38.48</v>
+        <v>38.16</v>
       </c>
       <c r="P43" s="33" t="n">
-        <v>38.44</v>
+        <v>38.14</v>
       </c>
       <c r="Q43" s="34" t="n">
-        <v>38.42</v>
+        <v>38.04</v>
       </c>
       <c r="R43" s="35" t="n">
-        <v>-0.67</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="44">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>27.93</v>
+        <v>27.75</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>27.59</v>
+        <v>27.47</v>
       </c>
       <c r="E44" s="26" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="F44" s="27" t="n">
         <v>27.31</v>
       </c>
-      <c r="F44" s="27" t="n">
-        <v>27.35</v>
-      </c>
       <c r="G44" s="27" t="n">
-        <v>27.53</v>
+        <v>27.45</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>27.19</v>
+        <v>27.17</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>27.01</v>
+        <v>27.03</v>
       </c>
       <c r="J44" s="29" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="K44" s="30" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="L44" s="31" t="n">
         <v>26.85</v>
       </c>
-      <c r="K44" s="30" t="n">
-        <v>27.11</v>
-      </c>
-      <c r="L44" s="31" t="n">
-        <v>26.83</v>
-      </c>
       <c r="M44" s="31" t="n">
-        <v>26.49</v>
+        <v>26.57</v>
       </c>
       <c r="N44" s="32" t="inlineStr">
         <is>
@@ -3374,16 +3374,16 @@
         </is>
       </c>
       <c r="O44" s="33" t="n">
-        <v>27.17</v>
+        <v>27.14</v>
       </c>
       <c r="P44" s="33" t="n">
-        <v>27.14</v>
+        <v>27.1</v>
       </c>
       <c r="Q44" s="34" t="n">
-        <v>27.16</v>
+        <v>27.18</v>
       </c>
       <c r="R44" s="36" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -3398,54 +3398,54 @@
         </is>
       </c>
       <c r="C45" s="25" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>26.44</v>
+        <v>26.38</v>
       </c>
       <c r="E45" s="26" t="n">
-        <v>26.22</v>
+        <v>26.19</v>
       </c>
       <c r="F45" s="27" t="n">
-        <v>26.3</v>
+        <v>26.17</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>26.42</v>
+        <v>26.31</v>
       </c>
       <c r="H45" s="28" t="n">
-        <v>26.16</v>
+        <v>26.09</v>
       </c>
       <c r="I45" s="29" t="n">
-        <v>26.04</v>
+        <v>25.95</v>
       </c>
       <c r="J45" s="29" t="n">
-        <v>25.9</v>
+        <v>25.87</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>26.08</v>
+        <v>26.07</v>
       </c>
       <c r="L45" s="31" t="n">
-        <v>25.86</v>
+        <v>25.88</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="N45" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>25.66</v>
+      </c>
+      <c r="N45" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O45" s="33" t="n">
-        <v>26.13</v>
+        <v>26.09</v>
       </c>
       <c r="P45" s="33" t="n">
-        <v>26.1</v>
+        <v>26.09</v>
       </c>
       <c r="Q45" s="34" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="R45" s="36" t="n">
-        <v>0.46</v>
+        <v>26.02</v>
+      </c>
+      <c r="R45" s="35" t="n">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="46">
@@ -3460,37 +3460,37 @@
         </is>
       </c>
       <c r="C46" s="25" t="n">
-        <v>8.68</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>8.369999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E46" s="26" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H46" s="28" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="F46" s="27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G46" s="27" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="H46" s="28" t="n">
-        <v>8.039999999999999</v>
-      </c>
       <c r="I46" s="29" t="n">
-        <v>7.89</v>
+        <v>8.02</v>
       </c>
       <c r="J46" s="29" t="n">
-        <v>7.73</v>
+        <v>7.95</v>
       </c>
       <c r="K46" s="30" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="L46" s="31" t="n">
         <v>7.94</v>
       </c>
-      <c r="L46" s="31" t="n">
-        <v>7.68</v>
-      </c>
       <c r="M46" s="31" t="n">
-        <v>7.37</v>
+        <v>7.78</v>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
@@ -3498,16 +3498,16 @@
         </is>
       </c>
       <c r="O46" s="33" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="P46" s="33" t="n">
-        <v>7.96</v>
+        <v>8.09</v>
       </c>
       <c r="Q46" s="34" t="n">
-        <v>8.06</v>
+        <v>8.09</v>
       </c>
       <c r="R46" s="36" t="n">
-        <v>3.6</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="47">
@@ -3522,37 +3522,37 @@
         </is>
       </c>
       <c r="C47" s="25" t="n">
-        <v>12.99</v>
+        <v>12.53</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>12.65</v>
+        <v>12.39</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>12.37</v>
+        <v>12.27</v>
       </c>
       <c r="F47" s="27" t="n">
-        <v>12.39</v>
+        <v>12.26</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>12.59</v>
+        <v>12.35</v>
       </c>
       <c r="H47" s="28" t="n">
-        <v>12.25</v>
+        <v>12.21</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>12.05</v>
+        <v>12.12</v>
       </c>
       <c r="J47" s="29" t="n">
-        <v>11.91</v>
+        <v>12.07</v>
       </c>
       <c r="K47" s="30" t="n">
-        <v>12.17</v>
+        <v>12.19</v>
       </c>
       <c r="L47" s="31" t="n">
-        <v>11.89</v>
+        <v>12.07</v>
       </c>
       <c r="M47" s="31" t="n">
-        <v>11.55</v>
+        <v>11.93</v>
       </c>
       <c r="N47" s="32" t="inlineStr">
         <is>
@@ -3560,16 +3560,16 @@
         </is>
       </c>
       <c r="O47" s="33" t="n">
-        <v>12.22</v>
+        <v>12.21</v>
       </c>
       <c r="P47" s="33" t="n">
         <v>12.2</v>
       </c>
       <c r="Q47" s="34" t="n">
-        <v>12.2</v>
+        <v>12.17</v>
       </c>
       <c r="R47" s="35" t="n">
-        <v>-1.45</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="48">
@@ -3584,54 +3584,54 @@
         </is>
       </c>
       <c r="C48" s="25" t="n">
-        <v>211.84</v>
+        <v>210.81</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>208.54</v>
+        <v>208.21</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>205.77</v>
+        <v>206.03</v>
       </c>
       <c r="F48" s="27" t="n">
-        <v>207.2</v>
+        <v>206.33</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>208.5</v>
+        <v>207.77</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>205.2</v>
+        <v>205.17</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>203.9</v>
+        <v>203.73</v>
       </c>
       <c r="J48" s="29" t="n">
-        <v>201.9</v>
+        <v>202.57</v>
       </c>
       <c r="K48" s="30" t="n">
-        <v>203.93</v>
+        <v>204.57</v>
       </c>
       <c r="L48" s="31" t="n">
-        <v>201.16</v>
+        <v>202.39</v>
       </c>
       <c r="M48" s="31" t="n">
-        <v>197.86</v>
-      </c>
-      <c r="N48" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>199.79</v>
+      </c>
+      <c r="N48" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O48" s="33" t="n">
-        <v>204.69</v>
+        <v>204.97</v>
       </c>
       <c r="P48" s="33" t="n">
-        <v>204.18</v>
+        <v>204.77</v>
       </c>
       <c r="Q48" s="34" t="n">
-        <v>205.9</v>
-      </c>
-      <c r="R48" s="36" t="n">
-        <v>1.13</v>
+        <v>204.9</v>
+      </c>
+      <c r="R48" s="35" t="n">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="49">
@@ -3646,37 +3646,37 @@
         </is>
       </c>
       <c r="C49" s="25" t="n">
-        <v>51.48</v>
+        <v>49.74</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>50.16</v>
+        <v>48.86</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>49.05</v>
+        <v>48.13</v>
       </c>
       <c r="F49" s="27" t="n">
-        <v>48.95</v>
+        <v>48.07</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>49.81</v>
+        <v>48.63</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>48.49</v>
+        <v>47.75</v>
       </c>
       <c r="I49" s="29" t="n">
+        <v>47.19</v>
+      </c>
+      <c r="J49" s="29" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="K49" s="30" t="n">
         <v>47.63</v>
       </c>
-      <c r="J49" s="29" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="K49" s="30" t="n">
-        <v>48.31</v>
-      </c>
       <c r="L49" s="31" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
       <c r="M49" s="31" t="n">
-        <v>45.88</v>
+        <v>46.02</v>
       </c>
       <c r="N49" s="32" t="inlineStr">
         <is>
@@ -3684,16 +3684,16 @@
         </is>
       </c>
       <c r="O49" s="33" t="n">
-        <v>48.45</v>
+        <v>47.73</v>
       </c>
       <c r="P49" s="33" t="n">
-        <v>48.41</v>
+        <v>47.7</v>
       </c>
       <c r="Q49" s="34" t="n">
-        <v>48.1</v>
+        <v>47.5</v>
       </c>
       <c r="R49" s="35" t="n">
-        <v>-1.84</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="50">
@@ -3708,37 +3708,37 @@
         </is>
       </c>
       <c r="C50" s="25" t="n">
-        <v>35.38</v>
+        <v>34.96</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>34.74</v>
+        <v>34.54</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>34.2</v>
+        <v>34.19</v>
       </c>
       <c r="F50" s="27" t="n">
-        <v>34.35</v>
+        <v>34.17</v>
       </c>
       <c r="G50" s="27" t="n">
-        <v>34.67</v>
+        <v>34.43</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>34.03</v>
+        <v>34.01</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>33.71</v>
+        <v>33.75</v>
       </c>
       <c r="J50" s="29" t="n">
-        <v>33.39</v>
+        <v>33.59</v>
       </c>
       <c r="K50" s="30" t="n">
-        <v>33.84</v>
+        <v>33.95</v>
       </c>
       <c r="L50" s="31" t="n">
-        <v>33.3</v>
+        <v>33.6</v>
       </c>
       <c r="M50" s="31" t="n">
-        <v>32.66</v>
+        <v>33.18</v>
       </c>
       <c r="N50" s="32" t="inlineStr">
         <is>
@@ -3746,16 +3746,16 @@
         </is>
       </c>
       <c r="O50" s="33" t="n">
-        <v>33.96</v>
+        <v>34</v>
       </c>
       <c r="P50" s="33" t="n">
-        <v>33.89</v>
+        <v>33.99</v>
       </c>
       <c r="Q50" s="34" t="n">
-        <v>34.04</v>
-      </c>
-      <c r="R50" s="36" t="n">
-        <v>0.18</v>
+        <v>33.9</v>
+      </c>
+      <c r="R50" s="35" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="51">
@@ -3770,37 +3770,37 @@
         </is>
       </c>
       <c r="C51" s="25" t="n">
-        <v>13.73</v>
+        <v>13.56</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>13.49</v>
+        <v>13.38</v>
       </c>
       <c r="E51" s="26" t="n">
-        <v>13.29</v>
+        <v>13.23</v>
       </c>
       <c r="F51" s="27" t="n">
-        <v>13.37</v>
+        <v>13.24</v>
       </c>
       <c r="G51" s="27" t="n">
-        <v>13.48</v>
+        <v>13.35</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>13.24</v>
+        <v>13.17</v>
       </c>
       <c r="I51" s="29" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="J51" s="29" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="K51" s="30" t="n">
         <v>13.13</v>
       </c>
-      <c r="J51" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="K51" s="30" t="n">
-        <v>13.15</v>
-      </c>
       <c r="L51" s="31" t="n">
-        <v>12.95</v>
+        <v>12.98</v>
       </c>
       <c r="M51" s="31" t="n">
-        <v>12.71</v>
+        <v>12.8</v>
       </c>
       <c r="N51" s="32" t="inlineStr">
         <is>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="O51" s="33" t="n">
-        <v>13.2</v>
+        <v>13.16</v>
       </c>
       <c r="P51" s="33" t="n">
-        <v>13.17</v>
+        <v>13.14</v>
       </c>
       <c r="Q51" s="34" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="R51" s="36" t="n">
-        <v>0.45</v>
+        <v>13.14</v>
+      </c>
+      <c r="R51" s="35" t="n">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="52">
@@ -3832,37 +3832,37 @@
         </is>
       </c>
       <c r="C52" s="25" t="n">
-        <v>64.53</v>
+        <v>61.27</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>62.78</v>
+        <v>60.67</v>
       </c>
       <c r="E52" s="26" t="n">
-        <v>61.32</v>
+        <v>60.17</v>
       </c>
       <c r="F52" s="27" t="n">
-        <v>61.35</v>
+        <v>60.5</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>62.4</v>
+        <v>60.7</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>60.65</v>
+        <v>60.1</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>59.6</v>
+        <v>59.9</v>
       </c>
       <c r="J52" s="29" t="n">
-        <v>58.9</v>
+        <v>59.5</v>
       </c>
       <c r="K52" s="30" t="n">
-        <v>60.34</v>
+        <v>59.83</v>
       </c>
       <c r="L52" s="31" t="n">
-        <v>58.87</v>
+        <v>59.33</v>
       </c>
       <c r="M52" s="31" t="n">
-        <v>57.12</v>
+        <v>58.73</v>
       </c>
       <c r="N52" s="32" t="inlineStr">
         <is>
@@ -3870,16 +3870,16 @@
         </is>
       </c>
       <c r="O52" s="33" t="n">
-        <v>60.56</v>
+        <v>59.99</v>
       </c>
       <c r="P52" s="33" t="n">
-        <v>60.47</v>
+        <v>59.88</v>
       </c>
       <c r="Q52" s="34" t="n">
         <v>60.3</v>
       </c>
-      <c r="R52" s="35" t="n">
-        <v>-2.27</v>
+      <c r="R52" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3894,54 +3894,54 @@
         </is>
       </c>
       <c r="C53" s="25" t="n">
-        <v>24.66</v>
+        <v>24.44</v>
       </c>
       <c r="D53" s="25" t="n">
-        <v>24.31</v>
+        <v>24.03</v>
       </c>
       <c r="E53" s="26" t="n">
-        <v>24.01</v>
+        <v>23.69</v>
       </c>
       <c r="F53" s="27" t="n">
-        <v>23.98</v>
+        <v>23.71</v>
       </c>
       <c r="G53" s="27" t="n">
-        <v>24.21</v>
+        <v>23.95</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>23.86</v>
+        <v>23.54</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>23.63</v>
+        <v>23.3</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>23.51</v>
+        <v>23.13</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>23.82</v>
+        <v>23.46</v>
       </c>
       <c r="L53" s="31" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="M53" s="31" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="N53" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O53" s="33" t="n">
         <v>23.52</v>
       </c>
-      <c r="M53" s="31" t="n">
-        <v>23.17</v>
-      </c>
-      <c r="N53" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O53" s="33" t="n">
-        <v>23.85</v>
-      </c>
       <c r="P53" s="33" t="n">
-        <v>23.84</v>
+        <v>23.49</v>
       </c>
       <c r="Q53" s="34" t="n">
-        <v>23.75</v>
+        <v>23.47</v>
       </c>
       <c r="R53" s="35" t="n">
-        <v>-0.42</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="54">
@@ -3956,54 +3956,54 @@
         </is>
       </c>
       <c r="C54" s="25" t="n">
-        <v>5.49</v>
+        <v>5.42</v>
       </c>
       <c r="D54" s="25" t="n">
-        <v>5.4</v>
+        <v>5.34</v>
       </c>
       <c r="E54" s="26" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="G54" s="27" t="n">
         <v>5.32</v>
       </c>
-      <c r="F54" s="27" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="G54" s="27" t="n">
-        <v>5.38</v>
-      </c>
       <c r="H54" s="28" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="J54" s="29" t="n">
-        <v>5.2</v>
+        <v>5.16</v>
       </c>
       <c r="K54" s="30" t="n">
-        <v>5.27</v>
+        <v>5.23</v>
       </c>
       <c r="L54" s="31" t="n">
-        <v>5.19</v>
+        <v>5.16</v>
       </c>
       <c r="M54" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N54" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>5.08</v>
+      </c>
+      <c r="N54" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O54" s="33" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="P54" s="33" t="n">
-        <v>5.28</v>
+        <v>5.23</v>
       </c>
       <c r="Q54" s="34" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="R54" s="36" t="n">
-        <v>0.57</v>
+        <v>5.23</v>
+      </c>
+      <c r="R54" s="35" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="55">
@@ -4018,37 +4018,37 @@
         </is>
       </c>
       <c r="C55" s="25" t="n">
-        <v>19.31</v>
+        <v>19.14</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>18.43</v>
+        <v>18.56</v>
       </c>
       <c r="E55" s="26" t="n">
-        <v>17.7</v>
+        <v>18.07</v>
       </c>
       <c r="F55" s="27" t="n">
-        <v>17.96</v>
+        <v>18.26</v>
       </c>
       <c r="G55" s="27" t="n">
-        <v>18.36</v>
+        <v>18.52</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>17.48</v>
+        <v>17.94</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>17.08</v>
+        <v>17.68</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>16.6</v>
+        <v>17.36</v>
       </c>
       <c r="K55" s="30" t="n">
-        <v>17.2</v>
+        <v>17.75</v>
       </c>
       <c r="L55" s="31" t="n">
-        <v>16.47</v>
+        <v>17.26</v>
       </c>
       <c r="M55" s="31" t="n">
-        <v>15.59</v>
+        <v>16.68</v>
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
@@ -4056,16 +4056,16 @@
         </is>
       </c>
       <c r="O55" s="33" t="n">
-        <v>17.38</v>
+        <v>17.87</v>
       </c>
       <c r="P55" s="33" t="n">
-        <v>17.27</v>
+        <v>17.79</v>
       </c>
       <c r="Q55" s="34" t="n">
-        <v>17.55</v>
+        <v>18</v>
       </c>
       <c r="R55" s="36" t="n">
-        <v>4.03</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="56">
@@ -4080,54 +4080,54 @@
         </is>
       </c>
       <c r="C56" s="25" t="n">
-        <v>102.62</v>
+        <v>101.29</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>99.67</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="E56" s="26" t="n">
-        <v>97.2</v>
+        <v>97.16</v>
       </c>
       <c r="F56" s="27" t="n">
-        <v>98.56999999999999</v>
+        <v>97.03</v>
       </c>
       <c r="G56" s="27" t="n">
-        <v>99.68000000000001</v>
+        <v>98.47</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>96.73</v>
+        <v>96.22</v>
       </c>
       <c r="I56" s="29" t="n">
-        <v>95.62</v>
+        <v>94.78</v>
       </c>
       <c r="J56" s="29" t="n">
-        <v>93.78</v>
+        <v>93.97</v>
       </c>
       <c r="K56" s="30" t="n">
-        <v>95.55</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L56" s="31" t="n">
-        <v>93.08</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="M56" s="31" t="n">
-        <v>90.13</v>
-      </c>
-      <c r="N56" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>91.76000000000001</v>
+      </c>
+      <c r="N56" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O56" s="33" t="n">
-        <v>96.26000000000001</v>
+        <v>96.14</v>
       </c>
       <c r="P56" s="33" t="n">
-        <v>95.78</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="Q56" s="34" t="n">
-        <v>97.45</v>
-      </c>
-      <c r="R56" s="36" t="n">
-        <v>2.69</v>
+        <v>95.59999999999999</v>
+      </c>
+      <c r="R56" s="35" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="57">
@@ -4142,37 +4142,37 @@
         </is>
       </c>
       <c r="C57" s="25" t="n">
-        <v>18.92</v>
+        <v>18.35</v>
       </c>
       <c r="D57" s="25" t="n">
-        <v>18.57</v>
+        <v>18.14</v>
       </c>
       <c r="E57" s="26" t="n">
-        <v>18.27</v>
+        <v>17.96</v>
       </c>
       <c r="F57" s="27" t="n">
-        <v>18.29</v>
+        <v>17.94</v>
       </c>
       <c r="G57" s="27" t="n">
-        <v>18.49</v>
+        <v>18.08</v>
       </c>
       <c r="H57" s="28" t="n">
-        <v>18.14</v>
+        <v>17.87</v>
       </c>
       <c r="I57" s="29" t="n">
-        <v>17.94</v>
+        <v>17.73</v>
       </c>
       <c r="J57" s="29" t="n">
-        <v>17.79</v>
+        <v>17.66</v>
       </c>
       <c r="K57" s="30" t="n">
-        <v>18.08</v>
+        <v>17.85</v>
       </c>
       <c r="L57" s="31" t="n">
-        <v>17.78</v>
+        <v>17.67</v>
       </c>
       <c r="M57" s="31" t="n">
-        <v>17.43</v>
+        <v>17.46</v>
       </c>
       <c r="N57" s="32" t="inlineStr">
         <is>
@@ -4180,16 +4180,16 @@
         </is>
       </c>
       <c r="O57" s="33" t="n">
-        <v>18.12</v>
+        <v>17.87</v>
       </c>
       <c r="P57" s="33" t="n">
-        <v>18.1</v>
+        <v>17.86</v>
       </c>
       <c r="Q57" s="34" t="n">
-        <v>18.08</v>
+        <v>17.8</v>
       </c>
       <c r="R57" s="35" t="n">
-        <v>-1.47</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="58">
@@ -4204,54 +4204,54 @@
         </is>
       </c>
       <c r="C58" s="25" t="n">
-        <v>22.88</v>
+        <v>21.85</v>
       </c>
       <c r="D58" s="25" t="n">
-        <v>22.39</v>
+        <v>21.75</v>
       </c>
       <c r="E58" s="26" t="n">
-        <v>21.98</v>
+        <v>21.67</v>
       </c>
       <c r="F58" s="27" t="n">
-        <v>22.01</v>
+        <v>21.72</v>
       </c>
       <c r="G58" s="27" t="n">
-        <v>22.3</v>
+        <v>21.76</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>21.81</v>
+        <v>21.66</v>
       </c>
       <c r="I58" s="29" t="n">
-        <v>21.52</v>
+        <v>21.62</v>
       </c>
       <c r="J58" s="29" t="n">
-        <v>21.32</v>
+        <v>21.56</v>
       </c>
       <c r="K58" s="30" t="n">
-        <v>21.71</v>
+        <v>21.61</v>
       </c>
       <c r="L58" s="31" t="n">
-        <v>21.3</v>
+        <v>21.53</v>
       </c>
       <c r="M58" s="31" t="n">
-        <v>20.81</v>
-      </c>
-      <c r="N58" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>21.43</v>
+      </c>
+      <c r="N58" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O58" s="33" t="n">
-        <v>21.78</v>
+        <v>21.64</v>
       </c>
       <c r="P58" s="33" t="n">
-        <v>21.75</v>
+        <v>21.62</v>
       </c>
       <c r="Q58" s="34" t="n">
-        <v>21.73</v>
-      </c>
-      <c r="R58" s="36" t="n">
-        <v>1.07</v>
+        <v>21.69</v>
+      </c>
+      <c r="R58" s="35" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="59">
@@ -4266,54 +4266,54 @@
         </is>
       </c>
       <c r="C59" s="25" t="n">
-        <v>23.88</v>
+        <v>23.59</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>23.55</v>
+        <v>23.39</v>
       </c>
       <c r="E59" s="26" t="n">
-        <v>23.28</v>
+        <v>23.23</v>
       </c>
       <c r="F59" s="27" t="n">
-        <v>23.38</v>
+        <v>23.3</v>
       </c>
       <c r="G59" s="27" t="n">
-        <v>23.53</v>
+        <v>23.39</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>23.2</v>
+        <v>23.19</v>
       </c>
       <c r="I59" s="29" t="n">
-        <v>23.05</v>
+        <v>23.1</v>
       </c>
       <c r="J59" s="29" t="n">
-        <v>22.87</v>
+        <v>22.99</v>
       </c>
       <c r="K59" s="30" t="n">
-        <v>23.09</v>
+        <v>23.11</v>
       </c>
       <c r="L59" s="31" t="n">
-        <v>22.82</v>
+        <v>22.95</v>
       </c>
       <c r="M59" s="31" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="N59" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>22.75</v>
+      </c>
+      <c r="N59" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O59" s="33" t="n">
         <v>23.16</v>
       </c>
       <c r="P59" s="33" t="n">
-        <v>23.12</v>
+        <v>23.13</v>
       </c>
       <c r="Q59" s="34" t="n">
-        <v>23.23</v>
+        <v>23.22</v>
       </c>
       <c r="R59" s="35" t="n">
-        <v>-0.39</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="60">
@@ -4328,54 +4328,54 @@
         </is>
       </c>
       <c r="C60" s="25" t="n">
-        <v>29.43</v>
+        <v>29.03</v>
       </c>
       <c r="D60" s="25" t="n">
-        <v>29.03</v>
+        <v>28.79</v>
       </c>
       <c r="E60" s="26" t="n">
-        <v>28.69</v>
+        <v>28.59</v>
       </c>
       <c r="F60" s="27" t="n">
-        <v>28.78</v>
+        <v>28.61</v>
       </c>
       <c r="G60" s="27" t="n">
-        <v>28.98</v>
+        <v>28.75</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>28.58</v>
+        <v>28.51</v>
       </c>
       <c r="I60" s="29" t="n">
-        <v>28.38</v>
+        <v>28.37</v>
       </c>
       <c r="J60" s="29" t="n">
-        <v>28.18</v>
+        <v>28.27</v>
       </c>
       <c r="K60" s="30" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="L60" s="31" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="M60" s="31" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="N60" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O60" s="33" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="P60" s="33" t="n">
         <v>28.47</v>
       </c>
-      <c r="L60" s="31" t="n">
-        <v>28.13</v>
-      </c>
-      <c r="M60" s="31" t="n">
-        <v>27.73</v>
-      </c>
-      <c r="N60" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O60" s="33" t="n">
-        <v>28.54</v>
-      </c>
-      <c r="P60" s="33" t="n">
-        <v>28.5</v>
-      </c>
       <c r="Q60" s="34" t="n">
-        <v>28.58</v>
-      </c>
-      <c r="R60" s="36" t="n">
-        <v>0.63</v>
+        <v>28.48</v>
+      </c>
+      <c r="R60" s="35" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="61">
@@ -4390,54 +4390,54 @@
         </is>
       </c>
       <c r="C61" s="25" t="n">
-        <v>46.17</v>
+        <v>45.83</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>45.79</v>
+        <v>45.65</v>
       </c>
       <c r="E61" s="26" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F61" s="27" t="n">
         <v>45.48</v>
       </c>
-      <c r="F61" s="27" t="n">
-        <v>45.54</v>
-      </c>
       <c r="G61" s="27" t="n">
-        <v>45.74</v>
+        <v>45.6</v>
       </c>
       <c r="H61" s="28" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="I61" s="29" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="J61" s="29" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="K61" s="30" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="L61" s="31" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="M61" s="31" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="N61" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O61" s="33" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="P61" s="33" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="Q61" s="34" t="n">
         <v>45.36</v>
       </c>
-      <c r="I61" s="29" t="n">
-        <v>45.16</v>
-      </c>
-      <c r="J61" s="29" t="n">
-        <v>44.98</v>
-      </c>
-      <c r="K61" s="30" t="n">
-        <v>45.26</v>
-      </c>
-      <c r="L61" s="31" t="n">
-        <v>44.95</v>
-      </c>
-      <c r="M61" s="31" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="N61" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O61" s="33" t="n">
-        <v>45.33</v>
-      </c>
-      <c r="P61" s="33" t="n">
-        <v>45.29</v>
-      </c>
-      <c r="Q61" s="34" t="n">
-        <v>45.34</v>
-      </c>
       <c r="R61" s="36" t="n">
-        <v>0.35</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="62">
@@ -4452,54 +4452,54 @@
         </is>
       </c>
       <c r="C62" s="25" t="n">
-        <v>20.17</v>
+        <v>19.99</v>
       </c>
       <c r="D62" s="25" t="n">
-        <v>19.9</v>
+        <v>19.78</v>
       </c>
       <c r="E62" s="26" t="n">
-        <v>19.67</v>
+        <v>19.6</v>
       </c>
       <c r="F62" s="27" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="G62" s="27" t="n">
         <v>19.73</v>
       </c>
-      <c r="G62" s="27" t="n">
-        <v>19.87</v>
-      </c>
       <c r="H62" s="28" t="n">
-        <v>19.6</v>
+        <v>19.52</v>
       </c>
       <c r="I62" s="29" t="n">
-        <v>19.46</v>
+        <v>19.4</v>
       </c>
       <c r="J62" s="29" t="n">
-        <v>19.33</v>
+        <v>19.31</v>
       </c>
       <c r="K62" s="30" t="n">
-        <v>19.52</v>
+        <v>19.49</v>
       </c>
       <c r="L62" s="31" t="n">
-        <v>19.29</v>
+        <v>19.31</v>
       </c>
       <c r="M62" s="31" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="N62" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>19.1</v>
+      </c>
+      <c r="N62" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O62" s="33" t="n">
-        <v>19.57</v>
+        <v>19.51</v>
       </c>
       <c r="P62" s="33" t="n">
-        <v>19.54</v>
+        <v>19.5</v>
       </c>
       <c r="Q62" s="34" t="n">
-        <v>19.6</v>
+        <v>19.48</v>
       </c>
       <c r="R62" s="35" t="n">
-        <v>-0.25</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="63">
@@ -4514,54 +4514,54 @@
         </is>
       </c>
       <c r="C63" s="25" t="n">
-        <v>16.09</v>
+        <v>15.87</v>
       </c>
       <c r="D63" s="25" t="n">
-        <v>15.71</v>
+        <v>15.63</v>
       </c>
       <c r="E63" s="26" t="n">
-        <v>15.4</v>
+        <v>15.43</v>
       </c>
       <c r="F63" s="27" t="n">
-        <v>15.61</v>
+        <v>15.45</v>
       </c>
       <c r="G63" s="27" t="n">
-        <v>15.73</v>
+        <v>15.58</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>15.35</v>
+        <v>15.34</v>
       </c>
       <c r="I63" s="29" t="n">
-        <v>15.23</v>
+        <v>15.21</v>
       </c>
       <c r="J63" s="29" t="n">
-        <v>14.97</v>
+        <v>15.1</v>
       </c>
       <c r="K63" s="30" t="n">
-        <v>15.18</v>
+        <v>15.29</v>
       </c>
       <c r="L63" s="31" t="n">
-        <v>14.87</v>
+        <v>15.09</v>
       </c>
       <c r="M63" s="31" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="N63" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>14.85</v>
+      </c>
+      <c r="N63" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O63" s="33" t="n">
-        <v>15.28</v>
+        <v>15.33</v>
       </c>
       <c r="P63" s="33" t="n">
-        <v>15.21</v>
+        <v>15.31</v>
       </c>
       <c r="Q63" s="34" t="n">
-        <v>15.48</v>
-      </c>
-      <c r="R63" s="36" t="n">
-        <v>2.38</v>
+        <v>15.31</v>
+      </c>
+      <c r="R63" s="35" t="n">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="64">
@@ -4576,54 +4576,54 @@
         </is>
       </c>
       <c r="C64" s="25" t="n">
-        <v>25.75</v>
+        <v>25.73</v>
       </c>
       <c r="D64" s="25" t="n">
-        <v>25.51</v>
+        <v>25.49</v>
       </c>
       <c r="E64" s="26" t="n">
-        <v>25.31</v>
+        <v>25.29</v>
       </c>
       <c r="F64" s="27" t="n">
-        <v>25.4</v>
+        <v>25.41</v>
       </c>
       <c r="G64" s="27" t="n">
-        <v>25.5</v>
+        <v>25.49</v>
       </c>
       <c r="H64" s="28" t="n">
-        <v>25.26</v>
+        <v>25.25</v>
       </c>
       <c r="I64" s="29" t="n">
-        <v>25.16</v>
+        <v>25.17</v>
       </c>
       <c r="J64" s="29" t="n">
-        <v>25.02</v>
+        <v>25.01</v>
       </c>
       <c r="K64" s="30" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="L64" s="31" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="M64" s="31" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="N64" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O64" s="33" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="P64" s="33" t="n">
         <v>25.17</v>
       </c>
-      <c r="L64" s="31" t="n">
-        <v>24.97</v>
-      </c>
-      <c r="M64" s="31" t="n">
-        <v>24.73</v>
-      </c>
-      <c r="N64" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O64" s="33" t="n">
-        <v>25.23</v>
-      </c>
-      <c r="P64" s="33" t="n">
-        <v>25.19</v>
-      </c>
       <c r="Q64" s="34" t="n">
-        <v>25.3</v>
+        <v>25.32</v>
       </c>
       <c r="R64" s="36" t="n">
-        <v>0.64</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="65">
@@ -4638,37 +4638,37 @@
         </is>
       </c>
       <c r="C65" s="25" t="n">
-        <v>7.49</v>
+        <v>7.48</v>
       </c>
       <c r="D65" s="25" t="n">
-        <v>7.43</v>
+        <v>7.41</v>
       </c>
       <c r="E65" s="26" t="n">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
       <c r="F65" s="27" t="n">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
       <c r="G65" s="27" t="n">
-        <v>7.42</v>
+        <v>7.4</v>
       </c>
       <c r="H65" s="28" t="n">
-        <v>7.36</v>
+        <v>7.33</v>
       </c>
       <c r="I65" s="29" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="J65" s="29" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="K65" s="30" t="n">
         <v>7.32</v>
       </c>
-      <c r="J65" s="29" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="K65" s="30" t="n">
-        <v>7.34</v>
-      </c>
       <c r="L65" s="31" t="n">
-        <v>7.29</v>
+        <v>7.26</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>7.23</v>
+        <v>7.19</v>
       </c>
       <c r="N65" s="32" t="inlineStr">
         <is>
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="O65" s="33" t="n">
-        <v>7.35</v>
+        <v>7.32</v>
       </c>
       <c r="P65" s="33" t="n">
-        <v>7.35</v>
+        <v>7.32</v>
       </c>
       <c r="Q65" s="34" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="R65" s="36" t="n">
-        <v>0.41</v>
+        <v>7.31</v>
+      </c>
+      <c r="R65" s="35" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="66">
@@ -4700,37 +4700,37 @@
         </is>
       </c>
       <c r="C66" s="25" t="n">
-        <v>5.05</v>
+        <v>5.03</v>
       </c>
       <c r="D66" s="25" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="E66" s="26" t="n">
-        <v>4.96</v>
+        <v>4.94</v>
       </c>
       <c r="F66" s="27" t="n">
         <v>4.97</v>
       </c>
       <c r="G66" s="27" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="H66" s="28" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="I66" s="29" t="n">
         <v>4.92</v>
       </c>
       <c r="J66" s="29" t="n">
-        <v>4.9</v>
+        <v>4.88</v>
       </c>
       <c r="K66" s="30" t="n">
-        <v>4.93</v>
+        <v>4.91</v>
       </c>
       <c r="L66" s="31" t="n">
-        <v>4.89</v>
+        <v>4.87</v>
       </c>
       <c r="M66" s="31" t="n">
-        <v>4.84</v>
+        <v>4.82</v>
       </c>
       <c r="N66" s="20" t="inlineStr">
         <is>
@@ -4738,16 +4738,16 @@
         </is>
       </c>
       <c r="O66" s="33" t="n">
-        <v>4.94</v>
+        <v>4.92</v>
       </c>
       <c r="P66" s="33" t="n">
-        <v>4.93</v>
+        <v>4.91</v>
       </c>
       <c r="Q66" s="34" t="n">
         <v>4.95</v>
       </c>
       <c r="R66" s="36" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4762,51 +4762,51 @@
         </is>
       </c>
       <c r="C67" s="25" t="n">
-        <v>5.07</v>
+        <v>5.06</v>
       </c>
       <c r="D67" s="25" t="n">
-        <v>5.03</v>
+        <v>5.02</v>
       </c>
       <c r="E67" s="26" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="F67" s="27" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="G67" s="27" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
       <c r="H67" s="28" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="I67" s="29" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="J67" s="29" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="K67" s="30" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L67" s="31" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="M67" s="31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O67" s="33" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="P67" s="33" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="Q67" s="34" t="n">
         <v>4.96</v>
-      </c>
-      <c r="J67" s="29" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="K67" s="30" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="L67" s="31" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="M67" s="31" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O67" s="33" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="P67" s="33" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="Q67" s="34" t="n">
-        <v>4.97</v>
       </c>
       <c r="R67" s="35" t="n">
         <v>-0.2</v>
@@ -4824,54 +4824,54 @@
         </is>
       </c>
       <c r="C68" s="25" t="n">
-        <v>70.06</v>
+        <v>67.38</v>
       </c>
       <c r="D68" s="25" t="n">
-        <v>68.11</v>
+        <v>66.53</v>
       </c>
       <c r="E68" s="26" t="n">
-        <v>66.47</v>
+        <v>65.81</v>
       </c>
       <c r="F68" s="27" t="n">
-        <v>66.88</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="G68" s="27" t="n">
-        <v>67.87</v>
+        <v>66.33</v>
       </c>
       <c r="H68" s="28" t="n">
-        <v>65.92</v>
+        <v>65.48</v>
       </c>
       <c r="I68" s="29" t="n">
-        <v>64.93000000000001</v>
+        <v>64.97</v>
       </c>
       <c r="J68" s="29" t="n">
-        <v>63.97</v>
+        <v>64.63</v>
       </c>
       <c r="K68" s="30" t="n">
-        <v>65.38</v>
+        <v>65.34</v>
       </c>
       <c r="L68" s="31" t="n">
-        <v>63.74</v>
+        <v>64.62</v>
       </c>
       <c r="M68" s="31" t="n">
-        <v>61.79</v>
-      </c>
-      <c r="N68" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>63.77</v>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O68" s="33" t="n">
-        <v>65.72</v>
+        <v>65.44</v>
       </c>
       <c r="P68" s="33" t="n">
-        <v>65.53</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="Q68" s="34" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="R68" s="36" t="n">
-        <v>0.84</v>
+        <v>65.3</v>
+      </c>
+      <c r="R68" s="35" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="69">
@@ -4886,54 +4886,54 @@
         </is>
       </c>
       <c r="C69" s="25" t="n">
-        <v>70.48999999999999</v>
+        <v>69.58</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>68.64</v>
+        <v>68.23</v>
       </c>
       <c r="E69" s="26" t="n">
-        <v>67.09</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F69" s="27" t="n">
-        <v>68.05</v>
+        <v>66.95</v>
       </c>
       <c r="G69" s="27" t="n">
-        <v>68.7</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>66.84999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="I69" s="29" t="n">
-        <v>66.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J69" s="29" t="n">
-        <v>65</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K69" s="30" t="n">
-        <v>66.06</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="L69" s="31" t="n">
-        <v>64.51000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>62.66</v>
-      </c>
-      <c r="N69" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>63.87</v>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O69" s="33" t="n">
-        <v>66.53</v>
+        <v>66.48</v>
       </c>
       <c r="P69" s="33" t="n">
-        <v>66.2</v>
+        <v>66.45</v>
       </c>
       <c r="Q69" s="34" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="R69" s="36" t="n">
-        <v>3.3</v>
+        <v>66.05</v>
+      </c>
+      <c r="R69" s="35" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="70">
@@ -4948,54 +4948,54 @@
         </is>
       </c>
       <c r="C70" s="25" t="n">
-        <v>93.52</v>
+        <v>87.72</v>
       </c>
       <c r="D70" s="25" t="n">
-        <v>89.92</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="E70" s="26" t="n">
-        <v>86.91</v>
+        <v>85.14</v>
       </c>
       <c r="F70" s="27" t="n">
-        <v>87.37</v>
+        <v>84.98</v>
       </c>
       <c r="G70" s="27" t="n">
-        <v>89.33</v>
+        <v>85.92</v>
       </c>
       <c r="H70" s="28" t="n">
-        <v>85.73</v>
+        <v>84.52</v>
       </c>
       <c r="I70" s="29" t="n">
-        <v>83.77</v>
+        <v>83.58</v>
       </c>
       <c r="J70" s="29" t="n">
-        <v>82.13</v>
+        <v>83.12</v>
       </c>
       <c r="K70" s="30" t="n">
-        <v>84.89</v>
+        <v>84.36</v>
       </c>
       <c r="L70" s="31" t="n">
-        <v>81.88</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>78.28</v>
-      </c>
-      <c r="N70" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>81.78</v>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O70" s="33" t="n">
-        <v>85.45</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="P70" s="33" t="n">
-        <v>85.17</v>
+        <v>84.47</v>
       </c>
       <c r="Q70" s="34" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="R70" s="36" t="n">
-        <v>0.47</v>
+        <v>84.05</v>
+      </c>
+      <c r="R70" s="35" t="n">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="71">
@@ -5010,37 +5010,37 @@
         </is>
       </c>
       <c r="C71" s="25" t="n">
-        <v>129.38</v>
+        <v>128.92</v>
       </c>
       <c r="D71" s="25" t="n">
-        <v>126.98</v>
+        <v>125.82</v>
       </c>
       <c r="E71" s="26" t="n">
-        <v>124.97</v>
+        <v>123.22</v>
       </c>
       <c r="F71" s="27" t="n">
-        <v>125.03</v>
+        <v>122.87</v>
       </c>
       <c r="G71" s="27" t="n">
-        <v>126.47</v>
+        <v>124.93</v>
       </c>
       <c r="H71" s="28" t="n">
-        <v>124.07</v>
+        <v>121.83</v>
       </c>
       <c r="I71" s="29" t="n">
-        <v>122.63</v>
+        <v>119.77</v>
       </c>
       <c r="J71" s="29" t="n">
-        <v>121.67</v>
+        <v>118.73</v>
       </c>
       <c r="K71" s="30" t="n">
-        <v>123.63</v>
+        <v>121.48</v>
       </c>
       <c r="L71" s="31" t="n">
-        <v>121.62</v>
+        <v>118.88</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>119.22</v>
+        <v>115.78</v>
       </c>
       <c r="N71" s="32" t="inlineStr">
         <is>
@@ -5048,16 +5048,16 @@
         </is>
       </c>
       <c r="O71" s="33" t="n">
-        <v>123.94</v>
+        <v>121.78</v>
       </c>
       <c r="P71" s="33" t="n">
-        <v>123.82</v>
+        <v>121.72</v>
       </c>
       <c r="Q71" s="34" t="n">
-        <v>123.6</v>
+        <v>120.8</v>
       </c>
       <c r="R71" s="35" t="n">
-        <v>-0.24</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="72">
@@ -5072,37 +5072,37 @@
         </is>
       </c>
       <c r="C72" s="25" t="n">
-        <v>25.69</v>
+        <v>25.71</v>
       </c>
       <c r="D72" s="25" t="n">
-        <v>25.39</v>
+        <v>25.25</v>
       </c>
       <c r="E72" s="26" t="n">
-        <v>25.13</v>
+        <v>24.87</v>
       </c>
       <c r="F72" s="27" t="n">
-        <v>25.13</v>
+        <v>24.9</v>
       </c>
       <c r="G72" s="27" t="n">
-        <v>25.32</v>
+        <v>25.16</v>
       </c>
       <c r="H72" s="28" t="n">
-        <v>25.02</v>
+        <v>24.7</v>
       </c>
       <c r="I72" s="29" t="n">
-        <v>24.83</v>
+        <v>24.44</v>
       </c>
       <c r="J72" s="29" t="n">
-        <v>24.72</v>
+        <v>24.24</v>
       </c>
       <c r="K72" s="30" t="n">
-        <v>24.97</v>
+        <v>24.61</v>
       </c>
       <c r="L72" s="31" t="n">
-        <v>24.71</v>
+        <v>24.23</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>24.41</v>
+        <v>23.77</v>
       </c>
       <c r="N72" s="32" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         </is>
       </c>
       <c r="O72" s="33" t="n">
-        <v>25</v>
+        <v>24.68</v>
       </c>
       <c r="P72" s="33" t="n">
-        <v>24.99</v>
+        <v>24.65</v>
       </c>
       <c r="Q72" s="34" t="n">
-        <v>24.95</v>
+        <v>24.63</v>
       </c>
       <c r="R72" s="35" t="n">
-        <v>-0.68</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="73">
@@ -5134,37 +5134,37 @@
         </is>
       </c>
       <c r="C73" s="25" t="n">
-        <v>21.43</v>
+        <v>21.66</v>
       </c>
       <c r="D73" s="25" t="n">
-        <v>21.19</v>
+        <v>21.28</v>
       </c>
       <c r="E73" s="26" t="n">
-        <v>20.99</v>
+        <v>20.97</v>
       </c>
       <c r="F73" s="27" t="n">
-        <v>20.96</v>
+        <v>20.98</v>
       </c>
       <c r="G73" s="27" t="n">
-        <v>21.12</v>
+        <v>21.2</v>
       </c>
       <c r="H73" s="28" t="n">
-        <v>20.88</v>
+        <v>20.82</v>
       </c>
       <c r="I73" s="29" t="n">
-        <v>20.72</v>
+        <v>20.6</v>
       </c>
       <c r="J73" s="29" t="n">
-        <v>20.64</v>
+        <v>20.44</v>
       </c>
       <c r="K73" s="30" t="n">
-        <v>20.85</v>
+        <v>20.75</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>20.65</v>
+        <v>20.44</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>20.41</v>
+        <v>20.06</v>
       </c>
       <c r="N73" s="32" t="inlineStr">
         <is>
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="O73" s="33" t="n">
-        <v>20.88</v>
+        <v>20.8</v>
       </c>
       <c r="P73" s="33" t="n">
-        <v>20.87</v>
+        <v>20.78</v>
       </c>
       <c r="Q73" s="34" t="n">
-        <v>20.8</v>
+        <v>20.75</v>
       </c>
       <c r="R73" s="35" t="n">
-        <v>-0.76</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="74">
@@ -5196,37 +5196,37 @@
         </is>
       </c>
       <c r="C74" s="25" t="n">
-        <v>243.02</v>
+        <v>243.43</v>
       </c>
       <c r="D74" s="25" t="n">
-        <v>239.42</v>
+        <v>238.53</v>
       </c>
       <c r="E74" s="26" t="n">
-        <v>236.41</v>
+        <v>234.42</v>
       </c>
       <c r="F74" s="27" t="n">
-        <v>236.93</v>
+        <v>234</v>
       </c>
       <c r="G74" s="27" t="n">
-        <v>238.87</v>
+        <v>237.2</v>
       </c>
       <c r="H74" s="28" t="n">
-        <v>235.27</v>
+        <v>232.3</v>
       </c>
       <c r="I74" s="29" t="n">
-        <v>233.33</v>
+        <v>229.1</v>
       </c>
       <c r="J74" s="29" t="n">
-        <v>231.67</v>
+        <v>227.4</v>
       </c>
       <c r="K74" s="30" t="n">
-        <v>234.39</v>
+        <v>231.68</v>
       </c>
       <c r="L74" s="31" t="n">
-        <v>231.38</v>
+        <v>227.57</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>227.78</v>
+        <v>222.67</v>
       </c>
       <c r="N74" s="32" t="inlineStr">
         <is>
@@ -5234,16 +5234,16 @@
         </is>
       </c>
       <c r="O74" s="33" t="n">
-        <v>234.97</v>
+        <v>232.18</v>
       </c>
       <c r="P74" s="33" t="n">
-        <v>234.67</v>
+        <v>232.06</v>
       </c>
       <c r="Q74" s="34" t="n">
-        <v>235</v>
-      </c>
-      <c r="R74" s="36" t="n">
-        <v>0.9</v>
+        <v>230.8</v>
+      </c>
+      <c r="R74" s="35" t="n">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="75">
@@ -5258,37 +5258,37 @@
         </is>
       </c>
       <c r="C75" s="25" t="n">
-        <v>15.85</v>
+        <v>15.56</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>15.58</v>
+        <v>15.32</v>
       </c>
       <c r="E75" s="26" t="n">
-        <v>15.35</v>
+        <v>15.12</v>
       </c>
       <c r="F75" s="27" t="n">
-        <v>15.32</v>
+        <v>15.12</v>
       </c>
       <c r="G75" s="27" t="n">
-        <v>15.5</v>
+        <v>15.27</v>
       </c>
       <c r="H75" s="28" t="n">
-        <v>15.23</v>
+        <v>15.03</v>
       </c>
       <c r="I75" s="29" t="n">
-        <v>15.05</v>
+        <v>14.88</v>
       </c>
       <c r="J75" s="29" t="n">
-        <v>14.96</v>
+        <v>14.79</v>
       </c>
       <c r="K75" s="30" t="n">
-        <v>15.2</v>
+        <v>14.98</v>
       </c>
       <c r="L75" s="31" t="n">
-        <v>14.97</v>
+        <v>14.78</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>14.7</v>
+        <v>14.54</v>
       </c>
       <c r="N75" s="32" t="inlineStr">
         <is>
@@ -5296,16 +5296,16 @@
         </is>
       </c>
       <c r="O75" s="33" t="n">
-        <v>15.23</v>
+        <v>15.01</v>
       </c>
       <c r="P75" s="33" t="n">
-        <v>15.22</v>
+        <v>15</v>
       </c>
       <c r="Q75" s="34" t="n">
-        <v>15.14</v>
+        <v>14.98</v>
       </c>
       <c r="R75" s="35" t="n">
-        <v>-1.62</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="76">
@@ -5320,54 +5320,54 @@
         </is>
       </c>
       <c r="C76" s="25" t="n">
-        <v>36.25</v>
+        <v>37.55</v>
       </c>
       <c r="D76" s="25" t="n">
-        <v>35.85</v>
+        <v>36.73</v>
       </c>
       <c r="E76" s="26" t="n">
-        <v>35.51</v>
+        <v>36.04</v>
       </c>
       <c r="F76" s="27" t="n">
-        <v>35.57</v>
+        <v>36.07</v>
       </c>
       <c r="G76" s="27" t="n">
-        <v>35.79</v>
+        <v>36.55</v>
       </c>
       <c r="H76" s="28" t="n">
-        <v>35.39</v>
+        <v>35.73</v>
       </c>
       <c r="I76" s="29" t="n">
-        <v>35.17</v>
+        <v>35.25</v>
       </c>
       <c r="J76" s="29" t="n">
-        <v>34.99</v>
+        <v>34.91</v>
       </c>
       <c r="K76" s="30" t="n">
-        <v>35.29</v>
+        <v>35.58</v>
       </c>
       <c r="L76" s="31" t="n">
-        <v>34.95</v>
+        <v>34.89</v>
       </c>
       <c r="M76" s="31" t="n">
-        <v>34.55</v>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>34.07</v>
+      </c>
+      <c r="N76" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O76" s="33" t="n">
-        <v>35.35</v>
+        <v>35.69</v>
       </c>
       <c r="P76" s="33" t="n">
-        <v>35.32</v>
+        <v>35.64</v>
       </c>
       <c r="Q76" s="34" t="n">
-        <v>35.36</v>
+        <v>35.58</v>
       </c>
       <c r="R76" s="36" t="n">
-        <v>0.4</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="77">
@@ -5382,37 +5382,37 @@
         </is>
       </c>
       <c r="C77" s="25" t="n">
-        <v>27.51</v>
+        <v>27.7</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>27.33</v>
+        <v>27.34</v>
       </c>
       <c r="E77" s="26" t="n">
-        <v>27.18</v>
+        <v>27.04</v>
       </c>
       <c r="F77" s="27" t="n">
-        <v>27.28</v>
+        <v>27</v>
       </c>
       <c r="G77" s="27" t="n">
-        <v>27.34</v>
+        <v>27.24</v>
       </c>
       <c r="H77" s="28" t="n">
-        <v>27.16</v>
+        <v>26.88</v>
       </c>
       <c r="I77" s="29" t="n">
-        <v>27.1</v>
+        <v>26.64</v>
       </c>
       <c r="J77" s="29" t="n">
-        <v>26.98</v>
+        <v>26.52</v>
       </c>
       <c r="K77" s="30" t="n">
-        <v>27.08</v>
+        <v>26.84</v>
       </c>
       <c r="L77" s="31" t="n">
-        <v>26.93</v>
+        <v>26.54</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>26.75</v>
+        <v>26.18</v>
       </c>
       <c r="N77" s="32" t="inlineStr">
         <is>
@@ -5420,16 +5420,16 @@
         </is>
       </c>
       <c r="O77" s="33" t="n">
-        <v>27.13</v>
+        <v>26.87</v>
       </c>
       <c r="P77" s="33" t="n">
-        <v>27.09</v>
+        <v>26.87</v>
       </c>
       <c r="Q77" s="34" t="n">
-        <v>27.22</v>
-      </c>
-      <c r="R77" s="36" t="n">
-        <v>0.15</v>
+        <v>26.76</v>
+      </c>
+      <c r="R77" s="35" t="n">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="78">
@@ -5444,54 +5444,54 @@
         </is>
       </c>
       <c r="C78" s="25" t="n">
-        <v>43.96</v>
+        <v>44.48</v>
       </c>
       <c r="D78" s="25" t="n">
-        <v>43.18</v>
+        <v>43.38</v>
       </c>
       <c r="E78" s="26" t="n">
-        <v>42.53</v>
+        <v>42.46</v>
       </c>
       <c r="F78" s="27" t="n">
-        <v>42.93</v>
+        <v>42.4</v>
       </c>
       <c r="G78" s="27" t="n">
-        <v>43.21</v>
+        <v>43.1</v>
       </c>
       <c r="H78" s="28" t="n">
-        <v>42.43</v>
+        <v>42</v>
       </c>
       <c r="I78" s="29" t="n">
-        <v>42.15</v>
+        <v>41.3</v>
       </c>
       <c r="J78" s="29" t="n">
-        <v>41.65</v>
+        <v>40.9</v>
       </c>
       <c r="K78" s="30" t="n">
-        <v>42.09</v>
+        <v>41.84</v>
       </c>
       <c r="L78" s="31" t="n">
-        <v>41.44</v>
+        <v>40.92</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>40.66</v>
-      </c>
-      <c r="N78" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>39.82</v>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O78" s="33" t="n">
-        <v>42.29</v>
+        <v>41.96</v>
       </c>
       <c r="P78" s="33" t="n">
-        <v>42.15</v>
+        <v>41.93</v>
       </c>
       <c r="Q78" s="34" t="n">
-        <v>42.66</v>
-      </c>
-      <c r="R78" s="36" t="n">
-        <v>1.09</v>
+        <v>41.7</v>
+      </c>
+      <c r="R78" s="35" t="n">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="79">
@@ -5506,34 +5506,34 @@
         </is>
       </c>
       <c r="C79" s="25" t="n">
-        <v>5.61</v>
+        <v>5.56</v>
       </c>
       <c r="D79" s="25" t="n">
-        <v>5.55</v>
+        <v>5.51</v>
       </c>
       <c r="E79" s="26" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="F79" s="27" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="G79" s="27" t="n">
         <v>5.51</v>
       </c>
-      <c r="G79" s="27" t="n">
-        <v>5.54</v>
-      </c>
       <c r="H79" s="28" t="n">
-        <v>5.48</v>
+        <v>5.46</v>
       </c>
       <c r="I79" s="29" t="n">
-        <v>5.45</v>
+        <v>5.44</v>
       </c>
       <c r="J79" s="29" t="n">
-        <v>5.42</v>
+        <v>5.41</v>
       </c>
       <c r="K79" s="30" t="n">
-        <v>5.46</v>
+        <v>5.44</v>
       </c>
       <c r="L79" s="31" t="n">
-        <v>5.41</v>
+        <v>5.4</v>
       </c>
       <c r="M79" s="31" t="n">
         <v>5.35</v>
@@ -5544,13 +5544,13 @@
         </is>
       </c>
       <c r="O79" s="33" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="P79" s="33" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="Q79" s="34" t="n">
         <v>5.47</v>
-      </c>
-      <c r="P79" s="33" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="Q79" s="34" t="n">
-        <v>5.48</v>
       </c>
       <c r="R79" s="35" t="n">
         <v>-0.18</v>
@@ -5568,37 +5568,37 @@
         </is>
       </c>
       <c r="C80" s="25" t="n">
-        <v>20.81</v>
+        <v>21.34</v>
       </c>
       <c r="D80" s="25" t="n">
-        <v>19.97</v>
+        <v>20.3</v>
       </c>
       <c r="E80" s="26" t="n">
-        <v>19.27</v>
+        <v>19.43</v>
       </c>
       <c r="F80" s="27" t="n">
-        <v>19.38</v>
+        <v>20.01</v>
       </c>
       <c r="G80" s="27" t="n">
-        <v>19.83</v>
+        <v>20.35</v>
       </c>
       <c r="H80" s="28" t="n">
-        <v>18.99</v>
+        <v>19.31</v>
       </c>
       <c r="I80" s="29" t="n">
-        <v>18.54</v>
+        <v>18.97</v>
       </c>
       <c r="J80" s="29" t="n">
-        <v>18.15</v>
+        <v>18.27</v>
       </c>
       <c r="K80" s="30" t="n">
-        <v>18.79</v>
+        <v>18.85</v>
       </c>
       <c r="L80" s="31" t="n">
-        <v>18.09</v>
+        <v>17.98</v>
       </c>
       <c r="M80" s="31" t="n">
-        <v>17.25</v>
+        <v>16.94</v>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
@@ -5606,16 +5606,16 @@
         </is>
       </c>
       <c r="O80" s="33" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="P80" s="33" t="n">
         <v>18.93</v>
       </c>
-      <c r="P80" s="33" t="n">
-        <v>18.86</v>
-      </c>
       <c r="Q80" s="34" t="n">
-        <v>18.92</v>
+        <v>19.66</v>
       </c>
       <c r="R80" s="36" t="n">
-        <v>0.16</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="81">
@@ -5630,54 +5630,54 @@
         </is>
       </c>
       <c r="C81" s="25" t="n">
-        <v>85.29000000000001</v>
+        <v>83.59</v>
       </c>
       <c r="D81" s="25" t="n">
-        <v>83.69</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="E81" s="26" t="n">
-        <v>82.34999999999999</v>
+        <v>82.12</v>
       </c>
       <c r="F81" s="27" t="n">
-        <v>83.23</v>
+        <v>82.33</v>
       </c>
       <c r="G81" s="27" t="n">
-        <v>83.77</v>
+        <v>82.72</v>
       </c>
       <c r="H81" s="28" t="n">
-        <v>82.17</v>
+        <v>81.92</v>
       </c>
       <c r="I81" s="29" t="n">
-        <v>81.63</v>
+        <v>81.53</v>
       </c>
       <c r="J81" s="29" t="n">
-        <v>80.56999999999999</v>
+        <v>81.12</v>
       </c>
       <c r="K81" s="30" t="n">
-        <v>81.45</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="L81" s="31" t="n">
-        <v>80.11</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="M81" s="31" t="n">
-        <v>78.51000000000001</v>
-      </c>
-      <c r="N81" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>80.20999999999999</v>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O81" s="33" t="n">
-        <v>81.87</v>
+        <v>81.83</v>
       </c>
       <c r="P81" s="33" t="n">
-        <v>81.58</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="Q81" s="34" t="n">
-        <v>82.7</v>
+        <v>81.95</v>
       </c>
       <c r="R81" s="35" t="n">
-        <v>-0.3</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="82">
@@ -5695,51 +5695,51 @@
         <v>4.79</v>
       </c>
       <c r="D82" s="25" t="n">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="E82" s="26" t="n">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="F82" s="27" t="n">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="G82" s="27" t="n">
-        <v>4.73</v>
+        <v>4.72</v>
       </c>
       <c r="H82" s="28" t="n">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="I82" s="29" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="J82" s="29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K82" s="30" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="L82" s="31" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="M82" s="31" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O82" s="33" t="n">
         <v>4.65</v>
       </c>
-      <c r="J82" s="29" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="K82" s="30" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="L82" s="31" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="M82" s="31" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O82" s="33" t="n">
-        <v>4.68</v>
-      </c>
       <c r="P82" s="33" t="n">
-        <v>4.67</v>
+        <v>4.65</v>
       </c>
       <c r="Q82" s="34" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="R82" s="35" t="n">
-        <v>-0.43</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="83">
@@ -5754,54 +5754,54 @@
         </is>
       </c>
       <c r="C83" s="25" t="n">
-        <v>63.73</v>
+        <v>63.46</v>
       </c>
       <c r="D83" s="25" t="n">
-        <v>62.88</v>
+        <v>62.56</v>
       </c>
       <c r="E83" s="26" t="n">
-        <v>62.16</v>
+        <v>61.8</v>
       </c>
       <c r="F83" s="27" t="n">
-        <v>62.23</v>
+        <v>62.13</v>
       </c>
       <c r="G83" s="27" t="n">
-        <v>62.72</v>
+        <v>62.52</v>
       </c>
       <c r="H83" s="28" t="n">
-        <v>61.87</v>
+        <v>61.62</v>
       </c>
       <c r="I83" s="29" t="n">
-        <v>61.38</v>
+        <v>61.23</v>
       </c>
       <c r="J83" s="29" t="n">
-        <v>61.02</v>
+        <v>60.72</v>
       </c>
       <c r="K83" s="30" t="n">
-        <v>61.69</v>
+        <v>61.3</v>
       </c>
       <c r="L83" s="31" t="n">
-        <v>60.97</v>
+        <v>60.54</v>
       </c>
       <c r="M83" s="31" t="n">
-        <v>60.12</v>
-      </c>
-      <c r="N83" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>59.64</v>
+      </c>
+      <c r="N83" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O83" s="33" t="n">
-        <v>61.81</v>
+        <v>61.49</v>
       </c>
       <c r="P83" s="33" t="n">
-        <v>61.75</v>
+        <v>61.37</v>
       </c>
       <c r="Q83" s="34" t="n">
         <v>61.75</v>
       </c>
       <c r="R83" s="36" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5816,54 +5816,54 @@
         </is>
       </c>
       <c r="C84" s="25" t="n">
-        <v>39.34</v>
+        <v>39.25</v>
       </c>
       <c r="D84" s="25" t="n">
-        <v>39.02</v>
+        <v>38.91</v>
       </c>
       <c r="E84" s="26" t="n">
-        <v>38.75</v>
+        <v>38.63</v>
       </c>
       <c r="F84" s="27" t="n">
-        <v>38.85</v>
+        <v>38.59</v>
       </c>
       <c r="G84" s="27" t="n">
-        <v>38.99</v>
+        <v>38.81</v>
       </c>
       <c r="H84" s="28" t="n">
-        <v>38.67</v>
+        <v>38.47</v>
       </c>
       <c r="I84" s="29" t="n">
-        <v>38.53</v>
+        <v>38.25</v>
       </c>
       <c r="J84" s="29" t="n">
-        <v>38.35</v>
+        <v>38.13</v>
       </c>
       <c r="K84" s="30" t="n">
-        <v>38.57</v>
+        <v>38.43</v>
       </c>
       <c r="L84" s="31" t="n">
-        <v>38.3</v>
+        <v>38.15</v>
       </c>
       <c r="M84" s="31" t="n">
-        <v>37.98</v>
-      </c>
-      <c r="N84" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>37.81</v>
+      </c>
+      <c r="N84" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O84" s="33" t="n">
-        <v>38.63</v>
+        <v>38.47</v>
       </c>
       <c r="P84" s="33" t="n">
-        <v>38.6</v>
+        <v>38.46</v>
       </c>
       <c r="Q84" s="34" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="R84" s="36" t="n">
-        <v>0.73</v>
+        <v>38.36</v>
+      </c>
+      <c r="R84" s="35" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="85">
@@ -5878,37 +5878,37 @@
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>94.3</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>93.65000000000001</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="E85" s="26" t="n">
-        <v>93.11</v>
+        <v>92.59</v>
       </c>
       <c r="F85" s="27" t="n">
-        <v>93.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="G85" s="27" t="n">
-        <v>93.5</v>
+        <v>93</v>
       </c>
       <c r="H85" s="28" t="n">
-        <v>92.84999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="I85" s="29" t="n">
-        <v>92.45</v>
+        <v>92.3</v>
       </c>
       <c r="J85" s="29" t="n">
-        <v>92.2</v>
+        <v>92</v>
       </c>
       <c r="K85" s="30" t="n">
-        <v>92.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="L85" s="31" t="n">
-        <v>92.2</v>
+        <v>91.89</v>
       </c>
       <c r="M85" s="31" t="n">
-        <v>91.55</v>
+        <v>91.39</v>
       </c>
       <c r="N85" s="32" t="inlineStr">
         <is>
@@ -5916,16 +5916,16 @@
         </is>
       </c>
       <c r="O85" s="33" t="n">
-        <v>92.81999999999999</v>
+        <v>92.42</v>
       </c>
       <c r="P85" s="33" t="n">
-        <v>92.79000000000001</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="Q85" s="34" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="R85" s="36" t="n">
-        <v>0.27</v>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="R85" s="35" t="n">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="86">
@@ -5940,37 +5940,37 @@
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>18</v>
+        <v>17.18</v>
       </c>
       <c r="D86" s="25" t="n">
-        <v>17.53</v>
+        <v>16.93</v>
       </c>
       <c r="E86" s="26" t="n">
-        <v>17.14</v>
+        <v>16.73</v>
       </c>
       <c r="F86" s="27" t="n">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="G86" s="27" t="n">
-        <v>17.41</v>
+        <v>16.86</v>
       </c>
       <c r="H86" s="28" t="n">
-        <v>16.94</v>
+        <v>16.61</v>
       </c>
       <c r="I86" s="29" t="n">
-        <v>16.63</v>
+        <v>16.45</v>
       </c>
       <c r="J86" s="29" t="n">
-        <v>16.47</v>
+        <v>16.36</v>
       </c>
       <c r="K86" s="30" t="n">
-        <v>16.87</v>
+        <v>16.59</v>
       </c>
       <c r="L86" s="31" t="n">
-        <v>16.48</v>
+        <v>16.38</v>
       </c>
       <c r="M86" s="31" t="n">
-        <v>16.01</v>
+        <v>16.13</v>
       </c>
       <c r="N86" s="32" t="inlineStr">
         <is>
@@ -5978,16 +5978,16 @@
         </is>
       </c>
       <c r="O86" s="33" t="n">
-        <v>16.92</v>
+        <v>16.61</v>
       </c>
       <c r="P86" s="33" t="n">
-        <v>16.91</v>
+        <v>16.6</v>
       </c>
       <c r="Q86" s="34" t="n">
-        <v>16.8</v>
+        <v>16.53</v>
       </c>
       <c r="R86" s="35" t="n">
-        <v>-2.21</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="87">
@@ -6002,54 +6002,54 @@
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>125.85</v>
+        <v>124.44</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>122.85</v>
+        <v>122.44</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>120.34</v>
+        <v>120.76</v>
       </c>
       <c r="F87" s="27" t="n">
-        <v>122</v>
+        <v>120.87</v>
       </c>
       <c r="G87" s="27" t="n">
-        <v>123</v>
+        <v>122.03</v>
       </c>
       <c r="H87" s="28" t="n">
-        <v>120</v>
+        <v>120.03</v>
       </c>
       <c r="I87" s="29" t="n">
-        <v>119</v>
+        <v>118.87</v>
       </c>
       <c r="J87" s="29" t="n">
-        <v>117</v>
+        <v>118.03</v>
       </c>
       <c r="K87" s="30" t="n">
-        <v>118.66</v>
+        <v>119.64</v>
       </c>
       <c r="L87" s="31" t="n">
-        <v>116.15</v>
+        <v>117.96</v>
       </c>
       <c r="M87" s="31" t="n">
-        <v>113.15</v>
-      </c>
-      <c r="N87" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>115.96</v>
+      </c>
+      <c r="N87" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="33" t="n">
-        <v>119.45</v>
+        <v>119.91</v>
       </c>
       <c r="P87" s="33" t="n">
-        <v>118.89</v>
+        <v>119.8</v>
       </c>
       <c r="Q87" s="34" t="n">
-        <v>121</v>
-      </c>
-      <c r="R87" s="36" t="n">
-        <v>2.63</v>
+        <v>119.7</v>
+      </c>
+      <c r="R87" s="35" t="n">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="88">
@@ -6064,37 +6064,37 @@
         </is>
       </c>
       <c r="C88" s="25" t="n">
-        <v>64.40000000000001</v>
+        <v>63.86</v>
       </c>
       <c r="D88" s="25" t="n">
-        <v>63.35</v>
+        <v>62.71</v>
       </c>
       <c r="E88" s="26" t="n">
-        <v>62.47</v>
+        <v>61.75</v>
       </c>
       <c r="F88" s="27" t="n">
-        <v>62.58</v>
+        <v>61.65</v>
       </c>
       <c r="G88" s="27" t="n">
-        <v>63.17</v>
+        <v>62.4</v>
       </c>
       <c r="H88" s="28" t="n">
-        <v>62.12</v>
+        <v>61.25</v>
       </c>
       <c r="I88" s="29" t="n">
-        <v>61.53</v>
+        <v>60.5</v>
       </c>
       <c r="J88" s="29" t="n">
-        <v>61.07</v>
+        <v>60.1</v>
       </c>
       <c r="K88" s="30" t="n">
-        <v>61.88</v>
+        <v>61.1</v>
       </c>
       <c r="L88" s="31" t="n">
-        <v>61</v>
+        <v>60.14</v>
       </c>
       <c r="M88" s="31" t="n">
-        <v>59.95</v>
+        <v>58.99</v>
       </c>
       <c r="N88" s="32" t="inlineStr">
         <is>
@@ -6102,16 +6102,16 @@
         </is>
       </c>
       <c r="O88" s="33" t="n">
-        <v>62.04</v>
+        <v>61.22</v>
       </c>
       <c r="P88" s="33" t="n">
-        <v>61.96</v>
+        <v>61.19</v>
       </c>
       <c r="Q88" s="34" t="n">
-        <v>62</v>
+        <v>60.9</v>
       </c>
       <c r="R88" s="35" t="n">
-        <v>-0.64</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="89">
@@ -6126,54 +6126,54 @@
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="D89" s="25" t="n">
-        <v>10.05</v>
+        <v>9.91</v>
       </c>
       <c r="E89" s="26" t="n">
-        <v>9.93</v>
+        <v>9.83</v>
       </c>
       <c r="F89" s="27" t="n">
-        <v>9.94</v>
+        <v>9.85</v>
       </c>
       <c r="G89" s="27" t="n">
-        <v>10.02</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H89" s="28" t="n">
-        <v>9.869999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I89" s="29" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="J89" s="29" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="K89" s="30" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="L89" s="31" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M89" s="31" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="N89" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O89" s="33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P89" s="33" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="J89" s="29" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="K89" s="30" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="L89" s="31" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="M89" s="31" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="N89" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O89" s="33" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="P89" s="33" t="n">
-        <v>9.85</v>
-      </c>
       <c r="Q89" s="34" t="n">
-        <v>9.85</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R89" s="35" t="n">
-        <v>-1.1</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="90">
@@ -6188,54 +6188,54 @@
         </is>
       </c>
       <c r="C90" s="25" t="n">
-        <v>18.76</v>
+        <v>18.75</v>
       </c>
       <c r="D90" s="25" t="n">
-        <v>18.15</v>
+        <v>18.18</v>
       </c>
       <c r="E90" s="26" t="n">
-        <v>17.64</v>
+        <v>17.7</v>
       </c>
       <c r="F90" s="27" t="n">
-        <v>17.86</v>
+        <v>17.78</v>
       </c>
       <c r="G90" s="27" t="n">
-        <v>18.12</v>
+        <v>18.09</v>
       </c>
       <c r="H90" s="28" t="n">
-        <v>17.51</v>
+        <v>17.52</v>
       </c>
       <c r="I90" s="29" t="n">
-        <v>17.25</v>
+        <v>17.21</v>
       </c>
       <c r="J90" s="29" t="n">
-        <v>16.9</v>
+        <v>16.95</v>
       </c>
       <c r="K90" s="30" t="n">
-        <v>17.29</v>
+        <v>17.39</v>
       </c>
       <c r="L90" s="31" t="n">
-        <v>16.78</v>
+        <v>16.91</v>
       </c>
       <c r="M90" s="31" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="N90" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.34</v>
+      </c>
+      <c r="N90" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O90" s="33" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="P90" s="33" t="n">
         <v>17.43</v>
       </c>
-      <c r="P90" s="33" t="n">
-        <v>17.34</v>
-      </c>
       <c r="Q90" s="34" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="R90" s="36" t="n">
-        <v>1.38</v>
+        <v>17.47</v>
+      </c>
+      <c r="R90" s="35" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="91">
@@ -6250,54 +6250,54 @@
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>18.85</v>
+        <v>18.53</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>18.49</v>
+        <v>18.29</v>
       </c>
       <c r="E91" s="26" t="n">
-        <v>18.19</v>
+        <v>18.09</v>
       </c>
       <c r="F91" s="27" t="n">
-        <v>18.21</v>
+        <v>18.18</v>
       </c>
       <c r="G91" s="27" t="n">
-        <v>18.42</v>
+        <v>18.28</v>
       </c>
       <c r="H91" s="28" t="n">
-        <v>18.06</v>
+        <v>18.04</v>
       </c>
       <c r="I91" s="29" t="n">
-        <v>17.85</v>
+        <v>17.94</v>
       </c>
       <c r="J91" s="29" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="K91" s="30" t="n">
-        <v>17.99</v>
+        <v>17.95</v>
       </c>
       <c r="L91" s="31" t="n">
-        <v>17.69</v>
+        <v>17.75</v>
       </c>
       <c r="M91" s="31" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="N91" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>17.51</v>
+      </c>
+      <c r="N91" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O91" s="33" t="n">
-        <v>18.04</v>
+        <v>18.01</v>
       </c>
       <c r="P91" s="33" t="n">
-        <v>18.02</v>
+        <v>17.97</v>
       </c>
       <c r="Q91" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="R91" s="35" t="n">
-        <v>-1.85</v>
+        <v>18.08</v>
+      </c>
+      <c r="R91" s="36" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="92">
@@ -6312,54 +6312,54 @@
         </is>
       </c>
       <c r="C92" s="25" t="n">
-        <v>33.2</v>
+        <v>32.65</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>32.48</v>
+        <v>32.21</v>
       </c>
       <c r="E92" s="26" t="n">
-        <v>31.88</v>
+        <v>31.84</v>
       </c>
       <c r="F92" s="27" t="n">
-        <v>32.23</v>
+        <v>31.83</v>
       </c>
       <c r="G92" s="27" t="n">
-        <v>32.49</v>
+        <v>32.11</v>
       </c>
       <c r="H92" s="28" t="n">
-        <v>31.77</v>
+        <v>31.67</v>
       </c>
       <c r="I92" s="29" t="n">
-        <v>31.51</v>
+        <v>31.39</v>
       </c>
       <c r="J92" s="29" t="n">
-        <v>31.05</v>
+        <v>31.23</v>
       </c>
       <c r="K92" s="30" t="n">
-        <v>31.48</v>
+        <v>31.6</v>
       </c>
       <c r="L92" s="31" t="n">
-        <v>30.88</v>
+        <v>31.23</v>
       </c>
       <c r="M92" s="31" t="n">
-        <v>30.16</v>
-      </c>
-      <c r="N92" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>30.79</v>
+      </c>
+      <c r="N92" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O92" s="33" t="n">
         <v>31.65</v>
       </c>
       <c r="P92" s="33" t="n">
-        <v>31.53</v>
+        <v>31.63</v>
       </c>
       <c r="Q92" s="34" t="n">
-        <v>31.96</v>
-      </c>
-      <c r="R92" s="36" t="n">
-        <v>1.27</v>
+        <v>31.56</v>
+      </c>
+      <c r="R92" s="35" t="n">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="93">
@@ -6374,54 +6374,54 @@
         </is>
       </c>
       <c r="C93" s="25" t="n">
-        <v>22.21</v>
+        <v>21.67</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>21.78</v>
+        <v>21.42</v>
       </c>
       <c r="E93" s="26" t="n">
-        <v>21.42</v>
+        <v>21.22</v>
       </c>
       <c r="F93" s="27" t="n">
-        <v>21.48</v>
+        <v>21.22</v>
       </c>
       <c r="G93" s="27" t="n">
-        <v>21.71</v>
+        <v>21.37</v>
       </c>
       <c r="H93" s="28" t="n">
-        <v>21.28</v>
+        <v>21.12</v>
       </c>
       <c r="I93" s="29" t="n">
-        <v>21.05</v>
+        <v>20.97</v>
       </c>
       <c r="J93" s="29" t="n">
-        <v>20.85</v>
+        <v>20.87</v>
       </c>
       <c r="K93" s="30" t="n">
-        <v>21.17</v>
+        <v>21.08</v>
       </c>
       <c r="L93" s="31" t="n">
-        <v>20.81</v>
+        <v>20.87</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>20.38</v>
-      </c>
-      <c r="N93" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>20.62</v>
+      </c>
+      <c r="N93" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O93" s="33" t="n">
-        <v>21.24</v>
+        <v>21.11</v>
       </c>
       <c r="P93" s="33" t="n">
-        <v>21.21</v>
+        <v>21.09</v>
       </c>
       <c r="Q93" s="34" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="R93" s="36" t="n">
-        <v>0.71</v>
+        <v>21.07</v>
+      </c>
+      <c r="R93" s="35" t="n">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="94">
@@ -6436,54 +6436,54 @@
         </is>
       </c>
       <c r="C94" s="25" t="n">
-        <v>28.75</v>
+        <v>28.35</v>
       </c>
       <c r="D94" s="25" t="n">
-        <v>28.37</v>
+        <v>28.11</v>
       </c>
       <c r="E94" s="26" t="n">
-        <v>28.06</v>
+        <v>27.91</v>
       </c>
       <c r="F94" s="27" t="n">
-        <v>28.12</v>
+        <v>28.03</v>
       </c>
       <c r="G94" s="27" t="n">
-        <v>28.32</v>
+        <v>28.11</v>
       </c>
       <c r="H94" s="28" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="I94" s="29" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="J94" s="29" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="K94" s="30" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="L94" s="31" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="M94" s="31" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="N94" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O94" s="33" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="P94" s="33" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="Q94" s="34" t="n">
         <v>27.94</v>
       </c>
-      <c r="I94" s="29" t="n">
-        <v>27.74</v>
-      </c>
-      <c r="J94" s="29" t="n">
-        <v>27.56</v>
-      </c>
-      <c r="K94" s="30" t="n">
-        <v>27.84</v>
-      </c>
-      <c r="L94" s="31" t="n">
-        <v>27.53</v>
-      </c>
-      <c r="M94" s="31" t="n">
-        <v>27.15</v>
-      </c>
-      <c r="N94" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O94" s="33" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="P94" s="33" t="n">
-        <v>27.87</v>
-      </c>
-      <c r="Q94" s="34" t="n">
-        <v>27.92</v>
-      </c>
-      <c r="R94" s="35" t="n">
-        <v>-0.21</v>
+      <c r="R94" s="36" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6498,37 +6498,37 @@
         </is>
       </c>
       <c r="C95" s="25" t="n">
-        <v>174.36</v>
+        <v>179.04</v>
       </c>
       <c r="D95" s="25" t="n">
-        <v>170.86</v>
+        <v>174.44</v>
       </c>
       <c r="E95" s="26" t="n">
-        <v>167.93</v>
+        <v>170.59</v>
       </c>
       <c r="F95" s="27" t="n">
-        <v>168.6</v>
+        <v>172.2</v>
       </c>
       <c r="G95" s="27" t="n">
-        <v>170.4</v>
+        <v>174.2</v>
       </c>
       <c r="H95" s="28" t="n">
-        <v>166.9</v>
+        <v>169.6</v>
       </c>
       <c r="I95" s="29" t="n">
-        <v>165.1</v>
+        <v>167.6</v>
       </c>
       <c r="J95" s="29" t="n">
-        <v>163.4</v>
+        <v>165</v>
       </c>
       <c r="K95" s="30" t="n">
-        <v>165.97</v>
+        <v>168.01</v>
       </c>
       <c r="L95" s="31" t="n">
-        <v>163.04</v>
+        <v>164.16</v>
       </c>
       <c r="M95" s="31" t="n">
-        <v>159.54</v>
+        <v>159.56</v>
       </c>
       <c r="N95" s="20" t="inlineStr">
         <is>
@@ -6536,16 +6536,16 @@
         </is>
       </c>
       <c r="O95" s="33" t="n">
-        <v>166.57</v>
+        <v>168.99</v>
       </c>
       <c r="P95" s="33" t="n">
-        <v>166.24</v>
+        <v>168.37</v>
       </c>
       <c r="Q95" s="34" t="n">
-        <v>166.8</v>
+        <v>170.2</v>
       </c>
       <c r="R95" s="36" t="n">
-        <v>1.46</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="96">
@@ -6560,37 +6560,37 @@
         </is>
       </c>
       <c r="C96" s="25" t="n">
-        <v>15.25</v>
+        <v>16.72</v>
       </c>
       <c r="D96" s="25" t="n">
-        <v>14.82</v>
+        <v>15.53</v>
       </c>
       <c r="E96" s="26" t="n">
-        <v>14.46</v>
+        <v>14.53</v>
       </c>
       <c r="F96" s="27" t="n">
-        <v>14.47</v>
+        <v>14.77</v>
       </c>
       <c r="G96" s="27" t="n">
-        <v>14.73</v>
+        <v>15.37</v>
       </c>
       <c r="H96" s="28" t="n">
-        <v>14.3</v>
+        <v>14.18</v>
       </c>
       <c r="I96" s="29" t="n">
-        <v>14.04</v>
+        <v>13.58</v>
       </c>
       <c r="J96" s="29" t="n">
-        <v>13.87</v>
+        <v>12.99</v>
       </c>
       <c r="K96" s="30" t="n">
-        <v>14.21</v>
+        <v>13.86</v>
       </c>
       <c r="L96" s="31" t="n">
-        <v>13.85</v>
+        <v>12.86</v>
       </c>
       <c r="M96" s="31" t="n">
-        <v>13.42</v>
+        <v>11.67</v>
       </c>
       <c r="N96" s="32" t="inlineStr">
         <is>
@@ -6598,16 +6598,16 @@
         </is>
       </c>
       <c r="O96" s="33" t="n">
-        <v>14.27</v>
+        <v>14.07</v>
       </c>
       <c r="P96" s="33" t="n">
-        <v>14.25</v>
+        <v>13.95</v>
       </c>
       <c r="Q96" s="34" t="n">
-        <v>14.22</v>
+        <v>14.16</v>
       </c>
       <c r="R96" s="35" t="n">
-        <v>-1.46</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="97">
@@ -6622,37 +6622,37 @@
         </is>
       </c>
       <c r="C97" s="25" t="n">
-        <v>21.92</v>
+        <v>22.31</v>
       </c>
       <c r="D97" s="25" t="n">
-        <v>21.23</v>
+        <v>21.19</v>
       </c>
       <c r="E97" s="26" t="n">
-        <v>20.65</v>
+        <v>20.25</v>
       </c>
       <c r="F97" s="27" t="n">
-        <v>20.84</v>
+        <v>20.19</v>
       </c>
       <c r="G97" s="27" t="n">
-        <v>21.16</v>
+        <v>20.9</v>
       </c>
       <c r="H97" s="28" t="n">
-        <v>20.47</v>
+        <v>19.78</v>
       </c>
       <c r="I97" s="29" t="n">
-        <v>20.15</v>
+        <v>19.07</v>
       </c>
       <c r="J97" s="29" t="n">
-        <v>19.78</v>
+        <v>18.66</v>
       </c>
       <c r="K97" s="30" t="n">
-        <v>20.26</v>
+        <v>19.63</v>
       </c>
       <c r="L97" s="31" t="n">
-        <v>19.68</v>
+        <v>18.69</v>
       </c>
       <c r="M97" s="31" t="n">
-        <v>18.99</v>
+        <v>17.57</v>
       </c>
       <c r="N97" s="32" t="inlineStr">
         <is>
@@ -6660,16 +6660,16 @@
         </is>
       </c>
       <c r="O97" s="33" t="n">
-        <v>20.39</v>
+        <v>19.75</v>
       </c>
       <c r="P97" s="33" t="n">
-        <v>20.32</v>
+        <v>19.71</v>
       </c>
       <c r="Q97" s="34" t="n">
-        <v>20.51</v>
+        <v>19.47</v>
       </c>
       <c r="R97" s="35" t="n">
-        <v>-1.58</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="98">
@@ -6684,54 +6684,54 @@
         </is>
       </c>
       <c r="C98" s="25" t="n">
-        <v>16.5</v>
+        <v>16.87</v>
       </c>
       <c r="D98" s="25" t="n">
-        <v>16.35</v>
+        <v>16.61</v>
       </c>
       <c r="E98" s="26" t="n">
-        <v>16.23</v>
+        <v>16.39</v>
       </c>
       <c r="F98" s="27" t="n">
-        <v>16.23</v>
+        <v>16.46</v>
       </c>
       <c r="G98" s="27" t="n">
-        <v>16.32</v>
+        <v>16.59</v>
       </c>
       <c r="H98" s="28" t="n">
-        <v>16.17</v>
+        <v>16.33</v>
       </c>
       <c r="I98" s="29" t="n">
-        <v>16.08</v>
+        <v>16.2</v>
       </c>
       <c r="J98" s="29" t="n">
-        <v>16.02</v>
+        <v>16.07</v>
       </c>
       <c r="K98" s="30" t="n">
-        <v>16.14</v>
+        <v>16.25</v>
       </c>
       <c r="L98" s="31" t="n">
-        <v>16.02</v>
+        <v>16.03</v>
       </c>
       <c r="M98" s="31" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="N98" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>15.77</v>
+      </c>
+      <c r="N98" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O98" s="33" t="n">
-        <v>16.16</v>
+        <v>16.3</v>
       </c>
       <c r="P98" s="33" t="n">
-        <v>16.15</v>
+        <v>16.27</v>
       </c>
       <c r="Q98" s="34" t="n">
-        <v>16.14</v>
-      </c>
-      <c r="R98" s="35" t="n">
-        <v>-0.49</v>
+        <v>16.34</v>
+      </c>
+      <c r="R98" s="36" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="99">
@@ -6746,54 +6746,54 @@
         </is>
       </c>
       <c r="C99" s="25" t="n">
-        <v>10.56</v>
+        <v>10.21</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>10.22</v>
+        <v>10.07</v>
       </c>
       <c r="E99" s="26" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F99" s="27" t="n">
-        <v>10.08</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G99" s="27" t="n">
-        <v>10.21</v>
+        <v>10.04</v>
       </c>
       <c r="H99" s="28" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I99" s="29" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="J99" s="29" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="K99" s="30" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="I99" s="29" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="J99" s="29" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="K99" s="30" t="n">
-        <v>9.74</v>
-      </c>
       <c r="L99" s="31" t="n">
-        <v>9.460000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="M99" s="31" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="N99" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>9.609999999999999</v>
+      </c>
+      <c r="N99" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O99" s="33" t="n">
-        <v>9.82</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="P99" s="33" t="n">
-        <v>9.77</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="Q99" s="34" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="R99" s="36" t="n">
-        <v>1.74</v>
+        <v>9.869999999999999</v>
+      </c>
+      <c r="R99" s="35" t="n">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="100">
@@ -6808,37 +6808,37 @@
         </is>
       </c>
       <c r="C100" s="25" t="n">
-        <v>27.34</v>
+        <v>26.98</v>
       </c>
       <c r="D100" s="25" t="n">
-        <v>26.88</v>
+        <v>26.62</v>
       </c>
       <c r="E100" s="26" t="n">
-        <v>26.5</v>
+        <v>26.32</v>
       </c>
       <c r="F100" s="27" t="n">
-        <v>26.57</v>
+        <v>26.32</v>
       </c>
       <c r="G100" s="27" t="n">
-        <v>26.81</v>
+        <v>26.54</v>
       </c>
       <c r="H100" s="28" t="n">
-        <v>26.35</v>
+        <v>26.18</v>
       </c>
       <c r="I100" s="29" t="n">
-        <v>26.11</v>
+        <v>25.96</v>
       </c>
       <c r="J100" s="29" t="n">
-        <v>25.89</v>
+        <v>25.82</v>
       </c>
       <c r="K100" s="30" t="n">
-        <v>26.24</v>
+        <v>26.12</v>
       </c>
       <c r="L100" s="31" t="n">
-        <v>25.86</v>
+        <v>25.82</v>
       </c>
       <c r="M100" s="31" t="n">
-        <v>25.4</v>
+        <v>25.46</v>
       </c>
       <c r="N100" s="32" t="inlineStr">
         <is>
@@ -6846,16 +6846,16 @@
         </is>
       </c>
       <c r="O100" s="33" t="n">
-        <v>26.32</v>
+        <v>26.16</v>
       </c>
       <c r="P100" s="33" t="n">
-        <v>26.28</v>
+        <v>26.15</v>
       </c>
       <c r="Q100" s="34" t="n">
-        <v>26.32</v>
+        <v>26.1</v>
       </c>
       <c r="R100" s="35" t="n">
-        <v>-1.05</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="101">
@@ -6870,37 +6870,37 @@
         </is>
       </c>
       <c r="C101" s="25" t="n">
-        <v>17.8</v>
+        <v>17.86</v>
       </c>
       <c r="D101" s="25" t="n">
-        <v>17.56</v>
+        <v>17.51</v>
       </c>
       <c r="E101" s="26" t="n">
-        <v>17.36</v>
+        <v>17.21</v>
       </c>
       <c r="F101" s="27" t="n">
-        <v>17.44</v>
+        <v>17.17</v>
       </c>
       <c r="G101" s="27" t="n">
-        <v>17.55</v>
+        <v>17.41</v>
       </c>
       <c r="H101" s="28" t="n">
-        <v>17.31</v>
+        <v>17.06</v>
       </c>
       <c r="I101" s="29" t="n">
-        <v>17.2</v>
+        <v>16.82</v>
       </c>
       <c r="J101" s="29" t="n">
-        <v>17.07</v>
+        <v>16.71</v>
       </c>
       <c r="K101" s="30" t="n">
-        <v>17.22</v>
+        <v>17.02</v>
       </c>
       <c r="L101" s="31" t="n">
-        <v>17.02</v>
+        <v>16.72</v>
       </c>
       <c r="M101" s="31" t="n">
-        <v>16.78</v>
+        <v>16.37</v>
       </c>
       <c r="N101" s="32" t="inlineStr">
         <is>
@@ -6908,16 +6908,16 @@
         </is>
       </c>
       <c r="O101" s="33" t="n">
-        <v>17.27</v>
+        <v>17.05</v>
       </c>
       <c r="P101" s="33" t="n">
-        <v>17.24</v>
+        <v>17.04</v>
       </c>
       <c r="Q101" s="34" t="n">
-        <v>17.34</v>
+        <v>16.94</v>
       </c>
       <c r="R101" s="35" t="n">
-        <v>-0.74</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="102">
@@ -6932,37 +6932,37 @@
         </is>
       </c>
       <c r="C102" s="25" t="n">
-        <v>33.74</v>
+        <v>32.94</v>
       </c>
       <c r="D102" s="25" t="n">
-        <v>33.02</v>
+        <v>32.42</v>
       </c>
       <c r="E102" s="26" t="n">
-        <v>32.42</v>
+        <v>31.99</v>
       </c>
       <c r="F102" s="27" t="n">
-        <v>32.57</v>
+        <v>32.07</v>
       </c>
       <c r="G102" s="27" t="n">
-        <v>32.93</v>
+        <v>32.35</v>
       </c>
       <c r="H102" s="28" t="n">
-        <v>32.21</v>
+        <v>31.83</v>
       </c>
       <c r="I102" s="29" t="n">
-        <v>31.85</v>
+        <v>31.55</v>
       </c>
       <c r="J102" s="29" t="n">
-        <v>31.49</v>
+        <v>31.31</v>
       </c>
       <c r="K102" s="30" t="n">
-        <v>32.02</v>
+        <v>31.69</v>
       </c>
       <c r="L102" s="31" t="n">
-        <v>31.42</v>
+        <v>31.26</v>
       </c>
       <c r="M102" s="31" t="n">
-        <v>30.7</v>
+        <v>30.74</v>
       </c>
       <c r="N102" s="32" t="inlineStr">
         <is>
@@ -6970,16 +6970,16 @@
         </is>
       </c>
       <c r="O102" s="33" t="n">
-        <v>32.14</v>
+        <v>31.78</v>
       </c>
       <c r="P102" s="33" t="n">
-        <v>32.07</v>
+        <v>31.73</v>
       </c>
       <c r="Q102" s="34" t="n">
-        <v>32.2</v>
+        <v>31.8</v>
       </c>
       <c r="R102" s="35" t="n">
-        <v>-0.25</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="103">
@@ -6994,37 +6994,37 @@
         </is>
       </c>
       <c r="C103" s="25" t="n">
-        <v>16.62</v>
+        <v>15.9</v>
       </c>
       <c r="D103" s="25" t="n">
-        <v>16.23</v>
+        <v>15.75</v>
       </c>
       <c r="E103" s="26" t="n">
-        <v>15.9</v>
+        <v>15.63</v>
       </c>
       <c r="F103" s="27" t="n">
-        <v>15.86</v>
+        <v>15.66</v>
       </c>
       <c r="G103" s="27" t="n">
-        <v>16.12</v>
+        <v>15.74</v>
       </c>
       <c r="H103" s="28" t="n">
-        <v>15.73</v>
+        <v>15.59</v>
       </c>
       <c r="I103" s="29" t="n">
-        <v>15.47</v>
+        <v>15.51</v>
       </c>
       <c r="J103" s="29" t="n">
-        <v>15.34</v>
+        <v>15.44</v>
       </c>
       <c r="K103" s="30" t="n">
-        <v>15.69</v>
+        <v>15.54</v>
       </c>
       <c r="L103" s="31" t="n">
-        <v>15.36</v>
+        <v>15.42</v>
       </c>
       <c r="M103" s="31" t="n">
-        <v>14.97</v>
+        <v>15.27</v>
       </c>
       <c r="N103" s="32" t="inlineStr">
         <is>
@@ -7032,16 +7032,16 @@
         </is>
       </c>
       <c r="O103" s="33" t="n">
-        <v>15.72</v>
+        <v>15.57</v>
       </c>
       <c r="P103" s="33" t="n">
-        <v>15.72</v>
+        <v>15.55</v>
       </c>
       <c r="Q103" s="34" t="n">
-        <v>15.6</v>
+        <v>15.59</v>
       </c>
       <c r="R103" s="35" t="n">
-        <v>-1.52</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="104">
@@ -7056,37 +7056,37 @@
         </is>
       </c>
       <c r="C104" s="25" t="n">
-        <v>72.98999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>72.04000000000001</v>
+        <v>71.33</v>
       </c>
       <c r="E104" s="26" t="n">
-        <v>71.23999999999999</v>
+        <v>70.61</v>
       </c>
       <c r="F104" s="27" t="n">
-        <v>71.23</v>
+        <v>70.55</v>
       </c>
       <c r="G104" s="27" t="n">
-        <v>71.81999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H104" s="28" t="n">
-        <v>70.87</v>
+        <v>70.25</v>
       </c>
       <c r="I104" s="29" t="n">
-        <v>70.28</v>
+        <v>69.7</v>
       </c>
       <c r="J104" s="29" t="n">
-        <v>69.92</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K104" s="30" t="n">
-        <v>70.70999999999999</v>
+        <v>70.14</v>
       </c>
       <c r="L104" s="31" t="n">
-        <v>69.91</v>
+        <v>69.42</v>
       </c>
       <c r="M104" s="31" t="n">
-        <v>68.95999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="N104" s="32" t="inlineStr">
         <is>
@@ -7094,16 +7094,16 @@
         </is>
       </c>
       <c r="O104" s="33" t="n">
-        <v>70.81999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="P104" s="33" t="n">
-        <v>70.78</v>
+        <v>70.2</v>
       </c>
       <c r="Q104" s="34" t="n">
-        <v>70.65000000000001</v>
+        <v>70</v>
       </c>
       <c r="R104" s="35" t="n">
-        <v>-0.91</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="105">
@@ -7118,37 +7118,37 @@
         </is>
       </c>
       <c r="C105" s="25" t="n">
-        <v>15.8</v>
+        <v>16.08</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>15.57</v>
+        <v>15.66</v>
       </c>
       <c r="E105" s="26" t="n">
-        <v>15.38</v>
+        <v>15.31</v>
       </c>
       <c r="F105" s="27" t="n">
-        <v>15.37</v>
+        <v>15.41</v>
       </c>
       <c r="G105" s="27" t="n">
-        <v>15.51</v>
+        <v>15.61</v>
       </c>
       <c r="H105" s="28" t="n">
-        <v>15.28</v>
+        <v>15.19</v>
       </c>
       <c r="I105" s="29" t="n">
-        <v>15.14</v>
+        <v>14.99</v>
       </c>
       <c r="J105" s="29" t="n">
-        <v>15.05</v>
+        <v>14.77</v>
       </c>
       <c r="K105" s="30" t="n">
-        <v>15.25</v>
+        <v>15.07</v>
       </c>
       <c r="L105" s="31" t="n">
-        <v>15.06</v>
+        <v>14.72</v>
       </c>
       <c r="M105" s="31" t="n">
-        <v>14.83</v>
+        <v>14.3</v>
       </c>
       <c r="N105" s="32" t="inlineStr">
         <is>
@@ -7156,16 +7156,16 @@
         </is>
       </c>
       <c r="O105" s="33" t="n">
-        <v>15.28</v>
+        <v>15.15</v>
       </c>
       <c r="P105" s="33" t="n">
-        <v>15.27</v>
+        <v>15.11</v>
       </c>
       <c r="Q105" s="34" t="n">
-        <v>15.22</v>
+        <v>15.2</v>
       </c>
       <c r="R105" s="35" t="n">
-        <v>-0.52</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="106">
@@ -7180,54 +7180,54 @@
         </is>
       </c>
       <c r="C106" s="25" t="n">
-        <v>17.87</v>
+        <v>17.73</v>
       </c>
       <c r="D106" s="25" t="n">
-        <v>17.33</v>
+        <v>17.25</v>
       </c>
       <c r="E106" s="26" t="n">
-        <v>16.88</v>
+        <v>16.84</v>
       </c>
       <c r="F106" s="27" t="n">
-        <v>17.08</v>
+        <v>16.93</v>
       </c>
       <c r="G106" s="27" t="n">
-        <v>17.31</v>
+        <v>17.18</v>
       </c>
       <c r="H106" s="28" t="n">
-        <v>16.77</v>
+        <v>16.7</v>
       </c>
       <c r="I106" s="29" t="n">
-        <v>16.54</v>
+        <v>16.45</v>
       </c>
       <c r="J106" s="29" t="n">
-        <v>16.23</v>
+        <v>16.22</v>
       </c>
       <c r="K106" s="30" t="n">
         <v>16.58</v>
       </c>
       <c r="L106" s="31" t="n">
-        <v>16.13</v>
+        <v>16.17</v>
       </c>
       <c r="M106" s="31" t="n">
-        <v>15.59</v>
-      </c>
-      <c r="N106" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>15.69</v>
+      </c>
+      <c r="N106" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O106" s="33" t="n">
-        <v>16.7</v>
+        <v>16.66</v>
       </c>
       <c r="P106" s="33" t="n">
-        <v>16.62</v>
+        <v>16.61</v>
       </c>
       <c r="Q106" s="34" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="R106" s="36" t="n">
-        <v>0.54</v>
+        <v>16.68</v>
+      </c>
+      <c r="R106" s="35" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="107">
@@ -7242,54 +7242,54 @@
         </is>
       </c>
       <c r="C107" s="25" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="D107" s="25" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="E107" s="26" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="F107" s="27" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="G107" s="27" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="H107" s="28" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="I107" s="29" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="J107" s="29" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="K107" s="30" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="L107" s="31" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M107" s="31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N107" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O107" s="33" t="n">
         <v>2.42</v>
       </c>
-      <c r="M107" s="31" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="N107" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O107" s="33" t="n">
-        <v>2.48</v>
-      </c>
       <c r="P107" s="33" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="Q107" s="34" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="R107" s="35" t="n">
-        <v>-0.4</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="108">
@@ -7304,54 +7304,54 @@
         </is>
       </c>
       <c r="C108" s="25" t="n">
-        <v>40.89</v>
+        <v>40.37</v>
       </c>
       <c r="D108" s="25" t="n">
-        <v>40.45</v>
+        <v>40.13</v>
       </c>
       <c r="E108" s="26" t="n">
-        <v>40.08</v>
+        <v>39.93</v>
       </c>
       <c r="F108" s="27" t="n">
-        <v>40.19</v>
+        <v>39.98</v>
       </c>
       <c r="G108" s="27" t="n">
-        <v>40.41</v>
+        <v>40.1</v>
       </c>
       <c r="H108" s="28" t="n">
-        <v>39.97</v>
+        <v>39.86</v>
       </c>
       <c r="I108" s="29" t="n">
-        <v>39.75</v>
+        <v>39.74</v>
       </c>
       <c r="J108" s="29" t="n">
-        <v>39.53</v>
+        <v>39.62</v>
       </c>
       <c r="K108" s="30" t="n">
+        <v>39.79</v>
+      </c>
+      <c r="L108" s="31" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="M108" s="31" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="N108" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O108" s="33" t="n">
         <v>39.84</v>
       </c>
-      <c r="L108" s="31" t="n">
-        <v>39.47</v>
-      </c>
-      <c r="M108" s="31" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="N108" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O108" s="33" t="n">
-        <v>39.92</v>
-      </c>
       <c r="P108" s="33" t="n">
-        <v>39.87</v>
+        <v>39.81</v>
       </c>
       <c r="Q108" s="34" t="n">
-        <v>39.98</v>
-      </c>
-      <c r="R108" s="36" t="n">
-        <v>0.55</v>
+        <v>39.86</v>
+      </c>
+      <c r="R108" s="35" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="109">
@@ -7366,37 +7366,37 @@
         </is>
       </c>
       <c r="C109" s="25" t="n">
-        <v>8.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="D109" s="25" t="n">
-        <v>8.33</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E109" s="26" t="n">
-        <v>8.18</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="F109" s="27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="G109" s="27" t="n">
-        <v>8.289999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H109" s="28" t="n">
-        <v>8.119999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I109" s="29" t="n">
-        <v>8.029999999999999</v>
+        <v>8.01</v>
       </c>
       <c r="J109" s="29" t="n">
-        <v>7.95</v>
+        <v>7.92</v>
       </c>
       <c r="K109" s="30" t="n">
-        <v>8.09</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L109" s="31" t="n">
-        <v>7.94</v>
+        <v>7.89</v>
       </c>
       <c r="M109" s="31" t="n">
-        <v>7.77</v>
+        <v>7.71</v>
       </c>
       <c r="N109" s="32" t="inlineStr">
         <is>
@@ -7404,16 +7404,16 @@
         </is>
       </c>
       <c r="O109" s="33" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="P109" s="33" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="Q109" s="34" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="P109" s="33" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Q109" s="34" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="R109" s="35" t="n">
-        <v>-0.61</v>
+      <c r="R109" s="36" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="110">
@@ -7428,37 +7428,37 @@
         </is>
       </c>
       <c r="C110" s="25" t="n">
-        <v>45.46</v>
+        <v>45.06</v>
       </c>
       <c r="D110" s="25" t="n">
-        <v>44.98</v>
+        <v>44.6</v>
       </c>
       <c r="E110" s="26" t="n">
-        <v>44.57</v>
+        <v>44.22</v>
       </c>
       <c r="F110" s="27" t="n">
-        <v>44.61</v>
+        <v>44.17</v>
       </c>
       <c r="G110" s="27" t="n">
-        <v>44.89</v>
+        <v>44.47</v>
       </c>
       <c r="H110" s="28" t="n">
-        <v>44.41</v>
+        <v>44.01</v>
       </c>
       <c r="I110" s="29" t="n">
-        <v>44.13</v>
+        <v>43.71</v>
       </c>
       <c r="J110" s="29" t="n">
-        <v>43.93</v>
+        <v>43.55</v>
       </c>
       <c r="K110" s="30" t="n">
-        <v>44.31</v>
+        <v>43.96</v>
       </c>
       <c r="L110" s="31" t="n">
-        <v>43.9</v>
+        <v>43.58</v>
       </c>
       <c r="M110" s="31" t="n">
-        <v>43.42</v>
+        <v>43.12</v>
       </c>
       <c r="N110" s="32" t="inlineStr">
         <is>
@@ -7466,16 +7466,16 @@
         </is>
       </c>
       <c r="O110" s="33" t="n">
-        <v>44.37</v>
+        <v>44.01</v>
       </c>
       <c r="P110" s="33" t="n">
-        <v>44.34</v>
+        <v>44</v>
       </c>
       <c r="Q110" s="34" t="n">
-        <v>44.34</v>
+        <v>43.86</v>
       </c>
       <c r="R110" s="35" t="n">
-        <v>-0.85</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="111">
@@ -7490,37 +7490,37 @@
         </is>
       </c>
       <c r="C111" s="25" t="n">
-        <v>68.28</v>
+        <v>69.61</v>
       </c>
       <c r="D111" s="25" t="n">
-        <v>67.43000000000001</v>
+        <v>67.81</v>
       </c>
       <c r="E111" s="26" t="n">
-        <v>66.70999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="F111" s="27" t="n">
-        <v>66.78</v>
+        <v>66.27</v>
       </c>
       <c r="G111" s="27" t="n">
-        <v>67.27</v>
+        <v>67.38</v>
       </c>
       <c r="H111" s="28" t="n">
-        <v>66.42</v>
+        <v>65.58</v>
       </c>
       <c r="I111" s="29" t="n">
-        <v>65.93000000000001</v>
+        <v>64.47</v>
       </c>
       <c r="J111" s="29" t="n">
-        <v>65.56999999999999</v>
+        <v>63.78</v>
       </c>
       <c r="K111" s="30" t="n">
-        <v>66.23999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="L111" s="31" t="n">
-        <v>65.52</v>
+        <v>63.79</v>
       </c>
       <c r="M111" s="31" t="n">
-        <v>64.67</v>
+        <v>61.99</v>
       </c>
       <c r="N111" s="32" t="inlineStr">
         <is>
@@ -7528,16 +7528,16 @@
         </is>
       </c>
       <c r="O111" s="33" t="n">
-        <v>66.36</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="P111" s="33" t="n">
-        <v>66.3</v>
+        <v>65.44</v>
       </c>
       <c r="Q111" s="34" t="n">
-        <v>66.3</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="R111" s="35" t="n">
-        <v>-0.9</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="112">
@@ -7552,37 +7552,37 @@
         </is>
       </c>
       <c r="C112" s="25" t="n">
-        <v>10.47</v>
+        <v>10.44</v>
       </c>
       <c r="D112" s="25" t="n">
-        <v>10.41</v>
+        <v>10.36</v>
       </c>
       <c r="E112" s="26" t="n">
-        <v>10.36</v>
+        <v>10.29</v>
       </c>
       <c r="F112" s="27" t="n">
-        <v>10.36</v>
+        <v>10.28</v>
       </c>
       <c r="G112" s="27" t="n">
-        <v>10.39</v>
+        <v>10.34</v>
       </c>
       <c r="H112" s="28" t="n">
-        <v>10.33</v>
+        <v>10.26</v>
       </c>
       <c r="I112" s="29" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="J112" s="29" t="n">
-        <v>10.27</v>
+        <v>10.18</v>
       </c>
       <c r="K112" s="30" t="n">
-        <v>10.32</v>
+        <v>10.25</v>
       </c>
       <c r="L112" s="31" t="n">
-        <v>10.27</v>
+        <v>10.18</v>
       </c>
       <c r="M112" s="31" t="n">
-        <v>10.21</v>
+        <v>10.1</v>
       </c>
       <c r="N112" s="32" t="inlineStr">
         <is>
@@ -7590,16 +7590,16 @@
         </is>
       </c>
       <c r="O112" s="33" t="n">
-        <v>10.33</v>
+        <v>10.26</v>
       </c>
       <c r="P112" s="33" t="n">
-        <v>10.33</v>
+        <v>10.25</v>
       </c>
       <c r="Q112" s="34" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="R112" s="36" t="n">
-        <v>0.1</v>
+        <v>10.23</v>
+      </c>
+      <c r="R112" s="35" t="n">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="113">
@@ -7614,37 +7614,37 @@
         </is>
       </c>
       <c r="C113" s="25" t="n">
-        <v>346.36</v>
+        <v>343.45</v>
       </c>
       <c r="D113" s="25" t="n">
-        <v>326.36</v>
+        <v>325.25</v>
       </c>
       <c r="E113" s="26" t="n">
-        <v>309.6</v>
+        <v>310</v>
       </c>
       <c r="F113" s="27" t="n">
-        <v>320.67</v>
+        <v>315.8</v>
       </c>
       <c r="G113" s="27" t="n">
-        <v>327.33</v>
+        <v>324</v>
       </c>
       <c r="H113" s="28" t="n">
-        <v>307.33</v>
+        <v>305.8</v>
       </c>
       <c r="I113" s="29" t="n">
-        <v>300.67</v>
+        <v>297.6</v>
       </c>
       <c r="J113" s="29" t="n">
-        <v>287.33</v>
+        <v>287.6</v>
       </c>
       <c r="K113" s="30" t="n">
-        <v>298.4</v>
+        <v>299.8</v>
       </c>
       <c r="L113" s="31" t="n">
-        <v>281.64</v>
+        <v>284.55</v>
       </c>
       <c r="M113" s="31" t="n">
-        <v>261.64</v>
+        <v>266.35</v>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
@@ -7652,16 +7652,16 @@
         </is>
       </c>
       <c r="O113" s="33" t="n">
-        <v>303.65</v>
+        <v>303.51</v>
       </c>
       <c r="P113" s="33" t="n">
-        <v>299.96</v>
+        <v>301.22</v>
       </c>
       <c r="Q113" s="34" t="n">
-        <v>314</v>
-      </c>
-      <c r="R113" s="36" t="n">
-        <v>7.17</v>
+        <v>307.6</v>
+      </c>
+      <c r="R113" s="35" t="n">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="114">
@@ -7676,37 +7676,37 @@
         </is>
       </c>
       <c r="C114" s="25" t="n">
-        <v>231.04</v>
+        <v>232.49</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>222.24</v>
+        <v>225.39</v>
       </c>
       <c r="E114" s="26" t="n">
-        <v>214.86</v>
+        <v>219.44</v>
       </c>
       <c r="F114" s="27" t="n">
-        <v>219.2</v>
+        <v>220.7</v>
       </c>
       <c r="G114" s="27" t="n">
-        <v>222.4</v>
+        <v>224.4</v>
       </c>
       <c r="H114" s="28" t="n">
+        <v>217.3</v>
+      </c>
+      <c r="I114" s="29" t="n">
         <v>213.6</v>
       </c>
-      <c r="I114" s="29" t="n">
-        <v>210.4</v>
-      </c>
       <c r="J114" s="29" t="n">
-        <v>204.8</v>
+        <v>210.2</v>
       </c>
       <c r="K114" s="30" t="n">
-        <v>209.94</v>
+        <v>215.46</v>
       </c>
       <c r="L114" s="31" t="n">
-        <v>202.56</v>
+        <v>209.51</v>
       </c>
       <c r="M114" s="31" t="n">
-        <v>193.76</v>
+        <v>202.41</v>
       </c>
       <c r="N114" s="20" t="inlineStr">
         <is>
@@ -7714,16 +7714,16 @@
         </is>
       </c>
       <c r="O114" s="33" t="n">
-        <v>212.11</v>
+        <v>216.66</v>
       </c>
       <c r="P114" s="33" t="n">
-        <v>210.62</v>
+        <v>216.02</v>
       </c>
       <c r="Q114" s="34" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R114" s="36" t="n">
-        <v>5.88</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="115">
@@ -7738,37 +7738,37 @@
         </is>
       </c>
       <c r="C115" s="25" t="n">
-        <v>669.05</v>
+        <v>635.99</v>
       </c>
       <c r="D115" s="25" t="n">
-        <v>649.55</v>
+        <v>625.49</v>
       </c>
       <c r="E115" s="26" t="n">
-        <v>633.21</v>
+        <v>616.6900000000001</v>
       </c>
       <c r="F115" s="27" t="n">
-        <v>632.67</v>
+        <v>615.5</v>
       </c>
       <c r="G115" s="27" t="n">
-        <v>644.83</v>
+        <v>622.5</v>
       </c>
       <c r="H115" s="28" t="n">
-        <v>625.33</v>
+        <v>612</v>
       </c>
       <c r="I115" s="29" t="n">
-        <v>613.17</v>
+        <v>605</v>
       </c>
       <c r="J115" s="29" t="n">
-        <v>605.83</v>
+        <v>601.5</v>
       </c>
       <c r="K115" s="30" t="n">
-        <v>622.29</v>
+        <v>610.8099999999999</v>
       </c>
       <c r="L115" s="31" t="n">
-        <v>605.95</v>
+        <v>602.01</v>
       </c>
       <c r="M115" s="31" t="n">
-        <v>586.45</v>
+        <v>591.51</v>
       </c>
       <c r="N115" s="32" t="inlineStr">
         <is>
@@ -7776,16 +7776,16 @@
         </is>
       </c>
       <c r="O115" s="33" t="n">
-        <v>624.5700000000001</v>
+        <v>611.8099999999999</v>
       </c>
       <c r="P115" s="33" t="n">
-        <v>623.8099999999999</v>
+        <v>611.63</v>
       </c>
       <c r="Q115" s="34" t="n">
-        <v>620.5</v>
+        <v>608.5</v>
       </c>
       <c r="R115" s="35" t="n">
-        <v>-2.51</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="116">
@@ -7800,54 +7800,54 @@
         </is>
       </c>
       <c r="C116" s="25" t="n">
-        <v>7.58</v>
+        <v>7.12</v>
       </c>
       <c r="D116" s="25" t="n">
-        <v>7.26</v>
+        <v>6.97</v>
       </c>
       <c r="E116" s="26" t="n">
-        <v>6.99</v>
+        <v>6.85</v>
       </c>
       <c r="F116" s="27" t="n">
-        <v>7.03</v>
+        <v>6.84</v>
       </c>
       <c r="G116" s="27" t="n">
-        <v>7.21</v>
+        <v>6.94</v>
       </c>
       <c r="H116" s="28" t="n">
-        <v>6.89</v>
+        <v>6.79</v>
       </c>
       <c r="I116" s="29" t="n">
-        <v>6.71</v>
+        <v>6.69</v>
       </c>
       <c r="J116" s="29" t="n">
-        <v>6.57</v>
+        <v>6.64</v>
       </c>
       <c r="K116" s="30" t="n">
-        <v>6.81</v>
+        <v>6.76</v>
       </c>
       <c r="L116" s="31" t="n">
-        <v>6.54</v>
+        <v>6.64</v>
       </c>
       <c r="M116" s="31" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="N116" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>6.49</v>
+      </c>
+      <c r="N116" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O116" s="33" t="n">
-        <v>6.86</v>
+        <v>6.78</v>
       </c>
       <c r="P116" s="33" t="n">
-        <v>6.84</v>
+        <v>6.77</v>
       </c>
       <c r="Q116" s="34" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="R116" s="36" t="n">
-        <v>1.03</v>
+        <v>6.75</v>
+      </c>
+      <c r="R116" s="35" t="n">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="117">
@@ -7862,54 +7862,54 @@
         </is>
       </c>
       <c r="C117" s="25" t="n">
-        <v>144.64</v>
+        <v>144.66</v>
       </c>
       <c r="D117" s="25" t="n">
-        <v>141.34</v>
+        <v>140.36</v>
       </c>
       <c r="E117" s="26" t="n">
-        <v>138.57</v>
+        <v>136.75</v>
       </c>
       <c r="F117" s="27" t="n">
-        <v>139.4</v>
+        <v>136.67</v>
       </c>
       <c r="G117" s="27" t="n">
-        <v>141</v>
+        <v>139.33</v>
       </c>
       <c r="H117" s="28" t="n">
-        <v>137.7</v>
+        <v>135.03</v>
       </c>
       <c r="I117" s="29" t="n">
-        <v>136.1</v>
+        <v>132.37</v>
       </c>
       <c r="J117" s="29" t="n">
-        <v>134.4</v>
+        <v>130.73</v>
       </c>
       <c r="K117" s="30" t="n">
-        <v>136.73</v>
+        <v>134.35</v>
       </c>
       <c r="L117" s="31" t="n">
-        <v>133.96</v>
+        <v>130.74</v>
       </c>
       <c r="M117" s="31" t="n">
-        <v>130.66</v>
-      </c>
-      <c r="N117" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>126.44</v>
+      </c>
+      <c r="N117" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O117" s="33" t="n">
-        <v>137.34</v>
+        <v>134.86</v>
       </c>
       <c r="P117" s="33" t="n">
-        <v>136.98</v>
+        <v>134.68</v>
       </c>
       <c r="Q117" s="34" t="n">
-        <v>137.8</v>
-      </c>
-      <c r="R117" s="36" t="n">
-        <v>0.95</v>
+        <v>134</v>
+      </c>
+      <c r="R117" s="35" t="n">
+        <v>-2.76</v>
       </c>
     </row>
     <row r="118">
@@ -7924,54 +7924,54 @@
         </is>
       </c>
       <c r="C118" s="25" t="n">
-        <v>10.64</v>
+        <v>10.75</v>
       </c>
       <c r="D118" s="25" t="n">
-        <v>10.46</v>
+        <v>10.47</v>
       </c>
       <c r="E118" s="26" t="n">
-        <v>10.31</v>
+        <v>10.24</v>
       </c>
       <c r="F118" s="27" t="n">
-        <v>10.3</v>
+        <v>10.25</v>
       </c>
       <c r="G118" s="27" t="n">
-        <v>10.42</v>
+        <v>10.41</v>
       </c>
       <c r="H118" s="28" t="n">
-        <v>10.24</v>
+        <v>10.13</v>
       </c>
       <c r="I118" s="29" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="J118" s="29" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="K118" s="30" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="L118" s="31" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="M118" s="31" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="N118" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O118" s="33" t="n">
         <v>10.12</v>
       </c>
-      <c r="J118" s="29" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="K118" s="30" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="L118" s="31" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="M118" s="31" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="N118" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O118" s="33" t="n">
-        <v>10.23</v>
-      </c>
       <c r="P118" s="33" t="n">
-        <v>10.22</v>
+        <v>10.1</v>
       </c>
       <c r="Q118" s="34" t="n">
-        <v>10.19</v>
+        <v>10.08</v>
       </c>
       <c r="R118" s="35" t="n">
-        <v>-0.59</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="119">
@@ -7986,54 +7986,54 @@
         </is>
       </c>
       <c r="C119" s="25" t="n">
-        <v>17.49</v>
+        <v>17.47</v>
       </c>
       <c r="D119" s="25" t="n">
-        <v>17.25</v>
+        <v>17.14</v>
       </c>
       <c r="E119" s="26" t="n">
-        <v>17.05</v>
+        <v>16.87</v>
       </c>
       <c r="F119" s="27" t="n">
-        <v>17.05</v>
+        <v>16.88</v>
       </c>
       <c r="G119" s="27" t="n">
-        <v>17.19</v>
+        <v>17.08</v>
       </c>
       <c r="H119" s="28" t="n">
-        <v>16.95</v>
+        <v>16.75</v>
       </c>
       <c r="I119" s="29" t="n">
-        <v>16.81</v>
+        <v>16.55</v>
       </c>
       <c r="J119" s="29" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="K119" s="30" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="L119" s="31" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="M119" s="31" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="N119" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O119" s="33" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="P119" s="33" t="n">
         <v>16.71</v>
       </c>
-      <c r="K119" s="30" t="n">
-        <v>16.91</v>
-      </c>
-      <c r="L119" s="31" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="M119" s="31" t="n">
-        <v>16.47</v>
-      </c>
-      <c r="N119" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O119" s="33" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="P119" s="33" t="n">
-        <v>16.93</v>
-      </c>
       <c r="Q119" s="34" t="n">
-        <v>16.9</v>
+        <v>16.69</v>
       </c>
       <c r="R119" s="35" t="n">
-        <v>-0.53</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="120">
@@ -8048,54 +8048,54 @@
         </is>
       </c>
       <c r="C120" s="25" t="n">
-        <v>11.8</v>
+        <v>11.58</v>
       </c>
       <c r="D120" s="25" t="n">
-        <v>11.54</v>
+        <v>11.4</v>
       </c>
       <c r="E120" s="26" t="n">
-        <v>11.32</v>
+        <v>11.25</v>
       </c>
       <c r="F120" s="27" t="n">
-        <v>11.44</v>
+        <v>11.33</v>
       </c>
       <c r="G120" s="27" t="n">
-        <v>11.54</v>
+        <v>11.4</v>
       </c>
       <c r="H120" s="28" t="n">
-        <v>11.28</v>
+        <v>11.22</v>
       </c>
       <c r="I120" s="29" t="n">
-        <v>11.18</v>
+        <v>11.15</v>
       </c>
       <c r="J120" s="29" t="n">
-        <v>11.02</v>
+        <v>11.04</v>
       </c>
       <c r="K120" s="30" t="n">
-        <v>11.18</v>
+        <v>11.15</v>
       </c>
       <c r="L120" s="31" t="n">
-        <v>10.96</v>
+        <v>11</v>
       </c>
       <c r="M120" s="31" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="N120" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>10.82</v>
+      </c>
+      <c r="N120" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O120" s="33" t="n">
-        <v>11.24</v>
+        <v>11.19</v>
       </c>
       <c r="P120" s="33" t="n">
-        <v>11.2</v>
+        <v>11.16</v>
       </c>
       <c r="Q120" s="34" t="n">
-        <v>11.34</v>
-      </c>
-      <c r="R120" s="36" t="n">
-        <v>1.16</v>
+        <v>11.26</v>
+      </c>
+      <c r="R120" s="35" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="121">
@@ -8110,37 +8110,37 @@
         </is>
       </c>
       <c r="C121" s="25" t="n">
-        <v>12.73</v>
+        <v>12.89</v>
       </c>
       <c r="D121" s="25" t="n">
-        <v>12.55</v>
+        <v>12.53</v>
       </c>
       <c r="E121" s="26" t="n">
-        <v>12.4</v>
+        <v>12.23</v>
       </c>
       <c r="F121" s="27" t="n">
-        <v>12.43</v>
+        <v>12.22</v>
       </c>
       <c r="G121" s="27" t="n">
-        <v>12.52</v>
+        <v>12.45</v>
       </c>
       <c r="H121" s="28" t="n">
-        <v>12.34</v>
+        <v>12.09</v>
       </c>
       <c r="I121" s="29" t="n">
-        <v>12.25</v>
+        <v>11.86</v>
       </c>
       <c r="J121" s="29" t="n">
-        <v>12.16</v>
+        <v>11.73</v>
       </c>
       <c r="K121" s="30" t="n">
-        <v>12.3</v>
+        <v>12.03</v>
       </c>
       <c r="L121" s="31" t="n">
-        <v>12.15</v>
+        <v>11.73</v>
       </c>
       <c r="M121" s="31" t="n">
-        <v>11.97</v>
+        <v>11.37</v>
       </c>
       <c r="N121" s="32" t="inlineStr">
         <is>
@@ -8148,16 +8148,16 @@
         </is>
       </c>
       <c r="O121" s="33" t="n">
-        <v>12.33</v>
+        <v>12.07</v>
       </c>
       <c r="P121" s="33" t="n">
-        <v>12.31</v>
+        <v>12.06</v>
       </c>
       <c r="Q121" s="34" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="R121" s="36" t="n">
-        <v>0.65</v>
+        <v>12</v>
+      </c>
+      <c r="R121" s="35" t="n">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="122">
@@ -8172,54 +8172,54 @@
         </is>
       </c>
       <c r="C122" s="25" t="n">
-        <v>8.859999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="D122" s="25" t="n">
-        <v>8.640000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="E122" s="26" t="n">
-        <v>8.449999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="F122" s="27" t="n">
-        <v>8.449999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G122" s="27" t="n">
-        <v>8.59</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="H122" s="28" t="n">
-        <v>8.369999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="I122" s="29" t="n">
-        <v>8.23</v>
+        <v>8.19</v>
       </c>
       <c r="J122" s="29" t="n">
-        <v>8.15</v>
+        <v>8.06</v>
       </c>
       <c r="K122" s="30" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="L122" s="31" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="M122" s="31" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="N122" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O122" s="33" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="P122" s="33" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="Q122" s="34" t="n">
         <v>8.33</v>
       </c>
-      <c r="L122" s="31" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="M122" s="31" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="N122" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O122" s="33" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="P122" s="33" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="Q122" s="34" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="R122" s="35" t="n">
-        <v>-0.48</v>
+      <c r="R122" s="36" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="123">
@@ -8234,54 +8234,54 @@
         </is>
       </c>
       <c r="C123" s="25" t="n">
-        <v>8.76</v>
+        <v>8.43</v>
       </c>
       <c r="D123" s="25" t="n">
-        <v>8.48</v>
+        <v>8.26</v>
       </c>
       <c r="E123" s="26" t="n">
-        <v>8.25</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F123" s="27" t="n">
-        <v>8.279999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G123" s="27" t="n">
-        <v>8.43</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H123" s="28" t="n">
-        <v>8.15</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I123" s="29" t="n">
-        <v>8</v>
+        <v>7.95</v>
       </c>
       <c r="J123" s="29" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="K123" s="30" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="L123" s="31" t="n">
         <v>7.87</v>
       </c>
-      <c r="K123" s="30" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="L123" s="31" t="n">
-        <v>7.86</v>
-      </c>
       <c r="M123" s="31" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="N123" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>7.7</v>
+      </c>
+      <c r="N123" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O123" s="33" t="n">
-        <v>8.130000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="P123" s="33" t="n">
-        <v>8.109999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q123" s="34" t="n">
-        <v>8.119999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="R123" s="35" t="n">
-        <v>-0.25</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="124">
@@ -8296,37 +8296,37 @@
         </is>
       </c>
       <c r="C124" s="25" t="n">
-        <v>27.33</v>
+        <v>26.75</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>26.73</v>
+        <v>26.21</v>
       </c>
       <c r="E124" s="26" t="n">
-        <v>26.23</v>
+        <v>25.76</v>
       </c>
       <c r="F124" s="27" t="n">
-        <v>26.19</v>
+        <v>25.87</v>
       </c>
       <c r="G124" s="27" t="n">
-        <v>26.57</v>
+        <v>26.15</v>
       </c>
       <c r="H124" s="28" t="n">
-        <v>25.97</v>
+        <v>25.61</v>
       </c>
       <c r="I124" s="29" t="n">
-        <v>25.59</v>
+        <v>25.33</v>
       </c>
       <c r="J124" s="29" t="n">
-        <v>25.37</v>
+        <v>25.07</v>
       </c>
       <c r="K124" s="30" t="n">
-        <v>25.89</v>
+        <v>25.46</v>
       </c>
       <c r="L124" s="31" t="n">
-        <v>25.39</v>
+        <v>25.01</v>
       </c>
       <c r="M124" s="31" t="n">
-        <v>24.79</v>
+        <v>24.47</v>
       </c>
       <c r="N124" s="32" t="inlineStr">
         <is>
@@ -8334,16 +8334,16 @@
         </is>
       </c>
       <c r="O124" s="33" t="n">
-        <v>25.96</v>
+        <v>25.55</v>
       </c>
       <c r="P124" s="33" t="n">
-        <v>25.94</v>
+        <v>25.5</v>
       </c>
       <c r="Q124" s="34" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="R124" s="35" t="n">
-        <v>-1.6</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="125">
@@ -8358,37 +8358,37 @@
         </is>
       </c>
       <c r="C125" s="25" t="n">
-        <v>164.34</v>
+        <v>162.31</v>
       </c>
       <c r="D125" s="25" t="n">
-        <v>161.04</v>
+        <v>159.71</v>
       </c>
       <c r="E125" s="26" t="n">
-        <v>158.27</v>
+        <v>157.53</v>
       </c>
       <c r="F125" s="27" t="n">
-        <v>158.9</v>
+        <v>157.23</v>
       </c>
       <c r="G125" s="27" t="n">
-        <v>160.6</v>
+        <v>158.97</v>
       </c>
       <c r="H125" s="28" t="n">
-        <v>157.3</v>
+        <v>156.37</v>
       </c>
       <c r="I125" s="29" t="n">
-        <v>155.6</v>
+        <v>154.63</v>
       </c>
       <c r="J125" s="29" t="n">
-        <v>154</v>
+        <v>153.77</v>
       </c>
       <c r="K125" s="30" t="n">
-        <v>156.43</v>
+        <v>156.07</v>
       </c>
       <c r="L125" s="31" t="n">
-        <v>153.66</v>
+        <v>153.89</v>
       </c>
       <c r="M125" s="31" t="n">
-        <v>150.36</v>
+        <v>151.29</v>
       </c>
       <c r="N125" s="32" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         </is>
       </c>
       <c r="O125" s="33" t="n">
-        <v>156.99</v>
+        <v>156.32</v>
       </c>
       <c r="P125" s="33" t="n">
-        <v>156.68</v>
+        <v>156.27</v>
       </c>
       <c r="Q125" s="34" t="n">
-        <v>157.2</v>
-      </c>
-      <c r="R125" s="36" t="n">
-        <v>0.96</v>
+        <v>155.5</v>
+      </c>
+      <c r="R125" s="35" t="n">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="126">
@@ -8420,54 +8420,54 @@
         </is>
       </c>
       <c r="C126" s="25" t="n">
-        <v>61</v>
+        <v>59.27</v>
       </c>
       <c r="D126" s="25" t="n">
-        <v>58.65</v>
+        <v>57.62</v>
       </c>
       <c r="E126" s="26" t="n">
-        <v>56.68</v>
+        <v>56.24</v>
       </c>
       <c r="F126" s="27" t="n">
-        <v>57.62</v>
+        <v>56.28</v>
       </c>
       <c r="G126" s="27" t="n">
-        <v>58.58</v>
+        <v>57.27</v>
       </c>
       <c r="H126" s="28" t="n">
-        <v>56.23</v>
+        <v>55.62</v>
       </c>
       <c r="I126" s="29" t="n">
-        <v>55.27</v>
+        <v>54.63</v>
       </c>
       <c r="J126" s="29" t="n">
-        <v>53.88</v>
+        <v>53.97</v>
       </c>
       <c r="K126" s="30" t="n">
-        <v>55.37</v>
+        <v>55.31</v>
       </c>
       <c r="L126" s="31" t="n">
-        <v>53.4</v>
+        <v>53.93</v>
       </c>
       <c r="M126" s="31" t="n">
-        <v>51.05</v>
-      </c>
-      <c r="N126" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>52.28</v>
+      </c>
+      <c r="N126" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O126" s="33" t="n">
-        <v>55.89</v>
+        <v>55.53</v>
       </c>
       <c r="P126" s="33" t="n">
-        <v>55.55</v>
+        <v>55.44</v>
       </c>
       <c r="Q126" s="34" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="R126" s="36" t="n">
-        <v>2.35</v>
+        <v>55.3</v>
+      </c>
+      <c r="R126" s="35" t="n">
+        <v>-2.38</v>
       </c>
     </row>
     <row r="127">
@@ -8482,37 +8482,37 @@
         </is>
       </c>
       <c r="C127" s="25" t="n">
-        <v>15.81</v>
+        <v>15.64</v>
       </c>
       <c r="D127" s="25" t="n">
-        <v>15.53</v>
+        <v>15.37</v>
       </c>
       <c r="E127" s="26" t="n">
-        <v>15.3</v>
+        <v>15.14</v>
       </c>
       <c r="F127" s="27" t="n">
-        <v>15.35</v>
+        <v>15.22</v>
       </c>
       <c r="G127" s="27" t="n">
-        <v>15.49</v>
+        <v>15.34</v>
       </c>
       <c r="H127" s="28" t="n">
-        <v>15.21</v>
+        <v>15.07</v>
       </c>
       <c r="I127" s="29" t="n">
-        <v>15.07</v>
+        <v>14.95</v>
       </c>
       <c r="J127" s="29" t="n">
-        <v>14.93</v>
+        <v>14.8</v>
       </c>
       <c r="K127" s="30" t="n">
-        <v>15.14</v>
+        <v>14.99</v>
       </c>
       <c r="L127" s="31" t="n">
-        <v>14.91</v>
+        <v>14.76</v>
       </c>
       <c r="M127" s="31" t="n">
-        <v>14.63</v>
+        <v>14.49</v>
       </c>
       <c r="N127" s="32" t="inlineStr">
         <is>
@@ -8520,16 +8520,16 @@
         </is>
       </c>
       <c r="O127" s="33" t="n">
-        <v>15.19</v>
+        <v>15.04</v>
       </c>
       <c r="P127" s="33" t="n">
-        <v>15.16</v>
+        <v>15.01</v>
       </c>
       <c r="Q127" s="34" t="n">
-        <v>15.2</v>
+        <v>15.09</v>
       </c>
       <c r="R127" s="35" t="n">
-        <v>-0.65</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="128">
@@ -8544,54 +8544,54 @@
         </is>
       </c>
       <c r="C128" s="25" t="n">
-        <v>15.75</v>
+        <v>15.29</v>
       </c>
       <c r="D128" s="25" t="n">
-        <v>15.44</v>
+        <v>15.08</v>
       </c>
       <c r="E128" s="26" t="n">
-        <v>15.18</v>
+        <v>14.9</v>
       </c>
       <c r="F128" s="27" t="n">
-        <v>15.15</v>
+        <v>14.91</v>
       </c>
       <c r="G128" s="27" t="n">
-        <v>15.35</v>
+        <v>15.03</v>
       </c>
       <c r="H128" s="28" t="n">
-        <v>15.04</v>
+        <v>14.82</v>
       </c>
       <c r="I128" s="29" t="n">
-        <v>14.84</v>
+        <v>14.7</v>
       </c>
       <c r="J128" s="29" t="n">
-        <v>14.73</v>
+        <v>14.61</v>
       </c>
       <c r="K128" s="30" t="n">
-        <v>15.01</v>
+        <v>14.79</v>
       </c>
       <c r="L128" s="31" t="n">
-        <v>14.75</v>
+        <v>14.61</v>
       </c>
       <c r="M128" s="31" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="N128" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>14.4</v>
+      </c>
+      <c r="N128" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O128" s="33" t="n">
-        <v>15.04</v>
+        <v>14.81</v>
       </c>
       <c r="P128" s="33" t="n">
-        <v>15.03</v>
+        <v>14.8</v>
       </c>
       <c r="Q128" s="34" t="n">
-        <v>14.94</v>
+        <v>14.78</v>
       </c>
       <c r="R128" s="35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="129">
@@ -8606,54 +8606,54 @@
         </is>
       </c>
       <c r="C129" s="25" t="n">
-        <v>8.470000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="D129" s="25" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="E129" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="F129" s="27" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="G129" s="27" t="n">
         <v>8.18</v>
       </c>
-      <c r="E129" s="26" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="F129" s="27" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="G129" s="27" t="n">
-        <v>8.15</v>
-      </c>
       <c r="H129" s="28" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="I129" s="29" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="J129" s="29" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="K129" s="30" t="n">
         <v>7.86</v>
       </c>
-      <c r="I129" s="29" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="J129" s="29" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="K129" s="30" t="n">
-        <v>7.77</v>
-      </c>
       <c r="L129" s="31" t="n">
-        <v>7.53</v>
+        <v>7.64</v>
       </c>
       <c r="M129" s="31" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="N129" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>7.38</v>
+      </c>
+      <c r="N129" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O129" s="33" t="n">
-        <v>7.83</v>
+        <v>7.9</v>
       </c>
       <c r="P129" s="33" t="n">
-        <v>7.8</v>
+        <v>7.88</v>
       </c>
       <c r="Q129" s="34" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="R129" s="35" t="n">
-        <v>-0.25</v>
+        <v>7.9</v>
+      </c>
+      <c r="R129" s="36" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="130">
@@ -8668,37 +8668,37 @@
         </is>
       </c>
       <c r="C130" s="25" t="n">
-        <v>12.13</v>
+        <v>12.01</v>
       </c>
       <c r="D130" s="25" t="n">
-        <v>11.76</v>
+        <v>11.62</v>
       </c>
       <c r="E130" s="26" t="n">
-        <v>11.45</v>
+        <v>11.29</v>
       </c>
       <c r="F130" s="27" t="n">
-        <v>11.46</v>
+        <v>11.3</v>
       </c>
       <c r="G130" s="27" t="n">
-        <v>11.68</v>
+        <v>11.53</v>
       </c>
       <c r="H130" s="28" t="n">
-        <v>11.31</v>
+        <v>11.14</v>
       </c>
       <c r="I130" s="29" t="n">
-        <v>11.09</v>
+        <v>10.91</v>
       </c>
       <c r="J130" s="29" t="n">
-        <v>10.94</v>
+        <v>10.75</v>
       </c>
       <c r="K130" s="30" t="n">
-        <v>11.24</v>
+        <v>11.08</v>
       </c>
       <c r="L130" s="31" t="n">
-        <v>10.93</v>
+        <v>10.75</v>
       </c>
       <c r="M130" s="31" t="n">
-        <v>10.56</v>
+        <v>10.36</v>
       </c>
       <c r="N130" s="32" t="inlineStr">
         <is>
@@ -8706,16 +8706,16 @@
         </is>
       </c>
       <c r="O130" s="33" t="n">
-        <v>11.29</v>
+        <v>11.12</v>
       </c>
       <c r="P130" s="33" t="n">
-        <v>11.27</v>
+        <v>11.11</v>
       </c>
       <c r="Q130" s="34" t="n">
-        <v>11.24</v>
+        <v>11.06</v>
       </c>
       <c r="R130" s="35" t="n">
-        <v>-1.14</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="131">
@@ -8730,37 +8730,37 @@
         </is>
       </c>
       <c r="C131" s="25" t="n">
-        <v>145.3</v>
+        <v>138.96</v>
       </c>
       <c r="D131" s="25" t="n">
-        <v>141.1</v>
+        <v>136.76</v>
       </c>
       <c r="E131" s="26" t="n">
-        <v>137.58</v>
+        <v>134.92</v>
       </c>
       <c r="F131" s="27" t="n">
-        <v>137.3</v>
+        <v>134.67</v>
       </c>
       <c r="G131" s="27" t="n">
-        <v>140</v>
+        <v>136.13</v>
       </c>
       <c r="H131" s="28" t="n">
-        <v>135.8</v>
+        <v>133.93</v>
       </c>
       <c r="I131" s="29" t="n">
-        <v>133.1</v>
+        <v>132.47</v>
       </c>
       <c r="J131" s="29" t="n">
-        <v>131.6</v>
+        <v>131.73</v>
       </c>
       <c r="K131" s="30" t="n">
-        <v>135.22</v>
+        <v>133.68</v>
       </c>
       <c r="L131" s="31" t="n">
-        <v>131.7</v>
+        <v>131.84</v>
       </c>
       <c r="M131" s="31" t="n">
-        <v>127.5</v>
+        <v>129.64</v>
       </c>
       <c r="N131" s="32" t="inlineStr">
         <is>
@@ -8768,16 +8768,16 @@
         </is>
       </c>
       <c r="O131" s="33" t="n">
-        <v>135.68</v>
+        <v>133.89</v>
       </c>
       <c r="P131" s="33" t="n">
-        <v>135.55</v>
+        <v>133.86</v>
       </c>
       <c r="Q131" s="34" t="n">
-        <v>134.6</v>
+        <v>133.2</v>
       </c>
       <c r="R131" s="35" t="n">
-        <v>-1.54</v>
+        <v>-1.04</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -686,7 +686,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-03</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-06</t>
         </is>
       </c>
     </row>
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>11189.17</v>
+        <v>11128.32</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>11118.91</v>
+        <v>11096.91</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>11060.03</v>
+        <v>11070.59</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>11070.52</v>
+        <v>11082.07</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>11108.14</v>
+        <v>11095.49</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>11037.88</v>
+        <v>11064.08</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>11000.26</v>
+        <v>11050.66</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>10967.62</v>
+        <v>11032.67</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>11020.69</v>
+        <v>11053</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>10961.81</v>
+        <v>11026.68</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>10891.55</v>
+        <v>10995.27</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>11032.02</v>
+        <v>11059.77</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>11026.17</v>
+        <v>11055.45</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>11032.91</v>
+        <v>11068.65</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
@@ -856,37 +856,37 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>21.1</v>
+        <v>21.05</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.87</v>
+        <v>20.91</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>20.68</v>
+        <v>20.79</v>
       </c>
       <c r="F4" s="27" t="n">
-        <v>20.79</v>
+        <v>20.81</v>
       </c>
       <c r="G4" s="27" t="n">
         <v>20.88</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>20.65</v>
+        <v>20.74</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>20.56</v>
+        <v>20.67</v>
       </c>
       <c r="J4" s="29" t="n">
-        <v>20.42</v>
+        <v>20.6</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>20.55</v>
+        <v>20.71</v>
       </c>
       <c r="L4" s="31" t="n">
-        <v>20.36</v>
+        <v>20.59</v>
       </c>
       <c r="M4" s="31" t="n">
-        <v>20.13</v>
+        <v>20.45</v>
       </c>
       <c r="N4" s="20" t="inlineStr">
         <is>
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="O4" s="32" t="n">
-        <v>20.61</v>
+        <v>20.73</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>20.57</v>
+        <v>20.72</v>
       </c>
       <c r="Q4" s="33" t="n">
-        <v>20.71</v>
+        <v>20.73</v>
       </c>
       <c r="R4" s="34" t="n">
-        <v>1.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -918,54 +918,54 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>12.39</v>
+        <v>12.51</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>12.27</v>
+        <v>12.36</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>12.17</v>
+        <v>12.24</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>12.21</v>
+        <v>12.31</v>
       </c>
       <c r="G5" s="27" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="L5" s="31" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="M5" s="31" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O5" s="32" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="P5" s="32" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="Q5" s="33" t="n">
         <v>12.26</v>
       </c>
-      <c r="H5" s="28" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="J5" s="29" t="n">
-        <v>12.02</v>
-      </c>
-      <c r="K5" s="30" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="L5" s="31" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="M5" s="31" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="N5" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>12.13</v>
-      </c>
-      <c r="P5" s="32" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="Q5" s="33" t="n">
-        <v>12.15</v>
-      </c>
       <c r="R5" s="34" t="n">
-        <v>0.33</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="6">
@@ -980,54 +980,54 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>15.48</v>
+        <v>15.39</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>15.17</v>
+        <v>15.13</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>14.91</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>15.02</v>
+        <v>14.9</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>15.15</v>
+        <v>15.06</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>14.84</v>
+        <v>14.8</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>14.71</v>
+        <v>14.64</v>
       </c>
       <c r="J6" s="29" t="n">
-        <v>14.53</v>
+        <v>14.54</v>
       </c>
       <c r="K6" s="30" t="n">
-        <v>14.74</v>
+        <v>14.77</v>
       </c>
       <c r="L6" s="31" t="n">
-        <v>14.48</v>
+        <v>14.55</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="N6" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>14.29</v>
+      </c>
+      <c r="N6" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O6" s="32" t="n">
         <v>14.8</v>
       </c>
       <c r="P6" s="32" t="n">
-        <v>14.76</v>
+        <v>14.79</v>
       </c>
       <c r="Q6" s="33" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="R6" s="34" t="n">
-        <v>1.92</v>
+        <v>14.73</v>
+      </c>
+      <c r="R6" s="36" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="7">
@@ -1045,51 +1045,51 @@
         <v>22.44</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>22.1</v>
+        <v>22.18</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>21.82</v>
+        <v>21.96</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>21.99</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>22.11</v>
+        <v>22.14</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>21.77</v>
+        <v>21.88</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>21.65</v>
+        <v>21.73</v>
       </c>
       <c r="J7" s="29" t="n">
-        <v>21.43</v>
+        <v>21.62</v>
       </c>
       <c r="K7" s="30" t="n">
-        <v>21.62</v>
+        <v>21.82</v>
       </c>
       <c r="L7" s="31" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M7" s="31" t="n">
         <v>21.34</v>
       </c>
-      <c r="M7" s="31" t="n">
-        <v>21</v>
-      </c>
       <c r="N7" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O7" s="32" t="n">
-        <v>21.71</v>
+        <v>21.86</v>
       </c>
       <c r="P7" s="32" t="n">
-        <v>21.65</v>
+        <v>21.84</v>
       </c>
       <c r="Q7" s="33" t="n">
-        <v>21.87</v>
-      </c>
-      <c r="R7" s="34" t="n">
-        <v>0.83</v>
+        <v>21.85</v>
+      </c>
+      <c r="R7" s="36" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="8">
@@ -1104,37 +1104,37 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>34.93</v>
+        <v>34.57</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>34.59</v>
+        <v>34.43</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>34.31</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>34.37</v>
+        <v>34.39</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>34.55</v>
+        <v>34.43</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>34.21</v>
+        <v>34.29</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>34.03</v>
+        <v>34.25</v>
       </c>
       <c r="J8" s="29" t="n">
-        <v>33.87</v>
+        <v>34.15</v>
       </c>
       <c r="K8" s="30" t="n">
+        <v>34.23</v>
+      </c>
+      <c r="L8" s="31" t="n">
         <v>34.11</v>
       </c>
-      <c r="L8" s="31" t="n">
-        <v>33.83</v>
-      </c>
       <c r="M8" s="31" t="n">
-        <v>33.49</v>
+        <v>33.97</v>
       </c>
       <c r="N8" s="20" t="inlineStr">
         <is>
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="O8" s="32" t="n">
-        <v>34.17</v>
+        <v>34.27</v>
       </c>
       <c r="P8" s="32" t="n">
-        <v>34.14</v>
+        <v>34.24</v>
       </c>
       <c r="Q8" s="33" t="n">
-        <v>34.2</v>
+        <v>34.34</v>
       </c>
       <c r="R8" s="34" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="9">
@@ -1166,54 +1166,54 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>23.62</v>
+        <v>23.47</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>23.23</v>
+        <v>23.17</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>22.9</v>
+        <v>22.91</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>23.06</v>
+        <v>22.91</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>23.22</v>
+        <v>23.1</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>22.83</v>
+        <v>22.8</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>22.67</v>
+        <v>22.61</v>
       </c>
       <c r="J9" s="29" t="n">
-        <v>22.44</v>
+        <v>22.5</v>
       </c>
       <c r="K9" s="30" t="n">
-        <v>22.69</v>
+        <v>22.75</v>
       </c>
       <c r="L9" s="31" t="n">
-        <v>22.36</v>
+        <v>22.49</v>
       </c>
       <c r="M9" s="31" t="n">
-        <v>21.97</v>
-      </c>
-      <c r="N9" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>22.19</v>
+      </c>
+      <c r="N9" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O9" s="32" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="P9" s="32" t="n">
         <v>22.77</v>
       </c>
-      <c r="P9" s="32" t="n">
-        <v>22.72</v>
-      </c>
       <c r="Q9" s="33" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R9" s="34" t="n">
-        <v>1.37</v>
+        <v>22.73</v>
+      </c>
+      <c r="R9" s="36" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="10">
@@ -1228,54 +1228,54 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>133.87</v>
+        <v>137.42</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>131.97</v>
+        <v>134.32</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>130.38</v>
+        <v>131.72</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>130.3</v>
+        <v>133.17</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>131.5</v>
+        <v>134.33</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>129.6</v>
+        <v>131.23</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>128.4</v>
+        <v>130.07</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>127.7</v>
+        <v>128.13</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>129.32</v>
+        <v>129.98</v>
       </c>
       <c r="L10" s="31" t="n">
-        <v>127.73</v>
+        <v>127.38</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>125.83</v>
-      </c>
-      <c r="N10" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>124.28</v>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O10" s="32" t="n">
-        <v>129.53</v>
+        <v>130.73</v>
       </c>
       <c r="P10" s="32" t="n">
-        <v>129.47</v>
+        <v>130.22</v>
       </c>
       <c r="Q10" s="33" t="n">
-        <v>129.1</v>
+        <v>132</v>
       </c>
       <c r="R10" s="34" t="n">
-        <v>0.08</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="11">
@@ -1290,54 +1290,54 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>67.95</v>
+        <v>68</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>67.3</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>66.76000000000001</v>
+        <v>66.81</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>66.75</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>67.15000000000001</v>
+        <v>67.33</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>66.5</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>66.09999999999999</v>
+        <v>66.42</v>
       </c>
       <c r="J11" s="29" t="n">
-        <v>65.84999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>66.39</v>
+        <v>66.44</v>
       </c>
       <c r="L11" s="31" t="n">
-        <v>65.84999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M11" s="31" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="N11" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>65.25</v>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O11" s="32" t="n">
-        <v>66.47</v>
+        <v>66.59</v>
       </c>
       <c r="P11" s="32" t="n">
-        <v>66.44</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="Q11" s="33" t="n">
-        <v>66.34999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="R11" s="34" t="n">
-        <v>0.23</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="12">
@@ -1352,54 +1352,54 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>26.82</v>
+        <v>26.38</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>26.34</v>
+        <v>26.12</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>25.93</v>
+        <v>25.9</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>26.12</v>
+        <v>25.9</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>26.32</v>
+        <v>26.06</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>25.84</v>
+        <v>25.8</v>
       </c>
       <c r="I12" s="29" t="n">
         <v>25.64</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>25.36</v>
+        <v>25.54</v>
       </c>
       <c r="K12" s="30" t="n">
-        <v>25.67</v>
+        <v>25.76</v>
       </c>
       <c r="L12" s="31" t="n">
-        <v>25.26</v>
+        <v>25.54</v>
       </c>
       <c r="M12" s="31" t="n">
-        <v>24.78</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>25.28</v>
+      </c>
+      <c r="N12" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O12" s="32" t="n">
-        <v>25.77</v>
+        <v>25.79</v>
       </c>
       <c r="P12" s="32" t="n">
-        <v>25.7</v>
+        <v>25.78</v>
       </c>
       <c r="Q12" s="33" t="n">
-        <v>25.92</v>
-      </c>
-      <c r="R12" s="34" t="n">
-        <v>1.01</v>
+        <v>25.74</v>
+      </c>
+      <c r="R12" s="36" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1414,54 +1414,54 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>26.1</v>
+        <v>25.77</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>25.68</v>
+        <v>25.49</v>
       </c>
       <c r="E13" s="26" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="F13" s="27" t="n">
         <v>25.33</v>
       </c>
-      <c r="F13" s="27" t="n">
-        <v>25.41</v>
-      </c>
       <c r="G13" s="27" t="n">
-        <v>25.63</v>
+        <v>25.47</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>25.21</v>
+        <v>25.19</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>24.99</v>
+        <v>25.05</v>
       </c>
       <c r="J13" s="29" t="n">
-        <v>24.79</v>
+        <v>24.91</v>
       </c>
       <c r="K13" s="30" t="n">
-        <v>25.09</v>
+        <v>25.1</v>
       </c>
       <c r="L13" s="31" t="n">
-        <v>24.74</v>
+        <v>24.87</v>
       </c>
       <c r="M13" s="31" t="n">
-        <v>24.32</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>24.59</v>
+      </c>
+      <c r="N13" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O13" s="32" t="n">
-        <v>25.17</v>
+        <v>25.16</v>
       </c>
       <c r="P13" s="32" t="n">
-        <v>25.13</v>
+        <v>25.12</v>
       </c>
       <c r="Q13" s="33" t="n">
         <v>25.2</v>
       </c>
       <c r="R13" s="34" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1476,54 +1476,54 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>43.72</v>
+        <v>43.37</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>43.14</v>
+        <v>42.99</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>42.65</v>
+        <v>42.68</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>42.64</v>
+        <v>42.89</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>43</v>
+        <v>43.01</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>42.42</v>
+        <v>42.63</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>42.06</v>
+        <v>42.51</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>41.84</v>
+        <v>42.25</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>42.33</v>
+        <v>42.46</v>
       </c>
       <c r="L14" s="31" t="n">
-        <v>41.84</v>
+        <v>42.15</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>41.26</v>
-      </c>
-      <c r="N14" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>41.77</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O14" s="32" t="n">
-        <v>42.4</v>
+        <v>42.56</v>
       </c>
       <c r="P14" s="32" t="n">
-        <v>42.37</v>
+        <v>42.49</v>
       </c>
       <c r="Q14" s="33" t="n">
-        <v>42.28</v>
+        <v>42.76</v>
       </c>
       <c r="R14" s="34" t="n">
-        <v>0.33</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="15">
@@ -1538,37 +1538,37 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>8.92</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="D15" s="25" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="H15" s="28" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="E15" s="26" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="F15" s="27" t="n">
+      <c r="I15" s="29" t="n">
         <v>8.720000000000001</v>
       </c>
-      <c r="G15" s="27" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>8.65</v>
-      </c>
-      <c r="I15" s="29" t="n">
+      <c r="J15" s="29" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="L15" s="31" t="n">
         <v>8.59</v>
       </c>
-      <c r="J15" s="29" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="K15" s="30" t="n">
-        <v>8.609999999999999</v>
-      </c>
-      <c r="L15" s="31" t="n">
-        <v>8.5</v>
-      </c>
       <c r="M15" s="31" t="n">
-        <v>8.369999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
@@ -1576,16 +1576,16 @@
         </is>
       </c>
       <c r="O15" s="32" t="n">
-        <v>8.630000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="P15" s="32" t="n">
-        <v>8.619999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="Q15" s="33" t="n">
-        <v>8.66</v>
+        <v>8.82</v>
       </c>
       <c r="R15" s="34" t="n">
-        <v>0.58</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="16">
@@ -1600,37 +1600,37 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>15.45</v>
+        <v>15.44</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>15.06</v>
+        <v>15.19</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>14.73</v>
+        <v>14.98</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>14.93</v>
+        <v>14.96</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>15.07</v>
+        <v>15.12</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>14.68</v>
+        <v>14.87</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>14.54</v>
+        <v>14.71</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>14.29</v>
+        <v>14.62</v>
       </c>
       <c r="K16" s="30" t="n">
-        <v>14.52</v>
+        <v>14.84</v>
       </c>
       <c r="L16" s="31" t="n">
-        <v>14.19</v>
+        <v>14.64</v>
       </c>
       <c r="M16" s="31" t="n">
-        <v>13.8</v>
+        <v>14.39</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
@@ -1638,16 +1638,16 @@
         </is>
       </c>
       <c r="O16" s="32" t="n">
-        <v>14.61</v>
+        <v>14.87</v>
       </c>
       <c r="P16" s="32" t="n">
-        <v>14.55</v>
+        <v>14.86</v>
       </c>
       <c r="Q16" s="33" t="n">
         <v>14.79</v>
       </c>
       <c r="R16" s="34" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1662,54 +1662,54 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>4.82</v>
+        <v>5.58</v>
       </c>
       <c r="D17" s="25" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="K17" s="30" t="n">
         <v>4.76</v>
       </c>
-      <c r="E17" s="26" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="K17" s="30" t="n">
-        <v>4.67</v>
-      </c>
       <c r="L17" s="31" t="n">
-        <v>4.62</v>
+        <v>4.48</v>
       </c>
       <c r="M17" s="31" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="N17" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>4.14</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O17" s="32" t="n">
-        <v>4.68</v>
+        <v>4.81</v>
       </c>
       <c r="P17" s="32" t="n">
-        <v>4.68</v>
+        <v>4.79</v>
       </c>
       <c r="Q17" s="33" t="n">
-        <v>4.69</v>
+        <v>4.76</v>
       </c>
       <c r="R17" s="34" t="n">
-        <v>0.21</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="18">
@@ -1724,54 +1724,54 @@
         </is>
       </c>
       <c r="C18" s="25" t="n">
-        <v>19.23</v>
+        <v>18.78</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>18.84</v>
+        <v>18.6</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>18.51</v>
+        <v>18.45</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>18.54</v>
+        <v>18.48</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>18.77</v>
+        <v>18.57</v>
       </c>
       <c r="H18" s="28" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J18" s="29" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="L18" s="31" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M18" s="31" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O18" s="32" t="n">
         <v>18.38</v>
       </c>
-      <c r="I18" s="29" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="K18" s="30" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="L18" s="31" t="n">
-        <v>17.97</v>
-      </c>
-      <c r="M18" s="31" t="n">
-        <v>17.58</v>
-      </c>
-      <c r="N18" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O18" s="32" t="n">
-        <v>18.35</v>
-      </c>
       <c r="P18" s="32" t="n">
-        <v>18.33</v>
+        <v>18.36</v>
       </c>
       <c r="Q18" s="33" t="n">
-        <v>18.32</v>
-      </c>
-      <c r="R18" s="36" t="n">
-        <v>-1.13</v>
+        <v>18.38</v>
+      </c>
+      <c r="R18" s="34" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="19">
@@ -1786,37 +1786,37 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>26.44</v>
+        <v>27.87</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>25.86</v>
+        <v>26.95</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>25.37</v>
+        <v>26.18</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>25.67</v>
+        <v>26.49</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>25.87</v>
+        <v>26.89</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>25.29</v>
+        <v>25.97</v>
       </c>
       <c r="I19" s="29" t="n">
-        <v>25.09</v>
+        <v>25.57</v>
       </c>
       <c r="J19" s="29" t="n">
-        <v>24.71</v>
+        <v>25.05</v>
       </c>
       <c r="K19" s="30" t="n">
-        <v>25.05</v>
+        <v>25.66</v>
       </c>
       <c r="L19" s="31" t="n">
-        <v>24.56</v>
+        <v>24.89</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>23.98</v>
+        <v>23.97</v>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         </is>
       </c>
       <c r="O19" s="32" t="n">
-        <v>25.19</v>
+        <v>25.85</v>
       </c>
       <c r="P19" s="32" t="n">
-        <v>25.09</v>
+        <v>25.73</v>
       </c>
       <c r="Q19" s="33" t="n">
-        <v>25.46</v>
+        <v>26.08</v>
       </c>
       <c r="R19" s="34" t="n">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="20">
@@ -1848,37 +1848,37 @@
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>68.78</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>67.68000000000001</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>66.76000000000001</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>67.23</v>
+        <v>67.12</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>67.67</v>
+        <v>67.58</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>66.56999999999999</v>
+        <v>66.78</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>66.13</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>65.47</v>
+        <v>65.98</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>66.14</v>
+        <v>66.63</v>
       </c>
       <c r="L20" s="31" t="n">
-        <v>65.22</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>64.12</v>
+        <v>65.16</v>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="O20" s="32" t="n">
-        <v>66.40000000000001</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P20" s="32" t="n">
-        <v>66.23</v>
+        <v>66.69</v>
       </c>
       <c r="Q20" s="33" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="R20" s="34" t="n">
-        <v>1.67</v>
+        <v>66.65000000000001</v>
+      </c>
+      <c r="R20" s="36" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="21">
@@ -1910,54 +1910,54 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>12.3</v>
+        <v>12.67</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>12.2</v>
+        <v>12.44</v>
       </c>
       <c r="E21" s="26" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="H21" s="28" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="J21" s="29" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="K21" s="30" t="n">
         <v>12.12</v>
       </c>
-      <c r="F21" s="27" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="G21" s="27" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="H21" s="28" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>12.02</v>
-      </c>
-      <c r="J21" s="29" t="n">
-        <v>11.98</v>
-      </c>
-      <c r="K21" s="30" t="n">
-        <v>12.06</v>
-      </c>
       <c r="L21" s="31" t="n">
-        <v>11.98</v>
+        <v>11.93</v>
       </c>
       <c r="M21" s="31" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="N21" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>11.7</v>
+      </c>
+      <c r="N21" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O21" s="32" t="n">
-        <v>12.07</v>
+        <v>12.16</v>
       </c>
       <c r="P21" s="32" t="n">
-        <v>12.07</v>
+        <v>12.14</v>
       </c>
       <c r="Q21" s="33" t="n">
-        <v>12.06</v>
+        <v>12.16</v>
       </c>
       <c r="R21" s="34" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="22">
@@ -1972,54 +1972,54 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>18.81</v>
+        <v>19.51</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>18.62</v>
+        <v>18.97</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>18.46</v>
+        <v>18.52</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>18.5</v>
+        <v>18.63</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>18.59</v>
+        <v>18.91</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.4</v>
+        <v>18.37</v>
       </c>
       <c r="I22" s="29" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="J22" s="29" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="K22" s="30" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="L22" s="31" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="M22" s="31" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="N22" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O22" s="32" t="n">
         <v>18.31</v>
       </c>
-      <c r="J22" s="29" t="n">
-        <v>18.21</v>
-      </c>
-      <c r="K22" s="30" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="L22" s="31" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="M22" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="N22" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O22" s="32" t="n">
-        <v>18.38</v>
-      </c>
       <c r="P22" s="32" t="n">
-        <v>18.37</v>
+        <v>18.26</v>
       </c>
       <c r="Q22" s="33" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="R22" s="34" t="n">
-        <v>0.22</v>
+        <v>18.36</v>
+      </c>
+      <c r="R22" s="36" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="23">
@@ -2034,54 +2034,54 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>38.58</v>
+        <v>39.73</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>37.84</v>
+        <v>38.61</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>37.22</v>
+        <v>37.67</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>37.2</v>
+        <v>38.2</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>37.66</v>
+        <v>38.62</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>36.92</v>
+        <v>37.5</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>36.46</v>
+        <v>37.08</v>
       </c>
       <c r="J23" s="29" t="n">
-        <v>36.18</v>
+        <v>36.38</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>36.8</v>
+        <v>37.05</v>
       </c>
       <c r="L23" s="31" t="n">
-        <v>36.18</v>
+        <v>36.11</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>35.44</v>
-      </c>
-      <c r="N23" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>34.99</v>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O23" s="32" t="n">
-        <v>36.89</v>
+        <v>37.32</v>
       </c>
       <c r="P23" s="32" t="n">
-        <v>36.86</v>
+        <v>37.13</v>
       </c>
       <c r="Q23" s="33" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="R23" s="36" t="n">
-        <v>-1.55</v>
+        <v>37.78</v>
+      </c>
+      <c r="R23" s="34" t="n">
+        <v>2.83</v>
       </c>
     </row>
     <row r="24">
@@ -2096,37 +2096,37 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>16.4</v>
+        <v>15.82</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>15.98</v>
+        <v>15.6</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>15.63</v>
+        <v>15.41</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>15.67</v>
+        <v>15.43</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>15.9</v>
+        <v>15.56</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>15.48</v>
+        <v>15.34</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>15.25</v>
+        <v>15.21</v>
       </c>
       <c r="J24" s="29" t="n">
-        <v>15.06</v>
+        <v>15.12</v>
       </c>
       <c r="K24" s="30" t="n">
-        <v>15.39</v>
+        <v>15.29</v>
       </c>
       <c r="L24" s="31" t="n">
-        <v>15.04</v>
+        <v>15.1</v>
       </c>
       <c r="M24" s="31" t="n">
-        <v>14.62</v>
+        <v>14.88</v>
       </c>
       <c r="N24" s="35" t="inlineStr">
         <is>
@@ -2134,16 +2134,16 @@
         </is>
       </c>
       <c r="O24" s="32" t="n">
-        <v>15.45</v>
+        <v>15.32</v>
       </c>
       <c r="P24" s="32" t="n">
-        <v>15.43</v>
+        <v>15.31</v>
       </c>
       <c r="Q24" s="33" t="n">
-        <v>15.43</v>
+        <v>15.31</v>
       </c>
       <c r="R24" s="36" t="n">
-        <v>-1.72</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="25">
@@ -2158,54 +2158,54 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>38.1</v>
+        <v>37.68</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>37.42</v>
+        <v>37.1</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>36.85</v>
+        <v>36.61</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>36.8</v>
+        <v>36.57</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>37.24</v>
+        <v>36.95</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>36.56</v>
+        <v>36.37</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>36.12</v>
+        <v>35.99</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>35.88</v>
+        <v>35.79</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>36.47</v>
+        <v>36.29</v>
       </c>
       <c r="L25" s="31" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="M25" s="31" t="n">
         <v>35.22</v>
       </c>
-      <c r="N25" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+      <c r="N25" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O25" s="32" t="n">
-        <v>36.54</v>
+        <v>36.35</v>
       </c>
       <c r="P25" s="32" t="n">
-        <v>36.52</v>
+        <v>36.33</v>
       </c>
       <c r="Q25" s="33" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="R25" s="34" t="n">
-        <v>0.17</v>
+        <v>36.2</v>
+      </c>
+      <c r="R25" s="36" t="n">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="26">
@@ -2220,37 +2220,37 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>57.95</v>
+        <v>58.98</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>56.65</v>
+        <v>57.63</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>55.56</v>
+        <v>56.5</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>56.05</v>
+        <v>56.58</v>
       </c>
       <c r="G26" s="27" t="n">
-        <v>56.6</v>
+        <v>57.37</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>55.3</v>
+        <v>56.02</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>54.75</v>
+        <v>55.23</v>
       </c>
       <c r="J26" s="29" t="n">
-        <v>54</v>
+        <v>54.67</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>54.84</v>
+        <v>55.75</v>
       </c>
       <c r="L26" s="31" t="n">
-        <v>53.75</v>
+        <v>54.62</v>
       </c>
       <c r="M26" s="31" t="n">
-        <v>52.45</v>
+        <v>53.27</v>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
@@ -2258,16 +2258,16 @@
         </is>
       </c>
       <c r="O26" s="32" t="n">
-        <v>55.12</v>
+        <v>55.93</v>
       </c>
       <c r="P26" s="32" t="n">
-        <v>54.94</v>
+        <v>55.85</v>
       </c>
       <c r="Q26" s="33" t="n">
-        <v>55.5</v>
+        <v>55.8</v>
       </c>
       <c r="R26" s="34" t="n">
-        <v>1.37</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="27">
@@ -2282,37 +2282,37 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>212.09</v>
+        <v>222.77</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>209.19</v>
+        <v>216.67</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>206.76</v>
+        <v>211.56</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>207.77</v>
+        <v>211.2</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>209.03</v>
+        <v>215.1</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>206.13</v>
+        <v>209</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>204.87</v>
+        <v>205.1</v>
       </c>
       <c r="J27" s="29" t="n">
-        <v>203.23</v>
+        <v>202.9</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>205.14</v>
+        <v>208.14</v>
       </c>
       <c r="L27" s="31" t="n">
-        <v>202.71</v>
+        <v>203.03</v>
       </c>
       <c r="M27" s="31" t="n">
-        <v>199.81</v>
+        <v>196.93</v>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="O27" s="32" t="n">
-        <v>205.75</v>
+        <v>208.81</v>
       </c>
       <c r="P27" s="32" t="n">
-        <v>205.36</v>
+        <v>208.62</v>
       </c>
       <c r="Q27" s="33" t="n">
-        <v>206.5</v>
+        <v>207.3</v>
       </c>
       <c r="R27" s="34" t="n">
-        <v>0.63</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="28">
@@ -2344,37 +2344,37 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>87.31</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>85.36</v>
+        <v>85.41</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>83.72</v>
+        <v>84.11</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>84.5</v>
+        <v>84.67</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>85.3</v>
+        <v>85.33</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>83.34999999999999</v>
+        <v>83.78</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>82.55</v>
+        <v>83.12</v>
       </c>
       <c r="J28" s="29" t="n">
-        <v>81.40000000000001</v>
+        <v>82.23</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>82.63</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="L28" s="31" t="n">
-        <v>80.98999999999999</v>
+        <v>81.94</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>79.04000000000001</v>
+        <v>80.39</v>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="O28" s="32" t="n">
-        <v>83.06999999999999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="P28" s="32" t="n">
-        <v>82.78</v>
+        <v>83.36</v>
       </c>
       <c r="Q28" s="33" t="n">
-        <v>83.7</v>
+        <v>84</v>
       </c>
       <c r="R28" s="34" t="n">
-        <v>2.83</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="29">
@@ -2406,37 +2406,37 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>23.38</v>
+        <v>23.28</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>22.9</v>
+        <v>22.84</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>22.49</v>
+        <v>22.47</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>22.57</v>
+        <v>22.63</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>22.83</v>
+        <v>22.82</v>
       </c>
       <c r="H29" s="28" t="n">
-        <v>22.35</v>
+        <v>22.38</v>
       </c>
       <c r="I29" s="29" t="n">
-        <v>22.09</v>
+        <v>22.19</v>
       </c>
       <c r="J29" s="29" t="n">
-        <v>21.87</v>
+        <v>21.94</v>
       </c>
       <c r="K29" s="30" t="n">
         <v>22.23</v>
       </c>
       <c r="L29" s="31" t="n">
-        <v>21.82</v>
+        <v>21.86</v>
       </c>
       <c r="M29" s="31" t="n">
-        <v>21.34</v>
+        <v>21.42</v>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
@@ -2444,16 +2444,16 @@
         </is>
       </c>
       <c r="O29" s="32" t="n">
-        <v>22.3</v>
+        <v>22.32</v>
       </c>
       <c r="P29" s="32" t="n">
         <v>22.26</v>
       </c>
       <c r="Q29" s="33" t="n">
-        <v>22.32</v>
+        <v>22.44</v>
       </c>
       <c r="R29" s="34" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="30">
@@ -2468,54 +2468,54 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>81.87</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>80.47</v>
+        <v>79.56</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>79.29000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F30" s="27" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G30" s="27" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="G30" s="27" t="n">
-        <v>80.2</v>
-      </c>
       <c r="H30" s="28" t="n">
-        <v>78.8</v>
+        <v>78.25</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>78</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="J30" s="29" t="n">
-        <v>77.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>78.51000000000001</v>
+        <v>77.95</v>
       </c>
       <c r="L30" s="31" t="n">
-        <v>77.33</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>75.93000000000001</v>
-      </c>
-      <c r="N30" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>75.84</v>
+      </c>
+      <c r="N30" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O30" s="32" t="n">
-        <v>78.70999999999999</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="P30" s="32" t="n">
-        <v>78.62</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="Q30" s="33" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="R30" s="34" t="n">
-        <v>0.26</v>
+        <v>78.2</v>
+      </c>
+      <c r="R30" s="36" t="n">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="31">
@@ -2530,54 +2530,54 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>31.02</v>
+        <v>31.18</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>30.3</v>
+        <v>30.44</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>29.7</v>
+        <v>29.82</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>29.82</v>
+        <v>30.17</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>30.2</v>
+        <v>30.45</v>
       </c>
       <c r="H31" s="28" t="n">
-        <v>29.48</v>
+        <v>29.71</v>
       </c>
       <c r="I31" s="29" t="n">
-        <v>29.1</v>
+        <v>29.43</v>
       </c>
       <c r="J31" s="29" t="n">
-        <v>28.76</v>
+        <v>28.97</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="L31" s="31" t="n">
-        <v>28.7</v>
+        <v>28.78</v>
       </c>
       <c r="M31" s="31" t="n">
-        <v>27.98</v>
-      </c>
-      <c r="N31" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>28.04</v>
+      </c>
+      <c r="N31" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O31" s="32" t="n">
-        <v>29.42</v>
+        <v>29.58</v>
       </c>
       <c r="P31" s="32" t="n">
-        <v>29.35</v>
+        <v>29.46</v>
       </c>
       <c r="Q31" s="33" t="n">
-        <v>29.44</v>
+        <v>29.9</v>
       </c>
       <c r="R31" s="34" t="n">
-        <v>0.14</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="32">
@@ -2592,54 +2592,54 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>50.26</v>
+        <v>50.91</v>
       </c>
       <c r="D32" s="25" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="E32" s="26" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="H32" s="28" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="J32" s="29" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="K32" s="30" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="L32" s="31" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="M32" s="31" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O32" s="32" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="P32" s="32" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="Q32" s="33" t="n">
         <v>49.94</v>
       </c>
-      <c r="E32" s="26" t="n">
-        <v>49.67</v>
-      </c>
-      <c r="F32" s="27" t="n">
-        <v>49.65</v>
-      </c>
-      <c r="G32" s="27" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="H32" s="28" t="n">
-        <v>49.53</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>49.33</v>
-      </c>
-      <c r="J32" s="29" t="n">
-        <v>49.21</v>
-      </c>
-      <c r="K32" s="30" t="n">
-        <v>49.49</v>
-      </c>
-      <c r="L32" s="31" t="n">
-        <v>49.22</v>
-      </c>
-      <c r="M32" s="31" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="N32" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O32" s="32" t="n">
-        <v>49.52</v>
-      </c>
-      <c r="P32" s="32" t="n">
-        <v>49.52</v>
-      </c>
-      <c r="Q32" s="33" t="n">
-        <v>49.44</v>
-      </c>
-      <c r="R32" s="36" t="n">
-        <v>-0.12</v>
+      <c r="R32" s="34" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="33">
@@ -2654,54 +2654,54 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>133.55</v>
+        <v>131.33</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>131.85</v>
+        <v>130.63</v>
       </c>
       <c r="E33" s="26" t="n">
+        <v>130.05</v>
+      </c>
+      <c r="F33" s="27" t="n">
         <v>130.43</v>
       </c>
-      <c r="F33" s="27" t="n">
-        <v>130.57</v>
-      </c>
       <c r="G33" s="27" t="n">
-        <v>131.53</v>
+        <v>130.67</v>
       </c>
       <c r="H33" s="28" t="n">
-        <v>129.83</v>
+        <v>129.97</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>128.87</v>
+        <v>129.73</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>128.13</v>
+        <v>129.27</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>129.47</v>
+        <v>129.65</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>128.05</v>
+        <v>129.07</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>126.35</v>
-      </c>
-      <c r="N33" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>128.37</v>
+      </c>
+      <c r="N33" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O33" s="32" t="n">
-        <v>129.72</v>
+        <v>129.84</v>
       </c>
       <c r="P33" s="32" t="n">
-        <v>129.61</v>
+        <v>129.71</v>
       </c>
       <c r="Q33" s="33" t="n">
-        <v>129.6</v>
-      </c>
-      <c r="R33" s="36" t="n">
-        <v>-1.67</v>
+        <v>130.2</v>
+      </c>
+      <c r="R33" s="34" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="34">
@@ -2716,37 +2716,37 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>60.54</v>
+        <v>66.69</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>57.24</v>
+        <v>61.69</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>54.47</v>
+        <v>57.5</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>55.5</v>
+        <v>59.87</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>57</v>
+        <v>61.73</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>53.7</v>
+        <v>56.73</v>
       </c>
       <c r="I34" s="29" t="n">
-        <v>52.2</v>
+        <v>54.87</v>
       </c>
       <c r="J34" s="29" t="n">
-        <v>50.4</v>
+        <v>51.73</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>52.63</v>
+        <v>54.7</v>
       </c>
       <c r="L34" s="31" t="n">
-        <v>49.86</v>
+        <v>50.51</v>
       </c>
       <c r="M34" s="31" t="n">
-        <v>46.56</v>
+        <v>45.51</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="O34" s="32" t="n">
-        <v>53.29</v>
+        <v>55.91</v>
       </c>
       <c r="P34" s="32" t="n">
-        <v>52.88</v>
+        <v>55.09</v>
       </c>
       <c r="Q34" s="33" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="R34" s="34" t="n">
-        <v>4.85</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="35">
@@ -2778,54 +2778,54 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>25.87</v>
+        <v>26</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>25.57</v>
+        <v>25.68</v>
       </c>
       <c r="E35" s="26" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="H35" s="28" t="n">
         <v>25.31</v>
       </c>
-      <c r="F35" s="27" t="n">
-        <v>25.48</v>
-      </c>
-      <c r="G35" s="27" t="n">
-        <v>25.58</v>
-      </c>
-      <c r="H35" s="28" t="n">
+      <c r="I35" s="29" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="J35" s="29" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="K35" s="30" t="n">
+        <v>25.23</v>
+      </c>
+      <c r="L35" s="31" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="M35" s="31" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="N35" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O35" s="32" t="n">
         <v>25.28</v>
       </c>
-      <c r="I35" s="29" t="n">
-        <v>25.18</v>
-      </c>
-      <c r="J35" s="29" t="n">
-        <v>24.98</v>
-      </c>
-      <c r="K35" s="30" t="n">
-        <v>25.15</v>
-      </c>
-      <c r="L35" s="31" t="n">
-        <v>24.89</v>
-      </c>
-      <c r="M35" s="31" t="n">
-        <v>24.59</v>
-      </c>
-      <c r="N35" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O35" s="32" t="n">
-        <v>25.22</v>
-      </c>
       <c r="P35" s="32" t="n">
-        <v>25.17</v>
+        <v>25.26</v>
       </c>
       <c r="Q35" s="33" t="n">
-        <v>25.38</v>
-      </c>
-      <c r="R35" s="34" t="n">
-        <v>1.2</v>
+        <v>25.28</v>
+      </c>
+      <c r="R35" s="36" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="36">
@@ -2840,37 +2840,37 @@
         </is>
       </c>
       <c r="C36" s="25" t="n">
-        <v>27.82</v>
+        <v>26.83</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>27.24</v>
+        <v>26.59</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>26.75</v>
+        <v>26.39</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>26.79</v>
+        <v>26.52</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>27.13</v>
+        <v>26.6</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>26.55</v>
+        <v>26.36</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>26.21</v>
+        <v>26.28</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>25.97</v>
+        <v>26.12</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>26.43</v>
+        <v>26.25</v>
       </c>
       <c r="L36" s="31" t="n">
-        <v>25.94</v>
+        <v>26.05</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>25.36</v>
+        <v>25.81</v>
       </c>
       <c r="N36" s="35" t="inlineStr">
         <is>
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="O36" s="32" t="n">
-        <v>26.51</v>
+        <v>26.32</v>
       </c>
       <c r="P36" s="32" t="n">
-        <v>26.47</v>
+        <v>26.27</v>
       </c>
       <c r="Q36" s="33" t="n">
-        <v>26.46</v>
+        <v>26.44</v>
       </c>
       <c r="R36" s="36" t="n">
-        <v>-1.34</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="37">
@@ -2902,54 +2902,54 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>9.6</v>
+        <v>9.69</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>9.369999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="E37" s="26" t="n">
-        <v>9.18</v>
+        <v>9.27</v>
       </c>
       <c r="F37" s="27" t="n">
-        <v>9.300000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>9.380000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>9.15</v>
+        <v>9.17</v>
       </c>
       <c r="I37" s="29" t="n">
-        <v>9.07</v>
+        <v>9.02</v>
       </c>
       <c r="J37" s="29" t="n">
-        <v>8.92</v>
+        <v>8.94</v>
       </c>
       <c r="K37" s="30" t="n">
-        <v>9.050000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L37" s="31" t="n">
-        <v>8.859999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M37" s="31" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="N37" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>8.720000000000001</v>
+      </c>
+      <c r="N37" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O37" s="32" t="n">
-        <v>9.109999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="P37" s="32" t="n">
-        <v>9.07</v>
+        <v>9.16</v>
       </c>
       <c r="Q37" s="33" t="n">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="R37" s="34" t="n">
-        <v>2.67</v>
+        <v>9.1</v>
+      </c>
+      <c r="R37" s="36" t="n">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="38">
@@ -2964,54 +2964,54 @@
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>32.09</v>
+        <v>33.04</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>31.59</v>
+        <v>31.88</v>
       </c>
       <c r="E38" s="26" t="n">
-        <v>31.17</v>
+        <v>30.9</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>31.13</v>
+        <v>31.47</v>
       </c>
       <c r="G38" s="27" t="n">
-        <v>31.45</v>
+        <v>31.89</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>30.95</v>
+        <v>30.73</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>30.63</v>
+        <v>30.31</v>
       </c>
       <c r="J38" s="29" t="n">
-        <v>30.45</v>
+        <v>29.57</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>30.89</v>
+        <v>30.26</v>
       </c>
       <c r="L38" s="31" t="n">
-        <v>30.47</v>
+        <v>29.28</v>
       </c>
       <c r="M38" s="31" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="N38" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>28.12</v>
+      </c>
+      <c r="N38" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O38" s="32" t="n">
-        <v>30.94</v>
+        <v>30.54</v>
       </c>
       <c r="P38" s="32" t="n">
-        <v>30.93</v>
+        <v>30.35</v>
       </c>
       <c r="Q38" s="33" t="n">
-        <v>30.8</v>
+        <v>31.04</v>
       </c>
       <c r="R38" s="34" t="n">
-        <v>0.13</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="39">
@@ -3026,54 +3026,54 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>197.11</v>
+        <v>197.04</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>194.51</v>
+        <v>194.54</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>192.33</v>
+        <v>192.45</v>
       </c>
       <c r="F39" s="27" t="n">
-        <v>192.37</v>
+        <v>192.3</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>193.93</v>
+        <v>193.9</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>191.33</v>
+        <v>191.4</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>189.77</v>
+        <v>189.8</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>188.73</v>
+        <v>188.9</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>190.87</v>
+        <v>191.05</v>
       </c>
       <c r="L39" s="31" t="n">
-        <v>188.69</v>
+        <v>188.96</v>
       </c>
       <c r="M39" s="31" t="n">
-        <v>186.09</v>
-      </c>
-      <c r="N39" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>186.46</v>
+      </c>
+      <c r="N39" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O39" s="32" t="n">
-        <v>191.2</v>
+        <v>191.32</v>
       </c>
       <c r="P39" s="32" t="n">
-        <v>191.07</v>
+        <v>191.25</v>
       </c>
       <c r="Q39" s="33" t="n">
-        <v>190.8</v>
-      </c>
-      <c r="R39" s="34" t="n">
-        <v>0.1</v>
+        <v>190.7</v>
+      </c>
+      <c r="R39" s="36" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="40">
@@ -3088,54 +3088,54 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>13.43</v>
+        <v>13.61</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>13.3</v>
+        <v>13.42</v>
       </c>
       <c r="E40" s="26" t="n">
-        <v>13.19</v>
+        <v>13.26</v>
       </c>
       <c r="F40" s="27" t="n">
-        <v>13.22</v>
+        <v>13.34</v>
       </c>
       <c r="G40" s="27" t="n">
-        <v>13.28</v>
+        <v>13.42</v>
       </c>
       <c r="H40" s="28" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="I40" s="29" t="n">
         <v>13.15</v>
       </c>
-      <c r="I40" s="29" t="n">
-        <v>13.09</v>
-      </c>
       <c r="J40" s="29" t="n">
-        <v>13.02</v>
+        <v>13.04</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>13.12</v>
+        <v>13.15</v>
       </c>
       <c r="L40" s="31" t="n">
-        <v>13.01</v>
+        <v>12.99</v>
       </c>
       <c r="M40" s="31" t="n">
-        <v>12.88</v>
-      </c>
-      <c r="N40" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>12.8</v>
+      </c>
+      <c r="N40" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O40" s="32" t="n">
-        <v>13.14</v>
+        <v>13.2</v>
       </c>
       <c r="P40" s="32" t="n">
-        <v>13.13</v>
+        <v>13.17</v>
       </c>
       <c r="Q40" s="33" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="R40" s="36" t="n">
-        <v>-0.23</v>
+        <v>13.27</v>
+      </c>
+      <c r="R40" s="34" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="41">
@@ -3150,54 +3150,54 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>23.6</v>
+        <v>24.92</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>22.92</v>
+        <v>23.92</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>22.35</v>
+        <v>23.08</v>
       </c>
       <c r="F41" s="27" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="H41" s="28" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="I41" s="29" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="J41" s="29" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="K41" s="30" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="L41" s="31" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="M41" s="31" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="N41" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O41" s="32" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="P41" s="32" t="n">
         <v>22.6</v>
       </c>
-      <c r="G41" s="27" t="n">
-        <v>22.89</v>
-      </c>
-      <c r="H41" s="28" t="n">
-        <v>22.21</v>
-      </c>
-      <c r="I41" s="29" t="n">
-        <v>21.92</v>
-      </c>
-      <c r="J41" s="29" t="n">
-        <v>21.53</v>
-      </c>
-      <c r="K41" s="30" t="n">
-        <v>21.97</v>
-      </c>
-      <c r="L41" s="31" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="M41" s="31" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="N41" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O41" s="32" t="n">
-        <v>22.12</v>
-      </c>
-      <c r="P41" s="32" t="n">
-        <v>22.02</v>
-      </c>
       <c r="Q41" s="33" t="n">
-        <v>22.31</v>
+        <v>23.03</v>
       </c>
       <c r="R41" s="34" t="n">
-        <v>1.41</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="42">
@@ -3212,54 +3212,54 @@
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>192.87</v>
+        <v>193.37</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>190.17</v>
+        <v>190.67</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>187.91</v>
+        <v>188.41</v>
       </c>
       <c r="F42" s="27" t="n">
-        <v>188.4</v>
+        <v>188.5</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>189.8</v>
+        <v>190.1</v>
       </c>
       <c r="H42" s="28" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="I42" s="29" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="J42" s="29" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="K42" s="30" t="n">
+        <v>186.89</v>
+      </c>
+      <c r="L42" s="31" t="n">
+        <v>184.63</v>
+      </c>
+      <c r="M42" s="31" t="n">
+        <v>181.93</v>
+      </c>
+      <c r="N42" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O42" s="32" t="n">
+        <v>187.25</v>
+      </c>
+      <c r="P42" s="32" t="n">
         <v>187.1</v>
       </c>
-      <c r="I42" s="29" t="n">
-        <v>185.7</v>
-      </c>
-      <c r="J42" s="29" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="K42" s="30" t="n">
-        <v>186.39</v>
-      </c>
-      <c r="L42" s="31" t="n">
-        <v>184.13</v>
-      </c>
-      <c r="M42" s="31" t="n">
-        <v>181.43</v>
-      </c>
-      <c r="N42" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O42" s="32" t="n">
-        <v>186.85</v>
-      </c>
-      <c r="P42" s="32" t="n">
-        <v>186.6</v>
-      </c>
       <c r="Q42" s="33" t="n">
-        <v>187</v>
-      </c>
-      <c r="R42" s="34" t="n">
-        <v>0.54</v>
+        <v>186.9</v>
+      </c>
+      <c r="R42" s="36" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="43">
@@ -3274,37 +3274,37 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>39.23</v>
+        <v>39.06</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>38.57</v>
+        <v>38.32</v>
       </c>
       <c r="E43" s="26" t="n">
-        <v>38.01</v>
+        <v>37.7</v>
       </c>
       <c r="F43" s="27" t="n">
-        <v>37.95</v>
+        <v>37.73</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>38.39</v>
+        <v>38.17</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>37.73</v>
+        <v>37.43</v>
       </c>
       <c r="I43" s="29" t="n">
-        <v>37.29</v>
+        <v>36.99</v>
       </c>
       <c r="J43" s="29" t="n">
-        <v>37.07</v>
+        <v>36.69</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>37.65</v>
+        <v>37.28</v>
       </c>
       <c r="L43" s="31" t="n">
-        <v>37.09</v>
+        <v>36.66</v>
       </c>
       <c r="M43" s="31" t="n">
-        <v>36.43</v>
+        <v>35.92</v>
       </c>
       <c r="N43" s="35" t="inlineStr">
         <is>
@@ -3312,16 +3312,16 @@
         </is>
       </c>
       <c r="O43" s="32" t="n">
-        <v>37.71</v>
+        <v>37.38</v>
       </c>
       <c r="P43" s="32" t="n">
-        <v>37.7</v>
+        <v>37.34</v>
       </c>
       <c r="Q43" s="33" t="n">
-        <v>37.52</v>
+        <v>37.3</v>
       </c>
       <c r="R43" s="36" t="n">
-        <v>-1.37</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="44">
@@ -3336,54 +3336,54 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>27.6</v>
+        <v>29</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>27.4</v>
+        <v>28.28</v>
       </c>
       <c r="E44" s="26" t="n">
-        <v>27.24</v>
+        <v>27.68</v>
       </c>
       <c r="F44" s="27" t="n">
-        <v>27.23</v>
+        <v>27.91</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>27.35</v>
+        <v>28.23</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>27.15</v>
+        <v>27.51</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>27.03</v>
+        <v>27.19</v>
       </c>
       <c r="J44" s="29" t="n">
-        <v>26.95</v>
+        <v>26.79</v>
       </c>
       <c r="K44" s="30" t="n">
-        <v>27.12</v>
+        <v>27.28</v>
       </c>
       <c r="L44" s="31" t="n">
-        <v>26.96</v>
+        <v>26.68</v>
       </c>
       <c r="M44" s="31" t="n">
-        <v>26.76</v>
-      </c>
-      <c r="N44" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>25.96</v>
+      </c>
+      <c r="N44" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O44" s="32" t="n">
-        <v>27.15</v>
+        <v>27.42</v>
       </c>
       <c r="P44" s="32" t="n">
-        <v>27.14</v>
+        <v>27.33</v>
       </c>
       <c r="Q44" s="33" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="R44" s="36" t="n">
-        <v>-0.29</v>
+        <v>27.58</v>
+      </c>
+      <c r="R44" s="34" t="n">
+        <v>1.77</v>
       </c>
     </row>
     <row r="45">
@@ -3398,54 +3398,54 @@
         </is>
       </c>
       <c r="C45" s="25" t="n">
-        <v>26.42</v>
+        <v>26.27</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>26.22</v>
+        <v>26.15</v>
       </c>
       <c r="E45" s="26" t="n">
-        <v>26.06</v>
+        <v>26.05</v>
       </c>
       <c r="F45" s="27" t="n">
         <v>26.07</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>26.19</v>
+        <v>26.13</v>
       </c>
       <c r="H45" s="28" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="I45" s="29" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="J45" s="29" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="K45" s="30" t="n">
         <v>25.99</v>
       </c>
-      <c r="I45" s="29" t="n">
-        <v>25.87</v>
-      </c>
-      <c r="J45" s="29" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="K45" s="30" t="n">
-        <v>25.94</v>
-      </c>
       <c r="L45" s="31" t="n">
-        <v>25.78</v>
+        <v>25.89</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>25.58</v>
-      </c>
-      <c r="N45" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>25.77</v>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O45" s="32" t="n">
-        <v>25.97</v>
+        <v>26</v>
       </c>
       <c r="P45" s="32" t="n">
-        <v>25.96</v>
+        <v>26</v>
       </c>
       <c r="Q45" s="33" t="n">
-        <v>25.96</v>
-      </c>
-      <c r="R45" s="36" t="n">
-        <v>-0.23</v>
+        <v>26</v>
+      </c>
+      <c r="R45" s="34" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="46">
@@ -3460,54 +3460,54 @@
         </is>
       </c>
       <c r="C46" s="25" t="n">
-        <v>8.460000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>8.300000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="E46" s="26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="H46" s="28" t="n">
         <v>8.16</v>
       </c>
-      <c r="F46" s="27" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="G46" s="27" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="H46" s="28" t="n">
-        <v>8.109999999999999</v>
-      </c>
       <c r="I46" s="29" t="n">
-        <v>8.029999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="J46" s="29" t="n">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="K46" s="30" t="n">
-        <v>8.08</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L46" s="31" t="n">
-        <v>7.94</v>
+        <v>7.98</v>
       </c>
       <c r="M46" s="31" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="N46" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>7.82</v>
+      </c>
+      <c r="N46" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O46" s="32" t="n">
-        <v>8.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="P46" s="32" t="n">
-        <v>8.09</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="Q46" s="33" t="n">
-        <v>8.1</v>
+        <v>8.15</v>
       </c>
       <c r="R46" s="34" t="n">
-        <v>0.12</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="47">
@@ -3522,37 +3522,37 @@
         </is>
       </c>
       <c r="C47" s="25" t="n">
-        <v>12.95</v>
+        <v>12.92</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>12.66</v>
+        <v>12.72</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>12.42</v>
+        <v>12.56</v>
       </c>
       <c r="F47" s="27" t="n">
-        <v>12.53</v>
+        <v>12.58</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>12.65</v>
+        <v>12.69</v>
       </c>
       <c r="H47" s="28" t="n">
-        <v>12.36</v>
+        <v>12.49</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>12.24</v>
+        <v>12.38</v>
       </c>
       <c r="J47" s="29" t="n">
-        <v>12.07</v>
+        <v>12.29</v>
       </c>
       <c r="K47" s="30" t="n">
-        <v>12.25</v>
+        <v>12.44</v>
       </c>
       <c r="L47" s="31" t="n">
-        <v>12.01</v>
+        <v>12.28</v>
       </c>
       <c r="M47" s="31" t="n">
-        <v>11.72</v>
+        <v>12.08</v>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
@@ -3560,16 +3560,16 @@
         </is>
       </c>
       <c r="O47" s="32" t="n">
-        <v>12.32</v>
+        <v>12.47</v>
       </c>
       <c r="P47" s="32" t="n">
-        <v>12.28</v>
+        <v>12.46</v>
       </c>
       <c r="Q47" s="33" t="n">
-        <v>12.41</v>
+        <v>12.47</v>
       </c>
       <c r="R47" s="34" t="n">
-        <v>1.97</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="48">
@@ -3584,37 +3584,37 @@
         </is>
       </c>
       <c r="C48" s="25" t="n">
-        <v>213.82</v>
+        <v>215.18</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>210.22</v>
+        <v>211.98</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>207.21</v>
+        <v>209.3</v>
       </c>
       <c r="F48" s="27" t="n">
-        <v>208.67</v>
+        <v>209.53</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>210.13</v>
+        <v>211.37</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>206.53</v>
+        <v>208.17</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>205.07</v>
+        <v>206.33</v>
       </c>
       <c r="J48" s="29" t="n">
-        <v>202.93</v>
+        <v>204.97</v>
       </c>
       <c r="K48" s="30" t="n">
-        <v>205.19</v>
+        <v>207.5</v>
       </c>
       <c r="L48" s="31" t="n">
-        <v>202.18</v>
+        <v>204.82</v>
       </c>
       <c r="M48" s="31" t="n">
-        <v>198.58</v>
+        <v>201.62</v>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
@@ -3622,16 +3622,16 @@
         </is>
       </c>
       <c r="O48" s="32" t="n">
-        <v>206</v>
+        <v>207.96</v>
       </c>
       <c r="P48" s="32" t="n">
-        <v>205.47</v>
+        <v>207.75</v>
       </c>
       <c r="Q48" s="33" t="n">
-        <v>207.2</v>
+        <v>207.7</v>
       </c>
       <c r="R48" s="34" t="n">
-        <v>1.12</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="49">
@@ -3646,54 +3646,54 @@
         </is>
       </c>
       <c r="C49" s="25" t="n">
-        <v>48.44</v>
+        <v>48.52</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>47.92</v>
+        <v>48.06</v>
       </c>
       <c r="E49" s="26" t="n">
+        <v>47.68</v>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="G49" s="27" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="H49" s="28" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="I49" s="29" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="J49" s="29" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="K49" s="30" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="L49" s="31" t="n">
+        <v>47.04</v>
+      </c>
+      <c r="M49" s="31" t="n">
+        <v>46.58</v>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O49" s="32" t="n">
         <v>47.49</v>
       </c>
-      <c r="F49" s="27" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="G49" s="27" t="n">
-        <v>47.89</v>
-      </c>
-      <c r="H49" s="28" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>47.15</v>
-      </c>
-      <c r="J49" s="29" t="n">
-        <v>46.85</v>
-      </c>
-      <c r="K49" s="30" t="n">
-        <v>47.19</v>
-      </c>
-      <c r="L49" s="31" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="M49" s="31" t="n">
-        <v>46.24</v>
-      </c>
-      <c r="N49" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O49" s="32" t="n">
-        <v>47.3</v>
-      </c>
       <c r="P49" s="32" t="n">
-        <v>47.23</v>
+        <v>47.46</v>
       </c>
       <c r="Q49" s="33" t="n">
-        <v>47.44</v>
-      </c>
-      <c r="R49" s="36" t="n">
-        <v>-0.13</v>
+        <v>47.48</v>
+      </c>
+      <c r="R49" s="34" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="50">
@@ -3708,37 +3708,37 @@
         </is>
       </c>
       <c r="C50" s="25" t="n">
-        <v>34.64</v>
+        <v>34.98</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>34.32</v>
+        <v>34.5</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>34.05</v>
+        <v>34.09</v>
       </c>
       <c r="F50" s="27" t="n">
-        <v>34.07</v>
+        <v>34.15</v>
       </c>
       <c r="G50" s="27" t="n">
-        <v>34.25</v>
+        <v>34.41</v>
       </c>
       <c r="H50" s="28" t="n">
         <v>33.93</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>33.75</v>
+        <v>33.67</v>
       </c>
       <c r="J50" s="29" t="n">
-        <v>33.61</v>
+        <v>33.45</v>
       </c>
       <c r="K50" s="30" t="n">
-        <v>33.87</v>
+        <v>33.83</v>
       </c>
       <c r="L50" s="31" t="n">
-        <v>33.6</v>
+        <v>33.42</v>
       </c>
       <c r="M50" s="31" t="n">
-        <v>33.28</v>
+        <v>32.94</v>
       </c>
       <c r="N50" s="35" t="inlineStr">
         <is>
@@ -3746,16 +3746,16 @@
         </is>
       </c>
       <c r="O50" s="32" t="n">
-        <v>33.91</v>
+        <v>33.9</v>
       </c>
       <c r="P50" s="32" t="n">
-        <v>33.9</v>
+        <v>33.86</v>
       </c>
       <c r="Q50" s="33" t="n">
         <v>33.88</v>
       </c>
-      <c r="R50" s="36" t="n">
-        <v>-0.06</v>
+      <c r="R50" s="34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3770,37 +3770,37 @@
         </is>
       </c>
       <c r="C51" s="25" t="n">
-        <v>13.75</v>
+        <v>13.66</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>13.5</v>
+        <v>13.48</v>
       </c>
       <c r="E51" s="26" t="n">
-        <v>13.3</v>
+        <v>13.33</v>
       </c>
       <c r="F51" s="27" t="n">
         <v>13.33</v>
       </c>
       <c r="G51" s="27" t="n">
-        <v>13.46</v>
+        <v>13.44</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>13.21</v>
+        <v>13.26</v>
       </c>
       <c r="I51" s="29" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="J51" s="29" t="n">
         <v>13.08</v>
       </c>
-      <c r="J51" s="29" t="n">
-        <v>12.96</v>
-      </c>
       <c r="K51" s="30" t="n">
-        <v>13.16</v>
+        <v>13.23</v>
       </c>
       <c r="L51" s="31" t="n">
-        <v>12.95</v>
+        <v>13.08</v>
       </c>
       <c r="M51" s="31" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="O51" s="32" t="n">
-        <v>13.19</v>
+        <v>13.25</v>
       </c>
       <c r="P51" s="32" t="n">
-        <v>13.17</v>
+        <v>13.24</v>
       </c>
       <c r="Q51" s="33" t="n">
-        <v>13.19</v>
+        <v>13.22</v>
       </c>
       <c r="R51" s="34" t="n">
-        <v>0.38</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="52">
@@ -3841,19 +3841,19 @@
         <v>60.56</v>
       </c>
       <c r="F52" s="27" t="n">
-        <v>60.58</v>
+        <v>60.52</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>60.97</v>
+        <v>60.93</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>60.32</v>
+        <v>60.28</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>59.93</v>
+        <v>59.87</v>
       </c>
       <c r="J52" s="29" t="n">
-        <v>59.67</v>
+        <v>59.63</v>
       </c>
       <c r="K52" s="30" t="n">
         <v>60.19</v>
@@ -3864,19 +3864,19 @@
       <c r="M52" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="N52" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+      <c r="N52" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O52" s="32" t="n">
-        <v>60.28</v>
+        <v>60.26</v>
       </c>
       <c r="P52" s="32" t="n">
         <v>60.24</v>
       </c>
       <c r="Q52" s="33" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="R52" s="36" t="n">
         <v>-0.17</v>
@@ -3894,37 +3894,37 @@
         </is>
       </c>
       <c r="C53" s="25" t="n">
-        <v>24.17</v>
+        <v>24.63</v>
       </c>
       <c r="D53" s="25" t="n">
-        <v>23.89</v>
+        <v>24.21</v>
       </c>
       <c r="E53" s="26" t="n">
-        <v>23.66</v>
+        <v>23.86</v>
       </c>
       <c r="F53" s="27" t="n">
-        <v>23.71</v>
+        <v>23.86</v>
       </c>
       <c r="G53" s="27" t="n">
-        <v>23.85</v>
+        <v>24.11</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>23.57</v>
+        <v>23.69</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>23.43</v>
+        <v>23.44</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>23.29</v>
+        <v>23.27</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>23.5</v>
+        <v>23.62</v>
       </c>
       <c r="L53" s="31" t="n">
         <v>23.27</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>22.99</v>
+        <v>22.85</v>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="O53" s="32" t="n">
-        <v>23.55</v>
+        <v>23.67</v>
       </c>
       <c r="P53" s="32" t="n">
-        <v>23.52</v>
+        <v>23.66</v>
       </c>
       <c r="Q53" s="33" t="n">
-        <v>23.56</v>
+        <v>23.6</v>
       </c>
       <c r="R53" s="34" t="n">
-        <v>0.38</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="54">
@@ -3956,37 +3956,37 @@
         </is>
       </c>
       <c r="C54" s="25" t="n">
-        <v>5.75</v>
+        <v>5.69</v>
       </c>
       <c r="D54" s="25" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="E54" s="26" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="G54" s="27" t="n">
         <v>5.55</v>
       </c>
-      <c r="E54" s="26" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="F54" s="27" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="G54" s="27" t="n">
-        <v>5.54</v>
-      </c>
       <c r="H54" s="28" t="n">
-        <v>5.34</v>
+        <v>5.43</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>5.26</v>
+        <v>5.37</v>
       </c>
       <c r="J54" s="29" t="n">
-        <v>5.14</v>
+        <v>5.31</v>
       </c>
       <c r="K54" s="30" t="n">
-        <v>5.27</v>
+        <v>5.41</v>
       </c>
       <c r="L54" s="31" t="n">
-        <v>5.11</v>
+        <v>5.31</v>
       </c>
       <c r="M54" s="31" t="n">
-        <v>4.91</v>
+        <v>5.19</v>
       </c>
       <c r="N54" s="20" t="inlineStr">
         <is>
@@ -3994,16 +3994,16 @@
         </is>
       </c>
       <c r="O54" s="32" t="n">
-        <v>5.32</v>
+        <v>5.42</v>
       </c>
       <c r="P54" s="32" t="n">
-        <v>5.29</v>
+        <v>5.42</v>
       </c>
       <c r="Q54" s="33" t="n">
-        <v>5.37</v>
+        <v>5.42</v>
       </c>
       <c r="R54" s="34" t="n">
-        <v>2.68</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="55">
@@ -4018,54 +4018,54 @@
         </is>
       </c>
       <c r="C55" s="25" t="n">
-        <v>19.49</v>
+        <v>19.33</v>
       </c>
       <c r="D55" s="25" t="n">
         <v>18.86</v>
       </c>
       <c r="E55" s="26" t="n">
-        <v>18.33</v>
+        <v>18.47</v>
       </c>
       <c r="F55" s="27" t="n">
-        <v>18.6</v>
+        <v>18.45</v>
       </c>
       <c r="G55" s="27" t="n">
-        <v>18.85</v>
+        <v>18.74</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>18.22</v>
+        <v>18.27</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>17.97</v>
+        <v>17.98</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>17.59</v>
+        <v>17.8</v>
       </c>
       <c r="K55" s="30" t="n">
-        <v>17.98</v>
+        <v>18.2</v>
       </c>
       <c r="L55" s="31" t="n">
-        <v>17.45</v>
+        <v>17.81</v>
       </c>
       <c r="M55" s="31" t="n">
-        <v>16.82</v>
-      </c>
-      <c r="N55" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>17.34</v>
+      </c>
+      <c r="N55" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O55" s="32" t="n">
-        <v>18.12</v>
+        <v>18.26</v>
       </c>
       <c r="P55" s="32" t="n">
-        <v>18.03</v>
+        <v>18.24</v>
       </c>
       <c r="Q55" s="33" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="R55" s="34" t="n">
-        <v>1.94</v>
+        <v>18.15</v>
+      </c>
+      <c r="R55" s="36" t="n">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="56">
@@ -4080,54 +4080,54 @@
         </is>
       </c>
       <c r="C56" s="25" t="n">
-        <v>98.48999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>97.29000000000001</v>
+        <v>97.05</v>
       </c>
       <c r="E56" s="26" t="n">
-        <v>96.29000000000001</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="F56" s="27" t="n">
-        <v>96.62</v>
+        <v>96.63</v>
       </c>
       <c r="G56" s="27" t="n">
-        <v>97.18000000000001</v>
+        <v>96.97</v>
       </c>
       <c r="H56" s="28" t="n">
+        <v>96.31999999999999</v>
+      </c>
+      <c r="I56" s="29" t="n">
         <v>95.98</v>
       </c>
-      <c r="I56" s="29" t="n">
-        <v>95.42</v>
-      </c>
       <c r="J56" s="29" t="n">
-        <v>94.78</v>
+        <v>95.67</v>
       </c>
       <c r="K56" s="30" t="n">
-        <v>95.61</v>
+        <v>96.14</v>
       </c>
       <c r="L56" s="31" t="n">
-        <v>94.61</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M56" s="31" t="n">
-        <v>93.41</v>
-      </c>
-      <c r="N56" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>94.95</v>
+      </c>
+      <c r="N56" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O56" s="32" t="n">
-        <v>95.84999999999999</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="P56" s="32" t="n">
-        <v>95.70999999999999</v>
+        <v>96.19</v>
       </c>
       <c r="Q56" s="33" t="n">
-        <v>96.05</v>
+        <v>96.3</v>
       </c>
       <c r="R56" s="34" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="57">
@@ -4142,54 +4142,54 @@
         </is>
       </c>
       <c r="C57" s="25" t="n">
-        <v>18.13</v>
+        <v>18.25</v>
       </c>
       <c r="D57" s="25" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="E57" s="26" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="F57" s="27" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="G57" s="27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H57" s="28" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="I57" s="29" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="J57" s="29" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="K57" s="30" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="L57" s="31" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="M57" s="31" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="N57" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O57" s="32" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="P57" s="32" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="Q57" s="33" t="n">
         <v>17.99</v>
       </c>
-      <c r="E57" s="26" t="n">
-        <v>17.87</v>
-      </c>
-      <c r="F57" s="27" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="G57" s="27" t="n">
-        <v>17.97</v>
-      </c>
-      <c r="H57" s="28" t="n">
-        <v>17.83</v>
-      </c>
-      <c r="I57" s="29" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="J57" s="29" t="n">
-        <v>17.69</v>
-      </c>
-      <c r="K57" s="30" t="n">
-        <v>17.79</v>
-      </c>
-      <c r="L57" s="31" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="M57" s="31" t="n">
-        <v>17.53</v>
-      </c>
-      <c r="N57" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O57" s="32" t="n">
-        <v>17.81</v>
-      </c>
-      <c r="P57" s="32" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="Q57" s="33" t="n">
-        <v>17.82</v>
-      </c>
       <c r="R57" s="34" t="n">
-        <v>0.11</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="58">
@@ -4204,37 +4204,37 @@
         </is>
       </c>
       <c r="C58" s="25" t="n">
-        <v>21.9</v>
+        <v>21.94</v>
       </c>
       <c r="D58" s="25" t="n">
-        <v>21.79</v>
+        <v>21.81</v>
       </c>
       <c r="E58" s="26" t="n">
         <v>21.7</v>
       </c>
       <c r="F58" s="27" t="n">
-        <v>21.76</v>
+        <v>21.77</v>
       </c>
       <c r="G58" s="27" t="n">
-        <v>21.79</v>
+        <v>21.81</v>
       </c>
       <c r="H58" s="28" t="n">
         <v>21.68</v>
       </c>
       <c r="I58" s="29" t="n">
-        <v>21.65</v>
+        <v>21.64</v>
       </c>
       <c r="J58" s="29" t="n">
-        <v>21.57</v>
+        <v>21.55</v>
       </c>
       <c r="K58" s="30" t="n">
         <v>21.63</v>
       </c>
       <c r="L58" s="31" t="n">
-        <v>21.54</v>
+        <v>21.52</v>
       </c>
       <c r="M58" s="31" t="n">
-        <v>21.43</v>
+        <v>21.39</v>
       </c>
       <c r="N58" s="20" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>21.72</v>
       </c>
       <c r="R58" s="34" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4266,37 +4266,37 @@
         </is>
       </c>
       <c r="C59" s="25" t="n">
-        <v>23.56</v>
+        <v>23.41</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>23.4</v>
+        <v>23.29</v>
       </c>
       <c r="E59" s="26" t="n">
-        <v>23.26</v>
+        <v>23.19</v>
       </c>
       <c r="F59" s="27" t="n">
-        <v>23.26</v>
+        <v>23.21</v>
       </c>
       <c r="G59" s="27" t="n">
-        <v>23.36</v>
+        <v>23.27</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>23.2</v>
+        <v>23.15</v>
       </c>
       <c r="I59" s="29" t="n">
-        <v>23.1</v>
+        <v>23.09</v>
       </c>
       <c r="J59" s="29" t="n">
-        <v>23.04</v>
+        <v>23.03</v>
       </c>
       <c r="K59" s="30" t="n">
-        <v>23.18</v>
+        <v>23.13</v>
       </c>
       <c r="L59" s="31" t="n">
-        <v>23.04</v>
+        <v>23.03</v>
       </c>
       <c r="M59" s="31" t="n">
-        <v>22.88</v>
+        <v>22.91</v>
       </c>
       <c r="N59" s="35" t="inlineStr">
         <is>
@@ -4304,16 +4304,16 @@
         </is>
       </c>
       <c r="O59" s="32" t="n">
-        <v>23.19</v>
+        <v>23.14</v>
       </c>
       <c r="P59" s="32" t="n">
-        <v>23.19</v>
+        <v>23.14</v>
       </c>
       <c r="Q59" s="33" t="n">
-        <v>23.16</v>
+        <v>23.14</v>
       </c>
       <c r="R59" s="36" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="60">
@@ -4328,54 +4328,54 @@
         </is>
       </c>
       <c r="C60" s="25" t="n">
-        <v>28.94</v>
+        <v>28.8</v>
       </c>
       <c r="D60" s="25" t="n">
-        <v>28.72</v>
+        <v>28.64</v>
       </c>
       <c r="E60" s="26" t="n">
-        <v>28.53</v>
+        <v>28.5</v>
       </c>
       <c r="F60" s="27" t="n">
         <v>28.55</v>
       </c>
       <c r="G60" s="27" t="n">
-        <v>28.67</v>
+        <v>28.63</v>
       </c>
       <c r="H60" s="28" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="I60" s="29" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="J60" s="29" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="K60" s="30" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="L60" s="31" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="M60" s="31" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O60" s="32" t="n">
         <v>28.45</v>
-      </c>
-      <c r="I60" s="29" t="n">
-        <v>28.33</v>
-      </c>
-      <c r="J60" s="29" t="n">
-        <v>28.23</v>
-      </c>
-      <c r="K60" s="30" t="n">
-        <v>28.41</v>
-      </c>
-      <c r="L60" s="31" t="n">
-        <v>28.22</v>
-      </c>
-      <c r="M60" s="31" t="n">
-        <v>28</v>
-      </c>
-      <c r="N60" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O60" s="32" t="n">
-        <v>28.44</v>
       </c>
       <c r="P60" s="32" t="n">
         <v>28.43</v>
       </c>
       <c r="Q60" s="33" t="n">
-        <v>28.42</v>
-      </c>
-      <c r="R60" s="36" t="n">
-        <v>-0.21</v>
+        <v>28.48</v>
+      </c>
+      <c r="R60" s="34" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="61">
@@ -4390,37 +4390,37 @@
         </is>
       </c>
       <c r="C61" s="25" t="n">
-        <v>45.92</v>
+        <v>46.25</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>45.72</v>
+        <v>45.91</v>
       </c>
       <c r="E61" s="26" t="n">
+        <v>45.63</v>
+      </c>
+      <c r="F61" s="27" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="G61" s="27" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="H61" s="28" t="n">
         <v>45.56</v>
       </c>
-      <c r="F61" s="27" t="n">
-        <v>45.65</v>
-      </c>
-      <c r="G61" s="27" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="H61" s="28" t="n">
-        <v>45.53</v>
-      </c>
       <c r="I61" s="29" t="n">
-        <v>45.45</v>
+        <v>45.42</v>
       </c>
       <c r="J61" s="29" t="n">
-        <v>45.33</v>
+        <v>45.22</v>
       </c>
       <c r="K61" s="30" t="n">
-        <v>45.44</v>
+        <v>45.43</v>
       </c>
       <c r="L61" s="31" t="n">
-        <v>45.28</v>
+        <v>45.15</v>
       </c>
       <c r="M61" s="31" t="n">
-        <v>45.08</v>
+        <v>44.81</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
@@ -4428,16 +4428,16 @@
         </is>
       </c>
       <c r="O61" s="32" t="n">
-        <v>45.49</v>
+        <v>45.51</v>
       </c>
       <c r="P61" s="32" t="n">
         <v>45.46</v>
       </c>
       <c r="Q61" s="33" t="n">
-        <v>45.58</v>
+        <v>45.62</v>
       </c>
       <c r="R61" s="34" t="n">
-        <v>0.49</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="62">
@@ -4452,54 +4452,54 @@
         </is>
       </c>
       <c r="C62" s="25" t="n">
-        <v>20.2</v>
+        <v>19.94</v>
       </c>
       <c r="D62" s="25" t="n">
-        <v>19.91</v>
+        <v>19.81</v>
       </c>
       <c r="E62" s="26" t="n">
-        <v>19.67</v>
+        <v>19.7</v>
       </c>
       <c r="F62" s="27" t="n">
-        <v>19.81</v>
+        <v>19.7</v>
       </c>
       <c r="G62" s="27" t="n">
-        <v>19.91</v>
+        <v>19.78</v>
       </c>
       <c r="H62" s="28" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="I62" s="29" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="J62" s="29" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="K62" s="30" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="L62" s="31" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="M62" s="31" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="N62" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O62" s="32" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="P62" s="32" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="Q62" s="33" t="n">
         <v>19.62</v>
       </c>
-      <c r="I62" s="29" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="J62" s="29" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="K62" s="30" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L62" s="31" t="n">
-        <v>19.26</v>
-      </c>
-      <c r="M62" s="31" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="N62" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O62" s="32" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="P62" s="32" t="n">
-        <v>19.53</v>
-      </c>
-      <c r="Q62" s="33" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R62" s="34" t="n">
-        <v>1.13</v>
+      <c r="R62" s="36" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="63">
@@ -4514,54 +4514,54 @@
         </is>
       </c>
       <c r="C63" s="25" t="n">
-        <v>16.06</v>
+        <v>15.82</v>
       </c>
       <c r="D63" s="25" t="n">
-        <v>15.74</v>
+        <v>15.62</v>
       </c>
       <c r="E63" s="26" t="n">
-        <v>15.47</v>
+        <v>15.46</v>
       </c>
       <c r="F63" s="27" t="n">
-        <v>15.55</v>
+        <v>15.54</v>
       </c>
       <c r="G63" s="27" t="n">
-        <v>15.71</v>
+        <v>15.62</v>
       </c>
       <c r="H63" s="28" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="I63" s="29" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="J63" s="29" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="K63" s="30" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="L63" s="31" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="M63" s="31" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="N63" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O63" s="32" t="n">
         <v>15.39</v>
       </c>
-      <c r="I63" s="29" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="J63" s="29" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="K63" s="30" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="L63" s="31" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="M63" s="31" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="N63" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>15.35</v>
-      </c>
       <c r="P63" s="32" t="n">
-        <v>15.32</v>
+        <v>15.36</v>
       </c>
       <c r="Q63" s="33" t="n">
-        <v>15.4</v>
+        <v>15.46</v>
       </c>
       <c r="R63" s="34" t="n">
-        <v>0.59</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="64">
@@ -4576,54 +4576,54 @@
         </is>
       </c>
       <c r="C64" s="25" t="n">
-        <v>25.7</v>
+        <v>25.54</v>
       </c>
       <c r="D64" s="25" t="n">
-        <v>25.44</v>
+        <v>25.34</v>
       </c>
       <c r="E64" s="26" t="n">
-        <v>25.22</v>
+        <v>25.18</v>
       </c>
       <c r="F64" s="27" t="n">
         <v>25.27</v>
       </c>
       <c r="G64" s="27" t="n">
-        <v>25.41</v>
+        <v>25.35</v>
       </c>
       <c r="H64" s="28" t="n">
         <v>25.15</v>
       </c>
       <c r="I64" s="29" t="n">
-        <v>25.01</v>
+        <v>25.07</v>
       </c>
       <c r="J64" s="29" t="n">
-        <v>24.89</v>
+        <v>24.95</v>
       </c>
       <c r="K64" s="30" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="L64" s="31" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M64" s="31" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="N64" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O64" s="32" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="P64" s="32" t="n">
         <v>25.08</v>
       </c>
-      <c r="L64" s="31" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="M64" s="31" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="N64" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O64" s="32" t="n">
-        <v>25.12</v>
-      </c>
-      <c r="P64" s="32" t="n">
-        <v>25.1</v>
-      </c>
       <c r="Q64" s="33" t="n">
-        <v>25.14</v>
-      </c>
-      <c r="R64" s="36" t="n">
-        <v>-0.71</v>
+        <v>25.2</v>
+      </c>
+      <c r="R64" s="34" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="65">
@@ -4638,19 +4638,19 @@
         </is>
       </c>
       <c r="C65" s="25" t="n">
-        <v>7.46</v>
+        <v>7.4</v>
       </c>
       <c r="D65" s="25" t="n">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="E65" s="26" t="n">
-        <v>7.35</v>
+        <v>7.33</v>
       </c>
       <c r="F65" s="27" t="n">
-        <v>7.35</v>
+        <v>7.33</v>
       </c>
       <c r="G65" s="27" t="n">
-        <v>7.38</v>
+        <v>7.36</v>
       </c>
       <c r="H65" s="28" t="n">
         <v>7.32</v>
@@ -4659,16 +4659,16 @@
         <v>7.29</v>
       </c>
       <c r="J65" s="29" t="n">
-        <v>7.26</v>
+        <v>7.28</v>
       </c>
       <c r="K65" s="30" t="n">
         <v>7.31</v>
       </c>
       <c r="L65" s="31" t="n">
-        <v>7.26</v>
+        <v>7.28</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>7.2</v>
+        <v>7.24</v>
       </c>
       <c r="N65" s="35" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="O65" s="32" t="n">
-        <v>7.32</v>
+        <v>7.31</v>
       </c>
       <c r="P65" s="32" t="n">
-        <v>7.32</v>
+        <v>7.31</v>
       </c>
       <c r="Q65" s="33" t="n">
         <v>7.31</v>
@@ -4703,48 +4703,48 @@
         <v>5.01</v>
       </c>
       <c r="D66" s="25" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="E66" s="26" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="F66" s="27" t="n">
         <v>4.95</v>
-      </c>
-      <c r="F66" s="27" t="n">
-        <v>4.96</v>
       </c>
       <c r="G66" s="27" t="n">
         <v>4.97</v>
       </c>
       <c r="H66" s="28" t="n">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
       <c r="I66" s="29" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="J66" s="29" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="K66" s="30" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="L66" s="31" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="M66" s="31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="N66" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O66" s="32" t="n">
         <v>4.93</v>
       </c>
-      <c r="J66" s="29" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K66" s="30" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="L66" s="31" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="M66" s="31" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="N66" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>4.94</v>
-      </c>
       <c r="P66" s="32" t="n">
-        <v>4.94</v>
+        <v>4.92</v>
       </c>
       <c r="Q66" s="33" t="n">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
       <c r="R66" s="36" t="n">
         <v>-0.2</v>
@@ -4762,54 +4762,54 @@
         </is>
       </c>
       <c r="C67" s="25" t="n">
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="D67" s="25" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="E67" s="26" t="n">
         <v>5.01</v>
       </c>
-      <c r="E67" s="26" t="n">
+      <c r="F67" s="27" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="G67" s="27" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="H67" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I67" s="29" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="J67" s="29" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="K67" s="30" t="n">
         <v>4.98</v>
       </c>
-      <c r="F67" s="27" t="n">
+      <c r="L67" s="31" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="M67" s="31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="N67" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="P67" s="32" t="n">
         <v>4.98</v>
       </c>
-      <c r="G67" s="27" t="n">
+      <c r="Q67" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="H67" s="28" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="I67" s="29" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="J67" s="29" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="K67" s="30" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="L67" s="31" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="M67" s="31" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="N67" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="Q67" s="33" t="n">
-        <v>4.96</v>
-      </c>
       <c r="R67" s="34" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -4824,37 +4824,37 @@
         </is>
       </c>
       <c r="C68" s="25" t="n">
-        <v>67.11</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="D68" s="25" t="n">
-        <v>66.36</v>
+        <v>67.31</v>
       </c>
       <c r="E68" s="26" t="n">
-        <v>65.73999999999999</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="F68" s="27" t="n">
-        <v>65.88</v>
+        <v>66.98</v>
       </c>
       <c r="G68" s="27" t="n">
-        <v>66.27</v>
+        <v>67.37</v>
       </c>
       <c r="H68" s="28" t="n">
-        <v>65.52</v>
+        <v>66.22</v>
       </c>
       <c r="I68" s="29" t="n">
-        <v>65.13</v>
+        <v>65.83</v>
       </c>
       <c r="J68" s="29" t="n">
-        <v>64.77</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="K68" s="30" t="n">
-        <v>65.31999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="L68" s="31" t="n">
-        <v>64.69</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="M68" s="31" t="n">
-        <v>63.94</v>
+        <v>63.59</v>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
@@ -4862,16 +4862,16 @@
         </is>
       </c>
       <c r="O68" s="32" t="n">
-        <v>65.45</v>
+        <v>66</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>65.37</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="Q68" s="33" t="n">
-        <v>65.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="R68" s="34" t="n">
-        <v>0.31</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="69">
@@ -4886,54 +4886,54 @@
         </is>
       </c>
       <c r="C69" s="25" t="n">
-        <v>67.73</v>
+        <v>69.28</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>67.03</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="E69" s="26" t="n">
-        <v>66.45</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="F69" s="27" t="n">
-        <v>66.7</v>
+        <v>67.63</v>
       </c>
       <c r="G69" s="27" t="n">
-        <v>67</v>
+        <v>68.12</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>66.3</v>
+        <v>67.02</v>
       </c>
       <c r="I69" s="29" t="n">
-        <v>66</v>
+        <v>66.53</v>
       </c>
       <c r="J69" s="29" t="n">
-        <v>65.59999999999999</v>
+        <v>65.92</v>
       </c>
       <c r="K69" s="30" t="n">
-        <v>66.05</v>
+        <v>66.64</v>
       </c>
       <c r="L69" s="31" t="n">
-        <v>65.47</v>
+        <v>65.72</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>64.77</v>
-      </c>
-      <c r="N69" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>64.62</v>
+      </c>
+      <c r="N69" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>66.2</v>
+        <v>66.87</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>66.11</v>
+        <v>66.73</v>
       </c>
       <c r="Q69" s="33" t="n">
-        <v>66.40000000000001</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="R69" s="34" t="n">
-        <v>0.53</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="70">
@@ -4948,37 +4948,37 @@
         </is>
       </c>
       <c r="C70" s="25" t="n">
-        <v>86.97</v>
+        <v>85.3</v>
       </c>
       <c r="D70" s="25" t="n">
-        <v>85.31999999999999</v>
+        <v>84.25</v>
       </c>
       <c r="E70" s="26" t="n">
-        <v>83.94</v>
+        <v>83.37</v>
       </c>
       <c r="F70" s="27" t="n">
-        <v>83.81999999999999</v>
+        <v>83.55</v>
       </c>
       <c r="G70" s="27" t="n">
-        <v>84.88</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H70" s="28" t="n">
-        <v>83.23</v>
+        <v>83.05</v>
       </c>
       <c r="I70" s="29" t="n">
-        <v>82.17</v>
+        <v>82.5</v>
       </c>
       <c r="J70" s="29" t="n">
-        <v>81.58</v>
+        <v>82</v>
       </c>
       <c r="K70" s="30" t="n">
-        <v>83.01000000000001</v>
+        <v>82.78</v>
       </c>
       <c r="L70" s="31" t="n">
-        <v>81.63</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>79.98</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="N70" s="35" t="inlineStr">
         <is>
@@ -4986,16 +4986,16 @@
         </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>83.19</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>83.14</v>
+        <v>82.86</v>
       </c>
       <c r="Q70" s="33" t="n">
-        <v>82.75</v>
-      </c>
-      <c r="R70" s="36" t="n">
-        <v>-1.55</v>
+        <v>83</v>
+      </c>
+      <c r="R70" s="34" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="71">
@@ -5010,54 +5010,54 @@
         </is>
       </c>
       <c r="C71" s="25" t="n">
-        <v>124.92</v>
+        <v>124.38</v>
       </c>
       <c r="D71" s="25" t="n">
-        <v>122.62</v>
+        <v>121.98</v>
       </c>
       <c r="E71" s="26" t="n">
-        <v>120.69</v>
+        <v>119.97</v>
       </c>
       <c r="F71" s="27" t="n">
-        <v>120.77</v>
+        <v>121.23</v>
       </c>
       <c r="G71" s="27" t="n">
-        <v>122.13</v>
+        <v>122.07</v>
       </c>
       <c r="H71" s="28" t="n">
-        <v>119.83</v>
+        <v>119.67</v>
       </c>
       <c r="I71" s="29" t="n">
-        <v>118.47</v>
+        <v>118.83</v>
       </c>
       <c r="J71" s="29" t="n">
-        <v>117.53</v>
+        <v>117.27</v>
       </c>
       <c r="K71" s="30" t="n">
-        <v>119.41</v>
+        <v>118.63</v>
       </c>
       <c r="L71" s="31" t="n">
-        <v>117.48</v>
+        <v>116.62</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>115.18</v>
-      </c>
-      <c r="N71" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>114.22</v>
+      </c>
+      <c r="N71" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>119.71</v>
+        <v>119.24</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>119.59</v>
+        <v>118.82</v>
       </c>
       <c r="Q71" s="33" t="n">
-        <v>119.4</v>
-      </c>
-      <c r="R71" s="36" t="n">
-        <v>-1.16</v>
+        <v>120.4</v>
+      </c>
+      <c r="R71" s="34" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="72">
@@ -5072,54 +5072,54 @@
         </is>
       </c>
       <c r="C72" s="25" t="n">
-        <v>24.99</v>
+        <v>24.87</v>
       </c>
       <c r="D72" s="25" t="n">
-        <v>24.82</v>
+        <v>24.77</v>
       </c>
       <c r="E72" s="26" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="F72" s="27" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="G72" s="27" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="H72" s="28" t="n">
         <v>24.67</v>
       </c>
-      <c r="F72" s="27" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="G72" s="27" t="n">
-        <v>24.79</v>
-      </c>
-      <c r="H72" s="28" t="n">
+      <c r="I72" s="29" t="n">
         <v>24.62</v>
       </c>
-      <c r="I72" s="29" t="n">
-        <v>24.52</v>
-      </c>
       <c r="J72" s="29" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="K72" s="30" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="L72" s="31" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="M72" s="31" t="n">
         <v>24.45</v>
       </c>
-      <c r="K72" s="30" t="n">
-        <v>24.58</v>
-      </c>
-      <c r="L72" s="31" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="M72" s="31" t="n">
-        <v>24.26</v>
-      </c>
-      <c r="N72" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+      <c r="N72" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>24.6</v>
+        <v>24.65</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>24.59</v>
+        <v>24.64</v>
       </c>
       <c r="Q72" s="33" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="R72" s="36" t="n">
-        <v>-0.12</v>
+        <v>24.68</v>
+      </c>
+      <c r="R72" s="34" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="73">
@@ -5134,37 +5134,37 @@
         </is>
       </c>
       <c r="C73" s="25" t="n">
-        <v>21.23</v>
+        <v>21.66</v>
       </c>
       <c r="D73" s="25" t="n">
-        <v>20.99</v>
+        <v>21.19</v>
       </c>
       <c r="E73" s="26" t="n">
-        <v>20.79</v>
+        <v>20.8</v>
       </c>
       <c r="F73" s="27" t="n">
-        <v>20.76</v>
+        <v>20.88</v>
       </c>
       <c r="G73" s="27" t="n">
-        <v>20.92</v>
+        <v>21.13</v>
       </c>
       <c r="H73" s="28" t="n">
-        <v>20.68</v>
+        <v>20.66</v>
       </c>
       <c r="I73" s="29" t="n">
-        <v>20.52</v>
+        <v>20.41</v>
       </c>
       <c r="J73" s="29" t="n">
-        <v>20.44</v>
+        <v>20.19</v>
       </c>
       <c r="K73" s="30" t="n">
-        <v>20.65</v>
+        <v>20.53</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>20.45</v>
+        <v>20.14</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>20.21</v>
+        <v>19.67</v>
       </c>
       <c r="N73" s="35" t="inlineStr">
         <is>
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="O73" s="32" t="n">
-        <v>20.68</v>
+        <v>20.61</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>20.67</v>
+        <v>20.57</v>
       </c>
       <c r="Q73" s="33" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R73" s="36" t="n">
-        <v>-0.72</v>
+        <v>20.64</v>
+      </c>
+      <c r="R73" s="34" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="74">
@@ -5196,54 +5196,54 @@
         </is>
       </c>
       <c r="C74" s="25" t="n">
-        <v>238.35</v>
+        <v>236.91</v>
       </c>
       <c r="D74" s="25" t="n">
-        <v>234.55</v>
+        <v>234.31</v>
       </c>
       <c r="E74" s="26" t="n">
-        <v>231.36</v>
+        <v>232.13</v>
       </c>
       <c r="F74" s="27" t="n">
-        <v>232.13</v>
+        <v>233.37</v>
       </c>
       <c r="G74" s="27" t="n">
-        <v>234.07</v>
+        <v>234.33</v>
       </c>
       <c r="H74" s="28" t="n">
-        <v>230.27</v>
+        <v>231.73</v>
       </c>
       <c r="I74" s="29" t="n">
-        <v>228.33</v>
+        <v>230.77</v>
       </c>
       <c r="J74" s="29" t="n">
-        <v>226.47</v>
+        <v>229.13</v>
       </c>
       <c r="K74" s="30" t="n">
-        <v>229.24</v>
+        <v>230.67</v>
       </c>
       <c r="L74" s="31" t="n">
-        <v>226.05</v>
+        <v>228.49</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>222.25</v>
-      </c>
-      <c r="N74" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>225.89</v>
+      </c>
+      <c r="N74" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O74" s="32" t="n">
-        <v>229.9</v>
+        <v>231.3</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>229.53</v>
+        <v>230.87</v>
       </c>
       <c r="Q74" s="33" t="n">
-        <v>230.2</v>
-      </c>
-      <c r="R74" s="36" t="n">
-        <v>-0.26</v>
+        <v>232.4</v>
+      </c>
+      <c r="R74" s="34" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="75">
@@ -5258,54 +5258,54 @@
         </is>
       </c>
       <c r="C75" s="25" t="n">
-        <v>15.83</v>
+        <v>15.76</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>15.51</v>
+        <v>15.53</v>
       </c>
       <c r="E75" s="26" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="F75" s="27" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="G75" s="27" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="H75" s="28" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="I75" s="29" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="J75" s="29" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="K75" s="30" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="M75" s="31" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="N75" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="n">
         <v>15.24</v>
       </c>
-      <c r="F75" s="27" t="n">
-        <v>15.36</v>
-      </c>
-      <c r="G75" s="27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H75" s="28" t="n">
-        <v>15.18</v>
-      </c>
-      <c r="I75" s="29" t="n">
-        <v>15.04</v>
-      </c>
-      <c r="J75" s="29" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="K75" s="30" t="n">
-        <v>15.06</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="N75" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>15.13</v>
-      </c>
       <c r="P75" s="32" t="n">
-        <v>15.09</v>
+        <v>15.23</v>
       </c>
       <c r="Q75" s="33" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="R75" s="34" t="n">
-        <v>1.67</v>
+        <v>15.2</v>
+      </c>
+      <c r="R75" s="36" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="76">
@@ -5320,37 +5320,37 @@
         </is>
       </c>
       <c r="C76" s="25" t="n">
-        <v>37.14</v>
+        <v>36.49</v>
       </c>
       <c r="D76" s="25" t="n">
-        <v>36.3</v>
+        <v>35.73</v>
       </c>
       <c r="E76" s="26" t="n">
-        <v>35.6</v>
+        <v>35.09</v>
       </c>
       <c r="F76" s="27" t="n">
-        <v>35.55</v>
+        <v>35.26</v>
       </c>
       <c r="G76" s="27" t="n">
-        <v>36.09</v>
+        <v>35.64</v>
       </c>
       <c r="H76" s="28" t="n">
-        <v>35.25</v>
+        <v>34.88</v>
       </c>
       <c r="I76" s="29" t="n">
-        <v>34.71</v>
+        <v>34.5</v>
       </c>
       <c r="J76" s="29" t="n">
-        <v>34.41</v>
+        <v>34.12</v>
       </c>
       <c r="K76" s="30" t="n">
-        <v>35.12</v>
+        <v>34.67</v>
       </c>
       <c r="L76" s="31" t="n">
-        <v>34.42</v>
+        <v>34.03</v>
       </c>
       <c r="M76" s="31" t="n">
-        <v>33.58</v>
+        <v>33.27</v>
       </c>
       <c r="N76" s="35" t="inlineStr">
         <is>
@@ -5358,16 +5358,16 @@
         </is>
       </c>
       <c r="O76" s="32" t="n">
-        <v>35.22</v>
+        <v>34.8</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>35.19</v>
+        <v>34.73</v>
       </c>
       <c r="Q76" s="33" t="n">
-        <v>35.02</v>
+        <v>34.88</v>
       </c>
       <c r="R76" s="36" t="n">
-        <v>-1.57</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="77">
@@ -5382,54 +5382,54 @@
         </is>
       </c>
       <c r="C77" s="25" t="n">
-        <v>28.06</v>
+        <v>27.07</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>27.34</v>
+        <v>26.77</v>
       </c>
       <c r="E77" s="26" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="F77" s="27" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G77" s="27" t="n">
         <v>26.74</v>
       </c>
-      <c r="F77" s="27" t="n">
-        <v>26.66</v>
-      </c>
-      <c r="G77" s="27" t="n">
-        <v>27.14</v>
-      </c>
       <c r="H77" s="28" t="n">
-        <v>26.42</v>
+        <v>26.44</v>
       </c>
       <c r="I77" s="29" t="n">
-        <v>25.94</v>
+        <v>26.3</v>
       </c>
       <c r="J77" s="29" t="n">
-        <v>25.7</v>
+        <v>26.14</v>
       </c>
       <c r="K77" s="30" t="n">
-        <v>26.34</v>
+        <v>26.35</v>
       </c>
       <c r="L77" s="31" t="n">
-        <v>25.74</v>
+        <v>26.09</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>25.02</v>
-      </c>
-      <c r="N77" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>25.79</v>
+      </c>
+      <c r="N77" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>26.41</v>
+        <v>26.4</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>26.39</v>
+        <v>26.37</v>
       </c>
       <c r="Q77" s="33" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="R77" s="36" t="n">
-        <v>-2.17</v>
+        <v>26.46</v>
+      </c>
+      <c r="R77" s="34" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="78">
@@ -5444,37 +5444,37 @@
         </is>
       </c>
       <c r="C78" s="25" t="n">
-        <v>46.77</v>
+        <v>47.44</v>
       </c>
       <c r="D78" s="25" t="n">
-        <v>44.81</v>
+        <v>45.86</v>
       </c>
       <c r="E78" s="26" t="n">
-        <v>43.17</v>
+        <v>44.53</v>
       </c>
       <c r="F78" s="27" t="n">
-        <v>44.12</v>
+        <v>45.29</v>
       </c>
       <c r="G78" s="27" t="n">
-        <v>44.84</v>
+        <v>45.87</v>
       </c>
       <c r="H78" s="28" t="n">
-        <v>42.88</v>
+        <v>44.29</v>
       </c>
       <c r="I78" s="29" t="n">
-        <v>42.16</v>
+        <v>43.71</v>
       </c>
       <c r="J78" s="29" t="n">
-        <v>40.92</v>
+        <v>42.71</v>
       </c>
       <c r="K78" s="30" t="n">
-        <v>42.07</v>
+        <v>43.65</v>
       </c>
       <c r="L78" s="31" t="n">
-        <v>40.43</v>
+        <v>42.32</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>38.47</v>
+        <v>40.74</v>
       </c>
       <c r="N78" s="20" t="inlineStr">
         <is>
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>42.55</v>
+        <v>44.03</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>42.22</v>
+        <v>43.77</v>
       </c>
       <c r="Q78" s="33" t="n">
-        <v>43.4</v>
+        <v>44.7</v>
       </c>
       <c r="R78" s="34" t="n">
-        <v>4.08</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -5509,51 +5509,51 @@
         <v>5.54</v>
       </c>
       <c r="D79" s="25" t="n">
-        <v>5.51</v>
+        <v>5.5</v>
       </c>
       <c r="E79" s="26" t="n">
-        <v>5.48</v>
+        <v>5.47</v>
       </c>
       <c r="F79" s="27" t="n">
         <v>5.49</v>
       </c>
       <c r="G79" s="27" t="n">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="H79" s="28" t="n">
         <v>5.47</v>
       </c>
       <c r="I79" s="29" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="J79" s="29" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="K79" s="30" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="N79" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
         <v>5.46</v>
       </c>
-      <c r="J79" s="29" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="K79" s="30" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="N79" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>5.47</v>
-      </c>
       <c r="P79" s="32" t="n">
-        <v>5.47</v>
+        <v>5.45</v>
       </c>
       <c r="Q79" s="33" t="n">
-        <v>5.47</v>
+        <v>5.48</v>
       </c>
       <c r="R79" s="34" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="80">
@@ -5568,37 +5568,37 @@
         </is>
       </c>
       <c r="C80" s="25" t="n">
-        <v>20.49</v>
+        <v>20.32</v>
       </c>
       <c r="D80" s="25" t="n">
-        <v>19.88</v>
+        <v>19.78</v>
       </c>
       <c r="E80" s="26" t="n">
-        <v>19.37</v>
+        <v>19.33</v>
       </c>
       <c r="F80" s="27" t="n">
-        <v>19.48</v>
+        <v>19.33</v>
       </c>
       <c r="G80" s="27" t="n">
-        <v>19.8</v>
+        <v>19.66</v>
       </c>
       <c r="H80" s="28" t="n">
-        <v>19.19</v>
+        <v>19.12</v>
       </c>
       <c r="I80" s="29" t="n">
-        <v>18.87</v>
+        <v>18.79</v>
       </c>
       <c r="J80" s="29" t="n">
         <v>18.58</v>
       </c>
       <c r="K80" s="30" t="n">
-        <v>19.02</v>
+        <v>19.03</v>
       </c>
       <c r="L80" s="31" t="n">
-        <v>18.51</v>
+        <v>18.58</v>
       </c>
       <c r="M80" s="31" t="n">
-        <v>17.9</v>
+        <v>18.04</v>
       </c>
       <c r="N80" s="35" t="inlineStr">
         <is>
@@ -5606,16 +5606,16 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>19.13</v>
+        <v>19.1</v>
       </c>
       <c r="P80" s="32" t="n">
         <v>19.07</v>
       </c>
       <c r="Q80" s="33" t="n">
-        <v>19.17</v>
+        <v>19</v>
       </c>
       <c r="R80" s="36" t="n">
-        <v>-2.49</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="81">
@@ -5630,37 +5630,37 @@
         </is>
       </c>
       <c r="C81" s="25" t="n">
-        <v>84.2</v>
+        <v>83.64</v>
       </c>
       <c r="D81" s="25" t="n">
-        <v>82.90000000000001</v>
+        <v>82.44</v>
       </c>
       <c r="E81" s="26" t="n">
-        <v>81.81</v>
+        <v>81.44</v>
       </c>
       <c r="F81" s="27" t="n">
-        <v>82</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="G81" s="27" t="n">
-        <v>82.7</v>
+        <v>82.23</v>
       </c>
       <c r="H81" s="28" t="n">
-        <v>81.40000000000001</v>
+        <v>81.03</v>
       </c>
       <c r="I81" s="29" t="n">
-        <v>80.7</v>
+        <v>80.37</v>
       </c>
       <c r="J81" s="29" t="n">
-        <v>80.09999999999999</v>
+        <v>79.83</v>
       </c>
       <c r="K81" s="30" t="n">
-        <v>81.09</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="L81" s="31" t="n">
-        <v>80</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="M81" s="31" t="n">
-        <v>78.7</v>
+        <v>78.56</v>
       </c>
       <c r="N81" s="35" t="inlineStr">
         <is>
@@ -5668,16 +5668,16 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>81.29000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>81.19</v>
+        <v>80.86</v>
       </c>
       <c r="Q81" s="33" t="n">
-        <v>81.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="R81" s="36" t="n">
-        <v>-0.79</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="82">
@@ -5692,54 +5692,54 @@
         </is>
       </c>
       <c r="C82" s="25" t="n">
-        <v>4.74</v>
+        <v>5.03</v>
       </c>
       <c r="D82" s="25" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="E82" s="26" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="F82" s="27" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="G82" s="27" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H82" s="28" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="I82" s="29" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="J82" s="29" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="K82" s="30" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="L82" s="31" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="M82" s="31" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="N82" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="P82" s="32" t="n">
         <v>4.7</v>
       </c>
-      <c r="E82" s="26" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="F82" s="27" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="G82" s="27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H82" s="28" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="I82" s="29" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="J82" s="29" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="K82" s="30" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="L82" s="31" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="M82" s="31" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="N82" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>4.65</v>
-      </c>
       <c r="Q82" s="33" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="R82" s="36" t="n">
-        <v>-0.21</v>
+        <v>4.72</v>
+      </c>
+      <c r="R82" s="34" t="n">
+        <v>1.51</v>
       </c>
     </row>
     <row r="83">
@@ -5754,54 +5754,54 @@
         </is>
       </c>
       <c r="C83" s="25" t="n">
-        <v>62.96</v>
+        <v>62.21</v>
       </c>
       <c r="D83" s="25" t="n">
-        <v>62.21</v>
+        <v>61.71</v>
       </c>
       <c r="E83" s="26" t="n">
-        <v>61.59</v>
+        <v>61.29</v>
       </c>
       <c r="F83" s="27" t="n">
         <v>61.5</v>
       </c>
       <c r="G83" s="27" t="n">
-        <v>62</v>
+        <v>61.7</v>
       </c>
       <c r="H83" s="28" t="n">
-        <v>61.25</v>
+        <v>61.2</v>
       </c>
       <c r="I83" s="29" t="n">
-        <v>60.75</v>
+        <v>61</v>
       </c>
       <c r="J83" s="29" t="n">
-        <v>60.5</v>
+        <v>60.7</v>
       </c>
       <c r="K83" s="30" t="n">
-        <v>61.16</v>
+        <v>61.01</v>
       </c>
       <c r="L83" s="31" t="n">
-        <v>60.54</v>
+        <v>60.59</v>
       </c>
       <c r="M83" s="31" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="N83" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>60.09</v>
+      </c>
+      <c r="N83" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O83" s="32" t="n">
-        <v>61.24</v>
+        <v>61.12</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>61.22</v>
+        <v>61.05</v>
       </c>
       <c r="Q83" s="33" t="n">
-        <v>61</v>
-      </c>
-      <c r="R83" s="36" t="n">
-        <v>-1.21</v>
+        <v>61.3</v>
+      </c>
+      <c r="R83" s="34" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="84">
@@ -5816,54 +5816,54 @@
         </is>
       </c>
       <c r="C84" s="25" t="n">
-        <v>39.35</v>
+        <v>39.87</v>
       </c>
       <c r="D84" s="25" t="n">
-        <v>38.91</v>
+        <v>39.33</v>
       </c>
       <c r="E84" s="26" t="n">
-        <v>38.54</v>
+        <v>38.88</v>
       </c>
       <c r="F84" s="27" t="n">
-        <v>38.56</v>
+        <v>38.85</v>
       </c>
       <c r="G84" s="27" t="n">
-        <v>38.82</v>
+        <v>39.19</v>
       </c>
       <c r="H84" s="28" t="n">
-        <v>38.38</v>
+        <v>38.65</v>
       </c>
       <c r="I84" s="29" t="n">
-        <v>38.12</v>
+        <v>38.31</v>
       </c>
       <c r="J84" s="29" t="n">
-        <v>37.94</v>
+        <v>38.11</v>
       </c>
       <c r="K84" s="30" t="n">
-        <v>38.3</v>
+        <v>38.58</v>
       </c>
       <c r="L84" s="31" t="n">
-        <v>37.93</v>
+        <v>38.13</v>
       </c>
       <c r="M84" s="31" t="n">
-        <v>37.49</v>
-      </c>
-      <c r="N84" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>37.59</v>
+      </c>
+      <c r="N84" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O84" s="32" t="n">
-        <v>38.36</v>
+        <v>38.64</v>
       </c>
       <c r="P84" s="32" t="n">
-        <v>38.33</v>
+        <v>38.62</v>
       </c>
       <c r="Q84" s="33" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="R84" s="36" t="n">
-        <v>-0.16</v>
+        <v>38.5</v>
+      </c>
+      <c r="R84" s="34" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="85">
@@ -5878,54 +5878,54 @@
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>94.48</v>
+        <v>95.09</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>93.38</v>
+        <v>93.89</v>
       </c>
       <c r="E85" s="26" t="n">
-        <v>92.45999999999999</v>
+        <v>92.89</v>
       </c>
       <c r="F85" s="27" t="n">
-        <v>92.40000000000001</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="G85" s="27" t="n">
-        <v>93.09999999999999</v>
+        <v>93.75</v>
       </c>
       <c r="H85" s="28" t="n">
-        <v>92</v>
+        <v>92.55</v>
       </c>
       <c r="I85" s="29" t="n">
-        <v>91.3</v>
+        <v>91.95</v>
       </c>
       <c r="J85" s="29" t="n">
-        <v>90.90000000000001</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="K85" s="30" t="n">
-        <v>91.84</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="L85" s="31" t="n">
-        <v>90.92</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="M85" s="31" t="n">
-        <v>89.81999999999999</v>
-      </c>
-      <c r="N85" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>90.01000000000001</v>
+      </c>
+      <c r="N85" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O85" s="32" t="n">
-        <v>91.95999999999999</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="P85" s="32" t="n">
-        <v>91.93000000000001</v>
+        <v>92.31</v>
       </c>
       <c r="Q85" s="33" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="R85" s="36" t="n">
-        <v>-0.97</v>
+        <v>92.55</v>
+      </c>
+      <c r="R85" s="34" t="n">
+        <v>0.93</v>
       </c>
     </row>
     <row r="86">
@@ -5940,54 +5940,54 @@
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>16.97</v>
+        <v>16.88</v>
       </c>
       <c r="D86" s="25" t="n">
-        <v>16.7</v>
+        <v>16.61</v>
       </c>
       <c r="E86" s="26" t="n">
-        <v>16.47</v>
+        <v>16.38</v>
       </c>
       <c r="F86" s="27" t="n">
-        <v>16.47</v>
+        <v>16.49</v>
       </c>
       <c r="G86" s="27" t="n">
-        <v>16.63</v>
+        <v>16.6</v>
       </c>
       <c r="H86" s="28" t="n">
-        <v>16.36</v>
+        <v>16.33</v>
       </c>
       <c r="I86" s="29" t="n">
-        <v>16.2</v>
+        <v>16.22</v>
       </c>
       <c r="J86" s="29" t="n">
-        <v>16.09</v>
+        <v>16.06</v>
       </c>
       <c r="K86" s="30" t="n">
-        <v>16.32</v>
+        <v>16.23</v>
       </c>
       <c r="L86" s="31" t="n">
-        <v>16.09</v>
+        <v>16</v>
       </c>
       <c r="M86" s="31" t="n">
-        <v>15.82</v>
-      </c>
-      <c r="N86" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>15.73</v>
+      </c>
+      <c r="N86" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O86" s="32" t="n">
-        <v>16.35</v>
+        <v>16.29</v>
       </c>
       <c r="P86" s="32" t="n">
-        <v>16.34</v>
+        <v>16.25</v>
       </c>
       <c r="Q86" s="33" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="R86" s="36" t="n">
-        <v>-1.39</v>
+        <v>16.38</v>
+      </c>
+      <c r="R86" s="34" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="87">
@@ -6002,54 +6002,54 @@
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>123.75</v>
+        <v>122.97</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>122.05</v>
+        <v>121.57</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>120.63</v>
+        <v>120.39</v>
       </c>
       <c r="F87" s="27" t="n">
-        <v>121.37</v>
+        <v>120.7</v>
       </c>
       <c r="G87" s="27" t="n">
-        <v>122.03</v>
+        <v>121.4</v>
       </c>
       <c r="H87" s="28" t="n">
-        <v>120.33</v>
+        <v>120</v>
       </c>
       <c r="I87" s="29" t="n">
-        <v>119.67</v>
+        <v>119.3</v>
       </c>
       <c r="J87" s="29" t="n">
-        <v>118.63</v>
+        <v>118.6</v>
       </c>
       <c r="K87" s="30" t="n">
-        <v>119.67</v>
+        <v>119.61</v>
       </c>
       <c r="L87" s="31" t="n">
-        <v>118.25</v>
+        <v>118.43</v>
       </c>
       <c r="M87" s="31" t="n">
-        <v>116.55</v>
-      </c>
-      <c r="N87" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>117.03</v>
+      </c>
+      <c r="N87" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="32" t="n">
-        <v>120.07</v>
+        <v>119.86</v>
       </c>
       <c r="P87" s="32" t="n">
-        <v>119.81</v>
+        <v>119.72</v>
       </c>
       <c r="Q87" s="33" t="n">
-        <v>120.7</v>
-      </c>
-      <c r="R87" s="34" t="n">
-        <v>0.84</v>
+        <v>120</v>
+      </c>
+      <c r="R87" s="36" t="n">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="88">
@@ -6064,54 +6064,54 @@
         </is>
       </c>
       <c r="C88" s="25" t="n">
-        <v>64.65000000000001</v>
+        <v>65.52</v>
       </c>
       <c r="D88" s="25" t="n">
-        <v>62.95</v>
+        <v>63.47</v>
       </c>
       <c r="E88" s="26" t="n">
-        <v>61.53</v>
+        <v>61.75</v>
       </c>
       <c r="F88" s="27" t="n">
-        <v>61.43</v>
+        <v>62.62</v>
       </c>
       <c r="G88" s="27" t="n">
-        <v>62.52</v>
+        <v>63.43</v>
       </c>
       <c r="H88" s="28" t="n">
-        <v>60.82</v>
+        <v>61.38</v>
       </c>
       <c r="I88" s="29" t="n">
-        <v>59.73</v>
+        <v>60.57</v>
       </c>
       <c r="J88" s="29" t="n">
-        <v>59.12</v>
+        <v>59.33</v>
       </c>
       <c r="K88" s="30" t="n">
-        <v>60.57</v>
+        <v>60.6</v>
       </c>
       <c r="L88" s="31" t="n">
-        <v>59.15</v>
+        <v>58.88</v>
       </c>
       <c r="M88" s="31" t="n">
-        <v>57.45</v>
-      </c>
-      <c r="N88" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>56.83</v>
+      </c>
+      <c r="N88" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O88" s="32" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="P88" s="32" t="n">
         <v>60.76</v>
       </c>
-      <c r="P88" s="32" t="n">
-        <v>60.71</v>
-      </c>
       <c r="Q88" s="33" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="R88" s="36" t="n">
-        <v>-0.9</v>
+        <v>61.8</v>
+      </c>
+      <c r="R88" s="34" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="89">
@@ -6126,37 +6126,37 @@
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>10.46</v>
+        <v>10.2</v>
       </c>
       <c r="D89" s="25" t="n">
-        <v>10.2</v>
+        <v>10.05</v>
       </c>
       <c r="E89" s="26" t="n">
-        <v>9.98</v>
+        <v>9.93</v>
       </c>
       <c r="F89" s="27" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="G89" s="27" t="n">
-        <v>10.15</v>
+        <v>10.05</v>
       </c>
       <c r="H89" s="28" t="n">
-        <v>9.890000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="I89" s="29" t="n">
-        <v>9.74</v>
+        <v>9.84</v>
       </c>
       <c r="J89" s="29" t="n">
-        <v>9.630000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="K89" s="30" t="n">
         <v>9.84</v>
       </c>
       <c r="L89" s="31" t="n">
-        <v>9.619999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M89" s="31" t="n">
-        <v>9.359999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="N89" s="20" t="inlineStr">
         <is>
@@ -6164,16 +6164,16 @@
         </is>
       </c>
       <c r="O89" s="32" t="n">
-        <v>9.869999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="P89" s="32" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="Q89" s="33" t="n">
-        <v>9.85</v>
+        <v>9.93</v>
       </c>
       <c r="R89" s="34" t="n">
-        <v>0.51</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -6188,54 +6188,54 @@
         </is>
       </c>
       <c r="C90" s="25" t="n">
-        <v>19.75</v>
+        <v>18.93</v>
       </c>
       <c r="D90" s="25" t="n">
-        <v>18.89</v>
+        <v>18.34</v>
       </c>
       <c r="E90" s="26" t="n">
-        <v>18.17</v>
+        <v>17.85</v>
       </c>
       <c r="F90" s="27" t="n">
-        <v>18.19</v>
+        <v>17.84</v>
       </c>
       <c r="G90" s="27" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="H90" s="28" t="n">
-        <v>17.84</v>
+        <v>17.61</v>
       </c>
       <c r="I90" s="29" t="n">
-        <v>17.33</v>
+        <v>17.25</v>
       </c>
       <c r="J90" s="29" t="n">
-        <v>16.98</v>
+        <v>17.02</v>
       </c>
       <c r="K90" s="30" t="n">
-        <v>17.69</v>
+        <v>17.52</v>
       </c>
       <c r="L90" s="31" t="n">
-        <v>16.97</v>
+        <v>17.03</v>
       </c>
       <c r="M90" s="31" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="N90" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.44</v>
+      </c>
+      <c r="N90" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O90" s="32" t="n">
-        <v>17.8</v>
+        <v>17.59</v>
       </c>
       <c r="P90" s="32" t="n">
-        <v>17.76</v>
+        <v>17.57</v>
       </c>
       <c r="Q90" s="33" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="R90" s="34" t="n">
-        <v>1.14</v>
+        <v>17.47</v>
+      </c>
+      <c r="R90" s="36" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="91">
@@ -6250,54 +6250,54 @@
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>18.57</v>
+        <v>18.38</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>18.35</v>
+        <v>18.21</v>
       </c>
       <c r="E91" s="26" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="F91" s="27" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="G91" s="27" t="n">
         <v>18.16</v>
       </c>
-      <c r="F91" s="27" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="G91" s="27" t="n">
-        <v>18.29</v>
-      </c>
       <c r="H91" s="28" t="n">
-        <v>18.07</v>
+        <v>17.99</v>
       </c>
       <c r="I91" s="29" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="J91" s="29" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="K91" s="30" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="L91" s="31" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="M91" s="31" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="N91" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O91" s="32" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="P91" s="32" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="Q91" s="33" t="n">
         <v>17.93</v>
       </c>
-      <c r="J91" s="29" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="K91" s="30" t="n">
-        <v>18.04</v>
-      </c>
-      <c r="L91" s="31" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="M91" s="31" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="N91" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O91" s="32" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="P91" s="32" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="Q91" s="33" t="n">
-        <v>18.01</v>
-      </c>
       <c r="R91" s="36" t="n">
-        <v>-0.39</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="92">
@@ -6312,54 +6312,54 @@
         </is>
       </c>
       <c r="C92" s="25" t="n">
-        <v>32.45</v>
+        <v>32.51</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>32.07</v>
+        <v>32.13</v>
       </c>
       <c r="E92" s="26" t="n">
-        <v>31.76</v>
+        <v>31.82</v>
       </c>
       <c r="F92" s="27" t="n">
-        <v>31.82</v>
+        <v>31.77</v>
       </c>
       <c r="G92" s="27" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="H92" s="28" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="I92" s="29" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="J92" s="29" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="K92" s="30" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="L92" s="31" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="M92" s="31" t="n">
+        <v>30.91</v>
+      </c>
+      <c r="N92" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O92" s="32" t="n">
         <v>31.64</v>
       </c>
-      <c r="I92" s="29" t="n">
-        <v>31.44</v>
-      </c>
-      <c r="J92" s="29" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="K92" s="30" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="L92" s="31" t="n">
-        <v>31.23</v>
-      </c>
-      <c r="M92" s="31" t="n">
-        <v>30.85</v>
-      </c>
-      <c r="N92" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O92" s="32" t="n">
-        <v>31.61</v>
-      </c>
       <c r="P92" s="32" t="n">
-        <v>31.57</v>
+        <v>31.63</v>
       </c>
       <c r="Q92" s="33" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="R92" s="34" t="n">
-        <v>0.19</v>
+        <v>31.52</v>
+      </c>
+      <c r="R92" s="36" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="93">
@@ -6374,54 +6374,54 @@
         </is>
       </c>
       <c r="C93" s="25" t="n">
-        <v>21.55</v>
+        <v>22.92</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>21.32</v>
+        <v>22.2</v>
       </c>
       <c r="E93" s="26" t="n">
-        <v>21.13</v>
+        <v>21.6</v>
       </c>
       <c r="F93" s="27" t="n">
-        <v>21.13</v>
+        <v>21.76</v>
       </c>
       <c r="G93" s="27" t="n">
-        <v>21.27</v>
+        <v>22.12</v>
       </c>
       <c r="H93" s="28" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I93" s="29" t="n">
         <v>21.04</v>
       </c>
-      <c r="I93" s="29" t="n">
-        <v>20.9</v>
-      </c>
       <c r="J93" s="29" t="n">
-        <v>20.81</v>
+        <v>20.68</v>
       </c>
       <c r="K93" s="30" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="L93" s="31" t="n">
-        <v>20.81</v>
+        <v>20.6</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="N93" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>19.88</v>
+      </c>
+      <c r="N93" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O93" s="32" t="n">
-        <v>21.03</v>
+        <v>21.33</v>
       </c>
       <c r="P93" s="32" t="n">
-        <v>21.02</v>
+        <v>21.25</v>
       </c>
       <c r="Q93" s="33" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="R93" s="36" t="n">
-        <v>-0.38</v>
+        <v>21.4</v>
+      </c>
+      <c r="R93" s="34" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="94">
@@ -6436,54 +6436,54 @@
         </is>
       </c>
       <c r="C94" s="25" t="n">
-        <v>28.34</v>
+        <v>28.9</v>
       </c>
       <c r="D94" s="25" t="n">
-        <v>28.12</v>
+        <v>28.48</v>
       </c>
       <c r="E94" s="26" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="F94" s="27" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="G94" s="27" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H94" s="28" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="I94" s="29" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="J94" s="29" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="K94" s="30" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="L94" s="31" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M94" s="31" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="N94" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O94" s="32" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="P94" s="32" t="n">
         <v>27.93</v>
       </c>
-      <c r="F94" s="27" t="n">
-        <v>27.95</v>
-      </c>
-      <c r="G94" s="27" t="n">
-        <v>28.07</v>
-      </c>
-      <c r="H94" s="28" t="n">
-        <v>27.85</v>
-      </c>
-      <c r="I94" s="29" t="n">
-        <v>27.73</v>
-      </c>
-      <c r="J94" s="29" t="n">
-        <v>27.63</v>
-      </c>
-      <c r="K94" s="30" t="n">
-        <v>27.81</v>
-      </c>
-      <c r="L94" s="31" t="n">
-        <v>27.62</v>
-      </c>
-      <c r="M94" s="31" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="N94" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O94" s="32" t="n">
-        <v>27.84</v>
-      </c>
-      <c r="P94" s="32" t="n">
-        <v>27.83</v>
-      </c>
       <c r="Q94" s="33" t="n">
-        <v>27.82</v>
-      </c>
-      <c r="R94" s="36" t="n">
-        <v>-0.43</v>
+        <v>27.92</v>
+      </c>
+      <c r="R94" s="34" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="95">
@@ -6498,54 +6498,54 @@
         </is>
       </c>
       <c r="C95" s="25" t="n">
-        <v>174.51</v>
+        <v>174.19</v>
       </c>
       <c r="D95" s="25" t="n">
-        <v>172.71</v>
+        <v>172.59</v>
       </c>
       <c r="E95" s="26" t="n">
+        <v>171.25</v>
+      </c>
+      <c r="F95" s="27" t="n">
+        <v>171.87</v>
+      </c>
+      <c r="G95" s="27" t="n">
+        <v>172.53</v>
+      </c>
+      <c r="H95" s="28" t="n">
+        <v>170.93</v>
+      </c>
+      <c r="I95" s="29" t="n">
+        <v>170.27</v>
+      </c>
+      <c r="J95" s="29" t="n">
+        <v>169.33</v>
+      </c>
+      <c r="K95" s="30" t="n">
+        <v>170.35</v>
+      </c>
+      <c r="L95" s="31" t="n">
+        <v>169.01</v>
+      </c>
+      <c r="M95" s="31" t="n">
+        <v>167.41</v>
+      </c>
+      <c r="N95" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O95" s="32" t="n">
+        <v>170.71</v>
+      </c>
+      <c r="P95" s="32" t="n">
+        <v>170.48</v>
+      </c>
+      <c r="Q95" s="33" t="n">
         <v>171.2</v>
       </c>
-      <c r="F95" s="27" t="n">
-        <v>171.2</v>
-      </c>
-      <c r="G95" s="27" t="n">
-        <v>172.3</v>
-      </c>
-      <c r="H95" s="28" t="n">
-        <v>170.5</v>
-      </c>
-      <c r="I95" s="29" t="n">
-        <v>169.4</v>
-      </c>
-      <c r="J95" s="29" t="n">
-        <v>168.7</v>
-      </c>
-      <c r="K95" s="30" t="n">
-        <v>170.2</v>
-      </c>
-      <c r="L95" s="31" t="n">
-        <v>168.69</v>
-      </c>
-      <c r="M95" s="31" t="n">
-        <v>166.89</v>
-      </c>
-      <c r="N95" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O95" s="32" t="n">
-        <v>170.42</v>
-      </c>
-      <c r="P95" s="32" t="n">
-        <v>170.34</v>
-      </c>
-      <c r="Q95" s="33" t="n">
-        <v>170.1</v>
-      </c>
-      <c r="R95" s="36" t="n">
-        <v>-0.06</v>
+      <c r="R95" s="34" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="96">
@@ -6560,54 +6560,54 @@
         </is>
       </c>
       <c r="C96" s="25" t="n">
-        <v>14.91</v>
+        <v>14.84</v>
       </c>
       <c r="D96" s="25" t="n">
-        <v>14.6</v>
+        <v>14.51</v>
       </c>
       <c r="E96" s="26" t="n">
-        <v>14.34</v>
+        <v>14.24</v>
       </c>
       <c r="F96" s="27" t="n">
-        <v>14.45</v>
+        <v>14.21</v>
       </c>
       <c r="G96" s="27" t="n">
-        <v>14.58</v>
+        <v>14.43</v>
       </c>
       <c r="H96" s="28" t="n">
-        <v>14.27</v>
+        <v>14.1</v>
       </c>
       <c r="I96" s="29" t="n">
-        <v>14.14</v>
+        <v>13.88</v>
       </c>
       <c r="J96" s="29" t="n">
-        <v>13.96</v>
+        <v>13.77</v>
       </c>
       <c r="K96" s="30" t="n">
-        <v>14.17</v>
+        <v>14.05</v>
       </c>
       <c r="L96" s="31" t="n">
-        <v>13.91</v>
+        <v>13.78</v>
       </c>
       <c r="M96" s="31" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="N96" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>13.45</v>
+      </c>
+      <c r="N96" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O96" s="32" t="n">
-        <v>14.23</v>
+        <v>14.09</v>
       </c>
       <c r="P96" s="32" t="n">
-        <v>14.19</v>
+        <v>14.08</v>
       </c>
       <c r="Q96" s="33" t="n">
-        <v>14.31</v>
-      </c>
-      <c r="R96" s="34" t="n">
-        <v>1.06</v>
+        <v>14</v>
+      </c>
+      <c r="R96" s="36" t="n">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="97">
@@ -6622,37 +6622,37 @@
         </is>
       </c>
       <c r="C97" s="25" t="n">
-        <v>20.12</v>
+        <v>20.16</v>
       </c>
       <c r="D97" s="25" t="n">
-        <v>19.8</v>
+        <v>19.87</v>
       </c>
       <c r="E97" s="26" t="n">
-        <v>19.53</v>
+        <v>19.63</v>
       </c>
       <c r="F97" s="27" t="n">
-        <v>19.56</v>
+        <v>19.6</v>
       </c>
       <c r="G97" s="27" t="n">
-        <v>19.74</v>
+        <v>19.79</v>
       </c>
       <c r="H97" s="28" t="n">
-        <v>19.42</v>
+        <v>19.5</v>
       </c>
       <c r="I97" s="29" t="n">
-        <v>19.24</v>
+        <v>19.31</v>
       </c>
       <c r="J97" s="29" t="n">
-        <v>19.1</v>
+        <v>19.21</v>
       </c>
       <c r="K97" s="30" t="n">
-        <v>19.35</v>
+        <v>19.46</v>
       </c>
       <c r="L97" s="31" t="n">
-        <v>19.08</v>
+        <v>19.22</v>
       </c>
       <c r="M97" s="31" t="n">
-        <v>18.76</v>
+        <v>18.93</v>
       </c>
       <c r="N97" s="35" t="inlineStr">
         <is>
@@ -6660,16 +6660,16 @@
         </is>
       </c>
       <c r="O97" s="32" t="n">
-        <v>19.4</v>
+        <v>19.49</v>
       </c>
       <c r="P97" s="32" t="n">
-        <v>19.38</v>
+        <v>19.49</v>
       </c>
       <c r="Q97" s="33" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="R97" s="36" t="n">
-        <v>-0.46</v>
+        <v>19.41</v>
+      </c>
+      <c r="R97" s="34" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="98">
@@ -6684,54 +6684,54 @@
         </is>
       </c>
       <c r="C98" s="25" t="n">
-        <v>16.94</v>
+        <v>16.67</v>
       </c>
       <c r="D98" s="25" t="n">
-        <v>16.71</v>
+        <v>16.53</v>
       </c>
       <c r="E98" s="26" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="F98" s="27" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="G98" s="27" t="n">
         <v>16.52</v>
       </c>
-      <c r="F98" s="27" t="n">
-        <v>16.53</v>
-      </c>
-      <c r="G98" s="27" t="n">
-        <v>16.66</v>
-      </c>
       <c r="H98" s="28" t="n">
-        <v>16.43</v>
+        <v>16.38</v>
       </c>
       <c r="I98" s="29" t="n">
-        <v>16.3</v>
+        <v>16.31</v>
       </c>
       <c r="J98" s="29" t="n">
-        <v>16.2</v>
+        <v>16.24</v>
       </c>
       <c r="K98" s="30" t="n">
-        <v>16.39</v>
+        <v>16.33</v>
       </c>
       <c r="L98" s="31" t="n">
-        <v>16.2</v>
+        <v>16.21</v>
       </c>
       <c r="M98" s="31" t="n">
-        <v>15.97</v>
-      </c>
-      <c r="N98" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.07</v>
+      </c>
+      <c r="N98" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O98" s="32" t="n">
-        <v>16.42</v>
+        <v>16.36</v>
       </c>
       <c r="P98" s="32" t="n">
-        <v>16.41</v>
+        <v>16.34</v>
       </c>
       <c r="Q98" s="33" t="n">
         <v>16.39</v>
       </c>
       <c r="R98" s="34" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -6746,37 +6746,37 @@
         </is>
       </c>
       <c r="C99" s="25" t="n">
-        <v>10.11</v>
+        <v>10.18</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>10.01</v>
+        <v>10.05</v>
       </c>
       <c r="E99" s="26" t="n">
-        <v>9.93</v>
+        <v>9.94</v>
       </c>
       <c r="F99" s="27" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G99" s="27" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="H99" s="28" t="n">
-        <v>9.9</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I99" s="29" t="n">
-        <v>9.84</v>
+        <v>9.82</v>
       </c>
       <c r="J99" s="29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="K99" s="30" t="n">
         <v>9.869999999999999</v>
       </c>
       <c r="L99" s="31" t="n">
-        <v>9.789999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="M99" s="31" t="n">
-        <v>9.69</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N99" s="35" t="inlineStr">
         <is>
@@ -6790,10 +6790,10 @@
         <v>9.880000000000001</v>
       </c>
       <c r="Q99" s="33" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="R99" s="34" t="n">
-        <v>0.2</v>
+        <v>9.869999999999999</v>
+      </c>
+      <c r="R99" s="36" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="100">
@@ -6808,37 +6808,37 @@
         </is>
       </c>
       <c r="C100" s="25" t="n">
-        <v>26.71</v>
+        <v>26.73</v>
       </c>
       <c r="D100" s="25" t="n">
-        <v>26.47</v>
+        <v>26.45</v>
       </c>
       <c r="E100" s="26" t="n">
-        <v>26.27</v>
+        <v>26.22</v>
       </c>
       <c r="F100" s="27" t="n">
-        <v>26.28</v>
+        <v>26.24</v>
       </c>
       <c r="G100" s="27" t="n">
-        <v>26.42</v>
+        <v>26.4</v>
       </c>
       <c r="H100" s="28" t="n">
-        <v>26.18</v>
+        <v>26.12</v>
       </c>
       <c r="I100" s="29" t="n">
-        <v>26.04</v>
+        <v>25.96</v>
       </c>
       <c r="J100" s="29" t="n">
-        <v>25.94</v>
+        <v>25.84</v>
       </c>
       <c r="K100" s="30" t="n">
-        <v>26.13</v>
+        <v>26.06</v>
       </c>
       <c r="L100" s="31" t="n">
-        <v>25.93</v>
+        <v>25.83</v>
       </c>
       <c r="M100" s="31" t="n">
-        <v>25.69</v>
+        <v>25.55</v>
       </c>
       <c r="N100" s="35" t="inlineStr">
         <is>
@@ -6846,16 +6846,16 @@
         </is>
       </c>
       <c r="O100" s="32" t="n">
-        <v>26.17</v>
+        <v>26.1</v>
       </c>
       <c r="P100" s="32" t="n">
-        <v>26.15</v>
+        <v>26.08</v>
       </c>
       <c r="Q100" s="33" t="n">
-        <v>26.14</v>
-      </c>
-      <c r="R100" s="34" t="n">
-        <v>0.15</v>
+        <v>26.08</v>
+      </c>
+      <c r="R100" s="36" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="101">
@@ -6870,54 +6870,54 @@
         </is>
       </c>
       <c r="C101" s="25" t="n">
-        <v>17.62</v>
+        <v>17.37</v>
       </c>
       <c r="D101" s="25" t="n">
-        <v>17.23</v>
+        <v>17.06</v>
       </c>
       <c r="E101" s="26" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="F101" s="27" t="n">
-        <v>16.91</v>
+        <v>16.88</v>
       </c>
       <c r="G101" s="27" t="n">
-        <v>17.14</v>
+        <v>17.03</v>
       </c>
       <c r="H101" s="28" t="n">
-        <v>16.75</v>
+        <v>16.72</v>
       </c>
       <c r="I101" s="29" t="n">
-        <v>16.52</v>
+        <v>16.57</v>
       </c>
       <c r="J101" s="29" t="n">
-        <v>16.36</v>
+        <v>16.41</v>
       </c>
       <c r="K101" s="30" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="L101" s="31" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="M101" s="31" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="N101" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O101" s="32" t="n">
         <v>16.69</v>
       </c>
-      <c r="L101" s="31" t="n">
-        <v>16.36</v>
-      </c>
-      <c r="M101" s="31" t="n">
-        <v>15.97</v>
-      </c>
-      <c r="N101" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O101" s="32" t="n">
+      <c r="P101" s="32" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="Q101" s="33" t="n">
         <v>16.73</v>
       </c>
-      <c r="P101" s="32" t="n">
-        <v>16.72</v>
-      </c>
-      <c r="Q101" s="33" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="R101" s="36" t="n">
-        <v>-1.59</v>
+      <c r="R101" s="34" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="102">
@@ -6932,37 +6932,37 @@
         </is>
       </c>
       <c r="C102" s="25" t="n">
-        <v>32.41</v>
+        <v>32.51</v>
       </c>
       <c r="D102" s="25" t="n">
-        <v>32.11</v>
+        <v>32.13</v>
       </c>
       <c r="E102" s="26" t="n">
-        <v>31.85</v>
+        <v>31.82</v>
       </c>
       <c r="F102" s="27" t="n">
-        <v>31.82</v>
+        <v>31.88</v>
       </c>
       <c r="G102" s="27" t="n">
-        <v>32.02</v>
+        <v>32.08</v>
       </c>
       <c r="H102" s="28" t="n">
-        <v>31.72</v>
+        <v>31.7</v>
       </c>
       <c r="I102" s="29" t="n">
-        <v>31.52</v>
+        <v>31.5</v>
       </c>
       <c r="J102" s="29" t="n">
-        <v>31.42</v>
+        <v>31.32</v>
       </c>
       <c r="K102" s="30" t="n">
-        <v>31.69</v>
+        <v>31.6</v>
       </c>
       <c r="L102" s="31" t="n">
-        <v>31.43</v>
+        <v>31.29</v>
       </c>
       <c r="M102" s="31" t="n">
-        <v>31.13</v>
+        <v>30.91</v>
       </c>
       <c r="N102" s="35" t="inlineStr">
         <is>
@@ -6970,16 +6970,16 @@
         </is>
       </c>
       <c r="O102" s="32" t="n">
-        <v>31.71</v>
+        <v>31.67</v>
       </c>
       <c r="P102" s="32" t="n">
-        <v>31.71</v>
+        <v>31.63</v>
       </c>
       <c r="Q102" s="33" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="R102" s="36" t="n">
-        <v>-0.57</v>
+        <v>31.68</v>
+      </c>
+      <c r="R102" s="34" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="103">
@@ -6994,54 +6994,54 @@
         </is>
       </c>
       <c r="C103" s="25" t="n">
-        <v>16.18</v>
+        <v>16.4</v>
       </c>
       <c r="D103" s="25" t="n">
-        <v>15.94</v>
+        <v>16.08</v>
       </c>
       <c r="E103" s="26" t="n">
-        <v>15.74</v>
+        <v>15.81</v>
       </c>
       <c r="F103" s="27" t="n">
-        <v>15.85</v>
+        <v>15.79</v>
       </c>
       <c r="G103" s="27" t="n">
-        <v>15.94</v>
+        <v>15.99</v>
       </c>
       <c r="H103" s="28" t="n">
-        <v>15.7</v>
+        <v>15.67</v>
       </c>
       <c r="I103" s="29" t="n">
-        <v>15.61</v>
+        <v>15.47</v>
       </c>
       <c r="J103" s="29" t="n">
-        <v>15.46</v>
+        <v>15.35</v>
       </c>
       <c r="K103" s="30" t="n">
-        <v>15.6</v>
+        <v>15.63</v>
       </c>
       <c r="L103" s="31" t="n">
-        <v>15.4</v>
+        <v>15.36</v>
       </c>
       <c r="M103" s="31" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="N103" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>15.04</v>
+      </c>
+      <c r="N103" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O103" s="32" t="n">
         <v>15.66</v>
       </c>
       <c r="P103" s="32" t="n">
-        <v>15.62</v>
+        <v>15.66</v>
       </c>
       <c r="Q103" s="33" t="n">
-        <v>15.76</v>
-      </c>
-      <c r="R103" s="34" t="n">
-        <v>1.09</v>
+        <v>15.58</v>
+      </c>
+      <c r="R103" s="36" t="n">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="104">
@@ -7056,54 +7056,54 @@
         </is>
       </c>
       <c r="C104" s="25" t="n">
-        <v>71.66</v>
+        <v>73.67</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>70.91</v>
+        <v>72.27</v>
       </c>
       <c r="E104" s="26" t="n">
-        <v>70.28</v>
+        <v>71.09</v>
       </c>
       <c r="F104" s="27" t="n">
-        <v>70.37</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G104" s="27" t="n">
-        <v>70.78</v>
+        <v>72.12</v>
       </c>
       <c r="H104" s="28" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="I104" s="29" t="n">
         <v>70.03</v>
       </c>
-      <c r="I104" s="29" t="n">
-        <v>69.62</v>
-      </c>
       <c r="J104" s="29" t="n">
-        <v>69.28</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="K104" s="30" t="n">
-        <v>69.86</v>
+        <v>70.31</v>
       </c>
       <c r="L104" s="31" t="n">
-        <v>69.23999999999999</v>
+        <v>69.13</v>
       </c>
       <c r="M104" s="31" t="n">
-        <v>68.48999999999999</v>
-      </c>
-      <c r="N104" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>67.73</v>
+      </c>
+      <c r="N104" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O104" s="32" t="n">
-        <v>69.98</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="P104" s="32" t="n">
-        <v>69.92</v>
+        <v>70.42</v>
       </c>
       <c r="Q104" s="33" t="n">
-        <v>69.95</v>
-      </c>
-      <c r="R104" s="36" t="n">
-        <v>-0.07000000000000001</v>
+        <v>70.75</v>
+      </c>
+      <c r="R104" s="34" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="105">
@@ -7118,54 +7118,54 @@
         </is>
       </c>
       <c r="C105" s="25" t="n">
-        <v>15.62</v>
+        <v>15.85</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>15.41</v>
+        <v>15.56</v>
       </c>
       <c r="E105" s="26" t="n">
-        <v>15.23</v>
+        <v>15.32</v>
       </c>
       <c r="F105" s="27" t="n">
-        <v>15.24</v>
+        <v>15.34</v>
       </c>
       <c r="G105" s="27" t="n">
-        <v>15.37</v>
+        <v>15.51</v>
       </c>
       <c r="H105" s="28" t="n">
-        <v>15.16</v>
+        <v>15.22</v>
       </c>
       <c r="I105" s="29" t="n">
-        <v>15.03</v>
+        <v>15.05</v>
       </c>
       <c r="J105" s="29" t="n">
-        <v>14.95</v>
+        <v>14.93</v>
       </c>
       <c r="K105" s="30" t="n">
-        <v>15.12</v>
+        <v>15.15</v>
       </c>
       <c r="L105" s="31" t="n">
-        <v>14.94</v>
+        <v>14.91</v>
       </c>
       <c r="M105" s="31" t="n">
-        <v>14.73</v>
-      </c>
-      <c r="N105" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>14.62</v>
+      </c>
+      <c r="N105" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O105" s="32" t="n">
-        <v>15.14</v>
+        <v>15.2</v>
       </c>
       <c r="P105" s="32" t="n">
-        <v>15.13</v>
+        <v>15.18</v>
       </c>
       <c r="Q105" s="33" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="R105" s="36" t="n">
-        <v>-0.53</v>
+        <v>15.18</v>
+      </c>
+      <c r="R105" s="34" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="106">
@@ -7180,37 +7180,37 @@
         </is>
       </c>
       <c r="C106" s="25" t="n">
-        <v>17.26</v>
+        <v>17.62</v>
       </c>
       <c r="D106" s="25" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="E106" s="26" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="F106" s="27" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="G106" s="27" t="n">
         <v>16.96</v>
       </c>
-      <c r="E106" s="26" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F106" s="27" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="G106" s="27" t="n">
-        <v>16.87</v>
-      </c>
       <c r="H106" s="28" t="n">
-        <v>16.57</v>
+        <v>16.43</v>
       </c>
       <c r="I106" s="29" t="n">
-        <v>16.37</v>
+        <v>16.09</v>
       </c>
       <c r="J106" s="29" t="n">
-        <v>16.27</v>
+        <v>15.9</v>
       </c>
       <c r="K106" s="30" t="n">
-        <v>16.54</v>
+        <v>16.35</v>
       </c>
       <c r="L106" s="31" t="n">
-        <v>16.28</v>
+        <v>15.9</v>
       </c>
       <c r="M106" s="31" t="n">
-        <v>15.98</v>
+        <v>15.37</v>
       </c>
       <c r="N106" s="35" t="inlineStr">
         <is>
@@ -7218,16 +7218,16 @@
         </is>
       </c>
       <c r="O106" s="32" t="n">
-        <v>16.56</v>
+        <v>16.41</v>
       </c>
       <c r="P106" s="32" t="n">
-        <v>16.56</v>
+        <v>16.39</v>
       </c>
       <c r="Q106" s="33" t="n">
-        <v>16.47</v>
+        <v>16.29</v>
       </c>
       <c r="R106" s="36" t="n">
-        <v>-1.26</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="107">
@@ -7242,37 +7242,37 @@
         </is>
       </c>
       <c r="C107" s="25" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="D107" s="25" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="E107" s="26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="F107" s="27" t="n">
         <v>2.47</v>
       </c>
-      <c r="F107" s="27" t="n">
+      <c r="G107" s="27" t="n">
         <v>2.49</v>
       </c>
-      <c r="G107" s="27" t="n">
-        <v>2.51</v>
-      </c>
       <c r="H107" s="28" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I107" s="29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J107" s="29" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K107" s="30" t="n">
         <v>2.45</v>
       </c>
-      <c r="I107" s="29" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="J107" s="29" t="n">
+      <c r="L107" s="31" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M107" s="31" t="n">
         <v>2.39</v>
-      </c>
-      <c r="K107" s="30" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="L107" s="31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="M107" s="31" t="n">
-        <v>2.32</v>
       </c>
       <c r="N107" s="20" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>2.45</v>
       </c>
       <c r="P107" s="32" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="Q107" s="33" t="n">
         <v>2.46</v>
       </c>
       <c r="R107" s="34" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -7304,54 +7304,54 @@
         </is>
       </c>
       <c r="C108" s="25" t="n">
-        <v>40.51</v>
+        <v>42.75</v>
       </c>
       <c r="D108" s="25" t="n">
-        <v>40.17</v>
+        <v>41.67</v>
       </c>
       <c r="E108" s="26" t="n">
-        <v>39.89</v>
+        <v>40.76</v>
       </c>
       <c r="F108" s="27" t="n">
-        <v>39.97</v>
+        <v>41.33</v>
       </c>
       <c r="G108" s="27" t="n">
-        <v>40.13</v>
+        <v>41.71</v>
       </c>
       <c r="H108" s="28" t="n">
-        <v>39.79</v>
+        <v>40.63</v>
       </c>
       <c r="I108" s="29" t="n">
-        <v>39.63</v>
+        <v>40.25</v>
       </c>
       <c r="J108" s="29" t="n">
-        <v>39.45</v>
+        <v>39.55</v>
       </c>
       <c r="K108" s="30" t="n">
-        <v>39.69</v>
+        <v>40.16</v>
       </c>
       <c r="L108" s="31" t="n">
-        <v>39.41</v>
+        <v>39.25</v>
       </c>
       <c r="M108" s="31" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="N108" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>38.17</v>
+      </c>
+      <c r="N108" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O108" s="32" t="n">
-        <v>39.76</v>
+        <v>40.43</v>
       </c>
       <c r="P108" s="32" t="n">
-        <v>39.72</v>
+        <v>40.24</v>
       </c>
       <c r="Q108" s="33" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="R108" s="36" t="n">
-        <v>-0.15</v>
+        <v>40.96</v>
+      </c>
+      <c r="R108" s="34" t="n">
+        <v>2.91</v>
       </c>
     </row>
     <row r="109">
@@ -7366,37 +7366,37 @@
         </is>
       </c>
       <c r="C109" s="25" t="n">
-        <v>8.94</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D109" s="25" t="n">
-        <v>8.609999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="E109" s="26" t="n">
-        <v>8.34</v>
+        <v>8.83</v>
       </c>
       <c r="F109" s="27" t="n">
-        <v>8.52</v>
+        <v>8.82</v>
       </c>
       <c r="G109" s="27" t="n">
-        <v>8.630000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="H109" s="28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="I109" s="29" t="n">
-        <v>8.19</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J109" s="29" t="n">
-        <v>7.97</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K109" s="30" t="n">
-        <v>8.15</v>
+        <v>8.58</v>
       </c>
       <c r="L109" s="31" t="n">
-        <v>7.88</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M109" s="31" t="n">
-        <v>7.55</v>
+        <v>7.79</v>
       </c>
       <c r="N109" s="20" t="inlineStr">
         <is>
@@ -7404,16 +7404,16 @@
         </is>
       </c>
       <c r="O109" s="32" t="n">
-        <v>8.24</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="P109" s="32" t="n">
-        <v>8.18</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="Q109" s="33" t="n">
-        <v>8.41</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="R109" s="34" t="n">
-        <v>3.7</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="110">
@@ -7428,54 +7428,54 @@
         </is>
       </c>
       <c r="C110" s="25" t="n">
-        <v>44.38</v>
+        <v>44.66</v>
       </c>
       <c r="D110" s="25" t="n">
-        <v>44.16</v>
+        <v>44.34</v>
       </c>
       <c r="E110" s="26" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="F110" s="27" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="G110" s="27" t="n">
+        <v>44.35</v>
+      </c>
+      <c r="H110" s="28" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="I110" s="29" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="J110" s="29" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="K110" s="30" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="L110" s="31" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="M110" s="31" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="N110" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O110" s="32" t="n">
         <v>43.97</v>
       </c>
-      <c r="F110" s="27" t="n">
-        <v>43.99</v>
-      </c>
-      <c r="G110" s="27" t="n">
-        <v>44.11</v>
-      </c>
-      <c r="H110" s="28" t="n">
-        <v>43.89</v>
-      </c>
-      <c r="I110" s="29" t="n">
-        <v>43.77</v>
-      </c>
-      <c r="J110" s="29" t="n">
-        <v>43.67</v>
-      </c>
-      <c r="K110" s="30" t="n">
-        <v>43.85</v>
-      </c>
-      <c r="L110" s="31" t="n">
-        <v>43.66</v>
-      </c>
-      <c r="M110" s="31" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="N110" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O110" s="32" t="n">
-        <v>43.88</v>
-      </c>
       <c r="P110" s="32" t="n">
-        <v>43.87</v>
+        <v>43.92</v>
       </c>
       <c r="Q110" s="33" t="n">
-        <v>43.86</v>
+        <v>44.14</v>
       </c>
       <c r="R110" s="34" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="111">
@@ -7490,54 +7490,54 @@
         </is>
       </c>
       <c r="C111" s="25" t="n">
-        <v>67.55</v>
+        <v>67.34</v>
       </c>
       <c r="D111" s="25" t="n">
-        <v>66.5</v>
+        <v>66.39</v>
       </c>
       <c r="E111" s="26" t="n">
-        <v>65.62</v>
+        <v>65.59</v>
       </c>
       <c r="F111" s="27" t="n">
-        <v>65.63</v>
+        <v>66.12</v>
       </c>
       <c r="G111" s="27" t="n">
-        <v>66.27</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="H111" s="28" t="n">
-        <v>65.22</v>
+        <v>65.48</v>
       </c>
       <c r="I111" s="29" t="n">
-        <v>64.58</v>
+        <v>65.17</v>
       </c>
       <c r="J111" s="29" t="n">
-        <v>64.17</v>
+        <v>64.53</v>
       </c>
       <c r="K111" s="30" t="n">
-        <v>65.03</v>
+        <v>65.06</v>
       </c>
       <c r="L111" s="31" t="n">
-        <v>64.15000000000001</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="M111" s="31" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="N111" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>63.31</v>
+      </c>
+      <c r="N111" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O111" s="32" t="n">
-        <v>65.16</v>
+        <v>65.31</v>
       </c>
       <c r="P111" s="32" t="n">
-        <v>65.11</v>
+        <v>65.13</v>
       </c>
       <c r="Q111" s="33" t="n">
-        <v>65</v>
-      </c>
-      <c r="R111" s="36" t="n">
-        <v>-0.23</v>
+        <v>65.8</v>
+      </c>
+      <c r="R111" s="34" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="112">
@@ -7552,54 +7552,54 @@
         </is>
       </c>
       <c r="C112" s="25" t="n">
-        <v>10.37</v>
+        <v>10.4</v>
       </c>
       <c r="D112" s="25" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="E112" s="26" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="F112" s="27" t="n">
         <v>10.31</v>
       </c>
-      <c r="E112" s="26" t="n">
+      <c r="G112" s="27" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="H112" s="28" t="n">
         <v>10.26</v>
       </c>
-      <c r="F112" s="27" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="G112" s="27" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="H112" s="28" t="n">
-        <v>10.23</v>
-      </c>
       <c r="I112" s="29" t="n">
-        <v>10.2</v>
+        <v>10.24</v>
       </c>
       <c r="J112" s="29" t="n">
-        <v>10.17</v>
+        <v>10.19</v>
       </c>
       <c r="K112" s="30" t="n">
-        <v>10.22</v>
+        <v>10.24</v>
       </c>
       <c r="L112" s="31" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="M112" s="31" t="n">
         <v>10.11</v>
       </c>
-      <c r="N112" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+      <c r="N112" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O112" s="32" t="n">
-        <v>10.23</v>
+        <v>10.25</v>
       </c>
       <c r="P112" s="32" t="n">
-        <v>10.23</v>
+        <v>10.24</v>
       </c>
       <c r="Q112" s="33" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="R112" s="36" t="n">
-        <v>-0.1</v>
+        <v>10.28</v>
+      </c>
+      <c r="R112" s="34" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="113">
@@ -7614,37 +7614,37 @@
         </is>
       </c>
       <c r="C113" s="25" t="n">
-        <v>319.94</v>
+        <v>323.24</v>
       </c>
       <c r="D113" s="25" t="n">
-        <v>311.94</v>
+        <v>314.44</v>
       </c>
       <c r="E113" s="26" t="n">
-        <v>305.24</v>
+        <v>307.06</v>
       </c>
       <c r="F113" s="27" t="n">
-        <v>305.4</v>
+        <v>306.47</v>
       </c>
       <c r="G113" s="27" t="n">
-        <v>310.2</v>
+        <v>312.13</v>
       </c>
       <c r="H113" s="28" t="n">
-        <v>302.2</v>
+        <v>303.33</v>
       </c>
       <c r="I113" s="29" t="n">
-        <v>297.4</v>
+        <v>297.67</v>
       </c>
       <c r="J113" s="29" t="n">
-        <v>294.2</v>
+        <v>294.53</v>
       </c>
       <c r="K113" s="30" t="n">
-        <v>300.76</v>
+        <v>302.14</v>
       </c>
       <c r="L113" s="31" t="n">
-        <v>294.06</v>
+        <v>294.76</v>
       </c>
       <c r="M113" s="31" t="n">
-        <v>286.06</v>
+        <v>285.96</v>
       </c>
       <c r="N113" s="35" t="inlineStr">
         <is>
@@ -7652,16 +7652,16 @@
         </is>
       </c>
       <c r="O113" s="32" t="n">
-        <v>301.79</v>
+        <v>303.08</v>
       </c>
       <c r="P113" s="32" t="n">
-        <v>301.38</v>
+        <v>302.82</v>
       </c>
       <c r="Q113" s="33" t="n">
-        <v>300.6</v>
-      </c>
-      <c r="R113" s="36" t="n">
-        <v>-2.28</v>
+        <v>300.8</v>
+      </c>
+      <c r="R113" s="34" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="114">
@@ -7676,54 +7676,54 @@
         </is>
       </c>
       <c r="C114" s="25" t="n">
-        <v>228.57</v>
+        <v>230.09</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>223.77</v>
+        <v>225.09</v>
       </c>
       <c r="E114" s="26" t="n">
-        <v>219.74</v>
+        <v>220.9</v>
       </c>
       <c r="F114" s="27" t="n">
-        <v>219.87</v>
+        <v>223.47</v>
       </c>
       <c r="G114" s="27" t="n">
-        <v>222.73</v>
+        <v>225.23</v>
       </c>
       <c r="H114" s="28" t="n">
-        <v>217.93</v>
+        <v>220.23</v>
       </c>
       <c r="I114" s="29" t="n">
-        <v>215.07</v>
+        <v>218.47</v>
       </c>
       <c r="J114" s="29" t="n">
-        <v>213.13</v>
+        <v>215.23</v>
       </c>
       <c r="K114" s="30" t="n">
-        <v>217.06</v>
+        <v>218.1</v>
       </c>
       <c r="L114" s="31" t="n">
-        <v>213.03</v>
+        <v>213.91</v>
       </c>
       <c r="M114" s="31" t="n">
-        <v>208.23</v>
-      </c>
-      <c r="N114" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>208.91</v>
+      </c>
+      <c r="N114" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O114" s="32" t="n">
-        <v>217.68</v>
+        <v>219.36</v>
       </c>
       <c r="P114" s="32" t="n">
-        <v>217.43</v>
+        <v>218.49</v>
       </c>
       <c r="Q114" s="33" t="n">
-        <v>217</v>
+        <v>221.7</v>
       </c>
       <c r="R114" s="34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="115">
@@ -7738,54 +7738,54 @@
         </is>
       </c>
       <c r="C115" s="25" t="n">
-        <v>645.46</v>
+        <v>646.89</v>
       </c>
       <c r="D115" s="25" t="n">
-        <v>630.96</v>
+        <v>630.89</v>
       </c>
       <c r="E115" s="26" t="n">
-        <v>618.8099999999999</v>
+        <v>617.48</v>
       </c>
       <c r="F115" s="27" t="n">
-        <v>621.17</v>
+        <v>616.67</v>
       </c>
       <c r="G115" s="27" t="n">
-        <v>628.83</v>
+        <v>626.83</v>
       </c>
       <c r="H115" s="28" t="n">
-        <v>614.33</v>
+        <v>610.83</v>
       </c>
       <c r="I115" s="29" t="n">
-        <v>606.67</v>
+        <v>600.67</v>
       </c>
       <c r="J115" s="29" t="n">
-        <v>599.83</v>
+        <v>594.83</v>
       </c>
       <c r="K115" s="30" t="n">
-        <v>610.6900000000001</v>
+        <v>608.52</v>
       </c>
       <c r="L115" s="31" t="n">
-        <v>598.54</v>
+        <v>595.11</v>
       </c>
       <c r="M115" s="31" t="n">
-        <v>584.04</v>
-      </c>
-      <c r="N115" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>579.11</v>
+      </c>
+      <c r="N115" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O115" s="32" t="n">
-        <v>613.08</v>
+        <v>610.3</v>
       </c>
       <c r="P115" s="32" t="n">
-        <v>611.8200000000001</v>
+        <v>609.77</v>
       </c>
       <c r="Q115" s="33" t="n">
-        <v>613.5</v>
-      </c>
-      <c r="R115" s="34" t="n">
-        <v>0.82</v>
+        <v>606.5</v>
+      </c>
+      <c r="R115" s="36" t="n">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="116">
@@ -7800,54 +7800,54 @@
         </is>
       </c>
       <c r="C116" s="25" t="n">
-        <v>6.94</v>
+        <v>6.95</v>
       </c>
       <c r="D116" s="25" t="n">
-        <v>6.85</v>
+        <v>6.86</v>
       </c>
       <c r="E116" s="26" t="n">
-        <v>6.77</v>
+        <v>6.78</v>
       </c>
       <c r="F116" s="27" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="G116" s="27" t="n">
-        <v>6.83</v>
+        <v>6.84</v>
       </c>
       <c r="H116" s="28" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="I116" s="29" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="J116" s="29" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="K116" s="30" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="L116" s="31" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="M116" s="31" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="N116" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O116" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P116" s="32" t="n">
         <v>6.74</v>
       </c>
-      <c r="I116" s="29" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="J116" s="29" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="K116" s="30" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L116" s="31" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="M116" s="31" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="N116" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O116" s="32" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="P116" s="32" t="n">
-        <v>6.73</v>
-      </c>
       <c r="Q116" s="33" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="R116" s="36" t="n">
-        <v>-0.44</v>
+        <v>6.75</v>
+      </c>
+      <c r="R116" s="34" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="117">
@@ -7862,37 +7862,37 @@
         </is>
       </c>
       <c r="C117" s="25" t="n">
-        <v>143.16</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="D117" s="25" t="n">
-        <v>139.66</v>
+        <v>93.56</v>
       </c>
       <c r="E117" s="26" t="n">
-        <v>136.73</v>
+        <v>91.92</v>
       </c>
       <c r="F117" s="27" t="n">
-        <v>137.67</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G117" s="27" t="n">
-        <v>139.33</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H117" s="28" t="n">
-        <v>135.83</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I117" s="29" t="n">
-        <v>134.17</v>
+        <v>89.95</v>
       </c>
       <c r="J117" s="29" t="n">
-        <v>132.33</v>
+        <v>89.2</v>
       </c>
       <c r="K117" s="30" t="n">
-        <v>134.77</v>
+        <v>90.83</v>
       </c>
       <c r="L117" s="31" t="n">
-        <v>131.84</v>
+        <v>89.19</v>
       </c>
       <c r="M117" s="31" t="n">
-        <v>128.34</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
@@ -7900,16 +7900,16 @@
         </is>
       </c>
       <c r="O117" s="32" t="n">
-        <v>135.44</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="P117" s="32" t="n">
-        <v>135.04</v>
+        <v>90.98</v>
       </c>
       <c r="Q117" s="33" t="n">
-        <v>136</v>
+        <v>90.7</v>
       </c>
       <c r="R117" s="34" t="n">
-        <v>1.49</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="118">
@@ -7927,51 +7927,51 @@
         <v>10.92</v>
       </c>
       <c r="D118" s="25" t="n">
-        <v>10.58</v>
+        <v>10.66</v>
       </c>
       <c r="E118" s="26" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="F118" s="27" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="G118" s="27" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="H118" s="28" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="I118" s="29" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="J118" s="29" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="K118" s="30" t="n">
         <v>10.3</v>
       </c>
-      <c r="F118" s="27" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="G118" s="27" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="H118" s="28" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="I118" s="29" t="n">
+      <c r="L118" s="31" t="n">
         <v>10.08</v>
       </c>
-      <c r="J118" s="29" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="K118" s="30" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L118" s="31" t="n">
+      <c r="M118" s="31" t="n">
         <v>9.82</v>
       </c>
-      <c r="M118" s="31" t="n">
-        <v>9.48</v>
-      </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O118" s="32" t="n">
-        <v>10.18</v>
+        <v>10.32</v>
       </c>
       <c r="P118" s="32" t="n">
-        <v>10.13</v>
+        <v>10.32</v>
       </c>
       <c r="Q118" s="33" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="R118" s="34" t="n">
-        <v>1.88</v>
+        <v>10.24</v>
+      </c>
+      <c r="R118" s="36" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="119">
@@ -7986,54 +7986,54 @@
         </is>
       </c>
       <c r="C119" s="25" t="n">
-        <v>18.03</v>
+        <v>17.9</v>
       </c>
       <c r="D119" s="25" t="n">
-        <v>17.52</v>
+        <v>17.51</v>
       </c>
       <c r="E119" s="26" t="n">
-        <v>17.09</v>
+        <v>17.18</v>
       </c>
       <c r="F119" s="27" t="n">
-        <v>17.2</v>
+        <v>17.15</v>
       </c>
       <c r="G119" s="27" t="n">
-        <v>17.46</v>
+        <v>17.41</v>
       </c>
       <c r="H119" s="28" t="n">
-        <v>16.95</v>
+        <v>17.02</v>
       </c>
       <c r="I119" s="29" t="n">
-        <v>16.69</v>
+        <v>16.76</v>
       </c>
       <c r="J119" s="29" t="n">
-        <v>16.44</v>
+        <v>16.63</v>
       </c>
       <c r="K119" s="30" t="n">
-        <v>16.8</v>
+        <v>16.97</v>
       </c>
       <c r="L119" s="31" t="n">
-        <v>16.37</v>
+        <v>16.64</v>
       </c>
       <c r="M119" s="31" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="N119" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.25</v>
+      </c>
+      <c r="N119" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O119" s="32" t="n">
-        <v>16.89</v>
+        <v>17.01</v>
       </c>
       <c r="P119" s="32" t="n">
-        <v>16.84</v>
+        <v>17</v>
       </c>
       <c r="Q119" s="33" t="n">
-        <v>16.95</v>
-      </c>
-      <c r="R119" s="34" t="n">
-        <v>1.56</v>
+        <v>16.9</v>
+      </c>
+      <c r="R119" s="36" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="120">
@@ -8048,37 +8048,37 @@
         </is>
       </c>
       <c r="C120" s="25" t="n">
-        <v>12.86</v>
+        <v>12.39</v>
       </c>
       <c r="D120" s="25" t="n">
-        <v>12.24</v>
+        <v>12.11</v>
       </c>
       <c r="E120" s="26" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="F120" s="27" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="G120" s="27" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H120" s="28" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="I120" s="29" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="J120" s="29" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="K120" s="30" t="n">
         <v>11.72</v>
       </c>
-      <c r="F120" s="27" t="n">
-        <v>12.01</v>
-      </c>
-      <c r="G120" s="27" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="H120" s="28" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="I120" s="29" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="J120" s="29" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="K120" s="30" t="n">
-        <v>11.38</v>
-      </c>
       <c r="L120" s="31" t="n">
-        <v>10.86</v>
+        <v>11.49</v>
       </c>
       <c r="M120" s="31" t="n">
-        <v>10.24</v>
+        <v>11.21</v>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
@@ -8086,16 +8086,16 @@
         </is>
       </c>
       <c r="O120" s="32" t="n">
-        <v>11.53</v>
+        <v>11.78</v>
       </c>
       <c r="P120" s="32" t="n">
-        <v>11.42</v>
+        <v>11.74</v>
       </c>
       <c r="Q120" s="33" t="n">
-        <v>11.78</v>
+        <v>11.85</v>
       </c>
       <c r="R120" s="34" t="n">
-        <v>4.62</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="121">
@@ -8110,54 +8110,54 @@
         </is>
       </c>
       <c r="C121" s="25" t="n">
-        <v>12.42</v>
+        <v>12.51</v>
       </c>
       <c r="D121" s="25" t="n">
-        <v>12.26</v>
+        <v>12.32</v>
       </c>
       <c r="E121" s="26" t="n">
-        <v>12.12</v>
+        <v>12.16</v>
       </c>
       <c r="F121" s="27" t="n">
-        <v>12.2</v>
+        <v>12.14</v>
       </c>
       <c r="G121" s="27" t="n">
         <v>12.26</v>
       </c>
       <c r="H121" s="28" t="n">
-        <v>12.1</v>
+        <v>12.07</v>
       </c>
       <c r="I121" s="29" t="n">
-        <v>12.04</v>
+        <v>11.95</v>
       </c>
       <c r="J121" s="29" t="n">
-        <v>11.94</v>
+        <v>11.88</v>
       </c>
       <c r="K121" s="30" t="n">
-        <v>12.04</v>
+        <v>12.05</v>
       </c>
       <c r="L121" s="31" t="n">
-        <v>11.9</v>
+        <v>11.89</v>
       </c>
       <c r="M121" s="31" t="n">
-        <v>11.74</v>
-      </c>
-      <c r="N121" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>11.7</v>
+      </c>
+      <c r="N121" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O121" s="32" t="n">
         <v>12.07</v>
       </c>
       <c r="P121" s="32" t="n">
-        <v>12.05</v>
+        <v>12.07</v>
       </c>
       <c r="Q121" s="33" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="R121" s="34" t="n">
-        <v>1.17</v>
+        <v>12.01</v>
+      </c>
+      <c r="R121" s="36" t="n">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="122">
@@ -8172,54 +8172,54 @@
         </is>
       </c>
       <c r="C122" s="25" t="n">
-        <v>8.640000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="D122" s="25" t="n">
-        <v>8.51</v>
+        <v>8.56</v>
       </c>
       <c r="E122" s="26" t="n">
-        <v>8.4</v>
+        <v>8.42</v>
       </c>
       <c r="F122" s="27" t="n">
         <v>8.41</v>
       </c>
       <c r="G122" s="27" t="n">
-        <v>8.49</v>
+        <v>8.52</v>
       </c>
       <c r="H122" s="28" t="n">
         <v>8.359999999999999</v>
       </c>
       <c r="I122" s="29" t="n">
-        <v>8.279999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="J122" s="29" t="n">
-        <v>8.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K122" s="30" t="n">
-        <v>8.33</v>
+        <v>8.34</v>
       </c>
       <c r="L122" s="31" t="n">
-        <v>8.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M122" s="31" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="N122" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>8.039999999999999</v>
+      </c>
+      <c r="N122" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O122" s="32" t="n">
         <v>8.35</v>
       </c>
       <c r="P122" s="32" t="n">
-        <v>8.34</v>
+        <v>8.35</v>
       </c>
       <c r="Q122" s="33" t="n">
-        <v>8.34</v>
-      </c>
-      <c r="R122" s="34" t="n">
-        <v>0.12</v>
+        <v>8.31</v>
+      </c>
+      <c r="R122" s="36" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="123">
@@ -8234,54 +8234,54 @@
         </is>
       </c>
       <c r="C123" s="25" t="n">
-        <v>8.58</v>
+        <v>8.44</v>
       </c>
       <c r="D123" s="25" t="n">
-        <v>8.359999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E123" s="26" t="n">
         <v>8.17</v>
       </c>
       <c r="F123" s="27" t="n">
-        <v>8.23</v>
+        <v>8.16</v>
       </c>
       <c r="G123" s="27" t="n">
-        <v>8.34</v>
+        <v>8.25</v>
       </c>
       <c r="H123" s="28" t="n">
-        <v>8.119999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I123" s="29" t="n">
         <v>8.01</v>
       </c>
       <c r="J123" s="29" t="n">
-        <v>7.9</v>
+        <v>7.95</v>
       </c>
       <c r="K123" s="30" t="n">
-        <v>8.050000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="L123" s="31" t="n">
-        <v>7.86</v>
+        <v>7.96</v>
       </c>
       <c r="M123" s="31" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="N123" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>7.81</v>
+      </c>
+      <c r="N123" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O123" s="32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="P123" s="32" t="n">
         <v>8.09</v>
       </c>
-      <c r="P123" s="32" t="n">
-        <v>8.07</v>
-      </c>
       <c r="Q123" s="33" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="R123" s="34" t="n">
-        <v>1.37</v>
+        <v>8.06</v>
+      </c>
+      <c r="R123" s="36" t="n">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="124">
@@ -8296,54 +8296,54 @@
         </is>
       </c>
       <c r="C124" s="25" t="n">
-        <v>26.17</v>
+        <v>26.41</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>25.89</v>
+        <v>25.97</v>
       </c>
       <c r="E124" s="26" t="n">
-        <v>25.66</v>
+        <v>25.6</v>
       </c>
       <c r="F124" s="27" t="n">
-        <v>25.68</v>
+        <v>25.57</v>
       </c>
       <c r="G124" s="27" t="n">
-        <v>25.84</v>
+        <v>25.85</v>
       </c>
       <c r="H124" s="28" t="n">
-        <v>25.56</v>
+        <v>25.41</v>
       </c>
       <c r="I124" s="29" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="J124" s="29" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="K124" s="30" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="L124" s="31" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="M124" s="31" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="N124" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O124" s="32" t="n">
         <v>25.4</v>
       </c>
-      <c r="J124" s="29" t="n">
+      <c r="P124" s="32" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="Q124" s="33" t="n">
         <v>25.28</v>
       </c>
-      <c r="K124" s="30" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="L124" s="31" t="n">
-        <v>25.27</v>
-      </c>
-      <c r="M124" s="31" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="N124" s="35" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O124" s="32" t="n">
-        <v>25.54</v>
-      </c>
-      <c r="P124" s="32" t="n">
-        <v>25.52</v>
-      </c>
-      <c r="Q124" s="33" t="n">
-        <v>25.52</v>
-      </c>
       <c r="R124" s="36" t="n">
-        <v>-0.31</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -8358,37 +8358,37 @@
         </is>
       </c>
       <c r="C125" s="25" t="n">
-        <v>166.26</v>
+        <v>161.89</v>
       </c>
       <c r="D125" s="25" t="n">
-        <v>161.96</v>
+        <v>160.29</v>
       </c>
       <c r="E125" s="26" t="n">
-        <v>158.35</v>
+        <v>158.95</v>
       </c>
       <c r="F125" s="27" t="n">
-        <v>159.87</v>
+        <v>159.23</v>
       </c>
       <c r="G125" s="27" t="n">
-        <v>161.73</v>
+        <v>160.07</v>
       </c>
       <c r="H125" s="28" t="n">
-        <v>157.43</v>
+        <v>158.47</v>
       </c>
       <c r="I125" s="29" t="n">
-        <v>155.57</v>
+        <v>157.63</v>
       </c>
       <c r="J125" s="29" t="n">
-        <v>153.13</v>
+        <v>156.87</v>
       </c>
       <c r="K125" s="30" t="n">
-        <v>155.95</v>
+        <v>158.05</v>
       </c>
       <c r="L125" s="31" t="n">
-        <v>152.34</v>
+        <v>156.71</v>
       </c>
       <c r="M125" s="31" t="n">
-        <v>148.04</v>
+        <v>155.11</v>
       </c>
       <c r="N125" s="20" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         </is>
       </c>
       <c r="O125" s="32" t="n">
-        <v>156.86</v>
+        <v>158.32</v>
       </c>
       <c r="P125" s="32" t="n">
-        <v>156.28</v>
+        <v>158.18</v>
       </c>
       <c r="Q125" s="33" t="n">
-        <v>158</v>
+        <v>158.4</v>
       </c>
       <c r="R125" s="34" t="n">
-        <v>1.61</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="126">
@@ -8420,37 +8420,37 @@
         </is>
       </c>
       <c r="C126" s="25" t="n">
-        <v>56.67</v>
+        <v>58.02</v>
       </c>
       <c r="D126" s="25" t="n">
-        <v>56.07</v>
+        <v>56.77</v>
       </c>
       <c r="E126" s="26" t="n">
-        <v>55.57</v>
+        <v>55.73</v>
       </c>
       <c r="F126" s="27" t="n">
-        <v>55.63</v>
+        <v>55.75</v>
       </c>
       <c r="G126" s="27" t="n">
-        <v>55.97</v>
+        <v>56.5</v>
       </c>
       <c r="H126" s="28" t="n">
-        <v>55.37</v>
+        <v>55.25</v>
       </c>
       <c r="I126" s="29" t="n">
-        <v>55.03</v>
+        <v>54.5</v>
       </c>
       <c r="J126" s="29" t="n">
-        <v>54.77</v>
+        <v>54</v>
       </c>
       <c r="K126" s="30" t="n">
-        <v>55.23</v>
+        <v>55.02</v>
       </c>
       <c r="L126" s="31" t="n">
-        <v>54.73</v>
+        <v>53.98</v>
       </c>
       <c r="M126" s="31" t="n">
-        <v>54.13</v>
+        <v>52.73</v>
       </c>
       <c r="N126" s="35" t="inlineStr">
         <is>
@@ -8458,16 +8458,16 @@
         </is>
       </c>
       <c r="O126" s="32" t="n">
-        <v>55.32</v>
+        <v>55.19</v>
       </c>
       <c r="P126" s="32" t="n">
-        <v>55.28</v>
+        <v>55.12</v>
       </c>
       <c r="Q126" s="33" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="R126" s="34" t="n">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="R126" s="36" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="127">
@@ -8482,37 +8482,37 @@
         </is>
       </c>
       <c r="C127" s="25" t="n">
-        <v>15.54</v>
+        <v>15.83</v>
       </c>
       <c r="D127" s="25" t="n">
-        <v>15.3</v>
+        <v>15.38</v>
       </c>
       <c r="E127" s="26" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F127" s="27" t="n">
-        <v>15.1</v>
+        <v>14.96</v>
       </c>
       <c r="G127" s="27" t="n">
         <v>15.25</v>
       </c>
       <c r="H127" s="28" t="n">
-        <v>15.01</v>
+        <v>14.8</v>
       </c>
       <c r="I127" s="29" t="n">
-        <v>14.86</v>
+        <v>14.51</v>
       </c>
       <c r="J127" s="29" t="n">
-        <v>14.77</v>
+        <v>14.35</v>
       </c>
       <c r="K127" s="30" t="n">
-        <v>14.96</v>
+        <v>14.75</v>
       </c>
       <c r="L127" s="31" t="n">
-        <v>14.76</v>
+        <v>14.37</v>
       </c>
       <c r="M127" s="31" t="n">
-        <v>14.52</v>
+        <v>13.92</v>
       </c>
       <c r="N127" s="35" t="inlineStr">
         <is>
@@ -8520,16 +8520,16 @@
         </is>
       </c>
       <c r="O127" s="32" t="n">
-        <v>14.99</v>
+        <v>14.79</v>
       </c>
       <c r="P127" s="32" t="n">
-        <v>14.98</v>
+        <v>14.78</v>
       </c>
       <c r="Q127" s="33" t="n">
-        <v>14.96</v>
+        <v>14.66</v>
       </c>
       <c r="R127" s="36" t="n">
-        <v>-0.86</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="128">
@@ -8544,54 +8544,54 @@
         </is>
       </c>
       <c r="C128" s="25" t="n">
-        <v>16.13</v>
+        <v>15.79</v>
       </c>
       <c r="D128" s="25" t="n">
-        <v>15.62</v>
+        <v>15.47</v>
       </c>
       <c r="E128" s="26" t="n">
-        <v>15.19</v>
+        <v>15.2</v>
       </c>
       <c r="F128" s="27" t="n">
-        <v>15.36</v>
+        <v>15.22</v>
       </c>
       <c r="G128" s="27" t="n">
-        <v>15.58</v>
+        <v>15.4</v>
       </c>
       <c r="H128" s="28" t="n">
-        <v>15.07</v>
+        <v>15.08</v>
       </c>
       <c r="I128" s="29" t="n">
-        <v>14.85</v>
+        <v>14.9</v>
       </c>
       <c r="J128" s="29" t="n">
-        <v>14.56</v>
+        <v>14.76</v>
       </c>
       <c r="K128" s="30" t="n">
-        <v>14.9</v>
+        <v>15.02</v>
       </c>
       <c r="L128" s="31" t="n">
-        <v>14.47</v>
+        <v>14.75</v>
       </c>
       <c r="M128" s="31" t="n">
-        <v>13.96</v>
-      </c>
-      <c r="N128" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>14.43</v>
+      </c>
+      <c r="N128" s="35" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O128" s="32" t="n">
-        <v>15.01</v>
+        <v>15.06</v>
       </c>
       <c r="P128" s="32" t="n">
-        <v>14.94</v>
+        <v>15.05</v>
       </c>
       <c r="Q128" s="33" t="n">
-        <v>15.13</v>
-      </c>
-      <c r="R128" s="34" t="n">
-        <v>2.37</v>
+        <v>15.03</v>
+      </c>
+      <c r="R128" s="36" t="n">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="129">
@@ -8606,54 +8606,54 @@
         </is>
       </c>
       <c r="C129" s="25" t="n">
-        <v>8.33</v>
+        <v>8.84</v>
       </c>
       <c r="D129" s="25" t="n">
-        <v>8.18</v>
+        <v>8.52</v>
       </c>
       <c r="E129" s="26" t="n">
-        <v>8.06</v>
+        <v>8.25</v>
       </c>
       <c r="F129" s="27" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="G129" s="27" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="H129" s="28" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I129" s="29" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J129" s="29" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="K129" s="30" t="n">
         <v>8.07</v>
       </c>
-      <c r="G129" s="27" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="H129" s="28" t="n">
+      <c r="L129" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M129" s="31" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="N129" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O129" s="32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="P129" s="32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Q129" s="33" t="n">
         <v>8.01</v>
       </c>
-      <c r="I129" s="29" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="J129" s="29" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="K129" s="30" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="L129" s="31" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="M129" s="31" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="N129" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O129" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="P129" s="32" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="Q129" s="33" t="n">
-        <v>7.99</v>
-      </c>
       <c r="R129" s="34" t="n">
-        <v>1.14</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="130">
@@ -8668,37 +8668,37 @@
         </is>
       </c>
       <c r="C130" s="25" t="n">
-        <v>11.43</v>
+        <v>11.81</v>
       </c>
       <c r="D130" s="25" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="E130" s="26" t="n">
         <v>11.28</v>
       </c>
-      <c r="E130" s="26" t="n">
-        <v>11.16</v>
-      </c>
       <c r="F130" s="27" t="n">
-        <v>11.17</v>
+        <v>11.24</v>
       </c>
       <c r="G130" s="27" t="n">
-        <v>11.26</v>
+        <v>11.44</v>
       </c>
       <c r="H130" s="28" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="I130" s="29" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="J130" s="29" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="K130" s="30" t="n">
         <v>11.11</v>
       </c>
-      <c r="I130" s="29" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="J130" s="29" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="K130" s="30" t="n">
-        <v>11.07</v>
-      </c>
       <c r="L130" s="31" t="n">
-        <v>10.95</v>
+        <v>10.87</v>
       </c>
       <c r="M130" s="31" t="n">
-        <v>10.8</v>
+        <v>10.58</v>
       </c>
       <c r="N130" s="35" t="inlineStr">
         <is>
@@ -8706,16 +8706,16 @@
         </is>
       </c>
       <c r="O130" s="32" t="n">
-        <v>11.1</v>
+        <v>11.14</v>
       </c>
       <c r="P130" s="32" t="n">
-        <v>11.08</v>
+        <v>11.14</v>
       </c>
       <c r="Q130" s="33" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="R130" s="34" t="n">
-        <v>0.27</v>
+        <v>11.05</v>
+      </c>
+      <c r="R130" s="36" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="131">
@@ -8730,37 +8730,37 @@
         </is>
       </c>
       <c r="C131" s="25" t="n">
-        <v>141.4</v>
+        <v>142.21</v>
       </c>
       <c r="D131" s="25" t="n">
-        <v>138</v>
+        <v>139.61</v>
       </c>
       <c r="E131" s="26" t="n">
-        <v>135.15</v>
+        <v>137.43</v>
       </c>
       <c r="F131" s="27" t="n">
-        <v>137.03</v>
+        <v>137.93</v>
       </c>
       <c r="G131" s="27" t="n">
-        <v>138.17</v>
+        <v>139.27</v>
       </c>
       <c r="H131" s="28" t="n">
-        <v>134.77</v>
+        <v>136.67</v>
       </c>
       <c r="I131" s="29" t="n">
-        <v>133.63</v>
+        <v>135.33</v>
       </c>
       <c r="J131" s="29" t="n">
-        <v>131.37</v>
+        <v>134.07</v>
       </c>
       <c r="K131" s="30" t="n">
-        <v>133.25</v>
+        <v>135.97</v>
       </c>
       <c r="L131" s="31" t="n">
-        <v>130.4</v>
+        <v>133.79</v>
       </c>
       <c r="M131" s="31" t="n">
-        <v>127</v>
+        <v>131.19</v>
       </c>
       <c r="N131" s="20" t="inlineStr">
         <is>
@@ -8768,16 +8768,16 @@
         </is>
       </c>
       <c r="O131" s="32" t="n">
-        <v>134.14</v>
+        <v>136.42</v>
       </c>
       <c r="P131" s="32" t="n">
-        <v>133.51</v>
+        <v>136.17</v>
       </c>
       <c r="Q131" s="33" t="n">
-        <v>135.9</v>
+        <v>136.6</v>
       </c>
       <c r="R131" s="34" t="n">
-        <v>2.03</v>
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -686,7 +686,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-07</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>11203.8</v>
+        <v>11141.74</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>11135.4</v>
+        <v>11083.78</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>11078.08</v>
+        <v>11035.21</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>11070.33</v>
+        <v>11059.47</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>11115.93</v>
+        <v>11082.7</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>11047.53</v>
+        <v>11024.74</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>11001.93</v>
+        <v>11001.51</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>10979.13</v>
+        <v>10966.78</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>11039.78</v>
+        <v>11002.75</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>10982.46</v>
+        <v>10954.18</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>10914.06</v>
+        <v>10896.22</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>11046.32</v>
+        <v>11016</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>11045.11</v>
+        <v>11007.27</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>11024.73</v>
+        <v>11036.25</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="4">
@@ -856,54 +856,54 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>21.29</v>
+        <v>20.82</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>21.02</v>
+        <v>20.72</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>20.79</v>
+        <v>20.64</v>
       </c>
       <c r="F4" s="27" t="n">
-        <v>20.76</v>
+        <v>20.63</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>20.94</v>
+        <v>20.69</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>20.67</v>
+        <v>20.59</v>
       </c>
       <c r="I4" s="29" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="J4" s="29" t="n">
         <v>20.49</v>
       </c>
-      <c r="J4" s="29" t="n">
+      <c r="K4" s="30" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="L4" s="31" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="M4" s="31" t="n">
         <v>20.4</v>
       </c>
-      <c r="K4" s="30" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="L4" s="31" t="n">
-        <v>20.41</v>
-      </c>
-      <c r="M4" s="31" t="n">
-        <v>20.14</v>
-      </c>
       <c r="N4" s="32" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O4" s="33" t="n">
-        <v>20.67</v>
+        <v>20.59</v>
       </c>
       <c r="P4" s="33" t="n">
-        <v>20.66</v>
+        <v>20.59</v>
       </c>
       <c r="Q4" s="34" t="n">
-        <v>20.58</v>
+        <v>20.56</v>
       </c>
       <c r="R4" s="35" t="n">
-        <v>-0.63</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="5">
@@ -918,37 +918,37 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>12.65</v>
+        <v>12.24</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>12.41</v>
+        <v>12.13</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>12.21</v>
+        <v>12.04</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>12.18</v>
+        <v>12.1</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>12.34</v>
+        <v>12.13</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>12.1</v>
+        <v>12.02</v>
       </c>
       <c r="I5" s="29" t="n">
-        <v>11.94</v>
+        <v>11.99</v>
       </c>
       <c r="J5" s="29" t="n">
-        <v>11.86</v>
+        <v>11.91</v>
       </c>
       <c r="K5" s="30" t="n">
-        <v>12.07</v>
+        <v>11.97</v>
       </c>
       <c r="L5" s="31" t="n">
-        <v>11.87</v>
+        <v>11.88</v>
       </c>
       <c r="M5" s="31" t="n">
-        <v>11.63</v>
+        <v>11.77</v>
       </c>
       <c r="N5" s="32" t="inlineStr">
         <is>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="O5" s="33" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="P5" s="33" t="n">
-        <v>12.09</v>
+        <v>11.98</v>
       </c>
       <c r="Q5" s="34" t="n">
-        <v>12.02</v>
+        <v>12.06</v>
       </c>
       <c r="R5" s="35" t="n">
-        <v>-1.07</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="6">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>15.09</v>
+        <v>15.1</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>14.95</v>
@@ -992,36 +992,36 @@
         <v>14.86</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>14.93</v>
+        <v>14.94</v>
       </c>
       <c r="H6" s="28" t="n">
         <v>14.79</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>14.72</v>
+        <v>14.71</v>
       </c>
       <c r="J6" s="29" t="n">
-        <v>14.65</v>
+        <v>14.64</v>
       </c>
       <c r="K6" s="30" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="L6" s="31" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="M6" s="31" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="N6" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O6" s="33" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="P6" s="33" t="n">
         <v>14.75</v>
-      </c>
-      <c r="L6" s="31" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="M6" s="31" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="N6" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O6" s="33" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="P6" s="33" t="n">
-        <v>14.76</v>
       </c>
       <c r="Q6" s="34" t="n">
         <v>14.79</v>
@@ -1042,37 +1042,37 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>22.58</v>
+        <v>22.04</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>22.22</v>
+        <v>21.86</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>21.92</v>
+        <v>21.71</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>21.91</v>
+        <v>21.75</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>22.14</v>
+        <v>21.84</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>21.78</v>
+        <v>21.66</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>21.55</v>
+        <v>21.57</v>
       </c>
       <c r="J7" s="29" t="n">
-        <v>21.42</v>
+        <v>21.48</v>
       </c>
       <c r="K7" s="30" t="n">
-        <v>21.72</v>
+        <v>21.61</v>
       </c>
       <c r="L7" s="31" t="n">
-        <v>21.42</v>
+        <v>21.46</v>
       </c>
       <c r="M7" s="31" t="n">
-        <v>21.06</v>
+        <v>21.28</v>
       </c>
       <c r="N7" s="32" t="inlineStr">
         <is>
@@ -1080,16 +1080,16 @@
         </is>
       </c>
       <c r="O7" s="33" t="n">
-        <v>21.76</v>
+        <v>21.64</v>
       </c>
       <c r="P7" s="33" t="n">
-        <v>21.75</v>
+        <v>21.62</v>
       </c>
       <c r="Q7" s="34" t="n">
-        <v>21.69</v>
+        <v>21.66</v>
       </c>
       <c r="R7" s="35" t="n">
-        <v>-0.82</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="8">
@@ -1104,54 +1104,54 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>34.92</v>
+        <v>34.56</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>34.66</v>
+        <v>34.4</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>34.44</v>
+        <v>34.26</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>34.41</v>
+        <v>34.29</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>34.59</v>
+        <v>34.37</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>34.33</v>
+        <v>34.21</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>34.15</v>
+        <v>34.13</v>
       </c>
       <c r="J8" s="29" t="n">
-        <v>34.07</v>
+        <v>34.05</v>
       </c>
       <c r="K8" s="30" t="n">
-        <v>34.3</v>
+        <v>34.18</v>
       </c>
       <c r="L8" s="31" t="n">
-        <v>34.08</v>
+        <v>34.04</v>
       </c>
       <c r="M8" s="31" t="n">
-        <v>33.82</v>
-      </c>
-      <c r="N8" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>33.88</v>
+      </c>
+      <c r="N8" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O8" s="33" t="n">
-        <v>34.32</v>
+        <v>34.2</v>
       </c>
       <c r="P8" s="33" t="n">
-        <v>34.32</v>
+        <v>34.19</v>
       </c>
       <c r="Q8" s="34" t="n">
-        <v>34.24</v>
+        <v>34.2</v>
       </c>
       <c r="R8" s="36" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1166,37 +1166,37 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>23.4</v>
+        <v>22.92</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>23.06</v>
+        <v>22.73</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>22.78</v>
+        <v>22.57</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>22.82</v>
+        <v>22.67</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>23</v>
+        <v>22.73</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>22.66</v>
+        <v>22.54</v>
       </c>
       <c r="I9" s="29" t="n">
         <v>22.48</v>
       </c>
       <c r="J9" s="29" t="n">
-        <v>22.32</v>
+        <v>22.35</v>
       </c>
       <c r="K9" s="30" t="n">
-        <v>22.58</v>
+        <v>22.46</v>
       </c>
       <c r="L9" s="31" t="n">
         <v>22.3</v>
       </c>
       <c r="M9" s="31" t="n">
-        <v>21.96</v>
+        <v>22.11</v>
       </c>
       <c r="N9" s="32" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="O9" s="33" t="n">
-        <v>22.64</v>
+        <v>22.51</v>
       </c>
       <c r="P9" s="33" t="n">
-        <v>22.61</v>
+        <v>22.48</v>
       </c>
       <c r="Q9" s="34" t="n">
-        <v>22.63</v>
+        <v>22.6</v>
       </c>
       <c r="R9" s="35" t="n">
-        <v>-1.18</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="10">
@@ -1228,54 +1228,54 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>136.26</v>
+        <v>135.99</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>134.06</v>
+        <v>133.09</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>132.22</v>
+        <v>130.66</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>131.97</v>
+        <v>130.47</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>133.43</v>
+        <v>132.33</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>131.23</v>
+        <v>129.43</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>129.77</v>
+        <v>127.57</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>129.03</v>
+        <v>126.53</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>130.98</v>
+        <v>129.04</v>
       </c>
       <c r="L10" s="31" t="n">
-        <v>129.14</v>
+        <v>126.61</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>126.94</v>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>123.71</v>
+      </c>
+      <c r="N10" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O10" s="33" t="n">
-        <v>131.19</v>
+        <v>129.35</v>
       </c>
       <c r="P10" s="33" t="n">
-        <v>131.16</v>
+        <v>129.26</v>
       </c>
       <c r="Q10" s="34" t="n">
-        <v>130.5</v>
-      </c>
-      <c r="R10" s="36" t="n">
-        <v>1.08</v>
+        <v>128.6</v>
+      </c>
+      <c r="R10" s="35" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="11">
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>68.33</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>67.63</v>
+        <v>67.23</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>67.05</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="F11" s="27" t="n">
         <v>66.97</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>67.43000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>66.73</v>
+        <v>66.53</v>
       </c>
       <c r="I11" s="29" t="n">
         <v>66.27</v>
       </c>
       <c r="J11" s="29" t="n">
-        <v>66.03</v>
+        <v>65.83</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>66.65000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="L11" s="31" t="n">
-        <v>66.06999999999999</v>
+        <v>65.67</v>
       </c>
       <c r="M11" s="31" t="n">
-        <v>65.37</v>
+        <v>64.97</v>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="O11" s="33" t="n">
-        <v>66.72</v>
+        <v>66.42</v>
       </c>
       <c r="P11" s="33" t="n">
-        <v>66.70999999999999</v>
+        <v>66.31</v>
       </c>
       <c r="Q11" s="34" t="n">
-        <v>66.5</v>
+        <v>66.7</v>
       </c>
       <c r="R11" s="36" t="n">
-        <v>0.23</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="12">
@@ -1352,37 +1352,37 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>26.42</v>
+        <v>25.98</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>26.1</v>
+        <v>25.76</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>25.83</v>
+        <v>25.57</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>25.83</v>
+        <v>25.67</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>26.03</v>
+        <v>25.75</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>25.71</v>
+        <v>25.53</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>25.51</v>
+        <v>25.45</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>25.39</v>
+        <v>25.31</v>
       </c>
       <c r="K12" s="30" t="n">
-        <v>25.65</v>
+        <v>25.45</v>
       </c>
       <c r="L12" s="31" t="n">
-        <v>25.38</v>
+        <v>25.26</v>
       </c>
       <c r="M12" s="31" t="n">
-        <v>25.06</v>
+        <v>25.04</v>
       </c>
       <c r="N12" s="32" t="inlineStr">
         <is>
@@ -1390,16 +1390,16 @@
         </is>
       </c>
       <c r="O12" s="33" t="n">
-        <v>25.69</v>
+        <v>25.5</v>
       </c>
       <c r="P12" s="33" t="n">
-        <v>25.68</v>
+        <v>25.47</v>
       </c>
       <c r="Q12" s="34" t="n">
-        <v>25.64</v>
+        <v>25.58</v>
       </c>
       <c r="R12" s="35" t="n">
-        <v>-1.08</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="13">
@@ -1414,37 +1414,37 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>25.82</v>
+        <v>25.44</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>25.56</v>
+        <v>25.28</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>25.34</v>
+        <v>25.14</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>25.31</v>
+        <v>25.17</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>25.49</v>
+        <v>25.25</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>25.23</v>
+        <v>25.09</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>25.05</v>
+        <v>25.01</v>
       </c>
       <c r="J13" s="29" t="n">
-        <v>24.97</v>
+        <v>24.93</v>
       </c>
       <c r="K13" s="30" t="n">
-        <v>25.2</v>
+        <v>25.06</v>
       </c>
       <c r="L13" s="31" t="n">
-        <v>24.98</v>
+        <v>24.92</v>
       </c>
       <c r="M13" s="31" t="n">
-        <v>24.72</v>
+        <v>24.76</v>
       </c>
       <c r="N13" s="32" t="inlineStr">
         <is>
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="O13" s="33" t="n">
-        <v>25.22</v>
+        <v>25.08</v>
       </c>
       <c r="P13" s="33" t="n">
-        <v>25.22</v>
+        <v>25.07</v>
       </c>
       <c r="Q13" s="34" t="n">
-        <v>25.14</v>
+        <v>25.08</v>
       </c>
       <c r="R13" s="35" t="n">
-        <v>-0.24</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="14">
@@ -1476,54 +1476,54 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>43.91</v>
+        <v>42.84</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>43.37</v>
+        <v>42.62</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>42.92</v>
+        <v>42.43</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>42.86</v>
+        <v>42.5</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>43.22</v>
+        <v>42.6</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>42.68</v>
+        <v>42.38</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>42.32</v>
+        <v>42.28</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>42.14</v>
+        <v>42.16</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>42.62</v>
+        <v>42.31</v>
       </c>
       <c r="L14" s="31" t="n">
-        <v>42.17</v>
+        <v>42.12</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>41.63</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>41.9</v>
+      </c>
+      <c r="N14" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O14" s="33" t="n">
-        <v>42.67</v>
+        <v>42.35</v>
       </c>
       <c r="P14" s="33" t="n">
-        <v>42.66</v>
+        <v>42.33</v>
       </c>
       <c r="Q14" s="34" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="15">
@@ -1538,37 +1538,37 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>9.140000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>9.01</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="E15" s="26" t="n">
         <v>8.9</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>8.91</v>
+        <v>8.93</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>8.98</v>
+        <v>9.02</v>
       </c>
       <c r="H15" s="28" t="n">
         <v>8.85</v>
       </c>
       <c r="I15" s="29" t="n">
-        <v>8.779999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="J15" s="29" t="n">
-        <v>8.720000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="K15" s="30" t="n">
-        <v>8.83</v>
+        <v>8.81</v>
       </c>
       <c r="L15" s="31" t="n">
-        <v>8.720000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="M15" s="31" t="n">
-        <v>8.59</v>
+        <v>8.49</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
@@ -1576,16 +1576,16 @@
         </is>
       </c>
       <c r="O15" s="33" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
       <c r="P15" s="33" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="Q15" s="34" t="n">
         <v>8.84</v>
       </c>
-      <c r="Q15" s="34" t="n">
-        <v>8.83</v>
-      </c>
       <c r="R15" s="36" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="16">
@@ -1600,37 +1600,37 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>15.31</v>
+        <v>15.17</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>15</v>
+        <v>14.92</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>14.74</v>
+        <v>14.72</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>14.81</v>
+        <v>14.69</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>14.96</v>
+        <v>14.85</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>14.65</v>
+        <v>14.6</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>14.5</v>
+        <v>14.44</v>
       </c>
       <c r="J16" s="29" t="n">
-        <v>14.34</v>
+        <v>14.35</v>
       </c>
       <c r="K16" s="30" t="n">
-        <v>14.57</v>
+        <v>14.58</v>
       </c>
       <c r="L16" s="31" t="n">
-        <v>14.31</v>
+        <v>14.37</v>
       </c>
       <c r="M16" s="31" t="n">
-        <v>14</v>
+        <v>14.12</v>
       </c>
       <c r="N16" s="32" t="inlineStr">
         <is>
@@ -1638,16 +1638,16 @@
         </is>
       </c>
       <c r="O16" s="33" t="n">
-        <v>14.62</v>
+        <v>14.6</v>
       </c>
       <c r="P16" s="33" t="n">
         <v>14.59</v>
       </c>
       <c r="Q16" s="34" t="n">
-        <v>14.65</v>
+        <v>14.52</v>
       </c>
       <c r="R16" s="35" t="n">
-        <v>-0.95</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="17">
@@ -1662,54 +1662,54 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>4.92</v>
+        <v>5.18</v>
       </c>
       <c r="D17" s="25" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="E17" s="26" t="n">
         <v>4.83</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="F17" s="27" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="H17" s="28" t="n">
         <v>4.75</v>
       </c>
-      <c r="F17" s="27" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="H17" s="28" t="n">
+      <c r="I17" s="29" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="K17" s="30" t="n">
         <v>4.72</v>
       </c>
-      <c r="I17" s="29" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="K17" s="30" t="n">
+      <c r="L17" s="31" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="M17" s="31" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O17" s="33" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="P17" s="33" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q17" s="34" t="n">
         <v>4.7</v>
       </c>
-      <c r="L17" s="31" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="M17" s="31" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O17" s="33" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="P17" s="33" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="Q17" s="34" t="n">
-        <v>4.72</v>
-      </c>
       <c r="R17" s="36" t="n">
-        <v>0.64</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="18">
@@ -1724,37 +1724,37 @@
         </is>
       </c>
       <c r="C18" s="25" t="n">
-        <v>19.28</v>
+        <v>18.72</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>18.79</v>
+        <v>18.45</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>18.38</v>
+        <v>18.22</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>18.7</v>
+        <v>18.46</v>
       </c>
       <c r="H18" s="28" t="n">
-        <v>18.21</v>
+        <v>18.19</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>17.94</v>
+        <v>18.1</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>17.72</v>
+        <v>17.92</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>18.11</v>
+        <v>18.07</v>
       </c>
       <c r="L18" s="31" t="n">
-        <v>17.7</v>
+        <v>17.84</v>
       </c>
       <c r="M18" s="31" t="n">
-        <v>17.21</v>
+        <v>17.57</v>
       </c>
       <c r="N18" s="32" t="inlineStr">
         <is>
@@ -1762,16 +1762,16 @@
         </is>
       </c>
       <c r="O18" s="33" t="n">
-        <v>18.18</v>
+        <v>18.14</v>
       </c>
       <c r="P18" s="33" t="n">
-        <v>18.15</v>
+        <v>18.09</v>
       </c>
       <c r="Q18" s="34" t="n">
-        <v>18.15</v>
+        <v>18.28</v>
       </c>
       <c r="R18" s="35" t="n">
-        <v>-0.93</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="19">
@@ -1786,37 +1786,37 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>26.81</v>
+        <v>26.13</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>26.43</v>
+        <v>25.85</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>26.12</v>
+        <v>25.62</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>26.14</v>
+        <v>25.68</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>26.36</v>
+        <v>25.82</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>25.98</v>
+        <v>25.54</v>
       </c>
       <c r="I19" s="29" t="n">
-        <v>25.76</v>
+        <v>25.4</v>
       </c>
       <c r="J19" s="29" t="n">
-        <v>25.6</v>
+        <v>25.26</v>
       </c>
       <c r="K19" s="30" t="n">
-        <v>25.9</v>
+        <v>25.46</v>
       </c>
       <c r="L19" s="31" t="n">
-        <v>25.59</v>
+        <v>25.23</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>25.21</v>
+        <v>24.95</v>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         </is>
       </c>
       <c r="O19" s="33" t="n">
-        <v>25.96</v>
+        <v>25.51</v>
       </c>
       <c r="P19" s="33" t="n">
-        <v>25.93</v>
+        <v>25.48</v>
       </c>
       <c r="Q19" s="34" t="n">
-        <v>25.92</v>
+        <v>25.54</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>1.81</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="20">
@@ -1848,54 +1848,54 @@
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>67.41</v>
+        <v>67.88</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>66.91</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>66.48999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>66.47</v>
+        <v>66.95</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>66.78</v>
+        <v>67.2</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>66.28</v>
+        <v>66.5</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>65.97</v>
+        <v>66.25</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>65.78</v>
+        <v>65.8</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>66.20999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="L20" s="31" t="n">
-        <v>65.79000000000001</v>
+        <v>65.62</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>65.29000000000001</v>
-      </c>
-      <c r="N20" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>64.92</v>
+      </c>
+      <c r="N20" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O20" s="33" t="n">
-        <v>66.27</v>
+        <v>66.38</v>
       </c>
       <c r="P20" s="33" t="n">
-        <v>66.25</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="Q20" s="34" t="n">
-        <v>66.15000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="R20" s="35" t="n">
-        <v>-0.97</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="21">
@@ -1910,54 +1910,54 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>12.47</v>
+        <v>12.35</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>12.33</v>
+        <v>12.2</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>12.21</v>
+        <v>12.08</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>12.21</v>
+        <v>12.11</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>12.29</v>
+        <v>12.18</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>12.15</v>
+        <v>12.03</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>12.07</v>
+        <v>11.96</v>
       </c>
       <c r="J21" s="29" t="n">
-        <v>12.01</v>
+        <v>11.88</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>12.13</v>
+        <v>11.99</v>
       </c>
       <c r="L21" s="31" t="n">
-        <v>12.01</v>
+        <v>11.87</v>
       </c>
       <c r="M21" s="31" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="N21" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>11.72</v>
+      </c>
+      <c r="N21" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O21" s="33" t="n">
-        <v>12.15</v>
+        <v>12.02</v>
       </c>
       <c r="P21" s="33" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="Q21" s="34" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="R21" s="36" t="n">
-        <v>0.5</v>
+        <v>12.03</v>
+      </c>
+      <c r="R21" s="35" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="22">
@@ -1972,54 +1972,54 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>18.79</v>
+        <v>18.78</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>18.55</v>
+        <v>18.53</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>18.35</v>
+        <v>18.32</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>18.34</v>
+        <v>18.3</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>18.49</v>
+        <v>18.47</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.25</v>
+        <v>18.22</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>18.1</v>
+        <v>18.05</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>18.01</v>
+        <v>17.97</v>
       </c>
       <c r="K22" s="30" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="L22" s="31" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="M22" s="31" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="N22" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O22" s="33" t="n">
         <v>18.21</v>
       </c>
-      <c r="L22" s="31" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="M22" s="31" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="N22" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O22" s="33" t="n">
-        <v>18.24</v>
-      </c>
       <c r="P22" s="33" t="n">
-        <v>18.23</v>
+        <v>18.2</v>
       </c>
       <c r="Q22" s="34" t="n">
-        <v>18.19</v>
+        <v>18.14</v>
       </c>
       <c r="R22" s="35" t="n">
-        <v>-1.14</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="23">
@@ -2034,37 +2034,37 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>40.19</v>
+        <v>38.95</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>39.21</v>
+        <v>38.41</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>38.38</v>
+        <v>37.96</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>38.66</v>
+        <v>38.21</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>39.12</v>
+        <v>38.41</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>38.14</v>
+        <v>37.87</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>37.68</v>
+        <v>37.67</v>
       </c>
       <c r="J23" s="29" t="n">
-        <v>37.16</v>
+        <v>37.33</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>37.84</v>
+        <v>37.66</v>
       </c>
       <c r="L23" s="31" t="n">
-        <v>37.01</v>
+        <v>37.21</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>36.03</v>
+        <v>36.67</v>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="O23" s="33" t="n">
-        <v>38.03</v>
+        <v>37.79</v>
       </c>
       <c r="P23" s="33" t="n">
-        <v>37.91</v>
+        <v>37.7</v>
       </c>
       <c r="Q23" s="34" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="R23" s="36" t="n">
-        <v>3.97</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="24">
@@ -2096,54 +2096,54 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>15.69</v>
+        <v>16.63</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>15.52</v>
+        <v>16.14</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>15.37</v>
+        <v>15.73</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>15.42</v>
+        <v>15.84</v>
       </c>
       <c r="G24" s="27" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="H24" s="28" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="J24" s="29" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="K24" s="30" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="L24" s="31" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="M24" s="31" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O24" s="33" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="P24" s="33" t="n">
         <v>15.5</v>
       </c>
-      <c r="H24" s="28" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="J24" s="29" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="K24" s="30" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="L24" s="31" t="n">
-        <v>15.13</v>
-      </c>
-      <c r="M24" s="31" t="n">
-        <v>14.96</v>
-      </c>
-      <c r="N24" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O24" s="33" t="n">
-        <v>15.31</v>
-      </c>
-      <c r="P24" s="33" t="n">
-        <v>15.29</v>
-      </c>
       <c r="Q24" s="34" t="n">
-        <v>15.34</v>
-      </c>
-      <c r="R24" s="35" t="n">
-        <v>-0.58</v>
+        <v>15.6</v>
+      </c>
+      <c r="R24" s="36" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="25">
@@ -2158,54 +2158,54 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>37.33</v>
+        <v>38.99</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>36.77</v>
+        <v>37.77</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>36.3</v>
+        <v>36.75</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>36.25</v>
+        <v>37.28</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>36.61</v>
+        <v>37.76</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>36.05</v>
+        <v>36.54</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>35.69</v>
+        <v>36.06</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>35.49</v>
+        <v>35.32</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>35.98</v>
+        <v>36.07</v>
       </c>
       <c r="L25" s="31" t="n">
-        <v>35.51</v>
+        <v>35.05</v>
       </c>
       <c r="M25" s="31" t="n">
-        <v>34.95</v>
-      </c>
-      <c r="N25" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>33.83</v>
+      </c>
+      <c r="N25" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O25" s="33" t="n">
-        <v>36.04</v>
+        <v>36.35</v>
       </c>
       <c r="P25" s="33" t="n">
-        <v>36.03</v>
+        <v>36.16</v>
       </c>
       <c r="Q25" s="34" t="n">
-        <v>35.88</v>
-      </c>
-      <c r="R25" s="35" t="n">
-        <v>-1.32</v>
+        <v>36.8</v>
+      </c>
+      <c r="R25" s="36" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="26">
@@ -2220,37 +2220,37 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>58.63</v>
+        <v>59.45</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>57.53</v>
+        <v>58.15</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>56.61</v>
+        <v>57.06</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>57.12</v>
+        <v>56.98</v>
       </c>
       <c r="G26" s="27" t="n">
-        <v>57.53</v>
+        <v>57.82</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>56.43</v>
+        <v>56.52</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>56.02</v>
+        <v>55.68</v>
       </c>
       <c r="J26" s="29" t="n">
-        <v>55.33</v>
+        <v>55.22</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>55.99</v>
+        <v>56.34</v>
       </c>
       <c r="L26" s="31" t="n">
-        <v>55.07</v>
+        <v>55.25</v>
       </c>
       <c r="M26" s="31" t="n">
-        <v>53.97</v>
+        <v>53.95</v>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
@@ -2258,16 +2258,16 @@
         </is>
       </c>
       <c r="O26" s="33" t="n">
-        <v>56.26</v>
+        <v>56.48</v>
       </c>
       <c r="P26" s="33" t="n">
-        <v>56.08</v>
+        <v>56.44</v>
       </c>
       <c r="Q26" s="34" t="n">
-        <v>56.7</v>
+        <v>56.15</v>
       </c>
       <c r="R26" s="36" t="n">
-        <v>2.16</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="27">
@@ -2282,37 +2282,37 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>215.22</v>
+        <v>215.95</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>211.62</v>
+        <v>212.15</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>208.61</v>
+        <v>208.96</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>208.73</v>
+        <v>208.67</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>210.87</v>
+        <v>211.13</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>207.27</v>
+        <v>207.33</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>205.13</v>
+        <v>204.87</v>
       </c>
       <c r="J27" s="29" t="n">
-        <v>203.67</v>
+        <v>203.53</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>206.59</v>
+        <v>206.84</v>
       </c>
       <c r="L27" s="31" t="n">
-        <v>203.58</v>
+        <v>203.65</v>
       </c>
       <c r="M27" s="31" t="n">
-        <v>199.98</v>
+        <v>199.85</v>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="O27" s="33" t="n">
-        <v>207.07</v>
+        <v>207.23</v>
       </c>
       <c r="P27" s="33" t="n">
-        <v>206.87</v>
+        <v>207.13</v>
       </c>
       <c r="Q27" s="34" t="n">
-        <v>206.6</v>
-      </c>
-      <c r="R27" s="36" t="n">
-        <v>0.05</v>
+        <v>206.2</v>
+      </c>
+      <c r="R27" s="35" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="28">
@@ -2344,37 +2344,37 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>85.05</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>84</v>
+        <v>84.34</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>83.12</v>
+        <v>83.34</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>83.33</v>
+        <v>83.73</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>83.87</v>
+        <v>84.27</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>82.81999999999999</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>82.28</v>
+        <v>82.53</v>
       </c>
       <c r="J28" s="29" t="n">
-        <v>81.77</v>
+        <v>81.87</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>82.53</v>
+        <v>82.66</v>
       </c>
       <c r="L28" s="31" t="n">
-        <v>81.65000000000001</v>
+        <v>81.66</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>80.59999999999999</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="N28" s="32" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="O28" s="33" t="n">
-        <v>82.70999999999999</v>
+        <v>82.91</v>
       </c>
       <c r="P28" s="33" t="n">
-        <v>82.61</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="Q28" s="34" t="n">
-        <v>82.8</v>
+        <v>83.2</v>
       </c>
       <c r="R28" s="35" t="n">
-        <v>-1.08</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="29">
@@ -2406,54 +2406,54 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>23.61</v>
+        <v>23.53</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>23.08</v>
+        <v>23.05</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>22.63</v>
+        <v>22.64</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>22.77</v>
+        <v>22.74</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>23.02</v>
+        <v>22.98</v>
       </c>
       <c r="H29" s="28" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I29" s="29" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="J29" s="29" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="K29" s="30" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="L29" s="31" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="M29" s="31" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="N29" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O29" s="33" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="P29" s="33" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="Q29" s="34" t="n">
         <v>22.49</v>
       </c>
-      <c r="I29" s="29" t="n">
-        <v>22.24</v>
-      </c>
-      <c r="J29" s="29" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="K29" s="30" t="n">
-        <v>22.34</v>
-      </c>
-      <c r="L29" s="31" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="M29" s="31" t="n">
-        <v>21.36</v>
-      </c>
-      <c r="N29" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O29" s="33" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="P29" s="33" t="n">
-        <v>22.38</v>
-      </c>
-      <c r="Q29" s="34" t="n">
-        <v>22.51</v>
-      </c>
       <c r="R29" s="36" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="30">
@@ -2468,54 +2468,54 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>81.31999999999999</v>
+        <v>85.02</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>79.42</v>
+        <v>81.92</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>77.83</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>78.05</v>
+        <v>81.03</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>79.09999999999999</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>77.2</v>
+        <v>78.97</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>76.15000000000001</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J30" s="29" t="n">
-        <v>75.3</v>
+        <v>75.87</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>76.77</v>
+        <v>77.58</v>
       </c>
       <c r="L30" s="31" t="n">
-        <v>75.18000000000001</v>
+        <v>74.98</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>73.28</v>
-      </c>
-      <c r="N30" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>71.88</v>
+      </c>
+      <c r="N30" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O30" s="33" t="n">
-        <v>77.06</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="P30" s="33" t="n">
-        <v>76.92</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="Q30" s="34" t="n">
-        <v>77</v>
-      </c>
-      <c r="R30" s="35" t="n">
-        <v>-2.04</v>
+        <v>80</v>
+      </c>
+      <c r="R30" s="36" t="n">
+        <v>1.78</v>
       </c>
     </row>
     <row r="31">
@@ -2530,37 +2530,37 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>33.92</v>
+        <v>34.18</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>32.24</v>
+        <v>32.34</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>30.83</v>
+        <v>30.8</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>30.83</v>
+        <v>30.77</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>31.85</v>
+        <v>31.91</v>
       </c>
       <c r="H31" s="28" t="n">
-        <v>30.17</v>
+        <v>30.07</v>
       </c>
       <c r="I31" s="29" t="n">
-        <v>29.15</v>
+        <v>28.93</v>
       </c>
       <c r="J31" s="29" t="n">
-        <v>28.49</v>
+        <v>28.23</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>29.89</v>
+        <v>29.76</v>
       </c>
       <c r="L31" s="31" t="n">
-        <v>28.48</v>
+        <v>28.22</v>
       </c>
       <c r="M31" s="31" t="n">
-        <v>26.8</v>
+        <v>26.38</v>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
@@ -2568,16 +2568,16 @@
         </is>
       </c>
       <c r="O31" s="33" t="n">
-        <v>30.1</v>
+        <v>29.99</v>
       </c>
       <c r="P31" s="33" t="n">
-        <v>30.02</v>
+        <v>29.91</v>
       </c>
       <c r="Q31" s="34" t="n">
-        <v>29.8</v>
+        <v>29.64</v>
       </c>
       <c r="R31" s="36" t="n">
-        <v>1.22</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="32">
@@ -2592,54 +2592,54 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>51.3</v>
+        <v>49.97</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>50.56</v>
+        <v>49.73</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>49.94</v>
+        <v>49.53</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>49.85</v>
+        <v>49.66</v>
       </c>
       <c r="G32" s="27" t="n">
-        <v>50.35</v>
+        <v>49.74</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>49.61</v>
+        <v>49.5</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>49.11</v>
+        <v>49.42</v>
       </c>
       <c r="J32" s="29" t="n">
-        <v>48.87</v>
+        <v>49.26</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>49.52</v>
+        <v>49.39</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>48.9</v>
+        <v>49.19</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>48.16</v>
-      </c>
-      <c r="N32" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>48.95</v>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O32" s="33" t="n">
-        <v>49.59</v>
+        <v>49.46</v>
       </c>
       <c r="P32" s="33" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="Q32" s="34" t="n">
         <v>49.58</v>
       </c>
-      <c r="Q32" s="34" t="n">
-        <v>49.36</v>
-      </c>
-      <c r="R32" s="35" t="n">
-        <v>-0.16</v>
+      <c r="R32" s="36" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="33">
@@ -2654,37 +2654,37 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>133.17</v>
+        <v>132.4</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>131.27</v>
+        <v>130.3</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>129.68</v>
+        <v>128.54</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>130.27</v>
+        <v>129.7</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>131.13</v>
+        <v>130.4</v>
       </c>
       <c r="H33" s="28" t="n">
-        <v>129.23</v>
+        <v>128.3</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>128.37</v>
+        <v>127.6</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>127.33</v>
+        <v>126.2</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>128.62</v>
+        <v>127.36</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>127.03</v>
+        <v>125.6</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>125.13</v>
+        <v>123.5</v>
       </c>
       <c r="N33" s="32" t="inlineStr">
         <is>
@@ -2692,16 +2692,16 @@
         </is>
       </c>
       <c r="O33" s="33" t="n">
+        <v>127.91</v>
+      </c>
+      <c r="P33" s="33" t="n">
+        <v>127.53</v>
+      </c>
+      <c r="Q33" s="34" t="n">
         <v>129</v>
       </c>
-      <c r="P33" s="33" t="n">
-        <v>128.77</v>
-      </c>
-      <c r="Q33" s="34" t="n">
-        <v>129.4</v>
-      </c>
       <c r="R33" s="35" t="n">
-        <v>-0.15</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="34">
@@ -2716,37 +2716,37 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>66.02</v>
+        <v>60.5</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>62.67</v>
+        <v>58.8</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>59.86</v>
+        <v>57.38</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>59.85</v>
+        <v>57.35</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>61.9</v>
+        <v>58.4</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>58.55</v>
+        <v>56.7</v>
       </c>
       <c r="I34" s="29" t="n">
-        <v>56.5</v>
+        <v>55.65</v>
       </c>
       <c r="J34" s="29" t="n">
-        <v>55.2</v>
+        <v>55</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>57.99</v>
+        <v>56.42</v>
       </c>
       <c r="L34" s="31" t="n">
-        <v>55.18</v>
+        <v>55</v>
       </c>
       <c r="M34" s="31" t="n">
-        <v>51.83</v>
+        <v>53.3</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="O34" s="33" t="n">
-        <v>58.4</v>
+        <v>56.63</v>
       </c>
       <c r="P34" s="33" t="n">
-        <v>58.25</v>
+        <v>56.56</v>
       </c>
       <c r="Q34" s="34" t="n">
-        <v>57.8</v>
+        <v>56.3</v>
       </c>
       <c r="R34" s="36" t="n">
-        <v>7.04</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="35">
@@ -2778,37 +2778,37 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>26.16</v>
+        <v>25.75</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>25.64</v>
+        <v>25.36</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>25.21</v>
+        <v>25.03</v>
       </c>
       <c r="F35" s="27" t="n">
-        <v>25.18</v>
+        <v>25.16</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>25.51</v>
+        <v>25.33</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>24.99</v>
+        <v>24.94</v>
       </c>
       <c r="I35" s="29" t="n">
-        <v>24.66</v>
+        <v>24.77</v>
       </c>
       <c r="J35" s="29" t="n">
-        <v>24.47</v>
+        <v>24.55</v>
       </c>
       <c r="K35" s="30" t="n">
-        <v>24.91</v>
+        <v>24.82</v>
       </c>
       <c r="L35" s="31" t="n">
-        <v>24.48</v>
+        <v>24.49</v>
       </c>
       <c r="M35" s="31" t="n">
-        <v>23.96</v>
+        <v>24.1</v>
       </c>
       <c r="N35" s="32" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="O35" s="33" t="n">
-        <v>24.97</v>
+        <v>24.89</v>
       </c>
       <c r="P35" s="33" t="n">
-        <v>24.95</v>
+        <v>24.85</v>
       </c>
       <c r="Q35" s="34" t="n">
-        <v>24.85</v>
+        <v>24.98</v>
       </c>
       <c r="R35" s="35" t="n">
-        <v>-2.09</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="36">
@@ -2840,37 +2840,37 @@
         </is>
       </c>
       <c r="C36" s="25" t="n">
-        <v>26.91</v>
+        <v>26.94</v>
       </c>
       <c r="D36" s="25" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="E36" s="26" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="G36" s="27" t="n">
         <v>26.63</v>
       </c>
-      <c r="E36" s="26" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="F36" s="27" t="n">
-        <v>26.46</v>
-      </c>
-      <c r="G36" s="27" t="n">
-        <v>26.6</v>
-      </c>
       <c r="H36" s="28" t="n">
-        <v>26.32</v>
+        <v>26.31</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>26.18</v>
+        <v>26.21</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>26.04</v>
+        <v>25.99</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>26.24</v>
+        <v>26.17</v>
       </c>
       <c r="L36" s="31" t="n">
-        <v>26.01</v>
+        <v>25.9</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>25.73</v>
+        <v>25.58</v>
       </c>
       <c r="N36" s="32" t="inlineStr">
         <is>
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="O36" s="33" t="n">
-        <v>26.29</v>
+        <v>26.25</v>
       </c>
       <c r="P36" s="33" t="n">
-        <v>26.26</v>
+        <v>26.2</v>
       </c>
       <c r="Q36" s="34" t="n">
-        <v>26.32</v>
+        <v>26.42</v>
       </c>
       <c r="R36" s="35" t="n">
-        <v>-0.53</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="37">
@@ -2902,37 +2902,37 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>9.41</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>9.279999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E37" s="26" t="n">
-        <v>9.17</v>
+        <v>9.18</v>
       </c>
       <c r="F37" s="27" t="n">
-        <v>9.18</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>9.25</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>9.119999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="I37" s="29" t="n">
-        <v>9.050000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="J37" s="29" t="n">
         <v>8.99</v>
       </c>
       <c r="K37" s="30" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="L37" s="31" t="n">
-        <v>8.99</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M37" s="31" t="n">
-        <v>8.859999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="N37" s="32" t="inlineStr">
         <is>
@@ -2943,13 +2943,13 @@
         <v>9.119999999999999</v>
       </c>
       <c r="P37" s="33" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="Q37" s="34" t="n">
-        <v>9.1</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="R37" s="35" t="n">
-        <v>-1.3</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="38">
@@ -2964,37 +2964,37 @@
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>33.64</v>
+        <v>34.03</v>
       </c>
       <c r="D38" s="25" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="E38" s="26" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="F38" s="27" t="n">
         <v>32.54</v>
       </c>
-      <c r="E38" s="26" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>31.99</v>
-      </c>
       <c r="G38" s="27" t="n">
-        <v>32.47</v>
+        <v>32.98</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>31.37</v>
+        <v>32</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>30.89</v>
+        <v>31.56</v>
       </c>
       <c r="J38" s="29" t="n">
-        <v>30.27</v>
+        <v>31.02</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>31</v>
+        <v>31.68</v>
       </c>
       <c r="L38" s="31" t="n">
-        <v>30.08</v>
+        <v>30.85</v>
       </c>
       <c r="M38" s="31" t="n">
-        <v>28.98</v>
+        <v>29.87</v>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
@@ -3002,16 +3002,16 @@
         </is>
       </c>
       <c r="O38" s="33" t="n">
-        <v>31.23</v>
+        <v>31.88</v>
       </c>
       <c r="P38" s="33" t="n">
-        <v>31.09</v>
+        <v>31.75</v>
       </c>
       <c r="Q38" s="34" t="n">
-        <v>31.5</v>
+        <v>32.1</v>
       </c>
       <c r="R38" s="36" t="n">
-        <v>2.27</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="39">
@@ -3026,54 +3026,54 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>204.78</v>
+        <v>196.54</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>199.48</v>
+        <v>194.04</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>195.03</v>
+        <v>191.95</v>
       </c>
       <c r="F39" s="27" t="n">
-        <v>195.17</v>
+        <v>191.67</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>198.33</v>
+        <v>193.33</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>193.03</v>
+        <v>190.83</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>189.87</v>
+        <v>189.17</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>187.73</v>
+        <v>188.33</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>192.07</v>
+        <v>190.55</v>
       </c>
       <c r="L39" s="31" t="n">
-        <v>187.62</v>
+        <v>188.46</v>
       </c>
       <c r="M39" s="31" t="n">
-        <v>182.32</v>
-      </c>
-      <c r="N39" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>185.96</v>
+      </c>
+      <c r="N39" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O39" s="33" t="n">
-        <v>192.76</v>
+        <v>190.79</v>
       </c>
       <c r="P39" s="33" t="n">
-        <v>192.48</v>
+        <v>190.75</v>
       </c>
       <c r="Q39" s="34" t="n">
-        <v>192</v>
-      </c>
-      <c r="R39" s="36" t="n">
-        <v>0.63</v>
+        <v>190</v>
+      </c>
+      <c r="R39" s="35" t="n">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="40">
@@ -3088,54 +3088,54 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>13.64</v>
+        <v>14.01</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>13.44</v>
+        <v>13.41</v>
       </c>
       <c r="E40" s="26" t="n">
-        <v>13.28</v>
+        <v>12.91</v>
       </c>
       <c r="F40" s="27" t="n">
-        <v>13.29</v>
+        <v>13.01</v>
       </c>
       <c r="G40" s="27" t="n">
-        <v>13.4</v>
+        <v>13.33</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>13.2</v>
+        <v>12.73</v>
       </c>
       <c r="I40" s="29" t="n">
-        <v>13.09</v>
+        <v>12.41</v>
       </c>
       <c r="J40" s="29" t="n">
-        <v>13</v>
+        <v>12.13</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>13.16</v>
+        <v>12.57</v>
       </c>
       <c r="L40" s="31" t="n">
-        <v>13</v>
+        <v>12.07</v>
       </c>
       <c r="M40" s="31" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N40" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>11.47</v>
+      </c>
+      <c r="N40" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O40" s="33" t="n">
-        <v>13.19</v>
+        <v>12.67</v>
       </c>
       <c r="P40" s="33" t="n">
-        <v>13.18</v>
+        <v>12.62</v>
       </c>
       <c r="Q40" s="34" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="R40" s="36" t="n">
-        <v>0.15</v>
+        <v>12.7</v>
+      </c>
+      <c r="R40" s="35" t="n">
+        <v>-3.42</v>
       </c>
     </row>
     <row r="41">
@@ -3150,37 +3150,37 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>25.81</v>
+        <v>24.43</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>24.66</v>
+        <v>23.75</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>23.7</v>
+        <v>23.18</v>
       </c>
       <c r="F41" s="27" t="n">
-        <v>23.57</v>
+        <v>23.18</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>24.33</v>
+        <v>23.59</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>23.18</v>
+        <v>22.91</v>
       </c>
       <c r="I41" s="29" t="n">
-        <v>22.42</v>
+        <v>22.5</v>
       </c>
       <c r="J41" s="29" t="n">
-        <v>22.03</v>
+        <v>22.23</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>23.05</v>
+        <v>22.8</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>22.09</v>
+        <v>22.23</v>
       </c>
       <c r="M41" s="31" t="n">
-        <v>20.94</v>
+        <v>21.55</v>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="O41" s="33" t="n">
-        <v>23.16</v>
+        <v>22.88</v>
       </c>
       <c r="P41" s="33" t="n">
-        <v>23.14</v>
+        <v>22.85</v>
       </c>
       <c r="Q41" s="34" t="n">
-        <v>22.8</v>
+        <v>22.76</v>
       </c>
       <c r="R41" s="36" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="42">
@@ -3212,37 +3212,37 @@
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>193.85</v>
+        <v>193.07</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>190.85</v>
+        <v>190.37</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>188.34</v>
+        <v>188.11</v>
       </c>
       <c r="F42" s="27" t="n">
-        <v>189</v>
+        <v>189.07</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>190.5</v>
+        <v>190.23</v>
       </c>
       <c r="H42" s="28" t="n">
-        <v>187.5</v>
+        <v>187.53</v>
       </c>
       <c r="I42" s="29" t="n">
-        <v>186</v>
+        <v>186.37</v>
       </c>
       <c r="J42" s="29" t="n">
-        <v>184.5</v>
+        <v>184.83</v>
       </c>
       <c r="K42" s="30" t="n">
-        <v>186.66</v>
+        <v>186.59</v>
       </c>
       <c r="L42" s="31" t="n">
-        <v>184.15</v>
+        <v>184.33</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>181.15</v>
+        <v>181.63</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
@@ -3250,16 +3250,16 @@
         </is>
       </c>
       <c r="O42" s="33" t="n">
-        <v>187.2</v>
+        <v>187.17</v>
       </c>
       <c r="P42" s="33" t="n">
-        <v>186.89</v>
+        <v>186.8</v>
       </c>
       <c r="Q42" s="34" t="n">
-        <v>187.5</v>
+        <v>187.9</v>
       </c>
       <c r="R42" s="36" t="n">
-        <v>0.27</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="43">
@@ -3274,37 +3274,37 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>37.92</v>
+        <v>38.07</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>37.6</v>
+        <v>37.57</v>
       </c>
       <c r="E43" s="26" t="n">
-        <v>37.33</v>
+        <v>37.15</v>
       </c>
       <c r="F43" s="27" t="n">
-        <v>37.41</v>
+        <v>37.37</v>
       </c>
       <c r="G43" s="27" t="n">
         <v>37.57</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>37.25</v>
+        <v>37.07</v>
       </c>
       <c r="I43" s="29" t="n">
-        <v>37.09</v>
+        <v>36.87</v>
       </c>
       <c r="J43" s="29" t="n">
-        <v>36.93</v>
+        <v>36.57</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>37.15</v>
+        <v>36.87</v>
       </c>
       <c r="L43" s="31" t="n">
-        <v>36.88</v>
+        <v>36.45</v>
       </c>
       <c r="M43" s="31" t="n">
-        <v>36.56</v>
+        <v>35.95</v>
       </c>
       <c r="N43" s="32" t="inlineStr">
         <is>
@@ -3312,16 +3312,16 @@
         </is>
       </c>
       <c r="O43" s="33" t="n">
-        <v>37.21</v>
+        <v>36.99</v>
       </c>
       <c r="P43" s="33" t="n">
+        <v>36.91</v>
+      </c>
+      <c r="Q43" s="34" t="n">
         <v>37.18</v>
       </c>
-      <c r="Q43" s="34" t="n">
-        <v>37.26</v>
-      </c>
       <c r="R43" s="35" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="44">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>28.83</v>
+        <v>28.55</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>28.29</v>
+        <v>28.15</v>
       </c>
       <c r="E44" s="26" t="n">
-        <v>27.84</v>
+        <v>27.81</v>
       </c>
       <c r="F44" s="27" t="n">
-        <v>27.99</v>
+        <v>28.01</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>28.25</v>
+        <v>28.15</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>27.71</v>
+        <v>27.75</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>27.45</v>
+        <v>27.61</v>
       </c>
       <c r="J44" s="29" t="n">
-        <v>27.17</v>
+        <v>27.35</v>
       </c>
       <c r="K44" s="30" t="n">
-        <v>27.54</v>
+        <v>27.59</v>
       </c>
       <c r="L44" s="31" t="n">
-        <v>27.09</v>
+        <v>27.25</v>
       </c>
       <c r="M44" s="31" t="n">
-        <v>26.55</v>
+        <v>26.85</v>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
@@ -3374,16 +3374,16 @@
         </is>
       </c>
       <c r="O44" s="33" t="n">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="P44" s="33" t="n">
-        <v>27.58</v>
+        <v>27.62</v>
       </c>
       <c r="Q44" s="34" t="n">
-        <v>27.74</v>
+        <v>27.86</v>
       </c>
       <c r="R44" s="36" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="45">
@@ -3398,54 +3398,54 @@
         </is>
       </c>
       <c r="C45" s="25" t="n">
-        <v>26.33</v>
+        <v>26.65</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>26.19</v>
+        <v>26.37</v>
       </c>
       <c r="E45" s="26" t="n">
-        <v>26.07</v>
+        <v>26.14</v>
       </c>
       <c r="F45" s="27" t="n">
-        <v>26.05</v>
+        <v>26.2</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>26.15</v>
+        <v>26.34</v>
       </c>
       <c r="H45" s="28" t="n">
-        <v>26.01</v>
+        <v>26.06</v>
       </c>
       <c r="I45" s="29" t="n">
-        <v>25.91</v>
+        <v>25.92</v>
       </c>
       <c r="J45" s="29" t="n">
-        <v>25.87</v>
+        <v>25.78</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>25.99</v>
+        <v>25.98</v>
       </c>
       <c r="L45" s="31" t="n">
-        <v>25.87</v>
+        <v>25.75</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="N45" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>25.47</v>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O45" s="33" t="n">
-        <v>26</v>
+        <v>26.03</v>
       </c>
       <c r="P45" s="33" t="n">
         <v>26</v>
       </c>
       <c r="Q45" s="34" t="n">
-        <v>25.96</v>
+        <v>26.06</v>
       </c>
       <c r="R45" s="36" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="46">
@@ -3460,54 +3460,54 @@
         </is>
       </c>
       <c r="C46" s="25" t="n">
-        <v>8.48</v>
+        <v>8.77</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>8.33</v>
+        <v>8.52</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>8.210000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="F46" s="27" t="n">
-        <v>8.289999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G46" s="27" t="n">
-        <v>8.34</v>
+        <v>8.5</v>
       </c>
       <c r="H46" s="28" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="J46" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K46" s="30" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="L46" s="31" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="M46" s="31" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="N46" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O46" s="33" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="P46" s="33" t="n">
         <v>8.19</v>
       </c>
-      <c r="I46" s="29" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="J46" s="29" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="K46" s="30" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="L46" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="M46" s="31" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="N46" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O46" s="33" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="P46" s="33" t="n">
-        <v>8.130000000000001</v>
-      </c>
       <c r="Q46" s="34" t="n">
-        <v>8.24</v>
+        <v>8.26</v>
       </c>
       <c r="R46" s="36" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="47">
@@ -3522,54 +3522,54 @@
         </is>
       </c>
       <c r="C47" s="25" t="n">
-        <v>12.84</v>
+        <v>12.59</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>12.66</v>
+        <v>12.46</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>12.51</v>
+        <v>12.35</v>
       </c>
       <c r="F47" s="27" t="n">
-        <v>12.5</v>
+        <v>12.39</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>12.61</v>
+        <v>12.45</v>
       </c>
       <c r="H47" s="28" t="n">
-        <v>12.43</v>
+        <v>12.32</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>12.32</v>
+        <v>12.26</v>
       </c>
       <c r="J47" s="29" t="n">
-        <v>12.25</v>
+        <v>12.19</v>
       </c>
       <c r="K47" s="30" t="n">
-        <v>12.41</v>
+        <v>12.28</v>
       </c>
       <c r="L47" s="31" t="n">
-        <v>12.26</v>
+        <v>12.17</v>
       </c>
       <c r="M47" s="31" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="N47" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>12.04</v>
+      </c>
+      <c r="N47" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O47" s="33" t="n">
-        <v>12.43</v>
+        <v>12.3</v>
       </c>
       <c r="P47" s="33" t="n">
-        <v>12.42</v>
+        <v>12.29</v>
       </c>
       <c r="Q47" s="34" t="n">
-        <v>12.38</v>
+        <v>12.33</v>
       </c>
       <c r="R47" s="35" t="n">
-        <v>-0.24</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="48">
@@ -3584,37 +3584,37 @@
         </is>
       </c>
       <c r="C48" s="25" t="n">
-        <v>214.7</v>
+        <v>209.28</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>210.5</v>
+        <v>206.88</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>206.98</v>
+        <v>204.87</v>
       </c>
       <c r="F48" s="27" t="n">
-        <v>206.5</v>
+        <v>205.4</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>209.3</v>
+        <v>206.6</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>205.1</v>
+        <v>204.2</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>202.3</v>
+        <v>203</v>
       </c>
       <c r="J48" s="29" t="n">
-        <v>200.9</v>
+        <v>201.8</v>
       </c>
       <c r="K48" s="30" t="n">
-        <v>204.62</v>
+        <v>203.53</v>
       </c>
       <c r="L48" s="31" t="n">
-        <v>201.1</v>
+        <v>201.52</v>
       </c>
       <c r="M48" s="31" t="n">
-        <v>196.9</v>
+        <v>199.12</v>
       </c>
       <c r="N48" s="32" t="inlineStr">
         <is>
@@ -3622,16 +3622,16 @@
         </is>
       </c>
       <c r="O48" s="33" t="n">
-        <v>205.03</v>
+        <v>203.96</v>
       </c>
       <c r="P48" s="33" t="n">
-        <v>204.95</v>
+        <v>203.72</v>
       </c>
       <c r="Q48" s="34" t="n">
-        <v>203.7</v>
+        <v>204.2</v>
       </c>
       <c r="R48" s="35" t="n">
-        <v>-1.69</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="49">
@@ -3646,37 +3646,37 @@
         </is>
       </c>
       <c r="C49" s="25" t="n">
-        <v>49.22</v>
+        <v>48.47</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>48.22</v>
+        <v>47.77</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>47.38</v>
+        <v>47.19</v>
       </c>
       <c r="F49" s="27" t="n">
-        <v>47.48</v>
+        <v>47.32</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>48.04</v>
+        <v>47.68</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>47.04</v>
+        <v>46.98</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>46.48</v>
+        <v>46.62</v>
       </c>
       <c r="J49" s="29" t="n">
-        <v>46.04</v>
+        <v>46.28</v>
       </c>
       <c r="K49" s="30" t="n">
-        <v>46.82</v>
+        <v>46.79</v>
       </c>
       <c r="L49" s="31" t="n">
-        <v>45.98</v>
+        <v>46.21</v>
       </c>
       <c r="M49" s="31" t="n">
-        <v>44.98</v>
+        <v>45.51</v>
       </c>
       <c r="N49" s="32" t="inlineStr">
         <is>
@@ -3684,16 +3684,16 @@
         </is>
       </c>
       <c r="O49" s="33" t="n">
-        <v>46.97</v>
+        <v>46.91</v>
       </c>
       <c r="P49" s="33" t="n">
-        <v>46.9</v>
+        <v>46.85</v>
       </c>
       <c r="Q49" s="34" t="n">
-        <v>46.92</v>
+        <v>46.96</v>
       </c>
       <c r="R49" s="35" t="n">
-        <v>-1.1</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="50">
@@ -3708,37 +3708,37 @@
         </is>
       </c>
       <c r="C50" s="25" t="n">
-        <v>34.2</v>
+        <v>34.59</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>33.46</v>
+        <v>33.67</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>32.84</v>
+        <v>32.9</v>
       </c>
       <c r="F50" s="27" t="n">
-        <v>32.91</v>
+        <v>33.38</v>
       </c>
       <c r="G50" s="27" t="n">
-        <v>33.33</v>
+        <v>33.7</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>32.59</v>
+        <v>32.78</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>32.17</v>
+        <v>32.46</v>
       </c>
       <c r="J50" s="29" t="n">
-        <v>31.85</v>
+        <v>31.86</v>
       </c>
       <c r="K50" s="30" t="n">
-        <v>32.42</v>
+        <v>32.38</v>
       </c>
       <c r="L50" s="31" t="n">
-        <v>31.8</v>
+        <v>31.61</v>
       </c>
       <c r="M50" s="31" t="n">
-        <v>31.06</v>
+        <v>30.69</v>
       </c>
       <c r="N50" s="32" t="inlineStr">
         <is>
@@ -3746,16 +3746,16 @@
         </is>
       </c>
       <c r="O50" s="33" t="n">
-        <v>32.53</v>
+        <v>32.62</v>
       </c>
       <c r="P50" s="33" t="n">
-        <v>32.48</v>
+        <v>32.45</v>
       </c>
       <c r="Q50" s="34" t="n">
-        <v>32.5</v>
+        <v>33.06</v>
       </c>
       <c r="R50" s="35" t="n">
-        <v>-4.07</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="51">
@@ -3770,37 +3770,37 @@
         </is>
       </c>
       <c r="C51" s="25" t="n">
-        <v>13.44</v>
+        <v>13.33</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>13.33</v>
+        <v>13.24</v>
       </c>
       <c r="E51" s="26" t="n">
-        <v>13.24</v>
+        <v>13.16</v>
       </c>
       <c r="F51" s="27" t="n">
-        <v>13.22</v>
+        <v>13.16</v>
       </c>
       <c r="G51" s="27" t="n">
-        <v>13.3</v>
+        <v>13.21</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>13.19</v>
+        <v>13.12</v>
       </c>
       <c r="I51" s="29" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="J51" s="29" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="K51" s="30" t="n">
         <v>13.11</v>
       </c>
-      <c r="J51" s="29" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="K51" s="30" t="n">
-        <v>13.17</v>
-      </c>
       <c r="L51" s="31" t="n">
-        <v>13.08</v>
+        <v>13.03</v>
       </c>
       <c r="M51" s="31" t="n">
-        <v>12.97</v>
+        <v>12.94</v>
       </c>
       <c r="N51" s="32" t="inlineStr">
         <is>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="O51" s="33" t="n">
-        <v>13.18</v>
+        <v>13.12</v>
       </c>
       <c r="P51" s="33" t="n">
-        <v>13.18</v>
+        <v>13.12</v>
       </c>
       <c r="Q51" s="34" t="n">
-        <v>13.15</v>
+        <v>13.1</v>
       </c>
       <c r="R51" s="35" t="n">
-        <v>-0.3</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="52">
@@ -3832,54 +3832,54 @@
         </is>
       </c>
       <c r="C52" s="25" t="n">
-        <v>60.82</v>
+        <v>64.41</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>60.47</v>
+        <v>62.61</v>
       </c>
       <c r="E52" s="26" t="n">
-        <v>60.17</v>
+        <v>61.1</v>
       </c>
       <c r="F52" s="27" t="n">
-        <v>60.27</v>
+        <v>62.1</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>60.43</v>
+        <v>62.7</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>60.08</v>
+        <v>60.9</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>59.92</v>
+        <v>60.3</v>
       </c>
       <c r="J52" s="29" t="n">
-        <v>59.73</v>
+        <v>59.1</v>
       </c>
       <c r="K52" s="30" t="n">
-        <v>59.98</v>
+        <v>60.1</v>
       </c>
       <c r="L52" s="31" t="n">
-        <v>59.68</v>
+        <v>58.59</v>
       </c>
       <c r="M52" s="31" t="n">
-        <v>59.33</v>
-      </c>
-      <c r="N52" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>56.79</v>
+      </c>
+      <c r="N52" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O52" s="33" t="n">
-        <v>60.04</v>
+        <v>60.57</v>
       </c>
       <c r="P52" s="33" t="n">
-        <v>60</v>
+        <v>60.24</v>
       </c>
       <c r="Q52" s="34" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="R52" s="35" t="n">
-        <v>-0.17</v>
+        <v>61.5</v>
+      </c>
+      <c r="R52" s="36" t="n">
+        <v>2.16</v>
       </c>
     </row>
     <row r="53">
@@ -3894,37 +3894,37 @@
         </is>
       </c>
       <c r="C53" s="25" t="n">
-        <v>24.1</v>
+        <v>24.24</v>
       </c>
       <c r="D53" s="25" t="n">
-        <v>23.87</v>
+        <v>23.94</v>
       </c>
       <c r="E53" s="26" t="n">
         <v>23.68</v>
       </c>
       <c r="F53" s="27" t="n">
-        <v>23.79</v>
+        <v>23.78</v>
       </c>
       <c r="G53" s="27" t="n">
-        <v>23.88</v>
+        <v>23.91</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>23.65</v>
+        <v>23.61</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>23.56</v>
+        <v>23.48</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>23.42</v>
+        <v>23.31</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>23.55</v>
+        <v>23.52</v>
       </c>
       <c r="L53" s="31" t="n">
-        <v>23.36</v>
+        <v>23.26</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>23.13</v>
+        <v>22.96</v>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="O53" s="33" t="n">
-        <v>23.61</v>
+        <v>23.58</v>
       </c>
       <c r="P53" s="33" t="n">
-        <v>23.57</v>
+        <v>23.54</v>
       </c>
       <c r="Q53" s="34" t="n">
-        <v>23.71</v>
+        <v>23.64</v>
       </c>
       <c r="R53" s="36" t="n">
-        <v>0.64</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="54">
@@ -3956,54 +3956,54 @@
         </is>
       </c>
       <c r="C54" s="25" t="n">
-        <v>5.57</v>
+        <v>5.52</v>
       </c>
       <c r="D54" s="25" t="n">
-        <v>5.48</v>
+        <v>5.44</v>
       </c>
       <c r="E54" s="26" t="n">
-        <v>5.4</v>
+        <v>5.37</v>
       </c>
       <c r="F54" s="27" t="n">
-        <v>5.4</v>
+        <v>5.41</v>
       </c>
       <c r="G54" s="27" t="n">
-        <v>5.45</v>
+        <v>5.44</v>
       </c>
       <c r="H54" s="28" t="n">
         <v>5.36</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>5.31</v>
+        <v>5.33</v>
       </c>
       <c r="J54" s="29" t="n">
-        <v>5.27</v>
+        <v>5.28</v>
       </c>
       <c r="K54" s="30" t="n">
-        <v>5.35</v>
+        <v>5.33</v>
       </c>
       <c r="L54" s="31" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="M54" s="31" t="n">
         <v>5.18</v>
       </c>
-      <c r="N54" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+      <c r="N54" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O54" s="33" t="n">
-        <v>5.36</v>
+        <v>5.35</v>
       </c>
       <c r="P54" s="33" t="n">
-        <v>5.36</v>
+        <v>5.33</v>
       </c>
       <c r="Q54" s="34" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="R54" s="35" t="n">
-        <v>-0.5600000000000001</v>
+        <v>5.38</v>
+      </c>
+      <c r="R54" s="36" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="55">
@@ -4018,37 +4018,37 @@
         </is>
       </c>
       <c r="C55" s="25" t="n">
-        <v>19.27</v>
+        <v>18.48</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>18.7</v>
+        <v>18.25</v>
       </c>
       <c r="E55" s="26" t="n">
-        <v>18.22</v>
+        <v>18.06</v>
       </c>
       <c r="F55" s="27" t="n">
-        <v>18.21</v>
+        <v>18.13</v>
       </c>
       <c r="G55" s="27" t="n">
-        <v>18.57</v>
+        <v>18.24</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>18</v>
+        <v>18.01</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>17.64</v>
+        <v>17.9</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>17.43</v>
+        <v>17.78</v>
       </c>
       <c r="K55" s="30" t="n">
-        <v>17.91</v>
+        <v>17.93</v>
       </c>
       <c r="L55" s="31" t="n">
-        <v>17.43</v>
+        <v>17.74</v>
       </c>
       <c r="M55" s="31" t="n">
-        <v>16.86</v>
+        <v>17.51</v>
       </c>
       <c r="N55" s="32" t="inlineStr">
         <is>
@@ -4056,16 +4056,16 @@
         </is>
       </c>
       <c r="O55" s="33" t="n">
-        <v>17.97</v>
+        <v>17.98</v>
       </c>
       <c r="P55" s="33" t="n">
         <v>17.95</v>
       </c>
       <c r="Q55" s="34" t="n">
-        <v>17.86</v>
+        <v>18.03</v>
       </c>
       <c r="R55" s="35" t="n">
-        <v>-2.67</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="56">
@@ -4080,37 +4080,37 @@
         </is>
       </c>
       <c r="C56" s="25" t="n">
-        <v>100.09</v>
+        <v>97.17</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>98.48999999999999</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="E56" s="26" t="n">
-        <v>97.15000000000001</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="F56" s="27" t="n">
-        <v>97.06999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="G56" s="27" t="n">
-        <v>98.08</v>
+        <v>96.55</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>96.48</v>
+        <v>95.95</v>
       </c>
       <c r="I56" s="29" t="n">
-        <v>95.47</v>
+        <v>95.7</v>
       </c>
       <c r="J56" s="29" t="n">
-        <v>94.88</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="K56" s="30" t="n">
-        <v>96.25</v>
+        <v>95.73</v>
       </c>
       <c r="L56" s="31" t="n">
-        <v>94.91</v>
+        <v>95.23</v>
       </c>
       <c r="M56" s="31" t="n">
-        <v>93.31</v>
+        <v>94.63</v>
       </c>
       <c r="N56" s="20" t="inlineSt